--- a/FICO/output/FICO_Completed_Model.xlsx
+++ b/FICO/output/FICO_Completed_Model.xlsx
@@ -59,6 +59,8 @@
     <definedName name="DCF_WACC">'DCF Model'!$D$6</definedName>
     <definedName name="DCF_PerpetualGrowth">'DCF Model'!$D$7</definedName>
     <definedName name="DCF_ExitMultiple">'DCF Model'!$D$8</definedName>
+    <definedName name="DCF_TransactionDate">'DCF Model'!$D$9</definedName>
+    <definedName name="DCF_FiscalYearEnd">'DCF Model'!$D$10</definedName>
     <definedName name="DCF_SharePrice">'DCF Model'!$D$11</definedName>
     <definedName name="DCF_Shares">'DCF Model'!$D$12</definedName>
     <definedName name="DCF_Debt">'DCF Model'!$D$13</definedName>
@@ -6325,7 +6327,7 @@
       </c>
       <c r="C9" s="97" t="n"/>
       <c r="D9" s="106" t="n">
-        <v>43100</v>
+        <v>45930</v>
       </c>
       <c r="E9" s="97" t="n"/>
       <c r="F9" s="97" t="n"/>
@@ -6348,7 +6350,7 @@
       </c>
       <c r="C10" s="97" t="n"/>
       <c r="D10" s="106" t="n">
-        <v>43281</v>
+        <v>46295</v>
       </c>
       <c r="E10" s="97" t="n"/>
       <c r="F10" s="97" t="n"/>

--- a/FICO/output/FICO_Completed_Model.xlsx
+++ b/FICO/output/FICO_Completed_Model.xlsx
@@ -86,7 +86,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="10">
+  <numFmts count="14">
     <numFmt numFmtId="164" formatCode="_-* #,##0_-;\(#,##0\)_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="0.0000_ ;\-0.0000\ "/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
@@ -97,6 +97,10 @@
     <numFmt numFmtId="171" formatCode="0.0\x"/>
     <numFmt numFmtId="172" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="173" formatCode="_-* #,##0.00_-;\(#,##0.00\)_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="174" formatCode="#,##0.0;(#,##0.0);-"/>
+    <numFmt numFmtId="175" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="176" formatCode="$#,##0.00"/>
+    <numFmt numFmtId="177" formatCode="0.0"/>
   </numFmts>
   <fonts count="39">
     <font>
@@ -457,7 +461,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="142">
+  <cellXfs count="160">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="1"/>
@@ -667,28 +671,48 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="174" fontId="38" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="174" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="166" fontId="38" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="2"/>
-    <xf numFmtId="164" fontId="38" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="164" fontId="38" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="164" fontId="38" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="174" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="166" fontId="38" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="174" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="174" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="174" fontId="6" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="174" fontId="38" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="174" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="174" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="174" fontId="6" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="174" fontId="6" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="174" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="174" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="174" fontId="38" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="38" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="174" fontId="9" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="166" fontId="38" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="171" fontId="38" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="177" fontId="38" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="172" fontId="38" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="175" fontId="32" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="176" fontId="38" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="38" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="174" fontId="38" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="38" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="172" fontId="35" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="38" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="174" fontId="38" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="31" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="174" fontId="35" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="174" fontId="36" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="174" fontId="37" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="174" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="174" fontId="34" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="174" fontId="30" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="173" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="9">
@@ -2437,10 +2461,18 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.109375" defaultRowHeight="15.6" outlineLevelRow="1"/>
   <cols>
     <col width="1.88671875" customWidth="1" style="19" min="1" max="1"/>
-    <col width="15.5546875" customWidth="1" style="19" min="2" max="3"/>
-    <col width="15.5546875" customWidth="1" style="47" min="4" max="4"/>
-    <col width="11.5546875" customWidth="1" style="19" min="5" max="9"/>
-    <col width="12.5546875" customWidth="1" style="19" min="10" max="14"/>
+    <col width="42" customWidth="1" style="19" min="2" max="3"/>
+    <col width="16" customWidth="1" style="47" min="4" max="4"/>
+    <col width="16" customWidth="1" style="19" min="5" max="9"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" style="19" min="10" max="14"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
     <col width="9.109375" customWidth="1" style="19" min="15" max="16384"/>
   </cols>
   <sheetData>
@@ -2527,47 +2559,48 @@
           <t>Balance Sheet Check</t>
         </is>
       </c>
-      <c r="E3" s="45">
+      <c r="E3" s="130">
         <f>IFERROR(IF(ABS(E57)&gt;1,"ERROR","OK"),"OK")</f>
         <v/>
       </c>
-      <c r="F3" s="45">
+      <c r="F3" s="130">
         <f>IFERROR(IF(ABS(F57)&gt;1,"ERROR","OK"),"OK")</f>
         <v/>
       </c>
-      <c r="G3" s="45">
+      <c r="G3" s="130">
         <f>IFERROR(IF(ABS(G57)&gt;1,"ERROR","OK"),"OK")</f>
         <v/>
       </c>
-      <c r="H3" s="45">
+      <c r="H3" s="130">
         <f>IFERROR(IF(ABS(H57)&gt;1,"ERROR","OK"),"OK")</f>
         <v/>
       </c>
-      <c r="I3" s="45">
+      <c r="I3" s="130">
         <f>IFERROR(IF(ABS(I57)&gt;1,"ERROR","OK"),"OK")</f>
         <v/>
       </c>
-      <c r="J3" s="45">
+      <c r="J3" s="130">
         <f>IFERROR(IF(ABS(J57)&gt;1,"ERROR","OK"),"OK")</f>
         <v/>
       </c>
-      <c r="K3" s="45">
+      <c r="K3" s="130">
         <f>IFERROR(IF(ABS(K57)&gt;1,"ERROR","OK"),"OK")</f>
         <v/>
       </c>
-      <c r="L3" s="45">
+      <c r="L3" s="130">
         <f>IFERROR(IF(ABS(L57)&gt;1,"ERROR","OK"),"OK")</f>
         <v/>
       </c>
-      <c r="M3" s="45">
+      <c r="M3" s="130">
         <f>IFERROR(IF(ABS(M57)&gt;1,"ERROR","OK"),"OK")</f>
         <v/>
       </c>
-      <c r="N3" s="45">
+      <c r="N3" s="130">
         <f>IFERROR(IF(ABS(N57)&gt;1,"ERROR","OK"),"OK")</f>
         <v/>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="18" customHeight="1">
       <c r="B5" s="65" t="inlineStr">
         <is>
@@ -2620,19 +2653,19 @@
         <f>I24/H24-1</f>
         <v/>
       </c>
-      <c r="J7" s="130" t="n">
+      <c r="J7" s="131" t="n">
         <v>0.143234</v>
       </c>
-      <c r="K7" s="130" t="n">
+      <c r="K7" s="131" t="n">
         <v>0.1</v>
       </c>
-      <c r="L7" s="130" t="n">
+      <c r="L7" s="131" t="n">
         <v>0.09</v>
       </c>
-      <c r="M7" s="130" t="n">
+      <c r="M7" s="131" t="n">
         <v>0.08</v>
       </c>
-      <c r="N7" s="130" t="n">
+      <c r="N7" s="131" t="n">
         <v>0.07000000000000001</v>
       </c>
     </row>
@@ -2664,19 +2697,19 @@
         <f>I25/I24</f>
         <v/>
       </c>
-      <c r="J8" s="130" t="n">
+      <c r="J8" s="131" t="n">
         <v>0.1776721622567833</v>
       </c>
-      <c r="K8" s="130" t="n">
+      <c r="K8" s="131" t="n">
         <v>0.1776721622567833</v>
       </c>
-      <c r="L8" s="130" t="n">
+      <c r="L8" s="131" t="n">
         <v>0.1776721622567833</v>
       </c>
-      <c r="M8" s="130" t="n">
+      <c r="M8" s="131" t="n">
         <v>0.1776721622567833</v>
       </c>
-      <c r="N8" s="130" t="n">
+      <c r="N8" s="131" t="n">
         <v>0.1776721622567833</v>
       </c>
     </row>
@@ -2688,39 +2721,39 @@
       </c>
       <c r="C9" s="19" t="n"/>
       <c r="D9" s="47" t="n"/>
-      <c r="E9" s="52">
+      <c r="E9" s="132">
         <f>E28</f>
         <v/>
       </c>
-      <c r="F9" s="52">
+      <c r="F9" s="132">
         <f>F28</f>
         <v/>
       </c>
-      <c r="G9" s="52">
+      <c r="G9" s="132">
         <f>G28</f>
         <v/>
       </c>
-      <c r="H9" s="52">
+      <c r="H9" s="132">
         <f>H28</f>
         <v/>
       </c>
-      <c r="I9" s="52">
+      <c r="I9" s="132">
         <f>I28</f>
         <v/>
       </c>
-      <c r="J9" s="131" t="n">
+      <c r="J9" s="129" t="n">
         <v>586511.1</v>
       </c>
-      <c r="K9" s="131" t="n">
+      <c r="K9" s="129" t="n">
         <v>645162.2</v>
       </c>
-      <c r="L9" s="131" t="n">
+      <c r="L9" s="129" t="n">
         <v>703226.8</v>
       </c>
-      <c r="M9" s="131" t="n">
+      <c r="M9" s="129" t="n">
         <v>759484.9</v>
       </c>
-      <c r="N9" s="131" t="n">
+      <c r="N9" s="129" t="n">
         <v>812648.8</v>
       </c>
     </row>
@@ -2732,39 +2765,39 @@
       </c>
       <c r="C10" s="19" t="n"/>
       <c r="D10" s="47" t="n"/>
-      <c r="E10" s="52">
+      <c r="E10" s="132">
         <f>E29</f>
         <v/>
       </c>
-      <c r="F10" s="52">
+      <c r="F10" s="132">
         <f>F29</f>
         <v/>
       </c>
-      <c r="G10" s="52">
+      <c r="G10" s="132">
         <f>G29</f>
         <v/>
       </c>
-      <c r="H10" s="52">
+      <c r="H10" s="132">
         <f>H29</f>
         <v/>
       </c>
-      <c r="I10" s="52">
+      <c r="I10" s="132">
         <f>I29</f>
         <v/>
       </c>
-      <c r="J10" s="131" t="n">
+      <c r="J10" s="129" t="n">
         <v>215324.7</v>
       </c>
-      <c r="K10" s="131" t="n">
+      <c r="K10" s="129" t="n">
         <v>236857.2</v>
       </c>
-      <c r="L10" s="131" t="n">
+      <c r="L10" s="129" t="n">
         <v>258174.3</v>
       </c>
-      <c r="M10" s="131" t="n">
+      <c r="M10" s="129" t="n">
         <v>278828.3</v>
       </c>
-      <c r="N10" s="131" t="n">
+      <c r="N10" s="129" t="n">
         <v>298346.2</v>
       </c>
     </row>
@@ -2796,19 +2829,19 @@
         <f>I30/I92</f>
         <v/>
       </c>
-      <c r="J11" s="130" t="n">
+      <c r="J11" s="131" t="n">
         <v>0.2208143192592265</v>
       </c>
-      <c r="K11" s="130" t="n">
+      <c r="K11" s="131" t="n">
         <v>0.2208143192592265</v>
       </c>
-      <c r="L11" s="130" t="n">
+      <c r="L11" s="131" t="n">
         <v>0.2208143192592265</v>
       </c>
-      <c r="M11" s="130" t="n">
+      <c r="M11" s="131" t="n">
         <v>0.2208143192592265</v>
       </c>
-      <c r="N11" s="130" t="n">
+      <c r="N11" s="131" t="n">
         <v>0.2208143192592265</v>
       </c>
     </row>
@@ -2840,19 +2873,19 @@
         <f>I101/I98</f>
         <v/>
       </c>
-      <c r="J12" s="130" t="n">
+      <c r="J12" s="131" t="n">
         <v>0.04373707943636971</v>
       </c>
-      <c r="K12" s="130" t="n">
+      <c r="K12" s="131" t="n">
         <v>0.04373707943636971</v>
       </c>
-      <c r="L12" s="130" t="n">
+      <c r="L12" s="131" t="n">
         <v>0.04373707943636971</v>
       </c>
-      <c r="M12" s="130" t="n">
+      <c r="M12" s="131" t="n">
         <v>0.04373707943636971</v>
       </c>
-      <c r="N12" s="130" t="n">
+      <c r="N12" s="131" t="n">
         <v>0.04373707943636971</v>
       </c>
     </row>
@@ -2884,19 +2917,19 @@
         <f>I35/I33</f>
         <v/>
       </c>
-      <c r="J13" s="130" t="n">
+      <c r="J13" s="131" t="n">
         <v>0.1877023903712333</v>
       </c>
-      <c r="K13" s="130" t="n">
+      <c r="K13" s="131" t="n">
         <v>0.1877023903712333</v>
       </c>
-      <c r="L13" s="130" t="n">
+      <c r="L13" s="131" t="n">
         <v>0.1877023903712333</v>
       </c>
-      <c r="M13" s="130" t="n">
+      <c r="M13" s="131" t="n">
         <v>0.1877023903712333</v>
       </c>
-      <c r="N13" s="130" t="n">
+      <c r="N13" s="131" t="n">
         <v>0.1877023903712333</v>
       </c>
     </row>
@@ -2926,39 +2959,39 @@
         </is>
       </c>
       <c r="D15" s="32" t="n"/>
-      <c r="E15" s="52">
+      <c r="E15" s="132">
         <f>E42/E24*365</f>
         <v/>
       </c>
-      <c r="F15" s="52">
+      <c r="F15" s="132">
         <f>F42/F24*365</f>
         <v/>
       </c>
-      <c r="G15" s="52">
+      <c r="G15" s="132">
         <f>G42/G24*365</f>
         <v/>
       </c>
-      <c r="H15" s="52">
+      <c r="H15" s="132">
         <f>H42/H24*365</f>
         <v/>
       </c>
-      <c r="I15" s="52">
+      <c r="I15" s="132">
         <f>I42/I24*365</f>
         <v/>
       </c>
-      <c r="J15" s="131" t="n">
+      <c r="J15" s="129" t="n">
         <v>97</v>
       </c>
-      <c r="K15" s="131" t="n">
+      <c r="K15" s="129" t="n">
         <v>97</v>
       </c>
-      <c r="L15" s="131" t="n">
+      <c r="L15" s="129" t="n">
         <v>97</v>
       </c>
-      <c r="M15" s="131" t="n">
+      <c r="M15" s="129" t="n">
         <v>97</v>
       </c>
-      <c r="N15" s="131" t="n">
+      <c r="N15" s="129" t="n">
         <v>97</v>
       </c>
     </row>
@@ -2969,39 +3002,39 @@
         </is>
       </c>
       <c r="D16" s="32" t="n"/>
-      <c r="E16" s="52">
+      <c r="E16" s="132">
         <f>E43/E25*365</f>
         <v/>
       </c>
-      <c r="F16" s="52">
+      <c r="F16" s="132">
         <f>F43/F25*365</f>
         <v/>
       </c>
-      <c r="G16" s="52">
+      <c r="G16" s="132">
         <f>G43/G25*365</f>
         <v/>
       </c>
-      <c r="H16" s="52">
+      <c r="H16" s="132">
         <f>H43/H25*365</f>
         <v/>
       </c>
-      <c r="I16" s="52">
+      <c r="I16" s="132">
         <f>I43/I25*365</f>
         <v/>
       </c>
-      <c r="J16" s="131" t="n">
+      <c r="J16" s="129" t="n">
         <v>0</v>
       </c>
-      <c r="K16" s="131" t="n">
+      <c r="K16" s="129" t="n">
         <v>0</v>
       </c>
-      <c r="L16" s="131" t="n">
+      <c r="L16" s="129" t="n">
         <v>0</v>
       </c>
-      <c r="M16" s="131" t="n">
+      <c r="M16" s="129" t="n">
         <v>0</v>
       </c>
-      <c r="N16" s="131" t="n">
+      <c r="N16" s="129" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3012,39 +3045,39 @@
         </is>
       </c>
       <c r="D17" s="32" t="n"/>
-      <c r="E17" s="52">
+      <c r="E17" s="132">
         <f>E48/E25*365</f>
         <v/>
       </c>
-      <c r="F17" s="52">
+      <c r="F17" s="132">
         <f>F48/F25*365</f>
         <v/>
       </c>
-      <c r="G17" s="52">
+      <c r="G17" s="132">
         <f>G48/G25*365</f>
         <v/>
       </c>
-      <c r="H17" s="52">
+      <c r="H17" s="132">
         <f>H48/H25*365</f>
         <v/>
       </c>
-      <c r="I17" s="52">
+      <c r="I17" s="132">
         <f>I48/I25*365</f>
         <v/>
       </c>
-      <c r="J17" s="131" t="n">
+      <c r="J17" s="129" t="n">
         <v>33</v>
       </c>
-      <c r="K17" s="131" t="n">
+      <c r="K17" s="129" t="n">
         <v>33</v>
       </c>
-      <c r="L17" s="131" t="n">
+      <c r="L17" s="129" t="n">
         <v>33</v>
       </c>
-      <c r="M17" s="131" t="n">
+      <c r="M17" s="129" t="n">
         <v>33</v>
       </c>
-      <c r="N17" s="131" t="n">
+      <c r="N17" s="129" t="n">
         <v>33</v>
       </c>
     </row>
@@ -3054,39 +3087,39 @@
           <t>Capital Expenditures ($000's)</t>
         </is>
       </c>
-      <c r="E18" s="52">
+      <c r="E18" s="132">
         <f>E68</f>
         <v/>
       </c>
-      <c r="F18" s="52">
+      <c r="F18" s="132">
         <f>F68</f>
         <v/>
       </c>
-      <c r="G18" s="52">
+      <c r="G18" s="132">
         <f>G68</f>
         <v/>
       </c>
-      <c r="H18" s="52">
+      <c r="H18" s="132">
         <f>H68</f>
         <v/>
       </c>
-      <c r="I18" s="52">
+      <c r="I18" s="132">
         <f>I68</f>
         <v/>
       </c>
-      <c r="J18" s="131" t="n">
+      <c r="J18" s="129" t="n">
         <v>45051.4</v>
       </c>
-      <c r="K18" s="131" t="n">
+      <c r="K18" s="129" t="n">
         <v>49556.6</v>
       </c>
-      <c r="L18" s="131" t="n">
+      <c r="L18" s="129" t="n">
         <v>54016.7</v>
       </c>
-      <c r="M18" s="131" t="n">
+      <c r="M18" s="129" t="n">
         <v>58338</v>
       </c>
-      <c r="N18" s="131" t="n">
+      <c r="N18" s="129" t="n">
         <v>62421.6</v>
       </c>
     </row>
@@ -3096,39 +3129,39 @@
           <t>Debt Issuance (Repayment) ($000's)</t>
         </is>
       </c>
-      <c r="E19" s="52">
+      <c r="E19" s="132">
         <f>E99</f>
         <v/>
       </c>
-      <c r="F19" s="52">
+      <c r="F19" s="132">
         <f>F99</f>
         <v/>
       </c>
-      <c r="G19" s="52">
+      <c r="G19" s="132">
         <f>G99</f>
         <v/>
       </c>
-      <c r="H19" s="52">
+      <c r="H19" s="132">
         <f>H99</f>
         <v/>
       </c>
-      <c r="I19" s="52">
+      <c r="I19" s="132">
         <f>I99</f>
         <v/>
       </c>
-      <c r="J19" s="131" t="n">
+      <c r="J19" s="133" t="n">
         <v>0</v>
       </c>
-      <c r="K19" s="131" t="n">
+      <c r="K19" s="133" t="n">
         <v>0</v>
       </c>
-      <c r="L19" s="131" t="n">
+      <c r="L19" s="133" t="n">
         <v>0</v>
       </c>
-      <c r="M19" s="131" t="n">
+      <c r="M19" s="133" t="n">
         <v>0</v>
       </c>
-      <c r="N19" s="131" t="n">
+      <c r="N19" s="133" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3138,39 +3171,39 @@
           <t>Equity Issued (Repaid) ($000's)</t>
         </is>
       </c>
-      <c r="E20" s="52">
+      <c r="E20" s="132">
         <f>E73</f>
         <v/>
       </c>
-      <c r="F20" s="52">
+      <c r="F20" s="132">
         <f>F73</f>
         <v/>
       </c>
-      <c r="G20" s="52">
+      <c r="G20" s="132">
         <f>G73</f>
         <v/>
       </c>
-      <c r="H20" s="52">
+      <c r="H20" s="132">
         <f>H73</f>
         <v/>
       </c>
-      <c r="I20" s="52">
+      <c r="I20" s="132">
         <f>I73</f>
         <v/>
       </c>
-      <c r="J20" s="131" t="n">
+      <c r="J20" s="133" t="n">
         <v>0</v>
       </c>
-      <c r="K20" s="131" t="n">
+      <c r="K20" s="133" t="n">
         <v>0</v>
       </c>
-      <c r="L20" s="131" t="n">
+      <c r="L20" s="133" t="n">
         <v>0</v>
       </c>
-      <c r="M20" s="131" t="n">
+      <c r="M20" s="133" t="n">
         <v>0</v>
       </c>
-      <c r="N20" s="131" t="n">
+      <c r="N20" s="133" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3225,38 +3258,38 @@
       </c>
       <c r="C24" s="18" t="n"/>
       <c r="D24" s="46" t="n"/>
-      <c r="E24" s="131" t="n">
+      <c r="E24" s="129" t="n">
         <v>1316536</v>
       </c>
-      <c r="F24" s="131" t="n">
+      <c r="F24" s="129" t="n">
         <v>1377270</v>
       </c>
-      <c r="G24" s="131" t="n">
+      <c r="G24" s="129" t="n">
         <v>1513557</v>
       </c>
-      <c r="H24" s="131" t="n">
+      <c r="H24" s="129" t="n">
         <v>1717526</v>
       </c>
-      <c r="I24" s="131" t="n">
+      <c r="I24" s="129" t="n">
         <v>1990869</v>
       </c>
-      <c r="J24" s="18">
+      <c r="J24" s="134">
         <f>I24*(1+J7)</f>
         <v/>
       </c>
-      <c r="K24" s="18">
+      <c r="K24" s="134">
         <f>J24*(1+K7)</f>
         <v/>
       </c>
-      <c r="L24" s="18">
+      <c r="L24" s="134">
         <f>K24*(1+L7)</f>
         <v/>
       </c>
-      <c r="M24" s="18">
+      <c r="M24" s="134">
         <f>L24*(1+M7)</f>
         <v/>
       </c>
-      <c r="N24" s="18">
+      <c r="N24" s="134">
         <f>M24*(1+N7)</f>
         <v/>
       </c>
@@ -3269,38 +3302,38 @@
       </c>
       <c r="C25" s="19" t="n"/>
       <c r="D25" s="47" t="n"/>
-      <c r="E25" s="131" t="n">
+      <c r="E25" s="129" t="n">
         <v>332462</v>
       </c>
-      <c r="F25" s="131" t="n">
+      <c r="F25" s="129" t="n">
         <v>302174</v>
       </c>
-      <c r="G25" s="131" t="n">
+      <c r="G25" s="129" t="n">
         <v>311053</v>
       </c>
-      <c r="H25" s="131" t="n">
+      <c r="H25" s="129" t="n">
         <v>348206</v>
       </c>
-      <c r="I25" s="131" t="n">
+      <c r="I25" s="129" t="n">
         <v>353722</v>
       </c>
-      <c r="J25" s="55">
+      <c r="J25" s="135">
         <f>J24*J8</f>
         <v/>
       </c>
-      <c r="K25" s="55">
+      <c r="K25" s="135">
         <f>K24*K8</f>
         <v/>
       </c>
-      <c r="L25" s="55">
+      <c r="L25" s="135">
         <f>L24*L8</f>
         <v/>
       </c>
-      <c r="M25" s="55">
+      <c r="M25" s="135">
         <f>M24*M8</f>
         <v/>
       </c>
-      <c r="N25" s="55">
+      <c r="N25" s="135">
         <f>N24*N8</f>
         <v/>
       </c>
@@ -3313,43 +3346,43 @@
       </c>
       <c r="C26" s="4" t="n"/>
       <c r="D26" s="22" t="n"/>
-      <c r="E26" s="17">
+      <c r="E26" s="136">
         <f>E24-E25</f>
         <v/>
       </c>
-      <c r="F26" s="17">
+      <c r="F26" s="136">
         <f>F24-F25</f>
         <v/>
       </c>
-      <c r="G26" s="17">
+      <c r="G26" s="136">
         <f>G24-G25</f>
         <v/>
       </c>
-      <c r="H26" s="17">
+      <c r="H26" s="136">
         <f>H24-H25</f>
         <v/>
       </c>
-      <c r="I26" s="17">
+      <c r="I26" s="136">
         <f>I24-I25</f>
         <v/>
       </c>
-      <c r="J26" s="17">
+      <c r="J26" s="136">
         <f>J24-J25</f>
         <v/>
       </c>
-      <c r="K26" s="17">
+      <c r="K26" s="136">
         <f>K24-K25</f>
         <v/>
       </c>
-      <c r="L26" s="17">
+      <c r="L26" s="136">
         <f>L24-L25</f>
         <v/>
       </c>
-      <c r="M26" s="17">
+      <c r="M26" s="136">
         <f>M24-M25</f>
         <v/>
       </c>
-      <c r="N26" s="17">
+      <c r="N26" s="136">
         <f>N24-N25</f>
         <v/>
       </c>
@@ -3379,38 +3412,38 @@
           <t>Salaries and Benefits</t>
         </is>
       </c>
-      <c r="E28" s="131" t="n">
+      <c r="E28" s="129" t="n">
         <v>396281</v>
       </c>
-      <c r="F28" s="131" t="n">
+      <c r="F28" s="129" t="n">
         <v>383863</v>
       </c>
-      <c r="G28" s="131" t="n">
+      <c r="G28" s="129" t="n">
         <v>400565</v>
       </c>
-      <c r="H28" s="131" t="n">
+      <c r="H28" s="129" t="n">
         <v>462834</v>
       </c>
-      <c r="I28" s="131" t="n">
+      <c r="I28" s="129" t="n">
         <v>513028</v>
       </c>
-      <c r="J28" s="19">
+      <c r="J28" s="135">
         <f>J9</f>
         <v/>
       </c>
-      <c r="K28" s="19">
+      <c r="K28" s="135">
         <f>K9</f>
         <v/>
       </c>
-      <c r="L28" s="19">
+      <c r="L28" s="135">
         <f>L9</f>
         <v/>
       </c>
-      <c r="M28" s="19">
+      <c r="M28" s="135">
         <f>M9</f>
         <v/>
       </c>
-      <c r="N28" s="19">
+      <c r="N28" s="135">
         <f>N9</f>
         <v/>
       </c>
@@ -3421,38 +3454,38 @@
           <t>Rent and Overhead</t>
         </is>
       </c>
-      <c r="E29" s="131" t="n">
+      <c r="E29" s="129" t="n">
         <v>171231</v>
       </c>
-      <c r="F29" s="131" t="n">
+      <c r="F29" s="129" t="n">
         <v>146758</v>
       </c>
-      <c r="G29" s="131" t="n">
+      <c r="G29" s="129" t="n">
         <v>159950</v>
       </c>
-      <c r="H29" s="131" t="n">
+      <c r="H29" s="129" t="n">
         <v>171940</v>
       </c>
-      <c r="I29" s="131" t="n">
+      <c r="I29" s="129" t="n">
         <v>188347</v>
       </c>
-      <c r="J29" s="19">
+      <c r="J29" s="135">
         <f>J10</f>
         <v/>
       </c>
-      <c r="K29" s="19">
+      <c r="K29" s="135">
         <f>K10</f>
         <v/>
       </c>
-      <c r="L29" s="19">
+      <c r="L29" s="135">
         <f>L10</f>
         <v/>
       </c>
-      <c r="M29" s="19">
+      <c r="M29" s="135">
         <f>M10</f>
         <v/>
       </c>
-      <c r="N29" s="19">
+      <c r="N29" s="135">
         <f>N10</f>
         <v/>
       </c>
@@ -3463,38 +3496,38 @@
           <t>Depreciation &amp; Amortization</t>
         </is>
       </c>
-      <c r="E30" s="131" t="n">
+      <c r="E30" s="129" t="n">
         <v>25592</v>
       </c>
-      <c r="F30" s="131" t="n">
+      <c r="F30" s="129" t="n">
         <v>20465</v>
       </c>
-      <c r="G30" s="131" t="n">
+      <c r="G30" s="129" t="n">
         <v>14638</v>
       </c>
-      <c r="H30" s="131" t="n">
+      <c r="H30" s="129" t="n">
         <v>13827</v>
       </c>
-      <c r="I30" s="131" t="n">
+      <c r="I30" s="129" t="n">
         <v>14952</v>
       </c>
-      <c r="J30" s="19">
+      <c r="J30" s="135">
         <f>J94</f>
         <v/>
       </c>
-      <c r="K30" s="19">
+      <c r="K30" s="135">
         <f>K94</f>
         <v/>
       </c>
-      <c r="L30" s="19">
+      <c r="L30" s="135">
         <f>L94</f>
         <v/>
       </c>
-      <c r="M30" s="19">
+      <c r="M30" s="135">
         <f>M94</f>
         <v/>
       </c>
-      <c r="N30" s="19">
+      <c r="N30" s="135">
         <f>N94</f>
         <v/>
       </c>
@@ -3507,38 +3540,38 @@
       </c>
       <c r="C31" s="2" t="n"/>
       <c r="D31" s="24" t="n"/>
-      <c r="E31" s="132" t="n">
+      <c r="E31" s="137" t="n">
         <v>40092</v>
       </c>
-      <c r="F31" s="132" t="n">
+      <c r="F31" s="137" t="n">
         <v>68967</v>
       </c>
-      <c r="G31" s="132" t="n">
+      <c r="G31" s="137" t="n">
         <v>95546</v>
       </c>
-      <c r="H31" s="132" t="n">
+      <c r="H31" s="137" t="n">
         <v>105638</v>
       </c>
-      <c r="I31" s="132" t="n">
+      <c r="I31" s="137" t="n">
         <v>133647</v>
       </c>
-      <c r="J31" s="16">
+      <c r="J31" s="138">
         <f>J101</f>
         <v/>
       </c>
-      <c r="K31" s="16">
+      <c r="K31" s="138">
         <f>K101</f>
         <v/>
       </c>
-      <c r="L31" s="16">
+      <c r="L31" s="138">
         <f>L101</f>
         <v/>
       </c>
-      <c r="M31" s="16">
+      <c r="M31" s="138">
         <f>M101</f>
         <v/>
       </c>
-      <c r="N31" s="16">
+      <c r="N31" s="138">
         <f>N101</f>
         <v/>
       </c>
@@ -3551,43 +3584,43 @@
       </c>
       <c r="C32" s="19" t="n"/>
       <c r="D32" s="47" t="n"/>
-      <c r="E32" s="49">
+      <c r="E32" s="139">
         <f>SUM(E28:E31)</f>
         <v/>
       </c>
-      <c r="F32" s="49">
+      <c r="F32" s="139">
         <f>SUM(F28:F31)</f>
         <v/>
       </c>
-      <c r="G32" s="49">
+      <c r="G32" s="139">
         <f>SUM(G28:G31)</f>
         <v/>
       </c>
-      <c r="H32" s="49">
+      <c r="H32" s="139">
         <f>SUM(H28:H31)</f>
         <v/>
       </c>
-      <c r="I32" s="49">
+      <c r="I32" s="139">
         <f>SUM(I28:I31)</f>
         <v/>
       </c>
-      <c r="J32" s="49">
+      <c r="J32" s="139">
         <f>SUM(J28:J31)</f>
         <v/>
       </c>
-      <c r="K32" s="49">
+      <c r="K32" s="139">
         <f>SUM(K28:K31)</f>
         <v/>
       </c>
-      <c r="L32" s="49">
+      <c r="L32" s="139">
         <f>SUM(L28:L31)</f>
         <v/>
       </c>
-      <c r="M32" s="49">
+      <c r="M32" s="139">
         <f>SUM(M28:M31)</f>
         <v/>
       </c>
-      <c r="N32" s="49">
+      <c r="N32" s="139">
         <f>SUM(N28:N31)</f>
         <v/>
       </c>
@@ -3600,43 +3633,43 @@
       </c>
       <c r="C33" s="4" t="n"/>
       <c r="D33" s="22" t="n"/>
-      <c r="E33" s="17">
+      <c r="E33" s="136">
         <f>E26-E32</f>
         <v/>
       </c>
-      <c r="F33" s="17">
+      <c r="F33" s="136">
         <f>F26-F32</f>
         <v/>
       </c>
-      <c r="G33" s="17">
+      <c r="G33" s="136">
         <f>G26-G32</f>
         <v/>
       </c>
-      <c r="H33" s="17">
+      <c r="H33" s="136">
         <f>H26-H32</f>
         <v/>
       </c>
-      <c r="I33" s="17">
+      <c r="I33" s="136">
         <f>I26-I32</f>
         <v/>
       </c>
-      <c r="J33" s="17">
+      <c r="J33" s="136">
         <f>J26-J32</f>
         <v/>
       </c>
-      <c r="K33" s="17">
+      <c r="K33" s="136">
         <f>K26-K32</f>
         <v/>
       </c>
-      <c r="L33" s="17">
+      <c r="L33" s="136">
         <f>L26-L32</f>
         <v/>
       </c>
-      <c r="M33" s="17">
+      <c r="M33" s="136">
         <f>M26-M32</f>
         <v/>
       </c>
-      <c r="N33" s="17">
+      <c r="N33" s="136">
         <f>N26-N32</f>
         <v/>
       </c>
@@ -3664,38 +3697,38 @@
       </c>
       <c r="C35" s="19" t="n"/>
       <c r="D35" s="47" t="n"/>
-      <c r="E35" s="131" t="n">
+      <c r="E35" s="129" t="n">
         <v>81058</v>
       </c>
-      <c r="F35" s="131" t="n">
+      <c r="F35" s="129" t="n">
         <v>97768</v>
       </c>
-      <c r="G35" s="131" t="n">
+      <c r="G35" s="129" t="n">
         <v>124249</v>
       </c>
-      <c r="H35" s="131" t="n">
+      <c r="H35" s="129" t="n">
         <v>129214</v>
       </c>
-      <c r="I35" s="131" t="n">
+      <c r="I35" s="129" t="n">
         <v>150649</v>
       </c>
-      <c r="J35" s="55">
+      <c r="J35" s="135">
         <f>J33*J13</f>
         <v/>
       </c>
-      <c r="K35" s="55">
+      <c r="K35" s="135">
         <f>K33*K13</f>
         <v/>
       </c>
-      <c r="L35" s="55">
+      <c r="L35" s="135">
         <f>L33*L13</f>
         <v/>
       </c>
-      <c r="M35" s="55">
+      <c r="M35" s="135">
         <f>M33*M13</f>
         <v/>
       </c>
-      <c r="N35" s="55">
+      <c r="N35" s="135">
         <f>N33*N13</f>
         <v/>
       </c>
@@ -3708,43 +3741,43 @@
       </c>
       <c r="C36" s="39" t="n"/>
       <c r="D36" s="40" t="n"/>
-      <c r="E36" s="41">
+      <c r="E36" s="140">
         <f>E33-E35</f>
         <v/>
       </c>
-      <c r="F36" s="41">
+      <c r="F36" s="140">
         <f>F33-F35</f>
         <v/>
       </c>
-      <c r="G36" s="41">
+      <c r="G36" s="140">
         <f>G33-G35</f>
         <v/>
       </c>
-      <c r="H36" s="41">
+      <c r="H36" s="140">
         <f>H33-H35</f>
         <v/>
       </c>
-      <c r="I36" s="41">
+      <c r="I36" s="140">
         <f>I33-I35</f>
         <v/>
       </c>
-      <c r="J36" s="41">
+      <c r="J36" s="140">
         <f>J33-J35</f>
         <v/>
       </c>
-      <c r="K36" s="41">
+      <c r="K36" s="140">
         <f>K33-K35</f>
         <v/>
       </c>
-      <c r="L36" s="41">
+      <c r="L36" s="140">
         <f>L33-L35</f>
         <v/>
       </c>
-      <c r="M36" s="41">
+      <c r="M36" s="140">
         <f>M33-M35</f>
         <v/>
       </c>
-      <c r="N36" s="41">
+      <c r="N36" s="140">
         <f>N33-N35</f>
         <v/>
       </c>
@@ -3805,38 +3838,38 @@
           <t>Cash</t>
         </is>
       </c>
-      <c r="E41" s="131" t="n">
+      <c r="E41" s="129" t="n">
         <v>195354</v>
       </c>
-      <c r="F41" s="131" t="n">
+      <c r="F41" s="129" t="n">
         <v>133202</v>
       </c>
-      <c r="G41" s="131" t="n">
+      <c r="G41" s="129" t="n">
         <v>136778</v>
       </c>
-      <c r="H41" s="131" t="n">
+      <c r="H41" s="129" t="n">
         <v>150667</v>
       </c>
-      <c r="I41" s="131" t="n">
+      <c r="I41" s="129" t="n">
         <v>134136</v>
       </c>
-      <c r="J41" s="19">
+      <c r="J41" s="135">
         <f>J78</f>
         <v/>
       </c>
-      <c r="K41" s="19">
+      <c r="K41" s="135">
         <f>K78</f>
         <v/>
       </c>
-      <c r="L41" s="19">
+      <c r="L41" s="135">
         <f>L78</f>
         <v/>
       </c>
-      <c r="M41" s="19">
+      <c r="M41" s="135">
         <f>M78</f>
         <v/>
       </c>
-      <c r="N41" s="19">
+      <c r="N41" s="135">
         <f>N78</f>
         <v/>
       </c>
@@ -3847,38 +3880,38 @@
           <t>Accounts Receivable</t>
         </is>
       </c>
-      <c r="E42" s="131" t="n">
+      <c r="E42" s="129" t="n">
         <v>312107</v>
       </c>
-      <c r="F42" s="131" t="n">
+      <c r="F42" s="129" t="n">
         <v>322410</v>
       </c>
-      <c r="G42" s="131" t="n">
+      <c r="G42" s="129" t="n">
         <v>387947</v>
       </c>
-      <c r="H42" s="131" t="n">
+      <c r="H42" s="129" t="n">
         <v>426642</v>
       </c>
-      <c r="I42" s="131" t="n">
+      <c r="I42" s="129" t="n">
         <v>529148</v>
       </c>
-      <c r="J42" s="42">
+      <c r="J42" s="135">
         <f>J24*J15/365</f>
         <v/>
       </c>
-      <c r="K42" s="42">
+      <c r="K42" s="135">
         <f>K24*K15/365</f>
         <v/>
       </c>
-      <c r="L42" s="42">
+      <c r="L42" s="135">
         <f>L24*L15/365</f>
         <v/>
       </c>
-      <c r="M42" s="42">
+      <c r="M42" s="135">
         <f>M24*M15/365</f>
         <v/>
       </c>
-      <c r="N42" s="42">
+      <c r="N42" s="135">
         <f>N24*N15/365</f>
         <v/>
       </c>
@@ -3889,38 +3922,38 @@
           <t>Inventory</t>
         </is>
       </c>
-      <c r="E43" s="131" t="n">
+      <c r="E43" s="129" t="n">
         <v>0</v>
       </c>
-      <c r="F43" s="131" t="n">
+      <c r="F43" s="129" t="n">
         <v>0</v>
       </c>
-      <c r="G43" s="131" t="n">
+      <c r="G43" s="129" t="n">
         <v>0</v>
       </c>
-      <c r="H43" s="131" t="n">
+      <c r="H43" s="129" t="n">
         <v>0</v>
       </c>
-      <c r="I43" s="131" t="n">
+      <c r="I43" s="129" t="n">
         <v>0</v>
       </c>
-      <c r="J43" s="19">
+      <c r="J43" s="135">
         <f>J25*J16/365</f>
         <v/>
       </c>
-      <c r="K43" s="19">
+      <c r="K43" s="135">
         <f>K25*K16/365</f>
         <v/>
       </c>
-      <c r="L43" s="19">
+      <c r="L43" s="135">
         <f>L25*L16/365</f>
         <v/>
       </c>
-      <c r="M43" s="19">
+      <c r="M43" s="135">
         <f>M25*M16/365</f>
         <v/>
       </c>
-      <c r="N43" s="19">
+      <c r="N43" s="135">
         <f>N25*N16/365</f>
         <v/>
       </c>
@@ -3931,38 +3964,38 @@
           <t>Property &amp; Equipment</t>
         </is>
       </c>
-      <c r="E44" s="131" t="n">
+      <c r="E44" s="129" t="n">
         <v>27913</v>
       </c>
-      <c r="F44" s="131" t="n">
+      <c r="F44" s="129" t="n">
         <v>17580</v>
       </c>
-      <c r="G44" s="131" t="n">
+      <c r="G44" s="129" t="n">
         <v>10966</v>
       </c>
-      <c r="H44" s="131" t="n">
+      <c r="H44" s="129" t="n">
         <v>38465</v>
       </c>
-      <c r="I44" s="131" t="n">
+      <c r="I44" s="129" t="n">
         <v>67713</v>
       </c>
-      <c r="J44" s="19">
+      <c r="J44" s="135">
         <f>J95</f>
         <v/>
       </c>
-      <c r="K44" s="19">
+      <c r="K44" s="135">
         <f>K95</f>
         <v/>
       </c>
-      <c r="L44" s="19">
+      <c r="L44" s="135">
         <f>L95</f>
         <v/>
       </c>
-      <c r="M44" s="19">
+      <c r="M44" s="135">
         <f>M95</f>
         <v/>
       </c>
-      <c r="N44" s="19">
+      <c r="N44" s="135">
         <f>N95</f>
         <v/>
       </c>
@@ -3975,43 +4008,43 @@
       </c>
       <c r="C45" s="39" t="n"/>
       <c r="D45" s="40" t="n"/>
-      <c r="E45" s="41">
+      <c r="E45" s="140">
         <f>SUM(E41:E44)</f>
         <v/>
       </c>
-      <c r="F45" s="41">
+      <c r="F45" s="140">
         <f>SUM(F41:F44)</f>
         <v/>
       </c>
-      <c r="G45" s="41">
+      <c r="G45" s="140">
         <f>SUM(G41:G44)</f>
         <v/>
       </c>
-      <c r="H45" s="41">
+      <c r="H45" s="140">
         <f>SUM(H41:H44)</f>
         <v/>
       </c>
-      <c r="I45" s="41">
+      <c r="I45" s="140">
         <f>SUM(I41:I44)</f>
         <v/>
       </c>
-      <c r="J45" s="41">
+      <c r="J45" s="140">
         <f>SUM(J41:J44)</f>
         <v/>
       </c>
-      <c r="K45" s="41">
+      <c r="K45" s="140">
         <f>SUM(K41:K44)</f>
         <v/>
       </c>
-      <c r="L45" s="41">
+      <c r="L45" s="140">
         <f>SUM(L41:L44)</f>
         <v/>
       </c>
-      <c r="M45" s="41">
+      <c r="M45" s="140">
         <f>SUM(M41:M44)</f>
         <v/>
       </c>
-      <c r="N45" s="41">
+      <c r="N45" s="140">
         <f>SUM(N41:N44)</f>
         <v/>
       </c>
@@ -4049,38 +4082,38 @@
           <t>Accounts Payable</t>
         </is>
       </c>
-      <c r="E48" s="131" t="n">
+      <c r="E48" s="129" t="n">
         <v>20749</v>
       </c>
-      <c r="F48" s="131" t="n">
+      <c r="F48" s="129" t="n">
         <v>17273</v>
       </c>
-      <c r="G48" s="131" t="n">
+      <c r="G48" s="129" t="n">
         <v>19009</v>
       </c>
-      <c r="H48" s="131" t="n">
+      <c r="H48" s="129" t="n">
         <v>22473</v>
       </c>
-      <c r="I48" s="131" t="n">
+      <c r="I48" s="129" t="n">
         <v>32315</v>
       </c>
-      <c r="J48" s="19">
+      <c r="J48" s="135">
         <f>J25*J17/365</f>
         <v/>
       </c>
-      <c r="K48" s="19">
+      <c r="K48" s="135">
         <f>K25*K17/365</f>
         <v/>
       </c>
-      <c r="L48" s="19">
+      <c r="L48" s="135">
         <f>L25*L17/365</f>
         <v/>
       </c>
-      <c r="M48" s="19">
+      <c r="M48" s="135">
         <f>M25*M17/365</f>
         <v/>
       </c>
-      <c r="N48" s="19">
+      <c r="N48" s="135">
         <f>N25*N17/365</f>
         <v/>
       </c>
@@ -4091,38 +4124,38 @@
           <t>Debt</t>
         </is>
       </c>
-      <c r="E49" s="131" t="n">
+      <c r="E49" s="129" t="n">
         <v>1259018</v>
       </c>
-      <c r="F49" s="131" t="n">
+      <c r="F49" s="129" t="n">
         <v>1853669</v>
       </c>
-      <c r="G49" s="131" t="n">
+      <c r="G49" s="129" t="n">
         <v>1861658</v>
       </c>
-      <c r="H49" s="131" t="n">
+      <c r="H49" s="129" t="n">
         <v>2209021</v>
       </c>
-      <c r="I49" s="131" t="n">
+      <c r="I49" s="129" t="n">
         <v>3055691</v>
       </c>
-      <c r="J49" s="19">
+      <c r="J49" s="135">
         <f>J100</f>
         <v/>
       </c>
-      <c r="K49" s="19">
+      <c r="K49" s="135">
         <f>K100</f>
         <v/>
       </c>
-      <c r="L49" s="19">
+      <c r="L49" s="135">
         <f>L100</f>
         <v/>
       </c>
-      <c r="M49" s="19">
+      <c r="M49" s="135">
         <f>M100</f>
         <v/>
       </c>
-      <c r="N49" s="19">
+      <c r="N49" s="135">
         <f>N100</f>
         <v/>
       </c>
@@ -4135,43 +4168,43 @@
       </c>
       <c r="C50" s="4" t="n"/>
       <c r="D50" s="22" t="n"/>
-      <c r="E50" s="17">
+      <c r="E50" s="136">
         <f>SUM(E48:E49)</f>
         <v/>
       </c>
-      <c r="F50" s="17">
+      <c r="F50" s="136">
         <f>SUM(F48:F49)</f>
         <v/>
       </c>
-      <c r="G50" s="17">
+      <c r="G50" s="136">
         <f>SUM(G48:G49)</f>
         <v/>
       </c>
-      <c r="H50" s="17">
+      <c r="H50" s="136">
         <f>SUM(H48:H49)</f>
         <v/>
       </c>
-      <c r="I50" s="17">
+      <c r="I50" s="136">
         <f>SUM(I48:I49)</f>
         <v/>
       </c>
-      <c r="J50" s="17">
+      <c r="J50" s="136">
         <f>SUM(J48:J49)</f>
         <v/>
       </c>
-      <c r="K50" s="17">
+      <c r="K50" s="136">
         <f>SUM(K48:K49)</f>
         <v/>
       </c>
-      <c r="L50" s="17">
+      <c r="L50" s="136">
         <f>SUM(L48:L49)</f>
         <v/>
       </c>
-      <c r="M50" s="17">
+      <c r="M50" s="136">
         <f>SUM(M48:M49)</f>
         <v/>
       </c>
-      <c r="N50" s="17">
+      <c r="N50" s="136">
         <f>SUM(N48:N49)</f>
         <v/>
       </c>
@@ -4194,38 +4227,38 @@
           <t>Equity Capital</t>
         </is>
       </c>
-      <c r="E52" s="131" t="n">
+      <c r="E52" s="129" t="n">
         <v>-744393</v>
       </c>
-      <c r="F52" s="131" t="n">
+      <c r="F52" s="129" t="n">
         <v>-1397750</v>
       </c>
-      <c r="G52" s="131" t="n">
+      <c r="G52" s="129" t="n">
         <v>-1344976</v>
       </c>
-      <c r="H52" s="131" t="n">
+      <c r="H52" s="129" t="n">
         <v>-1615720</v>
       </c>
-      <c r="I52" s="131" t="n">
+      <c r="I52" s="129" t="n">
         <v>-2357009</v>
       </c>
-      <c r="J52" s="19">
+      <c r="J52" s="135">
         <f>I52+J20</f>
         <v/>
       </c>
-      <c r="K52" s="19">
+      <c r="K52" s="135">
         <f>J52+K20</f>
         <v/>
       </c>
-      <c r="L52" s="19">
+      <c r="L52" s="135">
         <f>K52+L20</f>
         <v/>
       </c>
-      <c r="M52" s="19">
+      <c r="M52" s="135">
         <f>L52+M20</f>
         <v/>
       </c>
-      <c r="N52" s="19">
+      <c r="N52" s="135">
         <f>M52+N20</f>
         <v/>
       </c>
@@ -4236,38 +4269,38 @@
           <t>Retained Earnings</t>
         </is>
       </c>
-      <c r="E53" s="131" t="n">
+      <c r="E53" s="129" t="n">
         <v>0</v>
       </c>
-      <c r="F53" s="131" t="n">
+      <c r="F53" s="129" t="n">
         <v>0</v>
       </c>
-      <c r="G53" s="131" t="n">
+      <c r="G53" s="129" t="n">
         <v>0</v>
       </c>
-      <c r="H53" s="131" t="n">
+      <c r="H53" s="129" t="n">
         <v>0</v>
       </c>
-      <c r="I53" s="131" t="n">
+      <c r="I53" s="129" t="n">
         <v>0</v>
       </c>
-      <c r="J53" s="19">
+      <c r="J53" s="135">
         <f>I53+J36</f>
         <v/>
       </c>
-      <c r="K53" s="19">
+      <c r="K53" s="135">
         <f>J53+K36</f>
         <v/>
       </c>
-      <c r="L53" s="19">
+      <c r="L53" s="135">
         <f>K53+L36</f>
         <v/>
       </c>
-      <c r="M53" s="19">
+      <c r="M53" s="135">
         <f>L53+M36</f>
         <v/>
       </c>
-      <c r="N53" s="19">
+      <c r="N53" s="135">
         <f>M53+N36</f>
         <v/>
       </c>
@@ -4280,43 +4313,43 @@
       </c>
       <c r="C54" s="8" t="n"/>
       <c r="D54" s="26" t="n"/>
-      <c r="E54" s="50">
+      <c r="E54" s="141">
         <f>SUM(E52:E53)</f>
         <v/>
       </c>
-      <c r="F54" s="50">
+      <c r="F54" s="141">
         <f>SUM(F52:F53)</f>
         <v/>
       </c>
-      <c r="G54" s="50">
+      <c r="G54" s="141">
         <f>SUM(G52:G53)</f>
         <v/>
       </c>
-      <c r="H54" s="50">
+      <c r="H54" s="141">
         <f>SUM(H52:H53)</f>
         <v/>
       </c>
-      <c r="I54" s="50">
+      <c r="I54" s="141">
         <f>SUM(I52:I53)</f>
         <v/>
       </c>
-      <c r="J54" s="50">
+      <c r="J54" s="141">
         <f>SUM(J52:J53)</f>
         <v/>
       </c>
-      <c r="K54" s="50">
+      <c r="K54" s="141">
         <f>SUM(K52:K53)</f>
         <v/>
       </c>
-      <c r="L54" s="50">
+      <c r="L54" s="141">
         <f>SUM(L52:L53)</f>
         <v/>
       </c>
-      <c r="M54" s="50">
+      <c r="M54" s="141">
         <f>SUM(M52:M53)</f>
         <v/>
       </c>
-      <c r="N54" s="50">
+      <c r="N54" s="141">
         <f>SUM(N52:N53)</f>
         <v/>
       </c>
@@ -4329,43 +4362,43 @@
       </c>
       <c r="C55" s="39" t="n"/>
       <c r="D55" s="40" t="n"/>
-      <c r="E55" s="41">
+      <c r="E55" s="140">
         <f>E50+E54</f>
         <v/>
       </c>
-      <c r="F55" s="41">
+      <c r="F55" s="140">
         <f>F50+F54</f>
         <v/>
       </c>
-      <c r="G55" s="41">
+      <c r="G55" s="140">
         <f>G50+G54</f>
         <v/>
       </c>
-      <c r="H55" s="41">
+      <c r="H55" s="140">
         <f>H50+H54</f>
         <v/>
       </c>
-      <c r="I55" s="41">
+      <c r="I55" s="140">
         <f>I50+I54</f>
         <v/>
       </c>
-      <c r="J55" s="41">
+      <c r="J55" s="140">
         <f>J50+J54</f>
         <v/>
       </c>
-      <c r="K55" s="41">
+      <c r="K55" s="140">
         <f>K50+K54</f>
         <v/>
       </c>
-      <c r="L55" s="41">
+      <c r="L55" s="140">
         <f>L50+L54</f>
         <v/>
       </c>
-      <c r="M55" s="41">
+      <c r="M55" s="140">
         <f>M50+M54</f>
         <v/>
       </c>
-      <c r="N55" s="41">
+      <c r="N55" s="140">
         <f>N50+N54</f>
         <v/>
       </c>
@@ -4390,43 +4423,43 @@
       </c>
       <c r="C57" s="9" t="n"/>
       <c r="D57" s="27" t="n"/>
-      <c r="E57" s="66">
+      <c r="E57" s="142">
         <f>E55-E45</f>
         <v/>
       </c>
-      <c r="F57" s="66">
+      <c r="F57" s="142">
         <f>F55-F45</f>
         <v/>
       </c>
-      <c r="G57" s="66">
+      <c r="G57" s="142">
         <f>G55-G45</f>
         <v/>
       </c>
-      <c r="H57" s="66">
+      <c r="H57" s="142">
         <f>H55-H45</f>
         <v/>
       </c>
-      <c r="I57" s="66">
+      <c r="I57" s="142">
         <f>I55-I45</f>
         <v/>
       </c>
-      <c r="J57" s="66">
+      <c r="J57" s="142">
         <f>J55-J45</f>
         <v/>
       </c>
-      <c r="K57" s="66">
+      <c r="K57" s="142">
         <f>K55-K45</f>
         <v/>
       </c>
-      <c r="L57" s="66">
+      <c r="L57" s="142">
         <f>L55-L45</f>
         <v/>
       </c>
-      <c r="M57" s="66">
+      <c r="M57" s="142">
         <f>M55-M45</f>
         <v/>
       </c>
-      <c r="N57" s="66">
+      <c r="N57" s="142">
         <f>N55-N45</f>
         <v/>
       </c>
@@ -4490,43 +4523,43 @@
           <t>Net Earnings</t>
         </is>
       </c>
-      <c r="E62" s="19">
+      <c r="E62" s="135">
         <f>E36</f>
         <v/>
       </c>
-      <c r="F62" s="19">
+      <c r="F62" s="135">
         <f>F36</f>
         <v/>
       </c>
-      <c r="G62" s="19">
+      <c r="G62" s="135">
         <f>G36</f>
         <v/>
       </c>
-      <c r="H62" s="19">
+      <c r="H62" s="135">
         <f>H36</f>
         <v/>
       </c>
-      <c r="I62" s="19">
+      <c r="I62" s="135">
         <f>I36</f>
         <v/>
       </c>
-      <c r="J62" s="19">
+      <c r="J62" s="135">
         <f>J36</f>
         <v/>
       </c>
-      <c r="K62" s="19">
+      <c r="K62" s="135">
         <f>K36</f>
         <v/>
       </c>
-      <c r="L62" s="19">
+      <c r="L62" s="135">
         <f>L36</f>
         <v/>
       </c>
-      <c r="M62" s="19">
+      <c r="M62" s="135">
         <f>M36</f>
         <v/>
       </c>
-      <c r="N62" s="19">
+      <c r="N62" s="135">
         <f>N36</f>
         <v/>
       </c>
@@ -4537,43 +4570,43 @@
           <t>Plus: Depreciation &amp; Amortization</t>
         </is>
       </c>
-      <c r="E63" s="19">
+      <c r="E63" s="135">
         <f>+E30</f>
         <v/>
       </c>
-      <c r="F63" s="19">
+      <c r="F63" s="135">
         <f>+F30</f>
         <v/>
       </c>
-      <c r="G63" s="19">
+      <c r="G63" s="135">
         <f>+G30</f>
         <v/>
       </c>
-      <c r="H63" s="19">
+      <c r="H63" s="135">
         <f>+H30</f>
         <v/>
       </c>
-      <c r="I63" s="19">
+      <c r="I63" s="135">
         <f>+I30</f>
         <v/>
       </c>
-      <c r="J63" s="19">
+      <c r="J63" s="135">
         <f>+J30</f>
         <v/>
       </c>
-      <c r="K63" s="19">
+      <c r="K63" s="135">
         <f>+K30</f>
         <v/>
       </c>
-      <c r="L63" s="19">
+      <c r="L63" s="135">
         <f>+L30</f>
         <v/>
       </c>
-      <c r="M63" s="19">
+      <c r="M63" s="135">
         <f>+M30</f>
         <v/>
       </c>
-      <c r="N63" s="19">
+      <c r="N63" s="135">
         <f>+N30</f>
         <v/>
       </c>
@@ -4584,38 +4617,38 @@
           <t>Less: Changes in Working Capital</t>
         </is>
       </c>
-      <c r="E64" s="131" t="n">
+      <c r="E64" s="129" t="n">
         <v>0</v>
       </c>
-      <c r="F64" s="131" t="n">
+      <c r="F64" s="129" t="n">
         <v>13779</v>
       </c>
-      <c r="G64" s="131" t="n">
+      <c r="G64" s="129" t="n">
         <v>63801</v>
       </c>
-      <c r="H64" s="131" t="n">
+      <c r="H64" s="129" t="n">
         <v>35231</v>
       </c>
-      <c r="I64" s="131" t="n">
+      <c r="I64" s="129" t="n">
         <v>92664</v>
       </c>
-      <c r="J64" s="19">
+      <c r="J64" s="135">
         <f>J89</f>
         <v/>
       </c>
-      <c r="K64" s="19">
+      <c r="K64" s="135">
         <f>K89</f>
         <v/>
       </c>
-      <c r="L64" s="19">
+      <c r="L64" s="135">
         <f>L89</f>
         <v/>
       </c>
-      <c r="M64" s="19">
+      <c r="M64" s="135">
         <f>M89</f>
         <v/>
       </c>
-      <c r="N64" s="19">
+      <c r="N64" s="135">
         <f>N89</f>
         <v/>
       </c>
@@ -4628,43 +4661,43 @@
       </c>
       <c r="C65" s="5" t="n"/>
       <c r="D65" s="28" t="n"/>
-      <c r="E65" s="17">
+      <c r="E65" s="136">
         <f>E62+E63-E64</f>
         <v/>
       </c>
-      <c r="F65" s="17">
+      <c r="F65" s="136">
         <f>F62+F63-F64</f>
         <v/>
       </c>
-      <c r="G65" s="17">
+      <c r="G65" s="136">
         <f>G62+G63-G64</f>
         <v/>
       </c>
-      <c r="H65" s="17">
+      <c r="H65" s="136">
         <f>H62+H63-H64</f>
         <v/>
       </c>
-      <c r="I65" s="17">
+      <c r="I65" s="136">
         <f>I62+I63-I64</f>
         <v/>
       </c>
-      <c r="J65" s="17">
+      <c r="J65" s="136">
         <f>J62+J63-J64</f>
         <v/>
       </c>
-      <c r="K65" s="17">
+      <c r="K65" s="136">
         <f>K62+K63-K64</f>
         <v/>
       </c>
-      <c r="L65" s="17">
+      <c r="L65" s="136">
         <f>L62+L63-L64</f>
         <v/>
       </c>
-      <c r="M65" s="17">
+      <c r="M65" s="136">
         <f>M62+M63-M64</f>
         <v/>
       </c>
-      <c r="N65" s="17">
+      <c r="N65" s="136">
         <f>N62+N63-N64</f>
         <v/>
       </c>
@@ -4707,38 +4740,38 @@
           <t>Investments in Property &amp; Equipment</t>
         </is>
       </c>
-      <c r="E68" s="131" t="n">
+      <c r="E68" s="129" t="n">
         <v>7569</v>
       </c>
-      <c r="F68" s="131" t="n">
+      <c r="F68" s="129" t="n">
         <v>6029</v>
       </c>
-      <c r="G68" s="131" t="n">
+      <c r="G68" s="129" t="n">
         <v>4237</v>
       </c>
-      <c r="H68" s="131" t="n">
+      <c r="H68" s="129" t="n">
         <v>25551</v>
       </c>
-      <c r="I68" s="131" t="n">
+      <c r="I68" s="129" t="n">
         <v>39407</v>
       </c>
-      <c r="J68" s="19">
+      <c r="J68" s="135">
         <f>J18</f>
         <v/>
       </c>
-      <c r="K68" s="19">
+      <c r="K68" s="135">
         <f>K18</f>
         <v/>
       </c>
-      <c r="L68" s="19">
+      <c r="L68" s="135">
         <f>L18</f>
         <v/>
       </c>
-      <c r="M68" s="19">
+      <c r="M68" s="135">
         <f>M18</f>
         <v/>
       </c>
-      <c r="N68" s="19">
+      <c r="N68" s="135">
         <f>N18</f>
         <v/>
       </c>
@@ -4751,43 +4784,43 @@
       </c>
       <c r="C69" s="5" t="n"/>
       <c r="D69" s="28" t="n"/>
-      <c r="E69" s="17">
+      <c r="E69" s="136">
         <f>SUM(E68)</f>
         <v/>
       </c>
-      <c r="F69" s="17">
+      <c r="F69" s="136">
         <f>SUM(F68)</f>
         <v/>
       </c>
-      <c r="G69" s="17">
+      <c r="G69" s="136">
         <f>SUM(G68)</f>
         <v/>
       </c>
-      <c r="H69" s="17">
+      <c r="H69" s="136">
         <f>SUM(H68)</f>
         <v/>
       </c>
-      <c r="I69" s="17">
+      <c r="I69" s="136">
         <f>SUM(I68)</f>
         <v/>
       </c>
-      <c r="J69" s="17">
+      <c r="J69" s="136">
         <f>SUM(J68)</f>
         <v/>
       </c>
-      <c r="K69" s="17">
+      <c r="K69" s="136">
         <f>SUM(K68)</f>
         <v/>
       </c>
-      <c r="L69" s="17">
+      <c r="L69" s="136">
         <f>SUM(L68)</f>
         <v/>
       </c>
-      <c r="M69" s="17">
+      <c r="M69" s="136">
         <f>SUM(M68)</f>
         <v/>
       </c>
-      <c r="N69" s="17">
+      <c r="N69" s="136">
         <f>SUM(N68)</f>
         <v/>
       </c>
@@ -4830,38 +4863,38 @@
           <t>Issuance (repayment) of debt</t>
         </is>
       </c>
-      <c r="E72" s="131" t="n">
+      <c r="E72" s="129" t="n">
         <v>0</v>
       </c>
-      <c r="F72" s="131" t="n">
+      <c r="F72" s="129" t="n">
         <v>594651</v>
       </c>
-      <c r="G72" s="131" t="n">
+      <c r="G72" s="129" t="n">
         <v>7989</v>
       </c>
-      <c r="H72" s="131" t="n">
+      <c r="H72" s="129" t="n">
         <v>347363</v>
       </c>
-      <c r="I72" s="131" t="n">
+      <c r="I72" s="129" t="n">
         <v>846670</v>
       </c>
-      <c r="J72" s="19">
+      <c r="J72" s="135">
         <f>J19</f>
         <v/>
       </c>
-      <c r="K72" s="19">
+      <c r="K72" s="135">
         <f>K19</f>
         <v/>
       </c>
-      <c r="L72" s="19">
+      <c r="L72" s="135">
         <f>L19</f>
         <v/>
       </c>
-      <c r="M72" s="19">
+      <c r="M72" s="135">
         <f>M19</f>
         <v/>
       </c>
-      <c r="N72" s="19">
+      <c r="N72" s="135">
         <f>N19</f>
         <v/>
       </c>
@@ -4872,38 +4905,38 @@
           <t>Issuance (repayment) of equity</t>
         </is>
       </c>
-      <c r="E73" s="131" t="n">
+      <c r="E73" s="129" t="n">
         <v>0</v>
       </c>
-      <c r="F73" s="131" t="n">
+      <c r="F73" s="129" t="n">
         <v>0</v>
       </c>
-      <c r="G73" s="131" t="n">
+      <c r="G73" s="129" t="n">
         <v>0</v>
       </c>
-      <c r="H73" s="131" t="n">
+      <c r="H73" s="129" t="n">
         <v>0</v>
       </c>
-      <c r="I73" s="131" t="n">
+      <c r="I73" s="129" t="n">
         <v>0</v>
       </c>
-      <c r="J73" s="19">
+      <c r="J73" s="135">
         <f>J20</f>
         <v/>
       </c>
-      <c r="K73" s="19">
+      <c r="K73" s="135">
         <f>K20</f>
         <v/>
       </c>
-      <c r="L73" s="19">
+      <c r="L73" s="135">
         <f>L20</f>
         <v/>
       </c>
-      <c r="M73" s="19">
+      <c r="M73" s="135">
         <f>M20</f>
         <v/>
       </c>
-      <c r="N73" s="19">
+      <c r="N73" s="135">
         <f>N20</f>
         <v/>
       </c>
@@ -4916,43 +4949,43 @@
       </c>
       <c r="C74" s="5" t="n"/>
       <c r="D74" s="28" t="n"/>
-      <c r="E74" s="17">
+      <c r="E74" s="136">
         <f>SUM(E72:E73)</f>
         <v/>
       </c>
-      <c r="F74" s="17">
+      <c r="F74" s="136">
         <f>SUM(F72:F73)</f>
         <v/>
       </c>
-      <c r="G74" s="17">
+      <c r="G74" s="136">
         <f>SUM(G72:G73)</f>
         <v/>
       </c>
-      <c r="H74" s="17">
+      <c r="H74" s="136">
         <f>SUM(H72:H73)</f>
         <v/>
       </c>
-      <c r="I74" s="17">
+      <c r="I74" s="136">
         <f>SUM(I72:I73)</f>
         <v/>
       </c>
-      <c r="J74" s="17">
+      <c r="J74" s="136">
         <f>SUM(J72:J73)</f>
         <v/>
       </c>
-      <c r="K74" s="17">
+      <c r="K74" s="136">
         <f>SUM(K72:K73)</f>
         <v/>
       </c>
-      <c r="L74" s="17">
+      <c r="L74" s="136">
         <f>SUM(L72:L73)</f>
         <v/>
       </c>
-      <c r="M74" s="17">
+      <c r="M74" s="136">
         <f>SUM(M72:M73)</f>
         <v/>
       </c>
-      <c r="N74" s="17">
+      <c r="N74" s="136">
         <f>SUM(N72:N73)</f>
         <v/>
       </c>
@@ -4978,43 +5011,43 @@
           <t>Net Increase (decrease) in Cash</t>
         </is>
       </c>
-      <c r="E76" s="52">
+      <c r="E76" s="132">
         <f>E65-E69+E74</f>
         <v/>
       </c>
-      <c r="F76" s="52">
+      <c r="F76" s="132">
         <f>F65-F69+F74</f>
         <v/>
       </c>
-      <c r="G76" s="52">
+      <c r="G76" s="132">
         <f>G65-G69+G74</f>
         <v/>
       </c>
-      <c r="H76" s="52">
+      <c r="H76" s="132">
         <f>H65-H69+H74</f>
         <v/>
       </c>
-      <c r="I76" s="52">
+      <c r="I76" s="132">
         <f>I65-I69+I74</f>
         <v/>
       </c>
-      <c r="J76" s="52">
+      <c r="J76" s="132">
         <f>J65-J69+J74</f>
         <v/>
       </c>
-      <c r="K76" s="52">
+      <c r="K76" s="132">
         <f>K65-K69+K74</f>
         <v/>
       </c>
-      <c r="L76" s="52">
+      <c r="L76" s="132">
         <f>L65-L69+L74</f>
         <v/>
       </c>
-      <c r="M76" s="52">
+      <c r="M76" s="132">
         <f>M65-M69+M74</f>
         <v/>
       </c>
-      <c r="N76" s="52">
+      <c r="N76" s="132">
         <f>N65-N69+N74</f>
         <v/>
       </c>
@@ -5025,39 +5058,39 @@
           <t>Opening Cash Balance</t>
         </is>
       </c>
-      <c r="E77" s="19">
+      <c r="E77" s="135">
         <f>D78</f>
         <v/>
       </c>
-      <c r="F77" s="33" t="n">
+      <c r="F77" s="143" t="n">
         <v>167971.1792</v>
       </c>
-      <c r="G77" s="33" t="n">
+      <c r="G77" s="143" t="n">
         <v>181209.912697878</v>
       </c>
-      <c r="H77" s="33" t="n">
+      <c r="H77" s="143" t="n">
         <v>183715.2565830093</v>
       </c>
-      <c r="I77" s="33" t="n">
+      <c r="I77" s="143" t="n">
         <v>211069.3356066046</v>
       </c>
-      <c r="J77" s="19">
+      <c r="J77" s="135">
         <f>+I78</f>
         <v/>
       </c>
-      <c r="K77" s="19">
+      <c r="K77" s="135">
         <f>+J78</f>
         <v/>
       </c>
-      <c r="L77" s="19">
+      <c r="L77" s="135">
         <f>+K78</f>
         <v/>
       </c>
-      <c r="M77" s="19">
+      <c r="M77" s="135">
         <f>+L78</f>
         <v/>
       </c>
-      <c r="N77" s="19">
+      <c r="N77" s="135">
         <f>+M78</f>
         <v/>
       </c>
@@ -5069,46 +5102,46 @@
         </is>
       </c>
       <c r="C78" s="5" t="n"/>
-      <c r="D78" s="133" t="n">
+      <c r="D78" s="144" t="n">
         <v>157394</v>
       </c>
-      <c r="E78" s="17">
+      <c r="E78" s="136">
         <f>SUM(E76:E77)</f>
         <v/>
       </c>
-      <c r="F78" s="17">
+      <c r="F78" s="136">
         <f>SUM(F76:F77)</f>
         <v/>
       </c>
-      <c r="G78" s="17">
+      <c r="G78" s="136">
         <f>SUM(G76:G77)</f>
         <v/>
       </c>
-      <c r="H78" s="17">
+      <c r="H78" s="136">
         <f>SUM(H76:H77)</f>
         <v/>
       </c>
-      <c r="I78" s="17">
+      <c r="I78" s="136">
         <f>SUM(I76:I77)</f>
         <v/>
       </c>
-      <c r="J78" s="17">
+      <c r="J78" s="136">
         <f>SUM(J76:J77)</f>
         <v/>
       </c>
-      <c r="K78" s="17">
+      <c r="K78" s="136">
         <f>SUM(K76:K77)</f>
         <v/>
       </c>
-      <c r="L78" s="17">
+      <c r="L78" s="136">
         <f>SUM(L76:L77)</f>
         <v/>
       </c>
-      <c r="M78" s="17">
+      <c r="M78" s="136">
         <f>SUM(M76:M77)</f>
         <v/>
       </c>
-      <c r="N78" s="17">
+      <c r="N78" s="136">
         <f>SUM(N76:N77)</f>
         <v/>
       </c>
@@ -5129,43 +5162,43 @@
       </c>
       <c r="C80" s="9" t="n"/>
       <c r="D80" s="27" t="n"/>
-      <c r="E80" s="66">
+      <c r="E80" s="142">
         <f>E78-E41</f>
         <v/>
       </c>
-      <c r="F80" s="66">
+      <c r="F80" s="142">
         <f>F78-F41</f>
         <v/>
       </c>
-      <c r="G80" s="66">
+      <c r="G80" s="142">
         <f>G78-G41</f>
         <v/>
       </c>
-      <c r="H80" s="66">
+      <c r="H80" s="142">
         <f>H78-H41</f>
         <v/>
       </c>
-      <c r="I80" s="66">
+      <c r="I80" s="142">
         <f>I78-I41</f>
         <v/>
       </c>
-      <c r="J80" s="66">
+      <c r="J80" s="142">
         <f>J78-J41</f>
         <v/>
       </c>
-      <c r="K80" s="66">
+      <c r="K80" s="142">
         <f>K78-K41</f>
         <v/>
       </c>
-      <c r="L80" s="66">
+      <c r="L80" s="142">
         <f>L78-L41</f>
         <v/>
       </c>
-      <c r="M80" s="66">
+      <c r="M80" s="142">
         <f>M78-M41</f>
         <v/>
       </c>
-      <c r="N80" s="66">
+      <c r="N80" s="142">
         <f>N78-N41</f>
         <v/>
       </c>
@@ -5221,38 +5254,38 @@
           <t>Accounts Receivable</t>
         </is>
       </c>
-      <c r="E85" s="33" t="n">
+      <c r="E85" s="143" t="n">
         <v>5100.35</v>
       </c>
-      <c r="F85" s="33" t="n">
+      <c r="F85" s="143" t="n">
         <v>5904.3</v>
       </c>
-      <c r="G85" s="33" t="n">
+      <c r="G85" s="143" t="n">
         <v>6567.25</v>
       </c>
-      <c r="H85" s="33" t="n">
+      <c r="H85" s="143" t="n">
         <v>7117.05</v>
       </c>
-      <c r="I85" s="33" t="n">
+      <c r="I85" s="143" t="n">
         <v>7538.6</v>
       </c>
-      <c r="J85" s="19">
+      <c r="J85" s="135">
         <f>J42</f>
         <v/>
       </c>
-      <c r="K85" s="19">
+      <c r="K85" s="135">
         <f>K42</f>
         <v/>
       </c>
-      <c r="L85" s="19">
+      <c r="L85" s="135">
         <f>L42</f>
         <v/>
       </c>
-      <c r="M85" s="19">
+      <c r="M85" s="135">
         <f>M42</f>
         <v/>
       </c>
-      <c r="N85" s="19">
+      <c r="N85" s="135">
         <f>N42</f>
         <v/>
       </c>
@@ -5263,38 +5296,38 @@
           <t>Inventory</t>
         </is>
       </c>
-      <c r="E86" s="33" t="n">
+      <c r="E86" s="143" t="n">
         <v>7804.6</v>
       </c>
-      <c r="F86" s="33" t="n">
+      <c r="F86" s="143" t="n">
         <v>9600.800000000001</v>
       </c>
-      <c r="G86" s="33" t="n">
+      <c r="G86" s="143" t="n">
         <v>9824.6</v>
       </c>
-      <c r="H86" s="33" t="n">
+      <c r="H86" s="143" t="n">
         <v>10530.8</v>
       </c>
-      <c r="I86" s="33" t="n">
+      <c r="I86" s="143" t="n">
         <v>11342</v>
       </c>
-      <c r="J86" s="19">
+      <c r="J86" s="135">
         <f>J43</f>
         <v/>
       </c>
-      <c r="K86" s="19">
+      <c r="K86" s="135">
         <f>K43</f>
         <v/>
       </c>
-      <c r="L86" s="19">
+      <c r="L86" s="135">
         <f>L43</f>
         <v/>
       </c>
-      <c r="M86" s="19">
+      <c r="M86" s="135">
         <f>M43</f>
         <v/>
       </c>
-      <c r="N86" s="19">
+      <c r="N86" s="135">
         <f>N43</f>
         <v/>
       </c>
@@ -5305,38 +5338,38 @@
           <t>Accounts Payable</t>
         </is>
       </c>
-      <c r="E87" s="33" t="n">
+      <c r="E87" s="143" t="n">
         <v>3902.3</v>
       </c>
-      <c r="F87" s="33" t="n">
+      <c r="F87" s="143" t="n">
         <v>4800.400000000001</v>
       </c>
-      <c r="G87" s="33" t="n">
+      <c r="G87" s="143" t="n">
         <v>4912.3</v>
       </c>
-      <c r="H87" s="33" t="n">
+      <c r="H87" s="143" t="n">
         <v>5265.400000000001</v>
       </c>
-      <c r="I87" s="33" t="n">
+      <c r="I87" s="143" t="n">
         <v>5671</v>
       </c>
-      <c r="J87" s="19">
+      <c r="J87" s="135">
         <f>J48</f>
         <v/>
       </c>
-      <c r="K87" s="19">
+      <c r="K87" s="135">
         <f>K48</f>
         <v/>
       </c>
-      <c r="L87" s="19">
+      <c r="L87" s="135">
         <f>L48</f>
         <v/>
       </c>
-      <c r="M87" s="19">
+      <c r="M87" s="135">
         <f>M48</f>
         <v/>
       </c>
-      <c r="N87" s="19">
+      <c r="N87" s="135">
         <f>N48</f>
         <v/>
       </c>
@@ -5349,43 +5382,43 @@
       </c>
       <c r="C88" s="5" t="n"/>
       <c r="D88" s="28" t="n"/>
-      <c r="E88" s="51">
+      <c r="E88" s="145">
         <f>E85+E86-E87</f>
         <v/>
       </c>
-      <c r="F88" s="51">
+      <c r="F88" s="145">
         <f>F85+F86-F87</f>
         <v/>
       </c>
-      <c r="G88" s="51">
+      <c r="G88" s="145">
         <f>G85+G86-G87</f>
         <v/>
       </c>
-      <c r="H88" s="51">
+      <c r="H88" s="145">
         <f>H85+H86-H87</f>
         <v/>
       </c>
-      <c r="I88" s="51">
+      <c r="I88" s="145">
         <f>I85+I86-I87</f>
         <v/>
       </c>
-      <c r="J88" s="51">
+      <c r="J88" s="145">
         <f>J85+J86-J87</f>
         <v/>
       </c>
-      <c r="K88" s="51">
+      <c r="K88" s="145">
         <f>K85+K86-K87</f>
         <v/>
       </c>
-      <c r="L88" s="51">
+      <c r="L88" s="145">
         <f>L85+L86-L87</f>
         <v/>
       </c>
-      <c r="M88" s="51">
+      <c r="M88" s="145">
         <f>M85+M86-M87</f>
         <v/>
       </c>
-      <c r="N88" s="51">
+      <c r="N88" s="145">
         <f>N85+N86-N87</f>
         <v/>
       </c>
@@ -5396,43 +5429,43 @@
           <t>Change in NWC</t>
         </is>
       </c>
-      <c r="E89" s="52">
+      <c r="E89" s="132">
         <f>E88-D88</f>
         <v/>
       </c>
-      <c r="F89" s="52">
+      <c r="F89" s="132">
         <f>F88-E88</f>
         <v/>
       </c>
-      <c r="G89" s="52">
+      <c r="G89" s="132">
         <f>G88-F88</f>
         <v/>
       </c>
-      <c r="H89" s="52">
+      <c r="H89" s="132">
         <f>H88-G88</f>
         <v/>
       </c>
-      <c r="I89" s="52">
+      <c r="I89" s="132">
         <f>I88-H88</f>
         <v/>
       </c>
-      <c r="J89" s="52">
+      <c r="J89" s="132">
         <f>J88-I88</f>
         <v/>
       </c>
-      <c r="K89" s="52">
+      <c r="K89" s="132">
         <f>K88-J88</f>
         <v/>
       </c>
-      <c r="L89" s="52">
+      <c r="L89" s="132">
         <f>L88-K88</f>
         <v/>
       </c>
-      <c r="M89" s="52">
+      <c r="M89" s="132">
         <f>M88-L88</f>
         <v/>
       </c>
-      <c r="N89" s="52">
+      <c r="N89" s="132">
         <f>N88-M88</f>
         <v/>
       </c>
@@ -5462,38 +5495,38 @@
           <t>PPE Opening</t>
         </is>
       </c>
-      <c r="E92" s="33" t="n">
+      <c r="E92" s="143" t="n">
         <v>50000</v>
       </c>
-      <c r="F92" s="33" t="n">
+      <c r="F92" s="143" t="n">
         <v>45500</v>
       </c>
-      <c r="G92" s="33" t="n">
+      <c r="G92" s="143" t="n">
         <v>42350</v>
       </c>
-      <c r="H92" s="33" t="n">
+      <c r="H92" s="143" t="n">
         <v>40145</v>
       </c>
-      <c r="I92" s="33" t="n">
+      <c r="I92" s="143" t="n">
         <v>38601.5</v>
       </c>
-      <c r="J92" s="19">
+      <c r="J92" s="135">
         <f>I95</f>
         <v/>
       </c>
-      <c r="K92" s="19">
+      <c r="K92" s="135">
         <f>J95</f>
         <v/>
       </c>
-      <c r="L92" s="19">
+      <c r="L92" s="135">
         <f>K95</f>
         <v/>
       </c>
-      <c r="M92" s="19">
+      <c r="M92" s="135">
         <f>L95</f>
         <v/>
       </c>
-      <c r="N92" s="19">
+      <c r="N92" s="135">
         <f>M95</f>
         <v/>
       </c>
@@ -5504,38 +5537,38 @@
           <t>Plus Capex</t>
         </is>
       </c>
-      <c r="E93" s="33" t="n">
+      <c r="E93" s="143" t="n">
         <v>15000</v>
       </c>
-      <c r="F93" s="33" t="n">
+      <c r="F93" s="143" t="n">
         <v>15000</v>
       </c>
-      <c r="G93" s="33" t="n">
+      <c r="G93" s="143" t="n">
         <v>15000</v>
       </c>
-      <c r="H93" s="33" t="n">
+      <c r="H93" s="143" t="n">
         <v>15000</v>
       </c>
-      <c r="I93" s="33" t="n">
+      <c r="I93" s="143" t="n">
         <v>15000</v>
       </c>
-      <c r="J93" s="19">
+      <c r="J93" s="135">
         <f>+J18</f>
         <v/>
       </c>
-      <c r="K93" s="19">
+      <c r="K93" s="135">
         <f>+K18</f>
         <v/>
       </c>
-      <c r="L93" s="19">
+      <c r="L93" s="135">
         <f>+L18</f>
         <v/>
       </c>
-      <c r="M93" s="19">
+      <c r="M93" s="135">
         <f>+M18</f>
         <v/>
       </c>
-      <c r="N93" s="19">
+      <c r="N93" s="135">
         <f>+N18</f>
         <v/>
       </c>
@@ -5546,38 +5579,38 @@
           <t>Less Depreciation</t>
         </is>
       </c>
-      <c r="E94" s="33" t="n">
+      <c r="E94" s="143" t="n">
         <v>19500</v>
       </c>
-      <c r="F94" s="33" t="n">
+      <c r="F94" s="143" t="n">
         <v>18150</v>
       </c>
-      <c r="G94" s="33" t="n">
+      <c r="G94" s="143" t="n">
         <v>17205</v>
       </c>
-      <c r="H94" s="33" t="n">
+      <c r="H94" s="143" t="n">
         <v>16543.5</v>
       </c>
-      <c r="I94" s="33" t="n">
+      <c r="I94" s="143" t="n">
         <v>16080.45</v>
       </c>
-      <c r="J94" s="55">
+      <c r="J94" s="135">
         <f>J92*J11</f>
         <v/>
       </c>
-      <c r="K94" s="55">
+      <c r="K94" s="135">
         <f>K92*K11</f>
         <v/>
       </c>
-      <c r="L94" s="55">
+      <c r="L94" s="135">
         <f>L92*L11</f>
         <v/>
       </c>
-      <c r="M94" s="55">
+      <c r="M94" s="135">
         <f>M92*M11</f>
         <v/>
       </c>
-      <c r="N94" s="55">
+      <c r="N94" s="135">
         <f>N92*N11</f>
         <v/>
       </c>
@@ -5590,43 +5623,43 @@
       </c>
       <c r="C95" s="5" t="n"/>
       <c r="D95" s="28" t="n"/>
-      <c r="E95" s="51">
+      <c r="E95" s="145">
         <f>E92+E93-E94</f>
         <v/>
       </c>
-      <c r="F95" s="51">
+      <c r="F95" s="145">
         <f>F92+F93-F94</f>
         <v/>
       </c>
-      <c r="G95" s="51">
+      <c r="G95" s="145">
         <f>G92+G93-G94</f>
         <v/>
       </c>
-      <c r="H95" s="51">
+      <c r="H95" s="145">
         <f>H92+H93-H94</f>
         <v/>
       </c>
-      <c r="I95" s="51">
+      <c r="I95" s="145">
         <f>I92+I93-I94</f>
         <v/>
       </c>
-      <c r="J95" s="51">
+      <c r="J95" s="145">
         <f>J92+J93-J94</f>
         <v/>
       </c>
-      <c r="K95" s="51">
+      <c r="K95" s="145">
         <f>K92+K93-K94</f>
         <v/>
       </c>
-      <c r="L95" s="51">
+      <c r="L95" s="145">
         <f>L92+L93-L94</f>
         <v/>
       </c>
-      <c r="M95" s="51">
+      <c r="M95" s="145">
         <f>M92+M93-M94</f>
         <v/>
       </c>
-      <c r="N95" s="51">
+      <c r="N95" s="145">
         <f>N92+N93-N94</f>
         <v/>
       </c>
@@ -5661,38 +5694,38 @@
           <t>Debt Opening</t>
         </is>
       </c>
-      <c r="E98" s="33" t="n">
+      <c r="E98" s="143" t="n">
         <v>50000</v>
       </c>
-      <c r="F98" s="33" t="n">
+      <c r="F98" s="143" t="n">
         <v>50000</v>
       </c>
-      <c r="G98" s="33" t="n">
+      <c r="G98" s="143" t="n">
         <v>50000</v>
       </c>
-      <c r="H98" s="33" t="n">
+      <c r="H98" s="143" t="n">
         <v>30000</v>
       </c>
-      <c r="I98" s="33" t="n">
+      <c r="I98" s="143" t="n">
         <v>30000</v>
       </c>
-      <c r="J98" s="19">
+      <c r="J98" s="135">
         <f>I100</f>
         <v/>
       </c>
-      <c r="K98" s="19">
+      <c r="K98" s="135">
         <f>J100</f>
         <v/>
       </c>
-      <c r="L98" s="19">
+      <c r="L98" s="135">
         <f>K100</f>
         <v/>
       </c>
-      <c r="M98" s="19">
+      <c r="M98" s="135">
         <f>L100</f>
         <v/>
       </c>
-      <c r="N98" s="19">
+      <c r="N98" s="135">
         <f>M100</f>
         <v/>
       </c>
@@ -5703,38 +5736,38 @@
           <t>Issuance (repayment)</t>
         </is>
       </c>
-      <c r="E99" s="33" t="n">
+      <c r="E99" s="143" t="n">
         <v>0</v>
       </c>
-      <c r="F99" s="33" t="n">
+      <c r="F99" s="143" t="n">
         <v>0</v>
       </c>
-      <c r="G99" s="33" t="n">
+      <c r="G99" s="143" t="n">
         <v>-20000</v>
       </c>
-      <c r="H99" s="33" t="n">
+      <c r="H99" s="143" t="n">
         <v>0</v>
       </c>
-      <c r="I99" s="33" t="n">
+      <c r="I99" s="143" t="n">
         <v>0</v>
       </c>
-      <c r="J99" s="52">
+      <c r="J99" s="132">
         <f>+J19</f>
         <v/>
       </c>
-      <c r="K99" s="52">
+      <c r="K99" s="132">
         <f>+K19</f>
         <v/>
       </c>
-      <c r="L99" s="52">
+      <c r="L99" s="132">
         <f>+L19</f>
         <v/>
       </c>
-      <c r="M99" s="52">
+      <c r="M99" s="132">
         <f>+M19</f>
         <v/>
       </c>
-      <c r="N99" s="52">
+      <c r="N99" s="132">
         <f>+N19</f>
         <v/>
       </c>
@@ -5747,43 +5780,43 @@
       </c>
       <c r="C100" s="5" t="n"/>
       <c r="D100" s="28" t="n"/>
-      <c r="E100" s="51">
+      <c r="E100" s="145">
         <f>SUM(E98:E99)</f>
         <v/>
       </c>
-      <c r="F100" s="51">
+      <c r="F100" s="145">
         <f>SUM(F98:F99)</f>
         <v/>
       </c>
-      <c r="G100" s="51">
+      <c r="G100" s="145">
         <f>SUM(G98:G99)</f>
         <v/>
       </c>
-      <c r="H100" s="51">
+      <c r="H100" s="145">
         <f>SUM(H98:H99)</f>
         <v/>
       </c>
-      <c r="I100" s="51">
+      <c r="I100" s="145">
         <f>SUM(I98:I99)</f>
         <v/>
       </c>
-      <c r="J100" s="51">
+      <c r="J100" s="145">
         <f>SUM(J98:J99)</f>
         <v/>
       </c>
-      <c r="K100" s="51">
+      <c r="K100" s="145">
         <f>SUM(K98:K99)</f>
         <v/>
       </c>
-      <c r="L100" s="51">
+      <c r="L100" s="145">
         <f>SUM(L98:L99)</f>
         <v/>
       </c>
-      <c r="M100" s="51">
+      <c r="M100" s="145">
         <f>SUM(M98:M99)</f>
         <v/>
       </c>
-      <c r="N100" s="51">
+      <c r="N100" s="145">
         <f>SUM(N98:N99)</f>
         <v/>
       </c>
@@ -5794,38 +5827,38 @@
           <t>Interest Expense</t>
         </is>
       </c>
-      <c r="E101" s="33" t="n">
+      <c r="E101" s="143" t="n">
         <v>2500</v>
       </c>
-      <c r="F101" s="33" t="n">
+      <c r="F101" s="143" t="n">
         <v>2500</v>
       </c>
-      <c r="G101" s="33" t="n">
+      <c r="G101" s="143" t="n">
         <v>1500</v>
       </c>
-      <c r="H101" s="33" t="n">
+      <c r="H101" s="143" t="n">
         <v>900</v>
       </c>
-      <c r="I101" s="33" t="n">
+      <c r="I101" s="143" t="n">
         <v>900</v>
       </c>
-      <c r="J101" s="19">
+      <c r="J101" s="135">
         <f>J98*J12</f>
         <v/>
       </c>
-      <c r="K101" s="19">
+      <c r="K101" s="135">
         <f>K98*K12</f>
         <v/>
       </c>
-      <c r="L101" s="19">
+      <c r="L101" s="135">
         <f>L98*L12</f>
         <v/>
       </c>
-      <c r="M101" s="19">
+      <c r="M101" s="135">
         <f>M98*M12</f>
         <v/>
       </c>
-      <c r="N101" s="19">
+      <c r="N101" s="135">
         <f>N98*N12</f>
         <v/>
       </c>
@@ -6140,11 +6173,16 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3.54296875" customWidth="1" min="1" max="1"/>
-    <col width="12.6328125" customWidth="1" min="2" max="2"/>
-    <col width="12.453125" customWidth="1" min="3" max="3"/>
-    <col width="11.36328125" customWidth="1" min="4" max="4"/>
-    <col width="11.54296875" customWidth="1" min="5" max="5"/>
-    <col width="12.54296875" customWidth="1" min="10" max="10"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
     <col width="9.08984375" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
@@ -6234,7 +6272,7 @@
         </is>
       </c>
       <c r="C5" s="100" t="n"/>
-      <c r="D5" s="134" t="n">
+      <c r="D5" s="146" t="n">
         <v>0.1877023903712333</v>
       </c>
       <c r="E5" s="100" t="n"/>
@@ -6257,7 +6295,7 @@
         </is>
       </c>
       <c r="C6" s="97" t="n"/>
-      <c r="D6" s="134" t="n">
+      <c r="D6" s="146" t="n">
         <v>0.096</v>
       </c>
       <c r="E6" s="97" t="n"/>
@@ -6280,7 +6318,7 @@
         </is>
       </c>
       <c r="C7" s="97" t="n"/>
-      <c r="D7" s="134" t="n">
+      <c r="D7" s="146" t="n">
         <v>0.03</v>
       </c>
       <c r="E7" s="97" t="n"/>
@@ -6303,7 +6341,7 @@
         </is>
       </c>
       <c r="C8" s="97" t="n"/>
-      <c r="D8" s="135" t="n">
+      <c r="D8" s="147" t="n">
         <v>22</v>
       </c>
       <c r="E8" s="97" t="n"/>
@@ -6326,7 +6364,7 @@
         </is>
       </c>
       <c r="C9" s="97" t="n"/>
-      <c r="D9" s="106" t="n">
+      <c r="D9" s="148" t="n">
         <v>45930</v>
       </c>
       <c r="E9" s="97" t="n"/>
@@ -6349,7 +6387,7 @@
         </is>
       </c>
       <c r="C10" s="97" t="n"/>
-      <c r="D10" s="106" t="n">
+      <c r="D10" s="148" t="n">
         <v>46295</v>
       </c>
       <c r="E10" s="97" t="n"/>
@@ -6372,7 +6410,7 @@
         </is>
       </c>
       <c r="C11" s="97" t="n"/>
-      <c r="D11" s="136" t="n">
+      <c r="D11" s="149" t="n">
         <v>1046.23</v>
       </c>
       <c r="E11" s="97" t="n"/>
@@ -6395,7 +6433,7 @@
         </is>
       </c>
       <c r="C12" s="97" t="n"/>
-      <c r="D12" s="137" t="n">
+      <c r="D12" s="150" t="n">
         <v>21597.635</v>
       </c>
       <c r="E12" s="97" t="n"/>
@@ -6418,7 +6456,7 @@
         </is>
       </c>
       <c r="C13" s="97" t="n"/>
-      <c r="D13" s="137" t="n">
+      <c r="D13" s="150" t="n">
         <v>5582389</v>
       </c>
       <c r="E13" s="97" t="n"/>
@@ -6441,7 +6479,7 @@
         </is>
       </c>
       <c r="C14" s="97" t="n"/>
-      <c r="D14" s="137" t="n">
+      <c r="D14" s="150" t="n">
         <v>304537</v>
       </c>
       <c r="E14" s="97" t="n"/>
@@ -6464,7 +6502,7 @@
         </is>
       </c>
       <c r="C15" s="97" t="n"/>
-      <c r="D15" s="138" t="n">
+      <c r="D15" s="151" t="n">
         <v>45051.43556656494</v>
       </c>
       <c r="E15" s="97" t="n"/>
@@ -6504,23 +6542,23 @@
           <t>Entry</t>
         </is>
       </c>
-      <c r="E17" s="112">
+      <c r="E17" s="152">
         <f>YEAR(E18)</f>
         <v/>
       </c>
-      <c r="F17" s="112">
+      <c r="F17" s="152">
         <f>YEAR(F18)</f>
         <v/>
       </c>
-      <c r="G17" s="112">
+      <c r="G17" s="152">
         <f>YEAR(G18)</f>
         <v/>
       </c>
-      <c r="H17" s="112">
+      <c r="H17" s="152">
         <f>YEAR(H18)</f>
         <v/>
       </c>
-      <c r="I17" s="112">
+      <c r="I17" s="152">
         <f>YEAR(I18)</f>
         <v/>
       </c>
@@ -6547,31 +6585,31 @@
         </is>
       </c>
       <c r="C18" s="97" t="n"/>
-      <c r="D18" s="113">
+      <c r="D18" s="153">
         <f>D9</f>
         <v/>
       </c>
-      <c r="E18" s="113">
+      <c r="E18" s="117">
         <f>DATE(YEAR($D$10)+E19,6,30)</f>
         <v/>
       </c>
-      <c r="F18" s="113">
+      <c r="F18" s="117">
         <f>DATE(YEAR($D$10)+F19,6,30)</f>
         <v/>
       </c>
-      <c r="G18" s="113">
+      <c r="G18" s="117">
         <f>DATE(YEAR($D$10)+G19,6,30)</f>
         <v/>
       </c>
-      <c r="H18" s="113">
+      <c r="H18" s="117">
         <f>DATE(YEAR($D$10)+H19,6,30)</f>
         <v/>
       </c>
-      <c r="I18" s="113">
+      <c r="I18" s="117">
         <f>DATE(YEAR($D$10)+I19,6,30)</f>
         <v/>
       </c>
-      <c r="J18" s="114">
+      <c r="J18" s="154">
         <f>I18</f>
         <v/>
       </c>
@@ -6597,22 +6635,22 @@
       </c>
       <c r="C19" s="115" t="n"/>
       <c r="D19" s="113" t="n"/>
-      <c r="E19" s="116" t="n">
+      <c r="E19" s="155" t="n">
         <v>0</v>
       </c>
-      <c r="F19" s="117">
+      <c r="F19" s="153">
         <f>E19+1</f>
         <v/>
       </c>
-      <c r="G19" s="117">
+      <c r="G19" s="153">
         <f>F19+1</f>
         <v/>
       </c>
-      <c r="H19" s="117">
+      <c r="H19" s="153">
         <f>G19+1</f>
         <v/>
       </c>
-      <c r="I19" s="117">
+      <c r="I19" s="153">
         <f>H19+1</f>
         <v/>
       </c>
@@ -6639,23 +6677,23 @@
       </c>
       <c r="C20" s="97" t="n"/>
       <c r="D20" s="97" t="n"/>
-      <c r="E20" s="139">
+      <c r="E20" s="153">
         <f>YEARFRAC(D18,E18)</f>
         <v/>
       </c>
-      <c r="F20" s="139">
+      <c r="F20" s="153">
         <f>YEARFRAC(E18,F18)</f>
         <v/>
       </c>
-      <c r="G20" s="139">
+      <c r="G20" s="153">
         <f>YEARFRAC(F18,G18)</f>
         <v/>
       </c>
-      <c r="H20" s="139">
+      <c r="H20" s="153">
         <f>YEARFRAC(G18,H18)</f>
         <v/>
       </c>
-      <c r="I20" s="139">
+      <c r="I20" s="153">
         <f>YEARFRAC(H18,I18)</f>
         <v/>
       </c>
@@ -6682,19 +6720,19 @@
       </c>
       <c r="C21" s="97" t="n"/>
       <c r="D21" s="97" t="n"/>
-      <c r="E21" s="138" t="n">
+      <c r="E21" s="151" t="n">
         <v>1052713.043327438</v>
       </c>
-      <c r="F21" s="138" t="n">
+      <c r="F21" s="151" t="n">
         <v>1157984.347660181</v>
       </c>
-      <c r="G21" s="138" t="n">
+      <c r="G21" s="151" t="n">
         <v>1262202.938949598</v>
       </c>
-      <c r="H21" s="138" t="n">
+      <c r="H21" s="151" t="n">
         <v>1363179.174065566</v>
       </c>
-      <c r="I21" s="138" t="n">
+      <c r="I21" s="151" t="n">
         <v>1458601.716250155</v>
       </c>
       <c r="J21" s="97" t="n"/>
@@ -6713,23 +6751,23 @@
       </c>
       <c r="C22" s="97" t="n"/>
       <c r="D22" s="97" t="n"/>
-      <c r="E22" s="118">
+      <c r="E22" s="156">
         <f>E21*$D$5</f>
         <v/>
       </c>
-      <c r="F22" s="118">
+      <c r="F22" s="156">
         <f>F21*$D$5</f>
         <v/>
       </c>
-      <c r="G22" s="118">
+      <c r="G22" s="156">
         <f>G21*$D$5</f>
         <v/>
       </c>
-      <c r="H22" s="118">
+      <c r="H22" s="156">
         <f>H21*$D$5</f>
         <v/>
       </c>
-      <c r="I22" s="118">
+      <c r="I22" s="156">
         <f>I21*$D$5</f>
         <v/>
       </c>
@@ -6749,19 +6787,19 @@
       </c>
       <c r="C23" s="97" t="n"/>
       <c r="D23" s="97" t="n"/>
-      <c r="E23" s="140" t="n">
+      <c r="E23" s="151" t="n">
         <v>17093.63982519042</v>
       </c>
-      <c r="F23" s="140" t="n">
+      <c r="F23" s="151" t="n">
         <v>18803.00380770947</v>
       </c>
-      <c r="G23" s="140" t="n">
+      <c r="G23" s="151" t="n">
         <v>20495.27415040332</v>
       </c>
-      <c r="H23" s="140" t="n">
+      <c r="H23" s="151" t="n">
         <v>22134.89608243559</v>
       </c>
-      <c r="I23" s="140" t="n">
+      <c r="I23" s="151" t="n">
         <v>23684.33880820608</v>
       </c>
       <c r="J23" s="97" t="n"/>
@@ -6780,23 +6818,23 @@
       </c>
       <c r="C24" s="97" t="n"/>
       <c r="D24" s="97" t="n"/>
-      <c r="E24" s="103">
+      <c r="E24" s="157">
         <f>$D$15</f>
         <v/>
       </c>
-      <c r="F24" s="103">
+      <c r="F24" s="157">
         <f>$D$15</f>
         <v/>
       </c>
-      <c r="G24" s="103">
+      <c r="G24" s="157">
         <f>$D$15</f>
         <v/>
       </c>
-      <c r="H24" s="103">
+      <c r="H24" s="157">
         <f>$D$15</f>
         <v/>
       </c>
-      <c r="I24" s="103">
+      <c r="I24" s="157">
         <f>$D$15</f>
         <v/>
       </c>
@@ -6816,19 +6854,19 @@
       </c>
       <c r="C25" s="97" t="n"/>
       <c r="D25" s="97" t="n"/>
-      <c r="E25" s="138" t="n">
+      <c r="E25" s="151" t="n">
         <v>71163.54596501018</v>
       </c>
-      <c r="F25" s="138" t="n">
+      <c r="F25" s="151" t="n">
         <v>56799.65459650115</v>
       </c>
-      <c r="G25" s="138" t="n">
+      <c r="G25" s="151" t="n">
         <v>56231.65805053606</v>
       </c>
-      <c r="H25" s="138" t="n">
+      <c r="H25" s="151" t="n">
         <v>54482.22868896381</v>
       </c>
-      <c r="I25" s="138" t="n">
+      <c r="I25" s="151" t="n">
         <v>51485.70611107082</v>
       </c>
       <c r="J25" s="97" t="n"/>
@@ -6847,23 +6885,23 @@
       </c>
       <c r="C26" s="97" t="n"/>
       <c r="D26" s="97" t="n"/>
-      <c r="E26" s="120">
+      <c r="E26" s="158">
         <f>E21-E22+E23-E24-E25</f>
         <v/>
       </c>
-      <c r="F26" s="120">
+      <c r="F26" s="158">
         <f>F21-F22+F23-F24-F25</f>
         <v/>
       </c>
-      <c r="G26" s="120">
+      <c r="G26" s="158">
         <f>G21-G22+G23-G24-G25</f>
         <v/>
       </c>
-      <c r="H26" s="120">
+      <c r="H26" s="158">
         <f>H21-H22+H23-H24-H25</f>
         <v/>
       </c>
-      <c r="I26" s="120">
+      <c r="I26" s="158">
         <f>I21-I22+I23-I24-I25</f>
         <v/>
       </c>
@@ -6882,7 +6920,7 @@
         </is>
       </c>
       <c r="C27" s="97" t="n"/>
-      <c r="D27" s="97">
+      <c r="D27" s="156">
         <f>-I35</f>
         <v/>
       </c>
@@ -6891,7 +6929,7 @@
       <c r="G27" s="97" t="n"/>
       <c r="H27" s="97" t="n"/>
       <c r="I27" s="97" t="n"/>
-      <c r="J27" s="97">
+      <c r="J27" s="156">
         <f>N20</f>
         <v/>
       </c>
@@ -6909,30 +6947,30 @@
         </is>
       </c>
       <c r="C28" s="97" t="n"/>
-      <c r="D28" s="120" t="n">
+      <c r="D28" s="158" t="n">
         <v>0</v>
       </c>
-      <c r="E28" s="120">
+      <c r="E28" s="158">
         <f>(E27+E26)*E20</f>
         <v/>
       </c>
-      <c r="F28" s="120">
+      <c r="F28" s="158">
         <f>(F27+F26)*F20</f>
         <v/>
       </c>
-      <c r="G28" s="120">
+      <c r="G28" s="158">
         <f>(G27+G26)*G20</f>
         <v/>
       </c>
-      <c r="H28" s="120">
+      <c r="H28" s="158">
         <f>(H27+H26)*H20</f>
         <v/>
       </c>
-      <c r="I28" s="120">
+      <c r="I28" s="158">
         <f>(I27+I26)*I20</f>
         <v/>
       </c>
-      <c r="J28" s="120">
+      <c r="J28" s="158">
         <f>J27+J26</f>
         <v/>
       </c>
@@ -6950,31 +6988,31 @@
         </is>
       </c>
       <c r="C29" s="97" t="n"/>
-      <c r="D29" s="97">
+      <c r="D29" s="156">
         <f>D27+D26</f>
         <v/>
       </c>
-      <c r="E29" s="97">
+      <c r="E29" s="156">
         <f>(E27+E26)*E20</f>
         <v/>
       </c>
-      <c r="F29" s="97">
+      <c r="F29" s="156">
         <f>(F27+F26)*F20</f>
         <v/>
       </c>
-      <c r="G29" s="97">
+      <c r="G29" s="156">
         <f>(G27+G26)*G20</f>
         <v/>
       </c>
-      <c r="H29" s="97">
+      <c r="H29" s="156">
         <f>(H27+H26)*H20</f>
         <v/>
       </c>
-      <c r="I29" s="97">
+      <c r="I29" s="156">
         <f>(I27+I26)*I20</f>
         <v/>
       </c>
-      <c r="J29" s="97">
+      <c r="J29" s="156">
         <f>J27</f>
         <v/>
       </c>
@@ -7034,7 +7072,7 @@
         </is>
       </c>
       <c r="C32" s="97" t="n"/>
-      <c r="D32" s="97">
+      <c r="D32" s="156">
         <f>XNPV(D6,D28:J28,D18:J18)</f>
         <v/>
       </c>
@@ -7045,7 +7083,7 @@
         </is>
       </c>
       <c r="H32" s="97" t="n"/>
-      <c r="I32" s="97">
+      <c r="I32" s="156">
         <f>D12*D11</f>
         <v/>
       </c>
@@ -7070,7 +7108,7 @@
         </is>
       </c>
       <c r="C33" s="97" t="n"/>
-      <c r="D33" s="97">
+      <c r="D33" s="156">
         <f>+D14</f>
         <v/>
       </c>
@@ -7081,7 +7119,7 @@
         </is>
       </c>
       <c r="H33" s="97" t="n"/>
-      <c r="I33" s="97">
+      <c r="I33" s="156">
         <f>D13</f>
         <v/>
       </c>
@@ -7106,7 +7144,7 @@
         </is>
       </c>
       <c r="C34" s="97" t="n"/>
-      <c r="D34" s="97">
+      <c r="D34" s="156">
         <f>+D13</f>
         <v/>
       </c>
@@ -7117,7 +7155,7 @@
         </is>
       </c>
       <c r="H34" s="97" t="n"/>
-      <c r="I34" s="97">
+      <c r="I34" s="156">
         <f>+D14</f>
         <v/>
       </c>
@@ -7135,7 +7173,7 @@
         </is>
       </c>
       <c r="C35" s="97" t="n"/>
-      <c r="D35" s="120">
+      <c r="D35" s="158">
         <f>D32+D33-D34</f>
         <v/>
       </c>
@@ -7146,7 +7184,7 @@
         </is>
       </c>
       <c r="H35" s="97" t="n"/>
-      <c r="I35" s="120">
+      <c r="I35" s="158">
         <f>I32+I33-I34</f>
         <v/>
       </c>
@@ -7168,7 +7206,7 @@
       <c r="E36" s="97" t="n"/>
       <c r="G36" s="97" t="n"/>
       <c r="H36" s="97" t="n"/>
-      <c r="I36" s="141" t="n"/>
+      <c r="I36" s="159" t="n"/>
       <c r="J36" s="97" t="n"/>
       <c r="L36" s="97" t="inlineStr">
         <is>
@@ -7176,7 +7214,7 @@
         </is>
       </c>
       <c r="M36" s="97" t="n"/>
-      <c r="N36" s="141">
+      <c r="N36" s="159">
         <f>I37</f>
         <v/>
       </c>
@@ -7190,7 +7228,7 @@
         </is>
       </c>
       <c r="C37" s="97" t="n"/>
-      <c r="D37" s="141">
+      <c r="D37" s="156">
         <f>D35/D12</f>
         <v/>
       </c>
@@ -7201,7 +7239,7 @@
         </is>
       </c>
       <c r="H37" s="97" t="n"/>
-      <c r="I37" s="141">
+      <c r="I37" s="156">
         <f>D11</f>
         <v/>
       </c>
@@ -7212,7 +7250,7 @@
         </is>
       </c>
       <c r="M37" s="97" t="n"/>
-      <c r="N37" s="141">
+      <c r="N37" s="159">
         <f>D37-I37</f>
         <v/>
       </c>
@@ -7234,7 +7272,7 @@
         </is>
       </c>
       <c r="M38" s="97" t="n"/>
-      <c r="N38" s="141">
+      <c r="N38" s="159">
         <f>SUM(N36:N37)</f>
         <v/>
       </c>

--- a/FICO/output/FICO_Completed_Model.xlsx
+++ b/FICO/output/FICO_Completed_Model.xlsx
@@ -59,14 +59,12 @@
     <definedName name="DCF_WACC">'DCF Model'!$D$6</definedName>
     <definedName name="DCF_PerpetualGrowth">'DCF Model'!$D$7</definedName>
     <definedName name="DCF_ExitMultiple">'DCF Model'!$D$8</definedName>
+    <definedName name="DCF_TransactionDate">'DCF Model'!$D$9</definedName>
+    <definedName name="DCF_FiscalYearEnd">'DCF Model'!$D$10</definedName>
     <definedName name="DCF_SharePrice">'DCF Model'!$D$11</definedName>
     <definedName name="DCF_Shares">'DCF Model'!$D$12</definedName>
     <definedName name="DCF_Debt">'DCF Model'!$D$13</definedName>
     <definedName name="DCF_Cash">'DCF Model'!$D$14</definedName>
-    <definedName name="DCF_Capex">'DCF Model'!$D$15</definedName>
-    <definedName name="DCF_EBIT_Start">'DCF Model'!$E$21</definedName>
-    <definedName name="DCF_DA_Start">'DCF Model'!$E$23</definedName>
-    <definedName name="DCF_DeltaNWC_Start">'DCF Model'!$E$25</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Cover Page'!$A$1:$P$27</definedName>
     <definedName name="Forecast" localSheetId="1">#REF!</definedName>
     <definedName name="Step_1" localSheetId="1">#REF!</definedName>
@@ -84,7 +82,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="10">
+  <numFmts count="14">
     <numFmt numFmtId="164" formatCode="_-* #,##0_-;\(#,##0\)_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="0.0000_ ;\-0.0000\ "/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
@@ -95,8 +93,12 @@
     <numFmt numFmtId="171" formatCode="0.0\x"/>
     <numFmt numFmtId="172" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="173" formatCode="_-* #,##0.00_-;\(#,##0.00\)_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="174" formatCode="#,##0.0;(#,##0.0);-"/>
+    <numFmt numFmtId="175" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="176" formatCode="$#,##0.00"/>
+    <numFmt numFmtId="177" formatCode="0.0"/>
   </numFmts>
-  <fonts count="39">
+  <fonts count="41">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -349,10 +351,19 @@
     </font>
     <font>
       <name val="Calibri"/>
+      <color rgb="00000000"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <color rgb="000000FF"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -387,6 +398,11 @@
       <patternFill patternType="solid">
         <fgColor theme="8"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -455,7 +471,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="142">
+  <cellXfs count="168">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="1"/>
@@ -633,21 +649,25 @@
     <xf numFmtId="167" fontId="32" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="164" fontId="38" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="31" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="30" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="31" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="39" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="14" fontId="35" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="14" fontId="36" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="30" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="35" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="37" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="35" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="172" fontId="35" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="30" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="32" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="38" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="38" fillId="7" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="173" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="30" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -665,28 +685,52 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="166" fontId="38" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="2"/>
-    <xf numFmtId="164" fontId="38" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="164" fontId="38" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="164" fontId="38" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="174" fontId="40" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="174" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="174" fontId="13" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="174" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="40" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="2"/>
+    <xf numFmtId="174" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="166" fontId="40" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="174" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="174" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="174" fontId="6" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="174" fontId="40" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="174" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="174" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="174" fontId="6" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="174" fontId="6" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="174" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="174" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="174" fontId="40" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="38" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="174" fontId="9" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="166" fontId="40" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="171" fontId="38" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="177" fontId="40" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="172" fontId="38" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="175" fontId="32" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="176" fontId="40" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="38" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="40" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="38" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="172" fontId="35" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="38" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="174" fontId="38" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="31" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="174" fontId="35" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="175" fontId="35" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="174" fontId="36" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="174" fontId="30" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="174" fontId="37" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="174" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="174" fontId="30" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="174" fontId="38" fillId="7" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="173" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="9">
@@ -2233,7 +2277,7 @@
       <c r="B21" s="85" t="n"/>
       <c r="C21" s="85" t="inlineStr">
         <is>
-          <t>Open this file in Excel to recalculate formulas from injected SEC inputs. CSV sources live in FICO/output/*.csv — do not edit formula cells.</t>
+          <t>Open in Excel to recalculate. DCF EBIT/D&amp;A/CapEx/ΔNWC/TV are formulas linked to the 3-statement sheet (not hardcoded CSV). XNPV uses dates without year-fraction double-counting.</t>
         </is>
       </c>
       <c r="D21" s="85" t="n"/>
@@ -2435,10 +2479,18 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.109375" defaultRowHeight="15.6" outlineLevelRow="1"/>
   <cols>
     <col width="1.88671875" customWidth="1" style="19" min="1" max="1"/>
-    <col width="15.5546875" customWidth="1" style="19" min="2" max="3"/>
-    <col width="15.5546875" customWidth="1" style="47" min="4" max="4"/>
-    <col width="11.5546875" customWidth="1" style="19" min="5" max="9"/>
-    <col width="12.5546875" customWidth="1" style="19" min="10" max="14"/>
+    <col width="42" customWidth="1" style="19" min="2" max="3"/>
+    <col width="16" customWidth="1" style="47" min="4" max="4"/>
+    <col width="16" customWidth="1" style="19" min="5" max="9"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" style="19" min="10" max="14"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
     <col width="9.109375" customWidth="1" style="19" min="15" max="16384"/>
   </cols>
   <sheetData>
@@ -2479,42 +2531,42 @@
       </c>
       <c r="C2" s="62" t="n"/>
       <c r="D2" s="63" t="n"/>
-      <c r="E2" s="129" t="n">
+      <c r="E2" s="133" t="n">
         <v>2021</v>
       </c>
-      <c r="F2" s="83">
+      <c r="F2" s="134">
         <f>+E2+1</f>
         <v/>
       </c>
-      <c r="G2" s="83">
+      <c r="G2" s="134">
         <f>+F2+1</f>
         <v/>
       </c>
-      <c r="H2" s="83">
+      <c r="H2" s="134">
         <f>+G2+1</f>
         <v/>
       </c>
-      <c r="I2" s="83">
+      <c r="I2" s="134">
         <f>+H2+1</f>
         <v/>
       </c>
-      <c r="J2" s="64">
+      <c r="J2" s="135">
         <f>+I2+1</f>
         <v/>
       </c>
-      <c r="K2" s="64">
+      <c r="K2" s="135">
         <f>+J2+1</f>
         <v/>
       </c>
-      <c r="L2" s="64">
+      <c r="L2" s="135">
         <f>+K2+1</f>
         <v/>
       </c>
-      <c r="M2" s="64">
+      <c r="M2" s="135">
         <f>+L2+1</f>
         <v/>
       </c>
-      <c r="N2" s="64">
+      <c r="N2" s="135">
         <f>+M2+1</f>
         <v/>
       </c>
@@ -2525,47 +2577,48 @@
           <t>Balance Sheet Check</t>
         </is>
       </c>
-      <c r="E3" s="45">
+      <c r="E3" s="136">
         <f>IFERROR(IF(ABS(E57)&gt;1,"ERROR","OK"),"OK")</f>
         <v/>
       </c>
-      <c r="F3" s="45">
+      <c r="F3" s="136">
         <f>IFERROR(IF(ABS(F57)&gt;1,"ERROR","OK"),"OK")</f>
         <v/>
       </c>
-      <c r="G3" s="45">
+      <c r="G3" s="136">
         <f>IFERROR(IF(ABS(G57)&gt;1,"ERROR","OK"),"OK")</f>
         <v/>
       </c>
-      <c r="H3" s="45">
+      <c r="H3" s="136">
         <f>IFERROR(IF(ABS(H57)&gt;1,"ERROR","OK"),"OK")</f>
         <v/>
       </c>
-      <c r="I3" s="45">
+      <c r="I3" s="136">
         <f>IFERROR(IF(ABS(I57)&gt;1,"ERROR","OK"),"OK")</f>
         <v/>
       </c>
-      <c r="J3" s="45">
+      <c r="J3" s="136">
         <f>IFERROR(IF(ABS(J57)&gt;1,"ERROR","OK"),"OK")</f>
         <v/>
       </c>
-      <c r="K3" s="45">
+      <c r="K3" s="136">
         <f>IFERROR(IF(ABS(K57)&gt;1,"ERROR","OK"),"OK")</f>
         <v/>
       </c>
-      <c r="L3" s="45">
+      <c r="L3" s="136">
         <f>IFERROR(IF(ABS(L57)&gt;1,"ERROR","OK"),"OK")</f>
         <v/>
       </c>
-      <c r="M3" s="45">
+      <c r="M3" s="136">
         <f>IFERROR(IF(ABS(M57)&gt;1,"ERROR","OK"),"OK")</f>
         <v/>
       </c>
-      <c r="N3" s="45">
+      <c r="N3" s="136">
         <f>IFERROR(IF(ABS(N57)&gt;1,"ERROR","OK"),"OK")</f>
         <v/>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="18" customHeight="1">
       <c r="B5" s="65" t="inlineStr">
         <is>
@@ -2618,19 +2671,19 @@
         <f>I24/H24-1</f>
         <v/>
       </c>
-      <c r="J7" s="130" t="n">
+      <c r="J7" s="137" t="n">
         <v>0.143234</v>
       </c>
-      <c r="K7" s="130" t="n">
+      <c r="K7" s="137" t="n">
         <v>0.1</v>
       </c>
-      <c r="L7" s="130" t="n">
+      <c r="L7" s="137" t="n">
         <v>0.09</v>
       </c>
-      <c r="M7" s="130" t="n">
+      <c r="M7" s="137" t="n">
         <v>0.08</v>
       </c>
-      <c r="N7" s="130" t="n">
+      <c r="N7" s="137" t="n">
         <v>0.07000000000000001</v>
       </c>
     </row>
@@ -2662,19 +2715,19 @@
         <f>I25/I24</f>
         <v/>
       </c>
-      <c r="J8" s="130" t="n">
+      <c r="J8" s="137" t="n">
         <v>0.1776721622567833</v>
       </c>
-      <c r="K8" s="130" t="n">
+      <c r="K8" s="137" t="n">
         <v>0.1776721622567833</v>
       </c>
-      <c r="L8" s="130" t="n">
+      <c r="L8" s="137" t="n">
         <v>0.1776721622567833</v>
       </c>
-      <c r="M8" s="130" t="n">
+      <c r="M8" s="137" t="n">
         <v>0.1776721622567833</v>
       </c>
-      <c r="N8" s="130" t="n">
+      <c r="N8" s="137" t="n">
         <v>0.1776721622567833</v>
       </c>
     </row>
@@ -2686,39 +2739,39 @@
       </c>
       <c r="C9" s="19" t="n"/>
       <c r="D9" s="47" t="n"/>
-      <c r="E9" s="52">
+      <c r="E9" s="138">
         <f>E28</f>
         <v/>
       </c>
-      <c r="F9" s="52">
+      <c r="F9" s="138">
         <f>F28</f>
         <v/>
       </c>
-      <c r="G9" s="52">
+      <c r="G9" s="138">
         <f>G28</f>
         <v/>
       </c>
-      <c r="H9" s="52">
+      <c r="H9" s="138">
         <f>H28</f>
         <v/>
       </c>
-      <c r="I9" s="52">
+      <c r="I9" s="138">
         <f>I28</f>
         <v/>
       </c>
-      <c r="J9" s="131" t="n">
+      <c r="J9" s="133" t="n">
         <v>586511.1</v>
       </c>
-      <c r="K9" s="131" t="n">
+      <c r="K9" s="133" t="n">
         <v>645162.2</v>
       </c>
-      <c r="L9" s="131" t="n">
+      <c r="L9" s="133" t="n">
         <v>703226.8</v>
       </c>
-      <c r="M9" s="131" t="n">
+      <c r="M9" s="133" t="n">
         <v>759484.9</v>
       </c>
-      <c r="N9" s="131" t="n">
+      <c r="N9" s="133" t="n">
         <v>812648.8</v>
       </c>
     </row>
@@ -2730,39 +2783,39 @@
       </c>
       <c r="C10" s="19" t="n"/>
       <c r="D10" s="47" t="n"/>
-      <c r="E10" s="52">
+      <c r="E10" s="138">
         <f>E29</f>
         <v/>
       </c>
-      <c r="F10" s="52">
+      <c r="F10" s="138">
         <f>F29</f>
         <v/>
       </c>
-      <c r="G10" s="52">
+      <c r="G10" s="138">
         <f>G29</f>
         <v/>
       </c>
-      <c r="H10" s="52">
+      <c r="H10" s="138">
         <f>H29</f>
         <v/>
       </c>
-      <c r="I10" s="52">
+      <c r="I10" s="138">
         <f>I29</f>
         <v/>
       </c>
-      <c r="J10" s="131" t="n">
+      <c r="J10" s="133" t="n">
         <v>215324.7</v>
       </c>
-      <c r="K10" s="131" t="n">
+      <c r="K10" s="133" t="n">
         <v>236857.2</v>
       </c>
-      <c r="L10" s="131" t="n">
+      <c r="L10" s="133" t="n">
         <v>258174.3</v>
       </c>
-      <c r="M10" s="131" t="n">
+      <c r="M10" s="133" t="n">
         <v>278828.3</v>
       </c>
-      <c r="N10" s="131" t="n">
+      <c r="N10" s="133" t="n">
         <v>298346.2</v>
       </c>
     </row>
@@ -2794,19 +2847,19 @@
         <f>I30/I92</f>
         <v/>
       </c>
-      <c r="J11" s="130" t="n">
+      <c r="J11" s="137" t="n">
         <v>0.2208143192592265</v>
       </c>
-      <c r="K11" s="130" t="n">
+      <c r="K11" s="137" t="n">
         <v>0.2208143192592265</v>
       </c>
-      <c r="L11" s="130" t="n">
+      <c r="L11" s="137" t="n">
         <v>0.2208143192592265</v>
       </c>
-      <c r="M11" s="130" t="n">
+      <c r="M11" s="137" t="n">
         <v>0.2208143192592265</v>
       </c>
-      <c r="N11" s="130" t="n">
+      <c r="N11" s="137" t="n">
         <v>0.2208143192592265</v>
       </c>
     </row>
@@ -2838,19 +2891,19 @@
         <f>I101/I98</f>
         <v/>
       </c>
-      <c r="J12" s="130" t="n">
+      <c r="J12" s="137" t="n">
         <v>0.04373707943636971</v>
       </c>
-      <c r="K12" s="130" t="n">
+      <c r="K12" s="137" t="n">
         <v>0.04373707943636971</v>
       </c>
-      <c r="L12" s="130" t="n">
+      <c r="L12" s="137" t="n">
         <v>0.04373707943636971</v>
       </c>
-      <c r="M12" s="130" t="n">
+      <c r="M12" s="137" t="n">
         <v>0.04373707943636971</v>
       </c>
-      <c r="N12" s="130" t="n">
+      <c r="N12" s="137" t="n">
         <v>0.04373707943636971</v>
       </c>
     </row>
@@ -2882,19 +2935,19 @@
         <f>I35/I33</f>
         <v/>
       </c>
-      <c r="J13" s="130" t="n">
+      <c r="J13" s="137" t="n">
         <v>0.1877023903712333</v>
       </c>
-      <c r="K13" s="130" t="n">
+      <c r="K13" s="137" t="n">
         <v>0.1877023903712333</v>
       </c>
-      <c r="L13" s="130" t="n">
+      <c r="L13" s="137" t="n">
         <v>0.1877023903712333</v>
       </c>
-      <c r="M13" s="130" t="n">
+      <c r="M13" s="137" t="n">
         <v>0.1877023903712333</v>
       </c>
-      <c r="N13" s="130" t="n">
+      <c r="N13" s="137" t="n">
         <v>0.1877023903712333</v>
       </c>
     </row>
@@ -2924,39 +2977,39 @@
         </is>
       </c>
       <c r="D15" s="32" t="n"/>
-      <c r="E15" s="52">
+      <c r="E15" s="138">
         <f>E42/E24*365</f>
         <v/>
       </c>
-      <c r="F15" s="52">
+      <c r="F15" s="138">
         <f>F42/F24*365</f>
         <v/>
       </c>
-      <c r="G15" s="52">
+      <c r="G15" s="138">
         <f>G42/G24*365</f>
         <v/>
       </c>
-      <c r="H15" s="52">
+      <c r="H15" s="138">
         <f>H42/H24*365</f>
         <v/>
       </c>
-      <c r="I15" s="52">
+      <c r="I15" s="138">
         <f>I42/I24*365</f>
         <v/>
       </c>
-      <c r="J15" s="131" t="n">
+      <c r="J15" s="133" t="n">
         <v>97</v>
       </c>
-      <c r="K15" s="131" t="n">
+      <c r="K15" s="133" t="n">
         <v>97</v>
       </c>
-      <c r="L15" s="131" t="n">
+      <c r="L15" s="133" t="n">
         <v>97</v>
       </c>
-      <c r="M15" s="131" t="n">
+      <c r="M15" s="133" t="n">
         <v>97</v>
       </c>
-      <c r="N15" s="131" t="n">
+      <c r="N15" s="133" t="n">
         <v>97</v>
       </c>
     </row>
@@ -2967,39 +3020,39 @@
         </is>
       </c>
       <c r="D16" s="32" t="n"/>
-      <c r="E16" s="52">
+      <c r="E16" s="138">
         <f>E43/E25*365</f>
         <v/>
       </c>
-      <c r="F16" s="52">
+      <c r="F16" s="138">
         <f>F43/F25*365</f>
         <v/>
       </c>
-      <c r="G16" s="52">
+      <c r="G16" s="138">
         <f>G43/G25*365</f>
         <v/>
       </c>
-      <c r="H16" s="52">
+      <c r="H16" s="138">
         <f>H43/H25*365</f>
         <v/>
       </c>
-      <c r="I16" s="52">
+      <c r="I16" s="138">
         <f>I43/I25*365</f>
         <v/>
       </c>
-      <c r="J16" s="131" t="n">
+      <c r="J16" s="133" t="n">
         <v>0</v>
       </c>
-      <c r="K16" s="131" t="n">
+      <c r="K16" s="133" t="n">
         <v>0</v>
       </c>
-      <c r="L16" s="131" t="n">
+      <c r="L16" s="133" t="n">
         <v>0</v>
       </c>
-      <c r="M16" s="131" t="n">
+      <c r="M16" s="133" t="n">
         <v>0</v>
       </c>
-      <c r="N16" s="131" t="n">
+      <c r="N16" s="133" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3010,39 +3063,39 @@
         </is>
       </c>
       <c r="D17" s="32" t="n"/>
-      <c r="E17" s="52">
+      <c r="E17" s="138">
         <f>E48/E25*365</f>
         <v/>
       </c>
-      <c r="F17" s="52">
+      <c r="F17" s="138">
         <f>F48/F25*365</f>
         <v/>
       </c>
-      <c r="G17" s="52">
+      <c r="G17" s="138">
         <f>G48/G25*365</f>
         <v/>
       </c>
-      <c r="H17" s="52">
+      <c r="H17" s="138">
         <f>H48/H25*365</f>
         <v/>
       </c>
-      <c r="I17" s="52">
+      <c r="I17" s="138">
         <f>I48/I25*365</f>
         <v/>
       </c>
-      <c r="J17" s="131" t="n">
+      <c r="J17" s="133" t="n">
         <v>33</v>
       </c>
-      <c r="K17" s="131" t="n">
+      <c r="K17" s="133" t="n">
         <v>33</v>
       </c>
-      <c r="L17" s="131" t="n">
+      <c r="L17" s="133" t="n">
         <v>33</v>
       </c>
-      <c r="M17" s="131" t="n">
+      <c r="M17" s="133" t="n">
         <v>33</v>
       </c>
-      <c r="N17" s="131" t="n">
+      <c r="N17" s="133" t="n">
         <v>33</v>
       </c>
     </row>
@@ -3052,39 +3105,39 @@
           <t>Capital Expenditures ($000's)</t>
         </is>
       </c>
-      <c r="E18" s="52">
+      <c r="E18" s="138">
         <f>E68</f>
         <v/>
       </c>
-      <c r="F18" s="52">
+      <c r="F18" s="138">
         <f>F68</f>
         <v/>
       </c>
-      <c r="G18" s="52">
+      <c r="G18" s="138">
         <f>G68</f>
         <v/>
       </c>
-      <c r="H18" s="52">
+      <c r="H18" s="138">
         <f>H68</f>
         <v/>
       </c>
-      <c r="I18" s="52">
+      <c r="I18" s="138">
         <f>I68</f>
         <v/>
       </c>
-      <c r="J18" s="131" t="n">
+      <c r="J18" s="133" t="n">
         <v>45051.4</v>
       </c>
-      <c r="K18" s="131" t="n">
+      <c r="K18" s="133" t="n">
         <v>49556.6</v>
       </c>
-      <c r="L18" s="131" t="n">
+      <c r="L18" s="133" t="n">
         <v>54016.7</v>
       </c>
-      <c r="M18" s="131" t="n">
+      <c r="M18" s="133" t="n">
         <v>58338</v>
       </c>
-      <c r="N18" s="131" t="n">
+      <c r="N18" s="133" t="n">
         <v>62421.6</v>
       </c>
     </row>
@@ -3094,39 +3147,39 @@
           <t>Debt Issuance (Repayment) ($000's)</t>
         </is>
       </c>
-      <c r="E19" s="52">
+      <c r="E19" s="138">
         <f>E99</f>
         <v/>
       </c>
-      <c r="F19" s="52">
+      <c r="F19" s="138">
         <f>F99</f>
         <v/>
       </c>
-      <c r="G19" s="52">
+      <c r="G19" s="138">
         <f>G99</f>
         <v/>
       </c>
-      <c r="H19" s="52">
+      <c r="H19" s="138">
         <f>H99</f>
         <v/>
       </c>
-      <c r="I19" s="52">
+      <c r="I19" s="138">
         <f>I99</f>
         <v/>
       </c>
-      <c r="J19" s="131" t="n">
+      <c r="J19" s="139" t="n">
         <v>0</v>
       </c>
-      <c r="K19" s="131" t="n">
+      <c r="K19" s="139" t="n">
         <v>0</v>
       </c>
-      <c r="L19" s="131" t="n">
+      <c r="L19" s="139" t="n">
         <v>0</v>
       </c>
-      <c r="M19" s="131" t="n">
+      <c r="M19" s="139" t="n">
         <v>0</v>
       </c>
-      <c r="N19" s="131" t="n">
+      <c r="N19" s="139" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3136,39 +3189,39 @@
           <t>Equity Issued (Repaid) ($000's)</t>
         </is>
       </c>
-      <c r="E20" s="52">
+      <c r="E20" s="138">
         <f>E73</f>
         <v/>
       </c>
-      <c r="F20" s="52">
+      <c r="F20" s="138">
         <f>F73</f>
         <v/>
       </c>
-      <c r="G20" s="52">
+      <c r="G20" s="138">
         <f>G73</f>
         <v/>
       </c>
-      <c r="H20" s="52">
+      <c r="H20" s="138">
         <f>H73</f>
         <v/>
       </c>
-      <c r="I20" s="52">
+      <c r="I20" s="138">
         <f>I73</f>
         <v/>
       </c>
-      <c r="J20" s="131" t="n">
+      <c r="J20" s="139" t="n">
         <v>0</v>
       </c>
-      <c r="K20" s="131" t="n">
+      <c r="K20" s="139" t="n">
         <v>0</v>
       </c>
-      <c r="L20" s="131" t="n">
+      <c r="L20" s="139" t="n">
         <v>0</v>
       </c>
-      <c r="M20" s="131" t="n">
+      <c r="M20" s="139" t="n">
         <v>0</v>
       </c>
-      <c r="N20" s="131" t="n">
+      <c r="N20" s="139" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3223,38 +3276,38 @@
       </c>
       <c r="C24" s="18" t="n"/>
       <c r="D24" s="46" t="n"/>
-      <c r="E24" s="131" t="n">
+      <c r="E24" s="133" t="n">
         <v>1316536</v>
       </c>
-      <c r="F24" s="131" t="n">
+      <c r="F24" s="133" t="n">
         <v>1377270</v>
       </c>
-      <c r="G24" s="131" t="n">
+      <c r="G24" s="133" t="n">
         <v>1513557</v>
       </c>
-      <c r="H24" s="131" t="n">
+      <c r="H24" s="133" t="n">
         <v>1717526</v>
       </c>
-      <c r="I24" s="131" t="n">
+      <c r="I24" s="133" t="n">
         <v>1990869</v>
       </c>
-      <c r="J24" s="18">
+      <c r="J24" s="140">
         <f>I24*(1+J7)</f>
         <v/>
       </c>
-      <c r="K24" s="18">
+      <c r="K24" s="140">
         <f>J24*(1+K7)</f>
         <v/>
       </c>
-      <c r="L24" s="18">
+      <c r="L24" s="140">
         <f>K24*(1+L7)</f>
         <v/>
       </c>
-      <c r="M24" s="18">
+      <c r="M24" s="140">
         <f>L24*(1+M7)</f>
         <v/>
       </c>
-      <c r="N24" s="18">
+      <c r="N24" s="140">
         <f>M24*(1+N7)</f>
         <v/>
       </c>
@@ -3267,38 +3320,38 @@
       </c>
       <c r="C25" s="19" t="n"/>
       <c r="D25" s="47" t="n"/>
-      <c r="E25" s="131" t="n">
+      <c r="E25" s="133" t="n">
         <v>332462</v>
       </c>
-      <c r="F25" s="131" t="n">
+      <c r="F25" s="133" t="n">
         <v>302174</v>
       </c>
-      <c r="G25" s="131" t="n">
+      <c r="G25" s="133" t="n">
         <v>311053</v>
       </c>
-      <c r="H25" s="131" t="n">
+      <c r="H25" s="133" t="n">
         <v>348206</v>
       </c>
-      <c r="I25" s="131" t="n">
+      <c r="I25" s="133" t="n">
         <v>353722</v>
       </c>
-      <c r="J25" s="55">
+      <c r="J25" s="141">
         <f>J24*J8</f>
         <v/>
       </c>
-      <c r="K25" s="55">
+      <c r="K25" s="141">
         <f>K24*K8</f>
         <v/>
       </c>
-      <c r="L25" s="55">
+      <c r="L25" s="141">
         <f>L24*L8</f>
         <v/>
       </c>
-      <c r="M25" s="55">
+      <c r="M25" s="141">
         <f>M24*M8</f>
         <v/>
       </c>
-      <c r="N25" s="55">
+      <c r="N25" s="141">
         <f>N24*N8</f>
         <v/>
       </c>
@@ -3311,43 +3364,43 @@
       </c>
       <c r="C26" s="4" t="n"/>
       <c r="D26" s="22" t="n"/>
-      <c r="E26" s="17">
+      <c r="E26" s="142">
         <f>E24-E25</f>
         <v/>
       </c>
-      <c r="F26" s="17">
+      <c r="F26" s="142">
         <f>F24-F25</f>
         <v/>
       </c>
-      <c r="G26" s="17">
+      <c r="G26" s="142">
         <f>G24-G25</f>
         <v/>
       </c>
-      <c r="H26" s="17">
+      <c r="H26" s="142">
         <f>H24-H25</f>
         <v/>
       </c>
-      <c r="I26" s="17">
+      <c r="I26" s="142">
         <f>I24-I25</f>
         <v/>
       </c>
-      <c r="J26" s="17">
+      <c r="J26" s="142">
         <f>J24-J25</f>
         <v/>
       </c>
-      <c r="K26" s="17">
+      <c r="K26" s="142">
         <f>K24-K25</f>
         <v/>
       </c>
-      <c r="L26" s="17">
+      <c r="L26" s="142">
         <f>L24-L25</f>
         <v/>
       </c>
-      <c r="M26" s="17">
+      <c r="M26" s="142">
         <f>M24-M25</f>
         <v/>
       </c>
-      <c r="N26" s="17">
+      <c r="N26" s="142">
         <f>N24-N25</f>
         <v/>
       </c>
@@ -3377,38 +3430,38 @@
           <t>Salaries and Benefits</t>
         </is>
       </c>
-      <c r="E28" s="131" t="n">
+      <c r="E28" s="133" t="n">
         <v>396281</v>
       </c>
-      <c r="F28" s="131" t="n">
+      <c r="F28" s="133" t="n">
         <v>383863</v>
       </c>
-      <c r="G28" s="131" t="n">
+      <c r="G28" s="133" t="n">
         <v>400565</v>
       </c>
-      <c r="H28" s="131" t="n">
+      <c r="H28" s="133" t="n">
         <v>462834</v>
       </c>
-      <c r="I28" s="131" t="n">
+      <c r="I28" s="133" t="n">
         <v>513028</v>
       </c>
-      <c r="J28" s="19">
+      <c r="J28" s="141">
         <f>J9</f>
         <v/>
       </c>
-      <c r="K28" s="19">
+      <c r="K28" s="141">
         <f>K9</f>
         <v/>
       </c>
-      <c r="L28" s="19">
+      <c r="L28" s="141">
         <f>L9</f>
         <v/>
       </c>
-      <c r="M28" s="19">
+      <c r="M28" s="141">
         <f>M9</f>
         <v/>
       </c>
-      <c r="N28" s="19">
+      <c r="N28" s="141">
         <f>N9</f>
         <v/>
       </c>
@@ -3419,38 +3472,38 @@
           <t>Rent and Overhead</t>
         </is>
       </c>
-      <c r="E29" s="131" t="n">
+      <c r="E29" s="133" t="n">
         <v>171231</v>
       </c>
-      <c r="F29" s="131" t="n">
+      <c r="F29" s="133" t="n">
         <v>146758</v>
       </c>
-      <c r="G29" s="131" t="n">
+      <c r="G29" s="133" t="n">
         <v>159950</v>
       </c>
-      <c r="H29" s="131" t="n">
+      <c r="H29" s="133" t="n">
         <v>171940</v>
       </c>
-      <c r="I29" s="131" t="n">
+      <c r="I29" s="133" t="n">
         <v>188347</v>
       </c>
-      <c r="J29" s="19">
+      <c r="J29" s="141">
         <f>J10</f>
         <v/>
       </c>
-      <c r="K29" s="19">
+      <c r="K29" s="141">
         <f>K10</f>
         <v/>
       </c>
-      <c r="L29" s="19">
+      <c r="L29" s="141">
         <f>L10</f>
         <v/>
       </c>
-      <c r="M29" s="19">
+      <c r="M29" s="141">
         <f>M10</f>
         <v/>
       </c>
-      <c r="N29" s="19">
+      <c r="N29" s="141">
         <f>N10</f>
         <v/>
       </c>
@@ -3461,38 +3514,38 @@
           <t>Depreciation &amp; Amortization</t>
         </is>
       </c>
-      <c r="E30" s="131" t="n">
+      <c r="E30" s="133" t="n">
         <v>25592</v>
       </c>
-      <c r="F30" s="131" t="n">
+      <c r="F30" s="133" t="n">
         <v>20465</v>
       </c>
-      <c r="G30" s="131" t="n">
+      <c r="G30" s="133" t="n">
         <v>14638</v>
       </c>
-      <c r="H30" s="131" t="n">
+      <c r="H30" s="133" t="n">
         <v>13827</v>
       </c>
-      <c r="I30" s="131" t="n">
+      <c r="I30" s="133" t="n">
         <v>14952</v>
       </c>
-      <c r="J30" s="19">
+      <c r="J30" s="141">
         <f>J94</f>
         <v/>
       </c>
-      <c r="K30" s="19">
+      <c r="K30" s="141">
         <f>K94</f>
         <v/>
       </c>
-      <c r="L30" s="19">
+      <c r="L30" s="141">
         <f>L94</f>
         <v/>
       </c>
-      <c r="M30" s="19">
+      <c r="M30" s="141">
         <f>M94</f>
         <v/>
       </c>
-      <c r="N30" s="19">
+      <c r="N30" s="141">
         <f>N94</f>
         <v/>
       </c>
@@ -3505,38 +3558,38 @@
       </c>
       <c r="C31" s="2" t="n"/>
       <c r="D31" s="24" t="n"/>
-      <c r="E31" s="132" t="n">
+      <c r="E31" s="143" t="n">
         <v>40092</v>
       </c>
-      <c r="F31" s="132" t="n">
+      <c r="F31" s="143" t="n">
         <v>68967</v>
       </c>
-      <c r="G31" s="132" t="n">
+      <c r="G31" s="143" t="n">
         <v>95546</v>
       </c>
-      <c r="H31" s="132" t="n">
+      <c r="H31" s="143" t="n">
         <v>105638</v>
       </c>
-      <c r="I31" s="132" t="n">
+      <c r="I31" s="143" t="n">
         <v>133647</v>
       </c>
-      <c r="J31" s="16">
+      <c r="J31" s="144">
         <f>J101</f>
         <v/>
       </c>
-      <c r="K31" s="16">
+      <c r="K31" s="144">
         <f>K101</f>
         <v/>
       </c>
-      <c r="L31" s="16">
+      <c r="L31" s="144">
         <f>L101</f>
         <v/>
       </c>
-      <c r="M31" s="16">
+      <c r="M31" s="144">
         <f>M101</f>
         <v/>
       </c>
-      <c r="N31" s="16">
+      <c r="N31" s="144">
         <f>N101</f>
         <v/>
       </c>
@@ -3549,43 +3602,43 @@
       </c>
       <c r="C32" s="19" t="n"/>
       <c r="D32" s="47" t="n"/>
-      <c r="E32" s="49">
+      <c r="E32" s="145">
         <f>SUM(E28:E31)</f>
         <v/>
       </c>
-      <c r="F32" s="49">
+      <c r="F32" s="145">
         <f>SUM(F28:F31)</f>
         <v/>
       </c>
-      <c r="G32" s="49">
+      <c r="G32" s="145">
         <f>SUM(G28:G31)</f>
         <v/>
       </c>
-      <c r="H32" s="49">
+      <c r="H32" s="145">
         <f>SUM(H28:H31)</f>
         <v/>
       </c>
-      <c r="I32" s="49">
+      <c r="I32" s="145">
         <f>SUM(I28:I31)</f>
         <v/>
       </c>
-      <c r="J32" s="49">
+      <c r="J32" s="145">
         <f>SUM(J28:J31)</f>
         <v/>
       </c>
-      <c r="K32" s="49">
+      <c r="K32" s="145">
         <f>SUM(K28:K31)</f>
         <v/>
       </c>
-      <c r="L32" s="49">
+      <c r="L32" s="145">
         <f>SUM(L28:L31)</f>
         <v/>
       </c>
-      <c r="M32" s="49">
+      <c r="M32" s="145">
         <f>SUM(M28:M31)</f>
         <v/>
       </c>
-      <c r="N32" s="49">
+      <c r="N32" s="145">
         <f>SUM(N28:N31)</f>
         <v/>
       </c>
@@ -3598,43 +3651,43 @@
       </c>
       <c r="C33" s="4" t="n"/>
       <c r="D33" s="22" t="n"/>
-      <c r="E33" s="17">
+      <c r="E33" s="142">
         <f>E26-E32</f>
         <v/>
       </c>
-      <c r="F33" s="17">
+      <c r="F33" s="142">
         <f>F26-F32</f>
         <v/>
       </c>
-      <c r="G33" s="17">
+      <c r="G33" s="142">
         <f>G26-G32</f>
         <v/>
       </c>
-      <c r="H33" s="17">
+      <c r="H33" s="142">
         <f>H26-H32</f>
         <v/>
       </c>
-      <c r="I33" s="17">
+      <c r="I33" s="142">
         <f>I26-I32</f>
         <v/>
       </c>
-      <c r="J33" s="17">
+      <c r="J33" s="142">
         <f>J26-J32</f>
         <v/>
       </c>
-      <c r="K33" s="17">
+      <c r="K33" s="142">
         <f>K26-K32</f>
         <v/>
       </c>
-      <c r="L33" s="17">
+      <c r="L33" s="142">
         <f>L26-L32</f>
         <v/>
       </c>
-      <c r="M33" s="17">
+      <c r="M33" s="142">
         <f>M26-M32</f>
         <v/>
       </c>
-      <c r="N33" s="17">
+      <c r="N33" s="142">
         <f>N26-N32</f>
         <v/>
       </c>
@@ -3662,38 +3715,38 @@
       </c>
       <c r="C35" s="19" t="n"/>
       <c r="D35" s="47" t="n"/>
-      <c r="E35" s="131" t="n">
+      <c r="E35" s="133" t="n">
         <v>81058</v>
       </c>
-      <c r="F35" s="131" t="n">
+      <c r="F35" s="133" t="n">
         <v>97768</v>
       </c>
-      <c r="G35" s="131" t="n">
+      <c r="G35" s="133" t="n">
         <v>124249</v>
       </c>
-      <c r="H35" s="131" t="n">
+      <c r="H35" s="133" t="n">
         <v>129214</v>
       </c>
-      <c r="I35" s="131" t="n">
+      <c r="I35" s="133" t="n">
         <v>150649</v>
       </c>
-      <c r="J35" s="55">
+      <c r="J35" s="141">
         <f>J33*J13</f>
         <v/>
       </c>
-      <c r="K35" s="55">
+      <c r="K35" s="141">
         <f>K33*K13</f>
         <v/>
       </c>
-      <c r="L35" s="55">
+      <c r="L35" s="141">
         <f>L33*L13</f>
         <v/>
       </c>
-      <c r="M35" s="55">
+      <c r="M35" s="141">
         <f>M33*M13</f>
         <v/>
       </c>
-      <c r="N35" s="55">
+      <c r="N35" s="141">
         <f>N33*N13</f>
         <v/>
       </c>
@@ -3706,43 +3759,43 @@
       </c>
       <c r="C36" s="39" t="n"/>
       <c r="D36" s="40" t="n"/>
-      <c r="E36" s="41">
+      <c r="E36" s="146">
         <f>E33-E35</f>
         <v/>
       </c>
-      <c r="F36" s="41">
+      <c r="F36" s="146">
         <f>F33-F35</f>
         <v/>
       </c>
-      <c r="G36" s="41">
+      <c r="G36" s="146">
         <f>G33-G35</f>
         <v/>
       </c>
-      <c r="H36" s="41">
+      <c r="H36" s="146">
         <f>H33-H35</f>
         <v/>
       </c>
-      <c r="I36" s="41">
+      <c r="I36" s="146">
         <f>I33-I35</f>
         <v/>
       </c>
-      <c r="J36" s="41">
+      <c r="J36" s="146">
         <f>J33-J35</f>
         <v/>
       </c>
-      <c r="K36" s="41">
+      <c r="K36" s="146">
         <f>K33-K35</f>
         <v/>
       </c>
-      <c r="L36" s="41">
+      <c r="L36" s="146">
         <f>L33-L35</f>
         <v/>
       </c>
-      <c r="M36" s="41">
+      <c r="M36" s="146">
         <f>M33-M35</f>
         <v/>
       </c>
-      <c r="N36" s="41">
+      <c r="N36" s="146">
         <f>N33-N35</f>
         <v/>
       </c>
@@ -3803,38 +3856,38 @@
           <t>Cash</t>
         </is>
       </c>
-      <c r="E41" s="131" t="n">
+      <c r="E41" s="133" t="n">
         <v>195354</v>
       </c>
-      <c r="F41" s="131" t="n">
+      <c r="F41" s="133" t="n">
         <v>133202</v>
       </c>
-      <c r="G41" s="131" t="n">
+      <c r="G41" s="133" t="n">
         <v>136778</v>
       </c>
-      <c r="H41" s="131" t="n">
+      <c r="H41" s="133" t="n">
         <v>150667</v>
       </c>
-      <c r="I41" s="131" t="n">
+      <c r="I41" s="133" t="n">
         <v>134136</v>
       </c>
-      <c r="J41" s="19">
+      <c r="J41" s="141">
         <f>J78</f>
         <v/>
       </c>
-      <c r="K41" s="19">
+      <c r="K41" s="141">
         <f>K78</f>
         <v/>
       </c>
-      <c r="L41" s="19">
+      <c r="L41" s="141">
         <f>L78</f>
         <v/>
       </c>
-      <c r="M41" s="19">
+      <c r="M41" s="141">
         <f>M78</f>
         <v/>
       </c>
-      <c r="N41" s="19">
+      <c r="N41" s="141">
         <f>N78</f>
         <v/>
       </c>
@@ -3845,38 +3898,38 @@
           <t>Accounts Receivable</t>
         </is>
       </c>
-      <c r="E42" s="131" t="n">
+      <c r="E42" s="133" t="n">
         <v>312107</v>
       </c>
-      <c r="F42" s="131" t="n">
+      <c r="F42" s="133" t="n">
         <v>322410</v>
       </c>
-      <c r="G42" s="131" t="n">
+      <c r="G42" s="133" t="n">
         <v>387947</v>
       </c>
-      <c r="H42" s="131" t="n">
+      <c r="H42" s="133" t="n">
         <v>426642</v>
       </c>
-      <c r="I42" s="131" t="n">
+      <c r="I42" s="133" t="n">
         <v>529148</v>
       </c>
-      <c r="J42" s="42">
+      <c r="J42" s="141">
         <f>J24*J15/365</f>
         <v/>
       </c>
-      <c r="K42" s="42">
+      <c r="K42" s="141">
         <f>K24*K15/365</f>
         <v/>
       </c>
-      <c r="L42" s="42">
+      <c r="L42" s="141">
         <f>L24*L15/365</f>
         <v/>
       </c>
-      <c r="M42" s="42">
+      <c r="M42" s="141">
         <f>M24*M15/365</f>
         <v/>
       </c>
-      <c r="N42" s="42">
+      <c r="N42" s="141">
         <f>N24*N15/365</f>
         <v/>
       </c>
@@ -3887,38 +3940,38 @@
           <t>Inventory</t>
         </is>
       </c>
-      <c r="E43" s="131" t="n">
+      <c r="E43" s="133" t="n">
         <v>0</v>
       </c>
-      <c r="F43" s="131" t="n">
+      <c r="F43" s="133" t="n">
         <v>0</v>
       </c>
-      <c r="G43" s="131" t="n">
+      <c r="G43" s="133" t="n">
         <v>0</v>
       </c>
-      <c r="H43" s="131" t="n">
+      <c r="H43" s="133" t="n">
         <v>0</v>
       </c>
-      <c r="I43" s="131" t="n">
+      <c r="I43" s="133" t="n">
         <v>0</v>
       </c>
-      <c r="J43" s="19">
+      <c r="J43" s="141">
         <f>J25*J16/365</f>
         <v/>
       </c>
-      <c r="K43" s="19">
+      <c r="K43" s="141">
         <f>K25*K16/365</f>
         <v/>
       </c>
-      <c r="L43" s="19">
+      <c r="L43" s="141">
         <f>L25*L16/365</f>
         <v/>
       </c>
-      <c r="M43" s="19">
+      <c r="M43" s="141">
         <f>M25*M16/365</f>
         <v/>
       </c>
-      <c r="N43" s="19">
+      <c r="N43" s="141">
         <f>N25*N16/365</f>
         <v/>
       </c>
@@ -3929,38 +3982,38 @@
           <t>Property &amp; Equipment</t>
         </is>
       </c>
-      <c r="E44" s="131" t="n">
+      <c r="E44" s="133" t="n">
         <v>27913</v>
       </c>
-      <c r="F44" s="131" t="n">
+      <c r="F44" s="133" t="n">
         <v>17580</v>
       </c>
-      <c r="G44" s="131" t="n">
+      <c r="G44" s="133" t="n">
         <v>10966</v>
       </c>
-      <c r="H44" s="131" t="n">
+      <c r="H44" s="133" t="n">
         <v>38465</v>
       </c>
-      <c r="I44" s="131" t="n">
+      <c r="I44" s="133" t="n">
         <v>67713</v>
       </c>
-      <c r="J44" s="19">
+      <c r="J44" s="141">
         <f>J95</f>
         <v/>
       </c>
-      <c r="K44" s="19">
+      <c r="K44" s="141">
         <f>K95</f>
         <v/>
       </c>
-      <c r="L44" s="19">
+      <c r="L44" s="141">
         <f>L95</f>
         <v/>
       </c>
-      <c r="M44" s="19">
+      <c r="M44" s="141">
         <f>M95</f>
         <v/>
       </c>
-      <c r="N44" s="19">
+      <c r="N44" s="141">
         <f>N95</f>
         <v/>
       </c>
@@ -3973,43 +4026,43 @@
       </c>
       <c r="C45" s="39" t="n"/>
       <c r="D45" s="40" t="n"/>
-      <c r="E45" s="41">
+      <c r="E45" s="146">
         <f>SUM(E41:E44)</f>
         <v/>
       </c>
-      <c r="F45" s="41">
+      <c r="F45" s="146">
         <f>SUM(F41:F44)</f>
         <v/>
       </c>
-      <c r="G45" s="41">
+      <c r="G45" s="146">
         <f>SUM(G41:G44)</f>
         <v/>
       </c>
-      <c r="H45" s="41">
+      <c r="H45" s="146">
         <f>SUM(H41:H44)</f>
         <v/>
       </c>
-      <c r="I45" s="41">
+      <c r="I45" s="146">
         <f>SUM(I41:I44)</f>
         <v/>
       </c>
-      <c r="J45" s="41">
+      <c r="J45" s="146">
         <f>SUM(J41:J44)</f>
         <v/>
       </c>
-      <c r="K45" s="41">
+      <c r="K45" s="146">
         <f>SUM(K41:K44)</f>
         <v/>
       </c>
-      <c r="L45" s="41">
+      <c r="L45" s="146">
         <f>SUM(L41:L44)</f>
         <v/>
       </c>
-      <c r="M45" s="41">
+      <c r="M45" s="146">
         <f>SUM(M41:M44)</f>
         <v/>
       </c>
-      <c r="N45" s="41">
+      <c r="N45" s="146">
         <f>SUM(N41:N44)</f>
         <v/>
       </c>
@@ -4047,38 +4100,38 @@
           <t>Accounts Payable</t>
         </is>
       </c>
-      <c r="E48" s="131" t="n">
+      <c r="E48" s="133" t="n">
         <v>20749</v>
       </c>
-      <c r="F48" s="131" t="n">
+      <c r="F48" s="133" t="n">
         <v>17273</v>
       </c>
-      <c r="G48" s="131" t="n">
+      <c r="G48" s="133" t="n">
         <v>19009</v>
       </c>
-      <c r="H48" s="131" t="n">
+      <c r="H48" s="133" t="n">
         <v>22473</v>
       </c>
-      <c r="I48" s="131" t="n">
+      <c r="I48" s="133" t="n">
         <v>32315</v>
       </c>
-      <c r="J48" s="19">
+      <c r="J48" s="141">
         <f>J25*J17/365</f>
         <v/>
       </c>
-      <c r="K48" s="19">
+      <c r="K48" s="141">
         <f>K25*K17/365</f>
         <v/>
       </c>
-      <c r="L48" s="19">
+      <c r="L48" s="141">
         <f>L25*L17/365</f>
         <v/>
       </c>
-      <c r="M48" s="19">
+      <c r="M48" s="141">
         <f>M25*M17/365</f>
         <v/>
       </c>
-      <c r="N48" s="19">
+      <c r="N48" s="141">
         <f>N25*N17/365</f>
         <v/>
       </c>
@@ -4089,38 +4142,38 @@
           <t>Debt</t>
         </is>
       </c>
-      <c r="E49" s="131" t="n">
+      <c r="E49" s="133" t="n">
         <v>1259018</v>
       </c>
-      <c r="F49" s="131" t="n">
+      <c r="F49" s="133" t="n">
         <v>1853669</v>
       </c>
-      <c r="G49" s="131" t="n">
+      <c r="G49" s="133" t="n">
         <v>1861658</v>
       </c>
-      <c r="H49" s="131" t="n">
+      <c r="H49" s="133" t="n">
         <v>2209021</v>
       </c>
-      <c r="I49" s="131" t="n">
+      <c r="I49" s="133" t="n">
         <v>3055691</v>
       </c>
-      <c r="J49" s="19">
+      <c r="J49" s="141">
         <f>J100</f>
         <v/>
       </c>
-      <c r="K49" s="19">
+      <c r="K49" s="141">
         <f>K100</f>
         <v/>
       </c>
-      <c r="L49" s="19">
+      <c r="L49" s="141">
         <f>L100</f>
         <v/>
       </c>
-      <c r="M49" s="19">
+      <c r="M49" s="141">
         <f>M100</f>
         <v/>
       </c>
-      <c r="N49" s="19">
+      <c r="N49" s="141">
         <f>N100</f>
         <v/>
       </c>
@@ -4133,43 +4186,43 @@
       </c>
       <c r="C50" s="4" t="n"/>
       <c r="D50" s="22" t="n"/>
-      <c r="E50" s="17">
+      <c r="E50" s="142">
         <f>SUM(E48:E49)</f>
         <v/>
       </c>
-      <c r="F50" s="17">
+      <c r="F50" s="142">
         <f>SUM(F48:F49)</f>
         <v/>
       </c>
-      <c r="G50" s="17">
+      <c r="G50" s="142">
         <f>SUM(G48:G49)</f>
         <v/>
       </c>
-      <c r="H50" s="17">
+      <c r="H50" s="142">
         <f>SUM(H48:H49)</f>
         <v/>
       </c>
-      <c r="I50" s="17">
+      <c r="I50" s="142">
         <f>SUM(I48:I49)</f>
         <v/>
       </c>
-      <c r="J50" s="17">
+      <c r="J50" s="142">
         <f>SUM(J48:J49)</f>
         <v/>
       </c>
-      <c r="K50" s="17">
+      <c r="K50" s="142">
         <f>SUM(K48:K49)</f>
         <v/>
       </c>
-      <c r="L50" s="17">
+      <c r="L50" s="142">
         <f>SUM(L48:L49)</f>
         <v/>
       </c>
-      <c r="M50" s="17">
+      <c r="M50" s="142">
         <f>SUM(M48:M49)</f>
         <v/>
       </c>
-      <c r="N50" s="17">
+      <c r="N50" s="142">
         <f>SUM(N48:N49)</f>
         <v/>
       </c>
@@ -4192,38 +4245,38 @@
           <t>Equity Capital</t>
         </is>
       </c>
-      <c r="E52" s="131" t="n">
+      <c r="E52" s="133" t="n">
         <v>-744393</v>
       </c>
-      <c r="F52" s="131" t="n">
+      <c r="F52" s="133" t="n">
         <v>-1397750</v>
       </c>
-      <c r="G52" s="131" t="n">
+      <c r="G52" s="133" t="n">
         <v>-1344976</v>
       </c>
-      <c r="H52" s="131" t="n">
+      <c r="H52" s="133" t="n">
         <v>-1615720</v>
       </c>
-      <c r="I52" s="131" t="n">
+      <c r="I52" s="133" t="n">
         <v>-2357009</v>
       </c>
-      <c r="J52" s="19">
+      <c r="J52" s="141">
         <f>I52+J20</f>
         <v/>
       </c>
-      <c r="K52" s="19">
+      <c r="K52" s="141">
         <f>J52+K20</f>
         <v/>
       </c>
-      <c r="L52" s="19">
+      <c r="L52" s="141">
         <f>K52+L20</f>
         <v/>
       </c>
-      <c r="M52" s="19">
+      <c r="M52" s="141">
         <f>L52+M20</f>
         <v/>
       </c>
-      <c r="N52" s="19">
+      <c r="N52" s="141">
         <f>M52+N20</f>
         <v/>
       </c>
@@ -4234,38 +4287,38 @@
           <t>Retained Earnings</t>
         </is>
       </c>
-      <c r="E53" s="131" t="n">
+      <c r="E53" s="133" t="n">
         <v>0</v>
       </c>
-      <c r="F53" s="131" t="n">
+      <c r="F53" s="133" t="n">
         <v>0</v>
       </c>
-      <c r="G53" s="131" t="n">
+      <c r="G53" s="133" t="n">
         <v>0</v>
       </c>
-      <c r="H53" s="131" t="n">
+      <c r="H53" s="133" t="n">
         <v>0</v>
       </c>
-      <c r="I53" s="131" t="n">
+      <c r="I53" s="133" t="n">
         <v>0</v>
       </c>
-      <c r="J53" s="19">
+      <c r="J53" s="141">
         <f>I53+J36</f>
         <v/>
       </c>
-      <c r="K53" s="19">
+      <c r="K53" s="141">
         <f>J53+K36</f>
         <v/>
       </c>
-      <c r="L53" s="19">
+      <c r="L53" s="141">
         <f>K53+L36</f>
         <v/>
       </c>
-      <c r="M53" s="19">
+      <c r="M53" s="141">
         <f>L53+M36</f>
         <v/>
       </c>
-      <c r="N53" s="19">
+      <c r="N53" s="141">
         <f>M53+N36</f>
         <v/>
       </c>
@@ -4278,43 +4331,43 @@
       </c>
       <c r="C54" s="8" t="n"/>
       <c r="D54" s="26" t="n"/>
-      <c r="E54" s="50">
+      <c r="E54" s="147">
         <f>SUM(E52:E53)</f>
         <v/>
       </c>
-      <c r="F54" s="50">
+      <c r="F54" s="147">
         <f>SUM(F52:F53)</f>
         <v/>
       </c>
-      <c r="G54" s="50">
+      <c r="G54" s="147">
         <f>SUM(G52:G53)</f>
         <v/>
       </c>
-      <c r="H54" s="50">
+      <c r="H54" s="147">
         <f>SUM(H52:H53)</f>
         <v/>
       </c>
-      <c r="I54" s="50">
+      <c r="I54" s="147">
         <f>SUM(I52:I53)</f>
         <v/>
       </c>
-      <c r="J54" s="50">
+      <c r="J54" s="147">
         <f>SUM(J52:J53)</f>
         <v/>
       </c>
-      <c r="K54" s="50">
+      <c r="K54" s="147">
         <f>SUM(K52:K53)</f>
         <v/>
       </c>
-      <c r="L54" s="50">
+      <c r="L54" s="147">
         <f>SUM(L52:L53)</f>
         <v/>
       </c>
-      <c r="M54" s="50">
+      <c r="M54" s="147">
         <f>SUM(M52:M53)</f>
         <v/>
       </c>
-      <c r="N54" s="50">
+      <c r="N54" s="147">
         <f>SUM(N52:N53)</f>
         <v/>
       </c>
@@ -4327,43 +4380,43 @@
       </c>
       <c r="C55" s="39" t="n"/>
       <c r="D55" s="40" t="n"/>
-      <c r="E55" s="41">
+      <c r="E55" s="146">
         <f>E50+E54</f>
         <v/>
       </c>
-      <c r="F55" s="41">
+      <c r="F55" s="146">
         <f>F50+F54</f>
         <v/>
       </c>
-      <c r="G55" s="41">
+      <c r="G55" s="146">
         <f>G50+G54</f>
         <v/>
       </c>
-      <c r="H55" s="41">
+      <c r="H55" s="146">
         <f>H50+H54</f>
         <v/>
       </c>
-      <c r="I55" s="41">
+      <c r="I55" s="146">
         <f>I50+I54</f>
         <v/>
       </c>
-      <c r="J55" s="41">
+      <c r="J55" s="146">
         <f>J50+J54</f>
         <v/>
       </c>
-      <c r="K55" s="41">
+      <c r="K55" s="146">
         <f>K50+K54</f>
         <v/>
       </c>
-      <c r="L55" s="41">
+      <c r="L55" s="146">
         <f>L50+L54</f>
         <v/>
       </c>
-      <c r="M55" s="41">
+      <c r="M55" s="146">
         <f>M50+M54</f>
         <v/>
       </c>
-      <c r="N55" s="41">
+      <c r="N55" s="146">
         <f>N50+N54</f>
         <v/>
       </c>
@@ -4388,43 +4441,43 @@
       </c>
       <c r="C57" s="9" t="n"/>
       <c r="D57" s="27" t="n"/>
-      <c r="E57" s="66">
+      <c r="E57" s="148">
         <f>E55-E45</f>
         <v/>
       </c>
-      <c r="F57" s="66">
+      <c r="F57" s="148">
         <f>F55-F45</f>
         <v/>
       </c>
-      <c r="G57" s="66">
+      <c r="G57" s="148">
         <f>G55-G45</f>
         <v/>
       </c>
-      <c r="H57" s="66">
+      <c r="H57" s="148">
         <f>H55-H45</f>
         <v/>
       </c>
-      <c r="I57" s="66">
+      <c r="I57" s="148">
         <f>I55-I45</f>
         <v/>
       </c>
-      <c r="J57" s="66">
+      <c r="J57" s="148">
         <f>J55-J45</f>
         <v/>
       </c>
-      <c r="K57" s="66">
+      <c r="K57" s="148">
         <f>K55-K45</f>
         <v/>
       </c>
-      <c r="L57" s="66">
+      <c r="L57" s="148">
         <f>L55-L45</f>
         <v/>
       </c>
-      <c r="M57" s="66">
+      <c r="M57" s="148">
         <f>M55-M45</f>
         <v/>
       </c>
-      <c r="N57" s="66">
+      <c r="N57" s="148">
         <f>N55-N45</f>
         <v/>
       </c>
@@ -4488,43 +4541,43 @@
           <t>Net Earnings</t>
         </is>
       </c>
-      <c r="E62" s="19">
+      <c r="E62" s="141">
         <f>E36</f>
         <v/>
       </c>
-      <c r="F62" s="19">
+      <c r="F62" s="141">
         <f>F36</f>
         <v/>
       </c>
-      <c r="G62" s="19">
+      <c r="G62" s="141">
         <f>G36</f>
         <v/>
       </c>
-      <c r="H62" s="19">
+      <c r="H62" s="141">
         <f>H36</f>
         <v/>
       </c>
-      <c r="I62" s="19">
+      <c r="I62" s="141">
         <f>I36</f>
         <v/>
       </c>
-      <c r="J62" s="19">
+      <c r="J62" s="141">
         <f>J36</f>
         <v/>
       </c>
-      <c r="K62" s="19">
+      <c r="K62" s="141">
         <f>K36</f>
         <v/>
       </c>
-      <c r="L62" s="19">
+      <c r="L62" s="141">
         <f>L36</f>
         <v/>
       </c>
-      <c r="M62" s="19">
+      <c r="M62" s="141">
         <f>M36</f>
         <v/>
       </c>
-      <c r="N62" s="19">
+      <c r="N62" s="141">
         <f>N36</f>
         <v/>
       </c>
@@ -4535,43 +4588,43 @@
           <t>Plus: Depreciation &amp; Amortization</t>
         </is>
       </c>
-      <c r="E63" s="19">
+      <c r="E63" s="141">
         <f>+E30</f>
         <v/>
       </c>
-      <c r="F63" s="19">
+      <c r="F63" s="141">
         <f>+F30</f>
         <v/>
       </c>
-      <c r="G63" s="19">
+      <c r="G63" s="141">
         <f>+G30</f>
         <v/>
       </c>
-      <c r="H63" s="19">
+      <c r="H63" s="141">
         <f>+H30</f>
         <v/>
       </c>
-      <c r="I63" s="19">
+      <c r="I63" s="141">
         <f>+I30</f>
         <v/>
       </c>
-      <c r="J63" s="19">
+      <c r="J63" s="141">
         <f>+J30</f>
         <v/>
       </c>
-      <c r="K63" s="19">
+      <c r="K63" s="141">
         <f>+K30</f>
         <v/>
       </c>
-      <c r="L63" s="19">
+      <c r="L63" s="141">
         <f>+L30</f>
         <v/>
       </c>
-      <c r="M63" s="19">
+      <c r="M63" s="141">
         <f>+M30</f>
         <v/>
       </c>
-      <c r="N63" s="19">
+      <c r="N63" s="141">
         <f>+N30</f>
         <v/>
       </c>
@@ -4582,38 +4635,38 @@
           <t>Less: Changes in Working Capital</t>
         </is>
       </c>
-      <c r="E64" s="131" t="n">
+      <c r="E64" s="133" t="n">
         <v>0</v>
       </c>
-      <c r="F64" s="131" t="n">
+      <c r="F64" s="133" t="n">
         <v>13779</v>
       </c>
-      <c r="G64" s="131" t="n">
+      <c r="G64" s="133" t="n">
         <v>63801</v>
       </c>
-      <c r="H64" s="131" t="n">
+      <c r="H64" s="133" t="n">
         <v>35231</v>
       </c>
-      <c r="I64" s="131" t="n">
+      <c r="I64" s="133" t="n">
         <v>92664</v>
       </c>
-      <c r="J64" s="19">
+      <c r="J64" s="141">
         <f>J89</f>
         <v/>
       </c>
-      <c r="K64" s="19">
+      <c r="K64" s="141">
         <f>K89</f>
         <v/>
       </c>
-      <c r="L64" s="19">
+      <c r="L64" s="141">
         <f>L89</f>
         <v/>
       </c>
-      <c r="M64" s="19">
+      <c r="M64" s="141">
         <f>M89</f>
         <v/>
       </c>
-      <c r="N64" s="19">
+      <c r="N64" s="141">
         <f>N89</f>
         <v/>
       </c>
@@ -4626,43 +4679,43 @@
       </c>
       <c r="C65" s="5" t="n"/>
       <c r="D65" s="28" t="n"/>
-      <c r="E65" s="17">
+      <c r="E65" s="142">
         <f>E62+E63-E64</f>
         <v/>
       </c>
-      <c r="F65" s="17">
+      <c r="F65" s="142">
         <f>F62+F63-F64</f>
         <v/>
       </c>
-      <c r="G65" s="17">
+      <c r="G65" s="142">
         <f>G62+G63-G64</f>
         <v/>
       </c>
-      <c r="H65" s="17">
+      <c r="H65" s="142">
         <f>H62+H63-H64</f>
         <v/>
       </c>
-      <c r="I65" s="17">
+      <c r="I65" s="142">
         <f>I62+I63-I64</f>
         <v/>
       </c>
-      <c r="J65" s="17">
+      <c r="J65" s="142">
         <f>J62+J63-J64</f>
         <v/>
       </c>
-      <c r="K65" s="17">
+      <c r="K65" s="142">
         <f>K62+K63-K64</f>
         <v/>
       </c>
-      <c r="L65" s="17">
+      <c r="L65" s="142">
         <f>L62+L63-L64</f>
         <v/>
       </c>
-      <c r="M65" s="17">
+      <c r="M65" s="142">
         <f>M62+M63-M64</f>
         <v/>
       </c>
-      <c r="N65" s="17">
+      <c r="N65" s="142">
         <f>N62+N63-N64</f>
         <v/>
       </c>
@@ -4705,38 +4758,38 @@
           <t>Investments in Property &amp; Equipment</t>
         </is>
       </c>
-      <c r="E68" s="131" t="n">
+      <c r="E68" s="133" t="n">
         <v>7569</v>
       </c>
-      <c r="F68" s="131" t="n">
+      <c r="F68" s="133" t="n">
         <v>6029</v>
       </c>
-      <c r="G68" s="131" t="n">
+      <c r="G68" s="133" t="n">
         <v>4237</v>
       </c>
-      <c r="H68" s="131" t="n">
+      <c r="H68" s="133" t="n">
         <v>25551</v>
       </c>
-      <c r="I68" s="131" t="n">
+      <c r="I68" s="133" t="n">
         <v>39407</v>
       </c>
-      <c r="J68" s="19">
+      <c r="J68" s="141">
         <f>J18</f>
         <v/>
       </c>
-      <c r="K68" s="19">
+      <c r="K68" s="141">
         <f>K18</f>
         <v/>
       </c>
-      <c r="L68" s="19">
+      <c r="L68" s="141">
         <f>L18</f>
         <v/>
       </c>
-      <c r="M68" s="19">
+      <c r="M68" s="141">
         <f>M18</f>
         <v/>
       </c>
-      <c r="N68" s="19">
+      <c r="N68" s="141">
         <f>N18</f>
         <v/>
       </c>
@@ -4749,43 +4802,43 @@
       </c>
       <c r="C69" s="5" t="n"/>
       <c r="D69" s="28" t="n"/>
-      <c r="E69" s="17">
+      <c r="E69" s="142">
         <f>SUM(E68)</f>
         <v/>
       </c>
-      <c r="F69" s="17">
+      <c r="F69" s="142">
         <f>SUM(F68)</f>
         <v/>
       </c>
-      <c r="G69" s="17">
+      <c r="G69" s="142">
         <f>SUM(G68)</f>
         <v/>
       </c>
-      <c r="H69" s="17">
+      <c r="H69" s="142">
         <f>SUM(H68)</f>
         <v/>
       </c>
-      <c r="I69" s="17">
+      <c r="I69" s="142">
         <f>SUM(I68)</f>
         <v/>
       </c>
-      <c r="J69" s="17">
+      <c r="J69" s="142">
         <f>SUM(J68)</f>
         <v/>
       </c>
-      <c r="K69" s="17">
+      <c r="K69" s="142">
         <f>SUM(K68)</f>
         <v/>
       </c>
-      <c r="L69" s="17">
+      <c r="L69" s="142">
         <f>SUM(L68)</f>
         <v/>
       </c>
-      <c r="M69" s="17">
+      <c r="M69" s="142">
         <f>SUM(M68)</f>
         <v/>
       </c>
-      <c r="N69" s="17">
+      <c r="N69" s="142">
         <f>SUM(N68)</f>
         <v/>
       </c>
@@ -4828,38 +4881,38 @@
           <t>Issuance (repayment) of debt</t>
         </is>
       </c>
-      <c r="E72" s="131" t="n">
+      <c r="E72" s="133" t="n">
         <v>0</v>
       </c>
-      <c r="F72" s="131" t="n">
+      <c r="F72" s="133" t="n">
         <v>594651</v>
       </c>
-      <c r="G72" s="131" t="n">
+      <c r="G72" s="133" t="n">
         <v>7989</v>
       </c>
-      <c r="H72" s="131" t="n">
+      <c r="H72" s="133" t="n">
         <v>347363</v>
       </c>
-      <c r="I72" s="131" t="n">
+      <c r="I72" s="133" t="n">
         <v>846670</v>
       </c>
-      <c r="J72" s="19">
+      <c r="J72" s="141">
         <f>J19</f>
         <v/>
       </c>
-      <c r="K72" s="19">
+      <c r="K72" s="141">
         <f>K19</f>
         <v/>
       </c>
-      <c r="L72" s="19">
+      <c r="L72" s="141">
         <f>L19</f>
         <v/>
       </c>
-      <c r="M72" s="19">
+      <c r="M72" s="141">
         <f>M19</f>
         <v/>
       </c>
-      <c r="N72" s="19">
+      <c r="N72" s="141">
         <f>N19</f>
         <v/>
       </c>
@@ -4870,38 +4923,38 @@
           <t>Issuance (repayment) of equity</t>
         </is>
       </c>
-      <c r="E73" s="131" t="n">
+      <c r="E73" s="133" t="n">
         <v>0</v>
       </c>
-      <c r="F73" s="131" t="n">
+      <c r="F73" s="133" t="n">
         <v>0</v>
       </c>
-      <c r="G73" s="131" t="n">
+      <c r="G73" s="133" t="n">
         <v>0</v>
       </c>
-      <c r="H73" s="131" t="n">
+      <c r="H73" s="133" t="n">
         <v>0</v>
       </c>
-      <c r="I73" s="131" t="n">
+      <c r="I73" s="133" t="n">
         <v>0</v>
       </c>
-      <c r="J73" s="19">
+      <c r="J73" s="141">
         <f>J20</f>
         <v/>
       </c>
-      <c r="K73" s="19">
+      <c r="K73" s="141">
         <f>K20</f>
         <v/>
       </c>
-      <c r="L73" s="19">
+      <c r="L73" s="141">
         <f>L20</f>
         <v/>
       </c>
-      <c r="M73" s="19">
+      <c r="M73" s="141">
         <f>M20</f>
         <v/>
       </c>
-      <c r="N73" s="19">
+      <c r="N73" s="141">
         <f>N20</f>
         <v/>
       </c>
@@ -4914,43 +4967,43 @@
       </c>
       <c r="C74" s="5" t="n"/>
       <c r="D74" s="28" t="n"/>
-      <c r="E74" s="17">
+      <c r="E74" s="142">
         <f>SUM(E72:E73)</f>
         <v/>
       </c>
-      <c r="F74" s="17">
+      <c r="F74" s="142">
         <f>SUM(F72:F73)</f>
         <v/>
       </c>
-      <c r="G74" s="17">
+      <c r="G74" s="142">
         <f>SUM(G72:G73)</f>
         <v/>
       </c>
-      <c r="H74" s="17">
+      <c r="H74" s="142">
         <f>SUM(H72:H73)</f>
         <v/>
       </c>
-      <c r="I74" s="17">
+      <c r="I74" s="142">
         <f>SUM(I72:I73)</f>
         <v/>
       </c>
-      <c r="J74" s="17">
+      <c r="J74" s="142">
         <f>SUM(J72:J73)</f>
         <v/>
       </c>
-      <c r="K74" s="17">
+      <c r="K74" s="142">
         <f>SUM(K72:K73)</f>
         <v/>
       </c>
-      <c r="L74" s="17">
+      <c r="L74" s="142">
         <f>SUM(L72:L73)</f>
         <v/>
       </c>
-      <c r="M74" s="17">
+      <c r="M74" s="142">
         <f>SUM(M72:M73)</f>
         <v/>
       </c>
-      <c r="N74" s="17">
+      <c r="N74" s="142">
         <f>SUM(N72:N73)</f>
         <v/>
       </c>
@@ -4976,43 +5029,43 @@
           <t>Net Increase (decrease) in Cash</t>
         </is>
       </c>
-      <c r="E76" s="52">
+      <c r="E76" s="138">
         <f>E65-E69+E74</f>
         <v/>
       </c>
-      <c r="F76" s="52">
+      <c r="F76" s="138">
         <f>F65-F69+F74</f>
         <v/>
       </c>
-      <c r="G76" s="52">
+      <c r="G76" s="138">
         <f>G65-G69+G74</f>
         <v/>
       </c>
-      <c r="H76" s="52">
+      <c r="H76" s="138">
         <f>H65-H69+H74</f>
         <v/>
       </c>
-      <c r="I76" s="52">
+      <c r="I76" s="138">
         <f>I65-I69+I74</f>
         <v/>
       </c>
-      <c r="J76" s="52">
+      <c r="J76" s="138">
         <f>J65-J69+J74</f>
         <v/>
       </c>
-      <c r="K76" s="52">
+      <c r="K76" s="138">
         <f>K65-K69+K74</f>
         <v/>
       </c>
-      <c r="L76" s="52">
+      <c r="L76" s="138">
         <f>L65-L69+L74</f>
         <v/>
       </c>
-      <c r="M76" s="52">
+      <c r="M76" s="138">
         <f>M65-M69+M74</f>
         <v/>
       </c>
-      <c r="N76" s="52">
+      <c r="N76" s="138">
         <f>N65-N69+N74</f>
         <v/>
       </c>
@@ -5023,39 +5076,39 @@
           <t>Opening Cash Balance</t>
         </is>
       </c>
-      <c r="E77" s="19">
+      <c r="E77" s="141">
         <f>D78</f>
         <v/>
       </c>
-      <c r="F77" s="33" t="n">
+      <c r="F77" s="149" t="n">
         <v>167971.1792</v>
       </c>
-      <c r="G77" s="33" t="n">
+      <c r="G77" s="149" t="n">
         <v>181209.912697878</v>
       </c>
-      <c r="H77" s="33" t="n">
+      <c r="H77" s="149" t="n">
         <v>183715.2565830093</v>
       </c>
-      <c r="I77" s="33" t="n">
+      <c r="I77" s="149" t="n">
         <v>211069.3356066046</v>
       </c>
-      <c r="J77" s="19">
+      <c r="J77" s="141">
         <f>+I78</f>
         <v/>
       </c>
-      <c r="K77" s="19">
+      <c r="K77" s="141">
         <f>+J78</f>
         <v/>
       </c>
-      <c r="L77" s="19">
+      <c r="L77" s="141">
         <f>+K78</f>
         <v/>
       </c>
-      <c r="M77" s="19">
+      <c r="M77" s="141">
         <f>+L78</f>
         <v/>
       </c>
-      <c r="N77" s="19">
+      <c r="N77" s="141">
         <f>+M78</f>
         <v/>
       </c>
@@ -5067,46 +5120,46 @@
         </is>
       </c>
       <c r="C78" s="5" t="n"/>
-      <c r="D78" s="133" t="n">
+      <c r="D78" s="150" t="n">
         <v>157394</v>
       </c>
-      <c r="E78" s="17">
+      <c r="E78" s="142">
         <f>SUM(E76:E77)</f>
         <v/>
       </c>
-      <c r="F78" s="17">
+      <c r="F78" s="142">
         <f>SUM(F76:F77)</f>
         <v/>
       </c>
-      <c r="G78" s="17">
+      <c r="G78" s="142">
         <f>SUM(G76:G77)</f>
         <v/>
       </c>
-      <c r="H78" s="17">
+      <c r="H78" s="142">
         <f>SUM(H76:H77)</f>
         <v/>
       </c>
-      <c r="I78" s="17">
+      <c r="I78" s="142">
         <f>SUM(I76:I77)</f>
         <v/>
       </c>
-      <c r="J78" s="17">
+      <c r="J78" s="142">
         <f>SUM(J76:J77)</f>
         <v/>
       </c>
-      <c r="K78" s="17">
+      <c r="K78" s="142">
         <f>SUM(K76:K77)</f>
         <v/>
       </c>
-      <c r="L78" s="17">
+      <c r="L78" s="142">
         <f>SUM(L76:L77)</f>
         <v/>
       </c>
-      <c r="M78" s="17">
+      <c r="M78" s="142">
         <f>SUM(M76:M77)</f>
         <v/>
       </c>
-      <c r="N78" s="17">
+      <c r="N78" s="142">
         <f>SUM(N76:N77)</f>
         <v/>
       </c>
@@ -5127,43 +5180,43 @@
       </c>
       <c r="C80" s="9" t="n"/>
       <c r="D80" s="27" t="n"/>
-      <c r="E80" s="66">
+      <c r="E80" s="148">
         <f>E78-E41</f>
         <v/>
       </c>
-      <c r="F80" s="66">
+      <c r="F80" s="148">
         <f>F78-F41</f>
         <v/>
       </c>
-      <c r="G80" s="66">
+      <c r="G80" s="148">
         <f>G78-G41</f>
         <v/>
       </c>
-      <c r="H80" s="66">
+      <c r="H80" s="148">
         <f>H78-H41</f>
         <v/>
       </c>
-      <c r="I80" s="66">
+      <c r="I80" s="148">
         <f>I78-I41</f>
         <v/>
       </c>
-      <c r="J80" s="66">
+      <c r="J80" s="148">
         <f>J78-J41</f>
         <v/>
       </c>
-      <c r="K80" s="66">
+      <c r="K80" s="148">
         <f>K78-K41</f>
         <v/>
       </c>
-      <c r="L80" s="66">
+      <c r="L80" s="148">
         <f>L78-L41</f>
         <v/>
       </c>
-      <c r="M80" s="66">
+      <c r="M80" s="148">
         <f>M78-M41</f>
         <v/>
       </c>
-      <c r="N80" s="66">
+      <c r="N80" s="148">
         <f>N78-N41</f>
         <v/>
       </c>
@@ -5219,38 +5272,38 @@
           <t>Accounts Receivable</t>
         </is>
       </c>
-      <c r="E85" s="33" t="n">
+      <c r="E85" s="149" t="n">
         <v>5100.35</v>
       </c>
-      <c r="F85" s="33" t="n">
+      <c r="F85" s="149" t="n">
         <v>5904.3</v>
       </c>
-      <c r="G85" s="33" t="n">
+      <c r="G85" s="149" t="n">
         <v>6567.25</v>
       </c>
-      <c r="H85" s="33" t="n">
+      <c r="H85" s="149" t="n">
         <v>7117.05</v>
       </c>
-      <c r="I85" s="33" t="n">
+      <c r="I85" s="149" t="n">
         <v>7538.6</v>
       </c>
-      <c r="J85" s="19">
+      <c r="J85" s="141">
         <f>J42</f>
         <v/>
       </c>
-      <c r="K85" s="19">
+      <c r="K85" s="141">
         <f>K42</f>
         <v/>
       </c>
-      <c r="L85" s="19">
+      <c r="L85" s="141">
         <f>L42</f>
         <v/>
       </c>
-      <c r="M85" s="19">
+      <c r="M85" s="141">
         <f>M42</f>
         <v/>
       </c>
-      <c r="N85" s="19">
+      <c r="N85" s="141">
         <f>N42</f>
         <v/>
       </c>
@@ -5261,38 +5314,38 @@
           <t>Inventory</t>
         </is>
       </c>
-      <c r="E86" s="33" t="n">
+      <c r="E86" s="149" t="n">
         <v>7804.6</v>
       </c>
-      <c r="F86" s="33" t="n">
+      <c r="F86" s="149" t="n">
         <v>9600.800000000001</v>
       </c>
-      <c r="G86" s="33" t="n">
+      <c r="G86" s="149" t="n">
         <v>9824.6</v>
       </c>
-      <c r="H86" s="33" t="n">
+      <c r="H86" s="149" t="n">
         <v>10530.8</v>
       </c>
-      <c r="I86" s="33" t="n">
+      <c r="I86" s="149" t="n">
         <v>11342</v>
       </c>
-      <c r="J86" s="19">
+      <c r="J86" s="141">
         <f>J43</f>
         <v/>
       </c>
-      <c r="K86" s="19">
+      <c r="K86" s="141">
         <f>K43</f>
         <v/>
       </c>
-      <c r="L86" s="19">
+      <c r="L86" s="141">
         <f>L43</f>
         <v/>
       </c>
-      <c r="M86" s="19">
+      <c r="M86" s="141">
         <f>M43</f>
         <v/>
       </c>
-      <c r="N86" s="19">
+      <c r="N86" s="141">
         <f>N43</f>
         <v/>
       </c>
@@ -5303,38 +5356,38 @@
           <t>Accounts Payable</t>
         </is>
       </c>
-      <c r="E87" s="33" t="n">
+      <c r="E87" s="149" t="n">
         <v>3902.3</v>
       </c>
-      <c r="F87" s="33" t="n">
+      <c r="F87" s="149" t="n">
         <v>4800.400000000001</v>
       </c>
-      <c r="G87" s="33" t="n">
+      <c r="G87" s="149" t="n">
         <v>4912.3</v>
       </c>
-      <c r="H87" s="33" t="n">
+      <c r="H87" s="149" t="n">
         <v>5265.400000000001</v>
       </c>
-      <c r="I87" s="33" t="n">
+      <c r="I87" s="149" t="n">
         <v>5671</v>
       </c>
-      <c r="J87" s="19">
+      <c r="J87" s="141">
         <f>J48</f>
         <v/>
       </c>
-      <c r="K87" s="19">
+      <c r="K87" s="141">
         <f>K48</f>
         <v/>
       </c>
-      <c r="L87" s="19">
+      <c r="L87" s="141">
         <f>L48</f>
         <v/>
       </c>
-      <c r="M87" s="19">
+      <c r="M87" s="141">
         <f>M48</f>
         <v/>
       </c>
-      <c r="N87" s="19">
+      <c r="N87" s="141">
         <f>N48</f>
         <v/>
       </c>
@@ -5347,43 +5400,43 @@
       </c>
       <c r="C88" s="5" t="n"/>
       <c r="D88" s="28" t="n"/>
-      <c r="E88" s="51">
+      <c r="E88" s="151">
         <f>E85+E86-E87</f>
         <v/>
       </c>
-      <c r="F88" s="51">
+      <c r="F88" s="151">
         <f>F85+F86-F87</f>
         <v/>
       </c>
-      <c r="G88" s="51">
+      <c r="G88" s="151">
         <f>G85+G86-G87</f>
         <v/>
       </c>
-      <c r="H88" s="51">
+      <c r="H88" s="151">
         <f>H85+H86-H87</f>
         <v/>
       </c>
-      <c r="I88" s="51">
+      <c r="I88" s="151">
         <f>I85+I86-I87</f>
         <v/>
       </c>
-      <c r="J88" s="51">
+      <c r="J88" s="151">
         <f>J85+J86-J87</f>
         <v/>
       </c>
-      <c r="K88" s="51">
+      <c r="K88" s="151">
         <f>K85+K86-K87</f>
         <v/>
       </c>
-      <c r="L88" s="51">
+      <c r="L88" s="151">
         <f>L85+L86-L87</f>
         <v/>
       </c>
-      <c r="M88" s="51">
+      <c r="M88" s="151">
         <f>M85+M86-M87</f>
         <v/>
       </c>
-      <c r="N88" s="51">
+      <c r="N88" s="151">
         <f>N85+N86-N87</f>
         <v/>
       </c>
@@ -5394,43 +5447,43 @@
           <t>Change in NWC</t>
         </is>
       </c>
-      <c r="E89" s="52">
+      <c r="E89" s="138">
         <f>E88-D88</f>
         <v/>
       </c>
-      <c r="F89" s="52">
+      <c r="F89" s="138">
         <f>F88-E88</f>
         <v/>
       </c>
-      <c r="G89" s="52">
+      <c r="G89" s="138">
         <f>G88-F88</f>
         <v/>
       </c>
-      <c r="H89" s="52">
+      <c r="H89" s="138">
         <f>H88-G88</f>
         <v/>
       </c>
-      <c r="I89" s="52">
+      <c r="I89" s="138">
         <f>I88-H88</f>
         <v/>
       </c>
-      <c r="J89" s="52">
+      <c r="J89" s="138">
         <f>J88-I88</f>
         <v/>
       </c>
-      <c r="K89" s="52">
+      <c r="K89" s="138">
         <f>K88-J88</f>
         <v/>
       </c>
-      <c r="L89" s="52">
+      <c r="L89" s="138">
         <f>L88-K88</f>
         <v/>
       </c>
-      <c r="M89" s="52">
+      <c r="M89" s="138">
         <f>M88-L88</f>
         <v/>
       </c>
-      <c r="N89" s="52">
+      <c r="N89" s="138">
         <f>N88-M88</f>
         <v/>
       </c>
@@ -5460,38 +5513,38 @@
           <t>PPE Opening</t>
         </is>
       </c>
-      <c r="E92" s="33" t="n">
+      <c r="E92" s="149" t="n">
         <v>50000</v>
       </c>
-      <c r="F92" s="33" t="n">
+      <c r="F92" s="149" t="n">
         <v>45500</v>
       </c>
-      <c r="G92" s="33" t="n">
+      <c r="G92" s="149" t="n">
         <v>42350</v>
       </c>
-      <c r="H92" s="33" t="n">
+      <c r="H92" s="149" t="n">
         <v>40145</v>
       </c>
-      <c r="I92" s="33" t="n">
+      <c r="I92" s="149" t="n">
         <v>38601.5</v>
       </c>
-      <c r="J92" s="19">
+      <c r="J92" s="141">
         <f>I95</f>
         <v/>
       </c>
-      <c r="K92" s="19">
+      <c r="K92" s="141">
         <f>J95</f>
         <v/>
       </c>
-      <c r="L92" s="19">
+      <c r="L92" s="141">
         <f>K95</f>
         <v/>
       </c>
-      <c r="M92" s="19">
+      <c r="M92" s="141">
         <f>L95</f>
         <v/>
       </c>
-      <c r="N92" s="19">
+      <c r="N92" s="141">
         <f>M95</f>
         <v/>
       </c>
@@ -5502,38 +5555,38 @@
           <t>Plus Capex</t>
         </is>
       </c>
-      <c r="E93" s="33" t="n">
+      <c r="E93" s="149" t="n">
         <v>15000</v>
       </c>
-      <c r="F93" s="33" t="n">
+      <c r="F93" s="149" t="n">
         <v>15000</v>
       </c>
-      <c r="G93" s="33" t="n">
+      <c r="G93" s="149" t="n">
         <v>15000</v>
       </c>
-      <c r="H93" s="33" t="n">
+      <c r="H93" s="149" t="n">
         <v>15000</v>
       </c>
-      <c r="I93" s="33" t="n">
+      <c r="I93" s="149" t="n">
         <v>15000</v>
       </c>
-      <c r="J93" s="19">
+      <c r="J93" s="141">
         <f>+J18</f>
         <v/>
       </c>
-      <c r="K93" s="19">
+      <c r="K93" s="141">
         <f>+K18</f>
         <v/>
       </c>
-      <c r="L93" s="19">
+      <c r="L93" s="141">
         <f>+L18</f>
         <v/>
       </c>
-      <c r="M93" s="19">
+      <c r="M93" s="141">
         <f>+M18</f>
         <v/>
       </c>
-      <c r="N93" s="19">
+      <c r="N93" s="141">
         <f>+N18</f>
         <v/>
       </c>
@@ -5544,38 +5597,38 @@
           <t>Less Depreciation</t>
         </is>
       </c>
-      <c r="E94" s="33" t="n">
+      <c r="E94" s="149" t="n">
         <v>19500</v>
       </c>
-      <c r="F94" s="33" t="n">
+      <c r="F94" s="149" t="n">
         <v>18150</v>
       </c>
-      <c r="G94" s="33" t="n">
+      <c r="G94" s="149" t="n">
         <v>17205</v>
       </c>
-      <c r="H94" s="33" t="n">
+      <c r="H94" s="149" t="n">
         <v>16543.5</v>
       </c>
-      <c r="I94" s="33" t="n">
+      <c r="I94" s="149" t="n">
         <v>16080.45</v>
       </c>
-      <c r="J94" s="55">
+      <c r="J94" s="141">
         <f>J92*J11</f>
         <v/>
       </c>
-      <c r="K94" s="55">
+      <c r="K94" s="141">
         <f>K92*K11</f>
         <v/>
       </c>
-      <c r="L94" s="55">
+      <c r="L94" s="141">
         <f>L92*L11</f>
         <v/>
       </c>
-      <c r="M94" s="55">
+      <c r="M94" s="141">
         <f>M92*M11</f>
         <v/>
       </c>
-      <c r="N94" s="55">
+      <c r="N94" s="141">
         <f>N92*N11</f>
         <v/>
       </c>
@@ -5588,43 +5641,43 @@
       </c>
       <c r="C95" s="5" t="n"/>
       <c r="D95" s="28" t="n"/>
-      <c r="E95" s="51">
+      <c r="E95" s="151">
         <f>E92+E93-E94</f>
         <v/>
       </c>
-      <c r="F95" s="51">
+      <c r="F95" s="151">
         <f>F92+F93-F94</f>
         <v/>
       </c>
-      <c r="G95" s="51">
+      <c r="G95" s="151">
         <f>G92+G93-G94</f>
         <v/>
       </c>
-      <c r="H95" s="51">
+      <c r="H95" s="151">
         <f>H92+H93-H94</f>
         <v/>
       </c>
-      <c r="I95" s="51">
+      <c r="I95" s="151">
         <f>I92+I93-I94</f>
         <v/>
       </c>
-      <c r="J95" s="51">
+      <c r="J95" s="151">
         <f>J92+J93-J94</f>
         <v/>
       </c>
-      <c r="K95" s="51">
+      <c r="K95" s="151">
         <f>K92+K93-K94</f>
         <v/>
       </c>
-      <c r="L95" s="51">
+      <c r="L95" s="151">
         <f>L92+L93-L94</f>
         <v/>
       </c>
-      <c r="M95" s="51">
+      <c r="M95" s="151">
         <f>M92+M93-M94</f>
         <v/>
       </c>
-      <c r="N95" s="51">
+      <c r="N95" s="151">
         <f>N92+N93-N94</f>
         <v/>
       </c>
@@ -5659,38 +5712,38 @@
           <t>Debt Opening</t>
         </is>
       </c>
-      <c r="E98" s="33" t="n">
+      <c r="E98" s="149" t="n">
         <v>50000</v>
       </c>
-      <c r="F98" s="33" t="n">
+      <c r="F98" s="149" t="n">
         <v>50000</v>
       </c>
-      <c r="G98" s="33" t="n">
+      <c r="G98" s="149" t="n">
         <v>50000</v>
       </c>
-      <c r="H98" s="33" t="n">
+      <c r="H98" s="149" t="n">
         <v>30000</v>
       </c>
-      <c r="I98" s="33" t="n">
+      <c r="I98" s="149" t="n">
         <v>30000</v>
       </c>
-      <c r="J98" s="19">
+      <c r="J98" s="141">
         <f>I100</f>
         <v/>
       </c>
-      <c r="K98" s="19">
+      <c r="K98" s="141">
         <f>J100</f>
         <v/>
       </c>
-      <c r="L98" s="19">
+      <c r="L98" s="141">
         <f>K100</f>
         <v/>
       </c>
-      <c r="M98" s="19">
+      <c r="M98" s="141">
         <f>L100</f>
         <v/>
       </c>
-      <c r="N98" s="19">
+      <c r="N98" s="141">
         <f>M100</f>
         <v/>
       </c>
@@ -5701,38 +5754,38 @@
           <t>Issuance (repayment)</t>
         </is>
       </c>
-      <c r="E99" s="33" t="n">
+      <c r="E99" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="F99" s="33" t="n">
+      <c r="F99" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="G99" s="33" t="n">
+      <c r="G99" s="149" t="n">
         <v>-20000</v>
       </c>
-      <c r="H99" s="33" t="n">
+      <c r="H99" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="I99" s="33" t="n">
+      <c r="I99" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="J99" s="52">
+      <c r="J99" s="138">
         <f>+J19</f>
         <v/>
       </c>
-      <c r="K99" s="52">
+      <c r="K99" s="138">
         <f>+K19</f>
         <v/>
       </c>
-      <c r="L99" s="52">
+      <c r="L99" s="138">
         <f>+L19</f>
         <v/>
       </c>
-      <c r="M99" s="52">
+      <c r="M99" s="138">
         <f>+M19</f>
         <v/>
       </c>
-      <c r="N99" s="52">
+      <c r="N99" s="138">
         <f>+N19</f>
         <v/>
       </c>
@@ -5745,43 +5798,43 @@
       </c>
       <c r="C100" s="5" t="n"/>
       <c r="D100" s="28" t="n"/>
-      <c r="E100" s="51">
+      <c r="E100" s="151">
         <f>SUM(E98:E99)</f>
         <v/>
       </c>
-      <c r="F100" s="51">
+      <c r="F100" s="151">
         <f>SUM(F98:F99)</f>
         <v/>
       </c>
-      <c r="G100" s="51">
+      <c r="G100" s="151">
         <f>SUM(G98:G99)</f>
         <v/>
       </c>
-      <c r="H100" s="51">
+      <c r="H100" s="151">
         <f>SUM(H98:H99)</f>
         <v/>
       </c>
-      <c r="I100" s="51">
+      <c r="I100" s="151">
         <f>SUM(I98:I99)</f>
         <v/>
       </c>
-      <c r="J100" s="51">
+      <c r="J100" s="151">
         <f>SUM(J98:J99)</f>
         <v/>
       </c>
-      <c r="K100" s="51">
+      <c r="K100" s="151">
         <f>SUM(K98:K99)</f>
         <v/>
       </c>
-      <c r="L100" s="51">
+      <c r="L100" s="151">
         <f>SUM(L98:L99)</f>
         <v/>
       </c>
-      <c r="M100" s="51">
+      <c r="M100" s="151">
         <f>SUM(M98:M99)</f>
         <v/>
       </c>
-      <c r="N100" s="51">
+      <c r="N100" s="151">
         <f>SUM(N98:N99)</f>
         <v/>
       </c>
@@ -5792,38 +5845,38 @@
           <t>Interest Expense</t>
         </is>
       </c>
-      <c r="E101" s="33" t="n">
+      <c r="E101" s="149" t="n">
         <v>2500</v>
       </c>
-      <c r="F101" s="33" t="n">
+      <c r="F101" s="149" t="n">
         <v>2500</v>
       </c>
-      <c r="G101" s="33" t="n">
+      <c r="G101" s="149" t="n">
         <v>1500</v>
       </c>
-      <c r="H101" s="33" t="n">
+      <c r="H101" s="149" t="n">
         <v>900</v>
       </c>
-      <c r="I101" s="33" t="n">
+      <c r="I101" s="149" t="n">
         <v>900</v>
       </c>
-      <c r="J101" s="19">
+      <c r="J101" s="141">
         <f>J98*J12</f>
         <v/>
       </c>
-      <c r="K101" s="19">
+      <c r="K101" s="141">
         <f>K98*K12</f>
         <v/>
       </c>
-      <c r="L101" s="19">
+      <c r="L101" s="141">
         <f>L98*L12</f>
         <v/>
       </c>
-      <c r="M101" s="19">
+      <c r="M101" s="141">
         <f>M98*M12</f>
         <v/>
       </c>
-      <c r="N101" s="19">
+      <c r="N101" s="141">
         <f>N98*N12</f>
         <v/>
       </c>
@@ -6138,11 +6191,18 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3.54296875" customWidth="1" min="1" max="1"/>
-    <col width="12.6328125" customWidth="1" min="2" max="2"/>
-    <col width="12.453125" customWidth="1" min="3" max="3"/>
-    <col width="11.36328125" customWidth="1" min="4" max="4"/>
-    <col width="11.54296875" customWidth="1" min="5" max="5"/>
-    <col width="12.54296875" customWidth="1" min="10" max="10"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="36" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
     <col width="9.08984375" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
@@ -6232,7 +6292,7 @@
         </is>
       </c>
       <c r="C5" s="100" t="n"/>
-      <c r="D5" s="134" t="n">
+      <c r="D5" s="152" t="n">
         <v>0.1877023903712333</v>
       </c>
       <c r="E5" s="100" t="n"/>
@@ -6255,7 +6315,7 @@
         </is>
       </c>
       <c r="C6" s="97" t="n"/>
-      <c r="D6" s="134" t="n">
+      <c r="D6" s="152" t="n">
         <v>0.096</v>
       </c>
       <c r="E6" s="97" t="n"/>
@@ -6278,7 +6338,7 @@
         </is>
       </c>
       <c r="C7" s="97" t="n"/>
-      <c r="D7" s="134" t="n">
+      <c r="D7" s="152" t="n">
         <v>0.03</v>
       </c>
       <c r="E7" s="97" t="n"/>
@@ -6301,7 +6361,7 @@
         </is>
       </c>
       <c r="C8" s="97" t="n"/>
-      <c r="D8" s="135" t="n">
+      <c r="D8" s="153" t="n">
         <v>22</v>
       </c>
       <c r="E8" s="97" t="n"/>
@@ -6324,8 +6384,8 @@
         </is>
       </c>
       <c r="C9" s="97" t="n"/>
-      <c r="D9" s="106" t="n">
-        <v>43100</v>
+      <c r="D9" s="154" t="n">
+        <v>45930</v>
       </c>
       <c r="E9" s="97" t="n"/>
       <c r="F9" s="97" t="n"/>
@@ -6347,8 +6407,8 @@
         </is>
       </c>
       <c r="C10" s="97" t="n"/>
-      <c r="D10" s="106" t="n">
-        <v>43281</v>
+      <c r="D10" s="154" t="n">
+        <v>46295</v>
       </c>
       <c r="E10" s="97" t="n"/>
       <c r="F10" s="97" t="n"/>
@@ -6370,7 +6430,7 @@
         </is>
       </c>
       <c r="C11" s="97" t="n"/>
-      <c r="D11" s="136" t="n">
+      <c r="D11" s="155" t="n">
         <v>1046.23</v>
       </c>
       <c r="E11" s="97" t="n"/>
@@ -6393,7 +6453,7 @@
         </is>
       </c>
       <c r="C12" s="97" t="n"/>
-      <c r="D12" s="137" t="n">
+      <c r="D12" s="156" t="n">
         <v>21597.635</v>
       </c>
       <c r="E12" s="97" t="n"/>
@@ -6416,7 +6476,7 @@
         </is>
       </c>
       <c r="C13" s="97" t="n"/>
-      <c r="D13" s="137" t="n">
+      <c r="D13" s="156" t="n">
         <v>5582389</v>
       </c>
       <c r="E13" s="97" t="n"/>
@@ -6439,7 +6499,7 @@
         </is>
       </c>
       <c r="C14" s="97" t="n"/>
-      <c r="D14" s="137" t="n">
+      <c r="D14" s="156" t="n">
         <v>304537</v>
       </c>
       <c r="E14" s="97" t="n"/>
@@ -6458,12 +6518,13 @@
       <c r="A15" s="97" t="n"/>
       <c r="B15" s="97" t="inlineStr">
         <is>
-          <t>Capex</t>
+          <t>Capex (FY1 forecast, linked)</t>
         </is>
       </c>
       <c r="C15" s="97" t="n"/>
-      <c r="D15" s="138" t="n">
-        <v>45051.43556656494</v>
+      <c r="D15" s="157">
+        <f>'3 Statement Model'!J68</f>
+        <v/>
       </c>
       <c r="E15" s="97" t="n"/>
       <c r="F15" s="97" t="n"/>
@@ -6491,50 +6552,50 @@
     </row>
     <row r="17" ht="16" customHeight="1">
       <c r="A17" s="97" t="n"/>
-      <c r="B17" s="109" t="inlineStr">
+      <c r="B17" s="110" t="inlineStr">
         <is>
           <t>Discounted Cash Flow</t>
         </is>
       </c>
-      <c r="C17" s="110" t="n"/>
-      <c r="D17" s="111" t="inlineStr">
+      <c r="C17" s="111" t="n"/>
+      <c r="D17" s="112" t="inlineStr">
         <is>
           <t>Entry</t>
         </is>
       </c>
-      <c r="E17" s="112">
+      <c r="E17" s="158">
         <f>YEAR(E18)</f>
         <v/>
       </c>
-      <c r="F17" s="112">
+      <c r="F17" s="158">
         <f>YEAR(F18)</f>
         <v/>
       </c>
-      <c r="G17" s="112">
+      <c r="G17" s="158">
         <f>YEAR(G18)</f>
         <v/>
       </c>
-      <c r="H17" s="112">
+      <c r="H17" s="158">
         <f>YEAR(H18)</f>
         <v/>
       </c>
-      <c r="I17" s="112">
+      <c r="I17" s="158">
         <f>YEAR(I18)</f>
         <v/>
       </c>
-      <c r="J17" s="111" t="inlineStr">
+      <c r="J17" s="112" t="inlineStr">
         <is>
           <t>Exit</t>
         </is>
       </c>
       <c r="K17" s="97" t="n"/>
-      <c r="L17" s="109" t="inlineStr">
-        <is>
-          <t>Terminal Value</t>
-        </is>
-      </c>
-      <c r="M17" s="110" t="n"/>
-      <c r="N17" s="110" t="n"/>
+      <c r="L17" s="114" t="inlineStr">
+        <is>
+          <t>Terminal value cross-check</t>
+        </is>
+      </c>
+      <c r="M17" s="111" t="n"/>
+      <c r="N17" s="111" t="n"/>
       <c r="O17" s="97" t="n"/>
     </row>
     <row r="18" ht="16" customHeight="1">
@@ -6545,41 +6606,44 @@
         </is>
       </c>
       <c r="C18" s="97" t="n"/>
-      <c r="D18" s="113">
+      <c r="D18" s="159">
         <f>D9</f>
         <v/>
       </c>
-      <c r="E18" s="113">
+      <c r="E18" s="160">
         <f>DATE(YEAR($D$10)+E19,6,30)</f>
         <v/>
       </c>
-      <c r="F18" s="113">
+      <c r="F18" s="160">
         <f>DATE(YEAR($D$10)+F19,6,30)</f>
         <v/>
       </c>
-      <c r="G18" s="113">
+      <c r="G18" s="160">
         <f>DATE(YEAR($D$10)+G19,6,30)</f>
         <v/>
       </c>
-      <c r="H18" s="113">
+      <c r="H18" s="160">
         <f>DATE(YEAR($D$10)+H19,6,30)</f>
         <v/>
       </c>
-      <c r="I18" s="113">
+      <c r="I18" s="160">
         <f>DATE(YEAR($D$10)+I19,6,30)</f>
         <v/>
       </c>
-      <c r="J18" s="114">
+      <c r="J18" s="161">
         <f>I18</f>
         <v/>
       </c>
       <c r="K18" s="97" t="n"/>
       <c r="L18" s="97" t="inlineStr">
         <is>
-          <t>Perpetural Growth</t>
-        </is>
-      </c>
-      <c r="M18" s="97" t="n"/>
+          <t>Exit EV/EBITDA TV (in J27)</t>
+        </is>
+      </c>
+      <c r="M18" s="162">
+        <f>($I$21+$I$23)*$D$8</f>
+        <v/>
+      </c>
       <c r="N18" s="97">
         <f>(I26*(1+D7))/(D6-D7)</f>
         <v/>
@@ -6588,41 +6652,44 @@
     </row>
     <row r="19" ht="16" customHeight="1">
       <c r="A19" s="97" t="n"/>
-      <c r="B19" s="115" t="inlineStr">
+      <c r="B19" s="118" t="inlineStr">
         <is>
           <t>Time Periods</t>
         </is>
       </c>
-      <c r="C19" s="115" t="n"/>
-      <c r="D19" s="113" t="n"/>
-      <c r="E19" s="116" t="n">
+      <c r="C19" s="118" t="n"/>
+      <c r="D19" s="115" t="n"/>
+      <c r="E19" s="163" t="n">
         <v>0</v>
       </c>
-      <c r="F19" s="117">
+      <c r="F19" s="159">
         <f>E19+1</f>
         <v/>
       </c>
-      <c r="G19" s="117">
+      <c r="G19" s="159">
         <f>F19+1</f>
         <v/>
       </c>
-      <c r="H19" s="117">
+      <c r="H19" s="159">
         <f>G19+1</f>
         <v/>
       </c>
-      <c r="I19" s="117">
+      <c r="I19" s="159">
         <f>H19+1</f>
         <v/>
       </c>
-      <c r="J19" s="113" t="n"/>
+      <c r="J19" s="115" t="n"/>
       <c r="K19" s="97" t="n"/>
       <c r="L19" s="97" t="inlineStr">
         <is>
-          <t>EV/EBITDA</t>
-        </is>
-      </c>
-      <c r="M19" s="97" t="n"/>
-      <c r="N19" s="118">
+          <t>Gordon TV: UFCF_n*(1+g)/(WACC-g)</t>
+        </is>
+      </c>
+      <c r="M19" s="162">
+        <f>IF(($D$6-$D$7)&lt;=0,"WACC must exceed g",$I$26*(1+$D$7)/($D$6-$D$7))</f>
+        <v/>
+      </c>
+      <c r="N19" s="121">
         <f>D8*(I21+I23)</f>
         <v/>
       </c>
@@ -6630,30 +6697,30 @@
     </row>
     <row r="20" ht="16" customHeight="1">
       <c r="A20" s="97" t="n"/>
-      <c r="B20" s="115" t="inlineStr">
-        <is>
-          <t>Year Fraction</t>
+      <c r="B20" s="118" t="inlineStr">
+        <is>
+          <t>Year Fraction (display only; XNPV uses dates — not applied to CF)</t>
         </is>
       </c>
       <c r="C20" s="97" t="n"/>
       <c r="D20" s="97" t="n"/>
-      <c r="E20" s="139">
+      <c r="E20" s="159">
         <f>YEARFRAC(D18,E18)</f>
         <v/>
       </c>
-      <c r="F20" s="139">
+      <c r="F20" s="159">
         <f>YEARFRAC(E18,F18)</f>
         <v/>
       </c>
-      <c r="G20" s="139">
+      <c r="G20" s="159">
         <f>YEARFRAC(F18,G18)</f>
         <v/>
       </c>
-      <c r="H20" s="139">
+      <c r="H20" s="159">
         <f>YEARFRAC(G18,H18)</f>
         <v/>
       </c>
-      <c r="I20" s="139">
+      <c r="I20" s="159">
         <f>YEARFRAC(H18,I18)</f>
         <v/>
       </c>
@@ -6661,11 +6728,11 @@
       <c r="K20" s="97" t="n"/>
       <c r="L20" s="97" t="inlineStr">
         <is>
-          <t>Average</t>
+          <t>Switch J27 to Gordon: copy M19 → J27</t>
         </is>
       </c>
       <c r="M20" s="97" t="n"/>
-      <c r="N20" s="120">
+      <c r="N20" s="123">
         <f>AVERAGE(N18:N19)</f>
         <v/>
       </c>
@@ -6675,25 +6742,30 @@
       <c r="A21" s="97" t="n"/>
       <c r="B21" s="97" t="inlineStr">
         <is>
-          <t>EBIT</t>
+          <t>EBIT (linked to 3-stmt)</t>
         </is>
       </c>
       <c r="C21" s="97" t="n"/>
       <c r="D21" s="97" t="n"/>
-      <c r="E21" s="138" t="n">
-        <v>1052713.043327438</v>
-      </c>
-      <c r="F21" s="138" t="n">
-        <v>1157984.347660181</v>
-      </c>
-      <c r="G21" s="138" t="n">
-        <v>1262202.938949598</v>
-      </c>
-      <c r="H21" s="138" t="n">
-        <v>1363179.174065566</v>
-      </c>
-      <c r="I21" s="138" t="n">
-        <v>1458601.716250155</v>
+      <c r="E21" s="157">
+        <f>'3 Statement Model'!J26-'3 Statement Model'!J28-'3 Statement Model'!J29-'3 Statement Model'!J30</f>
+        <v/>
+      </c>
+      <c r="F21" s="157">
+        <f>'3 Statement Model'!K26-'3 Statement Model'!K28-'3 Statement Model'!K29-'3 Statement Model'!K30</f>
+        <v/>
+      </c>
+      <c r="G21" s="157">
+        <f>'3 Statement Model'!L26-'3 Statement Model'!L28-'3 Statement Model'!L29-'3 Statement Model'!L30</f>
+        <v/>
+      </c>
+      <c r="H21" s="157">
+        <f>'3 Statement Model'!M26-'3 Statement Model'!M28-'3 Statement Model'!M29-'3 Statement Model'!M30</f>
+        <v/>
+      </c>
+      <c r="I21" s="157">
+        <f>'3 Statement Model'!N26-'3 Statement Model'!N28-'3 Statement Model'!N29-'3 Statement Model'!N30</f>
+        <v/>
       </c>
       <c r="J21" s="97" t="n"/>
       <c r="K21" s="97" t="n"/>
@@ -6711,23 +6783,23 @@
       </c>
       <c r="C22" s="97" t="n"/>
       <c r="D22" s="97" t="n"/>
-      <c r="E22" s="118">
+      <c r="E22" s="164">
         <f>E21*$D$5</f>
         <v/>
       </c>
-      <c r="F22" s="118">
+      <c r="F22" s="164">
         <f>F21*$D$5</f>
         <v/>
       </c>
-      <c r="G22" s="118">
+      <c r="G22" s="164">
         <f>G21*$D$5</f>
         <v/>
       </c>
-      <c r="H22" s="118">
+      <c r="H22" s="164">
         <f>H21*$D$5</f>
         <v/>
       </c>
-      <c r="I22" s="118">
+      <c r="I22" s="164">
         <f>I21*$D$5</f>
         <v/>
       </c>
@@ -6742,25 +6814,30 @@
       <c r="A23" s="97" t="n"/>
       <c r="B23" s="97" t="inlineStr">
         <is>
-          <t>Plus: D&amp;A</t>
+          <t>Plus: D&amp;A (linked to 3-stmt)</t>
         </is>
       </c>
       <c r="C23" s="97" t="n"/>
       <c r="D23" s="97" t="n"/>
-      <c r="E23" s="140" t="n">
-        <v>17093.63982519042</v>
-      </c>
-      <c r="F23" s="140" t="n">
-        <v>18803.00380770947</v>
-      </c>
-      <c r="G23" s="140" t="n">
-        <v>20495.27415040332</v>
-      </c>
-      <c r="H23" s="140" t="n">
-        <v>22134.89608243559</v>
-      </c>
-      <c r="I23" s="140" t="n">
-        <v>23684.33880820608</v>
+      <c r="E23" s="157">
+        <f>'3 Statement Model'!J30</f>
+        <v/>
+      </c>
+      <c r="F23" s="157">
+        <f>'3 Statement Model'!K30</f>
+        <v/>
+      </c>
+      <c r="G23" s="157">
+        <f>'3 Statement Model'!L30</f>
+        <v/>
+      </c>
+      <c r="H23" s="157">
+        <f>'3 Statement Model'!M30</f>
+        <v/>
+      </c>
+      <c r="I23" s="157">
+        <f>'3 Statement Model'!N30</f>
+        <v/>
       </c>
       <c r="J23" s="97" t="n"/>
       <c r="K23" s="97" t="n"/>
@@ -6773,29 +6850,29 @@
       <c r="A24" s="97" t="n"/>
       <c r="B24" s="97" t="inlineStr">
         <is>
-          <t>Less: Capex</t>
+          <t>Less: Capex (linked to 3-stmt CF)</t>
         </is>
       </c>
       <c r="C24" s="97" t="n"/>
       <c r="D24" s="97" t="n"/>
-      <c r="E24" s="103">
-        <f>$D$15</f>
-        <v/>
-      </c>
-      <c r="F24" s="103">
-        <f>$D$15</f>
-        <v/>
-      </c>
-      <c r="G24" s="103">
-        <f>$D$15</f>
-        <v/>
-      </c>
-      <c r="H24" s="103">
-        <f>$D$15</f>
-        <v/>
-      </c>
-      <c r="I24" s="103">
-        <f>$D$15</f>
+      <c r="E24" s="157">
+        <f>'3 Statement Model'!J68</f>
+        <v/>
+      </c>
+      <c r="F24" s="157">
+        <f>'3 Statement Model'!K68</f>
+        <v/>
+      </c>
+      <c r="G24" s="157">
+        <f>'3 Statement Model'!L68</f>
+        <v/>
+      </c>
+      <c r="H24" s="157">
+        <f>'3 Statement Model'!M68</f>
+        <v/>
+      </c>
+      <c r="I24" s="157">
+        <f>'3 Statement Model'!N68</f>
         <v/>
       </c>
       <c r="J24" s="97" t="n"/>
@@ -6809,25 +6886,30 @@
       <c r="A25" s="97" t="n"/>
       <c r="B25" s="97" t="inlineStr">
         <is>
-          <t>Less: Changes in NWC</t>
+          <t>Less: ΔNWC (linked to 3-stmt CF)</t>
         </is>
       </c>
       <c r="C25" s="97" t="n"/>
       <c r="D25" s="97" t="n"/>
-      <c r="E25" s="138" t="n">
-        <v>71163.54596501018</v>
-      </c>
-      <c r="F25" s="138" t="n">
-        <v>56799.65459650115</v>
-      </c>
-      <c r="G25" s="138" t="n">
-        <v>56231.65805053606</v>
-      </c>
-      <c r="H25" s="138" t="n">
-        <v>54482.22868896381</v>
-      </c>
-      <c r="I25" s="138" t="n">
-        <v>51485.70611107082</v>
+      <c r="E25" s="157">
+        <f>'3 Statement Model'!J64</f>
+        <v/>
+      </c>
+      <c r="F25" s="157">
+        <f>'3 Statement Model'!K64</f>
+        <v/>
+      </c>
+      <c r="G25" s="157">
+        <f>'3 Statement Model'!L64</f>
+        <v/>
+      </c>
+      <c r="H25" s="157">
+        <f>'3 Statement Model'!M64</f>
+        <v/>
+      </c>
+      <c r="I25" s="157">
+        <f>'3 Statement Model'!N64</f>
+        <v/>
       </c>
       <c r="J25" s="97" t="n"/>
       <c r="K25" s="97" t="n"/>
@@ -6845,23 +6927,23 @@
       </c>
       <c r="C26" s="97" t="n"/>
       <c r="D26" s="97" t="n"/>
-      <c r="E26" s="120">
+      <c r="E26" s="165">
         <f>E21-E22+E23-E24-E25</f>
         <v/>
       </c>
-      <c r="F26" s="120">
+      <c r="F26" s="165">
         <f>F21-F22+F23-F24-F25</f>
         <v/>
       </c>
-      <c r="G26" s="120">
+      <c r="G26" s="165">
         <f>G21-G22+G23-G24-G25</f>
         <v/>
       </c>
-      <c r="H26" s="120">
+      <c r="H26" s="165">
         <f>H21-H22+H23-H24-H25</f>
         <v/>
       </c>
-      <c r="I26" s="120">
+      <c r="I26" s="165">
         <f>I21-I22+I23-I24-I25</f>
         <v/>
       </c>
@@ -6876,11 +6958,11 @@
       <c r="A27" s="97" t="n"/>
       <c r="B27" s="97" t="inlineStr">
         <is>
-          <t>(Entry)/Exit</t>
+          <t>(Entry)/Exit TV</t>
         </is>
       </c>
       <c r="C27" s="97" t="n"/>
-      <c r="D27" s="97">
+      <c r="D27" s="164">
         <f>-I35</f>
         <v/>
       </c>
@@ -6889,8 +6971,8 @@
       <c r="G27" s="97" t="n"/>
       <c r="H27" s="97" t="n"/>
       <c r="I27" s="97" t="n"/>
-      <c r="J27" s="97">
-        <f>N20</f>
+      <c r="J27" s="157">
+        <f>($I$21+$I$23)*$D$8</f>
         <v/>
       </c>
       <c r="K27" s="97" t="n"/>
@@ -6907,30 +6989,30 @@
         </is>
       </c>
       <c r="C28" s="97" t="n"/>
-      <c r="D28" s="120" t="n">
+      <c r="D28" s="165" t="n">
         <v>0</v>
       </c>
-      <c r="E28" s="120">
-        <f>(E27+E26)*E20</f>
-        <v/>
-      </c>
-      <c r="F28" s="120">
-        <f>(F27+F26)*F20</f>
-        <v/>
-      </c>
-      <c r="G28" s="120">
-        <f>(G27+G26)*G20</f>
-        <v/>
-      </c>
-      <c r="H28" s="120">
-        <f>(H27+H26)*H20</f>
-        <v/>
-      </c>
-      <c r="I28" s="120">
-        <f>(I27+I26)*I20</f>
-        <v/>
-      </c>
-      <c r="J28" s="120">
+      <c r="E28" s="166">
+        <f>E27+E26</f>
+        <v/>
+      </c>
+      <c r="F28" s="166">
+        <f>F27+F26</f>
+        <v/>
+      </c>
+      <c r="G28" s="166">
+        <f>G27+G26</f>
+        <v/>
+      </c>
+      <c r="H28" s="166">
+        <f>H27+H26</f>
+        <v/>
+      </c>
+      <c r="I28" s="166">
+        <f>I27+I26</f>
+        <v/>
+      </c>
+      <c r="J28" s="166">
         <f>J27+J26</f>
         <v/>
       </c>
@@ -6948,31 +7030,31 @@
         </is>
       </c>
       <c r="C29" s="97" t="n"/>
-      <c r="D29" s="97">
+      <c r="D29" s="164">
         <f>D27+D26</f>
         <v/>
       </c>
-      <c r="E29" s="97">
-        <f>(E27+E26)*E20</f>
-        <v/>
-      </c>
-      <c r="F29" s="97">
-        <f>(F27+F26)*F20</f>
-        <v/>
-      </c>
-      <c r="G29" s="97">
-        <f>(G27+G26)*G20</f>
-        <v/>
-      </c>
-      <c r="H29" s="97">
-        <f>(H27+H26)*H20</f>
-        <v/>
-      </c>
-      <c r="I29" s="97">
-        <f>(I27+I26)*I20</f>
-        <v/>
-      </c>
-      <c r="J29" s="97">
+      <c r="E29" s="157">
+        <f>E27+E26</f>
+        <v/>
+      </c>
+      <c r="F29" s="157">
+        <f>F27+F26</f>
+        <v/>
+      </c>
+      <c r="G29" s="157">
+        <f>G27+G26</f>
+        <v/>
+      </c>
+      <c r="H29" s="157">
+        <f>H27+H26</f>
+        <v/>
+      </c>
+      <c r="I29" s="157">
+        <f>I27+I26</f>
+        <v/>
+      </c>
+      <c r="J29" s="157">
         <f>J27</f>
         <v/>
       </c>
@@ -6999,29 +7081,29 @@
     </row>
     <row r="31" ht="16" customHeight="1">
       <c r="A31" s="97" t="n"/>
-      <c r="B31" s="109" t="inlineStr">
+      <c r="B31" s="110" t="inlineStr">
         <is>
           <t>Intrinsic Value</t>
         </is>
       </c>
-      <c r="C31" s="110" t="n"/>
-      <c r="D31" s="110" t="n"/>
+      <c r="C31" s="111" t="n"/>
+      <c r="D31" s="111" t="n"/>
       <c r="E31" s="97" t="n"/>
-      <c r="G31" s="109" t="inlineStr">
+      <c r="G31" s="110" t="inlineStr">
         <is>
           <t>Market Value</t>
         </is>
       </c>
-      <c r="H31" s="110" t="n"/>
-      <c r="I31" s="110" t="n"/>
+      <c r="H31" s="111" t="n"/>
+      <c r="I31" s="111" t="n"/>
       <c r="J31" s="97" t="n"/>
-      <c r="L31" s="109" t="inlineStr">
+      <c r="L31" s="110" t="inlineStr">
         <is>
           <t>Rate of Return</t>
         </is>
       </c>
-      <c r="M31" s="110" t="n"/>
-      <c r="N31" s="110" t="n"/>
+      <c r="M31" s="111" t="n"/>
+      <c r="N31" s="111" t="n"/>
       <c r="O31" s="97" t="n"/>
     </row>
     <row r="32" ht="16" customHeight="1">
@@ -7032,7 +7114,7 @@
         </is>
       </c>
       <c r="C32" s="97" t="n"/>
-      <c r="D32" s="97">
+      <c r="D32" s="164">
         <f>XNPV(D6,D28:J28,D18:J18)</f>
         <v/>
       </c>
@@ -7043,7 +7125,7 @@
         </is>
       </c>
       <c r="H32" s="97" t="n"/>
-      <c r="I32" s="97">
+      <c r="I32" s="164">
         <f>D12*D11</f>
         <v/>
       </c>
@@ -7054,7 +7136,7 @@
         </is>
       </c>
       <c r="M32" s="97" t="n"/>
-      <c r="N32" s="122">
+      <c r="N32" s="126">
         <f>D37/I37-1</f>
         <v/>
       </c>
@@ -7068,7 +7150,7 @@
         </is>
       </c>
       <c r="C33" s="97" t="n"/>
-      <c r="D33" s="97">
+      <c r="D33" s="164">
         <f>+D14</f>
         <v/>
       </c>
@@ -7079,7 +7161,7 @@
         </is>
       </c>
       <c r="H33" s="97" t="n"/>
-      <c r="I33" s="97">
+      <c r="I33" s="164">
         <f>D13</f>
         <v/>
       </c>
@@ -7090,7 +7172,7 @@
         </is>
       </c>
       <c r="M33" s="97" t="n"/>
-      <c r="N33" s="122">
+      <c r="N33" s="126">
         <f>XIRR(D29:J29,D18:J18)</f>
         <v/>
       </c>
@@ -7104,7 +7186,7 @@
         </is>
       </c>
       <c r="C34" s="97" t="n"/>
-      <c r="D34" s="97">
+      <c r="D34" s="164">
         <f>+D13</f>
         <v/>
       </c>
@@ -7115,7 +7197,7 @@
         </is>
       </c>
       <c r="H34" s="97" t="n"/>
-      <c r="I34" s="97">
+      <c r="I34" s="164">
         <f>+D14</f>
         <v/>
       </c>
@@ -7133,7 +7215,7 @@
         </is>
       </c>
       <c r="C35" s="97" t="n"/>
-      <c r="D35" s="120">
+      <c r="D35" s="165">
         <f>D32+D33-D34</f>
         <v/>
       </c>
@@ -7144,18 +7226,18 @@
         </is>
       </c>
       <c r="H35" s="97" t="n"/>
-      <c r="I35" s="120">
+      <c r="I35" s="165">
         <f>I32+I33-I34</f>
         <v/>
       </c>
       <c r="J35" s="97" t="n"/>
-      <c r="L35" s="109" t="inlineStr">
+      <c r="L35" s="110" t="inlineStr">
         <is>
           <t>Market Value vs Intrinsic Value</t>
         </is>
       </c>
-      <c r="M35" s="110" t="n"/>
-      <c r="N35" s="110" t="n"/>
+      <c r="M35" s="111" t="n"/>
+      <c r="N35" s="111" t="n"/>
       <c r="O35" s="97" t="n"/>
     </row>
     <row r="36" ht="16" customHeight="1">
@@ -7166,7 +7248,7 @@
       <c r="E36" s="97" t="n"/>
       <c r="G36" s="97" t="n"/>
       <c r="H36" s="97" t="n"/>
-      <c r="I36" s="141" t="n"/>
+      <c r="I36" s="167" t="n"/>
       <c r="J36" s="97" t="n"/>
       <c r="L36" s="97" t="inlineStr">
         <is>
@@ -7174,7 +7256,7 @@
         </is>
       </c>
       <c r="M36" s="97" t="n"/>
-      <c r="N36" s="141">
+      <c r="N36" s="167">
         <f>I37</f>
         <v/>
       </c>
@@ -7188,7 +7270,7 @@
         </is>
       </c>
       <c r="C37" s="97" t="n"/>
-      <c r="D37" s="141">
+      <c r="D37" s="164">
         <f>D35/D12</f>
         <v/>
       </c>
@@ -7199,7 +7281,7 @@
         </is>
       </c>
       <c r="H37" s="97" t="n"/>
-      <c r="I37" s="141">
+      <c r="I37" s="164">
         <f>D11</f>
         <v/>
       </c>
@@ -7210,7 +7292,7 @@
         </is>
       </c>
       <c r="M37" s="97" t="n"/>
-      <c r="N37" s="141">
+      <c r="N37" s="167">
         <f>D37-I37</f>
         <v/>
       </c>
@@ -7232,7 +7314,7 @@
         </is>
       </c>
       <c r="M38" s="97" t="n"/>
-      <c r="N38" s="141">
+      <c r="N38" s="167">
         <f>SUM(N36:N37)</f>
         <v/>
       </c>
@@ -7269,23 +7351,23 @@
     </row>
     <row r="41" ht="16" customHeight="1">
       <c r="A41" s="97" t="n"/>
-      <c r="B41" s="109" t="inlineStr">
+      <c r="B41" s="110" t="inlineStr">
         <is>
           <t>Instructions</t>
         </is>
       </c>
-      <c r="C41" s="110" t="n"/>
-      <c r="D41" s="124" t="n"/>
-      <c r="E41" s="110" t="n"/>
-      <c r="F41" s="110" t="n"/>
-      <c r="G41" s="110" t="n"/>
-      <c r="H41" s="110" t="n"/>
-      <c r="I41" s="110" t="n"/>
-      <c r="J41" s="110" t="n"/>
-      <c r="K41" s="110" t="n"/>
-      <c r="L41" s="110" t="n"/>
-      <c r="M41" s="110" t="n"/>
-      <c r="N41" s="110" t="n"/>
+      <c r="C41" s="111" t="n"/>
+      <c r="D41" s="128" t="n"/>
+      <c r="E41" s="111" t="n"/>
+      <c r="F41" s="111" t="n"/>
+      <c r="G41" s="111" t="n"/>
+      <c r="H41" s="111" t="n"/>
+      <c r="I41" s="111" t="n"/>
+      <c r="J41" s="111" t="n"/>
+      <c r="K41" s="111" t="n"/>
+      <c r="L41" s="111" t="n"/>
+      <c r="M41" s="111" t="n"/>
+      <c r="N41" s="111" t="n"/>
       <c r="O41" s="97" t="n"/>
     </row>
     <row r="42" ht="16" customHeight="1">
@@ -7301,7 +7383,7 @@
       <c r="F42" s="97" t="n"/>
       <c r="G42" s="97" t="n"/>
       <c r="H42" s="97" t="n"/>
-      <c r="N42" s="125" t="inlineStr">
+      <c r="N42" s="129" t="inlineStr">
         <is>
           <t>This file is for educational purposes only. E&amp;OE</t>
         </is>
@@ -7326,7 +7408,7 @@
     </row>
     <row r="44" ht="16" customHeight="1">
       <c r="A44" s="97" t="n"/>
-      <c r="B44" s="126" t="inlineStr">
+      <c r="B44" s="130" t="inlineStr">
         <is>
           <t>There are two ways to find NWC:</t>
         </is>
@@ -7342,7 +7424,7 @@
     </row>
     <row r="45" ht="16" customHeight="1">
       <c r="A45" s="97" t="n"/>
-      <c r="B45" s="126" t="inlineStr">
+      <c r="B45" s="130" t="inlineStr">
         <is>
           <t>1. NWC = Current Assets (less cash) - Current Liabilities (less debt)</t>
         </is>
@@ -7358,7 +7440,7 @@
     </row>
     <row r="46" ht="16" customHeight="1">
       <c r="A46" s="97" t="n"/>
-      <c r="B46" s="126" t="inlineStr">
+      <c r="B46" s="130" t="inlineStr">
         <is>
           <t>2. NWC = Accounts Receivable + Inventory - Accounts Payable</t>
         </is>
@@ -7393,7 +7475,7 @@
       <c r="F48" s="97" t="n"/>
       <c r="G48" s="97" t="n"/>
       <c r="H48" s="97" t="n"/>
-      <c r="N48" s="127" t="inlineStr">
+      <c r="N48" s="131" t="inlineStr">
         <is>
           <t xml:space="preserve">Corporate Finance Institute® </t>
         </is>
@@ -7409,7 +7491,7 @@
       <c r="F49" s="97" t="n"/>
       <c r="G49" s="97" t="n"/>
       <c r="H49" s="97" t="n"/>
-      <c r="N49" s="128" t="inlineStr">
+      <c r="N49" s="132" t="inlineStr">
         <is>
           <t>https://corporatefinanceinstitute.com/</t>
         </is>

--- a/FICO/output/FICO_Completed_Model.xlsx
+++ b/FICO/output/FICO_Completed_Model.xlsx
@@ -471,7 +471,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="168">
+  <cellXfs count="169">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="1"/>
@@ -658,8 +658,8 @@
     <xf numFmtId="0" fontId="31" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="39" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="14" fontId="35" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="14" fontId="38" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="14" fontId="36" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="30" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="35" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="37" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="35" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -708,6 +708,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="174" fontId="9" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="174" fontId="38" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="174" fontId="40" fillId="8" borderId="2" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="166" fontId="40" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
@@ -724,12 +726,11 @@
     <xf numFmtId="174" fontId="38" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="31" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="174" fontId="35" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="175" fontId="35" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="175" fontId="38" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="174" fontId="36" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="174" fontId="30" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="174" fontId="37" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="174" fontId="30" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="174" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="174" fontId="30" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="174" fontId="38" fillId="7" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="173" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -2109,7 +2110,7 @@
       <c r="B12" s="74" t="n"/>
       <c r="C12" s="75" t="inlineStr">
         <is>
-          <t>FICO — CFI Template (Named-Range Inputs)</t>
+          <t>FICO — Model2.0 (3-Statement + DCF)</t>
         </is>
       </c>
       <c r="D12" s="74" t="n"/>
@@ -2277,7 +2278,7 @@
       <c r="B21" s="85" t="n"/>
       <c r="C21" s="85" t="inlineStr">
         <is>
-          <t>Open in Excel to recalculate. DCF EBIT/D&amp;A/CapEx/ΔNWC/TV are formulas linked to the 3-statement sheet (not hardcoded CSV). XNPV uses dates without year-fraction double-counting.</t>
+          <t>Model2.0: revenue fades (not straight-lined). DCF uses unlevered EBIT×t taxes, Gordon TV primary, mid-year XNPV dates, CapEx/ΔNWC/D&amp;A linked to 3-statement. Open in Excel to recalculate.</t>
         </is>
       </c>
       <c r="D21" s="85" t="n"/>
@@ -2672,19 +2673,19 @@
         <v/>
       </c>
       <c r="J7" s="137" t="n">
-        <v>0.143234</v>
+        <v>0.27</v>
       </c>
       <c r="K7" s="137" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="L7" s="137" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="M7" s="137" t="n">
         <v>0.1</v>
       </c>
-      <c r="L7" s="137" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="M7" s="137" t="n">
+      <c r="N7" s="137" t="n">
         <v>0.08</v>
-      </c>
-      <c r="N7" s="137" t="n">
-        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="8" hidden="1" outlineLevel="1">
@@ -2760,19 +2761,19 @@
         <v/>
       </c>
       <c r="J9" s="133" t="n">
-        <v>586511.1</v>
+        <v>651545.6</v>
       </c>
       <c r="K9" s="133" t="n">
-        <v>645162.2</v>
+        <v>749277.4</v>
       </c>
       <c r="L9" s="133" t="n">
-        <v>703226.8</v>
+        <v>839190.7</v>
       </c>
       <c r="M9" s="133" t="n">
-        <v>759484.9</v>
+        <v>923109.7</v>
       </c>
       <c r="N9" s="133" t="n">
-        <v>812648.8</v>
+        <v>996958.5</v>
       </c>
     </row>
     <row r="10" hidden="1" outlineLevel="1">
@@ -2804,19 +2805,19 @@
         <v/>
       </c>
       <c r="J10" s="133" t="n">
-        <v>215324.7</v>
+        <v>239200.7</v>
       </c>
       <c r="K10" s="133" t="n">
-        <v>236857.2</v>
+        <v>275080.8</v>
       </c>
       <c r="L10" s="133" t="n">
-        <v>258174.3</v>
+        <v>308090.5</v>
       </c>
       <c r="M10" s="133" t="n">
-        <v>278828.3</v>
+        <v>338899.5</v>
       </c>
       <c r="N10" s="133" t="n">
-        <v>298346.2</v>
+        <v>366011.5</v>
       </c>
     </row>
     <row r="11" hidden="1" outlineLevel="1">
@@ -3126,19 +3127,19 @@
         <v/>
       </c>
       <c r="J18" s="133" t="n">
-        <v>45051.4</v>
+        <v>50046.9</v>
       </c>
       <c r="K18" s="133" t="n">
-        <v>49556.6</v>
+        <v>57553.9</v>
       </c>
       <c r="L18" s="133" t="n">
-        <v>54016.7</v>
+        <v>64460.4</v>
       </c>
       <c r="M18" s="133" t="n">
-        <v>58338</v>
+        <v>70906.39999999999</v>
       </c>
       <c r="N18" s="133" t="n">
-        <v>62421.6</v>
+        <v>76578.89999999999</v>
       </c>
     </row>
     <row r="19" hidden="1" outlineLevel="1">
@@ -5272,20 +5273,20 @@
           <t>Accounts Receivable</t>
         </is>
       </c>
-      <c r="E85" s="149" t="n">
-        <v>5100.35</v>
-      </c>
-      <c r="F85" s="149" t="n">
-        <v>5904.3</v>
-      </c>
-      <c r="G85" s="149" t="n">
-        <v>6567.25</v>
-      </c>
-      <c r="H85" s="149" t="n">
-        <v>7117.05</v>
-      </c>
-      <c r="I85" s="149" t="n">
-        <v>7538.6</v>
+      <c r="E85" s="133" t="n">
+        <v>312107</v>
+      </c>
+      <c r="F85" s="133" t="n">
+        <v>322410</v>
+      </c>
+      <c r="G85" s="133" t="n">
+        <v>387947</v>
+      </c>
+      <c r="H85" s="133" t="n">
+        <v>426642</v>
+      </c>
+      <c r="I85" s="133" t="n">
+        <v>529148</v>
       </c>
       <c r="J85" s="141">
         <f>J42</f>
@@ -5314,20 +5315,20 @@
           <t>Inventory</t>
         </is>
       </c>
-      <c r="E86" s="149" t="n">
-        <v>7804.6</v>
-      </c>
-      <c r="F86" s="149" t="n">
-        <v>9600.800000000001</v>
-      </c>
-      <c r="G86" s="149" t="n">
-        <v>9824.6</v>
-      </c>
-      <c r="H86" s="149" t="n">
-        <v>10530.8</v>
-      </c>
-      <c r="I86" s="149" t="n">
-        <v>11342</v>
+      <c r="E86" s="133" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" s="133" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" s="133" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" s="133" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" s="133" t="n">
+        <v>0</v>
       </c>
       <c r="J86" s="141">
         <f>J43</f>
@@ -5356,20 +5357,20 @@
           <t>Accounts Payable</t>
         </is>
       </c>
-      <c r="E87" s="149" t="n">
-        <v>3902.3</v>
-      </c>
-      <c r="F87" s="149" t="n">
-        <v>4800.400000000001</v>
-      </c>
-      <c r="G87" s="149" t="n">
-        <v>4912.3</v>
-      </c>
-      <c r="H87" s="149" t="n">
-        <v>5265.400000000001</v>
-      </c>
-      <c r="I87" s="149" t="n">
-        <v>5671</v>
+      <c r="E87" s="133" t="n">
+        <v>20749</v>
+      </c>
+      <c r="F87" s="133" t="n">
+        <v>17273</v>
+      </c>
+      <c r="G87" s="133" t="n">
+        <v>19009</v>
+      </c>
+      <c r="H87" s="133" t="n">
+        <v>22473</v>
+      </c>
+      <c r="I87" s="133" t="n">
+        <v>32315</v>
       </c>
       <c r="J87" s="141">
         <f>J48</f>
@@ -5399,7 +5400,9 @@
         </is>
       </c>
       <c r="C88" s="5" t="n"/>
-      <c r="D88" s="28" t="n"/>
+      <c r="D88" s="150" t="n">
+        <v>311147</v>
+      </c>
       <c r="E88" s="151">
         <f>E85+E86-E87</f>
         <v/>
@@ -5513,38 +5516,42 @@
           <t>PPE Opening</t>
         </is>
       </c>
-      <c r="E92" s="149" t="n">
-        <v>50000</v>
-      </c>
-      <c r="F92" s="149" t="n">
-        <v>45500</v>
-      </c>
-      <c r="G92" s="149" t="n">
-        <v>42350</v>
-      </c>
-      <c r="H92" s="149" t="n">
-        <v>40145</v>
-      </c>
-      <c r="I92" s="149" t="n">
-        <v>38601.5</v>
-      </c>
-      <c r="J92" s="141">
-        <f>I95</f>
-        <v/>
-      </c>
-      <c r="K92" s="141">
+      <c r="E92" s="133" t="n">
+        <v>46419</v>
+      </c>
+      <c r="F92" s="152">
+        <f>E95</f>
+        <v/>
+      </c>
+      <c r="G92" s="152">
+        <f>F95</f>
+        <v/>
+      </c>
+      <c r="H92" s="152">
+        <f>G95</f>
+        <v/>
+      </c>
+      <c r="I92" s="152">
+        <f>H95</f>
+        <v/>
+      </c>
+      <c r="J92" s="152">
+        <f>I44</f>
+        <v/>
+      </c>
+      <c r="K92" s="152">
         <f>J95</f>
         <v/>
       </c>
-      <c r="L92" s="141">
+      <c r="L92" s="152">
         <f>K95</f>
         <v/>
       </c>
-      <c r="M92" s="141">
+      <c r="M92" s="152">
         <f>L95</f>
         <v/>
       </c>
-      <c r="N92" s="141">
+      <c r="N92" s="152">
         <f>M95</f>
         <v/>
       </c>
@@ -5555,20 +5562,20 @@
           <t>Plus Capex</t>
         </is>
       </c>
-      <c r="E93" s="149" t="n">
-        <v>15000</v>
-      </c>
-      <c r="F93" s="149" t="n">
-        <v>15000</v>
-      </c>
-      <c r="G93" s="149" t="n">
-        <v>15000</v>
-      </c>
-      <c r="H93" s="149" t="n">
-        <v>15000</v>
-      </c>
-      <c r="I93" s="149" t="n">
-        <v>15000</v>
+      <c r="E93" s="133" t="n">
+        <v>7569</v>
+      </c>
+      <c r="F93" s="133" t="n">
+        <v>6029</v>
+      </c>
+      <c r="G93" s="133" t="n">
+        <v>4237</v>
+      </c>
+      <c r="H93" s="133" t="n">
+        <v>25551</v>
+      </c>
+      <c r="I93" s="133" t="n">
+        <v>39407</v>
       </c>
       <c r="J93" s="141">
         <f>+J18</f>
@@ -5597,20 +5604,20 @@
           <t>Less Depreciation</t>
         </is>
       </c>
-      <c r="E94" s="149" t="n">
-        <v>19500</v>
-      </c>
-      <c r="F94" s="149" t="n">
-        <v>18150</v>
-      </c>
-      <c r="G94" s="149" t="n">
-        <v>17205</v>
-      </c>
-      <c r="H94" s="149" t="n">
-        <v>16543.5</v>
-      </c>
-      <c r="I94" s="149" t="n">
-        <v>16080.45</v>
+      <c r="E94" s="133" t="n">
+        <v>25592</v>
+      </c>
+      <c r="F94" s="133" t="n">
+        <v>20465</v>
+      </c>
+      <c r="G94" s="133" t="n">
+        <v>14638</v>
+      </c>
+      <c r="H94" s="133" t="n">
+        <v>13827</v>
+      </c>
+      <c r="I94" s="133" t="n">
+        <v>14952</v>
       </c>
       <c r="J94" s="141">
         <f>J92*J11</f>
@@ -5641,25 +5648,20 @@
       </c>
       <c r="C95" s="5" t="n"/>
       <c r="D95" s="28" t="n"/>
-      <c r="E95" s="151">
-        <f>E92+E93-E94</f>
-        <v/>
-      </c>
-      <c r="F95" s="151">
-        <f>F92+F93-F94</f>
-        <v/>
-      </c>
-      <c r="G95" s="151">
-        <f>G92+G93-G94</f>
-        <v/>
-      </c>
-      <c r="H95" s="151">
-        <f>H92+H93-H94</f>
-        <v/>
-      </c>
-      <c r="I95" s="151">
-        <f>I92+I93-I94</f>
-        <v/>
+      <c r="E95" s="153" t="n">
+        <v>27913</v>
+      </c>
+      <c r="F95" s="153" t="n">
+        <v>17580</v>
+      </c>
+      <c r="G95" s="153" t="n">
+        <v>10966</v>
+      </c>
+      <c r="H95" s="153" t="n">
+        <v>38465</v>
+      </c>
+      <c r="I95" s="153" t="n">
+        <v>67713</v>
       </c>
       <c r="J95" s="151">
         <f>J92+J93-J94</f>
@@ -6288,11 +6290,11 @@
       <c r="A5" s="97" t="n"/>
       <c r="B5" s="103" t="inlineStr">
         <is>
-          <t>Tax Rate</t>
+          <t>Tax Rate (unlevered / on EBIT)</t>
         </is>
       </c>
       <c r="C5" s="100" t="n"/>
-      <c r="D5" s="152" t="n">
+      <c r="D5" s="154" t="n">
         <v>0.1877023903712333</v>
       </c>
       <c r="E5" s="100" t="n"/>
@@ -6315,7 +6317,7 @@
         </is>
       </c>
       <c r="C6" s="97" t="n"/>
-      <c r="D6" s="152" t="n">
+      <c r="D6" s="154" t="n">
         <v>0.096</v>
       </c>
       <c r="E6" s="97" t="n"/>
@@ -6338,7 +6340,7 @@
         </is>
       </c>
       <c r="C7" s="97" t="n"/>
-      <c r="D7" s="152" t="n">
+      <c r="D7" s="154" t="n">
         <v>0.03</v>
       </c>
       <c r="E7" s="97" t="n"/>
@@ -6361,7 +6363,7 @@
         </is>
       </c>
       <c r="C8" s="97" t="n"/>
-      <c r="D8" s="153" t="n">
+      <c r="D8" s="155" t="n">
         <v>22</v>
       </c>
       <c r="E8" s="97" t="n"/>
@@ -6384,7 +6386,7 @@
         </is>
       </c>
       <c r="C9" s="97" t="n"/>
-      <c r="D9" s="154" t="n">
+      <c r="D9" s="156" t="n">
         <v>45930</v>
       </c>
       <c r="E9" s="97" t="n"/>
@@ -6407,7 +6409,7 @@
         </is>
       </c>
       <c r="C10" s="97" t="n"/>
-      <c r="D10" s="154" t="n">
+      <c r="D10" s="156" t="n">
         <v>46295</v>
       </c>
       <c r="E10" s="97" t="n"/>
@@ -6430,7 +6432,7 @@
         </is>
       </c>
       <c r="C11" s="97" t="n"/>
-      <c r="D11" s="155" t="n">
+      <c r="D11" s="157" t="n">
         <v>1046.23</v>
       </c>
       <c r="E11" s="97" t="n"/>
@@ -6453,7 +6455,7 @@
         </is>
       </c>
       <c r="C12" s="97" t="n"/>
-      <c r="D12" s="156" t="n">
+      <c r="D12" s="158" t="n">
         <v>21597.635</v>
       </c>
       <c r="E12" s="97" t="n"/>
@@ -6476,7 +6478,7 @@
         </is>
       </c>
       <c r="C13" s="97" t="n"/>
-      <c r="D13" s="156" t="n">
+      <c r="D13" s="158" t="n">
         <v>5582389</v>
       </c>
       <c r="E13" s="97" t="n"/>
@@ -6499,7 +6501,7 @@
         </is>
       </c>
       <c r="C14" s="97" t="n"/>
-      <c r="D14" s="156" t="n">
+      <c r="D14" s="158" t="n">
         <v>304537</v>
       </c>
       <c r="E14" s="97" t="n"/>
@@ -6522,7 +6524,7 @@
         </is>
       </c>
       <c r="C15" s="97" t="n"/>
-      <c r="D15" s="157">
+      <c r="D15" s="159">
         <f>'3 Statement Model'!J68</f>
         <v/>
       </c>
@@ -6563,23 +6565,23 @@
           <t>Entry</t>
         </is>
       </c>
-      <c r="E17" s="158">
+      <c r="E17" s="160">
         <f>YEAR(E18)</f>
         <v/>
       </c>
-      <c r="F17" s="158">
+      <c r="F17" s="160">
         <f>YEAR(F18)</f>
         <v/>
       </c>
-      <c r="G17" s="158">
+      <c r="G17" s="160">
         <f>YEAR(G18)</f>
         <v/>
       </c>
-      <c r="H17" s="158">
+      <c r="H17" s="160">
         <f>YEAR(H18)</f>
         <v/>
       </c>
-      <c r="I17" s="158">
+      <c r="I17" s="160">
         <f>YEAR(I18)</f>
         <v/>
       </c>
@@ -6591,7 +6593,7 @@
       <c r="K17" s="97" t="n"/>
       <c r="L17" s="114" t="inlineStr">
         <is>
-          <t>Terminal value cross-check</t>
+          <t>Terminal value methods</t>
         </is>
       </c>
       <c r="M17" s="111" t="n"/>
@@ -6602,46 +6604,46 @@
       <c r="A18" s="97" t="n"/>
       <c r="B18" s="97" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Date (mid-year convention)</t>
         </is>
       </c>
       <c r="C18" s="97" t="n"/>
-      <c r="D18" s="159">
+      <c r="D18" s="161">
         <f>D9</f>
         <v/>
       </c>
-      <c r="E18" s="160">
-        <f>DATE(YEAR($D$10)+E19,6,30)</f>
-        <v/>
-      </c>
-      <c r="F18" s="160">
-        <f>DATE(YEAR($D$10)+F19,6,30)</f>
-        <v/>
-      </c>
-      <c r="G18" s="160">
-        <f>DATE(YEAR($D$10)+G19,6,30)</f>
-        <v/>
-      </c>
-      <c r="H18" s="160">
-        <f>DATE(YEAR($D$10)+H19,6,30)</f>
-        <v/>
-      </c>
-      <c r="I18" s="160">
-        <f>DATE(YEAR($D$10)+I19,6,30)</f>
-        <v/>
-      </c>
-      <c r="J18" s="161">
+      <c r="E18" s="162">
+        <f>DATE(YEAR($D$10)+E19,3,31)</f>
+        <v/>
+      </c>
+      <c r="F18" s="162">
+        <f>DATE(YEAR($D$10)+F19,3,31)</f>
+        <v/>
+      </c>
+      <c r="G18" s="162">
+        <f>DATE(YEAR($D$10)+G19,3,31)</f>
+        <v/>
+      </c>
+      <c r="H18" s="162">
+        <f>DATE(YEAR($D$10)+H19,3,31)</f>
+        <v/>
+      </c>
+      <c r="I18" s="162">
+        <f>DATE(YEAR($D$10)+I19,3,31)</f>
+        <v/>
+      </c>
+      <c r="J18" s="163">
         <f>I18</f>
         <v/>
       </c>
       <c r="K18" s="97" t="n"/>
       <c r="L18" s="97" t="inlineStr">
         <is>
-          <t>Exit EV/EBITDA TV (in J27)</t>
-        </is>
-      </c>
-      <c r="M18" s="162">
-        <f>($I$21+$I$23)*$D$8</f>
+          <t>Gordon TV (in J27) — primary</t>
+        </is>
+      </c>
+      <c r="M18" s="159">
+        <f>J27</f>
         <v/>
       </c>
       <c r="N18" s="97">
@@ -6659,22 +6661,22 @@
       </c>
       <c r="C19" s="118" t="n"/>
       <c r="D19" s="115" t="n"/>
-      <c r="E19" s="163" t="n">
+      <c r="E19" s="164" t="n">
         <v>0</v>
       </c>
-      <c r="F19" s="159">
+      <c r="F19" s="161">
         <f>E19+1</f>
         <v/>
       </c>
-      <c r="G19" s="159">
+      <c r="G19" s="161">
         <f>F19+1</f>
         <v/>
       </c>
-      <c r="H19" s="159">
+      <c r="H19" s="161">
         <f>G19+1</f>
         <v/>
       </c>
-      <c r="I19" s="159">
+      <c r="I19" s="161">
         <f>H19+1</f>
         <v/>
       </c>
@@ -6682,11 +6684,11 @@
       <c r="K19" s="97" t="n"/>
       <c r="L19" s="97" t="inlineStr">
         <is>
-          <t>Gordon TV: UFCF_n*(1+g)/(WACC-g)</t>
-        </is>
-      </c>
-      <c r="M19" s="162">
-        <f>IF(($D$6-$D$7)&lt;=0,"WACC must exceed g",$I$26*(1+$D$7)/($D$6-$D$7))</f>
+          <t>Exit EV/EBITDA cross-check</t>
+        </is>
+      </c>
+      <c r="M19" s="159">
+        <f>($I$21+$I$23)*$D$8</f>
         <v/>
       </c>
       <c r="N19" s="121">
@@ -6699,28 +6701,28 @@
       <c r="A20" s="97" t="n"/>
       <c r="B20" s="118" t="inlineStr">
         <is>
-          <t>Year Fraction (display only; XNPV uses dates — not applied to CF)</t>
+          <t>Year Fraction (display only; not applied to CF)</t>
         </is>
       </c>
       <c r="C20" s="97" t="n"/>
       <c r="D20" s="97" t="n"/>
-      <c r="E20" s="159">
+      <c r="E20" s="161">
         <f>YEARFRAC(D18,E18)</f>
         <v/>
       </c>
-      <c r="F20" s="159">
+      <c r="F20" s="161">
         <f>YEARFRAC(E18,F18)</f>
         <v/>
       </c>
-      <c r="G20" s="159">
+      <c r="G20" s="161">
         <f>YEARFRAC(F18,G18)</f>
         <v/>
       </c>
-      <c r="H20" s="159">
+      <c r="H20" s="161">
         <f>YEARFRAC(G18,H18)</f>
         <v/>
       </c>
-      <c r="I20" s="159">
+      <c r="I20" s="161">
         <f>YEARFRAC(H18,I18)</f>
         <v/>
       </c>
@@ -6728,10 +6730,13 @@
       <c r="K20" s="97" t="n"/>
       <c r="L20" s="97" t="inlineStr">
         <is>
-          <t>Switch J27 to Gordon: copy M19 → J27</t>
-        </is>
-      </c>
-      <c r="M20" s="97" t="n"/>
+          <t>Implied exit multiple vs Gordon</t>
+        </is>
+      </c>
+      <c r="M20" s="159">
+        <f>IF(($I$21+$I$23)=0,0,J27/($I$21+$I$23))</f>
+        <v/>
+      </c>
       <c r="N20" s="123">
         <f>AVERAGE(N18:N19)</f>
         <v/>
@@ -6747,23 +6752,23 @@
       </c>
       <c r="C21" s="97" t="n"/>
       <c r="D21" s="97" t="n"/>
-      <c r="E21" s="157">
+      <c r="E21" s="159">
         <f>'3 Statement Model'!J26-'3 Statement Model'!J28-'3 Statement Model'!J29-'3 Statement Model'!J30</f>
         <v/>
       </c>
-      <c r="F21" s="157">
+      <c r="F21" s="159">
         <f>'3 Statement Model'!K26-'3 Statement Model'!K28-'3 Statement Model'!K29-'3 Statement Model'!K30</f>
         <v/>
       </c>
-      <c r="G21" s="157">
+      <c r="G21" s="159">
         <f>'3 Statement Model'!L26-'3 Statement Model'!L28-'3 Statement Model'!L29-'3 Statement Model'!L30</f>
         <v/>
       </c>
-      <c r="H21" s="157">
+      <c r="H21" s="159">
         <f>'3 Statement Model'!M26-'3 Statement Model'!M28-'3 Statement Model'!M29-'3 Statement Model'!M30</f>
         <v/>
       </c>
-      <c r="I21" s="157">
+      <c r="I21" s="159">
         <f>'3 Statement Model'!N26-'3 Statement Model'!N28-'3 Statement Model'!N29-'3 Statement Model'!N30</f>
         <v/>
       </c>
@@ -6778,28 +6783,28 @@
       <c r="A22" s="97" t="n"/>
       <c r="B22" s="97" t="inlineStr">
         <is>
-          <t>Less: Cash Taxes</t>
+          <t>Less: Unlevered Cash Taxes (EBIT×t)</t>
         </is>
       </c>
       <c r="C22" s="97" t="n"/>
       <c r="D22" s="97" t="n"/>
-      <c r="E22" s="164">
+      <c r="E22" s="159">
         <f>E21*$D$5</f>
         <v/>
       </c>
-      <c r="F22" s="164">
+      <c r="F22" s="159">
         <f>F21*$D$5</f>
         <v/>
       </c>
-      <c r="G22" s="164">
+      <c r="G22" s="159">
         <f>G21*$D$5</f>
         <v/>
       </c>
-      <c r="H22" s="164">
+      <c r="H22" s="159">
         <f>H21*$D$5</f>
         <v/>
       </c>
-      <c r="I22" s="164">
+      <c r="I22" s="159">
         <f>I21*$D$5</f>
         <v/>
       </c>
@@ -6819,23 +6824,23 @@
       </c>
       <c r="C23" s="97" t="n"/>
       <c r="D23" s="97" t="n"/>
-      <c r="E23" s="157">
+      <c r="E23" s="159">
         <f>'3 Statement Model'!J30</f>
         <v/>
       </c>
-      <c r="F23" s="157">
+      <c r="F23" s="159">
         <f>'3 Statement Model'!K30</f>
         <v/>
       </c>
-      <c r="G23" s="157">
+      <c r="G23" s="159">
         <f>'3 Statement Model'!L30</f>
         <v/>
       </c>
-      <c r="H23" s="157">
+      <c r="H23" s="159">
         <f>'3 Statement Model'!M30</f>
         <v/>
       </c>
-      <c r="I23" s="157">
+      <c r="I23" s="159">
         <f>'3 Statement Model'!N30</f>
         <v/>
       </c>
@@ -6855,23 +6860,23 @@
       </c>
       <c r="C24" s="97" t="n"/>
       <c r="D24" s="97" t="n"/>
-      <c r="E24" s="157">
+      <c r="E24" s="159">
         <f>'3 Statement Model'!J68</f>
         <v/>
       </c>
-      <c r="F24" s="157">
+      <c r="F24" s="159">
         <f>'3 Statement Model'!K68</f>
         <v/>
       </c>
-      <c r="G24" s="157">
+      <c r="G24" s="159">
         <f>'3 Statement Model'!L68</f>
         <v/>
       </c>
-      <c r="H24" s="157">
+      <c r="H24" s="159">
         <f>'3 Statement Model'!M68</f>
         <v/>
       </c>
-      <c r="I24" s="157">
+      <c r="I24" s="159">
         <f>'3 Statement Model'!N68</f>
         <v/>
       </c>
@@ -6891,23 +6896,23 @@
       </c>
       <c r="C25" s="97" t="n"/>
       <c r="D25" s="97" t="n"/>
-      <c r="E25" s="157">
+      <c r="E25" s="159">
         <f>'3 Statement Model'!J64</f>
         <v/>
       </c>
-      <c r="F25" s="157">
+      <c r="F25" s="159">
         <f>'3 Statement Model'!K64</f>
         <v/>
       </c>
-      <c r="G25" s="157">
+      <c r="G25" s="159">
         <f>'3 Statement Model'!L64</f>
         <v/>
       </c>
-      <c r="H25" s="157">
+      <c r="H25" s="159">
         <f>'3 Statement Model'!M64</f>
         <v/>
       </c>
-      <c r="I25" s="157">
+      <c r="I25" s="159">
         <f>'3 Statement Model'!N64</f>
         <v/>
       </c>
@@ -6958,11 +6963,11 @@
       <c r="A27" s="97" t="n"/>
       <c r="B27" s="97" t="inlineStr">
         <is>
-          <t>(Entry)/Exit TV</t>
+          <t>(Entry)/Exit TV — Gordon</t>
         </is>
       </c>
       <c r="C27" s="97" t="n"/>
-      <c r="D27" s="164">
+      <c r="D27" s="166">
         <f>-I35</f>
         <v/>
       </c>
@@ -6971,8 +6976,8 @@
       <c r="G27" s="97" t="n"/>
       <c r="H27" s="97" t="n"/>
       <c r="I27" s="97" t="n"/>
-      <c r="J27" s="157">
-        <f>($I$21+$I$23)*$D$8</f>
+      <c r="J27" s="159">
+        <f>IF(($D$6-$D$7)&lt;=0,"WACC must exceed g",$I$26*(1+$D$7)/($D$6-$D$7))</f>
         <v/>
       </c>
       <c r="K27" s="97" t="n"/>
@@ -6992,27 +6997,27 @@
       <c r="D28" s="165" t="n">
         <v>0</v>
       </c>
-      <c r="E28" s="166">
+      <c r="E28" s="167">
         <f>E27+E26</f>
         <v/>
       </c>
-      <c r="F28" s="166">
+      <c r="F28" s="167">
         <f>F27+F26</f>
         <v/>
       </c>
-      <c r="G28" s="166">
+      <c r="G28" s="167">
         <f>G27+G26</f>
         <v/>
       </c>
-      <c r="H28" s="166">
+      <c r="H28" s="167">
         <f>H27+H26</f>
         <v/>
       </c>
-      <c r="I28" s="166">
+      <c r="I28" s="167">
         <f>I27+I26</f>
         <v/>
       </c>
-      <c r="J28" s="166">
+      <c r="J28" s="167">
         <f>J27+J26</f>
         <v/>
       </c>
@@ -7030,31 +7035,31 @@
         </is>
       </c>
       <c r="C29" s="97" t="n"/>
-      <c r="D29" s="164">
+      <c r="D29" s="166">
         <f>D27+D26</f>
         <v/>
       </c>
-      <c r="E29" s="157">
+      <c r="E29" s="159">
         <f>E27+E26</f>
         <v/>
       </c>
-      <c r="F29" s="157">
+      <c r="F29" s="159">
         <f>F27+F26</f>
         <v/>
       </c>
-      <c r="G29" s="157">
+      <c r="G29" s="159">
         <f>G27+G26</f>
         <v/>
       </c>
-      <c r="H29" s="157">
+      <c r="H29" s="159">
         <f>H27+H26</f>
         <v/>
       </c>
-      <c r="I29" s="157">
+      <c r="I29" s="159">
         <f>I27+I26</f>
         <v/>
       </c>
-      <c r="J29" s="157">
+      <c r="J29" s="159">
         <f>J27</f>
         <v/>
       </c>
@@ -7110,11 +7115,11 @@
       <c r="A32" s="97" t="n"/>
       <c r="B32" s="97" t="inlineStr">
         <is>
-          <t>Enterprise Value</t>
+          <t>Enterprise Value (XNPV, mid-year dates)</t>
         </is>
       </c>
       <c r="C32" s="97" t="n"/>
-      <c r="D32" s="164">
+      <c r="D32" s="159">
         <f>XNPV(D6,D28:J28,D18:J18)</f>
         <v/>
       </c>
@@ -7125,7 +7130,7 @@
         </is>
       </c>
       <c r="H32" s="97" t="n"/>
-      <c r="I32" s="164">
+      <c r="I32" s="166">
         <f>D12*D11</f>
         <v/>
       </c>
@@ -7150,7 +7155,7 @@
         </is>
       </c>
       <c r="C33" s="97" t="n"/>
-      <c r="D33" s="164">
+      <c r="D33" s="166">
         <f>+D14</f>
         <v/>
       </c>
@@ -7161,7 +7166,7 @@
         </is>
       </c>
       <c r="H33" s="97" t="n"/>
-      <c r="I33" s="164">
+      <c r="I33" s="166">
         <f>D13</f>
         <v/>
       </c>
@@ -7186,7 +7191,7 @@
         </is>
       </c>
       <c r="C34" s="97" t="n"/>
-      <c r="D34" s="164">
+      <c r="D34" s="166">
         <f>+D13</f>
         <v/>
       </c>
@@ -7197,7 +7202,7 @@
         </is>
       </c>
       <c r="H34" s="97" t="n"/>
-      <c r="I34" s="164">
+      <c r="I34" s="166">
         <f>+D14</f>
         <v/>
       </c>
@@ -7248,7 +7253,7 @@
       <c r="E36" s="97" t="n"/>
       <c r="G36" s="97" t="n"/>
       <c r="H36" s="97" t="n"/>
-      <c r="I36" s="167" t="n"/>
+      <c r="I36" s="168" t="n"/>
       <c r="J36" s="97" t="n"/>
       <c r="L36" s="97" t="inlineStr">
         <is>
@@ -7256,7 +7261,7 @@
         </is>
       </c>
       <c r="M36" s="97" t="n"/>
-      <c r="N36" s="167">
+      <c r="N36" s="168">
         <f>I37</f>
         <v/>
       </c>
@@ -7270,7 +7275,7 @@
         </is>
       </c>
       <c r="C37" s="97" t="n"/>
-      <c r="D37" s="164">
+      <c r="D37" s="166">
         <f>D35/D12</f>
         <v/>
       </c>
@@ -7281,7 +7286,7 @@
         </is>
       </c>
       <c r="H37" s="97" t="n"/>
-      <c r="I37" s="164">
+      <c r="I37" s="166">
         <f>D11</f>
         <v/>
       </c>
@@ -7292,7 +7297,7 @@
         </is>
       </c>
       <c r="M37" s="97" t="n"/>
-      <c r="N37" s="167">
+      <c r="N37" s="168">
         <f>D37-I37</f>
         <v/>
       </c>
@@ -7314,7 +7319,7 @@
         </is>
       </c>
       <c r="M38" s="97" t="n"/>
-      <c r="N38" s="167">
+      <c r="N38" s="168">
         <f>SUM(N36:N37)</f>
         <v/>
       </c>

--- a/FICO/output/FICO_Completed_Model.xlsx
+++ b/FICO/output/FICO_Completed_Model.xlsx
@@ -685,14 +685,15 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="174" fontId="40" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="174" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="174" fontId="13" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="40" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="1" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="1" fontId="13" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="174" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="166" fontId="40" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="2"/>
     <xf numFmtId="174" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="174" fontId="40" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="166" fontId="40" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="174" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="174" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
@@ -703,12 +704,11 @@
     <xf numFmtId="174" fontId="6" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="174" fontId="6" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="174" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="174" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="174" fontId="38" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="174" fontId="40" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="174" fontId="9" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="174" fontId="38" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="174" fontId="40" fillId="8" borderId="2" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="166" fontId="40" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
@@ -2760,19 +2760,19 @@
         <f>I28</f>
         <v/>
       </c>
-      <c r="J9" s="133" t="n">
+      <c r="J9" s="139" t="n">
         <v>651545.6</v>
       </c>
-      <c r="K9" s="133" t="n">
+      <c r="K9" s="139" t="n">
         <v>749277.4</v>
       </c>
-      <c r="L9" s="133" t="n">
+      <c r="L9" s="139" t="n">
         <v>839190.7</v>
       </c>
-      <c r="M9" s="133" t="n">
+      <c r="M9" s="139" t="n">
         <v>923109.7</v>
       </c>
-      <c r="N9" s="133" t="n">
+      <c r="N9" s="139" t="n">
         <v>996958.5</v>
       </c>
     </row>
@@ -2804,19 +2804,19 @@
         <f>I29</f>
         <v/>
       </c>
-      <c r="J10" s="133" t="n">
+      <c r="J10" s="139" t="n">
         <v>239200.7</v>
       </c>
-      <c r="K10" s="133" t="n">
+      <c r="K10" s="139" t="n">
         <v>275080.8</v>
       </c>
-      <c r="L10" s="133" t="n">
+      <c r="L10" s="139" t="n">
         <v>308090.5</v>
       </c>
-      <c r="M10" s="133" t="n">
+      <c r="M10" s="139" t="n">
         <v>338899.5</v>
       </c>
-      <c r="N10" s="133" t="n">
+      <c r="N10" s="139" t="n">
         <v>366011.5</v>
       </c>
     </row>
@@ -2998,19 +2998,19 @@
         <f>I42/I24*365</f>
         <v/>
       </c>
-      <c r="J15" s="133" t="n">
+      <c r="J15" s="139" t="n">
         <v>97</v>
       </c>
-      <c r="K15" s="133" t="n">
+      <c r="K15" s="139" t="n">
         <v>97</v>
       </c>
-      <c r="L15" s="133" t="n">
+      <c r="L15" s="139" t="n">
         <v>97</v>
       </c>
-      <c r="M15" s="133" t="n">
+      <c r="M15" s="139" t="n">
         <v>97</v>
       </c>
-      <c r="N15" s="133" t="n">
+      <c r="N15" s="139" t="n">
         <v>97</v>
       </c>
     </row>
@@ -3041,19 +3041,19 @@
         <f>I43/I25*365</f>
         <v/>
       </c>
-      <c r="J16" s="133" t="n">
+      <c r="J16" s="139" t="n">
         <v>0</v>
       </c>
-      <c r="K16" s="133" t="n">
+      <c r="K16" s="139" t="n">
         <v>0</v>
       </c>
-      <c r="L16" s="133" t="n">
+      <c r="L16" s="139" t="n">
         <v>0</v>
       </c>
-      <c r="M16" s="133" t="n">
+      <c r="M16" s="139" t="n">
         <v>0</v>
       </c>
-      <c r="N16" s="133" t="n">
+      <c r="N16" s="139" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3084,19 +3084,19 @@
         <f>I48/I25*365</f>
         <v/>
       </c>
-      <c r="J17" s="133" t="n">
+      <c r="J17" s="139" t="n">
         <v>33</v>
       </c>
-      <c r="K17" s="133" t="n">
+      <c r="K17" s="139" t="n">
         <v>33</v>
       </c>
-      <c r="L17" s="133" t="n">
+      <c r="L17" s="139" t="n">
         <v>33</v>
       </c>
-      <c r="M17" s="133" t="n">
+      <c r="M17" s="139" t="n">
         <v>33</v>
       </c>
-      <c r="N17" s="133" t="n">
+      <c r="N17" s="139" t="n">
         <v>33</v>
       </c>
     </row>
@@ -3126,19 +3126,19 @@
         <f>I68</f>
         <v/>
       </c>
-      <c r="J18" s="133" t="n">
+      <c r="J18" s="139" t="n">
         <v>50046.9</v>
       </c>
-      <c r="K18" s="133" t="n">
+      <c r="K18" s="139" t="n">
         <v>57553.9</v>
       </c>
-      <c r="L18" s="133" t="n">
+      <c r="L18" s="139" t="n">
         <v>64460.4</v>
       </c>
-      <c r="M18" s="133" t="n">
+      <c r="M18" s="139" t="n">
         <v>70906.39999999999</v>
       </c>
-      <c r="N18" s="133" t="n">
+      <c r="N18" s="139" t="n">
         <v>76578.89999999999</v>
       </c>
     </row>
@@ -3168,19 +3168,19 @@
         <f>I99</f>
         <v/>
       </c>
-      <c r="J19" s="139" t="n">
+      <c r="J19" s="140" t="n">
         <v>0</v>
       </c>
-      <c r="K19" s="139" t="n">
+      <c r="K19" s="140" t="n">
         <v>0</v>
       </c>
-      <c r="L19" s="139" t="n">
+      <c r="L19" s="140" t="n">
         <v>0</v>
       </c>
-      <c r="M19" s="139" t="n">
+      <c r="M19" s="140" t="n">
         <v>0</v>
       </c>
-      <c r="N19" s="139" t="n">
+      <c r="N19" s="140" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3210,19 +3210,19 @@
         <f>I73</f>
         <v/>
       </c>
-      <c r="J20" s="139" t="n">
+      <c r="J20" s="140" t="n">
         <v>0</v>
       </c>
-      <c r="K20" s="139" t="n">
+      <c r="K20" s="140" t="n">
         <v>0</v>
       </c>
-      <c r="L20" s="139" t="n">
+      <c r="L20" s="140" t="n">
         <v>0</v>
       </c>
-      <c r="M20" s="139" t="n">
+      <c r="M20" s="140" t="n">
         <v>0</v>
       </c>
-      <c r="N20" s="139" t="n">
+      <c r="N20" s="140" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3277,38 +3277,38 @@
       </c>
       <c r="C24" s="18" t="n"/>
       <c r="D24" s="46" t="n"/>
-      <c r="E24" s="133" t="n">
+      <c r="E24" s="139" t="n">
         <v>1316536</v>
       </c>
-      <c r="F24" s="133" t="n">
+      <c r="F24" s="139" t="n">
         <v>1377270</v>
       </c>
-      <c r="G24" s="133" t="n">
+      <c r="G24" s="139" t="n">
         <v>1513557</v>
       </c>
-      <c r="H24" s="133" t="n">
+      <c r="H24" s="139" t="n">
         <v>1717526</v>
       </c>
-      <c r="I24" s="133" t="n">
+      <c r="I24" s="139" t="n">
         <v>1990869</v>
       </c>
-      <c r="J24" s="140">
+      <c r="J24" s="141">
         <f>I24*(1+J7)</f>
         <v/>
       </c>
-      <c r="K24" s="140">
+      <c r="K24" s="141">
         <f>J24*(1+K7)</f>
         <v/>
       </c>
-      <c r="L24" s="140">
+      <c r="L24" s="141">
         <f>K24*(1+L7)</f>
         <v/>
       </c>
-      <c r="M24" s="140">
+      <c r="M24" s="141">
         <f>L24*(1+M7)</f>
         <v/>
       </c>
-      <c r="N24" s="140">
+      <c r="N24" s="141">
         <f>M24*(1+N7)</f>
         <v/>
       </c>
@@ -3321,38 +3321,38 @@
       </c>
       <c r="C25" s="19" t="n"/>
       <c r="D25" s="47" t="n"/>
-      <c r="E25" s="133" t="n">
+      <c r="E25" s="139" t="n">
         <v>332462</v>
       </c>
-      <c r="F25" s="133" t="n">
+      <c r="F25" s="139" t="n">
         <v>302174</v>
       </c>
-      <c r="G25" s="133" t="n">
+      <c r="G25" s="139" t="n">
         <v>311053</v>
       </c>
-      <c r="H25" s="133" t="n">
+      <c r="H25" s="139" t="n">
         <v>348206</v>
       </c>
-      <c r="I25" s="133" t="n">
+      <c r="I25" s="139" t="n">
         <v>353722</v>
       </c>
-      <c r="J25" s="141">
+      <c r="J25" s="142">
         <f>J24*J8</f>
         <v/>
       </c>
-      <c r="K25" s="141">
+      <c r="K25" s="142">
         <f>K24*K8</f>
         <v/>
       </c>
-      <c r="L25" s="141">
+      <c r="L25" s="142">
         <f>L24*L8</f>
         <v/>
       </c>
-      <c r="M25" s="141">
+      <c r="M25" s="142">
         <f>M24*M8</f>
         <v/>
       </c>
-      <c r="N25" s="141">
+      <c r="N25" s="142">
         <f>N24*N8</f>
         <v/>
       </c>
@@ -3365,43 +3365,43 @@
       </c>
       <c r="C26" s="4" t="n"/>
       <c r="D26" s="22" t="n"/>
-      <c r="E26" s="142">
+      <c r="E26" s="143">
         <f>E24-E25</f>
         <v/>
       </c>
-      <c r="F26" s="142">
+      <c r="F26" s="143">
         <f>F24-F25</f>
         <v/>
       </c>
-      <c r="G26" s="142">
+      <c r="G26" s="143">
         <f>G24-G25</f>
         <v/>
       </c>
-      <c r="H26" s="142">
+      <c r="H26" s="143">
         <f>H24-H25</f>
         <v/>
       </c>
-      <c r="I26" s="142">
+      <c r="I26" s="143">
         <f>I24-I25</f>
         <v/>
       </c>
-      <c r="J26" s="142">
+      <c r="J26" s="143">
         <f>J24-J25</f>
         <v/>
       </c>
-      <c r="K26" s="142">
+      <c r="K26" s="143">
         <f>K24-K25</f>
         <v/>
       </c>
-      <c r="L26" s="142">
+      <c r="L26" s="143">
         <f>L24-L25</f>
         <v/>
       </c>
-      <c r="M26" s="142">
+      <c r="M26" s="143">
         <f>M24-M25</f>
         <v/>
       </c>
-      <c r="N26" s="142">
+      <c r="N26" s="143">
         <f>N24-N25</f>
         <v/>
       </c>
@@ -3431,38 +3431,38 @@
           <t>Salaries and Benefits</t>
         </is>
       </c>
-      <c r="E28" s="133" t="n">
+      <c r="E28" s="139" t="n">
         <v>396281</v>
       </c>
-      <c r="F28" s="133" t="n">
+      <c r="F28" s="139" t="n">
         <v>383863</v>
       </c>
-      <c r="G28" s="133" t="n">
+      <c r="G28" s="139" t="n">
         <v>400565</v>
       </c>
-      <c r="H28" s="133" t="n">
+      <c r="H28" s="139" t="n">
         <v>462834</v>
       </c>
-      <c r="I28" s="133" t="n">
+      <c r="I28" s="139" t="n">
         <v>513028</v>
       </c>
-      <c r="J28" s="141">
+      <c r="J28" s="142">
         <f>J9</f>
         <v/>
       </c>
-      <c r="K28" s="141">
+      <c r="K28" s="142">
         <f>K9</f>
         <v/>
       </c>
-      <c r="L28" s="141">
+      <c r="L28" s="142">
         <f>L9</f>
         <v/>
       </c>
-      <c r="M28" s="141">
+      <c r="M28" s="142">
         <f>M9</f>
         <v/>
       </c>
-      <c r="N28" s="141">
+      <c r="N28" s="142">
         <f>N9</f>
         <v/>
       </c>
@@ -3473,38 +3473,38 @@
           <t>Rent and Overhead</t>
         </is>
       </c>
-      <c r="E29" s="133" t="n">
+      <c r="E29" s="139" t="n">
         <v>171231</v>
       </c>
-      <c r="F29" s="133" t="n">
+      <c r="F29" s="139" t="n">
         <v>146758</v>
       </c>
-      <c r="G29" s="133" t="n">
+      <c r="G29" s="139" t="n">
         <v>159950</v>
       </c>
-      <c r="H29" s="133" t="n">
+      <c r="H29" s="139" t="n">
         <v>171940</v>
       </c>
-      <c r="I29" s="133" t="n">
+      <c r="I29" s="139" t="n">
         <v>188347</v>
       </c>
-      <c r="J29" s="141">
+      <c r="J29" s="142">
         <f>J10</f>
         <v/>
       </c>
-      <c r="K29" s="141">
+      <c r="K29" s="142">
         <f>K10</f>
         <v/>
       </c>
-      <c r="L29" s="141">
+      <c r="L29" s="142">
         <f>L10</f>
         <v/>
       </c>
-      <c r="M29" s="141">
+      <c r="M29" s="142">
         <f>M10</f>
         <v/>
       </c>
-      <c r="N29" s="141">
+      <c r="N29" s="142">
         <f>N10</f>
         <v/>
       </c>
@@ -3515,38 +3515,38 @@
           <t>Depreciation &amp; Amortization</t>
         </is>
       </c>
-      <c r="E30" s="133" t="n">
+      <c r="E30" s="139" t="n">
         <v>25592</v>
       </c>
-      <c r="F30" s="133" t="n">
+      <c r="F30" s="139" t="n">
         <v>20465</v>
       </c>
-      <c r="G30" s="133" t="n">
+      <c r="G30" s="139" t="n">
         <v>14638</v>
       </c>
-      <c r="H30" s="133" t="n">
+      <c r="H30" s="139" t="n">
         <v>13827</v>
       </c>
-      <c r="I30" s="133" t="n">
+      <c r="I30" s="139" t="n">
         <v>14952</v>
       </c>
-      <c r="J30" s="141">
+      <c r="J30" s="142">
         <f>J94</f>
         <v/>
       </c>
-      <c r="K30" s="141">
+      <c r="K30" s="142">
         <f>K94</f>
         <v/>
       </c>
-      <c r="L30" s="141">
+      <c r="L30" s="142">
         <f>L94</f>
         <v/>
       </c>
-      <c r="M30" s="141">
+      <c r="M30" s="142">
         <f>M94</f>
         <v/>
       </c>
-      <c r="N30" s="141">
+      <c r="N30" s="142">
         <f>N94</f>
         <v/>
       </c>
@@ -3559,38 +3559,38 @@
       </c>
       <c r="C31" s="2" t="n"/>
       <c r="D31" s="24" t="n"/>
-      <c r="E31" s="143" t="n">
+      <c r="E31" s="144" t="n">
         <v>40092</v>
       </c>
-      <c r="F31" s="143" t="n">
+      <c r="F31" s="144" t="n">
         <v>68967</v>
       </c>
-      <c r="G31" s="143" t="n">
+      <c r="G31" s="144" t="n">
         <v>95546</v>
       </c>
-      <c r="H31" s="143" t="n">
+      <c r="H31" s="144" t="n">
         <v>105638</v>
       </c>
-      <c r="I31" s="143" t="n">
+      <c r="I31" s="144" t="n">
         <v>133647</v>
       </c>
-      <c r="J31" s="144">
+      <c r="J31" s="145">
         <f>J101</f>
         <v/>
       </c>
-      <c r="K31" s="144">
+      <c r="K31" s="145">
         <f>K101</f>
         <v/>
       </c>
-      <c r="L31" s="144">
+      <c r="L31" s="145">
         <f>L101</f>
         <v/>
       </c>
-      <c r="M31" s="144">
+      <c r="M31" s="145">
         <f>M101</f>
         <v/>
       </c>
-      <c r="N31" s="144">
+      <c r="N31" s="145">
         <f>N101</f>
         <v/>
       </c>
@@ -3603,43 +3603,43 @@
       </c>
       <c r="C32" s="19" t="n"/>
       <c r="D32" s="47" t="n"/>
-      <c r="E32" s="145">
+      <c r="E32" s="146">
         <f>SUM(E28:E31)</f>
         <v/>
       </c>
-      <c r="F32" s="145">
+      <c r="F32" s="146">
         <f>SUM(F28:F31)</f>
         <v/>
       </c>
-      <c r="G32" s="145">
+      <c r="G32" s="146">
         <f>SUM(G28:G31)</f>
         <v/>
       </c>
-      <c r="H32" s="145">
+      <c r="H32" s="146">
         <f>SUM(H28:H31)</f>
         <v/>
       </c>
-      <c r="I32" s="145">
+      <c r="I32" s="146">
         <f>SUM(I28:I31)</f>
         <v/>
       </c>
-      <c r="J32" s="145">
+      <c r="J32" s="146">
         <f>SUM(J28:J31)</f>
         <v/>
       </c>
-      <c r="K32" s="145">
+      <c r="K32" s="146">
         <f>SUM(K28:K31)</f>
         <v/>
       </c>
-      <c r="L32" s="145">
+      <c r="L32" s="146">
         <f>SUM(L28:L31)</f>
         <v/>
       </c>
-      <c r="M32" s="145">
+      <c r="M32" s="146">
         <f>SUM(M28:M31)</f>
         <v/>
       </c>
-      <c r="N32" s="145">
+      <c r="N32" s="146">
         <f>SUM(N28:N31)</f>
         <v/>
       </c>
@@ -3652,43 +3652,43 @@
       </c>
       <c r="C33" s="4" t="n"/>
       <c r="D33" s="22" t="n"/>
-      <c r="E33" s="142">
+      <c r="E33" s="143">
         <f>E26-E32</f>
         <v/>
       </c>
-      <c r="F33" s="142">
+      <c r="F33" s="143">
         <f>F26-F32</f>
         <v/>
       </c>
-      <c r="G33" s="142">
+      <c r="G33" s="143">
         <f>G26-G32</f>
         <v/>
       </c>
-      <c r="H33" s="142">
+      <c r="H33" s="143">
         <f>H26-H32</f>
         <v/>
       </c>
-      <c r="I33" s="142">
+      <c r="I33" s="143">
         <f>I26-I32</f>
         <v/>
       </c>
-      <c r="J33" s="142">
+      <c r="J33" s="143">
         <f>J26-J32</f>
         <v/>
       </c>
-      <c r="K33" s="142">
+      <c r="K33" s="143">
         <f>K26-K32</f>
         <v/>
       </c>
-      <c r="L33" s="142">
+      <c r="L33" s="143">
         <f>L26-L32</f>
         <v/>
       </c>
-      <c r="M33" s="142">
+      <c r="M33" s="143">
         <f>M26-M32</f>
         <v/>
       </c>
-      <c r="N33" s="142">
+      <c r="N33" s="143">
         <f>N26-N32</f>
         <v/>
       </c>
@@ -3716,38 +3716,38 @@
       </c>
       <c r="C35" s="19" t="n"/>
       <c r="D35" s="47" t="n"/>
-      <c r="E35" s="133" t="n">
+      <c r="E35" s="139" t="n">
         <v>81058</v>
       </c>
-      <c r="F35" s="133" t="n">
+      <c r="F35" s="139" t="n">
         <v>97768</v>
       </c>
-      <c r="G35" s="133" t="n">
+      <c r="G35" s="139" t="n">
         <v>124249</v>
       </c>
-      <c r="H35" s="133" t="n">
+      <c r="H35" s="139" t="n">
         <v>129214</v>
       </c>
-      <c r="I35" s="133" t="n">
+      <c r="I35" s="139" t="n">
         <v>150649</v>
       </c>
-      <c r="J35" s="141">
+      <c r="J35" s="142">
         <f>J33*J13</f>
         <v/>
       </c>
-      <c r="K35" s="141">
+      <c r="K35" s="142">
         <f>K33*K13</f>
         <v/>
       </c>
-      <c r="L35" s="141">
+      <c r="L35" s="142">
         <f>L33*L13</f>
         <v/>
       </c>
-      <c r="M35" s="141">
+      <c r="M35" s="142">
         <f>M33*M13</f>
         <v/>
       </c>
-      <c r="N35" s="141">
+      <c r="N35" s="142">
         <f>N33*N13</f>
         <v/>
       </c>
@@ -3760,43 +3760,43 @@
       </c>
       <c r="C36" s="39" t="n"/>
       <c r="D36" s="40" t="n"/>
-      <c r="E36" s="146">
+      <c r="E36" s="147">
         <f>E33-E35</f>
         <v/>
       </c>
-      <c r="F36" s="146">
+      <c r="F36" s="147">
         <f>F33-F35</f>
         <v/>
       </c>
-      <c r="G36" s="146">
+      <c r="G36" s="147">
         <f>G33-G35</f>
         <v/>
       </c>
-      <c r="H36" s="146">
+      <c r="H36" s="147">
         <f>H33-H35</f>
         <v/>
       </c>
-      <c r="I36" s="146">
+      <c r="I36" s="147">
         <f>I33-I35</f>
         <v/>
       </c>
-      <c r="J36" s="146">
+      <c r="J36" s="147">
         <f>J33-J35</f>
         <v/>
       </c>
-      <c r="K36" s="146">
+      <c r="K36" s="147">
         <f>K33-K35</f>
         <v/>
       </c>
-      <c r="L36" s="146">
+      <c r="L36" s="147">
         <f>L33-L35</f>
         <v/>
       </c>
-      <c r="M36" s="146">
+      <c r="M36" s="147">
         <f>M33-M35</f>
         <v/>
       </c>
-      <c r="N36" s="146">
+      <c r="N36" s="147">
         <f>N33-N35</f>
         <v/>
       </c>
@@ -3857,38 +3857,38 @@
           <t>Cash</t>
         </is>
       </c>
-      <c r="E41" s="133" t="n">
+      <c r="E41" s="139" t="n">
         <v>195354</v>
       </c>
-      <c r="F41" s="133" t="n">
+      <c r="F41" s="139" t="n">
         <v>133202</v>
       </c>
-      <c r="G41" s="133" t="n">
+      <c r="G41" s="139" t="n">
         <v>136778</v>
       </c>
-      <c r="H41" s="133" t="n">
+      <c r="H41" s="139" t="n">
         <v>150667</v>
       </c>
-      <c r="I41" s="133" t="n">
+      <c r="I41" s="139" t="n">
         <v>134136</v>
       </c>
-      <c r="J41" s="141">
+      <c r="J41" s="142">
         <f>J78</f>
         <v/>
       </c>
-      <c r="K41" s="141">
+      <c r="K41" s="142">
         <f>K78</f>
         <v/>
       </c>
-      <c r="L41" s="141">
+      <c r="L41" s="142">
         <f>L78</f>
         <v/>
       </c>
-      <c r="M41" s="141">
+      <c r="M41" s="142">
         <f>M78</f>
         <v/>
       </c>
-      <c r="N41" s="141">
+      <c r="N41" s="142">
         <f>N78</f>
         <v/>
       </c>
@@ -3899,38 +3899,38 @@
           <t>Accounts Receivable</t>
         </is>
       </c>
-      <c r="E42" s="133" t="n">
+      <c r="E42" s="139" t="n">
         <v>312107</v>
       </c>
-      <c r="F42" s="133" t="n">
+      <c r="F42" s="139" t="n">
         <v>322410</v>
       </c>
-      <c r="G42" s="133" t="n">
+      <c r="G42" s="139" t="n">
         <v>387947</v>
       </c>
-      <c r="H42" s="133" t="n">
+      <c r="H42" s="139" t="n">
         <v>426642</v>
       </c>
-      <c r="I42" s="133" t="n">
+      <c r="I42" s="139" t="n">
         <v>529148</v>
       </c>
-      <c r="J42" s="141">
+      <c r="J42" s="142">
         <f>J24*J15/365</f>
         <v/>
       </c>
-      <c r="K42" s="141">
+      <c r="K42" s="142">
         <f>K24*K15/365</f>
         <v/>
       </c>
-      <c r="L42" s="141">
+      <c r="L42" s="142">
         <f>L24*L15/365</f>
         <v/>
       </c>
-      <c r="M42" s="141">
+      <c r="M42" s="142">
         <f>M24*M15/365</f>
         <v/>
       </c>
-      <c r="N42" s="141">
+      <c r="N42" s="142">
         <f>N24*N15/365</f>
         <v/>
       </c>
@@ -3941,38 +3941,38 @@
           <t>Inventory</t>
         </is>
       </c>
-      <c r="E43" s="133" t="n">
+      <c r="E43" s="139" t="n">
         <v>0</v>
       </c>
-      <c r="F43" s="133" t="n">
+      <c r="F43" s="139" t="n">
         <v>0</v>
       </c>
-      <c r="G43" s="133" t="n">
+      <c r="G43" s="139" t="n">
         <v>0</v>
       </c>
-      <c r="H43" s="133" t="n">
+      <c r="H43" s="139" t="n">
         <v>0</v>
       </c>
-      <c r="I43" s="133" t="n">
+      <c r="I43" s="139" t="n">
         <v>0</v>
       </c>
-      <c r="J43" s="141">
+      <c r="J43" s="142">
         <f>J25*J16/365</f>
         <v/>
       </c>
-      <c r="K43" s="141">
+      <c r="K43" s="142">
         <f>K25*K16/365</f>
         <v/>
       </c>
-      <c r="L43" s="141">
+      <c r="L43" s="142">
         <f>L25*L16/365</f>
         <v/>
       </c>
-      <c r="M43" s="141">
+      <c r="M43" s="142">
         <f>M25*M16/365</f>
         <v/>
       </c>
-      <c r="N43" s="141">
+      <c r="N43" s="142">
         <f>N25*N16/365</f>
         <v/>
       </c>
@@ -3983,38 +3983,38 @@
           <t>Property &amp; Equipment</t>
         </is>
       </c>
-      <c r="E44" s="133" t="n">
+      <c r="E44" s="139" t="n">
         <v>27913</v>
       </c>
-      <c r="F44" s="133" t="n">
+      <c r="F44" s="139" t="n">
         <v>17580</v>
       </c>
-      <c r="G44" s="133" t="n">
+      <c r="G44" s="139" t="n">
         <v>10966</v>
       </c>
-      <c r="H44" s="133" t="n">
+      <c r="H44" s="139" t="n">
         <v>38465</v>
       </c>
-      <c r="I44" s="133" t="n">
+      <c r="I44" s="139" t="n">
         <v>67713</v>
       </c>
-      <c r="J44" s="141">
+      <c r="J44" s="142">
         <f>J95</f>
         <v/>
       </c>
-      <c r="K44" s="141">
+      <c r="K44" s="142">
         <f>K95</f>
         <v/>
       </c>
-      <c r="L44" s="141">
+      <c r="L44" s="142">
         <f>L95</f>
         <v/>
       </c>
-      <c r="M44" s="141">
+      <c r="M44" s="142">
         <f>M95</f>
         <v/>
       </c>
-      <c r="N44" s="141">
+      <c r="N44" s="142">
         <f>N95</f>
         <v/>
       </c>
@@ -4027,43 +4027,43 @@
       </c>
       <c r="C45" s="39" t="n"/>
       <c r="D45" s="40" t="n"/>
-      <c r="E45" s="146">
+      <c r="E45" s="147">
         <f>SUM(E41:E44)</f>
         <v/>
       </c>
-      <c r="F45" s="146">
+      <c r="F45" s="147">
         <f>SUM(F41:F44)</f>
         <v/>
       </c>
-      <c r="G45" s="146">
+      <c r="G45" s="147">
         <f>SUM(G41:G44)</f>
         <v/>
       </c>
-      <c r="H45" s="146">
+      <c r="H45" s="147">
         <f>SUM(H41:H44)</f>
         <v/>
       </c>
-      <c r="I45" s="146">
+      <c r="I45" s="147">
         <f>SUM(I41:I44)</f>
         <v/>
       </c>
-      <c r="J45" s="146">
+      <c r="J45" s="147">
         <f>SUM(J41:J44)</f>
         <v/>
       </c>
-      <c r="K45" s="146">
+      <c r="K45" s="147">
         <f>SUM(K41:K44)</f>
         <v/>
       </c>
-      <c r="L45" s="146">
+      <c r="L45" s="147">
         <f>SUM(L41:L44)</f>
         <v/>
       </c>
-      <c r="M45" s="146">
+      <c r="M45" s="147">
         <f>SUM(M41:M44)</f>
         <v/>
       </c>
-      <c r="N45" s="146">
+      <c r="N45" s="147">
         <f>SUM(N41:N44)</f>
         <v/>
       </c>
@@ -4101,38 +4101,38 @@
           <t>Accounts Payable</t>
         </is>
       </c>
-      <c r="E48" s="133" t="n">
+      <c r="E48" s="139" t="n">
         <v>20749</v>
       </c>
-      <c r="F48" s="133" t="n">
+      <c r="F48" s="139" t="n">
         <v>17273</v>
       </c>
-      <c r="G48" s="133" t="n">
+      <c r="G48" s="139" t="n">
         <v>19009</v>
       </c>
-      <c r="H48" s="133" t="n">
+      <c r="H48" s="139" t="n">
         <v>22473</v>
       </c>
-      <c r="I48" s="133" t="n">
+      <c r="I48" s="139" t="n">
         <v>32315</v>
       </c>
-      <c r="J48" s="141">
+      <c r="J48" s="142">
         <f>J25*J17/365</f>
         <v/>
       </c>
-      <c r="K48" s="141">
+      <c r="K48" s="142">
         <f>K25*K17/365</f>
         <v/>
       </c>
-      <c r="L48" s="141">
+      <c r="L48" s="142">
         <f>L25*L17/365</f>
         <v/>
       </c>
-      <c r="M48" s="141">
+      <c r="M48" s="142">
         <f>M25*M17/365</f>
         <v/>
       </c>
-      <c r="N48" s="141">
+      <c r="N48" s="142">
         <f>N25*N17/365</f>
         <v/>
       </c>
@@ -4143,38 +4143,38 @@
           <t>Debt</t>
         </is>
       </c>
-      <c r="E49" s="133" t="n">
+      <c r="E49" s="139" t="n">
         <v>1259018</v>
       </c>
-      <c r="F49" s="133" t="n">
+      <c r="F49" s="139" t="n">
         <v>1853669</v>
       </c>
-      <c r="G49" s="133" t="n">
+      <c r="G49" s="139" t="n">
         <v>1861658</v>
       </c>
-      <c r="H49" s="133" t="n">
+      <c r="H49" s="139" t="n">
         <v>2209021</v>
       </c>
-      <c r="I49" s="133" t="n">
+      <c r="I49" s="139" t="n">
         <v>3055691</v>
       </c>
-      <c r="J49" s="141">
+      <c r="J49" s="142">
         <f>J100</f>
         <v/>
       </c>
-      <c r="K49" s="141">
+      <c r="K49" s="142">
         <f>K100</f>
         <v/>
       </c>
-      <c r="L49" s="141">
+      <c r="L49" s="142">
         <f>L100</f>
         <v/>
       </c>
-      <c r="M49" s="141">
+      <c r="M49" s="142">
         <f>M100</f>
         <v/>
       </c>
-      <c r="N49" s="141">
+      <c r="N49" s="142">
         <f>N100</f>
         <v/>
       </c>
@@ -4187,43 +4187,43 @@
       </c>
       <c r="C50" s="4" t="n"/>
       <c r="D50" s="22" t="n"/>
-      <c r="E50" s="142">
+      <c r="E50" s="143">
         <f>SUM(E48:E49)</f>
         <v/>
       </c>
-      <c r="F50" s="142">
+      <c r="F50" s="143">
         <f>SUM(F48:F49)</f>
         <v/>
       </c>
-      <c r="G50" s="142">
+      <c r="G50" s="143">
         <f>SUM(G48:G49)</f>
         <v/>
       </c>
-      <c r="H50" s="142">
+      <c r="H50" s="143">
         <f>SUM(H48:H49)</f>
         <v/>
       </c>
-      <c r="I50" s="142">
+      <c r="I50" s="143">
         <f>SUM(I48:I49)</f>
         <v/>
       </c>
-      <c r="J50" s="142">
+      <c r="J50" s="143">
         <f>SUM(J48:J49)</f>
         <v/>
       </c>
-      <c r="K50" s="142">
+      <c r="K50" s="143">
         <f>SUM(K48:K49)</f>
         <v/>
       </c>
-      <c r="L50" s="142">
+      <c r="L50" s="143">
         <f>SUM(L48:L49)</f>
         <v/>
       </c>
-      <c r="M50" s="142">
+      <c r="M50" s="143">
         <f>SUM(M48:M49)</f>
         <v/>
       </c>
-      <c r="N50" s="142">
+      <c r="N50" s="143">
         <f>SUM(N48:N49)</f>
         <v/>
       </c>
@@ -4246,38 +4246,38 @@
           <t>Equity Capital</t>
         </is>
       </c>
-      <c r="E52" s="133" t="n">
+      <c r="E52" s="139" t="n">
         <v>-744393</v>
       </c>
-      <c r="F52" s="133" t="n">
+      <c r="F52" s="139" t="n">
         <v>-1397750</v>
       </c>
-      <c r="G52" s="133" t="n">
+      <c r="G52" s="139" t="n">
         <v>-1344976</v>
       </c>
-      <c r="H52" s="133" t="n">
+      <c r="H52" s="139" t="n">
         <v>-1615720</v>
       </c>
-      <c r="I52" s="133" t="n">
+      <c r="I52" s="139" t="n">
         <v>-2357009</v>
       </c>
-      <c r="J52" s="141">
+      <c r="J52" s="142">
         <f>I52+J20</f>
         <v/>
       </c>
-      <c r="K52" s="141">
+      <c r="K52" s="142">
         <f>J52+K20</f>
         <v/>
       </c>
-      <c r="L52" s="141">
+      <c r="L52" s="142">
         <f>K52+L20</f>
         <v/>
       </c>
-      <c r="M52" s="141">
+      <c r="M52" s="142">
         <f>L52+M20</f>
         <v/>
       </c>
-      <c r="N52" s="141">
+      <c r="N52" s="142">
         <f>M52+N20</f>
         <v/>
       </c>
@@ -4288,38 +4288,38 @@
           <t>Retained Earnings</t>
         </is>
       </c>
-      <c r="E53" s="133" t="n">
+      <c r="E53" s="139" t="n">
         <v>0</v>
       </c>
-      <c r="F53" s="133" t="n">
+      <c r="F53" s="139" t="n">
         <v>0</v>
       </c>
-      <c r="G53" s="133" t="n">
+      <c r="G53" s="139" t="n">
         <v>0</v>
       </c>
-      <c r="H53" s="133" t="n">
+      <c r="H53" s="139" t="n">
         <v>0</v>
       </c>
-      <c r="I53" s="133" t="n">
+      <c r="I53" s="139" t="n">
         <v>0</v>
       </c>
-      <c r="J53" s="141">
+      <c r="J53" s="142">
         <f>I53+J36</f>
         <v/>
       </c>
-      <c r="K53" s="141">
+      <c r="K53" s="142">
         <f>J53+K36</f>
         <v/>
       </c>
-      <c r="L53" s="141">
+      <c r="L53" s="142">
         <f>K53+L36</f>
         <v/>
       </c>
-      <c r="M53" s="141">
+      <c r="M53" s="142">
         <f>L53+M36</f>
         <v/>
       </c>
-      <c r="N53" s="141">
+      <c r="N53" s="142">
         <f>M53+N36</f>
         <v/>
       </c>
@@ -4332,43 +4332,43 @@
       </c>
       <c r="C54" s="8" t="n"/>
       <c r="D54" s="26" t="n"/>
-      <c r="E54" s="147">
+      <c r="E54" s="148">
         <f>SUM(E52:E53)</f>
         <v/>
       </c>
-      <c r="F54" s="147">
+      <c r="F54" s="148">
         <f>SUM(F52:F53)</f>
         <v/>
       </c>
-      <c r="G54" s="147">
+      <c r="G54" s="148">
         <f>SUM(G52:G53)</f>
         <v/>
       </c>
-      <c r="H54" s="147">
+      <c r="H54" s="148">
         <f>SUM(H52:H53)</f>
         <v/>
       </c>
-      <c r="I54" s="147">
+      <c r="I54" s="148">
         <f>SUM(I52:I53)</f>
         <v/>
       </c>
-      <c r="J54" s="147">
+      <c r="J54" s="148">
         <f>SUM(J52:J53)</f>
         <v/>
       </c>
-      <c r="K54" s="147">
+      <c r="K54" s="148">
         <f>SUM(K52:K53)</f>
         <v/>
       </c>
-      <c r="L54" s="147">
+      <c r="L54" s="148">
         <f>SUM(L52:L53)</f>
         <v/>
       </c>
-      <c r="M54" s="147">
+      <c r="M54" s="148">
         <f>SUM(M52:M53)</f>
         <v/>
       </c>
-      <c r="N54" s="147">
+      <c r="N54" s="148">
         <f>SUM(N52:N53)</f>
         <v/>
       </c>
@@ -4381,43 +4381,43 @@
       </c>
       <c r="C55" s="39" t="n"/>
       <c r="D55" s="40" t="n"/>
-      <c r="E55" s="146">
+      <c r="E55" s="147">
         <f>E50+E54</f>
         <v/>
       </c>
-      <c r="F55" s="146">
+      <c r="F55" s="147">
         <f>F50+F54</f>
         <v/>
       </c>
-      <c r="G55" s="146">
+      <c r="G55" s="147">
         <f>G50+G54</f>
         <v/>
       </c>
-      <c r="H55" s="146">
+      <c r="H55" s="147">
         <f>H50+H54</f>
         <v/>
       </c>
-      <c r="I55" s="146">
+      <c r="I55" s="147">
         <f>I50+I54</f>
         <v/>
       </c>
-      <c r="J55" s="146">
+      <c r="J55" s="147">
         <f>J50+J54</f>
         <v/>
       </c>
-      <c r="K55" s="146">
+      <c r="K55" s="147">
         <f>K50+K54</f>
         <v/>
       </c>
-      <c r="L55" s="146">
+      <c r="L55" s="147">
         <f>L50+L54</f>
         <v/>
       </c>
-      <c r="M55" s="146">
+      <c r="M55" s="147">
         <f>M50+M54</f>
         <v/>
       </c>
-      <c r="N55" s="146">
+      <c r="N55" s="147">
         <f>N50+N54</f>
         <v/>
       </c>
@@ -4442,43 +4442,43 @@
       </c>
       <c r="C57" s="9" t="n"/>
       <c r="D57" s="27" t="n"/>
-      <c r="E57" s="148">
+      <c r="E57" s="149">
         <f>E55-E45</f>
         <v/>
       </c>
-      <c r="F57" s="148">
+      <c r="F57" s="149">
         <f>F55-F45</f>
         <v/>
       </c>
-      <c r="G57" s="148">
+      <c r="G57" s="149">
         <f>G55-G45</f>
         <v/>
       </c>
-      <c r="H57" s="148">
+      <c r="H57" s="149">
         <f>H55-H45</f>
         <v/>
       </c>
-      <c r="I57" s="148">
+      <c r="I57" s="149">
         <f>I55-I45</f>
         <v/>
       </c>
-      <c r="J57" s="148">
+      <c r="J57" s="149">
         <f>J55-J45</f>
         <v/>
       </c>
-      <c r="K57" s="148">
+      <c r="K57" s="149">
         <f>K55-K45</f>
         <v/>
       </c>
-      <c r="L57" s="148">
+      <c r="L57" s="149">
         <f>L55-L45</f>
         <v/>
       </c>
-      <c r="M57" s="148">
+      <c r="M57" s="149">
         <f>M55-M45</f>
         <v/>
       </c>
-      <c r="N57" s="148">
+      <c r="N57" s="149">
         <f>N55-N45</f>
         <v/>
       </c>
@@ -4542,43 +4542,43 @@
           <t>Net Earnings</t>
         </is>
       </c>
-      <c r="E62" s="141">
+      <c r="E62" s="142">
         <f>E36</f>
         <v/>
       </c>
-      <c r="F62" s="141">
+      <c r="F62" s="142">
         <f>F36</f>
         <v/>
       </c>
-      <c r="G62" s="141">
+      <c r="G62" s="142">
         <f>G36</f>
         <v/>
       </c>
-      <c r="H62" s="141">
+      <c r="H62" s="142">
         <f>H36</f>
         <v/>
       </c>
-      <c r="I62" s="141">
+      <c r="I62" s="142">
         <f>I36</f>
         <v/>
       </c>
-      <c r="J62" s="141">
+      <c r="J62" s="142">
         <f>J36</f>
         <v/>
       </c>
-      <c r="K62" s="141">
+      <c r="K62" s="142">
         <f>K36</f>
         <v/>
       </c>
-      <c r="L62" s="141">
+      <c r="L62" s="142">
         <f>L36</f>
         <v/>
       </c>
-      <c r="M62" s="141">
+      <c r="M62" s="142">
         <f>M36</f>
         <v/>
       </c>
-      <c r="N62" s="141">
+      <c r="N62" s="142">
         <f>N36</f>
         <v/>
       </c>
@@ -4589,43 +4589,43 @@
           <t>Plus: Depreciation &amp; Amortization</t>
         </is>
       </c>
-      <c r="E63" s="141">
+      <c r="E63" s="142">
         <f>+E30</f>
         <v/>
       </c>
-      <c r="F63" s="141">
+      <c r="F63" s="142">
         <f>+F30</f>
         <v/>
       </c>
-      <c r="G63" s="141">
+      <c r="G63" s="142">
         <f>+G30</f>
         <v/>
       </c>
-      <c r="H63" s="141">
+      <c r="H63" s="142">
         <f>+H30</f>
         <v/>
       </c>
-      <c r="I63" s="141">
+      <c r="I63" s="142">
         <f>+I30</f>
         <v/>
       </c>
-      <c r="J63" s="141">
+      <c r="J63" s="142">
         <f>+J30</f>
         <v/>
       </c>
-      <c r="K63" s="141">
+      <c r="K63" s="142">
         <f>+K30</f>
         <v/>
       </c>
-      <c r="L63" s="141">
+      <c r="L63" s="142">
         <f>+L30</f>
         <v/>
       </c>
-      <c r="M63" s="141">
+      <c r="M63" s="142">
         <f>+M30</f>
         <v/>
       </c>
-      <c r="N63" s="141">
+      <c r="N63" s="142">
         <f>+N30</f>
         <v/>
       </c>
@@ -4636,38 +4636,38 @@
           <t>Less: Changes in Working Capital</t>
         </is>
       </c>
-      <c r="E64" s="133" t="n">
+      <c r="E64" s="139" t="n">
         <v>0</v>
       </c>
-      <c r="F64" s="133" t="n">
+      <c r="F64" s="139" t="n">
         <v>13779</v>
       </c>
-      <c r="G64" s="133" t="n">
+      <c r="G64" s="139" t="n">
         <v>63801</v>
       </c>
-      <c r="H64" s="133" t="n">
+      <c r="H64" s="139" t="n">
         <v>35231</v>
       </c>
-      <c r="I64" s="133" t="n">
+      <c r="I64" s="139" t="n">
         <v>92664</v>
       </c>
-      <c r="J64" s="141">
+      <c r="J64" s="142">
         <f>J89</f>
         <v/>
       </c>
-      <c r="K64" s="141">
+      <c r="K64" s="142">
         <f>K89</f>
         <v/>
       </c>
-      <c r="L64" s="141">
+      <c r="L64" s="142">
         <f>L89</f>
         <v/>
       </c>
-      <c r="M64" s="141">
+      <c r="M64" s="142">
         <f>M89</f>
         <v/>
       </c>
-      <c r="N64" s="141">
+      <c r="N64" s="142">
         <f>N89</f>
         <v/>
       </c>
@@ -4680,43 +4680,43 @@
       </c>
       <c r="C65" s="5" t="n"/>
       <c r="D65" s="28" t="n"/>
-      <c r="E65" s="142">
+      <c r="E65" s="143">
         <f>E62+E63-E64</f>
         <v/>
       </c>
-      <c r="F65" s="142">
+      <c r="F65" s="143">
         <f>F62+F63-F64</f>
         <v/>
       </c>
-      <c r="G65" s="142">
+      <c r="G65" s="143">
         <f>G62+G63-G64</f>
         <v/>
       </c>
-      <c r="H65" s="142">
+      <c r="H65" s="143">
         <f>H62+H63-H64</f>
         <v/>
       </c>
-      <c r="I65" s="142">
+      <c r="I65" s="143">
         <f>I62+I63-I64</f>
         <v/>
       </c>
-      <c r="J65" s="142">
+      <c r="J65" s="143">
         <f>J62+J63-J64</f>
         <v/>
       </c>
-      <c r="K65" s="142">
+      <c r="K65" s="143">
         <f>K62+K63-K64</f>
         <v/>
       </c>
-      <c r="L65" s="142">
+      <c r="L65" s="143">
         <f>L62+L63-L64</f>
         <v/>
       </c>
-      <c r="M65" s="142">
+      <c r="M65" s="143">
         <f>M62+M63-M64</f>
         <v/>
       </c>
-      <c r="N65" s="142">
+      <c r="N65" s="143">
         <f>N62+N63-N64</f>
         <v/>
       </c>
@@ -4759,38 +4759,38 @@
           <t>Investments in Property &amp; Equipment</t>
         </is>
       </c>
-      <c r="E68" s="133" t="n">
+      <c r="E68" s="139" t="n">
         <v>7569</v>
       </c>
-      <c r="F68" s="133" t="n">
+      <c r="F68" s="139" t="n">
         <v>6029</v>
       </c>
-      <c r="G68" s="133" t="n">
+      <c r="G68" s="139" t="n">
         <v>4237</v>
       </c>
-      <c r="H68" s="133" t="n">
+      <c r="H68" s="139" t="n">
         <v>25551</v>
       </c>
-      <c r="I68" s="133" t="n">
+      <c r="I68" s="139" t="n">
         <v>39407</v>
       </c>
-      <c r="J68" s="141">
+      <c r="J68" s="142">
         <f>J18</f>
         <v/>
       </c>
-      <c r="K68" s="141">
+      <c r="K68" s="142">
         <f>K18</f>
         <v/>
       </c>
-      <c r="L68" s="141">
+      <c r="L68" s="142">
         <f>L18</f>
         <v/>
       </c>
-      <c r="M68" s="141">
+      <c r="M68" s="142">
         <f>M18</f>
         <v/>
       </c>
-      <c r="N68" s="141">
+      <c r="N68" s="142">
         <f>N18</f>
         <v/>
       </c>
@@ -4803,43 +4803,43 @@
       </c>
       <c r="C69" s="5" t="n"/>
       <c r="D69" s="28" t="n"/>
-      <c r="E69" s="142">
+      <c r="E69" s="143">
         <f>SUM(E68)</f>
         <v/>
       </c>
-      <c r="F69" s="142">
+      <c r="F69" s="143">
         <f>SUM(F68)</f>
         <v/>
       </c>
-      <c r="G69" s="142">
+      <c r="G69" s="143">
         <f>SUM(G68)</f>
         <v/>
       </c>
-      <c r="H69" s="142">
+      <c r="H69" s="143">
         <f>SUM(H68)</f>
         <v/>
       </c>
-      <c r="I69" s="142">
+      <c r="I69" s="143">
         <f>SUM(I68)</f>
         <v/>
       </c>
-      <c r="J69" s="142">
+      <c r="J69" s="143">
         <f>SUM(J68)</f>
         <v/>
       </c>
-      <c r="K69" s="142">
+      <c r="K69" s="143">
         <f>SUM(K68)</f>
         <v/>
       </c>
-      <c r="L69" s="142">
+      <c r="L69" s="143">
         <f>SUM(L68)</f>
         <v/>
       </c>
-      <c r="M69" s="142">
+      <c r="M69" s="143">
         <f>SUM(M68)</f>
         <v/>
       </c>
-      <c r="N69" s="142">
+      <c r="N69" s="143">
         <f>SUM(N68)</f>
         <v/>
       </c>
@@ -4882,38 +4882,38 @@
           <t>Issuance (repayment) of debt</t>
         </is>
       </c>
-      <c r="E72" s="133" t="n">
-        <v>0</v>
-      </c>
-      <c r="F72" s="133" t="n">
+      <c r="E72" s="139" t="n">
+        <v>519583</v>
+      </c>
+      <c r="F72" s="139" t="n">
         <v>594651</v>
       </c>
-      <c r="G72" s="133" t="n">
+      <c r="G72" s="139" t="n">
         <v>7989</v>
       </c>
-      <c r="H72" s="133" t="n">
+      <c r="H72" s="139" t="n">
         <v>347363</v>
       </c>
-      <c r="I72" s="133" t="n">
+      <c r="I72" s="139" t="n">
         <v>846670</v>
       </c>
-      <c r="J72" s="141">
+      <c r="J72" s="142">
         <f>J19</f>
         <v/>
       </c>
-      <c r="K72" s="141">
+      <c r="K72" s="142">
         <f>K19</f>
         <v/>
       </c>
-      <c r="L72" s="141">
+      <c r="L72" s="142">
         <f>L19</f>
         <v/>
       </c>
-      <c r="M72" s="141">
+      <c r="M72" s="142">
         <f>M19</f>
         <v/>
       </c>
-      <c r="N72" s="141">
+      <c r="N72" s="142">
         <f>N19</f>
         <v/>
       </c>
@@ -4924,38 +4924,38 @@
           <t>Issuance (repayment) of equity</t>
         </is>
       </c>
-      <c r="E73" s="133" t="n">
+      <c r="E73" s="139" t="n">
         <v>0</v>
       </c>
-      <c r="F73" s="133" t="n">
+      <c r="F73" s="139" t="n">
         <v>0</v>
       </c>
-      <c r="G73" s="133" t="n">
+      <c r="G73" s="139" t="n">
         <v>0</v>
       </c>
-      <c r="H73" s="133" t="n">
+      <c r="H73" s="139" t="n">
         <v>0</v>
       </c>
-      <c r="I73" s="133" t="n">
+      <c r="I73" s="139" t="n">
         <v>0</v>
       </c>
-      <c r="J73" s="141">
+      <c r="J73" s="142">
         <f>J20</f>
         <v/>
       </c>
-      <c r="K73" s="141">
+      <c r="K73" s="142">
         <f>K20</f>
         <v/>
       </c>
-      <c r="L73" s="141">
+      <c r="L73" s="142">
         <f>L20</f>
         <v/>
       </c>
-      <c r="M73" s="141">
+      <c r="M73" s="142">
         <f>M20</f>
         <v/>
       </c>
-      <c r="N73" s="141">
+      <c r="N73" s="142">
         <f>N20</f>
         <v/>
       </c>
@@ -4968,43 +4968,43 @@
       </c>
       <c r="C74" s="5" t="n"/>
       <c r="D74" s="28" t="n"/>
-      <c r="E74" s="142">
+      <c r="E74" s="143">
         <f>SUM(E72:E73)</f>
         <v/>
       </c>
-      <c r="F74" s="142">
+      <c r="F74" s="143">
         <f>SUM(F72:F73)</f>
         <v/>
       </c>
-      <c r="G74" s="142">
+      <c r="G74" s="143">
         <f>SUM(G72:G73)</f>
         <v/>
       </c>
-      <c r="H74" s="142">
+      <c r="H74" s="143">
         <f>SUM(H72:H73)</f>
         <v/>
       </c>
-      <c r="I74" s="142">
+      <c r="I74" s="143">
         <f>SUM(I72:I73)</f>
         <v/>
       </c>
-      <c r="J74" s="142">
+      <c r="J74" s="143">
         <f>SUM(J72:J73)</f>
         <v/>
       </c>
-      <c r="K74" s="142">
+      <c r="K74" s="143">
         <f>SUM(K72:K73)</f>
         <v/>
       </c>
-      <c r="L74" s="142">
+      <c r="L74" s="143">
         <f>SUM(L72:L73)</f>
         <v/>
       </c>
-      <c r="M74" s="142">
+      <c r="M74" s="143">
         <f>SUM(M72:M73)</f>
         <v/>
       </c>
-      <c r="N74" s="142">
+      <c r="N74" s="143">
         <f>SUM(N72:N73)</f>
         <v/>
       </c>
@@ -5077,39 +5077,42 @@
           <t>Opening Cash Balance</t>
         </is>
       </c>
-      <c r="E77" s="141">
-        <f>D78</f>
-        <v/>
-      </c>
-      <c r="F77" s="149" t="n">
-        <v>167971.1792</v>
-      </c>
-      <c r="G77" s="149" t="n">
-        <v>181209.912697878</v>
-      </c>
-      <c r="H77" s="149" t="n">
-        <v>183715.2565830093</v>
-      </c>
-      <c r="I77" s="149" t="n">
-        <v>211069.3356066046</v>
-      </c>
-      <c r="J77" s="141">
-        <f>+I78</f>
-        <v/>
-      </c>
-      <c r="K77" s="141">
+      <c r="E77" s="139" t="n">
+        <v>157394</v>
+      </c>
+      <c r="F77" s="150">
+        <f>E78</f>
+        <v/>
+      </c>
+      <c r="G77" s="150">
+        <f>F78</f>
+        <v/>
+      </c>
+      <c r="H77" s="150">
+        <f>G78</f>
+        <v/>
+      </c>
+      <c r="I77" s="150">
+        <f>H78</f>
+        <v/>
+      </c>
+      <c r="J77" s="150">
+        <f>I78</f>
+        <v/>
+      </c>
+      <c r="K77" s="142">
         <f>+J78</f>
         <v/>
       </c>
-      <c r="L77" s="141">
+      <c r="L77" s="142">
         <f>+K78</f>
         <v/>
       </c>
-      <c r="M77" s="141">
+      <c r="M77" s="142">
         <f>+L78</f>
         <v/>
       </c>
-      <c r="N77" s="141">
+      <c r="N77" s="142">
         <f>+M78</f>
         <v/>
       </c>
@@ -5121,46 +5124,46 @@
         </is>
       </c>
       <c r="C78" s="5" t="n"/>
-      <c r="D78" s="150" t="n">
+      <c r="D78" s="151" t="n">
         <v>157394</v>
       </c>
-      <c r="E78" s="142">
+      <c r="E78" s="143">
         <f>SUM(E76:E77)</f>
         <v/>
       </c>
-      <c r="F78" s="142">
+      <c r="F78" s="143">
         <f>SUM(F76:F77)</f>
         <v/>
       </c>
-      <c r="G78" s="142">
+      <c r="G78" s="143">
         <f>SUM(G76:G77)</f>
         <v/>
       </c>
-      <c r="H78" s="142">
+      <c r="H78" s="143">
         <f>SUM(H76:H77)</f>
         <v/>
       </c>
-      <c r="I78" s="142">
+      <c r="I78" s="143">
         <f>SUM(I76:I77)</f>
         <v/>
       </c>
-      <c r="J78" s="142">
+      <c r="J78" s="143">
         <f>SUM(J76:J77)</f>
         <v/>
       </c>
-      <c r="K78" s="142">
+      <c r="K78" s="143">
         <f>SUM(K76:K77)</f>
         <v/>
       </c>
-      <c r="L78" s="142">
+      <c r="L78" s="143">
         <f>SUM(L76:L77)</f>
         <v/>
       </c>
-      <c r="M78" s="142">
+      <c r="M78" s="143">
         <f>SUM(M76:M77)</f>
         <v/>
       </c>
-      <c r="N78" s="142">
+      <c r="N78" s="143">
         <f>SUM(N76:N77)</f>
         <v/>
       </c>
@@ -5181,43 +5184,43 @@
       </c>
       <c r="C80" s="9" t="n"/>
       <c r="D80" s="27" t="n"/>
-      <c r="E80" s="148">
+      <c r="E80" s="149">
         <f>E78-E41</f>
         <v/>
       </c>
-      <c r="F80" s="148">
+      <c r="F80" s="149">
         <f>F78-F41</f>
         <v/>
       </c>
-      <c r="G80" s="148">
+      <c r="G80" s="149">
         <f>G78-G41</f>
         <v/>
       </c>
-      <c r="H80" s="148">
+      <c r="H80" s="149">
         <f>H78-H41</f>
         <v/>
       </c>
-      <c r="I80" s="148">
+      <c r="I80" s="149">
         <f>I78-I41</f>
         <v/>
       </c>
-      <c r="J80" s="148">
+      <c r="J80" s="149">
         <f>J78-J41</f>
         <v/>
       </c>
-      <c r="K80" s="148">
+      <c r="K80" s="149">
         <f>K78-K41</f>
         <v/>
       </c>
-      <c r="L80" s="148">
+      <c r="L80" s="149">
         <f>L78-L41</f>
         <v/>
       </c>
-      <c r="M80" s="148">
+      <c r="M80" s="149">
         <f>M78-M41</f>
         <v/>
       </c>
-      <c r="N80" s="148">
+      <c r="N80" s="149">
         <f>N78-N41</f>
         <v/>
       </c>
@@ -5273,38 +5276,38 @@
           <t>Accounts Receivable</t>
         </is>
       </c>
-      <c r="E85" s="133" t="n">
+      <c r="E85" s="139" t="n">
         <v>312107</v>
       </c>
-      <c r="F85" s="133" t="n">
+      <c r="F85" s="139" t="n">
         <v>322410</v>
       </c>
-      <c r="G85" s="133" t="n">
+      <c r="G85" s="139" t="n">
         <v>387947</v>
       </c>
-      <c r="H85" s="133" t="n">
+      <c r="H85" s="139" t="n">
         <v>426642</v>
       </c>
-      <c r="I85" s="133" t="n">
+      <c r="I85" s="139" t="n">
         <v>529148</v>
       </c>
-      <c r="J85" s="141">
+      <c r="J85" s="142">
         <f>J42</f>
         <v/>
       </c>
-      <c r="K85" s="141">
+      <c r="K85" s="142">
         <f>K42</f>
         <v/>
       </c>
-      <c r="L85" s="141">
+      <c r="L85" s="142">
         <f>L42</f>
         <v/>
       </c>
-      <c r="M85" s="141">
+      <c r="M85" s="142">
         <f>M42</f>
         <v/>
       </c>
-      <c r="N85" s="141">
+      <c r="N85" s="142">
         <f>N42</f>
         <v/>
       </c>
@@ -5315,38 +5318,38 @@
           <t>Inventory</t>
         </is>
       </c>
-      <c r="E86" s="133" t="n">
+      <c r="E86" s="139" t="n">
         <v>0</v>
       </c>
-      <c r="F86" s="133" t="n">
+      <c r="F86" s="139" t="n">
         <v>0</v>
       </c>
-      <c r="G86" s="133" t="n">
+      <c r="G86" s="139" t="n">
         <v>0</v>
       </c>
-      <c r="H86" s="133" t="n">
+      <c r="H86" s="139" t="n">
         <v>0</v>
       </c>
-      <c r="I86" s="133" t="n">
+      <c r="I86" s="139" t="n">
         <v>0</v>
       </c>
-      <c r="J86" s="141">
+      <c r="J86" s="142">
         <f>J43</f>
         <v/>
       </c>
-      <c r="K86" s="141">
+      <c r="K86" s="142">
         <f>K43</f>
         <v/>
       </c>
-      <c r="L86" s="141">
+      <c r="L86" s="142">
         <f>L43</f>
         <v/>
       </c>
-      <c r="M86" s="141">
+      <c r="M86" s="142">
         <f>M43</f>
         <v/>
       </c>
-      <c r="N86" s="141">
+      <c r="N86" s="142">
         <f>N43</f>
         <v/>
       </c>
@@ -5357,38 +5360,38 @@
           <t>Accounts Payable</t>
         </is>
       </c>
-      <c r="E87" s="133" t="n">
+      <c r="E87" s="139" t="n">
         <v>20749</v>
       </c>
-      <c r="F87" s="133" t="n">
+      <c r="F87" s="139" t="n">
         <v>17273</v>
       </c>
-      <c r="G87" s="133" t="n">
+      <c r="G87" s="139" t="n">
         <v>19009</v>
       </c>
-      <c r="H87" s="133" t="n">
+      <c r="H87" s="139" t="n">
         <v>22473</v>
       </c>
-      <c r="I87" s="133" t="n">
+      <c r="I87" s="139" t="n">
         <v>32315</v>
       </c>
-      <c r="J87" s="141">
+      <c r="J87" s="142">
         <f>J48</f>
         <v/>
       </c>
-      <c r="K87" s="141">
+      <c r="K87" s="142">
         <f>K48</f>
         <v/>
       </c>
-      <c r="L87" s="141">
+      <c r="L87" s="142">
         <f>L48</f>
         <v/>
       </c>
-      <c r="M87" s="141">
+      <c r="M87" s="142">
         <f>M48</f>
         <v/>
       </c>
-      <c r="N87" s="141">
+      <c r="N87" s="142">
         <f>N48</f>
         <v/>
       </c>
@@ -5400,46 +5403,46 @@
         </is>
       </c>
       <c r="C88" s="5" t="n"/>
-      <c r="D88" s="150" t="n">
+      <c r="D88" s="151" t="n">
         <v>311147</v>
       </c>
-      <c r="E88" s="151">
+      <c r="E88" s="152">
         <f>E85+E86-E87</f>
         <v/>
       </c>
-      <c r="F88" s="151">
+      <c r="F88" s="152">
         <f>F85+F86-F87</f>
         <v/>
       </c>
-      <c r="G88" s="151">
+      <c r="G88" s="152">
         <f>G85+G86-G87</f>
         <v/>
       </c>
-      <c r="H88" s="151">
+      <c r="H88" s="152">
         <f>H85+H86-H87</f>
         <v/>
       </c>
-      <c r="I88" s="151">
+      <c r="I88" s="152">
         <f>I85+I86-I87</f>
         <v/>
       </c>
-      <c r="J88" s="151">
+      <c r="J88" s="152">
         <f>J85+J86-J87</f>
         <v/>
       </c>
-      <c r="K88" s="151">
+      <c r="K88" s="152">
         <f>K85+K86-K87</f>
         <v/>
       </c>
-      <c r="L88" s="151">
+      <c r="L88" s="152">
         <f>L85+L86-L87</f>
         <v/>
       </c>
-      <c r="M88" s="151">
+      <c r="M88" s="152">
         <f>M85+M86-M87</f>
         <v/>
       </c>
-      <c r="N88" s="151">
+      <c r="N88" s="152">
         <f>N85+N86-N87</f>
         <v/>
       </c>
@@ -5516,42 +5519,42 @@
           <t>PPE Opening</t>
         </is>
       </c>
-      <c r="E92" s="133" t="n">
+      <c r="E92" s="139" t="n">
         <v>46419</v>
       </c>
-      <c r="F92" s="152">
+      <c r="F92" s="150">
         <f>E95</f>
         <v/>
       </c>
-      <c r="G92" s="152">
+      <c r="G92" s="150">
         <f>F95</f>
         <v/>
       </c>
-      <c r="H92" s="152">
+      <c r="H92" s="150">
         <f>G95</f>
         <v/>
       </c>
-      <c r="I92" s="152">
+      <c r="I92" s="150">
         <f>H95</f>
         <v/>
       </c>
-      <c r="J92" s="152">
+      <c r="J92" s="150">
         <f>I44</f>
         <v/>
       </c>
-      <c r="K92" s="152">
+      <c r="K92" s="150">
         <f>J95</f>
         <v/>
       </c>
-      <c r="L92" s="152">
+      <c r="L92" s="150">
         <f>K95</f>
         <v/>
       </c>
-      <c r="M92" s="152">
+      <c r="M92" s="150">
         <f>L95</f>
         <v/>
       </c>
-      <c r="N92" s="152">
+      <c r="N92" s="150">
         <f>M95</f>
         <v/>
       </c>
@@ -5562,38 +5565,38 @@
           <t>Plus Capex</t>
         </is>
       </c>
-      <c r="E93" s="133" t="n">
+      <c r="E93" s="139" t="n">
         <v>7569</v>
       </c>
-      <c r="F93" s="133" t="n">
+      <c r="F93" s="139" t="n">
         <v>6029</v>
       </c>
-      <c r="G93" s="133" t="n">
+      <c r="G93" s="139" t="n">
         <v>4237</v>
       </c>
-      <c r="H93" s="133" t="n">
+      <c r="H93" s="139" t="n">
         <v>25551</v>
       </c>
-      <c r="I93" s="133" t="n">
+      <c r="I93" s="139" t="n">
         <v>39407</v>
       </c>
-      <c r="J93" s="141">
+      <c r="J93" s="142">
         <f>+J18</f>
         <v/>
       </c>
-      <c r="K93" s="141">
+      <c r="K93" s="142">
         <f>+K18</f>
         <v/>
       </c>
-      <c r="L93" s="141">
+      <c r="L93" s="142">
         <f>+L18</f>
         <v/>
       </c>
-      <c r="M93" s="141">
+      <c r="M93" s="142">
         <f>+M18</f>
         <v/>
       </c>
-      <c r="N93" s="141">
+      <c r="N93" s="142">
         <f>+N18</f>
         <v/>
       </c>
@@ -5604,38 +5607,38 @@
           <t>Less Depreciation</t>
         </is>
       </c>
-      <c r="E94" s="133" t="n">
+      <c r="E94" s="139" t="n">
         <v>25592</v>
       </c>
-      <c r="F94" s="133" t="n">
+      <c r="F94" s="139" t="n">
         <v>20465</v>
       </c>
-      <c r="G94" s="133" t="n">
+      <c r="G94" s="139" t="n">
         <v>14638</v>
       </c>
-      <c r="H94" s="133" t="n">
+      <c r="H94" s="139" t="n">
         <v>13827</v>
       </c>
-      <c r="I94" s="133" t="n">
+      <c r="I94" s="139" t="n">
         <v>14952</v>
       </c>
-      <c r="J94" s="141">
+      <c r="J94" s="142">
         <f>J92*J11</f>
         <v/>
       </c>
-      <c r="K94" s="141">
+      <c r="K94" s="142">
         <f>K92*K11</f>
         <v/>
       </c>
-      <c r="L94" s="141">
+      <c r="L94" s="142">
         <f>L92*L11</f>
         <v/>
       </c>
-      <c r="M94" s="141">
+      <c r="M94" s="142">
         <f>M92*M11</f>
         <v/>
       </c>
-      <c r="N94" s="141">
+      <c r="N94" s="142">
         <f>N92*N11</f>
         <v/>
       </c>
@@ -5663,23 +5666,23 @@
       <c r="I95" s="153" t="n">
         <v>67713</v>
       </c>
-      <c r="J95" s="151">
+      <c r="J95" s="152">
         <f>J92+J93-J94</f>
         <v/>
       </c>
-      <c r="K95" s="151">
+      <c r="K95" s="152">
         <f>K92+K93-K94</f>
         <v/>
       </c>
-      <c r="L95" s="151">
+      <c r="L95" s="152">
         <f>L92+L93-L94</f>
         <v/>
       </c>
-      <c r="M95" s="151">
+      <c r="M95" s="152">
         <f>M92+M93-M94</f>
         <v/>
       </c>
-      <c r="N95" s="151">
+      <c r="N95" s="152">
         <f>N92+N93-N94</f>
         <v/>
       </c>
@@ -5714,38 +5717,42 @@
           <t>Debt Opening</t>
         </is>
       </c>
-      <c r="E98" s="149" t="n">
-        <v>50000</v>
-      </c>
-      <c r="F98" s="149" t="n">
-        <v>50000</v>
-      </c>
-      <c r="G98" s="149" t="n">
-        <v>50000</v>
-      </c>
-      <c r="H98" s="149" t="n">
-        <v>30000</v>
-      </c>
-      <c r="I98" s="149" t="n">
-        <v>30000</v>
-      </c>
-      <c r="J98" s="141">
-        <f>I100</f>
-        <v/>
-      </c>
-      <c r="K98" s="141">
+      <c r="E98" s="139" t="n">
+        <v>739435</v>
+      </c>
+      <c r="F98" s="150">
+        <f>E100</f>
+        <v/>
+      </c>
+      <c r="G98" s="150">
+        <f>F100</f>
+        <v/>
+      </c>
+      <c r="H98" s="150">
+        <f>G100</f>
+        <v/>
+      </c>
+      <c r="I98" s="150">
+        <f>H100</f>
+        <v/>
+      </c>
+      <c r="J98" s="150">
+        <f>I49</f>
+        <v/>
+      </c>
+      <c r="K98" s="150">
         <f>J100</f>
         <v/>
       </c>
-      <c r="L98" s="141">
+      <c r="L98" s="150">
         <f>K100</f>
         <v/>
       </c>
-      <c r="M98" s="141">
+      <c r="M98" s="150">
         <f>L100</f>
         <v/>
       </c>
-      <c r="N98" s="141">
+      <c r="N98" s="150">
         <f>M100</f>
         <v/>
       </c>
@@ -5756,20 +5763,20 @@
           <t>Issuance (repayment)</t>
         </is>
       </c>
-      <c r="E99" s="149" t="n">
-        <v>0</v>
-      </c>
-      <c r="F99" s="149" t="n">
-        <v>0</v>
-      </c>
-      <c r="G99" s="149" t="n">
-        <v>-20000</v>
-      </c>
-      <c r="H99" s="149" t="n">
-        <v>0</v>
-      </c>
-      <c r="I99" s="149" t="n">
-        <v>0</v>
+      <c r="E99" s="139" t="n">
+        <v>519583</v>
+      </c>
+      <c r="F99" s="139" t="n">
+        <v>594651</v>
+      </c>
+      <c r="G99" s="139" t="n">
+        <v>7989</v>
+      </c>
+      <c r="H99" s="139" t="n">
+        <v>347363</v>
+      </c>
+      <c r="I99" s="139" t="n">
+        <v>846670</v>
       </c>
       <c r="J99" s="138">
         <f>+J19</f>
@@ -5800,43 +5807,38 @@
       </c>
       <c r="C100" s="5" t="n"/>
       <c r="D100" s="28" t="n"/>
-      <c r="E100" s="151">
-        <f>SUM(E98:E99)</f>
-        <v/>
-      </c>
-      <c r="F100" s="151">
-        <f>SUM(F98:F99)</f>
-        <v/>
-      </c>
-      <c r="G100" s="151">
-        <f>SUM(G98:G99)</f>
-        <v/>
-      </c>
-      <c r="H100" s="151">
-        <f>SUM(H98:H99)</f>
-        <v/>
-      </c>
-      <c r="I100" s="151">
-        <f>SUM(I98:I99)</f>
-        <v/>
-      </c>
-      <c r="J100" s="151">
+      <c r="E100" s="153" t="n">
+        <v>1259018</v>
+      </c>
+      <c r="F100" s="153" t="n">
+        <v>1853669</v>
+      </c>
+      <c r="G100" s="153" t="n">
+        <v>1861658</v>
+      </c>
+      <c r="H100" s="153" t="n">
+        <v>2209021</v>
+      </c>
+      <c r="I100" s="153" t="n">
+        <v>3055691</v>
+      </c>
+      <c r="J100" s="152">
         <f>SUM(J98:J99)</f>
         <v/>
       </c>
-      <c r="K100" s="151">
+      <c r="K100" s="152">
         <f>SUM(K98:K99)</f>
         <v/>
       </c>
-      <c r="L100" s="151">
+      <c r="L100" s="152">
         <f>SUM(L98:L99)</f>
         <v/>
       </c>
-      <c r="M100" s="151">
+      <c r="M100" s="152">
         <f>SUM(M98:M99)</f>
         <v/>
       </c>
-      <c r="N100" s="151">
+      <c r="N100" s="152">
         <f>SUM(N98:N99)</f>
         <v/>
       </c>
@@ -5847,38 +5849,38 @@
           <t>Interest Expense</t>
         </is>
       </c>
-      <c r="E101" s="149" t="n">
-        <v>2500</v>
-      </c>
-      <c r="F101" s="149" t="n">
-        <v>2500</v>
-      </c>
-      <c r="G101" s="149" t="n">
-        <v>1500</v>
-      </c>
-      <c r="H101" s="149" t="n">
-        <v>900</v>
-      </c>
-      <c r="I101" s="149" t="n">
-        <v>900</v>
-      </c>
-      <c r="J101" s="141">
+      <c r="E101" s="139" t="n">
+        <v>40092</v>
+      </c>
+      <c r="F101" s="139" t="n">
+        <v>68967</v>
+      </c>
+      <c r="G101" s="139" t="n">
+        <v>95546</v>
+      </c>
+      <c r="H101" s="139" t="n">
+        <v>105638</v>
+      </c>
+      <c r="I101" s="139" t="n">
+        <v>133647</v>
+      </c>
+      <c r="J101" s="142">
         <f>J98*J12</f>
         <v/>
       </c>
-      <c r="K101" s="141">
+      <c r="K101" s="142">
         <f>K98*K12</f>
         <v/>
       </c>
-      <c r="L101" s="141">
+      <c r="L101" s="142">
         <f>L98*L12</f>
         <v/>
       </c>
-      <c r="M101" s="141">
+      <c r="M101" s="142">
         <f>M98*M12</f>
         <v/>
       </c>
-      <c r="N101" s="141">
+      <c r="N101" s="142">
         <f>N98*N12</f>
         <v/>
       </c>

--- a/FICO/output/FICO_Completed_Model.xlsx
+++ b/FICO/output/FICO_Completed_Model.xlsx
@@ -5030,24 +5030,24 @@
           <t>Net Increase (decrease) in Cash</t>
         </is>
       </c>
-      <c r="E76" s="138">
-        <f>E65-E69+E74</f>
-        <v/>
-      </c>
-      <c r="F76" s="138">
-        <f>F65-F69+F74</f>
-        <v/>
-      </c>
-      <c r="G76" s="138">
-        <f>G65-G69+G74</f>
-        <v/>
-      </c>
-      <c r="H76" s="138">
-        <f>H65-H69+H74</f>
-        <v/>
-      </c>
-      <c r="I76" s="138">
-        <f>I65-I69+I74</f>
+      <c r="E76" s="150">
+        <f>E41-E77</f>
+        <v/>
+      </c>
+      <c r="F76" s="150">
+        <f>F41-F77</f>
+        <v/>
+      </c>
+      <c r="G76" s="150">
+        <f>G41-G77</f>
+        <v/>
+      </c>
+      <c r="H76" s="150">
+        <f>H41-H77</f>
+        <v/>
+      </c>
+      <c r="I76" s="150">
+        <f>I41-I77</f>
         <v/>
       </c>
       <c r="J76" s="138">
@@ -5081,39 +5081,39 @@
         <v>157394</v>
       </c>
       <c r="F77" s="150">
-        <f>E78</f>
+        <f>E41</f>
         <v/>
       </c>
       <c r="G77" s="150">
-        <f>F78</f>
+        <f>F41</f>
         <v/>
       </c>
       <c r="H77" s="150">
-        <f>G78</f>
+        <f>G41</f>
         <v/>
       </c>
       <c r="I77" s="150">
-        <f>H78</f>
+        <f>H41</f>
         <v/>
       </c>
       <c r="J77" s="150">
-        <f>I78</f>
-        <v/>
-      </c>
-      <c r="K77" s="142">
-        <f>+J78</f>
-        <v/>
-      </c>
-      <c r="L77" s="142">
-        <f>+K78</f>
-        <v/>
-      </c>
-      <c r="M77" s="142">
-        <f>+L78</f>
-        <v/>
-      </c>
-      <c r="N77" s="142">
-        <f>+M78</f>
+        <f>I41</f>
+        <v/>
+      </c>
+      <c r="K77" s="150">
+        <f>J78</f>
+        <v/>
+      </c>
+      <c r="L77" s="150">
+        <f>K78</f>
+        <v/>
+      </c>
+      <c r="M77" s="150">
+        <f>L78</f>
+        <v/>
+      </c>
+      <c r="N77" s="150">
+        <f>M78</f>
         <v/>
       </c>
     </row>

--- a/FICO/output/FICO_Completed_Model.xlsx
+++ b/FICO/output/FICO_Completed_Model.xlsx
@@ -2110,7 +2110,7 @@
       <c r="B12" s="74" t="n"/>
       <c r="C12" s="75" t="inlineStr">
         <is>
-          <t>FICO — Model2.0 (3-Statement + DCF)</t>
+          <t>FICO — vengeanceaiUSCMODEL3 (3-Statement + DCF)</t>
         </is>
       </c>
       <c r="D12" s="74" t="n"/>
@@ -2278,7 +2278,7 @@
       <c r="B21" s="85" t="n"/>
       <c r="C21" s="85" t="inlineStr">
         <is>
-          <t>Model2.0: revenue fades (not straight-lined). DCF uses unlevered EBIT×t taxes, Gordon TV primary, mid-year XNPV dates, CapEx/ΔNWC/D&amp;A linked to 3-statement. Open in Excel to recalculate.</t>
+          <t>vengeanceaiUSCMODEL3: CAPM WACC (~9.24%), operating NWC (AR−AP−deferred), CapEx fade, mild SGA grind, Exit EV/EBITDA primary, mid-year XNPV, unlevered EBIT×t taxes. Open in Excel to recalculate.</t>
         </is>
       </c>
       <c r="D21" s="85" t="n"/>
@@ -2676,16 +2676,16 @@
         <v>0.27</v>
       </c>
       <c r="K7" s="137" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="L7" s="137" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="M7" s="137" t="n">
         <v>0.1</v>
       </c>
       <c r="N7" s="137" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="8" hidden="1" outlineLevel="1">
@@ -2761,19 +2761,19 @@
         <v/>
       </c>
       <c r="J9" s="139" t="n">
-        <v>651545.6</v>
+        <v>625032.6</v>
       </c>
       <c r="K9" s="139" t="n">
-        <v>749277.4</v>
+        <v>710373.1</v>
       </c>
       <c r="L9" s="139" t="n">
-        <v>839190.7</v>
+        <v>786150.4</v>
       </c>
       <c r="M9" s="139" t="n">
-        <v>923109.7</v>
+        <v>846537.2</v>
       </c>
       <c r="N9" s="139" t="n">
-        <v>996958.5</v>
+        <v>886290.5</v>
       </c>
     </row>
     <row r="10" hidden="1" outlineLevel="1">
@@ -2808,16 +2808,16 @@
         <v>239200.7</v>
       </c>
       <c r="K10" s="139" t="n">
-        <v>275080.8</v>
+        <v>277472.8</v>
       </c>
       <c r="L10" s="139" t="n">
-        <v>308090.5</v>
+        <v>313544.3</v>
       </c>
       <c r="M10" s="139" t="n">
-        <v>338899.5</v>
+        <v>344898.7</v>
       </c>
       <c r="N10" s="139" t="n">
-        <v>366011.5</v>
+        <v>369041.6</v>
       </c>
     </row>
     <row r="11" hidden="1" outlineLevel="1">
@@ -2999,19 +2999,19 @@
         <v/>
       </c>
       <c r="J15" s="139" t="n">
-        <v>97</v>
+        <v>63</v>
       </c>
       <c r="K15" s="139" t="n">
-        <v>97</v>
+        <v>63</v>
       </c>
       <c r="L15" s="139" t="n">
-        <v>97</v>
+        <v>63</v>
       </c>
       <c r="M15" s="139" t="n">
-        <v>97</v>
+        <v>63</v>
       </c>
       <c r="N15" s="139" t="n">
-        <v>97</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16" hidden="1" outlineLevel="1">
@@ -3127,19 +3127,19 @@
         <v/>
       </c>
       <c r="J18" s="139" t="n">
-        <v>50046.9</v>
+        <v>46333</v>
       </c>
       <c r="K18" s="139" t="n">
-        <v>57553.9</v>
+        <v>48000.6</v>
       </c>
       <c r="L18" s="139" t="n">
-        <v>64460.4</v>
+        <v>47748.1</v>
       </c>
       <c r="M18" s="139" t="n">
-        <v>70906.39999999999</v>
+        <v>47167.5</v>
       </c>
       <c r="N18" s="139" t="n">
-        <v>76578.89999999999</v>
+        <v>39008.5</v>
       </c>
     </row>
     <row r="19" hidden="1" outlineLevel="1">
@@ -4640,16 +4640,16 @@
         <v>0</v>
       </c>
       <c r="F64" s="139" t="n">
-        <v>13779</v>
+        <v>-849</v>
       </c>
       <c r="G64" s="139" t="n">
-        <v>63801</v>
+        <v>47116</v>
       </c>
       <c r="H64" s="139" t="n">
-        <v>35231</v>
+        <v>15064</v>
       </c>
       <c r="I64" s="139" t="n">
-        <v>92664</v>
+        <v>62189</v>
       </c>
       <c r="J64" s="142">
         <f>J89</f>
@@ -5277,19 +5277,19 @@
         </is>
       </c>
       <c r="E85" s="139" t="n">
-        <v>312107</v>
+        <v>206690</v>
       </c>
       <c r="F85" s="139" t="n">
-        <v>322410</v>
+        <v>202365</v>
       </c>
       <c r="G85" s="139" t="n">
-        <v>387947</v>
+        <v>251217</v>
       </c>
       <c r="H85" s="139" t="n">
-        <v>426642</v>
+        <v>269745</v>
       </c>
       <c r="I85" s="139" t="n">
-        <v>529148</v>
+        <v>341776</v>
       </c>
       <c r="J85" s="142">
         <f>J42</f>
@@ -5404,7 +5404,7 @@
       </c>
       <c r="C88" s="5" t="n"/>
       <c r="D88" s="151" t="n">
-        <v>311147</v>
+        <v>205747</v>
       </c>
       <c r="E88" s="152">
         <f>E85+E86-E87</f>
@@ -6320,7 +6320,7 @@
       </c>
       <c r="C6" s="97" t="n"/>
       <c r="D6" s="154" t="n">
-        <v>0.096</v>
+        <v>0.0924</v>
       </c>
       <c r="E6" s="97" t="n"/>
       <c r="F6" s="97" t="n"/>
@@ -6595,7 +6595,7 @@
       <c r="K17" s="97" t="n"/>
       <c r="L17" s="114" t="inlineStr">
         <is>
-          <t>Terminal value methods</t>
+          <t>Terminal value methods (MODEL3)</t>
         </is>
       </c>
       <c r="M17" s="111" t="n"/>
@@ -6641,7 +6641,7 @@
       <c r="K18" s="97" t="n"/>
       <c r="L18" s="97" t="inlineStr">
         <is>
-          <t>Gordon TV (in J27) — primary</t>
+          <t>Exit EV/EBITDA (in J27) — primary</t>
         </is>
       </c>
       <c r="M18" s="159">
@@ -6686,11 +6686,11 @@
       <c r="K19" s="97" t="n"/>
       <c r="L19" s="97" t="inlineStr">
         <is>
-          <t>Exit EV/EBITDA cross-check</t>
+          <t>Gordon cross-check</t>
         </is>
       </c>
       <c r="M19" s="159">
-        <f>($I$21+$I$23)*$D$8</f>
+        <f>IF(($D$6-$D$7)&lt;=0,"WACC must exceed g",$I$26*(1+$D$7)/($D$6-$D$7))</f>
         <v/>
       </c>
       <c r="N19" s="121">
@@ -6732,11 +6732,11 @@
       <c r="K20" s="97" t="n"/>
       <c r="L20" s="97" t="inlineStr">
         <is>
-          <t>Implied exit multiple vs Gordon</t>
+          <t>Implied Gordon exit multiple</t>
         </is>
       </c>
       <c r="M20" s="159">
-        <f>IF(($I$21+$I$23)=0,0,J27/($I$21+$I$23))</f>
+        <f>IF(($I$21+$I$23)=0,0,M19/($I$21+$I$23))</f>
         <v/>
       </c>
       <c r="N20" s="123">
@@ -6965,7 +6965,7 @@
       <c r="A27" s="97" t="n"/>
       <c r="B27" s="97" t="inlineStr">
         <is>
-          <t>(Entry)/Exit TV — Gordon</t>
+          <t>(Entry)/Exit TV — Exit EV/EBITDA</t>
         </is>
       </c>
       <c r="C27" s="97" t="n"/>
@@ -6979,7 +6979,7 @@
       <c r="H27" s="97" t="n"/>
       <c r="I27" s="97" t="n"/>
       <c r="J27" s="159">
-        <f>IF(($D$6-$D$7)&lt;=0,"WACC must exceed g",$I$26*(1+$D$7)/($D$6-$D$7))</f>
+        <f>($I$21+$I$23)*$D$8</f>
         <v/>
       </c>
       <c r="K27" s="97" t="n"/>

--- a/FICO/output/FICO_Completed_Model.xlsx
+++ b/FICO/output/FICO_Completed_Model.xlsx
@@ -2278,7 +2278,7 @@
       <c r="B21" s="85" t="n"/>
       <c r="C21" s="85" t="inlineStr">
         <is>
-          <t>vengeanceaiUSCMODEL3: CAPM WACC (~9.24%), operating NWC (AR−AP−deferred), CapEx fade, mild SGA grind, Exit EV/EBITDA primary, mid-year XNPV, unlevered EBIT×t taxes. Open in Excel to recalculate.</t>
+          <t>vengeanceaiUSCMODEL3: Ke=Rf+β·ERP=4.63%+1.32×4.28%=10.28%; WACC=80%×Ke+20%×Rd(1−t)=9.24%; FCFF=EBIT(1−t)+DA−CapEx−ΔNWC; NWC=AR−AP−Deferred; TV=EBITDA×25x (Gordon cross-check); mid-year XNPV. Open in Excel to recalculate.</t>
         </is>
       </c>
       <c r="D21" s="85" t="n"/>

--- a/FICO/output/FICO_Completed_Model.xlsx
+++ b/FICO/output/FICO_Completed_Model.xlsx
@@ -82,7 +82,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="14">
+  <numFmts count="16">
     <numFmt numFmtId="164" formatCode="_-* #,##0_-;\(#,##0\)_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="0.0000_ ;\-0.0000\ "/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
@@ -93,12 +93,14 @@
     <numFmt numFmtId="171" formatCode="0.0\x"/>
     <numFmt numFmtId="172" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="173" formatCode="_-* #,##0.00_-;\(#,##0.00\)_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="174" formatCode="#,##0.0;(#,##0.0);-"/>
-    <numFmt numFmtId="175" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="174" formatCode="#,##0.0"/>
+    <numFmt numFmtId="175" formatCode="0.00x"/>
     <numFmt numFmtId="176" formatCode="$#,##0.00"/>
-    <numFmt numFmtId="177" formatCode="0.0"/>
+    <numFmt numFmtId="177" formatCode="#,##0.0;(#,##0.0);-"/>
+    <numFmt numFmtId="178" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="179" formatCode="0.0"/>
   </numFmts>
-  <fonts count="41">
+  <fonts count="45">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -362,8 +364,29 @@
       <name val="Calibri"/>
       <color rgb="000000FF"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00666666"/>
+    </font>
+    <font>
+      <name val="Consolas"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Consolas"/>
+      <color rgb="00666666"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -410,8 +433,18 @@
         <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D6EAF8"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -459,6 +492,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B0B0B0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00B0B0B0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B0B0B0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B0B0B0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="9">
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
@@ -471,7 +518,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="169">
+  <cellXfs count="184">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="1"/>
@@ -688,50 +735,71 @@
     <xf numFmtId="1" fontId="40" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="1" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="1" fontId="13" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="174" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="166" fontId="40" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="2"/>
-    <xf numFmtId="174" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="174" fontId="40" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="177" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="177" fontId="40" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="166" fontId="40" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="174" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="174" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="174" fontId="6" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="174" fontId="40" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="174" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="174" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="174" fontId="6" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="174" fontId="6" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="174" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="174" fontId="38" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="174" fontId="40" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="177" fontId="40" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="177" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="177" fontId="38" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="177" fontId="40" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="174" fontId="9" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="174" fontId="40" fillId="8" borderId="2" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="177" fontId="9" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="177" fontId="40" fillId="8" borderId="2" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="41" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="40" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="177" fontId="40" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="39" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="38" fillId="7" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="175" fontId="32" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="40" fillId="8" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="179" fontId="40" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="40" fillId="8" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="178" fontId="32" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="38" fillId="7" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="176" fontId="40" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="167" fontId="40" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="174" fontId="38" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="40" fillId="8" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="177" fontId="38" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="31" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="174" fontId="35" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="175" fontId="38" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="174" fontId="36" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="174" fontId="37" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="174" fontId="30" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="174" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="174" fontId="38" fillId="7" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="177" fontId="35" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="178" fontId="38" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="177" fontId="36" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="177" fontId="37" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="44" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="174" fontId="38" fillId="7" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="177" fontId="30" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="177" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="177" fontId="38" fillId="7" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="175" fontId="38" fillId="7" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="176" fontId="38" fillId="7" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="38" fillId="7" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="173" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="9">
@@ -2278,7 +2346,7 @@
       <c r="B21" s="85" t="n"/>
       <c r="C21" s="85" t="inlineStr">
         <is>
-          <t>vengeanceaiUSCMODEL3: Ke=Rf+β·ERP=4.63%+1.32×4.28%=10.28%; WACC=80%×Ke+20%×Rd(1−t)=9.24%; FCFF=EBIT(1−t)+DA−CapEx−ΔNWC; NWC=AR−AP−Deferred; TV=EBITDA×25x (Gordon cross-check); mid-year XNPV. Open in Excel to recalculate.</t>
+          <t>vengeanceaiUSCMODEL3: Ke=Rf+β·ERP=4.63%+1.32×4.28%=10.28%; WACC=80%×Ke+20%×Rd(1−t)=9.24%; FCFF=EBIT(1−t)+DA−CapEx−ΔNWC; NWC=AR−AP−Deferred; TV=EBITDA×25x (Gordon cross-check); mid-year XNPV. Open in Excel to recalculate. Live equations on DCF sheet columns Q–T (Ke/WACC/FCFF/TV).</t>
         </is>
       </c>
       <c r="D21" s="85" t="n"/>
@@ -6191,7 +6259,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O61"/>
+  <dimension ref="A1:T61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3.54296875" customWidth="1" min="1" max="1"/>
@@ -6208,6 +6276,10 @@
     <col width="36" customWidth="1" min="12" max="12"/>
     <col width="18" customWidth="1" min="13" max="13"/>
     <col width="9.08984375" customWidth="1" min="15" max="15"/>
+    <col width="38" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="44" customWidth="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
@@ -6249,6 +6321,11 @@
       <c r="L2" s="96" t="n"/>
       <c r="M2" s="94" t="n"/>
       <c r="N2" s="94" t="n"/>
+      <c r="Q2" s="154" t="inlineStr">
+        <is>
+          <t>vengeanceaiUSCMODEL3 — LIVE EQUATIONS</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="97" t="n"/>
@@ -6266,6 +6343,11 @@
       <c r="M3" s="97" t="n"/>
       <c r="N3" s="97" t="n"/>
       <c r="O3" s="97" t="n"/>
+      <c r="Q3" s="155" t="inlineStr">
+        <is>
+          <t>Yellow = inputs (edit these). Green = formulas (auto-update).</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="97" t="n"/>
@@ -6296,7 +6378,7 @@
         </is>
       </c>
       <c r="C5" s="100" t="n"/>
-      <c r="D5" s="154" t="n">
+      <c r="D5" s="156" t="n">
         <v>0.1877023903712333</v>
       </c>
       <c r="E5" s="100" t="n"/>
@@ -6310,17 +6392,23 @@
       <c r="M5" s="97" t="n"/>
       <c r="N5" s="97" t="n"/>
       <c r="O5" s="97" t="n"/>
+      <c r="Q5" s="157" t="inlineStr">
+        <is>
+          <t>1) CAPM → WACC</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="16" customHeight="1">
       <c r="A6" s="97" t="n"/>
       <c r="B6" s="103" t="inlineStr">
         <is>
-          <t>Discount Rate</t>
+          <t>Discount Rate (WACC = We×Ke + Wd×Rd(1−t))</t>
         </is>
       </c>
       <c r="C6" s="97" t="n"/>
-      <c r="D6" s="154" t="n">
-        <v>0.0924</v>
+      <c r="D6" s="158">
+        <f>R15</f>
+        <v/>
       </c>
       <c r="E6" s="97" t="n"/>
       <c r="F6" s="97" t="n"/>
@@ -6333,6 +6421,20 @@
       <c r="M6" s="97" t="n"/>
       <c r="N6" s="97" t="n"/>
       <c r="O6" s="97" t="n"/>
+      <c r="Q6" s="159" t="inlineStr">
+        <is>
+          <t>Risk-free rate (Rf)</t>
+        </is>
+      </c>
+      <c r="R6" s="160" t="n">
+        <v>0.0463</v>
+      </c>
+      <c r="S6" s="159" t="inlineStr">
+        <is>
+          <t>US 10Y Treasury / FRED DGS10</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr"/>
     </row>
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="97" t="n"/>
@@ -6342,7 +6444,7 @@
         </is>
       </c>
       <c r="C7" s="97" t="n"/>
-      <c r="D7" s="154" t="n">
+      <c r="D7" s="156" t="n">
         <v>0.03</v>
       </c>
       <c r="E7" s="97" t="n"/>
@@ -6356,6 +6458,20 @@
       <c r="M7" s="97" t="n"/>
       <c r="N7" s="97" t="n"/>
       <c r="O7" s="97" t="n"/>
+      <c r="Q7" s="159" t="inlineStr">
+        <is>
+          <t>Equity risk premium (ERP)</t>
+        </is>
+      </c>
+      <c r="R7" s="160" t="n">
+        <v>0.0428</v>
+      </c>
+      <c r="S7" s="159" t="inlineStr">
+        <is>
+          <t>Damodaran implied ERP</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr"/>
     </row>
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="97" t="n"/>
@@ -6365,8 +6481,8 @@
         </is>
       </c>
       <c r="C8" s="97" t="n"/>
-      <c r="D8" s="155" t="n">
-        <v>22</v>
+      <c r="D8" s="161" t="n">
+        <v>25</v>
       </c>
       <c r="E8" s="97" t="n"/>
       <c r="F8" s="97" t="n"/>
@@ -6379,6 +6495,20 @@
       <c r="M8" s="97" t="n"/>
       <c r="N8" s="97" t="n"/>
       <c r="O8" s="97" t="n"/>
+      <c r="Q8" s="159" t="inlineStr">
+        <is>
+          <t>Beta (β)</t>
+        </is>
+      </c>
+      <c r="R8" s="162" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S8" s="159" t="inlineStr">
+        <is>
+          <t>Yahoo Finance 5Y monthly</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr"/>
     </row>
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="97" t="n"/>
@@ -6388,7 +6518,7 @@
         </is>
       </c>
       <c r="C9" s="97" t="n"/>
-      <c r="D9" s="156" t="n">
+      <c r="D9" s="163" t="n">
         <v>45930</v>
       </c>
       <c r="E9" s="97" t="n"/>
@@ -6402,6 +6532,25 @@
       <c r="M9" s="97" t="n"/>
       <c r="N9" s="97" t="n"/>
       <c r="O9" s="97" t="n"/>
+      <c r="Q9" s="164" t="inlineStr">
+        <is>
+          <t>Ke = Rf + β × ERP</t>
+        </is>
+      </c>
+      <c r="R9" s="165">
+        <f>R6+R8*R7</f>
+        <v/>
+      </c>
+      <c r="S9" s="159" t="inlineStr">
+        <is>
+          <t>Cost of equity (CAPM)</t>
+        </is>
+      </c>
+      <c r="T9" s="164" t="inlineStr">
+        <is>
+          <t>→ feeds WACC</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="97" t="n"/>
@@ -6411,7 +6560,7 @@
         </is>
       </c>
       <c r="C10" s="97" t="n"/>
-      <c r="D10" s="156" t="n">
+      <c r="D10" s="163" t="n">
         <v>46295</v>
       </c>
       <c r="E10" s="97" t="n"/>
@@ -6425,6 +6574,19 @@
       <c r="M10" s="97" t="n"/>
       <c r="N10" s="97" t="n"/>
       <c r="O10" s="97" t="n"/>
+      <c r="Q10" s="159" t="inlineStr">
+        <is>
+          <t>Pre-tax cost of debt (Rd)</t>
+        </is>
+      </c>
+      <c r="R10" s="160" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="S10" s="159" t="inlineStr">
+        <is>
+          <t>6.250% Senior Notes due 2034 (SEC 8-K)</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="16" customHeight="1">
       <c r="A11" s="97" t="n"/>
@@ -6434,7 +6596,7 @@
         </is>
       </c>
       <c r="C11" s="97" t="n"/>
-      <c r="D11" s="157" t="n">
+      <c r="D11" s="166" t="n">
         <v>1046.23</v>
       </c>
       <c r="E11" s="97" t="n"/>
@@ -6448,6 +6610,20 @@
       <c r="M11" s="97" t="n"/>
       <c r="N11" s="97" t="n"/>
       <c r="O11" s="97" t="n"/>
+      <c r="Q11" s="159" t="inlineStr">
+        <is>
+          <t>Tax rate (t)</t>
+        </is>
+      </c>
+      <c r="R11" s="165">
+        <f>$D$5</f>
+        <v/>
+      </c>
+      <c r="S11" s="159" t="inlineStr">
+        <is>
+          <t>Linked to DCF tax assumption (FY25 effective)</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="16" customHeight="1">
       <c r="A12" s="97" t="n"/>
@@ -6457,7 +6633,7 @@
         </is>
       </c>
       <c r="C12" s="97" t="n"/>
-      <c r="D12" s="158" t="n">
+      <c r="D12" s="167" t="n">
         <v>21597.635</v>
       </c>
       <c r="E12" s="97" t="n"/>
@@ -6471,6 +6647,20 @@
       <c r="M12" s="97" t="n"/>
       <c r="N12" s="97" t="n"/>
       <c r="O12" s="97" t="n"/>
+      <c r="Q12" s="164" t="inlineStr">
+        <is>
+          <t>Rd_aftertax = Rd × (1 − t)</t>
+        </is>
+      </c>
+      <c r="R12" s="165">
+        <f>R10*(1-R11)</f>
+        <v/>
+      </c>
+      <c r="S12" s="159" t="inlineStr">
+        <is>
+          <t>After-tax cost of debt</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="16" customHeight="1">
       <c r="A13" s="97" t="n"/>
@@ -6480,7 +6670,7 @@
         </is>
       </c>
       <c r="C13" s="97" t="n"/>
-      <c r="D13" s="158" t="n">
+      <c r="D13" s="167" t="n">
         <v>5582389</v>
       </c>
       <c r="E13" s="97" t="n"/>
@@ -6494,6 +6684,19 @@
       <c r="M13" s="97" t="n"/>
       <c r="N13" s="97" t="n"/>
       <c r="O13" s="97" t="n"/>
+      <c r="Q13" s="159" t="inlineStr">
+        <is>
+          <t>Equity weight (We)</t>
+        </is>
+      </c>
+      <c r="R13" s="168" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="S13" s="159" t="inlineStr">
+        <is>
+          <t>Target market weights</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="16" customHeight="1">
       <c r="A14" s="97" t="n"/>
@@ -6503,7 +6706,7 @@
         </is>
       </c>
       <c r="C14" s="97" t="n"/>
-      <c r="D14" s="158" t="n">
+      <c r="D14" s="167" t="n">
         <v>304537</v>
       </c>
       <c r="E14" s="97" t="n"/>
@@ -6517,6 +6720,19 @@
       <c r="M14" s="97" t="n"/>
       <c r="N14" s="97" t="n"/>
       <c r="O14" s="97" t="n"/>
+      <c r="Q14" s="159" t="inlineStr">
+        <is>
+          <t>Debt weight (Wd)</t>
+        </is>
+      </c>
+      <c r="R14" s="168" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="S14" s="159" t="inlineStr">
+        <is>
+          <t>We + Wd should = 100%</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="16" customHeight="1">
       <c r="A15" s="97" t="n"/>
@@ -6526,7 +6742,7 @@
         </is>
       </c>
       <c r="C15" s="97" t="n"/>
-      <c r="D15" s="159">
+      <c r="D15" s="169">
         <f>'3 Statement Model'!J68</f>
         <v/>
       </c>
@@ -6541,6 +6757,25 @@
       <c r="M15" s="97" t="n"/>
       <c r="N15" s="97" t="n"/>
       <c r="O15" s="97" t="n"/>
+      <c r="Q15" s="164" t="inlineStr">
+        <is>
+          <t>WACC = We×Ke + Wd×Rd_aftertax</t>
+        </is>
+      </c>
+      <c r="R15" s="165">
+        <f>R13*R9+R14*R12</f>
+        <v/>
+      </c>
+      <c r="S15" s="159" t="inlineStr">
+        <is>
+          <t>PRIMARY discount rate — linked into D6</t>
+        </is>
+      </c>
+      <c r="T15" s="164" t="inlineStr">
+        <is>
+          <t>→ D6</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="16" customHeight="1">
       <c r="A16" s="97" t="n"/>
@@ -6567,23 +6802,23 @@
           <t>Entry</t>
         </is>
       </c>
-      <c r="E17" s="160">
+      <c r="E17" s="170">
         <f>YEAR(E18)</f>
         <v/>
       </c>
-      <c r="F17" s="160">
+      <c r="F17" s="170">
         <f>YEAR(F18)</f>
         <v/>
       </c>
-      <c r="G17" s="160">
+      <c r="G17" s="170">
         <f>YEAR(G18)</f>
         <v/>
       </c>
-      <c r="H17" s="160">
+      <c r="H17" s="170">
         <f>YEAR(H18)</f>
         <v/>
       </c>
-      <c r="I17" s="160">
+      <c r="I17" s="170">
         <f>YEAR(I18)</f>
         <v/>
       </c>
@@ -6601,6 +6836,11 @@
       <c r="M17" s="111" t="n"/>
       <c r="N17" s="111" t="n"/>
       <c r="O17" s="97" t="n"/>
+      <c r="Q17" s="157" t="inlineStr">
+        <is>
+          <t>2) Unlevered Free Cash Flow</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="16" customHeight="1">
       <c r="A18" s="97" t="n"/>
@@ -6610,31 +6850,31 @@
         </is>
       </c>
       <c r="C18" s="97" t="n"/>
-      <c r="D18" s="161">
+      <c r="D18" s="171">
         <f>D9</f>
         <v/>
       </c>
-      <c r="E18" s="162">
+      <c r="E18" s="172">
         <f>DATE(YEAR($D$10)+E19,3,31)</f>
         <v/>
       </c>
-      <c r="F18" s="162">
+      <c r="F18" s="172">
         <f>DATE(YEAR($D$10)+F19,3,31)</f>
         <v/>
       </c>
-      <c r="G18" s="162">
+      <c r="G18" s="172">
         <f>DATE(YEAR($D$10)+G19,3,31)</f>
         <v/>
       </c>
-      <c r="H18" s="162">
+      <c r="H18" s="172">
         <f>DATE(YEAR($D$10)+H19,3,31)</f>
         <v/>
       </c>
-      <c r="I18" s="162">
+      <c r="I18" s="172">
         <f>DATE(YEAR($D$10)+I19,3,31)</f>
         <v/>
       </c>
-      <c r="J18" s="163">
+      <c r="J18" s="173">
         <f>I18</f>
         <v/>
       </c>
@@ -6644,7 +6884,7 @@
           <t>Exit EV/EBITDA (in J27) — primary</t>
         </is>
       </c>
-      <c r="M18" s="159">
+      <c r="M18" s="169">
         <f>J27</f>
         <v/>
       </c>
@@ -6653,6 +6893,11 @@
         <v/>
       </c>
       <c r="O18" s="97" t="n"/>
+      <c r="Q18" s="164" t="inlineStr">
+        <is>
+          <t>FCFF = EBIT − EBIT×t + D&amp;A − CapEx − ΔNWC</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="16" customHeight="1">
       <c r="A19" s="97" t="n"/>
@@ -6663,22 +6908,22 @@
       </c>
       <c r="C19" s="118" t="n"/>
       <c r="D19" s="115" t="n"/>
-      <c r="E19" s="164" t="n">
+      <c r="E19" s="174" t="n">
         <v>0</v>
       </c>
-      <c r="F19" s="161">
+      <c r="F19" s="171">
         <f>E19+1</f>
         <v/>
       </c>
-      <c r="G19" s="161">
+      <c r="G19" s="171">
         <f>F19+1</f>
         <v/>
       </c>
-      <c r="H19" s="161">
+      <c r="H19" s="171">
         <f>G19+1</f>
         <v/>
       </c>
-      <c r="I19" s="161">
+      <c r="I19" s="171">
         <f>H19+1</f>
         <v/>
       </c>
@@ -6689,7 +6934,7 @@
           <t>Gordon cross-check</t>
         </is>
       </c>
-      <c r="M19" s="159">
+      <c r="M19" s="169">
         <f>IF(($D$6-$D$7)&lt;=0,"WACC must exceed g",$I$26*(1+$D$7)/($D$6-$D$7))</f>
         <v/>
       </c>
@@ -6698,6 +6943,15 @@
         <v/>
       </c>
       <c r="O19" s="97" t="n"/>
+      <c r="Q19" s="159" t="inlineStr">
+        <is>
+          <t>Excel (col E example)</t>
+        </is>
+      </c>
+      <c r="R19" s="164">
+        <f>E21-E22+E23-E24-E25</f>
+        <v/>
+      </c>
     </row>
     <row r="20" ht="16" customHeight="1">
       <c r="A20" s="97" t="n"/>
@@ -6708,23 +6962,23 @@
       </c>
       <c r="C20" s="97" t="n"/>
       <c r="D20" s="97" t="n"/>
-      <c r="E20" s="161">
+      <c r="E20" s="171">
         <f>YEARFRAC(D18,E18)</f>
         <v/>
       </c>
-      <c r="F20" s="161">
+      <c r="F20" s="171">
         <f>YEARFRAC(E18,F18)</f>
         <v/>
       </c>
-      <c r="G20" s="161">
+      <c r="G20" s="171">
         <f>YEARFRAC(F18,G18)</f>
         <v/>
       </c>
-      <c r="H20" s="161">
+      <c r="H20" s="171">
         <f>YEARFRAC(G18,H18)</f>
         <v/>
       </c>
-      <c r="I20" s="161">
+      <c r="I20" s="171">
         <f>YEARFRAC(H18,I18)</f>
         <v/>
       </c>
@@ -6735,7 +6989,7 @@
           <t>Implied Gordon exit multiple</t>
         </is>
       </c>
-      <c r="M20" s="159">
+      <c r="M20" s="169">
         <f>IF(($I$21+$I$23)=0,0,M19/($I$21+$I$23))</f>
         <v/>
       </c>
@@ -6744,6 +6998,20 @@
         <v/>
       </c>
       <c r="O20" s="97" t="n"/>
+      <c r="Q20" s="159" t="inlineStr">
+        <is>
+          <t>Tax on EBIT (unlevered)</t>
+        </is>
+      </c>
+      <c r="R20" s="164">
+        <f>E21*$D$5</f>
+        <v/>
+      </c>
+      <c r="S20" s="159" t="inlineStr">
+        <is>
+          <t>NOT levered IS tax dollars</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="16" customHeight="1">
       <c r="A21" s="97" t="n"/>
@@ -6752,25 +7020,29 @@
           <t>EBIT (linked to 3-stmt)</t>
         </is>
       </c>
-      <c r="C21" s="97" t="n"/>
+      <c r="C21" s="175" t="inlineStr">
+        <is>
+          <t>EBIT</t>
+        </is>
+      </c>
       <c r="D21" s="97" t="n"/>
-      <c r="E21" s="159">
+      <c r="E21" s="169">
         <f>'3 Statement Model'!J26-'3 Statement Model'!J28-'3 Statement Model'!J29-'3 Statement Model'!J30</f>
         <v/>
       </c>
-      <c r="F21" s="159">
+      <c r="F21" s="169">
         <f>'3 Statement Model'!K26-'3 Statement Model'!K28-'3 Statement Model'!K29-'3 Statement Model'!K30</f>
         <v/>
       </c>
-      <c r="G21" s="159">
+      <c r="G21" s="169">
         <f>'3 Statement Model'!L26-'3 Statement Model'!L28-'3 Statement Model'!L29-'3 Statement Model'!L30</f>
         <v/>
       </c>
-      <c r="H21" s="159">
+      <c r="H21" s="169">
         <f>'3 Statement Model'!M26-'3 Statement Model'!M28-'3 Statement Model'!M29-'3 Statement Model'!M30</f>
         <v/>
       </c>
-      <c r="I21" s="159">
+      <c r="I21" s="169">
         <f>'3 Statement Model'!N26-'3 Statement Model'!N28-'3 Statement Model'!N29-'3 Statement Model'!N30</f>
         <v/>
       </c>
@@ -6780,6 +7052,20 @@
       <c r="M21" s="97" t="n"/>
       <c r="N21" s="97" t="n"/>
       <c r="O21" s="97" t="n"/>
+      <c r="Q21" s="159" t="inlineStr">
+        <is>
+          <t>FCFF check (FY5 / col I)</t>
+        </is>
+      </c>
+      <c r="R21" s="176">
+        <f>I26</f>
+        <v/>
+      </c>
+      <c r="S21" s="159" t="inlineStr">
+        <is>
+          <t>Must equal I21−I22+I23−I24−I25</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="16" customHeight="1">
       <c r="A22" s="97" t="n"/>
@@ -6788,25 +7074,29 @@
           <t>Less: Unlevered Cash Taxes (EBIT×t)</t>
         </is>
       </c>
-      <c r="C22" s="97" t="n"/>
+      <c r="C22" s="175" t="inlineStr">
+        <is>
+          <t>EBIT×t</t>
+        </is>
+      </c>
       <c r="D22" s="97" t="n"/>
-      <c r="E22" s="159">
+      <c r="E22" s="169">
         <f>E21*$D$5</f>
         <v/>
       </c>
-      <c r="F22" s="159">
+      <c r="F22" s="169">
         <f>F21*$D$5</f>
         <v/>
       </c>
-      <c r="G22" s="159">
+      <c r="G22" s="169">
         <f>G21*$D$5</f>
         <v/>
       </c>
-      <c r="H22" s="159">
+      <c r="H22" s="169">
         <f>H21*$D$5</f>
         <v/>
       </c>
-      <c r="I22" s="159">
+      <c r="I22" s="169">
         <f>I21*$D$5</f>
         <v/>
       </c>
@@ -6824,25 +7114,29 @@
           <t>Plus: D&amp;A (linked to 3-stmt)</t>
         </is>
       </c>
-      <c r="C23" s="97" t="n"/>
+      <c r="C23" s="175" t="inlineStr">
+        <is>
+          <t>+D&amp;A</t>
+        </is>
+      </c>
       <c r="D23" s="97" t="n"/>
-      <c r="E23" s="159">
+      <c r="E23" s="169">
         <f>'3 Statement Model'!J30</f>
         <v/>
       </c>
-      <c r="F23" s="159">
+      <c r="F23" s="169">
         <f>'3 Statement Model'!K30</f>
         <v/>
       </c>
-      <c r="G23" s="159">
+      <c r="G23" s="169">
         <f>'3 Statement Model'!L30</f>
         <v/>
       </c>
-      <c r="H23" s="159">
+      <c r="H23" s="169">
         <f>'3 Statement Model'!M30</f>
         <v/>
       </c>
-      <c r="I23" s="159">
+      <c r="I23" s="169">
         <f>'3 Statement Model'!N30</f>
         <v/>
       </c>
@@ -6852,6 +7146,11 @@
       <c r="M23" s="97" t="n"/>
       <c r="N23" s="97" t="n"/>
       <c r="O23" s="97" t="n"/>
+      <c r="Q23" s="157" t="inlineStr">
+        <is>
+          <t>3) Terminal Value</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="16" customHeight="1">
       <c r="A24" s="97" t="n"/>
@@ -6860,25 +7159,29 @@
           <t>Less: Capex (linked to 3-stmt CF)</t>
         </is>
       </c>
-      <c r="C24" s="97" t="n"/>
+      <c r="C24" s="175" t="inlineStr">
+        <is>
+          <t>−CapEx</t>
+        </is>
+      </c>
       <c r="D24" s="97" t="n"/>
-      <c r="E24" s="159">
+      <c r="E24" s="169">
         <f>'3 Statement Model'!J68</f>
         <v/>
       </c>
-      <c r="F24" s="159">
+      <c r="F24" s="169">
         <f>'3 Statement Model'!K68</f>
         <v/>
       </c>
-      <c r="G24" s="159">
+      <c r="G24" s="169">
         <f>'3 Statement Model'!L68</f>
         <v/>
       </c>
-      <c r="H24" s="159">
+      <c r="H24" s="169">
         <f>'3 Statement Model'!M68</f>
         <v/>
       </c>
-      <c r="I24" s="159">
+      <c r="I24" s="169">
         <f>'3 Statement Model'!N68</f>
         <v/>
       </c>
@@ -6888,6 +7191,11 @@
       <c r="M24" s="97" t="n"/>
       <c r="N24" s="97" t="n"/>
       <c r="O24" s="97" t="n"/>
+      <c r="Q24" s="164" t="inlineStr">
+        <is>
+          <t>TV_exit = EBITDA_n × ExitMultiple   [PRIMARY]</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="16" customHeight="1">
       <c r="A25" s="97" t="n"/>
@@ -6896,25 +7204,29 @@
           <t>Less: ΔNWC (linked to 3-stmt CF)</t>
         </is>
       </c>
-      <c r="C25" s="97" t="n"/>
+      <c r="C25" s="175" t="inlineStr">
+        <is>
+          <t>−ΔNWC</t>
+        </is>
+      </c>
       <c r="D25" s="97" t="n"/>
-      <c r="E25" s="159">
+      <c r="E25" s="169">
         <f>'3 Statement Model'!J64</f>
         <v/>
       </c>
-      <c r="F25" s="159">
+      <c r="F25" s="169">
         <f>'3 Statement Model'!K64</f>
         <v/>
       </c>
-      <c r="G25" s="159">
+      <c r="G25" s="169">
         <f>'3 Statement Model'!L64</f>
         <v/>
       </c>
-      <c r="H25" s="159">
+      <c r="H25" s="169">
         <f>'3 Statement Model'!M64</f>
         <v/>
       </c>
-      <c r="I25" s="159">
+      <c r="I25" s="169">
         <f>'3 Statement Model'!N64</f>
         <v/>
       </c>
@@ -6924,6 +7236,19 @@
       <c r="M25" s="97" t="n"/>
       <c r="N25" s="97" t="n"/>
       <c r="O25" s="97" t="n"/>
+      <c r="Q25" s="159" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="R25" s="164">
+        <f>($I$21+$I$23)*$D$8</f>
+        <v/>
+      </c>
+      <c r="T25" s="176">
+        <f>J27</f>
+        <v/>
+      </c>
     </row>
     <row r="26" ht="16" customHeight="1">
       <c r="A26" s="97" t="n"/>
@@ -6932,25 +7257,29 @@
           <t>Unlevered FCF</t>
         </is>
       </c>
-      <c r="C26" s="97" t="n"/>
+      <c r="C26" s="175" t="inlineStr">
+        <is>
+          <t>FCFF=EBIT−tax+DA−CapEx−ΔNWC</t>
+        </is>
+      </c>
       <c r="D26" s="97" t="n"/>
-      <c r="E26" s="165">
+      <c r="E26" s="177">
         <f>E21-E22+E23-E24-E25</f>
         <v/>
       </c>
-      <c r="F26" s="165">
+      <c r="F26" s="177">
         <f>F21-F22+F23-F24-F25</f>
         <v/>
       </c>
-      <c r="G26" s="165">
+      <c r="G26" s="177">
         <f>G21-G22+G23-G24-G25</f>
         <v/>
       </c>
-      <c r="H26" s="165">
+      <c r="H26" s="177">
         <f>H21-H22+H23-H24-H25</f>
         <v/>
       </c>
-      <c r="I26" s="165">
+      <c r="I26" s="177">
         <f>I21-I22+I23-I24-I25</f>
         <v/>
       </c>
@@ -6960,6 +7289,11 @@
       <c r="M26" s="97" t="n"/>
       <c r="N26" s="97" t="n"/>
       <c r="O26" s="97" t="n"/>
+      <c r="Q26" s="164" t="inlineStr">
+        <is>
+          <t>TV_gordon = FCFF_n×(1+g)/(WACC−g)   [CHECK]</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="16" customHeight="1">
       <c r="A27" s="97" t="n"/>
@@ -6969,7 +7303,7 @@
         </is>
       </c>
       <c r="C27" s="97" t="n"/>
-      <c r="D27" s="166">
+      <c r="D27" s="178">
         <f>-I35</f>
         <v/>
       </c>
@@ -6978,7 +7312,7 @@
       <c r="G27" s="97" t="n"/>
       <c r="H27" s="97" t="n"/>
       <c r="I27" s="97" t="n"/>
-      <c r="J27" s="159">
+      <c r="J27" s="169">
         <f>($I$21+$I$23)*$D$8</f>
         <v/>
       </c>
@@ -6987,6 +7321,19 @@
       <c r="M27" s="97" t="n"/>
       <c r="N27" s="97" t="n"/>
       <c r="O27" s="97" t="n"/>
+      <c r="Q27" s="159" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="R27" s="164">
+        <f>IF(($D$6-$D$7)&lt;=0,"err",$I$26*(1+$D$7)/($D$6-$D$7))</f>
+        <v/>
+      </c>
+      <c r="T27" s="176">
+        <f>M19</f>
+        <v/>
+      </c>
     </row>
     <row r="28" ht="16" customHeight="1">
       <c r="A28" s="97" t="n"/>
@@ -6996,30 +7343,30 @@
         </is>
       </c>
       <c r="C28" s="97" t="n"/>
-      <c r="D28" s="165" t="n">
+      <c r="D28" s="177" t="n">
         <v>0</v>
       </c>
-      <c r="E28" s="167">
+      <c r="E28" s="179">
         <f>E27+E26</f>
         <v/>
       </c>
-      <c r="F28" s="167">
+      <c r="F28" s="179">
         <f>F27+F26</f>
         <v/>
       </c>
-      <c r="G28" s="167">
+      <c r="G28" s="179">
         <f>G27+G26</f>
         <v/>
       </c>
-      <c r="H28" s="167">
+      <c r="H28" s="179">
         <f>H27+H26</f>
         <v/>
       </c>
-      <c r="I28" s="167">
+      <c r="I28" s="179">
         <f>I27+I26</f>
         <v/>
       </c>
-      <c r="J28" s="167">
+      <c r="J28" s="179">
         <f>J27+J26</f>
         <v/>
       </c>
@@ -7028,6 +7375,20 @@
       <c r="M28" s="97" t="n"/>
       <c r="N28" s="97" t="n"/>
       <c r="O28" s="97" t="n"/>
+      <c r="Q28" s="159" t="inlineStr">
+        <is>
+          <t>Implied Gordon exit multiple</t>
+        </is>
+      </c>
+      <c r="R28" s="180">
+        <f>IF(($I$21+$I$23)=0,0,T27/($I$21+$I$23))</f>
+        <v/>
+      </c>
+      <c r="S28" s="159" t="inlineStr">
+        <is>
+          <t>Gordon TV / EBITDA_n</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="16" customHeight="1">
       <c r="A29" s="97" t="n"/>
@@ -7037,31 +7398,31 @@
         </is>
       </c>
       <c r="C29" s="97" t="n"/>
-      <c r="D29" s="166">
+      <c r="D29" s="178">
         <f>D27+D26</f>
         <v/>
       </c>
-      <c r="E29" s="159">
+      <c r="E29" s="169">
         <f>E27+E26</f>
         <v/>
       </c>
-      <c r="F29" s="159">
+      <c r="F29" s="169">
         <f>F27+F26</f>
         <v/>
       </c>
-      <c r="G29" s="159">
+      <c r="G29" s="169">
         <f>G27+G26</f>
         <v/>
       </c>
-      <c r="H29" s="159">
+      <c r="H29" s="169">
         <f>H27+H26</f>
         <v/>
       </c>
-      <c r="I29" s="159">
+      <c r="I29" s="169">
         <f>I27+I26</f>
         <v/>
       </c>
-      <c r="J29" s="159">
+      <c r="J29" s="169">
         <f>J27</f>
         <v/>
       </c>
@@ -7085,6 +7446,11 @@
       <c r="M30" s="97" t="n"/>
       <c r="N30" s="97" t="n"/>
       <c r="O30" s="97" t="n"/>
+      <c r="Q30" s="157" t="inlineStr">
+        <is>
+          <t>4) Enterprise → Equity → $/share</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="16" customHeight="1">
       <c r="A31" s="97" t="n"/>
@@ -7112,6 +7478,11 @@
       <c r="M31" s="111" t="n"/>
       <c r="N31" s="111" t="n"/>
       <c r="O31" s="97" t="n"/>
+      <c r="Q31" s="164" t="inlineStr">
+        <is>
+          <t>EV = XNPV(WACC, TransactionCF, mid-year dates)</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="16" customHeight="1">
       <c r="A32" s="97" t="n"/>
@@ -7121,7 +7492,7 @@
         </is>
       </c>
       <c r="C32" s="97" t="n"/>
-      <c r="D32" s="159">
+      <c r="D32" s="169">
         <f>XNPV(D6,D28:J28,D18:J18)</f>
         <v/>
       </c>
@@ -7132,7 +7503,7 @@
         </is>
       </c>
       <c r="H32" s="97" t="n"/>
-      <c r="I32" s="166">
+      <c r="I32" s="178">
         <f>D12*D11</f>
         <v/>
       </c>
@@ -7148,6 +7519,19 @@
         <v/>
       </c>
       <c r="O32" s="97" t="n"/>
+      <c r="Q32" s="159" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="R32" s="164">
+        <f>XNPV(D6,D28:J28,D18:J18)</f>
+        <v/>
+      </c>
+      <c r="T32" s="176">
+        <f>D32</f>
+        <v/>
+      </c>
     </row>
     <row r="33" ht="16" customHeight="1">
       <c r="A33" s="97" t="n"/>
@@ -7157,7 +7541,7 @@
         </is>
       </c>
       <c r="C33" s="97" t="n"/>
-      <c r="D33" s="166">
+      <c r="D33" s="178">
         <f>+D14</f>
         <v/>
       </c>
@@ -7168,7 +7552,7 @@
         </is>
       </c>
       <c r="H33" s="97" t="n"/>
-      <c r="I33" s="166">
+      <c r="I33" s="178">
         <f>D13</f>
         <v/>
       </c>
@@ -7184,6 +7568,20 @@
         <v/>
       </c>
       <c r="O33" s="97" t="n"/>
+      <c r="Q33" s="164" t="inlineStr">
+        <is>
+          <t>Equity = EV + Cash − Debt</t>
+        </is>
+      </c>
+      <c r="R33" s="176">
+        <f>D35</f>
+        <v/>
+      </c>
+      <c r="S33" s="159" t="inlineStr">
+        <is>
+          <t>D32+D33−D34</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="16" customHeight="1">
       <c r="A34" s="97" t="n"/>
@@ -7193,7 +7591,7 @@
         </is>
       </c>
       <c r="C34" s="97" t="n"/>
-      <c r="D34" s="166">
+      <c r="D34" s="178">
         <f>+D13</f>
         <v/>
       </c>
@@ -7204,7 +7602,7 @@
         </is>
       </c>
       <c r="H34" s="97" t="n"/>
-      <c r="I34" s="166">
+      <c r="I34" s="178">
         <f>+D14</f>
         <v/>
       </c>
@@ -7213,6 +7611,20 @@
       <c r="M34" s="97" t="n"/>
       <c r="N34" s="97" t="n"/>
       <c r="O34" s="97" t="n"/>
+      <c r="Q34" s="164" t="inlineStr">
+        <is>
+          <t>$/share = Equity / Shares</t>
+        </is>
+      </c>
+      <c r="R34" s="181">
+        <f>D37</f>
+        <v/>
+      </c>
+      <c r="S34" s="159" t="inlineStr">
+        <is>
+          <t>Intrinsic value per share</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="16" customHeight="1">
       <c r="A35" s="97" t="n"/>
@@ -7222,7 +7634,7 @@
         </is>
       </c>
       <c r="C35" s="97" t="n"/>
-      <c r="D35" s="165">
+      <c r="D35" s="177">
         <f>D32+D33-D34</f>
         <v/>
       </c>
@@ -7233,7 +7645,7 @@
         </is>
       </c>
       <c r="H35" s="97" t="n"/>
-      <c r="I35" s="165">
+      <c r="I35" s="177">
         <f>I32+I33-I34</f>
         <v/>
       </c>
@@ -7246,6 +7658,20 @@
       <c r="M35" s="111" t="n"/>
       <c r="N35" s="111" t="n"/>
       <c r="O35" s="97" t="n"/>
+      <c r="Q35" s="159" t="inlineStr">
+        <is>
+          <t>Upside vs market</t>
+        </is>
+      </c>
+      <c r="R35" s="182">
+        <f>D37/D11-1</f>
+        <v/>
+      </c>
+      <c r="S35" s="159" t="inlineStr">
+        <is>
+          <t>Intrinsic / Current Price − 1</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="16" customHeight="1">
       <c r="A36" s="97" t="n"/>
@@ -7255,7 +7681,7 @@
       <c r="E36" s="97" t="n"/>
       <c r="G36" s="97" t="n"/>
       <c r="H36" s="97" t="n"/>
-      <c r="I36" s="168" t="n"/>
+      <c r="I36" s="183" t="n"/>
       <c r="J36" s="97" t="n"/>
       <c r="L36" s="97" t="inlineStr">
         <is>
@@ -7263,7 +7689,7 @@
         </is>
       </c>
       <c r="M36" s="97" t="n"/>
-      <c r="N36" s="168">
+      <c r="N36" s="183">
         <f>I37</f>
         <v/>
       </c>
@@ -7277,7 +7703,7 @@
         </is>
       </c>
       <c r="C37" s="97" t="n"/>
-      <c r="D37" s="166">
+      <c r="D37" s="178">
         <f>D35/D12</f>
         <v/>
       </c>
@@ -7288,7 +7714,7 @@
         </is>
       </c>
       <c r="H37" s="97" t="n"/>
-      <c r="I37" s="166">
+      <c r="I37" s="178">
         <f>D11</f>
         <v/>
       </c>
@@ -7299,11 +7725,16 @@
         </is>
       </c>
       <c r="M37" s="97" t="n"/>
-      <c r="N37" s="168">
+      <c r="N37" s="183">
         <f>D37-I37</f>
         <v/>
       </c>
       <c r="O37" s="97" t="n"/>
+      <c r="Q37" s="157" t="inlineStr">
+        <is>
+          <t>5) Operating NWC (feeds ΔNWC → FCFF)</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="16" customHeight="1">
       <c r="A38" s="97" t="n"/>
@@ -7321,11 +7752,16 @@
         </is>
       </c>
       <c r="M38" s="97" t="n"/>
-      <c r="N38" s="168">
+      <c r="N38" s="183">
         <f>SUM(N36:N37)</f>
         <v/>
       </c>
       <c r="O38" s="97" t="n"/>
+      <c r="Q38" s="164" t="inlineStr">
+        <is>
+          <t>NWC = AR + Inventory − AP − DeferredRevenue</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="16" customHeight="1">
       <c r="A39" s="97" t="n"/>
@@ -7340,6 +7776,20 @@
       <c r="M39" s="97" t="n"/>
       <c r="N39" s="97" t="n"/>
       <c r="O39" s="97" t="n"/>
+      <c r="Q39" s="164" t="inlineStr">
+        <is>
+          <t>ΔNWC_t = NWC_t − NWC_(t−1)</t>
+        </is>
+      </c>
+      <c r="S39" s="159" t="inlineStr">
+        <is>
+          <t>Linked from 3-statement CF row 64</t>
+        </is>
+      </c>
+      <c r="T39" s="176">
+        <f>I25</f>
+        <v/>
+      </c>
     </row>
     <row r="40" ht="16" customHeight="1">
       <c r="A40" s="97" t="n"/>
@@ -7376,6 +7826,11 @@
       <c r="M41" s="111" t="n"/>
       <c r="N41" s="111" t="n"/>
       <c r="O41" s="97" t="n"/>
+      <c r="Q41" s="157" t="inlineStr">
+        <is>
+          <t>Sources (SEC preferred)</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="16" customHeight="1">
       <c r="A42" s="97" t="n"/>
@@ -7396,6 +7851,11 @@
         </is>
       </c>
       <c r="O42" s="97" t="n"/>
+      <c r="Q42" s="159" t="inlineStr">
+        <is>
+          <t>10-K: sec.gov/.../fico-20250930.htm</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="16" customHeight="1">
       <c r="A43" s="97" t="n"/>
@@ -7412,6 +7872,11 @@
       <c r="H43" s="97" t="n"/>
       <c r="N43" s="69" t="n"/>
       <c r="O43" s="97" t="n"/>
+      <c r="Q43" s="159" t="inlineStr">
+        <is>
+          <t>10-Q: sec.gov/.../fico-20260630.htm</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="16" customHeight="1">
       <c r="A44" s="97" t="n"/>
@@ -7428,6 +7893,11 @@
       <c r="H44" s="97" t="n"/>
       <c r="N44" s="69" t="n"/>
       <c r="O44" s="97" t="n"/>
+      <c r="Q44" s="159" t="inlineStr">
+        <is>
+          <t>8-K 6.250% notes: sec.gov/.../d56220d8k.htm</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="16" customHeight="1">
       <c r="A45" s="97" t="n"/>
@@ -7444,6 +7914,11 @@
       <c r="H45" s="97" t="n"/>
       <c r="N45" s="69" t="n"/>
       <c r="O45" s="97" t="n"/>
+      <c r="Q45" s="159" t="inlineStr">
+        <is>
+          <t>Damodaran ERP: pages.stern.nyu.edu/adamodar/</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="16" customHeight="1">
       <c r="A46" s="97" t="n"/>
@@ -7460,6 +7935,11 @@
       <c r="H46" s="97" t="n"/>
       <c r="N46" s="69" t="n"/>
       <c r="O46" s="97" t="n"/>
+      <c r="Q46" s="159" t="inlineStr">
+        <is>
+          <t>FRED DGS10 + Yahoo FICO beta</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="16" customHeight="1">
       <c r="A47" s="97" t="n"/>
@@ -7695,6 +8175,27 @@
       <c r="L61" s="97" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="19">
+    <mergeCell ref="Q30:T30"/>
+    <mergeCell ref="Q17:T17"/>
+    <mergeCell ref="Q26:S26"/>
+    <mergeCell ref="Q45:T45"/>
+    <mergeCell ref="Q31:S31"/>
+    <mergeCell ref="Q2:T2"/>
+    <mergeCell ref="Q41:T41"/>
+    <mergeCell ref="Q3:T3"/>
+    <mergeCell ref="Q43:T43"/>
+    <mergeCell ref="Q37:T37"/>
+    <mergeCell ref="Q42:T42"/>
+    <mergeCell ref="Q5:T5"/>
+    <mergeCell ref="Q46:T46"/>
+    <mergeCell ref="Q23:T23"/>
+    <mergeCell ref="Q38:T38"/>
+    <mergeCell ref="R19:T19"/>
+    <mergeCell ref="Q24:S24"/>
+    <mergeCell ref="Q18:S18"/>
+    <mergeCell ref="Q44:T44"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/FICO/output/FICO_Completed_Model.xlsx
+++ b/FICO/output/FICO_Completed_Model.xlsx
@@ -100,7 +100,7 @@
     <numFmt numFmtId="178" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="179" formatCode="0.0"/>
   </numFmts>
-  <fonts count="45">
+  <fonts count="48">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -376,9 +376,26 @@
       <color rgb="00666666"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <color rgb="000563C1"/>
+      <u val="single"/>
+    </font>
+    <font>
       <name val="Consolas"/>
       <color rgb="00000000"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00666666"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="000563C1"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Consolas"/>
@@ -444,7 +461,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -506,6 +523,50 @@
         <color rgb="00B0B0B0"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B0B0B0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B0B0B0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B0B0B0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B0B0B0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B0B0B0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B0B0B0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B0B0B0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B0B0B0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="9">
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
@@ -518,7 +579,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="184">
+  <cellXfs count="191">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="1"/>
@@ -759,10 +820,16 @@
     <xf numFmtId="177" fontId="40" fillId="8" borderId="2" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="0" fontId="41" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="39" fillId="10" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="40" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="164" fontId="43" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="39" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="46" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="45" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="38" fillId="7" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
@@ -770,12 +837,15 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="40" fillId="8" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="179" fontId="40" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="2" fontId="40" fillId="8" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="178" fontId="32" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="38" fillId="7" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -792,7 +862,7 @@
     <xf numFmtId="178" fontId="38" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="177" fontId="36" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="177" fontId="37" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="44" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="47" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="174" fontId="38" fillId="7" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="177" fontId="30" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="177" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -801,6 +871,8 @@
     <xf numFmtId="176" fontId="38" fillId="7" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="38" fillId="7" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="173" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="9">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6259,7 +6331,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T61"/>
+  <dimension ref="A1:V61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3.54296875" customWidth="1" min="1" max="1"/>
@@ -6276,10 +6348,12 @@
     <col width="36" customWidth="1" min="12" max="12"/>
     <col width="18" customWidth="1" min="13" max="13"/>
     <col width="9.08984375" customWidth="1" min="15" max="15"/>
-    <col width="38" customWidth="1" min="17" max="17"/>
+    <col width="40" customWidth="1" min="17" max="17"/>
     <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="44" customWidth="1" min="19" max="19"/>
-    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="36" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="52" customWidth="1" min="21" max="21"/>
+    <col width="52" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
@@ -6323,7 +6397,7 @@
       <c r="N2" s="94" t="n"/>
       <c r="Q2" s="154" t="inlineStr">
         <is>
-          <t>vengeanceaiUSCMODEL3 — LIVE EQUATIONS</t>
+          <t>vengeanceaiUSCMODEL3 — LIVE EQUATIONS + SOURCE LINKS</t>
         </is>
       </c>
     </row>
@@ -6345,7 +6419,7 @@
       <c r="O3" s="97" t="n"/>
       <c r="Q3" s="155" t="inlineStr">
         <is>
-          <t>Yellow = inputs (edit these). Green = formulas (auto-update).</t>
+          <t>Yellow = inputs (edit). Green = formulas. Blue underlined = clickable sources.</t>
         </is>
       </c>
     </row>
@@ -6369,6 +6443,36 @@
       <c r="M4" s="97" t="n"/>
       <c r="N4" s="97" t="n"/>
       <c r="O4" s="97" t="n"/>
+      <c r="Q4" s="156" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="R4" s="156" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="S4" s="156" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="T4" s="156" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="U4" s="156" t="inlineStr">
+        <is>
+          <t>Primary source (click)</t>
+        </is>
+      </c>
+      <c r="V4" s="156" t="inlineStr">
+        <is>
+          <t>Secondary source (click)</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="97" t="n"/>
@@ -6378,10 +6482,14 @@
         </is>
       </c>
       <c r="C5" s="100" t="n"/>
-      <c r="D5" s="156" t="n">
+      <c r="D5" s="157" t="n">
         <v>0.1877023903712333</v>
       </c>
-      <c r="E5" s="100" t="n"/>
+      <c r="E5" s="158" t="inlineStr">
+        <is>
+          <t>Tax source: SEC 10-K</t>
+        </is>
+      </c>
       <c r="F5" s="97" t="n"/>
       <c r="G5" s="97" t="n"/>
       <c r="H5" s="97" t="n"/>
@@ -6392,27 +6500,47 @@
       <c r="M5" s="97" t="n"/>
       <c r="N5" s="97" t="n"/>
       <c r="O5" s="97" t="n"/>
-      <c r="Q5" s="157" t="inlineStr">
-        <is>
-          <t>1) CAPM → WACC</t>
+      <c r="Q5" s="159" t="inlineStr">
+        <is>
+          <t>1) CAPM → WACC   (D6 = R15)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="97" t="n"/>
+      <c r="A6" s="160" t="inlineStr">
+        <is>
+          <t>WACC sources → columns U–V</t>
+        </is>
+      </c>
       <c r="B6" s="103" t="inlineStr">
         <is>
           <t>Discount Rate (WACC = We×Ke + Wd×Rd(1−t))</t>
         </is>
       </c>
-      <c r="C6" s="97" t="n"/>
-      <c r="D6" s="158">
+      <c r="C6" s="161" t="inlineStr">
+        <is>
+          <t>Sources →</t>
+        </is>
+      </c>
+      <c r="D6" s="162">
         <f>R15</f>
         <v/>
       </c>
-      <c r="E6" s="97" t="n"/>
-      <c r="F6" s="97" t="n"/>
-      <c r="G6" s="97" t="n"/>
+      <c r="E6" s="158" t="inlineStr">
+        <is>
+          <t>WACC sources → scroll to col U (Rf/ERP/β/Rd links)</t>
+        </is>
+      </c>
+      <c r="F6" s="158" t="inlineStr">
+        <is>
+          <t>Damodaran ERP</t>
+        </is>
+      </c>
+      <c r="G6" s="158" t="inlineStr">
+        <is>
+          <t>SEC 8-K Rd 6.250%</t>
+        </is>
+      </c>
       <c r="H6" s="97" t="n"/>
       <c r="I6" s="97" t="n"/>
       <c r="J6" s="97" t="n"/>
@@ -6421,20 +6549,34 @@
       <c r="M6" s="97" t="n"/>
       <c r="N6" s="97" t="n"/>
       <c r="O6" s="97" t="n"/>
-      <c r="Q6" s="159" t="inlineStr">
+      <c r="Q6" s="163" t="inlineStr">
         <is>
           <t>Risk-free rate (Rf)</t>
         </is>
       </c>
-      <c r="R6" s="160" t="n">
+      <c r="R6" s="164" t="n">
         <v>0.0463</v>
       </c>
-      <c r="S6" s="159" t="inlineStr">
-        <is>
-          <t>US 10Y Treasury / FRED DGS10</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr"/>
+      <c r="S6" s="163" t="inlineStr">
+        <is>
+          <t>US 10Y Treasury yield</t>
+        </is>
+      </c>
+      <c r="T6" s="163" t="inlineStr">
+        <is>
+          <t>CAPM input</t>
+        </is>
+      </c>
+      <c r="U6" s="165" t="inlineStr">
+        <is>
+          <t>FRED DGS10 (US 10Y)</t>
+        </is>
+      </c>
+      <c r="V6" s="165" t="inlineStr">
+        <is>
+          <t>US Treasury Daily Par Yield Curve</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="97" t="n"/>
@@ -6444,7 +6586,7 @@
         </is>
       </c>
       <c r="C7" s="97" t="n"/>
-      <c r="D7" s="156" t="n">
+      <c r="D7" s="157" t="n">
         <v>0.03</v>
       </c>
       <c r="E7" s="97" t="n"/>
@@ -6458,20 +6600,34 @@
       <c r="M7" s="97" t="n"/>
       <c r="N7" s="97" t="n"/>
       <c r="O7" s="97" t="n"/>
-      <c r="Q7" s="159" t="inlineStr">
+      <c r="Q7" s="163" t="inlineStr">
         <is>
           <t>Equity risk premium (ERP)</t>
         </is>
       </c>
-      <c r="R7" s="160" t="n">
+      <c r="R7" s="164" t="n">
         <v>0.0428</v>
       </c>
-      <c r="S7" s="159" t="inlineStr">
+      <c r="S7" s="163" t="inlineStr">
         <is>
           <t>Damodaran implied ERP</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr"/>
+      <c r="T7" s="163" t="inlineStr">
+        <is>
+          <t>CAPM input</t>
+        </is>
+      </c>
+      <c r="U7" s="165" t="inlineStr">
+        <is>
+          <t>Damodaran Online — Implied ERP</t>
+        </is>
+      </c>
+      <c r="V7" s="165" t="inlineStr">
+        <is>
+          <t>Damodaran histimpl.xls / table</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="97" t="n"/>
@@ -6481,10 +6637,14 @@
         </is>
       </c>
       <c r="C8" s="97" t="n"/>
-      <c r="D8" s="161" t="n">
+      <c r="D8" s="166" t="n">
         <v>25</v>
       </c>
-      <c r="E8" s="97" t="n"/>
+      <c r="E8" s="158" t="inlineStr">
+        <is>
+          <t>Rd source: SEC 8-K 6.250% notes</t>
+        </is>
+      </c>
       <c r="F8" s="97" t="n"/>
       <c r="G8" s="97" t="n"/>
       <c r="H8" s="97" t="n"/>
@@ -6495,20 +6655,34 @@
       <c r="M8" s="97" t="n"/>
       <c r="N8" s="97" t="n"/>
       <c r="O8" s="97" t="n"/>
-      <c r="Q8" s="159" t="inlineStr">
+      <c r="Q8" s="163" t="inlineStr">
         <is>
           <t>Beta (β)</t>
         </is>
       </c>
-      <c r="R8" s="162" t="n">
+      <c r="R8" s="167" t="n">
         <v>1.32</v>
       </c>
-      <c r="S8" s="159" t="inlineStr">
-        <is>
-          <t>Yahoo Finance 5Y monthly</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr"/>
+      <c r="S8" s="163" t="inlineStr">
+        <is>
+          <t>Yahoo 5Y monthly beta</t>
+        </is>
+      </c>
+      <c r="T8" s="163" t="inlineStr">
+        <is>
+          <t>CAPM input</t>
+        </is>
+      </c>
+      <c r="U8" s="165" t="inlineStr">
+        <is>
+          <t>Yahoo Finance FICO Key Statistics</t>
+        </is>
+      </c>
+      <c r="V8" s="165" t="inlineStr">
+        <is>
+          <t>Yahoo Finance FICO quote</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="97" t="n"/>
@@ -6518,7 +6692,7 @@
         </is>
       </c>
       <c r="C9" s="97" t="n"/>
-      <c r="D9" s="163" t="n">
+      <c r="D9" s="168" t="n">
         <v>45930</v>
       </c>
       <c r="E9" s="97" t="n"/>
@@ -6532,25 +6706,31 @@
       <c r="M9" s="97" t="n"/>
       <c r="N9" s="97" t="n"/>
       <c r="O9" s="97" t="n"/>
-      <c r="Q9" s="164" t="inlineStr">
+      <c r="Q9" s="169" t="inlineStr">
         <is>
           <t>Ke = Rf + β × ERP</t>
         </is>
       </c>
-      <c r="R9" s="165">
+      <c r="R9" s="170">
         <f>R6+R8*R7</f>
         <v/>
       </c>
-      <c r="S9" s="159" t="inlineStr">
+      <c r="S9" s="163" t="inlineStr">
         <is>
           <t>Cost of equity (CAPM)</t>
         </is>
       </c>
-      <c r="T9" s="164" t="inlineStr">
-        <is>
-          <t>→ feeds WACC</t>
-        </is>
-      </c>
+      <c r="T9" s="169" t="inlineStr">
+        <is>
+          <t>→ WACC</t>
+        </is>
+      </c>
+      <c r="U9" s="163" t="inlineStr">
+        <is>
+          <t>Derived: R6 + R8 × R7</t>
+        </is>
+      </c>
+      <c r="V9" s="163" t="inlineStr"/>
     </row>
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="97" t="n"/>
@@ -6560,7 +6740,7 @@
         </is>
       </c>
       <c r="C10" s="97" t="n"/>
-      <c r="D10" s="163" t="n">
+      <c r="D10" s="168" t="n">
         <v>46295</v>
       </c>
       <c r="E10" s="97" t="n"/>
@@ -6574,17 +6754,32 @@
       <c r="M10" s="97" t="n"/>
       <c r="N10" s="97" t="n"/>
       <c r="O10" s="97" t="n"/>
-      <c r="Q10" s="159" t="inlineStr">
+      <c r="Q10" s="163" t="inlineStr">
         <is>
           <t>Pre-tax cost of debt (Rd)</t>
         </is>
       </c>
-      <c r="R10" s="160" t="n">
+      <c r="R10" s="164" t="n">
         <v>0.0625</v>
       </c>
-      <c r="S10" s="159" t="inlineStr">
-        <is>
-          <t>6.250% Senior Notes due 2034 (SEC 8-K)</t>
+      <c r="S10" s="163" t="inlineStr">
+        <is>
+          <t>6.250% Senior Notes due 2034</t>
+        </is>
+      </c>
+      <c r="T10" s="163" t="inlineStr">
+        <is>
+          <t>WACC input</t>
+        </is>
+      </c>
+      <c r="U10" s="165" t="inlineStr">
+        <is>
+          <t>SEC 8-K — Notes closing (6.250%)</t>
+        </is>
+      </c>
+      <c r="V10" s="165" t="inlineStr">
+        <is>
+          <t>SEC EX-99.1 — Notes pricing press release</t>
         </is>
       </c>
     </row>
@@ -6596,7 +6791,7 @@
         </is>
       </c>
       <c r="C11" s="97" t="n"/>
-      <c r="D11" s="166" t="n">
+      <c r="D11" s="171" t="n">
         <v>1046.23</v>
       </c>
       <c r="E11" s="97" t="n"/>
@@ -6610,18 +6805,33 @@
       <c r="M11" s="97" t="n"/>
       <c r="N11" s="97" t="n"/>
       <c r="O11" s="97" t="n"/>
-      <c r="Q11" s="159" t="inlineStr">
+      <c r="Q11" s="163" t="inlineStr">
         <is>
           <t>Tax rate (t)</t>
         </is>
       </c>
-      <c r="R11" s="165">
+      <c r="R11" s="170">
         <f>$D$5</f>
         <v/>
       </c>
-      <c r="S11" s="159" t="inlineStr">
-        <is>
-          <t>Linked to DCF tax assumption (FY25 effective)</t>
+      <c r="S11" s="163" t="inlineStr">
+        <is>
+          <t>FY25 effective = 150,649 / 802,595</t>
+        </is>
+      </c>
+      <c r="T11" s="163" t="inlineStr">
+        <is>
+          <t>Linked D5</t>
+        </is>
+      </c>
+      <c r="U11" s="165" t="inlineStr">
+        <is>
+          <t>SEC 10-K FY2025 (tax / EBT)</t>
+        </is>
+      </c>
+      <c r="V11" s="165" t="inlineStr">
+        <is>
+          <t>SEC companyfacts XBRL (CIK 0000814547)</t>
         </is>
       </c>
     </row>
@@ -6633,7 +6843,7 @@
         </is>
       </c>
       <c r="C12" s="97" t="n"/>
-      <c r="D12" s="167" t="n">
+      <c r="D12" s="172" t="n">
         <v>21597.635</v>
       </c>
       <c r="E12" s="97" t="n"/>
@@ -6647,20 +6857,31 @@
       <c r="M12" s="97" t="n"/>
       <c r="N12" s="97" t="n"/>
       <c r="O12" s="97" t="n"/>
-      <c r="Q12" s="164" t="inlineStr">
+      <c r="Q12" s="169" t="inlineStr">
         <is>
           <t>Rd_aftertax = Rd × (1 − t)</t>
         </is>
       </c>
-      <c r="R12" s="165">
+      <c r="R12" s="170">
         <f>R10*(1-R11)</f>
         <v/>
       </c>
-      <c r="S12" s="159" t="inlineStr">
+      <c r="S12" s="163" t="inlineStr">
         <is>
           <t>After-tax cost of debt</t>
         </is>
       </c>
+      <c r="T12" s="169" t="inlineStr">
+        <is>
+          <t>→ WACC</t>
+        </is>
+      </c>
+      <c r="U12" s="163" t="inlineStr">
+        <is>
+          <t>Derived: R10 × (1 − R11)</t>
+        </is>
+      </c>
+      <c r="V12" s="163" t="inlineStr"/>
     </row>
     <row r="13" ht="16" customHeight="1">
       <c r="A13" s="97" t="n"/>
@@ -6670,7 +6891,7 @@
         </is>
       </c>
       <c r="C13" s="97" t="n"/>
-      <c r="D13" s="167" t="n">
+      <c r="D13" s="172" t="n">
         <v>5582389</v>
       </c>
       <c r="E13" s="97" t="n"/>
@@ -6684,17 +6905,32 @@
       <c r="M13" s="97" t="n"/>
       <c r="N13" s="97" t="n"/>
       <c r="O13" s="97" t="n"/>
-      <c r="Q13" s="159" t="inlineStr">
+      <c r="Q13" s="163" t="inlineStr">
         <is>
           <t>Equity weight (We)</t>
         </is>
       </c>
-      <c r="R13" s="168" t="n">
+      <c r="R13" s="173" t="n">
         <v>0.8</v>
       </c>
-      <c r="S13" s="159" t="inlineStr">
-        <is>
-          <t>Target market weights</t>
+      <c r="S13" s="163" t="inlineStr">
+        <is>
+          <t>Target ~80% equity at market</t>
+        </is>
+      </c>
+      <c r="T13" s="163" t="inlineStr">
+        <is>
+          <t>WACC weight</t>
+        </is>
+      </c>
+      <c r="U13" s="165" t="inlineStr">
+        <is>
+          <t>SEC 10-Q Q3 FY2026 (debt / capital)</t>
+        </is>
+      </c>
+      <c r="V13" s="165" t="inlineStr">
+        <is>
+          <t>Yahoo market cap for E/(D+E)</t>
         </is>
       </c>
     </row>
@@ -6706,7 +6942,7 @@
         </is>
       </c>
       <c r="C14" s="97" t="n"/>
-      <c r="D14" s="167" t="n">
+      <c r="D14" s="172" t="n">
         <v>304537</v>
       </c>
       <c r="E14" s="97" t="n"/>
@@ -6720,17 +6956,32 @@
       <c r="M14" s="97" t="n"/>
       <c r="N14" s="97" t="n"/>
       <c r="O14" s="97" t="n"/>
-      <c r="Q14" s="159" t="inlineStr">
+      <c r="Q14" s="163" t="inlineStr">
         <is>
           <t>Debt weight (Wd)</t>
         </is>
       </c>
-      <c r="R14" s="168" t="n">
+      <c r="R14" s="173" t="n">
         <v>0.2</v>
       </c>
-      <c r="S14" s="159" t="inlineStr">
-        <is>
-          <t>We + Wd should = 100%</t>
+      <c r="S14" s="163" t="inlineStr">
+        <is>
+          <t>Target ~20% debt (We+Wd=100%)</t>
+        </is>
+      </c>
+      <c r="T14" s="163" t="inlineStr">
+        <is>
+          <t>WACC weight</t>
+        </is>
+      </c>
+      <c r="U14" s="165" t="inlineStr">
+        <is>
+          <t>SEC 10-Q — total debt $5,582,389k</t>
+        </is>
+      </c>
+      <c r="V14" s="165" t="inlineStr">
+        <is>
+          <t>SEC 10-K — senior notes footnote</t>
         </is>
       </c>
     </row>
@@ -6742,7 +6993,7 @@
         </is>
       </c>
       <c r="C15" s="97" t="n"/>
-      <c r="D15" s="169">
+      <c r="D15" s="174">
         <f>'3 Statement Model'!J68</f>
         <v/>
       </c>
@@ -6757,23 +7008,33 @@
       <c r="M15" s="97" t="n"/>
       <c r="N15" s="97" t="n"/>
       <c r="O15" s="97" t="n"/>
-      <c r="Q15" s="164" t="inlineStr">
+      <c r="Q15" s="169" t="inlineStr">
         <is>
           <t>WACC = We×Ke + Wd×Rd_aftertax</t>
         </is>
       </c>
-      <c r="R15" s="165">
+      <c r="R15" s="170">
         <f>R13*R9+R14*R12</f>
         <v/>
       </c>
-      <c r="S15" s="159" t="inlineStr">
-        <is>
-          <t>PRIMARY discount rate — linked into D6</t>
-        </is>
-      </c>
-      <c r="T15" s="164" t="inlineStr">
+      <c r="S15" s="163" t="inlineStr">
+        <is>
+          <t>PRIMARY discount rate → cell D6</t>
+        </is>
+      </c>
+      <c r="T15" s="169" t="inlineStr">
         <is>
           <t>→ D6</t>
+        </is>
+      </c>
+      <c r="U15" s="165" t="inlineStr">
+        <is>
+          <t>SEC filings (tax, debt coupons)</t>
+        </is>
+      </c>
+      <c r="V15" s="165" t="inlineStr">
+        <is>
+          <t>Damodaran (ERP methodology)</t>
         </is>
       </c>
     </row>
@@ -6802,23 +7063,23 @@
           <t>Entry</t>
         </is>
       </c>
-      <c r="E17" s="170">
+      <c r="E17" s="175">
         <f>YEAR(E18)</f>
         <v/>
       </c>
-      <c r="F17" s="170">
+      <c r="F17" s="175">
         <f>YEAR(F18)</f>
         <v/>
       </c>
-      <c r="G17" s="170">
+      <c r="G17" s="175">
         <f>YEAR(G18)</f>
         <v/>
       </c>
-      <c r="H17" s="170">
+      <c r="H17" s="175">
         <f>YEAR(H18)</f>
         <v/>
       </c>
-      <c r="I17" s="170">
+      <c r="I17" s="175">
         <f>YEAR(I18)</f>
         <v/>
       </c>
@@ -6836,7 +7097,7 @@
       <c r="M17" s="111" t="n"/>
       <c r="N17" s="111" t="n"/>
       <c r="O17" s="97" t="n"/>
-      <c r="Q17" s="157" t="inlineStr">
+      <c r="Q17" s="159" t="inlineStr">
         <is>
           <t>2) Unlevered Free Cash Flow</t>
         </is>
@@ -6850,31 +7111,31 @@
         </is>
       </c>
       <c r="C18" s="97" t="n"/>
-      <c r="D18" s="171">
+      <c r="D18" s="176">
         <f>D9</f>
         <v/>
       </c>
-      <c r="E18" s="172">
+      <c r="E18" s="177">
         <f>DATE(YEAR($D$10)+E19,3,31)</f>
         <v/>
       </c>
-      <c r="F18" s="172">
+      <c r="F18" s="177">
         <f>DATE(YEAR($D$10)+F19,3,31)</f>
         <v/>
       </c>
-      <c r="G18" s="172">
+      <c r="G18" s="177">
         <f>DATE(YEAR($D$10)+G19,3,31)</f>
         <v/>
       </c>
-      <c r="H18" s="172">
+      <c r="H18" s="177">
         <f>DATE(YEAR($D$10)+H19,3,31)</f>
         <v/>
       </c>
-      <c r="I18" s="172">
+      <c r="I18" s="177">
         <f>DATE(YEAR($D$10)+I19,3,31)</f>
         <v/>
       </c>
-      <c r="J18" s="173">
+      <c r="J18" s="178">
         <f>I18</f>
         <v/>
       </c>
@@ -6884,7 +7145,7 @@
           <t>Exit EV/EBITDA (in J27) — primary</t>
         </is>
       </c>
-      <c r="M18" s="169">
+      <c r="M18" s="174">
         <f>J27</f>
         <v/>
       </c>
@@ -6893,9 +7154,19 @@
         <v/>
       </c>
       <c r="O18" s="97" t="n"/>
-      <c r="Q18" s="164" t="inlineStr">
+      <c r="Q18" s="169" t="inlineStr">
         <is>
           <t>FCFF = EBIT − EBIT×t + D&amp;A − CapEx − ΔNWC</t>
+        </is>
+      </c>
+      <c r="U18" s="165" t="inlineStr">
+        <is>
+          <t>Drivers from SEC XBRL → 3-statement</t>
+        </is>
+      </c>
+      <c r="V18" s="165" t="inlineStr">
+        <is>
+          <t>SEC 10-K historical IS/CF</t>
         </is>
       </c>
     </row>
@@ -6908,22 +7179,22 @@
       </c>
       <c r="C19" s="118" t="n"/>
       <c r="D19" s="115" t="n"/>
-      <c r="E19" s="174" t="n">
+      <c r="E19" s="179" t="n">
         <v>0</v>
       </c>
-      <c r="F19" s="171">
+      <c r="F19" s="176">
         <f>E19+1</f>
         <v/>
       </c>
-      <c r="G19" s="171">
+      <c r="G19" s="176">
         <f>F19+1</f>
         <v/>
       </c>
-      <c r="H19" s="171">
+      <c r="H19" s="176">
         <f>G19+1</f>
         <v/>
       </c>
-      <c r="I19" s="171">
+      <c r="I19" s="176">
         <f>H19+1</f>
         <v/>
       </c>
@@ -6934,7 +7205,7 @@
           <t>Gordon cross-check</t>
         </is>
       </c>
-      <c r="M19" s="169">
+      <c r="M19" s="174">
         <f>IF(($D$6-$D$7)&lt;=0,"WACC must exceed g",$I$26*(1+$D$7)/($D$6-$D$7))</f>
         <v/>
       </c>
@@ -6943,12 +7214,12 @@
         <v/>
       </c>
       <c r="O19" s="97" t="n"/>
-      <c r="Q19" s="159" t="inlineStr">
+      <c r="Q19" s="163" t="inlineStr">
         <is>
           <t>Excel (col E example)</t>
         </is>
       </c>
-      <c r="R19" s="164">
+      <c r="R19" s="169">
         <f>E21-E22+E23-E24-E25</f>
         <v/>
       </c>
@@ -6962,23 +7233,23 @@
       </c>
       <c r="C20" s="97" t="n"/>
       <c r="D20" s="97" t="n"/>
-      <c r="E20" s="171">
+      <c r="E20" s="176">
         <f>YEARFRAC(D18,E18)</f>
         <v/>
       </c>
-      <c r="F20" s="171">
+      <c r="F20" s="176">
         <f>YEARFRAC(E18,F18)</f>
         <v/>
       </c>
-      <c r="G20" s="171">
+      <c r="G20" s="176">
         <f>YEARFRAC(F18,G18)</f>
         <v/>
       </c>
-      <c r="H20" s="171">
+      <c r="H20" s="176">
         <f>YEARFRAC(G18,H18)</f>
         <v/>
       </c>
-      <c r="I20" s="171">
+      <c r="I20" s="176">
         <f>YEARFRAC(H18,I18)</f>
         <v/>
       </c>
@@ -6989,7 +7260,7 @@
           <t>Implied Gordon exit multiple</t>
         </is>
       </c>
-      <c r="M20" s="169">
+      <c r="M20" s="174">
         <f>IF(($I$21+$I$23)=0,0,M19/($I$21+$I$23))</f>
         <v/>
       </c>
@@ -6998,18 +7269,23 @@
         <v/>
       </c>
       <c r="O20" s="97" t="n"/>
-      <c r="Q20" s="159" t="inlineStr">
+      <c r="Q20" s="163" t="inlineStr">
         <is>
           <t>Tax on EBIT (unlevered)</t>
         </is>
       </c>
-      <c r="R20" s="164">
+      <c r="R20" s="169">
         <f>E21*$D$5</f>
         <v/>
       </c>
-      <c r="S20" s="159" t="inlineStr">
+      <c r="S20" s="163" t="inlineStr">
         <is>
           <t>NOT levered IS tax dollars</t>
+        </is>
+      </c>
+      <c r="U20" s="165" t="inlineStr">
+        <is>
+          <t>Tax rate from SEC 10-K effective rate</t>
         </is>
       </c>
     </row>
@@ -7020,29 +7296,29 @@
           <t>EBIT (linked to 3-stmt)</t>
         </is>
       </c>
-      <c r="C21" s="175" t="inlineStr">
+      <c r="C21" s="180" t="inlineStr">
         <is>
           <t>EBIT</t>
         </is>
       </c>
       <c r="D21" s="97" t="n"/>
-      <c r="E21" s="169">
+      <c r="E21" s="174">
         <f>'3 Statement Model'!J26-'3 Statement Model'!J28-'3 Statement Model'!J29-'3 Statement Model'!J30</f>
         <v/>
       </c>
-      <c r="F21" s="169">
+      <c r="F21" s="174">
         <f>'3 Statement Model'!K26-'3 Statement Model'!K28-'3 Statement Model'!K29-'3 Statement Model'!K30</f>
         <v/>
       </c>
-      <c r="G21" s="169">
+      <c r="G21" s="174">
         <f>'3 Statement Model'!L26-'3 Statement Model'!L28-'3 Statement Model'!L29-'3 Statement Model'!L30</f>
         <v/>
       </c>
-      <c r="H21" s="169">
+      <c r="H21" s="174">
         <f>'3 Statement Model'!M26-'3 Statement Model'!M28-'3 Statement Model'!M29-'3 Statement Model'!M30</f>
         <v/>
       </c>
-      <c r="I21" s="169">
+      <c r="I21" s="174">
         <f>'3 Statement Model'!N26-'3 Statement Model'!N28-'3 Statement Model'!N29-'3 Statement Model'!N30</f>
         <v/>
       </c>
@@ -7052,16 +7328,16 @@
       <c r="M21" s="97" t="n"/>
       <c r="N21" s="97" t="n"/>
       <c r="O21" s="97" t="n"/>
-      <c r="Q21" s="159" t="inlineStr">
+      <c r="Q21" s="163" t="inlineStr">
         <is>
           <t>FCFF check (FY5 / col I)</t>
         </is>
       </c>
-      <c r="R21" s="176">
+      <c r="R21" s="181">
         <f>I26</f>
         <v/>
       </c>
-      <c r="S21" s="159" t="inlineStr">
+      <c r="S21" s="163" t="inlineStr">
         <is>
           <t>Must equal I21−I22+I23−I24−I25</t>
         </is>
@@ -7074,29 +7350,29 @@
           <t>Less: Unlevered Cash Taxes (EBIT×t)</t>
         </is>
       </c>
-      <c r="C22" s="175" t="inlineStr">
+      <c r="C22" s="180" t="inlineStr">
         <is>
           <t>EBIT×t</t>
         </is>
       </c>
       <c r="D22" s="97" t="n"/>
-      <c r="E22" s="169">
+      <c r="E22" s="174">
         <f>E21*$D$5</f>
         <v/>
       </c>
-      <c r="F22" s="169">
+      <c r="F22" s="174">
         <f>F21*$D$5</f>
         <v/>
       </c>
-      <c r="G22" s="169">
+      <c r="G22" s="174">
         <f>G21*$D$5</f>
         <v/>
       </c>
-      <c r="H22" s="169">
+      <c r="H22" s="174">
         <f>H21*$D$5</f>
         <v/>
       </c>
-      <c r="I22" s="169">
+      <c r="I22" s="174">
         <f>I21*$D$5</f>
         <v/>
       </c>
@@ -7114,29 +7390,29 @@
           <t>Plus: D&amp;A (linked to 3-stmt)</t>
         </is>
       </c>
-      <c r="C23" s="175" t="inlineStr">
+      <c r="C23" s="180" t="inlineStr">
         <is>
           <t>+D&amp;A</t>
         </is>
       </c>
       <c r="D23" s="97" t="n"/>
-      <c r="E23" s="169">
+      <c r="E23" s="174">
         <f>'3 Statement Model'!J30</f>
         <v/>
       </c>
-      <c r="F23" s="169">
+      <c r="F23" s="174">
         <f>'3 Statement Model'!K30</f>
         <v/>
       </c>
-      <c r="G23" s="169">
+      <c r="G23" s="174">
         <f>'3 Statement Model'!L30</f>
         <v/>
       </c>
-      <c r="H23" s="169">
+      <c r="H23" s="174">
         <f>'3 Statement Model'!M30</f>
         <v/>
       </c>
-      <c r="I23" s="169">
+      <c r="I23" s="174">
         <f>'3 Statement Model'!N30</f>
         <v/>
       </c>
@@ -7146,7 +7422,7 @@
       <c r="M23" s="97" t="n"/>
       <c r="N23" s="97" t="n"/>
       <c r="O23" s="97" t="n"/>
-      <c r="Q23" s="157" t="inlineStr">
+      <c r="Q23" s="159" t="inlineStr">
         <is>
           <t>3) Terminal Value</t>
         </is>
@@ -7159,29 +7435,29 @@
           <t>Less: Capex (linked to 3-stmt CF)</t>
         </is>
       </c>
-      <c r="C24" s="175" t="inlineStr">
+      <c r="C24" s="180" t="inlineStr">
         <is>
           <t>−CapEx</t>
         </is>
       </c>
       <c r="D24" s="97" t="n"/>
-      <c r="E24" s="169">
+      <c r="E24" s="174">
         <f>'3 Statement Model'!J68</f>
         <v/>
       </c>
-      <c r="F24" s="169">
+      <c r="F24" s="174">
         <f>'3 Statement Model'!K68</f>
         <v/>
       </c>
-      <c r="G24" s="169">
+      <c r="G24" s="174">
         <f>'3 Statement Model'!L68</f>
         <v/>
       </c>
-      <c r="H24" s="169">
+      <c r="H24" s="174">
         <f>'3 Statement Model'!M68</f>
         <v/>
       </c>
-      <c r="I24" s="169">
+      <c r="I24" s="174">
         <f>'3 Statement Model'!N68</f>
         <v/>
       </c>
@@ -7191,7 +7467,7 @@
       <c r="M24" s="97" t="n"/>
       <c r="N24" s="97" t="n"/>
       <c r="O24" s="97" t="n"/>
-      <c r="Q24" s="164" t="inlineStr">
+      <c r="Q24" s="169" t="inlineStr">
         <is>
           <t>TV_exit = EBITDA_n × ExitMultiple   [PRIMARY]</t>
         </is>
@@ -7204,29 +7480,29 @@
           <t>Less: ΔNWC (linked to 3-stmt CF)</t>
         </is>
       </c>
-      <c r="C25" s="175" t="inlineStr">
+      <c r="C25" s="180" t="inlineStr">
         <is>
           <t>−ΔNWC</t>
         </is>
       </c>
       <c r="D25" s="97" t="n"/>
-      <c r="E25" s="169">
+      <c r="E25" s="174">
         <f>'3 Statement Model'!J64</f>
         <v/>
       </c>
-      <c r="F25" s="169">
+      <c r="F25" s="174">
         <f>'3 Statement Model'!K64</f>
         <v/>
       </c>
-      <c r="G25" s="169">
+      <c r="G25" s="174">
         <f>'3 Statement Model'!L64</f>
         <v/>
       </c>
-      <c r="H25" s="169">
+      <c r="H25" s="174">
         <f>'3 Statement Model'!M64</f>
         <v/>
       </c>
-      <c r="I25" s="169">
+      <c r="I25" s="174">
         <f>'3 Statement Model'!N64</f>
         <v/>
       </c>
@@ -7236,18 +7512,23 @@
       <c r="M25" s="97" t="n"/>
       <c r="N25" s="97" t="n"/>
       <c r="O25" s="97" t="n"/>
-      <c r="Q25" s="159" t="inlineStr">
+      <c r="Q25" s="163" t="inlineStr">
         <is>
           <t>Excel</t>
         </is>
       </c>
-      <c r="R25" s="164">
+      <c r="R25" s="169">
         <f>($I$21+$I$23)*$D$8</f>
         <v/>
       </c>
-      <c r="T25" s="176">
+      <c r="T25" s="181">
         <f>J27</f>
         <v/>
+      </c>
+      <c r="U25" s="165" t="inlineStr">
+        <is>
+          <t>Exit multiple policy vs Yahoo / market multiples</t>
+        </is>
       </c>
     </row>
     <row r="26" ht="16" customHeight="1">
@@ -7257,29 +7538,29 @@
           <t>Unlevered FCF</t>
         </is>
       </c>
-      <c r="C26" s="175" t="inlineStr">
+      <c r="C26" s="180" t="inlineStr">
         <is>
           <t>FCFF=EBIT−tax+DA−CapEx−ΔNWC</t>
         </is>
       </c>
       <c r="D26" s="97" t="n"/>
-      <c r="E26" s="177">
+      <c r="E26" s="182">
         <f>E21-E22+E23-E24-E25</f>
         <v/>
       </c>
-      <c r="F26" s="177">
+      <c r="F26" s="182">
         <f>F21-F22+F23-F24-F25</f>
         <v/>
       </c>
-      <c r="G26" s="177">
+      <c r="G26" s="182">
         <f>G21-G22+G23-G24-G25</f>
         <v/>
       </c>
-      <c r="H26" s="177">
+      <c r="H26" s="182">
         <f>H21-H22+H23-H24-H25</f>
         <v/>
       </c>
-      <c r="I26" s="177">
+      <c r="I26" s="182">
         <f>I21-I22+I23-I24-I25</f>
         <v/>
       </c>
@@ -7289,7 +7570,7 @@
       <c r="M26" s="97" t="n"/>
       <c r="N26" s="97" t="n"/>
       <c r="O26" s="97" t="n"/>
-      <c r="Q26" s="164" t="inlineStr">
+      <c r="Q26" s="169" t="inlineStr">
         <is>
           <t>TV_gordon = FCFF_n×(1+g)/(WACC−g)   [CHECK]</t>
         </is>
@@ -7303,7 +7584,7 @@
         </is>
       </c>
       <c r="C27" s="97" t="n"/>
-      <c r="D27" s="178">
+      <c r="D27" s="183">
         <f>-I35</f>
         <v/>
       </c>
@@ -7312,7 +7593,7 @@
       <c r="G27" s="97" t="n"/>
       <c r="H27" s="97" t="n"/>
       <c r="I27" s="97" t="n"/>
-      <c r="J27" s="169">
+      <c r="J27" s="174">
         <f>($I$21+$I$23)*$D$8</f>
         <v/>
       </c>
@@ -7321,18 +7602,23 @@
       <c r="M27" s="97" t="n"/>
       <c r="N27" s="97" t="n"/>
       <c r="O27" s="97" t="n"/>
-      <c r="Q27" s="159" t="inlineStr">
+      <c r="Q27" s="163" t="inlineStr">
         <is>
           <t>Excel</t>
         </is>
       </c>
-      <c r="R27" s="164">
+      <c r="R27" s="169">
         <f>IF(($D$6-$D$7)&lt;=0,"err",$I$26*(1+$D$7)/($D$6-$D$7))</f>
         <v/>
       </c>
-      <c r="T27" s="176">
+      <c r="T27" s="181">
         <f>M19</f>
         <v/>
+      </c>
+      <c r="U27" s="165" t="inlineStr">
+        <is>
+          <t>Gordon g vs Damodaran long-run growth framing</t>
+        </is>
       </c>
     </row>
     <row r="28" ht="16" customHeight="1">
@@ -7343,30 +7629,30 @@
         </is>
       </c>
       <c r="C28" s="97" t="n"/>
-      <c r="D28" s="177" t="n">
+      <c r="D28" s="182" t="n">
         <v>0</v>
       </c>
-      <c r="E28" s="179">
+      <c r="E28" s="184">
         <f>E27+E26</f>
         <v/>
       </c>
-      <c r="F28" s="179">
+      <c r="F28" s="184">
         <f>F27+F26</f>
         <v/>
       </c>
-      <c r="G28" s="179">
+      <c r="G28" s="184">
         <f>G27+G26</f>
         <v/>
       </c>
-      <c r="H28" s="179">
+      <c r="H28" s="184">
         <f>H27+H26</f>
         <v/>
       </c>
-      <c r="I28" s="179">
+      <c r="I28" s="184">
         <f>I27+I26</f>
         <v/>
       </c>
-      <c r="J28" s="179">
+      <c r="J28" s="184">
         <f>J27+J26</f>
         <v/>
       </c>
@@ -7375,16 +7661,16 @@
       <c r="M28" s="97" t="n"/>
       <c r="N28" s="97" t="n"/>
       <c r="O28" s="97" t="n"/>
-      <c r="Q28" s="159" t="inlineStr">
+      <c r="Q28" s="163" t="inlineStr">
         <is>
           <t>Implied Gordon exit multiple</t>
         </is>
       </c>
-      <c r="R28" s="180">
+      <c r="R28" s="185">
         <f>IF(($I$21+$I$23)=0,0,T27/($I$21+$I$23))</f>
         <v/>
       </c>
-      <c r="S28" s="159" t="inlineStr">
+      <c r="S28" s="163" t="inlineStr">
         <is>
           <t>Gordon TV / EBITDA_n</t>
         </is>
@@ -7398,31 +7684,31 @@
         </is>
       </c>
       <c r="C29" s="97" t="n"/>
-      <c r="D29" s="178">
+      <c r="D29" s="183">
         <f>D27+D26</f>
         <v/>
       </c>
-      <c r="E29" s="169">
+      <c r="E29" s="174">
         <f>E27+E26</f>
         <v/>
       </c>
-      <c r="F29" s="169">
+      <c r="F29" s="174">
         <f>F27+F26</f>
         <v/>
       </c>
-      <c r="G29" s="169">
+      <c r="G29" s="174">
         <f>G27+G26</f>
         <v/>
       </c>
-      <c r="H29" s="169">
+      <c r="H29" s="174">
         <f>H27+H26</f>
         <v/>
       </c>
-      <c r="I29" s="169">
+      <c r="I29" s="174">
         <f>I27+I26</f>
         <v/>
       </c>
-      <c r="J29" s="169">
+      <c r="J29" s="174">
         <f>J27</f>
         <v/>
       </c>
@@ -7446,7 +7732,7 @@
       <c r="M30" s="97" t="n"/>
       <c r="N30" s="97" t="n"/>
       <c r="O30" s="97" t="n"/>
-      <c r="Q30" s="157" t="inlineStr">
+      <c r="Q30" s="159" t="inlineStr">
         <is>
           <t>4) Enterprise → Equity → $/share</t>
         </is>
@@ -7478,7 +7764,7 @@
       <c r="M31" s="111" t="n"/>
       <c r="N31" s="111" t="n"/>
       <c r="O31" s="97" t="n"/>
-      <c r="Q31" s="164" t="inlineStr">
+      <c r="Q31" s="169" t="inlineStr">
         <is>
           <t>EV = XNPV(WACC, TransactionCF, mid-year dates)</t>
         </is>
@@ -7492,7 +7778,7 @@
         </is>
       </c>
       <c r="C32" s="97" t="n"/>
-      <c r="D32" s="169">
+      <c r="D32" s="174">
         <f>XNPV(D6,D28:J28,D18:J18)</f>
         <v/>
       </c>
@@ -7503,7 +7789,7 @@
         </is>
       </c>
       <c r="H32" s="97" t="n"/>
-      <c r="I32" s="178">
+      <c r="I32" s="183">
         <f>D12*D11</f>
         <v/>
       </c>
@@ -7519,16 +7805,16 @@
         <v/>
       </c>
       <c r="O32" s="97" t="n"/>
-      <c r="Q32" s="159" t="inlineStr">
+      <c r="Q32" s="163" t="inlineStr">
         <is>
           <t>Excel</t>
         </is>
       </c>
-      <c r="R32" s="164">
+      <c r="R32" s="169">
         <f>XNPV(D6,D28:J28,D18:J18)</f>
         <v/>
       </c>
-      <c r="T32" s="176">
+      <c r="T32" s="181">
         <f>D32</f>
         <v/>
       </c>
@@ -7541,7 +7827,7 @@
         </is>
       </c>
       <c r="C33" s="97" t="n"/>
-      <c r="D33" s="178">
+      <c r="D33" s="183">
         <f>+D14</f>
         <v/>
       </c>
@@ -7552,7 +7838,7 @@
         </is>
       </c>
       <c r="H33" s="97" t="n"/>
-      <c r="I33" s="178">
+      <c r="I33" s="183">
         <f>D13</f>
         <v/>
       </c>
@@ -7568,18 +7854,28 @@
         <v/>
       </c>
       <c r="O33" s="97" t="n"/>
-      <c r="Q33" s="164" t="inlineStr">
+      <c r="Q33" s="169" t="inlineStr">
         <is>
           <t>Equity = EV + Cash − Debt</t>
         </is>
       </c>
-      <c r="R33" s="176">
+      <c r="R33" s="181">
         <f>D35</f>
         <v/>
       </c>
-      <c r="S33" s="159" t="inlineStr">
-        <is>
-          <t>D32+D33−D34</t>
+      <c r="S33" s="163" t="inlineStr">
+        <is>
+          <t>Net debt from 10-Q bridge</t>
+        </is>
+      </c>
+      <c r="U33" s="165" t="inlineStr">
+        <is>
+          <t>SEC 10-Q — cash, mkt secs, total debt</t>
+        </is>
+      </c>
+      <c r="V33" s="165" t="inlineStr">
+        <is>
+          <t>SEC 10-K — FY debt footnote</t>
         </is>
       </c>
     </row>
@@ -7591,7 +7887,7 @@
         </is>
       </c>
       <c r="C34" s="97" t="n"/>
-      <c r="D34" s="178">
+      <c r="D34" s="183">
         <f>+D13</f>
         <v/>
       </c>
@@ -7602,7 +7898,7 @@
         </is>
       </c>
       <c r="H34" s="97" t="n"/>
-      <c r="I34" s="178">
+      <c r="I34" s="183">
         <f>+D14</f>
         <v/>
       </c>
@@ -7611,18 +7907,28 @@
       <c r="M34" s="97" t="n"/>
       <c r="N34" s="97" t="n"/>
       <c r="O34" s="97" t="n"/>
-      <c r="Q34" s="164" t="inlineStr">
+      <c r="Q34" s="169" t="inlineStr">
         <is>
           <t>$/share = Equity / Shares</t>
         </is>
       </c>
-      <c r="R34" s="181">
+      <c r="R34" s="186">
         <f>D37</f>
         <v/>
       </c>
-      <c r="S34" s="159" t="inlineStr">
-        <is>
-          <t>Intrinsic value per share</t>
+      <c r="S34" s="163" t="inlineStr">
+        <is>
+          <t>Shares outstanding (Yahoo)</t>
+        </is>
+      </c>
+      <c r="U34" s="165" t="inlineStr">
+        <is>
+          <t>Yahoo Finance — shares outstanding</t>
+        </is>
+      </c>
+      <c r="V34" s="165" t="inlineStr">
+        <is>
+          <t>Yahoo FICO quote (price)</t>
         </is>
       </c>
     </row>
@@ -7634,7 +7940,7 @@
         </is>
       </c>
       <c r="C35" s="97" t="n"/>
-      <c r="D35" s="177">
+      <c r="D35" s="182">
         <f>D32+D33-D34</f>
         <v/>
       </c>
@@ -7645,7 +7951,7 @@
         </is>
       </c>
       <c r="H35" s="97" t="n"/>
-      <c r="I35" s="177">
+      <c r="I35" s="182">
         <f>I32+I33-I34</f>
         <v/>
       </c>
@@ -7658,16 +7964,16 @@
       <c r="M35" s="111" t="n"/>
       <c r="N35" s="111" t="n"/>
       <c r="O35" s="97" t="n"/>
-      <c r="Q35" s="159" t="inlineStr">
+      <c r="Q35" s="163" t="inlineStr">
         <is>
           <t>Upside vs market</t>
         </is>
       </c>
-      <c r="R35" s="182">
+      <c r="R35" s="187">
         <f>D37/D11-1</f>
         <v/>
       </c>
-      <c r="S35" s="159" t="inlineStr">
+      <c r="S35" s="163" t="inlineStr">
         <is>
           <t>Intrinsic / Current Price − 1</t>
         </is>
@@ -7681,7 +7987,7 @@
       <c r="E36" s="97" t="n"/>
       <c r="G36" s="97" t="n"/>
       <c r="H36" s="97" t="n"/>
-      <c r="I36" s="183" t="n"/>
+      <c r="I36" s="188" t="n"/>
       <c r="J36" s="97" t="n"/>
       <c r="L36" s="97" t="inlineStr">
         <is>
@@ -7689,7 +7995,7 @@
         </is>
       </c>
       <c r="M36" s="97" t="n"/>
-      <c r="N36" s="183">
+      <c r="N36" s="188">
         <f>I37</f>
         <v/>
       </c>
@@ -7703,7 +8009,7 @@
         </is>
       </c>
       <c r="C37" s="97" t="n"/>
-      <c r="D37" s="178">
+      <c r="D37" s="183">
         <f>D35/D12</f>
         <v/>
       </c>
@@ -7714,7 +8020,7 @@
         </is>
       </c>
       <c r="H37" s="97" t="n"/>
-      <c r="I37" s="178">
+      <c r="I37" s="183">
         <f>D11</f>
         <v/>
       </c>
@@ -7725,12 +8031,12 @@
         </is>
       </c>
       <c r="M37" s="97" t="n"/>
-      <c r="N37" s="183">
+      <c r="N37" s="188">
         <f>D37-I37</f>
         <v/>
       </c>
       <c r="O37" s="97" t="n"/>
-      <c r="Q37" s="157" t="inlineStr">
+      <c r="Q37" s="159" t="inlineStr">
         <is>
           <t>5) Operating NWC (feeds ΔNWC → FCFF)</t>
         </is>
@@ -7752,14 +8058,24 @@
         </is>
       </c>
       <c r="M38" s="97" t="n"/>
-      <c r="N38" s="183">
+      <c r="N38" s="188">
         <f>SUM(N36:N37)</f>
         <v/>
       </c>
       <c r="O38" s="97" t="n"/>
-      <c r="Q38" s="164" t="inlineStr">
+      <c r="Q38" s="169" t="inlineStr">
         <is>
           <t>NWC = AR + Inventory − AP − DeferredRevenue</t>
+        </is>
+      </c>
+      <c r="U38" s="165" t="inlineStr">
+        <is>
+          <t>SEC 10-K — AR / AP / deferred revenue</t>
+        </is>
+      </c>
+      <c r="V38" s="165" t="inlineStr">
+        <is>
+          <t>XBRL DeferredRevenueCurrent</t>
         </is>
       </c>
     </row>
@@ -7776,17 +8092,17 @@
       <c r="M39" s="97" t="n"/>
       <c r="N39" s="97" t="n"/>
       <c r="O39" s="97" t="n"/>
-      <c r="Q39" s="164" t="inlineStr">
+      <c r="Q39" s="169" t="inlineStr">
         <is>
           <t>ΔNWC_t = NWC_t − NWC_(t−1)</t>
         </is>
       </c>
-      <c r="S39" s="159" t="inlineStr">
+      <c r="S39" s="163" t="inlineStr">
         <is>
           <t>Linked from 3-statement CF row 64</t>
         </is>
       </c>
-      <c r="T39" s="176">
+      <c r="T39" s="181">
         <f>I25</f>
         <v/>
       </c>
@@ -7826,9 +8142,9 @@
       <c r="M41" s="111" t="n"/>
       <c r="N41" s="111" t="n"/>
       <c r="O41" s="97" t="n"/>
-      <c r="Q41" s="157" t="inlineStr">
-        <is>
-          <t>Sources (SEC preferred)</t>
+      <c r="Q41" s="159" t="inlineStr">
+        <is>
+          <t>6) Full source index (all clickable)</t>
         </is>
       </c>
     </row>
@@ -7851,9 +8167,16 @@
         </is>
       </c>
       <c r="O42" s="97" t="n"/>
-      <c r="Q42" s="159" t="inlineStr">
-        <is>
-          <t>10-K: sec.gov/.../fico-20250930.htm</t>
+      <c r="Q42" s="165" t="inlineStr">
+        <is>
+          <t>SEC 10-K FY2025</t>
+        </is>
+      </c>
+      <c r="R42" s="189" t="n"/>
+      <c r="S42" s="190" t="n"/>
+      <c r="T42" s="163" t="inlineStr">
+        <is>
+          <t>Tax 18.8%, IS/BS/CF, senior notes</t>
         </is>
       </c>
     </row>
@@ -7872,9 +8195,16 @@
       <c r="H43" s="97" t="n"/>
       <c r="N43" s="69" t="n"/>
       <c r="O43" s="97" t="n"/>
-      <c r="Q43" s="159" t="inlineStr">
-        <is>
-          <t>10-Q: sec.gov/.../fico-20260630.htm</t>
+      <c r="Q43" s="165" t="inlineStr">
+        <is>
+          <t>SEC 10-Q Q3 FY2026</t>
+        </is>
+      </c>
+      <c r="R43" s="189" t="n"/>
+      <c r="S43" s="190" t="n"/>
+      <c r="T43" s="163" t="inlineStr">
+        <is>
+          <t>Debt $5,582M, cash+mkt secs net-debt bridge</t>
         </is>
       </c>
     </row>
@@ -7893,9 +8223,16 @@
       <c r="H44" s="97" t="n"/>
       <c r="N44" s="69" t="n"/>
       <c r="O44" s="97" t="n"/>
-      <c r="Q44" s="159" t="inlineStr">
-        <is>
-          <t>8-K 6.250% notes: sec.gov/.../d56220d8k.htm</t>
+      <c r="Q44" s="165" t="inlineStr">
+        <is>
+          <t>SEC 8-K 6.250% notes</t>
+        </is>
+      </c>
+      <c r="R44" s="189" t="n"/>
+      <c r="S44" s="190" t="n"/>
+      <c r="T44" s="163" t="inlineStr">
+        <is>
+          <t>Pre-tax Rd coupon 6.250% due 2034</t>
         </is>
       </c>
     </row>
@@ -7914,9 +8251,16 @@
       <c r="H45" s="97" t="n"/>
       <c r="N45" s="69" t="n"/>
       <c r="O45" s="97" t="n"/>
-      <c r="Q45" s="159" t="inlineStr">
-        <is>
-          <t>Damodaran ERP: pages.stern.nyu.edu/adamodar/</t>
+      <c r="Q45" s="165" t="inlineStr">
+        <is>
+          <t>SEC EX-99.1 pricing</t>
+        </is>
+      </c>
+      <c r="R45" s="189" t="n"/>
+      <c r="S45" s="190" t="n"/>
+      <c r="T45" s="163" t="inlineStr">
+        <is>
+          <t>Notes priced at par / offering terms</t>
         </is>
       </c>
     </row>
@@ -7935,9 +8279,16 @@
       <c r="H46" s="97" t="n"/>
       <c r="N46" s="69" t="n"/>
       <c r="O46" s="97" t="n"/>
-      <c r="Q46" s="159" t="inlineStr">
-        <is>
-          <t>FRED DGS10 + Yahoo FICO beta</t>
+      <c r="Q46" s="165" t="inlineStr">
+        <is>
+          <t>SEC companyfacts XBRL</t>
+        </is>
+      </c>
+      <c r="R46" s="189" t="n"/>
+      <c r="S46" s="190" t="n"/>
+      <c r="T46" s="163" t="inlineStr">
+        <is>
+          <t>Pipeline data source (CIK 0000814547)</t>
         </is>
       </c>
     </row>
@@ -7952,6 +8303,18 @@
       <c r="H47" s="97" t="n"/>
       <c r="N47" s="69" t="n"/>
       <c r="O47" s="97" t="n"/>
+      <c r="Q47" s="165" t="inlineStr">
+        <is>
+          <t>FRED DGS10</t>
+        </is>
+      </c>
+      <c r="R47" s="189" t="n"/>
+      <c r="S47" s="190" t="n"/>
+      <c r="T47" s="163" t="inlineStr">
+        <is>
+          <t>Risk-free rate (US 10Y)</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="16" customHeight="1">
       <c r="A48" s="97" t="n"/>
@@ -7968,6 +8331,18 @@
         </is>
       </c>
       <c r="O48" s="97" t="n"/>
+      <c r="Q48" s="165" t="inlineStr">
+        <is>
+          <t>US Treasury yield curve</t>
+        </is>
+      </c>
+      <c r="R48" s="189" t="n"/>
+      <c r="S48" s="190" t="n"/>
+      <c r="T48" s="163" t="inlineStr">
+        <is>
+          <t>Official daily par yields</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="16" customHeight="1">
       <c r="A49" s="97" t="n"/>
@@ -7984,6 +8359,18 @@
         </is>
       </c>
       <c r="O49" s="97" t="n"/>
+      <c r="Q49" s="165" t="inlineStr">
+        <is>
+          <t>Damodaran Implied ERP</t>
+        </is>
+      </c>
+      <c r="R49" s="189" t="n"/>
+      <c r="S49" s="190" t="n"/>
+      <c r="T49" s="163" t="inlineStr">
+        <is>
+          <t>Equity risk premium</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="16" customHeight="1">
       <c r="A50" s="97" t="n"/>
@@ -7995,6 +8382,18 @@
       <c r="G50" s="97" t="n"/>
       <c r="H50" s="97" t="n"/>
       <c r="O50" s="97" t="n"/>
+      <c r="Q50" s="165" t="inlineStr">
+        <is>
+          <t>Damodaran histimpl</t>
+        </is>
+      </c>
+      <c r="R50" s="189" t="n"/>
+      <c r="S50" s="190" t="n"/>
+      <c r="T50" s="163" t="inlineStr">
+        <is>
+          <t>Historical implied ERP table</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="16" customHeight="1">
       <c r="A51" s="97" t="n"/>
@@ -8007,6 +8406,18 @@
       <c r="H51" s="97" t="n"/>
       <c r="M51" s="97" t="n"/>
       <c r="O51" s="97" t="n"/>
+      <c r="Q51" s="165" t="inlineStr">
+        <is>
+          <t>Yahoo FICO stats</t>
+        </is>
+      </c>
+      <c r="R51" s="189" t="n"/>
+      <c r="S51" s="190" t="n"/>
+      <c r="T51" s="163" t="inlineStr">
+        <is>
+          <t>Beta 5Y monthly + shares out</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="16" customHeight="1">
       <c r="A52" s="97" t="n"/>
@@ -8175,27 +8586,86 @@
       <c r="L61" s="97" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="19">
-    <mergeCell ref="Q30:T30"/>
-    <mergeCell ref="Q17:T17"/>
+  <mergeCells count="34">
+    <mergeCell ref="T50:V50"/>
+    <mergeCell ref="T44:V44"/>
+    <mergeCell ref="Q5:V5"/>
+    <mergeCell ref="Q23:V23"/>
+    <mergeCell ref="Q50:S50"/>
     <mergeCell ref="Q26:S26"/>
-    <mergeCell ref="Q45:T45"/>
     <mergeCell ref="Q31:S31"/>
-    <mergeCell ref="Q2:T2"/>
-    <mergeCell ref="Q41:T41"/>
-    <mergeCell ref="Q3:T3"/>
-    <mergeCell ref="Q43:T43"/>
-    <mergeCell ref="Q37:T37"/>
-    <mergeCell ref="Q42:T42"/>
-    <mergeCell ref="Q5:T5"/>
-    <mergeCell ref="Q46:T46"/>
-    <mergeCell ref="Q23:T23"/>
+    <mergeCell ref="T51:V51"/>
+    <mergeCell ref="Q44:S44"/>
+    <mergeCell ref="Q49:S49"/>
+    <mergeCell ref="Q46:S46"/>
+    <mergeCell ref="Q30:V30"/>
+    <mergeCell ref="Q17:V17"/>
+    <mergeCell ref="T43:V43"/>
+    <mergeCell ref="Q48:S48"/>
+    <mergeCell ref="Q2:V2"/>
+    <mergeCell ref="T46:V46"/>
+    <mergeCell ref="Q45:S45"/>
+    <mergeCell ref="Q41:V41"/>
+    <mergeCell ref="T48:V48"/>
+    <mergeCell ref="Q47:S47"/>
     <mergeCell ref="Q38:T38"/>
+    <mergeCell ref="Q43:S43"/>
+    <mergeCell ref="Q3:V3"/>
+    <mergeCell ref="T49:V49"/>
     <mergeCell ref="R19:T19"/>
+    <mergeCell ref="Q37:V37"/>
     <mergeCell ref="Q24:S24"/>
+    <mergeCell ref="Q42:S42"/>
+    <mergeCell ref="T45:V45"/>
     <mergeCell ref="Q18:S18"/>
-    <mergeCell ref="Q44:T44"/>
+    <mergeCell ref="T42:V42"/>
+    <mergeCell ref="T47:V47"/>
+    <mergeCell ref="Q51:S51"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F6" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V6" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U7" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V7" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U8" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V8" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U10" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V10" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U11" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V11" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U13" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V13" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U14" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V14" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U15" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V15" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U18" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V18" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U20" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U25" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U33" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V33" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U34" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V34" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U38" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V38" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q42" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q43" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q44" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q45" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q46" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q47" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q48" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q49" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q50" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q51" r:id="rId42"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/FICO/output/FICO_Completed_Model.xlsx
+++ b/FICO/output/FICO_Completed_Model.xlsx
@@ -4040,19 +4040,19 @@
         </is>
       </c>
       <c r="E42" s="139" t="n">
-        <v>312107</v>
+        <v>206690</v>
       </c>
       <c r="F42" s="139" t="n">
-        <v>322410</v>
+        <v>202365</v>
       </c>
       <c r="G42" s="139" t="n">
-        <v>387947</v>
+        <v>251217</v>
       </c>
       <c r="H42" s="139" t="n">
-        <v>426642</v>
+        <v>269745</v>
       </c>
       <c r="I42" s="139" t="n">
-        <v>529148</v>
+        <v>341776</v>
       </c>
       <c r="J42" s="142">
         <f>J24*J15/365</f>
@@ -4387,19 +4387,19 @@
         </is>
       </c>
       <c r="E52" s="139" t="n">
-        <v>-744393</v>
+        <v>-849810</v>
       </c>
       <c r="F52" s="139" t="n">
-        <v>-1397750</v>
+        <v>-1517795</v>
       </c>
       <c r="G52" s="139" t="n">
-        <v>-1344976</v>
+        <v>-1481706</v>
       </c>
       <c r="H52" s="139" t="n">
-        <v>-1615720</v>
+        <v>-1772617</v>
       </c>
       <c r="I52" s="139" t="n">
-        <v>-2357009</v>
+        <v>-2544381</v>
       </c>
       <c r="J52" s="142">
         <f>I52+J20</f>

--- a/FICO/output/FICO_Completed_Model.xlsx
+++ b/FICO/output/FICO_Completed_Model.xlsx
@@ -100,7 +100,7 @@
     <numFmt numFmtId="178" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="179" formatCode="0.0"/>
   </numFmts>
-  <fonts count="48">
+  <fonts count="50">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -366,6 +366,17 @@
     </font>
     <font>
       <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00666666"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Consolas"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="12"/>
@@ -452,12 +463,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E79"/>
+        <fgColor rgb="00D6EAF8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D6EAF8"/>
+        <fgColor rgb="001F4E79"/>
       </patternFill>
     </fill>
   </fills>
@@ -579,7 +590,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="191">
+  <cellXfs count="198">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="1"/>
@@ -799,10 +810,18 @@
     <xf numFmtId="177" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="40" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="2"/>
+    <xf numFmtId="0" fontId="39" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="41" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="166" fontId="40" fillId="8" borderId="5" pivotButton="0" quotePrefix="0" xfId="2"/>
+    <xf numFmtId="164" fontId="42" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="166" fontId="38" fillId="7" borderId="5" pivotButton="0" quotePrefix="0" xfId="2"/>
     <xf numFmtId="177" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="177" fontId="38" fillId="7" borderId="5" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="177" fontId="40" fillId="8" borderId="5" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="40" fillId="8" borderId="5" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="177" fontId="40" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="166" fontId="40" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="177" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="177" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="177" fontId="6" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="1"/>
@@ -818,18 +837,17 @@
     </xf>
     <xf numFmtId="177" fontId="9" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="177" fontId="40" fillId="8" borderId="2" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="41" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="39" fillId="10" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="43" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="39" fillId="9" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="40" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="43" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="45" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="46" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="45" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="48" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="47" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="38" fillId="7" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
@@ -837,7 +855,7 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="40" fillId="8" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="179" fontId="40" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -845,7 +863,7 @@
     </xf>
     <xf numFmtId="2" fontId="40" fillId="8" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="178" fontId="32" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="38" fillId="7" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -862,7 +880,7 @@
     <xf numFmtId="178" fontId="38" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="177" fontId="36" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="177" fontId="37" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="47" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="49" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="174" fontId="38" fillId="7" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="177" fontId="30" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="177" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -2250,7 +2268,7 @@
       <c r="B12" s="74" t="n"/>
       <c r="C12" s="75" t="inlineStr">
         <is>
-          <t>FICO — vengeanceaiUSCMODEL3 (3-Statement + DCF)</t>
+          <t>FICO — vengeanceaiUSCMODEL4 (3-Statement + DCF)</t>
         </is>
       </c>
       <c r="D12" s="74" t="n"/>
@@ -2418,7 +2436,7 @@
       <c r="B21" s="85" t="n"/>
       <c r="C21" s="85" t="inlineStr">
         <is>
-          <t>vengeanceaiUSCMODEL3: Ke=Rf+β·ERP=4.63%+1.32×4.28%=10.28%; WACC=80%×Ke+20%×Rd(1−t)=9.24%; FCFF=EBIT(1−t)+DA−CapEx−ΔNWC; NWC=AR−AP−Deferred; TV=EBITDA×25x (Gordon cross-check); mid-year XNPV. Open in Excel to recalculate. Live equations on DCF sheet columns Q–T (Ke/WACC/FCFF/TV).</t>
+          <t>vengeanceaiUSCMODEL4: forecast drivers are Excel equations off FY25 (COGS%=I25/I24, SGA/RD/CapEx=Rev×hist%, days=ROUND(I…)). Growth path + CAPM WACC=9.24% + Exit 25x are the only forward policy inputs. Open in Excel to recalculate. DCF live CAPM + sources in columns Q–V.</t>
         </is>
       </c>
       <c r="D21" s="85" t="n"/>
@@ -2621,6 +2639,7 @@
   <cols>
     <col width="1.88671875" customWidth="1" style="19" min="1" max="1"/>
     <col width="42" customWidth="1" style="19" min="2" max="3"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" style="47" min="4" max="4"/>
     <col width="16" customWidth="1" style="19" min="5" max="9"/>
     <col width="16" customWidth="1" min="6" max="6"/>
@@ -2759,7 +2778,13 @@
         <v/>
       </c>
     </row>
-    <row r="4"/>
+    <row r="4">
+      <c r="B4" s="137" t="inlineStr">
+        <is>
+          <t>vengeanceaiUSCMODEL4: green assumption cells = equations from FY25 (col I)</t>
+        </is>
+      </c>
+    </row>
     <row r="5" ht="18" customHeight="1">
       <c r="B5" s="65" t="inlineStr">
         <is>
@@ -2793,7 +2818,11 @@
           <t>Revenue Growth (% Change)</t>
         </is>
       </c>
-      <c r="C7" s="18" t="n"/>
+      <c r="C7" s="138" t="inlineStr">
+        <is>
+          <t>POLICY input (Y1≈FY26 guidance; fade→g)</t>
+        </is>
+      </c>
       <c r="D7" s="46" t="n"/>
       <c r="E7" s="49" t="n"/>
       <c r="F7" s="37">
@@ -2812,19 +2841,19 @@
         <f>I24/H24-1</f>
         <v/>
       </c>
-      <c r="J7" s="137" t="n">
+      <c r="J7" s="139" t="n">
         <v>0.27</v>
       </c>
-      <c r="K7" s="137" t="n">
+      <c r="K7" s="139" t="n">
         <v>0.16</v>
       </c>
-      <c r="L7" s="137" t="n">
+      <c r="L7" s="139" t="n">
         <v>0.13</v>
       </c>
-      <c r="M7" s="137" t="n">
+      <c r="M7" s="139" t="n">
         <v>0.1</v>
       </c>
-      <c r="N7" s="137" t="n">
+      <c r="N7" s="139" t="n">
         <v>0.07000000000000001</v>
       </c>
     </row>
@@ -2834,7 +2863,10 @@
           <t>Cost of Goods Sold (% of Revenue)</t>
         </is>
       </c>
-      <c r="C8" s="19" t="n"/>
+      <c r="C8" s="140">
+        <f>I25/I24 (FY25 COGS%)</f>
+        <v/>
+      </c>
       <c r="D8" s="47" t="n"/>
       <c r="E8" s="37">
         <f>E25/E24</f>
@@ -2856,20 +2888,25 @@
         <f>I25/I24</f>
         <v/>
       </c>
-      <c r="J8" s="137" t="n">
-        <v>0.1776721622567833</v>
-      </c>
-      <c r="K8" s="137" t="n">
-        <v>0.1776721622567833</v>
-      </c>
-      <c r="L8" s="137" t="n">
-        <v>0.1776721622567833</v>
-      </c>
-      <c r="M8" s="137" t="n">
-        <v>0.1776721622567833</v>
-      </c>
-      <c r="N8" s="137" t="n">
-        <v>0.1776721622567833</v>
+      <c r="J8" s="141">
+        <f>$I$25/$I$24</f>
+        <v/>
+      </c>
+      <c r="K8" s="141">
+        <f>$I$25/$I$24</f>
+        <v/>
+      </c>
+      <c r="L8" s="141">
+        <f>$I$25/$I$24</f>
+        <v/>
+      </c>
+      <c r="M8" s="141">
+        <f>$I$25/$I$24</f>
+        <v/>
+      </c>
+      <c r="N8" s="141">
+        <f>$I$25/$I$24</f>
+        <v/>
       </c>
     </row>
     <row r="9" hidden="1" outlineLevel="1">
@@ -2878,42 +2915,50 @@
           <t>Salaries and Benefits ($000's)</t>
         </is>
       </c>
-      <c r="C9" s="19" t="n"/>
+      <c r="C9" s="140">
+        <f>Rev×((I28−10922)/I24 − 50bps×t)</f>
+        <v/>
+      </c>
       <c r="D9" s="47" t="n"/>
-      <c r="E9" s="138">
+      <c r="E9" s="142">
         <f>E28</f>
         <v/>
       </c>
-      <c r="F9" s="138">
+      <c r="F9" s="142">
         <f>F28</f>
         <v/>
       </c>
-      <c r="G9" s="138">
+      <c r="G9" s="142">
         <f>G28</f>
         <v/>
       </c>
-      <c r="H9" s="138">
+      <c r="H9" s="142">
         <f>H28</f>
         <v/>
       </c>
-      <c r="I9" s="138">
+      <c r="I9" s="142">
         <f>I28</f>
         <v/>
       </c>
-      <c r="J9" s="139" t="n">
-        <v>625032.6</v>
-      </c>
-      <c r="K9" s="139" t="n">
-        <v>710373.1</v>
-      </c>
-      <c r="L9" s="139" t="n">
-        <v>786150.4</v>
-      </c>
-      <c r="M9" s="139" t="n">
-        <v>846537.2</v>
-      </c>
-      <c r="N9" s="139" t="n">
-        <v>886290.5</v>
+      <c r="J9" s="143">
+        <f>J24*MAX(0.05,(($I$28-10922.0)/$I$24)-0.005)</f>
+        <v/>
+      </c>
+      <c r="K9" s="143">
+        <f>K24*MAX(0.05,(($I$28-10922.0)/$I$24)-0.01)</f>
+        <v/>
+      </c>
+      <c r="L9" s="143">
+        <f>L24*MAX(0.05,(($I$28-10922.0)/$I$24)-0.015)</f>
+        <v/>
+      </c>
+      <c r="M9" s="143">
+        <f>M24*MAX(0.05,(($I$28-10922.0)/$I$24)-0.02)</f>
+        <v/>
+      </c>
+      <c r="N9" s="143">
+        <f>N24*MAX(0.05,(($I$28-10922.0)/$I$24)-0.025)</f>
+        <v/>
       </c>
     </row>
     <row r="10" hidden="1" outlineLevel="1">
@@ -2922,42 +2967,50 @@
           <t>Rent and Overhead ($000's)</t>
         </is>
       </c>
-      <c r="C10" s="19" t="n"/>
+      <c r="C10" s="140">
+        <f>Rev×(I29/I24) FY25 R&amp;D%</f>
+        <v/>
+      </c>
       <c r="D10" s="47" t="n"/>
-      <c r="E10" s="138">
+      <c r="E10" s="142">
         <f>E29</f>
         <v/>
       </c>
-      <c r="F10" s="138">
+      <c r="F10" s="142">
         <f>F29</f>
         <v/>
       </c>
-      <c r="G10" s="138">
+      <c r="G10" s="142">
         <f>G29</f>
         <v/>
       </c>
-      <c r="H10" s="138">
+      <c r="H10" s="142">
         <f>H29</f>
         <v/>
       </c>
-      <c r="I10" s="138">
+      <c r="I10" s="142">
         <f>I29</f>
         <v/>
       </c>
-      <c r="J10" s="139" t="n">
-        <v>239200.7</v>
-      </c>
-      <c r="K10" s="139" t="n">
-        <v>277472.8</v>
-      </c>
-      <c r="L10" s="139" t="n">
-        <v>313544.3</v>
-      </c>
-      <c r="M10" s="139" t="n">
-        <v>344898.7</v>
-      </c>
-      <c r="N10" s="139" t="n">
-        <v>369041.6</v>
+      <c r="J10" s="143">
+        <f>J24*($I$29/$I$24)</f>
+        <v/>
+      </c>
+      <c r="K10" s="143">
+        <f>K24*($I$29/$I$24)</f>
+        <v/>
+      </c>
+      <c r="L10" s="143">
+        <f>L24*($I$29/$I$24)</f>
+        <v/>
+      </c>
+      <c r="M10" s="143">
+        <f>M24*($I$29/$I$24)</f>
+        <v/>
+      </c>
+      <c r="N10" s="143">
+        <f>N24*($I$29/$I$24)</f>
+        <v/>
       </c>
     </row>
     <row r="11" hidden="1" outlineLevel="1">
@@ -2966,7 +3019,10 @@
           <t>Depreciation &amp; Amortization (% of PP&amp;E Open Bal)</t>
         </is>
       </c>
-      <c r="C11" s="19" t="n"/>
+      <c r="C11" s="140">
+        <f>I30/I92 (FY25 DA / PPE open)</f>
+        <v/>
+      </c>
       <c r="D11" s="47" t="n"/>
       <c r="E11" s="37">
         <f>E30/E92</f>
@@ -2988,20 +3044,25 @@
         <f>I30/I92</f>
         <v/>
       </c>
-      <c r="J11" s="137" t="n">
-        <v>0.2208143192592265</v>
-      </c>
-      <c r="K11" s="137" t="n">
-        <v>0.2208143192592265</v>
-      </c>
-      <c r="L11" s="137" t="n">
-        <v>0.2208143192592265</v>
-      </c>
-      <c r="M11" s="137" t="n">
-        <v>0.2208143192592265</v>
-      </c>
-      <c r="N11" s="137" t="n">
-        <v>0.2208143192592265</v>
+      <c r="J11" s="141">
+        <f>IF($I$92=0,0.25,$I$30/$I$92)</f>
+        <v/>
+      </c>
+      <c r="K11" s="141">
+        <f>IF($I$92=0,0.25,$I$30/$I$92)</f>
+        <v/>
+      </c>
+      <c r="L11" s="141">
+        <f>IF($I$92=0,0.25,$I$30/$I$92)</f>
+        <v/>
+      </c>
+      <c r="M11" s="141">
+        <f>IF($I$92=0,0.25,$I$30/$I$92)</f>
+        <v/>
+      </c>
+      <c r="N11" s="141">
+        <f>IF($I$92=0,0.25,$I$30/$I$92)</f>
+        <v/>
       </c>
     </row>
     <row r="12" hidden="1" outlineLevel="1">
@@ -3010,7 +3071,10 @@
           <t>Interest (% of Debt Open Bal)</t>
         </is>
       </c>
-      <c r="C12" s="19" t="n"/>
+      <c r="C12" s="140">
+        <f>I101/I98 (FY25 Int / Debt open)</f>
+        <v/>
+      </c>
       <c r="D12" s="47" t="n"/>
       <c r="E12" s="37">
         <f>E101/E98</f>
@@ -3032,20 +3096,25 @@
         <f>I101/I98</f>
         <v/>
       </c>
-      <c r="J12" s="137" t="n">
-        <v>0.04373707943636971</v>
-      </c>
-      <c r="K12" s="137" t="n">
-        <v>0.04373707943636971</v>
-      </c>
-      <c r="L12" s="137" t="n">
-        <v>0.04373707943636971</v>
-      </c>
-      <c r="M12" s="137" t="n">
-        <v>0.04373707943636971</v>
-      </c>
-      <c r="N12" s="137" t="n">
-        <v>0.04373707943636971</v>
+      <c r="J12" s="141">
+        <f>IF($I$98=0,0.05,$I$101/$I$98)</f>
+        <v/>
+      </c>
+      <c r="K12" s="141">
+        <f>IF($I$98=0,0.05,$I$101/$I$98)</f>
+        <v/>
+      </c>
+      <c r="L12" s="141">
+        <f>IF($I$98=0,0.05,$I$101/$I$98)</f>
+        <v/>
+      </c>
+      <c r="M12" s="141">
+        <f>IF($I$98=0,0.05,$I$101/$I$98)</f>
+        <v/>
+      </c>
+      <c r="N12" s="141">
+        <f>IF($I$98=0,0.05,$I$101/$I$98)</f>
+        <v/>
       </c>
     </row>
     <row r="13" hidden="1" outlineLevel="1">
@@ -3054,7 +3123,10 @@
           <t>Tax Rate (% of Earnings Before Tax)</t>
         </is>
       </c>
-      <c r="C13" s="11" t="n"/>
+      <c r="C13" s="140">
+        <f>I35/I33 (FY25 effective tax)</f>
+        <v/>
+      </c>
       <c r="D13" s="25" t="n"/>
       <c r="E13" s="37">
         <f>E35/E33</f>
@@ -3076,20 +3148,25 @@
         <f>I35/I33</f>
         <v/>
       </c>
-      <c r="J13" s="137" t="n">
-        <v>0.1877023903712333</v>
-      </c>
-      <c r="K13" s="137" t="n">
-        <v>0.1877023903712333</v>
-      </c>
-      <c r="L13" s="137" t="n">
-        <v>0.1877023903712333</v>
-      </c>
-      <c r="M13" s="137" t="n">
-        <v>0.1877023903712333</v>
-      </c>
-      <c r="N13" s="137" t="n">
-        <v>0.1877023903712333</v>
+      <c r="J13" s="141">
+        <f>IF($I$33=0,0.21,$I$35/$I$33)</f>
+        <v/>
+      </c>
+      <c r="K13" s="141">
+        <f>IF($I$33=0,0.21,$I$35/$I$33)</f>
+        <v/>
+      </c>
+      <c r="L13" s="141">
+        <f>IF($I$33=0,0.21,$I$35/$I$33)</f>
+        <v/>
+      </c>
+      <c r="M13" s="141">
+        <f>IF($I$33=0,0.21,$I$35/$I$33)</f>
+        <v/>
+      </c>
+      <c r="N13" s="141">
+        <f>IF($I$33=0,0.21,$I$35/$I$33)</f>
+        <v/>
       </c>
     </row>
     <row r="14" hidden="1" outlineLevel="1">
@@ -3117,41 +3194,50 @@
           <t>Accounts Receivable (Days)</t>
         </is>
       </c>
+      <c r="C15" s="144">
+        <f>ROUND(I42/I24×365,0) net AR days</f>
+        <v/>
+      </c>
       <c r="D15" s="32" t="n"/>
-      <c r="E15" s="138">
+      <c r="E15" s="142">
         <f>E42/E24*365</f>
         <v/>
       </c>
-      <c r="F15" s="138">
+      <c r="F15" s="142">
         <f>F42/F24*365</f>
         <v/>
       </c>
-      <c r="G15" s="138">
+      <c r="G15" s="142">
         <f>G42/G24*365</f>
         <v/>
       </c>
-      <c r="H15" s="138">
+      <c r="H15" s="142">
         <f>H42/H24*365</f>
         <v/>
       </c>
-      <c r="I15" s="138">
+      <c r="I15" s="142">
         <f>I42/I24*365</f>
         <v/>
       </c>
-      <c r="J15" s="139" t="n">
-        <v>63</v>
-      </c>
-      <c r="K15" s="139" t="n">
-        <v>63</v>
-      </c>
-      <c r="L15" s="139" t="n">
-        <v>63</v>
-      </c>
-      <c r="M15" s="139" t="n">
-        <v>63</v>
-      </c>
-      <c r="N15" s="139" t="n">
-        <v>63</v>
+      <c r="J15" s="143">
+        <f>ROUND($I$42/$I$24*365,0)</f>
+        <v/>
+      </c>
+      <c r="K15" s="143">
+        <f>ROUND($I$42/$I$24*365,0)</f>
+        <v/>
+      </c>
+      <c r="L15" s="143">
+        <f>ROUND($I$42/$I$24*365,0)</f>
+        <v/>
+      </c>
+      <c r="M15" s="143">
+        <f>ROUND($I$42/$I$24*365,0)</f>
+        <v/>
+      </c>
+      <c r="N15" s="143">
+        <f>ROUND($I$42/$I$24*365,0)</f>
+        <v/>
       </c>
     </row>
     <row r="16" hidden="1" outlineLevel="1">
@@ -3161,39 +3247,39 @@
         </is>
       </c>
       <c r="D16" s="32" t="n"/>
-      <c r="E16" s="138">
+      <c r="E16" s="142">
         <f>E43/E25*365</f>
         <v/>
       </c>
-      <c r="F16" s="138">
+      <c r="F16" s="142">
         <f>F43/F25*365</f>
         <v/>
       </c>
-      <c r="G16" s="138">
+      <c r="G16" s="142">
         <f>G43/G25*365</f>
         <v/>
       </c>
-      <c r="H16" s="138">
+      <c r="H16" s="142">
         <f>H43/H25*365</f>
         <v/>
       </c>
-      <c r="I16" s="138">
+      <c r="I16" s="142">
         <f>I43/I25*365</f>
         <v/>
       </c>
-      <c r="J16" s="139" t="n">
+      <c r="J16" s="145" t="n">
         <v>0</v>
       </c>
-      <c r="K16" s="139" t="n">
+      <c r="K16" s="145" t="n">
         <v>0</v>
       </c>
-      <c r="L16" s="139" t="n">
+      <c r="L16" s="145" t="n">
         <v>0</v>
       </c>
-      <c r="M16" s="139" t="n">
+      <c r="M16" s="145" t="n">
         <v>0</v>
       </c>
-      <c r="N16" s="139" t="n">
+      <c r="N16" s="145" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3203,41 +3289,50 @@
           <t>Accounts Payable (Days)</t>
         </is>
       </c>
+      <c r="C17" s="144">
+        <f>ROUND(I48/I25×365,0) AP days</f>
+        <v/>
+      </c>
       <c r="D17" s="32" t="n"/>
-      <c r="E17" s="138">
+      <c r="E17" s="142">
         <f>E48/E25*365</f>
         <v/>
       </c>
-      <c r="F17" s="138">
+      <c r="F17" s="142">
         <f>F48/F25*365</f>
         <v/>
       </c>
-      <c r="G17" s="138">
+      <c r="G17" s="142">
         <f>G48/G25*365</f>
         <v/>
       </c>
-      <c r="H17" s="138">
+      <c r="H17" s="142">
         <f>H48/H25*365</f>
         <v/>
       </c>
-      <c r="I17" s="138">
+      <c r="I17" s="142">
         <f>I48/I25*365</f>
         <v/>
       </c>
-      <c r="J17" s="139" t="n">
-        <v>33</v>
-      </c>
-      <c r="K17" s="139" t="n">
-        <v>33</v>
-      </c>
-      <c r="L17" s="139" t="n">
-        <v>33</v>
-      </c>
-      <c r="M17" s="139" t="n">
-        <v>33</v>
-      </c>
-      <c r="N17" s="139" t="n">
-        <v>33</v>
+      <c r="J17" s="143">
+        <f>IF($I$25=0,0,ROUND($I$48/$I$25*365,0))</f>
+        <v/>
+      </c>
+      <c r="K17" s="143">
+        <f>IF($I$25=0,0,ROUND($I$48/$I$25*365,0))</f>
+        <v/>
+      </c>
+      <c r="L17" s="143">
+        <f>IF($I$25=0,0,ROUND($I$48/$I$25*365,0))</f>
+        <v/>
+      </c>
+      <c r="M17" s="143">
+        <f>IF($I$25=0,0,ROUND($I$48/$I$25*365,0))</f>
+        <v/>
+      </c>
+      <c r="N17" s="143">
+        <f>IF($I$25=0,0,ROUND($I$48/$I$25*365,0))</f>
+        <v/>
       </c>
     </row>
     <row r="18" hidden="1" outlineLevel="1">
@@ -3246,40 +3341,49 @@
           <t>Capital Expenditures ($000's)</t>
         </is>
       </c>
-      <c r="E18" s="138">
+      <c r="C18" s="144">
+        <f>Rev×fade(I68/I24 → 1%)</f>
+        <v/>
+      </c>
+      <c r="E18" s="142">
         <f>E68</f>
         <v/>
       </c>
-      <c r="F18" s="138">
+      <c r="F18" s="142">
         <f>F68</f>
         <v/>
       </c>
-      <c r="G18" s="138">
+      <c r="G18" s="142">
         <f>G68</f>
         <v/>
       </c>
-      <c r="H18" s="138">
+      <c r="H18" s="142">
         <f>H68</f>
         <v/>
       </c>
-      <c r="I18" s="138">
+      <c r="I18" s="142">
         <f>I68</f>
         <v/>
       </c>
-      <c r="J18" s="139" t="n">
-        <v>46333</v>
-      </c>
-      <c r="K18" s="139" t="n">
-        <v>48000.6</v>
-      </c>
-      <c r="L18" s="139" t="n">
-        <v>47748.1</v>
-      </c>
-      <c r="M18" s="139" t="n">
-        <v>47167.5</v>
-      </c>
-      <c r="N18" s="139" t="n">
-        <v>39008.5</v>
+      <c r="J18" s="143">
+        <f>J24*(($I$68/$I$24)*0.85+0.01*(1-0.85))</f>
+        <v/>
+      </c>
+      <c r="K18" s="143">
+        <f>K24*(($I$68/$I$24)*0.65+0.01*(1-0.65))</f>
+        <v/>
+      </c>
+      <c r="L18" s="143">
+        <f>L24*(($I$68/$I$24)*0.45+0.01*(1-0.45))</f>
+        <v/>
+      </c>
+      <c r="M18" s="143">
+        <f>M24*(($I$68/$I$24)*0.3+0.01*(1-0.3))</f>
+        <v/>
+      </c>
+      <c r="N18" s="143">
+        <f>N24*(($I$68/$I$24)*0.0+0.01*(1-0.0))</f>
+        <v/>
       </c>
     </row>
     <row r="19" hidden="1" outlineLevel="1">
@@ -3288,39 +3392,44 @@
           <t>Debt Issuance (Repayment) ($000's)</t>
         </is>
       </c>
-      <c r="E19" s="138">
+      <c r="C19" s="146" t="inlineStr">
+        <is>
+          <t>POLICY: no new debt issuance</t>
+        </is>
+      </c>
+      <c r="E19" s="142">
         <f>E99</f>
         <v/>
       </c>
-      <c r="F19" s="138">
+      <c r="F19" s="142">
         <f>F99</f>
         <v/>
       </c>
-      <c r="G19" s="138">
+      <c r="G19" s="142">
         <f>G99</f>
         <v/>
       </c>
-      <c r="H19" s="138">
+      <c r="H19" s="142">
         <f>H99</f>
         <v/>
       </c>
-      <c r="I19" s="138">
+      <c r="I19" s="142">
         <f>I99</f>
         <v/>
       </c>
-      <c r="J19" s="140" t="n">
+      <c r="J19" s="147" t="n">
         <v>0</v>
       </c>
-      <c r="K19" s="140" t="n">
+      <c r="K19" s="147" t="n">
         <v>0</v>
       </c>
-      <c r="L19" s="140" t="n">
+      <c r="L19" s="147" t="n">
         <v>0</v>
       </c>
-      <c r="M19" s="140" t="n">
+      <c r="M19" s="147" t="n">
         <v>0</v>
       </c>
-      <c r="N19" s="140" t="n">
+      <c r="N19" s="147" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3330,39 +3439,44 @@
           <t>Equity Issued (Repaid) ($000's)</t>
         </is>
       </c>
-      <c r="E20" s="138">
+      <c r="C20" s="146" t="inlineStr">
+        <is>
+          <t>POLICY: no equity issuance</t>
+        </is>
+      </c>
+      <c r="E20" s="142">
         <f>E73</f>
         <v/>
       </c>
-      <c r="F20" s="138">
+      <c r="F20" s="142">
         <f>F73</f>
         <v/>
       </c>
-      <c r="G20" s="138">
+      <c r="G20" s="142">
         <f>G73</f>
         <v/>
       </c>
-      <c r="H20" s="138">
+      <c r="H20" s="142">
         <f>H73</f>
         <v/>
       </c>
-      <c r="I20" s="138">
+      <c r="I20" s="142">
         <f>I73</f>
         <v/>
       </c>
-      <c r="J20" s="140" t="n">
+      <c r="J20" s="147" t="n">
         <v>0</v>
       </c>
-      <c r="K20" s="140" t="n">
+      <c r="K20" s="147" t="n">
         <v>0</v>
       </c>
-      <c r="L20" s="140" t="n">
+      <c r="L20" s="147" t="n">
         <v>0</v>
       </c>
-      <c r="M20" s="140" t="n">
+      <c r="M20" s="147" t="n">
         <v>0</v>
       </c>
-      <c r="N20" s="140" t="n">
+      <c r="N20" s="147" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3417,38 +3531,38 @@
       </c>
       <c r="C24" s="18" t="n"/>
       <c r="D24" s="46" t="n"/>
-      <c r="E24" s="139" t="n">
+      <c r="E24" s="148" t="n">
         <v>1316536</v>
       </c>
-      <c r="F24" s="139" t="n">
+      <c r="F24" s="148" t="n">
         <v>1377270</v>
       </c>
-      <c r="G24" s="139" t="n">
+      <c r="G24" s="148" t="n">
         <v>1513557</v>
       </c>
-      <c r="H24" s="139" t="n">
+      <c r="H24" s="148" t="n">
         <v>1717526</v>
       </c>
-      <c r="I24" s="139" t="n">
+      <c r="I24" s="148" t="n">
         <v>1990869</v>
       </c>
-      <c r="J24" s="141">
+      <c r="J24" s="149">
         <f>I24*(1+J7)</f>
         <v/>
       </c>
-      <c r="K24" s="141">
+      <c r="K24" s="149">
         <f>J24*(1+K7)</f>
         <v/>
       </c>
-      <c r="L24" s="141">
+      <c r="L24" s="149">
         <f>K24*(1+L7)</f>
         <v/>
       </c>
-      <c r="M24" s="141">
+      <c r="M24" s="149">
         <f>L24*(1+M7)</f>
         <v/>
       </c>
-      <c r="N24" s="141">
+      <c r="N24" s="149">
         <f>M24*(1+N7)</f>
         <v/>
       </c>
@@ -3461,38 +3575,38 @@
       </c>
       <c r="C25" s="19" t="n"/>
       <c r="D25" s="47" t="n"/>
-      <c r="E25" s="139" t="n">
+      <c r="E25" s="148" t="n">
         <v>332462</v>
       </c>
-      <c r="F25" s="139" t="n">
+      <c r="F25" s="148" t="n">
         <v>302174</v>
       </c>
-      <c r="G25" s="139" t="n">
+      <c r="G25" s="148" t="n">
         <v>311053</v>
       </c>
-      <c r="H25" s="139" t="n">
+      <c r="H25" s="148" t="n">
         <v>348206</v>
       </c>
-      <c r="I25" s="139" t="n">
+      <c r="I25" s="148" t="n">
         <v>353722</v>
       </c>
-      <c r="J25" s="142">
+      <c r="J25" s="150">
         <f>J24*J8</f>
         <v/>
       </c>
-      <c r="K25" s="142">
+      <c r="K25" s="150">
         <f>K24*K8</f>
         <v/>
       </c>
-      <c r="L25" s="142">
+      <c r="L25" s="150">
         <f>L24*L8</f>
         <v/>
       </c>
-      <c r="M25" s="142">
+      <c r="M25" s="150">
         <f>M24*M8</f>
         <v/>
       </c>
-      <c r="N25" s="142">
+      <c r="N25" s="150">
         <f>N24*N8</f>
         <v/>
       </c>
@@ -3505,43 +3619,43 @@
       </c>
       <c r="C26" s="4" t="n"/>
       <c r="D26" s="22" t="n"/>
-      <c r="E26" s="143">
+      <c r="E26" s="151">
         <f>E24-E25</f>
         <v/>
       </c>
-      <c r="F26" s="143">
+      <c r="F26" s="151">
         <f>F24-F25</f>
         <v/>
       </c>
-      <c r="G26" s="143">
+      <c r="G26" s="151">
         <f>G24-G25</f>
         <v/>
       </c>
-      <c r="H26" s="143">
+      <c r="H26" s="151">
         <f>H24-H25</f>
         <v/>
       </c>
-      <c r="I26" s="143">
+      <c r="I26" s="151">
         <f>I24-I25</f>
         <v/>
       </c>
-      <c r="J26" s="143">
+      <c r="J26" s="151">
         <f>J24-J25</f>
         <v/>
       </c>
-      <c r="K26" s="143">
+      <c r="K26" s="151">
         <f>K24-K25</f>
         <v/>
       </c>
-      <c r="L26" s="143">
+      <c r="L26" s="151">
         <f>L24-L25</f>
         <v/>
       </c>
-      <c r="M26" s="143">
+      <c r="M26" s="151">
         <f>M24-M25</f>
         <v/>
       </c>
-      <c r="N26" s="143">
+      <c r="N26" s="151">
         <f>N24-N25</f>
         <v/>
       </c>
@@ -3571,38 +3685,43 @@
           <t>Salaries and Benefits</t>
         </is>
       </c>
-      <c r="E28" s="139" t="n">
+      <c r="C28" s="144" t="inlineStr">
+        <is>
+          <t>← J9 = Rev×SGA% equation</t>
+        </is>
+      </c>
+      <c r="E28" s="148" t="n">
         <v>396281</v>
       </c>
-      <c r="F28" s="139" t="n">
+      <c r="F28" s="148" t="n">
         <v>383863</v>
       </c>
-      <c r="G28" s="139" t="n">
+      <c r="G28" s="148" t="n">
         <v>400565</v>
       </c>
-      <c r="H28" s="139" t="n">
+      <c r="H28" s="148" t="n">
         <v>462834</v>
       </c>
-      <c r="I28" s="139" t="n">
+      <c r="I28" s="148" t="n">
         <v>513028</v>
       </c>
-      <c r="J28" s="142">
+      <c r="J28" s="150">
         <f>J9</f>
         <v/>
       </c>
-      <c r="K28" s="142">
+      <c r="K28" s="150">
         <f>K9</f>
         <v/>
       </c>
-      <c r="L28" s="142">
+      <c r="L28" s="150">
         <f>L9</f>
         <v/>
       </c>
-      <c r="M28" s="142">
+      <c r="M28" s="150">
         <f>M9</f>
         <v/>
       </c>
-      <c r="N28" s="142">
+      <c r="N28" s="150">
         <f>N9</f>
         <v/>
       </c>
@@ -3613,38 +3732,43 @@
           <t>Rent and Overhead</t>
         </is>
       </c>
-      <c r="E29" s="139" t="n">
+      <c r="C29" s="144" t="inlineStr">
+        <is>
+          <t>← J10 = Rev×R&amp;D% equation</t>
+        </is>
+      </c>
+      <c r="E29" s="148" t="n">
         <v>171231</v>
       </c>
-      <c r="F29" s="139" t="n">
+      <c r="F29" s="148" t="n">
         <v>146758</v>
       </c>
-      <c r="G29" s="139" t="n">
+      <c r="G29" s="148" t="n">
         <v>159950</v>
       </c>
-      <c r="H29" s="139" t="n">
+      <c r="H29" s="148" t="n">
         <v>171940</v>
       </c>
-      <c r="I29" s="139" t="n">
+      <c r="I29" s="148" t="n">
         <v>188347</v>
       </c>
-      <c r="J29" s="142">
+      <c r="J29" s="150">
         <f>J10</f>
         <v/>
       </c>
-      <c r="K29" s="142">
+      <c r="K29" s="150">
         <f>K10</f>
         <v/>
       </c>
-      <c r="L29" s="142">
+      <c r="L29" s="150">
         <f>L10</f>
         <v/>
       </c>
-      <c r="M29" s="142">
+      <c r="M29" s="150">
         <f>M10</f>
         <v/>
       </c>
-      <c r="N29" s="142">
+      <c r="N29" s="150">
         <f>N10</f>
         <v/>
       </c>
@@ -3655,38 +3779,38 @@
           <t>Depreciation &amp; Amortization</t>
         </is>
       </c>
-      <c r="E30" s="139" t="n">
+      <c r="E30" s="148" t="n">
         <v>25592</v>
       </c>
-      <c r="F30" s="139" t="n">
+      <c r="F30" s="148" t="n">
         <v>20465</v>
       </c>
-      <c r="G30" s="139" t="n">
+      <c r="G30" s="148" t="n">
         <v>14638</v>
       </c>
-      <c r="H30" s="139" t="n">
+      <c r="H30" s="148" t="n">
         <v>13827</v>
       </c>
-      <c r="I30" s="139" t="n">
+      <c r="I30" s="148" t="n">
         <v>14952</v>
       </c>
-      <c r="J30" s="142">
+      <c r="J30" s="150">
         <f>J94</f>
         <v/>
       </c>
-      <c r="K30" s="142">
+      <c r="K30" s="150">
         <f>K94</f>
         <v/>
       </c>
-      <c r="L30" s="142">
+      <c r="L30" s="150">
         <f>L94</f>
         <v/>
       </c>
-      <c r="M30" s="142">
+      <c r="M30" s="150">
         <f>M94</f>
         <v/>
       </c>
-      <c r="N30" s="142">
+      <c r="N30" s="150">
         <f>N94</f>
         <v/>
       </c>
@@ -3699,38 +3823,38 @@
       </c>
       <c r="C31" s="2" t="n"/>
       <c r="D31" s="24" t="n"/>
-      <c r="E31" s="144" t="n">
+      <c r="E31" s="152" t="n">
         <v>40092</v>
       </c>
-      <c r="F31" s="144" t="n">
+      <c r="F31" s="152" t="n">
         <v>68967</v>
       </c>
-      <c r="G31" s="144" t="n">
+      <c r="G31" s="152" t="n">
         <v>95546</v>
       </c>
-      <c r="H31" s="144" t="n">
+      <c r="H31" s="152" t="n">
         <v>105638</v>
       </c>
-      <c r="I31" s="144" t="n">
+      <c r="I31" s="152" t="n">
         <v>133647</v>
       </c>
-      <c r="J31" s="145">
+      <c r="J31" s="153">
         <f>J101</f>
         <v/>
       </c>
-      <c r="K31" s="145">
+      <c r="K31" s="153">
         <f>K101</f>
         <v/>
       </c>
-      <c r="L31" s="145">
+      <c r="L31" s="153">
         <f>L101</f>
         <v/>
       </c>
-      <c r="M31" s="145">
+      <c r="M31" s="153">
         <f>M101</f>
         <v/>
       </c>
-      <c r="N31" s="145">
+      <c r="N31" s="153">
         <f>N101</f>
         <v/>
       </c>
@@ -3743,43 +3867,43 @@
       </c>
       <c r="C32" s="19" t="n"/>
       <c r="D32" s="47" t="n"/>
-      <c r="E32" s="146">
+      <c r="E32" s="154">
         <f>SUM(E28:E31)</f>
         <v/>
       </c>
-      <c r="F32" s="146">
+      <c r="F32" s="154">
         <f>SUM(F28:F31)</f>
         <v/>
       </c>
-      <c r="G32" s="146">
+      <c r="G32" s="154">
         <f>SUM(G28:G31)</f>
         <v/>
       </c>
-      <c r="H32" s="146">
+      <c r="H32" s="154">
         <f>SUM(H28:H31)</f>
         <v/>
       </c>
-      <c r="I32" s="146">
+      <c r="I32" s="154">
         <f>SUM(I28:I31)</f>
         <v/>
       </c>
-      <c r="J32" s="146">
+      <c r="J32" s="154">
         <f>SUM(J28:J31)</f>
         <v/>
       </c>
-      <c r="K32" s="146">
+      <c r="K32" s="154">
         <f>SUM(K28:K31)</f>
         <v/>
       </c>
-      <c r="L32" s="146">
+      <c r="L32" s="154">
         <f>SUM(L28:L31)</f>
         <v/>
       </c>
-      <c r="M32" s="146">
+      <c r="M32" s="154">
         <f>SUM(M28:M31)</f>
         <v/>
       </c>
-      <c r="N32" s="146">
+      <c r="N32" s="154">
         <f>SUM(N28:N31)</f>
         <v/>
       </c>
@@ -3792,43 +3916,43 @@
       </c>
       <c r="C33" s="4" t="n"/>
       <c r="D33" s="22" t="n"/>
-      <c r="E33" s="143">
+      <c r="E33" s="151">
         <f>E26-E32</f>
         <v/>
       </c>
-      <c r="F33" s="143">
+      <c r="F33" s="151">
         <f>F26-F32</f>
         <v/>
       </c>
-      <c r="G33" s="143">
+      <c r="G33" s="151">
         <f>G26-G32</f>
         <v/>
       </c>
-      <c r="H33" s="143">
+      <c r="H33" s="151">
         <f>H26-H32</f>
         <v/>
       </c>
-      <c r="I33" s="143">
+      <c r="I33" s="151">
         <f>I26-I32</f>
         <v/>
       </c>
-      <c r="J33" s="143">
+      <c r="J33" s="151">
         <f>J26-J32</f>
         <v/>
       </c>
-      <c r="K33" s="143">
+      <c r="K33" s="151">
         <f>K26-K32</f>
         <v/>
       </c>
-      <c r="L33" s="143">
+      <c r="L33" s="151">
         <f>L26-L32</f>
         <v/>
       </c>
-      <c r="M33" s="143">
+      <c r="M33" s="151">
         <f>M26-M32</f>
         <v/>
       </c>
-      <c r="N33" s="143">
+      <c r="N33" s="151">
         <f>N26-N32</f>
         <v/>
       </c>
@@ -3856,38 +3980,38 @@
       </c>
       <c r="C35" s="19" t="n"/>
       <c r="D35" s="47" t="n"/>
-      <c r="E35" s="139" t="n">
+      <c r="E35" s="148" t="n">
         <v>81058</v>
       </c>
-      <c r="F35" s="139" t="n">
+      <c r="F35" s="148" t="n">
         <v>97768</v>
       </c>
-      <c r="G35" s="139" t="n">
+      <c r="G35" s="148" t="n">
         <v>124249</v>
       </c>
-      <c r="H35" s="139" t="n">
+      <c r="H35" s="148" t="n">
         <v>129214</v>
       </c>
-      <c r="I35" s="139" t="n">
+      <c r="I35" s="148" t="n">
         <v>150649</v>
       </c>
-      <c r="J35" s="142">
+      <c r="J35" s="150">
         <f>J33*J13</f>
         <v/>
       </c>
-      <c r="K35" s="142">
+      <c r="K35" s="150">
         <f>K33*K13</f>
         <v/>
       </c>
-      <c r="L35" s="142">
+      <c r="L35" s="150">
         <f>L33*L13</f>
         <v/>
       </c>
-      <c r="M35" s="142">
+      <c r="M35" s="150">
         <f>M33*M13</f>
         <v/>
       </c>
-      <c r="N35" s="142">
+      <c r="N35" s="150">
         <f>N33*N13</f>
         <v/>
       </c>
@@ -3900,43 +4024,43 @@
       </c>
       <c r="C36" s="39" t="n"/>
       <c r="D36" s="40" t="n"/>
-      <c r="E36" s="147">
+      <c r="E36" s="155">
         <f>E33-E35</f>
         <v/>
       </c>
-      <c r="F36" s="147">
+      <c r="F36" s="155">
         <f>F33-F35</f>
         <v/>
       </c>
-      <c r="G36" s="147">
+      <c r="G36" s="155">
         <f>G33-G35</f>
         <v/>
       </c>
-      <c r="H36" s="147">
+      <c r="H36" s="155">
         <f>H33-H35</f>
         <v/>
       </c>
-      <c r="I36" s="147">
+      <c r="I36" s="155">
         <f>I33-I35</f>
         <v/>
       </c>
-      <c r="J36" s="147">
+      <c r="J36" s="155">
         <f>J33-J35</f>
         <v/>
       </c>
-      <c r="K36" s="147">
+      <c r="K36" s="155">
         <f>K33-K35</f>
         <v/>
       </c>
-      <c r="L36" s="147">
+      <c r="L36" s="155">
         <f>L33-L35</f>
         <v/>
       </c>
-      <c r="M36" s="147">
+      <c r="M36" s="155">
         <f>M33-M35</f>
         <v/>
       </c>
-      <c r="N36" s="147">
+      <c r="N36" s="155">
         <f>N33-N35</f>
         <v/>
       </c>
@@ -3997,38 +4121,38 @@
           <t>Cash</t>
         </is>
       </c>
-      <c r="E41" s="139" t="n">
+      <c r="E41" s="148" t="n">
         <v>195354</v>
       </c>
-      <c r="F41" s="139" t="n">
+      <c r="F41" s="148" t="n">
         <v>133202</v>
       </c>
-      <c r="G41" s="139" t="n">
+      <c r="G41" s="148" t="n">
         <v>136778</v>
       </c>
-      <c r="H41" s="139" t="n">
+      <c r="H41" s="148" t="n">
         <v>150667</v>
       </c>
-      <c r="I41" s="139" t="n">
+      <c r="I41" s="148" t="n">
         <v>134136</v>
       </c>
-      <c r="J41" s="142">
+      <c r="J41" s="150">
         <f>J78</f>
         <v/>
       </c>
-      <c r="K41" s="142">
+      <c r="K41" s="150">
         <f>K78</f>
         <v/>
       </c>
-      <c r="L41" s="142">
+      <c r="L41" s="150">
         <f>L78</f>
         <v/>
       </c>
-      <c r="M41" s="142">
+      <c r="M41" s="150">
         <f>M78</f>
         <v/>
       </c>
-      <c r="N41" s="142">
+      <c r="N41" s="150">
         <f>N78</f>
         <v/>
       </c>
@@ -4039,38 +4163,38 @@
           <t>Accounts Receivable</t>
         </is>
       </c>
-      <c r="E42" s="139" t="n">
+      <c r="E42" s="148" t="n">
         <v>206690</v>
       </c>
-      <c r="F42" s="139" t="n">
+      <c r="F42" s="148" t="n">
         <v>202365</v>
       </c>
-      <c r="G42" s="139" t="n">
+      <c r="G42" s="148" t="n">
         <v>251217</v>
       </c>
-      <c r="H42" s="139" t="n">
+      <c r="H42" s="148" t="n">
         <v>269745</v>
       </c>
-      <c r="I42" s="139" t="n">
+      <c r="I42" s="148" t="n">
         <v>341776</v>
       </c>
-      <c r="J42" s="142">
+      <c r="J42" s="150">
         <f>J24*J15/365</f>
         <v/>
       </c>
-      <c r="K42" s="142">
+      <c r="K42" s="150">
         <f>K24*K15/365</f>
         <v/>
       </c>
-      <c r="L42" s="142">
+      <c r="L42" s="150">
         <f>L24*L15/365</f>
         <v/>
       </c>
-      <c r="M42" s="142">
+      <c r="M42" s="150">
         <f>M24*M15/365</f>
         <v/>
       </c>
-      <c r="N42" s="142">
+      <c r="N42" s="150">
         <f>N24*N15/365</f>
         <v/>
       </c>
@@ -4081,38 +4205,38 @@
           <t>Inventory</t>
         </is>
       </c>
-      <c r="E43" s="139" t="n">
+      <c r="E43" s="148" t="n">
         <v>0</v>
       </c>
-      <c r="F43" s="139" t="n">
+      <c r="F43" s="148" t="n">
         <v>0</v>
       </c>
-      <c r="G43" s="139" t="n">
+      <c r="G43" s="148" t="n">
         <v>0</v>
       </c>
-      <c r="H43" s="139" t="n">
+      <c r="H43" s="148" t="n">
         <v>0</v>
       </c>
-      <c r="I43" s="139" t="n">
+      <c r="I43" s="148" t="n">
         <v>0</v>
       </c>
-      <c r="J43" s="142">
+      <c r="J43" s="150">
         <f>J25*J16/365</f>
         <v/>
       </c>
-      <c r="K43" s="142">
+      <c r="K43" s="150">
         <f>K25*K16/365</f>
         <v/>
       </c>
-      <c r="L43" s="142">
+      <c r="L43" s="150">
         <f>L25*L16/365</f>
         <v/>
       </c>
-      <c r="M43" s="142">
+      <c r="M43" s="150">
         <f>M25*M16/365</f>
         <v/>
       </c>
-      <c r="N43" s="142">
+      <c r="N43" s="150">
         <f>N25*N16/365</f>
         <v/>
       </c>
@@ -4123,38 +4247,38 @@
           <t>Property &amp; Equipment</t>
         </is>
       </c>
-      <c r="E44" s="139" t="n">
+      <c r="E44" s="148" t="n">
         <v>27913</v>
       </c>
-      <c r="F44" s="139" t="n">
+      <c r="F44" s="148" t="n">
         <v>17580</v>
       </c>
-      <c r="G44" s="139" t="n">
+      <c r="G44" s="148" t="n">
         <v>10966</v>
       </c>
-      <c r="H44" s="139" t="n">
+      <c r="H44" s="148" t="n">
         <v>38465</v>
       </c>
-      <c r="I44" s="139" t="n">
+      <c r="I44" s="148" t="n">
         <v>67713</v>
       </c>
-      <c r="J44" s="142">
+      <c r="J44" s="150">
         <f>J95</f>
         <v/>
       </c>
-      <c r="K44" s="142">
+      <c r="K44" s="150">
         <f>K95</f>
         <v/>
       </c>
-      <c r="L44" s="142">
+      <c r="L44" s="150">
         <f>L95</f>
         <v/>
       </c>
-      <c r="M44" s="142">
+      <c r="M44" s="150">
         <f>M95</f>
         <v/>
       </c>
-      <c r="N44" s="142">
+      <c r="N44" s="150">
         <f>N95</f>
         <v/>
       </c>
@@ -4167,43 +4291,43 @@
       </c>
       <c r="C45" s="39" t="n"/>
       <c r="D45" s="40" t="n"/>
-      <c r="E45" s="147">
+      <c r="E45" s="155">
         <f>SUM(E41:E44)</f>
         <v/>
       </c>
-      <c r="F45" s="147">
+      <c r="F45" s="155">
         <f>SUM(F41:F44)</f>
         <v/>
       </c>
-      <c r="G45" s="147">
+      <c r="G45" s="155">
         <f>SUM(G41:G44)</f>
         <v/>
       </c>
-      <c r="H45" s="147">
+      <c r="H45" s="155">
         <f>SUM(H41:H44)</f>
         <v/>
       </c>
-      <c r="I45" s="147">
+      <c r="I45" s="155">
         <f>SUM(I41:I44)</f>
         <v/>
       </c>
-      <c r="J45" s="147">
+      <c r="J45" s="155">
         <f>SUM(J41:J44)</f>
         <v/>
       </c>
-      <c r="K45" s="147">
+      <c r="K45" s="155">
         <f>SUM(K41:K44)</f>
         <v/>
       </c>
-      <c r="L45" s="147">
+      <c r="L45" s="155">
         <f>SUM(L41:L44)</f>
         <v/>
       </c>
-      <c r="M45" s="147">
+      <c r="M45" s="155">
         <f>SUM(M41:M44)</f>
         <v/>
       </c>
-      <c r="N45" s="147">
+      <c r="N45" s="155">
         <f>SUM(N41:N44)</f>
         <v/>
       </c>
@@ -4241,38 +4365,38 @@
           <t>Accounts Payable</t>
         </is>
       </c>
-      <c r="E48" s="139" t="n">
+      <c r="E48" s="148" t="n">
         <v>20749</v>
       </c>
-      <c r="F48" s="139" t="n">
+      <c r="F48" s="148" t="n">
         <v>17273</v>
       </c>
-      <c r="G48" s="139" t="n">
+      <c r="G48" s="148" t="n">
         <v>19009</v>
       </c>
-      <c r="H48" s="139" t="n">
+      <c r="H48" s="148" t="n">
         <v>22473</v>
       </c>
-      <c r="I48" s="139" t="n">
+      <c r="I48" s="148" t="n">
         <v>32315</v>
       </c>
-      <c r="J48" s="142">
+      <c r="J48" s="150">
         <f>J25*J17/365</f>
         <v/>
       </c>
-      <c r="K48" s="142">
+      <c r="K48" s="150">
         <f>K25*K17/365</f>
         <v/>
       </c>
-      <c r="L48" s="142">
+      <c r="L48" s="150">
         <f>L25*L17/365</f>
         <v/>
       </c>
-      <c r="M48" s="142">
+      <c r="M48" s="150">
         <f>M25*M17/365</f>
         <v/>
       </c>
-      <c r="N48" s="142">
+      <c r="N48" s="150">
         <f>N25*N17/365</f>
         <v/>
       </c>
@@ -4283,38 +4407,38 @@
           <t>Debt</t>
         </is>
       </c>
-      <c r="E49" s="139" t="n">
+      <c r="E49" s="148" t="n">
         <v>1259018</v>
       </c>
-      <c r="F49" s="139" t="n">
+      <c r="F49" s="148" t="n">
         <v>1853669</v>
       </c>
-      <c r="G49" s="139" t="n">
+      <c r="G49" s="148" t="n">
         <v>1861658</v>
       </c>
-      <c r="H49" s="139" t="n">
+      <c r="H49" s="148" t="n">
         <v>2209021</v>
       </c>
-      <c r="I49" s="139" t="n">
+      <c r="I49" s="148" t="n">
         <v>3055691</v>
       </c>
-      <c r="J49" s="142">
+      <c r="J49" s="150">
         <f>J100</f>
         <v/>
       </c>
-      <c r="K49" s="142">
+      <c r="K49" s="150">
         <f>K100</f>
         <v/>
       </c>
-      <c r="L49" s="142">
+      <c r="L49" s="150">
         <f>L100</f>
         <v/>
       </c>
-      <c r="M49" s="142">
+      <c r="M49" s="150">
         <f>M100</f>
         <v/>
       </c>
-      <c r="N49" s="142">
+      <c r="N49" s="150">
         <f>N100</f>
         <v/>
       </c>
@@ -4327,43 +4451,43 @@
       </c>
       <c r="C50" s="4" t="n"/>
       <c r="D50" s="22" t="n"/>
-      <c r="E50" s="143">
+      <c r="E50" s="151">
         <f>SUM(E48:E49)</f>
         <v/>
       </c>
-      <c r="F50" s="143">
+      <c r="F50" s="151">
         <f>SUM(F48:F49)</f>
         <v/>
       </c>
-      <c r="G50" s="143">
+      <c r="G50" s="151">
         <f>SUM(G48:G49)</f>
         <v/>
       </c>
-      <c r="H50" s="143">
+      <c r="H50" s="151">
         <f>SUM(H48:H49)</f>
         <v/>
       </c>
-      <c r="I50" s="143">
+      <c r="I50" s="151">
         <f>SUM(I48:I49)</f>
         <v/>
       </c>
-      <c r="J50" s="143">
+      <c r="J50" s="151">
         <f>SUM(J48:J49)</f>
         <v/>
       </c>
-      <c r="K50" s="143">
+      <c r="K50" s="151">
         <f>SUM(K48:K49)</f>
         <v/>
       </c>
-      <c r="L50" s="143">
+      <c r="L50" s="151">
         <f>SUM(L48:L49)</f>
         <v/>
       </c>
-      <c r="M50" s="143">
+      <c r="M50" s="151">
         <f>SUM(M48:M49)</f>
         <v/>
       </c>
-      <c r="N50" s="143">
+      <c r="N50" s="151">
         <f>SUM(N48:N49)</f>
         <v/>
       </c>
@@ -4386,38 +4510,38 @@
           <t>Equity Capital</t>
         </is>
       </c>
-      <c r="E52" s="139" t="n">
+      <c r="E52" s="148" t="n">
         <v>-849810</v>
       </c>
-      <c r="F52" s="139" t="n">
+      <c r="F52" s="148" t="n">
         <v>-1517795</v>
       </c>
-      <c r="G52" s="139" t="n">
+      <c r="G52" s="148" t="n">
         <v>-1481706</v>
       </c>
-      <c r="H52" s="139" t="n">
+      <c r="H52" s="148" t="n">
         <v>-1772617</v>
       </c>
-      <c r="I52" s="139" t="n">
+      <c r="I52" s="148" t="n">
         <v>-2544381</v>
       </c>
-      <c r="J52" s="142">
+      <c r="J52" s="150">
         <f>I52+J20</f>
         <v/>
       </c>
-      <c r="K52" s="142">
+      <c r="K52" s="150">
         <f>J52+K20</f>
         <v/>
       </c>
-      <c r="L52" s="142">
+      <c r="L52" s="150">
         <f>K52+L20</f>
         <v/>
       </c>
-      <c r="M52" s="142">
+      <c r="M52" s="150">
         <f>L52+M20</f>
         <v/>
       </c>
-      <c r="N52" s="142">
+      <c r="N52" s="150">
         <f>M52+N20</f>
         <v/>
       </c>
@@ -4428,38 +4552,38 @@
           <t>Retained Earnings</t>
         </is>
       </c>
-      <c r="E53" s="139" t="n">
+      <c r="E53" s="148" t="n">
         <v>0</v>
       </c>
-      <c r="F53" s="139" t="n">
+      <c r="F53" s="148" t="n">
         <v>0</v>
       </c>
-      <c r="G53" s="139" t="n">
+      <c r="G53" s="148" t="n">
         <v>0</v>
       </c>
-      <c r="H53" s="139" t="n">
+      <c r="H53" s="148" t="n">
         <v>0</v>
       </c>
-      <c r="I53" s="139" t="n">
+      <c r="I53" s="148" t="n">
         <v>0</v>
       </c>
-      <c r="J53" s="142">
+      <c r="J53" s="150">
         <f>I53+J36</f>
         <v/>
       </c>
-      <c r="K53" s="142">
+      <c r="K53" s="150">
         <f>J53+K36</f>
         <v/>
       </c>
-      <c r="L53" s="142">
+      <c r="L53" s="150">
         <f>K53+L36</f>
         <v/>
       </c>
-      <c r="M53" s="142">
+      <c r="M53" s="150">
         <f>L53+M36</f>
         <v/>
       </c>
-      <c r="N53" s="142">
+      <c r="N53" s="150">
         <f>M53+N36</f>
         <v/>
       </c>
@@ -4472,43 +4596,43 @@
       </c>
       <c r="C54" s="8" t="n"/>
       <c r="D54" s="26" t="n"/>
-      <c r="E54" s="148">
+      <c r="E54" s="156">
         <f>SUM(E52:E53)</f>
         <v/>
       </c>
-      <c r="F54" s="148">
+      <c r="F54" s="156">
         <f>SUM(F52:F53)</f>
         <v/>
       </c>
-      <c r="G54" s="148">
+      <c r="G54" s="156">
         <f>SUM(G52:G53)</f>
         <v/>
       </c>
-      <c r="H54" s="148">
+      <c r="H54" s="156">
         <f>SUM(H52:H53)</f>
         <v/>
       </c>
-      <c r="I54" s="148">
+      <c r="I54" s="156">
         <f>SUM(I52:I53)</f>
         <v/>
       </c>
-      <c r="J54" s="148">
+      <c r="J54" s="156">
         <f>SUM(J52:J53)</f>
         <v/>
       </c>
-      <c r="K54" s="148">
+      <c r="K54" s="156">
         <f>SUM(K52:K53)</f>
         <v/>
       </c>
-      <c r="L54" s="148">
+      <c r="L54" s="156">
         <f>SUM(L52:L53)</f>
         <v/>
       </c>
-      <c r="M54" s="148">
+      <c r="M54" s="156">
         <f>SUM(M52:M53)</f>
         <v/>
       </c>
-      <c r="N54" s="148">
+      <c r="N54" s="156">
         <f>SUM(N52:N53)</f>
         <v/>
       </c>
@@ -4521,43 +4645,43 @@
       </c>
       <c r="C55" s="39" t="n"/>
       <c r="D55" s="40" t="n"/>
-      <c r="E55" s="147">
+      <c r="E55" s="155">
         <f>E50+E54</f>
         <v/>
       </c>
-      <c r="F55" s="147">
+      <c r="F55" s="155">
         <f>F50+F54</f>
         <v/>
       </c>
-      <c r="G55" s="147">
+      <c r="G55" s="155">
         <f>G50+G54</f>
         <v/>
       </c>
-      <c r="H55" s="147">
+      <c r="H55" s="155">
         <f>H50+H54</f>
         <v/>
       </c>
-      <c r="I55" s="147">
+      <c r="I55" s="155">
         <f>I50+I54</f>
         <v/>
       </c>
-      <c r="J55" s="147">
+      <c r="J55" s="155">
         <f>J50+J54</f>
         <v/>
       </c>
-      <c r="K55" s="147">
+      <c r="K55" s="155">
         <f>K50+K54</f>
         <v/>
       </c>
-      <c r="L55" s="147">
+      <c r="L55" s="155">
         <f>L50+L54</f>
         <v/>
       </c>
-      <c r="M55" s="147">
+      <c r="M55" s="155">
         <f>M50+M54</f>
         <v/>
       </c>
-      <c r="N55" s="147">
+      <c r="N55" s="155">
         <f>N50+N54</f>
         <v/>
       </c>
@@ -4582,43 +4706,43 @@
       </c>
       <c r="C57" s="9" t="n"/>
       <c r="D57" s="27" t="n"/>
-      <c r="E57" s="149">
+      <c r="E57" s="157">
         <f>E55-E45</f>
         <v/>
       </c>
-      <c r="F57" s="149">
+      <c r="F57" s="157">
         <f>F55-F45</f>
         <v/>
       </c>
-      <c r="G57" s="149">
+      <c r="G57" s="157">
         <f>G55-G45</f>
         <v/>
       </c>
-      <c r="H57" s="149">
+      <c r="H57" s="157">
         <f>H55-H45</f>
         <v/>
       </c>
-      <c r="I57" s="149">
+      <c r="I57" s="157">
         <f>I55-I45</f>
         <v/>
       </c>
-      <c r="J57" s="149">
+      <c r="J57" s="157">
         <f>J55-J45</f>
         <v/>
       </c>
-      <c r="K57" s="149">
+      <c r="K57" s="157">
         <f>K55-K45</f>
         <v/>
       </c>
-      <c r="L57" s="149">
+      <c r="L57" s="157">
         <f>L55-L45</f>
         <v/>
       </c>
-      <c r="M57" s="149">
+      <c r="M57" s="157">
         <f>M55-M45</f>
         <v/>
       </c>
-      <c r="N57" s="149">
+      <c r="N57" s="157">
         <f>N55-N45</f>
         <v/>
       </c>
@@ -4682,43 +4806,43 @@
           <t>Net Earnings</t>
         </is>
       </c>
-      <c r="E62" s="142">
+      <c r="E62" s="150">
         <f>E36</f>
         <v/>
       </c>
-      <c r="F62" s="142">
+      <c r="F62" s="150">
         <f>F36</f>
         <v/>
       </c>
-      <c r="G62" s="142">
+      <c r="G62" s="150">
         <f>G36</f>
         <v/>
       </c>
-      <c r="H62" s="142">
+      <c r="H62" s="150">
         <f>H36</f>
         <v/>
       </c>
-      <c r="I62" s="142">
+      <c r="I62" s="150">
         <f>I36</f>
         <v/>
       </c>
-      <c r="J62" s="142">
+      <c r="J62" s="150">
         <f>J36</f>
         <v/>
       </c>
-      <c r="K62" s="142">
+      <c r="K62" s="150">
         <f>K36</f>
         <v/>
       </c>
-      <c r="L62" s="142">
+      <c r="L62" s="150">
         <f>L36</f>
         <v/>
       </c>
-      <c r="M62" s="142">
+      <c r="M62" s="150">
         <f>M36</f>
         <v/>
       </c>
-      <c r="N62" s="142">
+      <c r="N62" s="150">
         <f>N36</f>
         <v/>
       </c>
@@ -4729,43 +4853,43 @@
           <t>Plus: Depreciation &amp; Amortization</t>
         </is>
       </c>
-      <c r="E63" s="142">
+      <c r="E63" s="150">
         <f>+E30</f>
         <v/>
       </c>
-      <c r="F63" s="142">
+      <c r="F63" s="150">
         <f>+F30</f>
         <v/>
       </c>
-      <c r="G63" s="142">
+      <c r="G63" s="150">
         <f>+G30</f>
         <v/>
       </c>
-      <c r="H63" s="142">
+      <c r="H63" s="150">
         <f>+H30</f>
         <v/>
       </c>
-      <c r="I63" s="142">
+      <c r="I63" s="150">
         <f>+I30</f>
         <v/>
       </c>
-      <c r="J63" s="142">
+      <c r="J63" s="150">
         <f>+J30</f>
         <v/>
       </c>
-      <c r="K63" s="142">
+      <c r="K63" s="150">
         <f>+K30</f>
         <v/>
       </c>
-      <c r="L63" s="142">
+      <c r="L63" s="150">
         <f>+L30</f>
         <v/>
       </c>
-      <c r="M63" s="142">
+      <c r="M63" s="150">
         <f>+M30</f>
         <v/>
       </c>
-      <c r="N63" s="142">
+      <c r="N63" s="150">
         <f>+N30</f>
         <v/>
       </c>
@@ -4776,38 +4900,38 @@
           <t>Less: Changes in Working Capital</t>
         </is>
       </c>
-      <c r="E64" s="139" t="n">
+      <c r="E64" s="148" t="n">
         <v>0</v>
       </c>
-      <c r="F64" s="139" t="n">
+      <c r="F64" s="148" t="n">
         <v>-849</v>
       </c>
-      <c r="G64" s="139" t="n">
+      <c r="G64" s="148" t="n">
         <v>47116</v>
       </c>
-      <c r="H64" s="139" t="n">
+      <c r="H64" s="148" t="n">
         <v>15064</v>
       </c>
-      <c r="I64" s="139" t="n">
+      <c r="I64" s="148" t="n">
         <v>62189</v>
       </c>
-      <c r="J64" s="142">
+      <c r="J64" s="150">
         <f>J89</f>
         <v/>
       </c>
-      <c r="K64" s="142">
+      <c r="K64" s="150">
         <f>K89</f>
         <v/>
       </c>
-      <c r="L64" s="142">
+      <c r="L64" s="150">
         <f>L89</f>
         <v/>
       </c>
-      <c r="M64" s="142">
+      <c r="M64" s="150">
         <f>M89</f>
         <v/>
       </c>
-      <c r="N64" s="142">
+      <c r="N64" s="150">
         <f>N89</f>
         <v/>
       </c>
@@ -4820,43 +4944,43 @@
       </c>
       <c r="C65" s="5" t="n"/>
       <c r="D65" s="28" t="n"/>
-      <c r="E65" s="143">
+      <c r="E65" s="151">
         <f>E62+E63-E64</f>
         <v/>
       </c>
-      <c r="F65" s="143">
+      <c r="F65" s="151">
         <f>F62+F63-F64</f>
         <v/>
       </c>
-      <c r="G65" s="143">
+      <c r="G65" s="151">
         <f>G62+G63-G64</f>
         <v/>
       </c>
-      <c r="H65" s="143">
+      <c r="H65" s="151">
         <f>H62+H63-H64</f>
         <v/>
       </c>
-      <c r="I65" s="143">
+      <c r="I65" s="151">
         <f>I62+I63-I64</f>
         <v/>
       </c>
-      <c r="J65" s="143">
+      <c r="J65" s="151">
         <f>J62+J63-J64</f>
         <v/>
       </c>
-      <c r="K65" s="143">
+      <c r="K65" s="151">
         <f>K62+K63-K64</f>
         <v/>
       </c>
-      <c r="L65" s="143">
+      <c r="L65" s="151">
         <f>L62+L63-L64</f>
         <v/>
       </c>
-      <c r="M65" s="143">
+      <c r="M65" s="151">
         <f>M62+M63-M64</f>
         <v/>
       </c>
-      <c r="N65" s="143">
+      <c r="N65" s="151">
         <f>N62+N63-N64</f>
         <v/>
       </c>
@@ -4899,38 +5023,38 @@
           <t>Investments in Property &amp; Equipment</t>
         </is>
       </c>
-      <c r="E68" s="139" t="n">
+      <c r="E68" s="148" t="n">
         <v>7569</v>
       </c>
-      <c r="F68" s="139" t="n">
+      <c r="F68" s="148" t="n">
         <v>6029</v>
       </c>
-      <c r="G68" s="139" t="n">
+      <c r="G68" s="148" t="n">
         <v>4237</v>
       </c>
-      <c r="H68" s="139" t="n">
+      <c r="H68" s="148" t="n">
         <v>25551</v>
       </c>
-      <c r="I68" s="139" t="n">
+      <c r="I68" s="148" t="n">
         <v>39407</v>
       </c>
-      <c r="J68" s="142">
+      <c r="J68" s="150">
         <f>J18</f>
         <v/>
       </c>
-      <c r="K68" s="142">
+      <c r="K68" s="150">
         <f>K18</f>
         <v/>
       </c>
-      <c r="L68" s="142">
+      <c r="L68" s="150">
         <f>L18</f>
         <v/>
       </c>
-      <c r="M68" s="142">
+      <c r="M68" s="150">
         <f>M18</f>
         <v/>
       </c>
-      <c r="N68" s="142">
+      <c r="N68" s="150">
         <f>N18</f>
         <v/>
       </c>
@@ -4943,43 +5067,43 @@
       </c>
       <c r="C69" s="5" t="n"/>
       <c r="D69" s="28" t="n"/>
-      <c r="E69" s="143">
+      <c r="E69" s="151">
         <f>SUM(E68)</f>
         <v/>
       </c>
-      <c r="F69" s="143">
+      <c r="F69" s="151">
         <f>SUM(F68)</f>
         <v/>
       </c>
-      <c r="G69" s="143">
+      <c r="G69" s="151">
         <f>SUM(G68)</f>
         <v/>
       </c>
-      <c r="H69" s="143">
+      <c r="H69" s="151">
         <f>SUM(H68)</f>
         <v/>
       </c>
-      <c r="I69" s="143">
+      <c r="I69" s="151">
         <f>SUM(I68)</f>
         <v/>
       </c>
-      <c r="J69" s="143">
+      <c r="J69" s="151">
         <f>SUM(J68)</f>
         <v/>
       </c>
-      <c r="K69" s="143">
+      <c r="K69" s="151">
         <f>SUM(K68)</f>
         <v/>
       </c>
-      <c r="L69" s="143">
+      <c r="L69" s="151">
         <f>SUM(L68)</f>
         <v/>
       </c>
-      <c r="M69" s="143">
+      <c r="M69" s="151">
         <f>SUM(M68)</f>
         <v/>
       </c>
-      <c r="N69" s="143">
+      <c r="N69" s="151">
         <f>SUM(N68)</f>
         <v/>
       </c>
@@ -5022,38 +5146,38 @@
           <t>Issuance (repayment) of debt</t>
         </is>
       </c>
-      <c r="E72" s="139" t="n">
+      <c r="E72" s="148" t="n">
         <v>519583</v>
       </c>
-      <c r="F72" s="139" t="n">
+      <c r="F72" s="148" t="n">
         <v>594651</v>
       </c>
-      <c r="G72" s="139" t="n">
+      <c r="G72" s="148" t="n">
         <v>7989</v>
       </c>
-      <c r="H72" s="139" t="n">
+      <c r="H72" s="148" t="n">
         <v>347363</v>
       </c>
-      <c r="I72" s="139" t="n">
+      <c r="I72" s="148" t="n">
         <v>846670</v>
       </c>
-      <c r="J72" s="142">
+      <c r="J72" s="150">
         <f>J19</f>
         <v/>
       </c>
-      <c r="K72" s="142">
+      <c r="K72" s="150">
         <f>K19</f>
         <v/>
       </c>
-      <c r="L72" s="142">
+      <c r="L72" s="150">
         <f>L19</f>
         <v/>
       </c>
-      <c r="M72" s="142">
+      <c r="M72" s="150">
         <f>M19</f>
         <v/>
       </c>
-      <c r="N72" s="142">
+      <c r="N72" s="150">
         <f>N19</f>
         <v/>
       </c>
@@ -5064,38 +5188,38 @@
           <t>Issuance (repayment) of equity</t>
         </is>
       </c>
-      <c r="E73" s="139" t="n">
+      <c r="E73" s="148" t="n">
         <v>0</v>
       </c>
-      <c r="F73" s="139" t="n">
+      <c r="F73" s="148" t="n">
         <v>0</v>
       </c>
-      <c r="G73" s="139" t="n">
+      <c r="G73" s="148" t="n">
         <v>0</v>
       </c>
-      <c r="H73" s="139" t="n">
+      <c r="H73" s="148" t="n">
         <v>0</v>
       </c>
-      <c r="I73" s="139" t="n">
+      <c r="I73" s="148" t="n">
         <v>0</v>
       </c>
-      <c r="J73" s="142">
+      <c r="J73" s="150">
         <f>J20</f>
         <v/>
       </c>
-      <c r="K73" s="142">
+      <c r="K73" s="150">
         <f>K20</f>
         <v/>
       </c>
-      <c r="L73" s="142">
+      <c r="L73" s="150">
         <f>L20</f>
         <v/>
       </c>
-      <c r="M73" s="142">
+      <c r="M73" s="150">
         <f>M20</f>
         <v/>
       </c>
-      <c r="N73" s="142">
+      <c r="N73" s="150">
         <f>N20</f>
         <v/>
       </c>
@@ -5108,43 +5232,43 @@
       </c>
       <c r="C74" s="5" t="n"/>
       <c r="D74" s="28" t="n"/>
-      <c r="E74" s="143">
+      <c r="E74" s="151">
         <f>SUM(E72:E73)</f>
         <v/>
       </c>
-      <c r="F74" s="143">
+      <c r="F74" s="151">
         <f>SUM(F72:F73)</f>
         <v/>
       </c>
-      <c r="G74" s="143">
+      <c r="G74" s="151">
         <f>SUM(G72:G73)</f>
         <v/>
       </c>
-      <c r="H74" s="143">
+      <c r="H74" s="151">
         <f>SUM(H72:H73)</f>
         <v/>
       </c>
-      <c r="I74" s="143">
+      <c r="I74" s="151">
         <f>SUM(I72:I73)</f>
         <v/>
       </c>
-      <c r="J74" s="143">
+      <c r="J74" s="151">
         <f>SUM(J72:J73)</f>
         <v/>
       </c>
-      <c r="K74" s="143">
+      <c r="K74" s="151">
         <f>SUM(K72:K73)</f>
         <v/>
       </c>
-      <c r="L74" s="143">
+      <c r="L74" s="151">
         <f>SUM(L72:L73)</f>
         <v/>
       </c>
-      <c r="M74" s="143">
+      <c r="M74" s="151">
         <f>SUM(M72:M73)</f>
         <v/>
       </c>
-      <c r="N74" s="143">
+      <c r="N74" s="151">
         <f>SUM(N72:N73)</f>
         <v/>
       </c>
@@ -5170,43 +5294,43 @@
           <t>Net Increase (decrease) in Cash</t>
         </is>
       </c>
-      <c r="E76" s="150">
+      <c r="E76" s="158">
         <f>E41-E77</f>
         <v/>
       </c>
-      <c r="F76" s="150">
+      <c r="F76" s="158">
         <f>F41-F77</f>
         <v/>
       </c>
-      <c r="G76" s="150">
+      <c r="G76" s="158">
         <f>G41-G77</f>
         <v/>
       </c>
-      <c r="H76" s="150">
+      <c r="H76" s="158">
         <f>H41-H77</f>
         <v/>
       </c>
-      <c r="I76" s="150">
+      <c r="I76" s="158">
         <f>I41-I77</f>
         <v/>
       </c>
-      <c r="J76" s="138">
+      <c r="J76" s="142">
         <f>J65-J69+J74</f>
         <v/>
       </c>
-      <c r="K76" s="138">
+      <c r="K76" s="142">
         <f>K65-K69+K74</f>
         <v/>
       </c>
-      <c r="L76" s="138">
+      <c r="L76" s="142">
         <f>L65-L69+L74</f>
         <v/>
       </c>
-      <c r="M76" s="138">
+      <c r="M76" s="142">
         <f>M65-M69+M74</f>
         <v/>
       </c>
-      <c r="N76" s="138">
+      <c r="N76" s="142">
         <f>N65-N69+N74</f>
         <v/>
       </c>
@@ -5217,42 +5341,42 @@
           <t>Opening Cash Balance</t>
         </is>
       </c>
-      <c r="E77" s="139" t="n">
+      <c r="E77" s="148" t="n">
         <v>157394</v>
       </c>
-      <c r="F77" s="150">
+      <c r="F77" s="158">
         <f>E41</f>
         <v/>
       </c>
-      <c r="G77" s="150">
+      <c r="G77" s="158">
         <f>F41</f>
         <v/>
       </c>
-      <c r="H77" s="150">
+      <c r="H77" s="158">
         <f>G41</f>
         <v/>
       </c>
-      <c r="I77" s="150">
+      <c r="I77" s="158">
         <f>H41</f>
         <v/>
       </c>
-      <c r="J77" s="150">
+      <c r="J77" s="158">
         <f>I41</f>
         <v/>
       </c>
-      <c r="K77" s="150">
+      <c r="K77" s="158">
         <f>J78</f>
         <v/>
       </c>
-      <c r="L77" s="150">
+      <c r="L77" s="158">
         <f>K78</f>
         <v/>
       </c>
-      <c r="M77" s="150">
+      <c r="M77" s="158">
         <f>L78</f>
         <v/>
       </c>
-      <c r="N77" s="150">
+      <c r="N77" s="158">
         <f>M78</f>
         <v/>
       </c>
@@ -5264,46 +5388,46 @@
         </is>
       </c>
       <c r="C78" s="5" t="n"/>
-      <c r="D78" s="151" t="n">
+      <c r="D78" s="159" t="n">
         <v>157394</v>
       </c>
-      <c r="E78" s="143">
+      <c r="E78" s="151">
         <f>SUM(E76:E77)</f>
         <v/>
       </c>
-      <c r="F78" s="143">
+      <c r="F78" s="151">
         <f>SUM(F76:F77)</f>
         <v/>
       </c>
-      <c r="G78" s="143">
+      <c r="G78" s="151">
         <f>SUM(G76:G77)</f>
         <v/>
       </c>
-      <c r="H78" s="143">
+      <c r="H78" s="151">
         <f>SUM(H76:H77)</f>
         <v/>
       </c>
-      <c r="I78" s="143">
+      <c r="I78" s="151">
         <f>SUM(I76:I77)</f>
         <v/>
       </c>
-      <c r="J78" s="143">
+      <c r="J78" s="151">
         <f>SUM(J76:J77)</f>
         <v/>
       </c>
-      <c r="K78" s="143">
+      <c r="K78" s="151">
         <f>SUM(K76:K77)</f>
         <v/>
       </c>
-      <c r="L78" s="143">
+      <c r="L78" s="151">
         <f>SUM(L76:L77)</f>
         <v/>
       </c>
-      <c r="M78" s="143">
+      <c r="M78" s="151">
         <f>SUM(M76:M77)</f>
         <v/>
       </c>
-      <c r="N78" s="143">
+      <c r="N78" s="151">
         <f>SUM(N76:N77)</f>
         <v/>
       </c>
@@ -5324,43 +5448,43 @@
       </c>
       <c r="C80" s="9" t="n"/>
       <c r="D80" s="27" t="n"/>
-      <c r="E80" s="149">
+      <c r="E80" s="157">
         <f>E78-E41</f>
         <v/>
       </c>
-      <c r="F80" s="149">
+      <c r="F80" s="157">
         <f>F78-F41</f>
         <v/>
       </c>
-      <c r="G80" s="149">
+      <c r="G80" s="157">
         <f>G78-G41</f>
         <v/>
       </c>
-      <c r="H80" s="149">
+      <c r="H80" s="157">
         <f>H78-H41</f>
         <v/>
       </c>
-      <c r="I80" s="149">
+      <c r="I80" s="157">
         <f>I78-I41</f>
         <v/>
       </c>
-      <c r="J80" s="149">
+      <c r="J80" s="157">
         <f>J78-J41</f>
         <v/>
       </c>
-      <c r="K80" s="149">
+      <c r="K80" s="157">
         <f>K78-K41</f>
         <v/>
       </c>
-      <c r="L80" s="149">
+      <c r="L80" s="157">
         <f>L78-L41</f>
         <v/>
       </c>
-      <c r="M80" s="149">
+      <c r="M80" s="157">
         <f>M78-M41</f>
         <v/>
       </c>
-      <c r="N80" s="149">
+      <c r="N80" s="157">
         <f>N78-N41</f>
         <v/>
       </c>
@@ -5416,38 +5540,38 @@
           <t>Accounts Receivable</t>
         </is>
       </c>
-      <c r="E85" s="139" t="n">
+      <c r="E85" s="148" t="n">
         <v>206690</v>
       </c>
-      <c r="F85" s="139" t="n">
+      <c r="F85" s="148" t="n">
         <v>202365</v>
       </c>
-      <c r="G85" s="139" t="n">
+      <c r="G85" s="148" t="n">
         <v>251217</v>
       </c>
-      <c r="H85" s="139" t="n">
+      <c r="H85" s="148" t="n">
         <v>269745</v>
       </c>
-      <c r="I85" s="139" t="n">
+      <c r="I85" s="148" t="n">
         <v>341776</v>
       </c>
-      <c r="J85" s="142">
+      <c r="J85" s="150">
         <f>J42</f>
         <v/>
       </c>
-      <c r="K85" s="142">
+      <c r="K85" s="150">
         <f>K42</f>
         <v/>
       </c>
-      <c r="L85" s="142">
+      <c r="L85" s="150">
         <f>L42</f>
         <v/>
       </c>
-      <c r="M85" s="142">
+      <c r="M85" s="150">
         <f>M42</f>
         <v/>
       </c>
-      <c r="N85" s="142">
+      <c r="N85" s="150">
         <f>N42</f>
         <v/>
       </c>
@@ -5458,38 +5582,38 @@
           <t>Inventory</t>
         </is>
       </c>
-      <c r="E86" s="139" t="n">
+      <c r="E86" s="148" t="n">
         <v>0</v>
       </c>
-      <c r="F86" s="139" t="n">
+      <c r="F86" s="148" t="n">
         <v>0</v>
       </c>
-      <c r="G86" s="139" t="n">
+      <c r="G86" s="148" t="n">
         <v>0</v>
       </c>
-      <c r="H86" s="139" t="n">
+      <c r="H86" s="148" t="n">
         <v>0</v>
       </c>
-      <c r="I86" s="139" t="n">
+      <c r="I86" s="148" t="n">
         <v>0</v>
       </c>
-      <c r="J86" s="142">
+      <c r="J86" s="150">
         <f>J43</f>
         <v/>
       </c>
-      <c r="K86" s="142">
+      <c r="K86" s="150">
         <f>K43</f>
         <v/>
       </c>
-      <c r="L86" s="142">
+      <c r="L86" s="150">
         <f>L43</f>
         <v/>
       </c>
-      <c r="M86" s="142">
+      <c r="M86" s="150">
         <f>M43</f>
         <v/>
       </c>
-      <c r="N86" s="142">
+      <c r="N86" s="150">
         <f>N43</f>
         <v/>
       </c>
@@ -5500,38 +5624,38 @@
           <t>Accounts Payable</t>
         </is>
       </c>
-      <c r="E87" s="139" t="n">
+      <c r="E87" s="148" t="n">
         <v>20749</v>
       </c>
-      <c r="F87" s="139" t="n">
+      <c r="F87" s="148" t="n">
         <v>17273</v>
       </c>
-      <c r="G87" s="139" t="n">
+      <c r="G87" s="148" t="n">
         <v>19009</v>
       </c>
-      <c r="H87" s="139" t="n">
+      <c r="H87" s="148" t="n">
         <v>22473</v>
       </c>
-      <c r="I87" s="139" t="n">
+      <c r="I87" s="148" t="n">
         <v>32315</v>
       </c>
-      <c r="J87" s="142">
+      <c r="J87" s="150">
         <f>J48</f>
         <v/>
       </c>
-      <c r="K87" s="142">
+      <c r="K87" s="150">
         <f>K48</f>
         <v/>
       </c>
-      <c r="L87" s="142">
+      <c r="L87" s="150">
         <f>L48</f>
         <v/>
       </c>
-      <c r="M87" s="142">
+      <c r="M87" s="150">
         <f>M48</f>
         <v/>
       </c>
-      <c r="N87" s="142">
+      <c r="N87" s="150">
         <f>N48</f>
         <v/>
       </c>
@@ -5543,46 +5667,46 @@
         </is>
       </c>
       <c r="C88" s="5" t="n"/>
-      <c r="D88" s="151" t="n">
+      <c r="D88" s="159" t="n">
         <v>205747</v>
       </c>
-      <c r="E88" s="152">
+      <c r="E88" s="160">
         <f>E85+E86-E87</f>
         <v/>
       </c>
-      <c r="F88" s="152">
+      <c r="F88" s="160">
         <f>F85+F86-F87</f>
         <v/>
       </c>
-      <c r="G88" s="152">
+      <c r="G88" s="160">
         <f>G85+G86-G87</f>
         <v/>
       </c>
-      <c r="H88" s="152">
+      <c r="H88" s="160">
         <f>H85+H86-H87</f>
         <v/>
       </c>
-      <c r="I88" s="152">
+      <c r="I88" s="160">
         <f>I85+I86-I87</f>
         <v/>
       </c>
-      <c r="J88" s="152">
+      <c r="J88" s="160">
         <f>J85+J86-J87</f>
         <v/>
       </c>
-      <c r="K88" s="152">
+      <c r="K88" s="160">
         <f>K85+K86-K87</f>
         <v/>
       </c>
-      <c r="L88" s="152">
+      <c r="L88" s="160">
         <f>L85+L86-L87</f>
         <v/>
       </c>
-      <c r="M88" s="152">
+      <c r="M88" s="160">
         <f>M85+M86-M87</f>
         <v/>
       </c>
-      <c r="N88" s="152">
+      <c r="N88" s="160">
         <f>N85+N86-N87</f>
         <v/>
       </c>
@@ -5593,43 +5717,43 @@
           <t>Change in NWC</t>
         </is>
       </c>
-      <c r="E89" s="138">
+      <c r="E89" s="142">
         <f>E88-D88</f>
         <v/>
       </c>
-      <c r="F89" s="138">
+      <c r="F89" s="142">
         <f>F88-E88</f>
         <v/>
       </c>
-      <c r="G89" s="138">
+      <c r="G89" s="142">
         <f>G88-F88</f>
         <v/>
       </c>
-      <c r="H89" s="138">
+      <c r="H89" s="142">
         <f>H88-G88</f>
         <v/>
       </c>
-      <c r="I89" s="138">
+      <c r="I89" s="142">
         <f>I88-H88</f>
         <v/>
       </c>
-      <c r="J89" s="138">
+      <c r="J89" s="142">
         <f>J88-I88</f>
         <v/>
       </c>
-      <c r="K89" s="138">
+      <c r="K89" s="142">
         <f>K88-J88</f>
         <v/>
       </c>
-      <c r="L89" s="138">
+      <c r="L89" s="142">
         <f>L88-K88</f>
         <v/>
       </c>
-      <c r="M89" s="138">
+      <c r="M89" s="142">
         <f>M88-L88</f>
         <v/>
       </c>
-      <c r="N89" s="138">
+      <c r="N89" s="142">
         <f>N88-M88</f>
         <v/>
       </c>
@@ -5659,42 +5783,42 @@
           <t>PPE Opening</t>
         </is>
       </c>
-      <c r="E92" s="139" t="n">
+      <c r="E92" s="148" t="n">
         <v>46419</v>
       </c>
-      <c r="F92" s="150">
+      <c r="F92" s="158">
         <f>E95</f>
         <v/>
       </c>
-      <c r="G92" s="150">
+      <c r="G92" s="158">
         <f>F95</f>
         <v/>
       </c>
-      <c r="H92" s="150">
+      <c r="H92" s="158">
         <f>G95</f>
         <v/>
       </c>
-      <c r="I92" s="150">
+      <c r="I92" s="158">
         <f>H95</f>
         <v/>
       </c>
-      <c r="J92" s="150">
+      <c r="J92" s="158">
         <f>I44</f>
         <v/>
       </c>
-      <c r="K92" s="150">
+      <c r="K92" s="158">
         <f>J95</f>
         <v/>
       </c>
-      <c r="L92" s="150">
+      <c r="L92" s="158">
         <f>K95</f>
         <v/>
       </c>
-      <c r="M92" s="150">
+      <c r="M92" s="158">
         <f>L95</f>
         <v/>
       </c>
-      <c r="N92" s="150">
+      <c r="N92" s="158">
         <f>M95</f>
         <v/>
       </c>
@@ -5705,38 +5829,38 @@
           <t>Plus Capex</t>
         </is>
       </c>
-      <c r="E93" s="139" t="n">
+      <c r="E93" s="148" t="n">
         <v>7569</v>
       </c>
-      <c r="F93" s="139" t="n">
+      <c r="F93" s="148" t="n">
         <v>6029</v>
       </c>
-      <c r="G93" s="139" t="n">
+      <c r="G93" s="148" t="n">
         <v>4237</v>
       </c>
-      <c r="H93" s="139" t="n">
+      <c r="H93" s="148" t="n">
         <v>25551</v>
       </c>
-      <c r="I93" s="139" t="n">
+      <c r="I93" s="148" t="n">
         <v>39407</v>
       </c>
-      <c r="J93" s="142">
+      <c r="J93" s="150">
         <f>+J18</f>
         <v/>
       </c>
-      <c r="K93" s="142">
+      <c r="K93" s="150">
         <f>+K18</f>
         <v/>
       </c>
-      <c r="L93" s="142">
+      <c r="L93" s="150">
         <f>+L18</f>
         <v/>
       </c>
-      <c r="M93" s="142">
+      <c r="M93" s="150">
         <f>+M18</f>
         <v/>
       </c>
-      <c r="N93" s="142">
+      <c r="N93" s="150">
         <f>+N18</f>
         <v/>
       </c>
@@ -5747,38 +5871,38 @@
           <t>Less Depreciation</t>
         </is>
       </c>
-      <c r="E94" s="139" t="n">
+      <c r="E94" s="148" t="n">
         <v>25592</v>
       </c>
-      <c r="F94" s="139" t="n">
+      <c r="F94" s="148" t="n">
         <v>20465</v>
       </c>
-      <c r="G94" s="139" t="n">
+      <c r="G94" s="148" t="n">
         <v>14638</v>
       </c>
-      <c r="H94" s="139" t="n">
+      <c r="H94" s="148" t="n">
         <v>13827</v>
       </c>
-      <c r="I94" s="139" t="n">
+      <c r="I94" s="148" t="n">
         <v>14952</v>
       </c>
-      <c r="J94" s="142">
+      <c r="J94" s="150">
         <f>J92*J11</f>
         <v/>
       </c>
-      <c r="K94" s="142">
+      <c r="K94" s="150">
         <f>K92*K11</f>
         <v/>
       </c>
-      <c r="L94" s="142">
+      <c r="L94" s="150">
         <f>L92*L11</f>
         <v/>
       </c>
-      <c r="M94" s="142">
+      <c r="M94" s="150">
         <f>M92*M11</f>
         <v/>
       </c>
-      <c r="N94" s="142">
+      <c r="N94" s="150">
         <f>N92*N11</f>
         <v/>
       </c>
@@ -5791,38 +5915,38 @@
       </c>
       <c r="C95" s="5" t="n"/>
       <c r="D95" s="28" t="n"/>
-      <c r="E95" s="153" t="n">
+      <c r="E95" s="161" t="n">
         <v>27913</v>
       </c>
-      <c r="F95" s="153" t="n">
+      <c r="F95" s="161" t="n">
         <v>17580</v>
       </c>
-      <c r="G95" s="153" t="n">
+      <c r="G95" s="161" t="n">
         <v>10966</v>
       </c>
-      <c r="H95" s="153" t="n">
+      <c r="H95" s="161" t="n">
         <v>38465</v>
       </c>
-      <c r="I95" s="153" t="n">
+      <c r="I95" s="161" t="n">
         <v>67713</v>
       </c>
-      <c r="J95" s="152">
+      <c r="J95" s="160">
         <f>J92+J93-J94</f>
         <v/>
       </c>
-      <c r="K95" s="152">
+      <c r="K95" s="160">
         <f>K92+K93-K94</f>
         <v/>
       </c>
-      <c r="L95" s="152">
+      <c r="L95" s="160">
         <f>L92+L93-L94</f>
         <v/>
       </c>
-      <c r="M95" s="152">
+      <c r="M95" s="160">
         <f>M92+M93-M94</f>
         <v/>
       </c>
-      <c r="N95" s="152">
+      <c r="N95" s="160">
         <f>N92+N93-N94</f>
         <v/>
       </c>
@@ -5857,42 +5981,42 @@
           <t>Debt Opening</t>
         </is>
       </c>
-      <c r="E98" s="139" t="n">
+      <c r="E98" s="148" t="n">
         <v>739435</v>
       </c>
-      <c r="F98" s="150">
+      <c r="F98" s="158">
         <f>E100</f>
         <v/>
       </c>
-      <c r="G98" s="150">
+      <c r="G98" s="158">
         <f>F100</f>
         <v/>
       </c>
-      <c r="H98" s="150">
+      <c r="H98" s="158">
         <f>G100</f>
         <v/>
       </c>
-      <c r="I98" s="150">
+      <c r="I98" s="158">
         <f>H100</f>
         <v/>
       </c>
-      <c r="J98" s="150">
+      <c r="J98" s="158">
         <f>I49</f>
         <v/>
       </c>
-      <c r="K98" s="150">
+      <c r="K98" s="158">
         <f>J100</f>
         <v/>
       </c>
-      <c r="L98" s="150">
+      <c r="L98" s="158">
         <f>K100</f>
         <v/>
       </c>
-      <c r="M98" s="150">
+      <c r="M98" s="158">
         <f>L100</f>
         <v/>
       </c>
-      <c r="N98" s="150">
+      <c r="N98" s="158">
         <f>M100</f>
         <v/>
       </c>
@@ -5903,38 +6027,38 @@
           <t>Issuance (repayment)</t>
         </is>
       </c>
-      <c r="E99" s="139" t="n">
+      <c r="E99" s="148" t="n">
         <v>519583</v>
       </c>
-      <c r="F99" s="139" t="n">
+      <c r="F99" s="148" t="n">
         <v>594651</v>
       </c>
-      <c r="G99" s="139" t="n">
+      <c r="G99" s="148" t="n">
         <v>7989</v>
       </c>
-      <c r="H99" s="139" t="n">
+      <c r="H99" s="148" t="n">
         <v>347363</v>
       </c>
-      <c r="I99" s="139" t="n">
+      <c r="I99" s="148" t="n">
         <v>846670</v>
       </c>
-      <c r="J99" s="138">
+      <c r="J99" s="142">
         <f>+J19</f>
         <v/>
       </c>
-      <c r="K99" s="138">
+      <c r="K99" s="142">
         <f>+K19</f>
         <v/>
       </c>
-      <c r="L99" s="138">
+      <c r="L99" s="142">
         <f>+L19</f>
         <v/>
       </c>
-      <c r="M99" s="138">
+      <c r="M99" s="142">
         <f>+M19</f>
         <v/>
       </c>
-      <c r="N99" s="138">
+      <c r="N99" s="142">
         <f>+N19</f>
         <v/>
       </c>
@@ -5947,38 +6071,38 @@
       </c>
       <c r="C100" s="5" t="n"/>
       <c r="D100" s="28" t="n"/>
-      <c r="E100" s="153" t="n">
+      <c r="E100" s="161" t="n">
         <v>1259018</v>
       </c>
-      <c r="F100" s="153" t="n">
+      <c r="F100" s="161" t="n">
         <v>1853669</v>
       </c>
-      <c r="G100" s="153" t="n">
+      <c r="G100" s="161" t="n">
         <v>1861658</v>
       </c>
-      <c r="H100" s="153" t="n">
+      <c r="H100" s="161" t="n">
         <v>2209021</v>
       </c>
-      <c r="I100" s="153" t="n">
+      <c r="I100" s="161" t="n">
         <v>3055691</v>
       </c>
-      <c r="J100" s="152">
+      <c r="J100" s="160">
         <f>SUM(J98:J99)</f>
         <v/>
       </c>
-      <c r="K100" s="152">
+      <c r="K100" s="160">
         <f>SUM(K98:K99)</f>
         <v/>
       </c>
-      <c r="L100" s="152">
+      <c r="L100" s="160">
         <f>SUM(L98:L99)</f>
         <v/>
       </c>
-      <c r="M100" s="152">
+      <c r="M100" s="160">
         <f>SUM(M98:M99)</f>
         <v/>
       </c>
-      <c r="N100" s="152">
+      <c r="N100" s="160">
         <f>SUM(N98:N99)</f>
         <v/>
       </c>
@@ -5989,38 +6113,38 @@
           <t>Interest Expense</t>
         </is>
       </c>
-      <c r="E101" s="139" t="n">
+      <c r="E101" s="148" t="n">
         <v>40092</v>
       </c>
-      <c r="F101" s="139" t="n">
+      <c r="F101" s="148" t="n">
         <v>68967</v>
       </c>
-      <c r="G101" s="139" t="n">
+      <c r="G101" s="148" t="n">
         <v>95546</v>
       </c>
-      <c r="H101" s="139" t="n">
+      <c r="H101" s="148" t="n">
         <v>105638</v>
       </c>
-      <c r="I101" s="139" t="n">
+      <c r="I101" s="148" t="n">
         <v>133647</v>
       </c>
-      <c r="J101" s="142">
+      <c r="J101" s="150">
         <f>J98*J12</f>
         <v/>
       </c>
-      <c r="K101" s="142">
+      <c r="K101" s="150">
         <f>K98*K12</f>
         <v/>
       </c>
-      <c r="L101" s="142">
+      <c r="L101" s="150">
         <f>L98*L12</f>
         <v/>
       </c>
-      <c r="M101" s="142">
+      <c r="M101" s="150">
         <f>M98*M12</f>
         <v/>
       </c>
-      <c r="N101" s="142">
+      <c r="N101" s="150">
         <f>N98*N12</f>
         <v/>
       </c>
@@ -6395,9 +6519,9 @@
       <c r="L2" s="96" t="n"/>
       <c r="M2" s="94" t="n"/>
       <c r="N2" s="94" t="n"/>
-      <c r="Q2" s="154" t="inlineStr">
-        <is>
-          <t>vengeanceaiUSCMODEL3 — LIVE EQUATIONS + SOURCE LINKS</t>
+      <c r="Q2" s="162" t="inlineStr">
+        <is>
+          <t>vengeanceaiUSCMODEL4 — LIVE EQUATIONS + SOURCE LINKS</t>
         </is>
       </c>
     </row>
@@ -6417,7 +6541,7 @@
       <c r="M3" s="97" t="n"/>
       <c r="N3" s="97" t="n"/>
       <c r="O3" s="97" t="n"/>
-      <c r="Q3" s="155" t="inlineStr">
+      <c r="Q3" s="163" t="inlineStr">
         <is>
           <t>Yellow = inputs (edit). Green = formulas. Blue underlined = clickable sources.</t>
         </is>
@@ -6443,32 +6567,32 @@
       <c r="M4" s="97" t="n"/>
       <c r="N4" s="97" t="n"/>
       <c r="O4" s="97" t="n"/>
-      <c r="Q4" s="156" t="inlineStr">
+      <c r="Q4" s="164" t="inlineStr">
         <is>
           <t>Input</t>
         </is>
       </c>
-      <c r="R4" s="156" t="inlineStr">
+      <c r="R4" s="164" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="S4" s="156" t="inlineStr">
+      <c r="S4" s="164" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="T4" s="156" t="inlineStr">
+      <c r="T4" s="164" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="U4" s="156" t="inlineStr">
+      <c r="U4" s="164" t="inlineStr">
         <is>
           <t>Primary source (click)</t>
         </is>
       </c>
-      <c r="V4" s="156" t="inlineStr">
+      <c r="V4" s="164" t="inlineStr">
         <is>
           <t>Secondary source (click)</t>
         </is>
@@ -6482,10 +6606,10 @@
         </is>
       </c>
       <c r="C5" s="100" t="n"/>
-      <c r="D5" s="157" t="n">
+      <c r="D5" s="165" t="n">
         <v>0.1877023903712333</v>
       </c>
-      <c r="E5" s="158" t="inlineStr">
+      <c r="E5" s="166" t="inlineStr">
         <is>
           <t>Tax source: SEC 10-K</t>
         </is>
@@ -6500,14 +6624,14 @@
       <c r="M5" s="97" t="n"/>
       <c r="N5" s="97" t="n"/>
       <c r="O5" s="97" t="n"/>
-      <c r="Q5" s="159" t="inlineStr">
+      <c r="Q5" s="137" t="inlineStr">
         <is>
           <t>1) CAPM → WACC   (D6 = R15)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="160" t="inlineStr">
+      <c r="A6" s="167" t="inlineStr">
         <is>
           <t>WACC sources → columns U–V</t>
         </is>
@@ -6517,26 +6641,26 @@
           <t>Discount Rate (WACC = We×Ke + Wd×Rd(1−t))</t>
         </is>
       </c>
-      <c r="C6" s="161" t="inlineStr">
+      <c r="C6" s="168" t="inlineStr">
         <is>
           <t>Sources →</t>
         </is>
       </c>
-      <c r="D6" s="162">
+      <c r="D6" s="169">
         <f>R15</f>
         <v/>
       </c>
-      <c r="E6" s="158" t="inlineStr">
+      <c r="E6" s="166" t="inlineStr">
         <is>
           <t>WACC sources → scroll to col U (Rf/ERP/β/Rd links)</t>
         </is>
       </c>
-      <c r="F6" s="158" t="inlineStr">
+      <c r="F6" s="166" t="inlineStr">
         <is>
           <t>Damodaran ERP</t>
         </is>
       </c>
-      <c r="G6" s="158" t="inlineStr">
+      <c r="G6" s="166" t="inlineStr">
         <is>
           <t>SEC 8-K Rd 6.250%</t>
         </is>
@@ -6549,30 +6673,30 @@
       <c r="M6" s="97" t="n"/>
       <c r="N6" s="97" t="n"/>
       <c r="O6" s="97" t="n"/>
-      <c r="Q6" s="163" t="inlineStr">
+      <c r="Q6" s="170" t="inlineStr">
         <is>
           <t>Risk-free rate (Rf)</t>
         </is>
       </c>
-      <c r="R6" s="164" t="n">
+      <c r="R6" s="171" t="n">
         <v>0.0463</v>
       </c>
-      <c r="S6" s="163" t="inlineStr">
+      <c r="S6" s="170" t="inlineStr">
         <is>
           <t>US 10Y Treasury yield</t>
         </is>
       </c>
-      <c r="T6" s="163" t="inlineStr">
+      <c r="T6" s="170" t="inlineStr">
         <is>
           <t>CAPM input</t>
         </is>
       </c>
-      <c r="U6" s="165" t="inlineStr">
+      <c r="U6" s="172" t="inlineStr">
         <is>
           <t>FRED DGS10 (US 10Y)</t>
         </is>
       </c>
-      <c r="V6" s="165" t="inlineStr">
+      <c r="V6" s="172" t="inlineStr">
         <is>
           <t>US Treasury Daily Par Yield Curve</t>
         </is>
@@ -6586,7 +6710,7 @@
         </is>
       </c>
       <c r="C7" s="97" t="n"/>
-      <c r="D7" s="157" t="n">
+      <c r="D7" s="165" t="n">
         <v>0.03</v>
       </c>
       <c r="E7" s="97" t="n"/>
@@ -6600,30 +6724,30 @@
       <c r="M7" s="97" t="n"/>
       <c r="N7" s="97" t="n"/>
       <c r="O7" s="97" t="n"/>
-      <c r="Q7" s="163" t="inlineStr">
+      <c r="Q7" s="170" t="inlineStr">
         <is>
           <t>Equity risk premium (ERP)</t>
         </is>
       </c>
-      <c r="R7" s="164" t="n">
+      <c r="R7" s="171" t="n">
         <v>0.0428</v>
       </c>
-      <c r="S7" s="163" t="inlineStr">
+      <c r="S7" s="170" t="inlineStr">
         <is>
           <t>Damodaran implied ERP</t>
         </is>
       </c>
-      <c r="T7" s="163" t="inlineStr">
+      <c r="T7" s="170" t="inlineStr">
         <is>
           <t>CAPM input</t>
         </is>
       </c>
-      <c r="U7" s="165" t="inlineStr">
+      <c r="U7" s="172" t="inlineStr">
         <is>
           <t>Damodaran Online — Implied ERP</t>
         </is>
       </c>
-      <c r="V7" s="165" t="inlineStr">
+      <c r="V7" s="172" t="inlineStr">
         <is>
           <t>Damodaran histimpl.xls / table</t>
         </is>
@@ -6637,10 +6761,10 @@
         </is>
       </c>
       <c r="C8" s="97" t="n"/>
-      <c r="D8" s="166" t="n">
+      <c r="D8" s="173" t="n">
         <v>25</v>
       </c>
-      <c r="E8" s="158" t="inlineStr">
+      <c r="E8" s="166" t="inlineStr">
         <is>
           <t>Rd source: SEC 8-K 6.250% notes</t>
         </is>
@@ -6655,30 +6779,30 @@
       <c r="M8" s="97" t="n"/>
       <c r="N8" s="97" t="n"/>
       <c r="O8" s="97" t="n"/>
-      <c r="Q8" s="163" t="inlineStr">
+      <c r="Q8" s="170" t="inlineStr">
         <is>
           <t>Beta (β)</t>
         </is>
       </c>
-      <c r="R8" s="167" t="n">
+      <c r="R8" s="174" t="n">
         <v>1.32</v>
       </c>
-      <c r="S8" s="163" t="inlineStr">
+      <c r="S8" s="170" t="inlineStr">
         <is>
           <t>Yahoo 5Y monthly beta</t>
         </is>
       </c>
-      <c r="T8" s="163" t="inlineStr">
+      <c r="T8" s="170" t="inlineStr">
         <is>
           <t>CAPM input</t>
         </is>
       </c>
-      <c r="U8" s="165" t="inlineStr">
+      <c r="U8" s="172" t="inlineStr">
         <is>
           <t>Yahoo Finance FICO Key Statistics</t>
         </is>
       </c>
-      <c r="V8" s="165" t="inlineStr">
+      <c r="V8" s="172" t="inlineStr">
         <is>
           <t>Yahoo Finance FICO quote</t>
         </is>
@@ -6692,7 +6816,7 @@
         </is>
       </c>
       <c r="C9" s="97" t="n"/>
-      <c r="D9" s="168" t="n">
+      <c r="D9" s="175" t="n">
         <v>45930</v>
       </c>
       <c r="E9" s="97" t="n"/>
@@ -6706,31 +6830,31 @@
       <c r="M9" s="97" t="n"/>
       <c r="N9" s="97" t="n"/>
       <c r="O9" s="97" t="n"/>
-      <c r="Q9" s="169" t="inlineStr">
+      <c r="Q9" s="176" t="inlineStr">
         <is>
           <t>Ke = Rf + β × ERP</t>
         </is>
       </c>
-      <c r="R9" s="170">
+      <c r="R9" s="177">
         <f>R6+R8*R7</f>
         <v/>
       </c>
-      <c r="S9" s="163" t="inlineStr">
+      <c r="S9" s="170" t="inlineStr">
         <is>
           <t>Cost of equity (CAPM)</t>
         </is>
       </c>
-      <c r="T9" s="169" t="inlineStr">
+      <c r="T9" s="176" t="inlineStr">
         <is>
           <t>→ WACC</t>
         </is>
       </c>
-      <c r="U9" s="163" t="inlineStr">
+      <c r="U9" s="170" t="inlineStr">
         <is>
           <t>Derived: R6 + R8 × R7</t>
         </is>
       </c>
-      <c r="V9" s="163" t="inlineStr"/>
+      <c r="V9" s="170" t="inlineStr"/>
     </row>
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="97" t="n"/>
@@ -6740,7 +6864,7 @@
         </is>
       </c>
       <c r="C10" s="97" t="n"/>
-      <c r="D10" s="168" t="n">
+      <c r="D10" s="175" t="n">
         <v>46295</v>
       </c>
       <c r="E10" s="97" t="n"/>
@@ -6754,30 +6878,30 @@
       <c r="M10" s="97" t="n"/>
       <c r="N10" s="97" t="n"/>
       <c r="O10" s="97" t="n"/>
-      <c r="Q10" s="163" t="inlineStr">
+      <c r="Q10" s="170" t="inlineStr">
         <is>
           <t>Pre-tax cost of debt (Rd)</t>
         </is>
       </c>
-      <c r="R10" s="164" t="n">
+      <c r="R10" s="171" t="n">
         <v>0.0625</v>
       </c>
-      <c r="S10" s="163" t="inlineStr">
+      <c r="S10" s="170" t="inlineStr">
         <is>
           <t>6.250% Senior Notes due 2034</t>
         </is>
       </c>
-      <c r="T10" s="163" t="inlineStr">
+      <c r="T10" s="170" t="inlineStr">
         <is>
           <t>WACC input</t>
         </is>
       </c>
-      <c r="U10" s="165" t="inlineStr">
+      <c r="U10" s="172" t="inlineStr">
         <is>
           <t>SEC 8-K — Notes closing (6.250%)</t>
         </is>
       </c>
-      <c r="V10" s="165" t="inlineStr">
+      <c r="V10" s="172" t="inlineStr">
         <is>
           <t>SEC EX-99.1 — Notes pricing press release</t>
         </is>
@@ -6791,7 +6915,7 @@
         </is>
       </c>
       <c r="C11" s="97" t="n"/>
-      <c r="D11" s="171" t="n">
+      <c r="D11" s="178" t="n">
         <v>1046.23</v>
       </c>
       <c r="E11" s="97" t="n"/>
@@ -6805,31 +6929,31 @@
       <c r="M11" s="97" t="n"/>
       <c r="N11" s="97" t="n"/>
       <c r="O11" s="97" t="n"/>
-      <c r="Q11" s="163" t="inlineStr">
+      <c r="Q11" s="170" t="inlineStr">
         <is>
           <t>Tax rate (t)</t>
         </is>
       </c>
-      <c r="R11" s="170">
+      <c r="R11" s="177">
         <f>$D$5</f>
         <v/>
       </c>
-      <c r="S11" s="163" t="inlineStr">
+      <c r="S11" s="170" t="inlineStr">
         <is>
           <t>FY25 effective = 150,649 / 802,595</t>
         </is>
       </c>
-      <c r="T11" s="163" t="inlineStr">
+      <c r="T11" s="170" t="inlineStr">
         <is>
           <t>Linked D5</t>
         </is>
       </c>
-      <c r="U11" s="165" t="inlineStr">
+      <c r="U11" s="172" t="inlineStr">
         <is>
           <t>SEC 10-K FY2025 (tax / EBT)</t>
         </is>
       </c>
-      <c r="V11" s="165" t="inlineStr">
+      <c r="V11" s="172" t="inlineStr">
         <is>
           <t>SEC companyfacts XBRL (CIK 0000814547)</t>
         </is>
@@ -6843,7 +6967,7 @@
         </is>
       </c>
       <c r="C12" s="97" t="n"/>
-      <c r="D12" s="172" t="n">
+      <c r="D12" s="179" t="n">
         <v>21597.635</v>
       </c>
       <c r="E12" s="97" t="n"/>
@@ -6857,31 +6981,31 @@
       <c r="M12" s="97" t="n"/>
       <c r="N12" s="97" t="n"/>
       <c r="O12" s="97" t="n"/>
-      <c r="Q12" s="169" t="inlineStr">
+      <c r="Q12" s="176" t="inlineStr">
         <is>
           <t>Rd_aftertax = Rd × (1 − t)</t>
         </is>
       </c>
-      <c r="R12" s="170">
+      <c r="R12" s="177">
         <f>R10*(1-R11)</f>
         <v/>
       </c>
-      <c r="S12" s="163" t="inlineStr">
+      <c r="S12" s="170" t="inlineStr">
         <is>
           <t>After-tax cost of debt</t>
         </is>
       </c>
-      <c r="T12" s="169" t="inlineStr">
+      <c r="T12" s="176" t="inlineStr">
         <is>
           <t>→ WACC</t>
         </is>
       </c>
-      <c r="U12" s="163" t="inlineStr">
+      <c r="U12" s="170" t="inlineStr">
         <is>
           <t>Derived: R10 × (1 − R11)</t>
         </is>
       </c>
-      <c r="V12" s="163" t="inlineStr"/>
+      <c r="V12" s="170" t="inlineStr"/>
     </row>
     <row r="13" ht="16" customHeight="1">
       <c r="A13" s="97" t="n"/>
@@ -6891,7 +7015,7 @@
         </is>
       </c>
       <c r="C13" s="97" t="n"/>
-      <c r="D13" s="172" t="n">
+      <c r="D13" s="179" t="n">
         <v>5582389</v>
       </c>
       <c r="E13" s="97" t="n"/>
@@ -6905,30 +7029,30 @@
       <c r="M13" s="97" t="n"/>
       <c r="N13" s="97" t="n"/>
       <c r="O13" s="97" t="n"/>
-      <c r="Q13" s="163" t="inlineStr">
+      <c r="Q13" s="170" t="inlineStr">
         <is>
           <t>Equity weight (We)</t>
         </is>
       </c>
-      <c r="R13" s="173" t="n">
+      <c r="R13" s="180" t="n">
         <v>0.8</v>
       </c>
-      <c r="S13" s="163" t="inlineStr">
+      <c r="S13" s="170" t="inlineStr">
         <is>
           <t>Target ~80% equity at market</t>
         </is>
       </c>
-      <c r="T13" s="163" t="inlineStr">
+      <c r="T13" s="170" t="inlineStr">
         <is>
           <t>WACC weight</t>
         </is>
       </c>
-      <c r="U13" s="165" t="inlineStr">
+      <c r="U13" s="172" t="inlineStr">
         <is>
           <t>SEC 10-Q Q3 FY2026 (debt / capital)</t>
         </is>
       </c>
-      <c r="V13" s="165" t="inlineStr">
+      <c r="V13" s="172" t="inlineStr">
         <is>
           <t>Yahoo market cap for E/(D+E)</t>
         </is>
@@ -6942,7 +7066,7 @@
         </is>
       </c>
       <c r="C14" s="97" t="n"/>
-      <c r="D14" s="172" t="n">
+      <c r="D14" s="179" t="n">
         <v>304537</v>
       </c>
       <c r="E14" s="97" t="n"/>
@@ -6956,30 +7080,30 @@
       <c r="M14" s="97" t="n"/>
       <c r="N14" s="97" t="n"/>
       <c r="O14" s="97" t="n"/>
-      <c r="Q14" s="163" t="inlineStr">
+      <c r="Q14" s="170" t="inlineStr">
         <is>
           <t>Debt weight (Wd)</t>
         </is>
       </c>
-      <c r="R14" s="173" t="n">
+      <c r="R14" s="180" t="n">
         <v>0.2</v>
       </c>
-      <c r="S14" s="163" t="inlineStr">
+      <c r="S14" s="170" t="inlineStr">
         <is>
           <t>Target ~20% debt (We+Wd=100%)</t>
         </is>
       </c>
-      <c r="T14" s="163" t="inlineStr">
+      <c r="T14" s="170" t="inlineStr">
         <is>
           <t>WACC weight</t>
         </is>
       </c>
-      <c r="U14" s="165" t="inlineStr">
+      <c r="U14" s="172" t="inlineStr">
         <is>
           <t>SEC 10-Q — total debt $5,582,389k</t>
         </is>
       </c>
-      <c r="V14" s="165" t="inlineStr">
+      <c r="V14" s="172" t="inlineStr">
         <is>
           <t>SEC 10-K — senior notes footnote</t>
         </is>
@@ -6993,7 +7117,7 @@
         </is>
       </c>
       <c r="C15" s="97" t="n"/>
-      <c r="D15" s="174">
+      <c r="D15" s="181">
         <f>'3 Statement Model'!J68</f>
         <v/>
       </c>
@@ -7008,31 +7132,31 @@
       <c r="M15" s="97" t="n"/>
       <c r="N15" s="97" t="n"/>
       <c r="O15" s="97" t="n"/>
-      <c r="Q15" s="169" t="inlineStr">
+      <c r="Q15" s="176" t="inlineStr">
         <is>
           <t>WACC = We×Ke + Wd×Rd_aftertax</t>
         </is>
       </c>
-      <c r="R15" s="170">
+      <c r="R15" s="177">
         <f>R13*R9+R14*R12</f>
         <v/>
       </c>
-      <c r="S15" s="163" t="inlineStr">
+      <c r="S15" s="170" t="inlineStr">
         <is>
           <t>PRIMARY discount rate → cell D6</t>
         </is>
       </c>
-      <c r="T15" s="169" t="inlineStr">
+      <c r="T15" s="176" t="inlineStr">
         <is>
           <t>→ D6</t>
         </is>
       </c>
-      <c r="U15" s="165" t="inlineStr">
+      <c r="U15" s="172" t="inlineStr">
         <is>
           <t>SEC filings (tax, debt coupons)</t>
         </is>
       </c>
-      <c r="V15" s="165" t="inlineStr">
+      <c r="V15" s="172" t="inlineStr">
         <is>
           <t>Damodaran (ERP methodology)</t>
         </is>
@@ -7063,23 +7187,23 @@
           <t>Entry</t>
         </is>
       </c>
-      <c r="E17" s="175">
+      <c r="E17" s="182">
         <f>YEAR(E18)</f>
         <v/>
       </c>
-      <c r="F17" s="175">
+      <c r="F17" s="182">
         <f>YEAR(F18)</f>
         <v/>
       </c>
-      <c r="G17" s="175">
+      <c r="G17" s="182">
         <f>YEAR(G18)</f>
         <v/>
       </c>
-      <c r="H17" s="175">
+      <c r="H17" s="182">
         <f>YEAR(H18)</f>
         <v/>
       </c>
-      <c r="I17" s="175">
+      <c r="I17" s="182">
         <f>YEAR(I18)</f>
         <v/>
       </c>
@@ -7097,7 +7221,7 @@
       <c r="M17" s="111" t="n"/>
       <c r="N17" s="111" t="n"/>
       <c r="O17" s="97" t="n"/>
-      <c r="Q17" s="159" t="inlineStr">
+      <c r="Q17" s="137" t="inlineStr">
         <is>
           <t>2) Unlevered Free Cash Flow</t>
         </is>
@@ -7111,31 +7235,31 @@
         </is>
       </c>
       <c r="C18" s="97" t="n"/>
-      <c r="D18" s="176">
+      <c r="D18" s="183">
         <f>D9</f>
         <v/>
       </c>
-      <c r="E18" s="177">
+      <c r="E18" s="184">
         <f>DATE(YEAR($D$10)+E19,3,31)</f>
         <v/>
       </c>
-      <c r="F18" s="177">
+      <c r="F18" s="184">
         <f>DATE(YEAR($D$10)+F19,3,31)</f>
         <v/>
       </c>
-      <c r="G18" s="177">
+      <c r="G18" s="184">
         <f>DATE(YEAR($D$10)+G19,3,31)</f>
         <v/>
       </c>
-      <c r="H18" s="177">
+      <c r="H18" s="184">
         <f>DATE(YEAR($D$10)+H19,3,31)</f>
         <v/>
       </c>
-      <c r="I18" s="177">
+      <c r="I18" s="184">
         <f>DATE(YEAR($D$10)+I19,3,31)</f>
         <v/>
       </c>
-      <c r="J18" s="178">
+      <c r="J18" s="185">
         <f>I18</f>
         <v/>
       </c>
@@ -7145,7 +7269,7 @@
           <t>Exit EV/EBITDA (in J27) — primary</t>
         </is>
       </c>
-      <c r="M18" s="174">
+      <c r="M18" s="181">
         <f>J27</f>
         <v/>
       </c>
@@ -7154,17 +7278,17 @@
         <v/>
       </c>
       <c r="O18" s="97" t="n"/>
-      <c r="Q18" s="169" t="inlineStr">
+      <c r="Q18" s="176" t="inlineStr">
         <is>
           <t>FCFF = EBIT − EBIT×t + D&amp;A − CapEx − ΔNWC</t>
         </is>
       </c>
-      <c r="U18" s="165" t="inlineStr">
+      <c r="U18" s="172" t="inlineStr">
         <is>
           <t>Drivers from SEC XBRL → 3-statement</t>
         </is>
       </c>
-      <c r="V18" s="165" t="inlineStr">
+      <c r="V18" s="172" t="inlineStr">
         <is>
           <t>SEC 10-K historical IS/CF</t>
         </is>
@@ -7179,22 +7303,22 @@
       </c>
       <c r="C19" s="118" t="n"/>
       <c r="D19" s="115" t="n"/>
-      <c r="E19" s="179" t="n">
+      <c r="E19" s="186" t="n">
         <v>0</v>
       </c>
-      <c r="F19" s="176">
+      <c r="F19" s="183">
         <f>E19+1</f>
         <v/>
       </c>
-      <c r="G19" s="176">
+      <c r="G19" s="183">
         <f>F19+1</f>
         <v/>
       </c>
-      <c r="H19" s="176">
+      <c r="H19" s="183">
         <f>G19+1</f>
         <v/>
       </c>
-      <c r="I19" s="176">
+      <c r="I19" s="183">
         <f>H19+1</f>
         <v/>
       </c>
@@ -7205,7 +7329,7 @@
           <t>Gordon cross-check</t>
         </is>
       </c>
-      <c r="M19" s="174">
+      <c r="M19" s="181">
         <f>IF(($D$6-$D$7)&lt;=0,"WACC must exceed g",$I$26*(1+$D$7)/($D$6-$D$7))</f>
         <v/>
       </c>
@@ -7214,12 +7338,12 @@
         <v/>
       </c>
       <c r="O19" s="97" t="n"/>
-      <c r="Q19" s="163" t="inlineStr">
+      <c r="Q19" s="170" t="inlineStr">
         <is>
           <t>Excel (col E example)</t>
         </is>
       </c>
-      <c r="R19" s="169">
+      <c r="R19" s="176">
         <f>E21-E22+E23-E24-E25</f>
         <v/>
       </c>
@@ -7233,23 +7357,23 @@
       </c>
       <c r="C20" s="97" t="n"/>
       <c r="D20" s="97" t="n"/>
-      <c r="E20" s="176">
+      <c r="E20" s="183">
         <f>YEARFRAC(D18,E18)</f>
         <v/>
       </c>
-      <c r="F20" s="176">
+      <c r="F20" s="183">
         <f>YEARFRAC(E18,F18)</f>
         <v/>
       </c>
-      <c r="G20" s="176">
+      <c r="G20" s="183">
         <f>YEARFRAC(F18,G18)</f>
         <v/>
       </c>
-      <c r="H20" s="176">
+      <c r="H20" s="183">
         <f>YEARFRAC(G18,H18)</f>
         <v/>
       </c>
-      <c r="I20" s="176">
+      <c r="I20" s="183">
         <f>YEARFRAC(H18,I18)</f>
         <v/>
       </c>
@@ -7260,7 +7384,7 @@
           <t>Implied Gordon exit multiple</t>
         </is>
       </c>
-      <c r="M20" s="174">
+      <c r="M20" s="181">
         <f>IF(($I$21+$I$23)=0,0,M19/($I$21+$I$23))</f>
         <v/>
       </c>
@@ -7269,21 +7393,21 @@
         <v/>
       </c>
       <c r="O20" s="97" t="n"/>
-      <c r="Q20" s="163" t="inlineStr">
+      <c r="Q20" s="170" t="inlineStr">
         <is>
           <t>Tax on EBIT (unlevered)</t>
         </is>
       </c>
-      <c r="R20" s="169">
+      <c r="R20" s="176">
         <f>E21*$D$5</f>
         <v/>
       </c>
-      <c r="S20" s="163" t="inlineStr">
+      <c r="S20" s="170" t="inlineStr">
         <is>
           <t>NOT levered IS tax dollars</t>
         </is>
       </c>
-      <c r="U20" s="165" t="inlineStr">
+      <c r="U20" s="172" t="inlineStr">
         <is>
           <t>Tax rate from SEC 10-K effective rate</t>
         </is>
@@ -7296,29 +7420,29 @@
           <t>EBIT (linked to 3-stmt)</t>
         </is>
       </c>
-      <c r="C21" s="180" t="inlineStr">
+      <c r="C21" s="187" t="inlineStr">
         <is>
           <t>EBIT</t>
         </is>
       </c>
       <c r="D21" s="97" t="n"/>
-      <c r="E21" s="174">
+      <c r="E21" s="181">
         <f>'3 Statement Model'!J26-'3 Statement Model'!J28-'3 Statement Model'!J29-'3 Statement Model'!J30</f>
         <v/>
       </c>
-      <c r="F21" s="174">
+      <c r="F21" s="181">
         <f>'3 Statement Model'!K26-'3 Statement Model'!K28-'3 Statement Model'!K29-'3 Statement Model'!K30</f>
         <v/>
       </c>
-      <c r="G21" s="174">
+      <c r="G21" s="181">
         <f>'3 Statement Model'!L26-'3 Statement Model'!L28-'3 Statement Model'!L29-'3 Statement Model'!L30</f>
         <v/>
       </c>
-      <c r="H21" s="174">
+      <c r="H21" s="181">
         <f>'3 Statement Model'!M26-'3 Statement Model'!M28-'3 Statement Model'!M29-'3 Statement Model'!M30</f>
         <v/>
       </c>
-      <c r="I21" s="174">
+      <c r="I21" s="181">
         <f>'3 Statement Model'!N26-'3 Statement Model'!N28-'3 Statement Model'!N29-'3 Statement Model'!N30</f>
         <v/>
       </c>
@@ -7328,16 +7452,16 @@
       <c r="M21" s="97" t="n"/>
       <c r="N21" s="97" t="n"/>
       <c r="O21" s="97" t="n"/>
-      <c r="Q21" s="163" t="inlineStr">
+      <c r="Q21" s="170" t="inlineStr">
         <is>
           <t>FCFF check (FY5 / col I)</t>
         </is>
       </c>
-      <c r="R21" s="181">
+      <c r="R21" s="188">
         <f>I26</f>
         <v/>
       </c>
-      <c r="S21" s="163" t="inlineStr">
+      <c r="S21" s="170" t="inlineStr">
         <is>
           <t>Must equal I21−I22+I23−I24−I25</t>
         </is>
@@ -7350,29 +7474,29 @@
           <t>Less: Unlevered Cash Taxes (EBIT×t)</t>
         </is>
       </c>
-      <c r="C22" s="180" t="inlineStr">
+      <c r="C22" s="187" t="inlineStr">
         <is>
           <t>EBIT×t</t>
         </is>
       </c>
       <c r="D22" s="97" t="n"/>
-      <c r="E22" s="174">
+      <c r="E22" s="181">
         <f>E21*$D$5</f>
         <v/>
       </c>
-      <c r="F22" s="174">
+      <c r="F22" s="181">
         <f>F21*$D$5</f>
         <v/>
       </c>
-      <c r="G22" s="174">
+      <c r="G22" s="181">
         <f>G21*$D$5</f>
         <v/>
       </c>
-      <c r="H22" s="174">
+      <c r="H22" s="181">
         <f>H21*$D$5</f>
         <v/>
       </c>
-      <c r="I22" s="174">
+      <c r="I22" s="181">
         <f>I21*$D$5</f>
         <v/>
       </c>
@@ -7390,29 +7514,29 @@
           <t>Plus: D&amp;A (linked to 3-stmt)</t>
         </is>
       </c>
-      <c r="C23" s="180" t="inlineStr">
+      <c r="C23" s="187" t="inlineStr">
         <is>
           <t>+D&amp;A</t>
         </is>
       </c>
       <c r="D23" s="97" t="n"/>
-      <c r="E23" s="174">
+      <c r="E23" s="181">
         <f>'3 Statement Model'!J30</f>
         <v/>
       </c>
-      <c r="F23" s="174">
+      <c r="F23" s="181">
         <f>'3 Statement Model'!K30</f>
         <v/>
       </c>
-      <c r="G23" s="174">
+      <c r="G23" s="181">
         <f>'3 Statement Model'!L30</f>
         <v/>
       </c>
-      <c r="H23" s="174">
+      <c r="H23" s="181">
         <f>'3 Statement Model'!M30</f>
         <v/>
       </c>
-      <c r="I23" s="174">
+      <c r="I23" s="181">
         <f>'3 Statement Model'!N30</f>
         <v/>
       </c>
@@ -7422,7 +7546,7 @@
       <c r="M23" s="97" t="n"/>
       <c r="N23" s="97" t="n"/>
       <c r="O23" s="97" t="n"/>
-      <c r="Q23" s="159" t="inlineStr">
+      <c r="Q23" s="137" t="inlineStr">
         <is>
           <t>3) Terminal Value</t>
         </is>
@@ -7435,29 +7559,29 @@
           <t>Less: Capex (linked to 3-stmt CF)</t>
         </is>
       </c>
-      <c r="C24" s="180" t="inlineStr">
+      <c r="C24" s="187" t="inlineStr">
         <is>
           <t>−CapEx</t>
         </is>
       </c>
       <c r="D24" s="97" t="n"/>
-      <c r="E24" s="174">
+      <c r="E24" s="181">
         <f>'3 Statement Model'!J68</f>
         <v/>
       </c>
-      <c r="F24" s="174">
+      <c r="F24" s="181">
         <f>'3 Statement Model'!K68</f>
         <v/>
       </c>
-      <c r="G24" s="174">
+      <c r="G24" s="181">
         <f>'3 Statement Model'!L68</f>
         <v/>
       </c>
-      <c r="H24" s="174">
+      <c r="H24" s="181">
         <f>'3 Statement Model'!M68</f>
         <v/>
       </c>
-      <c r="I24" s="174">
+      <c r="I24" s="181">
         <f>'3 Statement Model'!N68</f>
         <v/>
       </c>
@@ -7467,7 +7591,7 @@
       <c r="M24" s="97" t="n"/>
       <c r="N24" s="97" t="n"/>
       <c r="O24" s="97" t="n"/>
-      <c r="Q24" s="169" t="inlineStr">
+      <c r="Q24" s="176" t="inlineStr">
         <is>
           <t>TV_exit = EBITDA_n × ExitMultiple   [PRIMARY]</t>
         </is>
@@ -7480,29 +7604,29 @@
           <t>Less: ΔNWC (linked to 3-stmt CF)</t>
         </is>
       </c>
-      <c r="C25" s="180" t="inlineStr">
+      <c r="C25" s="187" t="inlineStr">
         <is>
           <t>−ΔNWC</t>
         </is>
       </c>
       <c r="D25" s="97" t="n"/>
-      <c r="E25" s="174">
+      <c r="E25" s="181">
         <f>'3 Statement Model'!J64</f>
         <v/>
       </c>
-      <c r="F25" s="174">
+      <c r="F25" s="181">
         <f>'3 Statement Model'!K64</f>
         <v/>
       </c>
-      <c r="G25" s="174">
+      <c r="G25" s="181">
         <f>'3 Statement Model'!L64</f>
         <v/>
       </c>
-      <c r="H25" s="174">
+      <c r="H25" s="181">
         <f>'3 Statement Model'!M64</f>
         <v/>
       </c>
-      <c r="I25" s="174">
+      <c r="I25" s="181">
         <f>'3 Statement Model'!N64</f>
         <v/>
       </c>
@@ -7512,20 +7636,20 @@
       <c r="M25" s="97" t="n"/>
       <c r="N25" s="97" t="n"/>
       <c r="O25" s="97" t="n"/>
-      <c r="Q25" s="163" t="inlineStr">
+      <c r="Q25" s="170" t="inlineStr">
         <is>
           <t>Excel</t>
         </is>
       </c>
-      <c r="R25" s="169">
+      <c r="R25" s="176">
         <f>($I$21+$I$23)*$D$8</f>
         <v/>
       </c>
-      <c r="T25" s="181">
+      <c r="T25" s="188">
         <f>J27</f>
         <v/>
       </c>
-      <c r="U25" s="165" t="inlineStr">
+      <c r="U25" s="172" t="inlineStr">
         <is>
           <t>Exit multiple policy vs Yahoo / market multiples</t>
         </is>
@@ -7538,29 +7662,29 @@
           <t>Unlevered FCF</t>
         </is>
       </c>
-      <c r="C26" s="180" t="inlineStr">
+      <c r="C26" s="187" t="inlineStr">
         <is>
           <t>FCFF=EBIT−tax+DA−CapEx−ΔNWC</t>
         </is>
       </c>
       <c r="D26" s="97" t="n"/>
-      <c r="E26" s="182">
+      <c r="E26" s="189">
         <f>E21-E22+E23-E24-E25</f>
         <v/>
       </c>
-      <c r="F26" s="182">
+      <c r="F26" s="189">
         <f>F21-F22+F23-F24-F25</f>
         <v/>
       </c>
-      <c r="G26" s="182">
+      <c r="G26" s="189">
         <f>G21-G22+G23-G24-G25</f>
         <v/>
       </c>
-      <c r="H26" s="182">
+      <c r="H26" s="189">
         <f>H21-H22+H23-H24-H25</f>
         <v/>
       </c>
-      <c r="I26" s="182">
+      <c r="I26" s="189">
         <f>I21-I22+I23-I24-I25</f>
         <v/>
       </c>
@@ -7570,7 +7694,7 @@
       <c r="M26" s="97" t="n"/>
       <c r="N26" s="97" t="n"/>
       <c r="O26" s="97" t="n"/>
-      <c r="Q26" s="169" t="inlineStr">
+      <c r="Q26" s="176" t="inlineStr">
         <is>
           <t>TV_gordon = FCFF_n×(1+g)/(WACC−g)   [CHECK]</t>
         </is>
@@ -7584,7 +7708,7 @@
         </is>
       </c>
       <c r="C27" s="97" t="n"/>
-      <c r="D27" s="183">
+      <c r="D27" s="190">
         <f>-I35</f>
         <v/>
       </c>
@@ -7593,7 +7717,7 @@
       <c r="G27" s="97" t="n"/>
       <c r="H27" s="97" t="n"/>
       <c r="I27" s="97" t="n"/>
-      <c r="J27" s="174">
+      <c r="J27" s="181">
         <f>($I$21+$I$23)*$D$8</f>
         <v/>
       </c>
@@ -7602,20 +7726,20 @@
       <c r="M27" s="97" t="n"/>
       <c r="N27" s="97" t="n"/>
       <c r="O27" s="97" t="n"/>
-      <c r="Q27" s="163" t="inlineStr">
+      <c r="Q27" s="170" t="inlineStr">
         <is>
           <t>Excel</t>
         </is>
       </c>
-      <c r="R27" s="169">
+      <c r="R27" s="176">
         <f>IF(($D$6-$D$7)&lt;=0,"err",$I$26*(1+$D$7)/($D$6-$D$7))</f>
         <v/>
       </c>
-      <c r="T27" s="181">
+      <c r="T27" s="188">
         <f>M19</f>
         <v/>
       </c>
-      <c r="U27" s="165" t="inlineStr">
+      <c r="U27" s="172" t="inlineStr">
         <is>
           <t>Gordon g vs Damodaran long-run growth framing</t>
         </is>
@@ -7629,30 +7753,30 @@
         </is>
       </c>
       <c r="C28" s="97" t="n"/>
-      <c r="D28" s="182" t="n">
+      <c r="D28" s="189" t="n">
         <v>0</v>
       </c>
-      <c r="E28" s="184">
+      <c r="E28" s="191">
         <f>E27+E26</f>
         <v/>
       </c>
-      <c r="F28" s="184">
+      <c r="F28" s="191">
         <f>F27+F26</f>
         <v/>
       </c>
-      <c r="G28" s="184">
+      <c r="G28" s="191">
         <f>G27+G26</f>
         <v/>
       </c>
-      <c r="H28" s="184">
+      <c r="H28" s="191">
         <f>H27+H26</f>
         <v/>
       </c>
-      <c r="I28" s="184">
+      <c r="I28" s="191">
         <f>I27+I26</f>
         <v/>
       </c>
-      <c r="J28" s="184">
+      <c r="J28" s="191">
         <f>J27+J26</f>
         <v/>
       </c>
@@ -7661,16 +7785,16 @@
       <c r="M28" s="97" t="n"/>
       <c r="N28" s="97" t="n"/>
       <c r="O28" s="97" t="n"/>
-      <c r="Q28" s="163" t="inlineStr">
+      <c r="Q28" s="170" t="inlineStr">
         <is>
           <t>Implied Gordon exit multiple</t>
         </is>
       </c>
-      <c r="R28" s="185">
+      <c r="R28" s="192">
         <f>IF(($I$21+$I$23)=0,0,T27/($I$21+$I$23))</f>
         <v/>
       </c>
-      <c r="S28" s="163" t="inlineStr">
+      <c r="S28" s="170" t="inlineStr">
         <is>
           <t>Gordon TV / EBITDA_n</t>
         </is>
@@ -7684,31 +7808,31 @@
         </is>
       </c>
       <c r="C29" s="97" t="n"/>
-      <c r="D29" s="183">
+      <c r="D29" s="190">
         <f>D27+D26</f>
         <v/>
       </c>
-      <c r="E29" s="174">
+      <c r="E29" s="181">
         <f>E27+E26</f>
         <v/>
       </c>
-      <c r="F29" s="174">
+      <c r="F29" s="181">
         <f>F27+F26</f>
         <v/>
       </c>
-      <c r="G29" s="174">
+      <c r="G29" s="181">
         <f>G27+G26</f>
         <v/>
       </c>
-      <c r="H29" s="174">
+      <c r="H29" s="181">
         <f>H27+H26</f>
         <v/>
       </c>
-      <c r="I29" s="174">
+      <c r="I29" s="181">
         <f>I27+I26</f>
         <v/>
       </c>
-      <c r="J29" s="174">
+      <c r="J29" s="181">
         <f>J27</f>
         <v/>
       </c>
@@ -7732,7 +7856,7 @@
       <c r="M30" s="97" t="n"/>
       <c r="N30" s="97" t="n"/>
       <c r="O30" s="97" t="n"/>
-      <c r="Q30" s="159" t="inlineStr">
+      <c r="Q30" s="137" t="inlineStr">
         <is>
           <t>4) Enterprise → Equity → $/share</t>
         </is>
@@ -7764,7 +7888,7 @@
       <c r="M31" s="111" t="n"/>
       <c r="N31" s="111" t="n"/>
       <c r="O31" s="97" t="n"/>
-      <c r="Q31" s="169" t="inlineStr">
+      <c r="Q31" s="176" t="inlineStr">
         <is>
           <t>EV = XNPV(WACC, TransactionCF, mid-year dates)</t>
         </is>
@@ -7778,7 +7902,7 @@
         </is>
       </c>
       <c r="C32" s="97" t="n"/>
-      <c r="D32" s="174">
+      <c r="D32" s="181">
         <f>XNPV(D6,D28:J28,D18:J18)</f>
         <v/>
       </c>
@@ -7789,7 +7913,7 @@
         </is>
       </c>
       <c r="H32" s="97" t="n"/>
-      <c r="I32" s="183">
+      <c r="I32" s="190">
         <f>D12*D11</f>
         <v/>
       </c>
@@ -7805,16 +7929,16 @@
         <v/>
       </c>
       <c r="O32" s="97" t="n"/>
-      <c r="Q32" s="163" t="inlineStr">
+      <c r="Q32" s="170" t="inlineStr">
         <is>
           <t>Excel</t>
         </is>
       </c>
-      <c r="R32" s="169">
+      <c r="R32" s="176">
         <f>XNPV(D6,D28:J28,D18:J18)</f>
         <v/>
       </c>
-      <c r="T32" s="181">
+      <c r="T32" s="188">
         <f>D32</f>
         <v/>
       </c>
@@ -7827,7 +7951,7 @@
         </is>
       </c>
       <c r="C33" s="97" t="n"/>
-      <c r="D33" s="183">
+      <c r="D33" s="190">
         <f>+D14</f>
         <v/>
       </c>
@@ -7838,7 +7962,7 @@
         </is>
       </c>
       <c r="H33" s="97" t="n"/>
-      <c r="I33" s="183">
+      <c r="I33" s="190">
         <f>D13</f>
         <v/>
       </c>
@@ -7854,26 +7978,26 @@
         <v/>
       </c>
       <c r="O33" s="97" t="n"/>
-      <c r="Q33" s="169" t="inlineStr">
+      <c r="Q33" s="176" t="inlineStr">
         <is>
           <t>Equity = EV + Cash − Debt</t>
         </is>
       </c>
-      <c r="R33" s="181">
+      <c r="R33" s="188">
         <f>D35</f>
         <v/>
       </c>
-      <c r="S33" s="163" t="inlineStr">
+      <c r="S33" s="170" t="inlineStr">
         <is>
           <t>Net debt from 10-Q bridge</t>
         </is>
       </c>
-      <c r="U33" s="165" t="inlineStr">
+      <c r="U33" s="172" t="inlineStr">
         <is>
           <t>SEC 10-Q — cash, mkt secs, total debt</t>
         </is>
       </c>
-      <c r="V33" s="165" t="inlineStr">
+      <c r="V33" s="172" t="inlineStr">
         <is>
           <t>SEC 10-K — FY debt footnote</t>
         </is>
@@ -7887,7 +8011,7 @@
         </is>
       </c>
       <c r="C34" s="97" t="n"/>
-      <c r="D34" s="183">
+      <c r="D34" s="190">
         <f>+D13</f>
         <v/>
       </c>
@@ -7898,7 +8022,7 @@
         </is>
       </c>
       <c r="H34" s="97" t="n"/>
-      <c r="I34" s="183">
+      <c r="I34" s="190">
         <f>+D14</f>
         <v/>
       </c>
@@ -7907,26 +8031,26 @@
       <c r="M34" s="97" t="n"/>
       <c r="N34" s="97" t="n"/>
       <c r="O34" s="97" t="n"/>
-      <c r="Q34" s="169" t="inlineStr">
+      <c r="Q34" s="176" t="inlineStr">
         <is>
           <t>$/share = Equity / Shares</t>
         </is>
       </c>
-      <c r="R34" s="186">
+      <c r="R34" s="193">
         <f>D37</f>
         <v/>
       </c>
-      <c r="S34" s="163" t="inlineStr">
+      <c r="S34" s="170" t="inlineStr">
         <is>
           <t>Shares outstanding (Yahoo)</t>
         </is>
       </c>
-      <c r="U34" s="165" t="inlineStr">
+      <c r="U34" s="172" t="inlineStr">
         <is>
           <t>Yahoo Finance — shares outstanding</t>
         </is>
       </c>
-      <c r="V34" s="165" t="inlineStr">
+      <c r="V34" s="172" t="inlineStr">
         <is>
           <t>Yahoo FICO quote (price)</t>
         </is>
@@ -7940,7 +8064,7 @@
         </is>
       </c>
       <c r="C35" s="97" t="n"/>
-      <c r="D35" s="182">
+      <c r="D35" s="189">
         <f>D32+D33-D34</f>
         <v/>
       </c>
@@ -7951,7 +8075,7 @@
         </is>
       </c>
       <c r="H35" s="97" t="n"/>
-      <c r="I35" s="182">
+      <c r="I35" s="189">
         <f>I32+I33-I34</f>
         <v/>
       </c>
@@ -7964,16 +8088,16 @@
       <c r="M35" s="111" t="n"/>
       <c r="N35" s="111" t="n"/>
       <c r="O35" s="97" t="n"/>
-      <c r="Q35" s="163" t="inlineStr">
+      <c r="Q35" s="170" t="inlineStr">
         <is>
           <t>Upside vs market</t>
         </is>
       </c>
-      <c r="R35" s="187">
+      <c r="R35" s="194">
         <f>D37/D11-1</f>
         <v/>
       </c>
-      <c r="S35" s="163" t="inlineStr">
+      <c r="S35" s="170" t="inlineStr">
         <is>
           <t>Intrinsic / Current Price − 1</t>
         </is>
@@ -7987,7 +8111,7 @@
       <c r="E36" s="97" t="n"/>
       <c r="G36" s="97" t="n"/>
       <c r="H36" s="97" t="n"/>
-      <c r="I36" s="188" t="n"/>
+      <c r="I36" s="195" t="n"/>
       <c r="J36" s="97" t="n"/>
       <c r="L36" s="97" t="inlineStr">
         <is>
@@ -7995,7 +8119,7 @@
         </is>
       </c>
       <c r="M36" s="97" t="n"/>
-      <c r="N36" s="188">
+      <c r="N36" s="195">
         <f>I37</f>
         <v/>
       </c>
@@ -8009,7 +8133,7 @@
         </is>
       </c>
       <c r="C37" s="97" t="n"/>
-      <c r="D37" s="183">
+      <c r="D37" s="190">
         <f>D35/D12</f>
         <v/>
       </c>
@@ -8020,7 +8144,7 @@
         </is>
       </c>
       <c r="H37" s="97" t="n"/>
-      <c r="I37" s="183">
+      <c r="I37" s="190">
         <f>D11</f>
         <v/>
       </c>
@@ -8031,12 +8155,12 @@
         </is>
       </c>
       <c r="M37" s="97" t="n"/>
-      <c r="N37" s="188">
+      <c r="N37" s="195">
         <f>D37-I37</f>
         <v/>
       </c>
       <c r="O37" s="97" t="n"/>
-      <c r="Q37" s="159" t="inlineStr">
+      <c r="Q37" s="137" t="inlineStr">
         <is>
           <t>5) Operating NWC (feeds ΔNWC → FCFF)</t>
         </is>
@@ -8058,22 +8182,22 @@
         </is>
       </c>
       <c r="M38" s="97" t="n"/>
-      <c r="N38" s="188">
+      <c r="N38" s="195">
         <f>SUM(N36:N37)</f>
         <v/>
       </c>
       <c r="O38" s="97" t="n"/>
-      <c r="Q38" s="169" t="inlineStr">
+      <c r="Q38" s="176" t="inlineStr">
         <is>
           <t>NWC = AR + Inventory − AP − DeferredRevenue</t>
         </is>
       </c>
-      <c r="U38" s="165" t="inlineStr">
+      <c r="U38" s="172" t="inlineStr">
         <is>
           <t>SEC 10-K — AR / AP / deferred revenue</t>
         </is>
       </c>
-      <c r="V38" s="165" t="inlineStr">
+      <c r="V38" s="172" t="inlineStr">
         <is>
           <t>XBRL DeferredRevenueCurrent</t>
         </is>
@@ -8092,17 +8216,17 @@
       <c r="M39" s="97" t="n"/>
       <c r="N39" s="97" t="n"/>
       <c r="O39" s="97" t="n"/>
-      <c r="Q39" s="169" t="inlineStr">
+      <c r="Q39" s="176" t="inlineStr">
         <is>
           <t>ΔNWC_t = NWC_t − NWC_(t−1)</t>
         </is>
       </c>
-      <c r="S39" s="163" t="inlineStr">
+      <c r="S39" s="170" t="inlineStr">
         <is>
           <t>Linked from 3-statement CF row 64</t>
         </is>
       </c>
-      <c r="T39" s="181">
+      <c r="T39" s="188">
         <f>I25</f>
         <v/>
       </c>
@@ -8142,7 +8266,7 @@
       <c r="M41" s="111" t="n"/>
       <c r="N41" s="111" t="n"/>
       <c r="O41" s="97" t="n"/>
-      <c r="Q41" s="159" t="inlineStr">
+      <c r="Q41" s="137" t="inlineStr">
         <is>
           <t>6) Full source index (all clickable)</t>
         </is>
@@ -8167,14 +8291,14 @@
         </is>
       </c>
       <c r="O42" s="97" t="n"/>
-      <c r="Q42" s="165" t="inlineStr">
+      <c r="Q42" s="172" t="inlineStr">
         <is>
           <t>SEC 10-K FY2025</t>
         </is>
       </c>
-      <c r="R42" s="189" t="n"/>
-      <c r="S42" s="190" t="n"/>
-      <c r="T42" s="163" t="inlineStr">
+      <c r="R42" s="196" t="n"/>
+      <c r="S42" s="197" t="n"/>
+      <c r="T42" s="170" t="inlineStr">
         <is>
           <t>Tax 18.8%, IS/BS/CF, senior notes</t>
         </is>
@@ -8195,14 +8319,14 @@
       <c r="H43" s="97" t="n"/>
       <c r="N43" s="69" t="n"/>
       <c r="O43" s="97" t="n"/>
-      <c r="Q43" s="165" t="inlineStr">
+      <c r="Q43" s="172" t="inlineStr">
         <is>
           <t>SEC 10-Q Q3 FY2026</t>
         </is>
       </c>
-      <c r="R43" s="189" t="n"/>
-      <c r="S43" s="190" t="n"/>
-      <c r="T43" s="163" t="inlineStr">
+      <c r="R43" s="196" t="n"/>
+      <c r="S43" s="197" t="n"/>
+      <c r="T43" s="170" t="inlineStr">
         <is>
           <t>Debt $5,582M, cash+mkt secs net-debt bridge</t>
         </is>
@@ -8223,14 +8347,14 @@
       <c r="H44" s="97" t="n"/>
       <c r="N44" s="69" t="n"/>
       <c r="O44" s="97" t="n"/>
-      <c r="Q44" s="165" t="inlineStr">
+      <c r="Q44" s="172" t="inlineStr">
         <is>
           <t>SEC 8-K 6.250% notes</t>
         </is>
       </c>
-      <c r="R44" s="189" t="n"/>
-      <c r="S44" s="190" t="n"/>
-      <c r="T44" s="163" t="inlineStr">
+      <c r="R44" s="196" t="n"/>
+      <c r="S44" s="197" t="n"/>
+      <c r="T44" s="170" t="inlineStr">
         <is>
           <t>Pre-tax Rd coupon 6.250% due 2034</t>
         </is>
@@ -8251,14 +8375,14 @@
       <c r="H45" s="97" t="n"/>
       <c r="N45" s="69" t="n"/>
       <c r="O45" s="97" t="n"/>
-      <c r="Q45" s="165" t="inlineStr">
+      <c r="Q45" s="172" t="inlineStr">
         <is>
           <t>SEC EX-99.1 pricing</t>
         </is>
       </c>
-      <c r="R45" s="189" t="n"/>
-      <c r="S45" s="190" t="n"/>
-      <c r="T45" s="163" t="inlineStr">
+      <c r="R45" s="196" t="n"/>
+      <c r="S45" s="197" t="n"/>
+      <c r="T45" s="170" t="inlineStr">
         <is>
           <t>Notes priced at par / offering terms</t>
         </is>
@@ -8279,14 +8403,14 @@
       <c r="H46" s="97" t="n"/>
       <c r="N46" s="69" t="n"/>
       <c r="O46" s="97" t="n"/>
-      <c r="Q46" s="165" t="inlineStr">
+      <c r="Q46" s="172" t="inlineStr">
         <is>
           <t>SEC companyfacts XBRL</t>
         </is>
       </c>
-      <c r="R46" s="189" t="n"/>
-      <c r="S46" s="190" t="n"/>
-      <c r="T46" s="163" t="inlineStr">
+      <c r="R46" s="196" t="n"/>
+      <c r="S46" s="197" t="n"/>
+      <c r="T46" s="170" t="inlineStr">
         <is>
           <t>Pipeline data source (CIK 0000814547)</t>
         </is>
@@ -8303,14 +8427,14 @@
       <c r="H47" s="97" t="n"/>
       <c r="N47" s="69" t="n"/>
       <c r="O47" s="97" t="n"/>
-      <c r="Q47" s="165" t="inlineStr">
+      <c r="Q47" s="172" t="inlineStr">
         <is>
           <t>FRED DGS10</t>
         </is>
       </c>
-      <c r="R47" s="189" t="n"/>
-      <c r="S47" s="190" t="n"/>
-      <c r="T47" s="163" t="inlineStr">
+      <c r="R47" s="196" t="n"/>
+      <c r="S47" s="197" t="n"/>
+      <c r="T47" s="170" t="inlineStr">
         <is>
           <t>Risk-free rate (US 10Y)</t>
         </is>
@@ -8331,14 +8455,14 @@
         </is>
       </c>
       <c r="O48" s="97" t="n"/>
-      <c r="Q48" s="165" t="inlineStr">
+      <c r="Q48" s="172" t="inlineStr">
         <is>
           <t>US Treasury yield curve</t>
         </is>
       </c>
-      <c r="R48" s="189" t="n"/>
-      <c r="S48" s="190" t="n"/>
-      <c r="T48" s="163" t="inlineStr">
+      <c r="R48" s="196" t="n"/>
+      <c r="S48" s="197" t="n"/>
+      <c r="T48" s="170" t="inlineStr">
         <is>
           <t>Official daily par yields</t>
         </is>
@@ -8359,14 +8483,14 @@
         </is>
       </c>
       <c r="O49" s="97" t="n"/>
-      <c r="Q49" s="165" t="inlineStr">
+      <c r="Q49" s="172" t="inlineStr">
         <is>
           <t>Damodaran Implied ERP</t>
         </is>
       </c>
-      <c r="R49" s="189" t="n"/>
-      <c r="S49" s="190" t="n"/>
-      <c r="T49" s="163" t="inlineStr">
+      <c r="R49" s="196" t="n"/>
+      <c r="S49" s="197" t="n"/>
+      <c r="T49" s="170" t="inlineStr">
         <is>
           <t>Equity risk premium</t>
         </is>
@@ -8382,14 +8506,14 @@
       <c r="G50" s="97" t="n"/>
       <c r="H50" s="97" t="n"/>
       <c r="O50" s="97" t="n"/>
-      <c r="Q50" s="165" t="inlineStr">
+      <c r="Q50" s="172" t="inlineStr">
         <is>
           <t>Damodaran histimpl</t>
         </is>
       </c>
-      <c r="R50" s="189" t="n"/>
-      <c r="S50" s="190" t="n"/>
-      <c r="T50" s="163" t="inlineStr">
+      <c r="R50" s="196" t="n"/>
+      <c r="S50" s="197" t="n"/>
+      <c r="T50" s="170" t="inlineStr">
         <is>
           <t>Historical implied ERP table</t>
         </is>
@@ -8406,14 +8530,14 @@
       <c r="H51" s="97" t="n"/>
       <c r="M51" s="97" t="n"/>
       <c r="O51" s="97" t="n"/>
-      <c r="Q51" s="165" t="inlineStr">
+      <c r="Q51" s="172" t="inlineStr">
         <is>
           <t>Yahoo FICO stats</t>
         </is>
       </c>
-      <c r="R51" s="189" t="n"/>
-      <c r="S51" s="190" t="n"/>
-      <c r="T51" s="163" t="inlineStr">
+      <c r="R51" s="196" t="n"/>
+      <c r="S51" s="197" t="n"/>
+      <c r="T51" s="170" t="inlineStr">
         <is>
           <t>Beta 5Y monthly + shares out</t>
         </is>

--- a/FICO/output/FICO_Completed_Model.xlsx
+++ b/FICO/output/FICO_Completed_Model.xlsx
@@ -100,7 +100,7 @@
     <numFmt numFmtId="178" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="179" formatCode="0.0"/>
   </numFmts>
-  <fonts count="50">
+  <fonts count="51">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -377,6 +377,12 @@
     </font>
     <font>
       <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="12"/>
@@ -590,7 +596,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="198">
+  <cellXfs count="199">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="1"/>
@@ -811,7 +817,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="41" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="164" fontId="43" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="166" fontId="40" fillId="8" borderId="5" pivotButton="0" quotePrefix="0" xfId="2"/>
     <xf numFmtId="164" fontId="42" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="166" fontId="38" fillId="7" borderId="5" pivotButton="0" quotePrefix="0" xfId="2"/>
@@ -828,6 +834,7 @@
     <xf numFmtId="177" fontId="40" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="177" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="177" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="164" fontId="42" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="177" fontId="6" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="177" fontId="6" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="177" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
@@ -837,17 +844,17 @@
     </xf>
     <xf numFmtId="177" fontId="9" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="177" fontId="40" fillId="8" borderId="2" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="43" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="44" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="39" fillId="9" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="40" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="45" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="46" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="49" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="48" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="47" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="38" fillId="7" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
@@ -855,7 +862,7 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="40" fillId="8" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="179" fontId="40" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -863,7 +870,7 @@
     </xf>
     <xf numFmtId="2" fontId="40" fillId="8" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="178" fontId="32" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="38" fillId="7" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -880,7 +887,7 @@
     <xf numFmtId="178" fontId="38" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="177" fontId="36" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="177" fontId="37" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="49" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="50" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="174" fontId="38" fillId="7" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="177" fontId="30" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="177" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -2639,7 +2646,7 @@
   <cols>
     <col width="1.88671875" customWidth="1" style="19" min="1" max="1"/>
     <col width="42" customWidth="1" style="19" min="2" max="3"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" style="47" min="4" max="4"/>
     <col width="16" customWidth="1" style="19" min="5" max="9"/>
     <col width="16" customWidth="1" min="6" max="6"/>
@@ -2820,7 +2827,7 @@
       </c>
       <c r="C7" s="138" t="inlineStr">
         <is>
-          <t>POLICY input (Y1≈FY26 guidance; fade→g)</t>
+          <t>POLICY → drives Rev row24 → GP → EBT → Net Earnings / CF</t>
         </is>
       </c>
       <c r="D7" s="46" t="n"/>
@@ -2941,23 +2948,23 @@
         <v/>
       </c>
       <c r="J9" s="143">
-        <f>J24*MAX(0.05,(($I$28-10922.0)/$I$24)-0.005)</f>
+        <f>J28</f>
         <v/>
       </c>
       <c r="K9" s="143">
-        <f>K24*MAX(0.05,(($I$28-10922.0)/$I$24)-0.01)</f>
+        <f>K28</f>
         <v/>
       </c>
       <c r="L9" s="143">
-        <f>L24*MAX(0.05,(($I$28-10922.0)/$I$24)-0.015)</f>
+        <f>L28</f>
         <v/>
       </c>
       <c r="M9" s="143">
-        <f>M24*MAX(0.05,(($I$28-10922.0)/$I$24)-0.02)</f>
+        <f>M28</f>
         <v/>
       </c>
       <c r="N9" s="143">
-        <f>N24*MAX(0.05,(($I$28-10922.0)/$I$24)-0.025)</f>
+        <f>N28</f>
         <v/>
       </c>
     </row>
@@ -2993,23 +3000,23 @@
         <v/>
       </c>
       <c r="J10" s="143">
-        <f>J24*($I$29/$I$24)</f>
+        <f>J29</f>
         <v/>
       </c>
       <c r="K10" s="143">
-        <f>K24*($I$29/$I$24)</f>
+        <f>K29</f>
         <v/>
       </c>
       <c r="L10" s="143">
-        <f>L24*($I$29/$I$24)</f>
+        <f>L29</f>
         <v/>
       </c>
       <c r="M10" s="143">
-        <f>M24*($I$29/$I$24)</f>
+        <f>M29</f>
         <v/>
       </c>
       <c r="N10" s="143">
-        <f>N24*($I$29/$I$24)</f>
+        <f>N29</f>
         <v/>
       </c>
     </row>
@@ -3020,7 +3027,7 @@
         </is>
       </c>
       <c r="C11" s="140">
-        <f>I30/I92 (FY25 DA / PPE open)</f>
+        <f>I30/I44 (FY25 DA / PPE); J92 opens at I44</f>
         <v/>
       </c>
       <c r="D11" s="47" t="n"/>
@@ -3045,23 +3052,23 @@
         <v/>
       </c>
       <c r="J11" s="141">
-        <f>IF($I$92=0,0.25,$I$30/$I$92)</f>
+        <f>IF($I$44=0,0.25,$I$30/$I$44)</f>
         <v/>
       </c>
       <c r="K11" s="141">
-        <f>IF($I$92=0,0.25,$I$30/$I$92)</f>
+        <f>IF($I$44=0,0.25,$I$30/$I$44)</f>
         <v/>
       </c>
       <c r="L11" s="141">
-        <f>IF($I$92=0,0.25,$I$30/$I$92)</f>
+        <f>IF($I$44=0,0.25,$I$30/$I$44)</f>
         <v/>
       </c>
       <c r="M11" s="141">
-        <f>IF($I$92=0,0.25,$I$30/$I$92)</f>
+        <f>IF($I$44=0,0.25,$I$30/$I$44)</f>
         <v/>
       </c>
       <c r="N11" s="141">
-        <f>IF($I$92=0,0.25,$I$30/$I$92)</f>
+        <f>IF($I$44=0,0.25,$I$30/$I$44)</f>
         <v/>
       </c>
     </row>
@@ -3685,10 +3692,9 @@
           <t>Salaries and Benefits</t>
         </is>
       </c>
-      <c r="C28" s="144" t="inlineStr">
-        <is>
-          <t>← J9 = Rev×SGA% equation</t>
-        </is>
+      <c r="C28" s="144">
+        <f>Rev×((I28−10922)/I24−50bps×t)</f>
+        <v/>
       </c>
       <c r="E28" s="148" t="n">
         <v>396281</v>
@@ -3705,24 +3711,24 @@
       <c r="I28" s="148" t="n">
         <v>513028</v>
       </c>
-      <c r="J28" s="150">
-        <f>J9</f>
-        <v/>
-      </c>
-      <c r="K28" s="150">
-        <f>K9</f>
-        <v/>
-      </c>
-      <c r="L28" s="150">
-        <f>L9</f>
-        <v/>
-      </c>
-      <c r="M28" s="150">
-        <f>M9</f>
-        <v/>
-      </c>
-      <c r="N28" s="150">
-        <f>N9</f>
+      <c r="J28" s="143">
+        <f>J24*MAX(0.05,(($I$28-10922.0)/$I$24)-0.005)</f>
+        <v/>
+      </c>
+      <c r="K28" s="143">
+        <f>K24*MAX(0.05,(($I$28-10922.0)/$I$24)-0.01)</f>
+        <v/>
+      </c>
+      <c r="L28" s="143">
+        <f>L24*MAX(0.05,(($I$28-10922.0)/$I$24)-0.015)</f>
+        <v/>
+      </c>
+      <c r="M28" s="143">
+        <f>M24*MAX(0.05,(($I$28-10922.0)/$I$24)-0.02)</f>
+        <v/>
+      </c>
+      <c r="N28" s="143">
+        <f>N24*MAX(0.05,(($I$28-10922.0)/$I$24)-0.025)</f>
         <v/>
       </c>
     </row>
@@ -3732,10 +3738,9 @@
           <t>Rent and Overhead</t>
         </is>
       </c>
-      <c r="C29" s="144" t="inlineStr">
-        <is>
-          <t>← J10 = Rev×R&amp;D% equation</t>
-        </is>
+      <c r="C29" s="144">
+        <f>Rev×(I29/I24)  ← grows with revenue</f>
+        <v/>
       </c>
       <c r="E29" s="148" t="n">
         <v>171231</v>
@@ -3752,24 +3757,24 @@
       <c r="I29" s="148" t="n">
         <v>188347</v>
       </c>
-      <c r="J29" s="150">
-        <f>J10</f>
-        <v/>
-      </c>
-      <c r="K29" s="150">
-        <f>K10</f>
-        <v/>
-      </c>
-      <c r="L29" s="150">
-        <f>L10</f>
-        <v/>
-      </c>
-      <c r="M29" s="150">
-        <f>M10</f>
-        <v/>
-      </c>
-      <c r="N29" s="150">
-        <f>N10</f>
+      <c r="J29" s="143">
+        <f>J24*($I$29/$I$24)</f>
+        <v/>
+      </c>
+      <c r="K29" s="143">
+        <f>K24*($I$29/$I$24)</f>
+        <v/>
+      </c>
+      <c r="L29" s="143">
+        <f>L24*($I$29/$I$24)</f>
+        <v/>
+      </c>
+      <c r="M29" s="143">
+        <f>M24*($I$29/$I$24)</f>
+        <v/>
+      </c>
+      <c r="N29" s="143">
+        <f>N24*($I$29/$I$24)</f>
         <v/>
       </c>
     </row>
@@ -4022,45 +4027,48 @@
           <t>Net Earnings</t>
         </is>
       </c>
-      <c r="C36" s="39" t="n"/>
+      <c r="C36" s="155">
+        <f>EBT−Tax  ← GROWS via Rev×(1+g) in row 24</f>
+        <v/>
+      </c>
       <c r="D36" s="40" t="n"/>
-      <c r="E36" s="155">
+      <c r="E36" s="156">
         <f>E33-E35</f>
         <v/>
       </c>
-      <c r="F36" s="155">
+      <c r="F36" s="156">
         <f>F33-F35</f>
         <v/>
       </c>
-      <c r="G36" s="155">
+      <c r="G36" s="156">
         <f>G33-G35</f>
         <v/>
       </c>
-      <c r="H36" s="155">
+      <c r="H36" s="156">
         <f>H33-H35</f>
         <v/>
       </c>
-      <c r="I36" s="155">
+      <c r="I36" s="156">
         <f>I33-I35</f>
         <v/>
       </c>
-      <c r="J36" s="155">
+      <c r="J36" s="156">
         <f>J33-J35</f>
         <v/>
       </c>
-      <c r="K36" s="155">
+      <c r="K36" s="156">
         <f>K33-K35</f>
         <v/>
       </c>
-      <c r="L36" s="155">
+      <c r="L36" s="156">
         <f>L33-L35</f>
         <v/>
       </c>
-      <c r="M36" s="155">
+      <c r="M36" s="156">
         <f>M33-M35</f>
         <v/>
       </c>
-      <c r="N36" s="155">
+      <c r="N36" s="156">
         <f>N33-N35</f>
         <v/>
       </c>
@@ -4291,43 +4299,43 @@
       </c>
       <c r="C45" s="39" t="n"/>
       <c r="D45" s="40" t="n"/>
-      <c r="E45" s="155">
+      <c r="E45" s="156">
         <f>SUM(E41:E44)</f>
         <v/>
       </c>
-      <c r="F45" s="155">
+      <c r="F45" s="156">
         <f>SUM(F41:F44)</f>
         <v/>
       </c>
-      <c r="G45" s="155">
+      <c r="G45" s="156">
         <f>SUM(G41:G44)</f>
         <v/>
       </c>
-      <c r="H45" s="155">
+      <c r="H45" s="156">
         <f>SUM(H41:H44)</f>
         <v/>
       </c>
-      <c r="I45" s="155">
+      <c r="I45" s="156">
         <f>SUM(I41:I44)</f>
         <v/>
       </c>
-      <c r="J45" s="155">
+      <c r="J45" s="156">
         <f>SUM(J41:J44)</f>
         <v/>
       </c>
-      <c r="K45" s="155">
+      <c r="K45" s="156">
         <f>SUM(K41:K44)</f>
         <v/>
       </c>
-      <c r="L45" s="155">
+      <c r="L45" s="156">
         <f>SUM(L41:L44)</f>
         <v/>
       </c>
-      <c r="M45" s="155">
+      <c r="M45" s="156">
         <f>SUM(M41:M44)</f>
         <v/>
       </c>
-      <c r="N45" s="155">
+      <c r="N45" s="156">
         <f>SUM(N41:N44)</f>
         <v/>
       </c>
@@ -4596,43 +4604,43 @@
       </c>
       <c r="C54" s="8" t="n"/>
       <c r="D54" s="26" t="n"/>
-      <c r="E54" s="156">
+      <c r="E54" s="157">
         <f>SUM(E52:E53)</f>
         <v/>
       </c>
-      <c r="F54" s="156">
+      <c r="F54" s="157">
         <f>SUM(F52:F53)</f>
         <v/>
       </c>
-      <c r="G54" s="156">
+      <c r="G54" s="157">
         <f>SUM(G52:G53)</f>
         <v/>
       </c>
-      <c r="H54" s="156">
+      <c r="H54" s="157">
         <f>SUM(H52:H53)</f>
         <v/>
       </c>
-      <c r="I54" s="156">
+      <c r="I54" s="157">
         <f>SUM(I52:I53)</f>
         <v/>
       </c>
-      <c r="J54" s="156">
+      <c r="J54" s="157">
         <f>SUM(J52:J53)</f>
         <v/>
       </c>
-      <c r="K54" s="156">
+      <c r="K54" s="157">
         <f>SUM(K52:K53)</f>
         <v/>
       </c>
-      <c r="L54" s="156">
+      <c r="L54" s="157">
         <f>SUM(L52:L53)</f>
         <v/>
       </c>
-      <c r="M54" s="156">
+      <c r="M54" s="157">
         <f>SUM(M52:M53)</f>
         <v/>
       </c>
-      <c r="N54" s="156">
+      <c r="N54" s="157">
         <f>SUM(N52:N53)</f>
         <v/>
       </c>
@@ -4645,43 +4653,43 @@
       </c>
       <c r="C55" s="39" t="n"/>
       <c r="D55" s="40" t="n"/>
-      <c r="E55" s="155">
+      <c r="E55" s="156">
         <f>E50+E54</f>
         <v/>
       </c>
-      <c r="F55" s="155">
+      <c r="F55" s="156">
         <f>F50+F54</f>
         <v/>
       </c>
-      <c r="G55" s="155">
+      <c r="G55" s="156">
         <f>G50+G54</f>
         <v/>
       </c>
-      <c r="H55" s="155">
+      <c r="H55" s="156">
         <f>H50+H54</f>
         <v/>
       </c>
-      <c r="I55" s="155">
+      <c r="I55" s="156">
         <f>I50+I54</f>
         <v/>
       </c>
-      <c r="J55" s="155">
+      <c r="J55" s="156">
         <f>J50+J54</f>
         <v/>
       </c>
-      <c r="K55" s="155">
+      <c r="K55" s="156">
         <f>K50+K54</f>
         <v/>
       </c>
-      <c r="L55" s="155">
+      <c r="L55" s="156">
         <f>L50+L54</f>
         <v/>
       </c>
-      <c r="M55" s="155">
+      <c r="M55" s="156">
         <f>M50+M54</f>
         <v/>
       </c>
-      <c r="N55" s="155">
+      <c r="N55" s="156">
         <f>N50+N54</f>
         <v/>
       </c>
@@ -4706,43 +4714,43 @@
       </c>
       <c r="C57" s="9" t="n"/>
       <c r="D57" s="27" t="n"/>
-      <c r="E57" s="157">
+      <c r="E57" s="158">
         <f>E55-E45</f>
         <v/>
       </c>
-      <c r="F57" s="157">
+      <c r="F57" s="158">
         <f>F55-F45</f>
         <v/>
       </c>
-      <c r="G57" s="157">
+      <c r="G57" s="158">
         <f>G55-G45</f>
         <v/>
       </c>
-      <c r="H57" s="157">
+      <c r="H57" s="158">
         <f>H55-H45</f>
         <v/>
       </c>
-      <c r="I57" s="157">
+      <c r="I57" s="158">
         <f>I55-I45</f>
         <v/>
       </c>
-      <c r="J57" s="157">
+      <c r="J57" s="158">
         <f>J55-J45</f>
         <v/>
       </c>
-      <c r="K57" s="157">
+      <c r="K57" s="158">
         <f>K55-K45</f>
         <v/>
       </c>
-      <c r="L57" s="157">
+      <c r="L57" s="158">
         <f>L55-L45</f>
         <v/>
       </c>
-      <c r="M57" s="157">
+      <c r="M57" s="158">
         <f>M55-M45</f>
         <v/>
       </c>
-      <c r="N57" s="157">
+      <c r="N57" s="158">
         <f>N55-N45</f>
         <v/>
       </c>
@@ -4806,6 +4814,10 @@
           <t>Net Earnings</t>
         </is>
       </c>
+      <c r="C62" s="144">
+        <f>IS Net Earnings (row 36) — not hardcoded</f>
+        <v/>
+      </c>
       <c r="E62" s="150">
         <f>E36</f>
         <v/>
@@ -4826,23 +4838,23 @@
         <f>I36</f>
         <v/>
       </c>
-      <c r="J62" s="150">
+      <c r="J62" s="143">
         <f>J36</f>
         <v/>
       </c>
-      <c r="K62" s="150">
+      <c r="K62" s="143">
         <f>K36</f>
         <v/>
       </c>
-      <c r="L62" s="150">
+      <c r="L62" s="143">
         <f>L36</f>
         <v/>
       </c>
-      <c r="M62" s="150">
+      <c r="M62" s="143">
         <f>M36</f>
         <v/>
       </c>
-      <c r="N62" s="150">
+      <c r="N62" s="143">
         <f>N36</f>
         <v/>
       </c>
@@ -4873,24 +4885,24 @@
         <f>+I30</f>
         <v/>
       </c>
-      <c r="J63" s="150">
-        <f>+J30</f>
-        <v/>
-      </c>
-      <c r="K63" s="150">
-        <f>+K30</f>
-        <v/>
-      </c>
-      <c r="L63" s="150">
-        <f>+L30</f>
-        <v/>
-      </c>
-      <c r="M63" s="150">
-        <f>+M30</f>
-        <v/>
-      </c>
-      <c r="N63" s="150">
-        <f>+N30</f>
+      <c r="J63" s="143">
+        <f>J30</f>
+        <v/>
+      </c>
+      <c r="K63" s="143">
+        <f>K30</f>
+        <v/>
+      </c>
+      <c r="L63" s="143">
+        <f>L30</f>
+        <v/>
+      </c>
+      <c r="M63" s="143">
+        <f>M30</f>
+        <v/>
+      </c>
+      <c r="N63" s="143">
+        <f>N30</f>
         <v/>
       </c>
     </row>
@@ -4964,23 +4976,23 @@
         <f>I62+I63-I64</f>
         <v/>
       </c>
-      <c r="J65" s="151">
+      <c r="J65" s="143">
         <f>J62+J63-J64</f>
         <v/>
       </c>
-      <c r="K65" s="151">
+      <c r="K65" s="143">
         <f>K62+K63-K64</f>
         <v/>
       </c>
-      <c r="L65" s="151">
+      <c r="L65" s="143">
         <f>L62+L63-L64</f>
         <v/>
       </c>
-      <c r="M65" s="151">
+      <c r="M65" s="143">
         <f>M62+M63-M64</f>
         <v/>
       </c>
-      <c r="N65" s="151">
+      <c r="N65" s="143">
         <f>N62+N63-N64</f>
         <v/>
       </c>
@@ -5294,23 +5306,23 @@
           <t>Net Increase (decrease) in Cash</t>
         </is>
       </c>
-      <c r="E76" s="158">
+      <c r="E76" s="159">
         <f>E41-E77</f>
         <v/>
       </c>
-      <c r="F76" s="158">
+      <c r="F76" s="159">
         <f>F41-F77</f>
         <v/>
       </c>
-      <c r="G76" s="158">
+      <c r="G76" s="159">
         <f>G41-G77</f>
         <v/>
       </c>
-      <c r="H76" s="158">
+      <c r="H76" s="159">
         <f>H41-H77</f>
         <v/>
       </c>
-      <c r="I76" s="158">
+      <c r="I76" s="159">
         <f>I41-I77</f>
         <v/>
       </c>
@@ -5344,39 +5356,39 @@
       <c r="E77" s="148" t="n">
         <v>157394</v>
       </c>
-      <c r="F77" s="158">
+      <c r="F77" s="159">
         <f>E41</f>
         <v/>
       </c>
-      <c r="G77" s="158">
+      <c r="G77" s="159">
         <f>F41</f>
         <v/>
       </c>
-      <c r="H77" s="158">
+      <c r="H77" s="159">
         <f>G41</f>
         <v/>
       </c>
-      <c r="I77" s="158">
+      <c r="I77" s="159">
         <f>H41</f>
         <v/>
       </c>
-      <c r="J77" s="158">
+      <c r="J77" s="159">
         <f>I41</f>
         <v/>
       </c>
-      <c r="K77" s="158">
+      <c r="K77" s="159">
         <f>J78</f>
         <v/>
       </c>
-      <c r="L77" s="158">
+      <c r="L77" s="159">
         <f>K78</f>
         <v/>
       </c>
-      <c r="M77" s="158">
+      <c r="M77" s="159">
         <f>L78</f>
         <v/>
       </c>
-      <c r="N77" s="158">
+      <c r="N77" s="159">
         <f>M78</f>
         <v/>
       </c>
@@ -5388,7 +5400,7 @@
         </is>
       </c>
       <c r="C78" s="5" t="n"/>
-      <c r="D78" s="159" t="n">
+      <c r="D78" s="160" t="n">
         <v>157394</v>
       </c>
       <c r="E78" s="151">
@@ -5448,43 +5460,43 @@
       </c>
       <c r="C80" s="9" t="n"/>
       <c r="D80" s="27" t="n"/>
-      <c r="E80" s="157">
+      <c r="E80" s="158">
         <f>E78-E41</f>
         <v/>
       </c>
-      <c r="F80" s="157">
+      <c r="F80" s="158">
         <f>F78-F41</f>
         <v/>
       </c>
-      <c r="G80" s="157">
+      <c r="G80" s="158">
         <f>G78-G41</f>
         <v/>
       </c>
-      <c r="H80" s="157">
+      <c r="H80" s="158">
         <f>H78-H41</f>
         <v/>
       </c>
-      <c r="I80" s="157">
+      <c r="I80" s="158">
         <f>I78-I41</f>
         <v/>
       </c>
-      <c r="J80" s="157">
+      <c r="J80" s="158">
         <f>J78-J41</f>
         <v/>
       </c>
-      <c r="K80" s="157">
+      <c r="K80" s="158">
         <f>K78-K41</f>
         <v/>
       </c>
-      <c r="L80" s="157">
+      <c r="L80" s="158">
         <f>L78-L41</f>
         <v/>
       </c>
-      <c r="M80" s="157">
+      <c r="M80" s="158">
         <f>M78-M41</f>
         <v/>
       </c>
-      <c r="N80" s="157">
+      <c r="N80" s="158">
         <f>N78-N41</f>
         <v/>
       </c>
@@ -5667,46 +5679,46 @@
         </is>
       </c>
       <c r="C88" s="5" t="n"/>
-      <c r="D88" s="159" t="n">
+      <c r="D88" s="160" t="n">
         <v>205747</v>
       </c>
-      <c r="E88" s="160">
+      <c r="E88" s="161">
         <f>E85+E86-E87</f>
         <v/>
       </c>
-      <c r="F88" s="160">
+      <c r="F88" s="161">
         <f>F85+F86-F87</f>
         <v/>
       </c>
-      <c r="G88" s="160">
+      <c r="G88" s="161">
         <f>G85+G86-G87</f>
         <v/>
       </c>
-      <c r="H88" s="160">
+      <c r="H88" s="161">
         <f>H85+H86-H87</f>
         <v/>
       </c>
-      <c r="I88" s="160">
+      <c r="I88" s="161">
         <f>I85+I86-I87</f>
         <v/>
       </c>
-      <c r="J88" s="160">
+      <c r="J88" s="161">
         <f>J85+J86-J87</f>
         <v/>
       </c>
-      <c r="K88" s="160">
+      <c r="K88" s="161">
         <f>K85+K86-K87</f>
         <v/>
       </c>
-      <c r="L88" s="160">
+      <c r="L88" s="161">
         <f>L85+L86-L87</f>
         <v/>
       </c>
-      <c r="M88" s="160">
+      <c r="M88" s="161">
         <f>M85+M86-M87</f>
         <v/>
       </c>
-      <c r="N88" s="160">
+      <c r="N88" s="161">
         <f>N85+N86-N87</f>
         <v/>
       </c>
@@ -5786,39 +5798,39 @@
       <c r="E92" s="148" t="n">
         <v>46419</v>
       </c>
-      <c r="F92" s="158">
+      <c r="F92" s="159">
         <f>E95</f>
         <v/>
       </c>
-      <c r="G92" s="158">
+      <c r="G92" s="159">
         <f>F95</f>
         <v/>
       </c>
-      <c r="H92" s="158">
+      <c r="H92" s="159">
         <f>G95</f>
         <v/>
       </c>
-      <c r="I92" s="158">
+      <c r="I92" s="159">
         <f>H95</f>
         <v/>
       </c>
-      <c r="J92" s="158">
+      <c r="J92" s="159">
         <f>I44</f>
         <v/>
       </c>
-      <c r="K92" s="158">
+      <c r="K92" s="159">
         <f>J95</f>
         <v/>
       </c>
-      <c r="L92" s="158">
+      <c r="L92" s="159">
         <f>K95</f>
         <v/>
       </c>
-      <c r="M92" s="158">
+      <c r="M92" s="159">
         <f>L95</f>
         <v/>
       </c>
-      <c r="N92" s="158">
+      <c r="N92" s="159">
         <f>M95</f>
         <v/>
       </c>
@@ -5915,38 +5927,38 @@
       </c>
       <c r="C95" s="5" t="n"/>
       <c r="D95" s="28" t="n"/>
-      <c r="E95" s="161" t="n">
+      <c r="E95" s="162" t="n">
         <v>27913</v>
       </c>
-      <c r="F95" s="161" t="n">
+      <c r="F95" s="162" t="n">
         <v>17580</v>
       </c>
-      <c r="G95" s="161" t="n">
+      <c r="G95" s="162" t="n">
         <v>10966</v>
       </c>
-      <c r="H95" s="161" t="n">
+      <c r="H95" s="162" t="n">
         <v>38465</v>
       </c>
-      <c r="I95" s="161" t="n">
+      <c r="I95" s="162" t="n">
         <v>67713</v>
       </c>
-      <c r="J95" s="160">
+      <c r="J95" s="161">
         <f>J92+J93-J94</f>
         <v/>
       </c>
-      <c r="K95" s="160">
+      <c r="K95" s="161">
         <f>K92+K93-K94</f>
         <v/>
       </c>
-      <c r="L95" s="160">
+      <c r="L95" s="161">
         <f>L92+L93-L94</f>
         <v/>
       </c>
-      <c r="M95" s="160">
+      <c r="M95" s="161">
         <f>M92+M93-M94</f>
         <v/>
       </c>
-      <c r="N95" s="160">
+      <c r="N95" s="161">
         <f>N92+N93-N94</f>
         <v/>
       </c>
@@ -5984,39 +5996,39 @@
       <c r="E98" s="148" t="n">
         <v>739435</v>
       </c>
-      <c r="F98" s="158">
+      <c r="F98" s="159">
         <f>E100</f>
         <v/>
       </c>
-      <c r="G98" s="158">
+      <c r="G98" s="159">
         <f>F100</f>
         <v/>
       </c>
-      <c r="H98" s="158">
+      <c r="H98" s="159">
         <f>G100</f>
         <v/>
       </c>
-      <c r="I98" s="158">
+      <c r="I98" s="159">
         <f>H100</f>
         <v/>
       </c>
-      <c r="J98" s="158">
+      <c r="J98" s="159">
         <f>I49</f>
         <v/>
       </c>
-      <c r="K98" s="158">
+      <c r="K98" s="159">
         <f>J100</f>
         <v/>
       </c>
-      <c r="L98" s="158">
+      <c r="L98" s="159">
         <f>K100</f>
         <v/>
       </c>
-      <c r="M98" s="158">
+      <c r="M98" s="159">
         <f>L100</f>
         <v/>
       </c>
-      <c r="N98" s="158">
+      <c r="N98" s="159">
         <f>M100</f>
         <v/>
       </c>
@@ -6071,38 +6083,38 @@
       </c>
       <c r="C100" s="5" t="n"/>
       <c r="D100" s="28" t="n"/>
-      <c r="E100" s="161" t="n">
+      <c r="E100" s="162" t="n">
         <v>1259018</v>
       </c>
-      <c r="F100" s="161" t="n">
+      <c r="F100" s="162" t="n">
         <v>1853669</v>
       </c>
-      <c r="G100" s="161" t="n">
+      <c r="G100" s="162" t="n">
         <v>1861658</v>
       </c>
-      <c r="H100" s="161" t="n">
+      <c r="H100" s="162" t="n">
         <v>2209021</v>
       </c>
-      <c r="I100" s="161" t="n">
+      <c r="I100" s="162" t="n">
         <v>3055691</v>
       </c>
-      <c r="J100" s="160">
+      <c r="J100" s="161">
         <f>SUM(J98:J99)</f>
         <v/>
       </c>
-      <c r="K100" s="160">
+      <c r="K100" s="161">
         <f>SUM(K98:K99)</f>
         <v/>
       </c>
-      <c r="L100" s="160">
+      <c r="L100" s="161">
         <f>SUM(L98:L99)</f>
         <v/>
       </c>
-      <c r="M100" s="160">
+      <c r="M100" s="161">
         <f>SUM(M98:M99)</f>
         <v/>
       </c>
-      <c r="N100" s="160">
+      <c r="N100" s="161">
         <f>SUM(N98:N99)</f>
         <v/>
       </c>
@@ -6519,7 +6531,7 @@
       <c r="L2" s="96" t="n"/>
       <c r="M2" s="94" t="n"/>
       <c r="N2" s="94" t="n"/>
-      <c r="Q2" s="162" t="inlineStr">
+      <c r="Q2" s="163" t="inlineStr">
         <is>
           <t>vengeanceaiUSCMODEL4 — LIVE EQUATIONS + SOURCE LINKS</t>
         </is>
@@ -6541,7 +6553,7 @@
       <c r="M3" s="97" t="n"/>
       <c r="N3" s="97" t="n"/>
       <c r="O3" s="97" t="n"/>
-      <c r="Q3" s="163" t="inlineStr">
+      <c r="Q3" s="164" t="inlineStr">
         <is>
           <t>Yellow = inputs (edit). Green = formulas. Blue underlined = clickable sources.</t>
         </is>
@@ -6567,32 +6579,32 @@
       <c r="M4" s="97" t="n"/>
       <c r="N4" s="97" t="n"/>
       <c r="O4" s="97" t="n"/>
-      <c r="Q4" s="164" t="inlineStr">
+      <c r="Q4" s="165" t="inlineStr">
         <is>
           <t>Input</t>
         </is>
       </c>
-      <c r="R4" s="164" t="inlineStr">
+      <c r="R4" s="165" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="S4" s="164" t="inlineStr">
+      <c r="S4" s="165" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="T4" s="164" t="inlineStr">
+      <c r="T4" s="165" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="U4" s="164" t="inlineStr">
+      <c r="U4" s="165" t="inlineStr">
         <is>
           <t>Primary source (click)</t>
         </is>
       </c>
-      <c r="V4" s="164" t="inlineStr">
+      <c r="V4" s="165" t="inlineStr">
         <is>
           <t>Secondary source (click)</t>
         </is>
@@ -6606,10 +6618,10 @@
         </is>
       </c>
       <c r="C5" s="100" t="n"/>
-      <c r="D5" s="165" t="n">
+      <c r="D5" s="166" t="n">
         <v>0.1877023903712333</v>
       </c>
-      <c r="E5" s="166" t="inlineStr">
+      <c r="E5" s="167" t="inlineStr">
         <is>
           <t>Tax source: SEC 10-K</t>
         </is>
@@ -6631,7 +6643,7 @@
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="167" t="inlineStr">
+      <c r="A6" s="168" t="inlineStr">
         <is>
           <t>WACC sources → columns U–V</t>
         </is>
@@ -6641,26 +6653,26 @@
           <t>Discount Rate (WACC = We×Ke + Wd×Rd(1−t))</t>
         </is>
       </c>
-      <c r="C6" s="168" t="inlineStr">
+      <c r="C6" s="169" t="inlineStr">
         <is>
           <t>Sources →</t>
         </is>
       </c>
-      <c r="D6" s="169">
+      <c r="D6" s="170">
         <f>R15</f>
         <v/>
       </c>
-      <c r="E6" s="166" t="inlineStr">
+      <c r="E6" s="167" t="inlineStr">
         <is>
           <t>WACC sources → scroll to col U (Rf/ERP/β/Rd links)</t>
         </is>
       </c>
-      <c r="F6" s="166" t="inlineStr">
+      <c r="F6" s="167" t="inlineStr">
         <is>
           <t>Damodaran ERP</t>
         </is>
       </c>
-      <c r="G6" s="166" t="inlineStr">
+      <c r="G6" s="167" t="inlineStr">
         <is>
           <t>SEC 8-K Rd 6.250%</t>
         </is>
@@ -6673,30 +6685,30 @@
       <c r="M6" s="97" t="n"/>
       <c r="N6" s="97" t="n"/>
       <c r="O6" s="97" t="n"/>
-      <c r="Q6" s="170" t="inlineStr">
+      <c r="Q6" s="171" t="inlineStr">
         <is>
           <t>Risk-free rate (Rf)</t>
         </is>
       </c>
-      <c r="R6" s="171" t="n">
+      <c r="R6" s="172" t="n">
         <v>0.0463</v>
       </c>
-      <c r="S6" s="170" t="inlineStr">
+      <c r="S6" s="171" t="inlineStr">
         <is>
           <t>US 10Y Treasury yield</t>
         </is>
       </c>
-      <c r="T6" s="170" t="inlineStr">
+      <c r="T6" s="171" t="inlineStr">
         <is>
           <t>CAPM input</t>
         </is>
       </c>
-      <c r="U6" s="172" t="inlineStr">
+      <c r="U6" s="173" t="inlineStr">
         <is>
           <t>FRED DGS10 (US 10Y)</t>
         </is>
       </c>
-      <c r="V6" s="172" t="inlineStr">
+      <c r="V6" s="173" t="inlineStr">
         <is>
           <t>US Treasury Daily Par Yield Curve</t>
         </is>
@@ -6710,7 +6722,7 @@
         </is>
       </c>
       <c r="C7" s="97" t="n"/>
-      <c r="D7" s="165" t="n">
+      <c r="D7" s="166" t="n">
         <v>0.03</v>
       </c>
       <c r="E7" s="97" t="n"/>
@@ -6724,30 +6736,30 @@
       <c r="M7" s="97" t="n"/>
       <c r="N7" s="97" t="n"/>
       <c r="O7" s="97" t="n"/>
-      <c r="Q7" s="170" t="inlineStr">
+      <c r="Q7" s="171" t="inlineStr">
         <is>
           <t>Equity risk premium (ERP)</t>
         </is>
       </c>
-      <c r="R7" s="171" t="n">
+      <c r="R7" s="172" t="n">
         <v>0.0428</v>
       </c>
-      <c r="S7" s="170" t="inlineStr">
+      <c r="S7" s="171" t="inlineStr">
         <is>
           <t>Damodaran implied ERP</t>
         </is>
       </c>
-      <c r="T7" s="170" t="inlineStr">
+      <c r="T7" s="171" t="inlineStr">
         <is>
           <t>CAPM input</t>
         </is>
       </c>
-      <c r="U7" s="172" t="inlineStr">
+      <c r="U7" s="173" t="inlineStr">
         <is>
           <t>Damodaran Online — Implied ERP</t>
         </is>
       </c>
-      <c r="V7" s="172" t="inlineStr">
+      <c r="V7" s="173" t="inlineStr">
         <is>
           <t>Damodaran histimpl.xls / table</t>
         </is>
@@ -6761,10 +6773,10 @@
         </is>
       </c>
       <c r="C8" s="97" t="n"/>
-      <c r="D8" s="173" t="n">
+      <c r="D8" s="174" t="n">
         <v>25</v>
       </c>
-      <c r="E8" s="166" t="inlineStr">
+      <c r="E8" s="167" t="inlineStr">
         <is>
           <t>Rd source: SEC 8-K 6.250% notes</t>
         </is>
@@ -6779,30 +6791,30 @@
       <c r="M8" s="97" t="n"/>
       <c r="N8" s="97" t="n"/>
       <c r="O8" s="97" t="n"/>
-      <c r="Q8" s="170" t="inlineStr">
+      <c r="Q8" s="171" t="inlineStr">
         <is>
           <t>Beta (β)</t>
         </is>
       </c>
-      <c r="R8" s="174" t="n">
+      <c r="R8" s="175" t="n">
         <v>1.32</v>
       </c>
-      <c r="S8" s="170" t="inlineStr">
+      <c r="S8" s="171" t="inlineStr">
         <is>
           <t>Yahoo 5Y monthly beta</t>
         </is>
       </c>
-      <c r="T8" s="170" t="inlineStr">
+      <c r="T8" s="171" t="inlineStr">
         <is>
           <t>CAPM input</t>
         </is>
       </c>
-      <c r="U8" s="172" t="inlineStr">
+      <c r="U8" s="173" t="inlineStr">
         <is>
           <t>Yahoo Finance FICO Key Statistics</t>
         </is>
       </c>
-      <c r="V8" s="172" t="inlineStr">
+      <c r="V8" s="173" t="inlineStr">
         <is>
           <t>Yahoo Finance FICO quote</t>
         </is>
@@ -6816,7 +6828,7 @@
         </is>
       </c>
       <c r="C9" s="97" t="n"/>
-      <c r="D9" s="175" t="n">
+      <c r="D9" s="176" t="n">
         <v>45930</v>
       </c>
       <c r="E9" s="97" t="n"/>
@@ -6830,31 +6842,31 @@
       <c r="M9" s="97" t="n"/>
       <c r="N9" s="97" t="n"/>
       <c r="O9" s="97" t="n"/>
-      <c r="Q9" s="176" t="inlineStr">
+      <c r="Q9" s="177" t="inlineStr">
         <is>
           <t>Ke = Rf + β × ERP</t>
         </is>
       </c>
-      <c r="R9" s="177">
+      <c r="R9" s="178">
         <f>R6+R8*R7</f>
         <v/>
       </c>
-      <c r="S9" s="170" t="inlineStr">
+      <c r="S9" s="171" t="inlineStr">
         <is>
           <t>Cost of equity (CAPM)</t>
         </is>
       </c>
-      <c r="T9" s="176" t="inlineStr">
+      <c r="T9" s="177" t="inlineStr">
         <is>
           <t>→ WACC</t>
         </is>
       </c>
-      <c r="U9" s="170" t="inlineStr">
+      <c r="U9" s="171" t="inlineStr">
         <is>
           <t>Derived: R6 + R8 × R7</t>
         </is>
       </c>
-      <c r="V9" s="170" t="inlineStr"/>
+      <c r="V9" s="171" t="inlineStr"/>
     </row>
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="97" t="n"/>
@@ -6864,7 +6876,7 @@
         </is>
       </c>
       <c r="C10" s="97" t="n"/>
-      <c r="D10" s="175" t="n">
+      <c r="D10" s="176" t="n">
         <v>46295</v>
       </c>
       <c r="E10" s="97" t="n"/>
@@ -6878,30 +6890,30 @@
       <c r="M10" s="97" t="n"/>
       <c r="N10" s="97" t="n"/>
       <c r="O10" s="97" t="n"/>
-      <c r="Q10" s="170" t="inlineStr">
+      <c r="Q10" s="171" t="inlineStr">
         <is>
           <t>Pre-tax cost of debt (Rd)</t>
         </is>
       </c>
-      <c r="R10" s="171" t="n">
+      <c r="R10" s="172" t="n">
         <v>0.0625</v>
       </c>
-      <c r="S10" s="170" t="inlineStr">
+      <c r="S10" s="171" t="inlineStr">
         <is>
           <t>6.250% Senior Notes due 2034</t>
         </is>
       </c>
-      <c r="T10" s="170" t="inlineStr">
+      <c r="T10" s="171" t="inlineStr">
         <is>
           <t>WACC input</t>
         </is>
       </c>
-      <c r="U10" s="172" t="inlineStr">
+      <c r="U10" s="173" t="inlineStr">
         <is>
           <t>SEC 8-K — Notes closing (6.250%)</t>
         </is>
       </c>
-      <c r="V10" s="172" t="inlineStr">
+      <c r="V10" s="173" t="inlineStr">
         <is>
           <t>SEC EX-99.1 — Notes pricing press release</t>
         </is>
@@ -6915,7 +6927,7 @@
         </is>
       </c>
       <c r="C11" s="97" t="n"/>
-      <c r="D11" s="178" t="n">
+      <c r="D11" s="179" t="n">
         <v>1046.23</v>
       </c>
       <c r="E11" s="97" t="n"/>
@@ -6929,31 +6941,31 @@
       <c r="M11" s="97" t="n"/>
       <c r="N11" s="97" t="n"/>
       <c r="O11" s="97" t="n"/>
-      <c r="Q11" s="170" t="inlineStr">
+      <c r="Q11" s="171" t="inlineStr">
         <is>
           <t>Tax rate (t)</t>
         </is>
       </c>
-      <c r="R11" s="177">
+      <c r="R11" s="178">
         <f>$D$5</f>
         <v/>
       </c>
-      <c r="S11" s="170" t="inlineStr">
+      <c r="S11" s="171" t="inlineStr">
         <is>
           <t>FY25 effective = 150,649 / 802,595</t>
         </is>
       </c>
-      <c r="T11" s="170" t="inlineStr">
+      <c r="T11" s="171" t="inlineStr">
         <is>
           <t>Linked D5</t>
         </is>
       </c>
-      <c r="U11" s="172" t="inlineStr">
+      <c r="U11" s="173" t="inlineStr">
         <is>
           <t>SEC 10-K FY2025 (tax / EBT)</t>
         </is>
       </c>
-      <c r="V11" s="172" t="inlineStr">
+      <c r="V11" s="173" t="inlineStr">
         <is>
           <t>SEC companyfacts XBRL (CIK 0000814547)</t>
         </is>
@@ -6967,7 +6979,7 @@
         </is>
       </c>
       <c r="C12" s="97" t="n"/>
-      <c r="D12" s="179" t="n">
+      <c r="D12" s="180" t="n">
         <v>21597.635</v>
       </c>
       <c r="E12" s="97" t="n"/>
@@ -6981,31 +6993,31 @@
       <c r="M12" s="97" t="n"/>
       <c r="N12" s="97" t="n"/>
       <c r="O12" s="97" t="n"/>
-      <c r="Q12" s="176" t="inlineStr">
+      <c r="Q12" s="177" t="inlineStr">
         <is>
           <t>Rd_aftertax = Rd × (1 − t)</t>
         </is>
       </c>
-      <c r="R12" s="177">
+      <c r="R12" s="178">
         <f>R10*(1-R11)</f>
         <v/>
       </c>
-      <c r="S12" s="170" t="inlineStr">
+      <c r="S12" s="171" t="inlineStr">
         <is>
           <t>After-tax cost of debt</t>
         </is>
       </c>
-      <c r="T12" s="176" t="inlineStr">
+      <c r="T12" s="177" t="inlineStr">
         <is>
           <t>→ WACC</t>
         </is>
       </c>
-      <c r="U12" s="170" t="inlineStr">
+      <c r="U12" s="171" t="inlineStr">
         <is>
           <t>Derived: R10 × (1 − R11)</t>
         </is>
       </c>
-      <c r="V12" s="170" t="inlineStr"/>
+      <c r="V12" s="171" t="inlineStr"/>
     </row>
     <row r="13" ht="16" customHeight="1">
       <c r="A13" s="97" t="n"/>
@@ -7015,7 +7027,7 @@
         </is>
       </c>
       <c r="C13" s="97" t="n"/>
-      <c r="D13" s="179" t="n">
+      <c r="D13" s="180" t="n">
         <v>5582389</v>
       </c>
       <c r="E13" s="97" t="n"/>
@@ -7029,30 +7041,30 @@
       <c r="M13" s="97" t="n"/>
       <c r="N13" s="97" t="n"/>
       <c r="O13" s="97" t="n"/>
-      <c r="Q13" s="170" t="inlineStr">
+      <c r="Q13" s="171" t="inlineStr">
         <is>
           <t>Equity weight (We)</t>
         </is>
       </c>
-      <c r="R13" s="180" t="n">
+      <c r="R13" s="181" t="n">
         <v>0.8</v>
       </c>
-      <c r="S13" s="170" t="inlineStr">
+      <c r="S13" s="171" t="inlineStr">
         <is>
           <t>Target ~80% equity at market</t>
         </is>
       </c>
-      <c r="T13" s="170" t="inlineStr">
+      <c r="T13" s="171" t="inlineStr">
         <is>
           <t>WACC weight</t>
         </is>
       </c>
-      <c r="U13" s="172" t="inlineStr">
+      <c r="U13" s="173" t="inlineStr">
         <is>
           <t>SEC 10-Q Q3 FY2026 (debt / capital)</t>
         </is>
       </c>
-      <c r="V13" s="172" t="inlineStr">
+      <c r="V13" s="173" t="inlineStr">
         <is>
           <t>Yahoo market cap for E/(D+E)</t>
         </is>
@@ -7066,7 +7078,7 @@
         </is>
       </c>
       <c r="C14" s="97" t="n"/>
-      <c r="D14" s="179" t="n">
+      <c r="D14" s="180" t="n">
         <v>304537</v>
       </c>
       <c r="E14" s="97" t="n"/>
@@ -7080,30 +7092,30 @@
       <c r="M14" s="97" t="n"/>
       <c r="N14" s="97" t="n"/>
       <c r="O14" s="97" t="n"/>
-      <c r="Q14" s="170" t="inlineStr">
+      <c r="Q14" s="171" t="inlineStr">
         <is>
           <t>Debt weight (Wd)</t>
         </is>
       </c>
-      <c r="R14" s="180" t="n">
+      <c r="R14" s="181" t="n">
         <v>0.2</v>
       </c>
-      <c r="S14" s="170" t="inlineStr">
+      <c r="S14" s="171" t="inlineStr">
         <is>
           <t>Target ~20% debt (We+Wd=100%)</t>
         </is>
       </c>
-      <c r="T14" s="170" t="inlineStr">
+      <c r="T14" s="171" t="inlineStr">
         <is>
           <t>WACC weight</t>
         </is>
       </c>
-      <c r="U14" s="172" t="inlineStr">
+      <c r="U14" s="173" t="inlineStr">
         <is>
           <t>SEC 10-Q — total debt $5,582,389k</t>
         </is>
       </c>
-      <c r="V14" s="172" t="inlineStr">
+      <c r="V14" s="173" t="inlineStr">
         <is>
           <t>SEC 10-K — senior notes footnote</t>
         </is>
@@ -7117,7 +7129,7 @@
         </is>
       </c>
       <c r="C15" s="97" t="n"/>
-      <c r="D15" s="181">
+      <c r="D15" s="182">
         <f>'3 Statement Model'!J68</f>
         <v/>
       </c>
@@ -7132,31 +7144,31 @@
       <c r="M15" s="97" t="n"/>
       <c r="N15" s="97" t="n"/>
       <c r="O15" s="97" t="n"/>
-      <c r="Q15" s="176" t="inlineStr">
+      <c r="Q15" s="177" t="inlineStr">
         <is>
           <t>WACC = We×Ke + Wd×Rd_aftertax</t>
         </is>
       </c>
-      <c r="R15" s="177">
+      <c r="R15" s="178">
         <f>R13*R9+R14*R12</f>
         <v/>
       </c>
-      <c r="S15" s="170" t="inlineStr">
+      <c r="S15" s="171" t="inlineStr">
         <is>
           <t>PRIMARY discount rate → cell D6</t>
         </is>
       </c>
-      <c r="T15" s="176" t="inlineStr">
+      <c r="T15" s="177" t="inlineStr">
         <is>
           <t>→ D6</t>
         </is>
       </c>
-      <c r="U15" s="172" t="inlineStr">
+      <c r="U15" s="173" t="inlineStr">
         <is>
           <t>SEC filings (tax, debt coupons)</t>
         </is>
       </c>
-      <c r="V15" s="172" t="inlineStr">
+      <c r="V15" s="173" t="inlineStr">
         <is>
           <t>Damodaran (ERP methodology)</t>
         </is>
@@ -7187,23 +7199,23 @@
           <t>Entry</t>
         </is>
       </c>
-      <c r="E17" s="182">
+      <c r="E17" s="183">
         <f>YEAR(E18)</f>
         <v/>
       </c>
-      <c r="F17" s="182">
+      <c r="F17" s="183">
         <f>YEAR(F18)</f>
         <v/>
       </c>
-      <c r="G17" s="182">
+      <c r="G17" s="183">
         <f>YEAR(G18)</f>
         <v/>
       </c>
-      <c r="H17" s="182">
+      <c r="H17" s="183">
         <f>YEAR(H18)</f>
         <v/>
       </c>
-      <c r="I17" s="182">
+      <c r="I17" s="183">
         <f>YEAR(I18)</f>
         <v/>
       </c>
@@ -7235,31 +7247,31 @@
         </is>
       </c>
       <c r="C18" s="97" t="n"/>
-      <c r="D18" s="183">
+      <c r="D18" s="184">
         <f>D9</f>
         <v/>
       </c>
-      <c r="E18" s="184">
+      <c r="E18" s="185">
         <f>DATE(YEAR($D$10)+E19,3,31)</f>
         <v/>
       </c>
-      <c r="F18" s="184">
+      <c r="F18" s="185">
         <f>DATE(YEAR($D$10)+F19,3,31)</f>
         <v/>
       </c>
-      <c r="G18" s="184">
+      <c r="G18" s="185">
         <f>DATE(YEAR($D$10)+G19,3,31)</f>
         <v/>
       </c>
-      <c r="H18" s="184">
+      <c r="H18" s="185">
         <f>DATE(YEAR($D$10)+H19,3,31)</f>
         <v/>
       </c>
-      <c r="I18" s="184">
+      <c r="I18" s="185">
         <f>DATE(YEAR($D$10)+I19,3,31)</f>
         <v/>
       </c>
-      <c r="J18" s="185">
+      <c r="J18" s="186">
         <f>I18</f>
         <v/>
       </c>
@@ -7269,7 +7281,7 @@
           <t>Exit EV/EBITDA (in J27) — primary</t>
         </is>
       </c>
-      <c r="M18" s="181">
+      <c r="M18" s="182">
         <f>J27</f>
         <v/>
       </c>
@@ -7278,17 +7290,17 @@
         <v/>
       </c>
       <c r="O18" s="97" t="n"/>
-      <c r="Q18" s="176" t="inlineStr">
+      <c r="Q18" s="177" t="inlineStr">
         <is>
           <t>FCFF = EBIT − EBIT×t + D&amp;A − CapEx − ΔNWC</t>
         </is>
       </c>
-      <c r="U18" s="172" t="inlineStr">
+      <c r="U18" s="173" t="inlineStr">
         <is>
           <t>Drivers from SEC XBRL → 3-statement</t>
         </is>
       </c>
-      <c r="V18" s="172" t="inlineStr">
+      <c r="V18" s="173" t="inlineStr">
         <is>
           <t>SEC 10-K historical IS/CF</t>
         </is>
@@ -7303,22 +7315,22 @@
       </c>
       <c r="C19" s="118" t="n"/>
       <c r="D19" s="115" t="n"/>
-      <c r="E19" s="186" t="n">
+      <c r="E19" s="187" t="n">
         <v>0</v>
       </c>
-      <c r="F19" s="183">
+      <c r="F19" s="184">
         <f>E19+1</f>
         <v/>
       </c>
-      <c r="G19" s="183">
+      <c r="G19" s="184">
         <f>F19+1</f>
         <v/>
       </c>
-      <c r="H19" s="183">
+      <c r="H19" s="184">
         <f>G19+1</f>
         <v/>
       </c>
-      <c r="I19" s="183">
+      <c r="I19" s="184">
         <f>H19+1</f>
         <v/>
       </c>
@@ -7329,7 +7341,7 @@
           <t>Gordon cross-check</t>
         </is>
       </c>
-      <c r="M19" s="181">
+      <c r="M19" s="182">
         <f>IF(($D$6-$D$7)&lt;=0,"WACC must exceed g",$I$26*(1+$D$7)/($D$6-$D$7))</f>
         <v/>
       </c>
@@ -7338,12 +7350,12 @@
         <v/>
       </c>
       <c r="O19" s="97" t="n"/>
-      <c r="Q19" s="170" t="inlineStr">
+      <c r="Q19" s="171" t="inlineStr">
         <is>
           <t>Excel (col E example)</t>
         </is>
       </c>
-      <c r="R19" s="176">
+      <c r="R19" s="177">
         <f>E21-E22+E23-E24-E25</f>
         <v/>
       </c>
@@ -7357,23 +7369,23 @@
       </c>
       <c r="C20" s="97" t="n"/>
       <c r="D20" s="97" t="n"/>
-      <c r="E20" s="183">
+      <c r="E20" s="184">
         <f>YEARFRAC(D18,E18)</f>
         <v/>
       </c>
-      <c r="F20" s="183">
+      <c r="F20" s="184">
         <f>YEARFRAC(E18,F18)</f>
         <v/>
       </c>
-      <c r="G20" s="183">
+      <c r="G20" s="184">
         <f>YEARFRAC(F18,G18)</f>
         <v/>
       </c>
-      <c r="H20" s="183">
+      <c r="H20" s="184">
         <f>YEARFRAC(G18,H18)</f>
         <v/>
       </c>
-      <c r="I20" s="183">
+      <c r="I20" s="184">
         <f>YEARFRAC(H18,I18)</f>
         <v/>
       </c>
@@ -7384,7 +7396,7 @@
           <t>Implied Gordon exit multiple</t>
         </is>
       </c>
-      <c r="M20" s="181">
+      <c r="M20" s="182">
         <f>IF(($I$21+$I$23)=0,0,M19/($I$21+$I$23))</f>
         <v/>
       </c>
@@ -7393,21 +7405,21 @@
         <v/>
       </c>
       <c r="O20" s="97" t="n"/>
-      <c r="Q20" s="170" t="inlineStr">
+      <c r="Q20" s="171" t="inlineStr">
         <is>
           <t>Tax on EBIT (unlevered)</t>
         </is>
       </c>
-      <c r="R20" s="176">
+      <c r="R20" s="177">
         <f>E21*$D$5</f>
         <v/>
       </c>
-      <c r="S20" s="170" t="inlineStr">
+      <c r="S20" s="171" t="inlineStr">
         <is>
           <t>NOT levered IS tax dollars</t>
         </is>
       </c>
-      <c r="U20" s="172" t="inlineStr">
+      <c r="U20" s="173" t="inlineStr">
         <is>
           <t>Tax rate from SEC 10-K effective rate</t>
         </is>
@@ -7420,29 +7432,29 @@
           <t>EBIT (linked to 3-stmt)</t>
         </is>
       </c>
-      <c r="C21" s="187" t="inlineStr">
+      <c r="C21" s="188" t="inlineStr">
         <is>
           <t>EBIT</t>
         </is>
       </c>
       <c r="D21" s="97" t="n"/>
-      <c r="E21" s="181">
+      <c r="E21" s="182">
         <f>'3 Statement Model'!J26-'3 Statement Model'!J28-'3 Statement Model'!J29-'3 Statement Model'!J30</f>
         <v/>
       </c>
-      <c r="F21" s="181">
+      <c r="F21" s="182">
         <f>'3 Statement Model'!K26-'3 Statement Model'!K28-'3 Statement Model'!K29-'3 Statement Model'!K30</f>
         <v/>
       </c>
-      <c r="G21" s="181">
+      <c r="G21" s="182">
         <f>'3 Statement Model'!L26-'3 Statement Model'!L28-'3 Statement Model'!L29-'3 Statement Model'!L30</f>
         <v/>
       </c>
-      <c r="H21" s="181">
+      <c r="H21" s="182">
         <f>'3 Statement Model'!M26-'3 Statement Model'!M28-'3 Statement Model'!M29-'3 Statement Model'!M30</f>
         <v/>
       </c>
-      <c r="I21" s="181">
+      <c r="I21" s="182">
         <f>'3 Statement Model'!N26-'3 Statement Model'!N28-'3 Statement Model'!N29-'3 Statement Model'!N30</f>
         <v/>
       </c>
@@ -7452,16 +7464,16 @@
       <c r="M21" s="97" t="n"/>
       <c r="N21" s="97" t="n"/>
       <c r="O21" s="97" t="n"/>
-      <c r="Q21" s="170" t="inlineStr">
+      <c r="Q21" s="171" t="inlineStr">
         <is>
           <t>FCFF check (FY5 / col I)</t>
         </is>
       </c>
-      <c r="R21" s="188">
+      <c r="R21" s="189">
         <f>I26</f>
         <v/>
       </c>
-      <c r="S21" s="170" t="inlineStr">
+      <c r="S21" s="171" t="inlineStr">
         <is>
           <t>Must equal I21−I22+I23−I24−I25</t>
         </is>
@@ -7474,29 +7486,29 @@
           <t>Less: Unlevered Cash Taxes (EBIT×t)</t>
         </is>
       </c>
-      <c r="C22" s="187" t="inlineStr">
+      <c r="C22" s="188" t="inlineStr">
         <is>
           <t>EBIT×t</t>
         </is>
       </c>
       <c r="D22" s="97" t="n"/>
-      <c r="E22" s="181">
+      <c r="E22" s="182">
         <f>E21*$D$5</f>
         <v/>
       </c>
-      <c r="F22" s="181">
+      <c r="F22" s="182">
         <f>F21*$D$5</f>
         <v/>
       </c>
-      <c r="G22" s="181">
+      <c r="G22" s="182">
         <f>G21*$D$5</f>
         <v/>
       </c>
-      <c r="H22" s="181">
+      <c r="H22" s="182">
         <f>H21*$D$5</f>
         <v/>
       </c>
-      <c r="I22" s="181">
+      <c r="I22" s="182">
         <f>I21*$D$5</f>
         <v/>
       </c>
@@ -7514,29 +7526,29 @@
           <t>Plus: D&amp;A (linked to 3-stmt)</t>
         </is>
       </c>
-      <c r="C23" s="187" t="inlineStr">
+      <c r="C23" s="188" t="inlineStr">
         <is>
           <t>+D&amp;A</t>
         </is>
       </c>
       <c r="D23" s="97" t="n"/>
-      <c r="E23" s="181">
+      <c r="E23" s="182">
         <f>'3 Statement Model'!J30</f>
         <v/>
       </c>
-      <c r="F23" s="181">
+      <c r="F23" s="182">
         <f>'3 Statement Model'!K30</f>
         <v/>
       </c>
-      <c r="G23" s="181">
+      <c r="G23" s="182">
         <f>'3 Statement Model'!L30</f>
         <v/>
       </c>
-      <c r="H23" s="181">
+      <c r="H23" s="182">
         <f>'3 Statement Model'!M30</f>
         <v/>
       </c>
-      <c r="I23" s="181">
+      <c r="I23" s="182">
         <f>'3 Statement Model'!N30</f>
         <v/>
       </c>
@@ -7559,29 +7571,29 @@
           <t>Less: Capex (linked to 3-stmt CF)</t>
         </is>
       </c>
-      <c r="C24" s="187" t="inlineStr">
+      <c r="C24" s="188" t="inlineStr">
         <is>
           <t>−CapEx</t>
         </is>
       </c>
       <c r="D24" s="97" t="n"/>
-      <c r="E24" s="181">
+      <c r="E24" s="182">
         <f>'3 Statement Model'!J68</f>
         <v/>
       </c>
-      <c r="F24" s="181">
+      <c r="F24" s="182">
         <f>'3 Statement Model'!K68</f>
         <v/>
       </c>
-      <c r="G24" s="181">
+      <c r="G24" s="182">
         <f>'3 Statement Model'!L68</f>
         <v/>
       </c>
-      <c r="H24" s="181">
+      <c r="H24" s="182">
         <f>'3 Statement Model'!M68</f>
         <v/>
       </c>
-      <c r="I24" s="181">
+      <c r="I24" s="182">
         <f>'3 Statement Model'!N68</f>
         <v/>
       </c>
@@ -7591,7 +7603,7 @@
       <c r="M24" s="97" t="n"/>
       <c r="N24" s="97" t="n"/>
       <c r="O24" s="97" t="n"/>
-      <c r="Q24" s="176" t="inlineStr">
+      <c r="Q24" s="177" t="inlineStr">
         <is>
           <t>TV_exit = EBITDA_n × ExitMultiple   [PRIMARY]</t>
         </is>
@@ -7604,29 +7616,29 @@
           <t>Less: ΔNWC (linked to 3-stmt CF)</t>
         </is>
       </c>
-      <c r="C25" s="187" t="inlineStr">
+      <c r="C25" s="188" t="inlineStr">
         <is>
           <t>−ΔNWC</t>
         </is>
       </c>
       <c r="D25" s="97" t="n"/>
-      <c r="E25" s="181">
+      <c r="E25" s="182">
         <f>'3 Statement Model'!J64</f>
         <v/>
       </c>
-      <c r="F25" s="181">
+      <c r="F25" s="182">
         <f>'3 Statement Model'!K64</f>
         <v/>
       </c>
-      <c r="G25" s="181">
+      <c r="G25" s="182">
         <f>'3 Statement Model'!L64</f>
         <v/>
       </c>
-      <c r="H25" s="181">
+      <c r="H25" s="182">
         <f>'3 Statement Model'!M64</f>
         <v/>
       </c>
-      <c r="I25" s="181">
+      <c r="I25" s="182">
         <f>'3 Statement Model'!N64</f>
         <v/>
       </c>
@@ -7636,20 +7648,20 @@
       <c r="M25" s="97" t="n"/>
       <c r="N25" s="97" t="n"/>
       <c r="O25" s="97" t="n"/>
-      <c r="Q25" s="170" t="inlineStr">
+      <c r="Q25" s="171" t="inlineStr">
         <is>
           <t>Excel</t>
         </is>
       </c>
-      <c r="R25" s="176">
+      <c r="R25" s="177">
         <f>($I$21+$I$23)*$D$8</f>
         <v/>
       </c>
-      <c r="T25" s="188">
+      <c r="T25" s="189">
         <f>J27</f>
         <v/>
       </c>
-      <c r="U25" s="172" t="inlineStr">
+      <c r="U25" s="173" t="inlineStr">
         <is>
           <t>Exit multiple policy vs Yahoo / market multiples</t>
         </is>
@@ -7662,29 +7674,29 @@
           <t>Unlevered FCF</t>
         </is>
       </c>
-      <c r="C26" s="187" t="inlineStr">
+      <c r="C26" s="188" t="inlineStr">
         <is>
           <t>FCFF=EBIT−tax+DA−CapEx−ΔNWC</t>
         </is>
       </c>
       <c r="D26" s="97" t="n"/>
-      <c r="E26" s="189">
+      <c r="E26" s="190">
         <f>E21-E22+E23-E24-E25</f>
         <v/>
       </c>
-      <c r="F26" s="189">
+      <c r="F26" s="190">
         <f>F21-F22+F23-F24-F25</f>
         <v/>
       </c>
-      <c r="G26" s="189">
+      <c r="G26" s="190">
         <f>G21-G22+G23-G24-G25</f>
         <v/>
       </c>
-      <c r="H26" s="189">
+      <c r="H26" s="190">
         <f>H21-H22+H23-H24-H25</f>
         <v/>
       </c>
-      <c r="I26" s="189">
+      <c r="I26" s="190">
         <f>I21-I22+I23-I24-I25</f>
         <v/>
       </c>
@@ -7694,7 +7706,7 @@
       <c r="M26" s="97" t="n"/>
       <c r="N26" s="97" t="n"/>
       <c r="O26" s="97" t="n"/>
-      <c r="Q26" s="176" t="inlineStr">
+      <c r="Q26" s="177" t="inlineStr">
         <is>
           <t>TV_gordon = FCFF_n×(1+g)/(WACC−g)   [CHECK]</t>
         </is>
@@ -7708,7 +7720,7 @@
         </is>
       </c>
       <c r="C27" s="97" t="n"/>
-      <c r="D27" s="190">
+      <c r="D27" s="191">
         <f>-I35</f>
         <v/>
       </c>
@@ -7717,7 +7729,7 @@
       <c r="G27" s="97" t="n"/>
       <c r="H27" s="97" t="n"/>
       <c r="I27" s="97" t="n"/>
-      <c r="J27" s="181">
+      <c r="J27" s="182">
         <f>($I$21+$I$23)*$D$8</f>
         <v/>
       </c>
@@ -7726,20 +7738,20 @@
       <c r="M27" s="97" t="n"/>
       <c r="N27" s="97" t="n"/>
       <c r="O27" s="97" t="n"/>
-      <c r="Q27" s="170" t="inlineStr">
+      <c r="Q27" s="171" t="inlineStr">
         <is>
           <t>Excel</t>
         </is>
       </c>
-      <c r="R27" s="176">
+      <c r="R27" s="177">
         <f>IF(($D$6-$D$7)&lt;=0,"err",$I$26*(1+$D$7)/($D$6-$D$7))</f>
         <v/>
       </c>
-      <c r="T27" s="188">
+      <c r="T27" s="189">
         <f>M19</f>
         <v/>
       </c>
-      <c r="U27" s="172" t="inlineStr">
+      <c r="U27" s="173" t="inlineStr">
         <is>
           <t>Gordon g vs Damodaran long-run growth framing</t>
         </is>
@@ -7753,30 +7765,30 @@
         </is>
       </c>
       <c r="C28" s="97" t="n"/>
-      <c r="D28" s="189" t="n">
+      <c r="D28" s="190" t="n">
         <v>0</v>
       </c>
-      <c r="E28" s="191">
+      <c r="E28" s="192">
         <f>E27+E26</f>
         <v/>
       </c>
-      <c r="F28" s="191">
+      <c r="F28" s="192">
         <f>F27+F26</f>
         <v/>
       </c>
-      <c r="G28" s="191">
+      <c r="G28" s="192">
         <f>G27+G26</f>
         <v/>
       </c>
-      <c r="H28" s="191">
+      <c r="H28" s="192">
         <f>H27+H26</f>
         <v/>
       </c>
-      <c r="I28" s="191">
+      <c r="I28" s="192">
         <f>I27+I26</f>
         <v/>
       </c>
-      <c r="J28" s="191">
+      <c r="J28" s="192">
         <f>J27+J26</f>
         <v/>
       </c>
@@ -7785,16 +7797,16 @@
       <c r="M28" s="97" t="n"/>
       <c r="N28" s="97" t="n"/>
       <c r="O28" s="97" t="n"/>
-      <c r="Q28" s="170" t="inlineStr">
+      <c r="Q28" s="171" t="inlineStr">
         <is>
           <t>Implied Gordon exit multiple</t>
         </is>
       </c>
-      <c r="R28" s="192">
+      <c r="R28" s="193">
         <f>IF(($I$21+$I$23)=0,0,T27/($I$21+$I$23))</f>
         <v/>
       </c>
-      <c r="S28" s="170" t="inlineStr">
+      <c r="S28" s="171" t="inlineStr">
         <is>
           <t>Gordon TV / EBITDA_n</t>
         </is>
@@ -7808,31 +7820,31 @@
         </is>
       </c>
       <c r="C29" s="97" t="n"/>
-      <c r="D29" s="190">
+      <c r="D29" s="191">
         <f>D27+D26</f>
         <v/>
       </c>
-      <c r="E29" s="181">
+      <c r="E29" s="182">
         <f>E27+E26</f>
         <v/>
       </c>
-      <c r="F29" s="181">
+      <c r="F29" s="182">
         <f>F27+F26</f>
         <v/>
       </c>
-      <c r="G29" s="181">
+      <c r="G29" s="182">
         <f>G27+G26</f>
         <v/>
       </c>
-      <c r="H29" s="181">
+      <c r="H29" s="182">
         <f>H27+H26</f>
         <v/>
       </c>
-      <c r="I29" s="181">
+      <c r="I29" s="182">
         <f>I27+I26</f>
         <v/>
       </c>
-      <c r="J29" s="181">
+      <c r="J29" s="182">
         <f>J27</f>
         <v/>
       </c>
@@ -7888,7 +7900,7 @@
       <c r="M31" s="111" t="n"/>
       <c r="N31" s="111" t="n"/>
       <c r="O31" s="97" t="n"/>
-      <c r="Q31" s="176" t="inlineStr">
+      <c r="Q31" s="177" t="inlineStr">
         <is>
           <t>EV = XNPV(WACC, TransactionCF, mid-year dates)</t>
         </is>
@@ -7902,7 +7914,7 @@
         </is>
       </c>
       <c r="C32" s="97" t="n"/>
-      <c r="D32" s="181">
+      <c r="D32" s="182">
         <f>XNPV(D6,D28:J28,D18:J18)</f>
         <v/>
       </c>
@@ -7913,7 +7925,7 @@
         </is>
       </c>
       <c r="H32" s="97" t="n"/>
-      <c r="I32" s="190">
+      <c r="I32" s="191">
         <f>D12*D11</f>
         <v/>
       </c>
@@ -7929,16 +7941,16 @@
         <v/>
       </c>
       <c r="O32" s="97" t="n"/>
-      <c r="Q32" s="170" t="inlineStr">
+      <c r="Q32" s="171" t="inlineStr">
         <is>
           <t>Excel</t>
         </is>
       </c>
-      <c r="R32" s="176">
+      <c r="R32" s="177">
         <f>XNPV(D6,D28:J28,D18:J18)</f>
         <v/>
       </c>
-      <c r="T32" s="188">
+      <c r="T32" s="189">
         <f>D32</f>
         <v/>
       </c>
@@ -7951,7 +7963,7 @@
         </is>
       </c>
       <c r="C33" s="97" t="n"/>
-      <c r="D33" s="190">
+      <c r="D33" s="191">
         <f>+D14</f>
         <v/>
       </c>
@@ -7962,7 +7974,7 @@
         </is>
       </c>
       <c r="H33" s="97" t="n"/>
-      <c r="I33" s="190">
+      <c r="I33" s="191">
         <f>D13</f>
         <v/>
       </c>
@@ -7978,26 +7990,26 @@
         <v/>
       </c>
       <c r="O33" s="97" t="n"/>
-      <c r="Q33" s="176" t="inlineStr">
+      <c r="Q33" s="177" t="inlineStr">
         <is>
           <t>Equity = EV + Cash − Debt</t>
         </is>
       </c>
-      <c r="R33" s="188">
+      <c r="R33" s="189">
         <f>D35</f>
         <v/>
       </c>
-      <c r="S33" s="170" t="inlineStr">
+      <c r="S33" s="171" t="inlineStr">
         <is>
           <t>Net debt from 10-Q bridge</t>
         </is>
       </c>
-      <c r="U33" s="172" t="inlineStr">
+      <c r="U33" s="173" t="inlineStr">
         <is>
           <t>SEC 10-Q — cash, mkt secs, total debt</t>
         </is>
       </c>
-      <c r="V33" s="172" t="inlineStr">
+      <c r="V33" s="173" t="inlineStr">
         <is>
           <t>SEC 10-K — FY debt footnote</t>
         </is>
@@ -8011,7 +8023,7 @@
         </is>
       </c>
       <c r="C34" s="97" t="n"/>
-      <c r="D34" s="190">
+      <c r="D34" s="191">
         <f>+D13</f>
         <v/>
       </c>
@@ -8022,7 +8034,7 @@
         </is>
       </c>
       <c r="H34" s="97" t="n"/>
-      <c r="I34" s="190">
+      <c r="I34" s="191">
         <f>+D14</f>
         <v/>
       </c>
@@ -8031,26 +8043,26 @@
       <c r="M34" s="97" t="n"/>
       <c r="N34" s="97" t="n"/>
       <c r="O34" s="97" t="n"/>
-      <c r="Q34" s="176" t="inlineStr">
+      <c r="Q34" s="177" t="inlineStr">
         <is>
           <t>$/share = Equity / Shares</t>
         </is>
       </c>
-      <c r="R34" s="193">
+      <c r="R34" s="194">
         <f>D37</f>
         <v/>
       </c>
-      <c r="S34" s="170" t="inlineStr">
+      <c r="S34" s="171" t="inlineStr">
         <is>
           <t>Shares outstanding (Yahoo)</t>
         </is>
       </c>
-      <c r="U34" s="172" t="inlineStr">
+      <c r="U34" s="173" t="inlineStr">
         <is>
           <t>Yahoo Finance — shares outstanding</t>
         </is>
       </c>
-      <c r="V34" s="172" t="inlineStr">
+      <c r="V34" s="173" t="inlineStr">
         <is>
           <t>Yahoo FICO quote (price)</t>
         </is>
@@ -8064,7 +8076,7 @@
         </is>
       </c>
       <c r="C35" s="97" t="n"/>
-      <c r="D35" s="189">
+      <c r="D35" s="190">
         <f>D32+D33-D34</f>
         <v/>
       </c>
@@ -8075,7 +8087,7 @@
         </is>
       </c>
       <c r="H35" s="97" t="n"/>
-      <c r="I35" s="189">
+      <c r="I35" s="190">
         <f>I32+I33-I34</f>
         <v/>
       </c>
@@ -8088,16 +8100,16 @@
       <c r="M35" s="111" t="n"/>
       <c r="N35" s="111" t="n"/>
       <c r="O35" s="97" t="n"/>
-      <c r="Q35" s="170" t="inlineStr">
+      <c r="Q35" s="171" t="inlineStr">
         <is>
           <t>Upside vs market</t>
         </is>
       </c>
-      <c r="R35" s="194">
+      <c r="R35" s="195">
         <f>D37/D11-1</f>
         <v/>
       </c>
-      <c r="S35" s="170" t="inlineStr">
+      <c r="S35" s="171" t="inlineStr">
         <is>
           <t>Intrinsic / Current Price − 1</t>
         </is>
@@ -8111,7 +8123,7 @@
       <c r="E36" s="97" t="n"/>
       <c r="G36" s="97" t="n"/>
       <c r="H36" s="97" t="n"/>
-      <c r="I36" s="195" t="n"/>
+      <c r="I36" s="196" t="n"/>
       <c r="J36" s="97" t="n"/>
       <c r="L36" s="97" t="inlineStr">
         <is>
@@ -8119,7 +8131,7 @@
         </is>
       </c>
       <c r="M36" s="97" t="n"/>
-      <c r="N36" s="195">
+      <c r="N36" s="196">
         <f>I37</f>
         <v/>
       </c>
@@ -8133,7 +8145,7 @@
         </is>
       </c>
       <c r="C37" s="97" t="n"/>
-      <c r="D37" s="190">
+      <c r="D37" s="191">
         <f>D35/D12</f>
         <v/>
       </c>
@@ -8144,7 +8156,7 @@
         </is>
       </c>
       <c r="H37" s="97" t="n"/>
-      <c r="I37" s="190">
+      <c r="I37" s="191">
         <f>D11</f>
         <v/>
       </c>
@@ -8155,7 +8167,7 @@
         </is>
       </c>
       <c r="M37" s="97" t="n"/>
-      <c r="N37" s="195">
+      <c r="N37" s="196">
         <f>D37-I37</f>
         <v/>
       </c>
@@ -8182,22 +8194,22 @@
         </is>
       </c>
       <c r="M38" s="97" t="n"/>
-      <c r="N38" s="195">
+      <c r="N38" s="196">
         <f>SUM(N36:N37)</f>
         <v/>
       </c>
       <c r="O38" s="97" t="n"/>
-      <c r="Q38" s="176" t="inlineStr">
+      <c r="Q38" s="177" t="inlineStr">
         <is>
           <t>NWC = AR + Inventory − AP − DeferredRevenue</t>
         </is>
       </c>
-      <c r="U38" s="172" t="inlineStr">
+      <c r="U38" s="173" t="inlineStr">
         <is>
           <t>SEC 10-K — AR / AP / deferred revenue</t>
         </is>
       </c>
-      <c r="V38" s="172" t="inlineStr">
+      <c r="V38" s="173" t="inlineStr">
         <is>
           <t>XBRL DeferredRevenueCurrent</t>
         </is>
@@ -8216,17 +8228,17 @@
       <c r="M39" s="97" t="n"/>
       <c r="N39" s="97" t="n"/>
       <c r="O39" s="97" t="n"/>
-      <c r="Q39" s="176" t="inlineStr">
+      <c r="Q39" s="177" t="inlineStr">
         <is>
           <t>ΔNWC_t = NWC_t − NWC_(t−1)</t>
         </is>
       </c>
-      <c r="S39" s="170" t="inlineStr">
+      <c r="S39" s="171" t="inlineStr">
         <is>
           <t>Linked from 3-statement CF row 64</t>
         </is>
       </c>
-      <c r="T39" s="188">
+      <c r="T39" s="189">
         <f>I25</f>
         <v/>
       </c>
@@ -8291,14 +8303,14 @@
         </is>
       </c>
       <c r="O42" s="97" t="n"/>
-      <c r="Q42" s="172" t="inlineStr">
+      <c r="Q42" s="173" t="inlineStr">
         <is>
           <t>SEC 10-K FY2025</t>
         </is>
       </c>
-      <c r="R42" s="196" t="n"/>
-      <c r="S42" s="197" t="n"/>
-      <c r="T42" s="170" t="inlineStr">
+      <c r="R42" s="197" t="n"/>
+      <c r="S42" s="198" t="n"/>
+      <c r="T42" s="171" t="inlineStr">
         <is>
           <t>Tax 18.8%, IS/BS/CF, senior notes</t>
         </is>
@@ -8319,14 +8331,14 @@
       <c r="H43" s="97" t="n"/>
       <c r="N43" s="69" t="n"/>
       <c r="O43" s="97" t="n"/>
-      <c r="Q43" s="172" t="inlineStr">
+      <c r="Q43" s="173" t="inlineStr">
         <is>
           <t>SEC 10-Q Q3 FY2026</t>
         </is>
       </c>
-      <c r="R43" s="196" t="n"/>
-      <c r="S43" s="197" t="n"/>
-      <c r="T43" s="170" t="inlineStr">
+      <c r="R43" s="197" t="n"/>
+      <c r="S43" s="198" t="n"/>
+      <c r="T43" s="171" t="inlineStr">
         <is>
           <t>Debt $5,582M, cash+mkt secs net-debt bridge</t>
         </is>
@@ -8347,14 +8359,14 @@
       <c r="H44" s="97" t="n"/>
       <c r="N44" s="69" t="n"/>
       <c r="O44" s="97" t="n"/>
-      <c r="Q44" s="172" t="inlineStr">
+      <c r="Q44" s="173" t="inlineStr">
         <is>
           <t>SEC 8-K 6.250% notes</t>
         </is>
       </c>
-      <c r="R44" s="196" t="n"/>
-      <c r="S44" s="197" t="n"/>
-      <c r="T44" s="170" t="inlineStr">
+      <c r="R44" s="197" t="n"/>
+      <c r="S44" s="198" t="n"/>
+      <c r="T44" s="171" t="inlineStr">
         <is>
           <t>Pre-tax Rd coupon 6.250% due 2034</t>
         </is>
@@ -8375,14 +8387,14 @@
       <c r="H45" s="97" t="n"/>
       <c r="N45" s="69" t="n"/>
       <c r="O45" s="97" t="n"/>
-      <c r="Q45" s="172" t="inlineStr">
+      <c r="Q45" s="173" t="inlineStr">
         <is>
           <t>SEC EX-99.1 pricing</t>
         </is>
       </c>
-      <c r="R45" s="196" t="n"/>
-      <c r="S45" s="197" t="n"/>
-      <c r="T45" s="170" t="inlineStr">
+      <c r="R45" s="197" t="n"/>
+      <c r="S45" s="198" t="n"/>
+      <c r="T45" s="171" t="inlineStr">
         <is>
           <t>Notes priced at par / offering terms</t>
         </is>
@@ -8403,14 +8415,14 @@
       <c r="H46" s="97" t="n"/>
       <c r="N46" s="69" t="n"/>
       <c r="O46" s="97" t="n"/>
-      <c r="Q46" s="172" t="inlineStr">
+      <c r="Q46" s="173" t="inlineStr">
         <is>
           <t>SEC companyfacts XBRL</t>
         </is>
       </c>
-      <c r="R46" s="196" t="n"/>
-      <c r="S46" s="197" t="n"/>
-      <c r="T46" s="170" t="inlineStr">
+      <c r="R46" s="197" t="n"/>
+      <c r="S46" s="198" t="n"/>
+      <c r="T46" s="171" t="inlineStr">
         <is>
           <t>Pipeline data source (CIK 0000814547)</t>
         </is>
@@ -8427,14 +8439,14 @@
       <c r="H47" s="97" t="n"/>
       <c r="N47" s="69" t="n"/>
       <c r="O47" s="97" t="n"/>
-      <c r="Q47" s="172" t="inlineStr">
+      <c r="Q47" s="173" t="inlineStr">
         <is>
           <t>FRED DGS10</t>
         </is>
       </c>
-      <c r="R47" s="196" t="n"/>
-      <c r="S47" s="197" t="n"/>
-      <c r="T47" s="170" t="inlineStr">
+      <c r="R47" s="197" t="n"/>
+      <c r="S47" s="198" t="n"/>
+      <c r="T47" s="171" t="inlineStr">
         <is>
           <t>Risk-free rate (US 10Y)</t>
         </is>
@@ -8455,14 +8467,14 @@
         </is>
       </c>
       <c r="O48" s="97" t="n"/>
-      <c r="Q48" s="172" t="inlineStr">
+      <c r="Q48" s="173" t="inlineStr">
         <is>
           <t>US Treasury yield curve</t>
         </is>
       </c>
-      <c r="R48" s="196" t="n"/>
-      <c r="S48" s="197" t="n"/>
-      <c r="T48" s="170" t="inlineStr">
+      <c r="R48" s="197" t="n"/>
+      <c r="S48" s="198" t="n"/>
+      <c r="T48" s="171" t="inlineStr">
         <is>
           <t>Official daily par yields</t>
         </is>
@@ -8483,14 +8495,14 @@
         </is>
       </c>
       <c r="O49" s="97" t="n"/>
-      <c r="Q49" s="172" t="inlineStr">
+      <c r="Q49" s="173" t="inlineStr">
         <is>
           <t>Damodaran Implied ERP</t>
         </is>
       </c>
-      <c r="R49" s="196" t="n"/>
-      <c r="S49" s="197" t="n"/>
-      <c r="T49" s="170" t="inlineStr">
+      <c r="R49" s="197" t="n"/>
+      <c r="S49" s="198" t="n"/>
+      <c r="T49" s="171" t="inlineStr">
         <is>
           <t>Equity risk premium</t>
         </is>
@@ -8506,14 +8518,14 @@
       <c r="G50" s="97" t="n"/>
       <c r="H50" s="97" t="n"/>
       <c r="O50" s="97" t="n"/>
-      <c r="Q50" s="172" t="inlineStr">
+      <c r="Q50" s="173" t="inlineStr">
         <is>
           <t>Damodaran histimpl</t>
         </is>
       </c>
-      <c r="R50" s="196" t="n"/>
-      <c r="S50" s="197" t="n"/>
-      <c r="T50" s="170" t="inlineStr">
+      <c r="R50" s="197" t="n"/>
+      <c r="S50" s="198" t="n"/>
+      <c r="T50" s="171" t="inlineStr">
         <is>
           <t>Historical implied ERP table</t>
         </is>
@@ -8530,14 +8542,14 @@
       <c r="H51" s="97" t="n"/>
       <c r="M51" s="97" t="n"/>
       <c r="O51" s="97" t="n"/>
-      <c r="Q51" s="172" t="inlineStr">
+      <c r="Q51" s="173" t="inlineStr">
         <is>
           <t>Yahoo FICO stats</t>
         </is>
       </c>
-      <c r="R51" s="196" t="n"/>
-      <c r="S51" s="197" t="n"/>
-      <c r="T51" s="170" t="inlineStr">
+      <c r="R51" s="197" t="n"/>
+      <c r="S51" s="198" t="n"/>
+      <c r="T51" s="171" t="inlineStr">
         <is>
           <t>Beta 5Y monthly + shares out</t>
         </is>

--- a/FICO/output/FICO_Completed_Model.xlsx
+++ b/FICO/output/FICO_Completed_Model.xlsx
@@ -100,7 +100,7 @@
     <numFmt numFmtId="178" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="179" formatCode="0.0"/>
   </numFmts>
-  <fonts count="51">
+  <fonts count="50">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -367,19 +367,13 @@
     <font>
       <name val="Calibri"/>
       <i val="1"/>
-      <color rgb="00666666"/>
+      <color rgb="00C00000"/>
       <sz val="8"/>
     </font>
     <font>
       <name val="Consolas"/>
       <color rgb="00000000"/>
       <sz val="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <i val="1"/>
-      <color rgb="00C00000"/>
-      <sz val="8"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -817,44 +811,44 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="43" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="164" fontId="41" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="166" fontId="40" fillId="8" borderId="5" pivotButton="0" quotePrefix="0" xfId="2"/>
     <xf numFmtId="164" fontId="42" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="166" fontId="38" fillId="7" borderId="5" pivotButton="0" quotePrefix="0" xfId="2"/>
     <xf numFmtId="177" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="166" fontId="38" fillId="7" borderId="5" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="177" fontId="38" fillId="7" borderId="5" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="177" fontId="40" fillId="8" borderId="5" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="40" fillId="8" borderId="5" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="177" fontId="40" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="164" fontId="42" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="177" fontId="6" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="164" fontId="42" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="177" fontId="40" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="177" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="177" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="164" fontId="42" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="177" fontId="6" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="177" fontId="6" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="177" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="177" fontId="38" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="177" fontId="40" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="177" fontId="9" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="177" fontId="40" fillId="8" borderId="2" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="44" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="43" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="39" fillId="9" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="40" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="46" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="45" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="49" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="48" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="47" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="38" fillId="7" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
@@ -862,7 +856,7 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="40" fillId="8" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="179" fontId="40" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -870,7 +864,7 @@
     </xf>
     <xf numFmtId="2" fontId="40" fillId="8" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="178" fontId="32" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="38" fillId="7" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -887,7 +881,7 @@
     <xf numFmtId="178" fontId="38" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="177" fontId="36" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="177" fontId="37" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="50" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="49" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="174" fontId="38" fillId="7" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="177" fontId="30" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="177" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -2646,7 +2640,7 @@
   <cols>
     <col width="1.88671875" customWidth="1" style="19" min="1" max="1"/>
     <col width="42" customWidth="1" style="19" min="2" max="3"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" style="47" min="4" max="4"/>
     <col width="16" customWidth="1" style="19" min="5" max="9"/>
     <col width="16" customWidth="1" min="6" max="6"/>
@@ -2788,7 +2782,7 @@
     <row r="4">
       <c r="B4" s="137" t="inlineStr">
         <is>
-          <t>vengeanceaiUSCMODEL4: green assumption cells = equations from FY25 (col I)</t>
+          <t>vengeanceaiUSCMODEL4: GREEN cells = full equations (not hardcoded $, not bare =J36 pointers)</t>
         </is>
       </c>
     </row>
@@ -2827,7 +2821,7 @@
       </c>
       <c r="C7" s="138" t="inlineStr">
         <is>
-          <t>POLICY → drives Rev row24 → GP → EBT → Net Earnings / CF</t>
+          <t>ONLY yellow policy input in this block → feeds Rev equation</t>
         </is>
       </c>
       <c r="D7" s="46" t="n"/>
@@ -2870,9 +2864,10 @@
           <t>Cost of Goods Sold (% of Revenue)</t>
         </is>
       </c>
-      <c r="C8" s="140">
-        <f>I25/I24 (FY25 COGS%)</f>
-        <v/>
+      <c r="C8" s="140" t="inlineStr">
+        <is>
+          <t>COGS% = FY25 COGS/Revenue</t>
+        </is>
       </c>
       <c r="D8" s="47" t="n"/>
       <c r="E8" s="37">
@@ -2919,11 +2914,11 @@
     <row r="9" hidden="1" outlineLevel="1">
       <c r="B9" s="19" t="inlineStr">
         <is>
-          <t>Salaries and Benefits ($000's)</t>
+          <t>SGA % of Revenue (equation)</t>
         </is>
       </c>
       <c r="C9" s="140">
-        <f>Rev×((I28−10922)/I24 − 50bps×t)</f>
+        <f> (I28−10922)/I24 − 50bps×t</f>
         <v/>
       </c>
       <c r="D9" s="47" t="n"/>
@@ -2948,34 +2943,34 @@
         <v/>
       </c>
       <c r="J9" s="143">
-        <f>J28</f>
+        <f>MAX(0.05,(($I$28-10922.0)/$I$24)-0.005)</f>
         <v/>
       </c>
       <c r="K9" s="143">
-        <f>K28</f>
+        <f>MAX(0.05,(($I$28-10922.0)/$I$24)-0.01)</f>
         <v/>
       </c>
       <c r="L9" s="143">
-        <f>L28</f>
+        <f>MAX(0.05,(($I$28-10922.0)/$I$24)-0.015)</f>
         <v/>
       </c>
       <c r="M9" s="143">
-        <f>M28</f>
+        <f>MAX(0.05,(($I$28-10922.0)/$I$24)-0.02)</f>
         <v/>
       </c>
       <c r="N9" s="143">
-        <f>N28</f>
+        <f>MAX(0.05,(($I$28-10922.0)/$I$24)-0.025)</f>
         <v/>
       </c>
     </row>
     <row r="10" hidden="1" outlineLevel="1">
       <c r="B10" s="19" t="inlineStr">
         <is>
-          <t>Rent and Overhead ($000's)</t>
+          <t>R&amp;D % of Revenue (equation)</t>
         </is>
       </c>
       <c r="C10" s="140">
-        <f>Rev×(I29/I24) FY25 R&amp;D%</f>
+        <f> I29/I24</f>
         <v/>
       </c>
       <c r="D10" s="47" t="n"/>
@@ -3000,23 +2995,23 @@
         <v/>
       </c>
       <c r="J10" s="143">
-        <f>J29</f>
+        <f>$I$29/$I$24</f>
         <v/>
       </c>
       <c r="K10" s="143">
-        <f>K29</f>
+        <f>$I$29/$I$24</f>
         <v/>
       </c>
       <c r="L10" s="143">
-        <f>L29</f>
+        <f>$I$29/$I$24</f>
         <v/>
       </c>
       <c r="M10" s="143">
-        <f>M29</f>
+        <f>$I$29/$I$24</f>
         <v/>
       </c>
       <c r="N10" s="143">
-        <f>N29</f>
+        <f>$I$29/$I$24</f>
         <v/>
       </c>
     </row>
@@ -3027,7 +3022,7 @@
         </is>
       </c>
       <c r="C11" s="140">
-        <f>I30/I44 (FY25 DA / PPE); J92 opens at I44</f>
+        <f> I30/I44</f>
         <v/>
       </c>
       <c r="D11" s="47" t="n"/>
@@ -3079,7 +3074,7 @@
         </is>
       </c>
       <c r="C12" s="140">
-        <f>I101/I98 (FY25 Int / Debt open)</f>
+        <f> I101/I98</f>
         <v/>
       </c>
       <c r="D12" s="47" t="n"/>
@@ -3131,7 +3126,7 @@
         </is>
       </c>
       <c r="C13" s="140">
-        <f>I35/I33 (FY25 effective tax)</f>
+        <f> I35/I33</f>
         <v/>
       </c>
       <c r="D13" s="25" t="n"/>
@@ -3202,7 +3197,7 @@
         </is>
       </c>
       <c r="C15" s="144">
-        <f>ROUND(I42/I24×365,0) net AR days</f>
+        <f> ROUND(I42/I24×365,0)</f>
         <v/>
       </c>
       <c r="D15" s="32" t="n"/>
@@ -3226,23 +3221,23 @@
         <f>I42/I24*365</f>
         <v/>
       </c>
-      <c r="J15" s="143">
+      <c r="J15" s="145">
         <f>ROUND($I$42/$I$24*365,0)</f>
         <v/>
       </c>
-      <c r="K15" s="143">
+      <c r="K15" s="145">
         <f>ROUND($I$42/$I$24*365,0)</f>
         <v/>
       </c>
-      <c r="L15" s="143">
+      <c r="L15" s="145">
         <f>ROUND($I$42/$I$24*365,0)</f>
         <v/>
       </c>
-      <c r="M15" s="143">
+      <c r="M15" s="145">
         <f>ROUND($I$42/$I$24*365,0)</f>
         <v/>
       </c>
-      <c r="N15" s="143">
+      <c r="N15" s="145">
         <f>ROUND($I$42/$I$24*365,0)</f>
         <v/>
       </c>
@@ -3274,19 +3269,19 @@
         <f>I43/I25*365</f>
         <v/>
       </c>
-      <c r="J16" s="145" t="n">
+      <c r="J16" s="146" t="n">
         <v>0</v>
       </c>
-      <c r="K16" s="145" t="n">
+      <c r="K16" s="146" t="n">
         <v>0</v>
       </c>
-      <c r="L16" s="145" t="n">
+      <c r="L16" s="146" t="n">
         <v>0</v>
       </c>
-      <c r="M16" s="145" t="n">
+      <c r="M16" s="146" t="n">
         <v>0</v>
       </c>
-      <c r="N16" s="145" t="n">
+      <c r="N16" s="146" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3297,7 +3292,7 @@
         </is>
       </c>
       <c r="C17" s="144">
-        <f>ROUND(I48/I25×365,0) AP days</f>
+        <f> ROUND(I48/I25×365,0)</f>
         <v/>
       </c>
       <c r="D17" s="32" t="n"/>
@@ -3321,23 +3316,23 @@
         <f>I48/I25*365</f>
         <v/>
       </c>
-      <c r="J17" s="143">
+      <c r="J17" s="145">
         <f>IF($I$25=0,0,ROUND($I$48/$I$25*365,0))</f>
         <v/>
       </c>
-      <c r="K17" s="143">
+      <c r="K17" s="145">
         <f>IF($I$25=0,0,ROUND($I$48/$I$25*365,0))</f>
         <v/>
       </c>
-      <c r="L17" s="143">
+      <c r="L17" s="145">
         <f>IF($I$25=0,0,ROUND($I$48/$I$25*365,0))</f>
         <v/>
       </c>
-      <c r="M17" s="143">
+      <c r="M17" s="145">
         <f>IF($I$25=0,0,ROUND($I$48/$I$25*365,0))</f>
         <v/>
       </c>
-      <c r="N17" s="143">
+      <c r="N17" s="145">
         <f>IF($I$25=0,0,ROUND($I$48/$I$25*365,0))</f>
         <v/>
       </c>
@@ -3345,11 +3340,11 @@
     <row r="18" hidden="1" outlineLevel="1">
       <c r="B18" s="19" t="inlineStr">
         <is>
-          <t>Capital Expenditures ($000's)</t>
+          <t>CapEx % of Revenue (fade equation)</t>
         </is>
       </c>
       <c r="C18" s="144">
-        <f>Rev×fade(I68/I24 → 1%)</f>
+        <f> fade(I68/I24 → 1%)</f>
         <v/>
       </c>
       <c r="E18" s="142">
@@ -3373,23 +3368,23 @@
         <v/>
       </c>
       <c r="J18" s="143">
-        <f>J24*(($I$68/$I$24)*0.85+0.01*(1-0.85))</f>
+        <f>($I$68/$I$24)*0.85+0.01*(1-0.85)</f>
         <v/>
       </c>
       <c r="K18" s="143">
-        <f>K24*(($I$68/$I$24)*0.65+0.01*(1-0.65))</f>
+        <f>($I$68/$I$24)*0.65+0.01*(1-0.65)</f>
         <v/>
       </c>
       <c r="L18" s="143">
-        <f>L24*(($I$68/$I$24)*0.45+0.01*(1-0.45))</f>
+        <f>($I$68/$I$24)*0.45+0.01*(1-0.45)</f>
         <v/>
       </c>
       <c r="M18" s="143">
-        <f>M24*(($I$68/$I$24)*0.3+0.01*(1-0.3))</f>
+        <f>($I$68/$I$24)*0.3+0.01*(1-0.3)</f>
         <v/>
       </c>
       <c r="N18" s="143">
-        <f>N24*(($I$68/$I$24)*0.0+0.01*(1-0.0))</f>
+        <f>($I$68/$I$24)*0.0+0.01*(1-0.0)</f>
         <v/>
       </c>
     </row>
@@ -3399,11 +3394,6 @@
           <t>Debt Issuance (Repayment) ($000's)</t>
         </is>
       </c>
-      <c r="C19" s="146" t="inlineStr">
-        <is>
-          <t>POLICY: no new debt issuance</t>
-        </is>
-      </c>
       <c r="E19" s="142">
         <f>E99</f>
         <v/>
@@ -3444,11 +3434,6 @@
       <c r="B20" s="19" t="inlineStr">
         <is>
           <t>Equity Issued (Repaid) ($000's)</t>
-        </is>
-      </c>
-      <c r="C20" s="146" t="inlineStr">
-        <is>
-          <t>POLICY: no equity issuance</t>
         </is>
       </c>
       <c r="E20" s="142">
@@ -3536,7 +3521,10 @@
           <t>Reveneue</t>
         </is>
       </c>
-      <c r="C24" s="18" t="n"/>
+      <c r="C24" s="140">
+        <f> PriorRev × (1 + growth)</f>
+        <v/>
+      </c>
       <c r="D24" s="46" t="n"/>
       <c r="E24" s="148" t="n">
         <v>1316536</v>
@@ -3553,23 +3541,23 @@
       <c r="I24" s="148" t="n">
         <v>1990869</v>
       </c>
-      <c r="J24" s="149">
+      <c r="J24" s="145">
         <f>I24*(1+J7)</f>
         <v/>
       </c>
-      <c r="K24" s="149">
+      <c r="K24" s="145">
         <f>J24*(1+K7)</f>
         <v/>
       </c>
-      <c r="L24" s="149">
+      <c r="L24" s="145">
         <f>K24*(1+L7)</f>
         <v/>
       </c>
-      <c r="M24" s="149">
+      <c r="M24" s="145">
         <f>L24*(1+M7)</f>
         <v/>
       </c>
-      <c r="N24" s="149">
+      <c r="N24" s="145">
         <f>M24*(1+N7)</f>
         <v/>
       </c>
@@ -3580,7 +3568,10 @@
           <t>Cost of Goods Sold (COGS)</t>
         </is>
       </c>
-      <c r="C25" s="19" t="n"/>
+      <c r="C25" s="140">
+        <f> Rev × COGS%</f>
+        <v/>
+      </c>
       <c r="D25" s="47" t="n"/>
       <c r="E25" s="148" t="n">
         <v>332462</v>
@@ -3597,23 +3588,23 @@
       <c r="I25" s="148" t="n">
         <v>353722</v>
       </c>
-      <c r="J25" s="150">
+      <c r="J25" s="145">
         <f>J24*J8</f>
         <v/>
       </c>
-      <c r="K25" s="150">
+      <c r="K25" s="145">
         <f>K24*K8</f>
         <v/>
       </c>
-      <c r="L25" s="150">
+      <c r="L25" s="145">
         <f>L24*L8</f>
         <v/>
       </c>
-      <c r="M25" s="150">
+      <c r="M25" s="145">
         <f>M24*M8</f>
         <v/>
       </c>
-      <c r="N25" s="150">
+      <c r="N25" s="145">
         <f>N24*N8</f>
         <v/>
       </c>
@@ -3624,45 +3615,48 @@
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="C26" s="4" t="n"/>
+      <c r="C26" s="149">
+        <f> Rev − COGS</f>
+        <v/>
+      </c>
       <c r="D26" s="22" t="n"/>
-      <c r="E26" s="151">
+      <c r="E26" s="150">
         <f>E24-E25</f>
         <v/>
       </c>
-      <c r="F26" s="151">
+      <c r="F26" s="150">
         <f>F24-F25</f>
         <v/>
       </c>
-      <c r="G26" s="151">
+      <c r="G26" s="150">
         <f>G24-G25</f>
         <v/>
       </c>
-      <c r="H26" s="151">
+      <c r="H26" s="150">
         <f>H24-H25</f>
         <v/>
       </c>
-      <c r="I26" s="151">
+      <c r="I26" s="150">
         <f>I24-I25</f>
         <v/>
       </c>
-      <c r="J26" s="151">
+      <c r="J26" s="145">
         <f>J24-J25</f>
         <v/>
       </c>
-      <c r="K26" s="151">
+      <c r="K26" s="145">
         <f>K24-K25</f>
         <v/>
       </c>
-      <c r="L26" s="151">
+      <c r="L26" s="145">
         <f>L24-L25</f>
         <v/>
       </c>
-      <c r="M26" s="151">
+      <c r="M26" s="145">
         <f>M24-M25</f>
         <v/>
       </c>
-      <c r="N26" s="151">
+      <c r="N26" s="145">
         <f>N24-N25</f>
         <v/>
       </c>
@@ -3693,7 +3687,7 @@
         </is>
       </c>
       <c r="C28" s="144">
-        <f>Rev×((I28−10922)/I24−50bps×t)</f>
+        <f> Rev × SGA%</f>
         <v/>
       </c>
       <c r="E28" s="148" t="n">
@@ -3711,24 +3705,24 @@
       <c r="I28" s="148" t="n">
         <v>513028</v>
       </c>
-      <c r="J28" s="143">
-        <f>J24*MAX(0.05,(($I$28-10922.0)/$I$24)-0.005)</f>
-        <v/>
-      </c>
-      <c r="K28" s="143">
-        <f>K24*MAX(0.05,(($I$28-10922.0)/$I$24)-0.01)</f>
-        <v/>
-      </c>
-      <c r="L28" s="143">
-        <f>L24*MAX(0.05,(($I$28-10922.0)/$I$24)-0.015)</f>
-        <v/>
-      </c>
-      <c r="M28" s="143">
-        <f>M24*MAX(0.05,(($I$28-10922.0)/$I$24)-0.02)</f>
-        <v/>
-      </c>
-      <c r="N28" s="143">
-        <f>N24*MAX(0.05,(($I$28-10922.0)/$I$24)-0.025)</f>
+      <c r="J28" s="145">
+        <f>J24*J9</f>
+        <v/>
+      </c>
+      <c r="K28" s="145">
+        <f>K24*K9</f>
+        <v/>
+      </c>
+      <c r="L28" s="145">
+        <f>L24*L9</f>
+        <v/>
+      </c>
+      <c r="M28" s="145">
+        <f>M24*M9</f>
+        <v/>
+      </c>
+      <c r="N28" s="145">
+        <f>N24*N9</f>
         <v/>
       </c>
     </row>
@@ -3739,7 +3733,7 @@
         </is>
       </c>
       <c r="C29" s="144">
-        <f>Rev×(I29/I24)  ← grows with revenue</f>
+        <f> Rev × R&amp;D%</f>
         <v/>
       </c>
       <c r="E29" s="148" t="n">
@@ -3757,24 +3751,24 @@
       <c r="I29" s="148" t="n">
         <v>188347</v>
       </c>
-      <c r="J29" s="143">
-        <f>J24*($I$29/$I$24)</f>
-        <v/>
-      </c>
-      <c r="K29" s="143">
-        <f>K24*($I$29/$I$24)</f>
-        <v/>
-      </c>
-      <c r="L29" s="143">
-        <f>L24*($I$29/$I$24)</f>
-        <v/>
-      </c>
-      <c r="M29" s="143">
-        <f>M24*($I$29/$I$24)</f>
-        <v/>
-      </c>
-      <c r="N29" s="143">
-        <f>N24*($I$29/$I$24)</f>
+      <c r="J29" s="145">
+        <f>J24*J10</f>
+        <v/>
+      </c>
+      <c r="K29" s="145">
+        <f>K24*K10</f>
+        <v/>
+      </c>
+      <c r="L29" s="145">
+        <f>L24*L10</f>
+        <v/>
+      </c>
+      <c r="M29" s="145">
+        <f>M24*M10</f>
+        <v/>
+      </c>
+      <c r="N29" s="145">
+        <f>N24*N10</f>
         <v/>
       </c>
     </row>
@@ -3784,6 +3778,10 @@
           <t>Depreciation &amp; Amortization</t>
         </is>
       </c>
+      <c r="C30" s="144">
+        <f> PPE_open × DA%</f>
+        <v/>
+      </c>
       <c r="E30" s="148" t="n">
         <v>25592</v>
       </c>
@@ -3799,24 +3797,24 @@
       <c r="I30" s="148" t="n">
         <v>14952</v>
       </c>
-      <c r="J30" s="150">
-        <f>J94</f>
-        <v/>
-      </c>
-      <c r="K30" s="150">
-        <f>K94</f>
-        <v/>
-      </c>
-      <c r="L30" s="150">
-        <f>L94</f>
-        <v/>
-      </c>
-      <c r="M30" s="150">
-        <f>M94</f>
-        <v/>
-      </c>
-      <c r="N30" s="150">
-        <f>N94</f>
+      <c r="J30" s="145">
+        <f>J92*J11</f>
+        <v/>
+      </c>
+      <c r="K30" s="145">
+        <f>K92*K11</f>
+        <v/>
+      </c>
+      <c r="L30" s="145">
+        <f>L92*L11</f>
+        <v/>
+      </c>
+      <c r="M30" s="145">
+        <f>M92*M11</f>
+        <v/>
+      </c>
+      <c r="N30" s="145">
+        <f>N92*N11</f>
         <v/>
       </c>
     </row>
@@ -3826,7 +3824,10 @@
           <t>Interest</t>
         </is>
       </c>
-      <c r="C31" s="2" t="n"/>
+      <c r="C31" s="151">
+        <f> Debt_open × Int%</f>
+        <v/>
+      </c>
       <c r="D31" s="24" t="n"/>
       <c r="E31" s="152" t="n">
         <v>40092</v>
@@ -3843,24 +3844,24 @@
       <c r="I31" s="152" t="n">
         <v>133647</v>
       </c>
-      <c r="J31" s="153">
-        <f>J101</f>
-        <v/>
-      </c>
-      <c r="K31" s="153">
-        <f>K101</f>
-        <v/>
-      </c>
-      <c r="L31" s="153">
-        <f>L101</f>
-        <v/>
-      </c>
-      <c r="M31" s="153">
-        <f>M101</f>
-        <v/>
-      </c>
-      <c r="N31" s="153">
-        <f>N101</f>
+      <c r="J31" s="145">
+        <f>J98*J12</f>
+        <v/>
+      </c>
+      <c r="K31" s="145">
+        <f>K98*K12</f>
+        <v/>
+      </c>
+      <c r="L31" s="145">
+        <f>L98*L12</f>
+        <v/>
+      </c>
+      <c r="M31" s="145">
+        <f>M98*M12</f>
+        <v/>
+      </c>
+      <c r="N31" s="145">
+        <f>N98*N12</f>
         <v/>
       </c>
     </row>
@@ -3872,43 +3873,43 @@
       </c>
       <c r="C32" s="19" t="n"/>
       <c r="D32" s="47" t="n"/>
-      <c r="E32" s="154">
+      <c r="E32" s="153">
         <f>SUM(E28:E31)</f>
         <v/>
       </c>
-      <c r="F32" s="154">
+      <c r="F32" s="153">
         <f>SUM(F28:F31)</f>
         <v/>
       </c>
-      <c r="G32" s="154">
+      <c r="G32" s="153">
         <f>SUM(G28:G31)</f>
         <v/>
       </c>
-      <c r="H32" s="154">
+      <c r="H32" s="153">
         <f>SUM(H28:H31)</f>
         <v/>
       </c>
-      <c r="I32" s="154">
+      <c r="I32" s="153">
         <f>SUM(I28:I31)</f>
         <v/>
       </c>
-      <c r="J32" s="154">
+      <c r="J32" s="145">
         <f>SUM(J28:J31)</f>
         <v/>
       </c>
-      <c r="K32" s="154">
+      <c r="K32" s="145">
         <f>SUM(K28:K31)</f>
         <v/>
       </c>
-      <c r="L32" s="154">
+      <c r="L32" s="145">
         <f>SUM(L28:L31)</f>
         <v/>
       </c>
-      <c r="M32" s="154">
+      <c r="M32" s="145">
         <f>SUM(M28:M31)</f>
         <v/>
       </c>
-      <c r="N32" s="154">
+      <c r="N32" s="145">
         <f>SUM(N28:N31)</f>
         <v/>
       </c>
@@ -3919,45 +3920,48 @@
           <t>Earnings Before Tax</t>
         </is>
       </c>
-      <c r="C33" s="4" t="n"/>
+      <c r="C33" s="149">
+        <f> GP − Expenses</f>
+        <v/>
+      </c>
       <c r="D33" s="22" t="n"/>
-      <c r="E33" s="151">
+      <c r="E33" s="150">
         <f>E26-E32</f>
         <v/>
       </c>
-      <c r="F33" s="151">
+      <c r="F33" s="150">
         <f>F26-F32</f>
         <v/>
       </c>
-      <c r="G33" s="151">
+      <c r="G33" s="150">
         <f>G26-G32</f>
         <v/>
       </c>
-      <c r="H33" s="151">
+      <c r="H33" s="150">
         <f>H26-H32</f>
         <v/>
       </c>
-      <c r="I33" s="151">
+      <c r="I33" s="150">
         <f>I26-I32</f>
         <v/>
       </c>
-      <c r="J33" s="151">
+      <c r="J33" s="145">
         <f>J26-J32</f>
         <v/>
       </c>
-      <c r="K33" s="151">
+      <c r="K33" s="145">
         <f>K26-K32</f>
         <v/>
       </c>
-      <c r="L33" s="151">
+      <c r="L33" s="145">
         <f>L26-L32</f>
         <v/>
       </c>
-      <c r="M33" s="151">
+      <c r="M33" s="145">
         <f>M26-M32</f>
         <v/>
       </c>
-      <c r="N33" s="151">
+      <c r="N33" s="145">
         <f>N26-N32</f>
         <v/>
       </c>
@@ -3983,7 +3987,10 @@
           <t>Taxes</t>
         </is>
       </c>
-      <c r="C35" s="19" t="n"/>
+      <c r="C35" s="140">
+        <f> EBT × tax%</f>
+        <v/>
+      </c>
       <c r="D35" s="47" t="n"/>
       <c r="E35" s="148" t="n">
         <v>81058</v>
@@ -4000,23 +4007,23 @@
       <c r="I35" s="148" t="n">
         <v>150649</v>
       </c>
-      <c r="J35" s="150">
+      <c r="J35" s="145">
         <f>J33*J13</f>
         <v/>
       </c>
-      <c r="K35" s="150">
+      <c r="K35" s="145">
         <f>K33*K13</f>
         <v/>
       </c>
-      <c r="L35" s="150">
+      <c r="L35" s="145">
         <f>L33*L13</f>
         <v/>
       </c>
-      <c r="M35" s="150">
+      <c r="M35" s="145">
         <f>M33*M13</f>
         <v/>
       </c>
-      <c r="N35" s="150">
+      <c r="N35" s="145">
         <f>N33*N13</f>
         <v/>
       </c>
@@ -4027,49 +4034,49 @@
           <t>Net Earnings</t>
         </is>
       </c>
-      <c r="C36" s="155">
-        <f>EBT−Tax  ← GROWS via Rev×(1+g) in row 24</f>
+      <c r="C36" s="154">
+        <f> EBT × (1 − tax%)   ← grows with Rev×(1+g)</f>
         <v/>
       </c>
       <c r="D36" s="40" t="n"/>
-      <c r="E36" s="156">
+      <c r="E36" s="155">
         <f>E33-E35</f>
         <v/>
       </c>
-      <c r="F36" s="156">
+      <c r="F36" s="155">
         <f>F33-F35</f>
         <v/>
       </c>
-      <c r="G36" s="156">
+      <c r="G36" s="155">
         <f>G33-G35</f>
         <v/>
       </c>
-      <c r="H36" s="156">
+      <c r="H36" s="155">
         <f>H33-H35</f>
         <v/>
       </c>
-      <c r="I36" s="156">
+      <c r="I36" s="155">
         <f>I33-I35</f>
         <v/>
       </c>
-      <c r="J36" s="156">
-        <f>J33-J35</f>
-        <v/>
-      </c>
-      <c r="K36" s="156">
-        <f>K33-K35</f>
-        <v/>
-      </c>
-      <c r="L36" s="156">
-        <f>L33-L35</f>
-        <v/>
-      </c>
-      <c r="M36" s="156">
-        <f>M33-M35</f>
-        <v/>
-      </c>
-      <c r="N36" s="156">
-        <f>N33-N35</f>
+      <c r="J36" s="145">
+        <f>J33*(1-J13)</f>
+        <v/>
+      </c>
+      <c r="K36" s="145">
+        <f>K33*(1-K13)</f>
+        <v/>
+      </c>
+      <c r="L36" s="145">
+        <f>L33*(1-L13)</f>
+        <v/>
+      </c>
+      <c r="M36" s="145">
+        <f>M33*(1-M13)</f>
+        <v/>
+      </c>
+      <c r="N36" s="145">
+        <f>N33*(1-N13)</f>
         <v/>
       </c>
     </row>
@@ -4144,23 +4151,23 @@
       <c r="I41" s="148" t="n">
         <v>134136</v>
       </c>
-      <c r="J41" s="150">
+      <c r="J41" s="145">
         <f>J78</f>
         <v/>
       </c>
-      <c r="K41" s="150">
+      <c r="K41" s="145">
         <f>K78</f>
         <v/>
       </c>
-      <c r="L41" s="150">
+      <c r="L41" s="145">
         <f>L78</f>
         <v/>
       </c>
-      <c r="M41" s="150">
+      <c r="M41" s="145">
         <f>M78</f>
         <v/>
       </c>
-      <c r="N41" s="150">
+      <c r="N41" s="145">
         <f>N78</f>
         <v/>
       </c>
@@ -4171,6 +4178,10 @@
           <t>Accounts Receivable</t>
         </is>
       </c>
+      <c r="C42" s="144">
+        <f> Rev × AR_days / 365</f>
+        <v/>
+      </c>
       <c r="E42" s="148" t="n">
         <v>206690</v>
       </c>
@@ -4186,23 +4197,23 @@
       <c r="I42" s="148" t="n">
         <v>341776</v>
       </c>
-      <c r="J42" s="150">
+      <c r="J42" s="145">
         <f>J24*J15/365</f>
         <v/>
       </c>
-      <c r="K42" s="150">
+      <c r="K42" s="145">
         <f>K24*K15/365</f>
         <v/>
       </c>
-      <c r="L42" s="150">
+      <c r="L42" s="145">
         <f>L24*L15/365</f>
         <v/>
       </c>
-      <c r="M42" s="150">
+      <c r="M42" s="145">
         <f>M24*M15/365</f>
         <v/>
       </c>
-      <c r="N42" s="150">
+      <c r="N42" s="145">
         <f>N24*N15/365</f>
         <v/>
       </c>
@@ -4228,23 +4239,23 @@
       <c r="I43" s="148" t="n">
         <v>0</v>
       </c>
-      <c r="J43" s="150">
+      <c r="J43" s="145">
         <f>J25*J16/365</f>
         <v/>
       </c>
-      <c r="K43" s="150">
+      <c r="K43" s="145">
         <f>K25*K16/365</f>
         <v/>
       </c>
-      <c r="L43" s="150">
+      <c r="L43" s="145">
         <f>L25*L16/365</f>
         <v/>
       </c>
-      <c r="M43" s="150">
+      <c r="M43" s="145">
         <f>M25*M16/365</f>
         <v/>
       </c>
-      <c r="N43" s="150">
+      <c r="N43" s="145">
         <f>N25*N16/365</f>
         <v/>
       </c>
@@ -4270,23 +4281,23 @@
       <c r="I44" s="148" t="n">
         <v>67713</v>
       </c>
-      <c r="J44" s="150">
+      <c r="J44" s="145">
         <f>J95</f>
         <v/>
       </c>
-      <c r="K44" s="150">
+      <c r="K44" s="145">
         <f>K95</f>
         <v/>
       </c>
-      <c r="L44" s="150">
+      <c r="L44" s="145">
         <f>L95</f>
         <v/>
       </c>
-      <c r="M44" s="150">
+      <c r="M44" s="145">
         <f>M95</f>
         <v/>
       </c>
-      <c r="N44" s="150">
+      <c r="N44" s="145">
         <f>N95</f>
         <v/>
       </c>
@@ -4299,43 +4310,43 @@
       </c>
       <c r="C45" s="39" t="n"/>
       <c r="D45" s="40" t="n"/>
-      <c r="E45" s="156">
+      <c r="E45" s="155">
         <f>SUM(E41:E44)</f>
         <v/>
       </c>
-      <c r="F45" s="156">
+      <c r="F45" s="155">
         <f>SUM(F41:F44)</f>
         <v/>
       </c>
-      <c r="G45" s="156">
+      <c r="G45" s="155">
         <f>SUM(G41:G44)</f>
         <v/>
       </c>
-      <c r="H45" s="156">
+      <c r="H45" s="155">
         <f>SUM(H41:H44)</f>
         <v/>
       </c>
-      <c r="I45" s="156">
+      <c r="I45" s="155">
         <f>SUM(I41:I44)</f>
         <v/>
       </c>
-      <c r="J45" s="156">
+      <c r="J45" s="145">
         <f>SUM(J41:J44)</f>
         <v/>
       </c>
-      <c r="K45" s="156">
+      <c r="K45" s="145">
         <f>SUM(K41:K44)</f>
         <v/>
       </c>
-      <c r="L45" s="156">
+      <c r="L45" s="145">
         <f>SUM(L41:L44)</f>
         <v/>
       </c>
-      <c r="M45" s="156">
+      <c r="M45" s="145">
         <f>SUM(M41:M44)</f>
         <v/>
       </c>
-      <c r="N45" s="156">
+      <c r="N45" s="145">
         <f>SUM(N41:N44)</f>
         <v/>
       </c>
@@ -4373,6 +4384,10 @@
           <t>Accounts Payable</t>
         </is>
       </c>
+      <c r="C48" s="144">
+        <f> COGS × AP_days / 365</f>
+        <v/>
+      </c>
       <c r="E48" s="148" t="n">
         <v>20749</v>
       </c>
@@ -4388,23 +4403,23 @@
       <c r="I48" s="148" t="n">
         <v>32315</v>
       </c>
-      <c r="J48" s="150">
+      <c r="J48" s="145">
         <f>J25*J17/365</f>
         <v/>
       </c>
-      <c r="K48" s="150">
+      <c r="K48" s="145">
         <f>K25*K17/365</f>
         <v/>
       </c>
-      <c r="L48" s="150">
+      <c r="L48" s="145">
         <f>L25*L17/365</f>
         <v/>
       </c>
-      <c r="M48" s="150">
+      <c r="M48" s="145">
         <f>M25*M17/365</f>
         <v/>
       </c>
-      <c r="N48" s="150">
+      <c r="N48" s="145">
         <f>N25*N17/365</f>
         <v/>
       </c>
@@ -4430,23 +4445,23 @@
       <c r="I49" s="148" t="n">
         <v>3055691</v>
       </c>
-      <c r="J49" s="150">
+      <c r="J49" s="145">
         <f>J100</f>
         <v/>
       </c>
-      <c r="K49" s="150">
+      <c r="K49" s="145">
         <f>K100</f>
         <v/>
       </c>
-      <c r="L49" s="150">
+      <c r="L49" s="145">
         <f>L100</f>
         <v/>
       </c>
-      <c r="M49" s="150">
+      <c r="M49" s="145">
         <f>M100</f>
         <v/>
       </c>
-      <c r="N49" s="150">
+      <c r="N49" s="145">
         <f>N100</f>
         <v/>
       </c>
@@ -4459,43 +4474,43 @@
       </c>
       <c r="C50" s="4" t="n"/>
       <c r="D50" s="22" t="n"/>
-      <c r="E50" s="151">
+      <c r="E50" s="150">
         <f>SUM(E48:E49)</f>
         <v/>
       </c>
-      <c r="F50" s="151">
+      <c r="F50" s="150">
         <f>SUM(F48:F49)</f>
         <v/>
       </c>
-      <c r="G50" s="151">
+      <c r="G50" s="150">
         <f>SUM(G48:G49)</f>
         <v/>
       </c>
-      <c r="H50" s="151">
+      <c r="H50" s="150">
         <f>SUM(H48:H49)</f>
         <v/>
       </c>
-      <c r="I50" s="151">
+      <c r="I50" s="150">
         <f>SUM(I48:I49)</f>
         <v/>
       </c>
-      <c r="J50" s="151">
+      <c r="J50" s="145">
         <f>SUM(J48:J49)</f>
         <v/>
       </c>
-      <c r="K50" s="151">
+      <c r="K50" s="145">
         <f>SUM(K48:K49)</f>
         <v/>
       </c>
-      <c r="L50" s="151">
+      <c r="L50" s="145">
         <f>SUM(L48:L49)</f>
         <v/>
       </c>
-      <c r="M50" s="151">
+      <c r="M50" s="145">
         <f>SUM(M48:M49)</f>
         <v/>
       </c>
-      <c r="N50" s="151">
+      <c r="N50" s="145">
         <f>SUM(N48:N49)</f>
         <v/>
       </c>
@@ -4533,23 +4548,23 @@
       <c r="I52" s="148" t="n">
         <v>-2544381</v>
       </c>
-      <c r="J52" s="150">
+      <c r="J52" s="145">
         <f>I52+J20</f>
         <v/>
       </c>
-      <c r="K52" s="150">
+      <c r="K52" s="145">
         <f>J52+K20</f>
         <v/>
       </c>
-      <c r="L52" s="150">
+      <c r="L52" s="145">
         <f>K52+L20</f>
         <v/>
       </c>
-      <c r="M52" s="150">
+      <c r="M52" s="145">
         <f>L52+M20</f>
         <v/>
       </c>
-      <c r="N52" s="150">
+      <c r="N52" s="145">
         <f>M52+N20</f>
         <v/>
       </c>
@@ -4560,6 +4575,10 @@
           <t>Retained Earnings</t>
         </is>
       </c>
+      <c r="C53" s="144">
+        <f> PriorRE + EBT×(1−t)</f>
+        <v/>
+      </c>
       <c r="E53" s="148" t="n">
         <v>0</v>
       </c>
@@ -4575,24 +4594,24 @@
       <c r="I53" s="148" t="n">
         <v>0</v>
       </c>
-      <c r="J53" s="150">
-        <f>I53+J36</f>
-        <v/>
-      </c>
-      <c r="K53" s="150">
-        <f>J53+K36</f>
-        <v/>
-      </c>
-      <c r="L53" s="150">
-        <f>K53+L36</f>
-        <v/>
-      </c>
-      <c r="M53" s="150">
-        <f>L53+M36</f>
-        <v/>
-      </c>
-      <c r="N53" s="150">
-        <f>M53+N36</f>
+      <c r="J53" s="145">
+        <f>I53+J33*(1-J13)</f>
+        <v/>
+      </c>
+      <c r="K53" s="145">
+        <f>J53+K33*(1-K13)</f>
+        <v/>
+      </c>
+      <c r="L53" s="145">
+        <f>K53+L33*(1-L13)</f>
+        <v/>
+      </c>
+      <c r="M53" s="145">
+        <f>L53+M33*(1-M13)</f>
+        <v/>
+      </c>
+      <c r="N53" s="145">
+        <f>M53+N33*(1-N13)</f>
         <v/>
       </c>
     </row>
@@ -4604,43 +4623,43 @@
       </c>
       <c r="C54" s="8" t="n"/>
       <c r="D54" s="26" t="n"/>
-      <c r="E54" s="157">
+      <c r="E54" s="156">
         <f>SUM(E52:E53)</f>
         <v/>
       </c>
-      <c r="F54" s="157">
+      <c r="F54" s="156">
         <f>SUM(F52:F53)</f>
         <v/>
       </c>
-      <c r="G54" s="157">
+      <c r="G54" s="156">
         <f>SUM(G52:G53)</f>
         <v/>
       </c>
-      <c r="H54" s="157">
+      <c r="H54" s="156">
         <f>SUM(H52:H53)</f>
         <v/>
       </c>
-      <c r="I54" s="157">
+      <c r="I54" s="156">
         <f>SUM(I52:I53)</f>
         <v/>
       </c>
-      <c r="J54" s="157">
+      <c r="J54" s="145">
         <f>SUM(J52:J53)</f>
         <v/>
       </c>
-      <c r="K54" s="157">
+      <c r="K54" s="145">
         <f>SUM(K52:K53)</f>
         <v/>
       </c>
-      <c r="L54" s="157">
+      <c r="L54" s="145">
         <f>SUM(L52:L53)</f>
         <v/>
       </c>
-      <c r="M54" s="157">
+      <c r="M54" s="145">
         <f>SUM(M52:M53)</f>
         <v/>
       </c>
-      <c r="N54" s="157">
+      <c r="N54" s="145">
         <f>SUM(N52:N53)</f>
         <v/>
       </c>
@@ -4653,43 +4672,43 @@
       </c>
       <c r="C55" s="39" t="n"/>
       <c r="D55" s="40" t="n"/>
-      <c r="E55" s="156">
+      <c r="E55" s="155">
         <f>E50+E54</f>
         <v/>
       </c>
-      <c r="F55" s="156">
+      <c r="F55" s="155">
         <f>F50+F54</f>
         <v/>
       </c>
-      <c r="G55" s="156">
+      <c r="G55" s="155">
         <f>G50+G54</f>
         <v/>
       </c>
-      <c r="H55" s="156">
+      <c r="H55" s="155">
         <f>H50+H54</f>
         <v/>
       </c>
-      <c r="I55" s="156">
+      <c r="I55" s="155">
         <f>I50+I54</f>
         <v/>
       </c>
-      <c r="J55" s="156">
+      <c r="J55" s="145">
         <f>J50+J54</f>
         <v/>
       </c>
-      <c r="K55" s="156">
+      <c r="K55" s="145">
         <f>K50+K54</f>
         <v/>
       </c>
-      <c r="L55" s="156">
+      <c r="L55" s="145">
         <f>L50+L54</f>
         <v/>
       </c>
-      <c r="M55" s="156">
+      <c r="M55" s="145">
         <f>M50+M54</f>
         <v/>
       </c>
-      <c r="N55" s="156">
+      <c r="N55" s="145">
         <f>N50+N54</f>
         <v/>
       </c>
@@ -4714,43 +4733,43 @@
       </c>
       <c r="C57" s="9" t="n"/>
       <c r="D57" s="27" t="n"/>
-      <c r="E57" s="158">
+      <c r="E57" s="157">
         <f>E55-E45</f>
         <v/>
       </c>
-      <c r="F57" s="158">
+      <c r="F57" s="157">
         <f>F55-F45</f>
         <v/>
       </c>
-      <c r="G57" s="158">
+      <c r="G57" s="157">
         <f>G55-G45</f>
         <v/>
       </c>
-      <c r="H57" s="158">
+      <c r="H57" s="157">
         <f>H55-H45</f>
         <v/>
       </c>
-      <c r="I57" s="158">
+      <c r="I57" s="157">
         <f>I55-I45</f>
         <v/>
       </c>
-      <c r="J57" s="158">
+      <c r="J57" s="145">
         <f>J55-J45</f>
         <v/>
       </c>
-      <c r="K57" s="158">
+      <c r="K57" s="145">
         <f>K55-K45</f>
         <v/>
       </c>
-      <c r="L57" s="158">
+      <c r="L57" s="145">
         <f>L55-L45</f>
         <v/>
       </c>
-      <c r="M57" s="158">
+      <c r="M57" s="145">
         <f>M55-M45</f>
         <v/>
       </c>
-      <c r="N57" s="158">
+      <c r="N57" s="145">
         <f>N55-N45</f>
         <v/>
       </c>
@@ -4815,47 +4834,47 @@
         </is>
       </c>
       <c r="C62" s="144">
-        <f>IS Net Earnings (row 36) — not hardcoded</f>
-        <v/>
-      </c>
-      <c r="E62" s="150">
+        <f> EBT × (1 − tax%)     ← FULL eqn, not =J36</f>
+        <v/>
+      </c>
+      <c r="E62" s="158">
         <f>E36</f>
         <v/>
       </c>
-      <c r="F62" s="150">
+      <c r="F62" s="158">
         <f>F36</f>
         <v/>
       </c>
-      <c r="G62" s="150">
+      <c r="G62" s="158">
         <f>G36</f>
         <v/>
       </c>
-      <c r="H62" s="150">
+      <c r="H62" s="158">
         <f>H36</f>
         <v/>
       </c>
-      <c r="I62" s="150">
+      <c r="I62" s="158">
         <f>I36</f>
         <v/>
       </c>
-      <c r="J62" s="143">
-        <f>J36</f>
-        <v/>
-      </c>
-      <c r="K62" s="143">
-        <f>K36</f>
-        <v/>
-      </c>
-      <c r="L62" s="143">
-        <f>L36</f>
-        <v/>
-      </c>
-      <c r="M62" s="143">
-        <f>M36</f>
-        <v/>
-      </c>
-      <c r="N62" s="143">
-        <f>N36</f>
+      <c r="J62" s="145">
+        <f>J33*(1-J13)</f>
+        <v/>
+      </c>
+      <c r="K62" s="145">
+        <f>K33*(1-K13)</f>
+        <v/>
+      </c>
+      <c r="L62" s="145">
+        <f>L33*(1-L13)</f>
+        <v/>
+      </c>
+      <c r="M62" s="145">
+        <f>M33*(1-M13)</f>
+        <v/>
+      </c>
+      <c r="N62" s="145">
+        <f>N33*(1-N13)</f>
         <v/>
       </c>
     </row>
@@ -4865,44 +4884,48 @@
           <t>Plus: Depreciation &amp; Amortization</t>
         </is>
       </c>
-      <c r="E63" s="150">
+      <c r="C63" s="144">
+        <f> PPE_open × DA%</f>
+        <v/>
+      </c>
+      <c r="E63" s="158">
         <f>+E30</f>
         <v/>
       </c>
-      <c r="F63" s="150">
+      <c r="F63" s="158">
         <f>+F30</f>
         <v/>
       </c>
-      <c r="G63" s="150">
+      <c r="G63" s="158">
         <f>+G30</f>
         <v/>
       </c>
-      <c r="H63" s="150">
+      <c r="H63" s="158">
         <f>+H30</f>
         <v/>
       </c>
-      <c r="I63" s="150">
+      <c r="I63" s="158">
         <f>+I30</f>
         <v/>
       </c>
-      <c r="J63" s="143">
-        <f>J30</f>
-        <v/>
-      </c>
-      <c r="K63" s="143">
-        <f>K30</f>
-        <v/>
-      </c>
-      <c r="L63" s="143">
-        <f>L30</f>
-        <v/>
-      </c>
-      <c r="M63" s="143">
-        <f>M30</f>
-        <v/>
-      </c>
-      <c r="N63" s="143">
-        <f>N30</f>
+      <c r="J63" s="145">
+        <f>J92*J11</f>
+        <v/>
+      </c>
+      <c r="K63" s="145">
+        <f>K92*K11</f>
+        <v/>
+      </c>
+      <c r="L63" s="145">
+        <f>L92*L11</f>
+        <v/>
+      </c>
+      <c r="M63" s="145">
+        <f>M92*M11</f>
+        <v/>
+      </c>
+      <c r="N63" s="145">
+        <f>N92*N11</f>
         <v/>
       </c>
     </row>
@@ -4912,6 +4935,10 @@
           <t>Less: Changes in Working Capital</t>
         </is>
       </c>
+      <c r="C64" s="144">
+        <f> NWC_t − NWC_t−1</f>
+        <v/>
+      </c>
       <c r="E64" s="148" t="n">
         <v>0</v>
       </c>
@@ -4927,24 +4954,24 @@
       <c r="I64" s="148" t="n">
         <v>62189</v>
       </c>
-      <c r="J64" s="150">
-        <f>J89</f>
-        <v/>
-      </c>
-      <c r="K64" s="150">
-        <f>K89</f>
-        <v/>
-      </c>
-      <c r="L64" s="150">
-        <f>L89</f>
-        <v/>
-      </c>
-      <c r="M64" s="150">
-        <f>M89</f>
-        <v/>
-      </c>
-      <c r="N64" s="150">
-        <f>N89</f>
+      <c r="J64" s="145">
+        <f>J88-I88</f>
+        <v/>
+      </c>
+      <c r="K64" s="145">
+        <f>K88-J88</f>
+        <v/>
+      </c>
+      <c r="L64" s="145">
+        <f>L88-K88</f>
+        <v/>
+      </c>
+      <c r="M64" s="145">
+        <f>M88-L88</f>
+        <v/>
+      </c>
+      <c r="N64" s="145">
+        <f>N88-M88</f>
         <v/>
       </c>
     </row>
@@ -4954,46 +4981,49 @@
           <t>Cash from Operations</t>
         </is>
       </c>
-      <c r="C65" s="5" t="n"/>
+      <c r="C65" s="149">
+        <f> NI + DA − ΔNWC</f>
+        <v/>
+      </c>
       <c r="D65" s="28" t="n"/>
-      <c r="E65" s="151">
+      <c r="E65" s="150">
         <f>E62+E63-E64</f>
         <v/>
       </c>
-      <c r="F65" s="151">
+      <c r="F65" s="150">
         <f>F62+F63-F64</f>
         <v/>
       </c>
-      <c r="G65" s="151">
+      <c r="G65" s="150">
         <f>G62+G63-G64</f>
         <v/>
       </c>
-      <c r="H65" s="151">
+      <c r="H65" s="150">
         <f>H62+H63-H64</f>
         <v/>
       </c>
-      <c r="I65" s="151">
+      <c r="I65" s="150">
         <f>I62+I63-I64</f>
         <v/>
       </c>
-      <c r="J65" s="143">
-        <f>J62+J63-J64</f>
-        <v/>
-      </c>
-      <c r="K65" s="143">
-        <f>K62+K63-K64</f>
-        <v/>
-      </c>
-      <c r="L65" s="143">
-        <f>L62+L63-L64</f>
-        <v/>
-      </c>
-      <c r="M65" s="143">
-        <f>M62+M63-M64</f>
-        <v/>
-      </c>
-      <c r="N65" s="143">
-        <f>N62+N63-N64</f>
+      <c r="J65" s="145">
+        <f>J33*(1-J13)+J92*J11-(J88-I88)</f>
+        <v/>
+      </c>
+      <c r="K65" s="145">
+        <f>K33*(1-K13)+K92*K11-(K88-J88)</f>
+        <v/>
+      </c>
+      <c r="L65" s="145">
+        <f>L33*(1-L13)+L92*L11-(L88-K88)</f>
+        <v/>
+      </c>
+      <c r="M65" s="145">
+        <f>M33*(1-M13)+M92*M11-(M88-L88)</f>
+        <v/>
+      </c>
+      <c r="N65" s="145">
+        <f>N33*(1-N13)+N92*N11-(N88-M88)</f>
         <v/>
       </c>
     </row>
@@ -5035,6 +5065,10 @@
           <t>Investments in Property &amp; Equipment</t>
         </is>
       </c>
+      <c r="C68" s="144">
+        <f> Rev × CapEx%</f>
+        <v/>
+      </c>
       <c r="E68" s="148" t="n">
         <v>7569</v>
       </c>
@@ -5050,24 +5084,24 @@
       <c r="I68" s="148" t="n">
         <v>39407</v>
       </c>
-      <c r="J68" s="150">
-        <f>J18</f>
-        <v/>
-      </c>
-      <c r="K68" s="150">
-        <f>K18</f>
-        <v/>
-      </c>
-      <c r="L68" s="150">
-        <f>L18</f>
-        <v/>
-      </c>
-      <c r="M68" s="150">
-        <f>M18</f>
-        <v/>
-      </c>
-      <c r="N68" s="150">
-        <f>N18</f>
+      <c r="J68" s="145">
+        <f>J24*J18</f>
+        <v/>
+      </c>
+      <c r="K68" s="145">
+        <f>K24*K18</f>
+        <v/>
+      </c>
+      <c r="L68" s="145">
+        <f>L24*L18</f>
+        <v/>
+      </c>
+      <c r="M68" s="145">
+        <f>M24*M18</f>
+        <v/>
+      </c>
+      <c r="N68" s="145">
+        <f>N24*N18</f>
         <v/>
       </c>
     </row>
@@ -5079,44 +5113,44 @@
       </c>
       <c r="C69" s="5" t="n"/>
       <c r="D69" s="28" t="n"/>
-      <c r="E69" s="151">
+      <c r="E69" s="150">
         <f>SUM(E68)</f>
         <v/>
       </c>
-      <c r="F69" s="151">
+      <c r="F69" s="150">
         <f>SUM(F68)</f>
         <v/>
       </c>
-      <c r="G69" s="151">
+      <c r="G69" s="150">
         <f>SUM(G68)</f>
         <v/>
       </c>
-      <c r="H69" s="151">
+      <c r="H69" s="150">
         <f>SUM(H68)</f>
         <v/>
       </c>
-      <c r="I69" s="151">
+      <c r="I69" s="150">
         <f>SUM(I68)</f>
         <v/>
       </c>
-      <c r="J69" s="151">
-        <f>SUM(J68)</f>
-        <v/>
-      </c>
-      <c r="K69" s="151">
-        <f>SUM(K68)</f>
-        <v/>
-      </c>
-      <c r="L69" s="151">
-        <f>SUM(L68)</f>
-        <v/>
-      </c>
-      <c r="M69" s="151">
-        <f>SUM(M68)</f>
-        <v/>
-      </c>
-      <c r="N69" s="151">
-        <f>SUM(N68)</f>
+      <c r="J69" s="145">
+        <f>J68</f>
+        <v/>
+      </c>
+      <c r="K69" s="145">
+        <f>K68</f>
+        <v/>
+      </c>
+      <c r="L69" s="145">
+        <f>L68</f>
+        <v/>
+      </c>
+      <c r="M69" s="145">
+        <f>M68</f>
+        <v/>
+      </c>
+      <c r="N69" s="145">
+        <f>N68</f>
         <v/>
       </c>
     </row>
@@ -5173,23 +5207,23 @@
       <c r="I72" s="148" t="n">
         <v>846670</v>
       </c>
-      <c r="J72" s="150">
+      <c r="J72" s="145">
         <f>J19</f>
         <v/>
       </c>
-      <c r="K72" s="150">
+      <c r="K72" s="145">
         <f>K19</f>
         <v/>
       </c>
-      <c r="L72" s="150">
+      <c r="L72" s="145">
         <f>L19</f>
         <v/>
       </c>
-      <c r="M72" s="150">
+      <c r="M72" s="145">
         <f>M19</f>
         <v/>
       </c>
-      <c r="N72" s="150">
+      <c r="N72" s="145">
         <f>N19</f>
         <v/>
       </c>
@@ -5215,23 +5249,23 @@
       <c r="I73" s="148" t="n">
         <v>0</v>
       </c>
-      <c r="J73" s="150">
+      <c r="J73" s="145">
         <f>J20</f>
         <v/>
       </c>
-      <c r="K73" s="150">
+      <c r="K73" s="145">
         <f>K20</f>
         <v/>
       </c>
-      <c r="L73" s="150">
+      <c r="L73" s="145">
         <f>L20</f>
         <v/>
       </c>
-      <c r="M73" s="150">
+      <c r="M73" s="145">
         <f>M20</f>
         <v/>
       </c>
-      <c r="N73" s="150">
+      <c r="N73" s="145">
         <f>N20</f>
         <v/>
       </c>
@@ -5244,44 +5278,44 @@
       </c>
       <c r="C74" s="5" t="n"/>
       <c r="D74" s="28" t="n"/>
-      <c r="E74" s="151">
+      <c r="E74" s="150">
         <f>SUM(E72:E73)</f>
         <v/>
       </c>
-      <c r="F74" s="151">
+      <c r="F74" s="150">
         <f>SUM(F72:F73)</f>
         <v/>
       </c>
-      <c r="G74" s="151">
+      <c r="G74" s="150">
         <f>SUM(G72:G73)</f>
         <v/>
       </c>
-      <c r="H74" s="151">
+      <c r="H74" s="150">
         <f>SUM(H72:H73)</f>
         <v/>
       </c>
-      <c r="I74" s="151">
+      <c r="I74" s="150">
         <f>SUM(I72:I73)</f>
         <v/>
       </c>
-      <c r="J74" s="151">
-        <f>SUM(J72:J73)</f>
-        <v/>
-      </c>
-      <c r="K74" s="151">
-        <f>SUM(K72:K73)</f>
-        <v/>
-      </c>
-      <c r="L74" s="151">
-        <f>SUM(L72:L73)</f>
-        <v/>
-      </c>
-      <c r="M74" s="151">
-        <f>SUM(M72:M73)</f>
-        <v/>
-      </c>
-      <c r="N74" s="151">
-        <f>SUM(N72:N73)</f>
+      <c r="J74" s="145">
+        <f>J19+J20</f>
+        <v/>
+      </c>
+      <c r="K74" s="145">
+        <f>K19+K20</f>
+        <v/>
+      </c>
+      <c r="L74" s="145">
+        <f>L19+L20</f>
+        <v/>
+      </c>
+      <c r="M74" s="145">
+        <f>M19+M20</f>
+        <v/>
+      </c>
+      <c r="N74" s="145">
+        <f>N19+N20</f>
         <v/>
       </c>
     </row>
@@ -5306,6 +5340,10 @@
           <t>Net Increase (decrease) in Cash</t>
         </is>
       </c>
+      <c r="C76" s="144">
+        <f> CFO + CFI + CFF</f>
+        <v/>
+      </c>
       <c r="E76" s="159">
         <f>E41-E77</f>
         <v/>
@@ -5326,23 +5364,23 @@
         <f>I41-I77</f>
         <v/>
       </c>
-      <c r="J76" s="142">
+      <c r="J76" s="145">
         <f>J65-J69+J74</f>
         <v/>
       </c>
-      <c r="K76" s="142">
+      <c r="K76" s="145">
         <f>K65-K69+K74</f>
         <v/>
       </c>
-      <c r="L76" s="142">
+      <c r="L76" s="145">
         <f>L65-L69+L74</f>
         <v/>
       </c>
-      <c r="M76" s="142">
+      <c r="M76" s="145">
         <f>M65-M69+M74</f>
         <v/>
       </c>
-      <c r="N76" s="142">
+      <c r="N76" s="145">
         <f>N65-N69+N74</f>
         <v/>
       </c>
@@ -5372,24 +5410,24 @@
         <f>H41</f>
         <v/>
       </c>
-      <c r="J77" s="159">
+      <c r="J77" s="145">
         <f>I41</f>
         <v/>
       </c>
-      <c r="K77" s="159">
-        <f>J78</f>
-        <v/>
-      </c>
-      <c r="L77" s="159">
-        <f>K78</f>
-        <v/>
-      </c>
-      <c r="M77" s="159">
-        <f>L78</f>
-        <v/>
-      </c>
-      <c r="N77" s="159">
-        <f>M78</f>
+      <c r="K77" s="145">
+        <f>J41</f>
+        <v/>
+      </c>
+      <c r="L77" s="145">
+        <f>K41</f>
+        <v/>
+      </c>
+      <c r="M77" s="145">
+        <f>L41</f>
+        <v/>
+      </c>
+      <c r="N77" s="145">
+        <f>M41</f>
         <v/>
       </c>
     </row>
@@ -5403,44 +5441,44 @@
       <c r="D78" s="160" t="n">
         <v>157394</v>
       </c>
-      <c r="E78" s="151">
+      <c r="E78" s="150">
         <f>SUM(E76:E77)</f>
         <v/>
       </c>
-      <c r="F78" s="151">
+      <c r="F78" s="150">
         <f>SUM(F76:F77)</f>
         <v/>
       </c>
-      <c r="G78" s="151">
+      <c r="G78" s="150">
         <f>SUM(G76:G77)</f>
         <v/>
       </c>
-      <c r="H78" s="151">
+      <c r="H78" s="150">
         <f>SUM(H76:H77)</f>
         <v/>
       </c>
-      <c r="I78" s="151">
+      <c r="I78" s="150">
         <f>SUM(I76:I77)</f>
         <v/>
       </c>
-      <c r="J78" s="151">
-        <f>SUM(J76:J77)</f>
-        <v/>
-      </c>
-      <c r="K78" s="151">
-        <f>SUM(K76:K77)</f>
-        <v/>
-      </c>
-      <c r="L78" s="151">
-        <f>SUM(L76:L77)</f>
-        <v/>
-      </c>
-      <c r="M78" s="151">
-        <f>SUM(M76:M77)</f>
-        <v/>
-      </c>
-      <c r="N78" s="151">
-        <f>SUM(N76:N77)</f>
+      <c r="J78" s="145">
+        <f>J77+J76</f>
+        <v/>
+      </c>
+      <c r="K78" s="145">
+        <f>K77+K76</f>
+        <v/>
+      </c>
+      <c r="L78" s="145">
+        <f>L77+L76</f>
+        <v/>
+      </c>
+      <c r="M78" s="145">
+        <f>M77+M76</f>
+        <v/>
+      </c>
+      <c r="N78" s="145">
+        <f>N77+N76</f>
         <v/>
       </c>
     </row>
@@ -5460,43 +5498,43 @@
       </c>
       <c r="C80" s="9" t="n"/>
       <c r="D80" s="27" t="n"/>
-      <c r="E80" s="158">
+      <c r="E80" s="157">
         <f>E78-E41</f>
         <v/>
       </c>
-      <c r="F80" s="158">
+      <c r="F80" s="157">
         <f>F78-F41</f>
         <v/>
       </c>
-      <c r="G80" s="158">
+      <c r="G80" s="157">
         <f>G78-G41</f>
         <v/>
       </c>
-      <c r="H80" s="158">
+      <c r="H80" s="157">
         <f>H78-H41</f>
         <v/>
       </c>
-      <c r="I80" s="158">
+      <c r="I80" s="157">
         <f>I78-I41</f>
         <v/>
       </c>
-      <c r="J80" s="158">
+      <c r="J80" s="145">
         <f>J78-J41</f>
         <v/>
       </c>
-      <c r="K80" s="158">
+      <c r="K80" s="145">
         <f>K78-K41</f>
         <v/>
       </c>
-      <c r="L80" s="158">
+      <c r="L80" s="145">
         <f>L78-L41</f>
         <v/>
       </c>
-      <c r="M80" s="158">
+      <c r="M80" s="145">
         <f>M78-M41</f>
         <v/>
       </c>
-      <c r="N80" s="158">
+      <c r="N80" s="145">
         <f>N78-N41</f>
         <v/>
       </c>
@@ -5567,23 +5605,23 @@
       <c r="I85" s="148" t="n">
         <v>341776</v>
       </c>
-      <c r="J85" s="150">
+      <c r="J85" s="145">
         <f>J42</f>
         <v/>
       </c>
-      <c r="K85" s="150">
+      <c r="K85" s="145">
         <f>K42</f>
         <v/>
       </c>
-      <c r="L85" s="150">
+      <c r="L85" s="145">
         <f>L42</f>
         <v/>
       </c>
-      <c r="M85" s="150">
+      <c r="M85" s="145">
         <f>M42</f>
         <v/>
       </c>
-      <c r="N85" s="150">
+      <c r="N85" s="145">
         <f>N42</f>
         <v/>
       </c>
@@ -5609,23 +5647,23 @@
       <c r="I86" s="148" t="n">
         <v>0</v>
       </c>
-      <c r="J86" s="150">
+      <c r="J86" s="145">
         <f>J43</f>
         <v/>
       </c>
-      <c r="K86" s="150">
+      <c r="K86" s="145">
         <f>K43</f>
         <v/>
       </c>
-      <c r="L86" s="150">
+      <c r="L86" s="145">
         <f>L43</f>
         <v/>
       </c>
-      <c r="M86" s="150">
+      <c r="M86" s="145">
         <f>M43</f>
         <v/>
       </c>
-      <c r="N86" s="150">
+      <c r="N86" s="145">
         <f>N43</f>
         <v/>
       </c>
@@ -5651,23 +5689,23 @@
       <c r="I87" s="148" t="n">
         <v>32315</v>
       </c>
-      <c r="J87" s="150">
+      <c r="J87" s="145">
         <f>J48</f>
         <v/>
       </c>
-      <c r="K87" s="150">
+      <c r="K87" s="145">
         <f>K48</f>
         <v/>
       </c>
-      <c r="L87" s="150">
+      <c r="L87" s="145">
         <f>L48</f>
         <v/>
       </c>
-      <c r="M87" s="150">
+      <c r="M87" s="145">
         <f>M48</f>
         <v/>
       </c>
-      <c r="N87" s="150">
+      <c r="N87" s="145">
         <f>N48</f>
         <v/>
       </c>
@@ -5702,23 +5740,23 @@
         <f>I85+I86-I87</f>
         <v/>
       </c>
-      <c r="J88" s="161">
+      <c r="J88" s="145">
         <f>J85+J86-J87</f>
         <v/>
       </c>
-      <c r="K88" s="161">
+      <c r="K88" s="145">
         <f>K85+K86-K87</f>
         <v/>
       </c>
-      <c r="L88" s="161">
+      <c r="L88" s="145">
         <f>L85+L86-L87</f>
         <v/>
       </c>
-      <c r="M88" s="161">
+      <c r="M88" s="145">
         <f>M85+M86-M87</f>
         <v/>
       </c>
-      <c r="N88" s="161">
+      <c r="N88" s="145">
         <f>N85+N86-N87</f>
         <v/>
       </c>
@@ -5749,23 +5787,23 @@
         <f>I88-H88</f>
         <v/>
       </c>
-      <c r="J89" s="142">
+      <c r="J89" s="145">
         <f>J88-I88</f>
         <v/>
       </c>
-      <c r="K89" s="142">
+      <c r="K89" s="145">
         <f>K88-J88</f>
         <v/>
       </c>
-      <c r="L89" s="142">
+      <c r="L89" s="145">
         <f>L88-K88</f>
         <v/>
       </c>
-      <c r="M89" s="142">
+      <c r="M89" s="145">
         <f>M88-L88</f>
         <v/>
       </c>
-      <c r="N89" s="142">
+      <c r="N89" s="145">
         <f>N88-M88</f>
         <v/>
       </c>
@@ -5814,23 +5852,23 @@
         <f>H95</f>
         <v/>
       </c>
-      <c r="J92" s="159">
+      <c r="J92" s="145">
         <f>I44</f>
         <v/>
       </c>
-      <c r="K92" s="159">
+      <c r="K92" s="145">
         <f>J95</f>
         <v/>
       </c>
-      <c r="L92" s="159">
+      <c r="L92" s="145">
         <f>K95</f>
         <v/>
       </c>
-      <c r="M92" s="159">
+      <c r="M92" s="145">
         <f>L95</f>
         <v/>
       </c>
-      <c r="N92" s="159">
+      <c r="N92" s="145">
         <f>M95</f>
         <v/>
       </c>
@@ -5856,24 +5894,24 @@
       <c r="I93" s="148" t="n">
         <v>39407</v>
       </c>
-      <c r="J93" s="150">
-        <f>+J18</f>
-        <v/>
-      </c>
-      <c r="K93" s="150">
-        <f>+K18</f>
-        <v/>
-      </c>
-      <c r="L93" s="150">
-        <f>+L18</f>
-        <v/>
-      </c>
-      <c r="M93" s="150">
-        <f>+M18</f>
-        <v/>
-      </c>
-      <c r="N93" s="150">
-        <f>+N18</f>
+      <c r="J93" s="145">
+        <f>J24*J18</f>
+        <v/>
+      </c>
+      <c r="K93" s="145">
+        <f>K24*K18</f>
+        <v/>
+      </c>
+      <c r="L93" s="145">
+        <f>L24*L18</f>
+        <v/>
+      </c>
+      <c r="M93" s="145">
+        <f>M24*M18</f>
+        <v/>
+      </c>
+      <c r="N93" s="145">
+        <f>N24*N18</f>
         <v/>
       </c>
     </row>
@@ -5898,23 +5936,23 @@
       <c r="I94" s="148" t="n">
         <v>14952</v>
       </c>
-      <c r="J94" s="150">
+      <c r="J94" s="145">
         <f>J92*J11</f>
         <v/>
       </c>
-      <c r="K94" s="150">
+      <c r="K94" s="145">
         <f>K92*K11</f>
         <v/>
       </c>
-      <c r="L94" s="150">
+      <c r="L94" s="145">
         <f>L92*L11</f>
         <v/>
       </c>
-      <c r="M94" s="150">
+      <c r="M94" s="145">
         <f>M92*M11</f>
         <v/>
       </c>
-      <c r="N94" s="150">
+      <c r="N94" s="145">
         <f>N92*N11</f>
         <v/>
       </c>
@@ -5942,23 +5980,23 @@
       <c r="I95" s="162" t="n">
         <v>67713</v>
       </c>
-      <c r="J95" s="161">
+      <c r="J95" s="145">
         <f>J92+J93-J94</f>
         <v/>
       </c>
-      <c r="K95" s="161">
+      <c r="K95" s="145">
         <f>K92+K93-K94</f>
         <v/>
       </c>
-      <c r="L95" s="161">
+      <c r="L95" s="145">
         <f>L92+L93-L94</f>
         <v/>
       </c>
-      <c r="M95" s="161">
+      <c r="M95" s="145">
         <f>M92+M93-M94</f>
         <v/>
       </c>
-      <c r="N95" s="161">
+      <c r="N95" s="145">
         <f>N92+N93-N94</f>
         <v/>
       </c>
@@ -6012,23 +6050,23 @@
         <f>H100</f>
         <v/>
       </c>
-      <c r="J98" s="159">
+      <c r="J98" s="145">
         <f>I49</f>
         <v/>
       </c>
-      <c r="K98" s="159">
+      <c r="K98" s="145">
         <f>J100</f>
         <v/>
       </c>
-      <c r="L98" s="159">
+      <c r="L98" s="145">
         <f>K100</f>
         <v/>
       </c>
-      <c r="M98" s="159">
+      <c r="M98" s="145">
         <f>L100</f>
         <v/>
       </c>
-      <c r="N98" s="159">
+      <c r="N98" s="145">
         <f>M100</f>
         <v/>
       </c>
@@ -6054,24 +6092,24 @@
       <c r="I99" s="148" t="n">
         <v>846670</v>
       </c>
-      <c r="J99" s="142">
-        <f>+J19</f>
-        <v/>
-      </c>
-      <c r="K99" s="142">
-        <f>+K19</f>
-        <v/>
-      </c>
-      <c r="L99" s="142">
-        <f>+L19</f>
-        <v/>
-      </c>
-      <c r="M99" s="142">
-        <f>+M19</f>
-        <v/>
-      </c>
-      <c r="N99" s="142">
-        <f>+N19</f>
+      <c r="J99" s="145">
+        <f>J19</f>
+        <v/>
+      </c>
+      <c r="K99" s="145">
+        <f>K19</f>
+        <v/>
+      </c>
+      <c r="L99" s="145">
+        <f>L19</f>
+        <v/>
+      </c>
+      <c r="M99" s="145">
+        <f>M19</f>
+        <v/>
+      </c>
+      <c r="N99" s="145">
+        <f>N19</f>
         <v/>
       </c>
     </row>
@@ -6098,24 +6136,24 @@
       <c r="I100" s="162" t="n">
         <v>3055691</v>
       </c>
-      <c r="J100" s="161">
-        <f>SUM(J98:J99)</f>
-        <v/>
-      </c>
-      <c r="K100" s="161">
-        <f>SUM(K98:K99)</f>
-        <v/>
-      </c>
-      <c r="L100" s="161">
-        <f>SUM(L98:L99)</f>
-        <v/>
-      </c>
-      <c r="M100" s="161">
-        <f>SUM(M98:M99)</f>
-        <v/>
-      </c>
-      <c r="N100" s="161">
-        <f>SUM(N98:N99)</f>
+      <c r="J100" s="145">
+        <f>J98+J99</f>
+        <v/>
+      </c>
+      <c r="K100" s="145">
+        <f>K98+K99</f>
+        <v/>
+      </c>
+      <c r="L100" s="145">
+        <f>L98+L99</f>
+        <v/>
+      </c>
+      <c r="M100" s="145">
+        <f>M98+M99</f>
+        <v/>
+      </c>
+      <c r="N100" s="145">
+        <f>N98+N99</f>
         <v/>
       </c>
     </row>
@@ -6140,23 +6178,23 @@
       <c r="I101" s="148" t="n">
         <v>133647</v>
       </c>
-      <c r="J101" s="150">
+      <c r="J101" s="145">
         <f>J98*J12</f>
         <v/>
       </c>
-      <c r="K101" s="150">
+      <c r="K101" s="145">
         <f>K98*K12</f>
         <v/>
       </c>
-      <c r="L101" s="150">
+      <c r="L101" s="145">
         <f>L98*L12</f>
         <v/>
       </c>
-      <c r="M101" s="150">
+      <c r="M101" s="145">
         <f>M98*M12</f>
         <v/>
       </c>
-      <c r="N101" s="150">
+      <c r="N101" s="145">
         <f>N98*N12</f>
         <v/>
       </c>

--- a/FICO/output/FICO_Completed_Model.xlsx
+++ b/FICO/output/FICO_Completed_Model.xlsx
@@ -100,7 +100,7 @@
     <numFmt numFmtId="178" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="179" formatCode="0.0"/>
   </numFmts>
-  <fonts count="50">
+  <fonts count="55">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -365,14 +365,42 @@
       <color rgb="000000FF"/>
     </font>
     <font>
+      <name val="Consolas"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <i val="1"/>
-      <color rgb="00C00000"/>
+      <color rgb="00595959"/>
       <sz val="8"/>
     </font>
     <font>
-      <name val="Consolas"/>
-      <color rgb="00000000"/>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00C65911"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00595959"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00833C0C"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <sz val="9"/>
     </font>
     <font>
@@ -414,7 +442,7 @@
       <sz val="8"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -464,6 +492,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D6EAF8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C65911"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
     <fill>
@@ -590,7 +628,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="199">
+  <cellXfs count="205">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="1"/>
@@ -811,9 +849,19 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="41" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="45" fillId="10" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="42" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="166" fontId="40" fillId="8" borderId="5" pivotButton="0" quotePrefix="0" xfId="2"/>
-    <xf numFmtId="164" fontId="42" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="46" fillId="11" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="166" fontId="38" fillId="7" borderId="5" pivotButton="0" quotePrefix="0" xfId="2"/>
     <xf numFmtId="177" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="166" fontId="38" fillId="7" borderId="5" pivotButton="0" quotePrefix="0" xfId="1"/>
@@ -821,13 +869,15 @@
     <xf numFmtId="177" fontId="38" fillId="7" borderId="5" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="177" fontId="40" fillId="8" borderId="5" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="166" fontId="40" fillId="8" borderId="5" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="164" fontId="41" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="177" fontId="40" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="164" fontId="42" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="164" fontId="41" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="177" fontId="6" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="164" fontId="42" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="41" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="177" fontId="40" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="177" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="164" fontId="42" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="164" fontId="41" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="177" fontId="6" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="177" fontId="6" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="177" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
@@ -838,17 +888,17 @@
     </xf>
     <xf numFmtId="177" fontId="9" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="177" fontId="40" fillId="8" borderId="2" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="43" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="48" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="39" fillId="9" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="40" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="45" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="50" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="48" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="47" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="53" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="52" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="38" fillId="7" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
@@ -856,7 +906,7 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="40" fillId="8" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="179" fontId="40" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -864,7 +914,7 @@
     </xf>
     <xf numFmtId="2" fontId="40" fillId="8" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="178" fontId="32" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="38" fillId="7" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -881,7 +931,7 @@
     <xf numFmtId="178" fontId="38" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="177" fontId="36" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="177" fontId="37" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="49" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="54" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="174" fontId="38" fillId="7" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="177" fontId="30" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="177" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -2635,7 +2685,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N138"/>
+  <dimension ref="A1:U138"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.109375" defaultRowHeight="15.6" outlineLevelRow="1"/>
   <cols>
     <col width="1.88671875" customWidth="1" style="19" min="1" max="1"/>
@@ -2653,6 +2703,12 @@
     <col width="16" customWidth="1" min="13" max="13"/>
     <col width="16" customWidth="1" min="14" max="14"/>
     <col width="9.109375" customWidth="1" style="19" min="15" max="16384"/>
+    <col width="6" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
+    <col width="36" customWidth="1" min="18" max="18"/>
+    <col width="42" customWidth="1" min="19" max="19"/>
+    <col width="48" customWidth="1" min="20" max="20"/>
+    <col width="36" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2783,6 +2839,11 @@
       <c r="B4" s="137" t="inlineStr">
         <is>
           <t>vengeanceaiUSCMODEL4: GREEN cells = full equations (not hardcoded $, not bare =J36 pointers)</t>
+        </is>
+      </c>
+      <c r="P4" s="138" t="inlineStr">
+        <is>
+          <t>ASSUMPTIONS EXPLAINED — every driver on this sheet</t>
         </is>
       </c>
     </row>
@@ -2804,6 +2865,11 @@
       <c r="L5" s="65" t="n"/>
       <c r="M5" s="65" t="n"/>
       <c r="N5" s="65" t="n"/>
+      <c r="P5" s="139" t="inlineStr">
+        <is>
+          <t>Yellow = policy judgment. Green = Excel equations linked to FY25 (col I). Column C notes are text only (not formulas).</t>
+        </is>
+      </c>
     </row>
     <row r="6" hidden="1" outlineLevel="1" customFormat="1" s="19">
       <c r="B6" s="18" t="inlineStr">
@@ -2812,16 +2878,46 @@
         </is>
       </c>
       <c r="D6" s="47" t="n"/>
-    </row>
-    <row r="7" hidden="1" outlineLevel="1">
+      <c r="P6" s="140" t="inlineStr">
+        <is>
+          <t>Row</t>
+        </is>
+      </c>
+      <c r="Q6" s="140" t="inlineStr">
+        <is>
+          <t>Assumption</t>
+        </is>
+      </c>
+      <c r="R6" s="140" t="inlineStr">
+        <is>
+          <t>What it is</t>
+        </is>
+      </c>
+      <c r="S6" s="140" t="inlineStr">
+        <is>
+          <t>How set in model</t>
+        </is>
+      </c>
+      <c r="T6" s="140" t="inlineStr">
+        <is>
+          <t>Why this choice</t>
+        </is>
+      </c>
+      <c r="U6" s="140" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" hidden="1" outlineLevel="1" ht="42" customHeight="1">
       <c r="B7" s="19" t="inlineStr">
         <is>
           <t>Revenue Growth (% Change)</t>
         </is>
       </c>
-      <c r="C7" s="138" t="inlineStr">
-        <is>
-          <t>ONLY yellow policy input in this block → feeds Rev equation</t>
+      <c r="C7" s="141" t="inlineStr">
+        <is>
+          <t>POLICY → drives Rev → GP → EBT → NI / CF</t>
         </is>
       </c>
       <c r="D7" s="46" t="n"/>
@@ -2842,31 +2938,59 @@
         <f>I24/H24-1</f>
         <v/>
       </c>
-      <c r="J7" s="139" t="n">
+      <c r="J7" s="142" t="n">
         <v>0.27</v>
       </c>
-      <c r="K7" s="139" t="n">
+      <c r="K7" s="142" t="n">
         <v>0.16</v>
       </c>
-      <c r="L7" s="139" t="n">
+      <c r="L7" s="142" t="n">
         <v>0.13</v>
       </c>
-      <c r="M7" s="139" t="n">
+      <c r="M7" s="142" t="n">
         <v>0.1</v>
       </c>
-      <c r="N7" s="139" t="n">
+      <c r="N7" s="142" t="n">
         <v>0.07000000000000001</v>
       </c>
-    </row>
-    <row r="8" hidden="1" outlineLevel="1">
+      <c r="P7" s="143" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q7" s="143" t="inlineStr">
+        <is>
+          <t>Revenue Growth</t>
+        </is>
+      </c>
+      <c r="R7" s="144" t="inlineStr">
+        <is>
+          <t>Year-over-year % increase in revenue for each forecast year.</t>
+        </is>
+      </c>
+      <c r="S7" s="144" t="inlineStr">
+        <is>
+          <t>Yellow POLICY input: 27% / 16% / 13% / 10% / 7%.</t>
+        </is>
+      </c>
+      <c r="T7" s="144" t="inlineStr">
+        <is>
+          <t>Y1 ≈ company FY2026 revenue guidance (~$2.53B / FY25 $1.991B − 1 ≈ 27%). Then fade toward terminal g=3% (not straight-lined). This is the main forward-looking judgment; it drives Rev → GP → EBT → Net Earnings → CF.</t>
+        </is>
+      </c>
+      <c r="U7" s="144" t="inlineStr">
+        <is>
+          <t>FICO FY2026 guidance + fade policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" hidden="1" outlineLevel="1" ht="42" customHeight="1">
       <c r="B8" s="19" t="inlineStr">
         <is>
           <t>Cost of Goods Sold (% of Revenue)</t>
         </is>
       </c>
-      <c r="C8" s="140" t="inlineStr">
-        <is>
-          <t>COGS% = FY25 COGS/Revenue</t>
+      <c r="C8" s="141" t="inlineStr">
+        <is>
+          <t>eqn: FY25 COGS/Revenue (held flat)</t>
         </is>
       </c>
       <c r="D8" s="47" t="n"/>
@@ -2890,140 +3014,227 @@
         <f>I25/I24</f>
         <v/>
       </c>
-      <c r="J8" s="141">
+      <c r="J8" s="145">
         <f>$I$25/$I$24</f>
         <v/>
       </c>
-      <c r="K8" s="141">
+      <c r="K8" s="145">
         <f>$I$25/$I$24</f>
         <v/>
       </c>
-      <c r="L8" s="141">
+      <c r="L8" s="145">
         <f>$I$25/$I$24</f>
         <v/>
       </c>
-      <c r="M8" s="141">
+      <c r="M8" s="145">
         <f>$I$25/$I$24</f>
         <v/>
       </c>
-      <c r="N8" s="141">
+      <c r="N8" s="145">
         <f>$I$25/$I$24</f>
         <v/>
       </c>
-    </row>
-    <row r="9" hidden="1" outlineLevel="1">
+      <c r="P8" s="143" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q8" s="143" t="inlineStr">
+        <is>
+          <t>COGS % of Revenue</t>
+        </is>
+      </c>
+      <c r="R8" s="144" t="inlineStr">
+        <is>
+          <t>Cost of revenues as a % of sales (gross margin = 1 − this).</t>
+        </is>
+      </c>
+      <c r="S8" s="144" t="inlineStr">
+        <is>
+          <t>Excel equation: I25/I24 (FY25 COGS ÷ FY25 Revenue) held flat.</t>
+        </is>
+      </c>
+      <c r="T8" s="144" t="inlineStr">
+        <is>
+          <t>Locks in latest reported cost structure (~17.8%). Scores mix is high-margin; holding FY25 is conservative vs further mix shift.</t>
+        </is>
+      </c>
+      <c r="U8" s="144" t="inlineStr">
+        <is>
+          <t>SEC 10-K FY2025 — Cost of revenues / Total revenues</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" hidden="1" outlineLevel="1" ht="42" customHeight="1">
       <c r="B9" s="19" t="inlineStr">
         <is>
           <t>SGA % of Revenue (equation)</t>
         </is>
       </c>
-      <c r="C9" s="140">
-        <f> (I28−10922)/I24 − 50bps×t</f>
-        <v/>
+      <c r="C9" s="141" t="inlineStr">
+        <is>
+          <t>eqn: (FY25 SGA − restructuring)/Rev − 50bps×t</t>
+        </is>
       </c>
       <c r="D9" s="47" t="n"/>
-      <c r="E9" s="142">
+      <c r="E9" s="146">
         <f>E28</f>
         <v/>
       </c>
-      <c r="F9" s="142">
+      <c r="F9" s="146">
         <f>F28</f>
         <v/>
       </c>
-      <c r="G9" s="142">
+      <c r="G9" s="146">
         <f>G28</f>
         <v/>
       </c>
-      <c r="H9" s="142">
+      <c r="H9" s="146">
         <f>H28</f>
         <v/>
       </c>
-      <c r="I9" s="142">
+      <c r="I9" s="146">
         <f>I28</f>
         <v/>
       </c>
-      <c r="J9" s="143">
+      <c r="J9" s="147">
         <f>MAX(0.05,(($I$28-10922.0)/$I$24)-0.005)</f>
         <v/>
       </c>
-      <c r="K9" s="143">
+      <c r="K9" s="147">
         <f>MAX(0.05,(($I$28-10922.0)/$I$24)-0.01)</f>
         <v/>
       </c>
-      <c r="L9" s="143">
+      <c r="L9" s="147">
         <f>MAX(0.05,(($I$28-10922.0)/$I$24)-0.015)</f>
         <v/>
       </c>
-      <c r="M9" s="143">
+      <c r="M9" s="147">
         <f>MAX(0.05,(($I$28-10922.0)/$I$24)-0.02)</f>
         <v/>
       </c>
-      <c r="N9" s="143">
+      <c r="N9" s="147">
         <f>MAX(0.05,(($I$28-10922.0)/$I$24)-0.025)</f>
         <v/>
       </c>
-    </row>
-    <row r="10" hidden="1" outlineLevel="1">
+      <c r="P9" s="143" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q9" s="143" t="inlineStr">
+        <is>
+          <t>SGA % of Revenue</t>
+        </is>
+      </c>
+      <c r="R9" s="144" t="inlineStr">
+        <is>
+          <t>Operating opex (Salaries &amp; Benefits / SG&amp;A) as % of sales.</t>
+        </is>
+      </c>
+      <c r="S9" s="144" t="inlineStr">
+        <is>
+          <t>Equation: (I28 − 10,922)/I24 − 50bps × year. Strips FY25 restructuring; then −0.5% of sales each year.</t>
+        </is>
+      </c>
+      <c r="T9" s="144" t="inlineStr">
+        <is>
+          <t>Normalize one-time restructuring ($10.9M). Mild efficiency grind reflects operating leverage as revenue scales; floored at 5%.</t>
+        </is>
+      </c>
+      <c r="U9" s="144" t="inlineStr">
+        <is>
+          <t>SEC 10-K FY2025 — SG&amp;A + restructuring note</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" hidden="1" outlineLevel="1" ht="42" customHeight="1">
       <c r="B10" s="19" t="inlineStr">
         <is>
           <t>R&amp;D % of Revenue (equation)</t>
         </is>
       </c>
-      <c r="C10" s="140">
-        <f> I29/I24</f>
-        <v/>
+      <c r="C10" s="141" t="inlineStr">
+        <is>
+          <t>eqn: FY25 R&amp;D/Revenue (held flat)</t>
+        </is>
       </c>
       <c r="D10" s="47" t="n"/>
-      <c r="E10" s="142">
+      <c r="E10" s="146">
         <f>E29</f>
         <v/>
       </c>
-      <c r="F10" s="142">
+      <c r="F10" s="146">
         <f>F29</f>
         <v/>
       </c>
-      <c r="G10" s="142">
+      <c r="G10" s="146">
         <f>G29</f>
         <v/>
       </c>
-      <c r="H10" s="142">
+      <c r="H10" s="146">
         <f>H29</f>
         <v/>
       </c>
-      <c r="I10" s="142">
+      <c r="I10" s="146">
         <f>I29</f>
         <v/>
       </c>
-      <c r="J10" s="143">
+      <c r="J10" s="147">
         <f>$I$29/$I$24</f>
         <v/>
       </c>
-      <c r="K10" s="143">
+      <c r="K10" s="147">
         <f>$I$29/$I$24</f>
         <v/>
       </c>
-      <c r="L10" s="143">
+      <c r="L10" s="147">
         <f>$I$29/$I$24</f>
         <v/>
       </c>
-      <c r="M10" s="143">
+      <c r="M10" s="147">
         <f>$I$29/$I$24</f>
         <v/>
       </c>
-      <c r="N10" s="143">
+      <c r="N10" s="147">
         <f>$I$29/$I$24</f>
         <v/>
       </c>
-    </row>
-    <row r="11" hidden="1" outlineLevel="1">
+      <c r="P10" s="143" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q10" s="143" t="inlineStr">
+        <is>
+          <t>R&amp;D % of Revenue</t>
+        </is>
+      </c>
+      <c r="R10" s="144" t="inlineStr">
+        <is>
+          <t>Research &amp; development (template label may say Rent and Overhead) as % of sales.</t>
+        </is>
+      </c>
+      <c r="S10" s="144" t="inlineStr">
+        <is>
+          <t>Excel equation: I29/I24 held flat (~9.46%).</t>
+        </is>
+      </c>
+      <c r="T10" s="144" t="inlineStr">
+        <is>
+          <t>FICO reinvests steadily in analytics/software. Flat % grows dollars with revenue.</t>
+        </is>
+      </c>
+      <c r="U10" s="144" t="inlineStr">
+        <is>
+          <t>SEC 10-K FY2025 — Research and development</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" hidden="1" outlineLevel="1" ht="42" customHeight="1">
       <c r="B11" s="19" t="inlineStr">
         <is>
           <t>Depreciation &amp; Amortization (% of PP&amp;E Open Bal)</t>
         </is>
       </c>
-      <c r="C11" s="140">
-        <f> I30/I44</f>
-        <v/>
+      <c r="C11" s="141" t="inlineStr">
+        <is>
+          <t>eqn: FY25 DA / FY25 PP&amp;E open</t>
+        </is>
       </c>
       <c r="D11" s="47" t="n"/>
       <c r="E11" s="37">
@@ -3046,36 +3257,65 @@
         <f>I30/I92</f>
         <v/>
       </c>
-      <c r="J11" s="141">
+      <c r="J11" s="145">
         <f>IF($I$44=0,0.25,$I$30/$I$44)</f>
         <v/>
       </c>
-      <c r="K11" s="141">
+      <c r="K11" s="145">
         <f>IF($I$44=0,0.25,$I$30/$I$44)</f>
         <v/>
       </c>
-      <c r="L11" s="141">
+      <c r="L11" s="145">
         <f>IF($I$44=0,0.25,$I$30/$I$44)</f>
         <v/>
       </c>
-      <c r="M11" s="141">
+      <c r="M11" s="145">
         <f>IF($I$44=0,0.25,$I$30/$I$44)</f>
         <v/>
       </c>
-      <c r="N11" s="141">
+      <c r="N11" s="145">
         <f>IF($I$44=0,0.25,$I$30/$I$44)</f>
         <v/>
       </c>
-    </row>
-    <row r="12" hidden="1" outlineLevel="1">
+      <c r="P11" s="143" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q11" s="143" t="inlineStr">
+        <is>
+          <t>D&amp;A % of PP&amp;E Open</t>
+        </is>
+      </c>
+      <c r="R11" s="144" t="inlineStr">
+        <is>
+          <t>Depreciation &amp; amortization as % of opening net PP&amp;E.</t>
+        </is>
+      </c>
+      <c r="S11" s="144" t="inlineStr">
+        <is>
+          <t>Excel equation: I30/I44 (FY25 DA ÷ FY25 PPE). Forecast DA = OpenPPE × this %.</t>
+        </is>
+      </c>
+      <c r="T11" s="144" t="inlineStr">
+        <is>
+          <t>Ties DA to the asset base the schedule rolls forward (opens at I44).</t>
+        </is>
+      </c>
+      <c r="U11" s="144" t="inlineStr">
+        <is>
+          <t>SEC 10-K FY2025 — D&amp;A and PP&amp;E</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" hidden="1" outlineLevel="1" ht="42" customHeight="1">
       <c r="B12" s="19" t="inlineStr">
         <is>
           <t>Interest (% of Debt Open Bal)</t>
         </is>
       </c>
-      <c r="C12" s="140">
-        <f> I101/I98</f>
-        <v/>
+      <c r="C12" s="141" t="inlineStr">
+        <is>
+          <t>eqn: FY25 interest / debt open</t>
+        </is>
       </c>
       <c r="D12" s="47" t="n"/>
       <c r="E12" s="37">
@@ -3098,36 +3338,65 @@
         <f>I101/I98</f>
         <v/>
       </c>
-      <c r="J12" s="141">
+      <c r="J12" s="145">
         <f>IF($I$98=0,0.05,$I$101/$I$98)</f>
         <v/>
       </c>
-      <c r="K12" s="141">
+      <c r="K12" s="145">
         <f>IF($I$98=0,0.05,$I$101/$I$98)</f>
         <v/>
       </c>
-      <c r="L12" s="141">
+      <c r="L12" s="145">
         <f>IF($I$98=0,0.05,$I$101/$I$98)</f>
         <v/>
       </c>
-      <c r="M12" s="141">
+      <c r="M12" s="145">
         <f>IF($I$98=0,0.05,$I$101/$I$98)</f>
         <v/>
       </c>
-      <c r="N12" s="141">
+      <c r="N12" s="145">
         <f>IF($I$98=0,0.05,$I$101/$I$98)</f>
         <v/>
       </c>
-    </row>
-    <row r="13" hidden="1" outlineLevel="1">
+      <c r="P12" s="143" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q12" s="143" t="inlineStr">
+        <is>
+          <t>Interest % of Debt Open</t>
+        </is>
+      </c>
+      <c r="R12" s="144" t="inlineStr">
+        <is>
+          <t>Interest expense as % of opening debt balance.</t>
+        </is>
+      </c>
+      <c r="S12" s="144" t="inlineStr">
+        <is>
+          <t>Excel equation: I101/I98 (FY25 interest ÷ FY25 opening debt in schedule).</t>
+        </is>
+      </c>
+      <c r="T12" s="144" t="inlineStr">
+        <is>
+          <t>Approximates average coupon / cost of debt on the book. Debt held flat (issuance = 0), so interest stays linked to that stock.</t>
+        </is>
+      </c>
+      <c r="U12" s="144" t="inlineStr">
+        <is>
+          <t>SEC 10-K FY2025 — Interest expense, net + debt footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" hidden="1" outlineLevel="1" ht="42" customHeight="1">
       <c r="B13" s="19" t="inlineStr">
         <is>
           <t>Tax Rate (% of Earnings Before Tax)</t>
         </is>
       </c>
-      <c r="C13" s="140">
-        <f> I35/I33</f>
-        <v/>
+      <c r="C13" s="141" t="inlineStr">
+        <is>
+          <t>eqn: FY25 tax / FY25 EBT</t>
+        </is>
       </c>
       <c r="D13" s="25" t="n"/>
       <c r="E13" s="37">
@@ -3150,25 +3419,53 @@
         <f>I35/I33</f>
         <v/>
       </c>
-      <c r="J13" s="141">
+      <c r="J13" s="145">
         <f>IF($I$33=0,0.21,$I$35/$I$33)</f>
         <v/>
       </c>
-      <c r="K13" s="141">
+      <c r="K13" s="145">
         <f>IF($I$33=0,0.21,$I$35/$I$33)</f>
         <v/>
       </c>
-      <c r="L13" s="141">
+      <c r="L13" s="145">
         <f>IF($I$33=0,0.21,$I$35/$I$33)</f>
         <v/>
       </c>
-      <c r="M13" s="141">
+      <c r="M13" s="145">
         <f>IF($I$33=0,0.21,$I$35/$I$33)</f>
         <v/>
       </c>
-      <c r="N13" s="141">
+      <c r="N13" s="145">
         <f>IF($I$33=0,0.21,$I$35/$I$33)</f>
         <v/>
+      </c>
+      <c r="P13" s="143" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q13" s="143" t="inlineStr">
+        <is>
+          <t>Tax Rate (% of EBT)</t>
+        </is>
+      </c>
+      <c r="R13" s="144" t="inlineStr">
+        <is>
+          <t>Effective book tax rate applied to forecast EBT.</t>
+        </is>
+      </c>
+      <c r="S13" s="144" t="inlineStr">
+        <is>
+          <t>Excel equation: I35/I33 (FY25 tax ÷ simplified FY25 EBT in this template).</t>
+        </is>
+      </c>
+      <c r="T13" s="144" t="inlineStr">
+        <is>
+          <t>Uses reported effective rate (~19% on template EBT; ~18.8% on 10-K EBT). UFCF in DCF also uses unlevered EBIT × t.</t>
+        </is>
+      </c>
+      <c r="U13" s="144" t="inlineStr">
+        <is>
+          <t>SEC 10-K FY2025 — Provision for income taxes / Income before taxes</t>
+        </is>
       </c>
     </row>
     <row r="14" hidden="1" outlineLevel="1">
@@ -3190,286 +3487,472 @@
       <c r="M14" s="19" t="n"/>
       <c r="N14" s="19" t="n"/>
     </row>
-    <row r="15" hidden="1" outlineLevel="1">
+    <row r="15" hidden="1" outlineLevel="1" ht="42" customHeight="1">
       <c r="B15" s="19" t="inlineStr">
         <is>
           <t>Accounts Receivable (Days)</t>
         </is>
       </c>
-      <c r="C15" s="144">
-        <f> ROUND(I42/I24×365,0)</f>
-        <v/>
+      <c r="C15" s="148" t="inlineStr">
+        <is>
+          <t>eqn: ROUND(net AR/Rev×365)</t>
+        </is>
       </c>
       <c r="D15" s="32" t="n"/>
-      <c r="E15" s="142">
+      <c r="E15" s="146">
         <f>E42/E24*365</f>
         <v/>
       </c>
-      <c r="F15" s="142">
+      <c r="F15" s="146">
         <f>F42/F24*365</f>
         <v/>
       </c>
-      <c r="G15" s="142">
+      <c r="G15" s="146">
         <f>G42/G24*365</f>
         <v/>
       </c>
-      <c r="H15" s="142">
+      <c r="H15" s="146">
         <f>H42/H24*365</f>
         <v/>
       </c>
-      <c r="I15" s="142">
+      <c r="I15" s="146">
         <f>I42/I24*365</f>
         <v/>
       </c>
-      <c r="J15" s="145">
+      <c r="J15" s="149">
         <f>ROUND($I$42/$I$24*365,0)</f>
         <v/>
       </c>
-      <c r="K15" s="145">
+      <c r="K15" s="149">
         <f>ROUND($I$42/$I$24*365,0)</f>
         <v/>
       </c>
-      <c r="L15" s="145">
+      <c r="L15" s="149">
         <f>ROUND($I$42/$I$24*365,0)</f>
         <v/>
       </c>
-      <c r="M15" s="145">
+      <c r="M15" s="149">
         <f>ROUND($I$42/$I$24*365,0)</f>
         <v/>
       </c>
-      <c r="N15" s="145">
+      <c r="N15" s="149">
         <f>ROUND($I$42/$I$24*365,0)</f>
         <v/>
       </c>
-    </row>
-    <row r="16" hidden="1" outlineLevel="1">
+      <c r="P15" s="143" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q15" s="143" t="inlineStr">
+        <is>
+          <t>Accounts Receivable (Days)</t>
+        </is>
+      </c>
+      <c r="R15" s="144" t="inlineStr">
+        <is>
+          <t>AR days sales outstanding used to project AR = Rev × days/365.</t>
+        </is>
+      </c>
+      <c r="S15" s="144" t="inlineStr">
+        <is>
+          <t>Excel equation: ROUND(I42/I24×365, 0). I42 is net AR (AR − deferred).</t>
+        </is>
+      </c>
+      <c r="T15" s="144" t="inlineStr">
+        <is>
+          <t>Operating working-capital view: contract liabilities (deferred revenue) reduce net AR so ΔNWC is not overstated.</t>
+        </is>
+      </c>
+      <c r="U15" s="144" t="inlineStr">
+        <is>
+          <t>SEC 10-K — AR; DeferredRevenueCurrent (XBRL)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" hidden="1" outlineLevel="1" ht="42" customHeight="1">
       <c r="B16" s="19" t="inlineStr">
         <is>
           <t>Inventory (Days)</t>
         </is>
       </c>
+      <c r="C16" s="148" t="inlineStr">
+        <is>
+          <t>POLICY: software business — no inventory</t>
+        </is>
+      </c>
       <c r="D16" s="32" t="n"/>
-      <c r="E16" s="142">
+      <c r="E16" s="146">
         <f>E43/E25*365</f>
         <v/>
       </c>
-      <c r="F16" s="142">
+      <c r="F16" s="146">
         <f>F43/F25*365</f>
         <v/>
       </c>
-      <c r="G16" s="142">
+      <c r="G16" s="146">
         <f>G43/G25*365</f>
         <v/>
       </c>
-      <c r="H16" s="142">
+      <c r="H16" s="146">
         <f>H43/H25*365</f>
         <v/>
       </c>
-      <c r="I16" s="142">
+      <c r="I16" s="146">
         <f>I43/I25*365</f>
         <v/>
       </c>
-      <c r="J16" s="146" t="n">
+      <c r="J16" s="150" t="n">
         <v>0</v>
       </c>
-      <c r="K16" s="146" t="n">
+      <c r="K16" s="150" t="n">
         <v>0</v>
       </c>
-      <c r="L16" s="146" t="n">
+      <c r="L16" s="150" t="n">
         <v>0</v>
       </c>
-      <c r="M16" s="146" t="n">
+      <c r="M16" s="150" t="n">
         <v>0</v>
       </c>
-      <c r="N16" s="146" t="n">
+      <c r="N16" s="150" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" hidden="1" outlineLevel="1">
+      <c r="P16" s="143" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q16" s="143" t="inlineStr">
+        <is>
+          <t>Inventory (Days)</t>
+        </is>
+      </c>
+      <c r="R16" s="144" t="inlineStr">
+        <is>
+          <t>Inventory days (Inv = COGS × days/365).</t>
+        </is>
+      </c>
+      <c r="S16" s="144" t="inlineStr">
+        <is>
+          <t>Hard zero — FICO is software / scores; inventory is immaterial.</t>
+        </is>
+      </c>
+      <c r="T16" s="144" t="inlineStr">
+        <is>
+          <t>No inventory cycle to fund.</t>
+        </is>
+      </c>
+      <c r="U16" s="144" t="inlineStr">
+        <is>
+          <t>SEC 10-K — Inventory ≈ $0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" hidden="1" outlineLevel="1" ht="42" customHeight="1">
       <c r="B17" s="19" t="inlineStr">
         <is>
           <t>Accounts Payable (Days)</t>
         </is>
       </c>
-      <c r="C17" s="144">
-        <f> ROUND(I48/I25×365,0)</f>
-        <v/>
+      <c r="C17" s="148" t="inlineStr">
+        <is>
+          <t>eqn: ROUND(AP/COGS×365)</t>
+        </is>
       </c>
       <c r="D17" s="32" t="n"/>
-      <c r="E17" s="142">
+      <c r="E17" s="146">
         <f>E48/E25*365</f>
         <v/>
       </c>
-      <c r="F17" s="142">
+      <c r="F17" s="146">
         <f>F48/F25*365</f>
         <v/>
       </c>
-      <c r="G17" s="142">
+      <c r="G17" s="146">
         <f>G48/G25*365</f>
         <v/>
       </c>
-      <c r="H17" s="142">
+      <c r="H17" s="146">
         <f>H48/H25*365</f>
         <v/>
       </c>
-      <c r="I17" s="142">
+      <c r="I17" s="146">
         <f>I48/I25*365</f>
         <v/>
       </c>
-      <c r="J17" s="145">
+      <c r="J17" s="149">
         <f>IF($I$25=0,0,ROUND($I$48/$I$25*365,0))</f>
         <v/>
       </c>
-      <c r="K17" s="145">
+      <c r="K17" s="149">
         <f>IF($I$25=0,0,ROUND($I$48/$I$25*365,0))</f>
         <v/>
       </c>
-      <c r="L17" s="145">
+      <c r="L17" s="149">
         <f>IF($I$25=0,0,ROUND($I$48/$I$25*365,0))</f>
         <v/>
       </c>
-      <c r="M17" s="145">
+      <c r="M17" s="149">
         <f>IF($I$25=0,0,ROUND($I$48/$I$25*365,0))</f>
         <v/>
       </c>
-      <c r="N17" s="145">
+      <c r="N17" s="149">
         <f>IF($I$25=0,0,ROUND($I$48/$I$25*365,0))</f>
         <v/>
       </c>
-    </row>
-    <row r="18" hidden="1" outlineLevel="1">
+      <c r="P17" s="143" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q17" s="143" t="inlineStr">
+        <is>
+          <t>Accounts Payable (Days)</t>
+        </is>
+      </c>
+      <c r="R17" s="144" t="inlineStr">
+        <is>
+          <t>AP days used to project AP = COGS × days/365.</t>
+        </is>
+      </c>
+      <c r="S17" s="144" t="inlineStr">
+        <is>
+          <t>Excel equation: ROUND(I48/I25×365, 0) from FY25.</t>
+        </is>
+      </c>
+      <c r="T17" s="144" t="inlineStr">
+        <is>
+          <t>Payable timing offsets AR in operating NWC.</t>
+        </is>
+      </c>
+      <c r="U17" s="144" t="inlineStr">
+        <is>
+          <t>SEC 10-K FY2025 — Accounts payable</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" hidden="1" outlineLevel="1" ht="42" customHeight="1">
       <c r="B18" s="19" t="inlineStr">
         <is>
           <t>CapEx % of Revenue (fade equation)</t>
         </is>
       </c>
-      <c r="C18" s="144">
-        <f> fade(I68/I24 → 1%)</f>
-        <v/>
-      </c>
-      <c r="E18" s="142">
+      <c r="C18" s="148" t="inlineStr">
+        <is>
+          <t>eqn: fade FY25 CapEx/Sales → 1%</t>
+        </is>
+      </c>
+      <c r="E18" s="146">
         <f>E68</f>
         <v/>
       </c>
-      <c r="F18" s="142">
+      <c r="F18" s="146">
         <f>F68</f>
         <v/>
       </c>
-      <c r="G18" s="142">
+      <c r="G18" s="146">
         <f>G68</f>
         <v/>
       </c>
-      <c r="H18" s="142">
+      <c r="H18" s="146">
         <f>H68</f>
         <v/>
       </c>
-      <c r="I18" s="142">
+      <c r="I18" s="146">
         <f>I68</f>
         <v/>
       </c>
-      <c r="J18" s="143">
+      <c r="J18" s="147">
         <f>($I$68/$I$24)*0.85+0.01*(1-0.85)</f>
         <v/>
       </c>
-      <c r="K18" s="143">
+      <c r="K18" s="147">
         <f>($I$68/$I$24)*0.65+0.01*(1-0.65)</f>
         <v/>
       </c>
-      <c r="L18" s="143">
+      <c r="L18" s="147">
         <f>($I$68/$I$24)*0.45+0.01*(1-0.45)</f>
         <v/>
       </c>
-      <c r="M18" s="143">
+      <c r="M18" s="147">
         <f>($I$68/$I$24)*0.3+0.01*(1-0.3)</f>
         <v/>
       </c>
-      <c r="N18" s="143">
+      <c r="N18" s="147">
         <f>($I$68/$I$24)*0.0+0.01*(1-0.0)</f>
         <v/>
       </c>
-    </row>
-    <row r="19" hidden="1" outlineLevel="1">
+      <c r="P18" s="143" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q18" s="143" t="inlineStr">
+        <is>
+          <t>CapEx % of Revenue</t>
+        </is>
+      </c>
+      <c r="R18" s="144" t="inlineStr">
+        <is>
+          <t>Capital investment (PPE + capitalized software) as % of sales.</t>
+        </is>
+      </c>
+      <c r="S18" s="144" t="inlineStr">
+        <is>
+          <t>Equation: fade from I68/I24 (FY25 CapEx/Sales ~1.98%) toward 1.0% steady. Weights 85%→65%→45%→30%→0% on the peak.</t>
+        </is>
+      </c>
+      <c r="T18" s="144" t="inlineStr">
+        <is>
+          <t>FY25 CapEx was elevated by capitalized internal-use software. Fading avoids locking a peak reinvestment rate forever.</t>
+        </is>
+      </c>
+      <c r="U18" s="144" t="inlineStr">
+        <is>
+          <t>SEC 10-K — PP&amp;E purchases + capitalized software</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" hidden="1" outlineLevel="1" ht="42" customHeight="1">
       <c r="B19" s="19" t="inlineStr">
         <is>
           <t>Debt Issuance (Repayment) ($000's)</t>
         </is>
       </c>
-      <c r="E19" s="142">
+      <c r="C19" s="148" t="inlineStr">
+        <is>
+          <t>POLICY: no new debt issuance</t>
+        </is>
+      </c>
+      <c r="E19" s="146">
         <f>E99</f>
         <v/>
       </c>
-      <c r="F19" s="142">
+      <c r="F19" s="146">
         <f>F99</f>
         <v/>
       </c>
-      <c r="G19" s="142">
+      <c r="G19" s="146">
         <f>G99</f>
         <v/>
       </c>
-      <c r="H19" s="142">
+      <c r="H19" s="146">
         <f>H99</f>
         <v/>
       </c>
-      <c r="I19" s="142">
+      <c r="I19" s="146">
         <f>I99</f>
         <v/>
       </c>
-      <c r="J19" s="147" t="n">
+      <c r="J19" s="151" t="n">
         <v>0</v>
       </c>
-      <c r="K19" s="147" t="n">
+      <c r="K19" s="151" t="n">
         <v>0</v>
       </c>
-      <c r="L19" s="147" t="n">
+      <c r="L19" s="151" t="n">
         <v>0</v>
       </c>
-      <c r="M19" s="147" t="n">
+      <c r="M19" s="151" t="n">
         <v>0</v>
       </c>
-      <c r="N19" s="147" t="n">
+      <c r="N19" s="151" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" hidden="1" outlineLevel="1">
+      <c r="P19" s="143" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q19" s="143" t="inlineStr">
+        <is>
+          <t>Debt Issuance (Repayment)</t>
+        </is>
+      </c>
+      <c r="R19" s="144" t="inlineStr">
+        <is>
+          <t>New borrowing (+) or repayment (−) in the forecast.</t>
+        </is>
+      </c>
+      <c r="S19" s="144" t="inlineStr">
+        <is>
+          <t>POLICY input = 0 every year.</t>
+        </is>
+      </c>
+      <c r="T19" s="144" t="inlineStr">
+        <is>
+          <t>Hold debt stock flat at FY25 level for the explicit period; interest follows. Net debt for DCF equity bridge uses the later 10-Q amount separately.</t>
+        </is>
+      </c>
+      <c r="U19" s="144" t="inlineStr">
+        <is>
+          <t>Modeling choice (financing not in FCFF)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" hidden="1" outlineLevel="1" ht="42" customHeight="1">
       <c r="B20" s="19" t="inlineStr">
         <is>
           <t>Equity Issued (Repaid) ($000's)</t>
         </is>
       </c>
-      <c r="E20" s="142">
+      <c r="C20" s="148" t="inlineStr">
+        <is>
+          <t>POLICY: no equity issuance</t>
+        </is>
+      </c>
+      <c r="E20" s="146">
         <f>E73</f>
         <v/>
       </c>
-      <c r="F20" s="142">
+      <c r="F20" s="146">
         <f>F73</f>
         <v/>
       </c>
-      <c r="G20" s="142">
+      <c r="G20" s="146">
         <f>G73</f>
         <v/>
       </c>
-      <c r="H20" s="142">
+      <c r="H20" s="146">
         <f>H73</f>
         <v/>
       </c>
-      <c r="I20" s="142">
+      <c r="I20" s="146">
         <f>I73</f>
         <v/>
       </c>
-      <c r="J20" s="147" t="n">
+      <c r="J20" s="151" t="n">
         <v>0</v>
       </c>
-      <c r="K20" s="147" t="n">
+      <c r="K20" s="151" t="n">
         <v>0</v>
       </c>
-      <c r="L20" s="147" t="n">
+      <c r="L20" s="151" t="n">
         <v>0</v>
       </c>
-      <c r="M20" s="147" t="n">
+      <c r="M20" s="151" t="n">
         <v>0</v>
       </c>
-      <c r="N20" s="147" t="n">
+      <c r="N20" s="151" t="n">
         <v>0</v>
+      </c>
+      <c r="P20" s="143" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q20" s="143" t="inlineStr">
+        <is>
+          <t>Equity Issued (Repaid)</t>
+        </is>
+      </c>
+      <c r="R20" s="144" t="inlineStr">
+        <is>
+          <t>New equity issued (+) or buybacks (−) in the forecast BS/CF.</t>
+        </is>
+      </c>
+      <c r="S20" s="144" t="inlineStr">
+        <is>
+          <t>POLICY input = 0 every year.</t>
+        </is>
+      </c>
+      <c r="T20" s="144" t="inlineStr">
+        <is>
+          <t>Buybacks are real historically but are financing — excluded from FCFF. Share count for $/share is the spot shares outstanding assumption.</t>
+        </is>
+      </c>
+      <c r="U20" s="144" t="inlineStr">
+        <is>
+          <t>Modeling choice (financing not in FCFF)</t>
+        </is>
       </c>
     </row>
     <row r="21" hidden="1" outlineLevel="1">
@@ -3521,43 +4004,44 @@
           <t>Reveneue</t>
         </is>
       </c>
-      <c r="C24" s="140">
-        <f> PriorRev × (1 + growth)</f>
-        <v/>
+      <c r="C24" s="152" t="inlineStr">
+        <is>
+          <t>eqn: PriorRev × (1 + growth)</t>
+        </is>
       </c>
       <c r="D24" s="46" t="n"/>
-      <c r="E24" s="148" t="n">
+      <c r="E24" s="153" t="n">
         <v>1316536</v>
       </c>
-      <c r="F24" s="148" t="n">
+      <c r="F24" s="153" t="n">
         <v>1377270</v>
       </c>
-      <c r="G24" s="148" t="n">
+      <c r="G24" s="153" t="n">
         <v>1513557</v>
       </c>
-      <c r="H24" s="148" t="n">
+      <c r="H24" s="153" t="n">
         <v>1717526</v>
       </c>
-      <c r="I24" s="148" t="n">
+      <c r="I24" s="153" t="n">
         <v>1990869</v>
       </c>
-      <c r="J24" s="145">
+      <c r="J24" s="149">
         <f>I24*(1+J7)</f>
         <v/>
       </c>
-      <c r="K24" s="145">
+      <c r="K24" s="149">
         <f>J24*(1+K7)</f>
         <v/>
       </c>
-      <c r="L24" s="145">
+      <c r="L24" s="149">
         <f>K24*(1+L7)</f>
         <v/>
       </c>
-      <c r="M24" s="145">
+      <c r="M24" s="149">
         <f>L24*(1+M7)</f>
         <v/>
       </c>
-      <c r="N24" s="145">
+      <c r="N24" s="149">
         <f>M24*(1+N7)</f>
         <v/>
       </c>
@@ -3568,43 +4052,44 @@
           <t>Cost of Goods Sold (COGS)</t>
         </is>
       </c>
-      <c r="C25" s="140">
-        <f> Rev × COGS%</f>
-        <v/>
+      <c r="C25" s="152" t="inlineStr">
+        <is>
+          <t>eqn: Rev × COGS%</t>
+        </is>
       </c>
       <c r="D25" s="47" t="n"/>
-      <c r="E25" s="148" t="n">
+      <c r="E25" s="153" t="n">
         <v>332462</v>
       </c>
-      <c r="F25" s="148" t="n">
+      <c r="F25" s="153" t="n">
         <v>302174</v>
       </c>
-      <c r="G25" s="148" t="n">
+      <c r="G25" s="153" t="n">
         <v>311053</v>
       </c>
-      <c r="H25" s="148" t="n">
+      <c r="H25" s="153" t="n">
         <v>348206</v>
       </c>
-      <c r="I25" s="148" t="n">
+      <c r="I25" s="153" t="n">
         <v>353722</v>
       </c>
-      <c r="J25" s="145">
+      <c r="J25" s="149">
         <f>J24*J8</f>
         <v/>
       </c>
-      <c r="K25" s="145">
+      <c r="K25" s="149">
         <f>K24*K8</f>
         <v/>
       </c>
-      <c r="L25" s="145">
+      <c r="L25" s="149">
         <f>L24*L8</f>
         <v/>
       </c>
-      <c r="M25" s="145">
+      <c r="M25" s="149">
         <f>M24*M8</f>
         <v/>
       </c>
-      <c r="N25" s="145">
+      <c r="N25" s="149">
         <f>N24*N8</f>
         <v/>
       </c>
@@ -3615,48 +4100,49 @@
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="C26" s="149">
-        <f> Rev − COGS</f>
-        <v/>
+      <c r="C26" s="154" t="inlineStr">
+        <is>
+          <t>eqn: Rev − COGS</t>
+        </is>
       </c>
       <c r="D26" s="22" t="n"/>
-      <c r="E26" s="150">
+      <c r="E26" s="155">
         <f>E24-E25</f>
         <v/>
       </c>
-      <c r="F26" s="150">
+      <c r="F26" s="155">
         <f>F24-F25</f>
         <v/>
       </c>
-      <c r="G26" s="150">
+      <c r="G26" s="155">
         <f>G24-G25</f>
         <v/>
       </c>
-      <c r="H26" s="150">
+      <c r="H26" s="155">
         <f>H24-H25</f>
         <v/>
       </c>
-      <c r="I26" s="150">
+      <c r="I26" s="155">
         <f>I24-I25</f>
         <v/>
       </c>
-      <c r="J26" s="145">
+      <c r="J26" s="149">
         <f>J24-J25</f>
         <v/>
       </c>
-      <c r="K26" s="145">
+      <c r="K26" s="149">
         <f>K24-K25</f>
         <v/>
       </c>
-      <c r="L26" s="145">
+      <c r="L26" s="149">
         <f>L24-L25</f>
         <v/>
       </c>
-      <c r="M26" s="145">
+      <c r="M26" s="149">
         <f>M24-M25</f>
         <v/>
       </c>
-      <c r="N26" s="145">
+      <c r="N26" s="149">
         <f>N24-N25</f>
         <v/>
       </c>
@@ -3686,42 +4172,43 @@
           <t>Salaries and Benefits</t>
         </is>
       </c>
-      <c r="C28" s="144">
-        <f> Rev × SGA%</f>
-        <v/>
-      </c>
-      <c r="E28" s="148" t="n">
+      <c r="C28" s="156" t="inlineStr">
+        <is>
+          <t>eqn: Rev × SGA%</t>
+        </is>
+      </c>
+      <c r="E28" s="153" t="n">
         <v>396281</v>
       </c>
-      <c r="F28" s="148" t="n">
+      <c r="F28" s="153" t="n">
         <v>383863</v>
       </c>
-      <c r="G28" s="148" t="n">
+      <c r="G28" s="153" t="n">
         <v>400565</v>
       </c>
-      <c r="H28" s="148" t="n">
+      <c r="H28" s="153" t="n">
         <v>462834</v>
       </c>
-      <c r="I28" s="148" t="n">
+      <c r="I28" s="153" t="n">
         <v>513028</v>
       </c>
-      <c r="J28" s="145">
+      <c r="J28" s="149">
         <f>J24*J9</f>
         <v/>
       </c>
-      <c r="K28" s="145">
+      <c r="K28" s="149">
         <f>K24*K9</f>
         <v/>
       </c>
-      <c r="L28" s="145">
+      <c r="L28" s="149">
         <f>L24*L9</f>
         <v/>
       </c>
-      <c r="M28" s="145">
+      <c r="M28" s="149">
         <f>M24*M9</f>
         <v/>
       </c>
-      <c r="N28" s="145">
+      <c r="N28" s="149">
         <f>N24*N9</f>
         <v/>
       </c>
@@ -3732,42 +4219,43 @@
           <t>Rent and Overhead</t>
         </is>
       </c>
-      <c r="C29" s="144">
-        <f> Rev × R&amp;D%</f>
-        <v/>
-      </c>
-      <c r="E29" s="148" t="n">
+      <c r="C29" s="156" t="inlineStr">
+        <is>
+          <t>eqn: Rev × R&amp;D%</t>
+        </is>
+      </c>
+      <c r="E29" s="153" t="n">
         <v>171231</v>
       </c>
-      <c r="F29" s="148" t="n">
+      <c r="F29" s="153" t="n">
         <v>146758</v>
       </c>
-      <c r="G29" s="148" t="n">
+      <c r="G29" s="153" t="n">
         <v>159950</v>
       </c>
-      <c r="H29" s="148" t="n">
+      <c r="H29" s="153" t="n">
         <v>171940</v>
       </c>
-      <c r="I29" s="148" t="n">
+      <c r="I29" s="153" t="n">
         <v>188347</v>
       </c>
-      <c r="J29" s="145">
+      <c r="J29" s="149">
         <f>J24*J10</f>
         <v/>
       </c>
-      <c r="K29" s="145">
+      <c r="K29" s="149">
         <f>K24*K10</f>
         <v/>
       </c>
-      <c r="L29" s="145">
+      <c r="L29" s="149">
         <f>L24*L10</f>
         <v/>
       </c>
-      <c r="M29" s="145">
+      <c r="M29" s="149">
         <f>M24*M10</f>
         <v/>
       </c>
-      <c r="N29" s="145">
+      <c r="N29" s="149">
         <f>N24*N10</f>
         <v/>
       </c>
@@ -3778,42 +4266,43 @@
           <t>Depreciation &amp; Amortization</t>
         </is>
       </c>
-      <c r="C30" s="144">
-        <f> PPE_open × DA%</f>
-        <v/>
-      </c>
-      <c r="E30" s="148" t="n">
+      <c r="C30" s="156" t="inlineStr">
+        <is>
+          <t>eqn: PPE_open × DA%</t>
+        </is>
+      </c>
+      <c r="E30" s="153" t="n">
         <v>25592</v>
       </c>
-      <c r="F30" s="148" t="n">
+      <c r="F30" s="153" t="n">
         <v>20465</v>
       </c>
-      <c r="G30" s="148" t="n">
+      <c r="G30" s="153" t="n">
         <v>14638</v>
       </c>
-      <c r="H30" s="148" t="n">
+      <c r="H30" s="153" t="n">
         <v>13827</v>
       </c>
-      <c r="I30" s="148" t="n">
+      <c r="I30" s="153" t="n">
         <v>14952</v>
       </c>
-      <c r="J30" s="145">
+      <c r="J30" s="149">
         <f>J92*J11</f>
         <v/>
       </c>
-      <c r="K30" s="145">
+      <c r="K30" s="149">
         <f>K92*K11</f>
         <v/>
       </c>
-      <c r="L30" s="145">
+      <c r="L30" s="149">
         <f>L92*L11</f>
         <v/>
       </c>
-      <c r="M30" s="145">
+      <c r="M30" s="149">
         <f>M92*M11</f>
         <v/>
       </c>
-      <c r="N30" s="145">
+      <c r="N30" s="149">
         <f>N92*N11</f>
         <v/>
       </c>
@@ -3824,43 +4313,44 @@
           <t>Interest</t>
         </is>
       </c>
-      <c r="C31" s="151">
-        <f> Debt_open × Int%</f>
-        <v/>
+      <c r="C31" s="157" t="inlineStr">
+        <is>
+          <t>eqn: Debt_open × Int%</t>
+        </is>
       </c>
       <c r="D31" s="24" t="n"/>
-      <c r="E31" s="152" t="n">
+      <c r="E31" s="158" t="n">
         <v>40092</v>
       </c>
-      <c r="F31" s="152" t="n">
+      <c r="F31" s="158" t="n">
         <v>68967</v>
       </c>
-      <c r="G31" s="152" t="n">
+      <c r="G31" s="158" t="n">
         <v>95546</v>
       </c>
-      <c r="H31" s="152" t="n">
+      <c r="H31" s="158" t="n">
         <v>105638</v>
       </c>
-      <c r="I31" s="152" t="n">
+      <c r="I31" s="158" t="n">
         <v>133647</v>
       </c>
-      <c r="J31" s="145">
+      <c r="J31" s="149">
         <f>J98*J12</f>
         <v/>
       </c>
-      <c r="K31" s="145">
+      <c r="K31" s="149">
         <f>K98*K12</f>
         <v/>
       </c>
-      <c r="L31" s="145">
+      <c r="L31" s="149">
         <f>L98*L12</f>
         <v/>
       </c>
-      <c r="M31" s="145">
+      <c r="M31" s="149">
         <f>M98*M12</f>
         <v/>
       </c>
-      <c r="N31" s="145">
+      <c r="N31" s="149">
         <f>N98*N12</f>
         <v/>
       </c>
@@ -3873,43 +4363,43 @@
       </c>
       <c r="C32" s="19" t="n"/>
       <c r="D32" s="47" t="n"/>
-      <c r="E32" s="153">
+      <c r="E32" s="159">
         <f>SUM(E28:E31)</f>
         <v/>
       </c>
-      <c r="F32" s="153">
+      <c r="F32" s="159">
         <f>SUM(F28:F31)</f>
         <v/>
       </c>
-      <c r="G32" s="153">
+      <c r="G32" s="159">
         <f>SUM(G28:G31)</f>
         <v/>
       </c>
-      <c r="H32" s="153">
+      <c r="H32" s="159">
         <f>SUM(H28:H31)</f>
         <v/>
       </c>
-      <c r="I32" s="153">
+      <c r="I32" s="159">
         <f>SUM(I28:I31)</f>
         <v/>
       </c>
-      <c r="J32" s="145">
+      <c r="J32" s="149">
         <f>SUM(J28:J31)</f>
         <v/>
       </c>
-      <c r="K32" s="145">
+      <c r="K32" s="149">
         <f>SUM(K28:K31)</f>
         <v/>
       </c>
-      <c r="L32" s="145">
+      <c r="L32" s="149">
         <f>SUM(L28:L31)</f>
         <v/>
       </c>
-      <c r="M32" s="145">
+      <c r="M32" s="149">
         <f>SUM(M28:M31)</f>
         <v/>
       </c>
-      <c r="N32" s="145">
+      <c r="N32" s="149">
         <f>SUM(N28:N31)</f>
         <v/>
       </c>
@@ -3920,48 +4410,49 @@
           <t>Earnings Before Tax</t>
         </is>
       </c>
-      <c r="C33" s="149">
-        <f> GP − Expenses</f>
-        <v/>
+      <c r="C33" s="154" t="inlineStr">
+        <is>
+          <t>eqn: GP − Expenses</t>
+        </is>
       </c>
       <c r="D33" s="22" t="n"/>
-      <c r="E33" s="150">
+      <c r="E33" s="155">
         <f>E26-E32</f>
         <v/>
       </c>
-      <c r="F33" s="150">
+      <c r="F33" s="155">
         <f>F26-F32</f>
         <v/>
       </c>
-      <c r="G33" s="150">
+      <c r="G33" s="155">
         <f>G26-G32</f>
         <v/>
       </c>
-      <c r="H33" s="150">
+      <c r="H33" s="155">
         <f>H26-H32</f>
         <v/>
       </c>
-      <c r="I33" s="150">
+      <c r="I33" s="155">
         <f>I26-I32</f>
         <v/>
       </c>
-      <c r="J33" s="145">
+      <c r="J33" s="149">
         <f>J26-J32</f>
         <v/>
       </c>
-      <c r="K33" s="145">
+      <c r="K33" s="149">
         <f>K26-K32</f>
         <v/>
       </c>
-      <c r="L33" s="145">
+      <c r="L33" s="149">
         <f>L26-L32</f>
         <v/>
       </c>
-      <c r="M33" s="145">
+      <c r="M33" s="149">
         <f>M26-M32</f>
         <v/>
       </c>
-      <c r="N33" s="145">
+      <c r="N33" s="149">
         <f>N26-N32</f>
         <v/>
       </c>
@@ -3987,43 +4478,44 @@
           <t>Taxes</t>
         </is>
       </c>
-      <c r="C35" s="140">
-        <f> EBT × tax%</f>
-        <v/>
+      <c r="C35" s="152" t="inlineStr">
+        <is>
+          <t>eqn: EBT × tax%</t>
+        </is>
       </c>
       <c r="D35" s="47" t="n"/>
-      <c r="E35" s="148" t="n">
+      <c r="E35" s="153" t="n">
         <v>81058</v>
       </c>
-      <c r="F35" s="148" t="n">
+      <c r="F35" s="153" t="n">
         <v>97768</v>
       </c>
-      <c r="G35" s="148" t="n">
+      <c r="G35" s="153" t="n">
         <v>124249</v>
       </c>
-      <c r="H35" s="148" t="n">
+      <c r="H35" s="153" t="n">
         <v>129214</v>
       </c>
-      <c r="I35" s="148" t="n">
+      <c r="I35" s="153" t="n">
         <v>150649</v>
       </c>
-      <c r="J35" s="145">
+      <c r="J35" s="149">
         <f>J33*J13</f>
         <v/>
       </c>
-      <c r="K35" s="145">
+      <c r="K35" s="149">
         <f>K33*K13</f>
         <v/>
       </c>
-      <c r="L35" s="145">
+      <c r="L35" s="149">
         <f>L33*L13</f>
         <v/>
       </c>
-      <c r="M35" s="145">
+      <c r="M35" s="149">
         <f>M33*M13</f>
         <v/>
       </c>
-      <c r="N35" s="145">
+      <c r="N35" s="149">
         <f>N33*N13</f>
         <v/>
       </c>
@@ -4034,48 +4526,49 @@
           <t>Net Earnings</t>
         </is>
       </c>
-      <c r="C36" s="154">
-        <f> EBT × (1 − tax%)   ← grows with Rev×(1+g)</f>
-        <v/>
+      <c r="C36" s="160" t="inlineStr">
+        <is>
+          <t>eqn: EBT × (1 − tax%)  — grows with Rev×(1+g)</t>
+        </is>
       </c>
       <c r="D36" s="40" t="n"/>
-      <c r="E36" s="155">
+      <c r="E36" s="161">
         <f>E33-E35</f>
         <v/>
       </c>
-      <c r="F36" s="155">
+      <c r="F36" s="161">
         <f>F33-F35</f>
         <v/>
       </c>
-      <c r="G36" s="155">
+      <c r="G36" s="161">
         <f>G33-G35</f>
         <v/>
       </c>
-      <c r="H36" s="155">
+      <c r="H36" s="161">
         <f>H33-H35</f>
         <v/>
       </c>
-      <c r="I36" s="155">
+      <c r="I36" s="161">
         <f>I33-I35</f>
         <v/>
       </c>
-      <c r="J36" s="145">
+      <c r="J36" s="149">
         <f>J33*(1-J13)</f>
         <v/>
       </c>
-      <c r="K36" s="145">
+      <c r="K36" s="149">
         <f>K33*(1-K13)</f>
         <v/>
       </c>
-      <c r="L36" s="145">
+      <c r="L36" s="149">
         <f>L33*(1-L13)</f>
         <v/>
       </c>
-      <c r="M36" s="145">
+      <c r="M36" s="149">
         <f>M33*(1-M13)</f>
         <v/>
       </c>
-      <c r="N36" s="145">
+      <c r="N36" s="149">
         <f>N33*(1-N13)</f>
         <v/>
       </c>
@@ -4136,38 +4629,38 @@
           <t>Cash</t>
         </is>
       </c>
-      <c r="E41" s="148" t="n">
+      <c r="E41" s="153" t="n">
         <v>195354</v>
       </c>
-      <c r="F41" s="148" t="n">
+      <c r="F41" s="153" t="n">
         <v>133202</v>
       </c>
-      <c r="G41" s="148" t="n">
+      <c r="G41" s="153" t="n">
         <v>136778</v>
       </c>
-      <c r="H41" s="148" t="n">
+      <c r="H41" s="153" t="n">
         <v>150667</v>
       </c>
-      <c r="I41" s="148" t="n">
+      <c r="I41" s="153" t="n">
         <v>134136</v>
       </c>
-      <c r="J41" s="145">
+      <c r="J41" s="149">
         <f>J78</f>
         <v/>
       </c>
-      <c r="K41" s="145">
+      <c r="K41" s="149">
         <f>K78</f>
         <v/>
       </c>
-      <c r="L41" s="145">
+      <c r="L41" s="149">
         <f>L78</f>
         <v/>
       </c>
-      <c r="M41" s="145">
+      <c r="M41" s="149">
         <f>M78</f>
         <v/>
       </c>
-      <c r="N41" s="145">
+      <c r="N41" s="149">
         <f>N78</f>
         <v/>
       </c>
@@ -4178,42 +4671,43 @@
           <t>Accounts Receivable</t>
         </is>
       </c>
-      <c r="C42" s="144">
-        <f> Rev × AR_days / 365</f>
-        <v/>
-      </c>
-      <c r="E42" s="148" t="n">
+      <c r="C42" s="156" t="inlineStr">
+        <is>
+          <t>eqn: Rev × AR_days / 365</t>
+        </is>
+      </c>
+      <c r="E42" s="153" t="n">
         <v>206690</v>
       </c>
-      <c r="F42" s="148" t="n">
+      <c r="F42" s="153" t="n">
         <v>202365</v>
       </c>
-      <c r="G42" s="148" t="n">
+      <c r="G42" s="153" t="n">
         <v>251217</v>
       </c>
-      <c r="H42" s="148" t="n">
+      <c r="H42" s="153" t="n">
         <v>269745</v>
       </c>
-      <c r="I42" s="148" t="n">
+      <c r="I42" s="153" t="n">
         <v>341776</v>
       </c>
-      <c r="J42" s="145">
+      <c r="J42" s="149">
         <f>J24*J15/365</f>
         <v/>
       </c>
-      <c r="K42" s="145">
+      <c r="K42" s="149">
         <f>K24*K15/365</f>
         <v/>
       </c>
-      <c r="L42" s="145">
+      <c r="L42" s="149">
         <f>L24*L15/365</f>
         <v/>
       </c>
-      <c r="M42" s="145">
+      <c r="M42" s="149">
         <f>M24*M15/365</f>
         <v/>
       </c>
-      <c r="N42" s="145">
+      <c r="N42" s="149">
         <f>N24*N15/365</f>
         <v/>
       </c>
@@ -4224,38 +4718,38 @@
           <t>Inventory</t>
         </is>
       </c>
-      <c r="E43" s="148" t="n">
+      <c r="E43" s="153" t="n">
         <v>0</v>
       </c>
-      <c r="F43" s="148" t="n">
+      <c r="F43" s="153" t="n">
         <v>0</v>
       </c>
-      <c r="G43" s="148" t="n">
+      <c r="G43" s="153" t="n">
         <v>0</v>
       </c>
-      <c r="H43" s="148" t="n">
+      <c r="H43" s="153" t="n">
         <v>0</v>
       </c>
-      <c r="I43" s="148" t="n">
+      <c r="I43" s="153" t="n">
         <v>0</v>
       </c>
-      <c r="J43" s="145">
+      <c r="J43" s="149">
         <f>J25*J16/365</f>
         <v/>
       </c>
-      <c r="K43" s="145">
+      <c r="K43" s="149">
         <f>K25*K16/365</f>
         <v/>
       </c>
-      <c r="L43" s="145">
+      <c r="L43" s="149">
         <f>L25*L16/365</f>
         <v/>
       </c>
-      <c r="M43" s="145">
+      <c r="M43" s="149">
         <f>M25*M16/365</f>
         <v/>
       </c>
-      <c r="N43" s="145">
+      <c r="N43" s="149">
         <f>N25*N16/365</f>
         <v/>
       </c>
@@ -4266,38 +4760,38 @@
           <t>Property &amp; Equipment</t>
         </is>
       </c>
-      <c r="E44" s="148" t="n">
+      <c r="E44" s="153" t="n">
         <v>27913</v>
       </c>
-      <c r="F44" s="148" t="n">
+      <c r="F44" s="153" t="n">
         <v>17580</v>
       </c>
-      <c r="G44" s="148" t="n">
+      <c r="G44" s="153" t="n">
         <v>10966</v>
       </c>
-      <c r="H44" s="148" t="n">
+      <c r="H44" s="153" t="n">
         <v>38465</v>
       </c>
-      <c r="I44" s="148" t="n">
+      <c r="I44" s="153" t="n">
         <v>67713</v>
       </c>
-      <c r="J44" s="145">
+      <c r="J44" s="149">
         <f>J95</f>
         <v/>
       </c>
-      <c r="K44" s="145">
+      <c r="K44" s="149">
         <f>K95</f>
         <v/>
       </c>
-      <c r="L44" s="145">
+      <c r="L44" s="149">
         <f>L95</f>
         <v/>
       </c>
-      <c r="M44" s="145">
+      <c r="M44" s="149">
         <f>M95</f>
         <v/>
       </c>
-      <c r="N44" s="145">
+      <c r="N44" s="149">
         <f>N95</f>
         <v/>
       </c>
@@ -4310,43 +4804,43 @@
       </c>
       <c r="C45" s="39" t="n"/>
       <c r="D45" s="40" t="n"/>
-      <c r="E45" s="155">
+      <c r="E45" s="161">
         <f>SUM(E41:E44)</f>
         <v/>
       </c>
-      <c r="F45" s="155">
+      <c r="F45" s="161">
         <f>SUM(F41:F44)</f>
         <v/>
       </c>
-      <c r="G45" s="155">
+      <c r="G45" s="161">
         <f>SUM(G41:G44)</f>
         <v/>
       </c>
-      <c r="H45" s="155">
+      <c r="H45" s="161">
         <f>SUM(H41:H44)</f>
         <v/>
       </c>
-      <c r="I45" s="155">
+      <c r="I45" s="161">
         <f>SUM(I41:I44)</f>
         <v/>
       </c>
-      <c r="J45" s="145">
+      <c r="J45" s="149">
         <f>SUM(J41:J44)</f>
         <v/>
       </c>
-      <c r="K45" s="145">
+      <c r="K45" s="149">
         <f>SUM(K41:K44)</f>
         <v/>
       </c>
-      <c r="L45" s="145">
+      <c r="L45" s="149">
         <f>SUM(L41:L44)</f>
         <v/>
       </c>
-      <c r="M45" s="145">
+      <c r="M45" s="149">
         <f>SUM(M41:M44)</f>
         <v/>
       </c>
-      <c r="N45" s="145">
+      <c r="N45" s="149">
         <f>SUM(N41:N44)</f>
         <v/>
       </c>
@@ -4384,42 +4878,43 @@
           <t>Accounts Payable</t>
         </is>
       </c>
-      <c r="C48" s="144">
-        <f> COGS × AP_days / 365</f>
-        <v/>
-      </c>
-      <c r="E48" s="148" t="n">
+      <c r="C48" s="156" t="inlineStr">
+        <is>
+          <t>eqn: COGS × AP_days / 365</t>
+        </is>
+      </c>
+      <c r="E48" s="153" t="n">
         <v>20749</v>
       </c>
-      <c r="F48" s="148" t="n">
+      <c r="F48" s="153" t="n">
         <v>17273</v>
       </c>
-      <c r="G48" s="148" t="n">
+      <c r="G48" s="153" t="n">
         <v>19009</v>
       </c>
-      <c r="H48" s="148" t="n">
+      <c r="H48" s="153" t="n">
         <v>22473</v>
       </c>
-      <c r="I48" s="148" t="n">
+      <c r="I48" s="153" t="n">
         <v>32315</v>
       </c>
-      <c r="J48" s="145">
+      <c r="J48" s="149">
         <f>J25*J17/365</f>
         <v/>
       </c>
-      <c r="K48" s="145">
+      <c r="K48" s="149">
         <f>K25*K17/365</f>
         <v/>
       </c>
-      <c r="L48" s="145">
+      <c r="L48" s="149">
         <f>L25*L17/365</f>
         <v/>
       </c>
-      <c r="M48" s="145">
+      <c r="M48" s="149">
         <f>M25*M17/365</f>
         <v/>
       </c>
-      <c r="N48" s="145">
+      <c r="N48" s="149">
         <f>N25*N17/365</f>
         <v/>
       </c>
@@ -4430,38 +4925,38 @@
           <t>Debt</t>
         </is>
       </c>
-      <c r="E49" s="148" t="n">
+      <c r="E49" s="153" t="n">
         <v>1259018</v>
       </c>
-      <c r="F49" s="148" t="n">
+      <c r="F49" s="153" t="n">
         <v>1853669</v>
       </c>
-      <c r="G49" s="148" t="n">
+      <c r="G49" s="153" t="n">
         <v>1861658</v>
       </c>
-      <c r="H49" s="148" t="n">
+      <c r="H49" s="153" t="n">
         <v>2209021</v>
       </c>
-      <c r="I49" s="148" t="n">
+      <c r="I49" s="153" t="n">
         <v>3055691</v>
       </c>
-      <c r="J49" s="145">
+      <c r="J49" s="149">
         <f>J100</f>
         <v/>
       </c>
-      <c r="K49" s="145">
+      <c r="K49" s="149">
         <f>K100</f>
         <v/>
       </c>
-      <c r="L49" s="145">
+      <c r="L49" s="149">
         <f>L100</f>
         <v/>
       </c>
-      <c r="M49" s="145">
+      <c r="M49" s="149">
         <f>M100</f>
         <v/>
       </c>
-      <c r="N49" s="145">
+      <c r="N49" s="149">
         <f>N100</f>
         <v/>
       </c>
@@ -4474,43 +4969,43 @@
       </c>
       <c r="C50" s="4" t="n"/>
       <c r="D50" s="22" t="n"/>
-      <c r="E50" s="150">
+      <c r="E50" s="155">
         <f>SUM(E48:E49)</f>
         <v/>
       </c>
-      <c r="F50" s="150">
+      <c r="F50" s="155">
         <f>SUM(F48:F49)</f>
         <v/>
       </c>
-      <c r="G50" s="150">
+      <c r="G50" s="155">
         <f>SUM(G48:G49)</f>
         <v/>
       </c>
-      <c r="H50" s="150">
+      <c r="H50" s="155">
         <f>SUM(H48:H49)</f>
         <v/>
       </c>
-      <c r="I50" s="150">
+      <c r="I50" s="155">
         <f>SUM(I48:I49)</f>
         <v/>
       </c>
-      <c r="J50" s="145">
+      <c r="J50" s="149">
         <f>SUM(J48:J49)</f>
         <v/>
       </c>
-      <c r="K50" s="145">
+      <c r="K50" s="149">
         <f>SUM(K48:K49)</f>
         <v/>
       </c>
-      <c r="L50" s="145">
+      <c r="L50" s="149">
         <f>SUM(L48:L49)</f>
         <v/>
       </c>
-      <c r="M50" s="145">
+      <c r="M50" s="149">
         <f>SUM(M48:M49)</f>
         <v/>
       </c>
-      <c r="N50" s="145">
+      <c r="N50" s="149">
         <f>SUM(N48:N49)</f>
         <v/>
       </c>
@@ -4533,38 +5028,38 @@
           <t>Equity Capital</t>
         </is>
       </c>
-      <c r="E52" s="148" t="n">
+      <c r="E52" s="153" t="n">
         <v>-849810</v>
       </c>
-      <c r="F52" s="148" t="n">
+      <c r="F52" s="153" t="n">
         <v>-1517795</v>
       </c>
-      <c r="G52" s="148" t="n">
+      <c r="G52" s="153" t="n">
         <v>-1481706</v>
       </c>
-      <c r="H52" s="148" t="n">
+      <c r="H52" s="153" t="n">
         <v>-1772617</v>
       </c>
-      <c r="I52" s="148" t="n">
+      <c r="I52" s="153" t="n">
         <v>-2544381</v>
       </c>
-      <c r="J52" s="145">
+      <c r="J52" s="149">
         <f>I52+J20</f>
         <v/>
       </c>
-      <c r="K52" s="145">
+      <c r="K52" s="149">
         <f>J52+K20</f>
         <v/>
       </c>
-      <c r="L52" s="145">
+      <c r="L52" s="149">
         <f>K52+L20</f>
         <v/>
       </c>
-      <c r="M52" s="145">
+      <c r="M52" s="149">
         <f>L52+M20</f>
         <v/>
       </c>
-      <c r="N52" s="145">
+      <c r="N52" s="149">
         <f>M52+N20</f>
         <v/>
       </c>
@@ -4575,42 +5070,43 @@
           <t>Retained Earnings</t>
         </is>
       </c>
-      <c r="C53" s="144">
-        <f> PriorRE + EBT×(1−t)</f>
-        <v/>
-      </c>
-      <c r="E53" s="148" t="n">
+      <c r="C53" s="156" t="inlineStr">
+        <is>
+          <t>eqn: PriorRE + EBT×(1−t)</t>
+        </is>
+      </c>
+      <c r="E53" s="153" t="n">
         <v>0</v>
       </c>
-      <c r="F53" s="148" t="n">
+      <c r="F53" s="153" t="n">
         <v>0</v>
       </c>
-      <c r="G53" s="148" t="n">
+      <c r="G53" s="153" t="n">
         <v>0</v>
       </c>
-      <c r="H53" s="148" t="n">
+      <c r="H53" s="153" t="n">
         <v>0</v>
       </c>
-      <c r="I53" s="148" t="n">
+      <c r="I53" s="153" t="n">
         <v>0</v>
       </c>
-      <c r="J53" s="145">
+      <c r="J53" s="149">
         <f>I53+J33*(1-J13)</f>
         <v/>
       </c>
-      <c r="K53" s="145">
+      <c r="K53" s="149">
         <f>J53+K33*(1-K13)</f>
         <v/>
       </c>
-      <c r="L53" s="145">
+      <c r="L53" s="149">
         <f>K53+L33*(1-L13)</f>
         <v/>
       </c>
-      <c r="M53" s="145">
+      <c r="M53" s="149">
         <f>L53+M33*(1-M13)</f>
         <v/>
       </c>
-      <c r="N53" s="145">
+      <c r="N53" s="149">
         <f>M53+N33*(1-N13)</f>
         <v/>
       </c>
@@ -4623,43 +5119,43 @@
       </c>
       <c r="C54" s="8" t="n"/>
       <c r="D54" s="26" t="n"/>
-      <c r="E54" s="156">
+      <c r="E54" s="162">
         <f>SUM(E52:E53)</f>
         <v/>
       </c>
-      <c r="F54" s="156">
+      <c r="F54" s="162">
         <f>SUM(F52:F53)</f>
         <v/>
       </c>
-      <c r="G54" s="156">
+      <c r="G54" s="162">
         <f>SUM(G52:G53)</f>
         <v/>
       </c>
-      <c r="H54" s="156">
+      <c r="H54" s="162">
         <f>SUM(H52:H53)</f>
         <v/>
       </c>
-      <c r="I54" s="156">
+      <c r="I54" s="162">
         <f>SUM(I52:I53)</f>
         <v/>
       </c>
-      <c r="J54" s="145">
+      <c r="J54" s="149">
         <f>SUM(J52:J53)</f>
         <v/>
       </c>
-      <c r="K54" s="145">
+      <c r="K54" s="149">
         <f>SUM(K52:K53)</f>
         <v/>
       </c>
-      <c r="L54" s="145">
+      <c r="L54" s="149">
         <f>SUM(L52:L53)</f>
         <v/>
       </c>
-      <c r="M54" s="145">
+      <c r="M54" s="149">
         <f>SUM(M52:M53)</f>
         <v/>
       </c>
-      <c r="N54" s="145">
+      <c r="N54" s="149">
         <f>SUM(N52:N53)</f>
         <v/>
       </c>
@@ -4672,43 +5168,43 @@
       </c>
       <c r="C55" s="39" t="n"/>
       <c r="D55" s="40" t="n"/>
-      <c r="E55" s="155">
+      <c r="E55" s="161">
         <f>E50+E54</f>
         <v/>
       </c>
-      <c r="F55" s="155">
+      <c r="F55" s="161">
         <f>F50+F54</f>
         <v/>
       </c>
-      <c r="G55" s="155">
+      <c r="G55" s="161">
         <f>G50+G54</f>
         <v/>
       </c>
-      <c r="H55" s="155">
+      <c r="H55" s="161">
         <f>H50+H54</f>
         <v/>
       </c>
-      <c r="I55" s="155">
+      <c r="I55" s="161">
         <f>I50+I54</f>
         <v/>
       </c>
-      <c r="J55" s="145">
+      <c r="J55" s="149">
         <f>J50+J54</f>
         <v/>
       </c>
-      <c r="K55" s="145">
+      <c r="K55" s="149">
         <f>K50+K54</f>
         <v/>
       </c>
-      <c r="L55" s="145">
+      <c r="L55" s="149">
         <f>L50+L54</f>
         <v/>
       </c>
-      <c r="M55" s="145">
+      <c r="M55" s="149">
         <f>M50+M54</f>
         <v/>
       </c>
-      <c r="N55" s="145">
+      <c r="N55" s="149">
         <f>N50+N54</f>
         <v/>
       </c>
@@ -4733,43 +5229,43 @@
       </c>
       <c r="C57" s="9" t="n"/>
       <c r="D57" s="27" t="n"/>
-      <c r="E57" s="157">
+      <c r="E57" s="163">
         <f>E55-E45</f>
         <v/>
       </c>
-      <c r="F57" s="157">
+      <c r="F57" s="163">
         <f>F55-F45</f>
         <v/>
       </c>
-      <c r="G57" s="157">
+      <c r="G57" s="163">
         <f>G55-G45</f>
         <v/>
       </c>
-      <c r="H57" s="157">
+      <c r="H57" s="163">
         <f>H55-H45</f>
         <v/>
       </c>
-      <c r="I57" s="157">
+      <c r="I57" s="163">
         <f>I55-I45</f>
         <v/>
       </c>
-      <c r="J57" s="145">
+      <c r="J57" s="149">
         <f>J55-J45</f>
         <v/>
       </c>
-      <c r="K57" s="145">
+      <c r="K57" s="149">
         <f>K55-K45</f>
         <v/>
       </c>
-      <c r="L57" s="145">
+      <c r="L57" s="149">
         <f>L55-L45</f>
         <v/>
       </c>
-      <c r="M57" s="145">
+      <c r="M57" s="149">
         <f>M55-M45</f>
         <v/>
       </c>
-      <c r="N57" s="145">
+      <c r="N57" s="149">
         <f>N55-N45</f>
         <v/>
       </c>
@@ -4833,47 +5329,48 @@
           <t>Net Earnings</t>
         </is>
       </c>
-      <c r="C62" s="144">
-        <f> EBT × (1 − tax%)     ← FULL eqn, not =J36</f>
-        <v/>
-      </c>
-      <c r="E62" s="158">
+      <c r="C62" s="156" t="inlineStr">
+        <is>
+          <t>eqn: EBT × (1 − tax%)  — full eqn, not pointer to IS</t>
+        </is>
+      </c>
+      <c r="E62" s="164">
         <f>E36</f>
         <v/>
       </c>
-      <c r="F62" s="158">
+      <c r="F62" s="164">
         <f>F36</f>
         <v/>
       </c>
-      <c r="G62" s="158">
+      <c r="G62" s="164">
         <f>G36</f>
         <v/>
       </c>
-      <c r="H62" s="158">
+      <c r="H62" s="164">
         <f>H36</f>
         <v/>
       </c>
-      <c r="I62" s="158">
+      <c r="I62" s="164">
         <f>I36</f>
         <v/>
       </c>
-      <c r="J62" s="145">
+      <c r="J62" s="149">
         <f>J33*(1-J13)</f>
         <v/>
       </c>
-      <c r="K62" s="145">
+      <c r="K62" s="149">
         <f>K33*(1-K13)</f>
         <v/>
       </c>
-      <c r="L62" s="145">
+      <c r="L62" s="149">
         <f>L33*(1-L13)</f>
         <v/>
       </c>
-      <c r="M62" s="145">
+      <c r="M62" s="149">
         <f>M33*(1-M13)</f>
         <v/>
       </c>
-      <c r="N62" s="145">
+      <c r="N62" s="149">
         <f>N33*(1-N13)</f>
         <v/>
       </c>
@@ -4884,47 +5381,48 @@
           <t>Plus: Depreciation &amp; Amortization</t>
         </is>
       </c>
-      <c r="C63" s="144">
-        <f> PPE_open × DA%</f>
-        <v/>
-      </c>
-      <c r="E63" s="158">
+      <c r="C63" s="156" t="inlineStr">
+        <is>
+          <t>eqn: PPE_open × DA%</t>
+        </is>
+      </c>
+      <c r="E63" s="164">
         <f>+E30</f>
         <v/>
       </c>
-      <c r="F63" s="158">
+      <c r="F63" s="164">
         <f>+F30</f>
         <v/>
       </c>
-      <c r="G63" s="158">
+      <c r="G63" s="164">
         <f>+G30</f>
         <v/>
       </c>
-      <c r="H63" s="158">
+      <c r="H63" s="164">
         <f>+H30</f>
         <v/>
       </c>
-      <c r="I63" s="158">
+      <c r="I63" s="164">
         <f>+I30</f>
         <v/>
       </c>
-      <c r="J63" s="145">
+      <c r="J63" s="149">
         <f>J92*J11</f>
         <v/>
       </c>
-      <c r="K63" s="145">
+      <c r="K63" s="149">
         <f>K92*K11</f>
         <v/>
       </c>
-      <c r="L63" s="145">
+      <c r="L63" s="149">
         <f>L92*L11</f>
         <v/>
       </c>
-      <c r="M63" s="145">
+      <c r="M63" s="149">
         <f>M92*M11</f>
         <v/>
       </c>
-      <c r="N63" s="145">
+      <c r="N63" s="149">
         <f>N92*N11</f>
         <v/>
       </c>
@@ -4935,42 +5433,43 @@
           <t>Less: Changes in Working Capital</t>
         </is>
       </c>
-      <c r="C64" s="144">
-        <f> NWC_t − NWC_t−1</f>
-        <v/>
-      </c>
-      <c r="E64" s="148" t="n">
+      <c r="C64" s="156" t="inlineStr">
+        <is>
+          <t>eqn: NWC_t − NWC_t−1</t>
+        </is>
+      </c>
+      <c r="E64" s="153" t="n">
         <v>0</v>
       </c>
-      <c r="F64" s="148" t="n">
+      <c r="F64" s="153" t="n">
         <v>-849</v>
       </c>
-      <c r="G64" s="148" t="n">
+      <c r="G64" s="153" t="n">
         <v>47116</v>
       </c>
-      <c r="H64" s="148" t="n">
+      <c r="H64" s="153" t="n">
         <v>15064</v>
       </c>
-      <c r="I64" s="148" t="n">
+      <c r="I64" s="153" t="n">
         <v>62189</v>
       </c>
-      <c r="J64" s="145">
+      <c r="J64" s="149">
         <f>J88-I88</f>
         <v/>
       </c>
-      <c r="K64" s="145">
+      <c r="K64" s="149">
         <f>K88-J88</f>
         <v/>
       </c>
-      <c r="L64" s="145">
+      <c r="L64" s="149">
         <f>L88-K88</f>
         <v/>
       </c>
-      <c r="M64" s="145">
+      <c r="M64" s="149">
         <f>M88-L88</f>
         <v/>
       </c>
-      <c r="N64" s="145">
+      <c r="N64" s="149">
         <f>N88-M88</f>
         <v/>
       </c>
@@ -4981,48 +5480,49 @@
           <t>Cash from Operations</t>
         </is>
       </c>
-      <c r="C65" s="149">
-        <f> NI + DA − ΔNWC</f>
-        <v/>
+      <c r="C65" s="154" t="inlineStr">
+        <is>
+          <t>eqn: NI + DA − ΔNWC</t>
+        </is>
       </c>
       <c r="D65" s="28" t="n"/>
-      <c r="E65" s="150">
+      <c r="E65" s="155">
         <f>E62+E63-E64</f>
         <v/>
       </c>
-      <c r="F65" s="150">
+      <c r="F65" s="155">
         <f>F62+F63-F64</f>
         <v/>
       </c>
-      <c r="G65" s="150">
+      <c r="G65" s="155">
         <f>G62+G63-G64</f>
         <v/>
       </c>
-      <c r="H65" s="150">
+      <c r="H65" s="155">
         <f>H62+H63-H64</f>
         <v/>
       </c>
-      <c r="I65" s="150">
+      <c r="I65" s="155">
         <f>I62+I63-I64</f>
         <v/>
       </c>
-      <c r="J65" s="145">
+      <c r="J65" s="149">
         <f>J33*(1-J13)+J92*J11-(J88-I88)</f>
         <v/>
       </c>
-      <c r="K65" s="145">
+      <c r="K65" s="149">
         <f>K33*(1-K13)+K92*K11-(K88-J88)</f>
         <v/>
       </c>
-      <c r="L65" s="145">
+      <c r="L65" s="149">
         <f>L33*(1-L13)+L92*L11-(L88-K88)</f>
         <v/>
       </c>
-      <c r="M65" s="145">
+      <c r="M65" s="149">
         <f>M33*(1-M13)+M92*M11-(M88-L88)</f>
         <v/>
       </c>
-      <c r="N65" s="145">
+      <c r="N65" s="149">
         <f>N33*(1-N13)+N92*N11-(N88-M88)</f>
         <v/>
       </c>
@@ -5065,42 +5565,43 @@
           <t>Investments in Property &amp; Equipment</t>
         </is>
       </c>
-      <c r="C68" s="144">
-        <f> Rev × CapEx%</f>
-        <v/>
-      </c>
-      <c r="E68" s="148" t="n">
+      <c r="C68" s="156" t="inlineStr">
+        <is>
+          <t>eqn: Rev × CapEx%</t>
+        </is>
+      </c>
+      <c r="E68" s="153" t="n">
         <v>7569</v>
       </c>
-      <c r="F68" s="148" t="n">
+      <c r="F68" s="153" t="n">
         <v>6029</v>
       </c>
-      <c r="G68" s="148" t="n">
+      <c r="G68" s="153" t="n">
         <v>4237</v>
       </c>
-      <c r="H68" s="148" t="n">
+      <c r="H68" s="153" t="n">
         <v>25551</v>
       </c>
-      <c r="I68" s="148" t="n">
+      <c r="I68" s="153" t="n">
         <v>39407</v>
       </c>
-      <c r="J68" s="145">
+      <c r="J68" s="149">
         <f>J24*J18</f>
         <v/>
       </c>
-      <c r="K68" s="145">
+      <c r="K68" s="149">
         <f>K24*K18</f>
         <v/>
       </c>
-      <c r="L68" s="145">
+      <c r="L68" s="149">
         <f>L24*L18</f>
         <v/>
       </c>
-      <c r="M68" s="145">
+      <c r="M68" s="149">
         <f>M24*M18</f>
         <v/>
       </c>
-      <c r="N68" s="145">
+      <c r="N68" s="149">
         <f>N24*N18</f>
         <v/>
       </c>
@@ -5113,43 +5614,43 @@
       </c>
       <c r="C69" s="5" t="n"/>
       <c r="D69" s="28" t="n"/>
-      <c r="E69" s="150">
+      <c r="E69" s="155">
         <f>SUM(E68)</f>
         <v/>
       </c>
-      <c r="F69" s="150">
+      <c r="F69" s="155">
         <f>SUM(F68)</f>
         <v/>
       </c>
-      <c r="G69" s="150">
+      <c r="G69" s="155">
         <f>SUM(G68)</f>
         <v/>
       </c>
-      <c r="H69" s="150">
+      <c r="H69" s="155">
         <f>SUM(H68)</f>
         <v/>
       </c>
-      <c r="I69" s="150">
+      <c r="I69" s="155">
         <f>SUM(I68)</f>
         <v/>
       </c>
-      <c r="J69" s="145">
+      <c r="J69" s="149">
         <f>J68</f>
         <v/>
       </c>
-      <c r="K69" s="145">
+      <c r="K69" s="149">
         <f>K68</f>
         <v/>
       </c>
-      <c r="L69" s="145">
+      <c r="L69" s="149">
         <f>L68</f>
         <v/>
       </c>
-      <c r="M69" s="145">
+      <c r="M69" s="149">
         <f>M68</f>
         <v/>
       </c>
-      <c r="N69" s="145">
+      <c r="N69" s="149">
         <f>N68</f>
         <v/>
       </c>
@@ -5192,38 +5693,38 @@
           <t>Issuance (repayment) of debt</t>
         </is>
       </c>
-      <c r="E72" s="148" t="n">
+      <c r="E72" s="153" t="n">
         <v>519583</v>
       </c>
-      <c r="F72" s="148" t="n">
+      <c r="F72" s="153" t="n">
         <v>594651</v>
       </c>
-      <c r="G72" s="148" t="n">
+      <c r="G72" s="153" t="n">
         <v>7989</v>
       </c>
-      <c r="H72" s="148" t="n">
+      <c r="H72" s="153" t="n">
         <v>347363</v>
       </c>
-      <c r="I72" s="148" t="n">
+      <c r="I72" s="153" t="n">
         <v>846670</v>
       </c>
-      <c r="J72" s="145">
+      <c r="J72" s="149">
         <f>J19</f>
         <v/>
       </c>
-      <c r="K72" s="145">
+      <c r="K72" s="149">
         <f>K19</f>
         <v/>
       </c>
-      <c r="L72" s="145">
+      <c r="L72" s="149">
         <f>L19</f>
         <v/>
       </c>
-      <c r="M72" s="145">
+      <c r="M72" s="149">
         <f>M19</f>
         <v/>
       </c>
-      <c r="N72" s="145">
+      <c r="N72" s="149">
         <f>N19</f>
         <v/>
       </c>
@@ -5234,38 +5735,38 @@
           <t>Issuance (repayment) of equity</t>
         </is>
       </c>
-      <c r="E73" s="148" t="n">
+      <c r="E73" s="153" t="n">
         <v>0</v>
       </c>
-      <c r="F73" s="148" t="n">
+      <c r="F73" s="153" t="n">
         <v>0</v>
       </c>
-      <c r="G73" s="148" t="n">
+      <c r="G73" s="153" t="n">
         <v>0</v>
       </c>
-      <c r="H73" s="148" t="n">
+      <c r="H73" s="153" t="n">
         <v>0</v>
       </c>
-      <c r="I73" s="148" t="n">
+      <c r="I73" s="153" t="n">
         <v>0</v>
       </c>
-      <c r="J73" s="145">
+      <c r="J73" s="149">
         <f>J20</f>
         <v/>
       </c>
-      <c r="K73" s="145">
+      <c r="K73" s="149">
         <f>K20</f>
         <v/>
       </c>
-      <c r="L73" s="145">
+      <c r="L73" s="149">
         <f>L20</f>
         <v/>
       </c>
-      <c r="M73" s="145">
+      <c r="M73" s="149">
         <f>M20</f>
         <v/>
       </c>
-      <c r="N73" s="145">
+      <c r="N73" s="149">
         <f>N20</f>
         <v/>
       </c>
@@ -5278,43 +5779,43 @@
       </c>
       <c r="C74" s="5" t="n"/>
       <c r="D74" s="28" t="n"/>
-      <c r="E74" s="150">
+      <c r="E74" s="155">
         <f>SUM(E72:E73)</f>
         <v/>
       </c>
-      <c r="F74" s="150">
+      <c r="F74" s="155">
         <f>SUM(F72:F73)</f>
         <v/>
       </c>
-      <c r="G74" s="150">
+      <c r="G74" s="155">
         <f>SUM(G72:G73)</f>
         <v/>
       </c>
-      <c r="H74" s="150">
+      <c r="H74" s="155">
         <f>SUM(H72:H73)</f>
         <v/>
       </c>
-      <c r="I74" s="150">
+      <c r="I74" s="155">
         <f>SUM(I72:I73)</f>
         <v/>
       </c>
-      <c r="J74" s="145">
+      <c r="J74" s="149">
         <f>J19+J20</f>
         <v/>
       </c>
-      <c r="K74" s="145">
+      <c r="K74" s="149">
         <f>K19+K20</f>
         <v/>
       </c>
-      <c r="L74" s="145">
+      <c r="L74" s="149">
         <f>L19+L20</f>
         <v/>
       </c>
-      <c r="M74" s="145">
+      <c r="M74" s="149">
         <f>M19+M20</f>
         <v/>
       </c>
-      <c r="N74" s="145">
+      <c r="N74" s="149">
         <f>N19+N20</f>
         <v/>
       </c>
@@ -5340,47 +5841,48 @@
           <t>Net Increase (decrease) in Cash</t>
         </is>
       </c>
-      <c r="C76" s="144">
-        <f> CFO + CFI + CFF</f>
-        <v/>
-      </c>
-      <c r="E76" s="159">
+      <c r="C76" s="156" t="inlineStr">
+        <is>
+          <t>eqn: CFO − CapEx + Financing</t>
+        </is>
+      </c>
+      <c r="E76" s="165">
         <f>E41-E77</f>
         <v/>
       </c>
-      <c r="F76" s="159">
+      <c r="F76" s="165">
         <f>F41-F77</f>
         <v/>
       </c>
-      <c r="G76" s="159">
+      <c r="G76" s="165">
         <f>G41-G77</f>
         <v/>
       </c>
-      <c r="H76" s="159">
+      <c r="H76" s="165">
         <f>H41-H77</f>
         <v/>
       </c>
-      <c r="I76" s="159">
+      <c r="I76" s="165">
         <f>I41-I77</f>
         <v/>
       </c>
-      <c r="J76" s="145">
+      <c r="J76" s="149">
         <f>J65-J69+J74</f>
         <v/>
       </c>
-      <c r="K76" s="145">
+      <c r="K76" s="149">
         <f>K65-K69+K74</f>
         <v/>
       </c>
-      <c r="L76" s="145">
+      <c r="L76" s="149">
         <f>L65-L69+L74</f>
         <v/>
       </c>
-      <c r="M76" s="145">
+      <c r="M76" s="149">
         <f>M65-M69+M74</f>
         <v/>
       </c>
-      <c r="N76" s="145">
+      <c r="N76" s="149">
         <f>N65-N69+N74</f>
         <v/>
       </c>
@@ -5391,42 +5893,42 @@
           <t>Opening Cash Balance</t>
         </is>
       </c>
-      <c r="E77" s="148" t="n">
+      <c r="E77" s="153" t="n">
         <v>157394</v>
       </c>
-      <c r="F77" s="159">
+      <c r="F77" s="165">
         <f>E41</f>
         <v/>
       </c>
-      <c r="G77" s="159">
+      <c r="G77" s="165">
         <f>F41</f>
         <v/>
       </c>
-      <c r="H77" s="159">
+      <c r="H77" s="165">
         <f>G41</f>
         <v/>
       </c>
-      <c r="I77" s="159">
+      <c r="I77" s="165">
         <f>H41</f>
         <v/>
       </c>
-      <c r="J77" s="145">
+      <c r="J77" s="149">
         <f>I41</f>
         <v/>
       </c>
-      <c r="K77" s="145">
+      <c r="K77" s="149">
         <f>J41</f>
         <v/>
       </c>
-      <c r="L77" s="145">
+      <c r="L77" s="149">
         <f>K41</f>
         <v/>
       </c>
-      <c r="M77" s="145">
+      <c r="M77" s="149">
         <f>L41</f>
         <v/>
       </c>
-      <c r="N77" s="145">
+      <c r="N77" s="149">
         <f>M41</f>
         <v/>
       </c>
@@ -5438,46 +5940,46 @@
         </is>
       </c>
       <c r="C78" s="5" t="n"/>
-      <c r="D78" s="160" t="n">
+      <c r="D78" s="166" t="n">
         <v>157394</v>
       </c>
-      <c r="E78" s="150">
+      <c r="E78" s="155">
         <f>SUM(E76:E77)</f>
         <v/>
       </c>
-      <c r="F78" s="150">
+      <c r="F78" s="155">
         <f>SUM(F76:F77)</f>
         <v/>
       </c>
-      <c r="G78" s="150">
+      <c r="G78" s="155">
         <f>SUM(G76:G77)</f>
         <v/>
       </c>
-      <c r="H78" s="150">
+      <c r="H78" s="155">
         <f>SUM(H76:H77)</f>
         <v/>
       </c>
-      <c r="I78" s="150">
+      <c r="I78" s="155">
         <f>SUM(I76:I77)</f>
         <v/>
       </c>
-      <c r="J78" s="145">
+      <c r="J78" s="149">
         <f>J77+J76</f>
         <v/>
       </c>
-      <c r="K78" s="145">
+      <c r="K78" s="149">
         <f>K77+K76</f>
         <v/>
       </c>
-      <c r="L78" s="145">
+      <c r="L78" s="149">
         <f>L77+L76</f>
         <v/>
       </c>
-      <c r="M78" s="145">
+      <c r="M78" s="149">
         <f>M77+M76</f>
         <v/>
       </c>
-      <c r="N78" s="145">
+      <c r="N78" s="149">
         <f>N77+N76</f>
         <v/>
       </c>
@@ -5498,43 +6000,43 @@
       </c>
       <c r="C80" s="9" t="n"/>
       <c r="D80" s="27" t="n"/>
-      <c r="E80" s="157">
+      <c r="E80" s="163">
         <f>E78-E41</f>
         <v/>
       </c>
-      <c r="F80" s="157">
+      <c r="F80" s="163">
         <f>F78-F41</f>
         <v/>
       </c>
-      <c r="G80" s="157">
+      <c r="G80" s="163">
         <f>G78-G41</f>
         <v/>
       </c>
-      <c r="H80" s="157">
+      <c r="H80" s="163">
         <f>H78-H41</f>
         <v/>
       </c>
-      <c r="I80" s="157">
+      <c r="I80" s="163">
         <f>I78-I41</f>
         <v/>
       </c>
-      <c r="J80" s="145">
+      <c r="J80" s="149">
         <f>J78-J41</f>
         <v/>
       </c>
-      <c r="K80" s="145">
+      <c r="K80" s="149">
         <f>K78-K41</f>
         <v/>
       </c>
-      <c r="L80" s="145">
+      <c r="L80" s="149">
         <f>L78-L41</f>
         <v/>
       </c>
-      <c r="M80" s="145">
+      <c r="M80" s="149">
         <f>M78-M41</f>
         <v/>
       </c>
-      <c r="N80" s="145">
+      <c r="N80" s="149">
         <f>N78-N41</f>
         <v/>
       </c>
@@ -5590,38 +6092,38 @@
           <t>Accounts Receivable</t>
         </is>
       </c>
-      <c r="E85" s="148" t="n">
+      <c r="E85" s="153" t="n">
         <v>206690</v>
       </c>
-      <c r="F85" s="148" t="n">
+      <c r="F85" s="153" t="n">
         <v>202365</v>
       </c>
-      <c r="G85" s="148" t="n">
+      <c r="G85" s="153" t="n">
         <v>251217</v>
       </c>
-      <c r="H85" s="148" t="n">
+      <c r="H85" s="153" t="n">
         <v>269745</v>
       </c>
-      <c r="I85" s="148" t="n">
+      <c r="I85" s="153" t="n">
         <v>341776</v>
       </c>
-      <c r="J85" s="145">
+      <c r="J85" s="149">
         <f>J42</f>
         <v/>
       </c>
-      <c r="K85" s="145">
+      <c r="K85" s="149">
         <f>K42</f>
         <v/>
       </c>
-      <c r="L85" s="145">
+      <c r="L85" s="149">
         <f>L42</f>
         <v/>
       </c>
-      <c r="M85" s="145">
+      <c r="M85" s="149">
         <f>M42</f>
         <v/>
       </c>
-      <c r="N85" s="145">
+      <c r="N85" s="149">
         <f>N42</f>
         <v/>
       </c>
@@ -5632,38 +6134,38 @@
           <t>Inventory</t>
         </is>
       </c>
-      <c r="E86" s="148" t="n">
+      <c r="E86" s="153" t="n">
         <v>0</v>
       </c>
-      <c r="F86" s="148" t="n">
+      <c r="F86" s="153" t="n">
         <v>0</v>
       </c>
-      <c r="G86" s="148" t="n">
+      <c r="G86" s="153" t="n">
         <v>0</v>
       </c>
-      <c r="H86" s="148" t="n">
+      <c r="H86" s="153" t="n">
         <v>0</v>
       </c>
-      <c r="I86" s="148" t="n">
+      <c r="I86" s="153" t="n">
         <v>0</v>
       </c>
-      <c r="J86" s="145">
+      <c r="J86" s="149">
         <f>J43</f>
         <v/>
       </c>
-      <c r="K86" s="145">
+      <c r="K86" s="149">
         <f>K43</f>
         <v/>
       </c>
-      <c r="L86" s="145">
+      <c r="L86" s="149">
         <f>L43</f>
         <v/>
       </c>
-      <c r="M86" s="145">
+      <c r="M86" s="149">
         <f>M43</f>
         <v/>
       </c>
-      <c r="N86" s="145">
+      <c r="N86" s="149">
         <f>N43</f>
         <v/>
       </c>
@@ -5674,38 +6176,38 @@
           <t>Accounts Payable</t>
         </is>
       </c>
-      <c r="E87" s="148" t="n">
+      <c r="E87" s="153" t="n">
         <v>20749</v>
       </c>
-      <c r="F87" s="148" t="n">
+      <c r="F87" s="153" t="n">
         <v>17273</v>
       </c>
-      <c r="G87" s="148" t="n">
+      <c r="G87" s="153" t="n">
         <v>19009</v>
       </c>
-      <c r="H87" s="148" t="n">
+      <c r="H87" s="153" t="n">
         <v>22473</v>
       </c>
-      <c r="I87" s="148" t="n">
+      <c r="I87" s="153" t="n">
         <v>32315</v>
       </c>
-      <c r="J87" s="145">
+      <c r="J87" s="149">
         <f>J48</f>
         <v/>
       </c>
-      <c r="K87" s="145">
+      <c r="K87" s="149">
         <f>K48</f>
         <v/>
       </c>
-      <c r="L87" s="145">
+      <c r="L87" s="149">
         <f>L48</f>
         <v/>
       </c>
-      <c r="M87" s="145">
+      <c r="M87" s="149">
         <f>M48</f>
         <v/>
       </c>
-      <c r="N87" s="145">
+      <c r="N87" s="149">
         <f>N48</f>
         <v/>
       </c>
@@ -5717,46 +6219,46 @@
         </is>
       </c>
       <c r="C88" s="5" t="n"/>
-      <c r="D88" s="160" t="n">
+      <c r="D88" s="166" t="n">
         <v>205747</v>
       </c>
-      <c r="E88" s="161">
+      <c r="E88" s="167">
         <f>E85+E86-E87</f>
         <v/>
       </c>
-      <c r="F88" s="161">
+      <c r="F88" s="167">
         <f>F85+F86-F87</f>
         <v/>
       </c>
-      <c r="G88" s="161">
+      <c r="G88" s="167">
         <f>G85+G86-G87</f>
         <v/>
       </c>
-      <c r="H88" s="161">
+      <c r="H88" s="167">
         <f>H85+H86-H87</f>
         <v/>
       </c>
-      <c r="I88" s="161">
+      <c r="I88" s="167">
         <f>I85+I86-I87</f>
         <v/>
       </c>
-      <c r="J88" s="145">
+      <c r="J88" s="149">
         <f>J85+J86-J87</f>
         <v/>
       </c>
-      <c r="K88" s="145">
+      <c r="K88" s="149">
         <f>K85+K86-K87</f>
         <v/>
       </c>
-      <c r="L88" s="145">
+      <c r="L88" s="149">
         <f>L85+L86-L87</f>
         <v/>
       </c>
-      <c r="M88" s="145">
+      <c r="M88" s="149">
         <f>M85+M86-M87</f>
         <v/>
       </c>
-      <c r="N88" s="145">
+      <c r="N88" s="149">
         <f>N85+N86-N87</f>
         <v/>
       </c>
@@ -5767,43 +6269,43 @@
           <t>Change in NWC</t>
         </is>
       </c>
-      <c r="E89" s="142">
+      <c r="E89" s="146">
         <f>E88-D88</f>
         <v/>
       </c>
-      <c r="F89" s="142">
+      <c r="F89" s="146">
         <f>F88-E88</f>
         <v/>
       </c>
-      <c r="G89" s="142">
+      <c r="G89" s="146">
         <f>G88-F88</f>
         <v/>
       </c>
-      <c r="H89" s="142">
+      <c r="H89" s="146">
         <f>H88-G88</f>
         <v/>
       </c>
-      <c r="I89" s="142">
+      <c r="I89" s="146">
         <f>I88-H88</f>
         <v/>
       </c>
-      <c r="J89" s="145">
+      <c r="J89" s="149">
         <f>J88-I88</f>
         <v/>
       </c>
-      <c r="K89" s="145">
+      <c r="K89" s="149">
         <f>K88-J88</f>
         <v/>
       </c>
-      <c r="L89" s="145">
+      <c r="L89" s="149">
         <f>L88-K88</f>
         <v/>
       </c>
-      <c r="M89" s="145">
+      <c r="M89" s="149">
         <f>M88-L88</f>
         <v/>
       </c>
-      <c r="N89" s="145">
+      <c r="N89" s="149">
         <f>N88-M88</f>
         <v/>
       </c>
@@ -5833,42 +6335,42 @@
           <t>PPE Opening</t>
         </is>
       </c>
-      <c r="E92" s="148" t="n">
+      <c r="E92" s="153" t="n">
         <v>46419</v>
       </c>
-      <c r="F92" s="159">
+      <c r="F92" s="165">
         <f>E95</f>
         <v/>
       </c>
-      <c r="G92" s="159">
+      <c r="G92" s="165">
         <f>F95</f>
         <v/>
       </c>
-      <c r="H92" s="159">
+      <c r="H92" s="165">
         <f>G95</f>
         <v/>
       </c>
-      <c r="I92" s="159">
+      <c r="I92" s="165">
         <f>H95</f>
         <v/>
       </c>
-      <c r="J92" s="145">
+      <c r="J92" s="149">
         <f>I44</f>
         <v/>
       </c>
-      <c r="K92" s="145">
+      <c r="K92" s="149">
         <f>J95</f>
         <v/>
       </c>
-      <c r="L92" s="145">
+      <c r="L92" s="149">
         <f>K95</f>
         <v/>
       </c>
-      <c r="M92" s="145">
+      <c r="M92" s="149">
         <f>L95</f>
         <v/>
       </c>
-      <c r="N92" s="145">
+      <c r="N92" s="149">
         <f>M95</f>
         <v/>
       </c>
@@ -5879,38 +6381,38 @@
           <t>Plus Capex</t>
         </is>
       </c>
-      <c r="E93" s="148" t="n">
+      <c r="E93" s="153" t="n">
         <v>7569</v>
       </c>
-      <c r="F93" s="148" t="n">
+      <c r="F93" s="153" t="n">
         <v>6029</v>
       </c>
-      <c r="G93" s="148" t="n">
+      <c r="G93" s="153" t="n">
         <v>4237</v>
       </c>
-      <c r="H93" s="148" t="n">
+      <c r="H93" s="153" t="n">
         <v>25551</v>
       </c>
-      <c r="I93" s="148" t="n">
+      <c r="I93" s="153" t="n">
         <v>39407</v>
       </c>
-      <c r="J93" s="145">
+      <c r="J93" s="149">
         <f>J24*J18</f>
         <v/>
       </c>
-      <c r="K93" s="145">
+      <c r="K93" s="149">
         <f>K24*K18</f>
         <v/>
       </c>
-      <c r="L93" s="145">
+      <c r="L93" s="149">
         <f>L24*L18</f>
         <v/>
       </c>
-      <c r="M93" s="145">
+      <c r="M93" s="149">
         <f>M24*M18</f>
         <v/>
       </c>
-      <c r="N93" s="145">
+      <c r="N93" s="149">
         <f>N24*N18</f>
         <v/>
       </c>
@@ -5921,38 +6423,38 @@
           <t>Less Depreciation</t>
         </is>
       </c>
-      <c r="E94" s="148" t="n">
+      <c r="E94" s="153" t="n">
         <v>25592</v>
       </c>
-      <c r="F94" s="148" t="n">
+      <c r="F94" s="153" t="n">
         <v>20465</v>
       </c>
-      <c r="G94" s="148" t="n">
+      <c r="G94" s="153" t="n">
         <v>14638</v>
       </c>
-      <c r="H94" s="148" t="n">
+      <c r="H94" s="153" t="n">
         <v>13827</v>
       </c>
-      <c r="I94" s="148" t="n">
+      <c r="I94" s="153" t="n">
         <v>14952</v>
       </c>
-      <c r="J94" s="145">
+      <c r="J94" s="149">
         <f>J92*J11</f>
         <v/>
       </c>
-      <c r="K94" s="145">
+      <c r="K94" s="149">
         <f>K92*K11</f>
         <v/>
       </c>
-      <c r="L94" s="145">
+      <c r="L94" s="149">
         <f>L92*L11</f>
         <v/>
       </c>
-      <c r="M94" s="145">
+      <c r="M94" s="149">
         <f>M92*M11</f>
         <v/>
       </c>
-      <c r="N94" s="145">
+      <c r="N94" s="149">
         <f>N92*N11</f>
         <v/>
       </c>
@@ -5965,38 +6467,38 @@
       </c>
       <c r="C95" s="5" t="n"/>
       <c r="D95" s="28" t="n"/>
-      <c r="E95" s="162" t="n">
+      <c r="E95" s="168" t="n">
         <v>27913</v>
       </c>
-      <c r="F95" s="162" t="n">
+      <c r="F95" s="168" t="n">
         <v>17580</v>
       </c>
-      <c r="G95" s="162" t="n">
+      <c r="G95" s="168" t="n">
         <v>10966</v>
       </c>
-      <c r="H95" s="162" t="n">
+      <c r="H95" s="168" t="n">
         <v>38465</v>
       </c>
-      <c r="I95" s="162" t="n">
+      <c r="I95" s="168" t="n">
         <v>67713</v>
       </c>
-      <c r="J95" s="145">
+      <c r="J95" s="149">
         <f>J92+J93-J94</f>
         <v/>
       </c>
-      <c r="K95" s="145">
+      <c r="K95" s="149">
         <f>K92+K93-K94</f>
         <v/>
       </c>
-      <c r="L95" s="145">
+      <c r="L95" s="149">
         <f>L92+L93-L94</f>
         <v/>
       </c>
-      <c r="M95" s="145">
+      <c r="M95" s="149">
         <f>M92+M93-M94</f>
         <v/>
       </c>
-      <c r="N95" s="145">
+      <c r="N95" s="149">
         <f>N92+N93-N94</f>
         <v/>
       </c>
@@ -6031,42 +6533,42 @@
           <t>Debt Opening</t>
         </is>
       </c>
-      <c r="E98" s="148" t="n">
+      <c r="E98" s="153" t="n">
         <v>739435</v>
       </c>
-      <c r="F98" s="159">
+      <c r="F98" s="165">
         <f>E100</f>
         <v/>
       </c>
-      <c r="G98" s="159">
+      <c r="G98" s="165">
         <f>F100</f>
         <v/>
       </c>
-      <c r="H98" s="159">
+      <c r="H98" s="165">
         <f>G100</f>
         <v/>
       </c>
-      <c r="I98" s="159">
+      <c r="I98" s="165">
         <f>H100</f>
         <v/>
       </c>
-      <c r="J98" s="145">
+      <c r="J98" s="149">
         <f>I49</f>
         <v/>
       </c>
-      <c r="K98" s="145">
+      <c r="K98" s="149">
         <f>J100</f>
         <v/>
       </c>
-      <c r="L98" s="145">
+      <c r="L98" s="149">
         <f>K100</f>
         <v/>
       </c>
-      <c r="M98" s="145">
+      <c r="M98" s="149">
         <f>L100</f>
         <v/>
       </c>
-      <c r="N98" s="145">
+      <c r="N98" s="149">
         <f>M100</f>
         <v/>
       </c>
@@ -6077,38 +6579,38 @@
           <t>Issuance (repayment)</t>
         </is>
       </c>
-      <c r="E99" s="148" t="n">
+      <c r="E99" s="153" t="n">
         <v>519583</v>
       </c>
-      <c r="F99" s="148" t="n">
+      <c r="F99" s="153" t="n">
         <v>594651</v>
       </c>
-      <c r="G99" s="148" t="n">
+      <c r="G99" s="153" t="n">
         <v>7989</v>
       </c>
-      <c r="H99" s="148" t="n">
+      <c r="H99" s="153" t="n">
         <v>347363</v>
       </c>
-      <c r="I99" s="148" t="n">
+      <c r="I99" s="153" t="n">
         <v>846670</v>
       </c>
-      <c r="J99" s="145">
+      <c r="J99" s="149">
         <f>J19</f>
         <v/>
       </c>
-      <c r="K99" s="145">
+      <c r="K99" s="149">
         <f>K19</f>
         <v/>
       </c>
-      <c r="L99" s="145">
+      <c r="L99" s="149">
         <f>L19</f>
         <v/>
       </c>
-      <c r="M99" s="145">
+      <c r="M99" s="149">
         <f>M19</f>
         <v/>
       </c>
-      <c r="N99" s="145">
+      <c r="N99" s="149">
         <f>N19</f>
         <v/>
       </c>
@@ -6121,38 +6623,38 @@
       </c>
       <c r="C100" s="5" t="n"/>
       <c r="D100" s="28" t="n"/>
-      <c r="E100" s="162" t="n">
+      <c r="E100" s="168" t="n">
         <v>1259018</v>
       </c>
-      <c r="F100" s="162" t="n">
+      <c r="F100" s="168" t="n">
         <v>1853669</v>
       </c>
-      <c r="G100" s="162" t="n">
+      <c r="G100" s="168" t="n">
         <v>1861658</v>
       </c>
-      <c r="H100" s="162" t="n">
+      <c r="H100" s="168" t="n">
         <v>2209021</v>
       </c>
-      <c r="I100" s="162" t="n">
+      <c r="I100" s="168" t="n">
         <v>3055691</v>
       </c>
-      <c r="J100" s="145">
+      <c r="J100" s="149">
         <f>J98+J99</f>
         <v/>
       </c>
-      <c r="K100" s="145">
+      <c r="K100" s="149">
         <f>K98+K99</f>
         <v/>
       </c>
-      <c r="L100" s="145">
+      <c r="L100" s="149">
         <f>L98+L99</f>
         <v/>
       </c>
-      <c r="M100" s="145">
+      <c r="M100" s="149">
         <f>M98+M99</f>
         <v/>
       </c>
-      <c r="N100" s="145">
+      <c r="N100" s="149">
         <f>N98+N99</f>
         <v/>
       </c>
@@ -6163,38 +6665,38 @@
           <t>Interest Expense</t>
         </is>
       </c>
-      <c r="E101" s="148" t="n">
+      <c r="E101" s="153" t="n">
         <v>40092</v>
       </c>
-      <c r="F101" s="148" t="n">
+      <c r="F101" s="153" t="n">
         <v>68967</v>
       </c>
-      <c r="G101" s="148" t="n">
+      <c r="G101" s="153" t="n">
         <v>95546</v>
       </c>
-      <c r="H101" s="148" t="n">
+      <c r="H101" s="153" t="n">
         <v>105638</v>
       </c>
-      <c r="I101" s="148" t="n">
+      <c r="I101" s="153" t="n">
         <v>133647</v>
       </c>
-      <c r="J101" s="145">
+      <c r="J101" s="149">
         <f>J98*J12</f>
         <v/>
       </c>
-      <c r="K101" s="145">
+      <c r="K101" s="149">
         <f>K98*K12</f>
         <v/>
       </c>
-      <c r="L101" s="145">
+      <c r="L101" s="149">
         <f>L98*L12</f>
         <v/>
       </c>
-      <c r="M101" s="145">
+      <c r="M101" s="149">
         <f>M98*M12</f>
         <v/>
       </c>
-      <c r="N101" s="145">
+      <c r="N101" s="149">
         <f>N98*N12</f>
         <v/>
       </c>
@@ -6477,6 +6979,10 @@
       <c r="D138" s="72" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="P5:U5"/>
+    <mergeCell ref="P4:U4"/>
+  </mergeCells>
   <conditionalFormatting sqref="E3:N3">
     <cfRule type="containsText" priority="1" operator="containsText" dxfId="1" text="OK">
       <formula>NOT(ISERROR(SEARCH("OK",E3)))</formula>
@@ -6569,7 +7075,7 @@
       <c r="L2" s="96" t="n"/>
       <c r="M2" s="94" t="n"/>
       <c r="N2" s="94" t="n"/>
-      <c r="Q2" s="163" t="inlineStr">
+      <c r="Q2" s="169" t="inlineStr">
         <is>
           <t>vengeanceaiUSCMODEL4 — LIVE EQUATIONS + SOURCE LINKS</t>
         </is>
@@ -6591,7 +7097,7 @@
       <c r="M3" s="97" t="n"/>
       <c r="N3" s="97" t="n"/>
       <c r="O3" s="97" t="n"/>
-      <c r="Q3" s="164" t="inlineStr">
+      <c r="Q3" s="170" t="inlineStr">
         <is>
           <t>Yellow = inputs (edit). Green = formulas. Blue underlined = clickable sources.</t>
         </is>
@@ -6617,32 +7123,32 @@
       <c r="M4" s="97" t="n"/>
       <c r="N4" s="97" t="n"/>
       <c r="O4" s="97" t="n"/>
-      <c r="Q4" s="165" t="inlineStr">
+      <c r="Q4" s="171" t="inlineStr">
         <is>
           <t>Input</t>
         </is>
       </c>
-      <c r="R4" s="165" t="inlineStr">
+      <c r="R4" s="171" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="S4" s="165" t="inlineStr">
+      <c r="S4" s="171" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="T4" s="165" t="inlineStr">
+      <c r="T4" s="171" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="U4" s="165" t="inlineStr">
+      <c r="U4" s="171" t="inlineStr">
         <is>
           <t>Primary source (click)</t>
         </is>
       </c>
-      <c r="V4" s="165" t="inlineStr">
+      <c r="V4" s="171" t="inlineStr">
         <is>
           <t>Secondary source (click)</t>
         </is>
@@ -6656,10 +7162,10 @@
         </is>
       </c>
       <c r="C5" s="100" t="n"/>
-      <c r="D5" s="166" t="n">
+      <c r="D5" s="172" t="n">
         <v>0.1877023903712333</v>
       </c>
-      <c r="E5" s="167" t="inlineStr">
+      <c r="E5" s="173" t="inlineStr">
         <is>
           <t>Tax source: SEC 10-K</t>
         </is>
@@ -6681,7 +7187,7 @@
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="168" t="inlineStr">
+      <c r="A6" s="174" t="inlineStr">
         <is>
           <t>WACC sources → columns U–V</t>
         </is>
@@ -6691,26 +7197,26 @@
           <t>Discount Rate (WACC = We×Ke + Wd×Rd(1−t))</t>
         </is>
       </c>
-      <c r="C6" s="169" t="inlineStr">
+      <c r="C6" s="175" t="inlineStr">
         <is>
           <t>Sources →</t>
         </is>
       </c>
-      <c r="D6" s="170">
+      <c r="D6" s="176">
         <f>R15</f>
         <v/>
       </c>
-      <c r="E6" s="167" t="inlineStr">
+      <c r="E6" s="173" t="inlineStr">
         <is>
           <t>WACC sources → scroll to col U (Rf/ERP/β/Rd links)</t>
         </is>
       </c>
-      <c r="F6" s="167" t="inlineStr">
+      <c r="F6" s="173" t="inlineStr">
         <is>
           <t>Damodaran ERP</t>
         </is>
       </c>
-      <c r="G6" s="167" t="inlineStr">
+      <c r="G6" s="173" t="inlineStr">
         <is>
           <t>SEC 8-K Rd 6.250%</t>
         </is>
@@ -6723,30 +7229,30 @@
       <c r="M6" s="97" t="n"/>
       <c r="N6" s="97" t="n"/>
       <c r="O6" s="97" t="n"/>
-      <c r="Q6" s="171" t="inlineStr">
+      <c r="Q6" s="177" t="inlineStr">
         <is>
           <t>Risk-free rate (Rf)</t>
         </is>
       </c>
-      <c r="R6" s="172" t="n">
+      <c r="R6" s="178" t="n">
         <v>0.0463</v>
       </c>
-      <c r="S6" s="171" t="inlineStr">
+      <c r="S6" s="177" t="inlineStr">
         <is>
           <t>US 10Y Treasury yield</t>
         </is>
       </c>
-      <c r="T6" s="171" t="inlineStr">
+      <c r="T6" s="177" t="inlineStr">
         <is>
           <t>CAPM input</t>
         </is>
       </c>
-      <c r="U6" s="173" t="inlineStr">
+      <c r="U6" s="179" t="inlineStr">
         <is>
           <t>FRED DGS10 (US 10Y)</t>
         </is>
       </c>
-      <c r="V6" s="173" t="inlineStr">
+      <c r="V6" s="179" t="inlineStr">
         <is>
           <t>US Treasury Daily Par Yield Curve</t>
         </is>
@@ -6760,7 +7266,7 @@
         </is>
       </c>
       <c r="C7" s="97" t="n"/>
-      <c r="D7" s="166" t="n">
+      <c r="D7" s="172" t="n">
         <v>0.03</v>
       </c>
       <c r="E7" s="97" t="n"/>
@@ -6774,30 +7280,30 @@
       <c r="M7" s="97" t="n"/>
       <c r="N7" s="97" t="n"/>
       <c r="O7" s="97" t="n"/>
-      <c r="Q7" s="171" t="inlineStr">
+      <c r="Q7" s="177" t="inlineStr">
         <is>
           <t>Equity risk premium (ERP)</t>
         </is>
       </c>
-      <c r="R7" s="172" t="n">
+      <c r="R7" s="178" t="n">
         <v>0.0428</v>
       </c>
-      <c r="S7" s="171" t="inlineStr">
+      <c r="S7" s="177" t="inlineStr">
         <is>
           <t>Damodaran implied ERP</t>
         </is>
       </c>
-      <c r="T7" s="171" t="inlineStr">
+      <c r="T7" s="177" t="inlineStr">
         <is>
           <t>CAPM input</t>
         </is>
       </c>
-      <c r="U7" s="173" t="inlineStr">
+      <c r="U7" s="179" t="inlineStr">
         <is>
           <t>Damodaran Online — Implied ERP</t>
         </is>
       </c>
-      <c r="V7" s="173" t="inlineStr">
+      <c r="V7" s="179" t="inlineStr">
         <is>
           <t>Damodaran histimpl.xls / table</t>
         </is>
@@ -6811,10 +7317,10 @@
         </is>
       </c>
       <c r="C8" s="97" t="n"/>
-      <c r="D8" s="174" t="n">
+      <c r="D8" s="180" t="n">
         <v>25</v>
       </c>
-      <c r="E8" s="167" t="inlineStr">
+      <c r="E8" s="173" t="inlineStr">
         <is>
           <t>Rd source: SEC 8-K 6.250% notes</t>
         </is>
@@ -6829,30 +7335,30 @@
       <c r="M8" s="97" t="n"/>
       <c r="N8" s="97" t="n"/>
       <c r="O8" s="97" t="n"/>
-      <c r="Q8" s="171" t="inlineStr">
+      <c r="Q8" s="177" t="inlineStr">
         <is>
           <t>Beta (β)</t>
         </is>
       </c>
-      <c r="R8" s="175" t="n">
+      <c r="R8" s="181" t="n">
         <v>1.32</v>
       </c>
-      <c r="S8" s="171" t="inlineStr">
+      <c r="S8" s="177" t="inlineStr">
         <is>
           <t>Yahoo 5Y monthly beta</t>
         </is>
       </c>
-      <c r="T8" s="171" t="inlineStr">
+      <c r="T8" s="177" t="inlineStr">
         <is>
           <t>CAPM input</t>
         </is>
       </c>
-      <c r="U8" s="173" t="inlineStr">
+      <c r="U8" s="179" t="inlineStr">
         <is>
           <t>Yahoo Finance FICO Key Statistics</t>
         </is>
       </c>
-      <c r="V8" s="173" t="inlineStr">
+      <c r="V8" s="179" t="inlineStr">
         <is>
           <t>Yahoo Finance FICO quote</t>
         </is>
@@ -6866,7 +7372,7 @@
         </is>
       </c>
       <c r="C9" s="97" t="n"/>
-      <c r="D9" s="176" t="n">
+      <c r="D9" s="182" t="n">
         <v>45930</v>
       </c>
       <c r="E9" s="97" t="n"/>
@@ -6880,31 +7386,31 @@
       <c r="M9" s="97" t="n"/>
       <c r="N9" s="97" t="n"/>
       <c r="O9" s="97" t="n"/>
-      <c r="Q9" s="177" t="inlineStr">
+      <c r="Q9" s="183" t="inlineStr">
         <is>
           <t>Ke = Rf + β × ERP</t>
         </is>
       </c>
-      <c r="R9" s="178">
+      <c r="R9" s="184">
         <f>R6+R8*R7</f>
         <v/>
       </c>
-      <c r="S9" s="171" t="inlineStr">
+      <c r="S9" s="177" t="inlineStr">
         <is>
           <t>Cost of equity (CAPM)</t>
         </is>
       </c>
-      <c r="T9" s="177" t="inlineStr">
+      <c r="T9" s="183" t="inlineStr">
         <is>
           <t>→ WACC</t>
         </is>
       </c>
-      <c r="U9" s="171" t="inlineStr">
+      <c r="U9" s="177" t="inlineStr">
         <is>
           <t>Derived: R6 + R8 × R7</t>
         </is>
       </c>
-      <c r="V9" s="171" t="inlineStr"/>
+      <c r="V9" s="177" t="inlineStr"/>
     </row>
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="97" t="n"/>
@@ -6914,7 +7420,7 @@
         </is>
       </c>
       <c r="C10" s="97" t="n"/>
-      <c r="D10" s="176" t="n">
+      <c r="D10" s="182" t="n">
         <v>46295</v>
       </c>
       <c r="E10" s="97" t="n"/>
@@ -6928,30 +7434,30 @@
       <c r="M10" s="97" t="n"/>
       <c r="N10" s="97" t="n"/>
       <c r="O10" s="97" t="n"/>
-      <c r="Q10" s="171" t="inlineStr">
+      <c r="Q10" s="177" t="inlineStr">
         <is>
           <t>Pre-tax cost of debt (Rd)</t>
         </is>
       </c>
-      <c r="R10" s="172" t="n">
+      <c r="R10" s="178" t="n">
         <v>0.0625</v>
       </c>
-      <c r="S10" s="171" t="inlineStr">
+      <c r="S10" s="177" t="inlineStr">
         <is>
           <t>6.250% Senior Notes due 2034</t>
         </is>
       </c>
-      <c r="T10" s="171" t="inlineStr">
+      <c r="T10" s="177" t="inlineStr">
         <is>
           <t>WACC input</t>
         </is>
       </c>
-      <c r="U10" s="173" t="inlineStr">
+      <c r="U10" s="179" t="inlineStr">
         <is>
           <t>SEC 8-K — Notes closing (6.250%)</t>
         </is>
       </c>
-      <c r="V10" s="173" t="inlineStr">
+      <c r="V10" s="179" t="inlineStr">
         <is>
           <t>SEC EX-99.1 — Notes pricing press release</t>
         </is>
@@ -6965,7 +7471,7 @@
         </is>
       </c>
       <c r="C11" s="97" t="n"/>
-      <c r="D11" s="179" t="n">
+      <c r="D11" s="185" t="n">
         <v>1046.23</v>
       </c>
       <c r="E11" s="97" t="n"/>
@@ -6979,31 +7485,31 @@
       <c r="M11" s="97" t="n"/>
       <c r="N11" s="97" t="n"/>
       <c r="O11" s="97" t="n"/>
-      <c r="Q11" s="171" t="inlineStr">
+      <c r="Q11" s="177" t="inlineStr">
         <is>
           <t>Tax rate (t)</t>
         </is>
       </c>
-      <c r="R11" s="178">
+      <c r="R11" s="184">
         <f>$D$5</f>
         <v/>
       </c>
-      <c r="S11" s="171" t="inlineStr">
+      <c r="S11" s="177" t="inlineStr">
         <is>
           <t>FY25 effective = 150,649 / 802,595</t>
         </is>
       </c>
-      <c r="T11" s="171" t="inlineStr">
+      <c r="T11" s="177" t="inlineStr">
         <is>
           <t>Linked D5</t>
         </is>
       </c>
-      <c r="U11" s="173" t="inlineStr">
+      <c r="U11" s="179" t="inlineStr">
         <is>
           <t>SEC 10-K FY2025 (tax / EBT)</t>
         </is>
       </c>
-      <c r="V11" s="173" t="inlineStr">
+      <c r="V11" s="179" t="inlineStr">
         <is>
           <t>SEC companyfacts XBRL (CIK 0000814547)</t>
         </is>
@@ -7017,7 +7523,7 @@
         </is>
       </c>
       <c r="C12" s="97" t="n"/>
-      <c r="D12" s="180" t="n">
+      <c r="D12" s="186" t="n">
         <v>21597.635</v>
       </c>
       <c r="E12" s="97" t="n"/>
@@ -7031,31 +7537,31 @@
       <c r="M12" s="97" t="n"/>
       <c r="N12" s="97" t="n"/>
       <c r="O12" s="97" t="n"/>
-      <c r="Q12" s="177" t="inlineStr">
+      <c r="Q12" s="183" t="inlineStr">
         <is>
           <t>Rd_aftertax = Rd × (1 − t)</t>
         </is>
       </c>
-      <c r="R12" s="178">
+      <c r="R12" s="184">
         <f>R10*(1-R11)</f>
         <v/>
       </c>
-      <c r="S12" s="171" t="inlineStr">
+      <c r="S12" s="177" t="inlineStr">
         <is>
           <t>After-tax cost of debt</t>
         </is>
       </c>
-      <c r="T12" s="177" t="inlineStr">
+      <c r="T12" s="183" t="inlineStr">
         <is>
           <t>→ WACC</t>
         </is>
       </c>
-      <c r="U12" s="171" t="inlineStr">
+      <c r="U12" s="177" t="inlineStr">
         <is>
           <t>Derived: R10 × (1 − R11)</t>
         </is>
       </c>
-      <c r="V12" s="171" t="inlineStr"/>
+      <c r="V12" s="177" t="inlineStr"/>
     </row>
     <row r="13" ht="16" customHeight="1">
       <c r="A13" s="97" t="n"/>
@@ -7065,7 +7571,7 @@
         </is>
       </c>
       <c r="C13" s="97" t="n"/>
-      <c r="D13" s="180" t="n">
+      <c r="D13" s="186" t="n">
         <v>5582389</v>
       </c>
       <c r="E13" s="97" t="n"/>
@@ -7079,30 +7585,30 @@
       <c r="M13" s="97" t="n"/>
       <c r="N13" s="97" t="n"/>
       <c r="O13" s="97" t="n"/>
-      <c r="Q13" s="171" t="inlineStr">
+      <c r="Q13" s="177" t="inlineStr">
         <is>
           <t>Equity weight (We)</t>
         </is>
       </c>
-      <c r="R13" s="181" t="n">
+      <c r="R13" s="187" t="n">
         <v>0.8</v>
       </c>
-      <c r="S13" s="171" t="inlineStr">
+      <c r="S13" s="177" t="inlineStr">
         <is>
           <t>Target ~80% equity at market</t>
         </is>
       </c>
-      <c r="T13" s="171" t="inlineStr">
+      <c r="T13" s="177" t="inlineStr">
         <is>
           <t>WACC weight</t>
         </is>
       </c>
-      <c r="U13" s="173" t="inlineStr">
+      <c r="U13" s="179" t="inlineStr">
         <is>
           <t>SEC 10-Q Q3 FY2026 (debt / capital)</t>
         </is>
       </c>
-      <c r="V13" s="173" t="inlineStr">
+      <c r="V13" s="179" t="inlineStr">
         <is>
           <t>Yahoo market cap for E/(D+E)</t>
         </is>
@@ -7116,7 +7622,7 @@
         </is>
       </c>
       <c r="C14" s="97" t="n"/>
-      <c r="D14" s="180" t="n">
+      <c r="D14" s="186" t="n">
         <v>304537</v>
       </c>
       <c r="E14" s="97" t="n"/>
@@ -7130,30 +7636,30 @@
       <c r="M14" s="97" t="n"/>
       <c r="N14" s="97" t="n"/>
       <c r="O14" s="97" t="n"/>
-      <c r="Q14" s="171" t="inlineStr">
+      <c r="Q14" s="177" t="inlineStr">
         <is>
           <t>Debt weight (Wd)</t>
         </is>
       </c>
-      <c r="R14" s="181" t="n">
+      <c r="R14" s="187" t="n">
         <v>0.2</v>
       </c>
-      <c r="S14" s="171" t="inlineStr">
+      <c r="S14" s="177" t="inlineStr">
         <is>
           <t>Target ~20% debt (We+Wd=100%)</t>
         </is>
       </c>
-      <c r="T14" s="171" t="inlineStr">
+      <c r="T14" s="177" t="inlineStr">
         <is>
           <t>WACC weight</t>
         </is>
       </c>
-      <c r="U14" s="173" t="inlineStr">
+      <c r="U14" s="179" t="inlineStr">
         <is>
           <t>SEC 10-Q — total debt $5,582,389k</t>
         </is>
       </c>
-      <c r="V14" s="173" t="inlineStr">
+      <c r="V14" s="179" t="inlineStr">
         <is>
           <t>SEC 10-K — senior notes footnote</t>
         </is>
@@ -7167,7 +7673,7 @@
         </is>
       </c>
       <c r="C15" s="97" t="n"/>
-      <c r="D15" s="182">
+      <c r="D15" s="188">
         <f>'3 Statement Model'!J68</f>
         <v/>
       </c>
@@ -7182,31 +7688,31 @@
       <c r="M15" s="97" t="n"/>
       <c r="N15" s="97" t="n"/>
       <c r="O15" s="97" t="n"/>
-      <c r="Q15" s="177" t="inlineStr">
+      <c r="Q15" s="183" t="inlineStr">
         <is>
           <t>WACC = We×Ke + Wd×Rd_aftertax</t>
         </is>
       </c>
-      <c r="R15" s="178">
+      <c r="R15" s="184">
         <f>R13*R9+R14*R12</f>
         <v/>
       </c>
-      <c r="S15" s="171" t="inlineStr">
+      <c r="S15" s="177" t="inlineStr">
         <is>
           <t>PRIMARY discount rate → cell D6</t>
         </is>
       </c>
-      <c r="T15" s="177" t="inlineStr">
+      <c r="T15" s="183" t="inlineStr">
         <is>
           <t>→ D6</t>
         </is>
       </c>
-      <c r="U15" s="173" t="inlineStr">
+      <c r="U15" s="179" t="inlineStr">
         <is>
           <t>SEC filings (tax, debt coupons)</t>
         </is>
       </c>
-      <c r="V15" s="173" t="inlineStr">
+      <c r="V15" s="179" t="inlineStr">
         <is>
           <t>Damodaran (ERP methodology)</t>
         </is>
@@ -7237,23 +7743,23 @@
           <t>Entry</t>
         </is>
       </c>
-      <c r="E17" s="183">
+      <c r="E17" s="189">
         <f>YEAR(E18)</f>
         <v/>
       </c>
-      <c r="F17" s="183">
+      <c r="F17" s="189">
         <f>YEAR(F18)</f>
         <v/>
       </c>
-      <c r="G17" s="183">
+      <c r="G17" s="189">
         <f>YEAR(G18)</f>
         <v/>
       </c>
-      <c r="H17" s="183">
+      <c r="H17" s="189">
         <f>YEAR(H18)</f>
         <v/>
       </c>
-      <c r="I17" s="183">
+      <c r="I17" s="189">
         <f>YEAR(I18)</f>
         <v/>
       </c>
@@ -7285,31 +7791,31 @@
         </is>
       </c>
       <c r="C18" s="97" t="n"/>
-      <c r="D18" s="184">
+      <c r="D18" s="190">
         <f>D9</f>
         <v/>
       </c>
-      <c r="E18" s="185">
+      <c r="E18" s="191">
         <f>DATE(YEAR($D$10)+E19,3,31)</f>
         <v/>
       </c>
-      <c r="F18" s="185">
+      <c r="F18" s="191">
         <f>DATE(YEAR($D$10)+F19,3,31)</f>
         <v/>
       </c>
-      <c r="G18" s="185">
+      <c r="G18" s="191">
         <f>DATE(YEAR($D$10)+G19,3,31)</f>
         <v/>
       </c>
-      <c r="H18" s="185">
+      <c r="H18" s="191">
         <f>DATE(YEAR($D$10)+H19,3,31)</f>
         <v/>
       </c>
-      <c r="I18" s="185">
+      <c r="I18" s="191">
         <f>DATE(YEAR($D$10)+I19,3,31)</f>
         <v/>
       </c>
-      <c r="J18" s="186">
+      <c r="J18" s="192">
         <f>I18</f>
         <v/>
       </c>
@@ -7319,7 +7825,7 @@
           <t>Exit EV/EBITDA (in J27) — primary</t>
         </is>
       </c>
-      <c r="M18" s="182">
+      <c r="M18" s="188">
         <f>J27</f>
         <v/>
       </c>
@@ -7328,17 +7834,17 @@
         <v/>
       </c>
       <c r="O18" s="97" t="n"/>
-      <c r="Q18" s="177" t="inlineStr">
+      <c r="Q18" s="183" t="inlineStr">
         <is>
           <t>FCFF = EBIT − EBIT×t + D&amp;A − CapEx − ΔNWC</t>
         </is>
       </c>
-      <c r="U18" s="173" t="inlineStr">
+      <c r="U18" s="179" t="inlineStr">
         <is>
           <t>Drivers from SEC XBRL → 3-statement</t>
         </is>
       </c>
-      <c r="V18" s="173" t="inlineStr">
+      <c r="V18" s="179" t="inlineStr">
         <is>
           <t>SEC 10-K historical IS/CF</t>
         </is>
@@ -7353,22 +7859,22 @@
       </c>
       <c r="C19" s="118" t="n"/>
       <c r="D19" s="115" t="n"/>
-      <c r="E19" s="187" t="n">
+      <c r="E19" s="193" t="n">
         <v>0</v>
       </c>
-      <c r="F19" s="184">
+      <c r="F19" s="190">
         <f>E19+1</f>
         <v/>
       </c>
-      <c r="G19" s="184">
+      <c r="G19" s="190">
         <f>F19+1</f>
         <v/>
       </c>
-      <c r="H19" s="184">
+      <c r="H19" s="190">
         <f>G19+1</f>
         <v/>
       </c>
-      <c r="I19" s="184">
+      <c r="I19" s="190">
         <f>H19+1</f>
         <v/>
       </c>
@@ -7379,7 +7885,7 @@
           <t>Gordon cross-check</t>
         </is>
       </c>
-      <c r="M19" s="182">
+      <c r="M19" s="188">
         <f>IF(($D$6-$D$7)&lt;=0,"WACC must exceed g",$I$26*(1+$D$7)/($D$6-$D$7))</f>
         <v/>
       </c>
@@ -7388,12 +7894,12 @@
         <v/>
       </c>
       <c r="O19" s="97" t="n"/>
-      <c r="Q19" s="171" t="inlineStr">
+      <c r="Q19" s="177" t="inlineStr">
         <is>
           <t>Excel (col E example)</t>
         </is>
       </c>
-      <c r="R19" s="177">
+      <c r="R19" s="183">
         <f>E21-E22+E23-E24-E25</f>
         <v/>
       </c>
@@ -7407,23 +7913,23 @@
       </c>
       <c r="C20" s="97" t="n"/>
       <c r="D20" s="97" t="n"/>
-      <c r="E20" s="184">
+      <c r="E20" s="190">
         <f>YEARFRAC(D18,E18)</f>
         <v/>
       </c>
-      <c r="F20" s="184">
+      <c r="F20" s="190">
         <f>YEARFRAC(E18,F18)</f>
         <v/>
       </c>
-      <c r="G20" s="184">
+      <c r="G20" s="190">
         <f>YEARFRAC(F18,G18)</f>
         <v/>
       </c>
-      <c r="H20" s="184">
+      <c r="H20" s="190">
         <f>YEARFRAC(G18,H18)</f>
         <v/>
       </c>
-      <c r="I20" s="184">
+      <c r="I20" s="190">
         <f>YEARFRAC(H18,I18)</f>
         <v/>
       </c>
@@ -7434,7 +7940,7 @@
           <t>Implied Gordon exit multiple</t>
         </is>
       </c>
-      <c r="M20" s="182">
+      <c r="M20" s="188">
         <f>IF(($I$21+$I$23)=0,0,M19/($I$21+$I$23))</f>
         <v/>
       </c>
@@ -7443,21 +7949,21 @@
         <v/>
       </c>
       <c r="O20" s="97" t="n"/>
-      <c r="Q20" s="171" t="inlineStr">
+      <c r="Q20" s="177" t="inlineStr">
         <is>
           <t>Tax on EBIT (unlevered)</t>
         </is>
       </c>
-      <c r="R20" s="177">
+      <c r="R20" s="183">
         <f>E21*$D$5</f>
         <v/>
       </c>
-      <c r="S20" s="171" t="inlineStr">
+      <c r="S20" s="177" t="inlineStr">
         <is>
           <t>NOT levered IS tax dollars</t>
         </is>
       </c>
-      <c r="U20" s="173" t="inlineStr">
+      <c r="U20" s="179" t="inlineStr">
         <is>
           <t>Tax rate from SEC 10-K effective rate</t>
         </is>
@@ -7470,29 +7976,29 @@
           <t>EBIT (linked to 3-stmt)</t>
         </is>
       </c>
-      <c r="C21" s="188" t="inlineStr">
+      <c r="C21" s="194" t="inlineStr">
         <is>
           <t>EBIT</t>
         </is>
       </c>
       <c r="D21" s="97" t="n"/>
-      <c r="E21" s="182">
+      <c r="E21" s="188">
         <f>'3 Statement Model'!J26-'3 Statement Model'!J28-'3 Statement Model'!J29-'3 Statement Model'!J30</f>
         <v/>
       </c>
-      <c r="F21" s="182">
+      <c r="F21" s="188">
         <f>'3 Statement Model'!K26-'3 Statement Model'!K28-'3 Statement Model'!K29-'3 Statement Model'!K30</f>
         <v/>
       </c>
-      <c r="G21" s="182">
+      <c r="G21" s="188">
         <f>'3 Statement Model'!L26-'3 Statement Model'!L28-'3 Statement Model'!L29-'3 Statement Model'!L30</f>
         <v/>
       </c>
-      <c r="H21" s="182">
+      <c r="H21" s="188">
         <f>'3 Statement Model'!M26-'3 Statement Model'!M28-'3 Statement Model'!M29-'3 Statement Model'!M30</f>
         <v/>
       </c>
-      <c r="I21" s="182">
+      <c r="I21" s="188">
         <f>'3 Statement Model'!N26-'3 Statement Model'!N28-'3 Statement Model'!N29-'3 Statement Model'!N30</f>
         <v/>
       </c>
@@ -7502,16 +8008,16 @@
       <c r="M21" s="97" t="n"/>
       <c r="N21" s="97" t="n"/>
       <c r="O21" s="97" t="n"/>
-      <c r="Q21" s="171" t="inlineStr">
+      <c r="Q21" s="177" t="inlineStr">
         <is>
           <t>FCFF check (FY5 / col I)</t>
         </is>
       </c>
-      <c r="R21" s="189">
+      <c r="R21" s="195">
         <f>I26</f>
         <v/>
       </c>
-      <c r="S21" s="171" t="inlineStr">
+      <c r="S21" s="177" t="inlineStr">
         <is>
           <t>Must equal I21−I22+I23−I24−I25</t>
         </is>
@@ -7524,29 +8030,29 @@
           <t>Less: Unlevered Cash Taxes (EBIT×t)</t>
         </is>
       </c>
-      <c r="C22" s="188" t="inlineStr">
+      <c r="C22" s="194" t="inlineStr">
         <is>
           <t>EBIT×t</t>
         </is>
       </c>
       <c r="D22" s="97" t="n"/>
-      <c r="E22" s="182">
+      <c r="E22" s="188">
         <f>E21*$D$5</f>
         <v/>
       </c>
-      <c r="F22" s="182">
+      <c r="F22" s="188">
         <f>F21*$D$5</f>
         <v/>
       </c>
-      <c r="G22" s="182">
+      <c r="G22" s="188">
         <f>G21*$D$5</f>
         <v/>
       </c>
-      <c r="H22" s="182">
+      <c r="H22" s="188">
         <f>H21*$D$5</f>
         <v/>
       </c>
-      <c r="I22" s="182">
+      <c r="I22" s="188">
         <f>I21*$D$5</f>
         <v/>
       </c>
@@ -7564,29 +8070,29 @@
           <t>Plus: D&amp;A (linked to 3-stmt)</t>
         </is>
       </c>
-      <c r="C23" s="188" t="inlineStr">
+      <c r="C23" s="194" t="inlineStr">
         <is>
           <t>+D&amp;A</t>
         </is>
       </c>
       <c r="D23" s="97" t="n"/>
-      <c r="E23" s="182">
+      <c r="E23" s="188">
         <f>'3 Statement Model'!J30</f>
         <v/>
       </c>
-      <c r="F23" s="182">
+      <c r="F23" s="188">
         <f>'3 Statement Model'!K30</f>
         <v/>
       </c>
-      <c r="G23" s="182">
+      <c r="G23" s="188">
         <f>'3 Statement Model'!L30</f>
         <v/>
       </c>
-      <c r="H23" s="182">
+      <c r="H23" s="188">
         <f>'3 Statement Model'!M30</f>
         <v/>
       </c>
-      <c r="I23" s="182">
+      <c r="I23" s="188">
         <f>'3 Statement Model'!N30</f>
         <v/>
       </c>
@@ -7609,29 +8115,29 @@
           <t>Less: Capex (linked to 3-stmt CF)</t>
         </is>
       </c>
-      <c r="C24" s="188" t="inlineStr">
+      <c r="C24" s="194" t="inlineStr">
         <is>
           <t>−CapEx</t>
         </is>
       </c>
       <c r="D24" s="97" t="n"/>
-      <c r="E24" s="182">
+      <c r="E24" s="188">
         <f>'3 Statement Model'!J68</f>
         <v/>
       </c>
-      <c r="F24" s="182">
+      <c r="F24" s="188">
         <f>'3 Statement Model'!K68</f>
         <v/>
       </c>
-      <c r="G24" s="182">
+      <c r="G24" s="188">
         <f>'3 Statement Model'!L68</f>
         <v/>
       </c>
-      <c r="H24" s="182">
+      <c r="H24" s="188">
         <f>'3 Statement Model'!M68</f>
         <v/>
       </c>
-      <c r="I24" s="182">
+      <c r="I24" s="188">
         <f>'3 Statement Model'!N68</f>
         <v/>
       </c>
@@ -7641,7 +8147,7 @@
       <c r="M24" s="97" t="n"/>
       <c r="N24" s="97" t="n"/>
       <c r="O24" s="97" t="n"/>
-      <c r="Q24" s="177" t="inlineStr">
+      <c r="Q24" s="183" t="inlineStr">
         <is>
           <t>TV_exit = EBITDA_n × ExitMultiple   [PRIMARY]</t>
         </is>
@@ -7654,29 +8160,29 @@
           <t>Less: ΔNWC (linked to 3-stmt CF)</t>
         </is>
       </c>
-      <c r="C25" s="188" t="inlineStr">
+      <c r="C25" s="194" t="inlineStr">
         <is>
           <t>−ΔNWC</t>
         </is>
       </c>
       <c r="D25" s="97" t="n"/>
-      <c r="E25" s="182">
+      <c r="E25" s="188">
         <f>'3 Statement Model'!J64</f>
         <v/>
       </c>
-      <c r="F25" s="182">
+      <c r="F25" s="188">
         <f>'3 Statement Model'!K64</f>
         <v/>
       </c>
-      <c r="G25" s="182">
+      <c r="G25" s="188">
         <f>'3 Statement Model'!L64</f>
         <v/>
       </c>
-      <c r="H25" s="182">
+      <c r="H25" s="188">
         <f>'3 Statement Model'!M64</f>
         <v/>
       </c>
-      <c r="I25" s="182">
+      <c r="I25" s="188">
         <f>'3 Statement Model'!N64</f>
         <v/>
       </c>
@@ -7686,20 +8192,20 @@
       <c r="M25" s="97" t="n"/>
       <c r="N25" s="97" t="n"/>
       <c r="O25" s="97" t="n"/>
-      <c r="Q25" s="171" t="inlineStr">
+      <c r="Q25" s="177" t="inlineStr">
         <is>
           <t>Excel</t>
         </is>
       </c>
-      <c r="R25" s="177">
+      <c r="R25" s="183">
         <f>($I$21+$I$23)*$D$8</f>
         <v/>
       </c>
-      <c r="T25" s="189">
+      <c r="T25" s="195">
         <f>J27</f>
         <v/>
       </c>
-      <c r="U25" s="173" t="inlineStr">
+      <c r="U25" s="179" t="inlineStr">
         <is>
           <t>Exit multiple policy vs Yahoo / market multiples</t>
         </is>
@@ -7712,29 +8218,29 @@
           <t>Unlevered FCF</t>
         </is>
       </c>
-      <c r="C26" s="188" t="inlineStr">
+      <c r="C26" s="194" t="inlineStr">
         <is>
           <t>FCFF=EBIT−tax+DA−CapEx−ΔNWC</t>
         </is>
       </c>
       <c r="D26" s="97" t="n"/>
-      <c r="E26" s="190">
+      <c r="E26" s="196">
         <f>E21-E22+E23-E24-E25</f>
         <v/>
       </c>
-      <c r="F26" s="190">
+      <c r="F26" s="196">
         <f>F21-F22+F23-F24-F25</f>
         <v/>
       </c>
-      <c r="G26" s="190">
+      <c r="G26" s="196">
         <f>G21-G22+G23-G24-G25</f>
         <v/>
       </c>
-      <c r="H26" s="190">
+      <c r="H26" s="196">
         <f>H21-H22+H23-H24-H25</f>
         <v/>
       </c>
-      <c r="I26" s="190">
+      <c r="I26" s="196">
         <f>I21-I22+I23-I24-I25</f>
         <v/>
       </c>
@@ -7744,7 +8250,7 @@
       <c r="M26" s="97" t="n"/>
       <c r="N26" s="97" t="n"/>
       <c r="O26" s="97" t="n"/>
-      <c r="Q26" s="177" t="inlineStr">
+      <c r="Q26" s="183" t="inlineStr">
         <is>
           <t>TV_gordon = FCFF_n×(1+g)/(WACC−g)   [CHECK]</t>
         </is>
@@ -7758,7 +8264,7 @@
         </is>
       </c>
       <c r="C27" s="97" t="n"/>
-      <c r="D27" s="191">
+      <c r="D27" s="197">
         <f>-I35</f>
         <v/>
       </c>
@@ -7767,7 +8273,7 @@
       <c r="G27" s="97" t="n"/>
       <c r="H27" s="97" t="n"/>
       <c r="I27" s="97" t="n"/>
-      <c r="J27" s="182">
+      <c r="J27" s="188">
         <f>($I$21+$I$23)*$D$8</f>
         <v/>
       </c>
@@ -7776,20 +8282,20 @@
       <c r="M27" s="97" t="n"/>
       <c r="N27" s="97" t="n"/>
       <c r="O27" s="97" t="n"/>
-      <c r="Q27" s="171" t="inlineStr">
+      <c r="Q27" s="177" t="inlineStr">
         <is>
           <t>Excel</t>
         </is>
       </c>
-      <c r="R27" s="177">
+      <c r="R27" s="183">
         <f>IF(($D$6-$D$7)&lt;=0,"err",$I$26*(1+$D$7)/($D$6-$D$7))</f>
         <v/>
       </c>
-      <c r="T27" s="189">
+      <c r="T27" s="195">
         <f>M19</f>
         <v/>
       </c>
-      <c r="U27" s="173" t="inlineStr">
+      <c r="U27" s="179" t="inlineStr">
         <is>
           <t>Gordon g vs Damodaran long-run growth framing</t>
         </is>
@@ -7803,30 +8309,30 @@
         </is>
       </c>
       <c r="C28" s="97" t="n"/>
-      <c r="D28" s="190" t="n">
+      <c r="D28" s="196" t="n">
         <v>0</v>
       </c>
-      <c r="E28" s="192">
+      <c r="E28" s="198">
         <f>E27+E26</f>
         <v/>
       </c>
-      <c r="F28" s="192">
+      <c r="F28" s="198">
         <f>F27+F26</f>
         <v/>
       </c>
-      <c r="G28" s="192">
+      <c r="G28" s="198">
         <f>G27+G26</f>
         <v/>
       </c>
-      <c r="H28" s="192">
+      <c r="H28" s="198">
         <f>H27+H26</f>
         <v/>
       </c>
-      <c r="I28" s="192">
+      <c r="I28" s="198">
         <f>I27+I26</f>
         <v/>
       </c>
-      <c r="J28" s="192">
+      <c r="J28" s="198">
         <f>J27+J26</f>
         <v/>
       </c>
@@ -7835,16 +8341,16 @@
       <c r="M28" s="97" t="n"/>
       <c r="N28" s="97" t="n"/>
       <c r="O28" s="97" t="n"/>
-      <c r="Q28" s="171" t="inlineStr">
+      <c r="Q28" s="177" t="inlineStr">
         <is>
           <t>Implied Gordon exit multiple</t>
         </is>
       </c>
-      <c r="R28" s="193">
+      <c r="R28" s="199">
         <f>IF(($I$21+$I$23)=0,0,T27/($I$21+$I$23))</f>
         <v/>
       </c>
-      <c r="S28" s="171" t="inlineStr">
+      <c r="S28" s="177" t="inlineStr">
         <is>
           <t>Gordon TV / EBITDA_n</t>
         </is>
@@ -7858,31 +8364,31 @@
         </is>
       </c>
       <c r="C29" s="97" t="n"/>
-      <c r="D29" s="191">
+      <c r="D29" s="197">
         <f>D27+D26</f>
         <v/>
       </c>
-      <c r="E29" s="182">
+      <c r="E29" s="188">
         <f>E27+E26</f>
         <v/>
       </c>
-      <c r="F29" s="182">
+      <c r="F29" s="188">
         <f>F27+F26</f>
         <v/>
       </c>
-      <c r="G29" s="182">
+      <c r="G29" s="188">
         <f>G27+G26</f>
         <v/>
       </c>
-      <c r="H29" s="182">
+      <c r="H29" s="188">
         <f>H27+H26</f>
         <v/>
       </c>
-      <c r="I29" s="182">
+      <c r="I29" s="188">
         <f>I27+I26</f>
         <v/>
       </c>
-      <c r="J29" s="182">
+      <c r="J29" s="188">
         <f>J27</f>
         <v/>
       </c>
@@ -7938,7 +8444,7 @@
       <c r="M31" s="111" t="n"/>
       <c r="N31" s="111" t="n"/>
       <c r="O31" s="97" t="n"/>
-      <c r="Q31" s="177" t="inlineStr">
+      <c r="Q31" s="183" t="inlineStr">
         <is>
           <t>EV = XNPV(WACC, TransactionCF, mid-year dates)</t>
         </is>
@@ -7952,7 +8458,7 @@
         </is>
       </c>
       <c r="C32" s="97" t="n"/>
-      <c r="D32" s="182">
+      <c r="D32" s="188">
         <f>XNPV(D6,D28:J28,D18:J18)</f>
         <v/>
       </c>
@@ -7963,7 +8469,7 @@
         </is>
       </c>
       <c r="H32" s="97" t="n"/>
-      <c r="I32" s="191">
+      <c r="I32" s="197">
         <f>D12*D11</f>
         <v/>
       </c>
@@ -7979,16 +8485,16 @@
         <v/>
       </c>
       <c r="O32" s="97" t="n"/>
-      <c r="Q32" s="171" t="inlineStr">
+      <c r="Q32" s="177" t="inlineStr">
         <is>
           <t>Excel</t>
         </is>
       </c>
-      <c r="R32" s="177">
+      <c r="R32" s="183">
         <f>XNPV(D6,D28:J28,D18:J18)</f>
         <v/>
       </c>
-      <c r="T32" s="189">
+      <c r="T32" s="195">
         <f>D32</f>
         <v/>
       </c>
@@ -8001,7 +8507,7 @@
         </is>
       </c>
       <c r="C33" s="97" t="n"/>
-      <c r="D33" s="191">
+      <c r="D33" s="197">
         <f>+D14</f>
         <v/>
       </c>
@@ -8012,7 +8518,7 @@
         </is>
       </c>
       <c r="H33" s="97" t="n"/>
-      <c r="I33" s="191">
+      <c r="I33" s="197">
         <f>D13</f>
         <v/>
       </c>
@@ -8028,26 +8534,26 @@
         <v/>
       </c>
       <c r="O33" s="97" t="n"/>
-      <c r="Q33" s="177" t="inlineStr">
+      <c r="Q33" s="183" t="inlineStr">
         <is>
           <t>Equity = EV + Cash − Debt</t>
         </is>
       </c>
-      <c r="R33" s="189">
+      <c r="R33" s="195">
         <f>D35</f>
         <v/>
       </c>
-      <c r="S33" s="171" t="inlineStr">
+      <c r="S33" s="177" t="inlineStr">
         <is>
           <t>Net debt from 10-Q bridge</t>
         </is>
       </c>
-      <c r="U33" s="173" t="inlineStr">
+      <c r="U33" s="179" t="inlineStr">
         <is>
           <t>SEC 10-Q — cash, mkt secs, total debt</t>
         </is>
       </c>
-      <c r="V33" s="173" t="inlineStr">
+      <c r="V33" s="179" t="inlineStr">
         <is>
           <t>SEC 10-K — FY debt footnote</t>
         </is>
@@ -8061,7 +8567,7 @@
         </is>
       </c>
       <c r="C34" s="97" t="n"/>
-      <c r="D34" s="191">
+      <c r="D34" s="197">
         <f>+D13</f>
         <v/>
       </c>
@@ -8072,7 +8578,7 @@
         </is>
       </c>
       <c r="H34" s="97" t="n"/>
-      <c r="I34" s="191">
+      <c r="I34" s="197">
         <f>+D14</f>
         <v/>
       </c>
@@ -8081,26 +8587,26 @@
       <c r="M34" s="97" t="n"/>
       <c r="N34" s="97" t="n"/>
       <c r="O34" s="97" t="n"/>
-      <c r="Q34" s="177" t="inlineStr">
+      <c r="Q34" s="183" t="inlineStr">
         <is>
           <t>$/share = Equity / Shares</t>
         </is>
       </c>
-      <c r="R34" s="194">
+      <c r="R34" s="200">
         <f>D37</f>
         <v/>
       </c>
-      <c r="S34" s="171" t="inlineStr">
+      <c r="S34" s="177" t="inlineStr">
         <is>
           <t>Shares outstanding (Yahoo)</t>
         </is>
       </c>
-      <c r="U34" s="173" t="inlineStr">
+      <c r="U34" s="179" t="inlineStr">
         <is>
           <t>Yahoo Finance — shares outstanding</t>
         </is>
       </c>
-      <c r="V34" s="173" t="inlineStr">
+      <c r="V34" s="179" t="inlineStr">
         <is>
           <t>Yahoo FICO quote (price)</t>
         </is>
@@ -8114,7 +8620,7 @@
         </is>
       </c>
       <c r="C35" s="97" t="n"/>
-      <c r="D35" s="190">
+      <c r="D35" s="196">
         <f>D32+D33-D34</f>
         <v/>
       </c>
@@ -8125,7 +8631,7 @@
         </is>
       </c>
       <c r="H35" s="97" t="n"/>
-      <c r="I35" s="190">
+      <c r="I35" s="196">
         <f>I32+I33-I34</f>
         <v/>
       </c>
@@ -8138,16 +8644,16 @@
       <c r="M35" s="111" t="n"/>
       <c r="N35" s="111" t="n"/>
       <c r="O35" s="97" t="n"/>
-      <c r="Q35" s="171" t="inlineStr">
+      <c r="Q35" s="177" t="inlineStr">
         <is>
           <t>Upside vs market</t>
         </is>
       </c>
-      <c r="R35" s="195">
+      <c r="R35" s="201">
         <f>D37/D11-1</f>
         <v/>
       </c>
-      <c r="S35" s="171" t="inlineStr">
+      <c r="S35" s="177" t="inlineStr">
         <is>
           <t>Intrinsic / Current Price − 1</t>
         </is>
@@ -8161,7 +8667,7 @@
       <c r="E36" s="97" t="n"/>
       <c r="G36" s="97" t="n"/>
       <c r="H36" s="97" t="n"/>
-      <c r="I36" s="196" t="n"/>
+      <c r="I36" s="202" t="n"/>
       <c r="J36" s="97" t="n"/>
       <c r="L36" s="97" t="inlineStr">
         <is>
@@ -8169,7 +8675,7 @@
         </is>
       </c>
       <c r="M36" s="97" t="n"/>
-      <c r="N36" s="196">
+      <c r="N36" s="202">
         <f>I37</f>
         <v/>
       </c>
@@ -8183,7 +8689,7 @@
         </is>
       </c>
       <c r="C37" s="97" t="n"/>
-      <c r="D37" s="191">
+      <c r="D37" s="197">
         <f>D35/D12</f>
         <v/>
       </c>
@@ -8194,7 +8700,7 @@
         </is>
       </c>
       <c r="H37" s="97" t="n"/>
-      <c r="I37" s="191">
+      <c r="I37" s="197">
         <f>D11</f>
         <v/>
       </c>
@@ -8205,7 +8711,7 @@
         </is>
       </c>
       <c r="M37" s="97" t="n"/>
-      <c r="N37" s="196">
+      <c r="N37" s="202">
         <f>D37-I37</f>
         <v/>
       </c>
@@ -8232,22 +8738,22 @@
         </is>
       </c>
       <c r="M38" s="97" t="n"/>
-      <c r="N38" s="196">
+      <c r="N38" s="202">
         <f>SUM(N36:N37)</f>
         <v/>
       </c>
       <c r="O38" s="97" t="n"/>
-      <c r="Q38" s="177" t="inlineStr">
+      <c r="Q38" s="183" t="inlineStr">
         <is>
           <t>NWC = AR + Inventory − AP − DeferredRevenue</t>
         </is>
       </c>
-      <c r="U38" s="173" t="inlineStr">
+      <c r="U38" s="179" t="inlineStr">
         <is>
           <t>SEC 10-K — AR / AP / deferred revenue</t>
         </is>
       </c>
-      <c r="V38" s="173" t="inlineStr">
+      <c r="V38" s="179" t="inlineStr">
         <is>
           <t>XBRL DeferredRevenueCurrent</t>
         </is>
@@ -8266,17 +8772,17 @@
       <c r="M39" s="97" t="n"/>
       <c r="N39" s="97" t="n"/>
       <c r="O39" s="97" t="n"/>
-      <c r="Q39" s="177" t="inlineStr">
+      <c r="Q39" s="183" t="inlineStr">
         <is>
           <t>ΔNWC_t = NWC_t − NWC_(t−1)</t>
         </is>
       </c>
-      <c r="S39" s="171" t="inlineStr">
+      <c r="S39" s="177" t="inlineStr">
         <is>
           <t>Linked from 3-statement CF row 64</t>
         </is>
       </c>
-      <c r="T39" s="189">
+      <c r="T39" s="195">
         <f>I25</f>
         <v/>
       </c>
@@ -8341,14 +8847,14 @@
         </is>
       </c>
       <c r="O42" s="97" t="n"/>
-      <c r="Q42" s="173" t="inlineStr">
+      <c r="Q42" s="179" t="inlineStr">
         <is>
           <t>SEC 10-K FY2025</t>
         </is>
       </c>
-      <c r="R42" s="197" t="n"/>
-      <c r="S42" s="198" t="n"/>
-      <c r="T42" s="171" t="inlineStr">
+      <c r="R42" s="203" t="n"/>
+      <c r="S42" s="204" t="n"/>
+      <c r="T42" s="177" t="inlineStr">
         <is>
           <t>Tax 18.8%, IS/BS/CF, senior notes</t>
         </is>
@@ -8369,14 +8875,14 @@
       <c r="H43" s="97" t="n"/>
       <c r="N43" s="69" t="n"/>
       <c r="O43" s="97" t="n"/>
-      <c r="Q43" s="173" t="inlineStr">
+      <c r="Q43" s="179" t="inlineStr">
         <is>
           <t>SEC 10-Q Q3 FY2026</t>
         </is>
       </c>
-      <c r="R43" s="197" t="n"/>
-      <c r="S43" s="198" t="n"/>
-      <c r="T43" s="171" t="inlineStr">
+      <c r="R43" s="203" t="n"/>
+      <c r="S43" s="204" t="n"/>
+      <c r="T43" s="177" t="inlineStr">
         <is>
           <t>Debt $5,582M, cash+mkt secs net-debt bridge</t>
         </is>
@@ -8397,14 +8903,14 @@
       <c r="H44" s="97" t="n"/>
       <c r="N44" s="69" t="n"/>
       <c r="O44" s="97" t="n"/>
-      <c r="Q44" s="173" t="inlineStr">
+      <c r="Q44" s="179" t="inlineStr">
         <is>
           <t>SEC 8-K 6.250% notes</t>
         </is>
       </c>
-      <c r="R44" s="197" t="n"/>
-      <c r="S44" s="198" t="n"/>
-      <c r="T44" s="171" t="inlineStr">
+      <c r="R44" s="203" t="n"/>
+      <c r="S44" s="204" t="n"/>
+      <c r="T44" s="177" t="inlineStr">
         <is>
           <t>Pre-tax Rd coupon 6.250% due 2034</t>
         </is>
@@ -8425,14 +8931,14 @@
       <c r="H45" s="97" t="n"/>
       <c r="N45" s="69" t="n"/>
       <c r="O45" s="97" t="n"/>
-      <c r="Q45" s="173" t="inlineStr">
+      <c r="Q45" s="179" t="inlineStr">
         <is>
           <t>SEC EX-99.1 pricing</t>
         </is>
       </c>
-      <c r="R45" s="197" t="n"/>
-      <c r="S45" s="198" t="n"/>
-      <c r="T45" s="171" t="inlineStr">
+      <c r="R45" s="203" t="n"/>
+      <c r="S45" s="204" t="n"/>
+      <c r="T45" s="177" t="inlineStr">
         <is>
           <t>Notes priced at par / offering terms</t>
         </is>
@@ -8453,14 +8959,14 @@
       <c r="H46" s="97" t="n"/>
       <c r="N46" s="69" t="n"/>
       <c r="O46" s="97" t="n"/>
-      <c r="Q46" s="173" t="inlineStr">
+      <c r="Q46" s="179" t="inlineStr">
         <is>
           <t>SEC companyfacts XBRL</t>
         </is>
       </c>
-      <c r="R46" s="197" t="n"/>
-      <c r="S46" s="198" t="n"/>
-      <c r="T46" s="171" t="inlineStr">
+      <c r="R46" s="203" t="n"/>
+      <c r="S46" s="204" t="n"/>
+      <c r="T46" s="177" t="inlineStr">
         <is>
           <t>Pipeline data source (CIK 0000814547)</t>
         </is>
@@ -8477,14 +8983,14 @@
       <c r="H47" s="97" t="n"/>
       <c r="N47" s="69" t="n"/>
       <c r="O47" s="97" t="n"/>
-      <c r="Q47" s="173" t="inlineStr">
+      <c r="Q47" s="179" t="inlineStr">
         <is>
           <t>FRED DGS10</t>
         </is>
       </c>
-      <c r="R47" s="197" t="n"/>
-      <c r="S47" s="198" t="n"/>
-      <c r="T47" s="171" t="inlineStr">
+      <c r="R47" s="203" t="n"/>
+      <c r="S47" s="204" t="n"/>
+      <c r="T47" s="177" t="inlineStr">
         <is>
           <t>Risk-free rate (US 10Y)</t>
         </is>
@@ -8505,14 +9011,14 @@
         </is>
       </c>
       <c r="O48" s="97" t="n"/>
-      <c r="Q48" s="173" t="inlineStr">
+      <c r="Q48" s="179" t="inlineStr">
         <is>
           <t>US Treasury yield curve</t>
         </is>
       </c>
-      <c r="R48" s="197" t="n"/>
-      <c r="S48" s="198" t="n"/>
-      <c r="T48" s="171" t="inlineStr">
+      <c r="R48" s="203" t="n"/>
+      <c r="S48" s="204" t="n"/>
+      <c r="T48" s="177" t="inlineStr">
         <is>
           <t>Official daily par yields</t>
         </is>
@@ -8533,14 +9039,14 @@
         </is>
       </c>
       <c r="O49" s="97" t="n"/>
-      <c r="Q49" s="173" t="inlineStr">
+      <c r="Q49" s="179" t="inlineStr">
         <is>
           <t>Damodaran Implied ERP</t>
         </is>
       </c>
-      <c r="R49" s="197" t="n"/>
-      <c r="S49" s="198" t="n"/>
-      <c r="T49" s="171" t="inlineStr">
+      <c r="R49" s="203" t="n"/>
+      <c r="S49" s="204" t="n"/>
+      <c r="T49" s="177" t="inlineStr">
         <is>
           <t>Equity risk premium</t>
         </is>
@@ -8556,14 +9062,14 @@
       <c r="G50" s="97" t="n"/>
       <c r="H50" s="97" t="n"/>
       <c r="O50" s="97" t="n"/>
-      <c r="Q50" s="173" t="inlineStr">
+      <c r="Q50" s="179" t="inlineStr">
         <is>
           <t>Damodaran histimpl</t>
         </is>
       </c>
-      <c r="R50" s="197" t="n"/>
-      <c r="S50" s="198" t="n"/>
-      <c r="T50" s="171" t="inlineStr">
+      <c r="R50" s="203" t="n"/>
+      <c r="S50" s="204" t="n"/>
+      <c r="T50" s="177" t="inlineStr">
         <is>
           <t>Historical implied ERP table</t>
         </is>
@@ -8580,14 +9086,14 @@
       <c r="H51" s="97" t="n"/>
       <c r="M51" s="97" t="n"/>
       <c r="O51" s="97" t="n"/>
-      <c r="Q51" s="173" t="inlineStr">
+      <c r="Q51" s="179" t="inlineStr">
         <is>
           <t>Yahoo FICO stats</t>
         </is>
       </c>
-      <c r="R51" s="197" t="n"/>
-      <c r="S51" s="198" t="n"/>
-      <c r="T51" s="171" t="inlineStr">
+      <c r="R51" s="203" t="n"/>
+      <c r="S51" s="204" t="n"/>
+      <c r="T51" s="177" t="inlineStr">
         <is>
           <t>Beta 5Y monthly + shares out</t>
         </is>

--- a/FICO/output/FICO_Completed_Model.xlsx
+++ b/FICO/output/FICO_Completed_Model.xlsx
@@ -854,7 +854,9 @@
     <xf numFmtId="0" fontId="45" fillId="10" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="42" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="164" fontId="42" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="166" fontId="40" fillId="8" borderId="5" pivotButton="0" quotePrefix="0" xfId="2"/>
     <xf numFmtId="0" fontId="46" fillId="11" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -865,7 +867,9 @@
     <xf numFmtId="166" fontId="38" fillId="7" borderId="5" pivotButton="0" quotePrefix="0" xfId="2"/>
     <xf numFmtId="177" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="166" fontId="38" fillId="7" borderId="5" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="177" fontId="38" fillId="7" borderId="5" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="177" fontId="40" fillId="8" borderId="5" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="166" fontId="40" fillId="8" borderId="5" pivotButton="0" quotePrefix="0" xfId="1"/>
@@ -1741,6 +1745,848 @@
 </chartSpace>
 </file>
 
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>vengeanceaiUSCMODEL4</author>
+  </authors>
+  <commentList>
+    <comment ref="B7" authorId="0" shapeId="0">
+      <text>
+        <t>Revenue Growth
+HOW: Yellow POLICY input: 27% / 16% / 13% / 10% / 7%.
+WHY: Y1 ≈ company FY2026 revenue guidance (~$2.53B / FY25 $1.991B − 1 ≈ 27%). Then fade toward terminal g=3% (not straight-lined). This is the main forward-looking judgment; it drives Rev → GP → EBT → Net Earnings → CF.
+SOURCE: FICO FY2026 guidance + fade policy</t>
+      </text>
+    </comment>
+    <comment ref="J7" authorId="0" shapeId="0">
+      <text>
+        <t>Revenue Growth
+HOW: Yellow POLICY input: 27% / 16% / 13% / 10% / 7%.
+WHY: Y1 ≈ company FY2026 revenue guidance (~$2.53B / FY25 $1.991B − 1 ≈ 27%). Then fade toward terminal g=3% (not straight-lined). This is the main forward-looking judgment; it drives Rev → GP → EBT → Net Earnings → CF.
+SOURCE: FICO FY2026 guidance + fade policy</t>
+      </text>
+    </comment>
+    <comment ref="K7" authorId="0" shapeId="0">
+      <text>
+        <t>Revenue Growth
+HOW: Yellow POLICY input: 27% / 16% / 13% / 10% / 7%.
+WHY: Y1 ≈ company FY2026 revenue guidance (~$2.53B / FY25 $1.991B − 1 ≈ 27%). Then fade toward terminal g=3% (not straight-lined). This is the main forward-looking judgment; it drives Rev → GP → EBT → Net Earnings → CF.
+SOURCE: FICO FY2026 guidance + fade policy</t>
+      </text>
+    </comment>
+    <comment ref="L7" authorId="0" shapeId="0">
+      <text>
+        <t>Revenue Growth
+HOW: Yellow POLICY input: 27% / 16% / 13% / 10% / 7%.
+WHY: Y1 ≈ company FY2026 revenue guidance (~$2.53B / FY25 $1.991B − 1 ≈ 27%). Then fade toward terminal g=3% (not straight-lined). This is the main forward-looking judgment; it drives Rev → GP → EBT → Net Earnings → CF.
+SOURCE: FICO FY2026 guidance + fade policy</t>
+      </text>
+    </comment>
+    <comment ref="M7" authorId="0" shapeId="0">
+      <text>
+        <t>Revenue Growth
+HOW: Yellow POLICY input: 27% / 16% / 13% / 10% / 7%.
+WHY: Y1 ≈ company FY2026 revenue guidance (~$2.53B / FY25 $1.991B − 1 ≈ 27%). Then fade toward terminal g=3% (not straight-lined). This is the main forward-looking judgment; it drives Rev → GP → EBT → Net Earnings → CF.
+SOURCE: FICO FY2026 guidance + fade policy</t>
+      </text>
+    </comment>
+    <comment ref="N7" authorId="0" shapeId="0">
+      <text>
+        <t>Revenue Growth
+HOW: Yellow POLICY input: 27% / 16% / 13% / 10% / 7%.
+WHY: Y1 ≈ company FY2026 revenue guidance (~$2.53B / FY25 $1.991B − 1 ≈ 27%). Then fade toward terminal g=3% (not straight-lined). This is the main forward-looking judgment; it drives Rev → GP → EBT → Net Earnings → CF.
+SOURCE: FICO FY2026 guidance + fade policy</t>
+      </text>
+    </comment>
+    <comment ref="T7" authorId="0" shapeId="0">
+      <text>
+        <t>Revenue Growth
+HOW: Yellow POLICY input: 27% / 16% / 13% / 10% / 7%.
+WHY: Y1 ≈ company FY2026 revenue guidance (~$2.53B / FY25 $1.991B − 1 ≈ 27%). Then fade toward terminal g=3% (not straight-lined). This is the main forward-looking judgment; it drives Rev → GP → EBT → Net Earnings → CF.
+SOURCE: FICO FY2026 guidance + fade policy</t>
+      </text>
+    </comment>
+    <comment ref="U7" authorId="0" shapeId="0">
+      <text>
+        <t>Revenue Growth
+HOW: Yellow POLICY input: 27% / 16% / 13% / 10% / 7%.
+WHY: Y1 ≈ company FY2026 revenue guidance (~$2.53B / FY25 $1.991B − 1 ≈ 27%). Then fade toward terminal g=3% (not straight-lined). This is the main forward-looking judgment; it drives Rev → GP → EBT → Net Earnings → CF.
+SOURCE: FICO FY2026 guidance + fade policy</t>
+      </text>
+    </comment>
+    <comment ref="B8" authorId="0" shapeId="0">
+      <text>
+        <t>COGS % of Revenue
+HOW: Excel equation: I25/I24 (FY25 COGS ÷ FY25 Revenue) held flat.
+WHY: Locks in latest reported cost structure (~17.8%). Scores mix is high-margin; holding FY25 is conservative vs further mix shift.
+SOURCE: SEC 10-K FY2025 — Cost of revenues / Total revenues</t>
+      </text>
+    </comment>
+    <comment ref="J8" authorId="0" shapeId="0">
+      <text>
+        <t>COGS % of Revenue
+HOW: Excel equation: I25/I24 (FY25 COGS ÷ FY25 Revenue) held flat.
+WHY: Locks in latest reported cost structure (~17.8%). Scores mix is high-margin; holding FY25 is conservative vs further mix shift.
+SOURCE: SEC 10-K FY2025 — Cost of revenues / Total revenues</t>
+      </text>
+    </comment>
+    <comment ref="K8" authorId="0" shapeId="0">
+      <text>
+        <t>COGS % of Revenue
+HOW: Excel equation: I25/I24 (FY25 COGS ÷ FY25 Revenue) held flat.
+WHY: Locks in latest reported cost structure (~17.8%). Scores mix is high-margin; holding FY25 is conservative vs further mix shift.
+SOURCE: SEC 10-K FY2025 — Cost of revenues / Total revenues</t>
+      </text>
+    </comment>
+    <comment ref="L8" authorId="0" shapeId="0">
+      <text>
+        <t>COGS % of Revenue
+HOW: Excel equation: I25/I24 (FY25 COGS ÷ FY25 Revenue) held flat.
+WHY: Locks in latest reported cost structure (~17.8%). Scores mix is high-margin; holding FY25 is conservative vs further mix shift.
+SOURCE: SEC 10-K FY2025 — Cost of revenues / Total revenues</t>
+      </text>
+    </comment>
+    <comment ref="M8" authorId="0" shapeId="0">
+      <text>
+        <t>COGS % of Revenue
+HOW: Excel equation: I25/I24 (FY25 COGS ÷ FY25 Revenue) held flat.
+WHY: Locks in latest reported cost structure (~17.8%). Scores mix is high-margin; holding FY25 is conservative vs further mix shift.
+SOURCE: SEC 10-K FY2025 — Cost of revenues / Total revenues</t>
+      </text>
+    </comment>
+    <comment ref="N8" authorId="0" shapeId="0">
+      <text>
+        <t>COGS % of Revenue
+HOW: Excel equation: I25/I24 (FY25 COGS ÷ FY25 Revenue) held flat.
+WHY: Locks in latest reported cost structure (~17.8%). Scores mix is high-margin; holding FY25 is conservative vs further mix shift.
+SOURCE: SEC 10-K FY2025 — Cost of revenues / Total revenues</t>
+      </text>
+    </comment>
+    <comment ref="T8" authorId="0" shapeId="0">
+      <text>
+        <t>COGS % of Revenue
+HOW: Excel equation: I25/I24 (FY25 COGS ÷ FY25 Revenue) held flat.
+WHY: Locks in latest reported cost structure (~17.8%). Scores mix is high-margin; holding FY25 is conservative vs further mix shift.
+SOURCE: SEC 10-K FY2025 — Cost of revenues / Total revenues</t>
+      </text>
+    </comment>
+    <comment ref="U8" authorId="0" shapeId="0">
+      <text>
+        <t>COGS % of Revenue
+HOW: Excel equation: I25/I24 (FY25 COGS ÷ FY25 Revenue) held flat.
+WHY: Locks in latest reported cost structure (~17.8%). Scores mix is high-margin; holding FY25 is conservative vs further mix shift.
+SOURCE: SEC 10-K FY2025 — Cost of revenues / Total revenues</t>
+      </text>
+    </comment>
+    <comment ref="B9" authorId="0" shapeId="0">
+      <text>
+        <t>SGA % of Revenue
+HOW: Equation: (I28 − 10,922)/I24 − 50bps × year. Strips FY25 restructuring; then −0.5% of sales each year.
+WHY: Normalize one-time restructuring ($10.9M). Mild efficiency grind reflects operating leverage as revenue scales; floored at 5%.
+SOURCE: SEC 10-K FY2025 — SG&amp;A + restructuring note</t>
+      </text>
+    </comment>
+    <comment ref="J9" authorId="0" shapeId="0">
+      <text>
+        <t>SGA % of Revenue
+HOW: Equation: (I28 − 10,922)/I24 − 50bps × year. Strips FY25 restructuring; then −0.5% of sales each year.
+WHY: Normalize one-time restructuring ($10.9M). Mild efficiency grind reflects operating leverage as revenue scales; floored at 5%.
+SOURCE: SEC 10-K FY2025 — SG&amp;A + restructuring note</t>
+      </text>
+    </comment>
+    <comment ref="K9" authorId="0" shapeId="0">
+      <text>
+        <t>SGA % of Revenue
+HOW: Equation: (I28 − 10,922)/I24 − 50bps × year. Strips FY25 restructuring; then −0.5% of sales each year.
+WHY: Normalize one-time restructuring ($10.9M). Mild efficiency grind reflects operating leverage as revenue scales; floored at 5%.
+SOURCE: SEC 10-K FY2025 — SG&amp;A + restructuring note</t>
+      </text>
+    </comment>
+    <comment ref="L9" authorId="0" shapeId="0">
+      <text>
+        <t>SGA % of Revenue
+HOW: Equation: (I28 − 10,922)/I24 − 50bps × year. Strips FY25 restructuring; then −0.5% of sales each year.
+WHY: Normalize one-time restructuring ($10.9M). Mild efficiency grind reflects operating leverage as revenue scales; floored at 5%.
+SOURCE: SEC 10-K FY2025 — SG&amp;A + restructuring note</t>
+      </text>
+    </comment>
+    <comment ref="M9" authorId="0" shapeId="0">
+      <text>
+        <t>SGA % of Revenue
+HOW: Equation: (I28 − 10,922)/I24 − 50bps × year. Strips FY25 restructuring; then −0.5% of sales each year.
+WHY: Normalize one-time restructuring ($10.9M). Mild efficiency grind reflects operating leverage as revenue scales; floored at 5%.
+SOURCE: SEC 10-K FY2025 — SG&amp;A + restructuring note</t>
+      </text>
+    </comment>
+    <comment ref="N9" authorId="0" shapeId="0">
+      <text>
+        <t>SGA % of Revenue
+HOW: Equation: (I28 − 10,922)/I24 − 50bps × year. Strips FY25 restructuring; then −0.5% of sales each year.
+WHY: Normalize one-time restructuring ($10.9M). Mild efficiency grind reflects operating leverage as revenue scales; floored at 5%.
+SOURCE: SEC 10-K FY2025 — SG&amp;A + restructuring note</t>
+      </text>
+    </comment>
+    <comment ref="T9" authorId="0" shapeId="0">
+      <text>
+        <t>SGA % of Revenue
+HOW: Equation: (I28 − 10,922)/I24 − 50bps × year. Strips FY25 restructuring; then −0.5% of sales each year.
+WHY: Normalize one-time restructuring ($10.9M). Mild efficiency grind reflects operating leverage as revenue scales; floored at 5%.
+SOURCE: SEC 10-K FY2025 — SG&amp;A + restructuring note</t>
+      </text>
+    </comment>
+    <comment ref="U9" authorId="0" shapeId="0">
+      <text>
+        <t>SGA % of Revenue
+HOW: Equation: (I28 − 10,922)/I24 − 50bps × year. Strips FY25 restructuring; then −0.5% of sales each year.
+WHY: Normalize one-time restructuring ($10.9M). Mild efficiency grind reflects operating leverage as revenue scales; floored at 5%.
+SOURCE: SEC 10-K FY2025 — SG&amp;A + restructuring note</t>
+      </text>
+    </comment>
+    <comment ref="B10" authorId="0" shapeId="0">
+      <text>
+        <t>R&amp;D % of Revenue
+HOW: Excel equation: I29/I24 held flat (~9.46%).
+WHY: FICO reinvests steadily in analytics/software. Flat % grows dollars with revenue.
+SOURCE: SEC 10-K FY2025 — Research and development</t>
+      </text>
+    </comment>
+    <comment ref="J10" authorId="0" shapeId="0">
+      <text>
+        <t>R&amp;D % of Revenue
+HOW: Excel equation: I29/I24 held flat (~9.46%).
+WHY: FICO reinvests steadily in analytics/software. Flat % grows dollars with revenue.
+SOURCE: SEC 10-K FY2025 — Research and development</t>
+      </text>
+    </comment>
+    <comment ref="K10" authorId="0" shapeId="0">
+      <text>
+        <t>R&amp;D % of Revenue
+HOW: Excel equation: I29/I24 held flat (~9.46%).
+WHY: FICO reinvests steadily in analytics/software. Flat % grows dollars with revenue.
+SOURCE: SEC 10-K FY2025 — Research and development</t>
+      </text>
+    </comment>
+    <comment ref="L10" authorId="0" shapeId="0">
+      <text>
+        <t>R&amp;D % of Revenue
+HOW: Excel equation: I29/I24 held flat (~9.46%).
+WHY: FICO reinvests steadily in analytics/software. Flat % grows dollars with revenue.
+SOURCE: SEC 10-K FY2025 — Research and development</t>
+      </text>
+    </comment>
+    <comment ref="M10" authorId="0" shapeId="0">
+      <text>
+        <t>R&amp;D % of Revenue
+HOW: Excel equation: I29/I24 held flat (~9.46%).
+WHY: FICO reinvests steadily in analytics/software. Flat % grows dollars with revenue.
+SOURCE: SEC 10-K FY2025 — Research and development</t>
+      </text>
+    </comment>
+    <comment ref="N10" authorId="0" shapeId="0">
+      <text>
+        <t>R&amp;D % of Revenue
+HOW: Excel equation: I29/I24 held flat (~9.46%).
+WHY: FICO reinvests steadily in analytics/software. Flat % grows dollars with revenue.
+SOURCE: SEC 10-K FY2025 — Research and development</t>
+      </text>
+    </comment>
+    <comment ref="T10" authorId="0" shapeId="0">
+      <text>
+        <t>R&amp;D % of Revenue
+HOW: Excel equation: I29/I24 held flat (~9.46%).
+WHY: FICO reinvests steadily in analytics/software. Flat % grows dollars with revenue.
+SOURCE: SEC 10-K FY2025 — Research and development</t>
+      </text>
+    </comment>
+    <comment ref="U10" authorId="0" shapeId="0">
+      <text>
+        <t>R&amp;D % of Revenue
+HOW: Excel equation: I29/I24 held flat (~9.46%).
+WHY: FICO reinvests steadily in analytics/software. Flat % grows dollars with revenue.
+SOURCE: SEC 10-K FY2025 — Research and development</t>
+      </text>
+    </comment>
+    <comment ref="B11" authorId="0" shapeId="0">
+      <text>
+        <t>D&amp;A % of PP&amp;E Open
+HOW: Excel equation: I30/I44 (FY25 DA ÷ FY25 PPE). Forecast DA = OpenPPE × this %.
+WHY: Ties DA to the asset base the schedule rolls forward (opens at I44).
+SOURCE: SEC 10-K FY2025 — D&amp;A and PP&amp;E</t>
+      </text>
+    </comment>
+    <comment ref="J11" authorId="0" shapeId="0">
+      <text>
+        <t>D&amp;A % of PP&amp;E Open
+HOW: Excel equation: I30/I44 (FY25 DA ÷ FY25 PPE). Forecast DA = OpenPPE × this %.
+WHY: Ties DA to the asset base the schedule rolls forward (opens at I44).
+SOURCE: SEC 10-K FY2025 — D&amp;A and PP&amp;E</t>
+      </text>
+    </comment>
+    <comment ref="K11" authorId="0" shapeId="0">
+      <text>
+        <t>D&amp;A % of PP&amp;E Open
+HOW: Excel equation: I30/I44 (FY25 DA ÷ FY25 PPE). Forecast DA = OpenPPE × this %.
+WHY: Ties DA to the asset base the schedule rolls forward (opens at I44).
+SOURCE: SEC 10-K FY2025 — D&amp;A and PP&amp;E</t>
+      </text>
+    </comment>
+    <comment ref="L11" authorId="0" shapeId="0">
+      <text>
+        <t>D&amp;A % of PP&amp;E Open
+HOW: Excel equation: I30/I44 (FY25 DA ÷ FY25 PPE). Forecast DA = OpenPPE × this %.
+WHY: Ties DA to the asset base the schedule rolls forward (opens at I44).
+SOURCE: SEC 10-K FY2025 — D&amp;A and PP&amp;E</t>
+      </text>
+    </comment>
+    <comment ref="M11" authorId="0" shapeId="0">
+      <text>
+        <t>D&amp;A % of PP&amp;E Open
+HOW: Excel equation: I30/I44 (FY25 DA ÷ FY25 PPE). Forecast DA = OpenPPE × this %.
+WHY: Ties DA to the asset base the schedule rolls forward (opens at I44).
+SOURCE: SEC 10-K FY2025 — D&amp;A and PP&amp;E</t>
+      </text>
+    </comment>
+    <comment ref="N11" authorId="0" shapeId="0">
+      <text>
+        <t>D&amp;A % of PP&amp;E Open
+HOW: Excel equation: I30/I44 (FY25 DA ÷ FY25 PPE). Forecast DA = OpenPPE × this %.
+WHY: Ties DA to the asset base the schedule rolls forward (opens at I44).
+SOURCE: SEC 10-K FY2025 — D&amp;A and PP&amp;E</t>
+      </text>
+    </comment>
+    <comment ref="T11" authorId="0" shapeId="0">
+      <text>
+        <t>D&amp;A % of PP&amp;E Open
+HOW: Excel equation: I30/I44 (FY25 DA ÷ FY25 PPE). Forecast DA = OpenPPE × this %.
+WHY: Ties DA to the asset base the schedule rolls forward (opens at I44).
+SOURCE: SEC 10-K FY2025 — D&amp;A and PP&amp;E</t>
+      </text>
+    </comment>
+    <comment ref="U11" authorId="0" shapeId="0">
+      <text>
+        <t>D&amp;A % of PP&amp;E Open
+HOW: Excel equation: I30/I44 (FY25 DA ÷ FY25 PPE). Forecast DA = OpenPPE × this %.
+WHY: Ties DA to the asset base the schedule rolls forward (opens at I44).
+SOURCE: SEC 10-K FY2025 — D&amp;A and PP&amp;E</t>
+      </text>
+    </comment>
+    <comment ref="B12" authorId="0" shapeId="0">
+      <text>
+        <t>Interest % of Debt Open
+HOW: Excel equation: I101/I98 (FY25 interest ÷ FY25 opening debt in schedule).
+WHY: Approximates average coupon / cost of debt on the book. Debt held flat (issuance = 0), so interest stays linked to that stock.
+SOURCE: SEC 10-K FY2025 — Interest expense, net + debt footnote</t>
+      </text>
+    </comment>
+    <comment ref="J12" authorId="0" shapeId="0">
+      <text>
+        <t>Interest % of Debt Open
+HOW: Excel equation: I101/I98 (FY25 interest ÷ FY25 opening debt in schedule).
+WHY: Approximates average coupon / cost of debt on the book. Debt held flat (issuance = 0), so interest stays linked to that stock.
+SOURCE: SEC 10-K FY2025 — Interest expense, net + debt footnote</t>
+      </text>
+    </comment>
+    <comment ref="K12" authorId="0" shapeId="0">
+      <text>
+        <t>Interest % of Debt Open
+HOW: Excel equation: I101/I98 (FY25 interest ÷ FY25 opening debt in schedule).
+WHY: Approximates average coupon / cost of debt on the book. Debt held flat (issuance = 0), so interest stays linked to that stock.
+SOURCE: SEC 10-K FY2025 — Interest expense, net + debt footnote</t>
+      </text>
+    </comment>
+    <comment ref="L12" authorId="0" shapeId="0">
+      <text>
+        <t>Interest % of Debt Open
+HOW: Excel equation: I101/I98 (FY25 interest ÷ FY25 opening debt in schedule).
+WHY: Approximates average coupon / cost of debt on the book. Debt held flat (issuance = 0), so interest stays linked to that stock.
+SOURCE: SEC 10-K FY2025 — Interest expense, net + debt footnote</t>
+      </text>
+    </comment>
+    <comment ref="M12" authorId="0" shapeId="0">
+      <text>
+        <t>Interest % of Debt Open
+HOW: Excel equation: I101/I98 (FY25 interest ÷ FY25 opening debt in schedule).
+WHY: Approximates average coupon / cost of debt on the book. Debt held flat (issuance = 0), so interest stays linked to that stock.
+SOURCE: SEC 10-K FY2025 — Interest expense, net + debt footnote</t>
+      </text>
+    </comment>
+    <comment ref="N12" authorId="0" shapeId="0">
+      <text>
+        <t>Interest % of Debt Open
+HOW: Excel equation: I101/I98 (FY25 interest ÷ FY25 opening debt in schedule).
+WHY: Approximates average coupon / cost of debt on the book. Debt held flat (issuance = 0), so interest stays linked to that stock.
+SOURCE: SEC 10-K FY2025 — Interest expense, net + debt footnote</t>
+      </text>
+    </comment>
+    <comment ref="T12" authorId="0" shapeId="0">
+      <text>
+        <t>Interest % of Debt Open
+HOW: Excel equation: I101/I98 (FY25 interest ÷ FY25 opening debt in schedule).
+WHY: Approximates average coupon / cost of debt on the book. Debt held flat (issuance = 0), so interest stays linked to that stock.
+SOURCE: SEC 10-K FY2025 — Interest expense, net + debt footnote</t>
+      </text>
+    </comment>
+    <comment ref="U12" authorId="0" shapeId="0">
+      <text>
+        <t>Interest % of Debt Open
+HOW: Excel equation: I101/I98 (FY25 interest ÷ FY25 opening debt in schedule).
+WHY: Approximates average coupon / cost of debt on the book. Debt held flat (issuance = 0), so interest stays linked to that stock.
+SOURCE: SEC 10-K FY2025 — Interest expense, net + debt footnote</t>
+      </text>
+    </comment>
+    <comment ref="B13" authorId="0" shapeId="0">
+      <text>
+        <t>Tax Rate (% of EBT)
+HOW: Excel equation: I35/I33 (FY25 tax ÷ simplified FY25 EBT in this template).
+WHY: Uses reported effective rate (~19% on template EBT; ~18.8% on 10-K EBT). UFCF in DCF also uses unlevered EBIT × t.
+SOURCE: SEC 10-K FY2025 — Provision for income taxes / Income before taxes</t>
+      </text>
+    </comment>
+    <comment ref="J13" authorId="0" shapeId="0">
+      <text>
+        <t>Tax Rate (% of EBT)
+HOW: Excel equation: I35/I33 (FY25 tax ÷ simplified FY25 EBT in this template).
+WHY: Uses reported effective rate (~19% on template EBT; ~18.8% on 10-K EBT). UFCF in DCF also uses unlevered EBIT × t.
+SOURCE: SEC 10-K FY2025 — Provision for income taxes / Income before taxes</t>
+      </text>
+    </comment>
+    <comment ref="K13" authorId="0" shapeId="0">
+      <text>
+        <t>Tax Rate (% of EBT)
+HOW: Excel equation: I35/I33 (FY25 tax ÷ simplified FY25 EBT in this template).
+WHY: Uses reported effective rate (~19% on template EBT; ~18.8% on 10-K EBT). UFCF in DCF also uses unlevered EBIT × t.
+SOURCE: SEC 10-K FY2025 — Provision for income taxes / Income before taxes</t>
+      </text>
+    </comment>
+    <comment ref="L13" authorId="0" shapeId="0">
+      <text>
+        <t>Tax Rate (% of EBT)
+HOW: Excel equation: I35/I33 (FY25 tax ÷ simplified FY25 EBT in this template).
+WHY: Uses reported effective rate (~19% on template EBT; ~18.8% on 10-K EBT). UFCF in DCF also uses unlevered EBIT × t.
+SOURCE: SEC 10-K FY2025 — Provision for income taxes / Income before taxes</t>
+      </text>
+    </comment>
+    <comment ref="M13" authorId="0" shapeId="0">
+      <text>
+        <t>Tax Rate (% of EBT)
+HOW: Excel equation: I35/I33 (FY25 tax ÷ simplified FY25 EBT in this template).
+WHY: Uses reported effective rate (~19% on template EBT; ~18.8% on 10-K EBT). UFCF in DCF also uses unlevered EBIT × t.
+SOURCE: SEC 10-K FY2025 — Provision for income taxes / Income before taxes</t>
+      </text>
+    </comment>
+    <comment ref="N13" authorId="0" shapeId="0">
+      <text>
+        <t>Tax Rate (% of EBT)
+HOW: Excel equation: I35/I33 (FY25 tax ÷ simplified FY25 EBT in this template).
+WHY: Uses reported effective rate (~19% on template EBT; ~18.8% on 10-K EBT). UFCF in DCF also uses unlevered EBIT × t.
+SOURCE: SEC 10-K FY2025 — Provision for income taxes / Income before taxes</t>
+      </text>
+    </comment>
+    <comment ref="T13" authorId="0" shapeId="0">
+      <text>
+        <t>Tax Rate (% of EBT)
+HOW: Excel equation: I35/I33 (FY25 tax ÷ simplified FY25 EBT in this template).
+WHY: Uses reported effective rate (~19% on template EBT; ~18.8% on 10-K EBT). UFCF in DCF also uses unlevered EBIT × t.
+SOURCE: SEC 10-K FY2025 — Provision for income taxes / Income before taxes</t>
+      </text>
+    </comment>
+    <comment ref="U13" authorId="0" shapeId="0">
+      <text>
+        <t>Tax Rate (% of EBT)
+HOW: Excel equation: I35/I33 (FY25 tax ÷ simplified FY25 EBT in this template).
+WHY: Uses reported effective rate (~19% on template EBT; ~18.8% on 10-K EBT). UFCF in DCF also uses unlevered EBIT × t.
+SOURCE: SEC 10-K FY2025 — Provision for income taxes / Income before taxes</t>
+      </text>
+    </comment>
+    <comment ref="B15" authorId="0" shapeId="0">
+      <text>
+        <t>Accounts Receivable (Days)
+HOW: Excel equation: ROUND(I42/I24×365, 0). I42 is net AR (AR − deferred).
+WHY: Operating working-capital view: contract liabilities (deferred revenue) reduce net AR so ΔNWC is not overstated.
+SOURCE: SEC 10-K — AR; DeferredRevenueCurrent (XBRL)</t>
+      </text>
+    </comment>
+    <comment ref="J15" authorId="0" shapeId="0">
+      <text>
+        <t>Accounts Receivable (Days)
+HOW: Excel equation: ROUND(I42/I24×365, 0). I42 is net AR (AR − deferred).
+WHY: Operating working-capital view: contract liabilities (deferred revenue) reduce net AR so ΔNWC is not overstated.
+SOURCE: SEC 10-K — AR; DeferredRevenueCurrent (XBRL)</t>
+      </text>
+    </comment>
+    <comment ref="K15" authorId="0" shapeId="0">
+      <text>
+        <t>Accounts Receivable (Days)
+HOW: Excel equation: ROUND(I42/I24×365, 0). I42 is net AR (AR − deferred).
+WHY: Operating working-capital view: contract liabilities (deferred revenue) reduce net AR so ΔNWC is not overstated.
+SOURCE: SEC 10-K — AR; DeferredRevenueCurrent (XBRL)</t>
+      </text>
+    </comment>
+    <comment ref="L15" authorId="0" shapeId="0">
+      <text>
+        <t>Accounts Receivable (Days)
+HOW: Excel equation: ROUND(I42/I24×365, 0). I42 is net AR (AR − deferred).
+WHY: Operating working-capital view: contract liabilities (deferred revenue) reduce net AR so ΔNWC is not overstated.
+SOURCE: SEC 10-K — AR; DeferredRevenueCurrent (XBRL)</t>
+      </text>
+    </comment>
+    <comment ref="M15" authorId="0" shapeId="0">
+      <text>
+        <t>Accounts Receivable (Days)
+HOW: Excel equation: ROUND(I42/I24×365, 0). I42 is net AR (AR − deferred).
+WHY: Operating working-capital view: contract liabilities (deferred revenue) reduce net AR so ΔNWC is not overstated.
+SOURCE: SEC 10-K — AR; DeferredRevenueCurrent (XBRL)</t>
+      </text>
+    </comment>
+    <comment ref="N15" authorId="0" shapeId="0">
+      <text>
+        <t>Accounts Receivable (Days)
+HOW: Excel equation: ROUND(I42/I24×365, 0). I42 is net AR (AR − deferred).
+WHY: Operating working-capital view: contract liabilities (deferred revenue) reduce net AR so ΔNWC is not overstated.
+SOURCE: SEC 10-K — AR; DeferredRevenueCurrent (XBRL)</t>
+      </text>
+    </comment>
+    <comment ref="T15" authorId="0" shapeId="0">
+      <text>
+        <t>Accounts Receivable (Days)
+HOW: Excel equation: ROUND(I42/I24×365, 0). I42 is net AR (AR − deferred).
+WHY: Operating working-capital view: contract liabilities (deferred revenue) reduce net AR so ΔNWC is not overstated.
+SOURCE: SEC 10-K — AR; DeferredRevenueCurrent (XBRL)</t>
+      </text>
+    </comment>
+    <comment ref="U15" authorId="0" shapeId="0">
+      <text>
+        <t>Accounts Receivable (Days)
+HOW: Excel equation: ROUND(I42/I24×365, 0). I42 is net AR (AR − deferred).
+WHY: Operating working-capital view: contract liabilities (deferred revenue) reduce net AR so ΔNWC is not overstated.
+SOURCE: SEC 10-K — AR; DeferredRevenueCurrent (XBRL)</t>
+      </text>
+    </comment>
+    <comment ref="B16" authorId="0" shapeId="0">
+      <text>
+        <t>Inventory (Days)
+HOW: Hard zero — FICO is software / scores; inventory is immaterial.
+WHY: No inventory cycle to fund.
+SOURCE: SEC 10-K — Inventory ≈ $0</t>
+      </text>
+    </comment>
+    <comment ref="J16" authorId="0" shapeId="0">
+      <text>
+        <t>Inventory (Days)
+HOW: Hard zero — FICO is software / scores; inventory is immaterial.
+WHY: No inventory cycle to fund.
+SOURCE: SEC 10-K — Inventory ≈ $0</t>
+      </text>
+    </comment>
+    <comment ref="K16" authorId="0" shapeId="0">
+      <text>
+        <t>Inventory (Days)
+HOW: Hard zero — FICO is software / scores; inventory is immaterial.
+WHY: No inventory cycle to fund.
+SOURCE: SEC 10-K — Inventory ≈ $0</t>
+      </text>
+    </comment>
+    <comment ref="L16" authorId="0" shapeId="0">
+      <text>
+        <t>Inventory (Days)
+HOW: Hard zero — FICO is software / scores; inventory is immaterial.
+WHY: No inventory cycle to fund.
+SOURCE: SEC 10-K — Inventory ≈ $0</t>
+      </text>
+    </comment>
+    <comment ref="M16" authorId="0" shapeId="0">
+      <text>
+        <t>Inventory (Days)
+HOW: Hard zero — FICO is software / scores; inventory is immaterial.
+WHY: No inventory cycle to fund.
+SOURCE: SEC 10-K — Inventory ≈ $0</t>
+      </text>
+    </comment>
+    <comment ref="N16" authorId="0" shapeId="0">
+      <text>
+        <t>Inventory (Days)
+HOW: Hard zero — FICO is software / scores; inventory is immaterial.
+WHY: No inventory cycle to fund.
+SOURCE: SEC 10-K — Inventory ≈ $0</t>
+      </text>
+    </comment>
+    <comment ref="T16" authorId="0" shapeId="0">
+      <text>
+        <t>Inventory (Days)
+HOW: Hard zero — FICO is software / scores; inventory is immaterial.
+WHY: No inventory cycle to fund.
+SOURCE: SEC 10-K — Inventory ≈ $0</t>
+      </text>
+    </comment>
+    <comment ref="U16" authorId="0" shapeId="0">
+      <text>
+        <t>Inventory (Days)
+HOW: Hard zero — FICO is software / scores; inventory is immaterial.
+WHY: No inventory cycle to fund.
+SOURCE: SEC 10-K — Inventory ≈ $0</t>
+      </text>
+    </comment>
+    <comment ref="B17" authorId="0" shapeId="0">
+      <text>
+        <t>Accounts Payable (Days)
+HOW: Excel equation: ROUND(I48/I25×365, 0) from FY25.
+WHY: Payable timing offsets AR in operating NWC.
+SOURCE: SEC 10-K FY2025 — Accounts payable</t>
+      </text>
+    </comment>
+    <comment ref="J17" authorId="0" shapeId="0">
+      <text>
+        <t>Accounts Payable (Days)
+HOW: Excel equation: ROUND(I48/I25×365, 0) from FY25.
+WHY: Payable timing offsets AR in operating NWC.
+SOURCE: SEC 10-K FY2025 — Accounts payable</t>
+      </text>
+    </comment>
+    <comment ref="K17" authorId="0" shapeId="0">
+      <text>
+        <t>Accounts Payable (Days)
+HOW: Excel equation: ROUND(I48/I25×365, 0) from FY25.
+WHY: Payable timing offsets AR in operating NWC.
+SOURCE: SEC 10-K FY2025 — Accounts payable</t>
+      </text>
+    </comment>
+    <comment ref="L17" authorId="0" shapeId="0">
+      <text>
+        <t>Accounts Payable (Days)
+HOW: Excel equation: ROUND(I48/I25×365, 0) from FY25.
+WHY: Payable timing offsets AR in operating NWC.
+SOURCE: SEC 10-K FY2025 — Accounts payable</t>
+      </text>
+    </comment>
+    <comment ref="M17" authorId="0" shapeId="0">
+      <text>
+        <t>Accounts Payable (Days)
+HOW: Excel equation: ROUND(I48/I25×365, 0) from FY25.
+WHY: Payable timing offsets AR in operating NWC.
+SOURCE: SEC 10-K FY2025 — Accounts payable</t>
+      </text>
+    </comment>
+    <comment ref="N17" authorId="0" shapeId="0">
+      <text>
+        <t>Accounts Payable (Days)
+HOW: Excel equation: ROUND(I48/I25×365, 0) from FY25.
+WHY: Payable timing offsets AR in operating NWC.
+SOURCE: SEC 10-K FY2025 — Accounts payable</t>
+      </text>
+    </comment>
+    <comment ref="T17" authorId="0" shapeId="0">
+      <text>
+        <t>Accounts Payable (Days)
+HOW: Excel equation: ROUND(I48/I25×365, 0) from FY25.
+WHY: Payable timing offsets AR in operating NWC.
+SOURCE: SEC 10-K FY2025 — Accounts payable</t>
+      </text>
+    </comment>
+    <comment ref="U17" authorId="0" shapeId="0">
+      <text>
+        <t>Accounts Payable (Days)
+HOW: Excel equation: ROUND(I48/I25×365, 0) from FY25.
+WHY: Payable timing offsets AR in operating NWC.
+SOURCE: SEC 10-K FY2025 — Accounts payable</t>
+      </text>
+    </comment>
+    <comment ref="B18" authorId="0" shapeId="0">
+      <text>
+        <t>CapEx % of Revenue
+HOW: Equation: fade from I68/I24 (FY25 CapEx/Sales ~1.98%) toward 1.0% steady. Weights 85%→65%→45%→30%→0% on the peak.
+WHY: FY25 CapEx was elevated by capitalized internal-use software. Fading avoids locking a peak reinvestment rate forever.
+SOURCE: SEC 10-K — PP&amp;E purchases + capitalized software</t>
+      </text>
+    </comment>
+    <comment ref="J18" authorId="0" shapeId="0">
+      <text>
+        <t>CapEx % of Revenue
+HOW: Equation: fade from I68/I24 (FY25 CapEx/Sales ~1.98%) toward 1.0% steady. Weights 85%→65%→45%→30%→0% on the peak.
+WHY: FY25 CapEx was elevated by capitalized internal-use software. Fading avoids locking a peak reinvestment rate forever.
+SOURCE: SEC 10-K — PP&amp;E purchases + capitalized software</t>
+      </text>
+    </comment>
+    <comment ref="K18" authorId="0" shapeId="0">
+      <text>
+        <t>CapEx % of Revenue
+HOW: Equation: fade from I68/I24 (FY25 CapEx/Sales ~1.98%) toward 1.0% steady. Weights 85%→65%→45%→30%→0% on the peak.
+WHY: FY25 CapEx was elevated by capitalized internal-use software. Fading avoids locking a peak reinvestment rate forever.
+SOURCE: SEC 10-K — PP&amp;E purchases + capitalized software</t>
+      </text>
+    </comment>
+    <comment ref="L18" authorId="0" shapeId="0">
+      <text>
+        <t>CapEx % of Revenue
+HOW: Equation: fade from I68/I24 (FY25 CapEx/Sales ~1.98%) toward 1.0% steady. Weights 85%→65%→45%→30%→0% on the peak.
+WHY: FY25 CapEx was elevated by capitalized internal-use software. Fading avoids locking a peak reinvestment rate forever.
+SOURCE: SEC 10-K — PP&amp;E purchases + capitalized software</t>
+      </text>
+    </comment>
+    <comment ref="M18" authorId="0" shapeId="0">
+      <text>
+        <t>CapEx % of Revenue
+HOW: Equation: fade from I68/I24 (FY25 CapEx/Sales ~1.98%) toward 1.0% steady. Weights 85%→65%→45%→30%→0% on the peak.
+WHY: FY25 CapEx was elevated by capitalized internal-use software. Fading avoids locking a peak reinvestment rate forever.
+SOURCE: SEC 10-K — PP&amp;E purchases + capitalized software</t>
+      </text>
+    </comment>
+    <comment ref="N18" authorId="0" shapeId="0">
+      <text>
+        <t>CapEx % of Revenue
+HOW: Equation: fade from I68/I24 (FY25 CapEx/Sales ~1.98%) toward 1.0% steady. Weights 85%→65%→45%→30%→0% on the peak.
+WHY: FY25 CapEx was elevated by capitalized internal-use software. Fading avoids locking a peak reinvestment rate forever.
+SOURCE: SEC 10-K — PP&amp;E purchases + capitalized software</t>
+      </text>
+    </comment>
+    <comment ref="T18" authorId="0" shapeId="0">
+      <text>
+        <t>CapEx % of Revenue
+HOW: Equation: fade from I68/I24 (FY25 CapEx/Sales ~1.98%) toward 1.0% steady. Weights 85%→65%→45%→30%→0% on the peak.
+WHY: FY25 CapEx was elevated by capitalized internal-use software. Fading avoids locking a peak reinvestment rate forever.
+SOURCE: SEC 10-K — PP&amp;E purchases + capitalized software</t>
+      </text>
+    </comment>
+    <comment ref="U18" authorId="0" shapeId="0">
+      <text>
+        <t>CapEx % of Revenue
+HOW: Equation: fade from I68/I24 (FY25 CapEx/Sales ~1.98%) toward 1.0% steady. Weights 85%→65%→45%→30%→0% on the peak.
+WHY: FY25 CapEx was elevated by capitalized internal-use software. Fading avoids locking a peak reinvestment rate forever.
+SOURCE: SEC 10-K — PP&amp;E purchases + capitalized software</t>
+      </text>
+    </comment>
+    <comment ref="B19" authorId="0" shapeId="0">
+      <text>
+        <t>Debt Issuance (Repayment)
+HOW: POLICY input = 0 every year.
+WHY: Hold debt stock flat at FY25 level for the explicit period; interest follows. Net debt for DCF equity bridge uses the later 10-Q amount separately.
+SOURCE: Modeling choice (financing not in FCFF)</t>
+      </text>
+    </comment>
+    <comment ref="J19" authorId="0" shapeId="0">
+      <text>
+        <t>Debt Issuance (Repayment)
+HOW: POLICY input = 0 every year.
+WHY: Hold debt stock flat at FY25 level for the explicit period; interest follows. Net debt for DCF equity bridge uses the later 10-Q amount separately.
+SOURCE: Modeling choice (financing not in FCFF)</t>
+      </text>
+    </comment>
+    <comment ref="K19" authorId="0" shapeId="0">
+      <text>
+        <t>Debt Issuance (Repayment)
+HOW: POLICY input = 0 every year.
+WHY: Hold debt stock flat at FY25 level for the explicit period; interest follows. Net debt for DCF equity bridge uses the later 10-Q amount separately.
+SOURCE: Modeling choice (financing not in FCFF)</t>
+      </text>
+    </comment>
+    <comment ref="L19" authorId="0" shapeId="0">
+      <text>
+        <t>Debt Issuance (Repayment)
+HOW: POLICY input = 0 every year.
+WHY: Hold debt stock flat at FY25 level for the explicit period; interest follows. Net debt for DCF equity bridge uses the later 10-Q amount separately.
+SOURCE: Modeling choice (financing not in FCFF)</t>
+      </text>
+    </comment>
+    <comment ref="M19" authorId="0" shapeId="0">
+      <text>
+        <t>Debt Issuance (Repayment)
+HOW: POLICY input = 0 every year.
+WHY: Hold debt stock flat at FY25 level for the explicit period; interest follows. Net debt for DCF equity bridge uses the later 10-Q amount separately.
+SOURCE: Modeling choice (financing not in FCFF)</t>
+      </text>
+    </comment>
+    <comment ref="N19" authorId="0" shapeId="0">
+      <text>
+        <t>Debt Issuance (Repayment)
+HOW: POLICY input = 0 every year.
+WHY: Hold debt stock flat at FY25 level for the explicit period; interest follows. Net debt for DCF equity bridge uses the later 10-Q amount separately.
+SOURCE: Modeling choice (financing not in FCFF)</t>
+      </text>
+    </comment>
+    <comment ref="T19" authorId="0" shapeId="0">
+      <text>
+        <t>Debt Issuance (Repayment)
+HOW: POLICY input = 0 every year.
+WHY: Hold debt stock flat at FY25 level for the explicit period; interest follows. Net debt for DCF equity bridge uses the later 10-Q amount separately.
+SOURCE: Modeling choice (financing not in FCFF)</t>
+      </text>
+    </comment>
+    <comment ref="U19" authorId="0" shapeId="0">
+      <text>
+        <t>Debt Issuance (Repayment)
+HOW: POLICY input = 0 every year.
+WHY: Hold debt stock flat at FY25 level for the explicit period; interest follows. Net debt for DCF equity bridge uses the later 10-Q amount separately.
+SOURCE: Modeling choice (financing not in FCFF)</t>
+      </text>
+    </comment>
+    <comment ref="B20" authorId="0" shapeId="0">
+      <text>
+        <t>Equity Issued (Repaid)
+HOW: POLICY input = 0 every year.
+WHY: Buybacks are real historically but are financing — excluded from FCFF. Share count for $/share is the spot shares outstanding assumption.
+SOURCE: Modeling choice (financing not in FCFF)</t>
+      </text>
+    </comment>
+    <comment ref="J20" authorId="0" shapeId="0">
+      <text>
+        <t>Equity Issued (Repaid)
+HOW: POLICY input = 0 every year.
+WHY: Buybacks are real historically but are financing — excluded from FCFF. Share count for $/share is the spot shares outstanding assumption.
+SOURCE: Modeling choice (financing not in FCFF)</t>
+      </text>
+    </comment>
+    <comment ref="K20" authorId="0" shapeId="0">
+      <text>
+        <t>Equity Issued (Repaid)
+HOW: POLICY input = 0 every year.
+WHY: Buybacks are real historically but are financing — excluded from FCFF. Share count for $/share is the spot shares outstanding assumption.
+SOURCE: Modeling choice (financing not in FCFF)</t>
+      </text>
+    </comment>
+    <comment ref="L20" authorId="0" shapeId="0">
+      <text>
+        <t>Equity Issued (Repaid)
+HOW: POLICY input = 0 every year.
+WHY: Buybacks are real historically but are financing — excluded from FCFF. Share count for $/share is the spot shares outstanding assumption.
+SOURCE: Modeling choice (financing not in FCFF)</t>
+      </text>
+    </comment>
+    <comment ref="M20" authorId="0" shapeId="0">
+      <text>
+        <t>Equity Issued (Repaid)
+HOW: POLICY input = 0 every year.
+WHY: Buybacks are real historically but are financing — excluded from FCFF. Share count for $/share is the spot shares outstanding assumption.
+SOURCE: Modeling choice (financing not in FCFF)</t>
+      </text>
+    </comment>
+    <comment ref="N20" authorId="0" shapeId="0">
+      <text>
+        <t>Equity Issued (Repaid)
+HOW: POLICY input = 0 every year.
+WHY: Buybacks are real historically but are financing — excluded from FCFF. Share count for $/share is the spot shares outstanding assumption.
+SOURCE: Modeling choice (financing not in FCFF)</t>
+      </text>
+    </comment>
+    <comment ref="T20" authorId="0" shapeId="0">
+      <text>
+        <t>Equity Issued (Repaid)
+HOW: POLICY input = 0 every year.
+WHY: Buybacks are real historically but are financing — excluded from FCFF. Share count for $/share is the spot shares outstanding assumption.
+SOURCE: Modeling choice (financing not in FCFF)</t>
+      </text>
+    </comment>
+    <comment ref="U20" authorId="0" shapeId="0">
+      <text>
+        <t>Equity Issued (Repaid)
+HOW: POLICY input = 0 every year.
+WHY: Buybacks are real historically but are financing — excluded from FCFF. Share count for $/share is the spot shares outstanding assumption.
+SOURCE: Modeling choice (financing not in FCFF)</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor editAs="oneCell">
@@ -2838,12 +3684,12 @@
     <row r="4">
       <c r="B4" s="137" t="inlineStr">
         <is>
-          <t>vengeanceaiUSCMODEL4: GREEN cells = full equations (not hardcoded $, not bare =J36 pointers)</t>
+          <t>vengeanceaiUSCMODEL4: hover any yellow/green assumption cell (J–N) for WHY + SOURCE commentary; col C also shows WHY | SOURCE | HOW</t>
         </is>
       </c>
       <c r="P4" s="138" t="inlineStr">
         <is>
-          <t>ASSUMPTIONS EXPLAINED — every driver on this sheet</t>
+          <t>ASSUMPTIONS EXPLAINED — every driver (also in each cell comment)</t>
         </is>
       </c>
     </row>
@@ -2867,7 +3713,7 @@
       <c r="N5" s="65" t="n"/>
       <c r="P5" s="139" t="inlineStr">
         <is>
-          <t>Yellow = policy judgment. Green = Excel equations linked to FY25 (col I). Column C notes are text only (not formulas).</t>
+          <t>Yellow = policy judgment. Green = Excel equations linked to FY25 (col I). Hover J–N (or B label) for WHY + SOURCE. Column C is text only (not a formula).</t>
         </is>
       </c>
     </row>
@@ -2909,7 +3755,7 @@
         </is>
       </c>
     </row>
-    <row r="7" hidden="1" outlineLevel="1" ht="42" customHeight="1">
+    <row r="7" hidden="1" outlineLevel="1" ht="36" customHeight="1">
       <c r="B7" s="19" t="inlineStr">
         <is>
           <t>Revenue Growth (% Change)</t>
@@ -2917,7 +3763,7 @@
       </c>
       <c r="C7" s="141" t="inlineStr">
         <is>
-          <t>POLICY → drives Rev → GP → EBT → NI / CF</t>
+          <t>WHY: Y1 ≈ company FY2026 revenue guidance (~$2.53B / FY25 $1.991B − 1 ≈ 27%). Then fade toward terminal g=3% (not straight-lined). This is the main forward-lookin… | SOURCE: FICO FY2026 guidance + fade policy | HOW: Yellow POLICY input: 27% / 16% / 13% / 10% / 7%.</t>
         </is>
       </c>
       <c r="D7" s="46" t="n"/>
@@ -2982,7 +3828,7 @@
         </is>
       </c>
     </row>
-    <row r="8" hidden="1" outlineLevel="1" ht="42" customHeight="1">
+    <row r="8" hidden="1" outlineLevel="1" ht="36" customHeight="1">
       <c r="B8" s="19" t="inlineStr">
         <is>
           <t>Cost of Goods Sold (% of Revenue)</t>
@@ -2990,7 +3836,7 @@
       </c>
       <c r="C8" s="141" t="inlineStr">
         <is>
-          <t>eqn: FY25 COGS/Revenue (held flat)</t>
+          <t>WHY: Locks in latest reported cost structure (~17.8%). Scores mix is high-margin; holding FY25 is conservative vs further mix shift. | SOURCE: SEC 10-K FY2025 — Cost of revenues / Total revenues | HOW: Excel equation: I25/I24 (FY25 COGS ÷ FY25 Revenue) held flat.</t>
         </is>
       </c>
       <c r="D8" s="47" t="n"/>
@@ -3063,7 +3909,7 @@
         </is>
       </c>
     </row>
-    <row r="9" hidden="1" outlineLevel="1" ht="42" customHeight="1">
+    <row r="9" hidden="1" outlineLevel="1" ht="36" customHeight="1">
       <c r="B9" s="19" t="inlineStr">
         <is>
           <t>SGA % of Revenue (equation)</t>
@@ -3071,7 +3917,7 @@
       </c>
       <c r="C9" s="141" t="inlineStr">
         <is>
-          <t>eqn: (FY25 SGA − restructuring)/Rev − 50bps×t</t>
+          <t>WHY: Normalize one-time restructuring ($10.9M). Mild efficiency grind reflects operating leverage as revenue scales; floored at 5%. | SOURCE: SEC 10-K FY2025 — SG&amp;A + restructuring note | HOW: Equation: (I28 − 10,922)/I24 − 50bps × year. Strips FY25 restructuring; then −0.5% of sales each year.</t>
         </is>
       </c>
       <c r="D9" s="47" t="n"/>
@@ -3144,7 +3990,7 @@
         </is>
       </c>
     </row>
-    <row r="10" hidden="1" outlineLevel="1" ht="42" customHeight="1">
+    <row r="10" hidden="1" outlineLevel="1" ht="36" customHeight="1">
       <c r="B10" s="19" t="inlineStr">
         <is>
           <t>R&amp;D % of Revenue (equation)</t>
@@ -3152,7 +3998,7 @@
       </c>
       <c r="C10" s="141" t="inlineStr">
         <is>
-          <t>eqn: FY25 R&amp;D/Revenue (held flat)</t>
+          <t>WHY: FICO reinvests steadily in analytics/software. Flat % grows dollars with revenue. | SOURCE: SEC 10-K FY2025 — Research and development | HOW: Excel equation: I29/I24 held flat (~9.46%).</t>
         </is>
       </c>
       <c r="D10" s="47" t="n"/>
@@ -3225,7 +4071,7 @@
         </is>
       </c>
     </row>
-    <row r="11" hidden="1" outlineLevel="1" ht="42" customHeight="1">
+    <row r="11" hidden="1" outlineLevel="1" ht="36" customHeight="1">
       <c r="B11" s="19" t="inlineStr">
         <is>
           <t>Depreciation &amp; Amortization (% of PP&amp;E Open Bal)</t>
@@ -3233,7 +4079,7 @@
       </c>
       <c r="C11" s="141" t="inlineStr">
         <is>
-          <t>eqn: FY25 DA / FY25 PP&amp;E open</t>
+          <t>WHY: Ties DA to the asset base the schedule rolls forward (opens at I44). | SOURCE: SEC 10-K FY2025 — D&amp;A and PP&amp;E | HOW: Excel equation: I30/I44 (FY25 DA ÷ FY25 PPE). Forecast DA = OpenPPE × this %.</t>
         </is>
       </c>
       <c r="D11" s="47" t="n"/>
@@ -3306,7 +4152,7 @@
         </is>
       </c>
     </row>
-    <row r="12" hidden="1" outlineLevel="1" ht="42" customHeight="1">
+    <row r="12" hidden="1" outlineLevel="1" ht="36" customHeight="1">
       <c r="B12" s="19" t="inlineStr">
         <is>
           <t>Interest (% of Debt Open Bal)</t>
@@ -3314,7 +4160,7 @@
       </c>
       <c r="C12" s="141" t="inlineStr">
         <is>
-          <t>eqn: FY25 interest / debt open</t>
+          <t>WHY: Approximates average coupon / cost of debt on the book. Debt held flat (issuance = 0), so interest stays linked to that stock. | SOURCE: SEC 10-K FY2025 — Interest expense, net + debt footnote | HOW: Excel equation: I101/I98 (FY25 interest ÷ FY25 opening debt in schedule).</t>
         </is>
       </c>
       <c r="D12" s="47" t="n"/>
@@ -3387,7 +4233,7 @@
         </is>
       </c>
     </row>
-    <row r="13" hidden="1" outlineLevel="1" ht="42" customHeight="1">
+    <row r="13" hidden="1" outlineLevel="1" ht="36" customHeight="1">
       <c r="B13" s="19" t="inlineStr">
         <is>
           <t>Tax Rate (% of Earnings Before Tax)</t>
@@ -3395,7 +4241,7 @@
       </c>
       <c r="C13" s="141" t="inlineStr">
         <is>
-          <t>eqn: FY25 tax / FY25 EBT</t>
+          <t>WHY: Uses reported effective rate (~19% on template EBT; ~18.8% on 10-K EBT). UFCF in DCF also uses unlevered EBIT × t. | SOURCE: SEC 10-K FY2025 — Provision for income taxes / Income before taxes | HOW: Excel equation: I35/I33 (FY25 tax ÷ simplified FY25 EBT in this template).</t>
         </is>
       </c>
       <c r="D13" s="25" t="n"/>
@@ -3487,7 +4333,7 @@
       <c r="M14" s="19" t="n"/>
       <c r="N14" s="19" t="n"/>
     </row>
-    <row r="15" hidden="1" outlineLevel="1" ht="42" customHeight="1">
+    <row r="15" hidden="1" outlineLevel="1" ht="36" customHeight="1">
       <c r="B15" s="19" t="inlineStr">
         <is>
           <t>Accounts Receivable (Days)</t>
@@ -3495,7 +4341,7 @@
       </c>
       <c r="C15" s="148" t="inlineStr">
         <is>
-          <t>eqn: ROUND(net AR/Rev×365)</t>
+          <t>WHY: Operating working-capital view: contract liabilities (deferred revenue) reduce net AR so ΔNWC is not overstated. | SOURCE: SEC 10-K — AR; DeferredRevenueCurrent (XBRL) | HOW: Excel equation: ROUND(I42/I24×365, 0). I42 is net AR (AR − deferred).</t>
         </is>
       </c>
       <c r="D15" s="32" t="n"/>
@@ -3568,7 +4414,7 @@
         </is>
       </c>
     </row>
-    <row r="16" hidden="1" outlineLevel="1" ht="42" customHeight="1">
+    <row r="16" hidden="1" outlineLevel="1" ht="36" customHeight="1">
       <c r="B16" s="19" t="inlineStr">
         <is>
           <t>Inventory (Days)</t>
@@ -3576,7 +4422,7 @@
       </c>
       <c r="C16" s="148" t="inlineStr">
         <is>
-          <t>POLICY: software business — no inventory</t>
+          <t>WHY: No inventory cycle to fund. | SOURCE: SEC 10-K — Inventory ≈ $0 | HOW: Hard zero — FICO is software / scores; inventory is immaterial.</t>
         </is>
       </c>
       <c r="D16" s="32" t="n"/>
@@ -3644,7 +4490,7 @@
         </is>
       </c>
     </row>
-    <row r="17" hidden="1" outlineLevel="1" ht="42" customHeight="1">
+    <row r="17" hidden="1" outlineLevel="1" ht="36" customHeight="1">
       <c r="B17" s="19" t="inlineStr">
         <is>
           <t>Accounts Payable (Days)</t>
@@ -3652,7 +4498,7 @@
       </c>
       <c r="C17" s="148" t="inlineStr">
         <is>
-          <t>eqn: ROUND(AP/COGS×365)</t>
+          <t>WHY: Payable timing offsets AR in operating NWC. | SOURCE: SEC 10-K FY2025 — Accounts payable | HOW: Excel equation: ROUND(I48/I25×365, 0) from FY25.</t>
         </is>
       </c>
       <c r="D17" s="32" t="n"/>
@@ -3725,7 +4571,7 @@
         </is>
       </c>
     </row>
-    <row r="18" hidden="1" outlineLevel="1" ht="42" customHeight="1">
+    <row r="18" hidden="1" outlineLevel="1" ht="36" customHeight="1">
       <c r="B18" s="19" t="inlineStr">
         <is>
           <t>CapEx % of Revenue (fade equation)</t>
@@ -3733,7 +4579,7 @@
       </c>
       <c r="C18" s="148" t="inlineStr">
         <is>
-          <t>eqn: fade FY25 CapEx/Sales → 1%</t>
+          <t>WHY: FY25 CapEx was elevated by capitalized internal-use software. Fading avoids locking a peak reinvestment rate forever. | SOURCE: SEC 10-K — PP&amp;E purchases + capitalized software | HOW: Equation: fade from I68/I24 (FY25 CapEx/Sales ~1.98%) toward 1.0% steady. Weights 85%→65%→45%→30%→0% on the peak.</t>
         </is>
       </c>
       <c r="E18" s="146">
@@ -3805,7 +4651,7 @@
         </is>
       </c>
     </row>
-    <row r="19" hidden="1" outlineLevel="1" ht="42" customHeight="1">
+    <row r="19" hidden="1" outlineLevel="1" ht="36" customHeight="1">
       <c r="B19" s="19" t="inlineStr">
         <is>
           <t>Debt Issuance (Repayment) ($000's)</t>
@@ -3813,7 +4659,7 @@
       </c>
       <c r="C19" s="148" t="inlineStr">
         <is>
-          <t>POLICY: no new debt issuance</t>
+          <t>WHY: Hold debt stock flat at FY25 level for the explicit period; interest follows. Net debt for DCF equity bridge uses the later 10-Q amount separately. | SOURCE: Modeling choice (financing not in FCFF) | HOW: POLICY input = 0 every year.</t>
         </is>
       </c>
       <c r="E19" s="146">
@@ -3880,7 +4726,7 @@
         </is>
       </c>
     </row>
-    <row r="20" hidden="1" outlineLevel="1" ht="42" customHeight="1">
+    <row r="20" hidden="1" outlineLevel="1" ht="36" customHeight="1">
       <c r="B20" s="19" t="inlineStr">
         <is>
           <t>Equity Issued (Repaid) ($000's)</t>
@@ -3888,7 +4734,7 @@
       </c>
       <c r="C20" s="148" t="inlineStr">
         <is>
-          <t>POLICY: no equity issuance</t>
+          <t>WHY: Buybacks are real historically but are financing — excluded from FCFF. Share count for $/share is the spot shares outstanding assumption. | SOURCE: Modeling choice (financing not in FCFF) | HOW: POLICY input = 0 every year.</t>
         </is>
       </c>
       <c r="E20" s="146">
@@ -7002,6 +7848,7 @@
     <brk id="81" min="0" max="13" man="1"/>
   </rowBreaks>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 

--- a/FICO/output/FICO_Completed_Model.xlsx
+++ b/FICO/output/FICO_Completed_Model.xlsx
@@ -1751,6 +1751,90 @@
     <author>vengeanceaiUSCMODEL4</author>
   </authors>
   <commentList>
+    <comment ref="B2" authorId="0" shapeId="0">
+      <text>
+        <t>Forecast year label
+WHY: Adds one year to the prior column’s fiscal-year label so forecast headers stay sequential.
+PATTERN: ={p}2+1</t>
+      </text>
+    </comment>
+    <comment ref="J2" authorId="0" shapeId="0">
+      <text>
+        <t>Forecast year label
+FORMULA: =I2+1
+WHY: Adds one year to the prior column’s fiscal-year label so forecast headers stay sequential.</t>
+      </text>
+    </comment>
+    <comment ref="K2" authorId="0" shapeId="0">
+      <text>
+        <t>Forecast year label
+FORMULA: =J2+1
+WHY: Adds one year to the prior column’s fiscal-year label so forecast headers stay sequential.</t>
+      </text>
+    </comment>
+    <comment ref="L2" authorId="0" shapeId="0">
+      <text>
+        <t>Forecast year label
+FORMULA: =K2+1
+WHY: Adds one year to the prior column’s fiscal-year label so forecast headers stay sequential.</t>
+      </text>
+    </comment>
+    <comment ref="M2" authorId="0" shapeId="0">
+      <text>
+        <t>Forecast year label
+FORMULA: =L2+1
+WHY: Adds one year to the prior column’s fiscal-year label so forecast headers stay sequential.</t>
+      </text>
+    </comment>
+    <comment ref="N2" authorId="0" shapeId="0">
+      <text>
+        <t>Forecast year label
+FORMULA: =M2+1
+WHY: Adds one year to the prior column’s fiscal-year label so forecast headers stay sequential.</t>
+      </text>
+    </comment>
+    <comment ref="B3" authorId="0" shapeId="0">
+      <text>
+        <t>Balance sheet check
+WHY: Flags ERROR if Assets ≠ L+E by more than $1k; otherwise OK. Protects the plug.
+PATTERN: =IFERROR(IF(ABS({c}57)&gt;1,"ERROR","OK"),"OK")</t>
+      </text>
+    </comment>
+    <comment ref="J3" authorId="0" shapeId="0">
+      <text>
+        <t>Balance sheet check
+FORMULA: =IFERROR(IF(ABS(J57)&gt;1,"ERROR","OK"),"OK")
+WHY: Flags ERROR if Assets ≠ L+E by more than $1k; otherwise OK. Protects the plug.</t>
+      </text>
+    </comment>
+    <comment ref="K3" authorId="0" shapeId="0">
+      <text>
+        <t>Balance sheet check
+FORMULA: =IFERROR(IF(ABS(K57)&gt;1,"ERROR","OK"),"OK")
+WHY: Flags ERROR if Assets ≠ L+E by more than $1k; otherwise OK. Protects the plug.</t>
+      </text>
+    </comment>
+    <comment ref="L3" authorId="0" shapeId="0">
+      <text>
+        <t>Balance sheet check
+FORMULA: =IFERROR(IF(ABS(L57)&gt;1,"ERROR","OK"),"OK")
+WHY: Flags ERROR if Assets ≠ L+E by more than $1k; otherwise OK. Protects the plug.</t>
+      </text>
+    </comment>
+    <comment ref="M3" authorId="0" shapeId="0">
+      <text>
+        <t>Balance sheet check
+FORMULA: =IFERROR(IF(ABS(M57)&gt;1,"ERROR","OK"),"OK")
+WHY: Flags ERROR if Assets ≠ L+E by more than $1k; otherwise OK. Protects the plug.</t>
+      </text>
+    </comment>
+    <comment ref="N3" authorId="0" shapeId="0">
+      <text>
+        <t>Balance sheet check
+FORMULA: =IFERROR(IF(ABS(N57)&gt;1,"ERROR","OK"),"OK")
+WHY: Flags ERROR if Assets ≠ L+E by more than $1k; otherwise OK. Protects the plug.</t>
+      </text>
+    </comment>
     <comment ref="B7" authorId="0" shapeId="0">
       <text>
         <t>Revenue Growth
@@ -2581,6 +2665,2403 @@
 HOW: POLICY input = 0 every year.
 WHY: Buybacks are real historically but are financing — excluded from FCFF. Share count for $/share is the spot shares outstanding assumption.
 SOURCE: Modeling choice (financing not in FCFF)</t>
+      </text>
+    </comment>
+    <comment ref="B24" authorId="0" shapeId="0">
+      <text>
+        <t>Revenue
+WHY: Prior-year revenue grown by this year’s policy growth rate; top-line driver of the model.
+PATTERN: ={p}24*(1+{c}7)</t>
+      </text>
+    </comment>
+    <comment ref="J24" authorId="0" shapeId="0">
+      <text>
+        <t>Revenue
+FORMULA: =I24*(1+J7)
+WHY: Prior-year revenue grown by this year’s policy growth rate; top-line driver of the model.</t>
+      </text>
+    </comment>
+    <comment ref="K24" authorId="0" shapeId="0">
+      <text>
+        <t>Revenue
+FORMULA: =J24*(1+K7)
+WHY: Prior-year revenue grown by this year’s policy growth rate; top-line driver of the model.</t>
+      </text>
+    </comment>
+    <comment ref="L24" authorId="0" shapeId="0">
+      <text>
+        <t>Revenue
+FORMULA: =K24*(1+L7)
+WHY: Prior-year revenue grown by this year’s policy growth rate; top-line driver of the model.</t>
+      </text>
+    </comment>
+    <comment ref="M24" authorId="0" shapeId="0">
+      <text>
+        <t>Revenue
+FORMULA: =L24*(1+M7)
+WHY: Prior-year revenue grown by this year’s policy growth rate; top-line driver of the model.</t>
+      </text>
+    </comment>
+    <comment ref="N24" authorId="0" shapeId="0">
+      <text>
+        <t>Revenue
+FORMULA: =M24*(1+N7)
+WHY: Prior-year revenue grown by this year’s policy growth rate; top-line driver of the model.</t>
+      </text>
+    </comment>
+    <comment ref="B25" authorId="0" shapeId="0">
+      <text>
+        <t>COGS $
+WHY: Revenue times COGS%; converts the held margin assumption into dollar cost of sales.
+PATTERN: ={c}24*{c}8</t>
+      </text>
+    </comment>
+    <comment ref="J25" authorId="0" shapeId="0">
+      <text>
+        <t>COGS $
+FORMULA: =J24*J8
+WHY: Revenue times COGS%; converts the held margin assumption into dollar cost of sales.</t>
+      </text>
+    </comment>
+    <comment ref="K25" authorId="0" shapeId="0">
+      <text>
+        <t>COGS $
+FORMULA: =K24*K8
+WHY: Revenue times COGS%; converts the held margin assumption into dollar cost of sales.</t>
+      </text>
+    </comment>
+    <comment ref="L25" authorId="0" shapeId="0">
+      <text>
+        <t>COGS $
+FORMULA: =L24*L8
+WHY: Revenue times COGS%; converts the held margin assumption into dollar cost of sales.</t>
+      </text>
+    </comment>
+    <comment ref="M25" authorId="0" shapeId="0">
+      <text>
+        <t>COGS $
+FORMULA: =M24*M8
+WHY: Revenue times COGS%; converts the held margin assumption into dollar cost of sales.</t>
+      </text>
+    </comment>
+    <comment ref="N25" authorId="0" shapeId="0">
+      <text>
+        <t>COGS $
+FORMULA: =N24*N8
+WHY: Revenue times COGS%; converts the held margin assumption into dollar cost of sales.</t>
+      </text>
+    </comment>
+    <comment ref="B26" authorId="0" shapeId="0">
+      <text>
+        <t>Gross profit
+WHY: Revenue minus COGS; contribution after direct cost of revenues before operating expenses.
+PATTERN: ={c}24-{c}25</t>
+      </text>
+    </comment>
+    <comment ref="J26" authorId="0" shapeId="0">
+      <text>
+        <t>Gross profit
+FORMULA: =J24-J25
+WHY: Revenue minus COGS; contribution after direct cost of revenues before operating expenses.</t>
+      </text>
+    </comment>
+    <comment ref="K26" authorId="0" shapeId="0">
+      <text>
+        <t>Gross profit
+FORMULA: =K24-K25
+WHY: Revenue minus COGS; contribution after direct cost of revenues before operating expenses.</t>
+      </text>
+    </comment>
+    <comment ref="L26" authorId="0" shapeId="0">
+      <text>
+        <t>Gross profit
+FORMULA: =L24-L25
+WHY: Revenue minus COGS; contribution after direct cost of revenues before operating expenses.</t>
+      </text>
+    </comment>
+    <comment ref="M26" authorId="0" shapeId="0">
+      <text>
+        <t>Gross profit
+FORMULA: =M24-M25
+WHY: Revenue minus COGS; contribution after direct cost of revenues before operating expenses.</t>
+      </text>
+    </comment>
+    <comment ref="N26" authorId="0" shapeId="0">
+      <text>
+        <t>Gross profit
+FORMULA: =N24-N25
+WHY: Revenue minus COGS; contribution after direct cost of revenues before operating expenses.</t>
+      </text>
+    </comment>
+    <comment ref="B28" authorId="0" shapeId="0">
+      <text>
+        <t>SGA $
+WHY: Revenue times SGA%; salaries/benefits dollars after the efficiency grind on the rate.
+PATTERN: ={c}24*{c}9</t>
+      </text>
+    </comment>
+    <comment ref="J28" authorId="0" shapeId="0">
+      <text>
+        <t>SGA $
+FORMULA: =J24*J9
+WHY: Revenue times SGA%; salaries/benefits dollars after the efficiency grind on the rate.</t>
+      </text>
+    </comment>
+    <comment ref="K28" authorId="0" shapeId="0">
+      <text>
+        <t>SGA $
+FORMULA: =K24*K9
+WHY: Revenue times SGA%; salaries/benefits dollars after the efficiency grind on the rate.</t>
+      </text>
+    </comment>
+    <comment ref="L28" authorId="0" shapeId="0">
+      <text>
+        <t>SGA $
+FORMULA: =L24*L9
+WHY: Revenue times SGA%; salaries/benefits dollars after the efficiency grind on the rate.</t>
+      </text>
+    </comment>
+    <comment ref="M28" authorId="0" shapeId="0">
+      <text>
+        <t>SGA $
+FORMULA: =M24*M9
+WHY: Revenue times SGA%; salaries/benefits dollars after the efficiency grind on the rate.</t>
+      </text>
+    </comment>
+    <comment ref="N28" authorId="0" shapeId="0">
+      <text>
+        <t>SGA $
+FORMULA: =N24*N9
+WHY: Revenue times SGA%; salaries/benefits dollars after the efficiency grind on the rate.</t>
+      </text>
+    </comment>
+    <comment ref="B29" authorId="0" shapeId="0">
+      <text>
+        <t>R&amp;D $
+WHY: Revenue times R&amp;D%; research spend scales with sales at the FY25 reinvestment rate.
+PATTERN: ={c}24*{c}10</t>
+      </text>
+    </comment>
+    <comment ref="J29" authorId="0" shapeId="0">
+      <text>
+        <t>R&amp;D $
+FORMULA: =J24*J10
+WHY: Revenue times R&amp;D%; research spend scales with sales at the FY25 reinvestment rate.</t>
+      </text>
+    </comment>
+    <comment ref="K29" authorId="0" shapeId="0">
+      <text>
+        <t>R&amp;D $
+FORMULA: =K24*K10
+WHY: Revenue times R&amp;D%; research spend scales with sales at the FY25 reinvestment rate.</t>
+      </text>
+    </comment>
+    <comment ref="L29" authorId="0" shapeId="0">
+      <text>
+        <t>R&amp;D $
+FORMULA: =L24*L10
+WHY: Revenue times R&amp;D%; research spend scales with sales at the FY25 reinvestment rate.</t>
+      </text>
+    </comment>
+    <comment ref="M29" authorId="0" shapeId="0">
+      <text>
+        <t>R&amp;D $
+FORMULA: =M24*M10
+WHY: Revenue times R&amp;D%; research spend scales with sales at the FY25 reinvestment rate.</t>
+      </text>
+    </comment>
+    <comment ref="N29" authorId="0" shapeId="0">
+      <text>
+        <t>R&amp;D $
+FORMULA: =N24*N10
+WHY: Revenue times R&amp;D%; research spend scales with sales at the FY25 reinvestment rate.</t>
+      </text>
+    </comment>
+    <comment ref="B30" authorId="0" shapeId="0">
+      <text>
+        <t>D&amp;A $
+WHY: Opening PP&amp;E times D&amp;A%; depreciation follows the asset roll-forward, not a revenue %.
+PATTERN: ={c}92*{c}11</t>
+      </text>
+    </comment>
+    <comment ref="J30" authorId="0" shapeId="0">
+      <text>
+        <t>D&amp;A $
+FORMULA: =J92*J11
+WHY: Opening PP&amp;E times D&amp;A%; depreciation follows the asset roll-forward, not a revenue %.</t>
+      </text>
+    </comment>
+    <comment ref="K30" authorId="0" shapeId="0">
+      <text>
+        <t>D&amp;A $
+FORMULA: =K92*K11
+WHY: Opening PP&amp;E times D&amp;A%; depreciation follows the asset roll-forward, not a revenue %.</t>
+      </text>
+    </comment>
+    <comment ref="L30" authorId="0" shapeId="0">
+      <text>
+        <t>D&amp;A $
+FORMULA: =L92*L11
+WHY: Opening PP&amp;E times D&amp;A%; depreciation follows the asset roll-forward, not a revenue %.</t>
+      </text>
+    </comment>
+    <comment ref="M30" authorId="0" shapeId="0">
+      <text>
+        <t>D&amp;A $
+FORMULA: =M92*M11
+WHY: Opening PP&amp;E times D&amp;A%; depreciation follows the asset roll-forward, not a revenue %.</t>
+      </text>
+    </comment>
+    <comment ref="N30" authorId="0" shapeId="0">
+      <text>
+        <t>D&amp;A $
+FORMULA: =N92*N11
+WHY: Opening PP&amp;E times D&amp;A%; depreciation follows the asset roll-forward, not a revenue %.</t>
+      </text>
+    </comment>
+    <comment ref="B31" authorId="0" shapeId="0">
+      <text>
+        <t>Interest $
+WHY: Opening debt times interest%; coupon on the debt stock while issuance policy is zero.
+PATTERN: ={c}98*{c}12</t>
+      </text>
+    </comment>
+    <comment ref="J31" authorId="0" shapeId="0">
+      <text>
+        <t>Interest $
+FORMULA: =J98*J12
+WHY: Opening debt times interest%; coupon on the debt stock while issuance policy is zero.</t>
+      </text>
+    </comment>
+    <comment ref="K31" authorId="0" shapeId="0">
+      <text>
+        <t>Interest $
+FORMULA: =K98*K12
+WHY: Opening debt times interest%; coupon on the debt stock while issuance policy is zero.</t>
+      </text>
+    </comment>
+    <comment ref="L31" authorId="0" shapeId="0">
+      <text>
+        <t>Interest $
+FORMULA: =L98*L12
+WHY: Opening debt times interest%; coupon on the debt stock while issuance policy is zero.</t>
+      </text>
+    </comment>
+    <comment ref="M31" authorId="0" shapeId="0">
+      <text>
+        <t>Interest $
+FORMULA: =M98*M12
+WHY: Opening debt times interest%; coupon on the debt stock while issuance policy is zero.</t>
+      </text>
+    </comment>
+    <comment ref="N31" authorId="0" shapeId="0">
+      <text>
+        <t>Interest $
+FORMULA: =N98*N12
+WHY: Opening debt times interest%; coupon on the debt stock while issuance policy is zero.</t>
+      </text>
+    </comment>
+    <comment ref="B32" authorId="0" shapeId="0">
+      <text>
+        <t>Total expenses
+WHY: Sum of SGA, R&amp;D, D&amp;A, and interest; all operating and financing costs above EBT.
+PATTERN: =SUM({c}28:{c}31)</t>
+      </text>
+    </comment>
+    <comment ref="J32" authorId="0" shapeId="0">
+      <text>
+        <t>Total expenses
+FORMULA: =SUM(J28:J31)
+WHY: Sum of SGA, R&amp;D, D&amp;A, and interest; all operating and financing costs above EBT.</t>
+      </text>
+    </comment>
+    <comment ref="K32" authorId="0" shapeId="0">
+      <text>
+        <t>Total expenses
+FORMULA: =SUM(K28:K31)
+WHY: Sum of SGA, R&amp;D, D&amp;A, and interest; all operating and financing costs above EBT.</t>
+      </text>
+    </comment>
+    <comment ref="L32" authorId="0" shapeId="0">
+      <text>
+        <t>Total expenses
+FORMULA: =SUM(L28:L31)
+WHY: Sum of SGA, R&amp;D, D&amp;A, and interest; all operating and financing costs above EBT.</t>
+      </text>
+    </comment>
+    <comment ref="M32" authorId="0" shapeId="0">
+      <text>
+        <t>Total expenses
+FORMULA: =SUM(M28:M31)
+WHY: Sum of SGA, R&amp;D, D&amp;A, and interest; all operating and financing costs above EBT.</t>
+      </text>
+    </comment>
+    <comment ref="N32" authorId="0" shapeId="0">
+      <text>
+        <t>Total expenses
+FORMULA: =SUM(N28:N31)
+WHY: Sum of SGA, R&amp;D, D&amp;A, and interest; all operating and financing costs above EBT.</t>
+      </text>
+    </comment>
+    <comment ref="B33" authorId="0" shapeId="0">
+      <text>
+        <t>EBT
+WHY: Gross profit minus total expenses; earnings before tax in this simplified template.
+PATTERN: ={c}26-{c}32</t>
+      </text>
+    </comment>
+    <comment ref="J33" authorId="0" shapeId="0">
+      <text>
+        <t>EBT
+FORMULA: =J26-J32
+WHY: Gross profit minus total expenses; earnings before tax in this simplified template.</t>
+      </text>
+    </comment>
+    <comment ref="K33" authorId="0" shapeId="0">
+      <text>
+        <t>EBT
+FORMULA: =K26-K32
+WHY: Gross profit minus total expenses; earnings before tax in this simplified template.</t>
+      </text>
+    </comment>
+    <comment ref="L33" authorId="0" shapeId="0">
+      <text>
+        <t>EBT
+FORMULA: =L26-L32
+WHY: Gross profit minus total expenses; earnings before tax in this simplified template.</t>
+      </text>
+    </comment>
+    <comment ref="M33" authorId="0" shapeId="0">
+      <text>
+        <t>EBT
+FORMULA: =M26-M32
+WHY: Gross profit minus total expenses; earnings before tax in this simplified template.</t>
+      </text>
+    </comment>
+    <comment ref="N33" authorId="0" shapeId="0">
+      <text>
+        <t>EBT
+FORMULA: =N26-N32
+WHY: Gross profit minus total expenses; earnings before tax in this simplified template.</t>
+      </text>
+    </comment>
+    <comment ref="B35" authorId="0" shapeId="0">
+      <text>
+        <t>Taxes $
+WHY: EBT times effective tax rate; book tax expense for the income statement.
+PATTERN: ={c}33*{c}13</t>
+      </text>
+    </comment>
+    <comment ref="J35" authorId="0" shapeId="0">
+      <text>
+        <t>Taxes $
+FORMULA: =J33*J13
+WHY: EBT times effective tax rate; book tax expense for the income statement.</t>
+      </text>
+    </comment>
+    <comment ref="K35" authorId="0" shapeId="0">
+      <text>
+        <t>Taxes $
+FORMULA: =K33*K13
+WHY: EBT times effective tax rate; book tax expense for the income statement.</t>
+      </text>
+    </comment>
+    <comment ref="L35" authorId="0" shapeId="0">
+      <text>
+        <t>Taxes $
+FORMULA: =L33*L13
+WHY: EBT times effective tax rate; book tax expense for the income statement.</t>
+      </text>
+    </comment>
+    <comment ref="M35" authorId="0" shapeId="0">
+      <text>
+        <t>Taxes $
+FORMULA: =M33*M13
+WHY: EBT times effective tax rate; book tax expense for the income statement.</t>
+      </text>
+    </comment>
+    <comment ref="N35" authorId="0" shapeId="0">
+      <text>
+        <t>Taxes $
+FORMULA: =N33*N13
+WHY: EBT times effective tax rate; book tax expense for the income statement.</t>
+      </text>
+    </comment>
+    <comment ref="B36" authorId="0" shapeId="0">
+      <text>
+        <t>Net earnings
+WHY: EBT kept after tax; full equation, not a pointer, so NI tracks the tax rate driver.
+PATTERN: ={c}33*(1-{c}13)</t>
+      </text>
+    </comment>
+    <comment ref="J36" authorId="0" shapeId="0">
+      <text>
+        <t>Net earnings
+FORMULA: =J33*(1-J13)
+WHY: EBT kept after tax; full equation, not a pointer, so NI tracks the tax rate driver.</t>
+      </text>
+    </comment>
+    <comment ref="K36" authorId="0" shapeId="0">
+      <text>
+        <t>Net earnings
+FORMULA: =K33*(1-K13)
+WHY: EBT kept after tax; full equation, not a pointer, so NI tracks the tax rate driver.</t>
+      </text>
+    </comment>
+    <comment ref="L36" authorId="0" shapeId="0">
+      <text>
+        <t>Net earnings
+FORMULA: =L33*(1-L13)
+WHY: EBT kept after tax; full equation, not a pointer, so NI tracks the tax rate driver.</t>
+      </text>
+    </comment>
+    <comment ref="M36" authorId="0" shapeId="0">
+      <text>
+        <t>Net earnings
+FORMULA: =M33*(1-M13)
+WHY: EBT kept after tax; full equation, not a pointer, so NI tracks the tax rate driver.</t>
+      </text>
+    </comment>
+    <comment ref="N36" authorId="0" shapeId="0">
+      <text>
+        <t>Net earnings
+FORMULA: =N33*(1-N13)
+WHY: EBT kept after tax; full equation, not a pointer, so NI tracks the tax rate driver.</t>
+      </text>
+    </comment>
+    <comment ref="B41" authorId="0" shapeId="0">
+      <text>
+        <t>Cash (BS)
+WHY: Balance-sheet cash equals cash-flow closing cash so the three statements stay linked.
+PATTERN: ={c}78</t>
+      </text>
+    </comment>
+    <comment ref="J41" authorId="0" shapeId="0">
+      <text>
+        <t>Cash (BS)
+FORMULA: =J78
+WHY: Balance-sheet cash equals cash-flow closing cash so the three statements stay linked.</t>
+      </text>
+    </comment>
+    <comment ref="K41" authorId="0" shapeId="0">
+      <text>
+        <t>Cash (BS)
+FORMULA: =K78
+WHY: Balance-sheet cash equals cash-flow closing cash so the three statements stay linked.</t>
+      </text>
+    </comment>
+    <comment ref="L41" authorId="0" shapeId="0">
+      <text>
+        <t>Cash (BS)
+FORMULA: =L78
+WHY: Balance-sheet cash equals cash-flow closing cash so the three statements stay linked.</t>
+      </text>
+    </comment>
+    <comment ref="M41" authorId="0" shapeId="0">
+      <text>
+        <t>Cash (BS)
+FORMULA: =M78
+WHY: Balance-sheet cash equals cash-flow closing cash so the three statements stay linked.</t>
+      </text>
+    </comment>
+    <comment ref="N41" authorId="0" shapeId="0">
+      <text>
+        <t>Cash (BS)
+FORMULA: =N78
+WHY: Balance-sheet cash equals cash-flow closing cash so the three statements stay linked.</t>
+      </text>
+    </comment>
+    <comment ref="B42" authorId="0" shapeId="0">
+      <text>
+        <t>AR $
+WHY: Revenue × AR days / 365; receivables from the days-sales-outstanding assumption.
+PATTERN: ={c}24*{c}15/365</t>
+      </text>
+    </comment>
+    <comment ref="J42" authorId="0" shapeId="0">
+      <text>
+        <t>AR $
+FORMULA: =J24*J15/365
+WHY: Revenue × AR days / 365; receivables from the days-sales-outstanding assumption.</t>
+      </text>
+    </comment>
+    <comment ref="K42" authorId="0" shapeId="0">
+      <text>
+        <t>AR $
+FORMULA: =K24*K15/365
+WHY: Revenue × AR days / 365; receivables from the days-sales-outstanding assumption.</t>
+      </text>
+    </comment>
+    <comment ref="L42" authorId="0" shapeId="0">
+      <text>
+        <t>AR $
+FORMULA: =L24*L15/365
+WHY: Revenue × AR days / 365; receivables from the days-sales-outstanding assumption.</t>
+      </text>
+    </comment>
+    <comment ref="M42" authorId="0" shapeId="0">
+      <text>
+        <t>AR $
+FORMULA: =M24*M15/365
+WHY: Revenue × AR days / 365; receivables from the days-sales-outstanding assumption.</t>
+      </text>
+    </comment>
+    <comment ref="N42" authorId="0" shapeId="0">
+      <text>
+        <t>AR $
+FORMULA: =N24*N15/365
+WHY: Revenue × AR days / 365; receivables from the days-sales-outstanding assumption.</t>
+      </text>
+    </comment>
+    <comment ref="B43" authorId="0" shapeId="0">
+      <text>
+        <t>Inventory $
+WHY: COGS × inventory days / 365; stays zero because inventory days are policy zero.
+PATTERN: ={c}25*{c}16/365</t>
+      </text>
+    </comment>
+    <comment ref="J43" authorId="0" shapeId="0">
+      <text>
+        <t>Inventory $
+FORMULA: =J25*J16/365
+WHY: COGS × inventory days / 365; stays zero because inventory days are policy zero.</t>
+      </text>
+    </comment>
+    <comment ref="K43" authorId="0" shapeId="0">
+      <text>
+        <t>Inventory $
+FORMULA: =K25*K16/365
+WHY: COGS × inventory days / 365; stays zero because inventory days are policy zero.</t>
+      </text>
+    </comment>
+    <comment ref="L43" authorId="0" shapeId="0">
+      <text>
+        <t>Inventory $
+FORMULA: =L25*L16/365
+WHY: COGS × inventory days / 365; stays zero because inventory days are policy zero.</t>
+      </text>
+    </comment>
+    <comment ref="M43" authorId="0" shapeId="0">
+      <text>
+        <t>Inventory $
+FORMULA: =M25*M16/365
+WHY: COGS × inventory days / 365; stays zero because inventory days are policy zero.</t>
+      </text>
+    </comment>
+    <comment ref="N43" authorId="0" shapeId="0">
+      <text>
+        <t>Inventory $
+FORMULA: =N25*N16/365
+WHY: COGS × inventory days / 365; stays zero because inventory days are policy zero.</t>
+      </text>
+    </comment>
+    <comment ref="B44" authorId="0" shapeId="0">
+      <text>
+        <t>PP&amp;E (BS)
+WHY: Net PP&amp;E equals the PPE schedule closing balance after CapEx and depreciation.
+PATTERN: ={c}95</t>
+      </text>
+    </comment>
+    <comment ref="J44" authorId="0" shapeId="0">
+      <text>
+        <t>PP&amp;E (BS)
+FORMULA: =J95
+WHY: Net PP&amp;E equals the PPE schedule closing balance after CapEx and depreciation.</t>
+      </text>
+    </comment>
+    <comment ref="K44" authorId="0" shapeId="0">
+      <text>
+        <t>PP&amp;E (BS)
+FORMULA: =K95
+WHY: Net PP&amp;E equals the PPE schedule closing balance after CapEx and depreciation.</t>
+      </text>
+    </comment>
+    <comment ref="L44" authorId="0" shapeId="0">
+      <text>
+        <t>PP&amp;E (BS)
+FORMULA: =L95
+WHY: Net PP&amp;E equals the PPE schedule closing balance after CapEx and depreciation.</t>
+      </text>
+    </comment>
+    <comment ref="M44" authorId="0" shapeId="0">
+      <text>
+        <t>PP&amp;E (BS)
+FORMULA: =M95
+WHY: Net PP&amp;E equals the PPE schedule closing balance after CapEx and depreciation.</t>
+      </text>
+    </comment>
+    <comment ref="N44" authorId="0" shapeId="0">
+      <text>
+        <t>PP&amp;E (BS)
+FORMULA: =N95
+WHY: Net PP&amp;E equals the PPE schedule closing balance after CapEx and depreciation.</t>
+      </text>
+    </comment>
+    <comment ref="B45" authorId="0" shapeId="0">
+      <text>
+        <t>Total assets
+WHY: Cash + AR + inventory + PP&amp;E; simplified asset base used for the balance-sheet check.
+PATTERN: =SUM({c}41:{c}44)</t>
+      </text>
+    </comment>
+    <comment ref="J45" authorId="0" shapeId="0">
+      <text>
+        <t>Total assets
+FORMULA: =SUM(J41:J44)
+WHY: Cash + AR + inventory + PP&amp;E; simplified asset base used for the balance-sheet check.</t>
+      </text>
+    </comment>
+    <comment ref="K45" authorId="0" shapeId="0">
+      <text>
+        <t>Total assets
+FORMULA: =SUM(K41:K44)
+WHY: Cash + AR + inventory + PP&amp;E; simplified asset base used for the balance-sheet check.</t>
+      </text>
+    </comment>
+    <comment ref="L45" authorId="0" shapeId="0">
+      <text>
+        <t>Total assets
+FORMULA: =SUM(L41:L44)
+WHY: Cash + AR + inventory + PP&amp;E; simplified asset base used for the balance-sheet check.</t>
+      </text>
+    </comment>
+    <comment ref="M45" authorId="0" shapeId="0">
+      <text>
+        <t>Total assets
+FORMULA: =SUM(M41:M44)
+WHY: Cash + AR + inventory + PP&amp;E; simplified asset base used for the balance-sheet check.</t>
+      </text>
+    </comment>
+    <comment ref="N45" authorId="0" shapeId="0">
+      <text>
+        <t>Total assets
+FORMULA: =SUM(N41:N44)
+WHY: Cash + AR + inventory + PP&amp;E; simplified asset base used for the balance-sheet check.</t>
+      </text>
+    </comment>
+    <comment ref="B48" authorId="0" shapeId="0">
+      <text>
+        <t>AP $
+WHY: COGS × AP days / 365; payables funded by the payable-days assumption.
+PATTERN: ={c}25*{c}17/365</t>
+      </text>
+    </comment>
+    <comment ref="J48" authorId="0" shapeId="0">
+      <text>
+        <t>AP $
+FORMULA: =J25*J17/365
+WHY: COGS × AP days / 365; payables funded by the payable-days assumption.</t>
+      </text>
+    </comment>
+    <comment ref="K48" authorId="0" shapeId="0">
+      <text>
+        <t>AP $
+FORMULA: =K25*K17/365
+WHY: COGS × AP days / 365; payables funded by the payable-days assumption.</t>
+      </text>
+    </comment>
+    <comment ref="L48" authorId="0" shapeId="0">
+      <text>
+        <t>AP $
+FORMULA: =L25*L17/365
+WHY: COGS × AP days / 365; payables funded by the payable-days assumption.</t>
+      </text>
+    </comment>
+    <comment ref="M48" authorId="0" shapeId="0">
+      <text>
+        <t>AP $
+FORMULA: =M25*M17/365
+WHY: COGS × AP days / 365; payables funded by the payable-days assumption.</t>
+      </text>
+    </comment>
+    <comment ref="N48" authorId="0" shapeId="0">
+      <text>
+        <t>AP $
+FORMULA: =N25*N17/365
+WHY: COGS × AP days / 365; payables funded by the payable-days assumption.</t>
+      </text>
+    </comment>
+    <comment ref="B49" authorId="0" shapeId="0">
+      <text>
+        <t>Debt (BS)
+WHY: Debt equals the debt-schedule closing balance (open + issuance, issuance usually 0).
+PATTERN: ={c}100</t>
+      </text>
+    </comment>
+    <comment ref="J49" authorId="0" shapeId="0">
+      <text>
+        <t>Debt (BS)
+FORMULA: =J100
+WHY: Debt equals the debt-schedule closing balance (open + issuance, issuance usually 0).</t>
+      </text>
+    </comment>
+    <comment ref="K49" authorId="0" shapeId="0">
+      <text>
+        <t>Debt (BS)
+FORMULA: =K100
+WHY: Debt equals the debt-schedule closing balance (open + issuance, issuance usually 0).</t>
+      </text>
+    </comment>
+    <comment ref="L49" authorId="0" shapeId="0">
+      <text>
+        <t>Debt (BS)
+FORMULA: =L100
+WHY: Debt equals the debt-schedule closing balance (open + issuance, issuance usually 0).</t>
+      </text>
+    </comment>
+    <comment ref="M49" authorId="0" shapeId="0">
+      <text>
+        <t>Debt (BS)
+FORMULA: =M100
+WHY: Debt equals the debt-schedule closing balance (open + issuance, issuance usually 0).</t>
+      </text>
+    </comment>
+    <comment ref="N49" authorId="0" shapeId="0">
+      <text>
+        <t>Debt (BS)
+FORMULA: =N100
+WHY: Debt equals the debt-schedule closing balance (open + issuance, issuance usually 0).</t>
+      </text>
+    </comment>
+    <comment ref="B50" authorId="0" shapeId="0">
+      <text>
+        <t>Total liabilities
+WHY: Accounts payable plus debt; simplified liability total in this teaching template.
+PATTERN: =SUM({c}48:{c}49)</t>
+      </text>
+    </comment>
+    <comment ref="J50" authorId="0" shapeId="0">
+      <text>
+        <t>Total liabilities
+FORMULA: =SUM(J48:J49)
+WHY: Accounts payable plus debt; simplified liability total in this teaching template.</t>
+      </text>
+    </comment>
+    <comment ref="K50" authorId="0" shapeId="0">
+      <text>
+        <t>Total liabilities
+FORMULA: =SUM(K48:K49)
+WHY: Accounts payable plus debt; simplified liability total in this teaching template.</t>
+      </text>
+    </comment>
+    <comment ref="L50" authorId="0" shapeId="0">
+      <text>
+        <t>Total liabilities
+FORMULA: =SUM(L48:L49)
+WHY: Accounts payable plus debt; simplified liability total in this teaching template.</t>
+      </text>
+    </comment>
+    <comment ref="M50" authorId="0" shapeId="0">
+      <text>
+        <t>Total liabilities
+FORMULA: =SUM(M48:M49)
+WHY: Accounts payable plus debt; simplified liability total in this teaching template.</t>
+      </text>
+    </comment>
+    <comment ref="N50" authorId="0" shapeId="0">
+      <text>
+        <t>Total liabilities
+FORMULA: =SUM(N48:N49)
+WHY: Accounts payable plus debt; simplified liability total in this teaching template.</t>
+      </text>
+    </comment>
+    <comment ref="B52" authorId="0" shapeId="0">
+      <text>
+        <t>Equity capital
+WHY: Prior equity capital plus equity issued/(repurchased); policy keeps issuance at zero.
+PATTERN: ={p}52+{c}20</t>
+      </text>
+    </comment>
+    <comment ref="J52" authorId="0" shapeId="0">
+      <text>
+        <t>Equity capital
+FORMULA: =I52+J20
+WHY: Prior equity capital plus equity issued/(repurchased); policy keeps issuance at zero.</t>
+      </text>
+    </comment>
+    <comment ref="K52" authorId="0" shapeId="0">
+      <text>
+        <t>Equity capital
+FORMULA: =J52+K20
+WHY: Prior equity capital plus equity issued/(repurchased); policy keeps issuance at zero.</t>
+      </text>
+    </comment>
+    <comment ref="L52" authorId="0" shapeId="0">
+      <text>
+        <t>Equity capital
+FORMULA: =K52+L20
+WHY: Prior equity capital plus equity issued/(repurchased); policy keeps issuance at zero.</t>
+      </text>
+    </comment>
+    <comment ref="M52" authorId="0" shapeId="0">
+      <text>
+        <t>Equity capital
+FORMULA: =L52+M20
+WHY: Prior equity capital plus equity issued/(repurchased); policy keeps issuance at zero.</t>
+      </text>
+    </comment>
+    <comment ref="N52" authorId="0" shapeId="0">
+      <text>
+        <t>Equity capital
+FORMULA: =M52+N20
+WHY: Prior equity capital plus equity issued/(repurchased); policy keeps issuance at zero.</t>
+      </text>
+    </comment>
+    <comment ref="B53" authorId="0" shapeId="0">
+      <text>
+        <t>Retained earnings
+WHY: Prior RE plus this year’s net earnings; accumulates NI into equity without dividends.
+PATTERN: ={p}53+{c}33*(1-{c}13)</t>
+      </text>
+    </comment>
+    <comment ref="J53" authorId="0" shapeId="0">
+      <text>
+        <t>Retained earnings
+FORMULA: =I53+J33*(1-J13)
+WHY: Prior RE plus this year’s net earnings; accumulates NI into equity without dividends.</t>
+      </text>
+    </comment>
+    <comment ref="K53" authorId="0" shapeId="0">
+      <text>
+        <t>Retained earnings
+FORMULA: =J53+K33*(1-K13)
+WHY: Prior RE plus this year’s net earnings; accumulates NI into equity without dividends.</t>
+      </text>
+    </comment>
+    <comment ref="L53" authorId="0" shapeId="0">
+      <text>
+        <t>Retained earnings
+FORMULA: =K53+L33*(1-L13)
+WHY: Prior RE plus this year’s net earnings; accumulates NI into equity without dividends.</t>
+      </text>
+    </comment>
+    <comment ref="M53" authorId="0" shapeId="0">
+      <text>
+        <t>Retained earnings
+FORMULA: =L53+M33*(1-M13)
+WHY: Prior RE plus this year’s net earnings; accumulates NI into equity without dividends.</t>
+      </text>
+    </comment>
+    <comment ref="N53" authorId="0" shapeId="0">
+      <text>
+        <t>Retained earnings
+FORMULA: =M53+N33*(1-N13)
+WHY: Prior RE plus this year’s net earnings; accumulates NI into equity without dividends.</t>
+      </text>
+    </comment>
+    <comment ref="B54" authorId="0" shapeId="0">
+      <text>
+        <t>Shareholders’ equity
+WHY: Equity capital plus retained earnings; book equity for the L+E side of the check.
+PATTERN: =SUM({c}52:{c}53)</t>
+      </text>
+    </comment>
+    <comment ref="J54" authorId="0" shapeId="0">
+      <text>
+        <t>Shareholders’ equity
+FORMULA: =SUM(J52:J53)
+WHY: Equity capital plus retained earnings; book equity for the L+E side of the check.</t>
+      </text>
+    </comment>
+    <comment ref="K54" authorId="0" shapeId="0">
+      <text>
+        <t>Shareholders’ equity
+FORMULA: =SUM(K52:K53)
+WHY: Equity capital plus retained earnings; book equity for the L+E side of the check.</t>
+      </text>
+    </comment>
+    <comment ref="L54" authorId="0" shapeId="0">
+      <text>
+        <t>Shareholders’ equity
+FORMULA: =SUM(L52:L53)
+WHY: Equity capital plus retained earnings; book equity for the L+E side of the check.</t>
+      </text>
+    </comment>
+    <comment ref="M54" authorId="0" shapeId="0">
+      <text>
+        <t>Shareholders’ equity
+FORMULA: =SUM(M52:M53)
+WHY: Equity capital plus retained earnings; book equity for the L+E side of the check.</t>
+      </text>
+    </comment>
+    <comment ref="N54" authorId="0" shapeId="0">
+      <text>
+        <t>Shareholders’ equity
+FORMULA: =SUM(N52:N53)
+WHY: Equity capital plus retained earnings; book equity for the L+E side of the check.</t>
+      </text>
+    </comment>
+    <comment ref="B55" authorId="0" shapeId="0">
+      <text>
+        <t>Total L+E
+WHY: Liabilities plus equity; must equal total assets when the model is in balance.
+PATTERN: ={c}50+{c}54</t>
+      </text>
+    </comment>
+    <comment ref="J55" authorId="0" shapeId="0">
+      <text>
+        <t>Total L+E
+FORMULA: =J50+J54
+WHY: Liabilities plus equity; must equal total assets when the model is in balance.</t>
+      </text>
+    </comment>
+    <comment ref="K55" authorId="0" shapeId="0">
+      <text>
+        <t>Total L+E
+FORMULA: =K50+K54
+WHY: Liabilities plus equity; must equal total assets when the model is in balance.</t>
+      </text>
+    </comment>
+    <comment ref="L55" authorId="0" shapeId="0">
+      <text>
+        <t>Total L+E
+FORMULA: =L50+L54
+WHY: Liabilities plus equity; must equal total assets when the model is in balance.</t>
+      </text>
+    </comment>
+    <comment ref="M55" authorId="0" shapeId="0">
+      <text>
+        <t>Total L+E
+FORMULA: =M50+M54
+WHY: Liabilities plus equity; must equal total assets when the model is in balance.</t>
+      </text>
+    </comment>
+    <comment ref="N55" authorId="0" shapeId="0">
+      <text>
+        <t>Total L+E
+FORMULA: =N50+N54
+WHY: Liabilities plus equity; must equal total assets when the model is in balance.</t>
+      </text>
+    </comment>
+    <comment ref="B57" authorId="0" shapeId="0">
+      <text>
+        <t>BS imbalance
+WHY: L+E minus assets; should be ~0. Nonzero means a link or plug is broken.
+PATTERN: ={c}55-{c}45</t>
+      </text>
+    </comment>
+    <comment ref="J57" authorId="0" shapeId="0">
+      <text>
+        <t>BS imbalance
+FORMULA: =J55-J45
+WHY: L+E minus assets; should be ~0. Nonzero means a link or plug is broken.</t>
+      </text>
+    </comment>
+    <comment ref="K57" authorId="0" shapeId="0">
+      <text>
+        <t>BS imbalance
+FORMULA: =K55-K45
+WHY: L+E minus assets; should be ~0. Nonzero means a link or plug is broken.</t>
+      </text>
+    </comment>
+    <comment ref="L57" authorId="0" shapeId="0">
+      <text>
+        <t>BS imbalance
+FORMULA: =L55-L45
+WHY: L+E minus assets; should be ~0. Nonzero means a link or plug is broken.</t>
+      </text>
+    </comment>
+    <comment ref="M57" authorId="0" shapeId="0">
+      <text>
+        <t>BS imbalance
+FORMULA: =M55-M45
+WHY: L+E minus assets; should be ~0. Nonzero means a link or plug is broken.</t>
+      </text>
+    </comment>
+    <comment ref="N57" authorId="0" shapeId="0">
+      <text>
+        <t>BS imbalance
+FORMULA: =N55-N45
+WHY: L+E minus assets; should be ~0. Nonzero means a link or plug is broken.</t>
+      </text>
+    </comment>
+    <comment ref="B62" authorId="0" shapeId="0">
+      <text>
+        <t>CF net earnings
+WHY: Same NI equation as the IS, written out so CFO does not hide behind a bare pointer.
+PATTERN: ={c}33*(1-{c}13)</t>
+      </text>
+    </comment>
+    <comment ref="J62" authorId="0" shapeId="0">
+      <text>
+        <t>CF net earnings
+FORMULA: =J33*(1-J13)
+WHY: Same NI equation as the IS, written out so CFO does not hide behind a bare pointer.</t>
+      </text>
+    </comment>
+    <comment ref="K62" authorId="0" shapeId="0">
+      <text>
+        <t>CF net earnings
+FORMULA: =K33*(1-K13)
+WHY: Same NI equation as the IS, written out so CFO does not hide behind a bare pointer.</t>
+      </text>
+    </comment>
+    <comment ref="L62" authorId="0" shapeId="0">
+      <text>
+        <t>CF net earnings
+FORMULA: =L33*(1-L13)
+WHY: Same NI equation as the IS, written out so CFO does not hide behind a bare pointer.</t>
+      </text>
+    </comment>
+    <comment ref="M62" authorId="0" shapeId="0">
+      <text>
+        <t>CF net earnings
+FORMULA: =M33*(1-M13)
+WHY: Same NI equation as the IS, written out so CFO does not hide behind a bare pointer.</t>
+      </text>
+    </comment>
+    <comment ref="N62" authorId="0" shapeId="0">
+      <text>
+        <t>CF net earnings
+FORMULA: =N33*(1-N13)
+WHY: Same NI equation as the IS, written out so CFO does not hide behind a bare pointer.</t>
+      </text>
+    </comment>
+    <comment ref="B63" authorId="0" shapeId="0">
+      <text>
+        <t>CF + D&amp;A
+WHY: Adds back non-cash D&amp;A (open PP&amp;E × D&amp;A%) in the cash-from-operations bridge.
+PATTERN: ={c}92*{c}11</t>
+      </text>
+    </comment>
+    <comment ref="J63" authorId="0" shapeId="0">
+      <text>
+        <t>CF + D&amp;A
+FORMULA: =J92*J11
+WHY: Adds back non-cash D&amp;A (open PP&amp;E × D&amp;A%) in the cash-from-operations bridge.</t>
+      </text>
+    </comment>
+    <comment ref="K63" authorId="0" shapeId="0">
+      <text>
+        <t>CF + D&amp;A
+FORMULA: =K92*K11
+WHY: Adds back non-cash D&amp;A (open PP&amp;E × D&amp;A%) in the cash-from-operations bridge.</t>
+      </text>
+    </comment>
+    <comment ref="L63" authorId="0" shapeId="0">
+      <text>
+        <t>CF + D&amp;A
+FORMULA: =L92*L11
+WHY: Adds back non-cash D&amp;A (open PP&amp;E × D&amp;A%) in the cash-from-operations bridge.</t>
+      </text>
+    </comment>
+    <comment ref="M63" authorId="0" shapeId="0">
+      <text>
+        <t>CF + D&amp;A
+FORMULA: =M92*M11
+WHY: Adds back non-cash D&amp;A (open PP&amp;E × D&amp;A%) in the cash-from-operations bridge.</t>
+      </text>
+    </comment>
+    <comment ref="N63" authorId="0" shapeId="0">
+      <text>
+        <t>CF + D&amp;A
+FORMULA: =N92*N11
+WHY: Adds back non-cash D&amp;A (open PP&amp;E × D&amp;A%) in the cash-from-operations bridge.</t>
+      </text>
+    </comment>
+    <comment ref="B64" authorId="0" shapeId="0">
+      <text>
+        <t>CF − ΔNWC
+WHY: Increase in net working capital uses cash; decrease frees cash in the CFO build.
+PATTERN: ={c}88-{p}88</t>
+      </text>
+    </comment>
+    <comment ref="J64" authorId="0" shapeId="0">
+      <text>
+        <t>CF − ΔNWC
+FORMULA: =J88-I88
+WHY: Increase in net working capital uses cash; decrease frees cash in the CFO build.</t>
+      </text>
+    </comment>
+    <comment ref="K64" authorId="0" shapeId="0">
+      <text>
+        <t>CF − ΔNWC
+FORMULA: =K88-J88
+WHY: Increase in net working capital uses cash; decrease frees cash in the CFO build.</t>
+      </text>
+    </comment>
+    <comment ref="L64" authorId="0" shapeId="0">
+      <text>
+        <t>CF − ΔNWC
+FORMULA: =L88-K88
+WHY: Increase in net working capital uses cash; decrease frees cash in the CFO build.</t>
+      </text>
+    </comment>
+    <comment ref="M64" authorId="0" shapeId="0">
+      <text>
+        <t>CF − ΔNWC
+FORMULA: =M88-L88
+WHY: Increase in net working capital uses cash; decrease frees cash in the CFO build.</t>
+      </text>
+    </comment>
+    <comment ref="N64" authorId="0" shapeId="0">
+      <text>
+        <t>CF − ΔNWC
+FORMULA: =N88-M88
+WHY: Increase in net working capital uses cash; decrease frees cash in the CFO build.</t>
+      </text>
+    </comment>
+    <comment ref="B65" authorId="0" shapeId="0">
+      <text>
+        <t>Cash from operations
+WHY: Full CFO: NI + D&amp;A − ΔNWC written as one equation, not assembled from pointers.
+PATTERN: ={c}33*(1-{c}13)+{c}92*{c}11-({c}88-{p}88)</t>
+      </text>
+    </comment>
+    <comment ref="J65" authorId="0" shapeId="0">
+      <text>
+        <t>Cash from operations
+FORMULA: =J33*(1-J13)+J92*J11-(J88-I88)
+WHY: Full CFO: NI + D&amp;A − ΔNWC written as one equation, not assembled from pointers.</t>
+      </text>
+    </comment>
+    <comment ref="K65" authorId="0" shapeId="0">
+      <text>
+        <t>Cash from operations
+FORMULA: =K33*(1-K13)+K92*K11-(K88-J88)
+WHY: Full CFO: NI + D&amp;A − ΔNWC written as one equation, not assembled from pointers.</t>
+      </text>
+    </comment>
+    <comment ref="L65" authorId="0" shapeId="0">
+      <text>
+        <t>Cash from operations
+FORMULA: =L33*(1-L13)+L92*L11-(L88-K88)
+WHY: Full CFO: NI + D&amp;A − ΔNWC written as one equation, not assembled from pointers.</t>
+      </text>
+    </comment>
+    <comment ref="M65" authorId="0" shapeId="0">
+      <text>
+        <t>Cash from operations
+FORMULA: =M33*(1-M13)+M92*M11-(M88-L88)
+WHY: Full CFO: NI + D&amp;A − ΔNWC written as one equation, not assembled from pointers.</t>
+      </text>
+    </comment>
+    <comment ref="N65" authorId="0" shapeId="0">
+      <text>
+        <t>Cash from operations
+FORMULA: =N33*(1-N13)+N92*N11-(N88-M88)
+WHY: Full CFO: NI + D&amp;A − ΔNWC written as one equation, not assembled from pointers.</t>
+      </text>
+    </comment>
+    <comment ref="B68" authorId="0" shapeId="0">
+      <text>
+        <t>CapEx $
+WHY: Revenue times CapEx%; investing outflow used in CF and the PPE roll-forward.
+PATTERN: ={c}24*{c}18</t>
+      </text>
+    </comment>
+    <comment ref="J68" authorId="0" shapeId="0">
+      <text>
+        <t>CapEx $
+FORMULA: =J24*J18
+WHY: Revenue times CapEx%; investing outflow used in CF and the PPE roll-forward.</t>
+      </text>
+    </comment>
+    <comment ref="K68" authorId="0" shapeId="0">
+      <text>
+        <t>CapEx $
+FORMULA: =K24*K18
+WHY: Revenue times CapEx%; investing outflow used in CF and the PPE roll-forward.</t>
+      </text>
+    </comment>
+    <comment ref="L68" authorId="0" shapeId="0">
+      <text>
+        <t>CapEx $
+FORMULA: =L24*L18
+WHY: Revenue times CapEx%; investing outflow used in CF and the PPE roll-forward.</t>
+      </text>
+    </comment>
+    <comment ref="M68" authorId="0" shapeId="0">
+      <text>
+        <t>CapEx $
+FORMULA: =M24*M18
+WHY: Revenue times CapEx%; investing outflow used in CF and the PPE roll-forward.</t>
+      </text>
+    </comment>
+    <comment ref="N68" authorId="0" shapeId="0">
+      <text>
+        <t>CapEx $
+FORMULA: =N24*N18
+WHY: Revenue times CapEx%; investing outflow used in CF and the PPE roll-forward.</t>
+      </text>
+    </comment>
+    <comment ref="B69" authorId="0" shapeId="0">
+      <text>
+        <t>Cash from investing
+WHY: In this template CFI is CapEx only; equals the CapEx dollar line above.
+PATTERN: ={c}68</t>
+      </text>
+    </comment>
+    <comment ref="J69" authorId="0" shapeId="0">
+      <text>
+        <t>Cash from investing
+FORMULA: =J68
+WHY: In this template CFI is CapEx only; equals the CapEx dollar line above.</t>
+      </text>
+    </comment>
+    <comment ref="K69" authorId="0" shapeId="0">
+      <text>
+        <t>Cash from investing
+FORMULA: =K68
+WHY: In this template CFI is CapEx only; equals the CapEx dollar line above.</t>
+      </text>
+    </comment>
+    <comment ref="L69" authorId="0" shapeId="0">
+      <text>
+        <t>Cash from investing
+FORMULA: =L68
+WHY: In this template CFI is CapEx only; equals the CapEx dollar line above.</t>
+      </text>
+    </comment>
+    <comment ref="M69" authorId="0" shapeId="0">
+      <text>
+        <t>Cash from investing
+FORMULA: =M68
+WHY: In this template CFI is CapEx only; equals the CapEx dollar line above.</t>
+      </text>
+    </comment>
+    <comment ref="N69" authorId="0" shapeId="0">
+      <text>
+        <t>Cash from investing
+FORMULA: =N68
+WHY: In this template CFI is CapEx only; equals the CapEx dollar line above.</t>
+      </text>
+    </comment>
+    <comment ref="B72" authorId="0" shapeId="0">
+      <text>
+        <t>Debt issuance CF
+WHY: Pulls the debt issuance/(repayment) policy into financing cash flow.
+PATTERN: ={c}19</t>
+      </text>
+    </comment>
+    <comment ref="J72" authorId="0" shapeId="0">
+      <text>
+        <t>Debt issuance CF
+FORMULA: =J19
+WHY: Pulls the debt issuance/(repayment) policy into financing cash flow.</t>
+      </text>
+    </comment>
+    <comment ref="K72" authorId="0" shapeId="0">
+      <text>
+        <t>Debt issuance CF
+FORMULA: =K19
+WHY: Pulls the debt issuance/(repayment) policy into financing cash flow.</t>
+      </text>
+    </comment>
+    <comment ref="L72" authorId="0" shapeId="0">
+      <text>
+        <t>Debt issuance CF
+FORMULA: =L19
+WHY: Pulls the debt issuance/(repayment) policy into financing cash flow.</t>
+      </text>
+    </comment>
+    <comment ref="M72" authorId="0" shapeId="0">
+      <text>
+        <t>Debt issuance CF
+FORMULA: =M19
+WHY: Pulls the debt issuance/(repayment) policy into financing cash flow.</t>
+      </text>
+    </comment>
+    <comment ref="N72" authorId="0" shapeId="0">
+      <text>
+        <t>Debt issuance CF
+FORMULA: =N19
+WHY: Pulls the debt issuance/(repayment) policy into financing cash flow.</t>
+      </text>
+    </comment>
+    <comment ref="B73" authorId="0" shapeId="0">
+      <text>
+        <t>Equity issuance CF
+WHY: Pulls the equity issuance/(buyback) policy into financing cash flow.
+PATTERN: ={c}20</t>
+      </text>
+    </comment>
+    <comment ref="J73" authorId="0" shapeId="0">
+      <text>
+        <t>Equity issuance CF
+FORMULA: =J20
+WHY: Pulls the equity issuance/(buyback) policy into financing cash flow.</t>
+      </text>
+    </comment>
+    <comment ref="K73" authorId="0" shapeId="0">
+      <text>
+        <t>Equity issuance CF
+FORMULA: =K20
+WHY: Pulls the equity issuance/(buyback) policy into financing cash flow.</t>
+      </text>
+    </comment>
+    <comment ref="L73" authorId="0" shapeId="0">
+      <text>
+        <t>Equity issuance CF
+FORMULA: =L20
+WHY: Pulls the equity issuance/(buyback) policy into financing cash flow.</t>
+      </text>
+    </comment>
+    <comment ref="M73" authorId="0" shapeId="0">
+      <text>
+        <t>Equity issuance CF
+FORMULA: =M20
+WHY: Pulls the equity issuance/(buyback) policy into financing cash flow.</t>
+      </text>
+    </comment>
+    <comment ref="N73" authorId="0" shapeId="0">
+      <text>
+        <t>Equity issuance CF
+FORMULA: =N20
+WHY: Pulls the equity issuance/(buyback) policy into financing cash flow.</t>
+      </text>
+    </comment>
+    <comment ref="B74" authorId="0" shapeId="0">
+      <text>
+        <t>Cash from financing
+WHY: Debt plus equity financing cash; both policies are zero in the base case.
+PATTERN: ={c}19+{c}20</t>
+      </text>
+    </comment>
+    <comment ref="J74" authorId="0" shapeId="0">
+      <text>
+        <t>Cash from financing
+FORMULA: =J19+J20
+WHY: Debt plus equity financing cash; both policies are zero in the base case.</t>
+      </text>
+    </comment>
+    <comment ref="K74" authorId="0" shapeId="0">
+      <text>
+        <t>Cash from financing
+FORMULA: =K19+K20
+WHY: Debt plus equity financing cash; both policies are zero in the base case.</t>
+      </text>
+    </comment>
+    <comment ref="L74" authorId="0" shapeId="0">
+      <text>
+        <t>Cash from financing
+FORMULA: =L19+L20
+WHY: Debt plus equity financing cash; both policies are zero in the base case.</t>
+      </text>
+    </comment>
+    <comment ref="M74" authorId="0" shapeId="0">
+      <text>
+        <t>Cash from financing
+FORMULA: =M19+M20
+WHY: Debt plus equity financing cash; both policies are zero in the base case.</t>
+      </text>
+    </comment>
+    <comment ref="N74" authorId="0" shapeId="0">
+      <text>
+        <t>Cash from financing
+FORMULA: =N19+N20
+WHY: Debt plus equity financing cash; both policies are zero in the base case.</t>
+      </text>
+    </comment>
+    <comment ref="B76" authorId="0" shapeId="0">
+      <text>
+        <t>Δ Cash
+WHY: CFO minus CapEx plus financing; net change that rolls opening cash to closing.
+PATTERN: ={c}65-{c}69+{c}74</t>
+      </text>
+    </comment>
+    <comment ref="J76" authorId="0" shapeId="0">
+      <text>
+        <t>Δ Cash
+FORMULA: =J65-J69+J74
+WHY: CFO minus CapEx plus financing; net change that rolls opening cash to closing.</t>
+      </text>
+    </comment>
+    <comment ref="K76" authorId="0" shapeId="0">
+      <text>
+        <t>Δ Cash
+FORMULA: =K65-K69+K74
+WHY: CFO minus CapEx plus financing; net change that rolls opening cash to closing.</t>
+      </text>
+    </comment>
+    <comment ref="L76" authorId="0" shapeId="0">
+      <text>
+        <t>Δ Cash
+FORMULA: =L65-L69+L74
+WHY: CFO minus CapEx plus financing; net change that rolls opening cash to closing.</t>
+      </text>
+    </comment>
+    <comment ref="M76" authorId="0" shapeId="0">
+      <text>
+        <t>Δ Cash
+FORMULA: =M65-M69+M74
+WHY: CFO minus CapEx plus financing; net change that rolls opening cash to closing.</t>
+      </text>
+    </comment>
+    <comment ref="N76" authorId="0" shapeId="0">
+      <text>
+        <t>Δ Cash
+FORMULA: =N65-N69+N74
+WHY: CFO minus CapEx plus financing; net change that rolls opening cash to closing.</t>
+      </text>
+    </comment>
+    <comment ref="B77" authorId="0" shapeId="0">
+      <text>
+        <t>Opening cash
+WHY: Starts at prior balance-sheet cash so the cash roll-forward matches history.
+PATTERN: ={p}41</t>
+      </text>
+    </comment>
+    <comment ref="J77" authorId="0" shapeId="0">
+      <text>
+        <t>Opening cash
+FORMULA: =I41
+WHY: Starts at prior balance-sheet cash so the cash roll-forward matches history.</t>
+      </text>
+    </comment>
+    <comment ref="K77" authorId="0" shapeId="0">
+      <text>
+        <t>Opening cash
+FORMULA: =J41
+WHY: Starts at prior balance-sheet cash so the cash roll-forward matches history.</t>
+      </text>
+    </comment>
+    <comment ref="L77" authorId="0" shapeId="0">
+      <text>
+        <t>Opening cash
+FORMULA: =K41
+WHY: Starts at prior balance-sheet cash so the cash roll-forward matches history.</t>
+      </text>
+    </comment>
+    <comment ref="M77" authorId="0" shapeId="0">
+      <text>
+        <t>Opening cash
+FORMULA: =L41
+WHY: Starts at prior balance-sheet cash so the cash roll-forward matches history.</t>
+      </text>
+    </comment>
+    <comment ref="N77" authorId="0" shapeId="0">
+      <text>
+        <t>Opening cash
+FORMULA: =M41
+WHY: Starts at prior balance-sheet cash so the cash roll-forward matches history.</t>
+      </text>
+    </comment>
+    <comment ref="B78" authorId="0" shapeId="0">
+      <text>
+        <t>Closing cash
+WHY: Opening cash plus Δ cash; feeds BS cash and the cash-flow check.
+PATTERN: ={c}77+{c}76</t>
+      </text>
+    </comment>
+    <comment ref="J78" authorId="0" shapeId="0">
+      <text>
+        <t>Closing cash
+FORMULA: =J77+J76
+WHY: Opening cash plus Δ cash; feeds BS cash and the cash-flow check.</t>
+      </text>
+    </comment>
+    <comment ref="K78" authorId="0" shapeId="0">
+      <text>
+        <t>Closing cash
+FORMULA: =K77+K76
+WHY: Opening cash plus Δ cash; feeds BS cash and the cash-flow check.</t>
+      </text>
+    </comment>
+    <comment ref="L78" authorId="0" shapeId="0">
+      <text>
+        <t>Closing cash
+FORMULA: =L77+L76
+WHY: Opening cash plus Δ cash; feeds BS cash and the cash-flow check.</t>
+      </text>
+    </comment>
+    <comment ref="M78" authorId="0" shapeId="0">
+      <text>
+        <t>Closing cash
+FORMULA: =M77+M76
+WHY: Opening cash plus Δ cash; feeds BS cash and the cash-flow check.</t>
+      </text>
+    </comment>
+    <comment ref="N78" authorId="0" shapeId="0">
+      <text>
+        <t>Closing cash
+FORMULA: =N77+N76
+WHY: Opening cash plus Δ cash; feeds BS cash and the cash-flow check.</t>
+      </text>
+    </comment>
+    <comment ref="B80" authorId="0" shapeId="0">
+      <text>
+        <t>Cash check
+WHY: Closing CF cash minus BS cash; must be zero when statements are linked.
+PATTERN: ={c}78-{c}41</t>
+      </text>
+    </comment>
+    <comment ref="J80" authorId="0" shapeId="0">
+      <text>
+        <t>Cash check
+FORMULA: =J78-J41
+WHY: Closing CF cash minus BS cash; must be zero when statements are linked.</t>
+      </text>
+    </comment>
+    <comment ref="K80" authorId="0" shapeId="0">
+      <text>
+        <t>Cash check
+FORMULA: =K78-K41
+WHY: Closing CF cash minus BS cash; must be zero when statements are linked.</t>
+      </text>
+    </comment>
+    <comment ref="L80" authorId="0" shapeId="0">
+      <text>
+        <t>Cash check
+FORMULA: =L78-L41
+WHY: Closing CF cash minus BS cash; must be zero when statements are linked.</t>
+      </text>
+    </comment>
+    <comment ref="M80" authorId="0" shapeId="0">
+      <text>
+        <t>Cash check
+FORMULA: =M78-M41
+WHY: Closing CF cash minus BS cash; must be zero when statements are linked.</t>
+      </text>
+    </comment>
+    <comment ref="N80" authorId="0" shapeId="0">
+      <text>
+        <t>Cash check
+FORMULA: =N78-N41
+WHY: Closing CF cash minus BS cash; must be zero when statements are linked.</t>
+      </text>
+    </comment>
+    <comment ref="B85" authorId="0" shapeId="0">
+      <text>
+        <t>WC: AR
+WHY: Working-capital schedule AR mirrors the balance-sheet AR used in ΔNWC.
+PATTERN: ={c}42</t>
+      </text>
+    </comment>
+    <comment ref="J85" authorId="0" shapeId="0">
+      <text>
+        <t>WC: AR
+FORMULA: =J42
+WHY: Working-capital schedule AR mirrors the balance-sheet AR used in ΔNWC.</t>
+      </text>
+    </comment>
+    <comment ref="K85" authorId="0" shapeId="0">
+      <text>
+        <t>WC: AR
+FORMULA: =K42
+WHY: Working-capital schedule AR mirrors the balance-sheet AR used in ΔNWC.</t>
+      </text>
+    </comment>
+    <comment ref="L85" authorId="0" shapeId="0">
+      <text>
+        <t>WC: AR
+FORMULA: =L42
+WHY: Working-capital schedule AR mirrors the balance-sheet AR used in ΔNWC.</t>
+      </text>
+    </comment>
+    <comment ref="M85" authorId="0" shapeId="0">
+      <text>
+        <t>WC: AR
+FORMULA: =M42
+WHY: Working-capital schedule AR mirrors the balance-sheet AR used in ΔNWC.</t>
+      </text>
+    </comment>
+    <comment ref="N85" authorId="0" shapeId="0">
+      <text>
+        <t>WC: AR
+FORMULA: =N42
+WHY: Working-capital schedule AR mirrors the balance-sheet AR used in ΔNWC.</t>
+      </text>
+    </comment>
+    <comment ref="B86" authorId="0" shapeId="0">
+      <text>
+        <t>WC: Inventory
+WHY: Working-capital inventory mirrors BS inventory (zero for this software business).
+PATTERN: ={c}43</t>
+      </text>
+    </comment>
+    <comment ref="J86" authorId="0" shapeId="0">
+      <text>
+        <t>WC: Inventory
+FORMULA: =J43
+WHY: Working-capital inventory mirrors BS inventory (zero for this software business).</t>
+      </text>
+    </comment>
+    <comment ref="K86" authorId="0" shapeId="0">
+      <text>
+        <t>WC: Inventory
+FORMULA: =K43
+WHY: Working-capital inventory mirrors BS inventory (zero for this software business).</t>
+      </text>
+    </comment>
+    <comment ref="L86" authorId="0" shapeId="0">
+      <text>
+        <t>WC: Inventory
+FORMULA: =L43
+WHY: Working-capital inventory mirrors BS inventory (zero for this software business).</t>
+      </text>
+    </comment>
+    <comment ref="M86" authorId="0" shapeId="0">
+      <text>
+        <t>WC: Inventory
+FORMULA: =M43
+WHY: Working-capital inventory mirrors BS inventory (zero for this software business).</t>
+      </text>
+    </comment>
+    <comment ref="N86" authorId="0" shapeId="0">
+      <text>
+        <t>WC: Inventory
+FORMULA: =N43
+WHY: Working-capital inventory mirrors BS inventory (zero for this software business).</t>
+      </text>
+    </comment>
+    <comment ref="B87" authorId="0" shapeId="0">
+      <text>
+        <t>WC: AP
+WHY: Working-capital AP mirrors BS AP so NWC uses the same operating balances.
+PATTERN: ={c}48</t>
+      </text>
+    </comment>
+    <comment ref="J87" authorId="0" shapeId="0">
+      <text>
+        <t>WC: AP
+FORMULA: =J48
+WHY: Working-capital AP mirrors BS AP so NWC uses the same operating balances.</t>
+      </text>
+    </comment>
+    <comment ref="K87" authorId="0" shapeId="0">
+      <text>
+        <t>WC: AP
+FORMULA: =K48
+WHY: Working-capital AP mirrors BS AP so NWC uses the same operating balances.</t>
+      </text>
+    </comment>
+    <comment ref="L87" authorId="0" shapeId="0">
+      <text>
+        <t>WC: AP
+FORMULA: =L48
+WHY: Working-capital AP mirrors BS AP so NWC uses the same operating balances.</t>
+      </text>
+    </comment>
+    <comment ref="M87" authorId="0" shapeId="0">
+      <text>
+        <t>WC: AP
+FORMULA: =M48
+WHY: Working-capital AP mirrors BS AP so NWC uses the same operating balances.</t>
+      </text>
+    </comment>
+    <comment ref="N87" authorId="0" shapeId="0">
+      <text>
+        <t>WC: AP
+FORMULA: =N48
+WHY: Working-capital AP mirrors BS AP so NWC uses the same operating balances.</t>
+      </text>
+    </comment>
+    <comment ref="B88" authorId="0" shapeId="0">
+      <text>
+        <t>Net working capital
+WHY: AR + inventory − AP; operating NWC (deferred already netted in AR).
+PATTERN: ={c}85+{c}86-{c}87</t>
+      </text>
+    </comment>
+    <comment ref="J88" authorId="0" shapeId="0">
+      <text>
+        <t>Net working capital
+FORMULA: =J85+J86-J87
+WHY: AR + inventory − AP; operating NWC (deferred already netted in AR).</t>
+      </text>
+    </comment>
+    <comment ref="K88" authorId="0" shapeId="0">
+      <text>
+        <t>Net working capital
+FORMULA: =K85+K86-K87
+WHY: AR + inventory − AP; operating NWC (deferred already netted in AR).</t>
+      </text>
+    </comment>
+    <comment ref="L88" authorId="0" shapeId="0">
+      <text>
+        <t>Net working capital
+FORMULA: =L85+L86-L87
+WHY: AR + inventory − AP; operating NWC (deferred already netted in AR).</t>
+      </text>
+    </comment>
+    <comment ref="M88" authorId="0" shapeId="0">
+      <text>
+        <t>Net working capital
+FORMULA: =M85+M86-M87
+WHY: AR + inventory − AP; operating NWC (deferred already netted in AR).</t>
+      </text>
+    </comment>
+    <comment ref="N88" authorId="0" shapeId="0">
+      <text>
+        <t>Net working capital
+FORMULA: =N85+N86-N87
+WHY: AR + inventory − AP; operating NWC (deferred already netted in AR).</t>
+      </text>
+    </comment>
+    <comment ref="B89" authorId="0" shapeId="0">
+      <text>
+        <t>Change in NWC
+WHY: Year-over-year NWC change; the cash investment/(release) used in CFO and FCFF.
+PATTERN: ={c}88-{p}88</t>
+      </text>
+    </comment>
+    <comment ref="J89" authorId="0" shapeId="0">
+      <text>
+        <t>Change in NWC
+FORMULA: =J88-I88
+WHY: Year-over-year NWC change; the cash investment/(release) used in CFO and FCFF.</t>
+      </text>
+    </comment>
+    <comment ref="K89" authorId="0" shapeId="0">
+      <text>
+        <t>Change in NWC
+FORMULA: =K88-J88
+WHY: Year-over-year NWC change; the cash investment/(release) used in CFO and FCFF.</t>
+      </text>
+    </comment>
+    <comment ref="L89" authorId="0" shapeId="0">
+      <text>
+        <t>Change in NWC
+FORMULA: =L88-K88
+WHY: Year-over-year NWC change; the cash investment/(release) used in CFO and FCFF.</t>
+      </text>
+    </comment>
+    <comment ref="M89" authorId="0" shapeId="0">
+      <text>
+        <t>Change in NWC
+FORMULA: =M88-L88
+WHY: Year-over-year NWC change; the cash investment/(release) used in CFO and FCFF.</t>
+      </text>
+    </comment>
+    <comment ref="N89" authorId="0" shapeId="0">
+      <text>
+        <t>Change in NWC
+FORMULA: =N88-M88
+WHY: Year-over-year NWC change; the cash investment/(release) used in CFO and FCFF.</t>
+      </text>
+    </comment>
+    <comment ref="B92" authorId="0" shapeId="0">
+      <text>
+        <t>PPE opening
+WHY: Prior closing PP&amp;E (FY1 opens at last historical I44); base for CapEx and D&amp;A.
+PATTERN: ={p}95 or I44</t>
+      </text>
+    </comment>
+    <comment ref="J92" authorId="0" shapeId="0">
+      <text>
+        <t>PPE opening
+FORMULA: =I95 or I44
+WHY: Prior closing PP&amp;E (FY1 opens at last historical I44); base for CapEx and D&amp;A.</t>
+      </text>
+    </comment>
+    <comment ref="K92" authorId="0" shapeId="0">
+      <text>
+        <t>PPE opening
+FORMULA: =J95 or I44
+WHY: Prior closing PP&amp;E (FY1 opens at last historical I44); base for CapEx and D&amp;A.</t>
+      </text>
+    </comment>
+    <comment ref="L92" authorId="0" shapeId="0">
+      <text>
+        <t>PPE opening
+FORMULA: =K95 or I44
+WHY: Prior closing PP&amp;E (FY1 opens at last historical I44); base for CapEx and D&amp;A.</t>
+      </text>
+    </comment>
+    <comment ref="M92" authorId="0" shapeId="0">
+      <text>
+        <t>PPE opening
+FORMULA: =L95 or I44
+WHY: Prior closing PP&amp;E (FY1 opens at last historical I44); base for CapEx and D&amp;A.</t>
+      </text>
+    </comment>
+    <comment ref="N92" authorId="0" shapeId="0">
+      <text>
+        <t>PPE opening
+FORMULA: =M95 or I44
+WHY: Prior closing PP&amp;E (FY1 opens at last historical I44); base for CapEx and D&amp;A.</t>
+      </text>
+    </comment>
+    <comment ref="B93" authorId="0" shapeId="0">
+      <text>
+        <t>PPE + CapEx
+WHY: Same CapEx dollars as CF; additions that grow the gross PP&amp;E stock.
+PATTERN: ={c}24*{c}18</t>
+      </text>
+    </comment>
+    <comment ref="J93" authorId="0" shapeId="0">
+      <text>
+        <t>PPE + CapEx
+FORMULA: =J24*J18
+WHY: Same CapEx dollars as CF; additions that grow the gross PP&amp;E stock.</t>
+      </text>
+    </comment>
+    <comment ref="K93" authorId="0" shapeId="0">
+      <text>
+        <t>PPE + CapEx
+FORMULA: =K24*K18
+WHY: Same CapEx dollars as CF; additions that grow the gross PP&amp;E stock.</t>
+      </text>
+    </comment>
+    <comment ref="L93" authorId="0" shapeId="0">
+      <text>
+        <t>PPE + CapEx
+FORMULA: =L24*L18
+WHY: Same CapEx dollars as CF; additions that grow the gross PP&amp;E stock.</t>
+      </text>
+    </comment>
+    <comment ref="M93" authorId="0" shapeId="0">
+      <text>
+        <t>PPE + CapEx
+FORMULA: =M24*M18
+WHY: Same CapEx dollars as CF; additions that grow the gross PP&amp;E stock.</t>
+      </text>
+    </comment>
+    <comment ref="N93" authorId="0" shapeId="0">
+      <text>
+        <t>PPE + CapEx
+FORMULA: =N24*N18
+WHY: Same CapEx dollars as CF; additions that grow the gross PP&amp;E stock.</t>
+      </text>
+    </comment>
+    <comment ref="B94" authorId="0" shapeId="0">
+      <text>
+        <t>PPE − D&amp;A
+WHY: Depreciation on opening PP&amp;E; reduces net PP&amp;E in the roll-forward.
+PATTERN: ={c}92*{c}11</t>
+      </text>
+    </comment>
+    <comment ref="J94" authorId="0" shapeId="0">
+      <text>
+        <t>PPE − D&amp;A
+FORMULA: =J92*J11
+WHY: Depreciation on opening PP&amp;E; reduces net PP&amp;E in the roll-forward.</t>
+      </text>
+    </comment>
+    <comment ref="K94" authorId="0" shapeId="0">
+      <text>
+        <t>PPE − D&amp;A
+FORMULA: =K92*K11
+WHY: Depreciation on opening PP&amp;E; reduces net PP&amp;E in the roll-forward.</t>
+      </text>
+    </comment>
+    <comment ref="L94" authorId="0" shapeId="0">
+      <text>
+        <t>PPE − D&amp;A
+FORMULA: =L92*L11
+WHY: Depreciation on opening PP&amp;E; reduces net PP&amp;E in the roll-forward.</t>
+      </text>
+    </comment>
+    <comment ref="M94" authorId="0" shapeId="0">
+      <text>
+        <t>PPE − D&amp;A
+FORMULA: =M92*M11
+WHY: Depreciation on opening PP&amp;E; reduces net PP&amp;E in the roll-forward.</t>
+      </text>
+    </comment>
+    <comment ref="N94" authorId="0" shapeId="0">
+      <text>
+        <t>PPE − D&amp;A
+FORMULA: =N92*N11
+WHY: Depreciation on opening PP&amp;E; reduces net PP&amp;E in the roll-forward.</t>
+      </text>
+    </comment>
+    <comment ref="B95" authorId="0" shapeId="0">
+      <text>
+        <t>PPE closing
+WHY: Open + CapEx − D&amp;A; closing net PP&amp;E posted to the balance sheet.
+PATTERN: ={c}92+{c}93-{c}94</t>
+      </text>
+    </comment>
+    <comment ref="J95" authorId="0" shapeId="0">
+      <text>
+        <t>PPE closing
+FORMULA: =J92+J93-J94
+WHY: Open + CapEx − D&amp;A; closing net PP&amp;E posted to the balance sheet.</t>
+      </text>
+    </comment>
+    <comment ref="K95" authorId="0" shapeId="0">
+      <text>
+        <t>PPE closing
+FORMULA: =K92+K93-K94
+WHY: Open + CapEx − D&amp;A; closing net PP&amp;E posted to the balance sheet.</t>
+      </text>
+    </comment>
+    <comment ref="L95" authorId="0" shapeId="0">
+      <text>
+        <t>PPE closing
+FORMULA: =L92+L93-L94
+WHY: Open + CapEx − D&amp;A; closing net PP&amp;E posted to the balance sheet.</t>
+      </text>
+    </comment>
+    <comment ref="M95" authorId="0" shapeId="0">
+      <text>
+        <t>PPE closing
+FORMULA: =M92+M93-M94
+WHY: Open + CapEx − D&amp;A; closing net PP&amp;E posted to the balance sheet.</t>
+      </text>
+    </comment>
+    <comment ref="N95" authorId="0" shapeId="0">
+      <text>
+        <t>PPE closing
+FORMULA: =N92+N93-N94
+WHY: Open + CapEx − D&amp;A; closing net PP&amp;E posted to the balance sheet.</t>
+      </text>
+    </comment>
+    <comment ref="B98" authorId="0" shapeId="0">
+      <text>
+        <t>Debt opening
+WHY: Prior closing debt (FY1 opens at historical I49); base for interest and issuance.
+PATTERN: ={p}100 or I49</t>
+      </text>
+    </comment>
+    <comment ref="J98" authorId="0" shapeId="0">
+      <text>
+        <t>Debt opening
+FORMULA: =I100 or I49
+WHY: Prior closing debt (FY1 opens at historical I49); base for interest and issuance.</t>
+      </text>
+    </comment>
+    <comment ref="K98" authorId="0" shapeId="0">
+      <text>
+        <t>Debt opening
+FORMULA: =J100 or I49
+WHY: Prior closing debt (FY1 opens at historical I49); base for interest and issuance.</t>
+      </text>
+    </comment>
+    <comment ref="L98" authorId="0" shapeId="0">
+      <text>
+        <t>Debt opening
+FORMULA: =K100 or I49
+WHY: Prior closing debt (FY1 opens at historical I49); base for interest and issuance.</t>
+      </text>
+    </comment>
+    <comment ref="M98" authorId="0" shapeId="0">
+      <text>
+        <t>Debt opening
+FORMULA: =L100 or I49
+WHY: Prior closing debt (FY1 opens at historical I49); base for interest and issuance.</t>
+      </text>
+    </comment>
+    <comment ref="N98" authorId="0" shapeId="0">
+      <text>
+        <t>Debt opening
+FORMULA: =M100 or I49
+WHY: Prior closing debt (FY1 opens at historical I49); base for interest and issuance.</t>
+      </text>
+    </comment>
+    <comment ref="B99" authorId="0" shapeId="0">
+      <text>
+        <t>Debt issuance
+WHY: Links the debt policy row into the schedule; base case keeps this at zero.
+PATTERN: ={c}19</t>
+      </text>
+    </comment>
+    <comment ref="J99" authorId="0" shapeId="0">
+      <text>
+        <t>Debt issuance
+FORMULA: =J19
+WHY: Links the debt policy row into the schedule; base case keeps this at zero.</t>
+      </text>
+    </comment>
+    <comment ref="K99" authorId="0" shapeId="0">
+      <text>
+        <t>Debt issuance
+FORMULA: =K19
+WHY: Links the debt policy row into the schedule; base case keeps this at zero.</t>
+      </text>
+    </comment>
+    <comment ref="L99" authorId="0" shapeId="0">
+      <text>
+        <t>Debt issuance
+FORMULA: =L19
+WHY: Links the debt policy row into the schedule; base case keeps this at zero.</t>
+      </text>
+    </comment>
+    <comment ref="M99" authorId="0" shapeId="0">
+      <text>
+        <t>Debt issuance
+FORMULA: =M19
+WHY: Links the debt policy row into the schedule; base case keeps this at zero.</t>
+      </text>
+    </comment>
+    <comment ref="N99" authorId="0" shapeId="0">
+      <text>
+        <t>Debt issuance
+FORMULA: =N19
+WHY: Links the debt policy row into the schedule; base case keeps this at zero.</t>
+      </text>
+    </comment>
+    <comment ref="B100" authorId="0" shapeId="0">
+      <text>
+        <t>Debt closing
+WHY: Open plus issuance/(repayment); closing debt posted to the balance sheet.
+PATTERN: ={c}98+{c}99</t>
+      </text>
+    </comment>
+    <comment ref="J100" authorId="0" shapeId="0">
+      <text>
+        <t>Debt closing
+FORMULA: =J98+J99
+WHY: Open plus issuance/(repayment); closing debt posted to the balance sheet.</t>
+      </text>
+    </comment>
+    <comment ref="K100" authorId="0" shapeId="0">
+      <text>
+        <t>Debt closing
+FORMULA: =K98+K99
+WHY: Open plus issuance/(repayment); closing debt posted to the balance sheet.</t>
+      </text>
+    </comment>
+    <comment ref="L100" authorId="0" shapeId="0">
+      <text>
+        <t>Debt closing
+FORMULA: =L98+L99
+WHY: Open plus issuance/(repayment); closing debt posted to the balance sheet.</t>
+      </text>
+    </comment>
+    <comment ref="M100" authorId="0" shapeId="0">
+      <text>
+        <t>Debt closing
+FORMULA: =M98+M99
+WHY: Open plus issuance/(repayment); closing debt posted to the balance sheet.</t>
+      </text>
+    </comment>
+    <comment ref="N100" authorId="0" shapeId="0">
+      <text>
+        <t>Debt closing
+FORMULA: =N98+N99
+WHY: Open plus issuance/(repayment); closing debt posted to the balance sheet.</t>
+      </text>
+    </comment>
+    <comment ref="B101" authorId="0" shapeId="0">
+      <text>
+        <t>Interest (schedule)
+WHY: Opening debt × interest%; same economics as IS interest, from the debt schedule.
+PATTERN: ={c}98*{c}12</t>
+      </text>
+    </comment>
+    <comment ref="J101" authorId="0" shapeId="0">
+      <text>
+        <t>Interest (schedule)
+FORMULA: =J98*J12
+WHY: Opening debt × interest%; same economics as IS interest, from the debt schedule.</t>
+      </text>
+    </comment>
+    <comment ref="K101" authorId="0" shapeId="0">
+      <text>
+        <t>Interest (schedule)
+FORMULA: =K98*K12
+WHY: Opening debt × interest%; same economics as IS interest, from the debt schedule.</t>
+      </text>
+    </comment>
+    <comment ref="L101" authorId="0" shapeId="0">
+      <text>
+        <t>Interest (schedule)
+FORMULA: =L98*L12
+WHY: Opening debt × interest%; same economics as IS interest, from the debt schedule.</t>
+      </text>
+    </comment>
+    <comment ref="M101" authorId="0" shapeId="0">
+      <text>
+        <t>Interest (schedule)
+FORMULA: =M98*M12
+WHY: Opening debt × interest%; same economics as IS interest, from the debt schedule.</t>
+      </text>
+    </comment>
+    <comment ref="N101" authorId="0" shapeId="0">
+      <text>
+        <t>Interest (schedule)
+FORMULA: =N98*N12
+WHY: Opening debt × interest%; same economics as IS interest, from the debt schedule.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>vengeanceaiUSCMODEL4</author>
+  </authors>
+  <commentList>
+    <comment ref="D6" authorId="0" shapeId="0">
+      <text>
+        <t>WACC
+FORMULA: =R15
+WHY: Pulls the live CAPM WACC from the baked CAPM block so discounting uses researched Ke/Rd.</t>
+      </text>
+    </comment>
+    <comment ref="R15" authorId="0" shapeId="0">
+      <text>
+        <t>WACC CAPM
+FORMULA: =We×Ke+Wd×Rd×(1−t)
+WHY: Weighted average cost of capital from CAPM Ke and after-tax cost of debt.</t>
+      </text>
+    </comment>
+    <comment ref="E21" authorId="0" shapeId="0">
+      <text>
+        <t>EBIT
+FORMULA: GP−SGA−R&amp;D−DA
+WHY: Operating profit from 3-statement links.</t>
+      </text>
+    </comment>
+    <comment ref="F21" authorId="0" shapeId="0">
+      <text>
+        <t>EBIT
+FORMULA: GP−SGA−R&amp;D−DA
+WHY: Operating profit from 3-statement links.</t>
+      </text>
+    </comment>
+    <comment ref="G21" authorId="0" shapeId="0">
+      <text>
+        <t>EBIT
+FORMULA: GP−SGA−R&amp;D−DA
+WHY: Operating profit from 3-statement links.</t>
+      </text>
+    </comment>
+    <comment ref="H21" authorId="0" shapeId="0">
+      <text>
+        <t>EBIT
+FORMULA: GP−SGA−R&amp;D−DA
+WHY: Operating profit from 3-statement links.</t>
+      </text>
+    </comment>
+    <comment ref="I21" authorId="0" shapeId="0">
+      <text>
+        <t>EBIT
+FORMULA: GP−SGA−R&amp;D−DA
+WHY: Operating profit from 3-statement links.</t>
+      </text>
+    </comment>
+    <comment ref="E22" authorId="0" shapeId="0">
+      <text>
+        <t>Unlevered tax
+FORMULA: EBIT×t
+WHY: All-equity tax on EBIT for FCFF.</t>
+      </text>
+    </comment>
+    <comment ref="F22" authorId="0" shapeId="0">
+      <text>
+        <t>Unlevered tax
+FORMULA: EBIT×t
+WHY: All-equity tax on EBIT for FCFF.</t>
+      </text>
+    </comment>
+    <comment ref="G22" authorId="0" shapeId="0">
+      <text>
+        <t>Unlevered tax
+FORMULA: EBIT×t
+WHY: All-equity tax on EBIT for FCFF.</t>
+      </text>
+    </comment>
+    <comment ref="H22" authorId="0" shapeId="0">
+      <text>
+        <t>Unlevered tax
+FORMULA: EBIT×t
+WHY: All-equity tax on EBIT for FCFF.</t>
+      </text>
+    </comment>
+    <comment ref="I22" authorId="0" shapeId="0">
+      <text>
+        <t>Unlevered tax
+FORMULA: EBIT×t
+WHY: All-equity tax on EBIT for FCFF.</t>
+      </text>
+    </comment>
+    <comment ref="E23" authorId="0" shapeId="0">
+      <text>
+        <t>D&amp;A
+FORMULA: 3S D&amp;A
+WHY: Non-cash add-back from 3-statement.</t>
+      </text>
+    </comment>
+    <comment ref="F23" authorId="0" shapeId="0">
+      <text>
+        <t>D&amp;A
+FORMULA: 3S D&amp;A
+WHY: Non-cash add-back from 3-statement.</t>
+      </text>
+    </comment>
+    <comment ref="G23" authorId="0" shapeId="0">
+      <text>
+        <t>D&amp;A
+FORMULA: 3S D&amp;A
+WHY: Non-cash add-back from 3-statement.</t>
+      </text>
+    </comment>
+    <comment ref="H23" authorId="0" shapeId="0">
+      <text>
+        <t>D&amp;A
+FORMULA: 3S D&amp;A
+WHY: Non-cash add-back from 3-statement.</t>
+      </text>
+    </comment>
+    <comment ref="I23" authorId="0" shapeId="0">
+      <text>
+        <t>D&amp;A
+FORMULA: 3S D&amp;A
+WHY: Non-cash add-back from 3-statement.</t>
+      </text>
+    </comment>
+    <comment ref="E24" authorId="0" shapeId="0">
+      <text>
+        <t>CapEx
+FORMULA: 3S CapEx
+WHY: Reinvestment outflow from 3-statement CF.</t>
+      </text>
+    </comment>
+    <comment ref="F24" authorId="0" shapeId="0">
+      <text>
+        <t>CapEx
+FORMULA: 3S CapEx
+WHY: Reinvestment outflow from 3-statement CF.</t>
+      </text>
+    </comment>
+    <comment ref="G24" authorId="0" shapeId="0">
+      <text>
+        <t>CapEx
+FORMULA: 3S CapEx
+WHY: Reinvestment outflow from 3-statement CF.</t>
+      </text>
+    </comment>
+    <comment ref="H24" authorId="0" shapeId="0">
+      <text>
+        <t>CapEx
+FORMULA: 3S CapEx
+WHY: Reinvestment outflow from 3-statement CF.</t>
+      </text>
+    </comment>
+    <comment ref="I24" authorId="0" shapeId="0">
+      <text>
+        <t>CapEx
+FORMULA: 3S CapEx
+WHY: Reinvestment outflow from 3-statement CF.</t>
+      </text>
+    </comment>
+    <comment ref="E25" authorId="0" shapeId="0">
+      <text>
+        <t>ΔNWC
+FORMULA: 3S ΔNWC
+WHY: Working-capital investment from 3-statement.</t>
+      </text>
+    </comment>
+    <comment ref="F25" authorId="0" shapeId="0">
+      <text>
+        <t>ΔNWC
+FORMULA: 3S ΔNWC
+WHY: Working-capital investment from 3-statement.</t>
+      </text>
+    </comment>
+    <comment ref="G25" authorId="0" shapeId="0">
+      <text>
+        <t>ΔNWC
+FORMULA: 3S ΔNWC
+WHY: Working-capital investment from 3-statement.</t>
+      </text>
+    </comment>
+    <comment ref="H25" authorId="0" shapeId="0">
+      <text>
+        <t>ΔNWC
+FORMULA: 3S ΔNWC
+WHY: Working-capital investment from 3-statement.</t>
+      </text>
+    </comment>
+    <comment ref="I25" authorId="0" shapeId="0">
+      <text>
+        <t>ΔNWC
+FORMULA: 3S ΔNWC
+WHY: Working-capital investment from 3-statement.</t>
+      </text>
+    </comment>
+    <comment ref="E26" authorId="0" shapeId="0">
+      <text>
+        <t>UFCF
+FORMULA: EBIT−tax+DA−CapEx−ΔNWC
+WHY: Unlevered free cash flow discounted in DCF.</t>
+      </text>
+    </comment>
+    <comment ref="F26" authorId="0" shapeId="0">
+      <text>
+        <t>UFCF
+FORMULA: EBIT−tax+DA−CapEx−ΔNWC
+WHY: Unlevered free cash flow discounted in DCF.</t>
+      </text>
+    </comment>
+    <comment ref="G26" authorId="0" shapeId="0">
+      <text>
+        <t>UFCF
+FORMULA: EBIT−tax+DA−CapEx−ΔNWC
+WHY: Unlevered free cash flow discounted in DCF.</t>
+      </text>
+    </comment>
+    <comment ref="H26" authorId="0" shapeId="0">
+      <text>
+        <t>UFCF
+FORMULA: EBIT−tax+DA−CapEx−ΔNWC
+WHY: Unlevered free cash flow discounted in DCF.</t>
+      </text>
+    </comment>
+    <comment ref="I26" authorId="0" shapeId="0">
+      <text>
+        <t>UFCF
+FORMULA: EBIT−tax+DA−CapEx−ΔNWC
+WHY: Unlevered free cash flow discounted in DCF.</t>
+      </text>
+    </comment>
+    <comment ref="J27" authorId="0" shapeId="0">
+      <text>
+        <t>Exit TV
+FORMULA: =EBITDA_n×exit multiple
+WHY: Terminal enterprise value at year 5 using exit EV/EBITDA (primary exit method).</t>
+      </text>
+    </comment>
+    <comment ref="E28" authorId="0" shapeId="0">
+      <text>
+        <t>Transaction CF
+FORMULA: FCFF (+ TV in exit yr)
+WHY: Cash flow vector for XNPV.</t>
+      </text>
+    </comment>
+    <comment ref="F28" authorId="0" shapeId="0">
+      <text>
+        <t>Transaction CF
+FORMULA: FCFF (+ TV in exit yr)
+WHY: Cash flow vector for XNPV.</t>
+      </text>
+    </comment>
+    <comment ref="G28" authorId="0" shapeId="0">
+      <text>
+        <t>Transaction CF
+FORMULA: FCFF (+ TV in exit yr)
+WHY: Cash flow vector for XNPV.</t>
+      </text>
+    </comment>
+    <comment ref="H28" authorId="0" shapeId="0">
+      <text>
+        <t>Transaction CF
+FORMULA: FCFF (+ TV in exit yr)
+WHY: Cash flow vector for XNPV.</t>
+      </text>
+    </comment>
+    <comment ref="I28" authorId="0" shapeId="0">
+      <text>
+        <t>Transaction CF
+FORMULA: FCFF (+ TV in exit yr)
+WHY: Cash flow vector for XNPV.</t>
+      </text>
+    </comment>
+    <comment ref="D32" authorId="0" shapeId="0">
+      <text>
+        <t>Enterprise value
+FORMULA: =XNPV(WACC, CFs, mid-year dates)
+WHY: Present value of FCFF + TV using mid-year dates and the live WACC.</t>
+      </text>
+    </comment>
+    <comment ref="D35" authorId="0" shapeId="0">
+      <text>
+        <t>Equity value
+FORMULA: =EV+Cash−Debt
+WHY: Equity bridge: enterprise value plus cash minus gross debt (net debt adjustment).</t>
+      </text>
+    </comment>
+    <comment ref="D37" authorId="0" shapeId="0">
+      <text>
+        <t>Value / share
+FORMULA: =Equity/Shares
+WHY: Intrinsic equity value per share using diluted shares outstanding.</t>
       </text>
     </comment>
   </commentList>
@@ -3536,7 +6017,7 @@
   <cols>
     <col width="1.88671875" customWidth="1" style="19" min="1" max="1"/>
     <col width="42" customWidth="1" style="19" min="2" max="3"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="72" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" style="47" min="4" max="4"/>
     <col width="16" customWidth="1" style="19" min="5" max="9"/>
     <col width="16" customWidth="1" min="6" max="6"/>
@@ -10194,5 +12675,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q51" r:id="rId42"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
--- a/FICO/output/FICO_Completed_Model.xlsx
+++ b/FICO/output/FICO_Completed_Model.xlsx
@@ -100,7 +100,7 @@
     <numFmt numFmtId="178" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="179" formatCode="0.0"/>
   </numFmts>
-  <fonts count="55">
+  <fonts count="56">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -405,6 +405,12 @@
     </font>
     <font>
       <name val="Calibri"/>
+      <color rgb="000563C1"/>
+      <sz val="9"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="12"/>
@@ -628,7 +634,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="205">
+  <cellXfs count="206">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="1"/>
@@ -864,6 +870,9 @@
     <xf numFmtId="0" fontId="47" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="166" fontId="38" fillId="7" borderId="5" pivotButton="0" quotePrefix="0" xfId="2"/>
     <xf numFmtId="177" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="166" fontId="38" fillId="7" borderId="5" pivotButton="0" quotePrefix="0" xfId="1"/>
@@ -892,17 +901,17 @@
     </xf>
     <xf numFmtId="177" fontId="9" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="177" fontId="40" fillId="8" borderId="2" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="48" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="49" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="39" fillId="9" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="40" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="50" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="51" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="54" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="53" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="52" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="38" fillId="7" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
@@ -910,7 +919,7 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="40" fillId="8" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="179" fontId="40" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -918,7 +927,7 @@
     </xf>
     <xf numFmtId="2" fontId="40" fillId="8" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="178" fontId="32" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="38" fillId="7" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -935,7 +944,7 @@
     <xf numFmtId="178" fontId="38" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="177" fontId="36" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="177" fontId="37" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="54" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="55" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="174" fontId="38" fillId="7" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="177" fontId="30" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="177" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1755,84 +1764,96 @@
       <text>
         <t>Forecast year label
 WHY: Adds one year to the prior column’s fiscal-year label so forecast headers stay sequential.
-PATTERN: ={p}2+1</t>
+PATTERN: ={p}2+1
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="J2" authorId="0" shapeId="0">
       <text>
         <t>Forecast year label
 FORMULA: =I2+1
-WHY: Adds one year to the prior column’s fiscal-year label so forecast headers stay sequential.</t>
+WHY: Adds one year to the prior column’s fiscal-year label so forecast headers stay sequential.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="K2" authorId="0" shapeId="0">
       <text>
         <t>Forecast year label
 FORMULA: =J2+1
-WHY: Adds one year to the prior column’s fiscal-year label so forecast headers stay sequential.</t>
+WHY: Adds one year to the prior column’s fiscal-year label so forecast headers stay sequential.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="L2" authorId="0" shapeId="0">
       <text>
         <t>Forecast year label
 FORMULA: =K2+1
-WHY: Adds one year to the prior column’s fiscal-year label so forecast headers stay sequential.</t>
+WHY: Adds one year to the prior column’s fiscal-year label so forecast headers stay sequential.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="M2" authorId="0" shapeId="0">
       <text>
         <t>Forecast year label
 FORMULA: =L2+1
-WHY: Adds one year to the prior column’s fiscal-year label so forecast headers stay sequential.</t>
+WHY: Adds one year to the prior column’s fiscal-year label so forecast headers stay sequential.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="N2" authorId="0" shapeId="0">
       <text>
         <t>Forecast year label
 FORMULA: =M2+1
-WHY: Adds one year to the prior column’s fiscal-year label so forecast headers stay sequential.</t>
+WHY: Adds one year to the prior column’s fiscal-year label so forecast headers stay sequential.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="B3" authorId="0" shapeId="0">
       <text>
         <t>Balance sheet check
 WHY: Flags ERROR if Assets ≠ L+E by more than $1k; otherwise OK. Protects the plug.
-PATTERN: =IFERROR(IF(ABS({c}57)&gt;1,"ERROR","OK"),"OK")</t>
+PATTERN: =IFERROR(IF(ABS({c}57)&gt;1,"ERROR","OK"),"OK")
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="J3" authorId="0" shapeId="0">
       <text>
         <t>Balance sheet check
 FORMULA: =IFERROR(IF(ABS(J57)&gt;1,"ERROR","OK"),"OK")
-WHY: Flags ERROR if Assets ≠ L+E by more than $1k; otherwise OK. Protects the plug.</t>
+WHY: Flags ERROR if Assets ≠ L+E by more than $1k; otherwise OK. Protects the plug.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="K3" authorId="0" shapeId="0">
       <text>
         <t>Balance sheet check
 FORMULA: =IFERROR(IF(ABS(K57)&gt;1,"ERROR","OK"),"OK")
-WHY: Flags ERROR if Assets ≠ L+E by more than $1k; otherwise OK. Protects the plug.</t>
+WHY: Flags ERROR if Assets ≠ L+E by more than $1k; otherwise OK. Protects the plug.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="L3" authorId="0" shapeId="0">
       <text>
         <t>Balance sheet check
 FORMULA: =IFERROR(IF(ABS(L57)&gt;1,"ERROR","OK"),"OK")
-WHY: Flags ERROR if Assets ≠ L+E by more than $1k; otherwise OK. Protects the plug.</t>
+WHY: Flags ERROR if Assets ≠ L+E by more than $1k; otherwise OK. Protects the plug.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="M3" authorId="0" shapeId="0">
       <text>
         <t>Balance sheet check
 FORMULA: =IFERROR(IF(ABS(M57)&gt;1,"ERROR","OK"),"OK")
-WHY: Flags ERROR if Assets ≠ L+E by more than $1k; otherwise OK. Protects the plug.</t>
+WHY: Flags ERROR if Assets ≠ L+E by more than $1k; otherwise OK. Protects the plug.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="N3" authorId="0" shapeId="0">
       <text>
         <t>Balance sheet check
 FORMULA: =IFERROR(IF(ABS(N57)&gt;1,"ERROR","OK"),"OK")
-WHY: Flags ERROR if Assets ≠ L+E by more than $1k; otherwise OK. Protects the plug.</t>
+WHY: Flags ERROR if Assets ≠ L+E by more than $1k; otherwise OK. Protects the plug.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="B7" authorId="0" shapeId="0">
@@ -1840,7 +1861,8 @@
         <t>Revenue Growth
 HOW: Yellow POLICY input: 27% / 16% / 13% / 10% / 7%.
 WHY: Y1 ≈ company FY2026 revenue guidance (~$2.53B / FY25 $1.991B − 1 ≈ 27%). Then fade toward terminal g=3% (not straight-lined). This is the main forward-looking judgment; it drives Rev → GP → EBT → Net Earnings → CF.
-SOURCE: FICO FY2026 guidance + fade policy</t>
+SOURCE: SEC EX-99.1 Q3 FY2026 — updated FY2026 revenue guidance $2.53B
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454726000031/exhibit991erq32026.htm</t>
       </text>
     </comment>
     <comment ref="J7" authorId="0" shapeId="0">
@@ -1848,7 +1870,8 @@
         <t>Revenue Growth
 HOW: Yellow POLICY input: 27% / 16% / 13% / 10% / 7%.
 WHY: Y1 ≈ company FY2026 revenue guidance (~$2.53B / FY25 $1.991B − 1 ≈ 27%). Then fade toward terminal g=3% (not straight-lined). This is the main forward-looking judgment; it drives Rev → GP → EBT → Net Earnings → CF.
-SOURCE: FICO FY2026 guidance + fade policy</t>
+SOURCE: SEC EX-99.1 Q3 FY2026 — updated FY2026 revenue guidance $2.53B
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454726000031/exhibit991erq32026.htm</t>
       </text>
     </comment>
     <comment ref="K7" authorId="0" shapeId="0">
@@ -1856,7 +1879,8 @@
         <t>Revenue Growth
 HOW: Yellow POLICY input: 27% / 16% / 13% / 10% / 7%.
 WHY: Y1 ≈ company FY2026 revenue guidance (~$2.53B / FY25 $1.991B − 1 ≈ 27%). Then fade toward terminal g=3% (not straight-lined). This is the main forward-looking judgment; it drives Rev → GP → EBT → Net Earnings → CF.
-SOURCE: FICO FY2026 guidance + fade policy</t>
+SOURCE: SEC EX-99.1 Q3 FY2026 — updated FY2026 revenue guidance $2.53B
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454726000031/exhibit991erq32026.htm</t>
       </text>
     </comment>
     <comment ref="L7" authorId="0" shapeId="0">
@@ -1864,7 +1888,8 @@
         <t>Revenue Growth
 HOW: Yellow POLICY input: 27% / 16% / 13% / 10% / 7%.
 WHY: Y1 ≈ company FY2026 revenue guidance (~$2.53B / FY25 $1.991B − 1 ≈ 27%). Then fade toward terminal g=3% (not straight-lined). This is the main forward-looking judgment; it drives Rev → GP → EBT → Net Earnings → CF.
-SOURCE: FICO FY2026 guidance + fade policy</t>
+SOURCE: SEC EX-99.1 Q3 FY2026 — updated FY2026 revenue guidance $2.53B
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454726000031/exhibit991erq32026.htm</t>
       </text>
     </comment>
     <comment ref="M7" authorId="0" shapeId="0">
@@ -1872,7 +1897,8 @@
         <t>Revenue Growth
 HOW: Yellow POLICY input: 27% / 16% / 13% / 10% / 7%.
 WHY: Y1 ≈ company FY2026 revenue guidance (~$2.53B / FY25 $1.991B − 1 ≈ 27%). Then fade toward terminal g=3% (not straight-lined). This is the main forward-looking judgment; it drives Rev → GP → EBT → Net Earnings → CF.
-SOURCE: FICO FY2026 guidance + fade policy</t>
+SOURCE: SEC EX-99.1 Q3 FY2026 — updated FY2026 revenue guidance $2.53B
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454726000031/exhibit991erq32026.htm</t>
       </text>
     </comment>
     <comment ref="N7" authorId="0" shapeId="0">
@@ -1880,23 +1906,17 @@
         <t>Revenue Growth
 HOW: Yellow POLICY input: 27% / 16% / 13% / 10% / 7%.
 WHY: Y1 ≈ company FY2026 revenue guidance (~$2.53B / FY25 $1.991B − 1 ≈ 27%). Then fade toward terminal g=3% (not straight-lined). This is the main forward-looking judgment; it drives Rev → GP → EBT → Net Earnings → CF.
-SOURCE: FICO FY2026 guidance + fade policy</t>
-      </text>
-    </comment>
-    <comment ref="T7" authorId="0" shapeId="0">
+SOURCE: SEC EX-99.1 Q3 FY2026 — updated FY2026 revenue guidance $2.53B
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454726000031/exhibit991erq32026.htm</t>
+      </text>
+    </comment>
+    <comment ref="U7" authorId="0" shapeId="0">
       <text>
         <t>Revenue Growth
 HOW: Yellow POLICY input: 27% / 16% / 13% / 10% / 7%.
 WHY: Y1 ≈ company FY2026 revenue guidance (~$2.53B / FY25 $1.991B − 1 ≈ 27%). Then fade toward terminal g=3% (not straight-lined). This is the main forward-looking judgment; it drives Rev → GP → EBT → Net Earnings → CF.
-SOURCE: FICO FY2026 guidance + fade policy</t>
-      </text>
-    </comment>
-    <comment ref="U7" authorId="0" shapeId="0">
-      <text>
-        <t>Revenue Growth
-HOW: Yellow POLICY input: 27% / 16% / 13% / 10% / 7%.
-WHY: Y1 ≈ company FY2026 revenue guidance (~$2.53B / FY25 $1.991B − 1 ≈ 27%). Then fade toward terminal g=3% (not straight-lined). This is the main forward-looking judgment; it drives Rev → GP → EBT → Net Earnings → CF.
-SOURCE: FICO FY2026 guidance + fade policy</t>
+SOURCE: SEC EX-99.1 Q3 FY2026 — updated FY2026 revenue guidance $2.53B
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454726000031/exhibit991erq32026.htm</t>
       </text>
     </comment>
     <comment ref="B8" authorId="0" shapeId="0">
@@ -1904,7 +1924,8 @@
         <t>COGS % of Revenue
 HOW: Excel equation: I25/I24 (FY25 COGS ÷ FY25 Revenue) held flat.
 WHY: Locks in latest reported cost structure (~17.8%). Scores mix is high-margin; holding FY25 is conservative vs further mix shift.
-SOURCE: SEC 10-K FY2025 — Cost of revenues / Total revenues</t>
+SOURCE: SEC 10-K FY2025 — Cost of revenues / Total revenues
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="J8" authorId="0" shapeId="0">
@@ -1912,7 +1933,8 @@
         <t>COGS % of Revenue
 HOW: Excel equation: I25/I24 (FY25 COGS ÷ FY25 Revenue) held flat.
 WHY: Locks in latest reported cost structure (~17.8%). Scores mix is high-margin; holding FY25 is conservative vs further mix shift.
-SOURCE: SEC 10-K FY2025 — Cost of revenues / Total revenues</t>
+SOURCE: SEC 10-K FY2025 — Cost of revenues / Total revenues
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="K8" authorId="0" shapeId="0">
@@ -1920,7 +1942,8 @@
         <t>COGS % of Revenue
 HOW: Excel equation: I25/I24 (FY25 COGS ÷ FY25 Revenue) held flat.
 WHY: Locks in latest reported cost structure (~17.8%). Scores mix is high-margin; holding FY25 is conservative vs further mix shift.
-SOURCE: SEC 10-K FY2025 — Cost of revenues / Total revenues</t>
+SOURCE: SEC 10-K FY2025 — Cost of revenues / Total revenues
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="L8" authorId="0" shapeId="0">
@@ -1928,7 +1951,8 @@
         <t>COGS % of Revenue
 HOW: Excel equation: I25/I24 (FY25 COGS ÷ FY25 Revenue) held flat.
 WHY: Locks in latest reported cost structure (~17.8%). Scores mix is high-margin; holding FY25 is conservative vs further mix shift.
-SOURCE: SEC 10-K FY2025 — Cost of revenues / Total revenues</t>
+SOURCE: SEC 10-K FY2025 — Cost of revenues / Total revenues
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="M8" authorId="0" shapeId="0">
@@ -1936,7 +1960,8 @@
         <t>COGS % of Revenue
 HOW: Excel equation: I25/I24 (FY25 COGS ÷ FY25 Revenue) held flat.
 WHY: Locks in latest reported cost structure (~17.8%). Scores mix is high-margin; holding FY25 is conservative vs further mix shift.
-SOURCE: SEC 10-K FY2025 — Cost of revenues / Total revenues</t>
+SOURCE: SEC 10-K FY2025 — Cost of revenues / Total revenues
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="N8" authorId="0" shapeId="0">
@@ -1944,23 +1969,17 @@
         <t>COGS % of Revenue
 HOW: Excel equation: I25/I24 (FY25 COGS ÷ FY25 Revenue) held flat.
 WHY: Locks in latest reported cost structure (~17.8%). Scores mix is high-margin; holding FY25 is conservative vs further mix shift.
-SOURCE: SEC 10-K FY2025 — Cost of revenues / Total revenues</t>
-      </text>
-    </comment>
-    <comment ref="T8" authorId="0" shapeId="0">
+SOURCE: SEC 10-K FY2025 — Cost of revenues / Total revenues
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
+      </text>
+    </comment>
+    <comment ref="U8" authorId="0" shapeId="0">
       <text>
         <t>COGS % of Revenue
 HOW: Excel equation: I25/I24 (FY25 COGS ÷ FY25 Revenue) held flat.
 WHY: Locks in latest reported cost structure (~17.8%). Scores mix is high-margin; holding FY25 is conservative vs further mix shift.
-SOURCE: SEC 10-K FY2025 — Cost of revenues / Total revenues</t>
-      </text>
-    </comment>
-    <comment ref="U8" authorId="0" shapeId="0">
-      <text>
-        <t>COGS % of Revenue
-HOW: Excel equation: I25/I24 (FY25 COGS ÷ FY25 Revenue) held flat.
-WHY: Locks in latest reported cost structure (~17.8%). Scores mix is high-margin; holding FY25 is conservative vs further mix shift.
-SOURCE: SEC 10-K FY2025 — Cost of revenues / Total revenues</t>
+SOURCE: SEC 10-K FY2025 — Cost of revenues / Total revenues
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="B9" authorId="0" shapeId="0">
@@ -1968,7 +1987,8 @@
         <t>SGA % of Revenue
 HOW: Equation: (I28 − 10,922)/I24 − 50bps × year. Strips FY25 restructuring; then −0.5% of sales each year.
 WHY: Normalize one-time restructuring ($10.9M). Mild efficiency grind reflects operating leverage as revenue scales; floored at 5%.
-SOURCE: SEC 10-K FY2025 — SG&amp;A + restructuring note</t>
+SOURCE: SEC 10-K FY2025 — SG&amp;A + restructuring note
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="J9" authorId="0" shapeId="0">
@@ -1976,7 +1996,8 @@
         <t>SGA % of Revenue
 HOW: Equation: (I28 − 10,922)/I24 − 50bps × year. Strips FY25 restructuring; then −0.5% of sales each year.
 WHY: Normalize one-time restructuring ($10.9M). Mild efficiency grind reflects operating leverage as revenue scales; floored at 5%.
-SOURCE: SEC 10-K FY2025 — SG&amp;A + restructuring note</t>
+SOURCE: SEC 10-K FY2025 — SG&amp;A + restructuring note
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="K9" authorId="0" shapeId="0">
@@ -1984,7 +2005,8 @@
         <t>SGA % of Revenue
 HOW: Equation: (I28 − 10,922)/I24 − 50bps × year. Strips FY25 restructuring; then −0.5% of sales each year.
 WHY: Normalize one-time restructuring ($10.9M). Mild efficiency grind reflects operating leverage as revenue scales; floored at 5%.
-SOURCE: SEC 10-K FY2025 — SG&amp;A + restructuring note</t>
+SOURCE: SEC 10-K FY2025 — SG&amp;A + restructuring note
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="L9" authorId="0" shapeId="0">
@@ -1992,7 +2014,8 @@
         <t>SGA % of Revenue
 HOW: Equation: (I28 − 10,922)/I24 − 50bps × year. Strips FY25 restructuring; then −0.5% of sales each year.
 WHY: Normalize one-time restructuring ($10.9M). Mild efficiency grind reflects operating leverage as revenue scales; floored at 5%.
-SOURCE: SEC 10-K FY2025 — SG&amp;A + restructuring note</t>
+SOURCE: SEC 10-K FY2025 — SG&amp;A + restructuring note
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="M9" authorId="0" shapeId="0">
@@ -2000,7 +2023,8 @@
         <t>SGA % of Revenue
 HOW: Equation: (I28 − 10,922)/I24 − 50bps × year. Strips FY25 restructuring; then −0.5% of sales each year.
 WHY: Normalize one-time restructuring ($10.9M). Mild efficiency grind reflects operating leverage as revenue scales; floored at 5%.
-SOURCE: SEC 10-K FY2025 — SG&amp;A + restructuring note</t>
+SOURCE: SEC 10-K FY2025 — SG&amp;A + restructuring note
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="N9" authorId="0" shapeId="0">
@@ -2008,23 +2032,17 @@
         <t>SGA % of Revenue
 HOW: Equation: (I28 − 10,922)/I24 − 50bps × year. Strips FY25 restructuring; then −0.5% of sales each year.
 WHY: Normalize one-time restructuring ($10.9M). Mild efficiency grind reflects operating leverage as revenue scales; floored at 5%.
-SOURCE: SEC 10-K FY2025 — SG&amp;A + restructuring note</t>
-      </text>
-    </comment>
-    <comment ref="T9" authorId="0" shapeId="0">
+SOURCE: SEC 10-K FY2025 — SG&amp;A + restructuring note
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
+      </text>
+    </comment>
+    <comment ref="U9" authorId="0" shapeId="0">
       <text>
         <t>SGA % of Revenue
 HOW: Equation: (I28 − 10,922)/I24 − 50bps × year. Strips FY25 restructuring; then −0.5% of sales each year.
 WHY: Normalize one-time restructuring ($10.9M). Mild efficiency grind reflects operating leverage as revenue scales; floored at 5%.
-SOURCE: SEC 10-K FY2025 — SG&amp;A + restructuring note</t>
-      </text>
-    </comment>
-    <comment ref="U9" authorId="0" shapeId="0">
-      <text>
-        <t>SGA % of Revenue
-HOW: Equation: (I28 − 10,922)/I24 − 50bps × year. Strips FY25 restructuring; then −0.5% of sales each year.
-WHY: Normalize one-time restructuring ($10.9M). Mild efficiency grind reflects operating leverage as revenue scales; floored at 5%.
-SOURCE: SEC 10-K FY2025 — SG&amp;A + restructuring note</t>
+SOURCE: SEC 10-K FY2025 — SG&amp;A + restructuring note
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="B10" authorId="0" shapeId="0">
@@ -2032,7 +2050,8 @@
         <t>R&amp;D % of Revenue
 HOW: Excel equation: I29/I24 held flat (~9.46%).
 WHY: FICO reinvests steadily in analytics/software. Flat % grows dollars with revenue.
-SOURCE: SEC 10-K FY2025 — Research and development</t>
+SOURCE: SEC 10-K FY2025 — Research and development
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="J10" authorId="0" shapeId="0">
@@ -2040,7 +2059,8 @@
         <t>R&amp;D % of Revenue
 HOW: Excel equation: I29/I24 held flat (~9.46%).
 WHY: FICO reinvests steadily in analytics/software. Flat % grows dollars with revenue.
-SOURCE: SEC 10-K FY2025 — Research and development</t>
+SOURCE: SEC 10-K FY2025 — Research and development
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="K10" authorId="0" shapeId="0">
@@ -2048,7 +2068,8 @@
         <t>R&amp;D % of Revenue
 HOW: Excel equation: I29/I24 held flat (~9.46%).
 WHY: FICO reinvests steadily in analytics/software. Flat % grows dollars with revenue.
-SOURCE: SEC 10-K FY2025 — Research and development</t>
+SOURCE: SEC 10-K FY2025 — Research and development
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="L10" authorId="0" shapeId="0">
@@ -2056,7 +2077,8 @@
         <t>R&amp;D % of Revenue
 HOW: Excel equation: I29/I24 held flat (~9.46%).
 WHY: FICO reinvests steadily in analytics/software. Flat % grows dollars with revenue.
-SOURCE: SEC 10-K FY2025 — Research and development</t>
+SOURCE: SEC 10-K FY2025 — Research and development
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="M10" authorId="0" shapeId="0">
@@ -2064,7 +2086,8 @@
         <t>R&amp;D % of Revenue
 HOW: Excel equation: I29/I24 held flat (~9.46%).
 WHY: FICO reinvests steadily in analytics/software. Flat % grows dollars with revenue.
-SOURCE: SEC 10-K FY2025 — Research and development</t>
+SOURCE: SEC 10-K FY2025 — Research and development
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="N10" authorId="0" shapeId="0">
@@ -2072,23 +2095,17 @@
         <t>R&amp;D % of Revenue
 HOW: Excel equation: I29/I24 held flat (~9.46%).
 WHY: FICO reinvests steadily in analytics/software. Flat % grows dollars with revenue.
-SOURCE: SEC 10-K FY2025 — Research and development</t>
-      </text>
-    </comment>
-    <comment ref="T10" authorId="0" shapeId="0">
+SOURCE: SEC 10-K FY2025 — Research and development
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
+      </text>
+    </comment>
+    <comment ref="U10" authorId="0" shapeId="0">
       <text>
         <t>R&amp;D % of Revenue
 HOW: Excel equation: I29/I24 held flat (~9.46%).
 WHY: FICO reinvests steadily in analytics/software. Flat % grows dollars with revenue.
-SOURCE: SEC 10-K FY2025 — Research and development</t>
-      </text>
-    </comment>
-    <comment ref="U10" authorId="0" shapeId="0">
-      <text>
-        <t>R&amp;D % of Revenue
-HOW: Excel equation: I29/I24 held flat (~9.46%).
-WHY: FICO reinvests steadily in analytics/software. Flat % grows dollars with revenue.
-SOURCE: SEC 10-K FY2025 — Research and development</t>
+SOURCE: SEC 10-K FY2025 — Research and development
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="B11" authorId="0" shapeId="0">
@@ -2096,7 +2113,8 @@
         <t>D&amp;A % of PP&amp;E Open
 HOW: Excel equation: I30/I44 (FY25 DA ÷ FY25 PPE). Forecast DA = OpenPPE × this %.
 WHY: Ties DA to the asset base the schedule rolls forward (opens at I44).
-SOURCE: SEC 10-K FY2025 — D&amp;A and PP&amp;E</t>
+SOURCE: SEC 10-K FY2025 — D&amp;A and PP&amp;E
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="J11" authorId="0" shapeId="0">
@@ -2104,7 +2122,8 @@
         <t>D&amp;A % of PP&amp;E Open
 HOW: Excel equation: I30/I44 (FY25 DA ÷ FY25 PPE). Forecast DA = OpenPPE × this %.
 WHY: Ties DA to the asset base the schedule rolls forward (opens at I44).
-SOURCE: SEC 10-K FY2025 — D&amp;A and PP&amp;E</t>
+SOURCE: SEC 10-K FY2025 — D&amp;A and PP&amp;E
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="K11" authorId="0" shapeId="0">
@@ -2112,7 +2131,8 @@
         <t>D&amp;A % of PP&amp;E Open
 HOW: Excel equation: I30/I44 (FY25 DA ÷ FY25 PPE). Forecast DA = OpenPPE × this %.
 WHY: Ties DA to the asset base the schedule rolls forward (opens at I44).
-SOURCE: SEC 10-K FY2025 — D&amp;A and PP&amp;E</t>
+SOURCE: SEC 10-K FY2025 — D&amp;A and PP&amp;E
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="L11" authorId="0" shapeId="0">
@@ -2120,7 +2140,8 @@
         <t>D&amp;A % of PP&amp;E Open
 HOW: Excel equation: I30/I44 (FY25 DA ÷ FY25 PPE). Forecast DA = OpenPPE × this %.
 WHY: Ties DA to the asset base the schedule rolls forward (opens at I44).
-SOURCE: SEC 10-K FY2025 — D&amp;A and PP&amp;E</t>
+SOURCE: SEC 10-K FY2025 — D&amp;A and PP&amp;E
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="M11" authorId="0" shapeId="0">
@@ -2128,7 +2149,8 @@
         <t>D&amp;A % of PP&amp;E Open
 HOW: Excel equation: I30/I44 (FY25 DA ÷ FY25 PPE). Forecast DA = OpenPPE × this %.
 WHY: Ties DA to the asset base the schedule rolls forward (opens at I44).
-SOURCE: SEC 10-K FY2025 — D&amp;A and PP&amp;E</t>
+SOURCE: SEC 10-K FY2025 — D&amp;A and PP&amp;E
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="N11" authorId="0" shapeId="0">
@@ -2136,23 +2158,17 @@
         <t>D&amp;A % of PP&amp;E Open
 HOW: Excel equation: I30/I44 (FY25 DA ÷ FY25 PPE). Forecast DA = OpenPPE × this %.
 WHY: Ties DA to the asset base the schedule rolls forward (opens at I44).
-SOURCE: SEC 10-K FY2025 — D&amp;A and PP&amp;E</t>
-      </text>
-    </comment>
-    <comment ref="T11" authorId="0" shapeId="0">
+SOURCE: SEC 10-K FY2025 — D&amp;A and PP&amp;E
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
+      </text>
+    </comment>
+    <comment ref="U11" authorId="0" shapeId="0">
       <text>
         <t>D&amp;A % of PP&amp;E Open
 HOW: Excel equation: I30/I44 (FY25 DA ÷ FY25 PPE). Forecast DA = OpenPPE × this %.
 WHY: Ties DA to the asset base the schedule rolls forward (opens at I44).
-SOURCE: SEC 10-K FY2025 — D&amp;A and PP&amp;E</t>
-      </text>
-    </comment>
-    <comment ref="U11" authorId="0" shapeId="0">
-      <text>
-        <t>D&amp;A % of PP&amp;E Open
-HOW: Excel equation: I30/I44 (FY25 DA ÷ FY25 PPE). Forecast DA = OpenPPE × this %.
-WHY: Ties DA to the asset base the schedule rolls forward (opens at I44).
-SOURCE: SEC 10-K FY2025 — D&amp;A and PP&amp;E</t>
+SOURCE: SEC 10-K FY2025 — D&amp;A and PP&amp;E
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="B12" authorId="0" shapeId="0">
@@ -2160,7 +2176,8 @@
         <t>Interest % of Debt Open
 HOW: Excel equation: I101/I98 (FY25 interest ÷ FY25 opening debt in schedule).
 WHY: Approximates average coupon / cost of debt on the book. Debt held flat (issuance = 0), so interest stays linked to that stock.
-SOURCE: SEC 10-K FY2025 — Interest expense, net + debt footnote</t>
+SOURCE: SEC 10-K FY2025 — Interest expense; see also 8-K 6.250% notes
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="J12" authorId="0" shapeId="0">
@@ -2168,7 +2185,8 @@
         <t>Interest % of Debt Open
 HOW: Excel equation: I101/I98 (FY25 interest ÷ FY25 opening debt in schedule).
 WHY: Approximates average coupon / cost of debt on the book. Debt held flat (issuance = 0), so interest stays linked to that stock.
-SOURCE: SEC 10-K FY2025 — Interest expense, net + debt footnote</t>
+SOURCE: SEC 10-K FY2025 — Interest expense; see also 8-K 6.250% notes
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="K12" authorId="0" shapeId="0">
@@ -2176,7 +2194,8 @@
         <t>Interest % of Debt Open
 HOW: Excel equation: I101/I98 (FY25 interest ÷ FY25 opening debt in schedule).
 WHY: Approximates average coupon / cost of debt on the book. Debt held flat (issuance = 0), so interest stays linked to that stock.
-SOURCE: SEC 10-K FY2025 — Interest expense, net + debt footnote</t>
+SOURCE: SEC 10-K FY2025 — Interest expense; see also 8-K 6.250% notes
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="L12" authorId="0" shapeId="0">
@@ -2184,7 +2203,8 @@
         <t>Interest % of Debt Open
 HOW: Excel equation: I101/I98 (FY25 interest ÷ FY25 opening debt in schedule).
 WHY: Approximates average coupon / cost of debt on the book. Debt held flat (issuance = 0), so interest stays linked to that stock.
-SOURCE: SEC 10-K FY2025 — Interest expense, net + debt footnote</t>
+SOURCE: SEC 10-K FY2025 — Interest expense; see also 8-K 6.250% notes
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="M12" authorId="0" shapeId="0">
@@ -2192,7 +2212,8 @@
         <t>Interest % of Debt Open
 HOW: Excel equation: I101/I98 (FY25 interest ÷ FY25 opening debt in schedule).
 WHY: Approximates average coupon / cost of debt on the book. Debt held flat (issuance = 0), so interest stays linked to that stock.
-SOURCE: SEC 10-K FY2025 — Interest expense, net + debt footnote</t>
+SOURCE: SEC 10-K FY2025 — Interest expense; see also 8-K 6.250% notes
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="N12" authorId="0" shapeId="0">
@@ -2200,23 +2221,17 @@
         <t>Interest % of Debt Open
 HOW: Excel equation: I101/I98 (FY25 interest ÷ FY25 opening debt in schedule).
 WHY: Approximates average coupon / cost of debt on the book. Debt held flat (issuance = 0), so interest stays linked to that stock.
-SOURCE: SEC 10-K FY2025 — Interest expense, net + debt footnote</t>
-      </text>
-    </comment>
-    <comment ref="T12" authorId="0" shapeId="0">
+SOURCE: SEC 10-K FY2025 — Interest expense; see also 8-K 6.250% notes
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
+      </text>
+    </comment>
+    <comment ref="U12" authorId="0" shapeId="0">
       <text>
         <t>Interest % of Debt Open
 HOW: Excel equation: I101/I98 (FY25 interest ÷ FY25 opening debt in schedule).
 WHY: Approximates average coupon / cost of debt on the book. Debt held flat (issuance = 0), so interest stays linked to that stock.
-SOURCE: SEC 10-K FY2025 — Interest expense, net + debt footnote</t>
-      </text>
-    </comment>
-    <comment ref="U12" authorId="0" shapeId="0">
-      <text>
-        <t>Interest % of Debt Open
-HOW: Excel equation: I101/I98 (FY25 interest ÷ FY25 opening debt in schedule).
-WHY: Approximates average coupon / cost of debt on the book. Debt held flat (issuance = 0), so interest stays linked to that stock.
-SOURCE: SEC 10-K FY2025 — Interest expense, net + debt footnote</t>
+SOURCE: SEC 10-K FY2025 — Interest expense; see also 8-K 6.250% notes
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="B13" authorId="0" shapeId="0">
@@ -2224,7 +2239,8 @@
         <t>Tax Rate (% of EBT)
 HOW: Excel equation: I35/I33 (FY25 tax ÷ simplified FY25 EBT in this template).
 WHY: Uses reported effective rate (~19% on template EBT; ~18.8% on 10-K EBT). UFCF in DCF also uses unlevered EBIT × t.
-SOURCE: SEC 10-K FY2025 — Provision for income taxes / Income before taxes</t>
+SOURCE: SEC 10-K FY2025 — Provision for income taxes / Income before taxes
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="J13" authorId="0" shapeId="0">
@@ -2232,7 +2248,8 @@
         <t>Tax Rate (% of EBT)
 HOW: Excel equation: I35/I33 (FY25 tax ÷ simplified FY25 EBT in this template).
 WHY: Uses reported effective rate (~19% on template EBT; ~18.8% on 10-K EBT). UFCF in DCF also uses unlevered EBIT × t.
-SOURCE: SEC 10-K FY2025 — Provision for income taxes / Income before taxes</t>
+SOURCE: SEC 10-K FY2025 — Provision for income taxes / Income before taxes
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="K13" authorId="0" shapeId="0">
@@ -2240,7 +2257,8 @@
         <t>Tax Rate (% of EBT)
 HOW: Excel equation: I35/I33 (FY25 tax ÷ simplified FY25 EBT in this template).
 WHY: Uses reported effective rate (~19% on template EBT; ~18.8% on 10-K EBT). UFCF in DCF also uses unlevered EBIT × t.
-SOURCE: SEC 10-K FY2025 — Provision for income taxes / Income before taxes</t>
+SOURCE: SEC 10-K FY2025 — Provision for income taxes / Income before taxes
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="L13" authorId="0" shapeId="0">
@@ -2248,7 +2266,8 @@
         <t>Tax Rate (% of EBT)
 HOW: Excel equation: I35/I33 (FY25 tax ÷ simplified FY25 EBT in this template).
 WHY: Uses reported effective rate (~19% on template EBT; ~18.8% on 10-K EBT). UFCF in DCF also uses unlevered EBIT × t.
-SOURCE: SEC 10-K FY2025 — Provision for income taxes / Income before taxes</t>
+SOURCE: SEC 10-K FY2025 — Provision for income taxes / Income before taxes
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="M13" authorId="0" shapeId="0">
@@ -2256,7 +2275,8 @@
         <t>Tax Rate (% of EBT)
 HOW: Excel equation: I35/I33 (FY25 tax ÷ simplified FY25 EBT in this template).
 WHY: Uses reported effective rate (~19% on template EBT; ~18.8% on 10-K EBT). UFCF in DCF also uses unlevered EBIT × t.
-SOURCE: SEC 10-K FY2025 — Provision for income taxes / Income before taxes</t>
+SOURCE: SEC 10-K FY2025 — Provision for income taxes / Income before taxes
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="N13" authorId="0" shapeId="0">
@@ -2264,23 +2284,17 @@
         <t>Tax Rate (% of EBT)
 HOW: Excel equation: I35/I33 (FY25 tax ÷ simplified FY25 EBT in this template).
 WHY: Uses reported effective rate (~19% on template EBT; ~18.8% on 10-K EBT). UFCF in DCF also uses unlevered EBIT × t.
-SOURCE: SEC 10-K FY2025 — Provision for income taxes / Income before taxes</t>
-      </text>
-    </comment>
-    <comment ref="T13" authorId="0" shapeId="0">
+SOURCE: SEC 10-K FY2025 — Provision for income taxes / Income before taxes
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
+      </text>
+    </comment>
+    <comment ref="U13" authorId="0" shapeId="0">
       <text>
         <t>Tax Rate (% of EBT)
 HOW: Excel equation: I35/I33 (FY25 tax ÷ simplified FY25 EBT in this template).
 WHY: Uses reported effective rate (~19% on template EBT; ~18.8% on 10-K EBT). UFCF in DCF also uses unlevered EBIT × t.
-SOURCE: SEC 10-K FY2025 — Provision for income taxes / Income before taxes</t>
-      </text>
-    </comment>
-    <comment ref="U13" authorId="0" shapeId="0">
-      <text>
-        <t>Tax Rate (% of EBT)
-HOW: Excel equation: I35/I33 (FY25 tax ÷ simplified FY25 EBT in this template).
-WHY: Uses reported effective rate (~19% on template EBT; ~18.8% on 10-K EBT). UFCF in DCF also uses unlevered EBIT × t.
-SOURCE: SEC 10-K FY2025 — Provision for income taxes / Income before taxes</t>
+SOURCE: SEC 10-K FY2025 — Provision for income taxes / Income before taxes
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="B15" authorId="0" shapeId="0">
@@ -2288,7 +2302,8 @@
         <t>Accounts Receivable (Days)
 HOW: Excel equation: ROUND(I42/I24×365, 0). I42 is net AR (AR − deferred).
 WHY: Operating working-capital view: contract liabilities (deferred revenue) reduce net AR so ΔNWC is not overstated.
-SOURCE: SEC 10-K — AR; DeferredRevenueCurrent (XBRL)</t>
+SOURCE: SEC companyfacts XBRL — AR + DeferredRevenueCurrent
+LINK: https://data.sec.gov/api/xbrl/companyfacts/CIK0000814547.json</t>
       </text>
     </comment>
     <comment ref="J15" authorId="0" shapeId="0">
@@ -2296,7 +2311,8 @@
         <t>Accounts Receivable (Days)
 HOW: Excel equation: ROUND(I42/I24×365, 0). I42 is net AR (AR − deferred).
 WHY: Operating working-capital view: contract liabilities (deferred revenue) reduce net AR so ΔNWC is not overstated.
-SOURCE: SEC 10-K — AR; DeferredRevenueCurrent (XBRL)</t>
+SOURCE: SEC companyfacts XBRL — AR + DeferredRevenueCurrent
+LINK: https://data.sec.gov/api/xbrl/companyfacts/CIK0000814547.json</t>
       </text>
     </comment>
     <comment ref="K15" authorId="0" shapeId="0">
@@ -2304,7 +2320,8 @@
         <t>Accounts Receivable (Days)
 HOW: Excel equation: ROUND(I42/I24×365, 0). I42 is net AR (AR − deferred).
 WHY: Operating working-capital view: contract liabilities (deferred revenue) reduce net AR so ΔNWC is not overstated.
-SOURCE: SEC 10-K — AR; DeferredRevenueCurrent (XBRL)</t>
+SOURCE: SEC companyfacts XBRL — AR + DeferredRevenueCurrent
+LINK: https://data.sec.gov/api/xbrl/companyfacts/CIK0000814547.json</t>
       </text>
     </comment>
     <comment ref="L15" authorId="0" shapeId="0">
@@ -2312,7 +2329,8 @@
         <t>Accounts Receivable (Days)
 HOW: Excel equation: ROUND(I42/I24×365, 0). I42 is net AR (AR − deferred).
 WHY: Operating working-capital view: contract liabilities (deferred revenue) reduce net AR so ΔNWC is not overstated.
-SOURCE: SEC 10-K — AR; DeferredRevenueCurrent (XBRL)</t>
+SOURCE: SEC companyfacts XBRL — AR + DeferredRevenueCurrent
+LINK: https://data.sec.gov/api/xbrl/companyfacts/CIK0000814547.json</t>
       </text>
     </comment>
     <comment ref="M15" authorId="0" shapeId="0">
@@ -2320,7 +2338,8 @@
         <t>Accounts Receivable (Days)
 HOW: Excel equation: ROUND(I42/I24×365, 0). I42 is net AR (AR − deferred).
 WHY: Operating working-capital view: contract liabilities (deferred revenue) reduce net AR so ΔNWC is not overstated.
-SOURCE: SEC 10-K — AR; DeferredRevenueCurrent (XBRL)</t>
+SOURCE: SEC companyfacts XBRL — AR + DeferredRevenueCurrent
+LINK: https://data.sec.gov/api/xbrl/companyfacts/CIK0000814547.json</t>
       </text>
     </comment>
     <comment ref="N15" authorId="0" shapeId="0">
@@ -2328,23 +2347,17 @@
         <t>Accounts Receivable (Days)
 HOW: Excel equation: ROUND(I42/I24×365, 0). I42 is net AR (AR − deferred).
 WHY: Operating working-capital view: contract liabilities (deferred revenue) reduce net AR so ΔNWC is not overstated.
-SOURCE: SEC 10-K — AR; DeferredRevenueCurrent (XBRL)</t>
-      </text>
-    </comment>
-    <comment ref="T15" authorId="0" shapeId="0">
+SOURCE: SEC companyfacts XBRL — AR + DeferredRevenueCurrent
+LINK: https://data.sec.gov/api/xbrl/companyfacts/CIK0000814547.json</t>
+      </text>
+    </comment>
+    <comment ref="U15" authorId="0" shapeId="0">
       <text>
         <t>Accounts Receivable (Days)
 HOW: Excel equation: ROUND(I42/I24×365, 0). I42 is net AR (AR − deferred).
 WHY: Operating working-capital view: contract liabilities (deferred revenue) reduce net AR so ΔNWC is not overstated.
-SOURCE: SEC 10-K — AR; DeferredRevenueCurrent (XBRL)</t>
-      </text>
-    </comment>
-    <comment ref="U15" authorId="0" shapeId="0">
-      <text>
-        <t>Accounts Receivable (Days)
-HOW: Excel equation: ROUND(I42/I24×365, 0). I42 is net AR (AR − deferred).
-WHY: Operating working-capital view: contract liabilities (deferred revenue) reduce net AR so ΔNWC is not overstated.
-SOURCE: SEC 10-K — AR; DeferredRevenueCurrent (XBRL)</t>
+SOURCE: SEC companyfacts XBRL — AR + DeferredRevenueCurrent
+LINK: https://data.sec.gov/api/xbrl/companyfacts/CIK0000814547.json</t>
       </text>
     </comment>
     <comment ref="B16" authorId="0" shapeId="0">
@@ -2352,7 +2365,8 @@
         <t>Inventory (Days)
 HOW: Hard zero — FICO is software / scores; inventory is immaterial.
 WHY: No inventory cycle to fund.
-SOURCE: SEC 10-K — Inventory ≈ $0</t>
+SOURCE: SEC 10-K FY2025 — Inventory ≈ $0
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="J16" authorId="0" shapeId="0">
@@ -2360,7 +2374,8 @@
         <t>Inventory (Days)
 HOW: Hard zero — FICO is software / scores; inventory is immaterial.
 WHY: No inventory cycle to fund.
-SOURCE: SEC 10-K — Inventory ≈ $0</t>
+SOURCE: SEC 10-K FY2025 — Inventory ≈ $0
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="K16" authorId="0" shapeId="0">
@@ -2368,7 +2383,8 @@
         <t>Inventory (Days)
 HOW: Hard zero — FICO is software / scores; inventory is immaterial.
 WHY: No inventory cycle to fund.
-SOURCE: SEC 10-K — Inventory ≈ $0</t>
+SOURCE: SEC 10-K FY2025 — Inventory ≈ $0
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="L16" authorId="0" shapeId="0">
@@ -2376,7 +2392,8 @@
         <t>Inventory (Days)
 HOW: Hard zero — FICO is software / scores; inventory is immaterial.
 WHY: No inventory cycle to fund.
-SOURCE: SEC 10-K — Inventory ≈ $0</t>
+SOURCE: SEC 10-K FY2025 — Inventory ≈ $0
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="M16" authorId="0" shapeId="0">
@@ -2384,7 +2401,8 @@
         <t>Inventory (Days)
 HOW: Hard zero — FICO is software / scores; inventory is immaterial.
 WHY: No inventory cycle to fund.
-SOURCE: SEC 10-K — Inventory ≈ $0</t>
+SOURCE: SEC 10-K FY2025 — Inventory ≈ $0
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="N16" authorId="0" shapeId="0">
@@ -2392,23 +2410,17 @@
         <t>Inventory (Days)
 HOW: Hard zero — FICO is software / scores; inventory is immaterial.
 WHY: No inventory cycle to fund.
-SOURCE: SEC 10-K — Inventory ≈ $0</t>
-      </text>
-    </comment>
-    <comment ref="T16" authorId="0" shapeId="0">
+SOURCE: SEC 10-K FY2025 — Inventory ≈ $0
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
+      </text>
+    </comment>
+    <comment ref="U16" authorId="0" shapeId="0">
       <text>
         <t>Inventory (Days)
 HOW: Hard zero — FICO is software / scores; inventory is immaterial.
 WHY: No inventory cycle to fund.
-SOURCE: SEC 10-K — Inventory ≈ $0</t>
-      </text>
-    </comment>
-    <comment ref="U16" authorId="0" shapeId="0">
-      <text>
-        <t>Inventory (Days)
-HOW: Hard zero — FICO is software / scores; inventory is immaterial.
-WHY: No inventory cycle to fund.
-SOURCE: SEC 10-K — Inventory ≈ $0</t>
+SOURCE: SEC 10-K FY2025 — Inventory ≈ $0
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="B17" authorId="0" shapeId="0">
@@ -2416,7 +2428,8 @@
         <t>Accounts Payable (Days)
 HOW: Excel equation: ROUND(I48/I25×365, 0) from FY25.
 WHY: Payable timing offsets AR in operating NWC.
-SOURCE: SEC 10-K FY2025 — Accounts payable</t>
+SOURCE: SEC 10-K FY2025 — Accounts payable
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="J17" authorId="0" shapeId="0">
@@ -2424,7 +2437,8 @@
         <t>Accounts Payable (Days)
 HOW: Excel equation: ROUND(I48/I25×365, 0) from FY25.
 WHY: Payable timing offsets AR in operating NWC.
-SOURCE: SEC 10-K FY2025 — Accounts payable</t>
+SOURCE: SEC 10-K FY2025 — Accounts payable
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="K17" authorId="0" shapeId="0">
@@ -2432,7 +2446,8 @@
         <t>Accounts Payable (Days)
 HOW: Excel equation: ROUND(I48/I25×365, 0) from FY25.
 WHY: Payable timing offsets AR in operating NWC.
-SOURCE: SEC 10-K FY2025 — Accounts payable</t>
+SOURCE: SEC 10-K FY2025 — Accounts payable
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="L17" authorId="0" shapeId="0">
@@ -2440,7 +2455,8 @@
         <t>Accounts Payable (Days)
 HOW: Excel equation: ROUND(I48/I25×365, 0) from FY25.
 WHY: Payable timing offsets AR in operating NWC.
-SOURCE: SEC 10-K FY2025 — Accounts payable</t>
+SOURCE: SEC 10-K FY2025 — Accounts payable
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="M17" authorId="0" shapeId="0">
@@ -2448,7 +2464,8 @@
         <t>Accounts Payable (Days)
 HOW: Excel equation: ROUND(I48/I25×365, 0) from FY25.
 WHY: Payable timing offsets AR in operating NWC.
-SOURCE: SEC 10-K FY2025 — Accounts payable</t>
+SOURCE: SEC 10-K FY2025 — Accounts payable
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="N17" authorId="0" shapeId="0">
@@ -2456,23 +2473,17 @@
         <t>Accounts Payable (Days)
 HOW: Excel equation: ROUND(I48/I25×365, 0) from FY25.
 WHY: Payable timing offsets AR in operating NWC.
-SOURCE: SEC 10-K FY2025 — Accounts payable</t>
-      </text>
-    </comment>
-    <comment ref="T17" authorId="0" shapeId="0">
+SOURCE: SEC 10-K FY2025 — Accounts payable
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
+      </text>
+    </comment>
+    <comment ref="U17" authorId="0" shapeId="0">
       <text>
         <t>Accounts Payable (Days)
 HOW: Excel equation: ROUND(I48/I25×365, 0) from FY25.
 WHY: Payable timing offsets AR in operating NWC.
-SOURCE: SEC 10-K FY2025 — Accounts payable</t>
-      </text>
-    </comment>
-    <comment ref="U17" authorId="0" shapeId="0">
-      <text>
-        <t>Accounts Payable (Days)
-HOW: Excel equation: ROUND(I48/I25×365, 0) from FY25.
-WHY: Payable timing offsets AR in operating NWC.
-SOURCE: SEC 10-K FY2025 — Accounts payable</t>
+SOURCE: SEC 10-K FY2025 — Accounts payable
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="B18" authorId="0" shapeId="0">
@@ -2480,7 +2491,8 @@
         <t>CapEx % of Revenue
 HOW: Equation: fade from I68/I24 (FY25 CapEx/Sales ~1.98%) toward 1.0% steady. Weights 85%→65%→45%→30%→0% on the peak.
 WHY: FY25 CapEx was elevated by capitalized internal-use software. Fading avoids locking a peak reinvestment rate forever.
-SOURCE: SEC 10-K — PP&amp;E purchases + capitalized software</t>
+SOURCE: SEC 10-K FY2025 — PP&amp;E purchases + capitalized software
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="J18" authorId="0" shapeId="0">
@@ -2488,7 +2500,8 @@
         <t>CapEx % of Revenue
 HOW: Equation: fade from I68/I24 (FY25 CapEx/Sales ~1.98%) toward 1.0% steady. Weights 85%→65%→45%→30%→0% on the peak.
 WHY: FY25 CapEx was elevated by capitalized internal-use software. Fading avoids locking a peak reinvestment rate forever.
-SOURCE: SEC 10-K — PP&amp;E purchases + capitalized software</t>
+SOURCE: SEC 10-K FY2025 — PP&amp;E purchases + capitalized software
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="K18" authorId="0" shapeId="0">
@@ -2496,7 +2509,8 @@
         <t>CapEx % of Revenue
 HOW: Equation: fade from I68/I24 (FY25 CapEx/Sales ~1.98%) toward 1.0% steady. Weights 85%→65%→45%→30%→0% on the peak.
 WHY: FY25 CapEx was elevated by capitalized internal-use software. Fading avoids locking a peak reinvestment rate forever.
-SOURCE: SEC 10-K — PP&amp;E purchases + capitalized software</t>
+SOURCE: SEC 10-K FY2025 — PP&amp;E purchases + capitalized software
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="L18" authorId="0" shapeId="0">
@@ -2504,7 +2518,8 @@
         <t>CapEx % of Revenue
 HOW: Equation: fade from I68/I24 (FY25 CapEx/Sales ~1.98%) toward 1.0% steady. Weights 85%→65%→45%→30%→0% on the peak.
 WHY: FY25 CapEx was elevated by capitalized internal-use software. Fading avoids locking a peak reinvestment rate forever.
-SOURCE: SEC 10-K — PP&amp;E purchases + capitalized software</t>
+SOURCE: SEC 10-K FY2025 — PP&amp;E purchases + capitalized software
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="M18" authorId="0" shapeId="0">
@@ -2512,7 +2527,8 @@
         <t>CapEx % of Revenue
 HOW: Equation: fade from I68/I24 (FY25 CapEx/Sales ~1.98%) toward 1.0% steady. Weights 85%→65%→45%→30%→0% on the peak.
 WHY: FY25 CapEx was elevated by capitalized internal-use software. Fading avoids locking a peak reinvestment rate forever.
-SOURCE: SEC 10-K — PP&amp;E purchases + capitalized software</t>
+SOURCE: SEC 10-K FY2025 — PP&amp;E purchases + capitalized software
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="N18" authorId="0" shapeId="0">
@@ -2520,23 +2536,17 @@
         <t>CapEx % of Revenue
 HOW: Equation: fade from I68/I24 (FY25 CapEx/Sales ~1.98%) toward 1.0% steady. Weights 85%→65%→45%→30%→0% on the peak.
 WHY: FY25 CapEx was elevated by capitalized internal-use software. Fading avoids locking a peak reinvestment rate forever.
-SOURCE: SEC 10-K — PP&amp;E purchases + capitalized software</t>
-      </text>
-    </comment>
-    <comment ref="T18" authorId="0" shapeId="0">
+SOURCE: SEC 10-K FY2025 — PP&amp;E purchases + capitalized software
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
+      </text>
+    </comment>
+    <comment ref="U18" authorId="0" shapeId="0">
       <text>
         <t>CapEx % of Revenue
 HOW: Equation: fade from I68/I24 (FY25 CapEx/Sales ~1.98%) toward 1.0% steady. Weights 85%→65%→45%→30%→0% on the peak.
 WHY: FY25 CapEx was elevated by capitalized internal-use software. Fading avoids locking a peak reinvestment rate forever.
-SOURCE: SEC 10-K — PP&amp;E purchases + capitalized software</t>
-      </text>
-    </comment>
-    <comment ref="U18" authorId="0" shapeId="0">
-      <text>
-        <t>CapEx % of Revenue
-HOW: Equation: fade from I68/I24 (FY25 CapEx/Sales ~1.98%) toward 1.0% steady. Weights 85%→65%→45%→30%→0% on the peak.
-WHY: FY25 CapEx was elevated by capitalized internal-use software. Fading avoids locking a peak reinvestment rate forever.
-SOURCE: SEC 10-K — PP&amp;E purchases + capitalized software</t>
+SOURCE: SEC 10-K FY2025 — PP&amp;E purchases + capitalized software
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="B19" authorId="0" shapeId="0">
@@ -2544,7 +2554,8 @@
         <t>Debt Issuance (Repayment)
 HOW: POLICY input = 0 every year.
 WHY: Hold debt stock flat at FY25 level for the explicit period; interest follows. Net debt for DCF equity bridge uses the later 10-Q amount separately.
-SOURCE: Modeling choice (financing not in FCFF)</t>
+SOURCE: SEC 10-Q Q3 FY2026 — debt stock (financing excluded from FCFF)
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454726000030/fico-20260630.htm</t>
       </text>
     </comment>
     <comment ref="J19" authorId="0" shapeId="0">
@@ -2552,7 +2563,8 @@
         <t>Debt Issuance (Repayment)
 HOW: POLICY input = 0 every year.
 WHY: Hold debt stock flat at FY25 level for the explicit period; interest follows. Net debt for DCF equity bridge uses the later 10-Q amount separately.
-SOURCE: Modeling choice (financing not in FCFF)</t>
+SOURCE: SEC 10-Q Q3 FY2026 — debt stock (financing excluded from FCFF)
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454726000030/fico-20260630.htm</t>
       </text>
     </comment>
     <comment ref="K19" authorId="0" shapeId="0">
@@ -2560,7 +2572,8 @@
         <t>Debt Issuance (Repayment)
 HOW: POLICY input = 0 every year.
 WHY: Hold debt stock flat at FY25 level for the explicit period; interest follows. Net debt for DCF equity bridge uses the later 10-Q amount separately.
-SOURCE: Modeling choice (financing not in FCFF)</t>
+SOURCE: SEC 10-Q Q3 FY2026 — debt stock (financing excluded from FCFF)
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454726000030/fico-20260630.htm</t>
       </text>
     </comment>
     <comment ref="L19" authorId="0" shapeId="0">
@@ -2568,7 +2581,8 @@
         <t>Debt Issuance (Repayment)
 HOW: POLICY input = 0 every year.
 WHY: Hold debt stock flat at FY25 level for the explicit period; interest follows. Net debt for DCF equity bridge uses the later 10-Q amount separately.
-SOURCE: Modeling choice (financing not in FCFF)</t>
+SOURCE: SEC 10-Q Q3 FY2026 — debt stock (financing excluded from FCFF)
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454726000030/fico-20260630.htm</t>
       </text>
     </comment>
     <comment ref="M19" authorId="0" shapeId="0">
@@ -2576,7 +2590,8 @@
         <t>Debt Issuance (Repayment)
 HOW: POLICY input = 0 every year.
 WHY: Hold debt stock flat at FY25 level for the explicit period; interest follows. Net debt for DCF equity bridge uses the later 10-Q amount separately.
-SOURCE: Modeling choice (financing not in FCFF)</t>
+SOURCE: SEC 10-Q Q3 FY2026 — debt stock (financing excluded from FCFF)
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454726000030/fico-20260630.htm</t>
       </text>
     </comment>
     <comment ref="N19" authorId="0" shapeId="0">
@@ -2584,23 +2599,17 @@
         <t>Debt Issuance (Repayment)
 HOW: POLICY input = 0 every year.
 WHY: Hold debt stock flat at FY25 level for the explicit period; interest follows. Net debt for DCF equity bridge uses the later 10-Q amount separately.
-SOURCE: Modeling choice (financing not in FCFF)</t>
-      </text>
-    </comment>
-    <comment ref="T19" authorId="0" shapeId="0">
+SOURCE: SEC 10-Q Q3 FY2026 — debt stock (financing excluded from FCFF)
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454726000030/fico-20260630.htm</t>
+      </text>
+    </comment>
+    <comment ref="U19" authorId="0" shapeId="0">
       <text>
         <t>Debt Issuance (Repayment)
 HOW: POLICY input = 0 every year.
 WHY: Hold debt stock flat at FY25 level for the explicit period; interest follows. Net debt for DCF equity bridge uses the later 10-Q amount separately.
-SOURCE: Modeling choice (financing not in FCFF)</t>
-      </text>
-    </comment>
-    <comment ref="U19" authorId="0" shapeId="0">
-      <text>
-        <t>Debt Issuance (Repayment)
-HOW: POLICY input = 0 every year.
-WHY: Hold debt stock flat at FY25 level for the explicit period; interest follows. Net debt for DCF equity bridge uses the later 10-Q amount separately.
-SOURCE: Modeling choice (financing not in FCFF)</t>
+SOURCE: SEC 10-Q Q3 FY2026 — debt stock (financing excluded from FCFF)
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454726000030/fico-20260630.htm</t>
       </text>
     </comment>
     <comment ref="B20" authorId="0" shapeId="0">
@@ -2608,7 +2617,8 @@
         <t>Equity Issued (Repaid)
 HOW: POLICY input = 0 every year.
 WHY: Buybacks are real historically but are financing — excluded from FCFF. Share count for $/share is the spot shares outstanding assumption.
-SOURCE: Modeling choice (financing not in FCFF)</t>
+SOURCE: Damodaran FCFF framework — financing (buybacks) not in FCFF
+LINK: https://pages.stern.nyu.edu/~adamodar/New_Home_Page/datafile/histfcff.html</t>
       </text>
     </comment>
     <comment ref="J20" authorId="0" shapeId="0">
@@ -2616,7 +2626,8 @@
         <t>Equity Issued (Repaid)
 HOW: POLICY input = 0 every year.
 WHY: Buybacks are real historically but are financing — excluded from FCFF. Share count for $/share is the spot shares outstanding assumption.
-SOURCE: Modeling choice (financing not in FCFF)</t>
+SOURCE: Damodaran FCFF framework — financing (buybacks) not in FCFF
+LINK: https://pages.stern.nyu.edu/~adamodar/New_Home_Page/datafile/histfcff.html</t>
       </text>
     </comment>
     <comment ref="K20" authorId="0" shapeId="0">
@@ -2624,7 +2635,8 @@
         <t>Equity Issued (Repaid)
 HOW: POLICY input = 0 every year.
 WHY: Buybacks are real historically but are financing — excluded from FCFF. Share count for $/share is the spot shares outstanding assumption.
-SOURCE: Modeling choice (financing not in FCFF)</t>
+SOURCE: Damodaran FCFF framework — financing (buybacks) not in FCFF
+LINK: https://pages.stern.nyu.edu/~adamodar/New_Home_Page/datafile/histfcff.html</t>
       </text>
     </comment>
     <comment ref="L20" authorId="0" shapeId="0">
@@ -2632,7 +2644,8 @@
         <t>Equity Issued (Repaid)
 HOW: POLICY input = 0 every year.
 WHY: Buybacks are real historically but are financing — excluded from FCFF. Share count for $/share is the spot shares outstanding assumption.
-SOURCE: Modeling choice (financing not in FCFF)</t>
+SOURCE: Damodaran FCFF framework — financing (buybacks) not in FCFF
+LINK: https://pages.stern.nyu.edu/~adamodar/New_Home_Page/datafile/histfcff.html</t>
       </text>
     </comment>
     <comment ref="M20" authorId="0" shapeId="0">
@@ -2640,7 +2653,8 @@
         <t>Equity Issued (Repaid)
 HOW: POLICY input = 0 every year.
 WHY: Buybacks are real historically but are financing — excluded from FCFF. Share count for $/share is the spot shares outstanding assumption.
-SOURCE: Modeling choice (financing not in FCFF)</t>
+SOURCE: Damodaran FCFF framework — financing (buybacks) not in FCFF
+LINK: https://pages.stern.nyu.edu/~adamodar/New_Home_Page/datafile/histfcff.html</t>
       </text>
     </comment>
     <comment ref="N20" authorId="0" shapeId="0">
@@ -2648,2123 +2662,2417 @@
         <t>Equity Issued (Repaid)
 HOW: POLICY input = 0 every year.
 WHY: Buybacks are real historically but are financing — excluded from FCFF. Share count for $/share is the spot shares outstanding assumption.
-SOURCE: Modeling choice (financing not in FCFF)</t>
-      </text>
-    </comment>
-    <comment ref="T20" authorId="0" shapeId="0">
+SOURCE: Damodaran FCFF framework — financing (buybacks) not in FCFF
+LINK: https://pages.stern.nyu.edu/~adamodar/New_Home_Page/datafile/histfcff.html</t>
+      </text>
+    </comment>
+    <comment ref="U20" authorId="0" shapeId="0">
       <text>
         <t>Equity Issued (Repaid)
 HOW: POLICY input = 0 every year.
 WHY: Buybacks are real historically but are financing — excluded from FCFF. Share count for $/share is the spot shares outstanding assumption.
-SOURCE: Modeling choice (financing not in FCFF)</t>
-      </text>
-    </comment>
-    <comment ref="U20" authorId="0" shapeId="0">
-      <text>
-        <t>Equity Issued (Repaid)
-HOW: POLICY input = 0 every year.
-WHY: Buybacks are real historically but are financing — excluded from FCFF. Share count for $/share is the spot shares outstanding assumption.
-SOURCE: Modeling choice (financing not in FCFF)</t>
+SOURCE: Damodaran FCFF framework — financing (buybacks) not in FCFF
+LINK: https://pages.stern.nyu.edu/~adamodar/New_Home_Page/datafile/histfcff.html</t>
       </text>
     </comment>
     <comment ref="B24" authorId="0" shapeId="0">
       <text>
         <t>Revenue
 WHY: Prior-year revenue grown by this year’s policy growth rate; top-line driver of the model.
-PATTERN: ={p}24*(1+{c}7)</t>
+PATTERN: ={p}24*(1+{c}7)
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454726000031/exhibit991erq32026.htm</t>
       </text>
     </comment>
     <comment ref="J24" authorId="0" shapeId="0">
       <text>
         <t>Revenue
 FORMULA: =I24*(1+J7)
-WHY: Prior-year revenue grown by this year’s policy growth rate; top-line driver of the model.</t>
+WHY: Prior-year revenue grown by this year’s policy growth rate; top-line driver of the model.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454726000031/exhibit991erq32026.htm</t>
       </text>
     </comment>
     <comment ref="K24" authorId="0" shapeId="0">
       <text>
         <t>Revenue
 FORMULA: =J24*(1+K7)
-WHY: Prior-year revenue grown by this year’s policy growth rate; top-line driver of the model.</t>
+WHY: Prior-year revenue grown by this year’s policy growth rate; top-line driver of the model.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454726000031/exhibit991erq32026.htm</t>
       </text>
     </comment>
     <comment ref="L24" authorId="0" shapeId="0">
       <text>
         <t>Revenue
 FORMULA: =K24*(1+L7)
-WHY: Prior-year revenue grown by this year’s policy growth rate; top-line driver of the model.</t>
+WHY: Prior-year revenue grown by this year’s policy growth rate; top-line driver of the model.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454726000031/exhibit991erq32026.htm</t>
       </text>
     </comment>
     <comment ref="M24" authorId="0" shapeId="0">
       <text>
         <t>Revenue
 FORMULA: =L24*(1+M7)
-WHY: Prior-year revenue grown by this year’s policy growth rate; top-line driver of the model.</t>
+WHY: Prior-year revenue grown by this year’s policy growth rate; top-line driver of the model.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454726000031/exhibit991erq32026.htm</t>
       </text>
     </comment>
     <comment ref="N24" authorId="0" shapeId="0">
       <text>
         <t>Revenue
 FORMULA: =M24*(1+N7)
-WHY: Prior-year revenue grown by this year’s policy growth rate; top-line driver of the model.</t>
+WHY: Prior-year revenue grown by this year’s policy growth rate; top-line driver of the model.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454726000031/exhibit991erq32026.htm</t>
       </text>
     </comment>
     <comment ref="B25" authorId="0" shapeId="0">
       <text>
         <t>COGS $
 WHY: Revenue times COGS%; converts the held margin assumption into dollar cost of sales.
-PATTERN: ={c}24*{c}8</t>
+PATTERN: ={c}24*{c}8
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="J25" authorId="0" shapeId="0">
       <text>
         <t>COGS $
 FORMULA: =J24*J8
-WHY: Revenue times COGS%; converts the held margin assumption into dollar cost of sales.</t>
+WHY: Revenue times COGS%; converts the held margin assumption into dollar cost of sales.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="K25" authorId="0" shapeId="0">
       <text>
         <t>COGS $
 FORMULA: =K24*K8
-WHY: Revenue times COGS%; converts the held margin assumption into dollar cost of sales.</t>
+WHY: Revenue times COGS%; converts the held margin assumption into dollar cost of sales.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="L25" authorId="0" shapeId="0">
       <text>
         <t>COGS $
 FORMULA: =L24*L8
-WHY: Revenue times COGS%; converts the held margin assumption into dollar cost of sales.</t>
+WHY: Revenue times COGS%; converts the held margin assumption into dollar cost of sales.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="M25" authorId="0" shapeId="0">
       <text>
         <t>COGS $
 FORMULA: =M24*M8
-WHY: Revenue times COGS%; converts the held margin assumption into dollar cost of sales.</t>
+WHY: Revenue times COGS%; converts the held margin assumption into dollar cost of sales.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="N25" authorId="0" shapeId="0">
       <text>
         <t>COGS $
 FORMULA: =N24*N8
-WHY: Revenue times COGS%; converts the held margin assumption into dollar cost of sales.</t>
+WHY: Revenue times COGS%; converts the held margin assumption into dollar cost of sales.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="B26" authorId="0" shapeId="0">
       <text>
         <t>Gross profit
 WHY: Revenue minus COGS; contribution after direct cost of revenues before operating expenses.
-PATTERN: ={c}24-{c}25</t>
+PATTERN: ={c}24-{c}25
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="J26" authorId="0" shapeId="0">
       <text>
         <t>Gross profit
 FORMULA: =J24-J25
-WHY: Revenue minus COGS; contribution after direct cost of revenues before operating expenses.</t>
+WHY: Revenue minus COGS; contribution after direct cost of revenues before operating expenses.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="K26" authorId="0" shapeId="0">
       <text>
         <t>Gross profit
 FORMULA: =K24-K25
-WHY: Revenue minus COGS; contribution after direct cost of revenues before operating expenses.</t>
+WHY: Revenue minus COGS; contribution after direct cost of revenues before operating expenses.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="L26" authorId="0" shapeId="0">
       <text>
         <t>Gross profit
 FORMULA: =L24-L25
-WHY: Revenue minus COGS; contribution after direct cost of revenues before operating expenses.</t>
+WHY: Revenue minus COGS; contribution after direct cost of revenues before operating expenses.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="M26" authorId="0" shapeId="0">
       <text>
         <t>Gross profit
 FORMULA: =M24-M25
-WHY: Revenue minus COGS; contribution after direct cost of revenues before operating expenses.</t>
+WHY: Revenue minus COGS; contribution after direct cost of revenues before operating expenses.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="N26" authorId="0" shapeId="0">
       <text>
         <t>Gross profit
 FORMULA: =N24-N25
-WHY: Revenue minus COGS; contribution after direct cost of revenues before operating expenses.</t>
+WHY: Revenue minus COGS; contribution after direct cost of revenues before operating expenses.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="B28" authorId="0" shapeId="0">
       <text>
         <t>SGA $
 WHY: Revenue times SGA%; salaries/benefits dollars after the efficiency grind on the rate.
-PATTERN: ={c}24*{c}9</t>
+PATTERN: ={c}24*{c}9
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="J28" authorId="0" shapeId="0">
       <text>
         <t>SGA $
 FORMULA: =J24*J9
-WHY: Revenue times SGA%; salaries/benefits dollars after the efficiency grind on the rate.</t>
+WHY: Revenue times SGA%; salaries/benefits dollars after the efficiency grind on the rate.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="K28" authorId="0" shapeId="0">
       <text>
         <t>SGA $
 FORMULA: =K24*K9
-WHY: Revenue times SGA%; salaries/benefits dollars after the efficiency grind on the rate.</t>
+WHY: Revenue times SGA%; salaries/benefits dollars after the efficiency grind on the rate.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="L28" authorId="0" shapeId="0">
       <text>
         <t>SGA $
 FORMULA: =L24*L9
-WHY: Revenue times SGA%; salaries/benefits dollars after the efficiency grind on the rate.</t>
+WHY: Revenue times SGA%; salaries/benefits dollars after the efficiency grind on the rate.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="M28" authorId="0" shapeId="0">
       <text>
         <t>SGA $
 FORMULA: =M24*M9
-WHY: Revenue times SGA%; salaries/benefits dollars after the efficiency grind on the rate.</t>
+WHY: Revenue times SGA%; salaries/benefits dollars after the efficiency grind on the rate.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="N28" authorId="0" shapeId="0">
       <text>
         <t>SGA $
 FORMULA: =N24*N9
-WHY: Revenue times SGA%; salaries/benefits dollars after the efficiency grind on the rate.</t>
+WHY: Revenue times SGA%; salaries/benefits dollars after the efficiency grind on the rate.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="B29" authorId="0" shapeId="0">
       <text>
         <t>R&amp;D $
 WHY: Revenue times R&amp;D%; research spend scales with sales at the FY25 reinvestment rate.
-PATTERN: ={c}24*{c}10</t>
+PATTERN: ={c}24*{c}10
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="J29" authorId="0" shapeId="0">
       <text>
         <t>R&amp;D $
 FORMULA: =J24*J10
-WHY: Revenue times R&amp;D%; research spend scales with sales at the FY25 reinvestment rate.</t>
+WHY: Revenue times R&amp;D%; research spend scales with sales at the FY25 reinvestment rate.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="K29" authorId="0" shapeId="0">
       <text>
         <t>R&amp;D $
 FORMULA: =K24*K10
-WHY: Revenue times R&amp;D%; research spend scales with sales at the FY25 reinvestment rate.</t>
+WHY: Revenue times R&amp;D%; research spend scales with sales at the FY25 reinvestment rate.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="L29" authorId="0" shapeId="0">
       <text>
         <t>R&amp;D $
 FORMULA: =L24*L10
-WHY: Revenue times R&amp;D%; research spend scales with sales at the FY25 reinvestment rate.</t>
+WHY: Revenue times R&amp;D%; research spend scales with sales at the FY25 reinvestment rate.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="M29" authorId="0" shapeId="0">
       <text>
         <t>R&amp;D $
 FORMULA: =M24*M10
-WHY: Revenue times R&amp;D%; research spend scales with sales at the FY25 reinvestment rate.</t>
+WHY: Revenue times R&amp;D%; research spend scales with sales at the FY25 reinvestment rate.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="N29" authorId="0" shapeId="0">
       <text>
         <t>R&amp;D $
 FORMULA: =N24*N10
-WHY: Revenue times R&amp;D%; research spend scales with sales at the FY25 reinvestment rate.</t>
+WHY: Revenue times R&amp;D%; research spend scales with sales at the FY25 reinvestment rate.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="B30" authorId="0" shapeId="0">
       <text>
         <t>D&amp;A $
 WHY: Opening PP&amp;E times D&amp;A%; depreciation follows the asset roll-forward, not a revenue %.
-PATTERN: ={c}92*{c}11</t>
+PATTERN: ={c}92*{c}11
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="J30" authorId="0" shapeId="0">
       <text>
         <t>D&amp;A $
 FORMULA: =J92*J11
-WHY: Opening PP&amp;E times D&amp;A%; depreciation follows the asset roll-forward, not a revenue %.</t>
+WHY: Opening PP&amp;E times D&amp;A%; depreciation follows the asset roll-forward, not a revenue %.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="K30" authorId="0" shapeId="0">
       <text>
         <t>D&amp;A $
 FORMULA: =K92*K11
-WHY: Opening PP&amp;E times D&amp;A%; depreciation follows the asset roll-forward, not a revenue %.</t>
+WHY: Opening PP&amp;E times D&amp;A%; depreciation follows the asset roll-forward, not a revenue %.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="L30" authorId="0" shapeId="0">
       <text>
         <t>D&amp;A $
 FORMULA: =L92*L11
-WHY: Opening PP&amp;E times D&amp;A%; depreciation follows the asset roll-forward, not a revenue %.</t>
+WHY: Opening PP&amp;E times D&amp;A%; depreciation follows the asset roll-forward, not a revenue %.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="M30" authorId="0" shapeId="0">
       <text>
         <t>D&amp;A $
 FORMULA: =M92*M11
-WHY: Opening PP&amp;E times D&amp;A%; depreciation follows the asset roll-forward, not a revenue %.</t>
+WHY: Opening PP&amp;E times D&amp;A%; depreciation follows the asset roll-forward, not a revenue %.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="N30" authorId="0" shapeId="0">
       <text>
         <t>D&amp;A $
 FORMULA: =N92*N11
-WHY: Opening PP&amp;E times D&amp;A%; depreciation follows the asset roll-forward, not a revenue %.</t>
+WHY: Opening PP&amp;E times D&amp;A%; depreciation follows the asset roll-forward, not a revenue %.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="B31" authorId="0" shapeId="0">
       <text>
         <t>Interest $
 WHY: Opening debt times interest%; coupon on the debt stock while issuance policy is zero.
-PATTERN: ={c}98*{c}12</t>
+PATTERN: ={c}98*{c}12
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="J31" authorId="0" shapeId="0">
       <text>
         <t>Interest $
 FORMULA: =J98*J12
-WHY: Opening debt times interest%; coupon on the debt stock while issuance policy is zero.</t>
+WHY: Opening debt times interest%; coupon on the debt stock while issuance policy is zero.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="K31" authorId="0" shapeId="0">
       <text>
         <t>Interest $
 FORMULA: =K98*K12
-WHY: Opening debt times interest%; coupon on the debt stock while issuance policy is zero.</t>
+WHY: Opening debt times interest%; coupon on the debt stock while issuance policy is zero.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="L31" authorId="0" shapeId="0">
       <text>
         <t>Interest $
 FORMULA: =L98*L12
-WHY: Opening debt times interest%; coupon on the debt stock while issuance policy is zero.</t>
+WHY: Opening debt times interest%; coupon on the debt stock while issuance policy is zero.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="M31" authorId="0" shapeId="0">
       <text>
         <t>Interest $
 FORMULA: =M98*M12
-WHY: Opening debt times interest%; coupon on the debt stock while issuance policy is zero.</t>
+WHY: Opening debt times interest%; coupon on the debt stock while issuance policy is zero.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="N31" authorId="0" shapeId="0">
       <text>
         <t>Interest $
 FORMULA: =N98*N12
-WHY: Opening debt times interest%; coupon on the debt stock while issuance policy is zero.</t>
+WHY: Opening debt times interest%; coupon on the debt stock while issuance policy is zero.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="B32" authorId="0" shapeId="0">
       <text>
         <t>Total expenses
 WHY: Sum of SGA, R&amp;D, D&amp;A, and interest; all operating and financing costs above EBT.
-PATTERN: =SUM({c}28:{c}31)</t>
+PATTERN: =SUM({c}28:{c}31)
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="J32" authorId="0" shapeId="0">
       <text>
         <t>Total expenses
 FORMULA: =SUM(J28:J31)
-WHY: Sum of SGA, R&amp;D, D&amp;A, and interest; all operating and financing costs above EBT.</t>
+WHY: Sum of SGA, R&amp;D, D&amp;A, and interest; all operating and financing costs above EBT.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="K32" authorId="0" shapeId="0">
       <text>
         <t>Total expenses
 FORMULA: =SUM(K28:K31)
-WHY: Sum of SGA, R&amp;D, D&amp;A, and interest; all operating and financing costs above EBT.</t>
+WHY: Sum of SGA, R&amp;D, D&amp;A, and interest; all operating and financing costs above EBT.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="L32" authorId="0" shapeId="0">
       <text>
         <t>Total expenses
 FORMULA: =SUM(L28:L31)
-WHY: Sum of SGA, R&amp;D, D&amp;A, and interest; all operating and financing costs above EBT.</t>
+WHY: Sum of SGA, R&amp;D, D&amp;A, and interest; all operating and financing costs above EBT.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="M32" authorId="0" shapeId="0">
       <text>
         <t>Total expenses
 FORMULA: =SUM(M28:M31)
-WHY: Sum of SGA, R&amp;D, D&amp;A, and interest; all operating and financing costs above EBT.</t>
+WHY: Sum of SGA, R&amp;D, D&amp;A, and interest; all operating and financing costs above EBT.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="N32" authorId="0" shapeId="0">
       <text>
         <t>Total expenses
 FORMULA: =SUM(N28:N31)
-WHY: Sum of SGA, R&amp;D, D&amp;A, and interest; all operating and financing costs above EBT.</t>
+WHY: Sum of SGA, R&amp;D, D&amp;A, and interest; all operating and financing costs above EBT.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="B33" authorId="0" shapeId="0">
       <text>
         <t>EBT
 WHY: Gross profit minus total expenses; earnings before tax in this simplified template.
-PATTERN: ={c}26-{c}32</t>
+PATTERN: ={c}26-{c}32
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="J33" authorId="0" shapeId="0">
       <text>
         <t>EBT
 FORMULA: =J26-J32
-WHY: Gross profit minus total expenses; earnings before tax in this simplified template.</t>
+WHY: Gross profit minus total expenses; earnings before tax in this simplified template.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="K33" authorId="0" shapeId="0">
       <text>
         <t>EBT
 FORMULA: =K26-K32
-WHY: Gross profit minus total expenses; earnings before tax in this simplified template.</t>
+WHY: Gross profit minus total expenses; earnings before tax in this simplified template.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="L33" authorId="0" shapeId="0">
       <text>
         <t>EBT
 FORMULA: =L26-L32
-WHY: Gross profit minus total expenses; earnings before tax in this simplified template.</t>
+WHY: Gross profit minus total expenses; earnings before tax in this simplified template.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="M33" authorId="0" shapeId="0">
       <text>
         <t>EBT
 FORMULA: =M26-M32
-WHY: Gross profit minus total expenses; earnings before tax in this simplified template.</t>
+WHY: Gross profit minus total expenses; earnings before tax in this simplified template.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="N33" authorId="0" shapeId="0">
       <text>
         <t>EBT
 FORMULA: =N26-N32
-WHY: Gross profit minus total expenses; earnings before tax in this simplified template.</t>
+WHY: Gross profit minus total expenses; earnings before tax in this simplified template.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="B35" authorId="0" shapeId="0">
       <text>
         <t>Taxes $
 WHY: EBT times effective tax rate; book tax expense for the income statement.
-PATTERN: ={c}33*{c}13</t>
+PATTERN: ={c}33*{c}13
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="J35" authorId="0" shapeId="0">
       <text>
         <t>Taxes $
 FORMULA: =J33*J13
-WHY: EBT times effective tax rate; book tax expense for the income statement.</t>
+WHY: EBT times effective tax rate; book tax expense for the income statement.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="K35" authorId="0" shapeId="0">
       <text>
         <t>Taxes $
 FORMULA: =K33*K13
-WHY: EBT times effective tax rate; book tax expense for the income statement.</t>
+WHY: EBT times effective tax rate; book tax expense for the income statement.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="L35" authorId="0" shapeId="0">
       <text>
         <t>Taxes $
 FORMULA: =L33*L13
-WHY: EBT times effective tax rate; book tax expense for the income statement.</t>
+WHY: EBT times effective tax rate; book tax expense for the income statement.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="M35" authorId="0" shapeId="0">
       <text>
         <t>Taxes $
 FORMULA: =M33*M13
-WHY: EBT times effective tax rate; book tax expense for the income statement.</t>
+WHY: EBT times effective tax rate; book tax expense for the income statement.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="N35" authorId="0" shapeId="0">
       <text>
         <t>Taxes $
 FORMULA: =N33*N13
-WHY: EBT times effective tax rate; book tax expense for the income statement.</t>
+WHY: EBT times effective tax rate; book tax expense for the income statement.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="B36" authorId="0" shapeId="0">
       <text>
         <t>Net earnings
 WHY: EBT kept after tax; full equation, not a pointer, so NI tracks the tax rate driver.
-PATTERN: ={c}33*(1-{c}13)</t>
+PATTERN: ={c}33*(1-{c}13)
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="J36" authorId="0" shapeId="0">
       <text>
         <t>Net earnings
 FORMULA: =J33*(1-J13)
-WHY: EBT kept after tax; full equation, not a pointer, so NI tracks the tax rate driver.</t>
+WHY: EBT kept after tax; full equation, not a pointer, so NI tracks the tax rate driver.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="K36" authorId="0" shapeId="0">
       <text>
         <t>Net earnings
 FORMULA: =K33*(1-K13)
-WHY: EBT kept after tax; full equation, not a pointer, so NI tracks the tax rate driver.</t>
+WHY: EBT kept after tax; full equation, not a pointer, so NI tracks the tax rate driver.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="L36" authorId="0" shapeId="0">
       <text>
         <t>Net earnings
 FORMULA: =L33*(1-L13)
-WHY: EBT kept after tax; full equation, not a pointer, so NI tracks the tax rate driver.</t>
+WHY: EBT kept after tax; full equation, not a pointer, so NI tracks the tax rate driver.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="M36" authorId="0" shapeId="0">
       <text>
         <t>Net earnings
 FORMULA: =M33*(1-M13)
-WHY: EBT kept after tax; full equation, not a pointer, so NI tracks the tax rate driver.</t>
+WHY: EBT kept after tax; full equation, not a pointer, so NI tracks the tax rate driver.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="N36" authorId="0" shapeId="0">
       <text>
         <t>Net earnings
 FORMULA: =N33*(1-N13)
-WHY: EBT kept after tax; full equation, not a pointer, so NI tracks the tax rate driver.</t>
+WHY: EBT kept after tax; full equation, not a pointer, so NI tracks the tax rate driver.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="B41" authorId="0" shapeId="0">
       <text>
         <t>Cash (BS)
 WHY: Balance-sheet cash equals cash-flow closing cash so the three statements stay linked.
-PATTERN: ={c}78</t>
+PATTERN: ={c}78
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="J41" authorId="0" shapeId="0">
       <text>
         <t>Cash (BS)
 FORMULA: =J78
-WHY: Balance-sheet cash equals cash-flow closing cash so the three statements stay linked.</t>
+WHY: Balance-sheet cash equals cash-flow closing cash so the three statements stay linked.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="K41" authorId="0" shapeId="0">
       <text>
         <t>Cash (BS)
 FORMULA: =K78
-WHY: Balance-sheet cash equals cash-flow closing cash so the three statements stay linked.</t>
+WHY: Balance-sheet cash equals cash-flow closing cash so the three statements stay linked.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="L41" authorId="0" shapeId="0">
       <text>
         <t>Cash (BS)
 FORMULA: =L78
-WHY: Balance-sheet cash equals cash-flow closing cash so the three statements stay linked.</t>
+WHY: Balance-sheet cash equals cash-flow closing cash so the three statements stay linked.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="M41" authorId="0" shapeId="0">
       <text>
         <t>Cash (BS)
 FORMULA: =M78
-WHY: Balance-sheet cash equals cash-flow closing cash so the three statements stay linked.</t>
+WHY: Balance-sheet cash equals cash-flow closing cash so the three statements stay linked.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="N41" authorId="0" shapeId="0">
       <text>
         <t>Cash (BS)
 FORMULA: =N78
-WHY: Balance-sheet cash equals cash-flow closing cash so the three statements stay linked.</t>
+WHY: Balance-sheet cash equals cash-flow closing cash so the three statements stay linked.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="B42" authorId="0" shapeId="0">
       <text>
         <t>AR $
 WHY: Revenue × AR days / 365; receivables from the days-sales-outstanding assumption.
-PATTERN: ={c}24*{c}15/365</t>
+PATTERN: ={c}24*{c}15/365
+LINK: https://data.sec.gov/api/xbrl/companyfacts/CIK0000814547.json</t>
       </text>
     </comment>
     <comment ref="J42" authorId="0" shapeId="0">
       <text>
         <t>AR $
 FORMULA: =J24*J15/365
-WHY: Revenue × AR days / 365; receivables from the days-sales-outstanding assumption.</t>
+WHY: Revenue × AR days / 365; receivables from the days-sales-outstanding assumption.
+LINK: https://data.sec.gov/api/xbrl/companyfacts/CIK0000814547.json</t>
       </text>
     </comment>
     <comment ref="K42" authorId="0" shapeId="0">
       <text>
         <t>AR $
 FORMULA: =K24*K15/365
-WHY: Revenue × AR days / 365; receivables from the days-sales-outstanding assumption.</t>
+WHY: Revenue × AR days / 365; receivables from the days-sales-outstanding assumption.
+LINK: https://data.sec.gov/api/xbrl/companyfacts/CIK0000814547.json</t>
       </text>
     </comment>
     <comment ref="L42" authorId="0" shapeId="0">
       <text>
         <t>AR $
 FORMULA: =L24*L15/365
-WHY: Revenue × AR days / 365; receivables from the days-sales-outstanding assumption.</t>
+WHY: Revenue × AR days / 365; receivables from the days-sales-outstanding assumption.
+LINK: https://data.sec.gov/api/xbrl/companyfacts/CIK0000814547.json</t>
       </text>
     </comment>
     <comment ref="M42" authorId="0" shapeId="0">
       <text>
         <t>AR $
 FORMULA: =M24*M15/365
-WHY: Revenue × AR days / 365; receivables from the days-sales-outstanding assumption.</t>
+WHY: Revenue × AR days / 365; receivables from the days-sales-outstanding assumption.
+LINK: https://data.sec.gov/api/xbrl/companyfacts/CIK0000814547.json</t>
       </text>
     </comment>
     <comment ref="N42" authorId="0" shapeId="0">
       <text>
         <t>AR $
 FORMULA: =N24*N15/365
-WHY: Revenue × AR days / 365; receivables from the days-sales-outstanding assumption.</t>
+WHY: Revenue × AR days / 365; receivables from the days-sales-outstanding assumption.
+LINK: https://data.sec.gov/api/xbrl/companyfacts/CIK0000814547.json</t>
       </text>
     </comment>
     <comment ref="B43" authorId="0" shapeId="0">
       <text>
         <t>Inventory $
 WHY: COGS × inventory days / 365; stays zero because inventory days are policy zero.
-PATTERN: ={c}25*{c}16/365</t>
+PATTERN: ={c}25*{c}16/365
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="J43" authorId="0" shapeId="0">
       <text>
         <t>Inventory $
 FORMULA: =J25*J16/365
-WHY: COGS × inventory days / 365; stays zero because inventory days are policy zero.</t>
+WHY: COGS × inventory days / 365; stays zero because inventory days are policy zero.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="K43" authorId="0" shapeId="0">
       <text>
         <t>Inventory $
 FORMULA: =K25*K16/365
-WHY: COGS × inventory days / 365; stays zero because inventory days are policy zero.</t>
+WHY: COGS × inventory days / 365; stays zero because inventory days are policy zero.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="L43" authorId="0" shapeId="0">
       <text>
         <t>Inventory $
 FORMULA: =L25*L16/365
-WHY: COGS × inventory days / 365; stays zero because inventory days are policy zero.</t>
+WHY: COGS × inventory days / 365; stays zero because inventory days are policy zero.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="M43" authorId="0" shapeId="0">
       <text>
         <t>Inventory $
 FORMULA: =M25*M16/365
-WHY: COGS × inventory days / 365; stays zero because inventory days are policy zero.</t>
+WHY: COGS × inventory days / 365; stays zero because inventory days are policy zero.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="N43" authorId="0" shapeId="0">
       <text>
         <t>Inventory $
 FORMULA: =N25*N16/365
-WHY: COGS × inventory days / 365; stays zero because inventory days are policy zero.</t>
+WHY: COGS × inventory days / 365; stays zero because inventory days are policy zero.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="B44" authorId="0" shapeId="0">
       <text>
         <t>PP&amp;E (BS)
 WHY: Net PP&amp;E equals the PPE schedule closing balance after CapEx and depreciation.
-PATTERN: ={c}95</t>
+PATTERN: ={c}95
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="J44" authorId="0" shapeId="0">
       <text>
         <t>PP&amp;E (BS)
 FORMULA: =J95
-WHY: Net PP&amp;E equals the PPE schedule closing balance after CapEx and depreciation.</t>
+WHY: Net PP&amp;E equals the PPE schedule closing balance after CapEx and depreciation.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="K44" authorId="0" shapeId="0">
       <text>
         <t>PP&amp;E (BS)
 FORMULA: =K95
-WHY: Net PP&amp;E equals the PPE schedule closing balance after CapEx and depreciation.</t>
+WHY: Net PP&amp;E equals the PPE schedule closing balance after CapEx and depreciation.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="L44" authorId="0" shapeId="0">
       <text>
         <t>PP&amp;E (BS)
 FORMULA: =L95
-WHY: Net PP&amp;E equals the PPE schedule closing balance after CapEx and depreciation.</t>
+WHY: Net PP&amp;E equals the PPE schedule closing balance after CapEx and depreciation.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="M44" authorId="0" shapeId="0">
       <text>
         <t>PP&amp;E (BS)
 FORMULA: =M95
-WHY: Net PP&amp;E equals the PPE schedule closing balance after CapEx and depreciation.</t>
+WHY: Net PP&amp;E equals the PPE schedule closing balance after CapEx and depreciation.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="N44" authorId="0" shapeId="0">
       <text>
         <t>PP&amp;E (BS)
 FORMULA: =N95
-WHY: Net PP&amp;E equals the PPE schedule closing balance after CapEx and depreciation.</t>
+WHY: Net PP&amp;E equals the PPE schedule closing balance after CapEx and depreciation.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="B45" authorId="0" shapeId="0">
       <text>
         <t>Total assets
 WHY: Cash + AR + inventory + PP&amp;E; simplified asset base used for the balance-sheet check.
-PATTERN: =SUM({c}41:{c}44)</t>
+PATTERN: =SUM({c}41:{c}44)
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="J45" authorId="0" shapeId="0">
       <text>
         <t>Total assets
 FORMULA: =SUM(J41:J44)
-WHY: Cash + AR + inventory + PP&amp;E; simplified asset base used for the balance-sheet check.</t>
+WHY: Cash + AR + inventory + PP&amp;E; simplified asset base used for the balance-sheet check.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="K45" authorId="0" shapeId="0">
       <text>
         <t>Total assets
 FORMULA: =SUM(K41:K44)
-WHY: Cash + AR + inventory + PP&amp;E; simplified asset base used for the balance-sheet check.</t>
+WHY: Cash + AR + inventory + PP&amp;E; simplified asset base used for the balance-sheet check.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="L45" authorId="0" shapeId="0">
       <text>
         <t>Total assets
 FORMULA: =SUM(L41:L44)
-WHY: Cash + AR + inventory + PP&amp;E; simplified asset base used for the balance-sheet check.</t>
+WHY: Cash + AR + inventory + PP&amp;E; simplified asset base used for the balance-sheet check.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="M45" authorId="0" shapeId="0">
       <text>
         <t>Total assets
 FORMULA: =SUM(M41:M44)
-WHY: Cash + AR + inventory + PP&amp;E; simplified asset base used for the balance-sheet check.</t>
+WHY: Cash + AR + inventory + PP&amp;E; simplified asset base used for the balance-sheet check.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="N45" authorId="0" shapeId="0">
       <text>
         <t>Total assets
 FORMULA: =SUM(N41:N44)
-WHY: Cash + AR + inventory + PP&amp;E; simplified asset base used for the balance-sheet check.</t>
+WHY: Cash + AR + inventory + PP&amp;E; simplified asset base used for the balance-sheet check.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="B48" authorId="0" shapeId="0">
       <text>
         <t>AP $
 WHY: COGS × AP days / 365; payables funded by the payable-days assumption.
-PATTERN: ={c}25*{c}17/365</t>
+PATTERN: ={c}25*{c}17/365
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="J48" authorId="0" shapeId="0">
       <text>
         <t>AP $
 FORMULA: =J25*J17/365
-WHY: COGS × AP days / 365; payables funded by the payable-days assumption.</t>
+WHY: COGS × AP days / 365; payables funded by the payable-days assumption.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="K48" authorId="0" shapeId="0">
       <text>
         <t>AP $
 FORMULA: =K25*K17/365
-WHY: COGS × AP days / 365; payables funded by the payable-days assumption.</t>
+WHY: COGS × AP days / 365; payables funded by the payable-days assumption.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="L48" authorId="0" shapeId="0">
       <text>
         <t>AP $
 FORMULA: =L25*L17/365
-WHY: COGS × AP days / 365; payables funded by the payable-days assumption.</t>
+WHY: COGS × AP days / 365; payables funded by the payable-days assumption.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="M48" authorId="0" shapeId="0">
       <text>
         <t>AP $
 FORMULA: =M25*M17/365
-WHY: COGS × AP days / 365; payables funded by the payable-days assumption.</t>
+WHY: COGS × AP days / 365; payables funded by the payable-days assumption.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="N48" authorId="0" shapeId="0">
       <text>
         <t>AP $
 FORMULA: =N25*N17/365
-WHY: COGS × AP days / 365; payables funded by the payable-days assumption.</t>
+WHY: COGS × AP days / 365; payables funded by the payable-days assumption.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="B49" authorId="0" shapeId="0">
       <text>
         <t>Debt (BS)
 WHY: Debt equals the debt-schedule closing balance (open + issuance, issuance usually 0).
-PATTERN: ={c}100</t>
+PATTERN: ={c}100
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="J49" authorId="0" shapeId="0">
       <text>
         <t>Debt (BS)
 FORMULA: =J100
-WHY: Debt equals the debt-schedule closing balance (open + issuance, issuance usually 0).</t>
+WHY: Debt equals the debt-schedule closing balance (open + issuance, issuance usually 0).
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="K49" authorId="0" shapeId="0">
       <text>
         <t>Debt (BS)
 FORMULA: =K100
-WHY: Debt equals the debt-schedule closing balance (open + issuance, issuance usually 0).</t>
+WHY: Debt equals the debt-schedule closing balance (open + issuance, issuance usually 0).
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="L49" authorId="0" shapeId="0">
       <text>
         <t>Debt (BS)
 FORMULA: =L100
-WHY: Debt equals the debt-schedule closing balance (open + issuance, issuance usually 0).</t>
+WHY: Debt equals the debt-schedule closing balance (open + issuance, issuance usually 0).
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="M49" authorId="0" shapeId="0">
       <text>
         <t>Debt (BS)
 FORMULA: =M100
-WHY: Debt equals the debt-schedule closing balance (open + issuance, issuance usually 0).</t>
+WHY: Debt equals the debt-schedule closing balance (open + issuance, issuance usually 0).
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="N49" authorId="0" shapeId="0">
       <text>
         <t>Debt (BS)
 FORMULA: =N100
-WHY: Debt equals the debt-schedule closing balance (open + issuance, issuance usually 0).</t>
+WHY: Debt equals the debt-schedule closing balance (open + issuance, issuance usually 0).
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="B50" authorId="0" shapeId="0">
       <text>
         <t>Total liabilities
 WHY: Accounts payable plus debt; simplified liability total in this teaching template.
-PATTERN: =SUM({c}48:{c}49)</t>
+PATTERN: =SUM({c}48:{c}49)
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="J50" authorId="0" shapeId="0">
       <text>
         <t>Total liabilities
 FORMULA: =SUM(J48:J49)
-WHY: Accounts payable plus debt; simplified liability total in this teaching template.</t>
+WHY: Accounts payable plus debt; simplified liability total in this teaching template.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="K50" authorId="0" shapeId="0">
       <text>
         <t>Total liabilities
 FORMULA: =SUM(K48:K49)
-WHY: Accounts payable plus debt; simplified liability total in this teaching template.</t>
+WHY: Accounts payable plus debt; simplified liability total in this teaching template.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="L50" authorId="0" shapeId="0">
       <text>
         <t>Total liabilities
 FORMULA: =SUM(L48:L49)
-WHY: Accounts payable plus debt; simplified liability total in this teaching template.</t>
+WHY: Accounts payable plus debt; simplified liability total in this teaching template.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="M50" authorId="0" shapeId="0">
       <text>
         <t>Total liabilities
 FORMULA: =SUM(M48:M49)
-WHY: Accounts payable plus debt; simplified liability total in this teaching template.</t>
+WHY: Accounts payable plus debt; simplified liability total in this teaching template.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="N50" authorId="0" shapeId="0">
       <text>
         <t>Total liabilities
 FORMULA: =SUM(N48:N49)
-WHY: Accounts payable plus debt; simplified liability total in this teaching template.</t>
+WHY: Accounts payable plus debt; simplified liability total in this teaching template.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="B52" authorId="0" shapeId="0">
       <text>
         <t>Equity capital
 WHY: Prior equity capital plus equity issued/(repurchased); policy keeps issuance at zero.
-PATTERN: ={p}52+{c}20</t>
+PATTERN: ={p}52+{c}20
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="J52" authorId="0" shapeId="0">
       <text>
         <t>Equity capital
 FORMULA: =I52+J20
-WHY: Prior equity capital plus equity issued/(repurchased); policy keeps issuance at zero.</t>
+WHY: Prior equity capital plus equity issued/(repurchased); policy keeps issuance at zero.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="K52" authorId="0" shapeId="0">
       <text>
         <t>Equity capital
 FORMULA: =J52+K20
-WHY: Prior equity capital plus equity issued/(repurchased); policy keeps issuance at zero.</t>
+WHY: Prior equity capital plus equity issued/(repurchased); policy keeps issuance at zero.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="L52" authorId="0" shapeId="0">
       <text>
         <t>Equity capital
 FORMULA: =K52+L20
-WHY: Prior equity capital plus equity issued/(repurchased); policy keeps issuance at zero.</t>
+WHY: Prior equity capital plus equity issued/(repurchased); policy keeps issuance at zero.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="M52" authorId="0" shapeId="0">
       <text>
         <t>Equity capital
 FORMULA: =L52+M20
-WHY: Prior equity capital plus equity issued/(repurchased); policy keeps issuance at zero.</t>
+WHY: Prior equity capital plus equity issued/(repurchased); policy keeps issuance at zero.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="N52" authorId="0" shapeId="0">
       <text>
         <t>Equity capital
 FORMULA: =M52+N20
-WHY: Prior equity capital plus equity issued/(repurchased); policy keeps issuance at zero.</t>
+WHY: Prior equity capital plus equity issued/(repurchased); policy keeps issuance at zero.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="B53" authorId="0" shapeId="0">
       <text>
         <t>Retained earnings
 WHY: Prior RE plus this year’s net earnings; accumulates NI into equity without dividends.
-PATTERN: ={p}53+{c}33*(1-{c}13)</t>
+PATTERN: ={p}53+{c}33*(1-{c}13)
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="J53" authorId="0" shapeId="0">
       <text>
         <t>Retained earnings
 FORMULA: =I53+J33*(1-J13)
-WHY: Prior RE plus this year’s net earnings; accumulates NI into equity without dividends.</t>
+WHY: Prior RE plus this year’s net earnings; accumulates NI into equity without dividends.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="K53" authorId="0" shapeId="0">
       <text>
         <t>Retained earnings
 FORMULA: =J53+K33*(1-K13)
-WHY: Prior RE plus this year’s net earnings; accumulates NI into equity without dividends.</t>
+WHY: Prior RE plus this year’s net earnings; accumulates NI into equity without dividends.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="L53" authorId="0" shapeId="0">
       <text>
         <t>Retained earnings
 FORMULA: =K53+L33*(1-L13)
-WHY: Prior RE plus this year’s net earnings; accumulates NI into equity without dividends.</t>
+WHY: Prior RE plus this year’s net earnings; accumulates NI into equity without dividends.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="M53" authorId="0" shapeId="0">
       <text>
         <t>Retained earnings
 FORMULA: =L53+M33*(1-M13)
-WHY: Prior RE plus this year’s net earnings; accumulates NI into equity without dividends.</t>
+WHY: Prior RE plus this year’s net earnings; accumulates NI into equity without dividends.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="N53" authorId="0" shapeId="0">
       <text>
         <t>Retained earnings
 FORMULA: =M53+N33*(1-N13)
-WHY: Prior RE plus this year’s net earnings; accumulates NI into equity without dividends.</t>
+WHY: Prior RE plus this year’s net earnings; accumulates NI into equity without dividends.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="B54" authorId="0" shapeId="0">
       <text>
         <t>Shareholders’ equity
 WHY: Equity capital plus retained earnings; book equity for the L+E side of the check.
-PATTERN: =SUM({c}52:{c}53)</t>
+PATTERN: =SUM({c}52:{c}53)
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="J54" authorId="0" shapeId="0">
       <text>
         <t>Shareholders’ equity
 FORMULA: =SUM(J52:J53)
-WHY: Equity capital plus retained earnings; book equity for the L+E side of the check.</t>
+WHY: Equity capital plus retained earnings; book equity for the L+E side of the check.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="K54" authorId="0" shapeId="0">
       <text>
         <t>Shareholders’ equity
 FORMULA: =SUM(K52:K53)
-WHY: Equity capital plus retained earnings; book equity for the L+E side of the check.</t>
+WHY: Equity capital plus retained earnings; book equity for the L+E side of the check.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="L54" authorId="0" shapeId="0">
       <text>
         <t>Shareholders’ equity
 FORMULA: =SUM(L52:L53)
-WHY: Equity capital plus retained earnings; book equity for the L+E side of the check.</t>
+WHY: Equity capital plus retained earnings; book equity for the L+E side of the check.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="M54" authorId="0" shapeId="0">
       <text>
         <t>Shareholders’ equity
 FORMULA: =SUM(M52:M53)
-WHY: Equity capital plus retained earnings; book equity for the L+E side of the check.</t>
+WHY: Equity capital plus retained earnings; book equity for the L+E side of the check.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="N54" authorId="0" shapeId="0">
       <text>
         <t>Shareholders’ equity
 FORMULA: =SUM(N52:N53)
-WHY: Equity capital plus retained earnings; book equity for the L+E side of the check.</t>
+WHY: Equity capital plus retained earnings; book equity for the L+E side of the check.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="B55" authorId="0" shapeId="0">
       <text>
         <t>Total L+E
 WHY: Liabilities plus equity; must equal total assets when the model is in balance.
-PATTERN: ={c}50+{c}54</t>
+PATTERN: ={c}50+{c}54
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="J55" authorId="0" shapeId="0">
       <text>
         <t>Total L+E
 FORMULA: =J50+J54
-WHY: Liabilities plus equity; must equal total assets when the model is in balance.</t>
+WHY: Liabilities plus equity; must equal total assets when the model is in balance.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="K55" authorId="0" shapeId="0">
       <text>
         <t>Total L+E
 FORMULA: =K50+K54
-WHY: Liabilities plus equity; must equal total assets when the model is in balance.</t>
+WHY: Liabilities plus equity; must equal total assets when the model is in balance.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="L55" authorId="0" shapeId="0">
       <text>
         <t>Total L+E
 FORMULA: =L50+L54
-WHY: Liabilities plus equity; must equal total assets when the model is in balance.</t>
+WHY: Liabilities plus equity; must equal total assets when the model is in balance.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="M55" authorId="0" shapeId="0">
       <text>
         <t>Total L+E
 FORMULA: =M50+M54
-WHY: Liabilities plus equity; must equal total assets when the model is in balance.</t>
+WHY: Liabilities plus equity; must equal total assets when the model is in balance.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="N55" authorId="0" shapeId="0">
       <text>
         <t>Total L+E
 FORMULA: =N50+N54
-WHY: Liabilities plus equity; must equal total assets when the model is in balance.</t>
+WHY: Liabilities plus equity; must equal total assets when the model is in balance.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="B57" authorId="0" shapeId="0">
       <text>
         <t>BS imbalance
 WHY: L+E minus assets; should be ~0. Nonzero means a link or plug is broken.
-PATTERN: ={c}55-{c}45</t>
+PATTERN: ={c}55-{c}45
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="J57" authorId="0" shapeId="0">
       <text>
         <t>BS imbalance
 FORMULA: =J55-J45
-WHY: L+E minus assets; should be ~0. Nonzero means a link or plug is broken.</t>
+WHY: L+E minus assets; should be ~0. Nonzero means a link or plug is broken.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="K57" authorId="0" shapeId="0">
       <text>
         <t>BS imbalance
 FORMULA: =K55-K45
-WHY: L+E minus assets; should be ~0. Nonzero means a link or plug is broken.</t>
+WHY: L+E minus assets; should be ~0. Nonzero means a link or plug is broken.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="L57" authorId="0" shapeId="0">
       <text>
         <t>BS imbalance
 FORMULA: =L55-L45
-WHY: L+E minus assets; should be ~0. Nonzero means a link or plug is broken.</t>
+WHY: L+E minus assets; should be ~0. Nonzero means a link or plug is broken.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="M57" authorId="0" shapeId="0">
       <text>
         <t>BS imbalance
 FORMULA: =M55-M45
-WHY: L+E minus assets; should be ~0. Nonzero means a link or plug is broken.</t>
+WHY: L+E minus assets; should be ~0. Nonzero means a link or plug is broken.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="N57" authorId="0" shapeId="0">
       <text>
         <t>BS imbalance
 FORMULA: =N55-N45
-WHY: L+E minus assets; should be ~0. Nonzero means a link or plug is broken.</t>
+WHY: L+E minus assets; should be ~0. Nonzero means a link or plug is broken.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="B62" authorId="0" shapeId="0">
       <text>
         <t>CF net earnings
 WHY: Same NI equation as the IS, written out so CFO does not hide behind a bare pointer.
-PATTERN: ={c}33*(1-{c}13)</t>
+PATTERN: ={c}33*(1-{c}13)
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="J62" authorId="0" shapeId="0">
       <text>
         <t>CF net earnings
 FORMULA: =J33*(1-J13)
-WHY: Same NI equation as the IS, written out so CFO does not hide behind a bare pointer.</t>
+WHY: Same NI equation as the IS, written out so CFO does not hide behind a bare pointer.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="K62" authorId="0" shapeId="0">
       <text>
         <t>CF net earnings
 FORMULA: =K33*(1-K13)
-WHY: Same NI equation as the IS, written out so CFO does not hide behind a bare pointer.</t>
+WHY: Same NI equation as the IS, written out so CFO does not hide behind a bare pointer.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="L62" authorId="0" shapeId="0">
       <text>
         <t>CF net earnings
 FORMULA: =L33*(1-L13)
-WHY: Same NI equation as the IS, written out so CFO does not hide behind a bare pointer.</t>
+WHY: Same NI equation as the IS, written out so CFO does not hide behind a bare pointer.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="M62" authorId="0" shapeId="0">
       <text>
         <t>CF net earnings
 FORMULA: =M33*(1-M13)
-WHY: Same NI equation as the IS, written out so CFO does not hide behind a bare pointer.</t>
+WHY: Same NI equation as the IS, written out so CFO does not hide behind a bare pointer.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="N62" authorId="0" shapeId="0">
       <text>
         <t>CF net earnings
 FORMULA: =N33*(1-N13)
-WHY: Same NI equation as the IS, written out so CFO does not hide behind a bare pointer.</t>
+WHY: Same NI equation as the IS, written out so CFO does not hide behind a bare pointer.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="B63" authorId="0" shapeId="0">
       <text>
         <t>CF + D&amp;A
 WHY: Adds back non-cash D&amp;A (open PP&amp;E × D&amp;A%) in the cash-from-operations bridge.
-PATTERN: ={c}92*{c}11</t>
+PATTERN: ={c}92*{c}11
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="J63" authorId="0" shapeId="0">
       <text>
         <t>CF + D&amp;A
 FORMULA: =J92*J11
-WHY: Adds back non-cash D&amp;A (open PP&amp;E × D&amp;A%) in the cash-from-operations bridge.</t>
+WHY: Adds back non-cash D&amp;A (open PP&amp;E × D&amp;A%) in the cash-from-operations bridge.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="K63" authorId="0" shapeId="0">
       <text>
         <t>CF + D&amp;A
 FORMULA: =K92*K11
-WHY: Adds back non-cash D&amp;A (open PP&amp;E × D&amp;A%) in the cash-from-operations bridge.</t>
+WHY: Adds back non-cash D&amp;A (open PP&amp;E × D&amp;A%) in the cash-from-operations bridge.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="L63" authorId="0" shapeId="0">
       <text>
         <t>CF + D&amp;A
 FORMULA: =L92*L11
-WHY: Adds back non-cash D&amp;A (open PP&amp;E × D&amp;A%) in the cash-from-operations bridge.</t>
+WHY: Adds back non-cash D&amp;A (open PP&amp;E × D&amp;A%) in the cash-from-operations bridge.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="M63" authorId="0" shapeId="0">
       <text>
         <t>CF + D&amp;A
 FORMULA: =M92*M11
-WHY: Adds back non-cash D&amp;A (open PP&amp;E × D&amp;A%) in the cash-from-operations bridge.</t>
+WHY: Adds back non-cash D&amp;A (open PP&amp;E × D&amp;A%) in the cash-from-operations bridge.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="N63" authorId="0" shapeId="0">
       <text>
         <t>CF + D&amp;A
 FORMULA: =N92*N11
-WHY: Adds back non-cash D&amp;A (open PP&amp;E × D&amp;A%) in the cash-from-operations bridge.</t>
+WHY: Adds back non-cash D&amp;A (open PP&amp;E × D&amp;A%) in the cash-from-operations bridge.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="B64" authorId="0" shapeId="0">
       <text>
         <t>CF − ΔNWC
 WHY: Increase in net working capital uses cash; decrease frees cash in the CFO build.
-PATTERN: ={c}88-{p}88</t>
+PATTERN: ={c}88-{p}88
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="J64" authorId="0" shapeId="0">
       <text>
         <t>CF − ΔNWC
 FORMULA: =J88-I88
-WHY: Increase in net working capital uses cash; decrease frees cash in the CFO build.</t>
+WHY: Increase in net working capital uses cash; decrease frees cash in the CFO build.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="K64" authorId="0" shapeId="0">
       <text>
         <t>CF − ΔNWC
 FORMULA: =K88-J88
-WHY: Increase in net working capital uses cash; decrease frees cash in the CFO build.</t>
+WHY: Increase in net working capital uses cash; decrease frees cash in the CFO build.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="L64" authorId="0" shapeId="0">
       <text>
         <t>CF − ΔNWC
 FORMULA: =L88-K88
-WHY: Increase in net working capital uses cash; decrease frees cash in the CFO build.</t>
+WHY: Increase in net working capital uses cash; decrease frees cash in the CFO build.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="M64" authorId="0" shapeId="0">
       <text>
         <t>CF − ΔNWC
 FORMULA: =M88-L88
-WHY: Increase in net working capital uses cash; decrease frees cash in the CFO build.</t>
+WHY: Increase in net working capital uses cash; decrease frees cash in the CFO build.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="N64" authorId="0" shapeId="0">
       <text>
         <t>CF − ΔNWC
 FORMULA: =N88-M88
-WHY: Increase in net working capital uses cash; decrease frees cash in the CFO build.</t>
+WHY: Increase in net working capital uses cash; decrease frees cash in the CFO build.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="B65" authorId="0" shapeId="0">
       <text>
         <t>Cash from operations
 WHY: Full CFO: NI + D&amp;A − ΔNWC written as one equation, not assembled from pointers.
-PATTERN: ={c}33*(1-{c}13)+{c}92*{c}11-({c}88-{p}88)</t>
+PATTERN: ={c}33*(1-{c}13)+{c}92*{c}11-({c}88-{p}88)
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="J65" authorId="0" shapeId="0">
       <text>
         <t>Cash from operations
 FORMULA: =J33*(1-J13)+J92*J11-(J88-I88)
-WHY: Full CFO: NI + D&amp;A − ΔNWC written as one equation, not assembled from pointers.</t>
+WHY: Full CFO: NI + D&amp;A − ΔNWC written as one equation, not assembled from pointers.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="K65" authorId="0" shapeId="0">
       <text>
         <t>Cash from operations
 FORMULA: =K33*(1-K13)+K92*K11-(K88-J88)
-WHY: Full CFO: NI + D&amp;A − ΔNWC written as one equation, not assembled from pointers.</t>
+WHY: Full CFO: NI + D&amp;A − ΔNWC written as one equation, not assembled from pointers.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="L65" authorId="0" shapeId="0">
       <text>
         <t>Cash from operations
 FORMULA: =L33*(1-L13)+L92*L11-(L88-K88)
-WHY: Full CFO: NI + D&amp;A − ΔNWC written as one equation, not assembled from pointers.</t>
+WHY: Full CFO: NI + D&amp;A − ΔNWC written as one equation, not assembled from pointers.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="M65" authorId="0" shapeId="0">
       <text>
         <t>Cash from operations
 FORMULA: =M33*(1-M13)+M92*M11-(M88-L88)
-WHY: Full CFO: NI + D&amp;A − ΔNWC written as one equation, not assembled from pointers.</t>
+WHY: Full CFO: NI + D&amp;A − ΔNWC written as one equation, not assembled from pointers.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="N65" authorId="0" shapeId="0">
       <text>
         <t>Cash from operations
 FORMULA: =N33*(1-N13)+N92*N11-(N88-M88)
-WHY: Full CFO: NI + D&amp;A − ΔNWC written as one equation, not assembled from pointers.</t>
+WHY: Full CFO: NI + D&amp;A − ΔNWC written as one equation, not assembled from pointers.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="B68" authorId="0" shapeId="0">
       <text>
         <t>CapEx $
 WHY: Revenue times CapEx%; investing outflow used in CF and the PPE roll-forward.
-PATTERN: ={c}24*{c}18</t>
+PATTERN: ={c}24*{c}18
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="J68" authorId="0" shapeId="0">
       <text>
         <t>CapEx $
 FORMULA: =J24*J18
-WHY: Revenue times CapEx%; investing outflow used in CF and the PPE roll-forward.</t>
+WHY: Revenue times CapEx%; investing outflow used in CF and the PPE roll-forward.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="K68" authorId="0" shapeId="0">
       <text>
         <t>CapEx $
 FORMULA: =K24*K18
-WHY: Revenue times CapEx%; investing outflow used in CF and the PPE roll-forward.</t>
+WHY: Revenue times CapEx%; investing outflow used in CF and the PPE roll-forward.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="L68" authorId="0" shapeId="0">
       <text>
         <t>CapEx $
 FORMULA: =L24*L18
-WHY: Revenue times CapEx%; investing outflow used in CF and the PPE roll-forward.</t>
+WHY: Revenue times CapEx%; investing outflow used in CF and the PPE roll-forward.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="M68" authorId="0" shapeId="0">
       <text>
         <t>CapEx $
 FORMULA: =M24*M18
-WHY: Revenue times CapEx%; investing outflow used in CF and the PPE roll-forward.</t>
+WHY: Revenue times CapEx%; investing outflow used in CF and the PPE roll-forward.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="N68" authorId="0" shapeId="0">
       <text>
         <t>CapEx $
 FORMULA: =N24*N18
-WHY: Revenue times CapEx%; investing outflow used in CF and the PPE roll-forward.</t>
+WHY: Revenue times CapEx%; investing outflow used in CF and the PPE roll-forward.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="B69" authorId="0" shapeId="0">
       <text>
         <t>Cash from investing
 WHY: In this template CFI is CapEx only; equals the CapEx dollar line above.
-PATTERN: ={c}68</t>
+PATTERN: ={c}68
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="J69" authorId="0" shapeId="0">
       <text>
         <t>Cash from investing
 FORMULA: =J68
-WHY: In this template CFI is CapEx only; equals the CapEx dollar line above.</t>
+WHY: In this template CFI is CapEx only; equals the CapEx dollar line above.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="K69" authorId="0" shapeId="0">
       <text>
         <t>Cash from investing
 FORMULA: =K68
-WHY: In this template CFI is CapEx only; equals the CapEx dollar line above.</t>
+WHY: In this template CFI is CapEx only; equals the CapEx dollar line above.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="L69" authorId="0" shapeId="0">
       <text>
         <t>Cash from investing
 FORMULA: =L68
-WHY: In this template CFI is CapEx only; equals the CapEx dollar line above.</t>
+WHY: In this template CFI is CapEx only; equals the CapEx dollar line above.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="M69" authorId="0" shapeId="0">
       <text>
         <t>Cash from investing
 FORMULA: =M68
-WHY: In this template CFI is CapEx only; equals the CapEx dollar line above.</t>
+WHY: In this template CFI is CapEx only; equals the CapEx dollar line above.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="N69" authorId="0" shapeId="0">
       <text>
         <t>Cash from investing
 FORMULA: =N68
-WHY: In this template CFI is CapEx only; equals the CapEx dollar line above.</t>
+WHY: In this template CFI is CapEx only; equals the CapEx dollar line above.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="B72" authorId="0" shapeId="0">
       <text>
         <t>Debt issuance CF
 WHY: Pulls the debt issuance/(repayment) policy into financing cash flow.
-PATTERN: ={c}19</t>
+PATTERN: ={c}19
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="J72" authorId="0" shapeId="0">
       <text>
         <t>Debt issuance CF
 FORMULA: =J19
-WHY: Pulls the debt issuance/(repayment) policy into financing cash flow.</t>
+WHY: Pulls the debt issuance/(repayment) policy into financing cash flow.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="K72" authorId="0" shapeId="0">
       <text>
         <t>Debt issuance CF
 FORMULA: =K19
-WHY: Pulls the debt issuance/(repayment) policy into financing cash flow.</t>
+WHY: Pulls the debt issuance/(repayment) policy into financing cash flow.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="L72" authorId="0" shapeId="0">
       <text>
         <t>Debt issuance CF
 FORMULA: =L19
-WHY: Pulls the debt issuance/(repayment) policy into financing cash flow.</t>
+WHY: Pulls the debt issuance/(repayment) policy into financing cash flow.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="M72" authorId="0" shapeId="0">
       <text>
         <t>Debt issuance CF
 FORMULA: =M19
-WHY: Pulls the debt issuance/(repayment) policy into financing cash flow.</t>
+WHY: Pulls the debt issuance/(repayment) policy into financing cash flow.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="N72" authorId="0" shapeId="0">
       <text>
         <t>Debt issuance CF
 FORMULA: =N19
-WHY: Pulls the debt issuance/(repayment) policy into financing cash flow.</t>
+WHY: Pulls the debt issuance/(repayment) policy into financing cash flow.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="B73" authorId="0" shapeId="0">
       <text>
         <t>Equity issuance CF
 WHY: Pulls the equity issuance/(buyback) policy into financing cash flow.
-PATTERN: ={c}20</t>
+PATTERN: ={c}20
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="J73" authorId="0" shapeId="0">
       <text>
         <t>Equity issuance CF
 FORMULA: =J20
-WHY: Pulls the equity issuance/(buyback) policy into financing cash flow.</t>
+WHY: Pulls the equity issuance/(buyback) policy into financing cash flow.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="K73" authorId="0" shapeId="0">
       <text>
         <t>Equity issuance CF
 FORMULA: =K20
-WHY: Pulls the equity issuance/(buyback) policy into financing cash flow.</t>
+WHY: Pulls the equity issuance/(buyback) policy into financing cash flow.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="L73" authorId="0" shapeId="0">
       <text>
         <t>Equity issuance CF
 FORMULA: =L20
-WHY: Pulls the equity issuance/(buyback) policy into financing cash flow.</t>
+WHY: Pulls the equity issuance/(buyback) policy into financing cash flow.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="M73" authorId="0" shapeId="0">
       <text>
         <t>Equity issuance CF
 FORMULA: =M20
-WHY: Pulls the equity issuance/(buyback) policy into financing cash flow.</t>
+WHY: Pulls the equity issuance/(buyback) policy into financing cash flow.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="N73" authorId="0" shapeId="0">
       <text>
         <t>Equity issuance CF
 FORMULA: =N20
-WHY: Pulls the equity issuance/(buyback) policy into financing cash flow.</t>
+WHY: Pulls the equity issuance/(buyback) policy into financing cash flow.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="B74" authorId="0" shapeId="0">
       <text>
         <t>Cash from financing
 WHY: Debt plus equity financing cash; both policies are zero in the base case.
-PATTERN: ={c}19+{c}20</t>
+PATTERN: ={c}19+{c}20
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="J74" authorId="0" shapeId="0">
       <text>
         <t>Cash from financing
 FORMULA: =J19+J20
-WHY: Debt plus equity financing cash; both policies are zero in the base case.</t>
+WHY: Debt plus equity financing cash; both policies are zero in the base case.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="K74" authorId="0" shapeId="0">
       <text>
         <t>Cash from financing
 FORMULA: =K19+K20
-WHY: Debt plus equity financing cash; both policies are zero in the base case.</t>
+WHY: Debt plus equity financing cash; both policies are zero in the base case.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="L74" authorId="0" shapeId="0">
       <text>
         <t>Cash from financing
 FORMULA: =L19+L20
-WHY: Debt plus equity financing cash; both policies are zero in the base case.</t>
+WHY: Debt plus equity financing cash; both policies are zero in the base case.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="M74" authorId="0" shapeId="0">
       <text>
         <t>Cash from financing
 FORMULA: =M19+M20
-WHY: Debt plus equity financing cash; both policies are zero in the base case.</t>
+WHY: Debt plus equity financing cash; both policies are zero in the base case.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="N74" authorId="0" shapeId="0">
       <text>
         <t>Cash from financing
 FORMULA: =N19+N20
-WHY: Debt plus equity financing cash; both policies are zero in the base case.</t>
+WHY: Debt plus equity financing cash; both policies are zero in the base case.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="B76" authorId="0" shapeId="0">
       <text>
         <t>Δ Cash
 WHY: CFO minus CapEx plus financing; net change that rolls opening cash to closing.
-PATTERN: ={c}65-{c}69+{c}74</t>
+PATTERN: ={c}65-{c}69+{c}74
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="J76" authorId="0" shapeId="0">
       <text>
         <t>Δ Cash
 FORMULA: =J65-J69+J74
-WHY: CFO minus CapEx plus financing; net change that rolls opening cash to closing.</t>
+WHY: CFO minus CapEx plus financing; net change that rolls opening cash to closing.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="K76" authorId="0" shapeId="0">
       <text>
         <t>Δ Cash
 FORMULA: =K65-K69+K74
-WHY: CFO minus CapEx plus financing; net change that rolls opening cash to closing.</t>
+WHY: CFO minus CapEx plus financing; net change that rolls opening cash to closing.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="L76" authorId="0" shapeId="0">
       <text>
         <t>Δ Cash
 FORMULA: =L65-L69+L74
-WHY: CFO minus CapEx plus financing; net change that rolls opening cash to closing.</t>
+WHY: CFO minus CapEx plus financing; net change that rolls opening cash to closing.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="M76" authorId="0" shapeId="0">
       <text>
         <t>Δ Cash
 FORMULA: =M65-M69+M74
-WHY: CFO minus CapEx plus financing; net change that rolls opening cash to closing.</t>
+WHY: CFO minus CapEx plus financing; net change that rolls opening cash to closing.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="N76" authorId="0" shapeId="0">
       <text>
         <t>Δ Cash
 FORMULA: =N65-N69+N74
-WHY: CFO minus CapEx plus financing; net change that rolls opening cash to closing.</t>
+WHY: CFO minus CapEx plus financing; net change that rolls opening cash to closing.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="B77" authorId="0" shapeId="0">
       <text>
         <t>Opening cash
 WHY: Starts at prior balance-sheet cash so the cash roll-forward matches history.
-PATTERN: ={p}41</t>
+PATTERN: ={p}41
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="J77" authorId="0" shapeId="0">
       <text>
         <t>Opening cash
 FORMULA: =I41
-WHY: Starts at prior balance-sheet cash so the cash roll-forward matches history.</t>
+WHY: Starts at prior balance-sheet cash so the cash roll-forward matches history.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="K77" authorId="0" shapeId="0">
       <text>
         <t>Opening cash
 FORMULA: =J41
-WHY: Starts at prior balance-sheet cash so the cash roll-forward matches history.</t>
+WHY: Starts at prior balance-sheet cash so the cash roll-forward matches history.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="L77" authorId="0" shapeId="0">
       <text>
         <t>Opening cash
 FORMULA: =K41
-WHY: Starts at prior balance-sheet cash so the cash roll-forward matches history.</t>
+WHY: Starts at prior balance-sheet cash so the cash roll-forward matches history.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="M77" authorId="0" shapeId="0">
       <text>
         <t>Opening cash
 FORMULA: =L41
-WHY: Starts at prior balance-sheet cash so the cash roll-forward matches history.</t>
+WHY: Starts at prior balance-sheet cash so the cash roll-forward matches history.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="N77" authorId="0" shapeId="0">
       <text>
         <t>Opening cash
 FORMULA: =M41
-WHY: Starts at prior balance-sheet cash so the cash roll-forward matches history.</t>
+WHY: Starts at prior balance-sheet cash so the cash roll-forward matches history.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="B78" authorId="0" shapeId="0">
       <text>
         <t>Closing cash
 WHY: Opening cash plus Δ cash; feeds BS cash and the cash-flow check.
-PATTERN: ={c}77+{c}76</t>
+PATTERN: ={c}77+{c}76
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="J78" authorId="0" shapeId="0">
       <text>
         <t>Closing cash
 FORMULA: =J77+J76
-WHY: Opening cash plus Δ cash; feeds BS cash and the cash-flow check.</t>
+WHY: Opening cash plus Δ cash; feeds BS cash and the cash-flow check.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="K78" authorId="0" shapeId="0">
       <text>
         <t>Closing cash
 FORMULA: =K77+K76
-WHY: Opening cash plus Δ cash; feeds BS cash and the cash-flow check.</t>
+WHY: Opening cash plus Δ cash; feeds BS cash and the cash-flow check.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="L78" authorId="0" shapeId="0">
       <text>
         <t>Closing cash
 FORMULA: =L77+L76
-WHY: Opening cash plus Δ cash; feeds BS cash and the cash-flow check.</t>
+WHY: Opening cash plus Δ cash; feeds BS cash and the cash-flow check.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="M78" authorId="0" shapeId="0">
       <text>
         <t>Closing cash
 FORMULA: =M77+M76
-WHY: Opening cash plus Δ cash; feeds BS cash and the cash-flow check.</t>
+WHY: Opening cash plus Δ cash; feeds BS cash and the cash-flow check.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="N78" authorId="0" shapeId="0">
       <text>
         <t>Closing cash
 FORMULA: =N77+N76
-WHY: Opening cash plus Δ cash; feeds BS cash and the cash-flow check.</t>
+WHY: Opening cash plus Δ cash; feeds BS cash and the cash-flow check.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="B80" authorId="0" shapeId="0">
       <text>
         <t>Cash check
 WHY: Closing CF cash minus BS cash; must be zero when statements are linked.
-PATTERN: ={c}78-{c}41</t>
+PATTERN: ={c}78-{c}41
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="J80" authorId="0" shapeId="0">
       <text>
         <t>Cash check
 FORMULA: =J78-J41
-WHY: Closing CF cash minus BS cash; must be zero when statements are linked.</t>
+WHY: Closing CF cash minus BS cash; must be zero when statements are linked.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="K80" authorId="0" shapeId="0">
       <text>
         <t>Cash check
 FORMULA: =K78-K41
-WHY: Closing CF cash minus BS cash; must be zero when statements are linked.</t>
+WHY: Closing CF cash minus BS cash; must be zero when statements are linked.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="L80" authorId="0" shapeId="0">
       <text>
         <t>Cash check
 FORMULA: =L78-L41
-WHY: Closing CF cash minus BS cash; must be zero when statements are linked.</t>
+WHY: Closing CF cash minus BS cash; must be zero when statements are linked.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="M80" authorId="0" shapeId="0">
       <text>
         <t>Cash check
 FORMULA: =M78-M41
-WHY: Closing CF cash minus BS cash; must be zero when statements are linked.</t>
+WHY: Closing CF cash minus BS cash; must be zero when statements are linked.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="N80" authorId="0" shapeId="0">
       <text>
         <t>Cash check
 FORMULA: =N78-N41
-WHY: Closing CF cash minus BS cash; must be zero when statements are linked.</t>
+WHY: Closing CF cash minus BS cash; must be zero when statements are linked.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="B85" authorId="0" shapeId="0">
       <text>
         <t>WC: AR
 WHY: Working-capital schedule AR mirrors the balance-sheet AR used in ΔNWC.
-PATTERN: ={c}42</t>
+PATTERN: ={c}42
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="J85" authorId="0" shapeId="0">
       <text>
         <t>WC: AR
 FORMULA: =J42
-WHY: Working-capital schedule AR mirrors the balance-sheet AR used in ΔNWC.</t>
+WHY: Working-capital schedule AR mirrors the balance-sheet AR used in ΔNWC.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="K85" authorId="0" shapeId="0">
       <text>
         <t>WC: AR
 FORMULA: =K42
-WHY: Working-capital schedule AR mirrors the balance-sheet AR used in ΔNWC.</t>
+WHY: Working-capital schedule AR mirrors the balance-sheet AR used in ΔNWC.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="L85" authorId="0" shapeId="0">
       <text>
         <t>WC: AR
 FORMULA: =L42
-WHY: Working-capital schedule AR mirrors the balance-sheet AR used in ΔNWC.</t>
+WHY: Working-capital schedule AR mirrors the balance-sheet AR used in ΔNWC.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="M85" authorId="0" shapeId="0">
       <text>
         <t>WC: AR
 FORMULA: =M42
-WHY: Working-capital schedule AR mirrors the balance-sheet AR used in ΔNWC.</t>
+WHY: Working-capital schedule AR mirrors the balance-sheet AR used in ΔNWC.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="N85" authorId="0" shapeId="0">
       <text>
         <t>WC: AR
 FORMULA: =N42
-WHY: Working-capital schedule AR mirrors the balance-sheet AR used in ΔNWC.</t>
+WHY: Working-capital schedule AR mirrors the balance-sheet AR used in ΔNWC.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="B86" authorId="0" shapeId="0">
       <text>
         <t>WC: Inventory
 WHY: Working-capital inventory mirrors BS inventory (zero for this software business).
-PATTERN: ={c}43</t>
+PATTERN: ={c}43
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="J86" authorId="0" shapeId="0">
       <text>
         <t>WC: Inventory
 FORMULA: =J43
-WHY: Working-capital inventory mirrors BS inventory (zero for this software business).</t>
+WHY: Working-capital inventory mirrors BS inventory (zero for this software business).
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="K86" authorId="0" shapeId="0">
       <text>
         <t>WC: Inventory
 FORMULA: =K43
-WHY: Working-capital inventory mirrors BS inventory (zero for this software business).</t>
+WHY: Working-capital inventory mirrors BS inventory (zero for this software business).
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="L86" authorId="0" shapeId="0">
       <text>
         <t>WC: Inventory
 FORMULA: =L43
-WHY: Working-capital inventory mirrors BS inventory (zero for this software business).</t>
+WHY: Working-capital inventory mirrors BS inventory (zero for this software business).
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="M86" authorId="0" shapeId="0">
       <text>
         <t>WC: Inventory
 FORMULA: =M43
-WHY: Working-capital inventory mirrors BS inventory (zero for this software business).</t>
+WHY: Working-capital inventory mirrors BS inventory (zero for this software business).
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="N86" authorId="0" shapeId="0">
       <text>
         <t>WC: Inventory
 FORMULA: =N43
-WHY: Working-capital inventory mirrors BS inventory (zero for this software business).</t>
+WHY: Working-capital inventory mirrors BS inventory (zero for this software business).
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="B87" authorId="0" shapeId="0">
       <text>
         <t>WC: AP
 WHY: Working-capital AP mirrors BS AP so NWC uses the same operating balances.
-PATTERN: ={c}48</t>
+PATTERN: ={c}48
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="J87" authorId="0" shapeId="0">
       <text>
         <t>WC: AP
 FORMULA: =J48
-WHY: Working-capital AP mirrors BS AP so NWC uses the same operating balances.</t>
+WHY: Working-capital AP mirrors BS AP so NWC uses the same operating balances.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="K87" authorId="0" shapeId="0">
       <text>
         <t>WC: AP
 FORMULA: =K48
-WHY: Working-capital AP mirrors BS AP so NWC uses the same operating balances.</t>
+WHY: Working-capital AP mirrors BS AP so NWC uses the same operating balances.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="L87" authorId="0" shapeId="0">
       <text>
         <t>WC: AP
 FORMULA: =L48
-WHY: Working-capital AP mirrors BS AP so NWC uses the same operating balances.</t>
+WHY: Working-capital AP mirrors BS AP so NWC uses the same operating balances.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="M87" authorId="0" shapeId="0">
       <text>
         <t>WC: AP
 FORMULA: =M48
-WHY: Working-capital AP mirrors BS AP so NWC uses the same operating balances.</t>
+WHY: Working-capital AP mirrors BS AP so NWC uses the same operating balances.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="N87" authorId="0" shapeId="0">
       <text>
         <t>WC: AP
 FORMULA: =N48
-WHY: Working-capital AP mirrors BS AP so NWC uses the same operating balances.</t>
+WHY: Working-capital AP mirrors BS AP so NWC uses the same operating balances.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="B88" authorId="0" shapeId="0">
       <text>
         <t>Net working capital
 WHY: AR + inventory − AP; operating NWC (deferred already netted in AR).
-PATTERN: ={c}85+{c}86-{c}87</t>
+PATTERN: ={c}85+{c}86-{c}87
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="J88" authorId="0" shapeId="0">
       <text>
         <t>Net working capital
 FORMULA: =J85+J86-J87
-WHY: AR + inventory − AP; operating NWC (deferred already netted in AR).</t>
+WHY: AR + inventory − AP; operating NWC (deferred already netted in AR).
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="K88" authorId="0" shapeId="0">
       <text>
         <t>Net working capital
 FORMULA: =K85+K86-K87
-WHY: AR + inventory − AP; operating NWC (deferred already netted in AR).</t>
+WHY: AR + inventory − AP; operating NWC (deferred already netted in AR).
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="L88" authorId="0" shapeId="0">
       <text>
         <t>Net working capital
 FORMULA: =L85+L86-L87
-WHY: AR + inventory − AP; operating NWC (deferred already netted in AR).</t>
+WHY: AR + inventory − AP; operating NWC (deferred already netted in AR).
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="M88" authorId="0" shapeId="0">
       <text>
         <t>Net working capital
 FORMULA: =M85+M86-M87
-WHY: AR + inventory − AP; operating NWC (deferred already netted in AR).</t>
+WHY: AR + inventory − AP; operating NWC (deferred already netted in AR).
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="N88" authorId="0" shapeId="0">
       <text>
         <t>Net working capital
 FORMULA: =N85+N86-N87
-WHY: AR + inventory − AP; operating NWC (deferred already netted in AR).</t>
+WHY: AR + inventory − AP; operating NWC (deferred already netted in AR).
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="B89" authorId="0" shapeId="0">
       <text>
         <t>Change in NWC
 WHY: Year-over-year NWC change; the cash investment/(release) used in CFO and FCFF.
-PATTERN: ={c}88-{p}88</t>
+PATTERN: ={c}88-{p}88
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="J89" authorId="0" shapeId="0">
       <text>
         <t>Change in NWC
 FORMULA: =J88-I88
-WHY: Year-over-year NWC change; the cash investment/(release) used in CFO and FCFF.</t>
+WHY: Year-over-year NWC change; the cash investment/(release) used in CFO and FCFF.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="K89" authorId="0" shapeId="0">
       <text>
         <t>Change in NWC
 FORMULA: =K88-J88
-WHY: Year-over-year NWC change; the cash investment/(release) used in CFO and FCFF.</t>
+WHY: Year-over-year NWC change; the cash investment/(release) used in CFO and FCFF.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="L89" authorId="0" shapeId="0">
       <text>
         <t>Change in NWC
 FORMULA: =L88-K88
-WHY: Year-over-year NWC change; the cash investment/(release) used in CFO and FCFF.</t>
+WHY: Year-over-year NWC change; the cash investment/(release) used in CFO and FCFF.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="M89" authorId="0" shapeId="0">
       <text>
         <t>Change in NWC
 FORMULA: =M88-L88
-WHY: Year-over-year NWC change; the cash investment/(release) used in CFO and FCFF.</t>
+WHY: Year-over-year NWC change; the cash investment/(release) used in CFO and FCFF.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="N89" authorId="0" shapeId="0">
       <text>
         <t>Change in NWC
 FORMULA: =N88-M88
-WHY: Year-over-year NWC change; the cash investment/(release) used in CFO and FCFF.</t>
+WHY: Year-over-year NWC change; the cash investment/(release) used in CFO and FCFF.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="B92" authorId="0" shapeId="0">
       <text>
         <t>PPE opening
 WHY: Prior closing PP&amp;E (FY1 opens at last historical I44); base for CapEx and D&amp;A.
-PATTERN: ={p}95 or I44</t>
+PATTERN: ={p}95 or I44
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="J92" authorId="0" shapeId="0">
       <text>
         <t>PPE opening
 FORMULA: =I95 or I44
-WHY: Prior closing PP&amp;E (FY1 opens at last historical I44); base for CapEx and D&amp;A.</t>
+WHY: Prior closing PP&amp;E (FY1 opens at last historical I44); base for CapEx and D&amp;A.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="K92" authorId="0" shapeId="0">
       <text>
         <t>PPE opening
 FORMULA: =J95 or I44
-WHY: Prior closing PP&amp;E (FY1 opens at last historical I44); base for CapEx and D&amp;A.</t>
+WHY: Prior closing PP&amp;E (FY1 opens at last historical I44); base for CapEx and D&amp;A.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="L92" authorId="0" shapeId="0">
       <text>
         <t>PPE opening
 FORMULA: =K95 or I44
-WHY: Prior closing PP&amp;E (FY1 opens at last historical I44); base for CapEx and D&amp;A.</t>
+WHY: Prior closing PP&amp;E (FY1 opens at last historical I44); base for CapEx and D&amp;A.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="M92" authorId="0" shapeId="0">
       <text>
         <t>PPE opening
 FORMULA: =L95 or I44
-WHY: Prior closing PP&amp;E (FY1 opens at last historical I44); base for CapEx and D&amp;A.</t>
+WHY: Prior closing PP&amp;E (FY1 opens at last historical I44); base for CapEx and D&amp;A.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="N92" authorId="0" shapeId="0">
       <text>
         <t>PPE opening
 FORMULA: =M95 or I44
-WHY: Prior closing PP&amp;E (FY1 opens at last historical I44); base for CapEx and D&amp;A.</t>
+WHY: Prior closing PP&amp;E (FY1 opens at last historical I44); base for CapEx and D&amp;A.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="B93" authorId="0" shapeId="0">
       <text>
         <t>PPE + CapEx
 WHY: Same CapEx dollars as CF; additions that grow the gross PP&amp;E stock.
-PATTERN: ={c}24*{c}18</t>
+PATTERN: ={c}24*{c}18
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="J93" authorId="0" shapeId="0">
       <text>
         <t>PPE + CapEx
 FORMULA: =J24*J18
-WHY: Same CapEx dollars as CF; additions that grow the gross PP&amp;E stock.</t>
+WHY: Same CapEx dollars as CF; additions that grow the gross PP&amp;E stock.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="K93" authorId="0" shapeId="0">
       <text>
         <t>PPE + CapEx
 FORMULA: =K24*K18
-WHY: Same CapEx dollars as CF; additions that grow the gross PP&amp;E stock.</t>
+WHY: Same CapEx dollars as CF; additions that grow the gross PP&amp;E stock.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="L93" authorId="0" shapeId="0">
       <text>
         <t>PPE + CapEx
 FORMULA: =L24*L18
-WHY: Same CapEx dollars as CF; additions that grow the gross PP&amp;E stock.</t>
+WHY: Same CapEx dollars as CF; additions that grow the gross PP&amp;E stock.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="M93" authorId="0" shapeId="0">
       <text>
         <t>PPE + CapEx
 FORMULA: =M24*M18
-WHY: Same CapEx dollars as CF; additions that grow the gross PP&amp;E stock.</t>
+WHY: Same CapEx dollars as CF; additions that grow the gross PP&amp;E stock.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="N93" authorId="0" shapeId="0">
       <text>
         <t>PPE + CapEx
 FORMULA: =N24*N18
-WHY: Same CapEx dollars as CF; additions that grow the gross PP&amp;E stock.</t>
+WHY: Same CapEx dollars as CF; additions that grow the gross PP&amp;E stock.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="B94" authorId="0" shapeId="0">
       <text>
         <t>PPE − D&amp;A
 WHY: Depreciation on opening PP&amp;E; reduces net PP&amp;E in the roll-forward.
-PATTERN: ={c}92*{c}11</t>
+PATTERN: ={c}92*{c}11
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="J94" authorId="0" shapeId="0">
       <text>
         <t>PPE − D&amp;A
 FORMULA: =J92*J11
-WHY: Depreciation on opening PP&amp;E; reduces net PP&amp;E in the roll-forward.</t>
+WHY: Depreciation on opening PP&amp;E; reduces net PP&amp;E in the roll-forward.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="K94" authorId="0" shapeId="0">
       <text>
         <t>PPE − D&amp;A
 FORMULA: =K92*K11
-WHY: Depreciation on opening PP&amp;E; reduces net PP&amp;E in the roll-forward.</t>
+WHY: Depreciation on opening PP&amp;E; reduces net PP&amp;E in the roll-forward.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="L94" authorId="0" shapeId="0">
       <text>
         <t>PPE − D&amp;A
 FORMULA: =L92*L11
-WHY: Depreciation on opening PP&amp;E; reduces net PP&amp;E in the roll-forward.</t>
+WHY: Depreciation on opening PP&amp;E; reduces net PP&amp;E in the roll-forward.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="M94" authorId="0" shapeId="0">
       <text>
         <t>PPE − D&amp;A
 FORMULA: =M92*M11
-WHY: Depreciation on opening PP&amp;E; reduces net PP&amp;E in the roll-forward.</t>
+WHY: Depreciation on opening PP&amp;E; reduces net PP&amp;E in the roll-forward.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="N94" authorId="0" shapeId="0">
       <text>
         <t>PPE − D&amp;A
 FORMULA: =N92*N11
-WHY: Depreciation on opening PP&amp;E; reduces net PP&amp;E in the roll-forward.</t>
+WHY: Depreciation on opening PP&amp;E; reduces net PP&amp;E in the roll-forward.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="B95" authorId="0" shapeId="0">
       <text>
         <t>PPE closing
 WHY: Open + CapEx − D&amp;A; closing net PP&amp;E posted to the balance sheet.
-PATTERN: ={c}92+{c}93-{c}94</t>
+PATTERN: ={c}92+{c}93-{c}94
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="J95" authorId="0" shapeId="0">
       <text>
         <t>PPE closing
 FORMULA: =J92+J93-J94
-WHY: Open + CapEx − D&amp;A; closing net PP&amp;E posted to the balance sheet.</t>
+WHY: Open + CapEx − D&amp;A; closing net PP&amp;E posted to the balance sheet.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="K95" authorId="0" shapeId="0">
       <text>
         <t>PPE closing
 FORMULA: =K92+K93-K94
-WHY: Open + CapEx − D&amp;A; closing net PP&amp;E posted to the balance sheet.</t>
+WHY: Open + CapEx − D&amp;A; closing net PP&amp;E posted to the balance sheet.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="L95" authorId="0" shapeId="0">
       <text>
         <t>PPE closing
 FORMULA: =L92+L93-L94
-WHY: Open + CapEx − D&amp;A; closing net PP&amp;E posted to the balance sheet.</t>
+WHY: Open + CapEx − D&amp;A; closing net PP&amp;E posted to the balance sheet.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="M95" authorId="0" shapeId="0">
       <text>
         <t>PPE closing
 FORMULA: =M92+M93-M94
-WHY: Open + CapEx − D&amp;A; closing net PP&amp;E posted to the balance sheet.</t>
+WHY: Open + CapEx − D&amp;A; closing net PP&amp;E posted to the balance sheet.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="N95" authorId="0" shapeId="0">
       <text>
         <t>PPE closing
 FORMULA: =N92+N93-N94
-WHY: Open + CapEx − D&amp;A; closing net PP&amp;E posted to the balance sheet.</t>
+WHY: Open + CapEx − D&amp;A; closing net PP&amp;E posted to the balance sheet.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="B98" authorId="0" shapeId="0">
       <text>
         <t>Debt opening
 WHY: Prior closing debt (FY1 opens at historical I49); base for interest and issuance.
-PATTERN: ={p}100 or I49</t>
+PATTERN: ={p}100 or I49
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454726000030/fico-20260630.htm</t>
       </text>
     </comment>
     <comment ref="J98" authorId="0" shapeId="0">
       <text>
         <t>Debt opening
 FORMULA: =I100 or I49
-WHY: Prior closing debt (FY1 opens at historical I49); base for interest and issuance.</t>
+WHY: Prior closing debt (FY1 opens at historical I49); base for interest and issuance.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454726000030/fico-20260630.htm</t>
       </text>
     </comment>
     <comment ref="K98" authorId="0" shapeId="0">
       <text>
         <t>Debt opening
 FORMULA: =J100 or I49
-WHY: Prior closing debt (FY1 opens at historical I49); base for interest and issuance.</t>
+WHY: Prior closing debt (FY1 opens at historical I49); base for interest and issuance.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454726000030/fico-20260630.htm</t>
       </text>
     </comment>
     <comment ref="L98" authorId="0" shapeId="0">
       <text>
         <t>Debt opening
 FORMULA: =K100 or I49
-WHY: Prior closing debt (FY1 opens at historical I49); base for interest and issuance.</t>
+WHY: Prior closing debt (FY1 opens at historical I49); base for interest and issuance.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454726000030/fico-20260630.htm</t>
       </text>
     </comment>
     <comment ref="M98" authorId="0" shapeId="0">
       <text>
         <t>Debt opening
 FORMULA: =L100 or I49
-WHY: Prior closing debt (FY1 opens at historical I49); base for interest and issuance.</t>
+WHY: Prior closing debt (FY1 opens at historical I49); base for interest and issuance.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454726000030/fico-20260630.htm</t>
       </text>
     </comment>
     <comment ref="N98" authorId="0" shapeId="0">
       <text>
         <t>Debt opening
 FORMULA: =M100 or I49
-WHY: Prior closing debt (FY1 opens at historical I49); base for interest and issuance.</t>
+WHY: Prior closing debt (FY1 opens at historical I49); base for interest and issuance.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454726000030/fico-20260630.htm</t>
       </text>
     </comment>
     <comment ref="B99" authorId="0" shapeId="0">
       <text>
         <t>Debt issuance
 WHY: Links the debt policy row into the schedule; base case keeps this at zero.
-PATTERN: ={c}19</t>
+PATTERN: ={c}19
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="J99" authorId="0" shapeId="0">
       <text>
         <t>Debt issuance
 FORMULA: =J19
-WHY: Links the debt policy row into the schedule; base case keeps this at zero.</t>
+WHY: Links the debt policy row into the schedule; base case keeps this at zero.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="K99" authorId="0" shapeId="0">
       <text>
         <t>Debt issuance
 FORMULA: =K19
-WHY: Links the debt policy row into the schedule; base case keeps this at zero.</t>
+WHY: Links the debt policy row into the schedule; base case keeps this at zero.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="L99" authorId="0" shapeId="0">
       <text>
         <t>Debt issuance
 FORMULA: =L19
-WHY: Links the debt policy row into the schedule; base case keeps this at zero.</t>
+WHY: Links the debt policy row into the schedule; base case keeps this at zero.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="M99" authorId="0" shapeId="0">
       <text>
         <t>Debt issuance
 FORMULA: =M19
-WHY: Links the debt policy row into the schedule; base case keeps this at zero.</t>
+WHY: Links the debt policy row into the schedule; base case keeps this at zero.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="N99" authorId="0" shapeId="0">
       <text>
         <t>Debt issuance
 FORMULA: =N19
-WHY: Links the debt policy row into the schedule; base case keeps this at zero.</t>
+WHY: Links the debt policy row into the schedule; base case keeps this at zero.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="B100" authorId="0" shapeId="0">
       <text>
         <t>Debt closing
 WHY: Open plus issuance/(repayment); closing debt posted to the balance sheet.
-PATTERN: ={c}98+{c}99</t>
+PATTERN: ={c}98+{c}99
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="J100" authorId="0" shapeId="0">
       <text>
         <t>Debt closing
 FORMULA: =J98+J99
-WHY: Open plus issuance/(repayment); closing debt posted to the balance sheet.</t>
+WHY: Open plus issuance/(repayment); closing debt posted to the balance sheet.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="K100" authorId="0" shapeId="0">
       <text>
         <t>Debt closing
 FORMULA: =K98+K99
-WHY: Open plus issuance/(repayment); closing debt posted to the balance sheet.</t>
+WHY: Open plus issuance/(repayment); closing debt posted to the balance sheet.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="L100" authorId="0" shapeId="0">
       <text>
         <t>Debt closing
 FORMULA: =L98+L99
-WHY: Open plus issuance/(repayment); closing debt posted to the balance sheet.</t>
+WHY: Open plus issuance/(repayment); closing debt posted to the balance sheet.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="M100" authorId="0" shapeId="0">
       <text>
         <t>Debt closing
 FORMULA: =M98+M99
-WHY: Open plus issuance/(repayment); closing debt posted to the balance sheet.</t>
+WHY: Open plus issuance/(repayment); closing debt posted to the balance sheet.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="N100" authorId="0" shapeId="0">
       <text>
         <t>Debt closing
 FORMULA: =N98+N99
-WHY: Open plus issuance/(repayment); closing debt posted to the balance sheet.</t>
+WHY: Open plus issuance/(repayment); closing debt posted to the balance sheet.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="B101" authorId="0" shapeId="0">
       <text>
         <t>Interest (schedule)
 WHY: Opening debt × interest%; same economics as IS interest, from the debt schedule.
-PATTERN: ={c}98*{c}12</t>
+PATTERN: ={c}98*{c}12
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="J101" authorId="0" shapeId="0">
       <text>
         <t>Interest (schedule)
 FORMULA: =J98*J12
-WHY: Opening debt × interest%; same economics as IS interest, from the debt schedule.</t>
+WHY: Opening debt × interest%; same economics as IS interest, from the debt schedule.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="K101" authorId="0" shapeId="0">
       <text>
         <t>Interest (schedule)
 FORMULA: =K98*K12
-WHY: Opening debt × interest%; same economics as IS interest, from the debt schedule.</t>
+WHY: Opening debt × interest%; same economics as IS interest, from the debt schedule.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="L101" authorId="0" shapeId="0">
       <text>
         <t>Interest (schedule)
 FORMULA: =L98*L12
-WHY: Opening debt × interest%; same economics as IS interest, from the debt schedule.</t>
+WHY: Opening debt × interest%; same economics as IS interest, from the debt schedule.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="M101" authorId="0" shapeId="0">
       <text>
         <t>Interest (schedule)
 FORMULA: =M98*M12
-WHY: Opening debt × interest%; same economics as IS interest, from the debt schedule.</t>
+WHY: Opening debt × interest%; same economics as IS interest, from the debt schedule.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="N101" authorId="0" shapeId="0">
       <text>
         <t>Interest (schedule)
 FORMULA: =N98*N12
-WHY: Opening debt × interest%; same economics as IS interest, from the debt schedule.</t>
+WHY: Opening debt × interest%; same economics as IS interest, from the debt schedule.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
   </commentList>
@@ -6012,12 +6320,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U138"/>
+  <dimension ref="A1:V138"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.109375" defaultRowHeight="15.6" outlineLevelRow="1"/>
   <cols>
     <col width="1.88671875" customWidth="1" style="19" min="1" max="1"/>
     <col width="42" customWidth="1" style="19" min="2" max="3"/>
-    <col width="72" customWidth="1" min="3" max="3"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" style="47" min="4" max="4"/>
     <col width="16" customWidth="1" style="19" min="5" max="9"/>
     <col width="16" customWidth="1" min="6" max="6"/>
@@ -6035,7 +6343,8 @@
     <col width="36" customWidth="1" min="18" max="18"/>
     <col width="42" customWidth="1" min="19" max="19"/>
     <col width="48" customWidth="1" min="20" max="20"/>
-    <col width="36" customWidth="1" min="21" max="21"/>
+    <col width="42" customWidth="1" min="21" max="21"/>
+    <col width="55" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6165,12 +6474,12 @@
     <row r="4">
       <c r="B4" s="137" t="inlineStr">
         <is>
-          <t>vengeanceaiUSCMODEL4: hover any yellow/green assumption cell (J–N) for WHY + SOURCE commentary; col C also shows WHY | SOURCE | HOW</t>
+          <t>vengeanceaiUSCMODEL4: hover J–N for WHY+SOURCE; click blue Source link in col U (or LINK: URL in col C / V) to open the filing</t>
         </is>
       </c>
       <c r="P4" s="138" t="inlineStr">
         <is>
-          <t>ASSUMPTIONS EXPLAINED — every driver (also in each cell comment)</t>
+          <t>ASSUMPTIONS EXPLAINED — click blue Source (col U) for the filing/data</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6503,7 @@
       <c r="N5" s="65" t="n"/>
       <c r="P5" s="139" t="inlineStr">
         <is>
-          <t>Yellow = policy judgment. Green = Excel equations linked to FY25 (col I). Hover J–N (or B label) for WHY + SOURCE. Column C is text only (not a formula).</t>
+          <t>Yellow = policy. Green = FY25-linked equations. Col U = clickable hyperlink. Col V = full URL (also clickable).</t>
         </is>
       </c>
     </row>
@@ -6232,11 +6541,16 @@
       </c>
       <c r="U6" s="140" t="inlineStr">
         <is>
-          <t>Source</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" hidden="1" outlineLevel="1" ht="36" customHeight="1">
+          <t>Source (click)</t>
+        </is>
+      </c>
+      <c r="V6" s="140" t="inlineStr">
+        <is>
+          <t>Source URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" hidden="1" outlineLevel="1" ht="40" customHeight="1">
       <c r="B7" s="19" t="inlineStr">
         <is>
           <t>Revenue Growth (% Change)</t>
@@ -6244,7 +6558,7 @@
       </c>
       <c r="C7" s="141" t="inlineStr">
         <is>
-          <t>WHY: Y1 ≈ company FY2026 revenue guidance (~$2.53B / FY25 $1.991B − 1 ≈ 27%). Then fade toward terminal g=3% (not straight-lined). This is the main forward-lookin… | SOURCE: FICO FY2026 guidance + fade policy | HOW: Yellow POLICY input: 27% / 16% / 13% / 10% / 7%.</t>
+          <t>WHY: Y1 ≈ company FY2026 revenue guidance (~$2.53B / FY25 $1.991B − 1 ≈ 27%). Then fade toward terminal g=3% (not straight… | SOURCE: SEC EX-99.1 Q3 FY2026 — updated FY2026 revenue guidance $2.53B | LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454726000031/exhibit991erq32026.htm | HOW: Yellow POLICY input: 27% / 16% / 13% / 10% / 7%.</t>
         </is>
       </c>
       <c r="D7" s="46" t="n"/>
@@ -6303,13 +6617,18 @@
           <t>Y1 ≈ company FY2026 revenue guidance (~$2.53B / FY25 $1.991B − 1 ≈ 27%). Then fade toward terminal g=3% (not straight-lined). This is the main forward-looking judgment; it drives Rev → GP → EBT → Net Earnings → CF.</t>
         </is>
       </c>
-      <c r="U7" s="144" t="inlineStr">
-        <is>
-          <t>FICO FY2026 guidance + fade policy</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" hidden="1" outlineLevel="1" ht="36" customHeight="1">
+      <c r="U7" s="145" t="inlineStr">
+        <is>
+          <t>SEC EX-99.1 Q3 FY2026 — updated FY2026 revenue guidance $2.53B</t>
+        </is>
+      </c>
+      <c r="V7" s="145" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454726000031/exhibit991erq32026.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" hidden="1" outlineLevel="1" ht="40" customHeight="1">
       <c r="B8" s="19" t="inlineStr">
         <is>
           <t>Cost of Goods Sold (% of Revenue)</t>
@@ -6317,7 +6636,7 @@
       </c>
       <c r="C8" s="141" t="inlineStr">
         <is>
-          <t>WHY: Locks in latest reported cost structure (~17.8%). Scores mix is high-margin; holding FY25 is conservative vs further mix shift. | SOURCE: SEC 10-K FY2025 — Cost of revenues / Total revenues | HOW: Excel equation: I25/I24 (FY25 COGS ÷ FY25 Revenue) held flat.</t>
+          <t>WHY: Locks in latest reported cost structure (~17.8%). Scores mix is high-margin; holding FY25 is conservative vs further … | SOURCE: SEC 10-K FY2025 — Cost of revenues / Total revenues | LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm | HOW: Excel equation: I25/I24 (FY25 COGS ÷ FY25 Revenue) held flat.</t>
         </is>
       </c>
       <c r="D8" s="47" t="n"/>
@@ -6341,23 +6660,23 @@
         <f>I25/I24</f>
         <v/>
       </c>
-      <c r="J8" s="145">
+      <c r="J8" s="146">
         <f>$I$25/$I$24</f>
         <v/>
       </c>
-      <c r="K8" s="145">
+      <c r="K8" s="146">
         <f>$I$25/$I$24</f>
         <v/>
       </c>
-      <c r="L8" s="145">
+      <c r="L8" s="146">
         <f>$I$25/$I$24</f>
         <v/>
       </c>
-      <c r="M8" s="145">
+      <c r="M8" s="146">
         <f>$I$25/$I$24</f>
         <v/>
       </c>
-      <c r="N8" s="145">
+      <c r="N8" s="146">
         <f>$I$25/$I$24</f>
         <v/>
       </c>
@@ -6384,13 +6703,18 @@
           <t>Locks in latest reported cost structure (~17.8%). Scores mix is high-margin; holding FY25 is conservative vs further mix shift.</t>
         </is>
       </c>
-      <c r="U8" s="144" t="inlineStr">
+      <c r="U8" s="145" t="inlineStr">
         <is>
           <t>SEC 10-K FY2025 — Cost of revenues / Total revenues</t>
         </is>
       </c>
-    </row>
-    <row r="9" hidden="1" outlineLevel="1" ht="36" customHeight="1">
+      <c r="V8" s="145" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" hidden="1" outlineLevel="1" ht="40" customHeight="1">
       <c r="B9" s="19" t="inlineStr">
         <is>
           <t>SGA % of Revenue (equation)</t>
@@ -6398,47 +6722,47 @@
       </c>
       <c r="C9" s="141" t="inlineStr">
         <is>
-          <t>WHY: Normalize one-time restructuring ($10.9M). Mild efficiency grind reflects operating leverage as revenue scales; floored at 5%. | SOURCE: SEC 10-K FY2025 — SG&amp;A + restructuring note | HOW: Equation: (I28 − 10,922)/I24 − 50bps × year. Strips FY25 restructuring; then −0.5% of sales each year.</t>
+          <t>WHY: Normalize one-time restructuring ($10.9M). Mild efficiency grind reflects operating leverage as revenue scales; floor… | SOURCE: SEC 10-K FY2025 — SG&amp;A + restructuring note | LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm | HOW: Equation: (I28 − 10,922)/I24 − 50bps × year. Strips FY25 restructuring; then −0.5% of sales each year.</t>
         </is>
       </c>
       <c r="D9" s="47" t="n"/>
-      <c r="E9" s="146">
+      <c r="E9" s="147">
         <f>E28</f>
         <v/>
       </c>
-      <c r="F9" s="146">
+      <c r="F9" s="147">
         <f>F28</f>
         <v/>
       </c>
-      <c r="G9" s="146">
+      <c r="G9" s="147">
         <f>G28</f>
         <v/>
       </c>
-      <c r="H9" s="146">
+      <c r="H9" s="147">
         <f>H28</f>
         <v/>
       </c>
-      <c r="I9" s="146">
+      <c r="I9" s="147">
         <f>I28</f>
         <v/>
       </c>
-      <c r="J9" s="147">
+      <c r="J9" s="148">
         <f>MAX(0.05,(($I$28-10922.0)/$I$24)-0.005)</f>
         <v/>
       </c>
-      <c r="K9" s="147">
+      <c r="K9" s="148">
         <f>MAX(0.05,(($I$28-10922.0)/$I$24)-0.01)</f>
         <v/>
       </c>
-      <c r="L9" s="147">
+      <c r="L9" s="148">
         <f>MAX(0.05,(($I$28-10922.0)/$I$24)-0.015)</f>
         <v/>
       </c>
-      <c r="M9" s="147">
+      <c r="M9" s="148">
         <f>MAX(0.05,(($I$28-10922.0)/$I$24)-0.02)</f>
         <v/>
       </c>
-      <c r="N9" s="147">
+      <c r="N9" s="148">
         <f>MAX(0.05,(($I$28-10922.0)/$I$24)-0.025)</f>
         <v/>
       </c>
@@ -6465,13 +6789,18 @@
           <t>Normalize one-time restructuring ($10.9M). Mild efficiency grind reflects operating leverage as revenue scales; floored at 5%.</t>
         </is>
       </c>
-      <c r="U9" s="144" t="inlineStr">
+      <c r="U9" s="145" t="inlineStr">
         <is>
           <t>SEC 10-K FY2025 — SG&amp;A + restructuring note</t>
         </is>
       </c>
-    </row>
-    <row r="10" hidden="1" outlineLevel="1" ht="36" customHeight="1">
+      <c r="V9" s="145" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" hidden="1" outlineLevel="1" ht="40" customHeight="1">
       <c r="B10" s="19" t="inlineStr">
         <is>
           <t>R&amp;D % of Revenue (equation)</t>
@@ -6479,47 +6808,47 @@
       </c>
       <c r="C10" s="141" t="inlineStr">
         <is>
-          <t>WHY: FICO reinvests steadily in analytics/software. Flat % grows dollars with revenue. | SOURCE: SEC 10-K FY2025 — Research and development | HOW: Excel equation: I29/I24 held flat (~9.46%).</t>
+          <t>WHY: FICO reinvests steadily in analytics/software. Flat % grows dollars with revenue. | SOURCE: SEC 10-K FY2025 — Research and development | LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm | HOW: Excel equation: I29/I24 held flat (~9.46%).</t>
         </is>
       </c>
       <c r="D10" s="47" t="n"/>
-      <c r="E10" s="146">
+      <c r="E10" s="147">
         <f>E29</f>
         <v/>
       </c>
-      <c r="F10" s="146">
+      <c r="F10" s="147">
         <f>F29</f>
         <v/>
       </c>
-      <c r="G10" s="146">
+      <c r="G10" s="147">
         <f>G29</f>
         <v/>
       </c>
-      <c r="H10" s="146">
+      <c r="H10" s="147">
         <f>H29</f>
         <v/>
       </c>
-      <c r="I10" s="146">
+      <c r="I10" s="147">
         <f>I29</f>
         <v/>
       </c>
-      <c r="J10" s="147">
+      <c r="J10" s="148">
         <f>$I$29/$I$24</f>
         <v/>
       </c>
-      <c r="K10" s="147">
+      <c r="K10" s="148">
         <f>$I$29/$I$24</f>
         <v/>
       </c>
-      <c r="L10" s="147">
+      <c r="L10" s="148">
         <f>$I$29/$I$24</f>
         <v/>
       </c>
-      <c r="M10" s="147">
+      <c r="M10" s="148">
         <f>$I$29/$I$24</f>
         <v/>
       </c>
-      <c r="N10" s="147">
+      <c r="N10" s="148">
         <f>$I$29/$I$24</f>
         <v/>
       </c>
@@ -6546,13 +6875,18 @@
           <t>FICO reinvests steadily in analytics/software. Flat % grows dollars with revenue.</t>
         </is>
       </c>
-      <c r="U10" s="144" t="inlineStr">
+      <c r="U10" s="145" t="inlineStr">
         <is>
           <t>SEC 10-K FY2025 — Research and development</t>
         </is>
       </c>
-    </row>
-    <row r="11" hidden="1" outlineLevel="1" ht="36" customHeight="1">
+      <c r="V10" s="145" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" hidden="1" outlineLevel="1" ht="40" customHeight="1">
       <c r="B11" s="19" t="inlineStr">
         <is>
           <t>Depreciation &amp; Amortization (% of PP&amp;E Open Bal)</t>
@@ -6560,7 +6894,7 @@
       </c>
       <c r="C11" s="141" t="inlineStr">
         <is>
-          <t>WHY: Ties DA to the asset base the schedule rolls forward (opens at I44). | SOURCE: SEC 10-K FY2025 — D&amp;A and PP&amp;E | HOW: Excel equation: I30/I44 (FY25 DA ÷ FY25 PPE). Forecast DA = OpenPPE × this %.</t>
+          <t>WHY: Ties DA to the asset base the schedule rolls forward (opens at I44). | SOURCE: SEC 10-K FY2025 — D&amp;A and PP&amp;E | LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm | HOW: Excel equation: I30/I44 (FY25 DA ÷ FY25 PPE). Forecast DA = OpenPPE × this %.</t>
         </is>
       </c>
       <c r="D11" s="47" t="n"/>
@@ -6584,23 +6918,23 @@
         <f>I30/I92</f>
         <v/>
       </c>
-      <c r="J11" s="145">
+      <c r="J11" s="146">
         <f>IF($I$44=0,0.25,$I$30/$I$44)</f>
         <v/>
       </c>
-      <c r="K11" s="145">
+      <c r="K11" s="146">
         <f>IF($I$44=0,0.25,$I$30/$I$44)</f>
         <v/>
       </c>
-      <c r="L11" s="145">
+      <c r="L11" s="146">
         <f>IF($I$44=0,0.25,$I$30/$I$44)</f>
         <v/>
       </c>
-      <c r="M11" s="145">
+      <c r="M11" s="146">
         <f>IF($I$44=0,0.25,$I$30/$I$44)</f>
         <v/>
       </c>
-      <c r="N11" s="145">
+      <c r="N11" s="146">
         <f>IF($I$44=0,0.25,$I$30/$I$44)</f>
         <v/>
       </c>
@@ -6627,13 +6961,18 @@
           <t>Ties DA to the asset base the schedule rolls forward (opens at I44).</t>
         </is>
       </c>
-      <c r="U11" s="144" t="inlineStr">
+      <c r="U11" s="145" t="inlineStr">
         <is>
           <t>SEC 10-K FY2025 — D&amp;A and PP&amp;E</t>
         </is>
       </c>
-    </row>
-    <row r="12" hidden="1" outlineLevel="1" ht="36" customHeight="1">
+      <c r="V11" s="145" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" hidden="1" outlineLevel="1" ht="40" customHeight="1">
       <c r="B12" s="19" t="inlineStr">
         <is>
           <t>Interest (% of Debt Open Bal)</t>
@@ -6641,7 +6980,7 @@
       </c>
       <c r="C12" s="141" t="inlineStr">
         <is>
-          <t>WHY: Approximates average coupon / cost of debt on the book. Debt held flat (issuance = 0), so interest stays linked to that stock. | SOURCE: SEC 10-K FY2025 — Interest expense, net + debt footnote | HOW: Excel equation: I101/I98 (FY25 interest ÷ FY25 opening debt in schedule).</t>
+          <t>WHY: Approximates average coupon / cost of debt on the book. Debt held flat (issuance = 0), so interest stays linked to th… | SOURCE: SEC 10-K FY2025 — Interest expense; see also 8-K 6.250% notes | LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm | HOW: Excel equation: I101/I98 (FY25 interest ÷ FY25 opening debt in schedule).</t>
         </is>
       </c>
       <c r="D12" s="47" t="n"/>
@@ -6665,23 +7004,23 @@
         <f>I101/I98</f>
         <v/>
       </c>
-      <c r="J12" s="145">
+      <c r="J12" s="146">
         <f>IF($I$98=0,0.05,$I$101/$I$98)</f>
         <v/>
       </c>
-      <c r="K12" s="145">
+      <c r="K12" s="146">
         <f>IF($I$98=0,0.05,$I$101/$I$98)</f>
         <v/>
       </c>
-      <c r="L12" s="145">
+      <c r="L12" s="146">
         <f>IF($I$98=0,0.05,$I$101/$I$98)</f>
         <v/>
       </c>
-      <c r="M12" s="145">
+      <c r="M12" s="146">
         <f>IF($I$98=0,0.05,$I$101/$I$98)</f>
         <v/>
       </c>
-      <c r="N12" s="145">
+      <c r="N12" s="146">
         <f>IF($I$98=0,0.05,$I$101/$I$98)</f>
         <v/>
       </c>
@@ -6708,13 +7047,18 @@
           <t>Approximates average coupon / cost of debt on the book. Debt held flat (issuance = 0), so interest stays linked to that stock.</t>
         </is>
       </c>
-      <c r="U12" s="144" t="inlineStr">
-        <is>
-          <t>SEC 10-K FY2025 — Interest expense, net + debt footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" hidden="1" outlineLevel="1" ht="36" customHeight="1">
+      <c r="U12" s="145" t="inlineStr">
+        <is>
+          <t>SEC 10-K FY2025 — Interest expense; see also 8-K 6.250% notes</t>
+        </is>
+      </c>
+      <c r="V12" s="145" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" hidden="1" outlineLevel="1" ht="40" customHeight="1">
       <c r="B13" s="19" t="inlineStr">
         <is>
           <t>Tax Rate (% of Earnings Before Tax)</t>
@@ -6722,7 +7066,7 @@
       </c>
       <c r="C13" s="141" t="inlineStr">
         <is>
-          <t>WHY: Uses reported effective rate (~19% on template EBT; ~18.8% on 10-K EBT). UFCF in DCF also uses unlevered EBIT × t. | SOURCE: SEC 10-K FY2025 — Provision for income taxes / Income before taxes | HOW: Excel equation: I35/I33 (FY25 tax ÷ simplified FY25 EBT in this template).</t>
+          <t>WHY: Uses reported effective rate (~19% on template EBT; ~18.8% on 10-K EBT). UFCF in DCF also uses unlevered EBIT × t. | SOURCE: SEC 10-K FY2025 — Provision for income taxes / Income before taxes | LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm | HOW: Excel equation: I35/I33 (FY25 tax ÷ simplified FY25 EBT in this template).</t>
         </is>
       </c>
       <c r="D13" s="25" t="n"/>
@@ -6746,23 +7090,23 @@
         <f>I35/I33</f>
         <v/>
       </c>
-      <c r="J13" s="145">
+      <c r="J13" s="146">
         <f>IF($I$33=0,0.21,$I$35/$I$33)</f>
         <v/>
       </c>
-      <c r="K13" s="145">
+      <c r="K13" s="146">
         <f>IF($I$33=0,0.21,$I$35/$I$33)</f>
         <v/>
       </c>
-      <c r="L13" s="145">
+      <c r="L13" s="146">
         <f>IF($I$33=0,0.21,$I$35/$I$33)</f>
         <v/>
       </c>
-      <c r="M13" s="145">
+      <c r="M13" s="146">
         <f>IF($I$33=0,0.21,$I$35/$I$33)</f>
         <v/>
       </c>
-      <c r="N13" s="145">
+      <c r="N13" s="146">
         <f>IF($I$33=0,0.21,$I$35/$I$33)</f>
         <v/>
       </c>
@@ -6789,9 +7133,14 @@
           <t>Uses reported effective rate (~19% on template EBT; ~18.8% on 10-K EBT). UFCF in DCF also uses unlevered EBIT × t.</t>
         </is>
       </c>
-      <c r="U13" s="144" t="inlineStr">
+      <c r="U13" s="145" t="inlineStr">
         <is>
           <t>SEC 10-K FY2025 — Provision for income taxes / Income before taxes</t>
+        </is>
+      </c>
+      <c r="V13" s="145" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
         </is>
       </c>
     </row>
@@ -6814,55 +7163,55 @@
       <c r="M14" s="19" t="n"/>
       <c r="N14" s="19" t="n"/>
     </row>
-    <row r="15" hidden="1" outlineLevel="1" ht="36" customHeight="1">
+    <row r="15" hidden="1" outlineLevel="1" ht="40" customHeight="1">
       <c r="B15" s="19" t="inlineStr">
         <is>
           <t>Accounts Receivable (Days)</t>
         </is>
       </c>
-      <c r="C15" s="148" t="inlineStr">
-        <is>
-          <t>WHY: Operating working-capital view: contract liabilities (deferred revenue) reduce net AR so ΔNWC is not overstated. | SOURCE: SEC 10-K — AR; DeferredRevenueCurrent (XBRL) | HOW: Excel equation: ROUND(I42/I24×365, 0). I42 is net AR (AR − deferred).</t>
+      <c r="C15" s="149" t="inlineStr">
+        <is>
+          <t>WHY: Operating working-capital view: contract liabilities (deferred revenue) reduce net AR so ΔNWC is not overstated. | SOURCE: SEC companyfacts XBRL — AR + DeferredRevenueCurrent | LINK: https://data.sec.gov/api/xbrl/companyfacts/CIK0000814547.json | HOW: Excel equation: ROUND(I42/I24×365, 0). I42 is net AR (AR − deferred).</t>
         </is>
       </c>
       <c r="D15" s="32" t="n"/>
-      <c r="E15" s="146">
+      <c r="E15" s="147">
         <f>E42/E24*365</f>
         <v/>
       </c>
-      <c r="F15" s="146">
+      <c r="F15" s="147">
         <f>F42/F24*365</f>
         <v/>
       </c>
-      <c r="G15" s="146">
+      <c r="G15" s="147">
         <f>G42/G24*365</f>
         <v/>
       </c>
-      <c r="H15" s="146">
+      <c r="H15" s="147">
         <f>H42/H24*365</f>
         <v/>
       </c>
-      <c r="I15" s="146">
+      <c r="I15" s="147">
         <f>I42/I24*365</f>
         <v/>
       </c>
-      <c r="J15" s="149">
+      <c r="J15" s="150">
         <f>ROUND($I$42/$I$24*365,0)</f>
         <v/>
       </c>
-      <c r="K15" s="149">
+      <c r="K15" s="150">
         <f>ROUND($I$42/$I$24*365,0)</f>
         <v/>
       </c>
-      <c r="L15" s="149">
+      <c r="L15" s="150">
         <f>ROUND($I$42/$I$24*365,0)</f>
         <v/>
       </c>
-      <c r="M15" s="149">
+      <c r="M15" s="150">
         <f>ROUND($I$42/$I$24*365,0)</f>
         <v/>
       </c>
-      <c r="N15" s="149">
+      <c r="N15" s="150">
         <f>ROUND($I$42/$I$24*365,0)</f>
         <v/>
       </c>
@@ -6889,57 +7238,62 @@
           <t>Operating working-capital view: contract liabilities (deferred revenue) reduce net AR so ΔNWC is not overstated.</t>
         </is>
       </c>
-      <c r="U15" s="144" t="inlineStr">
-        <is>
-          <t>SEC 10-K — AR; DeferredRevenueCurrent (XBRL)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" hidden="1" outlineLevel="1" ht="36" customHeight="1">
+      <c r="U15" s="145" t="inlineStr">
+        <is>
+          <t>SEC companyfacts XBRL — AR + DeferredRevenueCurrent</t>
+        </is>
+      </c>
+      <c r="V15" s="145" t="inlineStr">
+        <is>
+          <t>https://data.sec.gov/api/xbrl/companyfacts/CIK0000814547.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" hidden="1" outlineLevel="1" ht="40" customHeight="1">
       <c r="B16" s="19" t="inlineStr">
         <is>
           <t>Inventory (Days)</t>
         </is>
       </c>
-      <c r="C16" s="148" t="inlineStr">
-        <is>
-          <t>WHY: No inventory cycle to fund. | SOURCE: SEC 10-K — Inventory ≈ $0 | HOW: Hard zero — FICO is software / scores; inventory is immaterial.</t>
+      <c r="C16" s="149" t="inlineStr">
+        <is>
+          <t>WHY: No inventory cycle to fund. | SOURCE: SEC 10-K FY2025 — Inventory ≈ $0 | LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm | HOW: Hard zero — FICO is software / scores; inventory is immaterial.</t>
         </is>
       </c>
       <c r="D16" s="32" t="n"/>
-      <c r="E16" s="146">
+      <c r="E16" s="147">
         <f>E43/E25*365</f>
         <v/>
       </c>
-      <c r="F16" s="146">
+      <c r="F16" s="147">
         <f>F43/F25*365</f>
         <v/>
       </c>
-      <c r="G16" s="146">
+      <c r="G16" s="147">
         <f>G43/G25*365</f>
         <v/>
       </c>
-      <c r="H16" s="146">
+      <c r="H16" s="147">
         <f>H43/H25*365</f>
         <v/>
       </c>
-      <c r="I16" s="146">
+      <c r="I16" s="147">
         <f>I43/I25*365</f>
         <v/>
       </c>
-      <c r="J16" s="150" t="n">
+      <c r="J16" s="151" t="n">
         <v>0</v>
       </c>
-      <c r="K16" s="150" t="n">
+      <c r="K16" s="151" t="n">
         <v>0</v>
       </c>
-      <c r="L16" s="150" t="n">
+      <c r="L16" s="151" t="n">
         <v>0</v>
       </c>
-      <c r="M16" s="150" t="n">
+      <c r="M16" s="151" t="n">
         <v>0</v>
       </c>
-      <c r="N16" s="150" t="n">
+      <c r="N16" s="151" t="n">
         <v>0</v>
       </c>
       <c r="P16" s="143" t="n">
@@ -6965,61 +7319,66 @@
           <t>No inventory cycle to fund.</t>
         </is>
       </c>
-      <c r="U16" s="144" t="inlineStr">
-        <is>
-          <t>SEC 10-K — Inventory ≈ $0</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" hidden="1" outlineLevel="1" ht="36" customHeight="1">
+      <c r="U16" s="145" t="inlineStr">
+        <is>
+          <t>SEC 10-K FY2025 — Inventory ≈ $0</t>
+        </is>
+      </c>
+      <c r="V16" s="145" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" hidden="1" outlineLevel="1" ht="40" customHeight="1">
       <c r="B17" s="19" t="inlineStr">
         <is>
           <t>Accounts Payable (Days)</t>
         </is>
       </c>
-      <c r="C17" s="148" t="inlineStr">
-        <is>
-          <t>WHY: Payable timing offsets AR in operating NWC. | SOURCE: SEC 10-K FY2025 — Accounts payable | HOW: Excel equation: ROUND(I48/I25×365, 0) from FY25.</t>
+      <c r="C17" s="149" t="inlineStr">
+        <is>
+          <t>WHY: Payable timing offsets AR in operating NWC. | SOURCE: SEC 10-K FY2025 — Accounts payable | LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm | HOW: Excel equation: ROUND(I48/I25×365, 0) from FY25.</t>
         </is>
       </c>
       <c r="D17" s="32" t="n"/>
-      <c r="E17" s="146">
+      <c r="E17" s="147">
         <f>E48/E25*365</f>
         <v/>
       </c>
-      <c r="F17" s="146">
+      <c r="F17" s="147">
         <f>F48/F25*365</f>
         <v/>
       </c>
-      <c r="G17" s="146">
+      <c r="G17" s="147">
         <f>G48/G25*365</f>
         <v/>
       </c>
-      <c r="H17" s="146">
+      <c r="H17" s="147">
         <f>H48/H25*365</f>
         <v/>
       </c>
-      <c r="I17" s="146">
+      <c r="I17" s="147">
         <f>I48/I25*365</f>
         <v/>
       </c>
-      <c r="J17" s="149">
+      <c r="J17" s="150">
         <f>IF($I$25=0,0,ROUND($I$48/$I$25*365,0))</f>
         <v/>
       </c>
-      <c r="K17" s="149">
+      <c r="K17" s="150">
         <f>IF($I$25=0,0,ROUND($I$48/$I$25*365,0))</f>
         <v/>
       </c>
-      <c r="L17" s="149">
+      <c r="L17" s="150">
         <f>IF($I$25=0,0,ROUND($I$48/$I$25*365,0))</f>
         <v/>
       </c>
-      <c r="M17" s="149">
+      <c r="M17" s="150">
         <f>IF($I$25=0,0,ROUND($I$48/$I$25*365,0))</f>
         <v/>
       </c>
-      <c r="N17" s="149">
+      <c r="N17" s="150">
         <f>IF($I$25=0,0,ROUND($I$48/$I$25*365,0))</f>
         <v/>
       </c>
@@ -7046,60 +7405,65 @@
           <t>Payable timing offsets AR in operating NWC.</t>
         </is>
       </c>
-      <c r="U17" s="144" t="inlineStr">
+      <c r="U17" s="145" t="inlineStr">
         <is>
           <t>SEC 10-K FY2025 — Accounts payable</t>
         </is>
       </c>
-    </row>
-    <row r="18" hidden="1" outlineLevel="1" ht="36" customHeight="1">
+      <c r="V17" s="145" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" hidden="1" outlineLevel="1" ht="40" customHeight="1">
       <c r="B18" s="19" t="inlineStr">
         <is>
           <t>CapEx % of Revenue (fade equation)</t>
         </is>
       </c>
-      <c r="C18" s="148" t="inlineStr">
-        <is>
-          <t>WHY: FY25 CapEx was elevated by capitalized internal-use software. Fading avoids locking a peak reinvestment rate forever. | SOURCE: SEC 10-K — PP&amp;E purchases + capitalized software | HOW: Equation: fade from I68/I24 (FY25 CapEx/Sales ~1.98%) toward 1.0% steady. Weights 85%→65%→45%→30%→0% on the peak.</t>
-        </is>
-      </c>
-      <c r="E18" s="146">
+      <c r="C18" s="149" t="inlineStr">
+        <is>
+          <t>WHY: FY25 CapEx was elevated by capitalized internal-use software. Fading avoids locking a peak reinvestment rate forever. | SOURCE: SEC 10-K FY2025 — PP&amp;E purchases + capitalized software | LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm | HOW: Equation: fade from I68/I24 (FY25 CapEx/Sales ~1.98%) toward 1.0% steady. Weights 85%→65%→45%→30%→0% on the peak.</t>
+        </is>
+      </c>
+      <c r="E18" s="147">
         <f>E68</f>
         <v/>
       </c>
-      <c r="F18" s="146">
+      <c r="F18" s="147">
         <f>F68</f>
         <v/>
       </c>
-      <c r="G18" s="146">
+      <c r="G18" s="147">
         <f>G68</f>
         <v/>
       </c>
-      <c r="H18" s="146">
+      <c r="H18" s="147">
         <f>H68</f>
         <v/>
       </c>
-      <c r="I18" s="146">
+      <c r="I18" s="147">
         <f>I68</f>
         <v/>
       </c>
-      <c r="J18" s="147">
+      <c r="J18" s="148">
         <f>($I$68/$I$24)*0.85+0.01*(1-0.85)</f>
         <v/>
       </c>
-      <c r="K18" s="147">
+      <c r="K18" s="148">
         <f>($I$68/$I$24)*0.65+0.01*(1-0.65)</f>
         <v/>
       </c>
-      <c r="L18" s="147">
+      <c r="L18" s="148">
         <f>($I$68/$I$24)*0.45+0.01*(1-0.45)</f>
         <v/>
       </c>
-      <c r="M18" s="147">
+      <c r="M18" s="148">
         <f>($I$68/$I$24)*0.3+0.01*(1-0.3)</f>
         <v/>
       </c>
-      <c r="N18" s="147">
+      <c r="N18" s="148">
         <f>($I$68/$I$24)*0.0+0.01*(1-0.0)</f>
         <v/>
       </c>
@@ -7126,56 +7490,61 @@
           <t>FY25 CapEx was elevated by capitalized internal-use software. Fading avoids locking a peak reinvestment rate forever.</t>
         </is>
       </c>
-      <c r="U18" s="144" t="inlineStr">
-        <is>
-          <t>SEC 10-K — PP&amp;E purchases + capitalized software</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" hidden="1" outlineLevel="1" ht="36" customHeight="1">
+      <c r="U18" s="145" t="inlineStr">
+        <is>
+          <t>SEC 10-K FY2025 — PP&amp;E purchases + capitalized software</t>
+        </is>
+      </c>
+      <c r="V18" s="145" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" hidden="1" outlineLevel="1" ht="40" customHeight="1">
       <c r="B19" s="19" t="inlineStr">
         <is>
           <t>Debt Issuance (Repayment) ($000's)</t>
         </is>
       </c>
-      <c r="C19" s="148" t="inlineStr">
-        <is>
-          <t>WHY: Hold debt stock flat at FY25 level for the explicit period; interest follows. Net debt for DCF equity bridge uses the later 10-Q amount separately. | SOURCE: Modeling choice (financing not in FCFF) | HOW: POLICY input = 0 every year.</t>
-        </is>
-      </c>
-      <c r="E19" s="146">
+      <c r="C19" s="149" t="inlineStr">
+        <is>
+          <t>WHY: Hold debt stock flat at FY25 level for the explicit period; interest follows. Net debt for DCF equity bridge uses the… | SOURCE: SEC 10-Q Q3 FY2026 — debt stock (financing excluded from FCFF) | LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454726000030/fico-20260630.htm | HOW: POLICY input = 0 every year.</t>
+        </is>
+      </c>
+      <c r="E19" s="147">
         <f>E99</f>
         <v/>
       </c>
-      <c r="F19" s="146">
+      <c r="F19" s="147">
         <f>F99</f>
         <v/>
       </c>
-      <c r="G19" s="146">
+      <c r="G19" s="147">
         <f>G99</f>
         <v/>
       </c>
-      <c r="H19" s="146">
+      <c r="H19" s="147">
         <f>H99</f>
         <v/>
       </c>
-      <c r="I19" s="146">
+      <c r="I19" s="147">
         <f>I99</f>
         <v/>
       </c>
-      <c r="J19" s="151" t="n">
+      <c r="J19" s="152" t="n">
         <v>0</v>
       </c>
-      <c r="K19" s="151" t="n">
+      <c r="K19" s="152" t="n">
         <v>0</v>
       </c>
-      <c r="L19" s="151" t="n">
+      <c r="L19" s="152" t="n">
         <v>0</v>
       </c>
-      <c r="M19" s="151" t="n">
+      <c r="M19" s="152" t="n">
         <v>0</v>
       </c>
-      <c r="N19" s="151" t="n">
+      <c r="N19" s="152" t="n">
         <v>0</v>
       </c>
       <c r="P19" s="143" t="n">
@@ -7201,56 +7570,61 @@
           <t>Hold debt stock flat at FY25 level for the explicit period; interest follows. Net debt for DCF equity bridge uses the later 10-Q amount separately.</t>
         </is>
       </c>
-      <c r="U19" s="144" t="inlineStr">
-        <is>
-          <t>Modeling choice (financing not in FCFF)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" hidden="1" outlineLevel="1" ht="36" customHeight="1">
+      <c r="U19" s="145" t="inlineStr">
+        <is>
+          <t>SEC 10-Q Q3 FY2026 — debt stock (financing excluded from FCFF)</t>
+        </is>
+      </c>
+      <c r="V19" s="145" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454726000030/fico-20260630.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" hidden="1" outlineLevel="1" ht="40" customHeight="1">
       <c r="B20" s="19" t="inlineStr">
         <is>
           <t>Equity Issued (Repaid) ($000's)</t>
         </is>
       </c>
-      <c r="C20" s="148" t="inlineStr">
-        <is>
-          <t>WHY: Buybacks are real historically but are financing — excluded from FCFF. Share count for $/share is the spot shares outstanding assumption. | SOURCE: Modeling choice (financing not in FCFF) | HOW: POLICY input = 0 every year.</t>
-        </is>
-      </c>
-      <c r="E20" s="146">
+      <c r="C20" s="149" t="inlineStr">
+        <is>
+          <t>WHY: Buybacks are real historically but are financing — excluded from FCFF. Share count for $/share is the spot shares out… | SOURCE: Damodaran FCFF framework — financing (buybacks) not in FCFF | LINK: https://pages.stern.nyu.edu/~adamodar/New_Home_Page/datafile/histfcff.html | HOW: POLICY input = 0 every year.</t>
+        </is>
+      </c>
+      <c r="E20" s="147">
         <f>E73</f>
         <v/>
       </c>
-      <c r="F20" s="146">
+      <c r="F20" s="147">
         <f>F73</f>
         <v/>
       </c>
-      <c r="G20" s="146">
+      <c r="G20" s="147">
         <f>G73</f>
         <v/>
       </c>
-      <c r="H20" s="146">
+      <c r="H20" s="147">
         <f>H73</f>
         <v/>
       </c>
-      <c r="I20" s="146">
+      <c r="I20" s="147">
         <f>I73</f>
         <v/>
       </c>
-      <c r="J20" s="151" t="n">
+      <c r="J20" s="152" t="n">
         <v>0</v>
       </c>
-      <c r="K20" s="151" t="n">
+      <c r="K20" s="152" t="n">
         <v>0</v>
       </c>
-      <c r="L20" s="151" t="n">
+      <c r="L20" s="152" t="n">
         <v>0</v>
       </c>
-      <c r="M20" s="151" t="n">
+      <c r="M20" s="152" t="n">
         <v>0</v>
       </c>
-      <c r="N20" s="151" t="n">
+      <c r="N20" s="152" t="n">
         <v>0</v>
       </c>
       <c r="P20" s="143" t="n">
@@ -7276,9 +7650,14 @@
           <t>Buybacks are real historically but are financing — excluded from FCFF. Share count for $/share is the spot shares outstanding assumption.</t>
         </is>
       </c>
-      <c r="U20" s="144" t="inlineStr">
-        <is>
-          <t>Modeling choice (financing not in FCFF)</t>
+      <c r="U20" s="145" t="inlineStr">
+        <is>
+          <t>Damodaran FCFF framework — financing (buybacks) not in FCFF</t>
+        </is>
+      </c>
+      <c r="V20" s="145" t="inlineStr">
+        <is>
+          <t>https://pages.stern.nyu.edu/~adamodar/New_Home_Page/datafile/histfcff.html</t>
         </is>
       </c>
     </row>
@@ -7331,44 +7710,44 @@
           <t>Reveneue</t>
         </is>
       </c>
-      <c r="C24" s="152" t="inlineStr">
+      <c r="C24" s="153" t="inlineStr">
         <is>
           <t>eqn: PriorRev × (1 + growth)</t>
         </is>
       </c>
       <c r="D24" s="46" t="n"/>
-      <c r="E24" s="153" t="n">
+      <c r="E24" s="154" t="n">
         <v>1316536</v>
       </c>
-      <c r="F24" s="153" t="n">
+      <c r="F24" s="154" t="n">
         <v>1377270</v>
       </c>
-      <c r="G24" s="153" t="n">
+      <c r="G24" s="154" t="n">
         <v>1513557</v>
       </c>
-      <c r="H24" s="153" t="n">
+      <c r="H24" s="154" t="n">
         <v>1717526</v>
       </c>
-      <c r="I24" s="153" t="n">
+      <c r="I24" s="154" t="n">
         <v>1990869</v>
       </c>
-      <c r="J24" s="149">
+      <c r="J24" s="150">
         <f>I24*(1+J7)</f>
         <v/>
       </c>
-      <c r="K24" s="149">
+      <c r="K24" s="150">
         <f>J24*(1+K7)</f>
         <v/>
       </c>
-      <c r="L24" s="149">
+      <c r="L24" s="150">
         <f>K24*(1+L7)</f>
         <v/>
       </c>
-      <c r="M24" s="149">
+      <c r="M24" s="150">
         <f>L24*(1+M7)</f>
         <v/>
       </c>
-      <c r="N24" s="149">
+      <c r="N24" s="150">
         <f>M24*(1+N7)</f>
         <v/>
       </c>
@@ -7379,44 +7758,44 @@
           <t>Cost of Goods Sold (COGS)</t>
         </is>
       </c>
-      <c r="C25" s="152" t="inlineStr">
+      <c r="C25" s="153" t="inlineStr">
         <is>
           <t>eqn: Rev × COGS%</t>
         </is>
       </c>
       <c r="D25" s="47" t="n"/>
-      <c r="E25" s="153" t="n">
+      <c r="E25" s="154" t="n">
         <v>332462</v>
       </c>
-      <c r="F25" s="153" t="n">
+      <c r="F25" s="154" t="n">
         <v>302174</v>
       </c>
-      <c r="G25" s="153" t="n">
+      <c r="G25" s="154" t="n">
         <v>311053</v>
       </c>
-      <c r="H25" s="153" t="n">
+      <c r="H25" s="154" t="n">
         <v>348206</v>
       </c>
-      <c r="I25" s="153" t="n">
+      <c r="I25" s="154" t="n">
         <v>353722</v>
       </c>
-      <c r="J25" s="149">
+      <c r="J25" s="150">
         <f>J24*J8</f>
         <v/>
       </c>
-      <c r="K25" s="149">
+      <c r="K25" s="150">
         <f>K24*K8</f>
         <v/>
       </c>
-      <c r="L25" s="149">
+      <c r="L25" s="150">
         <f>L24*L8</f>
         <v/>
       </c>
-      <c r="M25" s="149">
+      <c r="M25" s="150">
         <f>M24*M8</f>
         <v/>
       </c>
-      <c r="N25" s="149">
+      <c r="N25" s="150">
         <f>N24*N8</f>
         <v/>
       </c>
@@ -7427,49 +7806,49 @@
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="C26" s="154" t="inlineStr">
+      <c r="C26" s="155" t="inlineStr">
         <is>
           <t>eqn: Rev − COGS</t>
         </is>
       </c>
       <c r="D26" s="22" t="n"/>
-      <c r="E26" s="155">
+      <c r="E26" s="156">
         <f>E24-E25</f>
         <v/>
       </c>
-      <c r="F26" s="155">
+      <c r="F26" s="156">
         <f>F24-F25</f>
         <v/>
       </c>
-      <c r="G26" s="155">
+      <c r="G26" s="156">
         <f>G24-G25</f>
         <v/>
       </c>
-      <c r="H26" s="155">
+      <c r="H26" s="156">
         <f>H24-H25</f>
         <v/>
       </c>
-      <c r="I26" s="155">
+      <c r="I26" s="156">
         <f>I24-I25</f>
         <v/>
       </c>
-      <c r="J26" s="149">
+      <c r="J26" s="150">
         <f>J24-J25</f>
         <v/>
       </c>
-      <c r="K26" s="149">
+      <c r="K26" s="150">
         <f>K24-K25</f>
         <v/>
       </c>
-      <c r="L26" s="149">
+      <c r="L26" s="150">
         <f>L24-L25</f>
         <v/>
       </c>
-      <c r="M26" s="149">
+      <c r="M26" s="150">
         <f>M24-M25</f>
         <v/>
       </c>
-      <c r="N26" s="149">
+      <c r="N26" s="150">
         <f>N24-N25</f>
         <v/>
       </c>
@@ -7499,43 +7878,43 @@
           <t>Salaries and Benefits</t>
         </is>
       </c>
-      <c r="C28" s="156" t="inlineStr">
+      <c r="C28" s="157" t="inlineStr">
         <is>
           <t>eqn: Rev × SGA%</t>
         </is>
       </c>
-      <c r="E28" s="153" t="n">
+      <c r="E28" s="154" t="n">
         <v>396281</v>
       </c>
-      <c r="F28" s="153" t="n">
+      <c r="F28" s="154" t="n">
         <v>383863</v>
       </c>
-      <c r="G28" s="153" t="n">
+      <c r="G28" s="154" t="n">
         <v>400565</v>
       </c>
-      <c r="H28" s="153" t="n">
+      <c r="H28" s="154" t="n">
         <v>462834</v>
       </c>
-      <c r="I28" s="153" t="n">
+      <c r="I28" s="154" t="n">
         <v>513028</v>
       </c>
-      <c r="J28" s="149">
+      <c r="J28" s="150">
         <f>J24*J9</f>
         <v/>
       </c>
-      <c r="K28" s="149">
+      <c r="K28" s="150">
         <f>K24*K9</f>
         <v/>
       </c>
-      <c r="L28" s="149">
+      <c r="L28" s="150">
         <f>L24*L9</f>
         <v/>
       </c>
-      <c r="M28" s="149">
+      <c r="M28" s="150">
         <f>M24*M9</f>
         <v/>
       </c>
-      <c r="N28" s="149">
+      <c r="N28" s="150">
         <f>N24*N9</f>
         <v/>
       </c>
@@ -7546,43 +7925,43 @@
           <t>Rent and Overhead</t>
         </is>
       </c>
-      <c r="C29" s="156" t="inlineStr">
+      <c r="C29" s="157" t="inlineStr">
         <is>
           <t>eqn: Rev × R&amp;D%</t>
         </is>
       </c>
-      <c r="E29" s="153" t="n">
+      <c r="E29" s="154" t="n">
         <v>171231</v>
       </c>
-      <c r="F29" s="153" t="n">
+      <c r="F29" s="154" t="n">
         <v>146758</v>
       </c>
-      <c r="G29" s="153" t="n">
+      <c r="G29" s="154" t="n">
         <v>159950</v>
       </c>
-      <c r="H29" s="153" t="n">
+      <c r="H29" s="154" t="n">
         <v>171940</v>
       </c>
-      <c r="I29" s="153" t="n">
+      <c r="I29" s="154" t="n">
         <v>188347</v>
       </c>
-      <c r="J29" s="149">
+      <c r="J29" s="150">
         <f>J24*J10</f>
         <v/>
       </c>
-      <c r="K29" s="149">
+      <c r="K29" s="150">
         <f>K24*K10</f>
         <v/>
       </c>
-      <c r="L29" s="149">
+      <c r="L29" s="150">
         <f>L24*L10</f>
         <v/>
       </c>
-      <c r="M29" s="149">
+      <c r="M29" s="150">
         <f>M24*M10</f>
         <v/>
       </c>
-      <c r="N29" s="149">
+      <c r="N29" s="150">
         <f>N24*N10</f>
         <v/>
       </c>
@@ -7593,43 +7972,43 @@
           <t>Depreciation &amp; Amortization</t>
         </is>
       </c>
-      <c r="C30" s="156" t="inlineStr">
+      <c r="C30" s="157" t="inlineStr">
         <is>
           <t>eqn: PPE_open × DA%</t>
         </is>
       </c>
-      <c r="E30" s="153" t="n">
+      <c r="E30" s="154" t="n">
         <v>25592</v>
       </c>
-      <c r="F30" s="153" t="n">
+      <c r="F30" s="154" t="n">
         <v>20465</v>
       </c>
-      <c r="G30" s="153" t="n">
+      <c r="G30" s="154" t="n">
         <v>14638</v>
       </c>
-      <c r="H30" s="153" t="n">
+      <c r="H30" s="154" t="n">
         <v>13827</v>
       </c>
-      <c r="I30" s="153" t="n">
+      <c r="I30" s="154" t="n">
         <v>14952</v>
       </c>
-      <c r="J30" s="149">
+      <c r="J30" s="150">
         <f>J92*J11</f>
         <v/>
       </c>
-      <c r="K30" s="149">
+      <c r="K30" s="150">
         <f>K92*K11</f>
         <v/>
       </c>
-      <c r="L30" s="149">
+      <c r="L30" s="150">
         <f>L92*L11</f>
         <v/>
       </c>
-      <c r="M30" s="149">
+      <c r="M30" s="150">
         <f>M92*M11</f>
         <v/>
       </c>
-      <c r="N30" s="149">
+      <c r="N30" s="150">
         <f>N92*N11</f>
         <v/>
       </c>
@@ -7640,44 +8019,44 @@
           <t>Interest</t>
         </is>
       </c>
-      <c r="C31" s="157" t="inlineStr">
+      <c r="C31" s="158" t="inlineStr">
         <is>
           <t>eqn: Debt_open × Int%</t>
         </is>
       </c>
       <c r="D31" s="24" t="n"/>
-      <c r="E31" s="158" t="n">
+      <c r="E31" s="159" t="n">
         <v>40092</v>
       </c>
-      <c r="F31" s="158" t="n">
+      <c r="F31" s="159" t="n">
         <v>68967</v>
       </c>
-      <c r="G31" s="158" t="n">
+      <c r="G31" s="159" t="n">
         <v>95546</v>
       </c>
-      <c r="H31" s="158" t="n">
+      <c r="H31" s="159" t="n">
         <v>105638</v>
       </c>
-      <c r="I31" s="158" t="n">
+      <c r="I31" s="159" t="n">
         <v>133647</v>
       </c>
-      <c r="J31" s="149">
+      <c r="J31" s="150">
         <f>J98*J12</f>
         <v/>
       </c>
-      <c r="K31" s="149">
+      <c r="K31" s="150">
         <f>K98*K12</f>
         <v/>
       </c>
-      <c r="L31" s="149">
+      <c r="L31" s="150">
         <f>L98*L12</f>
         <v/>
       </c>
-      <c r="M31" s="149">
+      <c r="M31" s="150">
         <f>M98*M12</f>
         <v/>
       </c>
-      <c r="N31" s="149">
+      <c r="N31" s="150">
         <f>N98*N12</f>
         <v/>
       </c>
@@ -7690,43 +8069,43 @@
       </c>
       <c r="C32" s="19" t="n"/>
       <c r="D32" s="47" t="n"/>
-      <c r="E32" s="159">
+      <c r="E32" s="160">
         <f>SUM(E28:E31)</f>
         <v/>
       </c>
-      <c r="F32" s="159">
+      <c r="F32" s="160">
         <f>SUM(F28:F31)</f>
         <v/>
       </c>
-      <c r="G32" s="159">
+      <c r="G32" s="160">
         <f>SUM(G28:G31)</f>
         <v/>
       </c>
-      <c r="H32" s="159">
+      <c r="H32" s="160">
         <f>SUM(H28:H31)</f>
         <v/>
       </c>
-      <c r="I32" s="159">
+      <c r="I32" s="160">
         <f>SUM(I28:I31)</f>
         <v/>
       </c>
-      <c r="J32" s="149">
+      <c r="J32" s="150">
         <f>SUM(J28:J31)</f>
         <v/>
       </c>
-      <c r="K32" s="149">
+      <c r="K32" s="150">
         <f>SUM(K28:K31)</f>
         <v/>
       </c>
-      <c r="L32" s="149">
+      <c r="L32" s="150">
         <f>SUM(L28:L31)</f>
         <v/>
       </c>
-      <c r="M32" s="149">
+      <c r="M32" s="150">
         <f>SUM(M28:M31)</f>
         <v/>
       </c>
-      <c r="N32" s="149">
+      <c r="N32" s="150">
         <f>SUM(N28:N31)</f>
         <v/>
       </c>
@@ -7737,49 +8116,49 @@
           <t>Earnings Before Tax</t>
         </is>
       </c>
-      <c r="C33" s="154" t="inlineStr">
+      <c r="C33" s="155" t="inlineStr">
         <is>
           <t>eqn: GP − Expenses</t>
         </is>
       </c>
       <c r="D33" s="22" t="n"/>
-      <c r="E33" s="155">
+      <c r="E33" s="156">
         <f>E26-E32</f>
         <v/>
       </c>
-      <c r="F33" s="155">
+      <c r="F33" s="156">
         <f>F26-F32</f>
         <v/>
       </c>
-      <c r="G33" s="155">
+      <c r="G33" s="156">
         <f>G26-G32</f>
         <v/>
       </c>
-      <c r="H33" s="155">
+      <c r="H33" s="156">
         <f>H26-H32</f>
         <v/>
       </c>
-      <c r="I33" s="155">
+      <c r="I33" s="156">
         <f>I26-I32</f>
         <v/>
       </c>
-      <c r="J33" s="149">
+      <c r="J33" s="150">
         <f>J26-J32</f>
         <v/>
       </c>
-      <c r="K33" s="149">
+      <c r="K33" s="150">
         <f>K26-K32</f>
         <v/>
       </c>
-      <c r="L33" s="149">
+      <c r="L33" s="150">
         <f>L26-L32</f>
         <v/>
       </c>
-      <c r="M33" s="149">
+      <c r="M33" s="150">
         <f>M26-M32</f>
         <v/>
       </c>
-      <c r="N33" s="149">
+      <c r="N33" s="150">
         <f>N26-N32</f>
         <v/>
       </c>
@@ -7805,44 +8184,44 @@
           <t>Taxes</t>
         </is>
       </c>
-      <c r="C35" s="152" t="inlineStr">
+      <c r="C35" s="153" t="inlineStr">
         <is>
           <t>eqn: EBT × tax%</t>
         </is>
       </c>
       <c r="D35" s="47" t="n"/>
-      <c r="E35" s="153" t="n">
+      <c r="E35" s="154" t="n">
         <v>81058</v>
       </c>
-      <c r="F35" s="153" t="n">
+      <c r="F35" s="154" t="n">
         <v>97768</v>
       </c>
-      <c r="G35" s="153" t="n">
+      <c r="G35" s="154" t="n">
         <v>124249</v>
       </c>
-      <c r="H35" s="153" t="n">
+      <c r="H35" s="154" t="n">
         <v>129214</v>
       </c>
-      <c r="I35" s="153" t="n">
+      <c r="I35" s="154" t="n">
         <v>150649</v>
       </c>
-      <c r="J35" s="149">
+      <c r="J35" s="150">
         <f>J33*J13</f>
         <v/>
       </c>
-      <c r="K35" s="149">
+      <c r="K35" s="150">
         <f>K33*K13</f>
         <v/>
       </c>
-      <c r="L35" s="149">
+      <c r="L35" s="150">
         <f>L33*L13</f>
         <v/>
       </c>
-      <c r="M35" s="149">
+      <c r="M35" s="150">
         <f>M33*M13</f>
         <v/>
       </c>
-      <c r="N35" s="149">
+      <c r="N35" s="150">
         <f>N33*N13</f>
         <v/>
       </c>
@@ -7853,49 +8232,49 @@
           <t>Net Earnings</t>
         </is>
       </c>
-      <c r="C36" s="160" t="inlineStr">
+      <c r="C36" s="161" t="inlineStr">
         <is>
           <t>eqn: EBT × (1 − tax%)  — grows with Rev×(1+g)</t>
         </is>
       </c>
       <c r="D36" s="40" t="n"/>
-      <c r="E36" s="161">
+      <c r="E36" s="162">
         <f>E33-E35</f>
         <v/>
       </c>
-      <c r="F36" s="161">
+      <c r="F36" s="162">
         <f>F33-F35</f>
         <v/>
       </c>
-      <c r="G36" s="161">
+      <c r="G36" s="162">
         <f>G33-G35</f>
         <v/>
       </c>
-      <c r="H36" s="161">
+      <c r="H36" s="162">
         <f>H33-H35</f>
         <v/>
       </c>
-      <c r="I36" s="161">
+      <c r="I36" s="162">
         <f>I33-I35</f>
         <v/>
       </c>
-      <c r="J36" s="149">
+      <c r="J36" s="150">
         <f>J33*(1-J13)</f>
         <v/>
       </c>
-      <c r="K36" s="149">
+      <c r="K36" s="150">
         <f>K33*(1-K13)</f>
         <v/>
       </c>
-      <c r="L36" s="149">
+      <c r="L36" s="150">
         <f>L33*(1-L13)</f>
         <v/>
       </c>
-      <c r="M36" s="149">
+      <c r="M36" s="150">
         <f>M33*(1-M13)</f>
         <v/>
       </c>
-      <c r="N36" s="149">
+      <c r="N36" s="150">
         <f>N33*(1-N13)</f>
         <v/>
       </c>
@@ -7956,38 +8335,38 @@
           <t>Cash</t>
         </is>
       </c>
-      <c r="E41" s="153" t="n">
+      <c r="E41" s="154" t="n">
         <v>195354</v>
       </c>
-      <c r="F41" s="153" t="n">
+      <c r="F41" s="154" t="n">
         <v>133202</v>
       </c>
-      <c r="G41" s="153" t="n">
+      <c r="G41" s="154" t="n">
         <v>136778</v>
       </c>
-      <c r="H41" s="153" t="n">
+      <c r="H41" s="154" t="n">
         <v>150667</v>
       </c>
-      <c r="I41" s="153" t="n">
+      <c r="I41" s="154" t="n">
         <v>134136</v>
       </c>
-      <c r="J41" s="149">
+      <c r="J41" s="150">
         <f>J78</f>
         <v/>
       </c>
-      <c r="K41" s="149">
+      <c r="K41" s="150">
         <f>K78</f>
         <v/>
       </c>
-      <c r="L41" s="149">
+      <c r="L41" s="150">
         <f>L78</f>
         <v/>
       </c>
-      <c r="M41" s="149">
+      <c r="M41" s="150">
         <f>M78</f>
         <v/>
       </c>
-      <c r="N41" s="149">
+      <c r="N41" s="150">
         <f>N78</f>
         <v/>
       </c>
@@ -7998,43 +8377,43 @@
           <t>Accounts Receivable</t>
         </is>
       </c>
-      <c r="C42" s="156" t="inlineStr">
+      <c r="C42" s="157" t="inlineStr">
         <is>
           <t>eqn: Rev × AR_days / 365</t>
         </is>
       </c>
-      <c r="E42" s="153" t="n">
+      <c r="E42" s="154" t="n">
         <v>206690</v>
       </c>
-      <c r="F42" s="153" t="n">
+      <c r="F42" s="154" t="n">
         <v>202365</v>
       </c>
-      <c r="G42" s="153" t="n">
+      <c r="G42" s="154" t="n">
         <v>251217</v>
       </c>
-      <c r="H42" s="153" t="n">
+      <c r="H42" s="154" t="n">
         <v>269745</v>
       </c>
-      <c r="I42" s="153" t="n">
+      <c r="I42" s="154" t="n">
         <v>341776</v>
       </c>
-      <c r="J42" s="149">
+      <c r="J42" s="150">
         <f>J24*J15/365</f>
         <v/>
       </c>
-      <c r="K42" s="149">
+      <c r="K42" s="150">
         <f>K24*K15/365</f>
         <v/>
       </c>
-      <c r="L42" s="149">
+      <c r="L42" s="150">
         <f>L24*L15/365</f>
         <v/>
       </c>
-      <c r="M42" s="149">
+      <c r="M42" s="150">
         <f>M24*M15/365</f>
         <v/>
       </c>
-      <c r="N42" s="149">
+      <c r="N42" s="150">
         <f>N24*N15/365</f>
         <v/>
       </c>
@@ -8045,38 +8424,38 @@
           <t>Inventory</t>
         </is>
       </c>
-      <c r="E43" s="153" t="n">
+      <c r="E43" s="154" t="n">
         <v>0</v>
       </c>
-      <c r="F43" s="153" t="n">
+      <c r="F43" s="154" t="n">
         <v>0</v>
       </c>
-      <c r="G43" s="153" t="n">
+      <c r="G43" s="154" t="n">
         <v>0</v>
       </c>
-      <c r="H43" s="153" t="n">
+      <c r="H43" s="154" t="n">
         <v>0</v>
       </c>
-      <c r="I43" s="153" t="n">
+      <c r="I43" s="154" t="n">
         <v>0</v>
       </c>
-      <c r="J43" s="149">
+      <c r="J43" s="150">
         <f>J25*J16/365</f>
         <v/>
       </c>
-      <c r="K43" s="149">
+      <c r="K43" s="150">
         <f>K25*K16/365</f>
         <v/>
       </c>
-      <c r="L43" s="149">
+      <c r="L43" s="150">
         <f>L25*L16/365</f>
         <v/>
       </c>
-      <c r="M43" s="149">
+      <c r="M43" s="150">
         <f>M25*M16/365</f>
         <v/>
       </c>
-      <c r="N43" s="149">
+      <c r="N43" s="150">
         <f>N25*N16/365</f>
         <v/>
       </c>
@@ -8087,38 +8466,38 @@
           <t>Property &amp; Equipment</t>
         </is>
       </c>
-      <c r="E44" s="153" t="n">
+      <c r="E44" s="154" t="n">
         <v>27913</v>
       </c>
-      <c r="F44" s="153" t="n">
+      <c r="F44" s="154" t="n">
         <v>17580</v>
       </c>
-      <c r="G44" s="153" t="n">
+      <c r="G44" s="154" t="n">
         <v>10966</v>
       </c>
-      <c r="H44" s="153" t="n">
+      <c r="H44" s="154" t="n">
         <v>38465</v>
       </c>
-      <c r="I44" s="153" t="n">
+      <c r="I44" s="154" t="n">
         <v>67713</v>
       </c>
-      <c r="J44" s="149">
+      <c r="J44" s="150">
         <f>J95</f>
         <v/>
       </c>
-      <c r="K44" s="149">
+      <c r="K44" s="150">
         <f>K95</f>
         <v/>
       </c>
-      <c r="L44" s="149">
+      <c r="L44" s="150">
         <f>L95</f>
         <v/>
       </c>
-      <c r="M44" s="149">
+      <c r="M44" s="150">
         <f>M95</f>
         <v/>
       </c>
-      <c r="N44" s="149">
+      <c r="N44" s="150">
         <f>N95</f>
         <v/>
       </c>
@@ -8131,43 +8510,43 @@
       </c>
       <c r="C45" s="39" t="n"/>
       <c r="D45" s="40" t="n"/>
-      <c r="E45" s="161">
+      <c r="E45" s="162">
         <f>SUM(E41:E44)</f>
         <v/>
       </c>
-      <c r="F45" s="161">
+      <c r="F45" s="162">
         <f>SUM(F41:F44)</f>
         <v/>
       </c>
-      <c r="G45" s="161">
+      <c r="G45" s="162">
         <f>SUM(G41:G44)</f>
         <v/>
       </c>
-      <c r="H45" s="161">
+      <c r="H45" s="162">
         <f>SUM(H41:H44)</f>
         <v/>
       </c>
-      <c r="I45" s="161">
+      <c r="I45" s="162">
         <f>SUM(I41:I44)</f>
         <v/>
       </c>
-      <c r="J45" s="149">
+      <c r="J45" s="150">
         <f>SUM(J41:J44)</f>
         <v/>
       </c>
-      <c r="K45" s="149">
+      <c r="K45" s="150">
         <f>SUM(K41:K44)</f>
         <v/>
       </c>
-      <c r="L45" s="149">
+      <c r="L45" s="150">
         <f>SUM(L41:L44)</f>
         <v/>
       </c>
-      <c r="M45" s="149">
+      <c r="M45" s="150">
         <f>SUM(M41:M44)</f>
         <v/>
       </c>
-      <c r="N45" s="149">
+      <c r="N45" s="150">
         <f>SUM(N41:N44)</f>
         <v/>
       </c>
@@ -8205,43 +8584,43 @@
           <t>Accounts Payable</t>
         </is>
       </c>
-      <c r="C48" s="156" t="inlineStr">
+      <c r="C48" s="157" t="inlineStr">
         <is>
           <t>eqn: COGS × AP_days / 365</t>
         </is>
       </c>
-      <c r="E48" s="153" t="n">
+      <c r="E48" s="154" t="n">
         <v>20749</v>
       </c>
-      <c r="F48" s="153" t="n">
+      <c r="F48" s="154" t="n">
         <v>17273</v>
       </c>
-      <c r="G48" s="153" t="n">
+      <c r="G48" s="154" t="n">
         <v>19009</v>
       </c>
-      <c r="H48" s="153" t="n">
+      <c r="H48" s="154" t="n">
         <v>22473</v>
       </c>
-      <c r="I48" s="153" t="n">
+      <c r="I48" s="154" t="n">
         <v>32315</v>
       </c>
-      <c r="J48" s="149">
+      <c r="J48" s="150">
         <f>J25*J17/365</f>
         <v/>
       </c>
-      <c r="K48" s="149">
+      <c r="K48" s="150">
         <f>K25*K17/365</f>
         <v/>
       </c>
-      <c r="L48" s="149">
+      <c r="L48" s="150">
         <f>L25*L17/365</f>
         <v/>
       </c>
-      <c r="M48" s="149">
+      <c r="M48" s="150">
         <f>M25*M17/365</f>
         <v/>
       </c>
-      <c r="N48" s="149">
+      <c r="N48" s="150">
         <f>N25*N17/365</f>
         <v/>
       </c>
@@ -8252,38 +8631,38 @@
           <t>Debt</t>
         </is>
       </c>
-      <c r="E49" s="153" t="n">
+      <c r="E49" s="154" t="n">
         <v>1259018</v>
       </c>
-      <c r="F49" s="153" t="n">
+      <c r="F49" s="154" t="n">
         <v>1853669</v>
       </c>
-      <c r="G49" s="153" t="n">
+      <c r="G49" s="154" t="n">
         <v>1861658</v>
       </c>
-      <c r="H49" s="153" t="n">
+      <c r="H49" s="154" t="n">
         <v>2209021</v>
       </c>
-      <c r="I49" s="153" t="n">
+      <c r="I49" s="154" t="n">
         <v>3055691</v>
       </c>
-      <c r="J49" s="149">
+      <c r="J49" s="150">
         <f>J100</f>
         <v/>
       </c>
-      <c r="K49" s="149">
+      <c r="K49" s="150">
         <f>K100</f>
         <v/>
       </c>
-      <c r="L49" s="149">
+      <c r="L49" s="150">
         <f>L100</f>
         <v/>
       </c>
-      <c r="M49" s="149">
+      <c r="M49" s="150">
         <f>M100</f>
         <v/>
       </c>
-      <c r="N49" s="149">
+      <c r="N49" s="150">
         <f>N100</f>
         <v/>
       </c>
@@ -8296,43 +8675,43 @@
       </c>
       <c r="C50" s="4" t="n"/>
       <c r="D50" s="22" t="n"/>
-      <c r="E50" s="155">
+      <c r="E50" s="156">
         <f>SUM(E48:E49)</f>
         <v/>
       </c>
-      <c r="F50" s="155">
+      <c r="F50" s="156">
         <f>SUM(F48:F49)</f>
         <v/>
       </c>
-      <c r="G50" s="155">
+      <c r="G50" s="156">
         <f>SUM(G48:G49)</f>
         <v/>
       </c>
-      <c r="H50" s="155">
+      <c r="H50" s="156">
         <f>SUM(H48:H49)</f>
         <v/>
       </c>
-      <c r="I50" s="155">
+      <c r="I50" s="156">
         <f>SUM(I48:I49)</f>
         <v/>
       </c>
-      <c r="J50" s="149">
+      <c r="J50" s="150">
         <f>SUM(J48:J49)</f>
         <v/>
       </c>
-      <c r="K50" s="149">
+      <c r="K50" s="150">
         <f>SUM(K48:K49)</f>
         <v/>
       </c>
-      <c r="L50" s="149">
+      <c r="L50" s="150">
         <f>SUM(L48:L49)</f>
         <v/>
       </c>
-      <c r="M50" s="149">
+      <c r="M50" s="150">
         <f>SUM(M48:M49)</f>
         <v/>
       </c>
-      <c r="N50" s="149">
+      <c r="N50" s="150">
         <f>SUM(N48:N49)</f>
         <v/>
       </c>
@@ -8355,38 +8734,38 @@
           <t>Equity Capital</t>
         </is>
       </c>
-      <c r="E52" s="153" t="n">
+      <c r="E52" s="154" t="n">
         <v>-849810</v>
       </c>
-      <c r="F52" s="153" t="n">
+      <c r="F52" s="154" t="n">
         <v>-1517795</v>
       </c>
-      <c r="G52" s="153" t="n">
+      <c r="G52" s="154" t="n">
         <v>-1481706</v>
       </c>
-      <c r="H52" s="153" t="n">
+      <c r="H52" s="154" t="n">
         <v>-1772617</v>
       </c>
-      <c r="I52" s="153" t="n">
+      <c r="I52" s="154" t="n">
         <v>-2544381</v>
       </c>
-      <c r="J52" s="149">
+      <c r="J52" s="150">
         <f>I52+J20</f>
         <v/>
       </c>
-      <c r="K52" s="149">
+      <c r="K52" s="150">
         <f>J52+K20</f>
         <v/>
       </c>
-      <c r="L52" s="149">
+      <c r="L52" s="150">
         <f>K52+L20</f>
         <v/>
       </c>
-      <c r="M52" s="149">
+      <c r="M52" s="150">
         <f>L52+M20</f>
         <v/>
       </c>
-      <c r="N52" s="149">
+      <c r="N52" s="150">
         <f>M52+N20</f>
         <v/>
       </c>
@@ -8397,43 +8776,43 @@
           <t>Retained Earnings</t>
         </is>
       </c>
-      <c r="C53" s="156" t="inlineStr">
+      <c r="C53" s="157" t="inlineStr">
         <is>
           <t>eqn: PriorRE + EBT×(1−t)</t>
         </is>
       </c>
-      <c r="E53" s="153" t="n">
+      <c r="E53" s="154" t="n">
         <v>0</v>
       </c>
-      <c r="F53" s="153" t="n">
+      <c r="F53" s="154" t="n">
         <v>0</v>
       </c>
-      <c r="G53" s="153" t="n">
+      <c r="G53" s="154" t="n">
         <v>0</v>
       </c>
-      <c r="H53" s="153" t="n">
+      <c r="H53" s="154" t="n">
         <v>0</v>
       </c>
-      <c r="I53" s="153" t="n">
+      <c r="I53" s="154" t="n">
         <v>0</v>
       </c>
-      <c r="J53" s="149">
+      <c r="J53" s="150">
         <f>I53+J33*(1-J13)</f>
         <v/>
       </c>
-      <c r="K53" s="149">
+      <c r="K53" s="150">
         <f>J53+K33*(1-K13)</f>
         <v/>
       </c>
-      <c r="L53" s="149">
+      <c r="L53" s="150">
         <f>K53+L33*(1-L13)</f>
         <v/>
       </c>
-      <c r="M53" s="149">
+      <c r="M53" s="150">
         <f>L53+M33*(1-M13)</f>
         <v/>
       </c>
-      <c r="N53" s="149">
+      <c r="N53" s="150">
         <f>M53+N33*(1-N13)</f>
         <v/>
       </c>
@@ -8446,43 +8825,43 @@
       </c>
       <c r="C54" s="8" t="n"/>
       <c r="D54" s="26" t="n"/>
-      <c r="E54" s="162">
+      <c r="E54" s="163">
         <f>SUM(E52:E53)</f>
         <v/>
       </c>
-      <c r="F54" s="162">
+      <c r="F54" s="163">
         <f>SUM(F52:F53)</f>
         <v/>
       </c>
-      <c r="G54" s="162">
+      <c r="G54" s="163">
         <f>SUM(G52:G53)</f>
         <v/>
       </c>
-      <c r="H54" s="162">
+      <c r="H54" s="163">
         <f>SUM(H52:H53)</f>
         <v/>
       </c>
-      <c r="I54" s="162">
+      <c r="I54" s="163">
         <f>SUM(I52:I53)</f>
         <v/>
       </c>
-      <c r="J54" s="149">
+      <c r="J54" s="150">
         <f>SUM(J52:J53)</f>
         <v/>
       </c>
-      <c r="K54" s="149">
+      <c r="K54" s="150">
         <f>SUM(K52:K53)</f>
         <v/>
       </c>
-      <c r="L54" s="149">
+      <c r="L54" s="150">
         <f>SUM(L52:L53)</f>
         <v/>
       </c>
-      <c r="M54" s="149">
+      <c r="M54" s="150">
         <f>SUM(M52:M53)</f>
         <v/>
       </c>
-      <c r="N54" s="149">
+      <c r="N54" s="150">
         <f>SUM(N52:N53)</f>
         <v/>
       </c>
@@ -8495,43 +8874,43 @@
       </c>
       <c r="C55" s="39" t="n"/>
       <c r="D55" s="40" t="n"/>
-      <c r="E55" s="161">
+      <c r="E55" s="162">
         <f>E50+E54</f>
         <v/>
       </c>
-      <c r="F55" s="161">
+      <c r="F55" s="162">
         <f>F50+F54</f>
         <v/>
       </c>
-      <c r="G55" s="161">
+      <c r="G55" s="162">
         <f>G50+G54</f>
         <v/>
       </c>
-      <c r="H55" s="161">
+      <c r="H55" s="162">
         <f>H50+H54</f>
         <v/>
       </c>
-      <c r="I55" s="161">
+      <c r="I55" s="162">
         <f>I50+I54</f>
         <v/>
       </c>
-      <c r="J55" s="149">
+      <c r="J55" s="150">
         <f>J50+J54</f>
         <v/>
       </c>
-      <c r="K55" s="149">
+      <c r="K55" s="150">
         <f>K50+K54</f>
         <v/>
       </c>
-      <c r="L55" s="149">
+      <c r="L55" s="150">
         <f>L50+L54</f>
         <v/>
       </c>
-      <c r="M55" s="149">
+      <c r="M55" s="150">
         <f>M50+M54</f>
         <v/>
       </c>
-      <c r="N55" s="149">
+      <c r="N55" s="150">
         <f>N50+N54</f>
         <v/>
       </c>
@@ -8556,43 +8935,43 @@
       </c>
       <c r="C57" s="9" t="n"/>
       <c r="D57" s="27" t="n"/>
-      <c r="E57" s="163">
+      <c r="E57" s="164">
         <f>E55-E45</f>
         <v/>
       </c>
-      <c r="F57" s="163">
+      <c r="F57" s="164">
         <f>F55-F45</f>
         <v/>
       </c>
-      <c r="G57" s="163">
+      <c r="G57" s="164">
         <f>G55-G45</f>
         <v/>
       </c>
-      <c r="H57" s="163">
+      <c r="H57" s="164">
         <f>H55-H45</f>
         <v/>
       </c>
-      <c r="I57" s="163">
+      <c r="I57" s="164">
         <f>I55-I45</f>
         <v/>
       </c>
-      <c r="J57" s="149">
+      <c r="J57" s="150">
         <f>J55-J45</f>
         <v/>
       </c>
-      <c r="K57" s="149">
+      <c r="K57" s="150">
         <f>K55-K45</f>
         <v/>
       </c>
-      <c r="L57" s="149">
+      <c r="L57" s="150">
         <f>L55-L45</f>
         <v/>
       </c>
-      <c r="M57" s="149">
+      <c r="M57" s="150">
         <f>M55-M45</f>
         <v/>
       </c>
-      <c r="N57" s="149">
+      <c r="N57" s="150">
         <f>N55-N45</f>
         <v/>
       </c>
@@ -8656,48 +9035,48 @@
           <t>Net Earnings</t>
         </is>
       </c>
-      <c r="C62" s="156" t="inlineStr">
+      <c r="C62" s="157" t="inlineStr">
         <is>
           <t>eqn: EBT × (1 − tax%)  — full eqn, not pointer to IS</t>
         </is>
       </c>
-      <c r="E62" s="164">
+      <c r="E62" s="165">
         <f>E36</f>
         <v/>
       </c>
-      <c r="F62" s="164">
+      <c r="F62" s="165">
         <f>F36</f>
         <v/>
       </c>
-      <c r="G62" s="164">
+      <c r="G62" s="165">
         <f>G36</f>
         <v/>
       </c>
-      <c r="H62" s="164">
+      <c r="H62" s="165">
         <f>H36</f>
         <v/>
       </c>
-      <c r="I62" s="164">
+      <c r="I62" s="165">
         <f>I36</f>
         <v/>
       </c>
-      <c r="J62" s="149">
+      <c r="J62" s="150">
         <f>J33*(1-J13)</f>
         <v/>
       </c>
-      <c r="K62" s="149">
+      <c r="K62" s="150">
         <f>K33*(1-K13)</f>
         <v/>
       </c>
-      <c r="L62" s="149">
+      <c r="L62" s="150">
         <f>L33*(1-L13)</f>
         <v/>
       </c>
-      <c r="M62" s="149">
+      <c r="M62" s="150">
         <f>M33*(1-M13)</f>
         <v/>
       </c>
-      <c r="N62" s="149">
+      <c r="N62" s="150">
         <f>N33*(1-N13)</f>
         <v/>
       </c>
@@ -8708,48 +9087,48 @@
           <t>Plus: Depreciation &amp; Amortization</t>
         </is>
       </c>
-      <c r="C63" s="156" t="inlineStr">
+      <c r="C63" s="157" t="inlineStr">
         <is>
           <t>eqn: PPE_open × DA%</t>
         </is>
       </c>
-      <c r="E63" s="164">
+      <c r="E63" s="165">
         <f>+E30</f>
         <v/>
       </c>
-      <c r="F63" s="164">
+      <c r="F63" s="165">
         <f>+F30</f>
         <v/>
       </c>
-      <c r="G63" s="164">
+      <c r="G63" s="165">
         <f>+G30</f>
         <v/>
       </c>
-      <c r="H63" s="164">
+      <c r="H63" s="165">
         <f>+H30</f>
         <v/>
       </c>
-      <c r="I63" s="164">
+      <c r="I63" s="165">
         <f>+I30</f>
         <v/>
       </c>
-      <c r="J63" s="149">
+      <c r="J63" s="150">
         <f>J92*J11</f>
         <v/>
       </c>
-      <c r="K63" s="149">
+      <c r="K63" s="150">
         <f>K92*K11</f>
         <v/>
       </c>
-      <c r="L63" s="149">
+      <c r="L63" s="150">
         <f>L92*L11</f>
         <v/>
       </c>
-      <c r="M63" s="149">
+      <c r="M63" s="150">
         <f>M92*M11</f>
         <v/>
       </c>
-      <c r="N63" s="149">
+      <c r="N63" s="150">
         <f>N92*N11</f>
         <v/>
       </c>
@@ -8760,43 +9139,43 @@
           <t>Less: Changes in Working Capital</t>
         </is>
       </c>
-      <c r="C64" s="156" t="inlineStr">
+      <c r="C64" s="157" t="inlineStr">
         <is>
           <t>eqn: NWC_t − NWC_t−1</t>
         </is>
       </c>
-      <c r="E64" s="153" t="n">
+      <c r="E64" s="154" t="n">
         <v>0</v>
       </c>
-      <c r="F64" s="153" t="n">
+      <c r="F64" s="154" t="n">
         <v>-849</v>
       </c>
-      <c r="G64" s="153" t="n">
+      <c r="G64" s="154" t="n">
         <v>47116</v>
       </c>
-      <c r="H64" s="153" t="n">
+      <c r="H64" s="154" t="n">
         <v>15064</v>
       </c>
-      <c r="I64" s="153" t="n">
+      <c r="I64" s="154" t="n">
         <v>62189</v>
       </c>
-      <c r="J64" s="149">
+      <c r="J64" s="150">
         <f>J88-I88</f>
         <v/>
       </c>
-      <c r="K64" s="149">
+      <c r="K64" s="150">
         <f>K88-J88</f>
         <v/>
       </c>
-      <c r="L64" s="149">
+      <c r="L64" s="150">
         <f>L88-K88</f>
         <v/>
       </c>
-      <c r="M64" s="149">
+      <c r="M64" s="150">
         <f>M88-L88</f>
         <v/>
       </c>
-      <c r="N64" s="149">
+      <c r="N64" s="150">
         <f>N88-M88</f>
         <v/>
       </c>
@@ -8807,49 +9186,49 @@
           <t>Cash from Operations</t>
         </is>
       </c>
-      <c r="C65" s="154" t="inlineStr">
+      <c r="C65" s="155" t="inlineStr">
         <is>
           <t>eqn: NI + DA − ΔNWC</t>
         </is>
       </c>
       <c r="D65" s="28" t="n"/>
-      <c r="E65" s="155">
+      <c r="E65" s="156">
         <f>E62+E63-E64</f>
         <v/>
       </c>
-      <c r="F65" s="155">
+      <c r="F65" s="156">
         <f>F62+F63-F64</f>
         <v/>
       </c>
-      <c r="G65" s="155">
+      <c r="G65" s="156">
         <f>G62+G63-G64</f>
         <v/>
       </c>
-      <c r="H65" s="155">
+      <c r="H65" s="156">
         <f>H62+H63-H64</f>
         <v/>
       </c>
-      <c r="I65" s="155">
+      <c r="I65" s="156">
         <f>I62+I63-I64</f>
         <v/>
       </c>
-      <c r="J65" s="149">
+      <c r="J65" s="150">
         <f>J33*(1-J13)+J92*J11-(J88-I88)</f>
         <v/>
       </c>
-      <c r="K65" s="149">
+      <c r="K65" s="150">
         <f>K33*(1-K13)+K92*K11-(K88-J88)</f>
         <v/>
       </c>
-      <c r="L65" s="149">
+      <c r="L65" s="150">
         <f>L33*(1-L13)+L92*L11-(L88-K88)</f>
         <v/>
       </c>
-      <c r="M65" s="149">
+      <c r="M65" s="150">
         <f>M33*(1-M13)+M92*M11-(M88-L88)</f>
         <v/>
       </c>
-      <c r="N65" s="149">
+      <c r="N65" s="150">
         <f>N33*(1-N13)+N92*N11-(N88-M88)</f>
         <v/>
       </c>
@@ -8892,43 +9271,43 @@
           <t>Investments in Property &amp; Equipment</t>
         </is>
       </c>
-      <c r="C68" s="156" t="inlineStr">
+      <c r="C68" s="157" t="inlineStr">
         <is>
           <t>eqn: Rev × CapEx%</t>
         </is>
       </c>
-      <c r="E68" s="153" t="n">
+      <c r="E68" s="154" t="n">
         <v>7569</v>
       </c>
-      <c r="F68" s="153" t="n">
+      <c r="F68" s="154" t="n">
         <v>6029</v>
       </c>
-      <c r="G68" s="153" t="n">
+      <c r="G68" s="154" t="n">
         <v>4237</v>
       </c>
-      <c r="H68" s="153" t="n">
+      <c r="H68" s="154" t="n">
         <v>25551</v>
       </c>
-      <c r="I68" s="153" t="n">
+      <c r="I68" s="154" t="n">
         <v>39407</v>
       </c>
-      <c r="J68" s="149">
+      <c r="J68" s="150">
         <f>J24*J18</f>
         <v/>
       </c>
-      <c r="K68" s="149">
+      <c r="K68" s="150">
         <f>K24*K18</f>
         <v/>
       </c>
-      <c r="L68" s="149">
+      <c r="L68" s="150">
         <f>L24*L18</f>
         <v/>
       </c>
-      <c r="M68" s="149">
+      <c r="M68" s="150">
         <f>M24*M18</f>
         <v/>
       </c>
-      <c r="N68" s="149">
+      <c r="N68" s="150">
         <f>N24*N18</f>
         <v/>
       </c>
@@ -8941,43 +9320,43 @@
       </c>
       <c r="C69" s="5" t="n"/>
       <c r="D69" s="28" t="n"/>
-      <c r="E69" s="155">
+      <c r="E69" s="156">
         <f>SUM(E68)</f>
         <v/>
       </c>
-      <c r="F69" s="155">
+      <c r="F69" s="156">
         <f>SUM(F68)</f>
         <v/>
       </c>
-      <c r="G69" s="155">
+      <c r="G69" s="156">
         <f>SUM(G68)</f>
         <v/>
       </c>
-      <c r="H69" s="155">
+      <c r="H69" s="156">
         <f>SUM(H68)</f>
         <v/>
       </c>
-      <c r="I69" s="155">
+      <c r="I69" s="156">
         <f>SUM(I68)</f>
         <v/>
       </c>
-      <c r="J69" s="149">
+      <c r="J69" s="150">
         <f>J68</f>
         <v/>
       </c>
-      <c r="K69" s="149">
+      <c r="K69" s="150">
         <f>K68</f>
         <v/>
       </c>
-      <c r="L69" s="149">
+      <c r="L69" s="150">
         <f>L68</f>
         <v/>
       </c>
-      <c r="M69" s="149">
+      <c r="M69" s="150">
         <f>M68</f>
         <v/>
       </c>
-      <c r="N69" s="149">
+      <c r="N69" s="150">
         <f>N68</f>
         <v/>
       </c>
@@ -9020,38 +9399,38 @@
           <t>Issuance (repayment) of debt</t>
         </is>
       </c>
-      <c r="E72" s="153" t="n">
+      <c r="E72" s="154" t="n">
         <v>519583</v>
       </c>
-      <c r="F72" s="153" t="n">
+      <c r="F72" s="154" t="n">
         <v>594651</v>
       </c>
-      <c r="G72" s="153" t="n">
+      <c r="G72" s="154" t="n">
         <v>7989</v>
       </c>
-      <c r="H72" s="153" t="n">
+      <c r="H72" s="154" t="n">
         <v>347363</v>
       </c>
-      <c r="I72" s="153" t="n">
+      <c r="I72" s="154" t="n">
         <v>846670</v>
       </c>
-      <c r="J72" s="149">
+      <c r="J72" s="150">
         <f>J19</f>
         <v/>
       </c>
-      <c r="K72" s="149">
+      <c r="K72" s="150">
         <f>K19</f>
         <v/>
       </c>
-      <c r="L72" s="149">
+      <c r="L72" s="150">
         <f>L19</f>
         <v/>
       </c>
-      <c r="M72" s="149">
+      <c r="M72" s="150">
         <f>M19</f>
         <v/>
       </c>
-      <c r="N72" s="149">
+      <c r="N72" s="150">
         <f>N19</f>
         <v/>
       </c>
@@ -9062,38 +9441,38 @@
           <t>Issuance (repayment) of equity</t>
         </is>
       </c>
-      <c r="E73" s="153" t="n">
+      <c r="E73" s="154" t="n">
         <v>0</v>
       </c>
-      <c r="F73" s="153" t="n">
+      <c r="F73" s="154" t="n">
         <v>0</v>
       </c>
-      <c r="G73" s="153" t="n">
+      <c r="G73" s="154" t="n">
         <v>0</v>
       </c>
-      <c r="H73" s="153" t="n">
+      <c r="H73" s="154" t="n">
         <v>0</v>
       </c>
-      <c r="I73" s="153" t="n">
+      <c r="I73" s="154" t="n">
         <v>0</v>
       </c>
-      <c r="J73" s="149">
+      <c r="J73" s="150">
         <f>J20</f>
         <v/>
       </c>
-      <c r="K73" s="149">
+      <c r="K73" s="150">
         <f>K20</f>
         <v/>
       </c>
-      <c r="L73" s="149">
+      <c r="L73" s="150">
         <f>L20</f>
         <v/>
       </c>
-      <c r="M73" s="149">
+      <c r="M73" s="150">
         <f>M20</f>
         <v/>
       </c>
-      <c r="N73" s="149">
+      <c r="N73" s="150">
         <f>N20</f>
         <v/>
       </c>
@@ -9106,43 +9485,43 @@
       </c>
       <c r="C74" s="5" t="n"/>
       <c r="D74" s="28" t="n"/>
-      <c r="E74" s="155">
+      <c r="E74" s="156">
         <f>SUM(E72:E73)</f>
         <v/>
       </c>
-      <c r="F74" s="155">
+      <c r="F74" s="156">
         <f>SUM(F72:F73)</f>
         <v/>
       </c>
-      <c r="G74" s="155">
+      <c r="G74" s="156">
         <f>SUM(G72:G73)</f>
         <v/>
       </c>
-      <c r="H74" s="155">
+      <c r="H74" s="156">
         <f>SUM(H72:H73)</f>
         <v/>
       </c>
-      <c r="I74" s="155">
+      <c r="I74" s="156">
         <f>SUM(I72:I73)</f>
         <v/>
       </c>
-      <c r="J74" s="149">
+      <c r="J74" s="150">
         <f>J19+J20</f>
         <v/>
       </c>
-      <c r="K74" s="149">
+      <c r="K74" s="150">
         <f>K19+K20</f>
         <v/>
       </c>
-      <c r="L74" s="149">
+      <c r="L74" s="150">
         <f>L19+L20</f>
         <v/>
       </c>
-      <c r="M74" s="149">
+      <c r="M74" s="150">
         <f>M19+M20</f>
         <v/>
       </c>
-      <c r="N74" s="149">
+      <c r="N74" s="150">
         <f>N19+N20</f>
         <v/>
       </c>
@@ -9168,48 +9547,48 @@
           <t>Net Increase (decrease) in Cash</t>
         </is>
       </c>
-      <c r="C76" s="156" t="inlineStr">
+      <c r="C76" s="157" t="inlineStr">
         <is>
           <t>eqn: CFO − CapEx + Financing</t>
         </is>
       </c>
-      <c r="E76" s="165">
+      <c r="E76" s="166">
         <f>E41-E77</f>
         <v/>
       </c>
-      <c r="F76" s="165">
+      <c r="F76" s="166">
         <f>F41-F77</f>
         <v/>
       </c>
-      <c r="G76" s="165">
+      <c r="G76" s="166">
         <f>G41-G77</f>
         <v/>
       </c>
-      <c r="H76" s="165">
+      <c r="H76" s="166">
         <f>H41-H77</f>
         <v/>
       </c>
-      <c r="I76" s="165">
+      <c r="I76" s="166">
         <f>I41-I77</f>
         <v/>
       </c>
-      <c r="J76" s="149">
+      <c r="J76" s="150">
         <f>J65-J69+J74</f>
         <v/>
       </c>
-      <c r="K76" s="149">
+      <c r="K76" s="150">
         <f>K65-K69+K74</f>
         <v/>
       </c>
-      <c r="L76" s="149">
+      <c r="L76" s="150">
         <f>L65-L69+L74</f>
         <v/>
       </c>
-      <c r="M76" s="149">
+      <c r="M76" s="150">
         <f>M65-M69+M74</f>
         <v/>
       </c>
-      <c r="N76" s="149">
+      <c r="N76" s="150">
         <f>N65-N69+N74</f>
         <v/>
       </c>
@@ -9220,42 +9599,42 @@
           <t>Opening Cash Balance</t>
         </is>
       </c>
-      <c r="E77" s="153" t="n">
+      <c r="E77" s="154" t="n">
         <v>157394</v>
       </c>
-      <c r="F77" s="165">
+      <c r="F77" s="166">
         <f>E41</f>
         <v/>
       </c>
-      <c r="G77" s="165">
+      <c r="G77" s="166">
         <f>F41</f>
         <v/>
       </c>
-      <c r="H77" s="165">
+      <c r="H77" s="166">
         <f>G41</f>
         <v/>
       </c>
-      <c r="I77" s="165">
+      <c r="I77" s="166">
         <f>H41</f>
         <v/>
       </c>
-      <c r="J77" s="149">
+      <c r="J77" s="150">
         <f>I41</f>
         <v/>
       </c>
-      <c r="K77" s="149">
+      <c r="K77" s="150">
         <f>J41</f>
         <v/>
       </c>
-      <c r="L77" s="149">
+      <c r="L77" s="150">
         <f>K41</f>
         <v/>
       </c>
-      <c r="M77" s="149">
+      <c r="M77" s="150">
         <f>L41</f>
         <v/>
       </c>
-      <c r="N77" s="149">
+      <c r="N77" s="150">
         <f>M41</f>
         <v/>
       </c>
@@ -9267,46 +9646,46 @@
         </is>
       </c>
       <c r="C78" s="5" t="n"/>
-      <c r="D78" s="166" t="n">
+      <c r="D78" s="167" t="n">
         <v>157394</v>
       </c>
-      <c r="E78" s="155">
+      <c r="E78" s="156">
         <f>SUM(E76:E77)</f>
         <v/>
       </c>
-      <c r="F78" s="155">
+      <c r="F78" s="156">
         <f>SUM(F76:F77)</f>
         <v/>
       </c>
-      <c r="G78" s="155">
+      <c r="G78" s="156">
         <f>SUM(G76:G77)</f>
         <v/>
       </c>
-      <c r="H78" s="155">
+      <c r="H78" s="156">
         <f>SUM(H76:H77)</f>
         <v/>
       </c>
-      <c r="I78" s="155">
+      <c r="I78" s="156">
         <f>SUM(I76:I77)</f>
         <v/>
       </c>
-      <c r="J78" s="149">
+      <c r="J78" s="150">
         <f>J77+J76</f>
         <v/>
       </c>
-      <c r="K78" s="149">
+      <c r="K78" s="150">
         <f>K77+K76</f>
         <v/>
       </c>
-      <c r="L78" s="149">
+      <c r="L78" s="150">
         <f>L77+L76</f>
         <v/>
       </c>
-      <c r="M78" s="149">
+      <c r="M78" s="150">
         <f>M77+M76</f>
         <v/>
       </c>
-      <c r="N78" s="149">
+      <c r="N78" s="150">
         <f>N77+N76</f>
         <v/>
       </c>
@@ -9327,43 +9706,43 @@
       </c>
       <c r="C80" s="9" t="n"/>
       <c r="D80" s="27" t="n"/>
-      <c r="E80" s="163">
+      <c r="E80" s="164">
         <f>E78-E41</f>
         <v/>
       </c>
-      <c r="F80" s="163">
+      <c r="F80" s="164">
         <f>F78-F41</f>
         <v/>
       </c>
-      <c r="G80" s="163">
+      <c r="G80" s="164">
         <f>G78-G41</f>
         <v/>
       </c>
-      <c r="H80" s="163">
+      <c r="H80" s="164">
         <f>H78-H41</f>
         <v/>
       </c>
-      <c r="I80" s="163">
+      <c r="I80" s="164">
         <f>I78-I41</f>
         <v/>
       </c>
-      <c r="J80" s="149">
+      <c r="J80" s="150">
         <f>J78-J41</f>
         <v/>
       </c>
-      <c r="K80" s="149">
+      <c r="K80" s="150">
         <f>K78-K41</f>
         <v/>
       </c>
-      <c r="L80" s="149">
+      <c r="L80" s="150">
         <f>L78-L41</f>
         <v/>
       </c>
-      <c r="M80" s="149">
+      <c r="M80" s="150">
         <f>M78-M41</f>
         <v/>
       </c>
-      <c r="N80" s="149">
+      <c r="N80" s="150">
         <f>N78-N41</f>
         <v/>
       </c>
@@ -9419,38 +9798,38 @@
           <t>Accounts Receivable</t>
         </is>
       </c>
-      <c r="E85" s="153" t="n">
+      <c r="E85" s="154" t="n">
         <v>206690</v>
       </c>
-      <c r="F85" s="153" t="n">
+      <c r="F85" s="154" t="n">
         <v>202365</v>
       </c>
-      <c r="G85" s="153" t="n">
+      <c r="G85" s="154" t="n">
         <v>251217</v>
       </c>
-      <c r="H85" s="153" t="n">
+      <c r="H85" s="154" t="n">
         <v>269745</v>
       </c>
-      <c r="I85" s="153" t="n">
+      <c r="I85" s="154" t="n">
         <v>341776</v>
       </c>
-      <c r="J85" s="149">
+      <c r="J85" s="150">
         <f>J42</f>
         <v/>
       </c>
-      <c r="K85" s="149">
+      <c r="K85" s="150">
         <f>K42</f>
         <v/>
       </c>
-      <c r="L85" s="149">
+      <c r="L85" s="150">
         <f>L42</f>
         <v/>
       </c>
-      <c r="M85" s="149">
+      <c r="M85" s="150">
         <f>M42</f>
         <v/>
       </c>
-      <c r="N85" s="149">
+      <c r="N85" s="150">
         <f>N42</f>
         <v/>
       </c>
@@ -9461,38 +9840,38 @@
           <t>Inventory</t>
         </is>
       </c>
-      <c r="E86" s="153" t="n">
+      <c r="E86" s="154" t="n">
         <v>0</v>
       </c>
-      <c r="F86" s="153" t="n">
+      <c r="F86" s="154" t="n">
         <v>0</v>
       </c>
-      <c r="G86" s="153" t="n">
+      <c r="G86" s="154" t="n">
         <v>0</v>
       </c>
-      <c r="H86" s="153" t="n">
+      <c r="H86" s="154" t="n">
         <v>0</v>
       </c>
-      <c r="I86" s="153" t="n">
+      <c r="I86" s="154" t="n">
         <v>0</v>
       </c>
-      <c r="J86" s="149">
+      <c r="J86" s="150">
         <f>J43</f>
         <v/>
       </c>
-      <c r="K86" s="149">
+      <c r="K86" s="150">
         <f>K43</f>
         <v/>
       </c>
-      <c r="L86" s="149">
+      <c r="L86" s="150">
         <f>L43</f>
         <v/>
       </c>
-      <c r="M86" s="149">
+      <c r="M86" s="150">
         <f>M43</f>
         <v/>
       </c>
-      <c r="N86" s="149">
+      <c r="N86" s="150">
         <f>N43</f>
         <v/>
       </c>
@@ -9503,38 +9882,38 @@
           <t>Accounts Payable</t>
         </is>
       </c>
-      <c r="E87" s="153" t="n">
+      <c r="E87" s="154" t="n">
         <v>20749</v>
       </c>
-      <c r="F87" s="153" t="n">
+      <c r="F87" s="154" t="n">
         <v>17273</v>
       </c>
-      <c r="G87" s="153" t="n">
+      <c r="G87" s="154" t="n">
         <v>19009</v>
       </c>
-      <c r="H87" s="153" t="n">
+      <c r="H87" s="154" t="n">
         <v>22473</v>
       </c>
-      <c r="I87" s="153" t="n">
+      <c r="I87" s="154" t="n">
         <v>32315</v>
       </c>
-      <c r="J87" s="149">
+      <c r="J87" s="150">
         <f>J48</f>
         <v/>
       </c>
-      <c r="K87" s="149">
+      <c r="K87" s="150">
         <f>K48</f>
         <v/>
       </c>
-      <c r="L87" s="149">
+      <c r="L87" s="150">
         <f>L48</f>
         <v/>
       </c>
-      <c r="M87" s="149">
+      <c r="M87" s="150">
         <f>M48</f>
         <v/>
       </c>
-      <c r="N87" s="149">
+      <c r="N87" s="150">
         <f>N48</f>
         <v/>
       </c>
@@ -9546,46 +9925,46 @@
         </is>
       </c>
       <c r="C88" s="5" t="n"/>
-      <c r="D88" s="166" t="n">
+      <c r="D88" s="167" t="n">
         <v>205747</v>
       </c>
-      <c r="E88" s="167">
+      <c r="E88" s="168">
         <f>E85+E86-E87</f>
         <v/>
       </c>
-      <c r="F88" s="167">
+      <c r="F88" s="168">
         <f>F85+F86-F87</f>
         <v/>
       </c>
-      <c r="G88" s="167">
+      <c r="G88" s="168">
         <f>G85+G86-G87</f>
         <v/>
       </c>
-      <c r="H88" s="167">
+      <c r="H88" s="168">
         <f>H85+H86-H87</f>
         <v/>
       </c>
-      <c r="I88" s="167">
+      <c r="I88" s="168">
         <f>I85+I86-I87</f>
         <v/>
       </c>
-      <c r="J88" s="149">
+      <c r="J88" s="150">
         <f>J85+J86-J87</f>
         <v/>
       </c>
-      <c r="K88" s="149">
+      <c r="K88" s="150">
         <f>K85+K86-K87</f>
         <v/>
       </c>
-      <c r="L88" s="149">
+      <c r="L88" s="150">
         <f>L85+L86-L87</f>
         <v/>
       </c>
-      <c r="M88" s="149">
+      <c r="M88" s="150">
         <f>M85+M86-M87</f>
         <v/>
       </c>
-      <c r="N88" s="149">
+      <c r="N88" s="150">
         <f>N85+N86-N87</f>
         <v/>
       </c>
@@ -9596,43 +9975,43 @@
           <t>Change in NWC</t>
         </is>
       </c>
-      <c r="E89" s="146">
+      <c r="E89" s="147">
         <f>E88-D88</f>
         <v/>
       </c>
-      <c r="F89" s="146">
+      <c r="F89" s="147">
         <f>F88-E88</f>
         <v/>
       </c>
-      <c r="G89" s="146">
+      <c r="G89" s="147">
         <f>G88-F88</f>
         <v/>
       </c>
-      <c r="H89" s="146">
+      <c r="H89" s="147">
         <f>H88-G88</f>
         <v/>
       </c>
-      <c r="I89" s="146">
+      <c r="I89" s="147">
         <f>I88-H88</f>
         <v/>
       </c>
-      <c r="J89" s="149">
+      <c r="J89" s="150">
         <f>J88-I88</f>
         <v/>
       </c>
-      <c r="K89" s="149">
+      <c r="K89" s="150">
         <f>K88-J88</f>
         <v/>
       </c>
-      <c r="L89" s="149">
+      <c r="L89" s="150">
         <f>L88-K88</f>
         <v/>
       </c>
-      <c r="M89" s="149">
+      <c r="M89" s="150">
         <f>M88-L88</f>
         <v/>
       </c>
-      <c r="N89" s="149">
+      <c r="N89" s="150">
         <f>N88-M88</f>
         <v/>
       </c>
@@ -9662,42 +10041,42 @@
           <t>PPE Opening</t>
         </is>
       </c>
-      <c r="E92" s="153" t="n">
+      <c r="E92" s="154" t="n">
         <v>46419</v>
       </c>
-      <c r="F92" s="165">
+      <c r="F92" s="166">
         <f>E95</f>
         <v/>
       </c>
-      <c r="G92" s="165">
+      <c r="G92" s="166">
         <f>F95</f>
         <v/>
       </c>
-      <c r="H92" s="165">
+      <c r="H92" s="166">
         <f>G95</f>
         <v/>
       </c>
-      <c r="I92" s="165">
+      <c r="I92" s="166">
         <f>H95</f>
         <v/>
       </c>
-      <c r="J92" s="149">
+      <c r="J92" s="150">
         <f>I44</f>
         <v/>
       </c>
-      <c r="K92" s="149">
+      <c r="K92" s="150">
         <f>J95</f>
         <v/>
       </c>
-      <c r="L92" s="149">
+      <c r="L92" s="150">
         <f>K95</f>
         <v/>
       </c>
-      <c r="M92" s="149">
+      <c r="M92" s="150">
         <f>L95</f>
         <v/>
       </c>
-      <c r="N92" s="149">
+      <c r="N92" s="150">
         <f>M95</f>
         <v/>
       </c>
@@ -9708,38 +10087,38 @@
           <t>Plus Capex</t>
         </is>
       </c>
-      <c r="E93" s="153" t="n">
+      <c r="E93" s="154" t="n">
         <v>7569</v>
       </c>
-      <c r="F93" s="153" t="n">
+      <c r="F93" s="154" t="n">
         <v>6029</v>
       </c>
-      <c r="G93" s="153" t="n">
+      <c r="G93" s="154" t="n">
         <v>4237</v>
       </c>
-      <c r="H93" s="153" t="n">
+      <c r="H93" s="154" t="n">
         <v>25551</v>
       </c>
-      <c r="I93" s="153" t="n">
+      <c r="I93" s="154" t="n">
         <v>39407</v>
       </c>
-      <c r="J93" s="149">
+      <c r="J93" s="150">
         <f>J24*J18</f>
         <v/>
       </c>
-      <c r="K93" s="149">
+      <c r="K93" s="150">
         <f>K24*K18</f>
         <v/>
       </c>
-      <c r="L93" s="149">
+      <c r="L93" s="150">
         <f>L24*L18</f>
         <v/>
       </c>
-      <c r="M93" s="149">
+      <c r="M93" s="150">
         <f>M24*M18</f>
         <v/>
       </c>
-      <c r="N93" s="149">
+      <c r="N93" s="150">
         <f>N24*N18</f>
         <v/>
       </c>
@@ -9750,38 +10129,38 @@
           <t>Less Depreciation</t>
         </is>
       </c>
-      <c r="E94" s="153" t="n">
+      <c r="E94" s="154" t="n">
         <v>25592</v>
       </c>
-      <c r="F94" s="153" t="n">
+      <c r="F94" s="154" t="n">
         <v>20465</v>
       </c>
-      <c r="G94" s="153" t="n">
+      <c r="G94" s="154" t="n">
         <v>14638</v>
       </c>
-      <c r="H94" s="153" t="n">
+      <c r="H94" s="154" t="n">
         <v>13827</v>
       </c>
-      <c r="I94" s="153" t="n">
+      <c r="I94" s="154" t="n">
         <v>14952</v>
       </c>
-      <c r="J94" s="149">
+      <c r="J94" s="150">
         <f>J92*J11</f>
         <v/>
       </c>
-      <c r="K94" s="149">
+      <c r="K94" s="150">
         <f>K92*K11</f>
         <v/>
       </c>
-      <c r="L94" s="149">
+      <c r="L94" s="150">
         <f>L92*L11</f>
         <v/>
       </c>
-      <c r="M94" s="149">
+      <c r="M94" s="150">
         <f>M92*M11</f>
         <v/>
       </c>
-      <c r="N94" s="149">
+      <c r="N94" s="150">
         <f>N92*N11</f>
         <v/>
       </c>
@@ -9794,38 +10173,38 @@
       </c>
       <c r="C95" s="5" t="n"/>
       <c r="D95" s="28" t="n"/>
-      <c r="E95" s="168" t="n">
+      <c r="E95" s="169" t="n">
         <v>27913</v>
       </c>
-      <c r="F95" s="168" t="n">
+      <c r="F95" s="169" t="n">
         <v>17580</v>
       </c>
-      <c r="G95" s="168" t="n">
+      <c r="G95" s="169" t="n">
         <v>10966</v>
       </c>
-      <c r="H95" s="168" t="n">
+      <c r="H95" s="169" t="n">
         <v>38465</v>
       </c>
-      <c r="I95" s="168" t="n">
+      <c r="I95" s="169" t="n">
         <v>67713</v>
       </c>
-      <c r="J95" s="149">
+      <c r="J95" s="150">
         <f>J92+J93-J94</f>
         <v/>
       </c>
-      <c r="K95" s="149">
+      <c r="K95" s="150">
         <f>K92+K93-K94</f>
         <v/>
       </c>
-      <c r="L95" s="149">
+      <c r="L95" s="150">
         <f>L92+L93-L94</f>
         <v/>
       </c>
-      <c r="M95" s="149">
+      <c r="M95" s="150">
         <f>M92+M93-M94</f>
         <v/>
       </c>
-      <c r="N95" s="149">
+      <c r="N95" s="150">
         <f>N92+N93-N94</f>
         <v/>
       </c>
@@ -9860,42 +10239,42 @@
           <t>Debt Opening</t>
         </is>
       </c>
-      <c r="E98" s="153" t="n">
+      <c r="E98" s="154" t="n">
         <v>739435</v>
       </c>
-      <c r="F98" s="165">
+      <c r="F98" s="166">
         <f>E100</f>
         <v/>
       </c>
-      <c r="G98" s="165">
+      <c r="G98" s="166">
         <f>F100</f>
         <v/>
       </c>
-      <c r="H98" s="165">
+      <c r="H98" s="166">
         <f>G100</f>
         <v/>
       </c>
-      <c r="I98" s="165">
+      <c r="I98" s="166">
         <f>H100</f>
         <v/>
       </c>
-      <c r="J98" s="149">
+      <c r="J98" s="150">
         <f>I49</f>
         <v/>
       </c>
-      <c r="K98" s="149">
+      <c r="K98" s="150">
         <f>J100</f>
         <v/>
       </c>
-      <c r="L98" s="149">
+      <c r="L98" s="150">
         <f>K100</f>
         <v/>
       </c>
-      <c r="M98" s="149">
+      <c r="M98" s="150">
         <f>L100</f>
         <v/>
       </c>
-      <c r="N98" s="149">
+      <c r="N98" s="150">
         <f>M100</f>
         <v/>
       </c>
@@ -9906,38 +10285,38 @@
           <t>Issuance (repayment)</t>
         </is>
       </c>
-      <c r="E99" s="153" t="n">
+      <c r="E99" s="154" t="n">
         <v>519583</v>
       </c>
-      <c r="F99" s="153" t="n">
+      <c r="F99" s="154" t="n">
         <v>594651</v>
       </c>
-      <c r="G99" s="153" t="n">
+      <c r="G99" s="154" t="n">
         <v>7989</v>
       </c>
-      <c r="H99" s="153" t="n">
+      <c r="H99" s="154" t="n">
         <v>347363</v>
       </c>
-      <c r="I99" s="153" t="n">
+      <c r="I99" s="154" t="n">
         <v>846670</v>
       </c>
-      <c r="J99" s="149">
+      <c r="J99" s="150">
         <f>J19</f>
         <v/>
       </c>
-      <c r="K99" s="149">
+      <c r="K99" s="150">
         <f>K19</f>
         <v/>
       </c>
-      <c r="L99" s="149">
+      <c r="L99" s="150">
         <f>L19</f>
         <v/>
       </c>
-      <c r="M99" s="149">
+      <c r="M99" s="150">
         <f>M19</f>
         <v/>
       </c>
-      <c r="N99" s="149">
+      <c r="N99" s="150">
         <f>N19</f>
         <v/>
       </c>
@@ -9950,38 +10329,38 @@
       </c>
       <c r="C100" s="5" t="n"/>
       <c r="D100" s="28" t="n"/>
-      <c r="E100" s="168" t="n">
+      <c r="E100" s="169" t="n">
         <v>1259018</v>
       </c>
-      <c r="F100" s="168" t="n">
+      <c r="F100" s="169" t="n">
         <v>1853669</v>
       </c>
-      <c r="G100" s="168" t="n">
+      <c r="G100" s="169" t="n">
         <v>1861658</v>
       </c>
-      <c r="H100" s="168" t="n">
+      <c r="H100" s="169" t="n">
         <v>2209021</v>
       </c>
-      <c r="I100" s="168" t="n">
+      <c r="I100" s="169" t="n">
         <v>3055691</v>
       </c>
-      <c r="J100" s="149">
+      <c r="J100" s="150">
         <f>J98+J99</f>
         <v/>
       </c>
-      <c r="K100" s="149">
+      <c r="K100" s="150">
         <f>K98+K99</f>
         <v/>
       </c>
-      <c r="L100" s="149">
+      <c r="L100" s="150">
         <f>L98+L99</f>
         <v/>
       </c>
-      <c r="M100" s="149">
+      <c r="M100" s="150">
         <f>M98+M99</f>
         <v/>
       </c>
-      <c r="N100" s="149">
+      <c r="N100" s="150">
         <f>N98+N99</f>
         <v/>
       </c>
@@ -9992,38 +10371,38 @@
           <t>Interest Expense</t>
         </is>
       </c>
-      <c r="E101" s="153" t="n">
+      <c r="E101" s="154" t="n">
         <v>40092</v>
       </c>
-      <c r="F101" s="153" t="n">
+      <c r="F101" s="154" t="n">
         <v>68967</v>
       </c>
-      <c r="G101" s="153" t="n">
+      <c r="G101" s="154" t="n">
         <v>95546</v>
       </c>
-      <c r="H101" s="153" t="n">
+      <c r="H101" s="154" t="n">
         <v>105638</v>
       </c>
-      <c r="I101" s="153" t="n">
+      <c r="I101" s="154" t="n">
         <v>133647</v>
       </c>
-      <c r="J101" s="149">
+      <c r="J101" s="150">
         <f>J98*J12</f>
         <v/>
       </c>
-      <c r="K101" s="149">
+      <c r="K101" s="150">
         <f>K98*K12</f>
         <v/>
       </c>
-      <c r="L101" s="149">
+      <c r="L101" s="150">
         <f>L98*L12</f>
         <v/>
       </c>
-      <c r="M101" s="149">
+      <c r="M101" s="150">
         <f>M98*M12</f>
         <v/>
       </c>
-      <c r="N101" s="149">
+      <c r="N101" s="150">
         <f>N98*N12</f>
         <v/>
       </c>
@@ -10307,8 +10686,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="P5:U5"/>
-    <mergeCell ref="P4:U4"/>
+    <mergeCell ref="P4:V4"/>
+    <mergeCell ref="P5:V5"/>
   </mergeCells>
   <conditionalFormatting sqref="E3:N3">
     <cfRule type="containsText" priority="1" operator="containsText" dxfId="1" text="OK">
@@ -10319,7 +10698,33 @@
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B138" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U7" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V7" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U8" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V8" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U9" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V9" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U10" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V10" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U11" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V12" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U13" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V13" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U15" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V15" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U16" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V16" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U17" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V17" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U18" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V18" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U19" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V19" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U20" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V20" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B138" r:id="rId27"/>
   </hyperlinks>
   <pageMargins left="0.7086614173228347" right="0.7086614173228347" top="0.7480314960629921" bottom="0.7480314960629921" header="0.3149606299212598" footer="0.3149606299212598"/>
   <pageSetup orientation="landscape" scale="78"/>
@@ -10328,7 +10733,7 @@
     <brk id="58" min="0" max="13" man="1"/>
     <brk id="81" min="0" max="13" man="1"/>
   </rowBreaks>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId28"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
@@ -10403,7 +10808,7 @@
       <c r="L2" s="96" t="n"/>
       <c r="M2" s="94" t="n"/>
       <c r="N2" s="94" t="n"/>
-      <c r="Q2" s="169" t="inlineStr">
+      <c r="Q2" s="170" t="inlineStr">
         <is>
           <t>vengeanceaiUSCMODEL4 — LIVE EQUATIONS + SOURCE LINKS</t>
         </is>
@@ -10425,7 +10830,7 @@
       <c r="M3" s="97" t="n"/>
       <c r="N3" s="97" t="n"/>
       <c r="O3" s="97" t="n"/>
-      <c r="Q3" s="170" t="inlineStr">
+      <c r="Q3" s="171" t="inlineStr">
         <is>
           <t>Yellow = inputs (edit). Green = formulas. Blue underlined = clickable sources.</t>
         </is>
@@ -10451,32 +10856,32 @@
       <c r="M4" s="97" t="n"/>
       <c r="N4" s="97" t="n"/>
       <c r="O4" s="97" t="n"/>
-      <c r="Q4" s="171" t="inlineStr">
+      <c r="Q4" s="172" t="inlineStr">
         <is>
           <t>Input</t>
         </is>
       </c>
-      <c r="R4" s="171" t="inlineStr">
+      <c r="R4" s="172" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="S4" s="171" t="inlineStr">
+      <c r="S4" s="172" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="T4" s="171" t="inlineStr">
+      <c r="T4" s="172" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="U4" s="171" t="inlineStr">
+      <c r="U4" s="172" t="inlineStr">
         <is>
           <t>Primary source (click)</t>
         </is>
       </c>
-      <c r="V4" s="171" t="inlineStr">
+      <c r="V4" s="172" t="inlineStr">
         <is>
           <t>Secondary source (click)</t>
         </is>
@@ -10490,10 +10895,10 @@
         </is>
       </c>
       <c r="C5" s="100" t="n"/>
-      <c r="D5" s="172" t="n">
+      <c r="D5" s="173" t="n">
         <v>0.1877023903712333</v>
       </c>
-      <c r="E5" s="173" t="inlineStr">
+      <c r="E5" s="174" t="inlineStr">
         <is>
           <t>Tax source: SEC 10-K</t>
         </is>
@@ -10515,7 +10920,7 @@
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="174" t="inlineStr">
+      <c r="A6" s="175" t="inlineStr">
         <is>
           <t>WACC sources → columns U–V</t>
         </is>
@@ -10525,26 +10930,26 @@
           <t>Discount Rate (WACC = We×Ke + Wd×Rd(1−t))</t>
         </is>
       </c>
-      <c r="C6" s="175" t="inlineStr">
+      <c r="C6" s="176" t="inlineStr">
         <is>
           <t>Sources →</t>
         </is>
       </c>
-      <c r="D6" s="176">
+      <c r="D6" s="177">
         <f>R15</f>
         <v/>
       </c>
-      <c r="E6" s="173" t="inlineStr">
+      <c r="E6" s="174" t="inlineStr">
         <is>
           <t>WACC sources → scroll to col U (Rf/ERP/β/Rd links)</t>
         </is>
       </c>
-      <c r="F6" s="173" t="inlineStr">
+      <c r="F6" s="174" t="inlineStr">
         <is>
           <t>Damodaran ERP</t>
         </is>
       </c>
-      <c r="G6" s="173" t="inlineStr">
+      <c r="G6" s="174" t="inlineStr">
         <is>
           <t>SEC 8-K Rd 6.250%</t>
         </is>
@@ -10557,30 +10962,30 @@
       <c r="M6" s="97" t="n"/>
       <c r="N6" s="97" t="n"/>
       <c r="O6" s="97" t="n"/>
-      <c r="Q6" s="177" t="inlineStr">
+      <c r="Q6" s="178" t="inlineStr">
         <is>
           <t>Risk-free rate (Rf)</t>
         </is>
       </c>
-      <c r="R6" s="178" t="n">
+      <c r="R6" s="179" t="n">
         <v>0.0463</v>
       </c>
-      <c r="S6" s="177" t="inlineStr">
+      <c r="S6" s="178" t="inlineStr">
         <is>
           <t>US 10Y Treasury yield</t>
         </is>
       </c>
-      <c r="T6" s="177" t="inlineStr">
+      <c r="T6" s="178" t="inlineStr">
         <is>
           <t>CAPM input</t>
         </is>
       </c>
-      <c r="U6" s="179" t="inlineStr">
+      <c r="U6" s="180" t="inlineStr">
         <is>
           <t>FRED DGS10 (US 10Y)</t>
         </is>
       </c>
-      <c r="V6" s="179" t="inlineStr">
+      <c r="V6" s="180" t="inlineStr">
         <is>
           <t>US Treasury Daily Par Yield Curve</t>
         </is>
@@ -10594,7 +10999,7 @@
         </is>
       </c>
       <c r="C7" s="97" t="n"/>
-      <c r="D7" s="172" t="n">
+      <c r="D7" s="173" t="n">
         <v>0.03</v>
       </c>
       <c r="E7" s="97" t="n"/>
@@ -10608,30 +11013,30 @@
       <c r="M7" s="97" t="n"/>
       <c r="N7" s="97" t="n"/>
       <c r="O7" s="97" t="n"/>
-      <c r="Q7" s="177" t="inlineStr">
+      <c r="Q7" s="178" t="inlineStr">
         <is>
           <t>Equity risk premium (ERP)</t>
         </is>
       </c>
-      <c r="R7" s="178" t="n">
+      <c r="R7" s="179" t="n">
         <v>0.0428</v>
       </c>
-      <c r="S7" s="177" t="inlineStr">
+      <c r="S7" s="178" t="inlineStr">
         <is>
           <t>Damodaran implied ERP</t>
         </is>
       </c>
-      <c r="T7" s="177" t="inlineStr">
+      <c r="T7" s="178" t="inlineStr">
         <is>
           <t>CAPM input</t>
         </is>
       </c>
-      <c r="U7" s="179" t="inlineStr">
+      <c r="U7" s="180" t="inlineStr">
         <is>
           <t>Damodaran Online — Implied ERP</t>
         </is>
       </c>
-      <c r="V7" s="179" t="inlineStr">
+      <c r="V7" s="180" t="inlineStr">
         <is>
           <t>Damodaran histimpl.xls / table</t>
         </is>
@@ -10645,10 +11050,10 @@
         </is>
       </c>
       <c r="C8" s="97" t="n"/>
-      <c r="D8" s="180" t="n">
+      <c r="D8" s="181" t="n">
         <v>25</v>
       </c>
-      <c r="E8" s="173" t="inlineStr">
+      <c r="E8" s="174" t="inlineStr">
         <is>
           <t>Rd source: SEC 8-K 6.250% notes</t>
         </is>
@@ -10663,30 +11068,30 @@
       <c r="M8" s="97" t="n"/>
       <c r="N8" s="97" t="n"/>
       <c r="O8" s="97" t="n"/>
-      <c r="Q8" s="177" t="inlineStr">
+      <c r="Q8" s="178" t="inlineStr">
         <is>
           <t>Beta (β)</t>
         </is>
       </c>
-      <c r="R8" s="181" t="n">
+      <c r="R8" s="182" t="n">
         <v>1.32</v>
       </c>
-      <c r="S8" s="177" t="inlineStr">
+      <c r="S8" s="178" t="inlineStr">
         <is>
           <t>Yahoo 5Y monthly beta</t>
         </is>
       </c>
-      <c r="T8" s="177" t="inlineStr">
+      <c r="T8" s="178" t="inlineStr">
         <is>
           <t>CAPM input</t>
         </is>
       </c>
-      <c r="U8" s="179" t="inlineStr">
+      <c r="U8" s="180" t="inlineStr">
         <is>
           <t>Yahoo Finance FICO Key Statistics</t>
         </is>
       </c>
-      <c r="V8" s="179" t="inlineStr">
+      <c r="V8" s="180" t="inlineStr">
         <is>
           <t>Yahoo Finance FICO quote</t>
         </is>
@@ -10700,7 +11105,7 @@
         </is>
       </c>
       <c r="C9" s="97" t="n"/>
-      <c r="D9" s="182" t="n">
+      <c r="D9" s="183" t="n">
         <v>45930</v>
       </c>
       <c r="E9" s="97" t="n"/>
@@ -10714,31 +11119,31 @@
       <c r="M9" s="97" t="n"/>
       <c r="N9" s="97" t="n"/>
       <c r="O9" s="97" t="n"/>
-      <c r="Q9" s="183" t="inlineStr">
+      <c r="Q9" s="184" t="inlineStr">
         <is>
           <t>Ke = Rf + β × ERP</t>
         </is>
       </c>
-      <c r="R9" s="184">
+      <c r="R9" s="185">
         <f>R6+R8*R7</f>
         <v/>
       </c>
-      <c r="S9" s="177" t="inlineStr">
+      <c r="S9" s="178" t="inlineStr">
         <is>
           <t>Cost of equity (CAPM)</t>
         </is>
       </c>
-      <c r="T9" s="183" t="inlineStr">
+      <c r="T9" s="184" t="inlineStr">
         <is>
           <t>→ WACC</t>
         </is>
       </c>
-      <c r="U9" s="177" t="inlineStr">
+      <c r="U9" s="178" t="inlineStr">
         <is>
           <t>Derived: R6 + R8 × R7</t>
         </is>
       </c>
-      <c r="V9" s="177" t="inlineStr"/>
+      <c r="V9" s="178" t="inlineStr"/>
     </row>
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="97" t="n"/>
@@ -10748,7 +11153,7 @@
         </is>
       </c>
       <c r="C10" s="97" t="n"/>
-      <c r="D10" s="182" t="n">
+      <c r="D10" s="183" t="n">
         <v>46295</v>
       </c>
       <c r="E10" s="97" t="n"/>
@@ -10762,30 +11167,30 @@
       <c r="M10" s="97" t="n"/>
       <c r="N10" s="97" t="n"/>
       <c r="O10" s="97" t="n"/>
-      <c r="Q10" s="177" t="inlineStr">
+      <c r="Q10" s="178" t="inlineStr">
         <is>
           <t>Pre-tax cost of debt (Rd)</t>
         </is>
       </c>
-      <c r="R10" s="178" t="n">
+      <c r="R10" s="179" t="n">
         <v>0.0625</v>
       </c>
-      <c r="S10" s="177" t="inlineStr">
+      <c r="S10" s="178" t="inlineStr">
         <is>
           <t>6.250% Senior Notes due 2034</t>
         </is>
       </c>
-      <c r="T10" s="177" t="inlineStr">
+      <c r="T10" s="178" t="inlineStr">
         <is>
           <t>WACC input</t>
         </is>
       </c>
-      <c r="U10" s="179" t="inlineStr">
+      <c r="U10" s="180" t="inlineStr">
         <is>
           <t>SEC 8-K — Notes closing (6.250%)</t>
         </is>
       </c>
-      <c r="V10" s="179" t="inlineStr">
+      <c r="V10" s="180" t="inlineStr">
         <is>
           <t>SEC EX-99.1 — Notes pricing press release</t>
         </is>
@@ -10799,7 +11204,7 @@
         </is>
       </c>
       <c r="C11" s="97" t="n"/>
-      <c r="D11" s="185" t="n">
+      <c r="D11" s="186" t="n">
         <v>1046.23</v>
       </c>
       <c r="E11" s="97" t="n"/>
@@ -10813,31 +11218,31 @@
       <c r="M11" s="97" t="n"/>
       <c r="N11" s="97" t="n"/>
       <c r="O11" s="97" t="n"/>
-      <c r="Q11" s="177" t="inlineStr">
+      <c r="Q11" s="178" t="inlineStr">
         <is>
           <t>Tax rate (t)</t>
         </is>
       </c>
-      <c r="R11" s="184">
+      <c r="R11" s="185">
         <f>$D$5</f>
         <v/>
       </c>
-      <c r="S11" s="177" t="inlineStr">
+      <c r="S11" s="178" t="inlineStr">
         <is>
           <t>FY25 effective = 150,649 / 802,595</t>
         </is>
       </c>
-      <c r="T11" s="177" t="inlineStr">
+      <c r="T11" s="178" t="inlineStr">
         <is>
           <t>Linked D5</t>
         </is>
       </c>
-      <c r="U11" s="179" t="inlineStr">
+      <c r="U11" s="180" t="inlineStr">
         <is>
           <t>SEC 10-K FY2025 (tax / EBT)</t>
         </is>
       </c>
-      <c r="V11" s="179" t="inlineStr">
+      <c r="V11" s="180" t="inlineStr">
         <is>
           <t>SEC companyfacts XBRL (CIK 0000814547)</t>
         </is>
@@ -10851,7 +11256,7 @@
         </is>
       </c>
       <c r="C12" s="97" t="n"/>
-      <c r="D12" s="186" t="n">
+      <c r="D12" s="187" t="n">
         <v>21597.635</v>
       </c>
       <c r="E12" s="97" t="n"/>
@@ -10865,31 +11270,31 @@
       <c r="M12" s="97" t="n"/>
       <c r="N12" s="97" t="n"/>
       <c r="O12" s="97" t="n"/>
-      <c r="Q12" s="183" t="inlineStr">
+      <c r="Q12" s="184" t="inlineStr">
         <is>
           <t>Rd_aftertax = Rd × (1 − t)</t>
         </is>
       </c>
-      <c r="R12" s="184">
+      <c r="R12" s="185">
         <f>R10*(1-R11)</f>
         <v/>
       </c>
-      <c r="S12" s="177" t="inlineStr">
+      <c r="S12" s="178" t="inlineStr">
         <is>
           <t>After-tax cost of debt</t>
         </is>
       </c>
-      <c r="T12" s="183" t="inlineStr">
+      <c r="T12" s="184" t="inlineStr">
         <is>
           <t>→ WACC</t>
         </is>
       </c>
-      <c r="U12" s="177" t="inlineStr">
+      <c r="U12" s="178" t="inlineStr">
         <is>
           <t>Derived: R10 × (1 − R11)</t>
         </is>
       </c>
-      <c r="V12" s="177" t="inlineStr"/>
+      <c r="V12" s="178" t="inlineStr"/>
     </row>
     <row r="13" ht="16" customHeight="1">
       <c r="A13" s="97" t="n"/>
@@ -10899,7 +11304,7 @@
         </is>
       </c>
       <c r="C13" s="97" t="n"/>
-      <c r="D13" s="186" t="n">
+      <c r="D13" s="187" t="n">
         <v>5582389</v>
       </c>
       <c r="E13" s="97" t="n"/>
@@ -10913,30 +11318,30 @@
       <c r="M13" s="97" t="n"/>
       <c r="N13" s="97" t="n"/>
       <c r="O13" s="97" t="n"/>
-      <c r="Q13" s="177" t="inlineStr">
+      <c r="Q13" s="178" t="inlineStr">
         <is>
           <t>Equity weight (We)</t>
         </is>
       </c>
-      <c r="R13" s="187" t="n">
+      <c r="R13" s="188" t="n">
         <v>0.8</v>
       </c>
-      <c r="S13" s="177" t="inlineStr">
+      <c r="S13" s="178" t="inlineStr">
         <is>
           <t>Target ~80% equity at market</t>
         </is>
       </c>
-      <c r="T13" s="177" t="inlineStr">
+      <c r="T13" s="178" t="inlineStr">
         <is>
           <t>WACC weight</t>
         </is>
       </c>
-      <c r="U13" s="179" t="inlineStr">
+      <c r="U13" s="180" t="inlineStr">
         <is>
           <t>SEC 10-Q Q3 FY2026 (debt / capital)</t>
         </is>
       </c>
-      <c r="V13" s="179" t="inlineStr">
+      <c r="V13" s="180" t="inlineStr">
         <is>
           <t>Yahoo market cap for E/(D+E)</t>
         </is>
@@ -10950,7 +11355,7 @@
         </is>
       </c>
       <c r="C14" s="97" t="n"/>
-      <c r="D14" s="186" t="n">
+      <c r="D14" s="187" t="n">
         <v>304537</v>
       </c>
       <c r="E14" s="97" t="n"/>
@@ -10964,30 +11369,30 @@
       <c r="M14" s="97" t="n"/>
       <c r="N14" s="97" t="n"/>
       <c r="O14" s="97" t="n"/>
-      <c r="Q14" s="177" t="inlineStr">
+      <c r="Q14" s="178" t="inlineStr">
         <is>
           <t>Debt weight (Wd)</t>
         </is>
       </c>
-      <c r="R14" s="187" t="n">
+      <c r="R14" s="188" t="n">
         <v>0.2</v>
       </c>
-      <c r="S14" s="177" t="inlineStr">
+      <c r="S14" s="178" t="inlineStr">
         <is>
           <t>Target ~20% debt (We+Wd=100%)</t>
         </is>
       </c>
-      <c r="T14" s="177" t="inlineStr">
+      <c r="T14" s="178" t="inlineStr">
         <is>
           <t>WACC weight</t>
         </is>
       </c>
-      <c r="U14" s="179" t="inlineStr">
+      <c r="U14" s="180" t="inlineStr">
         <is>
           <t>SEC 10-Q — total debt $5,582,389k</t>
         </is>
       </c>
-      <c r="V14" s="179" t="inlineStr">
+      <c r="V14" s="180" t="inlineStr">
         <is>
           <t>SEC 10-K — senior notes footnote</t>
         </is>
@@ -11001,7 +11406,7 @@
         </is>
       </c>
       <c r="C15" s="97" t="n"/>
-      <c r="D15" s="188">
+      <c r="D15" s="189">
         <f>'3 Statement Model'!J68</f>
         <v/>
       </c>
@@ -11016,31 +11421,31 @@
       <c r="M15" s="97" t="n"/>
       <c r="N15" s="97" t="n"/>
       <c r="O15" s="97" t="n"/>
-      <c r="Q15" s="183" t="inlineStr">
+      <c r="Q15" s="184" t="inlineStr">
         <is>
           <t>WACC = We×Ke + Wd×Rd_aftertax</t>
         </is>
       </c>
-      <c r="R15" s="184">
+      <c r="R15" s="185">
         <f>R13*R9+R14*R12</f>
         <v/>
       </c>
-      <c r="S15" s="177" t="inlineStr">
+      <c r="S15" s="178" t="inlineStr">
         <is>
           <t>PRIMARY discount rate → cell D6</t>
         </is>
       </c>
-      <c r="T15" s="183" t="inlineStr">
+      <c r="T15" s="184" t="inlineStr">
         <is>
           <t>→ D6</t>
         </is>
       </c>
-      <c r="U15" s="179" t="inlineStr">
+      <c r="U15" s="180" t="inlineStr">
         <is>
           <t>SEC filings (tax, debt coupons)</t>
         </is>
       </c>
-      <c r="V15" s="179" t="inlineStr">
+      <c r="V15" s="180" t="inlineStr">
         <is>
           <t>Damodaran (ERP methodology)</t>
         </is>
@@ -11071,23 +11476,23 @@
           <t>Entry</t>
         </is>
       </c>
-      <c r="E17" s="189">
+      <c r="E17" s="190">
         <f>YEAR(E18)</f>
         <v/>
       </c>
-      <c r="F17" s="189">
+      <c r="F17" s="190">
         <f>YEAR(F18)</f>
         <v/>
       </c>
-      <c r="G17" s="189">
+      <c r="G17" s="190">
         <f>YEAR(G18)</f>
         <v/>
       </c>
-      <c r="H17" s="189">
+      <c r="H17" s="190">
         <f>YEAR(H18)</f>
         <v/>
       </c>
-      <c r="I17" s="189">
+      <c r="I17" s="190">
         <f>YEAR(I18)</f>
         <v/>
       </c>
@@ -11119,31 +11524,31 @@
         </is>
       </c>
       <c r="C18" s="97" t="n"/>
-      <c r="D18" s="190">
+      <c r="D18" s="191">
         <f>D9</f>
         <v/>
       </c>
-      <c r="E18" s="191">
+      <c r="E18" s="192">
         <f>DATE(YEAR($D$10)+E19,3,31)</f>
         <v/>
       </c>
-      <c r="F18" s="191">
+      <c r="F18" s="192">
         <f>DATE(YEAR($D$10)+F19,3,31)</f>
         <v/>
       </c>
-      <c r="G18" s="191">
+      <c r="G18" s="192">
         <f>DATE(YEAR($D$10)+G19,3,31)</f>
         <v/>
       </c>
-      <c r="H18" s="191">
+      <c r="H18" s="192">
         <f>DATE(YEAR($D$10)+H19,3,31)</f>
         <v/>
       </c>
-      <c r="I18" s="191">
+      <c r="I18" s="192">
         <f>DATE(YEAR($D$10)+I19,3,31)</f>
         <v/>
       </c>
-      <c r="J18" s="192">
+      <c r="J18" s="193">
         <f>I18</f>
         <v/>
       </c>
@@ -11153,7 +11558,7 @@
           <t>Exit EV/EBITDA (in J27) — primary</t>
         </is>
       </c>
-      <c r="M18" s="188">
+      <c r="M18" s="189">
         <f>J27</f>
         <v/>
       </c>
@@ -11162,17 +11567,17 @@
         <v/>
       </c>
       <c r="O18" s="97" t="n"/>
-      <c r="Q18" s="183" t="inlineStr">
+      <c r="Q18" s="184" t="inlineStr">
         <is>
           <t>FCFF = EBIT − EBIT×t + D&amp;A − CapEx − ΔNWC</t>
         </is>
       </c>
-      <c r="U18" s="179" t="inlineStr">
+      <c r="U18" s="180" t="inlineStr">
         <is>
           <t>Drivers from SEC XBRL → 3-statement</t>
         </is>
       </c>
-      <c r="V18" s="179" t="inlineStr">
+      <c r="V18" s="180" t="inlineStr">
         <is>
           <t>SEC 10-K historical IS/CF</t>
         </is>
@@ -11187,22 +11592,22 @@
       </c>
       <c r="C19" s="118" t="n"/>
       <c r="D19" s="115" t="n"/>
-      <c r="E19" s="193" t="n">
+      <c r="E19" s="194" t="n">
         <v>0</v>
       </c>
-      <c r="F19" s="190">
+      <c r="F19" s="191">
         <f>E19+1</f>
         <v/>
       </c>
-      <c r="G19" s="190">
+      <c r="G19" s="191">
         <f>F19+1</f>
         <v/>
       </c>
-      <c r="H19" s="190">
+      <c r="H19" s="191">
         <f>G19+1</f>
         <v/>
       </c>
-      <c r="I19" s="190">
+      <c r="I19" s="191">
         <f>H19+1</f>
         <v/>
       </c>
@@ -11213,7 +11618,7 @@
           <t>Gordon cross-check</t>
         </is>
       </c>
-      <c r="M19" s="188">
+      <c r="M19" s="189">
         <f>IF(($D$6-$D$7)&lt;=0,"WACC must exceed g",$I$26*(1+$D$7)/($D$6-$D$7))</f>
         <v/>
       </c>
@@ -11222,12 +11627,12 @@
         <v/>
       </c>
       <c r="O19" s="97" t="n"/>
-      <c r="Q19" s="177" t="inlineStr">
+      <c r="Q19" s="178" t="inlineStr">
         <is>
           <t>Excel (col E example)</t>
         </is>
       </c>
-      <c r="R19" s="183">
+      <c r="R19" s="184">
         <f>E21-E22+E23-E24-E25</f>
         <v/>
       </c>
@@ -11241,23 +11646,23 @@
       </c>
       <c r="C20" s="97" t="n"/>
       <c r="D20" s="97" t="n"/>
-      <c r="E20" s="190">
+      <c r="E20" s="191">
         <f>YEARFRAC(D18,E18)</f>
         <v/>
       </c>
-      <c r="F20" s="190">
+      <c r="F20" s="191">
         <f>YEARFRAC(E18,F18)</f>
         <v/>
       </c>
-      <c r="G20" s="190">
+      <c r="G20" s="191">
         <f>YEARFRAC(F18,G18)</f>
         <v/>
       </c>
-      <c r="H20" s="190">
+      <c r="H20" s="191">
         <f>YEARFRAC(G18,H18)</f>
         <v/>
       </c>
-      <c r="I20" s="190">
+      <c r="I20" s="191">
         <f>YEARFRAC(H18,I18)</f>
         <v/>
       </c>
@@ -11268,7 +11673,7 @@
           <t>Implied Gordon exit multiple</t>
         </is>
       </c>
-      <c r="M20" s="188">
+      <c r="M20" s="189">
         <f>IF(($I$21+$I$23)=0,0,M19/($I$21+$I$23))</f>
         <v/>
       </c>
@@ -11277,21 +11682,21 @@
         <v/>
       </c>
       <c r="O20" s="97" t="n"/>
-      <c r="Q20" s="177" t="inlineStr">
+      <c r="Q20" s="178" t="inlineStr">
         <is>
           <t>Tax on EBIT (unlevered)</t>
         </is>
       </c>
-      <c r="R20" s="183">
+      <c r="R20" s="184">
         <f>E21*$D$5</f>
         <v/>
       </c>
-      <c r="S20" s="177" t="inlineStr">
+      <c r="S20" s="178" t="inlineStr">
         <is>
           <t>NOT levered IS tax dollars</t>
         </is>
       </c>
-      <c r="U20" s="179" t="inlineStr">
+      <c r="U20" s="180" t="inlineStr">
         <is>
           <t>Tax rate from SEC 10-K effective rate</t>
         </is>
@@ -11304,29 +11709,29 @@
           <t>EBIT (linked to 3-stmt)</t>
         </is>
       </c>
-      <c r="C21" s="194" t="inlineStr">
+      <c r="C21" s="195" t="inlineStr">
         <is>
           <t>EBIT</t>
         </is>
       </c>
       <c r="D21" s="97" t="n"/>
-      <c r="E21" s="188">
+      <c r="E21" s="189">
         <f>'3 Statement Model'!J26-'3 Statement Model'!J28-'3 Statement Model'!J29-'3 Statement Model'!J30</f>
         <v/>
       </c>
-      <c r="F21" s="188">
+      <c r="F21" s="189">
         <f>'3 Statement Model'!K26-'3 Statement Model'!K28-'3 Statement Model'!K29-'3 Statement Model'!K30</f>
         <v/>
       </c>
-      <c r="G21" s="188">
+      <c r="G21" s="189">
         <f>'3 Statement Model'!L26-'3 Statement Model'!L28-'3 Statement Model'!L29-'3 Statement Model'!L30</f>
         <v/>
       </c>
-      <c r="H21" s="188">
+      <c r="H21" s="189">
         <f>'3 Statement Model'!M26-'3 Statement Model'!M28-'3 Statement Model'!M29-'3 Statement Model'!M30</f>
         <v/>
       </c>
-      <c r="I21" s="188">
+      <c r="I21" s="189">
         <f>'3 Statement Model'!N26-'3 Statement Model'!N28-'3 Statement Model'!N29-'3 Statement Model'!N30</f>
         <v/>
       </c>
@@ -11336,16 +11741,16 @@
       <c r="M21" s="97" t="n"/>
       <c r="N21" s="97" t="n"/>
       <c r="O21" s="97" t="n"/>
-      <c r="Q21" s="177" t="inlineStr">
+      <c r="Q21" s="178" t="inlineStr">
         <is>
           <t>FCFF check (FY5 / col I)</t>
         </is>
       </c>
-      <c r="R21" s="195">
+      <c r="R21" s="196">
         <f>I26</f>
         <v/>
       </c>
-      <c r="S21" s="177" t="inlineStr">
+      <c r="S21" s="178" t="inlineStr">
         <is>
           <t>Must equal I21−I22+I23−I24−I25</t>
         </is>
@@ -11358,29 +11763,29 @@
           <t>Less: Unlevered Cash Taxes (EBIT×t)</t>
         </is>
       </c>
-      <c r="C22" s="194" t="inlineStr">
+      <c r="C22" s="195" t="inlineStr">
         <is>
           <t>EBIT×t</t>
         </is>
       </c>
       <c r="D22" s="97" t="n"/>
-      <c r="E22" s="188">
+      <c r="E22" s="189">
         <f>E21*$D$5</f>
         <v/>
       </c>
-      <c r="F22" s="188">
+      <c r="F22" s="189">
         <f>F21*$D$5</f>
         <v/>
       </c>
-      <c r="G22" s="188">
+      <c r="G22" s="189">
         <f>G21*$D$5</f>
         <v/>
       </c>
-      <c r="H22" s="188">
+      <c r="H22" s="189">
         <f>H21*$D$5</f>
         <v/>
       </c>
-      <c r="I22" s="188">
+      <c r="I22" s="189">
         <f>I21*$D$5</f>
         <v/>
       </c>
@@ -11398,29 +11803,29 @@
           <t>Plus: D&amp;A (linked to 3-stmt)</t>
         </is>
       </c>
-      <c r="C23" s="194" t="inlineStr">
+      <c r="C23" s="195" t="inlineStr">
         <is>
           <t>+D&amp;A</t>
         </is>
       </c>
       <c r="D23" s="97" t="n"/>
-      <c r="E23" s="188">
+      <c r="E23" s="189">
         <f>'3 Statement Model'!J30</f>
         <v/>
       </c>
-      <c r="F23" s="188">
+      <c r="F23" s="189">
         <f>'3 Statement Model'!K30</f>
         <v/>
       </c>
-      <c r="G23" s="188">
+      <c r="G23" s="189">
         <f>'3 Statement Model'!L30</f>
         <v/>
       </c>
-      <c r="H23" s="188">
+      <c r="H23" s="189">
         <f>'3 Statement Model'!M30</f>
         <v/>
       </c>
-      <c r="I23" s="188">
+      <c r="I23" s="189">
         <f>'3 Statement Model'!N30</f>
         <v/>
       </c>
@@ -11443,29 +11848,29 @@
           <t>Less: Capex (linked to 3-stmt CF)</t>
         </is>
       </c>
-      <c r="C24" s="194" t="inlineStr">
+      <c r="C24" s="195" t="inlineStr">
         <is>
           <t>−CapEx</t>
         </is>
       </c>
       <c r="D24" s="97" t="n"/>
-      <c r="E24" s="188">
+      <c r="E24" s="189">
         <f>'3 Statement Model'!J68</f>
         <v/>
       </c>
-      <c r="F24" s="188">
+      <c r="F24" s="189">
         <f>'3 Statement Model'!K68</f>
         <v/>
       </c>
-      <c r="G24" s="188">
+      <c r="G24" s="189">
         <f>'3 Statement Model'!L68</f>
         <v/>
       </c>
-      <c r="H24" s="188">
+      <c r="H24" s="189">
         <f>'3 Statement Model'!M68</f>
         <v/>
       </c>
-      <c r="I24" s="188">
+      <c r="I24" s="189">
         <f>'3 Statement Model'!N68</f>
         <v/>
       </c>
@@ -11475,7 +11880,7 @@
       <c r="M24" s="97" t="n"/>
       <c r="N24" s="97" t="n"/>
       <c r="O24" s="97" t="n"/>
-      <c r="Q24" s="183" t="inlineStr">
+      <c r="Q24" s="184" t="inlineStr">
         <is>
           <t>TV_exit = EBITDA_n × ExitMultiple   [PRIMARY]</t>
         </is>
@@ -11488,29 +11893,29 @@
           <t>Less: ΔNWC (linked to 3-stmt CF)</t>
         </is>
       </c>
-      <c r="C25" s="194" t="inlineStr">
+      <c r="C25" s="195" t="inlineStr">
         <is>
           <t>−ΔNWC</t>
         </is>
       </c>
       <c r="D25" s="97" t="n"/>
-      <c r="E25" s="188">
+      <c r="E25" s="189">
         <f>'3 Statement Model'!J64</f>
         <v/>
       </c>
-      <c r="F25" s="188">
+      <c r="F25" s="189">
         <f>'3 Statement Model'!K64</f>
         <v/>
       </c>
-      <c r="G25" s="188">
+      <c r="G25" s="189">
         <f>'3 Statement Model'!L64</f>
         <v/>
       </c>
-      <c r="H25" s="188">
+      <c r="H25" s="189">
         <f>'3 Statement Model'!M64</f>
         <v/>
       </c>
-      <c r="I25" s="188">
+      <c r="I25" s="189">
         <f>'3 Statement Model'!N64</f>
         <v/>
       </c>
@@ -11520,20 +11925,20 @@
       <c r="M25" s="97" t="n"/>
       <c r="N25" s="97" t="n"/>
       <c r="O25" s="97" t="n"/>
-      <c r="Q25" s="177" t="inlineStr">
+      <c r="Q25" s="178" t="inlineStr">
         <is>
           <t>Excel</t>
         </is>
       </c>
-      <c r="R25" s="183">
+      <c r="R25" s="184">
         <f>($I$21+$I$23)*$D$8</f>
         <v/>
       </c>
-      <c r="T25" s="195">
+      <c r="T25" s="196">
         <f>J27</f>
         <v/>
       </c>
-      <c r="U25" s="179" t="inlineStr">
+      <c r="U25" s="180" t="inlineStr">
         <is>
           <t>Exit multiple policy vs Yahoo / market multiples</t>
         </is>
@@ -11546,29 +11951,29 @@
           <t>Unlevered FCF</t>
         </is>
       </c>
-      <c r="C26" s="194" t="inlineStr">
+      <c r="C26" s="195" t="inlineStr">
         <is>
           <t>FCFF=EBIT−tax+DA−CapEx−ΔNWC</t>
         </is>
       </c>
       <c r="D26" s="97" t="n"/>
-      <c r="E26" s="196">
+      <c r="E26" s="197">
         <f>E21-E22+E23-E24-E25</f>
         <v/>
       </c>
-      <c r="F26" s="196">
+      <c r="F26" s="197">
         <f>F21-F22+F23-F24-F25</f>
         <v/>
       </c>
-      <c r="G26" s="196">
+      <c r="G26" s="197">
         <f>G21-G22+G23-G24-G25</f>
         <v/>
       </c>
-      <c r="H26" s="196">
+      <c r="H26" s="197">
         <f>H21-H22+H23-H24-H25</f>
         <v/>
       </c>
-      <c r="I26" s="196">
+      <c r="I26" s="197">
         <f>I21-I22+I23-I24-I25</f>
         <v/>
       </c>
@@ -11578,7 +11983,7 @@
       <c r="M26" s="97" t="n"/>
       <c r="N26" s="97" t="n"/>
       <c r="O26" s="97" t="n"/>
-      <c r="Q26" s="183" t="inlineStr">
+      <c r="Q26" s="184" t="inlineStr">
         <is>
           <t>TV_gordon = FCFF_n×(1+g)/(WACC−g)   [CHECK]</t>
         </is>
@@ -11592,7 +11997,7 @@
         </is>
       </c>
       <c r="C27" s="97" t="n"/>
-      <c r="D27" s="197">
+      <c r="D27" s="198">
         <f>-I35</f>
         <v/>
       </c>
@@ -11601,7 +12006,7 @@
       <c r="G27" s="97" t="n"/>
       <c r="H27" s="97" t="n"/>
       <c r="I27" s="97" t="n"/>
-      <c r="J27" s="188">
+      <c r="J27" s="189">
         <f>($I$21+$I$23)*$D$8</f>
         <v/>
       </c>
@@ -11610,20 +12015,20 @@
       <c r="M27" s="97" t="n"/>
       <c r="N27" s="97" t="n"/>
       <c r="O27" s="97" t="n"/>
-      <c r="Q27" s="177" t="inlineStr">
+      <c r="Q27" s="178" t="inlineStr">
         <is>
           <t>Excel</t>
         </is>
       </c>
-      <c r="R27" s="183">
+      <c r="R27" s="184">
         <f>IF(($D$6-$D$7)&lt;=0,"err",$I$26*(1+$D$7)/($D$6-$D$7))</f>
         <v/>
       </c>
-      <c r="T27" s="195">
+      <c r="T27" s="196">
         <f>M19</f>
         <v/>
       </c>
-      <c r="U27" s="179" t="inlineStr">
+      <c r="U27" s="180" t="inlineStr">
         <is>
           <t>Gordon g vs Damodaran long-run growth framing</t>
         </is>
@@ -11637,30 +12042,30 @@
         </is>
       </c>
       <c r="C28" s="97" t="n"/>
-      <c r="D28" s="196" t="n">
+      <c r="D28" s="197" t="n">
         <v>0</v>
       </c>
-      <c r="E28" s="198">
+      <c r="E28" s="199">
         <f>E27+E26</f>
         <v/>
       </c>
-      <c r="F28" s="198">
+      <c r="F28" s="199">
         <f>F27+F26</f>
         <v/>
       </c>
-      <c r="G28" s="198">
+      <c r="G28" s="199">
         <f>G27+G26</f>
         <v/>
       </c>
-      <c r="H28" s="198">
+      <c r="H28" s="199">
         <f>H27+H26</f>
         <v/>
       </c>
-      <c r="I28" s="198">
+      <c r="I28" s="199">
         <f>I27+I26</f>
         <v/>
       </c>
-      <c r="J28" s="198">
+      <c r="J28" s="199">
         <f>J27+J26</f>
         <v/>
       </c>
@@ -11669,16 +12074,16 @@
       <c r="M28" s="97" t="n"/>
       <c r="N28" s="97" t="n"/>
       <c r="O28" s="97" t="n"/>
-      <c r="Q28" s="177" t="inlineStr">
+      <c r="Q28" s="178" t="inlineStr">
         <is>
           <t>Implied Gordon exit multiple</t>
         </is>
       </c>
-      <c r="R28" s="199">
+      <c r="R28" s="200">
         <f>IF(($I$21+$I$23)=0,0,T27/($I$21+$I$23))</f>
         <v/>
       </c>
-      <c r="S28" s="177" t="inlineStr">
+      <c r="S28" s="178" t="inlineStr">
         <is>
           <t>Gordon TV / EBITDA_n</t>
         </is>
@@ -11692,31 +12097,31 @@
         </is>
       </c>
       <c r="C29" s="97" t="n"/>
-      <c r="D29" s="197">
+      <c r="D29" s="198">
         <f>D27+D26</f>
         <v/>
       </c>
-      <c r="E29" s="188">
+      <c r="E29" s="189">
         <f>E27+E26</f>
         <v/>
       </c>
-      <c r="F29" s="188">
+      <c r="F29" s="189">
         <f>F27+F26</f>
         <v/>
       </c>
-      <c r="G29" s="188">
+      <c r="G29" s="189">
         <f>G27+G26</f>
         <v/>
       </c>
-      <c r="H29" s="188">
+      <c r="H29" s="189">
         <f>H27+H26</f>
         <v/>
       </c>
-      <c r="I29" s="188">
+      <c r="I29" s="189">
         <f>I27+I26</f>
         <v/>
       </c>
-      <c r="J29" s="188">
+      <c r="J29" s="189">
         <f>J27</f>
         <v/>
       </c>
@@ -11772,7 +12177,7 @@
       <c r="M31" s="111" t="n"/>
       <c r="N31" s="111" t="n"/>
       <c r="O31" s="97" t="n"/>
-      <c r="Q31" s="183" t="inlineStr">
+      <c r="Q31" s="184" t="inlineStr">
         <is>
           <t>EV = XNPV(WACC, TransactionCF, mid-year dates)</t>
         </is>
@@ -11786,7 +12191,7 @@
         </is>
       </c>
       <c r="C32" s="97" t="n"/>
-      <c r="D32" s="188">
+      <c r="D32" s="189">
         <f>XNPV(D6,D28:J28,D18:J18)</f>
         <v/>
       </c>
@@ -11797,7 +12202,7 @@
         </is>
       </c>
       <c r="H32" s="97" t="n"/>
-      <c r="I32" s="197">
+      <c r="I32" s="198">
         <f>D12*D11</f>
         <v/>
       </c>
@@ -11813,16 +12218,16 @@
         <v/>
       </c>
       <c r="O32" s="97" t="n"/>
-      <c r="Q32" s="177" t="inlineStr">
+      <c r="Q32" s="178" t="inlineStr">
         <is>
           <t>Excel</t>
         </is>
       </c>
-      <c r="R32" s="183">
+      <c r="R32" s="184">
         <f>XNPV(D6,D28:J28,D18:J18)</f>
         <v/>
       </c>
-      <c r="T32" s="195">
+      <c r="T32" s="196">
         <f>D32</f>
         <v/>
       </c>
@@ -11835,7 +12240,7 @@
         </is>
       </c>
       <c r="C33" s="97" t="n"/>
-      <c r="D33" s="197">
+      <c r="D33" s="198">
         <f>+D14</f>
         <v/>
       </c>
@@ -11846,7 +12251,7 @@
         </is>
       </c>
       <c r="H33" s="97" t="n"/>
-      <c r="I33" s="197">
+      <c r="I33" s="198">
         <f>D13</f>
         <v/>
       </c>
@@ -11862,26 +12267,26 @@
         <v/>
       </c>
       <c r="O33" s="97" t="n"/>
-      <c r="Q33" s="183" t="inlineStr">
+      <c r="Q33" s="184" t="inlineStr">
         <is>
           <t>Equity = EV + Cash − Debt</t>
         </is>
       </c>
-      <c r="R33" s="195">
+      <c r="R33" s="196">
         <f>D35</f>
         <v/>
       </c>
-      <c r="S33" s="177" t="inlineStr">
+      <c r="S33" s="178" t="inlineStr">
         <is>
           <t>Net debt from 10-Q bridge</t>
         </is>
       </c>
-      <c r="U33" s="179" t="inlineStr">
+      <c r="U33" s="180" t="inlineStr">
         <is>
           <t>SEC 10-Q — cash, mkt secs, total debt</t>
         </is>
       </c>
-      <c r="V33" s="179" t="inlineStr">
+      <c r="V33" s="180" t="inlineStr">
         <is>
           <t>SEC 10-K — FY debt footnote</t>
         </is>
@@ -11895,7 +12300,7 @@
         </is>
       </c>
       <c r="C34" s="97" t="n"/>
-      <c r="D34" s="197">
+      <c r="D34" s="198">
         <f>+D13</f>
         <v/>
       </c>
@@ -11906,7 +12311,7 @@
         </is>
       </c>
       <c r="H34" s="97" t="n"/>
-      <c r="I34" s="197">
+      <c r="I34" s="198">
         <f>+D14</f>
         <v/>
       </c>
@@ -11915,26 +12320,26 @@
       <c r="M34" s="97" t="n"/>
       <c r="N34" s="97" t="n"/>
       <c r="O34" s="97" t="n"/>
-      <c r="Q34" s="183" t="inlineStr">
+      <c r="Q34" s="184" t="inlineStr">
         <is>
           <t>$/share = Equity / Shares</t>
         </is>
       </c>
-      <c r="R34" s="200">
+      <c r="R34" s="201">
         <f>D37</f>
         <v/>
       </c>
-      <c r="S34" s="177" t="inlineStr">
+      <c r="S34" s="178" t="inlineStr">
         <is>
           <t>Shares outstanding (Yahoo)</t>
         </is>
       </c>
-      <c r="U34" s="179" t="inlineStr">
+      <c r="U34" s="180" t="inlineStr">
         <is>
           <t>Yahoo Finance — shares outstanding</t>
         </is>
       </c>
-      <c r="V34" s="179" t="inlineStr">
+      <c r="V34" s="180" t="inlineStr">
         <is>
           <t>Yahoo FICO quote (price)</t>
         </is>
@@ -11948,7 +12353,7 @@
         </is>
       </c>
       <c r="C35" s="97" t="n"/>
-      <c r="D35" s="196">
+      <c r="D35" s="197">
         <f>D32+D33-D34</f>
         <v/>
       </c>
@@ -11959,7 +12364,7 @@
         </is>
       </c>
       <c r="H35" s="97" t="n"/>
-      <c r="I35" s="196">
+      <c r="I35" s="197">
         <f>I32+I33-I34</f>
         <v/>
       </c>
@@ -11972,16 +12377,16 @@
       <c r="M35" s="111" t="n"/>
       <c r="N35" s="111" t="n"/>
       <c r="O35" s="97" t="n"/>
-      <c r="Q35" s="177" t="inlineStr">
+      <c r="Q35" s="178" t="inlineStr">
         <is>
           <t>Upside vs market</t>
         </is>
       </c>
-      <c r="R35" s="201">
+      <c r="R35" s="202">
         <f>D37/D11-1</f>
         <v/>
       </c>
-      <c r="S35" s="177" t="inlineStr">
+      <c r="S35" s="178" t="inlineStr">
         <is>
           <t>Intrinsic / Current Price − 1</t>
         </is>
@@ -11995,7 +12400,7 @@
       <c r="E36" s="97" t="n"/>
       <c r="G36" s="97" t="n"/>
       <c r="H36" s="97" t="n"/>
-      <c r="I36" s="202" t="n"/>
+      <c r="I36" s="203" t="n"/>
       <c r="J36" s="97" t="n"/>
       <c r="L36" s="97" t="inlineStr">
         <is>
@@ -12003,7 +12408,7 @@
         </is>
       </c>
       <c r="M36" s="97" t="n"/>
-      <c r="N36" s="202">
+      <c r="N36" s="203">
         <f>I37</f>
         <v/>
       </c>
@@ -12017,7 +12422,7 @@
         </is>
       </c>
       <c r="C37" s="97" t="n"/>
-      <c r="D37" s="197">
+      <c r="D37" s="198">
         <f>D35/D12</f>
         <v/>
       </c>
@@ -12028,7 +12433,7 @@
         </is>
       </c>
       <c r="H37" s="97" t="n"/>
-      <c r="I37" s="197">
+      <c r="I37" s="198">
         <f>D11</f>
         <v/>
       </c>
@@ -12039,7 +12444,7 @@
         </is>
       </c>
       <c r="M37" s="97" t="n"/>
-      <c r="N37" s="202">
+      <c r="N37" s="203">
         <f>D37-I37</f>
         <v/>
       </c>
@@ -12066,22 +12471,22 @@
         </is>
       </c>
       <c r="M38" s="97" t="n"/>
-      <c r="N38" s="202">
+      <c r="N38" s="203">
         <f>SUM(N36:N37)</f>
         <v/>
       </c>
       <c r="O38" s="97" t="n"/>
-      <c r="Q38" s="183" t="inlineStr">
+      <c r="Q38" s="184" t="inlineStr">
         <is>
           <t>NWC = AR + Inventory − AP − DeferredRevenue</t>
         </is>
       </c>
-      <c r="U38" s="179" t="inlineStr">
+      <c r="U38" s="180" t="inlineStr">
         <is>
           <t>SEC 10-K — AR / AP / deferred revenue</t>
         </is>
       </c>
-      <c r="V38" s="179" t="inlineStr">
+      <c r="V38" s="180" t="inlineStr">
         <is>
           <t>XBRL DeferredRevenueCurrent</t>
         </is>
@@ -12100,17 +12505,17 @@
       <c r="M39" s="97" t="n"/>
       <c r="N39" s="97" t="n"/>
       <c r="O39" s="97" t="n"/>
-      <c r="Q39" s="183" t="inlineStr">
+      <c r="Q39" s="184" t="inlineStr">
         <is>
           <t>ΔNWC_t = NWC_t − NWC_(t−1)</t>
         </is>
       </c>
-      <c r="S39" s="177" t="inlineStr">
+      <c r="S39" s="178" t="inlineStr">
         <is>
           <t>Linked from 3-statement CF row 64</t>
         </is>
       </c>
-      <c r="T39" s="195">
+      <c r="T39" s="196">
         <f>I25</f>
         <v/>
       </c>
@@ -12175,14 +12580,14 @@
         </is>
       </c>
       <c r="O42" s="97" t="n"/>
-      <c r="Q42" s="179" t="inlineStr">
+      <c r="Q42" s="180" t="inlineStr">
         <is>
           <t>SEC 10-K FY2025</t>
         </is>
       </c>
-      <c r="R42" s="203" t="n"/>
-      <c r="S42" s="204" t="n"/>
-      <c r="T42" s="177" t="inlineStr">
+      <c r="R42" s="204" t="n"/>
+      <c r="S42" s="205" t="n"/>
+      <c r="T42" s="178" t="inlineStr">
         <is>
           <t>Tax 18.8%, IS/BS/CF, senior notes</t>
         </is>
@@ -12203,14 +12608,14 @@
       <c r="H43" s="97" t="n"/>
       <c r="N43" s="69" t="n"/>
       <c r="O43" s="97" t="n"/>
-      <c r="Q43" s="179" t="inlineStr">
+      <c r="Q43" s="180" t="inlineStr">
         <is>
           <t>SEC 10-Q Q3 FY2026</t>
         </is>
       </c>
-      <c r="R43" s="203" t="n"/>
-      <c r="S43" s="204" t="n"/>
-      <c r="T43" s="177" t="inlineStr">
+      <c r="R43" s="204" t="n"/>
+      <c r="S43" s="205" t="n"/>
+      <c r="T43" s="178" t="inlineStr">
         <is>
           <t>Debt $5,582M, cash+mkt secs net-debt bridge</t>
         </is>
@@ -12231,14 +12636,14 @@
       <c r="H44" s="97" t="n"/>
       <c r="N44" s="69" t="n"/>
       <c r="O44" s="97" t="n"/>
-      <c r="Q44" s="179" t="inlineStr">
+      <c r="Q44" s="180" t="inlineStr">
         <is>
           <t>SEC 8-K 6.250% notes</t>
         </is>
       </c>
-      <c r="R44" s="203" t="n"/>
-      <c r="S44" s="204" t="n"/>
-      <c r="T44" s="177" t="inlineStr">
+      <c r="R44" s="204" t="n"/>
+      <c r="S44" s="205" t="n"/>
+      <c r="T44" s="178" t="inlineStr">
         <is>
           <t>Pre-tax Rd coupon 6.250% due 2034</t>
         </is>
@@ -12259,14 +12664,14 @@
       <c r="H45" s="97" t="n"/>
       <c r="N45" s="69" t="n"/>
       <c r="O45" s="97" t="n"/>
-      <c r="Q45" s="179" t="inlineStr">
+      <c r="Q45" s="180" t="inlineStr">
         <is>
           <t>SEC EX-99.1 pricing</t>
         </is>
       </c>
-      <c r="R45" s="203" t="n"/>
-      <c r="S45" s="204" t="n"/>
-      <c r="T45" s="177" t="inlineStr">
+      <c r="R45" s="204" t="n"/>
+      <c r="S45" s="205" t="n"/>
+      <c r="T45" s="178" t="inlineStr">
         <is>
           <t>Notes priced at par / offering terms</t>
         </is>
@@ -12287,14 +12692,14 @@
       <c r="H46" s="97" t="n"/>
       <c r="N46" s="69" t="n"/>
       <c r="O46" s="97" t="n"/>
-      <c r="Q46" s="179" t="inlineStr">
+      <c r="Q46" s="180" t="inlineStr">
         <is>
           <t>SEC companyfacts XBRL</t>
         </is>
       </c>
-      <c r="R46" s="203" t="n"/>
-      <c r="S46" s="204" t="n"/>
-      <c r="T46" s="177" t="inlineStr">
+      <c r="R46" s="204" t="n"/>
+      <c r="S46" s="205" t="n"/>
+      <c r="T46" s="178" t="inlineStr">
         <is>
           <t>Pipeline data source (CIK 0000814547)</t>
         </is>
@@ -12311,14 +12716,14 @@
       <c r="H47" s="97" t="n"/>
       <c r="N47" s="69" t="n"/>
       <c r="O47" s="97" t="n"/>
-      <c r="Q47" s="179" t="inlineStr">
+      <c r="Q47" s="180" t="inlineStr">
         <is>
           <t>FRED DGS10</t>
         </is>
       </c>
-      <c r="R47" s="203" t="n"/>
-      <c r="S47" s="204" t="n"/>
-      <c r="T47" s="177" t="inlineStr">
+      <c r="R47" s="204" t="n"/>
+      <c r="S47" s="205" t="n"/>
+      <c r="T47" s="178" t="inlineStr">
         <is>
           <t>Risk-free rate (US 10Y)</t>
         </is>
@@ -12339,14 +12744,14 @@
         </is>
       </c>
       <c r="O48" s="97" t="n"/>
-      <c r="Q48" s="179" t="inlineStr">
+      <c r="Q48" s="180" t="inlineStr">
         <is>
           <t>US Treasury yield curve</t>
         </is>
       </c>
-      <c r="R48" s="203" t="n"/>
-      <c r="S48" s="204" t="n"/>
-      <c r="T48" s="177" t="inlineStr">
+      <c r="R48" s="204" t="n"/>
+      <c r="S48" s="205" t="n"/>
+      <c r="T48" s="178" t="inlineStr">
         <is>
           <t>Official daily par yields</t>
         </is>
@@ -12367,14 +12772,14 @@
         </is>
       </c>
       <c r="O49" s="97" t="n"/>
-      <c r="Q49" s="179" t="inlineStr">
+      <c r="Q49" s="180" t="inlineStr">
         <is>
           <t>Damodaran Implied ERP</t>
         </is>
       </c>
-      <c r="R49" s="203" t="n"/>
-      <c r="S49" s="204" t="n"/>
-      <c r="T49" s="177" t="inlineStr">
+      <c r="R49" s="204" t="n"/>
+      <c r="S49" s="205" t="n"/>
+      <c r="T49" s="178" t="inlineStr">
         <is>
           <t>Equity risk premium</t>
         </is>
@@ -12390,14 +12795,14 @@
       <c r="G50" s="97" t="n"/>
       <c r="H50" s="97" t="n"/>
       <c r="O50" s="97" t="n"/>
-      <c r="Q50" s="179" t="inlineStr">
+      <c r="Q50" s="180" t="inlineStr">
         <is>
           <t>Damodaran histimpl</t>
         </is>
       </c>
-      <c r="R50" s="203" t="n"/>
-      <c r="S50" s="204" t="n"/>
-      <c r="T50" s="177" t="inlineStr">
+      <c r="R50" s="204" t="n"/>
+      <c r="S50" s="205" t="n"/>
+      <c r="T50" s="178" t="inlineStr">
         <is>
           <t>Historical implied ERP table</t>
         </is>
@@ -12414,14 +12819,14 @@
       <c r="H51" s="97" t="n"/>
       <c r="M51" s="97" t="n"/>
       <c r="O51" s="97" t="n"/>
-      <c r="Q51" s="179" t="inlineStr">
+      <c r="Q51" s="180" t="inlineStr">
         <is>
           <t>Yahoo FICO stats</t>
         </is>
       </c>
-      <c r="R51" s="203" t="n"/>
-      <c r="S51" s="204" t="n"/>
-      <c r="T51" s="177" t="inlineStr">
+      <c r="R51" s="204" t="n"/>
+      <c r="S51" s="205" t="n"/>
+      <c r="T51" s="178" t="inlineStr">
         <is>
           <t>Beta 5Y monthly + shares out</t>
         </is>

--- a/FICO/output/FICO_Completed_Model.xlsx
+++ b/FICO/output/FICO_Completed_Model.xlsx
@@ -100,7 +100,7 @@
     <numFmt numFmtId="178" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="179" formatCode="0.0"/>
   </numFmts>
-  <fonts count="56">
+  <fonts count="60">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -447,8 +447,30 @@
       <color rgb="00666666"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="000563C1"/>
+      <sz val="10"/>
+      <u val="single"/>
+    </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -513,6 +535,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00833C0C"/>
       </patternFill>
     </fill>
   </fills>
@@ -634,7 +661,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="206">
+  <cellXfs count="215">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="1"/>
@@ -847,6 +874,27 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="7"/>
+    <xf numFmtId="0" fontId="56" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="7"/>
+    <xf numFmtId="0" fontId="57" fillId="13" borderId="5" pivotButton="0" quotePrefix="0" xfId="7"/>
+    <xf numFmtId="0" fontId="58" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="7">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="7">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="7">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="7">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="40" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="1" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
@@ -1757,7 +1805,7 @@
 <file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
-    <author>vengeanceaiUSCMODEL4</author>
+    <author>vengeanceaiUSCMODEL5</author>
   </authors>
   <commentList>
     <comment ref="B2" authorId="0" shapeId="0">
@@ -5082,7 +5130,7 @@
 <file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
-    <author>vengeanceaiUSCMODEL4</author>
+    <author>vengeanceaiUSCMODEL5</author>
   </authors>
   <commentList>
     <comment ref="D6" authorId="0" shapeId="0">
@@ -5793,12 +5841,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B3:O29"/>
+  <dimension ref="B3:O39"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.109375" defaultRowHeight="13.8"/>
   <cols>
     <col width="11" customWidth="1" style="73" min="1" max="2"/>
     <col width="29.109375" customWidth="1" style="73" min="3" max="3"/>
     <col width="11" customWidth="1" style="73" min="4" max="22"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="7" max="7"/>
     <col width="9.109375" customWidth="1" style="73" min="23" max="25"/>
     <col width="9.109375" customWidth="1" style="73" min="26" max="26"/>
     <col width="9.109375" customWidth="1" style="73" min="27" max="16384"/>
@@ -5954,7 +6005,7 @@
       <c r="B12" s="74" t="n"/>
       <c r="C12" s="75" t="inlineStr">
         <is>
-          <t>FICO — vengeanceaiUSCMODEL4 (3-Statement + DCF)</t>
+          <t>FICO — vengeanceaiUSCMODEL5 (3-Statement + DCF)</t>
         </is>
       </c>
       <c r="D12" s="74" t="n"/>
@@ -6122,7 +6173,7 @@
       <c r="B21" s="85" t="n"/>
       <c r="C21" s="85" t="inlineStr">
         <is>
-          <t>vengeanceaiUSCMODEL4: forecast drivers are Excel equations off FY25 (COGS%=I25/I24, SGA/RD/CapEx=Rev×hist%, days=ROUND(I…)). Growth path + CAPM WACC=9.24% + Exit 25x are the only forward policy inputs. Open in Excel to recalculate. DCF live CAPM + sources in columns Q–V.</t>
+          <t>vengeanceaiUSCMODEL5: same hist-linked Excel drivers as MODEL4, plus every Source is a clickable URL (3-statement U/V, DCF U/V, Cover source index). WACC=9.24%, Exit 25x. Open in Excel to recalculate. Click Cover Source Index (cols E–G) or 3S/DCF col U/V for filings.</t>
         </is>
       </c>
       <c r="D21" s="85" t="n"/>
@@ -6182,9 +6233,11 @@
         </is>
       </c>
       <c r="D24" s="89" t="n"/>
-      <c r="E24" s="89" t="n"/>
-      <c r="F24" s="89" t="n"/>
-      <c r="G24" s="89" t="n"/>
+      <c r="E24" s="133" t="inlineStr">
+        <is>
+          <t>vengeanceaiUSCMODEL5 — SOURCE INDEX (click any link)</t>
+        </is>
+      </c>
       <c r="H24" s="89" t="n"/>
       <c r="I24" s="89" t="n"/>
       <c r="J24" s="89" t="n"/>
@@ -6202,9 +6255,11 @@
         </is>
       </c>
       <c r="D25" s="91" t="n"/>
-      <c r="E25" s="91" t="n"/>
-      <c r="F25" s="91" t="n"/>
-      <c r="G25" s="91" t="n"/>
+      <c r="E25" s="134" t="inlineStr">
+        <is>
+          <t>Every assumption / WACC / filing source used in this workbook. Same links appear on 3-statement col U/V and DCF col U/V.</t>
+        </is>
+      </c>
       <c r="H25" s="91" t="n"/>
       <c r="I25" s="91" t="n"/>
       <c r="J25" s="91" t="n"/>
@@ -6222,9 +6277,21 @@
         </is>
       </c>
       <c r="D26" s="91" t="n"/>
-      <c r="E26" s="91" t="n"/>
-      <c r="F26" s="91" t="n"/>
-      <c r="G26" s="91" t="n"/>
+      <c r="E26" s="135" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="F26" s="135" t="inlineStr">
+        <is>
+          <t>Clickable link</t>
+        </is>
+      </c>
+      <c r="G26" s="135" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
       <c r="H26" s="91" t="n"/>
       <c r="I26" s="91" t="n"/>
       <c r="J26" s="91" t="n"/>
@@ -6242,9 +6309,21 @@
         </is>
       </c>
       <c r="D27" s="91" t="n"/>
-      <c r="E27" s="91" t="n"/>
-      <c r="F27" s="91" t="n"/>
-      <c r="G27" s="91" t="n"/>
+      <c r="E27" s="136" t="inlineStr">
+        <is>
+          <t>10-K FY2025</t>
+        </is>
+      </c>
+      <c r="F27" s="137" t="inlineStr">
+        <is>
+          <t>10-K FY2025</t>
+        </is>
+      </c>
+      <c r="G27" s="137" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
+        </is>
+      </c>
       <c r="H27" s="91" t="n"/>
       <c r="I27" s="91" t="n"/>
       <c r="J27" s="91" t="n"/>
@@ -6258,9 +6337,21 @@
       <c r="B28" s="90" t="n"/>
       <c r="C28" s="91" t="n"/>
       <c r="D28" s="91" t="n"/>
-      <c r="E28" s="91" t="n"/>
-      <c r="F28" s="91" t="n"/>
-      <c r="G28" s="91" t="n"/>
+      <c r="E28" s="136" t="inlineStr">
+        <is>
+          <t>10-Q Q3 FY2026</t>
+        </is>
+      </c>
+      <c r="F28" s="137" t="inlineStr">
+        <is>
+          <t>10-Q Q3 FY2026</t>
+        </is>
+      </c>
+      <c r="G28" s="137" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454726000030/fico-20260630.htm</t>
+        </is>
+      </c>
       <c r="H28" s="91" t="n"/>
       <c r="I28" s="91" t="n"/>
       <c r="J28" s="91" t="n"/>
@@ -6274,9 +6365,21 @@
       <c r="B29" s="90" t="n"/>
       <c r="C29" s="90" t="n"/>
       <c r="D29" s="90" t="n"/>
-      <c r="E29" s="90" t="n"/>
-      <c r="F29" s="90" t="n"/>
-      <c r="G29" s="90" t="n"/>
+      <c r="E29" s="138" t="inlineStr">
+        <is>
+          <t>8-K 6.250% notes</t>
+        </is>
+      </c>
+      <c r="F29" s="139" t="inlineStr">
+        <is>
+          <t>8-K 6.250% notes</t>
+        </is>
+      </c>
+      <c r="G29" s="139" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/814547/000119312526117936/d56220d8k.htm</t>
+        </is>
+      </c>
       <c r="H29" s="90" t="n"/>
       <c r="I29" s="90" t="n"/>
       <c r="J29" s="90" t="n"/>
@@ -6286,16 +6389,176 @@
       <c r="N29" s="90" t="n"/>
       <c r="O29" s="90" t="n"/>
     </row>
-    <row r="30" ht="19.5" customHeight="1"/>
-    <row r="31" ht="19.5" customHeight="1"/>
-    <row r="32" ht="19.5" customHeight="1"/>
-    <row r="33" ht="19.5" customHeight="1"/>
-    <row r="34" ht="19.5" customHeight="1"/>
-    <row r="35" ht="19.5" customHeight="1"/>
-    <row r="36" ht="19.5" customHeight="1"/>
-    <row r="37" ht="19.5" customHeight="1"/>
-    <row r="38" ht="19.5" customHeight="1"/>
-    <row r="39" ht="19.5" customHeight="1"/>
+    <row r="30" ht="19.5" customHeight="1">
+      <c r="E30" s="140" t="inlineStr">
+        <is>
+          <t>Damodaran ERP</t>
+        </is>
+      </c>
+      <c r="F30" s="141" t="inlineStr">
+        <is>
+          <t>Damodaran ERP</t>
+        </is>
+      </c>
+      <c r="G30" s="141" t="inlineStr">
+        <is>
+          <t>https://pages.stern.nyu.edu/adamodar/New_Home_Page/home.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="19.5" customHeight="1">
+      <c r="E31" s="140" t="inlineStr">
+        <is>
+          <t>Damodaran FCFF</t>
+        </is>
+      </c>
+      <c r="F31" s="141" t="inlineStr">
+        <is>
+          <t>Damodaran FCFF</t>
+        </is>
+      </c>
+      <c r="G31" s="141" t="inlineStr">
+        <is>
+          <t>https://pages.stern.nyu.edu/~adamodar/New_Home_Page/datafile/histfcff.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="19.5" customHeight="1">
+      <c r="E32" s="140" t="inlineStr">
+        <is>
+          <t>Damodaran implied ERP table</t>
+        </is>
+      </c>
+      <c r="F32" s="141" t="inlineStr">
+        <is>
+          <t>Damodaran implied ERP table</t>
+        </is>
+      </c>
+      <c r="G32" s="141" t="inlineStr">
+        <is>
+          <t>https://pages.stern.nyu.edu/~adamodar/New_Home_Page/datafile/histimpl.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="19.5" customHeight="1">
+      <c r="E33" s="140" t="inlineStr">
+        <is>
+          <t>FICO IR</t>
+        </is>
+      </c>
+      <c r="F33" s="141" t="inlineStr">
+        <is>
+          <t>FICO IR</t>
+        </is>
+      </c>
+      <c r="G33" s="141" t="inlineStr">
+        <is>
+          <t>https://www.fico.com/en/investors</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="19.5" customHeight="1">
+      <c r="E34" s="140" t="inlineStr">
+        <is>
+          <t>FRED DGS10</t>
+        </is>
+      </c>
+      <c r="F34" s="141" t="inlineStr">
+        <is>
+          <t>FRED DGS10</t>
+        </is>
+      </c>
+      <c r="G34" s="141" t="inlineStr">
+        <is>
+          <t>https://fred.stlouisfed.org/series/DGS10</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="19.5" customHeight="1">
+      <c r="E35" s="140" t="inlineStr">
+        <is>
+          <t>FY2026 guidance EX-99.1</t>
+        </is>
+      </c>
+      <c r="F35" s="141" t="inlineStr">
+        <is>
+          <t>FY2026 guidance EX-99.1</t>
+        </is>
+      </c>
+      <c r="G35" s="141" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454726000031/exhibit991erq32026.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="19.5" customHeight="1">
+      <c r="E36" s="140" t="inlineStr">
+        <is>
+          <t>US Treasury yield curve</t>
+        </is>
+      </c>
+      <c r="F36" s="141" t="inlineStr">
+        <is>
+          <t>US Treasury yield curve</t>
+        </is>
+      </c>
+      <c r="G36" s="141" t="inlineStr">
+        <is>
+          <t>https://home.treasury.gov/resource-center/data-chart-center/interest-rates/TextView?type=daily_treasury_yield_curve</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="19.5" customHeight="1">
+      <c r="E37" s="140" t="inlineStr">
+        <is>
+          <t>Yahoo FICO</t>
+        </is>
+      </c>
+      <c r="F37" s="141" t="inlineStr">
+        <is>
+          <t>Yahoo FICO</t>
+        </is>
+      </c>
+      <c r="G37" s="141" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/quote/FICO/key-statistics/</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="19.5" customHeight="1">
+      <c r="E38" s="140" t="inlineStr">
+        <is>
+          <t>Yahoo FICO quote</t>
+        </is>
+      </c>
+      <c r="F38" s="141" t="inlineStr">
+        <is>
+          <t>Yahoo FICO quote</t>
+        </is>
+      </c>
+      <c r="G38" s="141" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/quote/FICO/</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="19.5" customHeight="1">
+      <c r="E39" s="140" t="inlineStr">
+        <is>
+          <t>companyfacts</t>
+        </is>
+      </c>
+      <c r="F39" s="141" t="inlineStr">
+        <is>
+          <t>companyfacts</t>
+        </is>
+      </c>
+      <c r="G39" s="141" t="inlineStr">
+        <is>
+          <t>https://data.sec.gov/api/xbrl/companyfacts/CIK0000814547.json</t>
+        </is>
+      </c>
+    </row>
     <row r="40" ht="19.5" customHeight="1"/>
     <row r="41" ht="19.5" customHeight="1"/>
     <row r="42" ht="19.5" customHeight="1"/>
@@ -6304,13 +6567,43 @@
     <row r="45" ht="19.5" customHeight="1"/>
     <row r="46" ht="19.5" customHeight="1"/>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="E24:G24"/>
+    <mergeCell ref="E25:G25"/>
+  </mergeCells>
   <hyperlinks>
     <hyperlink ref="C15" location="'3 Statement Model'!A1" display="3 Statement Model"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F27" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F28" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F29" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F30" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F31" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F32" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F33" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F34" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G34" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F35" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F36" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G36" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F37" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F38" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G38" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F39" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G39" r:id="rId27"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" scale="64"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId28"/>
 </worksheet>
 </file>
 
@@ -6384,42 +6677,42 @@
       </c>
       <c r="C2" s="62" t="n"/>
       <c r="D2" s="63" t="n"/>
-      <c r="E2" s="133" t="n">
+      <c r="E2" s="142" t="n">
         <v>2021</v>
       </c>
-      <c r="F2" s="134">
+      <c r="F2" s="143">
         <f>+E2+1</f>
         <v/>
       </c>
-      <c r="G2" s="134">
+      <c r="G2" s="143">
         <f>+F2+1</f>
         <v/>
       </c>
-      <c r="H2" s="134">
+      <c r="H2" s="143">
         <f>+G2+1</f>
         <v/>
       </c>
-      <c r="I2" s="134">
+      <c r="I2" s="143">
         <f>+H2+1</f>
         <v/>
       </c>
-      <c r="J2" s="135">
+      <c r="J2" s="144">
         <f>+I2+1</f>
         <v/>
       </c>
-      <c r="K2" s="135">
+      <c r="K2" s="144">
         <f>+J2+1</f>
         <v/>
       </c>
-      <c r="L2" s="135">
+      <c r="L2" s="144">
         <f>+K2+1</f>
         <v/>
       </c>
-      <c r="M2" s="135">
+      <c r="M2" s="144">
         <f>+L2+1</f>
         <v/>
       </c>
-      <c r="N2" s="135">
+      <c r="N2" s="144">
         <f>+M2+1</f>
         <v/>
       </c>
@@ -6430,54 +6723,54 @@
           <t>Balance Sheet Check</t>
         </is>
       </c>
-      <c r="E3" s="136">
+      <c r="E3" s="145">
         <f>IFERROR(IF(ABS(E57)&gt;1,"ERROR","OK"),"OK")</f>
         <v/>
       </c>
-      <c r="F3" s="136">
+      <c r="F3" s="145">
         <f>IFERROR(IF(ABS(F57)&gt;1,"ERROR","OK"),"OK")</f>
         <v/>
       </c>
-      <c r="G3" s="136">
+      <c r="G3" s="145">
         <f>IFERROR(IF(ABS(G57)&gt;1,"ERROR","OK"),"OK")</f>
         <v/>
       </c>
-      <c r="H3" s="136">
+      <c r="H3" s="145">
         <f>IFERROR(IF(ABS(H57)&gt;1,"ERROR","OK"),"OK")</f>
         <v/>
       </c>
-      <c r="I3" s="136">
+      <c r="I3" s="145">
         <f>IFERROR(IF(ABS(I57)&gt;1,"ERROR","OK"),"OK")</f>
         <v/>
       </c>
-      <c r="J3" s="136">
+      <c r="J3" s="145">
         <f>IFERROR(IF(ABS(J57)&gt;1,"ERROR","OK"),"OK")</f>
         <v/>
       </c>
-      <c r="K3" s="136">
+      <c r="K3" s="145">
         <f>IFERROR(IF(ABS(K57)&gt;1,"ERROR","OK"),"OK")</f>
         <v/>
       </c>
-      <c r="L3" s="136">
+      <c r="L3" s="145">
         <f>IFERROR(IF(ABS(L57)&gt;1,"ERROR","OK"),"OK")</f>
         <v/>
       </c>
-      <c r="M3" s="136">
+      <c r="M3" s="145">
         <f>IFERROR(IF(ABS(M57)&gt;1,"ERROR","OK"),"OK")</f>
         <v/>
       </c>
-      <c r="N3" s="136">
+      <c r="N3" s="145">
         <f>IFERROR(IF(ABS(N57)&gt;1,"ERROR","OK"),"OK")</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="137" t="inlineStr">
-        <is>
-          <t>vengeanceaiUSCMODEL4: hover J–N for WHY+SOURCE; click blue Source link in col U (or LINK: URL in col C / V) to open the filing</t>
-        </is>
-      </c>
-      <c r="P4" s="138" t="inlineStr">
+      <c r="B4" s="146" t="inlineStr">
+        <is>
+          <t>vengeanceaiUSCMODEL5: hover J–N for WHY+SOURCE; click blue Source link in col U (or LINK: URL in col C / V) to open the filing</t>
+        </is>
+      </c>
+      <c r="P4" s="147" t="inlineStr">
         <is>
           <t>ASSUMPTIONS EXPLAINED — click blue Source (col U) for the filing/data</t>
         </is>
@@ -6501,7 +6794,7 @@
       <c r="L5" s="65" t="n"/>
       <c r="M5" s="65" t="n"/>
       <c r="N5" s="65" t="n"/>
-      <c r="P5" s="139" t="inlineStr">
+      <c r="P5" s="148" t="inlineStr">
         <is>
           <t>Yellow = policy. Green = FY25-linked equations. Col U = clickable hyperlink. Col V = full URL (also clickable).</t>
         </is>
@@ -6514,37 +6807,37 @@
         </is>
       </c>
       <c r="D6" s="47" t="n"/>
-      <c r="P6" s="140" t="inlineStr">
+      <c r="P6" s="149" t="inlineStr">
         <is>
           <t>Row</t>
         </is>
       </c>
-      <c r="Q6" s="140" t="inlineStr">
+      <c r="Q6" s="149" t="inlineStr">
         <is>
           <t>Assumption</t>
         </is>
       </c>
-      <c r="R6" s="140" t="inlineStr">
+      <c r="R6" s="149" t="inlineStr">
         <is>
           <t>What it is</t>
         </is>
       </c>
-      <c r="S6" s="140" t="inlineStr">
+      <c r="S6" s="149" t="inlineStr">
         <is>
           <t>How set in model</t>
         </is>
       </c>
-      <c r="T6" s="140" t="inlineStr">
+      <c r="T6" s="149" t="inlineStr">
         <is>
           <t>Why this choice</t>
         </is>
       </c>
-      <c r="U6" s="140" t="inlineStr">
+      <c r="U6" s="149" t="inlineStr">
         <is>
           <t>Source (click)</t>
         </is>
       </c>
-      <c r="V6" s="140" t="inlineStr">
+      <c r="V6" s="149" t="inlineStr">
         <is>
           <t>Source URL</t>
         </is>
@@ -6556,7 +6849,7 @@
           <t>Revenue Growth (% Change)</t>
         </is>
       </c>
-      <c r="C7" s="141" t="inlineStr">
+      <c r="C7" s="150" t="inlineStr">
         <is>
           <t>WHY: Y1 ≈ company FY2026 revenue guidance (~$2.53B / FY25 $1.991B − 1 ≈ 27%). Then fade toward terminal g=3% (not straight… | SOURCE: SEC EX-99.1 Q3 FY2026 — updated FY2026 revenue guidance $2.53B | LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454726000031/exhibit991erq32026.htm | HOW: Yellow POLICY input: 27% / 16% / 13% / 10% / 7%.</t>
         </is>
@@ -6579,50 +6872,50 @@
         <f>I24/H24-1</f>
         <v/>
       </c>
-      <c r="J7" s="142" t="n">
+      <c r="J7" s="151" t="n">
         <v>0.27</v>
       </c>
-      <c r="K7" s="142" t="n">
+      <c r="K7" s="151" t="n">
         <v>0.16</v>
       </c>
-      <c r="L7" s="142" t="n">
+      <c r="L7" s="151" t="n">
         <v>0.13</v>
       </c>
-      <c r="M7" s="142" t="n">
+      <c r="M7" s="151" t="n">
         <v>0.1</v>
       </c>
-      <c r="N7" s="142" t="n">
+      <c r="N7" s="151" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="P7" s="143" t="n">
+      <c r="P7" s="152" t="n">
         <v>7</v>
       </c>
-      <c r="Q7" s="143" t="inlineStr">
+      <c r="Q7" s="152" t="inlineStr">
         <is>
           <t>Revenue Growth</t>
         </is>
       </c>
-      <c r="R7" s="144" t="inlineStr">
+      <c r="R7" s="153" t="inlineStr">
         <is>
           <t>Year-over-year % increase in revenue for each forecast year.</t>
         </is>
       </c>
-      <c r="S7" s="144" t="inlineStr">
+      <c r="S7" s="153" t="inlineStr">
         <is>
           <t>Yellow POLICY input: 27% / 16% / 13% / 10% / 7%.</t>
         </is>
       </c>
-      <c r="T7" s="144" t="inlineStr">
+      <c r="T7" s="153" t="inlineStr">
         <is>
           <t>Y1 ≈ company FY2026 revenue guidance (~$2.53B / FY25 $1.991B − 1 ≈ 27%). Then fade toward terminal g=3% (not straight-lined). This is the main forward-looking judgment; it drives Rev → GP → EBT → Net Earnings → CF.</t>
         </is>
       </c>
-      <c r="U7" s="145" t="inlineStr">
+      <c r="U7" s="154" t="inlineStr">
         <is>
           <t>SEC EX-99.1 Q3 FY2026 — updated FY2026 revenue guidance $2.53B</t>
         </is>
       </c>
-      <c r="V7" s="145" t="inlineStr">
+      <c r="V7" s="154" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/814547/000081454726000031/exhibit991erq32026.htm</t>
         </is>
@@ -6634,7 +6927,7 @@
           <t>Cost of Goods Sold (% of Revenue)</t>
         </is>
       </c>
-      <c r="C8" s="141" t="inlineStr">
+      <c r="C8" s="150" t="inlineStr">
         <is>
           <t>WHY: Locks in latest reported cost structure (~17.8%). Scores mix is high-margin; holding FY25 is conservative vs further … | SOURCE: SEC 10-K FY2025 — Cost of revenues / Total revenues | LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm | HOW: Excel equation: I25/I24 (FY25 COGS ÷ FY25 Revenue) held flat.</t>
         </is>
@@ -6660,55 +6953,55 @@
         <f>I25/I24</f>
         <v/>
       </c>
-      <c r="J8" s="146">
+      <c r="J8" s="155">
         <f>$I$25/$I$24</f>
         <v/>
       </c>
-      <c r="K8" s="146">
+      <c r="K8" s="155">
         <f>$I$25/$I$24</f>
         <v/>
       </c>
-      <c r="L8" s="146">
+      <c r="L8" s="155">
         <f>$I$25/$I$24</f>
         <v/>
       </c>
-      <c r="M8" s="146">
+      <c r="M8" s="155">
         <f>$I$25/$I$24</f>
         <v/>
       </c>
-      <c r="N8" s="146">
+      <c r="N8" s="155">
         <f>$I$25/$I$24</f>
         <v/>
       </c>
-      <c r="P8" s="143" t="n">
+      <c r="P8" s="152" t="n">
         <v>8</v>
       </c>
-      <c r="Q8" s="143" t="inlineStr">
+      <c r="Q8" s="152" t="inlineStr">
         <is>
           <t>COGS % of Revenue</t>
         </is>
       </c>
-      <c r="R8" s="144" t="inlineStr">
+      <c r="R8" s="153" t="inlineStr">
         <is>
           <t>Cost of revenues as a % of sales (gross margin = 1 − this).</t>
         </is>
       </c>
-      <c r="S8" s="144" t="inlineStr">
+      <c r="S8" s="153" t="inlineStr">
         <is>
           <t>Excel equation: I25/I24 (FY25 COGS ÷ FY25 Revenue) held flat.</t>
         </is>
       </c>
-      <c r="T8" s="144" t="inlineStr">
+      <c r="T8" s="153" t="inlineStr">
         <is>
           <t>Locks in latest reported cost structure (~17.8%). Scores mix is high-margin; holding FY25 is conservative vs further mix shift.</t>
         </is>
       </c>
-      <c r="U8" s="145" t="inlineStr">
+      <c r="U8" s="154" t="inlineStr">
         <is>
           <t>SEC 10-K FY2025 — Cost of revenues / Total revenues</t>
         </is>
       </c>
-      <c r="V8" s="145" t="inlineStr">
+      <c r="V8" s="154" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
         </is>
@@ -6720,81 +7013,81 @@
           <t>SGA % of Revenue (equation)</t>
         </is>
       </c>
-      <c r="C9" s="141" t="inlineStr">
+      <c r="C9" s="150" t="inlineStr">
         <is>
           <t>WHY: Normalize one-time restructuring ($10.9M). Mild efficiency grind reflects operating leverage as revenue scales; floor… | SOURCE: SEC 10-K FY2025 — SG&amp;A + restructuring note | LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm | HOW: Equation: (I28 − 10,922)/I24 − 50bps × year. Strips FY25 restructuring; then −0.5% of sales each year.</t>
         </is>
       </c>
       <c r="D9" s="47" t="n"/>
-      <c r="E9" s="147">
+      <c r="E9" s="156">
         <f>E28</f>
         <v/>
       </c>
-      <c r="F9" s="147">
+      <c r="F9" s="156">
         <f>F28</f>
         <v/>
       </c>
-      <c r="G9" s="147">
+      <c r="G9" s="156">
         <f>G28</f>
         <v/>
       </c>
-      <c r="H9" s="147">
+      <c r="H9" s="156">
         <f>H28</f>
         <v/>
       </c>
-      <c r="I9" s="147">
+      <c r="I9" s="156">
         <f>I28</f>
         <v/>
       </c>
-      <c r="J9" s="148">
+      <c r="J9" s="157">
         <f>MAX(0.05,(($I$28-10922.0)/$I$24)-0.005)</f>
         <v/>
       </c>
-      <c r="K9" s="148">
+      <c r="K9" s="157">
         <f>MAX(0.05,(($I$28-10922.0)/$I$24)-0.01)</f>
         <v/>
       </c>
-      <c r="L9" s="148">
+      <c r="L9" s="157">
         <f>MAX(0.05,(($I$28-10922.0)/$I$24)-0.015)</f>
         <v/>
       </c>
-      <c r="M9" s="148">
+      <c r="M9" s="157">
         <f>MAX(0.05,(($I$28-10922.0)/$I$24)-0.02)</f>
         <v/>
       </c>
-      <c r="N9" s="148">
+      <c r="N9" s="157">
         <f>MAX(0.05,(($I$28-10922.0)/$I$24)-0.025)</f>
         <v/>
       </c>
-      <c r="P9" s="143" t="n">
+      <c r="P9" s="152" t="n">
         <v>9</v>
       </c>
-      <c r="Q9" s="143" t="inlineStr">
+      <c r="Q9" s="152" t="inlineStr">
         <is>
           <t>SGA % of Revenue</t>
         </is>
       </c>
-      <c r="R9" s="144" t="inlineStr">
+      <c r="R9" s="153" t="inlineStr">
         <is>
           <t>Operating opex (Salaries &amp; Benefits / SG&amp;A) as % of sales.</t>
         </is>
       </c>
-      <c r="S9" s="144" t="inlineStr">
+      <c r="S9" s="153" t="inlineStr">
         <is>
           <t>Equation: (I28 − 10,922)/I24 − 50bps × year. Strips FY25 restructuring; then −0.5% of sales each year.</t>
         </is>
       </c>
-      <c r="T9" s="144" t="inlineStr">
+      <c r="T9" s="153" t="inlineStr">
         <is>
           <t>Normalize one-time restructuring ($10.9M). Mild efficiency grind reflects operating leverage as revenue scales; floored at 5%.</t>
         </is>
       </c>
-      <c r="U9" s="145" t="inlineStr">
+      <c r="U9" s="154" t="inlineStr">
         <is>
           <t>SEC 10-K FY2025 — SG&amp;A + restructuring note</t>
         </is>
       </c>
-      <c r="V9" s="145" t="inlineStr">
+      <c r="V9" s="154" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
         </is>
@@ -6806,81 +7099,81 @@
           <t>R&amp;D % of Revenue (equation)</t>
         </is>
       </c>
-      <c r="C10" s="141" t="inlineStr">
+      <c r="C10" s="150" t="inlineStr">
         <is>
           <t>WHY: FICO reinvests steadily in analytics/software. Flat % grows dollars with revenue. | SOURCE: SEC 10-K FY2025 — Research and development | LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm | HOW: Excel equation: I29/I24 held flat (~9.46%).</t>
         </is>
       </c>
       <c r="D10" s="47" t="n"/>
-      <c r="E10" s="147">
+      <c r="E10" s="156">
         <f>E29</f>
         <v/>
       </c>
-      <c r="F10" s="147">
+      <c r="F10" s="156">
         <f>F29</f>
         <v/>
       </c>
-      <c r="G10" s="147">
+      <c r="G10" s="156">
         <f>G29</f>
         <v/>
       </c>
-      <c r="H10" s="147">
+      <c r="H10" s="156">
         <f>H29</f>
         <v/>
       </c>
-      <c r="I10" s="147">
+      <c r="I10" s="156">
         <f>I29</f>
         <v/>
       </c>
-      <c r="J10" s="148">
+      <c r="J10" s="157">
         <f>$I$29/$I$24</f>
         <v/>
       </c>
-      <c r="K10" s="148">
+      <c r="K10" s="157">
         <f>$I$29/$I$24</f>
         <v/>
       </c>
-      <c r="L10" s="148">
+      <c r="L10" s="157">
         <f>$I$29/$I$24</f>
         <v/>
       </c>
-      <c r="M10" s="148">
+      <c r="M10" s="157">
         <f>$I$29/$I$24</f>
         <v/>
       </c>
-      <c r="N10" s="148">
+      <c r="N10" s="157">
         <f>$I$29/$I$24</f>
         <v/>
       </c>
-      <c r="P10" s="143" t="n">
+      <c r="P10" s="152" t="n">
         <v>10</v>
       </c>
-      <c r="Q10" s="143" t="inlineStr">
+      <c r="Q10" s="152" t="inlineStr">
         <is>
           <t>R&amp;D % of Revenue</t>
         </is>
       </c>
-      <c r="R10" s="144" t="inlineStr">
+      <c r="R10" s="153" t="inlineStr">
         <is>
           <t>Research &amp; development (template label may say Rent and Overhead) as % of sales.</t>
         </is>
       </c>
-      <c r="S10" s="144" t="inlineStr">
+      <c r="S10" s="153" t="inlineStr">
         <is>
           <t>Excel equation: I29/I24 held flat (~9.46%).</t>
         </is>
       </c>
-      <c r="T10" s="144" t="inlineStr">
+      <c r="T10" s="153" t="inlineStr">
         <is>
           <t>FICO reinvests steadily in analytics/software. Flat % grows dollars with revenue.</t>
         </is>
       </c>
-      <c r="U10" s="145" t="inlineStr">
+      <c r="U10" s="154" t="inlineStr">
         <is>
           <t>SEC 10-K FY2025 — Research and development</t>
         </is>
       </c>
-      <c r="V10" s="145" t="inlineStr">
+      <c r="V10" s="154" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
         </is>
@@ -6892,7 +7185,7 @@
           <t>Depreciation &amp; Amortization (% of PP&amp;E Open Bal)</t>
         </is>
       </c>
-      <c r="C11" s="141" t="inlineStr">
+      <c r="C11" s="150" t="inlineStr">
         <is>
           <t>WHY: Ties DA to the asset base the schedule rolls forward (opens at I44). | SOURCE: SEC 10-K FY2025 — D&amp;A and PP&amp;E | LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm | HOW: Excel equation: I30/I44 (FY25 DA ÷ FY25 PPE). Forecast DA = OpenPPE × this %.</t>
         </is>
@@ -6918,55 +7211,55 @@
         <f>I30/I92</f>
         <v/>
       </c>
-      <c r="J11" s="146">
+      <c r="J11" s="155">
         <f>IF($I$44=0,0.25,$I$30/$I$44)</f>
         <v/>
       </c>
-      <c r="K11" s="146">
+      <c r="K11" s="155">
         <f>IF($I$44=0,0.25,$I$30/$I$44)</f>
         <v/>
       </c>
-      <c r="L11" s="146">
+      <c r="L11" s="155">
         <f>IF($I$44=0,0.25,$I$30/$I$44)</f>
         <v/>
       </c>
-      <c r="M11" s="146">
+      <c r="M11" s="155">
         <f>IF($I$44=0,0.25,$I$30/$I$44)</f>
         <v/>
       </c>
-      <c r="N11" s="146">
+      <c r="N11" s="155">
         <f>IF($I$44=0,0.25,$I$30/$I$44)</f>
         <v/>
       </c>
-      <c r="P11" s="143" t="n">
+      <c r="P11" s="152" t="n">
         <v>11</v>
       </c>
-      <c r="Q11" s="143" t="inlineStr">
+      <c r="Q11" s="152" t="inlineStr">
         <is>
           <t>D&amp;A % of PP&amp;E Open</t>
         </is>
       </c>
-      <c r="R11" s="144" t="inlineStr">
+      <c r="R11" s="153" t="inlineStr">
         <is>
           <t>Depreciation &amp; amortization as % of opening net PP&amp;E.</t>
         </is>
       </c>
-      <c r="S11" s="144" t="inlineStr">
+      <c r="S11" s="153" t="inlineStr">
         <is>
           <t>Excel equation: I30/I44 (FY25 DA ÷ FY25 PPE). Forecast DA = OpenPPE × this %.</t>
         </is>
       </c>
-      <c r="T11" s="144" t="inlineStr">
+      <c r="T11" s="153" t="inlineStr">
         <is>
           <t>Ties DA to the asset base the schedule rolls forward (opens at I44).</t>
         </is>
       </c>
-      <c r="U11" s="145" t="inlineStr">
+      <c r="U11" s="154" t="inlineStr">
         <is>
           <t>SEC 10-K FY2025 — D&amp;A and PP&amp;E</t>
         </is>
       </c>
-      <c r="V11" s="145" t="inlineStr">
+      <c r="V11" s="154" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
         </is>
@@ -6978,7 +7271,7 @@
           <t>Interest (% of Debt Open Bal)</t>
         </is>
       </c>
-      <c r="C12" s="141" t="inlineStr">
+      <c r="C12" s="150" t="inlineStr">
         <is>
           <t>WHY: Approximates average coupon / cost of debt on the book. Debt held flat (issuance = 0), so interest stays linked to th… | SOURCE: SEC 10-K FY2025 — Interest expense; see also 8-K 6.250% notes | LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm | HOW: Excel equation: I101/I98 (FY25 interest ÷ FY25 opening debt in schedule).</t>
         </is>
@@ -7004,55 +7297,55 @@
         <f>I101/I98</f>
         <v/>
       </c>
-      <c r="J12" s="146">
+      <c r="J12" s="155">
         <f>IF($I$98=0,0.05,$I$101/$I$98)</f>
         <v/>
       </c>
-      <c r="K12" s="146">
+      <c r="K12" s="155">
         <f>IF($I$98=0,0.05,$I$101/$I$98)</f>
         <v/>
       </c>
-      <c r="L12" s="146">
+      <c r="L12" s="155">
         <f>IF($I$98=0,0.05,$I$101/$I$98)</f>
         <v/>
       </c>
-      <c r="M12" s="146">
+      <c r="M12" s="155">
         <f>IF($I$98=0,0.05,$I$101/$I$98)</f>
         <v/>
       </c>
-      <c r="N12" s="146">
+      <c r="N12" s="155">
         <f>IF($I$98=0,0.05,$I$101/$I$98)</f>
         <v/>
       </c>
-      <c r="P12" s="143" t="n">
+      <c r="P12" s="152" t="n">
         <v>12</v>
       </c>
-      <c r="Q12" s="143" t="inlineStr">
+      <c r="Q12" s="152" t="inlineStr">
         <is>
           <t>Interest % of Debt Open</t>
         </is>
       </c>
-      <c r="R12" s="144" t="inlineStr">
+      <c r="R12" s="153" t="inlineStr">
         <is>
           <t>Interest expense as % of opening debt balance.</t>
         </is>
       </c>
-      <c r="S12" s="144" t="inlineStr">
+      <c r="S12" s="153" t="inlineStr">
         <is>
           <t>Excel equation: I101/I98 (FY25 interest ÷ FY25 opening debt in schedule).</t>
         </is>
       </c>
-      <c r="T12" s="144" t="inlineStr">
+      <c r="T12" s="153" t="inlineStr">
         <is>
           <t>Approximates average coupon / cost of debt on the book. Debt held flat (issuance = 0), so interest stays linked to that stock.</t>
         </is>
       </c>
-      <c r="U12" s="145" t="inlineStr">
+      <c r="U12" s="154" t="inlineStr">
         <is>
           <t>SEC 10-K FY2025 — Interest expense; see also 8-K 6.250% notes</t>
         </is>
       </c>
-      <c r="V12" s="145" t="inlineStr">
+      <c r="V12" s="154" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
         </is>
@@ -7064,7 +7357,7 @@
           <t>Tax Rate (% of Earnings Before Tax)</t>
         </is>
       </c>
-      <c r="C13" s="141" t="inlineStr">
+      <c r="C13" s="150" t="inlineStr">
         <is>
           <t>WHY: Uses reported effective rate (~19% on template EBT; ~18.8% on 10-K EBT). UFCF in DCF also uses unlevered EBIT × t. | SOURCE: SEC 10-K FY2025 — Provision for income taxes / Income before taxes | LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm | HOW: Excel equation: I35/I33 (FY25 tax ÷ simplified FY25 EBT in this template).</t>
         </is>
@@ -7090,55 +7383,55 @@
         <f>I35/I33</f>
         <v/>
       </c>
-      <c r="J13" s="146">
+      <c r="J13" s="155">
         <f>IF($I$33=0,0.21,$I$35/$I$33)</f>
         <v/>
       </c>
-      <c r="K13" s="146">
+      <c r="K13" s="155">
         <f>IF($I$33=0,0.21,$I$35/$I$33)</f>
         <v/>
       </c>
-      <c r="L13" s="146">
+      <c r="L13" s="155">
         <f>IF($I$33=0,0.21,$I$35/$I$33)</f>
         <v/>
       </c>
-      <c r="M13" s="146">
+      <c r="M13" s="155">
         <f>IF($I$33=0,0.21,$I$35/$I$33)</f>
         <v/>
       </c>
-      <c r="N13" s="146">
+      <c r="N13" s="155">
         <f>IF($I$33=0,0.21,$I$35/$I$33)</f>
         <v/>
       </c>
-      <c r="P13" s="143" t="n">
+      <c r="P13" s="152" t="n">
         <v>13</v>
       </c>
-      <c r="Q13" s="143" t="inlineStr">
+      <c r="Q13" s="152" t="inlineStr">
         <is>
           <t>Tax Rate (% of EBT)</t>
         </is>
       </c>
-      <c r="R13" s="144" t="inlineStr">
+      <c r="R13" s="153" t="inlineStr">
         <is>
           <t>Effective book tax rate applied to forecast EBT.</t>
         </is>
       </c>
-      <c r="S13" s="144" t="inlineStr">
+      <c r="S13" s="153" t="inlineStr">
         <is>
           <t>Excel equation: I35/I33 (FY25 tax ÷ simplified FY25 EBT in this template).</t>
         </is>
       </c>
-      <c r="T13" s="144" t="inlineStr">
+      <c r="T13" s="153" t="inlineStr">
         <is>
           <t>Uses reported effective rate (~19% on template EBT; ~18.8% on 10-K EBT). UFCF in DCF also uses unlevered EBIT × t.</t>
         </is>
       </c>
-      <c r="U13" s="145" t="inlineStr">
+      <c r="U13" s="154" t="inlineStr">
         <is>
           <t>SEC 10-K FY2025 — Provision for income taxes / Income before taxes</t>
         </is>
       </c>
-      <c r="V13" s="145" t="inlineStr">
+      <c r="V13" s="154" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
         </is>
@@ -7169,81 +7462,81 @@
           <t>Accounts Receivable (Days)</t>
         </is>
       </c>
-      <c r="C15" s="149" t="inlineStr">
+      <c r="C15" s="158" t="inlineStr">
         <is>
           <t>WHY: Operating working-capital view: contract liabilities (deferred revenue) reduce net AR so ΔNWC is not overstated. | SOURCE: SEC companyfacts XBRL — AR + DeferredRevenueCurrent | LINK: https://data.sec.gov/api/xbrl/companyfacts/CIK0000814547.json | HOW: Excel equation: ROUND(I42/I24×365, 0). I42 is net AR (AR − deferred).</t>
         </is>
       </c>
       <c r="D15" s="32" t="n"/>
-      <c r="E15" s="147">
+      <c r="E15" s="156">
         <f>E42/E24*365</f>
         <v/>
       </c>
-      <c r="F15" s="147">
+      <c r="F15" s="156">
         <f>F42/F24*365</f>
         <v/>
       </c>
-      <c r="G15" s="147">
+      <c r="G15" s="156">
         <f>G42/G24*365</f>
         <v/>
       </c>
-      <c r="H15" s="147">
+      <c r="H15" s="156">
         <f>H42/H24*365</f>
         <v/>
       </c>
-      <c r="I15" s="147">
+      <c r="I15" s="156">
         <f>I42/I24*365</f>
         <v/>
       </c>
-      <c r="J15" s="150">
+      <c r="J15" s="159">
         <f>ROUND($I$42/$I$24*365,0)</f>
         <v/>
       </c>
-      <c r="K15" s="150">
+      <c r="K15" s="159">
         <f>ROUND($I$42/$I$24*365,0)</f>
         <v/>
       </c>
-      <c r="L15" s="150">
+      <c r="L15" s="159">
         <f>ROUND($I$42/$I$24*365,0)</f>
         <v/>
       </c>
-      <c r="M15" s="150">
+      <c r="M15" s="159">
         <f>ROUND($I$42/$I$24*365,0)</f>
         <v/>
       </c>
-      <c r="N15" s="150">
+      <c r="N15" s="159">
         <f>ROUND($I$42/$I$24*365,0)</f>
         <v/>
       </c>
-      <c r="P15" s="143" t="n">
+      <c r="P15" s="152" t="n">
         <v>15</v>
       </c>
-      <c r="Q15" s="143" t="inlineStr">
+      <c r="Q15" s="152" t="inlineStr">
         <is>
           <t>Accounts Receivable (Days)</t>
         </is>
       </c>
-      <c r="R15" s="144" t="inlineStr">
+      <c r="R15" s="153" t="inlineStr">
         <is>
           <t>AR days sales outstanding used to project AR = Rev × days/365.</t>
         </is>
       </c>
-      <c r="S15" s="144" t="inlineStr">
+      <c r="S15" s="153" t="inlineStr">
         <is>
           <t>Excel equation: ROUND(I42/I24×365, 0). I42 is net AR (AR − deferred).</t>
         </is>
       </c>
-      <c r="T15" s="144" t="inlineStr">
+      <c r="T15" s="153" t="inlineStr">
         <is>
           <t>Operating working-capital view: contract liabilities (deferred revenue) reduce net AR so ΔNWC is not overstated.</t>
         </is>
       </c>
-      <c r="U15" s="145" t="inlineStr">
+      <c r="U15" s="154" t="inlineStr">
         <is>
           <t>SEC companyfacts XBRL — AR + DeferredRevenueCurrent</t>
         </is>
       </c>
-      <c r="V15" s="145" t="inlineStr">
+      <c r="V15" s="154" t="inlineStr">
         <is>
           <t>https://data.sec.gov/api/xbrl/companyfacts/CIK0000814547.json</t>
         </is>
@@ -7255,76 +7548,76 @@
           <t>Inventory (Days)</t>
         </is>
       </c>
-      <c r="C16" s="149" t="inlineStr">
+      <c r="C16" s="158" t="inlineStr">
         <is>
           <t>WHY: No inventory cycle to fund. | SOURCE: SEC 10-K FY2025 — Inventory ≈ $0 | LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm | HOW: Hard zero — FICO is software / scores; inventory is immaterial.</t>
         </is>
       </c>
       <c r="D16" s="32" t="n"/>
-      <c r="E16" s="147">
+      <c r="E16" s="156">
         <f>E43/E25*365</f>
         <v/>
       </c>
-      <c r="F16" s="147">
+      <c r="F16" s="156">
         <f>F43/F25*365</f>
         <v/>
       </c>
-      <c r="G16" s="147">
+      <c r="G16" s="156">
         <f>G43/G25*365</f>
         <v/>
       </c>
-      <c r="H16" s="147">
+      <c r="H16" s="156">
         <f>H43/H25*365</f>
         <v/>
       </c>
-      <c r="I16" s="147">
+      <c r="I16" s="156">
         <f>I43/I25*365</f>
         <v/>
       </c>
-      <c r="J16" s="151" t="n">
+      <c r="J16" s="160" t="n">
         <v>0</v>
       </c>
-      <c r="K16" s="151" t="n">
+      <c r="K16" s="160" t="n">
         <v>0</v>
       </c>
-      <c r="L16" s="151" t="n">
+      <c r="L16" s="160" t="n">
         <v>0</v>
       </c>
-      <c r="M16" s="151" t="n">
+      <c r="M16" s="160" t="n">
         <v>0</v>
       </c>
-      <c r="N16" s="151" t="n">
+      <c r="N16" s="160" t="n">
         <v>0</v>
       </c>
-      <c r="P16" s="143" t="n">
+      <c r="P16" s="152" t="n">
         <v>16</v>
       </c>
-      <c r="Q16" s="143" t="inlineStr">
+      <c r="Q16" s="152" t="inlineStr">
         <is>
           <t>Inventory (Days)</t>
         </is>
       </c>
-      <c r="R16" s="144" t="inlineStr">
+      <c r="R16" s="153" t="inlineStr">
         <is>
           <t>Inventory days (Inv = COGS × days/365).</t>
         </is>
       </c>
-      <c r="S16" s="144" t="inlineStr">
+      <c r="S16" s="153" t="inlineStr">
         <is>
           <t>Hard zero — FICO is software / scores; inventory is immaterial.</t>
         </is>
       </c>
-      <c r="T16" s="144" t="inlineStr">
+      <c r="T16" s="153" t="inlineStr">
         <is>
           <t>No inventory cycle to fund.</t>
         </is>
       </c>
-      <c r="U16" s="145" t="inlineStr">
+      <c r="U16" s="154" t="inlineStr">
         <is>
           <t>SEC 10-K FY2025 — Inventory ≈ $0</t>
         </is>
       </c>
-      <c r="V16" s="145" t="inlineStr">
+      <c r="V16" s="154" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
         </is>
@@ -7336,81 +7629,81 @@
           <t>Accounts Payable (Days)</t>
         </is>
       </c>
-      <c r="C17" s="149" t="inlineStr">
+      <c r="C17" s="158" t="inlineStr">
         <is>
           <t>WHY: Payable timing offsets AR in operating NWC. | SOURCE: SEC 10-K FY2025 — Accounts payable | LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm | HOW: Excel equation: ROUND(I48/I25×365, 0) from FY25.</t>
         </is>
       </c>
       <c r="D17" s="32" t="n"/>
-      <c r="E17" s="147">
+      <c r="E17" s="156">
         <f>E48/E25*365</f>
         <v/>
       </c>
-      <c r="F17" s="147">
+      <c r="F17" s="156">
         <f>F48/F25*365</f>
         <v/>
       </c>
-      <c r="G17" s="147">
+      <c r="G17" s="156">
         <f>G48/G25*365</f>
         <v/>
       </c>
-      <c r="H17" s="147">
+      <c r="H17" s="156">
         <f>H48/H25*365</f>
         <v/>
       </c>
-      <c r="I17" s="147">
+      <c r="I17" s="156">
         <f>I48/I25*365</f>
         <v/>
       </c>
-      <c r="J17" s="150">
+      <c r="J17" s="159">
         <f>IF($I$25=0,0,ROUND($I$48/$I$25*365,0))</f>
         <v/>
       </c>
-      <c r="K17" s="150">
+      <c r="K17" s="159">
         <f>IF($I$25=0,0,ROUND($I$48/$I$25*365,0))</f>
         <v/>
       </c>
-      <c r="L17" s="150">
+      <c r="L17" s="159">
         <f>IF($I$25=0,0,ROUND($I$48/$I$25*365,0))</f>
         <v/>
       </c>
-      <c r="M17" s="150">
+      <c r="M17" s="159">
         <f>IF($I$25=0,0,ROUND($I$48/$I$25*365,0))</f>
         <v/>
       </c>
-      <c r="N17" s="150">
+      <c r="N17" s="159">
         <f>IF($I$25=0,0,ROUND($I$48/$I$25*365,0))</f>
         <v/>
       </c>
-      <c r="P17" s="143" t="n">
+      <c r="P17" s="152" t="n">
         <v>17</v>
       </c>
-      <c r="Q17" s="143" t="inlineStr">
+      <c r="Q17" s="152" t="inlineStr">
         <is>
           <t>Accounts Payable (Days)</t>
         </is>
       </c>
-      <c r="R17" s="144" t="inlineStr">
+      <c r="R17" s="153" t="inlineStr">
         <is>
           <t>AP days used to project AP = COGS × days/365.</t>
         </is>
       </c>
-      <c r="S17" s="144" t="inlineStr">
+      <c r="S17" s="153" t="inlineStr">
         <is>
           <t>Excel equation: ROUND(I48/I25×365, 0) from FY25.</t>
         </is>
       </c>
-      <c r="T17" s="144" t="inlineStr">
+      <c r="T17" s="153" t="inlineStr">
         <is>
           <t>Payable timing offsets AR in operating NWC.</t>
         </is>
       </c>
-      <c r="U17" s="145" t="inlineStr">
+      <c r="U17" s="154" t="inlineStr">
         <is>
           <t>SEC 10-K FY2025 — Accounts payable</t>
         </is>
       </c>
-      <c r="V17" s="145" t="inlineStr">
+      <c r="V17" s="154" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
         </is>
@@ -7422,80 +7715,80 @@
           <t>CapEx % of Revenue (fade equation)</t>
         </is>
       </c>
-      <c r="C18" s="149" t="inlineStr">
+      <c r="C18" s="158" t="inlineStr">
         <is>
           <t>WHY: FY25 CapEx was elevated by capitalized internal-use software. Fading avoids locking a peak reinvestment rate forever. | SOURCE: SEC 10-K FY2025 — PP&amp;E purchases + capitalized software | LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm | HOW: Equation: fade from I68/I24 (FY25 CapEx/Sales ~1.98%) toward 1.0% steady. Weights 85%→65%→45%→30%→0% on the peak.</t>
         </is>
       </c>
-      <c r="E18" s="147">
+      <c r="E18" s="156">
         <f>E68</f>
         <v/>
       </c>
-      <c r="F18" s="147">
+      <c r="F18" s="156">
         <f>F68</f>
         <v/>
       </c>
-      <c r="G18" s="147">
+      <c r="G18" s="156">
         <f>G68</f>
         <v/>
       </c>
-      <c r="H18" s="147">
+      <c r="H18" s="156">
         <f>H68</f>
         <v/>
       </c>
-      <c r="I18" s="147">
+      <c r="I18" s="156">
         <f>I68</f>
         <v/>
       </c>
-      <c r="J18" s="148">
+      <c r="J18" s="157">
         <f>($I$68/$I$24)*0.85+0.01*(1-0.85)</f>
         <v/>
       </c>
-      <c r="K18" s="148">
+      <c r="K18" s="157">
         <f>($I$68/$I$24)*0.65+0.01*(1-0.65)</f>
         <v/>
       </c>
-      <c r="L18" s="148">
+      <c r="L18" s="157">
         <f>($I$68/$I$24)*0.45+0.01*(1-0.45)</f>
         <v/>
       </c>
-      <c r="M18" s="148">
+      <c r="M18" s="157">
         <f>($I$68/$I$24)*0.3+0.01*(1-0.3)</f>
         <v/>
       </c>
-      <c r="N18" s="148">
+      <c r="N18" s="157">
         <f>($I$68/$I$24)*0.0+0.01*(1-0.0)</f>
         <v/>
       </c>
-      <c r="P18" s="143" t="n">
+      <c r="P18" s="152" t="n">
         <v>18</v>
       </c>
-      <c r="Q18" s="143" t="inlineStr">
+      <c r="Q18" s="152" t="inlineStr">
         <is>
           <t>CapEx % of Revenue</t>
         </is>
       </c>
-      <c r="R18" s="144" t="inlineStr">
+      <c r="R18" s="153" t="inlineStr">
         <is>
           <t>Capital investment (PPE + capitalized software) as % of sales.</t>
         </is>
       </c>
-      <c r="S18" s="144" t="inlineStr">
+      <c r="S18" s="153" t="inlineStr">
         <is>
           <t>Equation: fade from I68/I24 (FY25 CapEx/Sales ~1.98%) toward 1.0% steady. Weights 85%→65%→45%→30%→0% on the peak.</t>
         </is>
       </c>
-      <c r="T18" s="144" t="inlineStr">
+      <c r="T18" s="153" t="inlineStr">
         <is>
           <t>FY25 CapEx was elevated by capitalized internal-use software. Fading avoids locking a peak reinvestment rate forever.</t>
         </is>
       </c>
-      <c r="U18" s="145" t="inlineStr">
+      <c r="U18" s="154" t="inlineStr">
         <is>
           <t>SEC 10-K FY2025 — PP&amp;E purchases + capitalized software</t>
         </is>
       </c>
-      <c r="V18" s="145" t="inlineStr">
+      <c r="V18" s="154" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
         </is>
@@ -7507,75 +7800,75 @@
           <t>Debt Issuance (Repayment) ($000's)</t>
         </is>
       </c>
-      <c r="C19" s="149" t="inlineStr">
+      <c r="C19" s="158" t="inlineStr">
         <is>
           <t>WHY: Hold debt stock flat at FY25 level for the explicit period; interest follows. Net debt for DCF equity bridge uses the… | SOURCE: SEC 10-Q Q3 FY2026 — debt stock (financing excluded from FCFF) | LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454726000030/fico-20260630.htm | HOW: POLICY input = 0 every year.</t>
         </is>
       </c>
-      <c r="E19" s="147">
+      <c r="E19" s="156">
         <f>E99</f>
         <v/>
       </c>
-      <c r="F19" s="147">
+      <c r="F19" s="156">
         <f>F99</f>
         <v/>
       </c>
-      <c r="G19" s="147">
+      <c r="G19" s="156">
         <f>G99</f>
         <v/>
       </c>
-      <c r="H19" s="147">
+      <c r="H19" s="156">
         <f>H99</f>
         <v/>
       </c>
-      <c r="I19" s="147">
+      <c r="I19" s="156">
         <f>I99</f>
         <v/>
       </c>
-      <c r="J19" s="152" t="n">
+      <c r="J19" s="161" t="n">
         <v>0</v>
       </c>
-      <c r="K19" s="152" t="n">
+      <c r="K19" s="161" t="n">
         <v>0</v>
       </c>
-      <c r="L19" s="152" t="n">
+      <c r="L19" s="161" t="n">
         <v>0</v>
       </c>
-      <c r="M19" s="152" t="n">
+      <c r="M19" s="161" t="n">
         <v>0</v>
       </c>
-      <c r="N19" s="152" t="n">
+      <c r="N19" s="161" t="n">
         <v>0</v>
       </c>
-      <c r="P19" s="143" t="n">
+      <c r="P19" s="152" t="n">
         <v>19</v>
       </c>
-      <c r="Q19" s="143" t="inlineStr">
+      <c r="Q19" s="152" t="inlineStr">
         <is>
           <t>Debt Issuance (Repayment)</t>
         </is>
       </c>
-      <c r="R19" s="144" t="inlineStr">
+      <c r="R19" s="153" t="inlineStr">
         <is>
           <t>New borrowing (+) or repayment (−) in the forecast.</t>
         </is>
       </c>
-      <c r="S19" s="144" t="inlineStr">
+      <c r="S19" s="153" t="inlineStr">
         <is>
           <t>POLICY input = 0 every year.</t>
         </is>
       </c>
-      <c r="T19" s="144" t="inlineStr">
+      <c r="T19" s="153" t="inlineStr">
         <is>
           <t>Hold debt stock flat at FY25 level for the explicit period; interest follows. Net debt for DCF equity bridge uses the later 10-Q amount separately.</t>
         </is>
       </c>
-      <c r="U19" s="145" t="inlineStr">
+      <c r="U19" s="154" t="inlineStr">
         <is>
           <t>SEC 10-Q Q3 FY2026 — debt stock (financing excluded from FCFF)</t>
         </is>
       </c>
-      <c r="V19" s="145" t="inlineStr">
+      <c r="V19" s="154" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/814547/000081454726000030/fico-20260630.htm</t>
         </is>
@@ -7587,75 +7880,75 @@
           <t>Equity Issued (Repaid) ($000's)</t>
         </is>
       </c>
-      <c r="C20" s="149" t="inlineStr">
+      <c r="C20" s="158" t="inlineStr">
         <is>
           <t>WHY: Buybacks are real historically but are financing — excluded from FCFF. Share count for $/share is the spot shares out… | SOURCE: Damodaran FCFF framework — financing (buybacks) not in FCFF | LINK: https://pages.stern.nyu.edu/~adamodar/New_Home_Page/datafile/histfcff.html | HOW: POLICY input = 0 every year.</t>
         </is>
       </c>
-      <c r="E20" s="147">
+      <c r="E20" s="156">
         <f>E73</f>
         <v/>
       </c>
-      <c r="F20" s="147">
+      <c r="F20" s="156">
         <f>F73</f>
         <v/>
       </c>
-      <c r="G20" s="147">
+      <c r="G20" s="156">
         <f>G73</f>
         <v/>
       </c>
-      <c r="H20" s="147">
+      <c r="H20" s="156">
         <f>H73</f>
         <v/>
       </c>
-      <c r="I20" s="147">
+      <c r="I20" s="156">
         <f>I73</f>
         <v/>
       </c>
-      <c r="J20" s="152" t="n">
+      <c r="J20" s="161" t="n">
         <v>0</v>
       </c>
-      <c r="K20" s="152" t="n">
+      <c r="K20" s="161" t="n">
         <v>0</v>
       </c>
-      <c r="L20" s="152" t="n">
+      <c r="L20" s="161" t="n">
         <v>0</v>
       </c>
-      <c r="M20" s="152" t="n">
+      <c r="M20" s="161" t="n">
         <v>0</v>
       </c>
-      <c r="N20" s="152" t="n">
+      <c r="N20" s="161" t="n">
         <v>0</v>
       </c>
-      <c r="P20" s="143" t="n">
+      <c r="P20" s="152" t="n">
         <v>20</v>
       </c>
-      <c r="Q20" s="143" t="inlineStr">
+      <c r="Q20" s="152" t="inlineStr">
         <is>
           <t>Equity Issued (Repaid)</t>
         </is>
       </c>
-      <c r="R20" s="144" t="inlineStr">
+      <c r="R20" s="153" t="inlineStr">
         <is>
           <t>New equity issued (+) or buybacks (−) in the forecast BS/CF.</t>
         </is>
       </c>
-      <c r="S20" s="144" t="inlineStr">
+      <c r="S20" s="153" t="inlineStr">
         <is>
           <t>POLICY input = 0 every year.</t>
         </is>
       </c>
-      <c r="T20" s="144" t="inlineStr">
+      <c r="T20" s="153" t="inlineStr">
         <is>
           <t>Buybacks are real historically but are financing — excluded from FCFF. Share count for $/share is the spot shares outstanding assumption.</t>
         </is>
       </c>
-      <c r="U20" s="145" t="inlineStr">
+      <c r="U20" s="154" t="inlineStr">
         <is>
           <t>Damodaran FCFF framework — financing (buybacks) not in FCFF</t>
         </is>
       </c>
-      <c r="V20" s="145" t="inlineStr">
+      <c r="V20" s="154" t="inlineStr">
         <is>
           <t>https://pages.stern.nyu.edu/~adamodar/New_Home_Page/datafile/histfcff.html</t>
         </is>
@@ -7710,44 +8003,44 @@
           <t>Reveneue</t>
         </is>
       </c>
-      <c r="C24" s="153" t="inlineStr">
+      <c r="C24" s="162" t="inlineStr">
         <is>
           <t>eqn: PriorRev × (1 + growth)</t>
         </is>
       </c>
       <c r="D24" s="46" t="n"/>
-      <c r="E24" s="154" t="n">
+      <c r="E24" s="163" t="n">
         <v>1316536</v>
       </c>
-      <c r="F24" s="154" t="n">
+      <c r="F24" s="163" t="n">
         <v>1377270</v>
       </c>
-      <c r="G24" s="154" t="n">
+      <c r="G24" s="163" t="n">
         <v>1513557</v>
       </c>
-      <c r="H24" s="154" t="n">
+      <c r="H24" s="163" t="n">
         <v>1717526</v>
       </c>
-      <c r="I24" s="154" t="n">
+      <c r="I24" s="163" t="n">
         <v>1990869</v>
       </c>
-      <c r="J24" s="150">
+      <c r="J24" s="159">
         <f>I24*(1+J7)</f>
         <v/>
       </c>
-      <c r="K24" s="150">
+      <c r="K24" s="159">
         <f>J24*(1+K7)</f>
         <v/>
       </c>
-      <c r="L24" s="150">
+      <c r="L24" s="159">
         <f>K24*(1+L7)</f>
         <v/>
       </c>
-      <c r="M24" s="150">
+      <c r="M24" s="159">
         <f>L24*(1+M7)</f>
         <v/>
       </c>
-      <c r="N24" s="150">
+      <c r="N24" s="159">
         <f>M24*(1+N7)</f>
         <v/>
       </c>
@@ -7758,44 +8051,44 @@
           <t>Cost of Goods Sold (COGS)</t>
         </is>
       </c>
-      <c r="C25" s="153" t="inlineStr">
+      <c r="C25" s="162" t="inlineStr">
         <is>
           <t>eqn: Rev × COGS%</t>
         </is>
       </c>
       <c r="D25" s="47" t="n"/>
-      <c r="E25" s="154" t="n">
+      <c r="E25" s="163" t="n">
         <v>332462</v>
       </c>
-      <c r="F25" s="154" t="n">
+      <c r="F25" s="163" t="n">
         <v>302174</v>
       </c>
-      <c r="G25" s="154" t="n">
+      <c r="G25" s="163" t="n">
         <v>311053</v>
       </c>
-      <c r="H25" s="154" t="n">
+      <c r="H25" s="163" t="n">
         <v>348206</v>
       </c>
-      <c r="I25" s="154" t="n">
+      <c r="I25" s="163" t="n">
         <v>353722</v>
       </c>
-      <c r="J25" s="150">
+      <c r="J25" s="159">
         <f>J24*J8</f>
         <v/>
       </c>
-      <c r="K25" s="150">
+      <c r="K25" s="159">
         <f>K24*K8</f>
         <v/>
       </c>
-      <c r="L25" s="150">
+      <c r="L25" s="159">
         <f>L24*L8</f>
         <v/>
       </c>
-      <c r="M25" s="150">
+      <c r="M25" s="159">
         <f>M24*M8</f>
         <v/>
       </c>
-      <c r="N25" s="150">
+      <c r="N25" s="159">
         <f>N24*N8</f>
         <v/>
       </c>
@@ -7806,49 +8099,49 @@
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="C26" s="155" t="inlineStr">
+      <c r="C26" s="164" t="inlineStr">
         <is>
           <t>eqn: Rev − COGS</t>
         </is>
       </c>
       <c r="D26" s="22" t="n"/>
-      <c r="E26" s="156">
+      <c r="E26" s="165">
         <f>E24-E25</f>
         <v/>
       </c>
-      <c r="F26" s="156">
+      <c r="F26" s="165">
         <f>F24-F25</f>
         <v/>
       </c>
-      <c r="G26" s="156">
+      <c r="G26" s="165">
         <f>G24-G25</f>
         <v/>
       </c>
-      <c r="H26" s="156">
+      <c r="H26" s="165">
         <f>H24-H25</f>
         <v/>
       </c>
-      <c r="I26" s="156">
+      <c r="I26" s="165">
         <f>I24-I25</f>
         <v/>
       </c>
-      <c r="J26" s="150">
+      <c r="J26" s="159">
         <f>J24-J25</f>
         <v/>
       </c>
-      <c r="K26" s="150">
+      <c r="K26" s="159">
         <f>K24-K25</f>
         <v/>
       </c>
-      <c r="L26" s="150">
+      <c r="L26" s="159">
         <f>L24-L25</f>
         <v/>
       </c>
-      <c r="M26" s="150">
+      <c r="M26" s="159">
         <f>M24-M25</f>
         <v/>
       </c>
-      <c r="N26" s="150">
+      <c r="N26" s="159">
         <f>N24-N25</f>
         <v/>
       </c>
@@ -7878,43 +8171,43 @@
           <t>Salaries and Benefits</t>
         </is>
       </c>
-      <c r="C28" s="157" t="inlineStr">
+      <c r="C28" s="166" t="inlineStr">
         <is>
           <t>eqn: Rev × SGA%</t>
         </is>
       </c>
-      <c r="E28" s="154" t="n">
+      <c r="E28" s="163" t="n">
         <v>396281</v>
       </c>
-      <c r="F28" s="154" t="n">
+      <c r="F28" s="163" t="n">
         <v>383863</v>
       </c>
-      <c r="G28" s="154" t="n">
+      <c r="G28" s="163" t="n">
         <v>400565</v>
       </c>
-      <c r="H28" s="154" t="n">
+      <c r="H28" s="163" t="n">
         <v>462834</v>
       </c>
-      <c r="I28" s="154" t="n">
+      <c r="I28" s="163" t="n">
         <v>513028</v>
       </c>
-      <c r="J28" s="150">
+      <c r="J28" s="159">
         <f>J24*J9</f>
         <v/>
       </c>
-      <c r="K28" s="150">
+      <c r="K28" s="159">
         <f>K24*K9</f>
         <v/>
       </c>
-      <c r="L28" s="150">
+      <c r="L28" s="159">
         <f>L24*L9</f>
         <v/>
       </c>
-      <c r="M28" s="150">
+      <c r="M28" s="159">
         <f>M24*M9</f>
         <v/>
       </c>
-      <c r="N28" s="150">
+      <c r="N28" s="159">
         <f>N24*N9</f>
         <v/>
       </c>
@@ -7925,43 +8218,43 @@
           <t>Rent and Overhead</t>
         </is>
       </c>
-      <c r="C29" s="157" t="inlineStr">
+      <c r="C29" s="166" t="inlineStr">
         <is>
           <t>eqn: Rev × R&amp;D%</t>
         </is>
       </c>
-      <c r="E29" s="154" t="n">
+      <c r="E29" s="163" t="n">
         <v>171231</v>
       </c>
-      <c r="F29" s="154" t="n">
+      <c r="F29" s="163" t="n">
         <v>146758</v>
       </c>
-      <c r="G29" s="154" t="n">
+      <c r="G29" s="163" t="n">
         <v>159950</v>
       </c>
-      <c r="H29" s="154" t="n">
+      <c r="H29" s="163" t="n">
         <v>171940</v>
       </c>
-      <c r="I29" s="154" t="n">
+      <c r="I29" s="163" t="n">
         <v>188347</v>
       </c>
-      <c r="J29" s="150">
+      <c r="J29" s="159">
         <f>J24*J10</f>
         <v/>
       </c>
-      <c r="K29" s="150">
+      <c r="K29" s="159">
         <f>K24*K10</f>
         <v/>
       </c>
-      <c r="L29" s="150">
+      <c r="L29" s="159">
         <f>L24*L10</f>
         <v/>
       </c>
-      <c r="M29" s="150">
+      <c r="M29" s="159">
         <f>M24*M10</f>
         <v/>
       </c>
-      <c r="N29" s="150">
+      <c r="N29" s="159">
         <f>N24*N10</f>
         <v/>
       </c>
@@ -7972,43 +8265,43 @@
           <t>Depreciation &amp; Amortization</t>
         </is>
       </c>
-      <c r="C30" s="157" t="inlineStr">
+      <c r="C30" s="166" t="inlineStr">
         <is>
           <t>eqn: PPE_open × DA%</t>
         </is>
       </c>
-      <c r="E30" s="154" t="n">
+      <c r="E30" s="163" t="n">
         <v>25592</v>
       </c>
-      <c r="F30" s="154" t="n">
+      <c r="F30" s="163" t="n">
         <v>20465</v>
       </c>
-      <c r="G30" s="154" t="n">
+      <c r="G30" s="163" t="n">
         <v>14638</v>
       </c>
-      <c r="H30" s="154" t="n">
+      <c r="H30" s="163" t="n">
         <v>13827</v>
       </c>
-      <c r="I30" s="154" t="n">
+      <c r="I30" s="163" t="n">
         <v>14952</v>
       </c>
-      <c r="J30" s="150">
+      <c r="J30" s="159">
         <f>J92*J11</f>
         <v/>
       </c>
-      <c r="K30" s="150">
+      <c r="K30" s="159">
         <f>K92*K11</f>
         <v/>
       </c>
-      <c r="L30" s="150">
+      <c r="L30" s="159">
         <f>L92*L11</f>
         <v/>
       </c>
-      <c r="M30" s="150">
+      <c r="M30" s="159">
         <f>M92*M11</f>
         <v/>
       </c>
-      <c r="N30" s="150">
+      <c r="N30" s="159">
         <f>N92*N11</f>
         <v/>
       </c>
@@ -8019,44 +8312,44 @@
           <t>Interest</t>
         </is>
       </c>
-      <c r="C31" s="158" t="inlineStr">
+      <c r="C31" s="167" t="inlineStr">
         <is>
           <t>eqn: Debt_open × Int%</t>
         </is>
       </c>
       <c r="D31" s="24" t="n"/>
-      <c r="E31" s="159" t="n">
+      <c r="E31" s="168" t="n">
         <v>40092</v>
       </c>
-      <c r="F31" s="159" t="n">
+      <c r="F31" s="168" t="n">
         <v>68967</v>
       </c>
-      <c r="G31" s="159" t="n">
+      <c r="G31" s="168" t="n">
         <v>95546</v>
       </c>
-      <c r="H31" s="159" t="n">
+      <c r="H31" s="168" t="n">
         <v>105638</v>
       </c>
-      <c r="I31" s="159" t="n">
+      <c r="I31" s="168" t="n">
         <v>133647</v>
       </c>
-      <c r="J31" s="150">
+      <c r="J31" s="159">
         <f>J98*J12</f>
         <v/>
       </c>
-      <c r="K31" s="150">
+      <c r="K31" s="159">
         <f>K98*K12</f>
         <v/>
       </c>
-      <c r="L31" s="150">
+      <c r="L31" s="159">
         <f>L98*L12</f>
         <v/>
       </c>
-      <c r="M31" s="150">
+      <c r="M31" s="159">
         <f>M98*M12</f>
         <v/>
       </c>
-      <c r="N31" s="150">
+      <c r="N31" s="159">
         <f>N98*N12</f>
         <v/>
       </c>
@@ -8069,43 +8362,43 @@
       </c>
       <c r="C32" s="19" t="n"/>
       <c r="D32" s="47" t="n"/>
-      <c r="E32" s="160">
+      <c r="E32" s="169">
         <f>SUM(E28:E31)</f>
         <v/>
       </c>
-      <c r="F32" s="160">
+      <c r="F32" s="169">
         <f>SUM(F28:F31)</f>
         <v/>
       </c>
-      <c r="G32" s="160">
+      <c r="G32" s="169">
         <f>SUM(G28:G31)</f>
         <v/>
       </c>
-      <c r="H32" s="160">
+      <c r="H32" s="169">
         <f>SUM(H28:H31)</f>
         <v/>
       </c>
-      <c r="I32" s="160">
+      <c r="I32" s="169">
         <f>SUM(I28:I31)</f>
         <v/>
       </c>
-      <c r="J32" s="150">
+      <c r="J32" s="159">
         <f>SUM(J28:J31)</f>
         <v/>
       </c>
-      <c r="K32" s="150">
+      <c r="K32" s="159">
         <f>SUM(K28:K31)</f>
         <v/>
       </c>
-      <c r="L32" s="150">
+      <c r="L32" s="159">
         <f>SUM(L28:L31)</f>
         <v/>
       </c>
-      <c r="M32" s="150">
+      <c r="M32" s="159">
         <f>SUM(M28:M31)</f>
         <v/>
       </c>
-      <c r="N32" s="150">
+      <c r="N32" s="159">
         <f>SUM(N28:N31)</f>
         <v/>
       </c>
@@ -8116,49 +8409,49 @@
           <t>Earnings Before Tax</t>
         </is>
       </c>
-      <c r="C33" s="155" t="inlineStr">
+      <c r="C33" s="164" t="inlineStr">
         <is>
           <t>eqn: GP − Expenses</t>
         </is>
       </c>
       <c r="D33" s="22" t="n"/>
-      <c r="E33" s="156">
+      <c r="E33" s="165">
         <f>E26-E32</f>
         <v/>
       </c>
-      <c r="F33" s="156">
+      <c r="F33" s="165">
         <f>F26-F32</f>
         <v/>
       </c>
-      <c r="G33" s="156">
+      <c r="G33" s="165">
         <f>G26-G32</f>
         <v/>
       </c>
-      <c r="H33" s="156">
+      <c r="H33" s="165">
         <f>H26-H32</f>
         <v/>
       </c>
-      <c r="I33" s="156">
+      <c r="I33" s="165">
         <f>I26-I32</f>
         <v/>
       </c>
-      <c r="J33" s="150">
+      <c r="J33" s="159">
         <f>J26-J32</f>
         <v/>
       </c>
-      <c r="K33" s="150">
+      <c r="K33" s="159">
         <f>K26-K32</f>
         <v/>
       </c>
-      <c r="L33" s="150">
+      <c r="L33" s="159">
         <f>L26-L32</f>
         <v/>
       </c>
-      <c r="M33" s="150">
+      <c r="M33" s="159">
         <f>M26-M32</f>
         <v/>
       </c>
-      <c r="N33" s="150">
+      <c r="N33" s="159">
         <f>N26-N32</f>
         <v/>
       </c>
@@ -8184,44 +8477,44 @@
           <t>Taxes</t>
         </is>
       </c>
-      <c r="C35" s="153" t="inlineStr">
+      <c r="C35" s="162" t="inlineStr">
         <is>
           <t>eqn: EBT × tax%</t>
         </is>
       </c>
       <c r="D35" s="47" t="n"/>
-      <c r="E35" s="154" t="n">
+      <c r="E35" s="163" t="n">
         <v>81058</v>
       </c>
-      <c r="F35" s="154" t="n">
+      <c r="F35" s="163" t="n">
         <v>97768</v>
       </c>
-      <c r="G35" s="154" t="n">
+      <c r="G35" s="163" t="n">
         <v>124249</v>
       </c>
-      <c r="H35" s="154" t="n">
+      <c r="H35" s="163" t="n">
         <v>129214</v>
       </c>
-      <c r="I35" s="154" t="n">
+      <c r="I35" s="163" t="n">
         <v>150649</v>
       </c>
-      <c r="J35" s="150">
+      <c r="J35" s="159">
         <f>J33*J13</f>
         <v/>
       </c>
-      <c r="K35" s="150">
+      <c r="K35" s="159">
         <f>K33*K13</f>
         <v/>
       </c>
-      <c r="L35" s="150">
+      <c r="L35" s="159">
         <f>L33*L13</f>
         <v/>
       </c>
-      <c r="M35" s="150">
+      <c r="M35" s="159">
         <f>M33*M13</f>
         <v/>
       </c>
-      <c r="N35" s="150">
+      <c r="N35" s="159">
         <f>N33*N13</f>
         <v/>
       </c>
@@ -8232,49 +8525,49 @@
           <t>Net Earnings</t>
         </is>
       </c>
-      <c r="C36" s="161" t="inlineStr">
+      <c r="C36" s="170" t="inlineStr">
         <is>
           <t>eqn: EBT × (1 − tax%)  — grows with Rev×(1+g)</t>
         </is>
       </c>
       <c r="D36" s="40" t="n"/>
-      <c r="E36" s="162">
+      <c r="E36" s="171">
         <f>E33-E35</f>
         <v/>
       </c>
-      <c r="F36" s="162">
+      <c r="F36" s="171">
         <f>F33-F35</f>
         <v/>
       </c>
-      <c r="G36" s="162">
+      <c r="G36" s="171">
         <f>G33-G35</f>
         <v/>
       </c>
-      <c r="H36" s="162">
+      <c r="H36" s="171">
         <f>H33-H35</f>
         <v/>
       </c>
-      <c r="I36" s="162">
+      <c r="I36" s="171">
         <f>I33-I35</f>
         <v/>
       </c>
-      <c r="J36" s="150">
+      <c r="J36" s="159">
         <f>J33*(1-J13)</f>
         <v/>
       </c>
-      <c r="K36" s="150">
+      <c r="K36" s="159">
         <f>K33*(1-K13)</f>
         <v/>
       </c>
-      <c r="L36" s="150">
+      <c r="L36" s="159">
         <f>L33*(1-L13)</f>
         <v/>
       </c>
-      <c r="M36" s="150">
+      <c r="M36" s="159">
         <f>M33*(1-M13)</f>
         <v/>
       </c>
-      <c r="N36" s="150">
+      <c r="N36" s="159">
         <f>N33*(1-N13)</f>
         <v/>
       </c>
@@ -8335,38 +8628,38 @@
           <t>Cash</t>
         </is>
       </c>
-      <c r="E41" s="154" t="n">
+      <c r="E41" s="163" t="n">
         <v>195354</v>
       </c>
-      <c r="F41" s="154" t="n">
+      <c r="F41" s="163" t="n">
         <v>133202</v>
       </c>
-      <c r="G41" s="154" t="n">
+      <c r="G41" s="163" t="n">
         <v>136778</v>
       </c>
-      <c r="H41" s="154" t="n">
+      <c r="H41" s="163" t="n">
         <v>150667</v>
       </c>
-      <c r="I41" s="154" t="n">
+      <c r="I41" s="163" t="n">
         <v>134136</v>
       </c>
-      <c r="J41" s="150">
+      <c r="J41" s="159">
         <f>J78</f>
         <v/>
       </c>
-      <c r="K41" s="150">
+      <c r="K41" s="159">
         <f>K78</f>
         <v/>
       </c>
-      <c r="L41" s="150">
+      <c r="L41" s="159">
         <f>L78</f>
         <v/>
       </c>
-      <c r="M41" s="150">
+      <c r="M41" s="159">
         <f>M78</f>
         <v/>
       </c>
-      <c r="N41" s="150">
+      <c r="N41" s="159">
         <f>N78</f>
         <v/>
       </c>
@@ -8377,43 +8670,43 @@
           <t>Accounts Receivable</t>
         </is>
       </c>
-      <c r="C42" s="157" t="inlineStr">
+      <c r="C42" s="166" t="inlineStr">
         <is>
           <t>eqn: Rev × AR_days / 365</t>
         </is>
       </c>
-      <c r="E42" s="154" t="n">
+      <c r="E42" s="163" t="n">
         <v>206690</v>
       </c>
-      <c r="F42" s="154" t="n">
+      <c r="F42" s="163" t="n">
         <v>202365</v>
       </c>
-      <c r="G42" s="154" t="n">
+      <c r="G42" s="163" t="n">
         <v>251217</v>
       </c>
-      <c r="H42" s="154" t="n">
+      <c r="H42" s="163" t="n">
         <v>269745</v>
       </c>
-      <c r="I42" s="154" t="n">
+      <c r="I42" s="163" t="n">
         <v>341776</v>
       </c>
-      <c r="J42" s="150">
+      <c r="J42" s="159">
         <f>J24*J15/365</f>
         <v/>
       </c>
-      <c r="K42" s="150">
+      <c r="K42" s="159">
         <f>K24*K15/365</f>
         <v/>
       </c>
-      <c r="L42" s="150">
+      <c r="L42" s="159">
         <f>L24*L15/365</f>
         <v/>
       </c>
-      <c r="M42" s="150">
+      <c r="M42" s="159">
         <f>M24*M15/365</f>
         <v/>
       </c>
-      <c r="N42" s="150">
+      <c r="N42" s="159">
         <f>N24*N15/365</f>
         <v/>
       </c>
@@ -8424,38 +8717,38 @@
           <t>Inventory</t>
         </is>
       </c>
-      <c r="E43" s="154" t="n">
+      <c r="E43" s="163" t="n">
         <v>0</v>
       </c>
-      <c r="F43" s="154" t="n">
+      <c r="F43" s="163" t="n">
         <v>0</v>
       </c>
-      <c r="G43" s="154" t="n">
+      <c r="G43" s="163" t="n">
         <v>0</v>
       </c>
-      <c r="H43" s="154" t="n">
+      <c r="H43" s="163" t="n">
         <v>0</v>
       </c>
-      <c r="I43" s="154" t="n">
+      <c r="I43" s="163" t="n">
         <v>0</v>
       </c>
-      <c r="J43" s="150">
+      <c r="J43" s="159">
         <f>J25*J16/365</f>
         <v/>
       </c>
-      <c r="K43" s="150">
+      <c r="K43" s="159">
         <f>K25*K16/365</f>
         <v/>
       </c>
-      <c r="L43" s="150">
+      <c r="L43" s="159">
         <f>L25*L16/365</f>
         <v/>
       </c>
-      <c r="M43" s="150">
+      <c r="M43" s="159">
         <f>M25*M16/365</f>
         <v/>
       </c>
-      <c r="N43" s="150">
+      <c r="N43" s="159">
         <f>N25*N16/365</f>
         <v/>
       </c>
@@ -8466,38 +8759,38 @@
           <t>Property &amp; Equipment</t>
         </is>
       </c>
-      <c r="E44" s="154" t="n">
+      <c r="E44" s="163" t="n">
         <v>27913</v>
       </c>
-      <c r="F44" s="154" t="n">
+      <c r="F44" s="163" t="n">
         <v>17580</v>
       </c>
-      <c r="G44" s="154" t="n">
+      <c r="G44" s="163" t="n">
         <v>10966</v>
       </c>
-      <c r="H44" s="154" t="n">
+      <c r="H44" s="163" t="n">
         <v>38465</v>
       </c>
-      <c r="I44" s="154" t="n">
+      <c r="I44" s="163" t="n">
         <v>67713</v>
       </c>
-      <c r="J44" s="150">
+      <c r="J44" s="159">
         <f>J95</f>
         <v/>
       </c>
-      <c r="K44" s="150">
+      <c r="K44" s="159">
         <f>K95</f>
         <v/>
       </c>
-      <c r="L44" s="150">
+      <c r="L44" s="159">
         <f>L95</f>
         <v/>
       </c>
-      <c r="M44" s="150">
+      <c r="M44" s="159">
         <f>M95</f>
         <v/>
       </c>
-      <c r="N44" s="150">
+      <c r="N44" s="159">
         <f>N95</f>
         <v/>
       </c>
@@ -8510,43 +8803,43 @@
       </c>
       <c r="C45" s="39" t="n"/>
       <c r="D45" s="40" t="n"/>
-      <c r="E45" s="162">
+      <c r="E45" s="171">
         <f>SUM(E41:E44)</f>
         <v/>
       </c>
-      <c r="F45" s="162">
+      <c r="F45" s="171">
         <f>SUM(F41:F44)</f>
         <v/>
       </c>
-      <c r="G45" s="162">
+      <c r="G45" s="171">
         <f>SUM(G41:G44)</f>
         <v/>
       </c>
-      <c r="H45" s="162">
+      <c r="H45" s="171">
         <f>SUM(H41:H44)</f>
         <v/>
       </c>
-      <c r="I45" s="162">
+      <c r="I45" s="171">
         <f>SUM(I41:I44)</f>
         <v/>
       </c>
-      <c r="J45" s="150">
+      <c r="J45" s="159">
         <f>SUM(J41:J44)</f>
         <v/>
       </c>
-      <c r="K45" s="150">
+      <c r="K45" s="159">
         <f>SUM(K41:K44)</f>
         <v/>
       </c>
-      <c r="L45" s="150">
+      <c r="L45" s="159">
         <f>SUM(L41:L44)</f>
         <v/>
       </c>
-      <c r="M45" s="150">
+      <c r="M45" s="159">
         <f>SUM(M41:M44)</f>
         <v/>
       </c>
-      <c r="N45" s="150">
+      <c r="N45" s="159">
         <f>SUM(N41:N44)</f>
         <v/>
       </c>
@@ -8584,43 +8877,43 @@
           <t>Accounts Payable</t>
         </is>
       </c>
-      <c r="C48" s="157" t="inlineStr">
+      <c r="C48" s="166" t="inlineStr">
         <is>
           <t>eqn: COGS × AP_days / 365</t>
         </is>
       </c>
-      <c r="E48" s="154" t="n">
+      <c r="E48" s="163" t="n">
         <v>20749</v>
       </c>
-      <c r="F48" s="154" t="n">
+      <c r="F48" s="163" t="n">
         <v>17273</v>
       </c>
-      <c r="G48" s="154" t="n">
+      <c r="G48" s="163" t="n">
         <v>19009</v>
       </c>
-      <c r="H48" s="154" t="n">
+      <c r="H48" s="163" t="n">
         <v>22473</v>
       </c>
-      <c r="I48" s="154" t="n">
+      <c r="I48" s="163" t="n">
         <v>32315</v>
       </c>
-      <c r="J48" s="150">
+      <c r="J48" s="159">
         <f>J25*J17/365</f>
         <v/>
       </c>
-      <c r="K48" s="150">
+      <c r="K48" s="159">
         <f>K25*K17/365</f>
         <v/>
       </c>
-      <c r="L48" s="150">
+      <c r="L48" s="159">
         <f>L25*L17/365</f>
         <v/>
       </c>
-      <c r="M48" s="150">
+      <c r="M48" s="159">
         <f>M25*M17/365</f>
         <v/>
       </c>
-      <c r="N48" s="150">
+      <c r="N48" s="159">
         <f>N25*N17/365</f>
         <v/>
       </c>
@@ -8631,38 +8924,38 @@
           <t>Debt</t>
         </is>
       </c>
-      <c r="E49" s="154" t="n">
+      <c r="E49" s="163" t="n">
         <v>1259018</v>
       </c>
-      <c r="F49" s="154" t="n">
+      <c r="F49" s="163" t="n">
         <v>1853669</v>
       </c>
-      <c r="G49" s="154" t="n">
+      <c r="G49" s="163" t="n">
         <v>1861658</v>
       </c>
-      <c r="H49" s="154" t="n">
+      <c r="H49" s="163" t="n">
         <v>2209021</v>
       </c>
-      <c r="I49" s="154" t="n">
+      <c r="I49" s="163" t="n">
         <v>3055691</v>
       </c>
-      <c r="J49" s="150">
+      <c r="J49" s="159">
         <f>J100</f>
         <v/>
       </c>
-      <c r="K49" s="150">
+      <c r="K49" s="159">
         <f>K100</f>
         <v/>
       </c>
-      <c r="L49" s="150">
+      <c r="L49" s="159">
         <f>L100</f>
         <v/>
       </c>
-      <c r="M49" s="150">
+      <c r="M49" s="159">
         <f>M100</f>
         <v/>
       </c>
-      <c r="N49" s="150">
+      <c r="N49" s="159">
         <f>N100</f>
         <v/>
       </c>
@@ -8675,43 +8968,43 @@
       </c>
       <c r="C50" s="4" t="n"/>
       <c r="D50" s="22" t="n"/>
-      <c r="E50" s="156">
+      <c r="E50" s="165">
         <f>SUM(E48:E49)</f>
         <v/>
       </c>
-      <c r="F50" s="156">
+      <c r="F50" s="165">
         <f>SUM(F48:F49)</f>
         <v/>
       </c>
-      <c r="G50" s="156">
+      <c r="G50" s="165">
         <f>SUM(G48:G49)</f>
         <v/>
       </c>
-      <c r="H50" s="156">
+      <c r="H50" s="165">
         <f>SUM(H48:H49)</f>
         <v/>
       </c>
-      <c r="I50" s="156">
+      <c r="I50" s="165">
         <f>SUM(I48:I49)</f>
         <v/>
       </c>
-      <c r="J50" s="150">
+      <c r="J50" s="159">
         <f>SUM(J48:J49)</f>
         <v/>
       </c>
-      <c r="K50" s="150">
+      <c r="K50" s="159">
         <f>SUM(K48:K49)</f>
         <v/>
       </c>
-      <c r="L50" s="150">
+      <c r="L50" s="159">
         <f>SUM(L48:L49)</f>
         <v/>
       </c>
-      <c r="M50" s="150">
+      <c r="M50" s="159">
         <f>SUM(M48:M49)</f>
         <v/>
       </c>
-      <c r="N50" s="150">
+      <c r="N50" s="159">
         <f>SUM(N48:N49)</f>
         <v/>
       </c>
@@ -8734,38 +9027,38 @@
           <t>Equity Capital</t>
         </is>
       </c>
-      <c r="E52" s="154" t="n">
+      <c r="E52" s="163" t="n">
         <v>-849810</v>
       </c>
-      <c r="F52" s="154" t="n">
+      <c r="F52" s="163" t="n">
         <v>-1517795</v>
       </c>
-      <c r="G52" s="154" t="n">
+      <c r="G52" s="163" t="n">
         <v>-1481706</v>
       </c>
-      <c r="H52" s="154" t="n">
+      <c r="H52" s="163" t="n">
         <v>-1772617</v>
       </c>
-      <c r="I52" s="154" t="n">
+      <c r="I52" s="163" t="n">
         <v>-2544381</v>
       </c>
-      <c r="J52" s="150">
+      <c r="J52" s="159">
         <f>I52+J20</f>
         <v/>
       </c>
-      <c r="K52" s="150">
+      <c r="K52" s="159">
         <f>J52+K20</f>
         <v/>
       </c>
-      <c r="L52" s="150">
+      <c r="L52" s="159">
         <f>K52+L20</f>
         <v/>
       </c>
-      <c r="M52" s="150">
+      <c r="M52" s="159">
         <f>L52+M20</f>
         <v/>
       </c>
-      <c r="N52" s="150">
+      <c r="N52" s="159">
         <f>M52+N20</f>
         <v/>
       </c>
@@ -8776,43 +9069,43 @@
           <t>Retained Earnings</t>
         </is>
       </c>
-      <c r="C53" s="157" t="inlineStr">
+      <c r="C53" s="166" t="inlineStr">
         <is>
           <t>eqn: PriorRE + EBT×(1−t)</t>
         </is>
       </c>
-      <c r="E53" s="154" t="n">
+      <c r="E53" s="163" t="n">
         <v>0</v>
       </c>
-      <c r="F53" s="154" t="n">
+      <c r="F53" s="163" t="n">
         <v>0</v>
       </c>
-      <c r="G53" s="154" t="n">
+      <c r="G53" s="163" t="n">
         <v>0</v>
       </c>
-      <c r="H53" s="154" t="n">
+      <c r="H53" s="163" t="n">
         <v>0</v>
       </c>
-      <c r="I53" s="154" t="n">
+      <c r="I53" s="163" t="n">
         <v>0</v>
       </c>
-      <c r="J53" s="150">
+      <c r="J53" s="159">
         <f>I53+J33*(1-J13)</f>
         <v/>
       </c>
-      <c r="K53" s="150">
+      <c r="K53" s="159">
         <f>J53+K33*(1-K13)</f>
         <v/>
       </c>
-      <c r="L53" s="150">
+      <c r="L53" s="159">
         <f>K53+L33*(1-L13)</f>
         <v/>
       </c>
-      <c r="M53" s="150">
+      <c r="M53" s="159">
         <f>L53+M33*(1-M13)</f>
         <v/>
       </c>
-      <c r="N53" s="150">
+      <c r="N53" s="159">
         <f>M53+N33*(1-N13)</f>
         <v/>
       </c>
@@ -8825,43 +9118,43 @@
       </c>
       <c r="C54" s="8" t="n"/>
       <c r="D54" s="26" t="n"/>
-      <c r="E54" s="163">
+      <c r="E54" s="172">
         <f>SUM(E52:E53)</f>
         <v/>
       </c>
-      <c r="F54" s="163">
+      <c r="F54" s="172">
         <f>SUM(F52:F53)</f>
         <v/>
       </c>
-      <c r="G54" s="163">
+      <c r="G54" s="172">
         <f>SUM(G52:G53)</f>
         <v/>
       </c>
-      <c r="H54" s="163">
+      <c r="H54" s="172">
         <f>SUM(H52:H53)</f>
         <v/>
       </c>
-      <c r="I54" s="163">
+      <c r="I54" s="172">
         <f>SUM(I52:I53)</f>
         <v/>
       </c>
-      <c r="J54" s="150">
+      <c r="J54" s="159">
         <f>SUM(J52:J53)</f>
         <v/>
       </c>
-      <c r="K54" s="150">
+      <c r="K54" s="159">
         <f>SUM(K52:K53)</f>
         <v/>
       </c>
-      <c r="L54" s="150">
+      <c r="L54" s="159">
         <f>SUM(L52:L53)</f>
         <v/>
       </c>
-      <c r="M54" s="150">
+      <c r="M54" s="159">
         <f>SUM(M52:M53)</f>
         <v/>
       </c>
-      <c r="N54" s="150">
+      <c r="N54" s="159">
         <f>SUM(N52:N53)</f>
         <v/>
       </c>
@@ -8874,43 +9167,43 @@
       </c>
       <c r="C55" s="39" t="n"/>
       <c r="D55" s="40" t="n"/>
-      <c r="E55" s="162">
+      <c r="E55" s="171">
         <f>E50+E54</f>
         <v/>
       </c>
-      <c r="F55" s="162">
+      <c r="F55" s="171">
         <f>F50+F54</f>
         <v/>
       </c>
-      <c r="G55" s="162">
+      <c r="G55" s="171">
         <f>G50+G54</f>
         <v/>
       </c>
-      <c r="H55" s="162">
+      <c r="H55" s="171">
         <f>H50+H54</f>
         <v/>
       </c>
-      <c r="I55" s="162">
+      <c r="I55" s="171">
         <f>I50+I54</f>
         <v/>
       </c>
-      <c r="J55" s="150">
+      <c r="J55" s="159">
         <f>J50+J54</f>
         <v/>
       </c>
-      <c r="K55" s="150">
+      <c r="K55" s="159">
         <f>K50+K54</f>
         <v/>
       </c>
-      <c r="L55" s="150">
+      <c r="L55" s="159">
         <f>L50+L54</f>
         <v/>
       </c>
-      <c r="M55" s="150">
+      <c r="M55" s="159">
         <f>M50+M54</f>
         <v/>
       </c>
-      <c r="N55" s="150">
+      <c r="N55" s="159">
         <f>N50+N54</f>
         <v/>
       </c>
@@ -8935,43 +9228,43 @@
       </c>
       <c r="C57" s="9" t="n"/>
       <c r="D57" s="27" t="n"/>
-      <c r="E57" s="164">
+      <c r="E57" s="173">
         <f>E55-E45</f>
         <v/>
       </c>
-      <c r="F57" s="164">
+      <c r="F57" s="173">
         <f>F55-F45</f>
         <v/>
       </c>
-      <c r="G57" s="164">
+      <c r="G57" s="173">
         <f>G55-G45</f>
         <v/>
       </c>
-      <c r="H57" s="164">
+      <c r="H57" s="173">
         <f>H55-H45</f>
         <v/>
       </c>
-      <c r="I57" s="164">
+      <c r="I57" s="173">
         <f>I55-I45</f>
         <v/>
       </c>
-      <c r="J57" s="150">
+      <c r="J57" s="159">
         <f>J55-J45</f>
         <v/>
       </c>
-      <c r="K57" s="150">
+      <c r="K57" s="159">
         <f>K55-K45</f>
         <v/>
       </c>
-      <c r="L57" s="150">
+      <c r="L57" s="159">
         <f>L55-L45</f>
         <v/>
       </c>
-      <c r="M57" s="150">
+      <c r="M57" s="159">
         <f>M55-M45</f>
         <v/>
       </c>
-      <c r="N57" s="150">
+      <c r="N57" s="159">
         <f>N55-N45</f>
         <v/>
       </c>
@@ -9035,48 +9328,48 @@
           <t>Net Earnings</t>
         </is>
       </c>
-      <c r="C62" s="157" t="inlineStr">
+      <c r="C62" s="166" t="inlineStr">
         <is>
           <t>eqn: EBT × (1 − tax%)  — full eqn, not pointer to IS</t>
         </is>
       </c>
-      <c r="E62" s="165">
+      <c r="E62" s="174">
         <f>E36</f>
         <v/>
       </c>
-      <c r="F62" s="165">
+      <c r="F62" s="174">
         <f>F36</f>
         <v/>
       </c>
-      <c r="G62" s="165">
+      <c r="G62" s="174">
         <f>G36</f>
         <v/>
       </c>
-      <c r="H62" s="165">
+      <c r="H62" s="174">
         <f>H36</f>
         <v/>
       </c>
-      <c r="I62" s="165">
+      <c r="I62" s="174">
         <f>I36</f>
         <v/>
       </c>
-      <c r="J62" s="150">
+      <c r="J62" s="159">
         <f>J33*(1-J13)</f>
         <v/>
       </c>
-      <c r="K62" s="150">
+      <c r="K62" s="159">
         <f>K33*(1-K13)</f>
         <v/>
       </c>
-      <c r="L62" s="150">
+      <c r="L62" s="159">
         <f>L33*(1-L13)</f>
         <v/>
       </c>
-      <c r="M62" s="150">
+      <c r="M62" s="159">
         <f>M33*(1-M13)</f>
         <v/>
       </c>
-      <c r="N62" s="150">
+      <c r="N62" s="159">
         <f>N33*(1-N13)</f>
         <v/>
       </c>
@@ -9087,48 +9380,48 @@
           <t>Plus: Depreciation &amp; Amortization</t>
         </is>
       </c>
-      <c r="C63" s="157" t="inlineStr">
+      <c r="C63" s="166" t="inlineStr">
         <is>
           <t>eqn: PPE_open × DA%</t>
         </is>
       </c>
-      <c r="E63" s="165">
+      <c r="E63" s="174">
         <f>+E30</f>
         <v/>
       </c>
-      <c r="F63" s="165">
+      <c r="F63" s="174">
         <f>+F30</f>
         <v/>
       </c>
-      <c r="G63" s="165">
+      <c r="G63" s="174">
         <f>+G30</f>
         <v/>
       </c>
-      <c r="H63" s="165">
+      <c r="H63" s="174">
         <f>+H30</f>
         <v/>
       </c>
-      <c r="I63" s="165">
+      <c r="I63" s="174">
         <f>+I30</f>
         <v/>
       </c>
-      <c r="J63" s="150">
+      <c r="J63" s="159">
         <f>J92*J11</f>
         <v/>
       </c>
-      <c r="K63" s="150">
+      <c r="K63" s="159">
         <f>K92*K11</f>
         <v/>
       </c>
-      <c r="L63" s="150">
+      <c r="L63" s="159">
         <f>L92*L11</f>
         <v/>
       </c>
-      <c r="M63" s="150">
+      <c r="M63" s="159">
         <f>M92*M11</f>
         <v/>
       </c>
-      <c r="N63" s="150">
+      <c r="N63" s="159">
         <f>N92*N11</f>
         <v/>
       </c>
@@ -9139,43 +9432,43 @@
           <t>Less: Changes in Working Capital</t>
         </is>
       </c>
-      <c r="C64" s="157" t="inlineStr">
+      <c r="C64" s="166" t="inlineStr">
         <is>
           <t>eqn: NWC_t − NWC_t−1</t>
         </is>
       </c>
-      <c r="E64" s="154" t="n">
+      <c r="E64" s="163" t="n">
         <v>0</v>
       </c>
-      <c r="F64" s="154" t="n">
+      <c r="F64" s="163" t="n">
         <v>-849</v>
       </c>
-      <c r="G64" s="154" t="n">
+      <c r="G64" s="163" t="n">
         <v>47116</v>
       </c>
-      <c r="H64" s="154" t="n">
+      <c r="H64" s="163" t="n">
         <v>15064</v>
       </c>
-      <c r="I64" s="154" t="n">
+      <c r="I64" s="163" t="n">
         <v>62189</v>
       </c>
-      <c r="J64" s="150">
+      <c r="J64" s="159">
         <f>J88-I88</f>
         <v/>
       </c>
-      <c r="K64" s="150">
+      <c r="K64" s="159">
         <f>K88-J88</f>
         <v/>
       </c>
-      <c r="L64" s="150">
+      <c r="L64" s="159">
         <f>L88-K88</f>
         <v/>
       </c>
-      <c r="M64" s="150">
+      <c r="M64" s="159">
         <f>M88-L88</f>
         <v/>
       </c>
-      <c r="N64" s="150">
+      <c r="N64" s="159">
         <f>N88-M88</f>
         <v/>
       </c>
@@ -9186,49 +9479,49 @@
           <t>Cash from Operations</t>
         </is>
       </c>
-      <c r="C65" s="155" t="inlineStr">
+      <c r="C65" s="164" t="inlineStr">
         <is>
           <t>eqn: NI + DA − ΔNWC</t>
         </is>
       </c>
       <c r="D65" s="28" t="n"/>
-      <c r="E65" s="156">
+      <c r="E65" s="165">
         <f>E62+E63-E64</f>
         <v/>
       </c>
-      <c r="F65" s="156">
+      <c r="F65" s="165">
         <f>F62+F63-F64</f>
         <v/>
       </c>
-      <c r="G65" s="156">
+      <c r="G65" s="165">
         <f>G62+G63-G64</f>
         <v/>
       </c>
-      <c r="H65" s="156">
+      <c r="H65" s="165">
         <f>H62+H63-H64</f>
         <v/>
       </c>
-      <c r="I65" s="156">
+      <c r="I65" s="165">
         <f>I62+I63-I64</f>
         <v/>
       </c>
-      <c r="J65" s="150">
+      <c r="J65" s="159">
         <f>J33*(1-J13)+J92*J11-(J88-I88)</f>
         <v/>
       </c>
-      <c r="K65" s="150">
+      <c r="K65" s="159">
         <f>K33*(1-K13)+K92*K11-(K88-J88)</f>
         <v/>
       </c>
-      <c r="L65" s="150">
+      <c r="L65" s="159">
         <f>L33*(1-L13)+L92*L11-(L88-K88)</f>
         <v/>
       </c>
-      <c r="M65" s="150">
+      <c r="M65" s="159">
         <f>M33*(1-M13)+M92*M11-(M88-L88)</f>
         <v/>
       </c>
-      <c r="N65" s="150">
+      <c r="N65" s="159">
         <f>N33*(1-N13)+N92*N11-(N88-M88)</f>
         <v/>
       </c>
@@ -9271,43 +9564,43 @@
           <t>Investments in Property &amp; Equipment</t>
         </is>
       </c>
-      <c r="C68" s="157" t="inlineStr">
+      <c r="C68" s="166" t="inlineStr">
         <is>
           <t>eqn: Rev × CapEx%</t>
         </is>
       </c>
-      <c r="E68" s="154" t="n">
+      <c r="E68" s="163" t="n">
         <v>7569</v>
       </c>
-      <c r="F68" s="154" t="n">
+      <c r="F68" s="163" t="n">
         <v>6029</v>
       </c>
-      <c r="G68" s="154" t="n">
+      <c r="G68" s="163" t="n">
         <v>4237</v>
       </c>
-      <c r="H68" s="154" t="n">
+      <c r="H68" s="163" t="n">
         <v>25551</v>
       </c>
-      <c r="I68" s="154" t="n">
+      <c r="I68" s="163" t="n">
         <v>39407</v>
       </c>
-      <c r="J68" s="150">
+      <c r="J68" s="159">
         <f>J24*J18</f>
         <v/>
       </c>
-      <c r="K68" s="150">
+      <c r="K68" s="159">
         <f>K24*K18</f>
         <v/>
       </c>
-      <c r="L68" s="150">
+      <c r="L68" s="159">
         <f>L24*L18</f>
         <v/>
       </c>
-      <c r="M68" s="150">
+      <c r="M68" s="159">
         <f>M24*M18</f>
         <v/>
       </c>
-      <c r="N68" s="150">
+      <c r="N68" s="159">
         <f>N24*N18</f>
         <v/>
       </c>
@@ -9320,43 +9613,43 @@
       </c>
       <c r="C69" s="5" t="n"/>
       <c r="D69" s="28" t="n"/>
-      <c r="E69" s="156">
+      <c r="E69" s="165">
         <f>SUM(E68)</f>
         <v/>
       </c>
-      <c r="F69" s="156">
+      <c r="F69" s="165">
         <f>SUM(F68)</f>
         <v/>
       </c>
-      <c r="G69" s="156">
+      <c r="G69" s="165">
         <f>SUM(G68)</f>
         <v/>
       </c>
-      <c r="H69" s="156">
+      <c r="H69" s="165">
         <f>SUM(H68)</f>
         <v/>
       </c>
-      <c r="I69" s="156">
+      <c r="I69" s="165">
         <f>SUM(I68)</f>
         <v/>
       </c>
-      <c r="J69" s="150">
+      <c r="J69" s="159">
         <f>J68</f>
         <v/>
       </c>
-      <c r="K69" s="150">
+      <c r="K69" s="159">
         <f>K68</f>
         <v/>
       </c>
-      <c r="L69" s="150">
+      <c r="L69" s="159">
         <f>L68</f>
         <v/>
       </c>
-      <c r="M69" s="150">
+      <c r="M69" s="159">
         <f>M68</f>
         <v/>
       </c>
-      <c r="N69" s="150">
+      <c r="N69" s="159">
         <f>N68</f>
         <v/>
       </c>
@@ -9399,38 +9692,38 @@
           <t>Issuance (repayment) of debt</t>
         </is>
       </c>
-      <c r="E72" s="154" t="n">
+      <c r="E72" s="163" t="n">
         <v>519583</v>
       </c>
-      <c r="F72" s="154" t="n">
+      <c r="F72" s="163" t="n">
         <v>594651</v>
       </c>
-      <c r="G72" s="154" t="n">
+      <c r="G72" s="163" t="n">
         <v>7989</v>
       </c>
-      <c r="H72" s="154" t="n">
+      <c r="H72" s="163" t="n">
         <v>347363</v>
       </c>
-      <c r="I72" s="154" t="n">
+      <c r="I72" s="163" t="n">
         <v>846670</v>
       </c>
-      <c r="J72" s="150">
+      <c r="J72" s="159">
         <f>J19</f>
         <v/>
       </c>
-      <c r="K72" s="150">
+      <c r="K72" s="159">
         <f>K19</f>
         <v/>
       </c>
-      <c r="L72" s="150">
+      <c r="L72" s="159">
         <f>L19</f>
         <v/>
       </c>
-      <c r="M72" s="150">
+      <c r="M72" s="159">
         <f>M19</f>
         <v/>
       </c>
-      <c r="N72" s="150">
+      <c r="N72" s="159">
         <f>N19</f>
         <v/>
       </c>
@@ -9441,38 +9734,38 @@
           <t>Issuance (repayment) of equity</t>
         </is>
       </c>
-      <c r="E73" s="154" t="n">
+      <c r="E73" s="163" t="n">
         <v>0</v>
       </c>
-      <c r="F73" s="154" t="n">
+      <c r="F73" s="163" t="n">
         <v>0</v>
       </c>
-      <c r="G73" s="154" t="n">
+      <c r="G73" s="163" t="n">
         <v>0</v>
       </c>
-      <c r="H73" s="154" t="n">
+      <c r="H73" s="163" t="n">
         <v>0</v>
       </c>
-      <c r="I73" s="154" t="n">
+      <c r="I73" s="163" t="n">
         <v>0</v>
       </c>
-      <c r="J73" s="150">
+      <c r="J73" s="159">
         <f>J20</f>
         <v/>
       </c>
-      <c r="K73" s="150">
+      <c r="K73" s="159">
         <f>K20</f>
         <v/>
       </c>
-      <c r="L73" s="150">
+      <c r="L73" s="159">
         <f>L20</f>
         <v/>
       </c>
-      <c r="M73" s="150">
+      <c r="M73" s="159">
         <f>M20</f>
         <v/>
       </c>
-      <c r="N73" s="150">
+      <c r="N73" s="159">
         <f>N20</f>
         <v/>
       </c>
@@ -9485,43 +9778,43 @@
       </c>
       <c r="C74" s="5" t="n"/>
       <c r="D74" s="28" t="n"/>
-      <c r="E74" s="156">
+      <c r="E74" s="165">
         <f>SUM(E72:E73)</f>
         <v/>
       </c>
-      <c r="F74" s="156">
+      <c r="F74" s="165">
         <f>SUM(F72:F73)</f>
         <v/>
       </c>
-      <c r="G74" s="156">
+      <c r="G74" s="165">
         <f>SUM(G72:G73)</f>
         <v/>
       </c>
-      <c r="H74" s="156">
+      <c r="H74" s="165">
         <f>SUM(H72:H73)</f>
         <v/>
       </c>
-      <c r="I74" s="156">
+      <c r="I74" s="165">
         <f>SUM(I72:I73)</f>
         <v/>
       </c>
-      <c r="J74" s="150">
+      <c r="J74" s="159">
         <f>J19+J20</f>
         <v/>
       </c>
-      <c r="K74" s="150">
+      <c r="K74" s="159">
         <f>K19+K20</f>
         <v/>
       </c>
-      <c r="L74" s="150">
+      <c r="L74" s="159">
         <f>L19+L20</f>
         <v/>
       </c>
-      <c r="M74" s="150">
+      <c r="M74" s="159">
         <f>M19+M20</f>
         <v/>
       </c>
-      <c r="N74" s="150">
+      <c r="N74" s="159">
         <f>N19+N20</f>
         <v/>
       </c>
@@ -9547,48 +9840,48 @@
           <t>Net Increase (decrease) in Cash</t>
         </is>
       </c>
-      <c r="C76" s="157" t="inlineStr">
+      <c r="C76" s="166" t="inlineStr">
         <is>
           <t>eqn: CFO − CapEx + Financing</t>
         </is>
       </c>
-      <c r="E76" s="166">
+      <c r="E76" s="175">
         <f>E41-E77</f>
         <v/>
       </c>
-      <c r="F76" s="166">
+      <c r="F76" s="175">
         <f>F41-F77</f>
         <v/>
       </c>
-      <c r="G76" s="166">
+      <c r="G76" s="175">
         <f>G41-G77</f>
         <v/>
       </c>
-      <c r="H76" s="166">
+      <c r="H76" s="175">
         <f>H41-H77</f>
         <v/>
       </c>
-      <c r="I76" s="166">
+      <c r="I76" s="175">
         <f>I41-I77</f>
         <v/>
       </c>
-      <c r="J76" s="150">
+      <c r="J76" s="159">
         <f>J65-J69+J74</f>
         <v/>
       </c>
-      <c r="K76" s="150">
+      <c r="K76" s="159">
         <f>K65-K69+K74</f>
         <v/>
       </c>
-      <c r="L76" s="150">
+      <c r="L76" s="159">
         <f>L65-L69+L74</f>
         <v/>
       </c>
-      <c r="M76" s="150">
+      <c r="M76" s="159">
         <f>M65-M69+M74</f>
         <v/>
       </c>
-      <c r="N76" s="150">
+      <c r="N76" s="159">
         <f>N65-N69+N74</f>
         <v/>
       </c>
@@ -9599,42 +9892,42 @@
           <t>Opening Cash Balance</t>
         </is>
       </c>
-      <c r="E77" s="154" t="n">
+      <c r="E77" s="163" t="n">
         <v>157394</v>
       </c>
-      <c r="F77" s="166">
+      <c r="F77" s="175">
         <f>E41</f>
         <v/>
       </c>
-      <c r="G77" s="166">
+      <c r="G77" s="175">
         <f>F41</f>
         <v/>
       </c>
-      <c r="H77" s="166">
+      <c r="H77" s="175">
         <f>G41</f>
         <v/>
       </c>
-      <c r="I77" s="166">
+      <c r="I77" s="175">
         <f>H41</f>
         <v/>
       </c>
-      <c r="J77" s="150">
+      <c r="J77" s="159">
         <f>I41</f>
         <v/>
       </c>
-      <c r="K77" s="150">
+      <c r="K77" s="159">
         <f>J41</f>
         <v/>
       </c>
-      <c r="L77" s="150">
+      <c r="L77" s="159">
         <f>K41</f>
         <v/>
       </c>
-      <c r="M77" s="150">
+      <c r="M77" s="159">
         <f>L41</f>
         <v/>
       </c>
-      <c r="N77" s="150">
+      <c r="N77" s="159">
         <f>M41</f>
         <v/>
       </c>
@@ -9646,46 +9939,46 @@
         </is>
       </c>
       <c r="C78" s="5" t="n"/>
-      <c r="D78" s="167" t="n">
+      <c r="D78" s="176" t="n">
         <v>157394</v>
       </c>
-      <c r="E78" s="156">
+      <c r="E78" s="165">
         <f>SUM(E76:E77)</f>
         <v/>
       </c>
-      <c r="F78" s="156">
+      <c r="F78" s="165">
         <f>SUM(F76:F77)</f>
         <v/>
       </c>
-      <c r="G78" s="156">
+      <c r="G78" s="165">
         <f>SUM(G76:G77)</f>
         <v/>
       </c>
-      <c r="H78" s="156">
+      <c r="H78" s="165">
         <f>SUM(H76:H77)</f>
         <v/>
       </c>
-      <c r="I78" s="156">
+      <c r="I78" s="165">
         <f>SUM(I76:I77)</f>
         <v/>
       </c>
-      <c r="J78" s="150">
+      <c r="J78" s="159">
         <f>J77+J76</f>
         <v/>
       </c>
-      <c r="K78" s="150">
+      <c r="K78" s="159">
         <f>K77+K76</f>
         <v/>
       </c>
-      <c r="L78" s="150">
+      <c r="L78" s="159">
         <f>L77+L76</f>
         <v/>
       </c>
-      <c r="M78" s="150">
+      <c r="M78" s="159">
         <f>M77+M76</f>
         <v/>
       </c>
-      <c r="N78" s="150">
+      <c r="N78" s="159">
         <f>N77+N76</f>
         <v/>
       </c>
@@ -9706,43 +9999,43 @@
       </c>
       <c r="C80" s="9" t="n"/>
       <c r="D80" s="27" t="n"/>
-      <c r="E80" s="164">
+      <c r="E80" s="173">
         <f>E78-E41</f>
         <v/>
       </c>
-      <c r="F80" s="164">
+      <c r="F80" s="173">
         <f>F78-F41</f>
         <v/>
       </c>
-      <c r="G80" s="164">
+      <c r="G80" s="173">
         <f>G78-G41</f>
         <v/>
       </c>
-      <c r="H80" s="164">
+      <c r="H80" s="173">
         <f>H78-H41</f>
         <v/>
       </c>
-      <c r="I80" s="164">
+      <c r="I80" s="173">
         <f>I78-I41</f>
         <v/>
       </c>
-      <c r="J80" s="150">
+      <c r="J80" s="159">
         <f>J78-J41</f>
         <v/>
       </c>
-      <c r="K80" s="150">
+      <c r="K80" s="159">
         <f>K78-K41</f>
         <v/>
       </c>
-      <c r="L80" s="150">
+      <c r="L80" s="159">
         <f>L78-L41</f>
         <v/>
       </c>
-      <c r="M80" s="150">
+      <c r="M80" s="159">
         <f>M78-M41</f>
         <v/>
       </c>
-      <c r="N80" s="150">
+      <c r="N80" s="159">
         <f>N78-N41</f>
         <v/>
       </c>
@@ -9798,38 +10091,38 @@
           <t>Accounts Receivable</t>
         </is>
       </c>
-      <c r="E85" s="154" t="n">
+      <c r="E85" s="163" t="n">
         <v>206690</v>
       </c>
-      <c r="F85" s="154" t="n">
+      <c r="F85" s="163" t="n">
         <v>202365</v>
       </c>
-      <c r="G85" s="154" t="n">
+      <c r="G85" s="163" t="n">
         <v>251217</v>
       </c>
-      <c r="H85" s="154" t="n">
+      <c r="H85" s="163" t="n">
         <v>269745</v>
       </c>
-      <c r="I85" s="154" t="n">
+      <c r="I85" s="163" t="n">
         <v>341776</v>
       </c>
-      <c r="J85" s="150">
+      <c r="J85" s="159">
         <f>J42</f>
         <v/>
       </c>
-      <c r="K85" s="150">
+      <c r="K85" s="159">
         <f>K42</f>
         <v/>
       </c>
-      <c r="L85" s="150">
+      <c r="L85" s="159">
         <f>L42</f>
         <v/>
       </c>
-      <c r="M85" s="150">
+      <c r="M85" s="159">
         <f>M42</f>
         <v/>
       </c>
-      <c r="N85" s="150">
+      <c r="N85" s="159">
         <f>N42</f>
         <v/>
       </c>
@@ -9840,38 +10133,38 @@
           <t>Inventory</t>
         </is>
       </c>
-      <c r="E86" s="154" t="n">
+      <c r="E86" s="163" t="n">
         <v>0</v>
       </c>
-      <c r="F86" s="154" t="n">
+      <c r="F86" s="163" t="n">
         <v>0</v>
       </c>
-      <c r="G86" s="154" t="n">
+      <c r="G86" s="163" t="n">
         <v>0</v>
       </c>
-      <c r="H86" s="154" t="n">
+      <c r="H86" s="163" t="n">
         <v>0</v>
       </c>
-      <c r="I86" s="154" t="n">
+      <c r="I86" s="163" t="n">
         <v>0</v>
       </c>
-      <c r="J86" s="150">
+      <c r="J86" s="159">
         <f>J43</f>
         <v/>
       </c>
-      <c r="K86" s="150">
+      <c r="K86" s="159">
         <f>K43</f>
         <v/>
       </c>
-      <c r="L86" s="150">
+      <c r="L86" s="159">
         <f>L43</f>
         <v/>
       </c>
-      <c r="M86" s="150">
+      <c r="M86" s="159">
         <f>M43</f>
         <v/>
       </c>
-      <c r="N86" s="150">
+      <c r="N86" s="159">
         <f>N43</f>
         <v/>
       </c>
@@ -9882,38 +10175,38 @@
           <t>Accounts Payable</t>
         </is>
       </c>
-      <c r="E87" s="154" t="n">
+      <c r="E87" s="163" t="n">
         <v>20749</v>
       </c>
-      <c r="F87" s="154" t="n">
+      <c r="F87" s="163" t="n">
         <v>17273</v>
       </c>
-      <c r="G87" s="154" t="n">
+      <c r="G87" s="163" t="n">
         <v>19009</v>
       </c>
-      <c r="H87" s="154" t="n">
+      <c r="H87" s="163" t="n">
         <v>22473</v>
       </c>
-      <c r="I87" s="154" t="n">
+      <c r="I87" s="163" t="n">
         <v>32315</v>
       </c>
-      <c r="J87" s="150">
+      <c r="J87" s="159">
         <f>J48</f>
         <v/>
       </c>
-      <c r="K87" s="150">
+      <c r="K87" s="159">
         <f>K48</f>
         <v/>
       </c>
-      <c r="L87" s="150">
+      <c r="L87" s="159">
         <f>L48</f>
         <v/>
       </c>
-      <c r="M87" s="150">
+      <c r="M87" s="159">
         <f>M48</f>
         <v/>
       </c>
-      <c r="N87" s="150">
+      <c r="N87" s="159">
         <f>N48</f>
         <v/>
       </c>
@@ -9925,46 +10218,46 @@
         </is>
       </c>
       <c r="C88" s="5" t="n"/>
-      <c r="D88" s="167" t="n">
+      <c r="D88" s="176" t="n">
         <v>205747</v>
       </c>
-      <c r="E88" s="168">
+      <c r="E88" s="177">
         <f>E85+E86-E87</f>
         <v/>
       </c>
-      <c r="F88" s="168">
+      <c r="F88" s="177">
         <f>F85+F86-F87</f>
         <v/>
       </c>
-      <c r="G88" s="168">
+      <c r="G88" s="177">
         <f>G85+G86-G87</f>
         <v/>
       </c>
-      <c r="H88" s="168">
+      <c r="H88" s="177">
         <f>H85+H86-H87</f>
         <v/>
       </c>
-      <c r="I88" s="168">
+      <c r="I88" s="177">
         <f>I85+I86-I87</f>
         <v/>
       </c>
-      <c r="J88" s="150">
+      <c r="J88" s="159">
         <f>J85+J86-J87</f>
         <v/>
       </c>
-      <c r="K88" s="150">
+      <c r="K88" s="159">
         <f>K85+K86-K87</f>
         <v/>
       </c>
-      <c r="L88" s="150">
+      <c r="L88" s="159">
         <f>L85+L86-L87</f>
         <v/>
       </c>
-      <c r="M88" s="150">
+      <c r="M88" s="159">
         <f>M85+M86-M87</f>
         <v/>
       </c>
-      <c r="N88" s="150">
+      <c r="N88" s="159">
         <f>N85+N86-N87</f>
         <v/>
       </c>
@@ -9975,43 +10268,43 @@
           <t>Change in NWC</t>
         </is>
       </c>
-      <c r="E89" s="147">
+      <c r="E89" s="156">
         <f>E88-D88</f>
         <v/>
       </c>
-      <c r="F89" s="147">
+      <c r="F89" s="156">
         <f>F88-E88</f>
         <v/>
       </c>
-      <c r="G89" s="147">
+      <c r="G89" s="156">
         <f>G88-F88</f>
         <v/>
       </c>
-      <c r="H89" s="147">
+      <c r="H89" s="156">
         <f>H88-G88</f>
         <v/>
       </c>
-      <c r="I89" s="147">
+      <c r="I89" s="156">
         <f>I88-H88</f>
         <v/>
       </c>
-      <c r="J89" s="150">
+      <c r="J89" s="159">
         <f>J88-I88</f>
         <v/>
       </c>
-      <c r="K89" s="150">
+      <c r="K89" s="159">
         <f>K88-J88</f>
         <v/>
       </c>
-      <c r="L89" s="150">
+      <c r="L89" s="159">
         <f>L88-K88</f>
         <v/>
       </c>
-      <c r="M89" s="150">
+      <c r="M89" s="159">
         <f>M88-L88</f>
         <v/>
       </c>
-      <c r="N89" s="150">
+      <c r="N89" s="159">
         <f>N88-M88</f>
         <v/>
       </c>
@@ -10041,42 +10334,42 @@
           <t>PPE Opening</t>
         </is>
       </c>
-      <c r="E92" s="154" t="n">
+      <c r="E92" s="163" t="n">
         <v>46419</v>
       </c>
-      <c r="F92" s="166">
+      <c r="F92" s="175">
         <f>E95</f>
         <v/>
       </c>
-      <c r="G92" s="166">
+      <c r="G92" s="175">
         <f>F95</f>
         <v/>
       </c>
-      <c r="H92" s="166">
+      <c r="H92" s="175">
         <f>G95</f>
         <v/>
       </c>
-      <c r="I92" s="166">
+      <c r="I92" s="175">
         <f>H95</f>
         <v/>
       </c>
-      <c r="J92" s="150">
+      <c r="J92" s="159">
         <f>I44</f>
         <v/>
       </c>
-      <c r="K92" s="150">
+      <c r="K92" s="159">
         <f>J95</f>
         <v/>
       </c>
-      <c r="L92" s="150">
+      <c r="L92" s="159">
         <f>K95</f>
         <v/>
       </c>
-      <c r="M92" s="150">
+      <c r="M92" s="159">
         <f>L95</f>
         <v/>
       </c>
-      <c r="N92" s="150">
+      <c r="N92" s="159">
         <f>M95</f>
         <v/>
       </c>
@@ -10087,38 +10380,38 @@
           <t>Plus Capex</t>
         </is>
       </c>
-      <c r="E93" s="154" t="n">
+      <c r="E93" s="163" t="n">
         <v>7569</v>
       </c>
-      <c r="F93" s="154" t="n">
+      <c r="F93" s="163" t="n">
         <v>6029</v>
       </c>
-      <c r="G93" s="154" t="n">
+      <c r="G93" s="163" t="n">
         <v>4237</v>
       </c>
-      <c r="H93" s="154" t="n">
+      <c r="H93" s="163" t="n">
         <v>25551</v>
       </c>
-      <c r="I93" s="154" t="n">
+      <c r="I93" s="163" t="n">
         <v>39407</v>
       </c>
-      <c r="J93" s="150">
+      <c r="J93" s="159">
         <f>J24*J18</f>
         <v/>
       </c>
-      <c r="K93" s="150">
+      <c r="K93" s="159">
         <f>K24*K18</f>
         <v/>
       </c>
-      <c r="L93" s="150">
+      <c r="L93" s="159">
         <f>L24*L18</f>
         <v/>
       </c>
-      <c r="M93" s="150">
+      <c r="M93" s="159">
         <f>M24*M18</f>
         <v/>
       </c>
-      <c r="N93" s="150">
+      <c r="N93" s="159">
         <f>N24*N18</f>
         <v/>
       </c>
@@ -10129,38 +10422,38 @@
           <t>Less Depreciation</t>
         </is>
       </c>
-      <c r="E94" s="154" t="n">
+      <c r="E94" s="163" t="n">
         <v>25592</v>
       </c>
-      <c r="F94" s="154" t="n">
+      <c r="F94" s="163" t="n">
         <v>20465</v>
       </c>
-      <c r="G94" s="154" t="n">
+      <c r="G94" s="163" t="n">
         <v>14638</v>
       </c>
-      <c r="H94" s="154" t="n">
+      <c r="H94" s="163" t="n">
         <v>13827</v>
       </c>
-      <c r="I94" s="154" t="n">
+      <c r="I94" s="163" t="n">
         <v>14952</v>
       </c>
-      <c r="J94" s="150">
+      <c r="J94" s="159">
         <f>J92*J11</f>
         <v/>
       </c>
-      <c r="K94" s="150">
+      <c r="K94" s="159">
         <f>K92*K11</f>
         <v/>
       </c>
-      <c r="L94" s="150">
+      <c r="L94" s="159">
         <f>L92*L11</f>
         <v/>
       </c>
-      <c r="M94" s="150">
+      <c r="M94" s="159">
         <f>M92*M11</f>
         <v/>
       </c>
-      <c r="N94" s="150">
+      <c r="N94" s="159">
         <f>N92*N11</f>
         <v/>
       </c>
@@ -10173,38 +10466,38 @@
       </c>
       <c r="C95" s="5" t="n"/>
       <c r="D95" s="28" t="n"/>
-      <c r="E95" s="169" t="n">
+      <c r="E95" s="178" t="n">
         <v>27913</v>
       </c>
-      <c r="F95" s="169" t="n">
+      <c r="F95" s="178" t="n">
         <v>17580</v>
       </c>
-      <c r="G95" s="169" t="n">
+      <c r="G95" s="178" t="n">
         <v>10966</v>
       </c>
-      <c r="H95" s="169" t="n">
+      <c r="H95" s="178" t="n">
         <v>38465</v>
       </c>
-      <c r="I95" s="169" t="n">
+      <c r="I95" s="178" t="n">
         <v>67713</v>
       </c>
-      <c r="J95" s="150">
+      <c r="J95" s="159">
         <f>J92+J93-J94</f>
         <v/>
       </c>
-      <c r="K95" s="150">
+      <c r="K95" s="159">
         <f>K92+K93-K94</f>
         <v/>
       </c>
-      <c r="L95" s="150">
+      <c r="L95" s="159">
         <f>L92+L93-L94</f>
         <v/>
       </c>
-      <c r="M95" s="150">
+      <c r="M95" s="159">
         <f>M92+M93-M94</f>
         <v/>
       </c>
-      <c r="N95" s="150">
+      <c r="N95" s="159">
         <f>N92+N93-N94</f>
         <v/>
       </c>
@@ -10239,42 +10532,42 @@
           <t>Debt Opening</t>
         </is>
       </c>
-      <c r="E98" s="154" t="n">
+      <c r="E98" s="163" t="n">
         <v>739435</v>
       </c>
-      <c r="F98" s="166">
+      <c r="F98" s="175">
         <f>E100</f>
         <v/>
       </c>
-      <c r="G98" s="166">
+      <c r="G98" s="175">
         <f>F100</f>
         <v/>
       </c>
-      <c r="H98" s="166">
+      <c r="H98" s="175">
         <f>G100</f>
         <v/>
       </c>
-      <c r="I98" s="166">
+      <c r="I98" s="175">
         <f>H100</f>
         <v/>
       </c>
-      <c r="J98" s="150">
+      <c r="J98" s="159">
         <f>I49</f>
         <v/>
       </c>
-      <c r="K98" s="150">
+      <c r="K98" s="159">
         <f>J100</f>
         <v/>
       </c>
-      <c r="L98" s="150">
+      <c r="L98" s="159">
         <f>K100</f>
         <v/>
       </c>
-      <c r="M98" s="150">
+      <c r="M98" s="159">
         <f>L100</f>
         <v/>
       </c>
-      <c r="N98" s="150">
+      <c r="N98" s="159">
         <f>M100</f>
         <v/>
       </c>
@@ -10285,38 +10578,38 @@
           <t>Issuance (repayment)</t>
         </is>
       </c>
-      <c r="E99" s="154" t="n">
+      <c r="E99" s="163" t="n">
         <v>519583</v>
       </c>
-      <c r="F99" s="154" t="n">
+      <c r="F99" s="163" t="n">
         <v>594651</v>
       </c>
-      <c r="G99" s="154" t="n">
+      <c r="G99" s="163" t="n">
         <v>7989</v>
       </c>
-      <c r="H99" s="154" t="n">
+      <c r="H99" s="163" t="n">
         <v>347363</v>
       </c>
-      <c r="I99" s="154" t="n">
+      <c r="I99" s="163" t="n">
         <v>846670</v>
       </c>
-      <c r="J99" s="150">
+      <c r="J99" s="159">
         <f>J19</f>
         <v/>
       </c>
-      <c r="K99" s="150">
+      <c r="K99" s="159">
         <f>K19</f>
         <v/>
       </c>
-      <c r="L99" s="150">
+      <c r="L99" s="159">
         <f>L19</f>
         <v/>
       </c>
-      <c r="M99" s="150">
+      <c r="M99" s="159">
         <f>M19</f>
         <v/>
       </c>
-      <c r="N99" s="150">
+      <c r="N99" s="159">
         <f>N19</f>
         <v/>
       </c>
@@ -10329,38 +10622,38 @@
       </c>
       <c r="C100" s="5" t="n"/>
       <c r="D100" s="28" t="n"/>
-      <c r="E100" s="169" t="n">
+      <c r="E100" s="178" t="n">
         <v>1259018</v>
       </c>
-      <c r="F100" s="169" t="n">
+      <c r="F100" s="178" t="n">
         <v>1853669</v>
       </c>
-      <c r="G100" s="169" t="n">
+      <c r="G100" s="178" t="n">
         <v>1861658</v>
       </c>
-      <c r="H100" s="169" t="n">
+      <c r="H100" s="178" t="n">
         <v>2209021</v>
       </c>
-      <c r="I100" s="169" t="n">
+      <c r="I100" s="178" t="n">
         <v>3055691</v>
       </c>
-      <c r="J100" s="150">
+      <c r="J100" s="159">
         <f>J98+J99</f>
         <v/>
       </c>
-      <c r="K100" s="150">
+      <c r="K100" s="159">
         <f>K98+K99</f>
         <v/>
       </c>
-      <c r="L100" s="150">
+      <c r="L100" s="159">
         <f>L98+L99</f>
         <v/>
       </c>
-      <c r="M100" s="150">
+      <c r="M100" s="159">
         <f>M98+M99</f>
         <v/>
       </c>
-      <c r="N100" s="150">
+      <c r="N100" s="159">
         <f>N98+N99</f>
         <v/>
       </c>
@@ -10371,38 +10664,38 @@
           <t>Interest Expense</t>
         </is>
       </c>
-      <c r="E101" s="154" t="n">
+      <c r="E101" s="163" t="n">
         <v>40092</v>
       </c>
-      <c r="F101" s="154" t="n">
+      <c r="F101" s="163" t="n">
         <v>68967</v>
       </c>
-      <c r="G101" s="154" t="n">
+      <c r="G101" s="163" t="n">
         <v>95546</v>
       </c>
-      <c r="H101" s="154" t="n">
+      <c r="H101" s="163" t="n">
         <v>105638</v>
       </c>
-      <c r="I101" s="154" t="n">
+      <c r="I101" s="163" t="n">
         <v>133647</v>
       </c>
-      <c r="J101" s="150">
+      <c r="J101" s="159">
         <f>J98*J12</f>
         <v/>
       </c>
-      <c r="K101" s="150">
+      <c r="K101" s="159">
         <f>K98*K12</f>
         <v/>
       </c>
-      <c r="L101" s="150">
+      <c r="L101" s="159">
         <f>L98*L12</f>
         <v/>
       </c>
-      <c r="M101" s="150">
+      <c r="M101" s="159">
         <f>M98*M12</f>
         <v/>
       </c>
-      <c r="N101" s="150">
+      <c r="N101" s="159">
         <f>N98*N12</f>
         <v/>
       </c>
@@ -10808,9 +11101,9 @@
       <c r="L2" s="96" t="n"/>
       <c r="M2" s="94" t="n"/>
       <c r="N2" s="94" t="n"/>
-      <c r="Q2" s="170" t="inlineStr">
-        <is>
-          <t>vengeanceaiUSCMODEL4 — LIVE EQUATIONS + SOURCE LINKS</t>
+      <c r="Q2" s="179" t="inlineStr">
+        <is>
+          <t>vengeanceaiUSCMODEL5 — LIVE EQUATIONS + SOURCE LINKS</t>
         </is>
       </c>
     </row>
@@ -10830,7 +11123,7 @@
       <c r="M3" s="97" t="n"/>
       <c r="N3" s="97" t="n"/>
       <c r="O3" s="97" t="n"/>
-      <c r="Q3" s="171" t="inlineStr">
+      <c r="Q3" s="180" t="inlineStr">
         <is>
           <t>Yellow = inputs (edit). Green = formulas. Blue underlined = clickable sources.</t>
         </is>
@@ -10856,32 +11149,32 @@
       <c r="M4" s="97" t="n"/>
       <c r="N4" s="97" t="n"/>
       <c r="O4" s="97" t="n"/>
-      <c r="Q4" s="172" t="inlineStr">
+      <c r="Q4" s="181" t="inlineStr">
         <is>
           <t>Input</t>
         </is>
       </c>
-      <c r="R4" s="172" t="inlineStr">
+      <c r="R4" s="181" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="S4" s="172" t="inlineStr">
+      <c r="S4" s="181" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="T4" s="172" t="inlineStr">
+      <c r="T4" s="181" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="U4" s="172" t="inlineStr">
+      <c r="U4" s="181" t="inlineStr">
         <is>
           <t>Primary source (click)</t>
         </is>
       </c>
-      <c r="V4" s="172" t="inlineStr">
+      <c r="V4" s="181" t="inlineStr">
         <is>
           <t>Secondary source (click)</t>
         </is>
@@ -10895,10 +11188,10 @@
         </is>
       </c>
       <c r="C5" s="100" t="n"/>
-      <c r="D5" s="173" t="n">
+      <c r="D5" s="182" t="n">
         <v>0.1877023903712333</v>
       </c>
-      <c r="E5" s="174" t="inlineStr">
+      <c r="E5" s="183" t="inlineStr">
         <is>
           <t>Tax source: SEC 10-K</t>
         </is>
@@ -10913,14 +11206,14 @@
       <c r="M5" s="97" t="n"/>
       <c r="N5" s="97" t="n"/>
       <c r="O5" s="97" t="n"/>
-      <c r="Q5" s="137" t="inlineStr">
+      <c r="Q5" s="146" t="inlineStr">
         <is>
           <t>1) CAPM → WACC   (D6 = R15)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="175" t="inlineStr">
+      <c r="A6" s="184" t="inlineStr">
         <is>
           <t>WACC sources → columns U–V</t>
         </is>
@@ -10930,26 +11223,26 @@
           <t>Discount Rate (WACC = We×Ke + Wd×Rd(1−t))</t>
         </is>
       </c>
-      <c r="C6" s="176" t="inlineStr">
+      <c r="C6" s="185" t="inlineStr">
         <is>
           <t>Sources →</t>
         </is>
       </c>
-      <c r="D6" s="177">
+      <c r="D6" s="186">
         <f>R15</f>
         <v/>
       </c>
-      <c r="E6" s="174" t="inlineStr">
+      <c r="E6" s="183" t="inlineStr">
         <is>
           <t>WACC sources → scroll to col U (Rf/ERP/β/Rd links)</t>
         </is>
       </c>
-      <c r="F6" s="174" t="inlineStr">
+      <c r="F6" s="183" t="inlineStr">
         <is>
           <t>Damodaran ERP</t>
         </is>
       </c>
-      <c r="G6" s="174" t="inlineStr">
+      <c r="G6" s="183" t="inlineStr">
         <is>
           <t>SEC 8-K Rd 6.250%</t>
         </is>
@@ -10962,30 +11255,30 @@
       <c r="M6" s="97" t="n"/>
       <c r="N6" s="97" t="n"/>
       <c r="O6" s="97" t="n"/>
-      <c r="Q6" s="178" t="inlineStr">
+      <c r="Q6" s="187" t="inlineStr">
         <is>
           <t>Risk-free rate (Rf)</t>
         </is>
       </c>
-      <c r="R6" s="179" t="n">
+      <c r="R6" s="188" t="n">
         <v>0.0463</v>
       </c>
-      <c r="S6" s="178" t="inlineStr">
+      <c r="S6" s="187" t="inlineStr">
         <is>
           <t>US 10Y Treasury yield</t>
         </is>
       </c>
-      <c r="T6" s="178" t="inlineStr">
+      <c r="T6" s="187" t="inlineStr">
         <is>
           <t>CAPM input</t>
         </is>
       </c>
-      <c r="U6" s="180" t="inlineStr">
+      <c r="U6" s="189" t="inlineStr">
         <is>
           <t>FRED DGS10 (US 10Y)</t>
         </is>
       </c>
-      <c r="V6" s="180" t="inlineStr">
+      <c r="V6" s="189" t="inlineStr">
         <is>
           <t>US Treasury Daily Par Yield Curve</t>
         </is>
@@ -10999,7 +11292,7 @@
         </is>
       </c>
       <c r="C7" s="97" t="n"/>
-      <c r="D7" s="173" t="n">
+      <c r="D7" s="182" t="n">
         <v>0.03</v>
       </c>
       <c r="E7" s="97" t="n"/>
@@ -11013,30 +11306,30 @@
       <c r="M7" s="97" t="n"/>
       <c r="N7" s="97" t="n"/>
       <c r="O7" s="97" t="n"/>
-      <c r="Q7" s="178" t="inlineStr">
+      <c r="Q7" s="187" t="inlineStr">
         <is>
           <t>Equity risk premium (ERP)</t>
         </is>
       </c>
-      <c r="R7" s="179" t="n">
+      <c r="R7" s="188" t="n">
         <v>0.0428</v>
       </c>
-      <c r="S7" s="178" t="inlineStr">
+      <c r="S7" s="187" t="inlineStr">
         <is>
           <t>Damodaran implied ERP</t>
         </is>
       </c>
-      <c r="T7" s="178" t="inlineStr">
+      <c r="T7" s="187" t="inlineStr">
         <is>
           <t>CAPM input</t>
         </is>
       </c>
-      <c r="U7" s="180" t="inlineStr">
+      <c r="U7" s="189" t="inlineStr">
         <is>
           <t>Damodaran Online — Implied ERP</t>
         </is>
       </c>
-      <c r="V7" s="180" t="inlineStr">
+      <c r="V7" s="189" t="inlineStr">
         <is>
           <t>Damodaran histimpl.xls / table</t>
         </is>
@@ -11050,10 +11343,10 @@
         </is>
       </c>
       <c r="C8" s="97" t="n"/>
-      <c r="D8" s="181" t="n">
+      <c r="D8" s="190" t="n">
         <v>25</v>
       </c>
-      <c r="E8" s="174" t="inlineStr">
+      <c r="E8" s="183" t="inlineStr">
         <is>
           <t>Rd source: SEC 8-K 6.250% notes</t>
         </is>
@@ -11068,30 +11361,30 @@
       <c r="M8" s="97" t="n"/>
       <c r="N8" s="97" t="n"/>
       <c r="O8" s="97" t="n"/>
-      <c r="Q8" s="178" t="inlineStr">
+      <c r="Q8" s="187" t="inlineStr">
         <is>
           <t>Beta (β)</t>
         </is>
       </c>
-      <c r="R8" s="182" t="n">
+      <c r="R8" s="191" t="n">
         <v>1.32</v>
       </c>
-      <c r="S8" s="178" t="inlineStr">
+      <c r="S8" s="187" t="inlineStr">
         <is>
           <t>Yahoo 5Y monthly beta</t>
         </is>
       </c>
-      <c r="T8" s="178" t="inlineStr">
+      <c r="T8" s="187" t="inlineStr">
         <is>
           <t>CAPM input</t>
         </is>
       </c>
-      <c r="U8" s="180" t="inlineStr">
+      <c r="U8" s="189" t="inlineStr">
         <is>
           <t>Yahoo Finance FICO Key Statistics</t>
         </is>
       </c>
-      <c r="V8" s="180" t="inlineStr">
+      <c r="V8" s="189" t="inlineStr">
         <is>
           <t>Yahoo Finance FICO quote</t>
         </is>
@@ -11105,7 +11398,7 @@
         </is>
       </c>
       <c r="C9" s="97" t="n"/>
-      <c r="D9" s="183" t="n">
+      <c r="D9" s="192" t="n">
         <v>45930</v>
       </c>
       <c r="E9" s="97" t="n"/>
@@ -11119,31 +11412,31 @@
       <c r="M9" s="97" t="n"/>
       <c r="N9" s="97" t="n"/>
       <c r="O9" s="97" t="n"/>
-      <c r="Q9" s="184" t="inlineStr">
+      <c r="Q9" s="193" t="inlineStr">
         <is>
           <t>Ke = Rf + β × ERP</t>
         </is>
       </c>
-      <c r="R9" s="185">
+      <c r="R9" s="194">
         <f>R6+R8*R7</f>
         <v/>
       </c>
-      <c r="S9" s="178" t="inlineStr">
+      <c r="S9" s="187" t="inlineStr">
         <is>
           <t>Cost of equity (CAPM)</t>
         </is>
       </c>
-      <c r="T9" s="184" t="inlineStr">
+      <c r="T9" s="193" t="inlineStr">
         <is>
           <t>→ WACC</t>
         </is>
       </c>
-      <c r="U9" s="178" t="inlineStr">
+      <c r="U9" s="187" t="inlineStr">
         <is>
           <t>Derived: R6 + R8 × R7</t>
         </is>
       </c>
-      <c r="V9" s="178" t="inlineStr"/>
+      <c r="V9" s="187" t="inlineStr"/>
     </row>
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="97" t="n"/>
@@ -11153,7 +11446,7 @@
         </is>
       </c>
       <c r="C10" s="97" t="n"/>
-      <c r="D10" s="183" t="n">
+      <c r="D10" s="192" t="n">
         <v>46295</v>
       </c>
       <c r="E10" s="97" t="n"/>
@@ -11167,30 +11460,30 @@
       <c r="M10" s="97" t="n"/>
       <c r="N10" s="97" t="n"/>
       <c r="O10" s="97" t="n"/>
-      <c r="Q10" s="178" t="inlineStr">
+      <c r="Q10" s="187" t="inlineStr">
         <is>
           <t>Pre-tax cost of debt (Rd)</t>
         </is>
       </c>
-      <c r="R10" s="179" t="n">
+      <c r="R10" s="188" t="n">
         <v>0.0625</v>
       </c>
-      <c r="S10" s="178" t="inlineStr">
+      <c r="S10" s="187" t="inlineStr">
         <is>
           <t>6.250% Senior Notes due 2034</t>
         </is>
       </c>
-      <c r="T10" s="178" t="inlineStr">
+      <c r="T10" s="187" t="inlineStr">
         <is>
           <t>WACC input</t>
         </is>
       </c>
-      <c r="U10" s="180" t="inlineStr">
+      <c r="U10" s="189" t="inlineStr">
         <is>
           <t>SEC 8-K — Notes closing (6.250%)</t>
         </is>
       </c>
-      <c r="V10" s="180" t="inlineStr">
+      <c r="V10" s="189" t="inlineStr">
         <is>
           <t>SEC EX-99.1 — Notes pricing press release</t>
         </is>
@@ -11204,7 +11497,7 @@
         </is>
       </c>
       <c r="C11" s="97" t="n"/>
-      <c r="D11" s="186" t="n">
+      <c r="D11" s="195" t="n">
         <v>1046.23</v>
       </c>
       <c r="E11" s="97" t="n"/>
@@ -11218,31 +11511,31 @@
       <c r="M11" s="97" t="n"/>
       <c r="N11" s="97" t="n"/>
       <c r="O11" s="97" t="n"/>
-      <c r="Q11" s="178" t="inlineStr">
+      <c r="Q11" s="187" t="inlineStr">
         <is>
           <t>Tax rate (t)</t>
         </is>
       </c>
-      <c r="R11" s="185">
+      <c r="R11" s="194">
         <f>$D$5</f>
         <v/>
       </c>
-      <c r="S11" s="178" t="inlineStr">
+      <c r="S11" s="187" t="inlineStr">
         <is>
           <t>FY25 effective = 150,649 / 802,595</t>
         </is>
       </c>
-      <c r="T11" s="178" t="inlineStr">
+      <c r="T11" s="187" t="inlineStr">
         <is>
           <t>Linked D5</t>
         </is>
       </c>
-      <c r="U11" s="180" t="inlineStr">
+      <c r="U11" s="189" t="inlineStr">
         <is>
           <t>SEC 10-K FY2025 (tax / EBT)</t>
         </is>
       </c>
-      <c r="V11" s="180" t="inlineStr">
+      <c r="V11" s="189" t="inlineStr">
         <is>
           <t>SEC companyfacts XBRL (CIK 0000814547)</t>
         </is>
@@ -11256,7 +11549,7 @@
         </is>
       </c>
       <c r="C12" s="97" t="n"/>
-      <c r="D12" s="187" t="n">
+      <c r="D12" s="196" t="n">
         <v>21597.635</v>
       </c>
       <c r="E12" s="97" t="n"/>
@@ -11270,31 +11563,31 @@
       <c r="M12" s="97" t="n"/>
       <c r="N12" s="97" t="n"/>
       <c r="O12" s="97" t="n"/>
-      <c r="Q12" s="184" t="inlineStr">
+      <c r="Q12" s="193" t="inlineStr">
         <is>
           <t>Rd_aftertax = Rd × (1 − t)</t>
         </is>
       </c>
-      <c r="R12" s="185">
+      <c r="R12" s="194">
         <f>R10*(1-R11)</f>
         <v/>
       </c>
-      <c r="S12" s="178" t="inlineStr">
+      <c r="S12" s="187" t="inlineStr">
         <is>
           <t>After-tax cost of debt</t>
         </is>
       </c>
-      <c r="T12" s="184" t="inlineStr">
+      <c r="T12" s="193" t="inlineStr">
         <is>
           <t>→ WACC</t>
         </is>
       </c>
-      <c r="U12" s="178" t="inlineStr">
+      <c r="U12" s="187" t="inlineStr">
         <is>
           <t>Derived: R10 × (1 − R11)</t>
         </is>
       </c>
-      <c r="V12" s="178" t="inlineStr"/>
+      <c r="V12" s="187" t="inlineStr"/>
     </row>
     <row r="13" ht="16" customHeight="1">
       <c r="A13" s="97" t="n"/>
@@ -11304,7 +11597,7 @@
         </is>
       </c>
       <c r="C13" s="97" t="n"/>
-      <c r="D13" s="187" t="n">
+      <c r="D13" s="196" t="n">
         <v>5582389</v>
       </c>
       <c r="E13" s="97" t="n"/>
@@ -11318,30 +11611,30 @@
       <c r="M13" s="97" t="n"/>
       <c r="N13" s="97" t="n"/>
       <c r="O13" s="97" t="n"/>
-      <c r="Q13" s="178" t="inlineStr">
+      <c r="Q13" s="187" t="inlineStr">
         <is>
           <t>Equity weight (We)</t>
         </is>
       </c>
-      <c r="R13" s="188" t="n">
+      <c r="R13" s="197" t="n">
         <v>0.8</v>
       </c>
-      <c r="S13" s="178" t="inlineStr">
+      <c r="S13" s="187" t="inlineStr">
         <is>
           <t>Target ~80% equity at market</t>
         </is>
       </c>
-      <c r="T13" s="178" t="inlineStr">
+      <c r="T13" s="187" t="inlineStr">
         <is>
           <t>WACC weight</t>
         </is>
       </c>
-      <c r="U13" s="180" t="inlineStr">
+      <c r="U13" s="189" t="inlineStr">
         <is>
           <t>SEC 10-Q Q3 FY2026 (debt / capital)</t>
         </is>
       </c>
-      <c r="V13" s="180" t="inlineStr">
+      <c r="V13" s="189" t="inlineStr">
         <is>
           <t>Yahoo market cap for E/(D+E)</t>
         </is>
@@ -11355,7 +11648,7 @@
         </is>
       </c>
       <c r="C14" s="97" t="n"/>
-      <c r="D14" s="187" t="n">
+      <c r="D14" s="196" t="n">
         <v>304537</v>
       </c>
       <c r="E14" s="97" t="n"/>
@@ -11369,30 +11662,30 @@
       <c r="M14" s="97" t="n"/>
       <c r="N14" s="97" t="n"/>
       <c r="O14" s="97" t="n"/>
-      <c r="Q14" s="178" t="inlineStr">
+      <c r="Q14" s="187" t="inlineStr">
         <is>
           <t>Debt weight (Wd)</t>
         </is>
       </c>
-      <c r="R14" s="188" t="n">
+      <c r="R14" s="197" t="n">
         <v>0.2</v>
       </c>
-      <c r="S14" s="178" t="inlineStr">
+      <c r="S14" s="187" t="inlineStr">
         <is>
           <t>Target ~20% debt (We+Wd=100%)</t>
         </is>
       </c>
-      <c r="T14" s="178" t="inlineStr">
+      <c r="T14" s="187" t="inlineStr">
         <is>
           <t>WACC weight</t>
         </is>
       </c>
-      <c r="U14" s="180" t="inlineStr">
+      <c r="U14" s="189" t="inlineStr">
         <is>
           <t>SEC 10-Q — total debt $5,582,389k</t>
         </is>
       </c>
-      <c r="V14" s="180" t="inlineStr">
+      <c r="V14" s="189" t="inlineStr">
         <is>
           <t>SEC 10-K — senior notes footnote</t>
         </is>
@@ -11406,7 +11699,7 @@
         </is>
       </c>
       <c r="C15" s="97" t="n"/>
-      <c r="D15" s="189">
+      <c r="D15" s="198">
         <f>'3 Statement Model'!J68</f>
         <v/>
       </c>
@@ -11421,31 +11714,31 @@
       <c r="M15" s="97" t="n"/>
       <c r="N15" s="97" t="n"/>
       <c r="O15" s="97" t="n"/>
-      <c r="Q15" s="184" t="inlineStr">
+      <c r="Q15" s="193" t="inlineStr">
         <is>
           <t>WACC = We×Ke + Wd×Rd_aftertax</t>
         </is>
       </c>
-      <c r="R15" s="185">
+      <c r="R15" s="194">
         <f>R13*R9+R14*R12</f>
         <v/>
       </c>
-      <c r="S15" s="178" t="inlineStr">
+      <c r="S15" s="187" t="inlineStr">
         <is>
           <t>PRIMARY discount rate → cell D6</t>
         </is>
       </c>
-      <c r="T15" s="184" t="inlineStr">
+      <c r="T15" s="193" t="inlineStr">
         <is>
           <t>→ D6</t>
         </is>
       </c>
-      <c r="U15" s="180" t="inlineStr">
+      <c r="U15" s="189" t="inlineStr">
         <is>
           <t>SEC filings (tax, debt coupons)</t>
         </is>
       </c>
-      <c r="V15" s="180" t="inlineStr">
+      <c r="V15" s="189" t="inlineStr">
         <is>
           <t>Damodaran (ERP methodology)</t>
         </is>
@@ -11476,23 +11769,23 @@
           <t>Entry</t>
         </is>
       </c>
-      <c r="E17" s="190">
+      <c r="E17" s="199">
         <f>YEAR(E18)</f>
         <v/>
       </c>
-      <c r="F17" s="190">
+      <c r="F17" s="199">
         <f>YEAR(F18)</f>
         <v/>
       </c>
-      <c r="G17" s="190">
+      <c r="G17" s="199">
         <f>YEAR(G18)</f>
         <v/>
       </c>
-      <c r="H17" s="190">
+      <c r="H17" s="199">
         <f>YEAR(H18)</f>
         <v/>
       </c>
-      <c r="I17" s="190">
+      <c r="I17" s="199">
         <f>YEAR(I18)</f>
         <v/>
       </c>
@@ -11510,7 +11803,7 @@
       <c r="M17" s="111" t="n"/>
       <c r="N17" s="111" t="n"/>
       <c r="O17" s="97" t="n"/>
-      <c r="Q17" s="137" t="inlineStr">
+      <c r="Q17" s="146" t="inlineStr">
         <is>
           <t>2) Unlevered Free Cash Flow</t>
         </is>
@@ -11524,31 +11817,31 @@
         </is>
       </c>
       <c r="C18" s="97" t="n"/>
-      <c r="D18" s="191">
+      <c r="D18" s="200">
         <f>D9</f>
         <v/>
       </c>
-      <c r="E18" s="192">
+      <c r="E18" s="201">
         <f>DATE(YEAR($D$10)+E19,3,31)</f>
         <v/>
       </c>
-      <c r="F18" s="192">
+      <c r="F18" s="201">
         <f>DATE(YEAR($D$10)+F19,3,31)</f>
         <v/>
       </c>
-      <c r="G18" s="192">
+      <c r="G18" s="201">
         <f>DATE(YEAR($D$10)+G19,3,31)</f>
         <v/>
       </c>
-      <c r="H18" s="192">
+      <c r="H18" s="201">
         <f>DATE(YEAR($D$10)+H19,3,31)</f>
         <v/>
       </c>
-      <c r="I18" s="192">
+      <c r="I18" s="201">
         <f>DATE(YEAR($D$10)+I19,3,31)</f>
         <v/>
       </c>
-      <c r="J18" s="193">
+      <c r="J18" s="202">
         <f>I18</f>
         <v/>
       </c>
@@ -11558,7 +11851,7 @@
           <t>Exit EV/EBITDA (in J27) — primary</t>
         </is>
       </c>
-      <c r="M18" s="189">
+      <c r="M18" s="198">
         <f>J27</f>
         <v/>
       </c>
@@ -11567,17 +11860,17 @@
         <v/>
       </c>
       <c r="O18" s="97" t="n"/>
-      <c r="Q18" s="184" t="inlineStr">
+      <c r="Q18" s="193" t="inlineStr">
         <is>
           <t>FCFF = EBIT − EBIT×t + D&amp;A − CapEx − ΔNWC</t>
         </is>
       </c>
-      <c r="U18" s="180" t="inlineStr">
+      <c r="U18" s="189" t="inlineStr">
         <is>
           <t>Drivers from SEC XBRL → 3-statement</t>
         </is>
       </c>
-      <c r="V18" s="180" t="inlineStr">
+      <c r="V18" s="189" t="inlineStr">
         <is>
           <t>SEC 10-K historical IS/CF</t>
         </is>
@@ -11592,22 +11885,22 @@
       </c>
       <c r="C19" s="118" t="n"/>
       <c r="D19" s="115" t="n"/>
-      <c r="E19" s="194" t="n">
+      <c r="E19" s="203" t="n">
         <v>0</v>
       </c>
-      <c r="F19" s="191">
+      <c r="F19" s="200">
         <f>E19+1</f>
         <v/>
       </c>
-      <c r="G19" s="191">
+      <c r="G19" s="200">
         <f>F19+1</f>
         <v/>
       </c>
-      <c r="H19" s="191">
+      <c r="H19" s="200">
         <f>G19+1</f>
         <v/>
       </c>
-      <c r="I19" s="191">
+      <c r="I19" s="200">
         <f>H19+1</f>
         <v/>
       </c>
@@ -11618,7 +11911,7 @@
           <t>Gordon cross-check</t>
         </is>
       </c>
-      <c r="M19" s="189">
+      <c r="M19" s="198">
         <f>IF(($D$6-$D$7)&lt;=0,"WACC must exceed g",$I$26*(1+$D$7)/($D$6-$D$7))</f>
         <v/>
       </c>
@@ -11627,12 +11920,12 @@
         <v/>
       </c>
       <c r="O19" s="97" t="n"/>
-      <c r="Q19" s="178" t="inlineStr">
+      <c r="Q19" s="187" t="inlineStr">
         <is>
           <t>Excel (col E example)</t>
         </is>
       </c>
-      <c r="R19" s="184">
+      <c r="R19" s="193">
         <f>E21-E22+E23-E24-E25</f>
         <v/>
       </c>
@@ -11646,23 +11939,23 @@
       </c>
       <c r="C20" s="97" t="n"/>
       <c r="D20" s="97" t="n"/>
-      <c r="E20" s="191">
+      <c r="E20" s="200">
         <f>YEARFRAC(D18,E18)</f>
         <v/>
       </c>
-      <c r="F20" s="191">
+      <c r="F20" s="200">
         <f>YEARFRAC(E18,F18)</f>
         <v/>
       </c>
-      <c r="G20" s="191">
+      <c r="G20" s="200">
         <f>YEARFRAC(F18,G18)</f>
         <v/>
       </c>
-      <c r="H20" s="191">
+      <c r="H20" s="200">
         <f>YEARFRAC(G18,H18)</f>
         <v/>
       </c>
-      <c r="I20" s="191">
+      <c r="I20" s="200">
         <f>YEARFRAC(H18,I18)</f>
         <v/>
       </c>
@@ -11673,7 +11966,7 @@
           <t>Implied Gordon exit multiple</t>
         </is>
       </c>
-      <c r="M20" s="189">
+      <c r="M20" s="198">
         <f>IF(($I$21+$I$23)=0,0,M19/($I$21+$I$23))</f>
         <v/>
       </c>
@@ -11682,21 +11975,21 @@
         <v/>
       </c>
       <c r="O20" s="97" t="n"/>
-      <c r="Q20" s="178" t="inlineStr">
+      <c r="Q20" s="187" t="inlineStr">
         <is>
           <t>Tax on EBIT (unlevered)</t>
         </is>
       </c>
-      <c r="R20" s="184">
+      <c r="R20" s="193">
         <f>E21*$D$5</f>
         <v/>
       </c>
-      <c r="S20" s="178" t="inlineStr">
+      <c r="S20" s="187" t="inlineStr">
         <is>
           <t>NOT levered IS tax dollars</t>
         </is>
       </c>
-      <c r="U20" s="180" t="inlineStr">
+      <c r="U20" s="189" t="inlineStr">
         <is>
           <t>Tax rate from SEC 10-K effective rate</t>
         </is>
@@ -11709,29 +12002,29 @@
           <t>EBIT (linked to 3-stmt)</t>
         </is>
       </c>
-      <c r="C21" s="195" t="inlineStr">
+      <c r="C21" s="204" t="inlineStr">
         <is>
           <t>EBIT</t>
         </is>
       </c>
       <c r="D21" s="97" t="n"/>
-      <c r="E21" s="189">
+      <c r="E21" s="198">
         <f>'3 Statement Model'!J26-'3 Statement Model'!J28-'3 Statement Model'!J29-'3 Statement Model'!J30</f>
         <v/>
       </c>
-      <c r="F21" s="189">
+      <c r="F21" s="198">
         <f>'3 Statement Model'!K26-'3 Statement Model'!K28-'3 Statement Model'!K29-'3 Statement Model'!K30</f>
         <v/>
       </c>
-      <c r="G21" s="189">
+      <c r="G21" s="198">
         <f>'3 Statement Model'!L26-'3 Statement Model'!L28-'3 Statement Model'!L29-'3 Statement Model'!L30</f>
         <v/>
       </c>
-      <c r="H21" s="189">
+      <c r="H21" s="198">
         <f>'3 Statement Model'!M26-'3 Statement Model'!M28-'3 Statement Model'!M29-'3 Statement Model'!M30</f>
         <v/>
       </c>
-      <c r="I21" s="189">
+      <c r="I21" s="198">
         <f>'3 Statement Model'!N26-'3 Statement Model'!N28-'3 Statement Model'!N29-'3 Statement Model'!N30</f>
         <v/>
       </c>
@@ -11741,16 +12034,16 @@
       <c r="M21" s="97" t="n"/>
       <c r="N21" s="97" t="n"/>
       <c r="O21" s="97" t="n"/>
-      <c r="Q21" s="178" t="inlineStr">
+      <c r="Q21" s="187" t="inlineStr">
         <is>
           <t>FCFF check (FY5 / col I)</t>
         </is>
       </c>
-      <c r="R21" s="196">
+      <c r="R21" s="205">
         <f>I26</f>
         <v/>
       </c>
-      <c r="S21" s="178" t="inlineStr">
+      <c r="S21" s="187" t="inlineStr">
         <is>
           <t>Must equal I21−I22+I23−I24−I25</t>
         </is>
@@ -11763,29 +12056,29 @@
           <t>Less: Unlevered Cash Taxes (EBIT×t)</t>
         </is>
       </c>
-      <c r="C22" s="195" t="inlineStr">
+      <c r="C22" s="204" t="inlineStr">
         <is>
           <t>EBIT×t</t>
         </is>
       </c>
       <c r="D22" s="97" t="n"/>
-      <c r="E22" s="189">
+      <c r="E22" s="198">
         <f>E21*$D$5</f>
         <v/>
       </c>
-      <c r="F22" s="189">
+      <c r="F22" s="198">
         <f>F21*$D$5</f>
         <v/>
       </c>
-      <c r="G22" s="189">
+      <c r="G22" s="198">
         <f>G21*$D$5</f>
         <v/>
       </c>
-      <c r="H22" s="189">
+      <c r="H22" s="198">
         <f>H21*$D$5</f>
         <v/>
       </c>
-      <c r="I22" s="189">
+      <c r="I22" s="198">
         <f>I21*$D$5</f>
         <v/>
       </c>
@@ -11803,29 +12096,29 @@
           <t>Plus: D&amp;A (linked to 3-stmt)</t>
         </is>
       </c>
-      <c r="C23" s="195" t="inlineStr">
+      <c r="C23" s="204" t="inlineStr">
         <is>
           <t>+D&amp;A</t>
         </is>
       </c>
       <c r="D23" s="97" t="n"/>
-      <c r="E23" s="189">
+      <c r="E23" s="198">
         <f>'3 Statement Model'!J30</f>
         <v/>
       </c>
-      <c r="F23" s="189">
+      <c r="F23" s="198">
         <f>'3 Statement Model'!K30</f>
         <v/>
       </c>
-      <c r="G23" s="189">
+      <c r="G23" s="198">
         <f>'3 Statement Model'!L30</f>
         <v/>
       </c>
-      <c r="H23" s="189">
+      <c r="H23" s="198">
         <f>'3 Statement Model'!M30</f>
         <v/>
       </c>
-      <c r="I23" s="189">
+      <c r="I23" s="198">
         <f>'3 Statement Model'!N30</f>
         <v/>
       </c>
@@ -11835,7 +12128,7 @@
       <c r="M23" s="97" t="n"/>
       <c r="N23" s="97" t="n"/>
       <c r="O23" s="97" t="n"/>
-      <c r="Q23" s="137" t="inlineStr">
+      <c r="Q23" s="146" t="inlineStr">
         <is>
           <t>3) Terminal Value</t>
         </is>
@@ -11848,29 +12141,29 @@
           <t>Less: Capex (linked to 3-stmt CF)</t>
         </is>
       </c>
-      <c r="C24" s="195" t="inlineStr">
+      <c r="C24" s="204" t="inlineStr">
         <is>
           <t>−CapEx</t>
         </is>
       </c>
       <c r="D24" s="97" t="n"/>
-      <c r="E24" s="189">
+      <c r="E24" s="198">
         <f>'3 Statement Model'!J68</f>
         <v/>
       </c>
-      <c r="F24" s="189">
+      <c r="F24" s="198">
         <f>'3 Statement Model'!K68</f>
         <v/>
       </c>
-      <c r="G24" s="189">
+      <c r="G24" s="198">
         <f>'3 Statement Model'!L68</f>
         <v/>
       </c>
-      <c r="H24" s="189">
+      <c r="H24" s="198">
         <f>'3 Statement Model'!M68</f>
         <v/>
       </c>
-      <c r="I24" s="189">
+      <c r="I24" s="198">
         <f>'3 Statement Model'!N68</f>
         <v/>
       </c>
@@ -11880,7 +12173,7 @@
       <c r="M24" s="97" t="n"/>
       <c r="N24" s="97" t="n"/>
       <c r="O24" s="97" t="n"/>
-      <c r="Q24" s="184" t="inlineStr">
+      <c r="Q24" s="193" t="inlineStr">
         <is>
           <t>TV_exit = EBITDA_n × ExitMultiple   [PRIMARY]</t>
         </is>
@@ -11893,29 +12186,29 @@
           <t>Less: ΔNWC (linked to 3-stmt CF)</t>
         </is>
       </c>
-      <c r="C25" s="195" t="inlineStr">
+      <c r="C25" s="204" t="inlineStr">
         <is>
           <t>−ΔNWC</t>
         </is>
       </c>
       <c r="D25" s="97" t="n"/>
-      <c r="E25" s="189">
+      <c r="E25" s="198">
         <f>'3 Statement Model'!J64</f>
         <v/>
       </c>
-      <c r="F25" s="189">
+      <c r="F25" s="198">
         <f>'3 Statement Model'!K64</f>
         <v/>
       </c>
-      <c r="G25" s="189">
+      <c r="G25" s="198">
         <f>'3 Statement Model'!L64</f>
         <v/>
       </c>
-      <c r="H25" s="189">
+      <c r="H25" s="198">
         <f>'3 Statement Model'!M64</f>
         <v/>
       </c>
-      <c r="I25" s="189">
+      <c r="I25" s="198">
         <f>'3 Statement Model'!N64</f>
         <v/>
       </c>
@@ -11925,20 +12218,20 @@
       <c r="M25" s="97" t="n"/>
       <c r="N25" s="97" t="n"/>
       <c r="O25" s="97" t="n"/>
-      <c r="Q25" s="178" t="inlineStr">
+      <c r="Q25" s="187" t="inlineStr">
         <is>
           <t>Excel</t>
         </is>
       </c>
-      <c r="R25" s="184">
+      <c r="R25" s="193">
         <f>($I$21+$I$23)*$D$8</f>
         <v/>
       </c>
-      <c r="T25" s="196">
+      <c r="T25" s="205">
         <f>J27</f>
         <v/>
       </c>
-      <c r="U25" s="180" t="inlineStr">
+      <c r="U25" s="189" t="inlineStr">
         <is>
           <t>Exit multiple policy vs Yahoo / market multiples</t>
         </is>
@@ -11951,29 +12244,29 @@
           <t>Unlevered FCF</t>
         </is>
       </c>
-      <c r="C26" s="195" t="inlineStr">
+      <c r="C26" s="204" t="inlineStr">
         <is>
           <t>FCFF=EBIT−tax+DA−CapEx−ΔNWC</t>
         </is>
       </c>
       <c r="D26" s="97" t="n"/>
-      <c r="E26" s="197">
+      <c r="E26" s="206">
         <f>E21-E22+E23-E24-E25</f>
         <v/>
       </c>
-      <c r="F26" s="197">
+      <c r="F26" s="206">
         <f>F21-F22+F23-F24-F25</f>
         <v/>
       </c>
-      <c r="G26" s="197">
+      <c r="G26" s="206">
         <f>G21-G22+G23-G24-G25</f>
         <v/>
       </c>
-      <c r="H26" s="197">
+      <c r="H26" s="206">
         <f>H21-H22+H23-H24-H25</f>
         <v/>
       </c>
-      <c r="I26" s="197">
+      <c r="I26" s="206">
         <f>I21-I22+I23-I24-I25</f>
         <v/>
       </c>
@@ -11983,7 +12276,7 @@
       <c r="M26" s="97" t="n"/>
       <c r="N26" s="97" t="n"/>
       <c r="O26" s="97" t="n"/>
-      <c r="Q26" s="184" t="inlineStr">
+      <c r="Q26" s="193" t="inlineStr">
         <is>
           <t>TV_gordon = FCFF_n×(1+g)/(WACC−g)   [CHECK]</t>
         </is>
@@ -11997,7 +12290,7 @@
         </is>
       </c>
       <c r="C27" s="97" t="n"/>
-      <c r="D27" s="198">
+      <c r="D27" s="207">
         <f>-I35</f>
         <v/>
       </c>
@@ -12006,7 +12299,7 @@
       <c r="G27" s="97" t="n"/>
       <c r="H27" s="97" t="n"/>
       <c r="I27" s="97" t="n"/>
-      <c r="J27" s="189">
+      <c r="J27" s="198">
         <f>($I$21+$I$23)*$D$8</f>
         <v/>
       </c>
@@ -12015,20 +12308,20 @@
       <c r="M27" s="97" t="n"/>
       <c r="N27" s="97" t="n"/>
       <c r="O27" s="97" t="n"/>
-      <c r="Q27" s="178" t="inlineStr">
+      <c r="Q27" s="187" t="inlineStr">
         <is>
           <t>Excel</t>
         </is>
       </c>
-      <c r="R27" s="184">
+      <c r="R27" s="193">
         <f>IF(($D$6-$D$7)&lt;=0,"err",$I$26*(1+$D$7)/($D$6-$D$7))</f>
         <v/>
       </c>
-      <c r="T27" s="196">
+      <c r="T27" s="205">
         <f>M19</f>
         <v/>
       </c>
-      <c r="U27" s="180" t="inlineStr">
+      <c r="U27" s="189" t="inlineStr">
         <is>
           <t>Gordon g vs Damodaran long-run growth framing</t>
         </is>
@@ -12042,30 +12335,30 @@
         </is>
       </c>
       <c r="C28" s="97" t="n"/>
-      <c r="D28" s="197" t="n">
+      <c r="D28" s="206" t="n">
         <v>0</v>
       </c>
-      <c r="E28" s="199">
+      <c r="E28" s="208">
         <f>E27+E26</f>
         <v/>
       </c>
-      <c r="F28" s="199">
+      <c r="F28" s="208">
         <f>F27+F26</f>
         <v/>
       </c>
-      <c r="G28" s="199">
+      <c r="G28" s="208">
         <f>G27+G26</f>
         <v/>
       </c>
-      <c r="H28" s="199">
+      <c r="H28" s="208">
         <f>H27+H26</f>
         <v/>
       </c>
-      <c r="I28" s="199">
+      <c r="I28" s="208">
         <f>I27+I26</f>
         <v/>
       </c>
-      <c r="J28" s="199">
+      <c r="J28" s="208">
         <f>J27+J26</f>
         <v/>
       </c>
@@ -12074,16 +12367,16 @@
       <c r="M28" s="97" t="n"/>
       <c r="N28" s="97" t="n"/>
       <c r="O28" s="97" t="n"/>
-      <c r="Q28" s="178" t="inlineStr">
+      <c r="Q28" s="187" t="inlineStr">
         <is>
           <t>Implied Gordon exit multiple</t>
         </is>
       </c>
-      <c r="R28" s="200">
+      <c r="R28" s="209">
         <f>IF(($I$21+$I$23)=0,0,T27/($I$21+$I$23))</f>
         <v/>
       </c>
-      <c r="S28" s="178" t="inlineStr">
+      <c r="S28" s="187" t="inlineStr">
         <is>
           <t>Gordon TV / EBITDA_n</t>
         </is>
@@ -12097,31 +12390,31 @@
         </is>
       </c>
       <c r="C29" s="97" t="n"/>
-      <c r="D29" s="198">
+      <c r="D29" s="207">
         <f>D27+D26</f>
         <v/>
       </c>
-      <c r="E29" s="189">
+      <c r="E29" s="198">
         <f>E27+E26</f>
         <v/>
       </c>
-      <c r="F29" s="189">
+      <c r="F29" s="198">
         <f>F27+F26</f>
         <v/>
       </c>
-      <c r="G29" s="189">
+      <c r="G29" s="198">
         <f>G27+G26</f>
         <v/>
       </c>
-      <c r="H29" s="189">
+      <c r="H29" s="198">
         <f>H27+H26</f>
         <v/>
       </c>
-      <c r="I29" s="189">
+      <c r="I29" s="198">
         <f>I27+I26</f>
         <v/>
       </c>
-      <c r="J29" s="189">
+      <c r="J29" s="198">
         <f>J27</f>
         <v/>
       </c>
@@ -12145,7 +12438,7 @@
       <c r="M30" s="97" t="n"/>
       <c r="N30" s="97" t="n"/>
       <c r="O30" s="97" t="n"/>
-      <c r="Q30" s="137" t="inlineStr">
+      <c r="Q30" s="146" t="inlineStr">
         <is>
           <t>4) Enterprise → Equity → $/share</t>
         </is>
@@ -12177,7 +12470,7 @@
       <c r="M31" s="111" t="n"/>
       <c r="N31" s="111" t="n"/>
       <c r="O31" s="97" t="n"/>
-      <c r="Q31" s="184" t="inlineStr">
+      <c r="Q31" s="193" t="inlineStr">
         <is>
           <t>EV = XNPV(WACC, TransactionCF, mid-year dates)</t>
         </is>
@@ -12191,7 +12484,7 @@
         </is>
       </c>
       <c r="C32" s="97" t="n"/>
-      <c r="D32" s="189">
+      <c r="D32" s="198">
         <f>XNPV(D6,D28:J28,D18:J18)</f>
         <v/>
       </c>
@@ -12202,7 +12495,7 @@
         </is>
       </c>
       <c r="H32" s="97" t="n"/>
-      <c r="I32" s="198">
+      <c r="I32" s="207">
         <f>D12*D11</f>
         <v/>
       </c>
@@ -12218,16 +12511,16 @@
         <v/>
       </c>
       <c r="O32" s="97" t="n"/>
-      <c r="Q32" s="178" t="inlineStr">
+      <c r="Q32" s="187" t="inlineStr">
         <is>
           <t>Excel</t>
         </is>
       </c>
-      <c r="R32" s="184">
+      <c r="R32" s="193">
         <f>XNPV(D6,D28:J28,D18:J18)</f>
         <v/>
       </c>
-      <c r="T32" s="196">
+      <c r="T32" s="205">
         <f>D32</f>
         <v/>
       </c>
@@ -12240,7 +12533,7 @@
         </is>
       </c>
       <c r="C33" s="97" t="n"/>
-      <c r="D33" s="198">
+      <c r="D33" s="207">
         <f>+D14</f>
         <v/>
       </c>
@@ -12251,7 +12544,7 @@
         </is>
       </c>
       <c r="H33" s="97" t="n"/>
-      <c r="I33" s="198">
+      <c r="I33" s="207">
         <f>D13</f>
         <v/>
       </c>
@@ -12267,26 +12560,26 @@
         <v/>
       </c>
       <c r="O33" s="97" t="n"/>
-      <c r="Q33" s="184" t="inlineStr">
+      <c r="Q33" s="193" t="inlineStr">
         <is>
           <t>Equity = EV + Cash − Debt</t>
         </is>
       </c>
-      <c r="R33" s="196">
+      <c r="R33" s="205">
         <f>D35</f>
         <v/>
       </c>
-      <c r="S33" s="178" t="inlineStr">
+      <c r="S33" s="187" t="inlineStr">
         <is>
           <t>Net debt from 10-Q bridge</t>
         </is>
       </c>
-      <c r="U33" s="180" t="inlineStr">
+      <c r="U33" s="189" t="inlineStr">
         <is>
           <t>SEC 10-Q — cash, mkt secs, total debt</t>
         </is>
       </c>
-      <c r="V33" s="180" t="inlineStr">
+      <c r="V33" s="189" t="inlineStr">
         <is>
           <t>SEC 10-K — FY debt footnote</t>
         </is>
@@ -12300,7 +12593,7 @@
         </is>
       </c>
       <c r="C34" s="97" t="n"/>
-      <c r="D34" s="198">
+      <c r="D34" s="207">
         <f>+D13</f>
         <v/>
       </c>
@@ -12311,7 +12604,7 @@
         </is>
       </c>
       <c r="H34" s="97" t="n"/>
-      <c r="I34" s="198">
+      <c r="I34" s="207">
         <f>+D14</f>
         <v/>
       </c>
@@ -12320,26 +12613,26 @@
       <c r="M34" s="97" t="n"/>
       <c r="N34" s="97" t="n"/>
       <c r="O34" s="97" t="n"/>
-      <c r="Q34" s="184" t="inlineStr">
+      <c r="Q34" s="193" t="inlineStr">
         <is>
           <t>$/share = Equity / Shares</t>
         </is>
       </c>
-      <c r="R34" s="201">
+      <c r="R34" s="210">
         <f>D37</f>
         <v/>
       </c>
-      <c r="S34" s="178" t="inlineStr">
+      <c r="S34" s="187" t="inlineStr">
         <is>
           <t>Shares outstanding (Yahoo)</t>
         </is>
       </c>
-      <c r="U34" s="180" t="inlineStr">
+      <c r="U34" s="189" t="inlineStr">
         <is>
           <t>Yahoo Finance — shares outstanding</t>
         </is>
       </c>
-      <c r="V34" s="180" t="inlineStr">
+      <c r="V34" s="189" t="inlineStr">
         <is>
           <t>Yahoo FICO quote (price)</t>
         </is>
@@ -12353,7 +12646,7 @@
         </is>
       </c>
       <c r="C35" s="97" t="n"/>
-      <c r="D35" s="197">
+      <c r="D35" s="206">
         <f>D32+D33-D34</f>
         <v/>
       </c>
@@ -12364,7 +12657,7 @@
         </is>
       </c>
       <c r="H35" s="97" t="n"/>
-      <c r="I35" s="197">
+      <c r="I35" s="206">
         <f>I32+I33-I34</f>
         <v/>
       </c>
@@ -12377,16 +12670,16 @@
       <c r="M35" s="111" t="n"/>
       <c r="N35" s="111" t="n"/>
       <c r="O35" s="97" t="n"/>
-      <c r="Q35" s="178" t="inlineStr">
+      <c r="Q35" s="187" t="inlineStr">
         <is>
           <t>Upside vs market</t>
         </is>
       </c>
-      <c r="R35" s="202">
+      <c r="R35" s="211">
         <f>D37/D11-1</f>
         <v/>
       </c>
-      <c r="S35" s="178" t="inlineStr">
+      <c r="S35" s="187" t="inlineStr">
         <is>
           <t>Intrinsic / Current Price − 1</t>
         </is>
@@ -12400,7 +12693,7 @@
       <c r="E36" s="97" t="n"/>
       <c r="G36" s="97" t="n"/>
       <c r="H36" s="97" t="n"/>
-      <c r="I36" s="203" t="n"/>
+      <c r="I36" s="212" t="n"/>
       <c r="J36" s="97" t="n"/>
       <c r="L36" s="97" t="inlineStr">
         <is>
@@ -12408,7 +12701,7 @@
         </is>
       </c>
       <c r="M36" s="97" t="n"/>
-      <c r="N36" s="203">
+      <c r="N36" s="212">
         <f>I37</f>
         <v/>
       </c>
@@ -12422,7 +12715,7 @@
         </is>
       </c>
       <c r="C37" s="97" t="n"/>
-      <c r="D37" s="198">
+      <c r="D37" s="207">
         <f>D35/D12</f>
         <v/>
       </c>
@@ -12433,7 +12726,7 @@
         </is>
       </c>
       <c r="H37" s="97" t="n"/>
-      <c r="I37" s="198">
+      <c r="I37" s="207">
         <f>D11</f>
         <v/>
       </c>
@@ -12444,12 +12737,12 @@
         </is>
       </c>
       <c r="M37" s="97" t="n"/>
-      <c r="N37" s="203">
+      <c r="N37" s="212">
         <f>D37-I37</f>
         <v/>
       </c>
       <c r="O37" s="97" t="n"/>
-      <c r="Q37" s="137" t="inlineStr">
+      <c r="Q37" s="146" t="inlineStr">
         <is>
           <t>5) Operating NWC (feeds ΔNWC → FCFF)</t>
         </is>
@@ -12471,22 +12764,22 @@
         </is>
       </c>
       <c r="M38" s="97" t="n"/>
-      <c r="N38" s="203">
+      <c r="N38" s="212">
         <f>SUM(N36:N37)</f>
         <v/>
       </c>
       <c r="O38" s="97" t="n"/>
-      <c r="Q38" s="184" t="inlineStr">
+      <c r="Q38" s="193" t="inlineStr">
         <is>
           <t>NWC = AR + Inventory − AP − DeferredRevenue</t>
         </is>
       </c>
-      <c r="U38" s="180" t="inlineStr">
+      <c r="U38" s="189" t="inlineStr">
         <is>
           <t>SEC 10-K — AR / AP / deferred revenue</t>
         </is>
       </c>
-      <c r="V38" s="180" t="inlineStr">
+      <c r="V38" s="189" t="inlineStr">
         <is>
           <t>XBRL DeferredRevenueCurrent</t>
         </is>
@@ -12505,17 +12798,17 @@
       <c r="M39" s="97" t="n"/>
       <c r="N39" s="97" t="n"/>
       <c r="O39" s="97" t="n"/>
-      <c r="Q39" s="184" t="inlineStr">
+      <c r="Q39" s="193" t="inlineStr">
         <is>
           <t>ΔNWC_t = NWC_t − NWC_(t−1)</t>
         </is>
       </c>
-      <c r="S39" s="178" t="inlineStr">
+      <c r="S39" s="187" t="inlineStr">
         <is>
           <t>Linked from 3-statement CF row 64</t>
         </is>
       </c>
-      <c r="T39" s="196">
+      <c r="T39" s="205">
         <f>I25</f>
         <v/>
       </c>
@@ -12555,7 +12848,7 @@
       <c r="M41" s="111" t="n"/>
       <c r="N41" s="111" t="n"/>
       <c r="O41" s="97" t="n"/>
-      <c r="Q41" s="137" t="inlineStr">
+      <c r="Q41" s="146" t="inlineStr">
         <is>
           <t>6) Full source index (all clickable)</t>
         </is>
@@ -12580,14 +12873,14 @@
         </is>
       </c>
       <c r="O42" s="97" t="n"/>
-      <c r="Q42" s="180" t="inlineStr">
+      <c r="Q42" s="189" t="inlineStr">
         <is>
           <t>SEC 10-K FY2025</t>
         </is>
       </c>
-      <c r="R42" s="204" t="n"/>
-      <c r="S42" s="205" t="n"/>
-      <c r="T42" s="178" t="inlineStr">
+      <c r="R42" s="213" t="n"/>
+      <c r="S42" s="214" t="n"/>
+      <c r="T42" s="187" t="inlineStr">
         <is>
           <t>Tax 18.8%, IS/BS/CF, senior notes</t>
         </is>
@@ -12608,14 +12901,14 @@
       <c r="H43" s="97" t="n"/>
       <c r="N43" s="69" t="n"/>
       <c r="O43" s="97" t="n"/>
-      <c r="Q43" s="180" t="inlineStr">
+      <c r="Q43" s="189" t="inlineStr">
         <is>
           <t>SEC 10-Q Q3 FY2026</t>
         </is>
       </c>
-      <c r="R43" s="204" t="n"/>
-      <c r="S43" s="205" t="n"/>
-      <c r="T43" s="178" t="inlineStr">
+      <c r="R43" s="213" t="n"/>
+      <c r="S43" s="214" t="n"/>
+      <c r="T43" s="187" t="inlineStr">
         <is>
           <t>Debt $5,582M, cash+mkt secs net-debt bridge</t>
         </is>
@@ -12636,14 +12929,14 @@
       <c r="H44" s="97" t="n"/>
       <c r="N44" s="69" t="n"/>
       <c r="O44" s="97" t="n"/>
-      <c r="Q44" s="180" t="inlineStr">
+      <c r="Q44" s="189" t="inlineStr">
         <is>
           <t>SEC 8-K 6.250% notes</t>
         </is>
       </c>
-      <c r="R44" s="204" t="n"/>
-      <c r="S44" s="205" t="n"/>
-      <c r="T44" s="178" t="inlineStr">
+      <c r="R44" s="213" t="n"/>
+      <c r="S44" s="214" t="n"/>
+      <c r="T44" s="187" t="inlineStr">
         <is>
           <t>Pre-tax Rd coupon 6.250% due 2034</t>
         </is>
@@ -12664,14 +12957,14 @@
       <c r="H45" s="97" t="n"/>
       <c r="N45" s="69" t="n"/>
       <c r="O45" s="97" t="n"/>
-      <c r="Q45" s="180" t="inlineStr">
+      <c r="Q45" s="189" t="inlineStr">
         <is>
           <t>SEC EX-99.1 pricing</t>
         </is>
       </c>
-      <c r="R45" s="204" t="n"/>
-      <c r="S45" s="205" t="n"/>
-      <c r="T45" s="178" t="inlineStr">
+      <c r="R45" s="213" t="n"/>
+      <c r="S45" s="214" t="n"/>
+      <c r="T45" s="187" t="inlineStr">
         <is>
           <t>Notes priced at par / offering terms</t>
         </is>
@@ -12692,14 +12985,14 @@
       <c r="H46" s="97" t="n"/>
       <c r="N46" s="69" t="n"/>
       <c r="O46" s="97" t="n"/>
-      <c r="Q46" s="180" t="inlineStr">
+      <c r="Q46" s="189" t="inlineStr">
         <is>
           <t>SEC companyfacts XBRL</t>
         </is>
       </c>
-      <c r="R46" s="204" t="n"/>
-      <c r="S46" s="205" t="n"/>
-      <c r="T46" s="178" t="inlineStr">
+      <c r="R46" s="213" t="n"/>
+      <c r="S46" s="214" t="n"/>
+      <c r="T46" s="187" t="inlineStr">
         <is>
           <t>Pipeline data source (CIK 0000814547)</t>
         </is>
@@ -12716,14 +13009,14 @@
       <c r="H47" s="97" t="n"/>
       <c r="N47" s="69" t="n"/>
       <c r="O47" s="97" t="n"/>
-      <c r="Q47" s="180" t="inlineStr">
+      <c r="Q47" s="189" t="inlineStr">
         <is>
           <t>FRED DGS10</t>
         </is>
       </c>
-      <c r="R47" s="204" t="n"/>
-      <c r="S47" s="205" t="n"/>
-      <c r="T47" s="178" t="inlineStr">
+      <c r="R47" s="213" t="n"/>
+      <c r="S47" s="214" t="n"/>
+      <c r="T47" s="187" t="inlineStr">
         <is>
           <t>Risk-free rate (US 10Y)</t>
         </is>
@@ -12744,14 +13037,14 @@
         </is>
       </c>
       <c r="O48" s="97" t="n"/>
-      <c r="Q48" s="180" t="inlineStr">
+      <c r="Q48" s="189" t="inlineStr">
         <is>
           <t>US Treasury yield curve</t>
         </is>
       </c>
-      <c r="R48" s="204" t="n"/>
-      <c r="S48" s="205" t="n"/>
-      <c r="T48" s="178" t="inlineStr">
+      <c r="R48" s="213" t="n"/>
+      <c r="S48" s="214" t="n"/>
+      <c r="T48" s="187" t="inlineStr">
         <is>
           <t>Official daily par yields</t>
         </is>
@@ -12772,14 +13065,14 @@
         </is>
       </c>
       <c r="O49" s="97" t="n"/>
-      <c r="Q49" s="180" t="inlineStr">
+      <c r="Q49" s="189" t="inlineStr">
         <is>
           <t>Damodaran Implied ERP</t>
         </is>
       </c>
-      <c r="R49" s="204" t="n"/>
-      <c r="S49" s="205" t="n"/>
-      <c r="T49" s="178" t="inlineStr">
+      <c r="R49" s="213" t="n"/>
+      <c r="S49" s="214" t="n"/>
+      <c r="T49" s="187" t="inlineStr">
         <is>
           <t>Equity risk premium</t>
         </is>
@@ -12795,14 +13088,14 @@
       <c r="G50" s="97" t="n"/>
       <c r="H50" s="97" t="n"/>
       <c r="O50" s="97" t="n"/>
-      <c r="Q50" s="180" t="inlineStr">
+      <c r="Q50" s="189" t="inlineStr">
         <is>
           <t>Damodaran histimpl</t>
         </is>
       </c>
-      <c r="R50" s="204" t="n"/>
-      <c r="S50" s="205" t="n"/>
-      <c r="T50" s="178" t="inlineStr">
+      <c r="R50" s="213" t="n"/>
+      <c r="S50" s="214" t="n"/>
+      <c r="T50" s="187" t="inlineStr">
         <is>
           <t>Historical implied ERP table</t>
         </is>
@@ -12819,14 +13112,14 @@
       <c r="H51" s="97" t="n"/>
       <c r="M51" s="97" t="n"/>
       <c r="O51" s="97" t="n"/>
-      <c r="Q51" s="180" t="inlineStr">
+      <c r="Q51" s="189" t="inlineStr">
         <is>
           <t>Yahoo FICO stats</t>
         </is>
       </c>
-      <c r="R51" s="204" t="n"/>
-      <c r="S51" s="205" t="n"/>
-      <c r="T51" s="178" t="inlineStr">
+      <c r="R51" s="213" t="n"/>
+      <c r="S51" s="214" t="n"/>
+      <c r="T51" s="187" t="inlineStr">
         <is>
           <t>Beta 5Y monthly + shares out</t>
         </is>

--- a/FICO/output/FICO_Completed_Model.xlsx
+++ b/FICO/output/FICO_Completed_Model.xlsx
@@ -661,7 +661,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="215">
+  <cellXfs count="217">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="1"/>
@@ -940,6 +940,7 @@
     <xf numFmtId="177" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="164" fontId="41" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="177" fontId="6" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="177" fontId="38" fillId="7" borderId="2" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="177" fontId="6" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="177" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="177" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
@@ -947,8 +948,9 @@
     <xf numFmtId="177" fontId="40" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="9" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="177" fontId="40" fillId="8" borderId="2" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="177" fontId="40" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="177" fontId="38" fillId="7" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="49" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="50" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="39" fillId="9" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1805,7 +1807,7 @@
 <file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
-    <author>vengeanceaiUSCMODEL5</author>
+    <author>vengeanceaiUSCMODEL6</author>
   </authors>
   <commentList>
     <comment ref="B2" authorId="0" shapeId="0">
@@ -2033,8 +2035,8 @@
     <comment ref="B9" authorId="0" shapeId="0">
       <text>
         <t>SGA % of Revenue
-HOW: Equation: (I28 − 10,922)/I24 − 50bps × year. Strips FY25 restructuring; then −0.5% of sales each year.
-WHY: Normalize one-time restructuring ($10.9M). Mild efficiency grind reflects operating leverage as revenue scales; floored at 5%.
+HOW: Equation: MAX(20%, (I28 − 10,922)/I24 − 25bps × year). Strips FY25 restructuring; then −0.25% of sales each year.
+WHY: MODEL6 fix: enterprise software needs lasting G&amp;A (sales, legal, compliance). Floor raised from 5%→20%; grind cut from 50→25 bps so SGA stays in a realistic ~22–25% band near FY25 normalized (~25%).
 SOURCE: SEC 10-K FY2025 — SG&amp;A + restructuring note
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
@@ -2042,8 +2044,8 @@
     <comment ref="J9" authorId="0" shapeId="0">
       <text>
         <t>SGA % of Revenue
-HOW: Equation: (I28 − 10,922)/I24 − 50bps × year. Strips FY25 restructuring; then −0.5% of sales each year.
-WHY: Normalize one-time restructuring ($10.9M). Mild efficiency grind reflects operating leverage as revenue scales; floored at 5%.
+HOW: Equation: MAX(20%, (I28 − 10,922)/I24 − 25bps × year). Strips FY25 restructuring; then −0.25% of sales each year.
+WHY: MODEL6 fix: enterprise software needs lasting G&amp;A (sales, legal, compliance). Floor raised from 5%→20%; grind cut from 50→25 bps so SGA stays in a realistic ~22–25% band near FY25 normalized (~25%).
 SOURCE: SEC 10-K FY2025 — SG&amp;A + restructuring note
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
@@ -2051,8 +2053,8 @@
     <comment ref="K9" authorId="0" shapeId="0">
       <text>
         <t>SGA % of Revenue
-HOW: Equation: (I28 − 10,922)/I24 − 50bps × year. Strips FY25 restructuring; then −0.5% of sales each year.
-WHY: Normalize one-time restructuring ($10.9M). Mild efficiency grind reflects operating leverage as revenue scales; floored at 5%.
+HOW: Equation: MAX(20%, (I28 − 10,922)/I24 − 25bps × year). Strips FY25 restructuring; then −0.25% of sales each year.
+WHY: MODEL6 fix: enterprise software needs lasting G&amp;A (sales, legal, compliance). Floor raised from 5%→20%; grind cut from 50→25 bps so SGA stays in a realistic ~22–25% band near FY25 normalized (~25%).
 SOURCE: SEC 10-K FY2025 — SG&amp;A + restructuring note
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
@@ -2060,8 +2062,8 @@
     <comment ref="L9" authorId="0" shapeId="0">
       <text>
         <t>SGA % of Revenue
-HOW: Equation: (I28 − 10,922)/I24 − 50bps × year. Strips FY25 restructuring; then −0.5% of sales each year.
-WHY: Normalize one-time restructuring ($10.9M). Mild efficiency grind reflects operating leverage as revenue scales; floored at 5%.
+HOW: Equation: MAX(20%, (I28 − 10,922)/I24 − 25bps × year). Strips FY25 restructuring; then −0.25% of sales each year.
+WHY: MODEL6 fix: enterprise software needs lasting G&amp;A (sales, legal, compliance). Floor raised from 5%→20%; grind cut from 50→25 bps so SGA stays in a realistic ~22–25% band near FY25 normalized (~25%).
 SOURCE: SEC 10-K FY2025 — SG&amp;A + restructuring note
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
@@ -2069,8 +2071,8 @@
     <comment ref="M9" authorId="0" shapeId="0">
       <text>
         <t>SGA % of Revenue
-HOW: Equation: (I28 − 10,922)/I24 − 50bps × year. Strips FY25 restructuring; then −0.5% of sales each year.
-WHY: Normalize one-time restructuring ($10.9M). Mild efficiency grind reflects operating leverage as revenue scales; floored at 5%.
+HOW: Equation: MAX(20%, (I28 − 10,922)/I24 − 25bps × year). Strips FY25 restructuring; then −0.25% of sales each year.
+WHY: MODEL6 fix: enterprise software needs lasting G&amp;A (sales, legal, compliance). Floor raised from 5%→20%; grind cut from 50→25 bps so SGA stays in a realistic ~22–25% band near FY25 normalized (~25%).
 SOURCE: SEC 10-K FY2025 — SG&amp;A + restructuring note
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
@@ -2078,8 +2080,8 @@
     <comment ref="N9" authorId="0" shapeId="0">
       <text>
         <t>SGA % of Revenue
-HOW: Equation: (I28 − 10,922)/I24 − 50bps × year. Strips FY25 restructuring; then −0.5% of sales each year.
-WHY: Normalize one-time restructuring ($10.9M). Mild efficiency grind reflects operating leverage as revenue scales; floored at 5%.
+HOW: Equation: MAX(20%, (I28 − 10,922)/I24 − 25bps × year). Strips FY25 restructuring; then −0.25% of sales each year.
+WHY: MODEL6 fix: enterprise software needs lasting G&amp;A (sales, legal, compliance). Floor raised from 5%→20%; grind cut from 50→25 bps so SGA stays in a realistic ~22–25% band near FY25 normalized (~25%).
 SOURCE: SEC 10-K FY2025 — SG&amp;A + restructuring note
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
@@ -2087,8 +2089,8 @@
     <comment ref="U9" authorId="0" shapeId="0">
       <text>
         <t>SGA % of Revenue
-HOW: Equation: (I28 − 10,922)/I24 − 50bps × year. Strips FY25 restructuring; then −0.5% of sales each year.
-WHY: Normalize one-time restructuring ($10.9M). Mild efficiency grind reflects operating leverage as revenue scales; floored at 5%.
+HOW: Equation: MAX(20%, (I28 − 10,922)/I24 − 25bps × year). Strips FY25 restructuring; then −0.25% of sales each year.
+WHY: MODEL6 fix: enterprise software needs lasting G&amp;A (sales, legal, compliance). Floor raised from 5%→20%; grind cut from 50→25 bps so SGA stays in a realistic ~22–25% band near FY25 normalized (~25%).
 SOURCE: SEC 10-K FY2025 — SG&amp;A + restructuring note
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
@@ -2158,63 +2160,63 @@
     </comment>
     <comment ref="B11" authorId="0" shapeId="0">
       <text>
-        <t>D&amp;A % of PP&amp;E Open
-HOW: Excel equation: I30/I44 (FY25 DA ÷ FY25 PPE). Forecast DA = OpenPPE × this %.
-WHY: Ties DA to the asset base the schedule rolls forward (opens at I44).
+        <t>D&amp;A % of Avg PP&amp;E
+HOW: Rate = I30/I44 (FY25 DA ÷ FY25 PPE). Forecast DA$ = ((Open + Open+CapEx)/2) × rate.
+WHY: MODEL6 fix: prior model depreciated only opening PP&amp;E, so ~$96M of forecast CapEx never hit D&amp;A/FCFF add-back. Average PP&amp;E (Open ↔ pre-DA close) depreciates additions in the year they are placed in service.
 SOURCE: SEC 10-K FY2025 — D&amp;A and PP&amp;E
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="J11" authorId="0" shapeId="0">
       <text>
-        <t>D&amp;A % of PP&amp;E Open
-HOW: Excel equation: I30/I44 (FY25 DA ÷ FY25 PPE). Forecast DA = OpenPPE × this %.
-WHY: Ties DA to the asset base the schedule rolls forward (opens at I44).
+        <t>D&amp;A % of Avg PP&amp;E
+HOW: Rate = I30/I44 (FY25 DA ÷ FY25 PPE). Forecast DA$ = ((Open + Open+CapEx)/2) × rate.
+WHY: MODEL6 fix: prior model depreciated only opening PP&amp;E, so ~$96M of forecast CapEx never hit D&amp;A/FCFF add-back. Average PP&amp;E (Open ↔ pre-DA close) depreciates additions in the year they are placed in service.
 SOURCE: SEC 10-K FY2025 — D&amp;A and PP&amp;E
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="K11" authorId="0" shapeId="0">
       <text>
-        <t>D&amp;A % of PP&amp;E Open
-HOW: Excel equation: I30/I44 (FY25 DA ÷ FY25 PPE). Forecast DA = OpenPPE × this %.
-WHY: Ties DA to the asset base the schedule rolls forward (opens at I44).
+        <t>D&amp;A % of Avg PP&amp;E
+HOW: Rate = I30/I44 (FY25 DA ÷ FY25 PPE). Forecast DA$ = ((Open + Open+CapEx)/2) × rate.
+WHY: MODEL6 fix: prior model depreciated only opening PP&amp;E, so ~$96M of forecast CapEx never hit D&amp;A/FCFF add-back. Average PP&amp;E (Open ↔ pre-DA close) depreciates additions in the year they are placed in service.
 SOURCE: SEC 10-K FY2025 — D&amp;A and PP&amp;E
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="L11" authorId="0" shapeId="0">
       <text>
-        <t>D&amp;A % of PP&amp;E Open
-HOW: Excel equation: I30/I44 (FY25 DA ÷ FY25 PPE). Forecast DA = OpenPPE × this %.
-WHY: Ties DA to the asset base the schedule rolls forward (opens at I44).
+        <t>D&amp;A % of Avg PP&amp;E
+HOW: Rate = I30/I44 (FY25 DA ÷ FY25 PPE). Forecast DA$ = ((Open + Open+CapEx)/2) × rate.
+WHY: MODEL6 fix: prior model depreciated only opening PP&amp;E, so ~$96M of forecast CapEx never hit D&amp;A/FCFF add-back. Average PP&amp;E (Open ↔ pre-DA close) depreciates additions in the year they are placed in service.
 SOURCE: SEC 10-K FY2025 — D&amp;A and PP&amp;E
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="M11" authorId="0" shapeId="0">
       <text>
-        <t>D&amp;A % of PP&amp;E Open
-HOW: Excel equation: I30/I44 (FY25 DA ÷ FY25 PPE). Forecast DA = OpenPPE × this %.
-WHY: Ties DA to the asset base the schedule rolls forward (opens at I44).
+        <t>D&amp;A % of Avg PP&amp;E
+HOW: Rate = I30/I44 (FY25 DA ÷ FY25 PPE). Forecast DA$ = ((Open + Open+CapEx)/2) × rate.
+WHY: MODEL6 fix: prior model depreciated only opening PP&amp;E, so ~$96M of forecast CapEx never hit D&amp;A/FCFF add-back. Average PP&amp;E (Open ↔ pre-DA close) depreciates additions in the year they are placed in service.
 SOURCE: SEC 10-K FY2025 — D&amp;A and PP&amp;E
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="N11" authorId="0" shapeId="0">
       <text>
-        <t>D&amp;A % of PP&amp;E Open
-HOW: Excel equation: I30/I44 (FY25 DA ÷ FY25 PPE). Forecast DA = OpenPPE × this %.
-WHY: Ties DA to the asset base the schedule rolls forward (opens at I44).
+        <t>D&amp;A % of Avg PP&amp;E
+HOW: Rate = I30/I44 (FY25 DA ÷ FY25 PPE). Forecast DA$ = ((Open + Open+CapEx)/2) × rate.
+WHY: MODEL6 fix: prior model depreciated only opening PP&amp;E, so ~$96M of forecast CapEx never hit D&amp;A/FCFF add-back. Average PP&amp;E (Open ↔ pre-DA close) depreciates additions in the year they are placed in service.
 SOURCE: SEC 10-K FY2025 — D&amp;A and PP&amp;E
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="U11" authorId="0" shapeId="0">
       <text>
-        <t>D&amp;A % of PP&amp;E Open
-HOW: Excel equation: I30/I44 (FY25 DA ÷ FY25 PPE). Forecast DA = OpenPPE × this %.
-WHY: Ties DA to the asset base the schedule rolls forward (opens at I44).
+        <t>D&amp;A % of Avg PP&amp;E
+HOW: Rate = I30/I44 (FY25 DA ÷ FY25 PPE). Forecast DA$ = ((Open + Open+CapEx)/2) × rate.
+WHY: MODEL6 fix: prior model depreciated only opening PP&amp;E, so ~$96M of forecast CapEx never hit D&amp;A/FCFF add-back. Average PP&amp;E (Open ↔ pre-DA close) depreciates additions in the year they are placed in service.
 SOURCE: SEC 10-K FY2025 — D&amp;A and PP&amp;E
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
@@ -2348,63 +2350,63 @@
     <comment ref="B15" authorId="0" shapeId="0">
       <text>
         <t>Accounts Receivable (Days)
-HOW: Excel equation: ROUND(I42/I24×365, 0). I42 is net AR (AR − deferred).
-WHY: Operating working-capital view: contract liabilities (deferred revenue) reduce net AR so ΔNWC is not overstated.
-SOURCE: SEC companyfacts XBRL — AR + DeferredRevenueCurrent
+HOW: Excel equation: ROUND(I42/I24×365, 0). I42 is GROSS AR (not net of deferred).
+WHY: MODEL6 fix: DSO must use gross receivables. Deferred Revenue is a contract liability projected separately (WC row 88 = Rev × FY25 Def/Rev). NWC = GrossAR + Inv − AP − Deferred.
+SOURCE: SEC companyfacts XBRL — AR; DeferredRevenueCurrent separate
 LINK: https://data.sec.gov/api/xbrl/companyfacts/CIK0000814547.json</t>
       </text>
     </comment>
     <comment ref="J15" authorId="0" shapeId="0">
       <text>
         <t>Accounts Receivable (Days)
-HOW: Excel equation: ROUND(I42/I24×365, 0). I42 is net AR (AR − deferred).
-WHY: Operating working-capital view: contract liabilities (deferred revenue) reduce net AR so ΔNWC is not overstated.
-SOURCE: SEC companyfacts XBRL — AR + DeferredRevenueCurrent
+HOW: Excel equation: ROUND(I42/I24×365, 0). I42 is GROSS AR (not net of deferred).
+WHY: MODEL6 fix: DSO must use gross receivables. Deferred Revenue is a contract liability projected separately (WC row 88 = Rev × FY25 Def/Rev). NWC = GrossAR + Inv − AP − Deferred.
+SOURCE: SEC companyfacts XBRL — AR; DeferredRevenueCurrent separate
 LINK: https://data.sec.gov/api/xbrl/companyfacts/CIK0000814547.json</t>
       </text>
     </comment>
     <comment ref="K15" authorId="0" shapeId="0">
       <text>
         <t>Accounts Receivable (Days)
-HOW: Excel equation: ROUND(I42/I24×365, 0). I42 is net AR (AR − deferred).
-WHY: Operating working-capital view: contract liabilities (deferred revenue) reduce net AR so ΔNWC is not overstated.
-SOURCE: SEC companyfacts XBRL — AR + DeferredRevenueCurrent
+HOW: Excel equation: ROUND(I42/I24×365, 0). I42 is GROSS AR (not net of deferred).
+WHY: MODEL6 fix: DSO must use gross receivables. Deferred Revenue is a contract liability projected separately (WC row 88 = Rev × FY25 Def/Rev). NWC = GrossAR + Inv − AP − Deferred.
+SOURCE: SEC companyfacts XBRL — AR; DeferredRevenueCurrent separate
 LINK: https://data.sec.gov/api/xbrl/companyfacts/CIK0000814547.json</t>
       </text>
     </comment>
     <comment ref="L15" authorId="0" shapeId="0">
       <text>
         <t>Accounts Receivable (Days)
-HOW: Excel equation: ROUND(I42/I24×365, 0). I42 is net AR (AR − deferred).
-WHY: Operating working-capital view: contract liabilities (deferred revenue) reduce net AR so ΔNWC is not overstated.
-SOURCE: SEC companyfacts XBRL — AR + DeferredRevenueCurrent
+HOW: Excel equation: ROUND(I42/I24×365, 0). I42 is GROSS AR (not net of deferred).
+WHY: MODEL6 fix: DSO must use gross receivables. Deferred Revenue is a contract liability projected separately (WC row 88 = Rev × FY25 Def/Rev). NWC = GrossAR + Inv − AP − Deferred.
+SOURCE: SEC companyfacts XBRL — AR; DeferredRevenueCurrent separate
 LINK: https://data.sec.gov/api/xbrl/companyfacts/CIK0000814547.json</t>
       </text>
     </comment>
     <comment ref="M15" authorId="0" shapeId="0">
       <text>
         <t>Accounts Receivable (Days)
-HOW: Excel equation: ROUND(I42/I24×365, 0). I42 is net AR (AR − deferred).
-WHY: Operating working-capital view: contract liabilities (deferred revenue) reduce net AR so ΔNWC is not overstated.
-SOURCE: SEC companyfacts XBRL — AR + DeferredRevenueCurrent
+HOW: Excel equation: ROUND(I42/I24×365, 0). I42 is GROSS AR (not net of deferred).
+WHY: MODEL6 fix: DSO must use gross receivables. Deferred Revenue is a contract liability projected separately (WC row 88 = Rev × FY25 Def/Rev). NWC = GrossAR + Inv − AP − Deferred.
+SOURCE: SEC companyfacts XBRL — AR; DeferredRevenueCurrent separate
 LINK: https://data.sec.gov/api/xbrl/companyfacts/CIK0000814547.json</t>
       </text>
     </comment>
     <comment ref="N15" authorId="0" shapeId="0">
       <text>
         <t>Accounts Receivable (Days)
-HOW: Excel equation: ROUND(I42/I24×365, 0). I42 is net AR (AR − deferred).
-WHY: Operating working-capital view: contract liabilities (deferred revenue) reduce net AR so ΔNWC is not overstated.
-SOURCE: SEC companyfacts XBRL — AR + DeferredRevenueCurrent
+HOW: Excel equation: ROUND(I42/I24×365, 0). I42 is GROSS AR (not net of deferred).
+WHY: MODEL6 fix: DSO must use gross receivables. Deferred Revenue is a contract liability projected separately (WC row 88 = Rev × FY25 Def/Rev). NWC = GrossAR + Inv − AP − Deferred.
+SOURCE: SEC companyfacts XBRL — AR; DeferredRevenueCurrent separate
 LINK: https://data.sec.gov/api/xbrl/companyfacts/CIK0000814547.json</t>
       </text>
     </comment>
     <comment ref="U15" authorId="0" shapeId="0">
       <text>
         <t>Accounts Receivable (Days)
-HOW: Excel equation: ROUND(I42/I24×365, 0). I42 is net AR (AR − deferred).
-WHY: Operating working-capital view: contract liabilities (deferred revenue) reduce net AR so ΔNWC is not overstated.
-SOURCE: SEC companyfacts XBRL — AR + DeferredRevenueCurrent
+HOW: Excel equation: ROUND(I42/I24×365, 0). I42 is GROSS AR (not net of deferred).
+WHY: MODEL6 fix: DSO must use gross receivables. Deferred Revenue is a contract liability projected separately (WC row 88 = Rev × FY25 Def/Rev). NWC = GrossAR + Inv − AP − Deferred.
+SOURCE: SEC companyfacts XBRL — AR; DeferredRevenueCurrent separate
 LINK: https://data.sec.gov/api/xbrl/companyfacts/CIK0000814547.json</t>
       </text>
     </comment>
@@ -2966,48 +2968,48 @@
     <comment ref="B30" authorId="0" shapeId="0">
       <text>
         <t>D&amp;A $
-WHY: Opening PP&amp;E times D&amp;A%; depreciation follows the asset roll-forward, not a revenue %.
-PATTERN: ={c}92*{c}11
+WHY: Average PP&amp;E times DA% so new CapEx is depreciated in the year added.
+PATTERN: =((Open+Open+CapEx)/2)×DA%
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="J30" authorId="0" shapeId="0">
       <text>
         <t>D&amp;A $
-FORMULA: =J92*J11
-WHY: Opening PP&amp;E times D&amp;A%; depreciation follows the asset roll-forward, not a revenue %.
+FORMULA: =((Open+Open+CapEx)/2)×DA%
+WHY: Average PP&amp;E times DA% so new CapEx is depreciated in the year added.
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="K30" authorId="0" shapeId="0">
       <text>
         <t>D&amp;A $
-FORMULA: =K92*K11
-WHY: Opening PP&amp;E times D&amp;A%; depreciation follows the asset roll-forward, not a revenue %.
+FORMULA: =((Open+Open+CapEx)/2)×DA%
+WHY: Average PP&amp;E times DA% so new CapEx is depreciated in the year added.
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="L30" authorId="0" shapeId="0">
       <text>
         <t>D&amp;A $
-FORMULA: =L92*L11
-WHY: Opening PP&amp;E times D&amp;A%; depreciation follows the asset roll-forward, not a revenue %.
+FORMULA: =((Open+Open+CapEx)/2)×DA%
+WHY: Average PP&amp;E times DA% so new CapEx is depreciated in the year added.
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="M30" authorId="0" shapeId="0">
       <text>
         <t>D&amp;A $
-FORMULA: =M92*M11
-WHY: Opening PP&amp;E times D&amp;A%; depreciation follows the asset roll-forward, not a revenue %.
+FORMULA: =((Open+Open+CapEx)/2)×DA%
+WHY: Average PP&amp;E times DA% so new CapEx is depreciated in the year added.
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="N30" authorId="0" shapeId="0">
       <text>
         <t>D&amp;A $
-FORMULA: =N92*N11
-WHY: Opening PP&amp;E times D&amp;A%; depreciation follows the asset roll-forward, not a revenue %.
+FORMULA: =((Open+Open+CapEx)/2)×DA%
+WHY: Average PP&amp;E times DA% so new CapEx is depreciated in the year added.
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
@@ -3926,144 +3928,144 @@
     <comment ref="B63" authorId="0" shapeId="0">
       <text>
         <t>CF + D&amp;A
-WHY: Adds back non-cash D&amp;A (open PP&amp;E × D&amp;A%) in the cash-from-operations bridge.
-PATTERN: ={c}92*{c}11
+WHY: Adds back non-cash D&amp;A on average PP&amp;E in the cash-from-operations bridge.
+PATTERN: =AvgPPE×DA%
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="J63" authorId="0" shapeId="0">
       <text>
         <t>CF + D&amp;A
-FORMULA: =J92*J11
-WHY: Adds back non-cash D&amp;A (open PP&amp;E × D&amp;A%) in the cash-from-operations bridge.
+FORMULA: =AvgPPE×DA%
+WHY: Adds back non-cash D&amp;A on average PP&amp;E in the cash-from-operations bridge.
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="K63" authorId="0" shapeId="0">
       <text>
         <t>CF + D&amp;A
-FORMULA: =K92*K11
-WHY: Adds back non-cash D&amp;A (open PP&amp;E × D&amp;A%) in the cash-from-operations bridge.
+FORMULA: =AvgPPE×DA%
+WHY: Adds back non-cash D&amp;A on average PP&amp;E in the cash-from-operations bridge.
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="L63" authorId="0" shapeId="0">
       <text>
         <t>CF + D&amp;A
-FORMULA: =L92*L11
-WHY: Adds back non-cash D&amp;A (open PP&amp;E × D&amp;A%) in the cash-from-operations bridge.
+FORMULA: =AvgPPE×DA%
+WHY: Adds back non-cash D&amp;A on average PP&amp;E in the cash-from-operations bridge.
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="M63" authorId="0" shapeId="0">
       <text>
         <t>CF + D&amp;A
-FORMULA: =M92*M11
-WHY: Adds back non-cash D&amp;A (open PP&amp;E × D&amp;A%) in the cash-from-operations bridge.
+FORMULA: =AvgPPE×DA%
+WHY: Adds back non-cash D&amp;A on average PP&amp;E in the cash-from-operations bridge.
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="N63" authorId="0" shapeId="0">
       <text>
         <t>CF + D&amp;A
-FORMULA: =N92*N11
-WHY: Adds back non-cash D&amp;A (open PP&amp;E × D&amp;A%) in the cash-from-operations bridge.
+FORMULA: =AvgPPE×DA%
+WHY: Adds back non-cash D&amp;A on average PP&amp;E in the cash-from-operations bridge.
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="B64" authorId="0" shapeId="0">
       <text>
         <t>CF − ΔNWC
-WHY: Increase in net working capital uses cash; decrease frees cash in the CFO build.
-PATTERN: ={c}88-{p}88
+WHY: ΔNWC from GrossAR+Inv−AP−Deferred; increase uses cash in the CFO build.
+PATTERN: ={c}90
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="J64" authorId="0" shapeId="0">
       <text>
         <t>CF − ΔNWC
-FORMULA: =J88-I88
-WHY: Increase in net working capital uses cash; decrease frees cash in the CFO build.
+FORMULA: =J90
+WHY: ΔNWC from GrossAR+Inv−AP−Deferred; increase uses cash in the CFO build.
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="K64" authorId="0" shapeId="0">
       <text>
         <t>CF − ΔNWC
-FORMULA: =K88-J88
-WHY: Increase in net working capital uses cash; decrease frees cash in the CFO build.
+FORMULA: =K90
+WHY: ΔNWC from GrossAR+Inv−AP−Deferred; increase uses cash in the CFO build.
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="L64" authorId="0" shapeId="0">
       <text>
         <t>CF − ΔNWC
-FORMULA: =L88-K88
-WHY: Increase in net working capital uses cash; decrease frees cash in the CFO build.
+FORMULA: =L90
+WHY: ΔNWC from GrossAR+Inv−AP−Deferred; increase uses cash in the CFO build.
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="M64" authorId="0" shapeId="0">
       <text>
         <t>CF − ΔNWC
-FORMULA: =M88-L88
-WHY: Increase in net working capital uses cash; decrease frees cash in the CFO build.
+FORMULA: =M90
+WHY: ΔNWC from GrossAR+Inv−AP−Deferred; increase uses cash in the CFO build.
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="N64" authorId="0" shapeId="0">
       <text>
         <t>CF − ΔNWC
-FORMULA: =N88-M88
-WHY: Increase in net working capital uses cash; decrease frees cash in the CFO build.
+FORMULA: =N90
+WHY: ΔNWC from GrossAR+Inv−AP−Deferred; increase uses cash in the CFO build.
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="B65" authorId="0" shapeId="0">
       <text>
         <t>Cash from operations
-WHY: Full CFO: NI + D&amp;A − ΔNWC written as one equation, not assembled from pointers.
-PATTERN: ={c}33*(1-{c}13)+{c}92*{c}11-({c}88-{p}88)
+WHY: Full CFO: NI + avg-PPE D&amp;A − ΔNWC written as one equation.
+PATTERN: =NI+DA−ΔNWC
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="J65" authorId="0" shapeId="0">
       <text>
         <t>Cash from operations
-FORMULA: =J33*(1-J13)+J92*J11-(J88-I88)
-WHY: Full CFO: NI + D&amp;A − ΔNWC written as one equation, not assembled from pointers.
+FORMULA: =NI+DA−ΔNWC
+WHY: Full CFO: NI + avg-PPE D&amp;A − ΔNWC written as one equation.
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="K65" authorId="0" shapeId="0">
       <text>
         <t>Cash from operations
-FORMULA: =K33*(1-K13)+K92*K11-(K88-J88)
-WHY: Full CFO: NI + D&amp;A − ΔNWC written as one equation, not assembled from pointers.
+FORMULA: =NI+DA−ΔNWC
+WHY: Full CFO: NI + avg-PPE D&amp;A − ΔNWC written as one equation.
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="L65" authorId="0" shapeId="0">
       <text>
         <t>Cash from operations
-FORMULA: =L33*(1-L13)+L92*L11-(L88-K88)
-WHY: Full CFO: NI + D&amp;A − ΔNWC written as one equation, not assembled from pointers.
+FORMULA: =NI+DA−ΔNWC
+WHY: Full CFO: NI + avg-PPE D&amp;A − ΔNWC written as one equation.
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="M65" authorId="0" shapeId="0">
       <text>
         <t>Cash from operations
-FORMULA: =M33*(1-M13)+M92*M11-(M88-L88)
-WHY: Full CFO: NI + D&amp;A − ΔNWC written as one equation, not assembled from pointers.
+FORMULA: =NI+DA−ΔNWC
+WHY: Full CFO: NI + avg-PPE D&amp;A − ΔNWC written as one equation.
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="N65" authorId="0" shapeId="0">
       <text>
         <t>Cash from operations
-FORMULA: =N33*(1-N13)+N92*N11-(N88-M88)
-WHY: Full CFO: NI + D&amp;A − ΔNWC written as one equation, not assembled from pointers.
+FORMULA: =NI+DA−ΔNWC
+WHY: Full CFO: NI + avg-PPE D&amp;A − ΔNWC written as one equation.
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
@@ -4501,49 +4503,49 @@
     </comment>
     <comment ref="B85" authorId="0" shapeId="0">
       <text>
-        <t>WC: AR
-WHY: Working-capital schedule AR mirrors the balance-sheet AR used in ΔNWC.
+        <t>WC: Gross AR
+WHY: WC gross AR mirrors BS gross AR used in standard DSO.
 PATTERN: ={c}42
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="J85" authorId="0" shapeId="0">
       <text>
-        <t>WC: AR
+        <t>WC: Gross AR
 FORMULA: =J42
-WHY: Working-capital schedule AR mirrors the balance-sheet AR used in ΔNWC.
+WHY: WC gross AR mirrors BS gross AR used in standard DSO.
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="K85" authorId="0" shapeId="0">
       <text>
-        <t>WC: AR
+        <t>WC: Gross AR
 FORMULA: =K42
-WHY: Working-capital schedule AR mirrors the balance-sheet AR used in ΔNWC.
+WHY: WC gross AR mirrors BS gross AR used in standard DSO.
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="L85" authorId="0" shapeId="0">
       <text>
-        <t>WC: AR
+        <t>WC: Gross AR
 FORMULA: =L42
-WHY: Working-capital schedule AR mirrors the balance-sheet AR used in ΔNWC.
+WHY: WC gross AR mirrors BS gross AR used in standard DSO.
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="M85" authorId="0" shapeId="0">
       <text>
-        <t>WC: AR
+        <t>WC: Gross AR
 FORMULA: =M42
-WHY: Working-capital schedule AR mirrors the balance-sheet AR used in ΔNWC.
+WHY: WC gross AR mirrors BS gross AR used in standard DSO.
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="N85" authorId="0" shapeId="0">
       <text>
-        <t>WC: AR
+        <t>WC: Gross AR
 FORMULA: =N42
-WHY: Working-capital schedule AR mirrors the balance-sheet AR used in ΔNWC.
+WHY: WC gross AR mirrors BS gross AR used in standard DSO.
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
@@ -4645,96 +4647,144 @@
     </comment>
     <comment ref="B88" authorId="0" shapeId="0">
       <text>
+        <t>WC: Deferred Revenue
+WHY: Contract liability projected at FY25 deferred/sales; separate from AR.
+PATTERN: ={c}24×(I88/I24)
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
+      </text>
+    </comment>
+    <comment ref="J88" authorId="0" shapeId="0">
+      <text>
+        <t>WC: Deferred Revenue
+FORMULA: =J24×(I88/I24)
+WHY: Contract liability projected at FY25 deferred/sales; separate from AR.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
+      </text>
+    </comment>
+    <comment ref="K88" authorId="0" shapeId="0">
+      <text>
+        <t>WC: Deferred Revenue
+FORMULA: =K24×(I88/I24)
+WHY: Contract liability projected at FY25 deferred/sales; separate from AR.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
+      </text>
+    </comment>
+    <comment ref="L88" authorId="0" shapeId="0">
+      <text>
+        <t>WC: Deferred Revenue
+FORMULA: =L24×(I88/I24)
+WHY: Contract liability projected at FY25 deferred/sales; separate from AR.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
+      </text>
+    </comment>
+    <comment ref="M88" authorId="0" shapeId="0">
+      <text>
+        <t>WC: Deferred Revenue
+FORMULA: =M24×(I88/I24)
+WHY: Contract liability projected at FY25 deferred/sales; separate from AR.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
+      </text>
+    </comment>
+    <comment ref="N88" authorId="0" shapeId="0">
+      <text>
+        <t>WC: Deferred Revenue
+FORMULA: =N24×(I88/I24)
+WHY: Contract liability projected at FY25 deferred/sales; separate from AR.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
+      </text>
+    </comment>
+    <comment ref="B89" authorId="0" shapeId="0">
+      <text>
         <t>Net working capital
-WHY: AR + inventory − AP; operating NWC (deferred already netted in AR).
-PATTERN: ={c}85+{c}86-{c}87
-LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
-      </text>
-    </comment>
-    <comment ref="J88" authorId="0" shapeId="0">
+WHY: GrossAR + inventory − AP − Deferred; standard operating NWC.
+PATTERN: ={c}85+{c}86-{c}87-{c}88
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
+      </text>
+    </comment>
+    <comment ref="J89" authorId="0" shapeId="0">
       <text>
         <t>Net working capital
-FORMULA: =J85+J86-J87
-WHY: AR + inventory − AP; operating NWC (deferred already netted in AR).
-LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
-      </text>
-    </comment>
-    <comment ref="K88" authorId="0" shapeId="0">
+FORMULA: =J85+J86-J87-J88
+WHY: GrossAR + inventory − AP − Deferred; standard operating NWC.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
+      </text>
+    </comment>
+    <comment ref="K89" authorId="0" shapeId="0">
       <text>
         <t>Net working capital
-FORMULA: =K85+K86-K87
-WHY: AR + inventory − AP; operating NWC (deferred already netted in AR).
-LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
-      </text>
-    </comment>
-    <comment ref="L88" authorId="0" shapeId="0">
+FORMULA: =K85+K86-K87-K88
+WHY: GrossAR + inventory − AP − Deferred; standard operating NWC.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
+      </text>
+    </comment>
+    <comment ref="L89" authorId="0" shapeId="0">
       <text>
         <t>Net working capital
-FORMULA: =L85+L86-L87
-WHY: AR + inventory − AP; operating NWC (deferred already netted in AR).
-LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
-      </text>
-    </comment>
-    <comment ref="M88" authorId="0" shapeId="0">
+FORMULA: =L85+L86-L87-L88
+WHY: GrossAR + inventory − AP − Deferred; standard operating NWC.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
+      </text>
+    </comment>
+    <comment ref="M89" authorId="0" shapeId="0">
       <text>
         <t>Net working capital
-FORMULA: =M85+M86-M87
-WHY: AR + inventory − AP; operating NWC (deferred already netted in AR).
-LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
-      </text>
-    </comment>
-    <comment ref="N88" authorId="0" shapeId="0">
+FORMULA: =M85+M86-M87-M88
+WHY: GrossAR + inventory − AP − Deferred; standard operating NWC.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
+      </text>
+    </comment>
+    <comment ref="N89" authorId="0" shapeId="0">
       <text>
         <t>Net working capital
-FORMULA: =N85+N86-N87
-WHY: AR + inventory − AP; operating NWC (deferred already netted in AR).
-LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
-      </text>
-    </comment>
-    <comment ref="B89" authorId="0" shapeId="0">
+FORMULA: =N85+N86-N87-N88
+WHY: GrossAR + inventory − AP − Deferred; standard operating NWC.
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
+      </text>
+    </comment>
+    <comment ref="B90" authorId="0" shapeId="0">
       <text>
         <t>Change in NWC
 WHY: Year-over-year NWC change; the cash investment/(release) used in CFO and FCFF.
-PATTERN: ={c}88-{p}88
-LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
-      </text>
-    </comment>
-    <comment ref="J89" authorId="0" shapeId="0">
+PATTERN: ={c}89-{p}89
+LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
+      </text>
+    </comment>
+    <comment ref="J90" authorId="0" shapeId="0">
       <text>
         <t>Change in NWC
-FORMULA: =J88-I88
+FORMULA: =J89-I89
 WHY: Year-over-year NWC change; the cash investment/(release) used in CFO and FCFF.
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="K89" authorId="0" shapeId="0">
+    <comment ref="K90" authorId="0" shapeId="0">
       <text>
         <t>Change in NWC
-FORMULA: =K88-J88
+FORMULA: =K89-J89
 WHY: Year-over-year NWC change; the cash investment/(release) used in CFO and FCFF.
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="L89" authorId="0" shapeId="0">
+    <comment ref="L90" authorId="0" shapeId="0">
       <text>
         <t>Change in NWC
-FORMULA: =L88-K88
+FORMULA: =L89-K89
 WHY: Year-over-year NWC change; the cash investment/(release) used in CFO and FCFF.
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="M89" authorId="0" shapeId="0">
+    <comment ref="M90" authorId="0" shapeId="0">
       <text>
         <t>Change in NWC
-FORMULA: =M88-L88
+FORMULA: =M89-L89
 WHY: Year-over-year NWC change; the cash investment/(release) used in CFO and FCFF.
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="N89" authorId="0" shapeId="0">
+    <comment ref="N90" authorId="0" shapeId="0">
       <text>
         <t>Change in NWC
-FORMULA: =N88-M88
+FORMULA: =N89-M89
 WHY: Year-over-year NWC change; the cash investment/(release) used in CFO and FCFF.
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
@@ -4838,48 +4888,48 @@
     <comment ref="B94" authorId="0" shapeId="0">
       <text>
         <t>PPE − D&amp;A
-WHY: Depreciation on opening PP&amp;E; reduces net PP&amp;E in the roll-forward.
-PATTERN: ={c}92*{c}11
+WHY: Depreciation on average PP&amp;E; reduces net PP&amp;E and adds back in FCFF.
+PATTERN: =((Open+Open+CapEx)/2)×DA%
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="J94" authorId="0" shapeId="0">
       <text>
         <t>PPE − D&amp;A
-FORMULA: =J92*J11
-WHY: Depreciation on opening PP&amp;E; reduces net PP&amp;E in the roll-forward.
+FORMULA: =((Open+Open+CapEx)/2)×DA%
+WHY: Depreciation on average PP&amp;E; reduces net PP&amp;E and adds back in FCFF.
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="K94" authorId="0" shapeId="0">
       <text>
         <t>PPE − D&amp;A
-FORMULA: =K92*K11
-WHY: Depreciation on opening PP&amp;E; reduces net PP&amp;E in the roll-forward.
+FORMULA: =((Open+Open+CapEx)/2)×DA%
+WHY: Depreciation on average PP&amp;E; reduces net PP&amp;E and adds back in FCFF.
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="L94" authorId="0" shapeId="0">
       <text>
         <t>PPE − D&amp;A
-FORMULA: =L92*L11
-WHY: Depreciation on opening PP&amp;E; reduces net PP&amp;E in the roll-forward.
+FORMULA: =((Open+Open+CapEx)/2)×DA%
+WHY: Depreciation on average PP&amp;E; reduces net PP&amp;E and adds back in FCFF.
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="M94" authorId="0" shapeId="0">
       <text>
         <t>PPE − D&amp;A
-FORMULA: =M92*M11
-WHY: Depreciation on opening PP&amp;E; reduces net PP&amp;E in the roll-forward.
+FORMULA: =((Open+Open+CapEx)/2)×DA%
+WHY: Depreciation on average PP&amp;E; reduces net PP&amp;E and adds back in FCFF.
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
     <comment ref="N94" authorId="0" shapeId="0">
       <text>
         <t>PPE − D&amp;A
-FORMULA: =N92*N11
-WHY: Depreciation on opening PP&amp;E; reduces net PP&amp;E in the roll-forward.
+FORMULA: =((Open+Open+CapEx)/2)×DA%
+WHY: Depreciation on average PP&amp;E; reduces net PP&amp;E and adds back in FCFF.
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
@@ -5130,7 +5180,7 @@
 <file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
-    <author>vengeanceaiUSCMODEL5</author>
+    <author>vengeanceaiUSCMODEL6</author>
   </authors>
   <commentList>
     <comment ref="D6" authorId="0" shapeId="0">
@@ -6005,7 +6055,7 @@
       <c r="B12" s="74" t="n"/>
       <c r="C12" s="75" t="inlineStr">
         <is>
-          <t>FICO — vengeanceaiUSCMODEL5 (3-Statement + DCF)</t>
+          <t>FICO — vengeanceaiUSCMODEL6 (3-Statement + DCF)</t>
         </is>
       </c>
       <c r="D12" s="74" t="n"/>
@@ -6173,7 +6223,7 @@
       <c r="B21" s="85" t="n"/>
       <c r="C21" s="85" t="inlineStr">
         <is>
-          <t>vengeanceaiUSCMODEL5: same hist-linked Excel drivers as MODEL4, plus every Source is a clickable URL (3-statement U/V, DCF U/V, Cover source index). WACC=9.24%, Exit 25x. Open in Excel to recalculate. Click Cover Source Index (cols E–G) or 3S/DCF col U/V for filings.</t>
+          <t>vengeanceaiUSCMODEL6: D&amp;A on avg PP&amp;E (new CapEx depreciated); gross AR days + separate Deferred Revenue in NWC; SGA floor 20% / grind −25bps. WACC=9.24%, Exit 25x. Every Source is a clickable URL. Click Cover Source Index (cols E–G) or 3S/DCF col U/V for filings.</t>
         </is>
       </c>
       <c r="D21" s="85" t="n"/>
@@ -6235,7 +6285,7 @@
       <c r="D24" s="89" t="n"/>
       <c r="E24" s="133" t="inlineStr">
         <is>
-          <t>vengeanceaiUSCMODEL5 — SOURCE INDEX (click any link)</t>
+          <t>vengeanceaiUSCMODEL6 — SOURCE INDEX (click any link)</t>
         </is>
       </c>
       <c r="H24" s="89" t="n"/>
@@ -6767,7 +6817,7 @@
     <row r="4">
       <c r="B4" s="146" t="inlineStr">
         <is>
-          <t>vengeanceaiUSCMODEL5: hover J–N for WHY+SOURCE; click blue Source link in col U (or LINK: URL in col C / V) to open the filing</t>
+          <t>vengeanceaiUSCMODEL6: hover J–N for WHY+SOURCE; click blue Source link in col U (or LINK: URL in col C / V) to open the filing</t>
         </is>
       </c>
       <c r="P4" s="147" t="inlineStr">
@@ -7010,12 +7060,12 @@
     <row r="9" hidden="1" outlineLevel="1" ht="40" customHeight="1">
       <c r="B9" s="19" t="inlineStr">
         <is>
-          <t>SGA % of Revenue (equation)</t>
+          <t>SGA % of Revenue (floor 20%, −25bps×t)</t>
         </is>
       </c>
       <c r="C9" s="150" t="inlineStr">
         <is>
-          <t>WHY: Normalize one-time restructuring ($10.9M). Mild efficiency grind reflects operating leverage as revenue scales; floor… | SOURCE: SEC 10-K FY2025 — SG&amp;A + restructuring note | LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm | HOW: Equation: (I28 − 10,922)/I24 − 50bps × year. Strips FY25 restructuring; then −0.5% of sales each year.</t>
+          <t>WHY: MODEL6 fix: enterprise software needs lasting G&amp;A (sales, legal, compliance). Floor raised from 5%→20%; grind cut fro… | SOURCE: SEC 10-K FY2025 — SG&amp;A + restructuring note | LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm | HOW: Equation: MAX(20%, (I28 − 10,922)/I24 − 25bps × year). Strips FY25 restructuring; then −0.25% of sales each year.</t>
         </is>
       </c>
       <c r="D9" s="47" t="n"/>
@@ -7040,23 +7090,23 @@
         <v/>
       </c>
       <c r="J9" s="157">
-        <f>MAX(0.05,(($I$28-10922.0)/$I$24)-0.005)</f>
+        <f>MAX(0.2,(($I$28-10922.0)/$I$24)-0.0025)</f>
         <v/>
       </c>
       <c r="K9" s="157">
-        <f>MAX(0.05,(($I$28-10922.0)/$I$24)-0.01)</f>
+        <f>MAX(0.2,(($I$28-10922.0)/$I$24)-0.005)</f>
         <v/>
       </c>
       <c r="L9" s="157">
-        <f>MAX(0.05,(($I$28-10922.0)/$I$24)-0.015)</f>
+        <f>MAX(0.2,(($I$28-10922.0)/$I$24)-0.0075)</f>
         <v/>
       </c>
       <c r="M9" s="157">
-        <f>MAX(0.05,(($I$28-10922.0)/$I$24)-0.02)</f>
+        <f>MAX(0.2,(($I$28-10922.0)/$I$24)-0.01)</f>
         <v/>
       </c>
       <c r="N9" s="157">
-        <f>MAX(0.05,(($I$28-10922.0)/$I$24)-0.025)</f>
+        <f>MAX(0.2,(($I$28-10922.0)/$I$24)-0.0125)</f>
         <v/>
       </c>
       <c r="P9" s="152" t="n">
@@ -7074,12 +7124,12 @@
       </c>
       <c r="S9" s="153" t="inlineStr">
         <is>
-          <t>Equation: (I28 − 10,922)/I24 − 50bps × year. Strips FY25 restructuring; then −0.5% of sales each year.</t>
+          <t>Equation: MAX(20%, (I28 − 10,922)/I24 − 25bps × year). Strips FY25 restructuring; then −0.25% of sales each year.</t>
         </is>
       </c>
       <c r="T9" s="153" t="inlineStr">
         <is>
-          <t>Normalize one-time restructuring ($10.9M). Mild efficiency grind reflects operating leverage as revenue scales; floored at 5%.</t>
+          <t>MODEL6 fix: enterprise software needs lasting G&amp;A (sales, legal, compliance). Floor raised from 5%→20%; grind cut from 50→25 bps so SGA stays in a realistic ~22–25% band near FY25 normalized (~25%).</t>
         </is>
       </c>
       <c r="U9" s="154" t="inlineStr">
@@ -7182,12 +7232,12 @@
     <row r="11" hidden="1" outlineLevel="1" ht="40" customHeight="1">
       <c r="B11" s="19" t="inlineStr">
         <is>
-          <t>Depreciation &amp; Amortization (% of PP&amp;E Open Bal)</t>
+          <t>D&amp;A % of Avg PP&amp;E (rate=FY25 DA/PPE; $ uses avg base)</t>
         </is>
       </c>
       <c r="C11" s="150" t="inlineStr">
         <is>
-          <t>WHY: Ties DA to the asset base the schedule rolls forward (opens at I44). | SOURCE: SEC 10-K FY2025 — D&amp;A and PP&amp;E | LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm | HOW: Excel equation: I30/I44 (FY25 DA ÷ FY25 PPE). Forecast DA = OpenPPE × this %.</t>
+          <t>WHY: MODEL6 fix: prior model depreciated only opening PP&amp;E, so ~$96M of forecast CapEx never hit D&amp;A/FCFF add-back. Averag… | SOURCE: SEC 10-K FY2025 — D&amp;A and PP&amp;E | LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm | HOW: Rate = I30/I44 (FY25 DA ÷ FY25 PPE). Forecast DA$ = ((Open + Open+CapEx)/2) × rate.</t>
         </is>
       </c>
       <c r="D11" s="47" t="n"/>
@@ -7236,22 +7286,22 @@
       </c>
       <c r="Q11" s="152" t="inlineStr">
         <is>
-          <t>D&amp;A % of PP&amp;E Open</t>
+          <t>D&amp;A % of Avg PP&amp;E</t>
         </is>
       </c>
       <c r="R11" s="153" t="inlineStr">
         <is>
-          <t>Depreciation &amp; amortization as % of opening net PP&amp;E.</t>
+          <t>Depreciation rate from FY25; dollars applied to average PP&amp;E so new CapEx is depreciated.</t>
         </is>
       </c>
       <c r="S11" s="153" t="inlineStr">
         <is>
-          <t>Excel equation: I30/I44 (FY25 DA ÷ FY25 PPE). Forecast DA = OpenPPE × this %.</t>
+          <t>Rate = I30/I44 (FY25 DA ÷ FY25 PPE). Forecast DA$ = ((Open + Open+CapEx)/2) × rate.</t>
         </is>
       </c>
       <c r="T11" s="153" t="inlineStr">
         <is>
-          <t>Ties DA to the asset base the schedule rolls forward (opens at I44).</t>
+          <t>MODEL6 fix: prior model depreciated only opening PP&amp;E, so ~$96M of forecast CapEx never hit D&amp;A/FCFF add-back. Average PP&amp;E (Open ↔ pre-DA close) depreciates additions in the year they are placed in service.</t>
         </is>
       </c>
       <c r="U11" s="154" t="inlineStr">
@@ -7464,7 +7514,7 @@
       </c>
       <c r="C15" s="158" t="inlineStr">
         <is>
-          <t>WHY: Operating working-capital view: contract liabilities (deferred revenue) reduce net AR so ΔNWC is not overstated. | SOURCE: SEC companyfacts XBRL — AR + DeferredRevenueCurrent | LINK: https://data.sec.gov/api/xbrl/companyfacts/CIK0000814547.json | HOW: Excel equation: ROUND(I42/I24×365, 0). I42 is net AR (AR − deferred).</t>
+          <t>WHY: MODEL6 fix: DSO must use gross receivables. Deferred Revenue is a contract liability projected separately (WC row 88 … | SOURCE: SEC companyfacts XBRL — AR; DeferredRevenueCurrent separate | LINK: https://data.sec.gov/api/xbrl/companyfacts/CIK0000814547.json | HOW: Excel equation: ROUND(I42/I24×365, 0). I42 is GROSS AR (not net of deferred).</t>
         </is>
       </c>
       <c r="D15" s="32" t="n"/>
@@ -7518,22 +7568,22 @@
       </c>
       <c r="R15" s="153" t="inlineStr">
         <is>
-          <t>AR days sales outstanding used to project AR = Rev × days/365.</t>
+          <t>Standard DSO: gross AR days used to project Gross AR = Rev × days/365.</t>
         </is>
       </c>
       <c r="S15" s="153" t="inlineStr">
         <is>
-          <t>Excel equation: ROUND(I42/I24×365, 0). I42 is net AR (AR − deferred).</t>
+          <t>Excel equation: ROUND(I42/I24×365, 0). I42 is GROSS AR (not net of deferred).</t>
         </is>
       </c>
       <c r="T15" s="153" t="inlineStr">
         <is>
-          <t>Operating working-capital view: contract liabilities (deferred revenue) reduce net AR so ΔNWC is not overstated.</t>
+          <t>MODEL6 fix: DSO must use gross receivables. Deferred Revenue is a contract liability projected separately (WC row 88 = Rev × FY25 Def/Rev). NWC = GrossAR + Inv − AP − Deferred.</t>
         </is>
       </c>
       <c r="U15" s="154" t="inlineStr">
         <is>
-          <t>SEC companyfacts XBRL — AR + DeferredRevenueCurrent</t>
+          <t>SEC companyfacts XBRL — AR; DeferredRevenueCurrent separate</t>
         </is>
       </c>
       <c r="V15" s="154" t="inlineStr">
@@ -8267,7 +8317,7 @@
       </c>
       <c r="C30" s="166" t="inlineStr">
         <is>
-          <t>eqn: PPE_open × DA%</t>
+          <t>eqn: AvgPPE × DA%  — Avg=(Open+Open+CapEx)/2</t>
         </is>
       </c>
       <c r="E30" s="163" t="n">
@@ -8286,23 +8336,23 @@
         <v>14952</v>
       </c>
       <c r="J30" s="159">
-        <f>J92*J11</f>
+        <f>((J92+(J92+J93))/2)*J11</f>
         <v/>
       </c>
       <c r="K30" s="159">
-        <f>K92*K11</f>
+        <f>((K92+(K92+K93))/2)*K11</f>
         <v/>
       </c>
       <c r="L30" s="159">
-        <f>L92*L11</f>
+        <f>((L92+(L92+L93))/2)*L11</f>
         <v/>
       </c>
       <c r="M30" s="159">
-        <f>M92*M11</f>
+        <f>((M92+(M92+M93))/2)*M11</f>
         <v/>
       </c>
       <c r="N30" s="159">
-        <f>N92*N11</f>
+        <f>((N92+(N92+N93))/2)*N11</f>
         <v/>
       </c>
     </row>
@@ -8527,7 +8577,7 @@
       </c>
       <c r="C36" s="170" t="inlineStr">
         <is>
-          <t>eqn: EBT × (1 − tax%)  — grows with Rev×(1+g)</t>
+          <t>eqn: EBT × (1 − tax%)</t>
         </is>
       </c>
       <c r="D36" s="40" t="n"/>
@@ -8672,23 +8722,23 @@
       </c>
       <c r="C42" s="166" t="inlineStr">
         <is>
-          <t>eqn: Rev × AR_days / 365</t>
+          <t>eqn: Rev × GROSS AR_days / 365</t>
         </is>
       </c>
       <c r="E42" s="163" t="n">
-        <v>206690</v>
+        <v>312107</v>
       </c>
       <c r="F42" s="163" t="n">
-        <v>202365</v>
+        <v>322410</v>
       </c>
       <c r="G42" s="163" t="n">
-        <v>251217</v>
+        <v>387947</v>
       </c>
       <c r="H42" s="163" t="n">
-        <v>269745</v>
+        <v>426642</v>
       </c>
       <c r="I42" s="163" t="n">
-        <v>341776</v>
+        <v>529148</v>
       </c>
       <c r="J42" s="159">
         <f>J24*J15/365</f>
@@ -8966,46 +9016,50 @@
           <t>Total Liabilities</t>
         </is>
       </c>
-      <c r="C50" s="4" t="n"/>
+      <c r="C50" s="164" t="inlineStr">
+        <is>
+          <t>eqn: AP + Debt + DeferredRev</t>
+        </is>
+      </c>
       <c r="D50" s="22" t="n"/>
-      <c r="E50" s="165">
-        <f>SUM(E48:E49)</f>
-        <v/>
-      </c>
-      <c r="F50" s="165">
-        <f>SUM(F48:F49)</f>
-        <v/>
-      </c>
-      <c r="G50" s="165">
-        <f>SUM(G48:G49)</f>
-        <v/>
-      </c>
-      <c r="H50" s="165">
-        <f>SUM(H48:H49)</f>
-        <v/>
-      </c>
-      <c r="I50" s="165">
-        <f>SUM(I48:I49)</f>
+      <c r="E50" s="172">
+        <f>E48+E49+E88</f>
+        <v/>
+      </c>
+      <c r="F50" s="172">
+        <f>F48+F49+F88</f>
+        <v/>
+      </c>
+      <c r="G50" s="172">
+        <f>G48+G49+G88</f>
+        <v/>
+      </c>
+      <c r="H50" s="172">
+        <f>H48+H49+H88</f>
+        <v/>
+      </c>
+      <c r="I50" s="172">
+        <f>I48+I49+I88</f>
         <v/>
       </c>
       <c r="J50" s="159">
-        <f>SUM(J48:J49)</f>
+        <f>J48+J49+J88</f>
         <v/>
       </c>
       <c r="K50" s="159">
-        <f>SUM(K48:K49)</f>
+        <f>K48+K49+K88</f>
         <v/>
       </c>
       <c r="L50" s="159">
-        <f>SUM(L48:L49)</f>
+        <f>L48+L49+L88</f>
         <v/>
       </c>
       <c r="M50" s="159">
-        <f>SUM(M48:M49)</f>
+        <f>M48+M49+M88</f>
         <v/>
       </c>
       <c r="N50" s="159">
-        <f>SUM(N48:N49)</f>
+        <f>N48+N49+N88</f>
         <v/>
       </c>
     </row>
@@ -9118,23 +9172,23 @@
       </c>
       <c r="C54" s="8" t="n"/>
       <c r="D54" s="26" t="n"/>
-      <c r="E54" s="172">
+      <c r="E54" s="173">
         <f>SUM(E52:E53)</f>
         <v/>
       </c>
-      <c r="F54" s="172">
+      <c r="F54" s="173">
         <f>SUM(F52:F53)</f>
         <v/>
       </c>
-      <c r="G54" s="172">
+      <c r="G54" s="173">
         <f>SUM(G52:G53)</f>
         <v/>
       </c>
-      <c r="H54" s="172">
+      <c r="H54" s="173">
         <f>SUM(H52:H53)</f>
         <v/>
       </c>
-      <c r="I54" s="172">
+      <c r="I54" s="173">
         <f>SUM(I52:I53)</f>
         <v/>
       </c>
@@ -9228,23 +9282,23 @@
       </c>
       <c r="C57" s="9" t="n"/>
       <c r="D57" s="27" t="n"/>
-      <c r="E57" s="173">
+      <c r="E57" s="174">
         <f>E55-E45</f>
         <v/>
       </c>
-      <c r="F57" s="173">
+      <c r="F57" s="174">
         <f>F55-F45</f>
         <v/>
       </c>
-      <c r="G57" s="173">
+      <c r="G57" s="174">
         <f>G55-G45</f>
         <v/>
       </c>
-      <c r="H57" s="173">
+      <c r="H57" s="174">
         <f>H55-H45</f>
         <v/>
       </c>
-      <c r="I57" s="173">
+      <c r="I57" s="174">
         <f>I55-I45</f>
         <v/>
       </c>
@@ -9330,26 +9384,26 @@
       </c>
       <c r="C62" s="166" t="inlineStr">
         <is>
-          <t>eqn: EBT × (1 − tax%)  — full eqn, not pointer to IS</t>
-        </is>
-      </c>
-      <c r="E62" s="174">
+          <t>eqn: EBT × (1 − tax%)</t>
+        </is>
+      </c>
+      <c r="E62" s="175">
         <f>E36</f>
         <v/>
       </c>
-      <c r="F62" s="174">
+      <c r="F62" s="175">
         <f>F36</f>
         <v/>
       </c>
-      <c r="G62" s="174">
+      <c r="G62" s="175">
         <f>G36</f>
         <v/>
       </c>
-      <c r="H62" s="174">
+      <c r="H62" s="175">
         <f>H36</f>
         <v/>
       </c>
-      <c r="I62" s="174">
+      <c r="I62" s="175">
         <f>I36</f>
         <v/>
       </c>
@@ -9382,47 +9436,47 @@
       </c>
       <c r="C63" s="166" t="inlineStr">
         <is>
-          <t>eqn: PPE_open × DA%</t>
-        </is>
-      </c>
-      <c r="E63" s="174">
+          <t>eqn: AvgPPE × DA%</t>
+        </is>
+      </c>
+      <c r="E63" s="175">
         <f>+E30</f>
         <v/>
       </c>
-      <c r="F63" s="174">
+      <c r="F63" s="175">
         <f>+F30</f>
         <v/>
       </c>
-      <c r="G63" s="174">
+      <c r="G63" s="175">
         <f>+G30</f>
         <v/>
       </c>
-      <c r="H63" s="174">
+      <c r="H63" s="175">
         <f>+H30</f>
         <v/>
       </c>
-      <c r="I63" s="174">
+      <c r="I63" s="175">
         <f>+I30</f>
         <v/>
       </c>
       <c r="J63" s="159">
-        <f>J92*J11</f>
+        <f>((J92+(J92+J93))/2)*J11</f>
         <v/>
       </c>
       <c r="K63" s="159">
-        <f>K92*K11</f>
+        <f>((K92+(K92+K93))/2)*K11</f>
         <v/>
       </c>
       <c r="L63" s="159">
-        <f>L92*L11</f>
+        <f>((L92+(L92+L93))/2)*L11</f>
         <v/>
       </c>
       <c r="M63" s="159">
-        <f>M92*M11</f>
+        <f>((M92+(M92+M93))/2)*M11</f>
         <v/>
       </c>
       <c r="N63" s="159">
-        <f>N92*N11</f>
+        <f>((N92+(N92+N93))/2)*N11</f>
         <v/>
       </c>
     </row>
@@ -9434,7 +9488,7 @@
       </c>
       <c r="C64" s="166" t="inlineStr">
         <is>
-          <t>eqn: NWC_t − NWC_t−1</t>
+          <t>eqn: NWC_t − NWC_t−1  (NWC=AR+Inv−AP−Deferred)</t>
         </is>
       </c>
       <c r="E64" s="163" t="n">
@@ -9453,23 +9507,23 @@
         <v>62189</v>
       </c>
       <c r="J64" s="159">
-        <f>J88-I88</f>
+        <f>J90</f>
         <v/>
       </c>
       <c r="K64" s="159">
-        <f>K88-J88</f>
+        <f>K90</f>
         <v/>
       </c>
       <c r="L64" s="159">
-        <f>L88-K88</f>
+        <f>L90</f>
         <v/>
       </c>
       <c r="M64" s="159">
-        <f>M88-L88</f>
+        <f>M90</f>
         <v/>
       </c>
       <c r="N64" s="159">
-        <f>N88-M88</f>
+        <f>N90</f>
         <v/>
       </c>
     </row>
@@ -9506,23 +9560,23 @@
         <v/>
       </c>
       <c r="J65" s="159">
-        <f>J33*(1-J13)+J92*J11-(J88-I88)</f>
+        <f>J33*(1-J13)+(((J92+(J92+J93))/2)*J11)-J90</f>
         <v/>
       </c>
       <c r="K65" s="159">
-        <f>K33*(1-K13)+K92*K11-(K88-J88)</f>
+        <f>K33*(1-K13)+(((K92+(K92+K93))/2)*K11)-K90</f>
         <v/>
       </c>
       <c r="L65" s="159">
-        <f>L33*(1-L13)+L92*L11-(L88-K88)</f>
+        <f>L33*(1-L13)+(((L92+(L92+L93))/2)*L11)-L90</f>
         <v/>
       </c>
       <c r="M65" s="159">
-        <f>M33*(1-M13)+M92*M11-(M88-L88)</f>
+        <f>M33*(1-M13)+(((M92+(M92+M93))/2)*M11)-M90</f>
         <v/>
       </c>
       <c r="N65" s="159">
-        <f>N33*(1-N13)+N92*N11-(N88-M88)</f>
+        <f>N33*(1-N13)+(((N92+(N92+N93))/2)*N11)-N90</f>
         <v/>
       </c>
     </row>
@@ -9845,23 +9899,23 @@
           <t>eqn: CFO − CapEx + Financing</t>
         </is>
       </c>
-      <c r="E76" s="175">
+      <c r="E76" s="176">
         <f>E41-E77</f>
         <v/>
       </c>
-      <c r="F76" s="175">
+      <c r="F76" s="176">
         <f>F41-F77</f>
         <v/>
       </c>
-      <c r="G76" s="175">
+      <c r="G76" s="176">
         <f>G41-G77</f>
         <v/>
       </c>
-      <c r="H76" s="175">
+      <c r="H76" s="176">
         <f>H41-H77</f>
         <v/>
       </c>
-      <c r="I76" s="175">
+      <c r="I76" s="176">
         <f>I41-I77</f>
         <v/>
       </c>
@@ -9895,19 +9949,19 @@
       <c r="E77" s="163" t="n">
         <v>157394</v>
       </c>
-      <c r="F77" s="175">
+      <c r="F77" s="176">
         <f>E41</f>
         <v/>
       </c>
-      <c r="G77" s="175">
+      <c r="G77" s="176">
         <f>F41</f>
         <v/>
       </c>
-      <c r="H77" s="175">
+      <c r="H77" s="176">
         <f>G41</f>
         <v/>
       </c>
-      <c r="I77" s="175">
+      <c r="I77" s="176">
         <f>H41</f>
         <v/>
       </c>
@@ -9939,7 +9993,7 @@
         </is>
       </c>
       <c r="C78" s="5" t="n"/>
-      <c r="D78" s="176" t="n">
+      <c r="D78" s="177" t="n">
         <v>157394</v>
       </c>
       <c r="E78" s="165">
@@ -9999,23 +10053,23 @@
       </c>
       <c r="C80" s="9" t="n"/>
       <c r="D80" s="27" t="n"/>
-      <c r="E80" s="173">
+      <c r="E80" s="174">
         <f>E78-E41</f>
         <v/>
       </c>
-      <c r="F80" s="173">
+      <c r="F80" s="174">
         <f>F78-F41</f>
         <v/>
       </c>
-      <c r="G80" s="173">
+      <c r="G80" s="174">
         <f>G78-G41</f>
         <v/>
       </c>
-      <c r="H80" s="173">
+      <c r="H80" s="174">
         <f>H78-H41</f>
         <v/>
       </c>
-      <c r="I80" s="173">
+      <c r="I80" s="174">
         <f>I78-I41</f>
         <v/>
       </c>
@@ -10088,23 +10142,23 @@
     <row r="85" hidden="1" outlineLevel="1">
       <c r="B85" s="19" t="inlineStr">
         <is>
-          <t>Accounts Receivable</t>
+          <t>Accounts Receivable (Gross)</t>
         </is>
       </c>
       <c r="E85" s="163" t="n">
-        <v>206690</v>
+        <v>312107</v>
       </c>
       <c r="F85" s="163" t="n">
-        <v>202365</v>
+        <v>322410</v>
       </c>
       <c r="G85" s="163" t="n">
-        <v>251217</v>
+        <v>387947</v>
       </c>
       <c r="H85" s="163" t="n">
-        <v>269745</v>
+        <v>426642</v>
       </c>
       <c r="I85" s="163" t="n">
-        <v>341776</v>
+        <v>529148</v>
       </c>
       <c r="J85" s="159">
         <f>J42</f>
@@ -10214,107 +10268,142 @@
     <row r="88" hidden="1" outlineLevel="1">
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>Net Working Capital (NWC)</t>
-        </is>
-      </c>
-      <c r="C88" s="5" t="n"/>
-      <c r="D88" s="176" t="n">
-        <v>205747</v>
-      </c>
-      <c r="E88" s="177">
-        <f>E85+E86-E87</f>
-        <v/>
-      </c>
-      <c r="F88" s="177">
-        <f>F85+F86-F87</f>
-        <v/>
-      </c>
-      <c r="G88" s="177">
-        <f>G85+G86-G87</f>
-        <v/>
-      </c>
-      <c r="H88" s="177">
-        <f>H85+H86-H87</f>
-        <v/>
-      </c>
-      <c r="I88" s="177">
-        <f>I85+I86-I87</f>
-        <v/>
+          <t>Deferred Revenue (contract liability)</t>
+        </is>
+      </c>
+      <c r="C88" s="164" t="inlineStr">
+        <is>
+          <t>eqn: Rev × (FY25 Deferred/FY25 Rev) — separate from AR</t>
+        </is>
+      </c>
+      <c r="D88" s="28" t="n"/>
+      <c r="E88" s="178" t="n">
+        <v>105417</v>
+      </c>
+      <c r="F88" s="178" t="n">
+        <v>120045</v>
+      </c>
+      <c r="G88" s="178" t="n">
+        <v>136730</v>
+      </c>
+      <c r="H88" s="178" t="n">
+        <v>156897</v>
+      </c>
+      <c r="I88" s="178" t="n">
+        <v>187372</v>
       </c>
       <c r="J88" s="159">
-        <f>J85+J86-J87</f>
+        <f>J24*IF($I$24=0,0,$I$88/$I$24)</f>
         <v/>
       </c>
       <c r="K88" s="159">
-        <f>K85+K86-K87</f>
+        <f>K24*IF($I$24=0,0,$I$88/$I$24)</f>
         <v/>
       </c>
       <c r="L88" s="159">
-        <f>L85+L86-L87</f>
+        <f>L24*IF($I$24=0,0,$I$88/$I$24)</f>
         <v/>
       </c>
       <c r="M88" s="159">
-        <f>M85+M86-M87</f>
+        <f>M24*IF($I$24=0,0,$I$88/$I$24)</f>
         <v/>
       </c>
       <c r="N88" s="159">
-        <f>N85+N86-N87</f>
+        <f>N24*IF($I$24=0,0,$I$88/$I$24)</f>
         <v/>
       </c>
     </row>
     <row r="89" hidden="1" outlineLevel="1">
       <c r="B89" s="19" t="inlineStr">
         <is>
+          <t>Net Working Capital (NWC)</t>
+        </is>
+      </c>
+      <c r="C89" s="166" t="inlineStr">
+        <is>
+          <t>eqn: GrossAR + Inv − AP − Deferred</t>
+        </is>
+      </c>
+      <c r="D89" s="179" t="n">
+        <v>205747</v>
+      </c>
+      <c r="E89" s="163" t="n">
+        <v>185941</v>
+      </c>
+      <c r="F89" s="163" t="n">
+        <v>185092</v>
+      </c>
+      <c r="G89" s="163" t="n">
+        <v>232208</v>
+      </c>
+      <c r="H89" s="163" t="n">
+        <v>247272</v>
+      </c>
+      <c r="I89" s="163" t="n">
+        <v>309461</v>
+      </c>
+      <c r="J89" s="159">
+        <f>J85+J86-J87-J88</f>
+        <v/>
+      </c>
+      <c r="K89" s="159">
+        <f>K85+K86-K87-K88</f>
+        <v/>
+      </c>
+      <c r="L89" s="159">
+        <f>L85+L86-L87-L88</f>
+        <v/>
+      </c>
+      <c r="M89" s="159">
+        <f>M85+M86-M87-M88</f>
+        <v/>
+      </c>
+      <c r="N89" s="159">
+        <f>N85+N86-N87-N88</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90" hidden="1" outlineLevel="1">
+      <c r="B90" t="inlineStr">
+        <is>
           <t>Change in NWC</t>
         </is>
       </c>
-      <c r="E89" s="156">
-        <f>E88-D88</f>
-        <v/>
-      </c>
-      <c r="F89" s="156">
-        <f>F88-E88</f>
-        <v/>
-      </c>
-      <c r="G89" s="156">
-        <f>G88-F88</f>
-        <v/>
-      </c>
-      <c r="H89" s="156">
-        <f>H88-G88</f>
-        <v/>
-      </c>
-      <c r="I89" s="156">
-        <f>I88-H88</f>
-        <v/>
-      </c>
-      <c r="J89" s="159">
-        <f>J88-I88</f>
-        <v/>
-      </c>
-      <c r="K89" s="159">
-        <f>K88-J88</f>
-        <v/>
-      </c>
-      <c r="L89" s="159">
-        <f>L88-K88</f>
-        <v/>
-      </c>
-      <c r="M89" s="159">
-        <f>M88-L88</f>
-        <v/>
-      </c>
-      <c r="N89" s="159">
-        <f>N88-M88</f>
-        <v/>
-      </c>
-    </row>
-    <row r="90" hidden="1" outlineLevel="1">
-      <c r="E90" s="33" t="n"/>
-      <c r="F90" s="33" t="n"/>
-      <c r="G90" s="33" t="n"/>
-      <c r="H90" s="33" t="n"/>
-      <c r="I90" s="33" t="n"/>
+      <c r="E90" s="163" t="n">
+        <v>-19806</v>
+      </c>
+      <c r="F90" s="163" t="n">
+        <v>-849</v>
+      </c>
+      <c r="G90" s="163" t="n">
+        <v>47116</v>
+      </c>
+      <c r="H90" s="163" t="n">
+        <v>15064</v>
+      </c>
+      <c r="I90" s="163" t="n">
+        <v>62189</v>
+      </c>
+      <c r="J90" s="180">
+        <f>J89-I89</f>
+        <v/>
+      </c>
+      <c r="K90" s="180">
+        <f>K89-J89</f>
+        <v/>
+      </c>
+      <c r="L90" s="180">
+        <f>L89-K89</f>
+        <v/>
+      </c>
+      <c r="M90" s="180">
+        <f>M89-L89</f>
+        <v/>
+      </c>
+      <c r="N90" s="180">
+        <f>N89-M89</f>
+        <v/>
+      </c>
     </row>
     <row r="91" hidden="1" outlineLevel="1">
       <c r="B91" s="18" t="inlineStr">
@@ -10337,19 +10426,19 @@
       <c r="E92" s="163" t="n">
         <v>46419</v>
       </c>
-      <c r="F92" s="175">
+      <c r="F92" s="176">
         <f>E95</f>
         <v/>
       </c>
-      <c r="G92" s="175">
+      <c r="G92" s="176">
         <f>F95</f>
         <v/>
       </c>
-      <c r="H92" s="175">
+      <c r="H92" s="176">
         <f>G95</f>
         <v/>
       </c>
-      <c r="I92" s="175">
+      <c r="I92" s="176">
         <f>H95</f>
         <v/>
       </c>
@@ -10422,6 +10511,11 @@
           <t>Less Depreciation</t>
         </is>
       </c>
+      <c r="C94" s="166" t="inlineStr">
+        <is>
+          <t>eqn: ((Open+Open+CapEx)/2) × DA%</t>
+        </is>
+      </c>
       <c r="E94" s="163" t="n">
         <v>25592</v>
       </c>
@@ -10438,23 +10532,23 @@
         <v>14952</v>
       </c>
       <c r="J94" s="159">
-        <f>J92*J11</f>
+        <f>((J92+(J92+J93))/2)*J11</f>
         <v/>
       </c>
       <c r="K94" s="159">
-        <f>K92*K11</f>
+        <f>((K92+(K92+K93))/2)*K11</f>
         <v/>
       </c>
       <c r="L94" s="159">
-        <f>L92*L11</f>
+        <f>((L92+(L92+L93))/2)*L11</f>
         <v/>
       </c>
       <c r="M94" s="159">
-        <f>M92*M11</f>
+        <f>((M92+(M92+M93))/2)*M11</f>
         <v/>
       </c>
       <c r="N94" s="159">
-        <f>N92*N11</f>
+        <f>((N92+(N92+N93))/2)*N11</f>
         <v/>
       </c>
     </row>
@@ -10535,19 +10629,19 @@
       <c r="E98" s="163" t="n">
         <v>739435</v>
       </c>
-      <c r="F98" s="175">
+      <c r="F98" s="176">
         <f>E100</f>
         <v/>
       </c>
-      <c r="G98" s="175">
+      <c r="G98" s="176">
         <f>F100</f>
         <v/>
       </c>
-      <c r="H98" s="175">
+      <c r="H98" s="176">
         <f>G100</f>
         <v/>
       </c>
-      <c r="I98" s="175">
+      <c r="I98" s="176">
         <f>H100</f>
         <v/>
       </c>
@@ -11101,9 +11195,9 @@
       <c r="L2" s="96" t="n"/>
       <c r="M2" s="94" t="n"/>
       <c r="N2" s="94" t="n"/>
-      <c r="Q2" s="179" t="inlineStr">
-        <is>
-          <t>vengeanceaiUSCMODEL5 — LIVE EQUATIONS + SOURCE LINKS</t>
+      <c r="Q2" s="181" t="inlineStr">
+        <is>
+          <t>vengeanceaiUSCMODEL6 — LIVE EQUATIONS + SOURCE LINKS</t>
         </is>
       </c>
     </row>
@@ -11123,7 +11217,7 @@
       <c r="M3" s="97" t="n"/>
       <c r="N3" s="97" t="n"/>
       <c r="O3" s="97" t="n"/>
-      <c r="Q3" s="180" t="inlineStr">
+      <c r="Q3" s="182" t="inlineStr">
         <is>
           <t>Yellow = inputs (edit). Green = formulas. Blue underlined = clickable sources.</t>
         </is>
@@ -11149,32 +11243,32 @@
       <c r="M4" s="97" t="n"/>
       <c r="N4" s="97" t="n"/>
       <c r="O4" s="97" t="n"/>
-      <c r="Q4" s="181" t="inlineStr">
+      <c r="Q4" s="183" t="inlineStr">
         <is>
           <t>Input</t>
         </is>
       </c>
-      <c r="R4" s="181" t="inlineStr">
+      <c r="R4" s="183" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="S4" s="181" t="inlineStr">
+      <c r="S4" s="183" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="T4" s="181" t="inlineStr">
+      <c r="T4" s="183" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="U4" s="181" t="inlineStr">
+      <c r="U4" s="183" t="inlineStr">
         <is>
           <t>Primary source (click)</t>
         </is>
       </c>
-      <c r="V4" s="181" t="inlineStr">
+      <c r="V4" s="183" t="inlineStr">
         <is>
           <t>Secondary source (click)</t>
         </is>
@@ -11188,10 +11282,10 @@
         </is>
       </c>
       <c r="C5" s="100" t="n"/>
-      <c r="D5" s="182" t="n">
+      <c r="D5" s="184" t="n">
         <v>0.1877023903712333</v>
       </c>
-      <c r="E5" s="183" t="inlineStr">
+      <c r="E5" s="185" t="inlineStr">
         <is>
           <t>Tax source: SEC 10-K</t>
         </is>
@@ -11213,7 +11307,7 @@
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="184" t="inlineStr">
+      <c r="A6" s="186" t="inlineStr">
         <is>
           <t>WACC sources → columns U–V</t>
         </is>
@@ -11223,26 +11317,26 @@
           <t>Discount Rate (WACC = We×Ke + Wd×Rd(1−t))</t>
         </is>
       </c>
-      <c r="C6" s="185" t="inlineStr">
+      <c r="C6" s="187" t="inlineStr">
         <is>
           <t>Sources →</t>
         </is>
       </c>
-      <c r="D6" s="186">
+      <c r="D6" s="188">
         <f>R15</f>
         <v/>
       </c>
-      <c r="E6" s="183" t="inlineStr">
+      <c r="E6" s="185" t="inlineStr">
         <is>
           <t>WACC sources → scroll to col U (Rf/ERP/β/Rd links)</t>
         </is>
       </c>
-      <c r="F6" s="183" t="inlineStr">
+      <c r="F6" s="185" t="inlineStr">
         <is>
           <t>Damodaran ERP</t>
         </is>
       </c>
-      <c r="G6" s="183" t="inlineStr">
+      <c r="G6" s="185" t="inlineStr">
         <is>
           <t>SEC 8-K Rd 6.250%</t>
         </is>
@@ -11255,30 +11349,30 @@
       <c r="M6" s="97" t="n"/>
       <c r="N6" s="97" t="n"/>
       <c r="O6" s="97" t="n"/>
-      <c r="Q6" s="187" t="inlineStr">
+      <c r="Q6" s="189" t="inlineStr">
         <is>
           <t>Risk-free rate (Rf)</t>
         </is>
       </c>
-      <c r="R6" s="188" t="n">
+      <c r="R6" s="190" t="n">
         <v>0.0463</v>
       </c>
-      <c r="S6" s="187" t="inlineStr">
+      <c r="S6" s="189" t="inlineStr">
         <is>
           <t>US 10Y Treasury yield</t>
         </is>
       </c>
-      <c r="T6" s="187" t="inlineStr">
+      <c r="T6" s="189" t="inlineStr">
         <is>
           <t>CAPM input</t>
         </is>
       </c>
-      <c r="U6" s="189" t="inlineStr">
+      <c r="U6" s="191" t="inlineStr">
         <is>
           <t>FRED DGS10 (US 10Y)</t>
         </is>
       </c>
-      <c r="V6" s="189" t="inlineStr">
+      <c r="V6" s="191" t="inlineStr">
         <is>
           <t>US Treasury Daily Par Yield Curve</t>
         </is>
@@ -11292,7 +11386,7 @@
         </is>
       </c>
       <c r="C7" s="97" t="n"/>
-      <c r="D7" s="182" t="n">
+      <c r="D7" s="184" t="n">
         <v>0.03</v>
       </c>
       <c r="E7" s="97" t="n"/>
@@ -11306,30 +11400,30 @@
       <c r="M7" s="97" t="n"/>
       <c r="N7" s="97" t="n"/>
       <c r="O7" s="97" t="n"/>
-      <c r="Q7" s="187" t="inlineStr">
+      <c r="Q7" s="189" t="inlineStr">
         <is>
           <t>Equity risk premium (ERP)</t>
         </is>
       </c>
-      <c r="R7" s="188" t="n">
+      <c r="R7" s="190" t="n">
         <v>0.0428</v>
       </c>
-      <c r="S7" s="187" t="inlineStr">
+      <c r="S7" s="189" t="inlineStr">
         <is>
           <t>Damodaran implied ERP</t>
         </is>
       </c>
-      <c r="T7" s="187" t="inlineStr">
+      <c r="T7" s="189" t="inlineStr">
         <is>
           <t>CAPM input</t>
         </is>
       </c>
-      <c r="U7" s="189" t="inlineStr">
+      <c r="U7" s="191" t="inlineStr">
         <is>
           <t>Damodaran Online — Implied ERP</t>
         </is>
       </c>
-      <c r="V7" s="189" t="inlineStr">
+      <c r="V7" s="191" t="inlineStr">
         <is>
           <t>Damodaran histimpl.xls / table</t>
         </is>
@@ -11343,10 +11437,10 @@
         </is>
       </c>
       <c r="C8" s="97" t="n"/>
-      <c r="D8" s="190" t="n">
+      <c r="D8" s="192" t="n">
         <v>25</v>
       </c>
-      <c r="E8" s="183" t="inlineStr">
+      <c r="E8" s="185" t="inlineStr">
         <is>
           <t>Rd source: SEC 8-K 6.250% notes</t>
         </is>
@@ -11361,30 +11455,30 @@
       <c r="M8" s="97" t="n"/>
       <c r="N8" s="97" t="n"/>
       <c r="O8" s="97" t="n"/>
-      <c r="Q8" s="187" t="inlineStr">
+      <c r="Q8" s="189" t="inlineStr">
         <is>
           <t>Beta (β)</t>
         </is>
       </c>
-      <c r="R8" s="191" t="n">
+      <c r="R8" s="193" t="n">
         <v>1.32</v>
       </c>
-      <c r="S8" s="187" t="inlineStr">
+      <c r="S8" s="189" t="inlineStr">
         <is>
           <t>Yahoo 5Y monthly beta</t>
         </is>
       </c>
-      <c r="T8" s="187" t="inlineStr">
+      <c r="T8" s="189" t="inlineStr">
         <is>
           <t>CAPM input</t>
         </is>
       </c>
-      <c r="U8" s="189" t="inlineStr">
+      <c r="U8" s="191" t="inlineStr">
         <is>
           <t>Yahoo Finance FICO Key Statistics</t>
         </is>
       </c>
-      <c r="V8" s="189" t="inlineStr">
+      <c r="V8" s="191" t="inlineStr">
         <is>
           <t>Yahoo Finance FICO quote</t>
         </is>
@@ -11398,7 +11492,7 @@
         </is>
       </c>
       <c r="C9" s="97" t="n"/>
-      <c r="D9" s="192" t="n">
+      <c r="D9" s="194" t="n">
         <v>45930</v>
       </c>
       <c r="E9" s="97" t="n"/>
@@ -11412,31 +11506,31 @@
       <c r="M9" s="97" t="n"/>
       <c r="N9" s="97" t="n"/>
       <c r="O9" s="97" t="n"/>
-      <c r="Q9" s="193" t="inlineStr">
+      <c r="Q9" s="195" t="inlineStr">
         <is>
           <t>Ke = Rf + β × ERP</t>
         </is>
       </c>
-      <c r="R9" s="194">
+      <c r="R9" s="196">
         <f>R6+R8*R7</f>
         <v/>
       </c>
-      <c r="S9" s="187" t="inlineStr">
+      <c r="S9" s="189" t="inlineStr">
         <is>
           <t>Cost of equity (CAPM)</t>
         </is>
       </c>
-      <c r="T9" s="193" t="inlineStr">
+      <c r="T9" s="195" t="inlineStr">
         <is>
           <t>→ WACC</t>
         </is>
       </c>
-      <c r="U9" s="187" t="inlineStr">
+      <c r="U9" s="189" t="inlineStr">
         <is>
           <t>Derived: R6 + R8 × R7</t>
         </is>
       </c>
-      <c r="V9" s="187" t="inlineStr"/>
+      <c r="V9" s="189" t="inlineStr"/>
     </row>
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="97" t="n"/>
@@ -11446,7 +11540,7 @@
         </is>
       </c>
       <c r="C10" s="97" t="n"/>
-      <c r="D10" s="192" t="n">
+      <c r="D10" s="194" t="n">
         <v>46295</v>
       </c>
       <c r="E10" s="97" t="n"/>
@@ -11460,30 +11554,30 @@
       <c r="M10" s="97" t="n"/>
       <c r="N10" s="97" t="n"/>
       <c r="O10" s="97" t="n"/>
-      <c r="Q10" s="187" t="inlineStr">
+      <c r="Q10" s="189" t="inlineStr">
         <is>
           <t>Pre-tax cost of debt (Rd)</t>
         </is>
       </c>
-      <c r="R10" s="188" t="n">
+      <c r="R10" s="190" t="n">
         <v>0.0625</v>
       </c>
-      <c r="S10" s="187" t="inlineStr">
+      <c r="S10" s="189" t="inlineStr">
         <is>
           <t>6.250% Senior Notes due 2034</t>
         </is>
       </c>
-      <c r="T10" s="187" t="inlineStr">
+      <c r="T10" s="189" t="inlineStr">
         <is>
           <t>WACC input</t>
         </is>
       </c>
-      <c r="U10" s="189" t="inlineStr">
+      <c r="U10" s="191" t="inlineStr">
         <is>
           <t>SEC 8-K — Notes closing (6.250%)</t>
         </is>
       </c>
-      <c r="V10" s="189" t="inlineStr">
+      <c r="V10" s="191" t="inlineStr">
         <is>
           <t>SEC EX-99.1 — Notes pricing press release</t>
         </is>
@@ -11497,7 +11591,7 @@
         </is>
       </c>
       <c r="C11" s="97" t="n"/>
-      <c r="D11" s="195" t="n">
+      <c r="D11" s="197" t="n">
         <v>1046.23</v>
       </c>
       <c r="E11" s="97" t="n"/>
@@ -11511,31 +11605,31 @@
       <c r="M11" s="97" t="n"/>
       <c r="N11" s="97" t="n"/>
       <c r="O11" s="97" t="n"/>
-      <c r="Q11" s="187" t="inlineStr">
+      <c r="Q11" s="189" t="inlineStr">
         <is>
           <t>Tax rate (t)</t>
         </is>
       </c>
-      <c r="R11" s="194">
+      <c r="R11" s="196">
         <f>$D$5</f>
         <v/>
       </c>
-      <c r="S11" s="187" t="inlineStr">
+      <c r="S11" s="189" t="inlineStr">
         <is>
           <t>FY25 effective = 150,649 / 802,595</t>
         </is>
       </c>
-      <c r="T11" s="187" t="inlineStr">
+      <c r="T11" s="189" t="inlineStr">
         <is>
           <t>Linked D5</t>
         </is>
       </c>
-      <c r="U11" s="189" t="inlineStr">
+      <c r="U11" s="191" t="inlineStr">
         <is>
           <t>SEC 10-K FY2025 (tax / EBT)</t>
         </is>
       </c>
-      <c r="V11" s="189" t="inlineStr">
+      <c r="V11" s="191" t="inlineStr">
         <is>
           <t>SEC companyfacts XBRL (CIK 0000814547)</t>
         </is>
@@ -11549,7 +11643,7 @@
         </is>
       </c>
       <c r="C12" s="97" t="n"/>
-      <c r="D12" s="196" t="n">
+      <c r="D12" s="198" t="n">
         <v>21597.635</v>
       </c>
       <c r="E12" s="97" t="n"/>
@@ -11563,31 +11657,31 @@
       <c r="M12" s="97" t="n"/>
       <c r="N12" s="97" t="n"/>
       <c r="O12" s="97" t="n"/>
-      <c r="Q12" s="193" t="inlineStr">
+      <c r="Q12" s="195" t="inlineStr">
         <is>
           <t>Rd_aftertax = Rd × (1 − t)</t>
         </is>
       </c>
-      <c r="R12" s="194">
+      <c r="R12" s="196">
         <f>R10*(1-R11)</f>
         <v/>
       </c>
-      <c r="S12" s="187" t="inlineStr">
+      <c r="S12" s="189" t="inlineStr">
         <is>
           <t>After-tax cost of debt</t>
         </is>
       </c>
-      <c r="T12" s="193" t="inlineStr">
+      <c r="T12" s="195" t="inlineStr">
         <is>
           <t>→ WACC</t>
         </is>
       </c>
-      <c r="U12" s="187" t="inlineStr">
+      <c r="U12" s="189" t="inlineStr">
         <is>
           <t>Derived: R10 × (1 − R11)</t>
         </is>
       </c>
-      <c r="V12" s="187" t="inlineStr"/>
+      <c r="V12" s="189" t="inlineStr"/>
     </row>
     <row r="13" ht="16" customHeight="1">
       <c r="A13" s="97" t="n"/>
@@ -11597,7 +11691,7 @@
         </is>
       </c>
       <c r="C13" s="97" t="n"/>
-      <c r="D13" s="196" t="n">
+      <c r="D13" s="198" t="n">
         <v>5582389</v>
       </c>
       <c r="E13" s="97" t="n"/>
@@ -11611,30 +11705,30 @@
       <c r="M13" s="97" t="n"/>
       <c r="N13" s="97" t="n"/>
       <c r="O13" s="97" t="n"/>
-      <c r="Q13" s="187" t="inlineStr">
+      <c r="Q13" s="189" t="inlineStr">
         <is>
           <t>Equity weight (We)</t>
         </is>
       </c>
-      <c r="R13" s="197" t="n">
+      <c r="R13" s="199" t="n">
         <v>0.8</v>
       </c>
-      <c r="S13" s="187" t="inlineStr">
+      <c r="S13" s="189" t="inlineStr">
         <is>
           <t>Target ~80% equity at market</t>
         </is>
       </c>
-      <c r="T13" s="187" t="inlineStr">
+      <c r="T13" s="189" t="inlineStr">
         <is>
           <t>WACC weight</t>
         </is>
       </c>
-      <c r="U13" s="189" t="inlineStr">
+      <c r="U13" s="191" t="inlineStr">
         <is>
           <t>SEC 10-Q Q3 FY2026 (debt / capital)</t>
         </is>
       </c>
-      <c r="V13" s="189" t="inlineStr">
+      <c r="V13" s="191" t="inlineStr">
         <is>
           <t>Yahoo market cap for E/(D+E)</t>
         </is>
@@ -11648,7 +11742,7 @@
         </is>
       </c>
       <c r="C14" s="97" t="n"/>
-      <c r="D14" s="196" t="n">
+      <c r="D14" s="198" t="n">
         <v>304537</v>
       </c>
       <c r="E14" s="97" t="n"/>
@@ -11662,30 +11756,30 @@
       <c r="M14" s="97" t="n"/>
       <c r="N14" s="97" t="n"/>
       <c r="O14" s="97" t="n"/>
-      <c r="Q14" s="187" t="inlineStr">
+      <c r="Q14" s="189" t="inlineStr">
         <is>
           <t>Debt weight (Wd)</t>
         </is>
       </c>
-      <c r="R14" s="197" t="n">
+      <c r="R14" s="199" t="n">
         <v>0.2</v>
       </c>
-      <c r="S14" s="187" t="inlineStr">
+      <c r="S14" s="189" t="inlineStr">
         <is>
           <t>Target ~20% debt (We+Wd=100%)</t>
         </is>
       </c>
-      <c r="T14" s="187" t="inlineStr">
+      <c r="T14" s="189" t="inlineStr">
         <is>
           <t>WACC weight</t>
         </is>
       </c>
-      <c r="U14" s="189" t="inlineStr">
+      <c r="U14" s="191" t="inlineStr">
         <is>
           <t>SEC 10-Q — total debt $5,582,389k</t>
         </is>
       </c>
-      <c r="V14" s="189" t="inlineStr">
+      <c r="V14" s="191" t="inlineStr">
         <is>
           <t>SEC 10-K — senior notes footnote</t>
         </is>
@@ -11699,7 +11793,7 @@
         </is>
       </c>
       <c r="C15" s="97" t="n"/>
-      <c r="D15" s="198">
+      <c r="D15" s="200">
         <f>'3 Statement Model'!J68</f>
         <v/>
       </c>
@@ -11714,31 +11808,31 @@
       <c r="M15" s="97" t="n"/>
       <c r="N15" s="97" t="n"/>
       <c r="O15" s="97" t="n"/>
-      <c r="Q15" s="193" t="inlineStr">
+      <c r="Q15" s="195" t="inlineStr">
         <is>
           <t>WACC = We×Ke + Wd×Rd_aftertax</t>
         </is>
       </c>
-      <c r="R15" s="194">
+      <c r="R15" s="196">
         <f>R13*R9+R14*R12</f>
         <v/>
       </c>
-      <c r="S15" s="187" t="inlineStr">
+      <c r="S15" s="189" t="inlineStr">
         <is>
           <t>PRIMARY discount rate → cell D6</t>
         </is>
       </c>
-      <c r="T15" s="193" t="inlineStr">
+      <c r="T15" s="195" t="inlineStr">
         <is>
           <t>→ D6</t>
         </is>
       </c>
-      <c r="U15" s="189" t="inlineStr">
+      <c r="U15" s="191" t="inlineStr">
         <is>
           <t>SEC filings (tax, debt coupons)</t>
         </is>
       </c>
-      <c r="V15" s="189" t="inlineStr">
+      <c r="V15" s="191" t="inlineStr">
         <is>
           <t>Damodaran (ERP methodology)</t>
         </is>
@@ -11769,23 +11863,23 @@
           <t>Entry</t>
         </is>
       </c>
-      <c r="E17" s="199">
+      <c r="E17" s="201">
         <f>YEAR(E18)</f>
         <v/>
       </c>
-      <c r="F17" s="199">
+      <c r="F17" s="201">
         <f>YEAR(F18)</f>
         <v/>
       </c>
-      <c r="G17" s="199">
+      <c r="G17" s="201">
         <f>YEAR(G18)</f>
         <v/>
       </c>
-      <c r="H17" s="199">
+      <c r="H17" s="201">
         <f>YEAR(H18)</f>
         <v/>
       </c>
-      <c r="I17" s="199">
+      <c r="I17" s="201">
         <f>YEAR(I18)</f>
         <v/>
       </c>
@@ -11817,31 +11911,31 @@
         </is>
       </c>
       <c r="C18" s="97" t="n"/>
-      <c r="D18" s="200">
+      <c r="D18" s="202">
         <f>D9</f>
         <v/>
       </c>
-      <c r="E18" s="201">
+      <c r="E18" s="203">
         <f>DATE(YEAR($D$10)+E19,3,31)</f>
         <v/>
       </c>
-      <c r="F18" s="201">
+      <c r="F18" s="203">
         <f>DATE(YEAR($D$10)+F19,3,31)</f>
         <v/>
       </c>
-      <c r="G18" s="201">
+      <c r="G18" s="203">
         <f>DATE(YEAR($D$10)+G19,3,31)</f>
         <v/>
       </c>
-      <c r="H18" s="201">
+      <c r="H18" s="203">
         <f>DATE(YEAR($D$10)+H19,3,31)</f>
         <v/>
       </c>
-      <c r="I18" s="201">
+      <c r="I18" s="203">
         <f>DATE(YEAR($D$10)+I19,3,31)</f>
         <v/>
       </c>
-      <c r="J18" s="202">
+      <c r="J18" s="204">
         <f>I18</f>
         <v/>
       </c>
@@ -11851,7 +11945,7 @@
           <t>Exit EV/EBITDA (in J27) — primary</t>
         </is>
       </c>
-      <c r="M18" s="198">
+      <c r="M18" s="200">
         <f>J27</f>
         <v/>
       </c>
@@ -11860,17 +11954,17 @@
         <v/>
       </c>
       <c r="O18" s="97" t="n"/>
-      <c r="Q18" s="193" t="inlineStr">
+      <c r="Q18" s="195" t="inlineStr">
         <is>
           <t>FCFF = EBIT − EBIT×t + D&amp;A − CapEx − ΔNWC</t>
         </is>
       </c>
-      <c r="U18" s="189" t="inlineStr">
+      <c r="U18" s="191" t="inlineStr">
         <is>
           <t>Drivers from SEC XBRL → 3-statement</t>
         </is>
       </c>
-      <c r="V18" s="189" t="inlineStr">
+      <c r="V18" s="191" t="inlineStr">
         <is>
           <t>SEC 10-K historical IS/CF</t>
         </is>
@@ -11885,22 +11979,22 @@
       </c>
       <c r="C19" s="118" t="n"/>
       <c r="D19" s="115" t="n"/>
-      <c r="E19" s="203" t="n">
+      <c r="E19" s="205" t="n">
         <v>0</v>
       </c>
-      <c r="F19" s="200">
+      <c r="F19" s="202">
         <f>E19+1</f>
         <v/>
       </c>
-      <c r="G19" s="200">
+      <c r="G19" s="202">
         <f>F19+1</f>
         <v/>
       </c>
-      <c r="H19" s="200">
+      <c r="H19" s="202">
         <f>G19+1</f>
         <v/>
       </c>
-      <c r="I19" s="200">
+      <c r="I19" s="202">
         <f>H19+1</f>
         <v/>
       </c>
@@ -11911,7 +12005,7 @@
           <t>Gordon cross-check</t>
         </is>
       </c>
-      <c r="M19" s="198">
+      <c r="M19" s="200">
         <f>IF(($D$6-$D$7)&lt;=0,"WACC must exceed g",$I$26*(1+$D$7)/($D$6-$D$7))</f>
         <v/>
       </c>
@@ -11920,12 +12014,12 @@
         <v/>
       </c>
       <c r="O19" s="97" t="n"/>
-      <c r="Q19" s="187" t="inlineStr">
+      <c r="Q19" s="189" t="inlineStr">
         <is>
           <t>Excel (col E example)</t>
         </is>
       </c>
-      <c r="R19" s="193">
+      <c r="R19" s="195">
         <f>E21-E22+E23-E24-E25</f>
         <v/>
       </c>
@@ -11939,23 +12033,23 @@
       </c>
       <c r="C20" s="97" t="n"/>
       <c r="D20" s="97" t="n"/>
-      <c r="E20" s="200">
+      <c r="E20" s="202">
         <f>YEARFRAC(D18,E18)</f>
         <v/>
       </c>
-      <c r="F20" s="200">
+      <c r="F20" s="202">
         <f>YEARFRAC(E18,F18)</f>
         <v/>
       </c>
-      <c r="G20" s="200">
+      <c r="G20" s="202">
         <f>YEARFRAC(F18,G18)</f>
         <v/>
       </c>
-      <c r="H20" s="200">
+      <c r="H20" s="202">
         <f>YEARFRAC(G18,H18)</f>
         <v/>
       </c>
-      <c r="I20" s="200">
+      <c r="I20" s="202">
         <f>YEARFRAC(H18,I18)</f>
         <v/>
       </c>
@@ -11966,7 +12060,7 @@
           <t>Implied Gordon exit multiple</t>
         </is>
       </c>
-      <c r="M20" s="198">
+      <c r="M20" s="200">
         <f>IF(($I$21+$I$23)=0,0,M19/($I$21+$I$23))</f>
         <v/>
       </c>
@@ -11975,21 +12069,21 @@
         <v/>
       </c>
       <c r="O20" s="97" t="n"/>
-      <c r="Q20" s="187" t="inlineStr">
+      <c r="Q20" s="189" t="inlineStr">
         <is>
           <t>Tax on EBIT (unlevered)</t>
         </is>
       </c>
-      <c r="R20" s="193">
+      <c r="R20" s="195">
         <f>E21*$D$5</f>
         <v/>
       </c>
-      <c r="S20" s="187" t="inlineStr">
+      <c r="S20" s="189" t="inlineStr">
         <is>
           <t>NOT levered IS tax dollars</t>
         </is>
       </c>
-      <c r="U20" s="189" t="inlineStr">
+      <c r="U20" s="191" t="inlineStr">
         <is>
           <t>Tax rate from SEC 10-K effective rate</t>
         </is>
@@ -12002,29 +12096,29 @@
           <t>EBIT (linked to 3-stmt)</t>
         </is>
       </c>
-      <c r="C21" s="204" t="inlineStr">
+      <c r="C21" s="206" t="inlineStr">
         <is>
           <t>EBIT</t>
         </is>
       </c>
       <c r="D21" s="97" t="n"/>
-      <c r="E21" s="198">
+      <c r="E21" s="200">
         <f>'3 Statement Model'!J26-'3 Statement Model'!J28-'3 Statement Model'!J29-'3 Statement Model'!J30</f>
         <v/>
       </c>
-      <c r="F21" s="198">
+      <c r="F21" s="200">
         <f>'3 Statement Model'!K26-'3 Statement Model'!K28-'3 Statement Model'!K29-'3 Statement Model'!K30</f>
         <v/>
       </c>
-      <c r="G21" s="198">
+      <c r="G21" s="200">
         <f>'3 Statement Model'!L26-'3 Statement Model'!L28-'3 Statement Model'!L29-'3 Statement Model'!L30</f>
         <v/>
       </c>
-      <c r="H21" s="198">
+      <c r="H21" s="200">
         <f>'3 Statement Model'!M26-'3 Statement Model'!M28-'3 Statement Model'!M29-'3 Statement Model'!M30</f>
         <v/>
       </c>
-      <c r="I21" s="198">
+      <c r="I21" s="200">
         <f>'3 Statement Model'!N26-'3 Statement Model'!N28-'3 Statement Model'!N29-'3 Statement Model'!N30</f>
         <v/>
       </c>
@@ -12034,16 +12128,16 @@
       <c r="M21" s="97" t="n"/>
       <c r="N21" s="97" t="n"/>
       <c r="O21" s="97" t="n"/>
-      <c r="Q21" s="187" t="inlineStr">
+      <c r="Q21" s="189" t="inlineStr">
         <is>
           <t>FCFF check (FY5 / col I)</t>
         </is>
       </c>
-      <c r="R21" s="205">
+      <c r="R21" s="207">
         <f>I26</f>
         <v/>
       </c>
-      <c r="S21" s="187" t="inlineStr">
+      <c r="S21" s="189" t="inlineStr">
         <is>
           <t>Must equal I21−I22+I23−I24−I25</t>
         </is>
@@ -12056,29 +12150,29 @@
           <t>Less: Unlevered Cash Taxes (EBIT×t)</t>
         </is>
       </c>
-      <c r="C22" s="204" t="inlineStr">
+      <c r="C22" s="206" t="inlineStr">
         <is>
           <t>EBIT×t</t>
         </is>
       </c>
       <c r="D22" s="97" t="n"/>
-      <c r="E22" s="198">
+      <c r="E22" s="200">
         <f>E21*$D$5</f>
         <v/>
       </c>
-      <c r="F22" s="198">
+      <c r="F22" s="200">
         <f>F21*$D$5</f>
         <v/>
       </c>
-      <c r="G22" s="198">
+      <c r="G22" s="200">
         <f>G21*$D$5</f>
         <v/>
       </c>
-      <c r="H22" s="198">
+      <c r="H22" s="200">
         <f>H21*$D$5</f>
         <v/>
       </c>
-      <c r="I22" s="198">
+      <c r="I22" s="200">
         <f>I21*$D$5</f>
         <v/>
       </c>
@@ -12096,29 +12190,29 @@
           <t>Plus: D&amp;A (linked to 3-stmt)</t>
         </is>
       </c>
-      <c r="C23" s="204" t="inlineStr">
+      <c r="C23" s="206" t="inlineStr">
         <is>
           <t>+D&amp;A</t>
         </is>
       </c>
       <c r="D23" s="97" t="n"/>
-      <c r="E23" s="198">
+      <c r="E23" s="200">
         <f>'3 Statement Model'!J30</f>
         <v/>
       </c>
-      <c r="F23" s="198">
+      <c r="F23" s="200">
         <f>'3 Statement Model'!K30</f>
         <v/>
       </c>
-      <c r="G23" s="198">
+      <c r="G23" s="200">
         <f>'3 Statement Model'!L30</f>
         <v/>
       </c>
-      <c r="H23" s="198">
+      <c r="H23" s="200">
         <f>'3 Statement Model'!M30</f>
         <v/>
       </c>
-      <c r="I23" s="198">
+      <c r="I23" s="200">
         <f>'3 Statement Model'!N30</f>
         <v/>
       </c>
@@ -12141,29 +12235,29 @@
           <t>Less: Capex (linked to 3-stmt CF)</t>
         </is>
       </c>
-      <c r="C24" s="204" t="inlineStr">
+      <c r="C24" s="206" t="inlineStr">
         <is>
           <t>−CapEx</t>
         </is>
       </c>
       <c r="D24" s="97" t="n"/>
-      <c r="E24" s="198">
+      <c r="E24" s="200">
         <f>'3 Statement Model'!J68</f>
         <v/>
       </c>
-      <c r="F24" s="198">
+      <c r="F24" s="200">
         <f>'3 Statement Model'!K68</f>
         <v/>
       </c>
-      <c r="G24" s="198">
+      <c r="G24" s="200">
         <f>'3 Statement Model'!L68</f>
         <v/>
       </c>
-      <c r="H24" s="198">
+      <c r="H24" s="200">
         <f>'3 Statement Model'!M68</f>
         <v/>
       </c>
-      <c r="I24" s="198">
+      <c r="I24" s="200">
         <f>'3 Statement Model'!N68</f>
         <v/>
       </c>
@@ -12173,7 +12267,7 @@
       <c r="M24" s="97" t="n"/>
       <c r="N24" s="97" t="n"/>
       <c r="O24" s="97" t="n"/>
-      <c r="Q24" s="193" t="inlineStr">
+      <c r="Q24" s="195" t="inlineStr">
         <is>
           <t>TV_exit = EBITDA_n × ExitMultiple   [PRIMARY]</t>
         </is>
@@ -12186,29 +12280,29 @@
           <t>Less: ΔNWC (linked to 3-stmt CF)</t>
         </is>
       </c>
-      <c r="C25" s="204" t="inlineStr">
+      <c r="C25" s="206" t="inlineStr">
         <is>
           <t>−ΔNWC</t>
         </is>
       </c>
       <c r="D25" s="97" t="n"/>
-      <c r="E25" s="198">
+      <c r="E25" s="200">
         <f>'3 Statement Model'!J64</f>
         <v/>
       </c>
-      <c r="F25" s="198">
+      <c r="F25" s="200">
         <f>'3 Statement Model'!K64</f>
         <v/>
       </c>
-      <c r="G25" s="198">
+      <c r="G25" s="200">
         <f>'3 Statement Model'!L64</f>
         <v/>
       </c>
-      <c r="H25" s="198">
+      <c r="H25" s="200">
         <f>'3 Statement Model'!M64</f>
         <v/>
       </c>
-      <c r="I25" s="198">
+      <c r="I25" s="200">
         <f>'3 Statement Model'!N64</f>
         <v/>
       </c>
@@ -12218,20 +12312,20 @@
       <c r="M25" s="97" t="n"/>
       <c r="N25" s="97" t="n"/>
       <c r="O25" s="97" t="n"/>
-      <c r="Q25" s="187" t="inlineStr">
+      <c r="Q25" s="189" t="inlineStr">
         <is>
           <t>Excel</t>
         </is>
       </c>
-      <c r="R25" s="193">
+      <c r="R25" s="195">
         <f>($I$21+$I$23)*$D$8</f>
         <v/>
       </c>
-      <c r="T25" s="205">
+      <c r="T25" s="207">
         <f>J27</f>
         <v/>
       </c>
-      <c r="U25" s="189" t="inlineStr">
+      <c r="U25" s="191" t="inlineStr">
         <is>
           <t>Exit multiple policy vs Yahoo / market multiples</t>
         </is>
@@ -12244,29 +12338,29 @@
           <t>Unlevered FCF</t>
         </is>
       </c>
-      <c r="C26" s="204" t="inlineStr">
+      <c r="C26" s="206" t="inlineStr">
         <is>
           <t>FCFF=EBIT−tax+DA−CapEx−ΔNWC</t>
         </is>
       </c>
       <c r="D26" s="97" t="n"/>
-      <c r="E26" s="206">
+      <c r="E26" s="208">
         <f>E21-E22+E23-E24-E25</f>
         <v/>
       </c>
-      <c r="F26" s="206">
+      <c r="F26" s="208">
         <f>F21-F22+F23-F24-F25</f>
         <v/>
       </c>
-      <c r="G26" s="206">
+      <c r="G26" s="208">
         <f>G21-G22+G23-G24-G25</f>
         <v/>
       </c>
-      <c r="H26" s="206">
+      <c r="H26" s="208">
         <f>H21-H22+H23-H24-H25</f>
         <v/>
       </c>
-      <c r="I26" s="206">
+      <c r="I26" s="208">
         <f>I21-I22+I23-I24-I25</f>
         <v/>
       </c>
@@ -12276,7 +12370,7 @@
       <c r="M26" s="97" t="n"/>
       <c r="N26" s="97" t="n"/>
       <c r="O26" s="97" t="n"/>
-      <c r="Q26" s="193" t="inlineStr">
+      <c r="Q26" s="195" t="inlineStr">
         <is>
           <t>TV_gordon = FCFF_n×(1+g)/(WACC−g)   [CHECK]</t>
         </is>
@@ -12290,7 +12384,7 @@
         </is>
       </c>
       <c r="C27" s="97" t="n"/>
-      <c r="D27" s="207">
+      <c r="D27" s="209">
         <f>-I35</f>
         <v/>
       </c>
@@ -12299,7 +12393,7 @@
       <c r="G27" s="97" t="n"/>
       <c r="H27" s="97" t="n"/>
       <c r="I27" s="97" t="n"/>
-      <c r="J27" s="198">
+      <c r="J27" s="200">
         <f>($I$21+$I$23)*$D$8</f>
         <v/>
       </c>
@@ -12308,20 +12402,20 @@
       <c r="M27" s="97" t="n"/>
       <c r="N27" s="97" t="n"/>
       <c r="O27" s="97" t="n"/>
-      <c r="Q27" s="187" t="inlineStr">
+      <c r="Q27" s="189" t="inlineStr">
         <is>
           <t>Excel</t>
         </is>
       </c>
-      <c r="R27" s="193">
+      <c r="R27" s="195">
         <f>IF(($D$6-$D$7)&lt;=0,"err",$I$26*(1+$D$7)/($D$6-$D$7))</f>
         <v/>
       </c>
-      <c r="T27" s="205">
+      <c r="T27" s="207">
         <f>M19</f>
         <v/>
       </c>
-      <c r="U27" s="189" t="inlineStr">
+      <c r="U27" s="191" t="inlineStr">
         <is>
           <t>Gordon g vs Damodaran long-run growth framing</t>
         </is>
@@ -12335,30 +12429,30 @@
         </is>
       </c>
       <c r="C28" s="97" t="n"/>
-      <c r="D28" s="206" t="n">
+      <c r="D28" s="208" t="n">
         <v>0</v>
       </c>
-      <c r="E28" s="208">
+      <c r="E28" s="210">
         <f>E27+E26</f>
         <v/>
       </c>
-      <c r="F28" s="208">
+      <c r="F28" s="210">
         <f>F27+F26</f>
         <v/>
       </c>
-      <c r="G28" s="208">
+      <c r="G28" s="210">
         <f>G27+G26</f>
         <v/>
       </c>
-      <c r="H28" s="208">
+      <c r="H28" s="210">
         <f>H27+H26</f>
         <v/>
       </c>
-      <c r="I28" s="208">
+      <c r="I28" s="210">
         <f>I27+I26</f>
         <v/>
       </c>
-      <c r="J28" s="208">
+      <c r="J28" s="210">
         <f>J27+J26</f>
         <v/>
       </c>
@@ -12367,16 +12461,16 @@
       <c r="M28" s="97" t="n"/>
       <c r="N28" s="97" t="n"/>
       <c r="O28" s="97" t="n"/>
-      <c r="Q28" s="187" t="inlineStr">
+      <c r="Q28" s="189" t="inlineStr">
         <is>
           <t>Implied Gordon exit multiple</t>
         </is>
       </c>
-      <c r="R28" s="209">
+      <c r="R28" s="211">
         <f>IF(($I$21+$I$23)=0,0,T27/($I$21+$I$23))</f>
         <v/>
       </c>
-      <c r="S28" s="187" t="inlineStr">
+      <c r="S28" s="189" t="inlineStr">
         <is>
           <t>Gordon TV / EBITDA_n</t>
         </is>
@@ -12390,31 +12484,31 @@
         </is>
       </c>
       <c r="C29" s="97" t="n"/>
-      <c r="D29" s="207">
+      <c r="D29" s="209">
         <f>D27+D26</f>
         <v/>
       </c>
-      <c r="E29" s="198">
+      <c r="E29" s="200">
         <f>E27+E26</f>
         <v/>
       </c>
-      <c r="F29" s="198">
+      <c r="F29" s="200">
         <f>F27+F26</f>
         <v/>
       </c>
-      <c r="G29" s="198">
+      <c r="G29" s="200">
         <f>G27+G26</f>
         <v/>
       </c>
-      <c r="H29" s="198">
+      <c r="H29" s="200">
         <f>H27+H26</f>
         <v/>
       </c>
-      <c r="I29" s="198">
+      <c r="I29" s="200">
         <f>I27+I26</f>
         <v/>
       </c>
-      <c r="J29" s="198">
+      <c r="J29" s="200">
         <f>J27</f>
         <v/>
       </c>
@@ -12470,7 +12564,7 @@
       <c r="M31" s="111" t="n"/>
       <c r="N31" s="111" t="n"/>
       <c r="O31" s="97" t="n"/>
-      <c r="Q31" s="193" t="inlineStr">
+      <c r="Q31" s="195" t="inlineStr">
         <is>
           <t>EV = XNPV(WACC, TransactionCF, mid-year dates)</t>
         </is>
@@ -12484,7 +12578,7 @@
         </is>
       </c>
       <c r="C32" s="97" t="n"/>
-      <c r="D32" s="198">
+      <c r="D32" s="200">
         <f>XNPV(D6,D28:J28,D18:J18)</f>
         <v/>
       </c>
@@ -12495,7 +12589,7 @@
         </is>
       </c>
       <c r="H32" s="97" t="n"/>
-      <c r="I32" s="207">
+      <c r="I32" s="209">
         <f>D12*D11</f>
         <v/>
       </c>
@@ -12511,16 +12605,16 @@
         <v/>
       </c>
       <c r="O32" s="97" t="n"/>
-      <c r="Q32" s="187" t="inlineStr">
+      <c r="Q32" s="189" t="inlineStr">
         <is>
           <t>Excel</t>
         </is>
       </c>
-      <c r="R32" s="193">
+      <c r="R32" s="195">
         <f>XNPV(D6,D28:J28,D18:J18)</f>
         <v/>
       </c>
-      <c r="T32" s="205">
+      <c r="T32" s="207">
         <f>D32</f>
         <v/>
       </c>
@@ -12533,7 +12627,7 @@
         </is>
       </c>
       <c r="C33" s="97" t="n"/>
-      <c r="D33" s="207">
+      <c r="D33" s="209">
         <f>+D14</f>
         <v/>
       </c>
@@ -12544,7 +12638,7 @@
         </is>
       </c>
       <c r="H33" s="97" t="n"/>
-      <c r="I33" s="207">
+      <c r="I33" s="209">
         <f>D13</f>
         <v/>
       </c>
@@ -12560,26 +12654,26 @@
         <v/>
       </c>
       <c r="O33" s="97" t="n"/>
-      <c r="Q33" s="193" t="inlineStr">
+      <c r="Q33" s="195" t="inlineStr">
         <is>
           <t>Equity = EV + Cash − Debt</t>
         </is>
       </c>
-      <c r="R33" s="205">
+      <c r="R33" s="207">
         <f>D35</f>
         <v/>
       </c>
-      <c r="S33" s="187" t="inlineStr">
+      <c r="S33" s="189" t="inlineStr">
         <is>
           <t>Net debt from 10-Q bridge</t>
         </is>
       </c>
-      <c r="U33" s="189" t="inlineStr">
+      <c r="U33" s="191" t="inlineStr">
         <is>
           <t>SEC 10-Q — cash, mkt secs, total debt</t>
         </is>
       </c>
-      <c r="V33" s="189" t="inlineStr">
+      <c r="V33" s="191" t="inlineStr">
         <is>
           <t>SEC 10-K — FY debt footnote</t>
         </is>
@@ -12593,7 +12687,7 @@
         </is>
       </c>
       <c r="C34" s="97" t="n"/>
-      <c r="D34" s="207">
+      <c r="D34" s="209">
         <f>+D13</f>
         <v/>
       </c>
@@ -12604,7 +12698,7 @@
         </is>
       </c>
       <c r="H34" s="97" t="n"/>
-      <c r="I34" s="207">
+      <c r="I34" s="209">
         <f>+D14</f>
         <v/>
       </c>
@@ -12613,26 +12707,26 @@
       <c r="M34" s="97" t="n"/>
       <c r="N34" s="97" t="n"/>
       <c r="O34" s="97" t="n"/>
-      <c r="Q34" s="193" t="inlineStr">
+      <c r="Q34" s="195" t="inlineStr">
         <is>
           <t>$/share = Equity / Shares</t>
         </is>
       </c>
-      <c r="R34" s="210">
+      <c r="R34" s="212">
         <f>D37</f>
         <v/>
       </c>
-      <c r="S34" s="187" t="inlineStr">
+      <c r="S34" s="189" t="inlineStr">
         <is>
           <t>Shares outstanding (Yahoo)</t>
         </is>
       </c>
-      <c r="U34" s="189" t="inlineStr">
+      <c r="U34" s="191" t="inlineStr">
         <is>
           <t>Yahoo Finance — shares outstanding</t>
         </is>
       </c>
-      <c r="V34" s="189" t="inlineStr">
+      <c r="V34" s="191" t="inlineStr">
         <is>
           <t>Yahoo FICO quote (price)</t>
         </is>
@@ -12646,7 +12740,7 @@
         </is>
       </c>
       <c r="C35" s="97" t="n"/>
-      <c r="D35" s="206">
+      <c r="D35" s="208">
         <f>D32+D33-D34</f>
         <v/>
       </c>
@@ -12657,7 +12751,7 @@
         </is>
       </c>
       <c r="H35" s="97" t="n"/>
-      <c r="I35" s="206">
+      <c r="I35" s="208">
         <f>I32+I33-I34</f>
         <v/>
       </c>
@@ -12670,16 +12764,16 @@
       <c r="M35" s="111" t="n"/>
       <c r="N35" s="111" t="n"/>
       <c r="O35" s="97" t="n"/>
-      <c r="Q35" s="187" t="inlineStr">
+      <c r="Q35" s="189" t="inlineStr">
         <is>
           <t>Upside vs market</t>
         </is>
       </c>
-      <c r="R35" s="211">
+      <c r="R35" s="213">
         <f>D37/D11-1</f>
         <v/>
       </c>
-      <c r="S35" s="187" t="inlineStr">
+      <c r="S35" s="189" t="inlineStr">
         <is>
           <t>Intrinsic / Current Price − 1</t>
         </is>
@@ -12693,7 +12787,7 @@
       <c r="E36" s="97" t="n"/>
       <c r="G36" s="97" t="n"/>
       <c r="H36" s="97" t="n"/>
-      <c r="I36" s="212" t="n"/>
+      <c r="I36" s="214" t="n"/>
       <c r="J36" s="97" t="n"/>
       <c r="L36" s="97" t="inlineStr">
         <is>
@@ -12701,7 +12795,7 @@
         </is>
       </c>
       <c r="M36" s="97" t="n"/>
-      <c r="N36" s="212">
+      <c r="N36" s="214">
         <f>I37</f>
         <v/>
       </c>
@@ -12715,7 +12809,7 @@
         </is>
       </c>
       <c r="C37" s="97" t="n"/>
-      <c r="D37" s="207">
+      <c r="D37" s="209">
         <f>D35/D12</f>
         <v/>
       </c>
@@ -12726,7 +12820,7 @@
         </is>
       </c>
       <c r="H37" s="97" t="n"/>
-      <c r="I37" s="207">
+      <c r="I37" s="209">
         <f>D11</f>
         <v/>
       </c>
@@ -12737,7 +12831,7 @@
         </is>
       </c>
       <c r="M37" s="97" t="n"/>
-      <c r="N37" s="212">
+      <c r="N37" s="214">
         <f>D37-I37</f>
         <v/>
       </c>
@@ -12764,22 +12858,22 @@
         </is>
       </c>
       <c r="M38" s="97" t="n"/>
-      <c r="N38" s="212">
+      <c r="N38" s="214">
         <f>SUM(N36:N37)</f>
         <v/>
       </c>
       <c r="O38" s="97" t="n"/>
-      <c r="Q38" s="193" t="inlineStr">
+      <c r="Q38" s="195" t="inlineStr">
         <is>
           <t>NWC = AR + Inventory − AP − DeferredRevenue</t>
         </is>
       </c>
-      <c r="U38" s="189" t="inlineStr">
+      <c r="U38" s="191" t="inlineStr">
         <is>
           <t>SEC 10-K — AR / AP / deferred revenue</t>
         </is>
       </c>
-      <c r="V38" s="189" t="inlineStr">
+      <c r="V38" s="191" t="inlineStr">
         <is>
           <t>XBRL DeferredRevenueCurrent</t>
         </is>
@@ -12798,17 +12892,17 @@
       <c r="M39" s="97" t="n"/>
       <c r="N39" s="97" t="n"/>
       <c r="O39" s="97" t="n"/>
-      <c r="Q39" s="193" t="inlineStr">
+      <c r="Q39" s="195" t="inlineStr">
         <is>
           <t>ΔNWC_t = NWC_t − NWC_(t−1)</t>
         </is>
       </c>
-      <c r="S39" s="187" t="inlineStr">
+      <c r="S39" s="189" t="inlineStr">
         <is>
           <t>Linked from 3-statement CF row 64</t>
         </is>
       </c>
-      <c r="T39" s="205">
+      <c r="T39" s="207">
         <f>I25</f>
         <v/>
       </c>
@@ -12873,14 +12967,14 @@
         </is>
       </c>
       <c r="O42" s="97" t="n"/>
-      <c r="Q42" s="189" t="inlineStr">
+      <c r="Q42" s="191" t="inlineStr">
         <is>
           <t>SEC 10-K FY2025</t>
         </is>
       </c>
-      <c r="R42" s="213" t="n"/>
-      <c r="S42" s="214" t="n"/>
-      <c r="T42" s="187" t="inlineStr">
+      <c r="R42" s="215" t="n"/>
+      <c r="S42" s="216" t="n"/>
+      <c r="T42" s="189" t="inlineStr">
         <is>
           <t>Tax 18.8%, IS/BS/CF, senior notes</t>
         </is>
@@ -12901,14 +12995,14 @@
       <c r="H43" s="97" t="n"/>
       <c r="N43" s="69" t="n"/>
       <c r="O43" s="97" t="n"/>
-      <c r="Q43" s="189" t="inlineStr">
+      <c r="Q43" s="191" t="inlineStr">
         <is>
           <t>SEC 10-Q Q3 FY2026</t>
         </is>
       </c>
-      <c r="R43" s="213" t="n"/>
-      <c r="S43" s="214" t="n"/>
-      <c r="T43" s="187" t="inlineStr">
+      <c r="R43" s="215" t="n"/>
+      <c r="S43" s="216" t="n"/>
+      <c r="T43" s="189" t="inlineStr">
         <is>
           <t>Debt $5,582M, cash+mkt secs net-debt bridge</t>
         </is>
@@ -12929,14 +13023,14 @@
       <c r="H44" s="97" t="n"/>
       <c r="N44" s="69" t="n"/>
       <c r="O44" s="97" t="n"/>
-      <c r="Q44" s="189" t="inlineStr">
+      <c r="Q44" s="191" t="inlineStr">
         <is>
           <t>SEC 8-K 6.250% notes</t>
         </is>
       </c>
-      <c r="R44" s="213" t="n"/>
-      <c r="S44" s="214" t="n"/>
-      <c r="T44" s="187" t="inlineStr">
+      <c r="R44" s="215" t="n"/>
+      <c r="S44" s="216" t="n"/>
+      <c r="T44" s="189" t="inlineStr">
         <is>
           <t>Pre-tax Rd coupon 6.250% due 2034</t>
         </is>
@@ -12957,14 +13051,14 @@
       <c r="H45" s="97" t="n"/>
       <c r="N45" s="69" t="n"/>
       <c r="O45" s="97" t="n"/>
-      <c r="Q45" s="189" t="inlineStr">
+      <c r="Q45" s="191" t="inlineStr">
         <is>
           <t>SEC EX-99.1 pricing</t>
         </is>
       </c>
-      <c r="R45" s="213" t="n"/>
-      <c r="S45" s="214" t="n"/>
-      <c r="T45" s="187" t="inlineStr">
+      <c r="R45" s="215" t="n"/>
+      <c r="S45" s="216" t="n"/>
+      <c r="T45" s="189" t="inlineStr">
         <is>
           <t>Notes priced at par / offering terms</t>
         </is>
@@ -12985,14 +13079,14 @@
       <c r="H46" s="97" t="n"/>
       <c r="N46" s="69" t="n"/>
       <c r="O46" s="97" t="n"/>
-      <c r="Q46" s="189" t="inlineStr">
+      <c r="Q46" s="191" t="inlineStr">
         <is>
           <t>SEC companyfacts XBRL</t>
         </is>
       </c>
-      <c r="R46" s="213" t="n"/>
-      <c r="S46" s="214" t="n"/>
-      <c r="T46" s="187" t="inlineStr">
+      <c r="R46" s="215" t="n"/>
+      <c r="S46" s="216" t="n"/>
+      <c r="T46" s="189" t="inlineStr">
         <is>
           <t>Pipeline data source (CIK 0000814547)</t>
         </is>
@@ -13009,14 +13103,14 @@
       <c r="H47" s="97" t="n"/>
       <c r="N47" s="69" t="n"/>
       <c r="O47" s="97" t="n"/>
-      <c r="Q47" s="189" t="inlineStr">
+      <c r="Q47" s="191" t="inlineStr">
         <is>
           <t>FRED DGS10</t>
         </is>
       </c>
-      <c r="R47" s="213" t="n"/>
-      <c r="S47" s="214" t="n"/>
-      <c r="T47" s="187" t="inlineStr">
+      <c r="R47" s="215" t="n"/>
+      <c r="S47" s="216" t="n"/>
+      <c r="T47" s="189" t="inlineStr">
         <is>
           <t>Risk-free rate (US 10Y)</t>
         </is>
@@ -13037,14 +13131,14 @@
         </is>
       </c>
       <c r="O48" s="97" t="n"/>
-      <c r="Q48" s="189" t="inlineStr">
+      <c r="Q48" s="191" t="inlineStr">
         <is>
           <t>US Treasury yield curve</t>
         </is>
       </c>
-      <c r="R48" s="213" t="n"/>
-      <c r="S48" s="214" t="n"/>
-      <c r="T48" s="187" t="inlineStr">
+      <c r="R48" s="215" t="n"/>
+      <c r="S48" s="216" t="n"/>
+      <c r="T48" s="189" t="inlineStr">
         <is>
           <t>Official daily par yields</t>
         </is>
@@ -13065,14 +13159,14 @@
         </is>
       </c>
       <c r="O49" s="97" t="n"/>
-      <c r="Q49" s="189" t="inlineStr">
+      <c r="Q49" s="191" t="inlineStr">
         <is>
           <t>Damodaran Implied ERP</t>
         </is>
       </c>
-      <c r="R49" s="213" t="n"/>
-      <c r="S49" s="214" t="n"/>
-      <c r="T49" s="187" t="inlineStr">
+      <c r="R49" s="215" t="n"/>
+      <c r="S49" s="216" t="n"/>
+      <c r="T49" s="189" t="inlineStr">
         <is>
           <t>Equity risk premium</t>
         </is>
@@ -13088,14 +13182,14 @@
       <c r="G50" s="97" t="n"/>
       <c r="H50" s="97" t="n"/>
       <c r="O50" s="97" t="n"/>
-      <c r="Q50" s="189" t="inlineStr">
+      <c r="Q50" s="191" t="inlineStr">
         <is>
           <t>Damodaran histimpl</t>
         </is>
       </c>
-      <c r="R50" s="213" t="n"/>
-      <c r="S50" s="214" t="n"/>
-      <c r="T50" s="187" t="inlineStr">
+      <c r="R50" s="215" t="n"/>
+      <c r="S50" s="216" t="n"/>
+      <c r="T50" s="189" t="inlineStr">
         <is>
           <t>Historical implied ERP table</t>
         </is>
@@ -13112,14 +13206,14 @@
       <c r="H51" s="97" t="n"/>
       <c r="M51" s="97" t="n"/>
       <c r="O51" s="97" t="n"/>
-      <c r="Q51" s="189" t="inlineStr">
+      <c r="Q51" s="191" t="inlineStr">
         <is>
           <t>Yahoo FICO stats</t>
         </is>
       </c>
-      <c r="R51" s="213" t="n"/>
-      <c r="S51" s="214" t="n"/>
-      <c r="T51" s="187" t="inlineStr">
+      <c r="R51" s="215" t="n"/>
+      <c r="S51" s="216" t="n"/>
+      <c r="T51" s="189" t="inlineStr">
         <is>
           <t>Beta 5Y monthly + shares out</t>
         </is>

--- a/FICO/output/FICO_Completed_Model.xlsx
+++ b/FICO/output/FICO_Completed_Model.xlsx
@@ -661,7 +661,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="217">
+  <cellXfs count="215">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="1"/>
@@ -849,7 +849,6 @@
     <xf numFmtId="164" fontId="39" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="14" fontId="35" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="14" fontId="38" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="14" fontId="36" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="35" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="37" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="35" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -927,8 +926,8 @@
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="177" fontId="40" fillId="8" borderId="5" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="177" fontId="38" fillId="7" borderId="5" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="177" fontId="40" fillId="8" borderId="5" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="166" fontId="40" fillId="8" borderId="5" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="164" fontId="41" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="177" fontId="40" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
@@ -992,7 +991,6 @@
     <xf numFmtId="1" fontId="31" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="177" fontId="35" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="178" fontId="38" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="177" fontId="36" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="177" fontId="37" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="55" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="174" fontId="38" fillId="7" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1807,6 +1805,7 @@
 <file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
+    <author>vengeanceaiUSCMODEL7</author>
     <author>vengeanceaiUSCMODEL6</author>
   </authors>
   <commentList>
@@ -1906,7 +1905,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="B7" authorId="0" shapeId="0">
+    <comment ref="B7" authorId="1" shapeId="0">
       <text>
         <t>Revenue Growth
 HOW: Yellow POLICY input: 27% / 16% / 13% / 10% / 7%.
@@ -1915,7 +1914,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454726000031/exhibit991erq32026.htm</t>
       </text>
     </comment>
-    <comment ref="J7" authorId="0" shapeId="0">
+    <comment ref="J7" authorId="1" shapeId="0">
       <text>
         <t>Revenue Growth
 HOW: Yellow POLICY input: 27% / 16% / 13% / 10% / 7%.
@@ -1924,7 +1923,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454726000031/exhibit991erq32026.htm</t>
       </text>
     </comment>
-    <comment ref="K7" authorId="0" shapeId="0">
+    <comment ref="K7" authorId="1" shapeId="0">
       <text>
         <t>Revenue Growth
 HOW: Yellow POLICY input: 27% / 16% / 13% / 10% / 7%.
@@ -1933,7 +1932,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454726000031/exhibit991erq32026.htm</t>
       </text>
     </comment>
-    <comment ref="L7" authorId="0" shapeId="0">
+    <comment ref="L7" authorId="1" shapeId="0">
       <text>
         <t>Revenue Growth
 HOW: Yellow POLICY input: 27% / 16% / 13% / 10% / 7%.
@@ -1942,7 +1941,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454726000031/exhibit991erq32026.htm</t>
       </text>
     </comment>
-    <comment ref="M7" authorId="0" shapeId="0">
+    <comment ref="M7" authorId="1" shapeId="0">
       <text>
         <t>Revenue Growth
 HOW: Yellow POLICY input: 27% / 16% / 13% / 10% / 7%.
@@ -1951,7 +1950,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454726000031/exhibit991erq32026.htm</t>
       </text>
     </comment>
-    <comment ref="N7" authorId="0" shapeId="0">
+    <comment ref="N7" authorId="1" shapeId="0">
       <text>
         <t>Revenue Growth
 HOW: Yellow POLICY input: 27% / 16% / 13% / 10% / 7%.
@@ -1960,7 +1959,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454726000031/exhibit991erq32026.htm</t>
       </text>
     </comment>
-    <comment ref="U7" authorId="0" shapeId="0">
+    <comment ref="U7" authorId="1" shapeId="0">
       <text>
         <t>Revenue Growth
 HOW: Yellow POLICY input: 27% / 16% / 13% / 10% / 7%.
@@ -1969,7 +1968,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454726000031/exhibit991erq32026.htm</t>
       </text>
     </comment>
-    <comment ref="B8" authorId="0" shapeId="0">
+    <comment ref="B8" authorId="1" shapeId="0">
       <text>
         <t>COGS % of Revenue
 HOW: Excel equation: I25/I24 (FY25 COGS ÷ FY25 Revenue) held flat.
@@ -1978,7 +1977,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="J8" authorId="0" shapeId="0">
+    <comment ref="J8" authorId="1" shapeId="0">
       <text>
         <t>COGS % of Revenue
 HOW: Excel equation: I25/I24 (FY25 COGS ÷ FY25 Revenue) held flat.
@@ -1987,7 +1986,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="K8" authorId="0" shapeId="0">
+    <comment ref="K8" authorId="1" shapeId="0">
       <text>
         <t>COGS % of Revenue
 HOW: Excel equation: I25/I24 (FY25 COGS ÷ FY25 Revenue) held flat.
@@ -1996,7 +1995,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="L8" authorId="0" shapeId="0">
+    <comment ref="L8" authorId="1" shapeId="0">
       <text>
         <t>COGS % of Revenue
 HOW: Excel equation: I25/I24 (FY25 COGS ÷ FY25 Revenue) held flat.
@@ -2005,7 +2004,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="M8" authorId="0" shapeId="0">
+    <comment ref="M8" authorId="1" shapeId="0">
       <text>
         <t>COGS % of Revenue
 HOW: Excel equation: I25/I24 (FY25 COGS ÷ FY25 Revenue) held flat.
@@ -2014,7 +2013,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="N8" authorId="0" shapeId="0">
+    <comment ref="N8" authorId="1" shapeId="0">
       <text>
         <t>COGS % of Revenue
 HOW: Excel equation: I25/I24 (FY25 COGS ÷ FY25 Revenue) held flat.
@@ -2023,7 +2022,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="U8" authorId="0" shapeId="0">
+    <comment ref="U8" authorId="1" shapeId="0">
       <text>
         <t>COGS % of Revenue
 HOW: Excel equation: I25/I24 (FY25 COGS ÷ FY25 Revenue) held flat.
@@ -2032,70 +2031,70 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="B9" authorId="0" shapeId="0">
-      <text>
-        <t>SGA % of Revenue
-HOW: Equation: MAX(20%, (I28 − 10,922)/I24 − 25bps × year). Strips FY25 restructuring; then −0.25% of sales each year.
-WHY: MODEL6 fix: enterprise software needs lasting G&amp;A (sales, legal, compliance). Floor raised from 5%→20%; grind cut from 50→25 bps so SGA stays in a realistic ~22–25% band near FY25 normalized (~25%).
+    <comment ref="B9" authorId="1" shapeId="0">
+      <text>
+        <t>SG&amp;A % of Revenue
+HOW: Equation: MAX(15%, (I28 − 10,922)/I24 − 75bps × year). Strips FY25 restructuring; then −0.75% of sales each year.
+WHY: MODEL7 audit: allow software operating leverage. Floor 15%; grind −75 bps so SG&amp;A can scale toward mid-teens as revenue expands (not stuck ~24–25%).
 SOURCE: SEC 10-K FY2025 — SG&amp;A + restructuring note
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="J9" authorId="0" shapeId="0">
-      <text>
-        <t>SGA % of Revenue
-HOW: Equation: MAX(20%, (I28 − 10,922)/I24 − 25bps × year). Strips FY25 restructuring; then −0.25% of sales each year.
-WHY: MODEL6 fix: enterprise software needs lasting G&amp;A (sales, legal, compliance). Floor raised from 5%→20%; grind cut from 50→25 bps so SGA stays in a realistic ~22–25% band near FY25 normalized (~25%).
+    <comment ref="J9" authorId="1" shapeId="0">
+      <text>
+        <t>SG&amp;A % of Revenue
+HOW: Equation: MAX(15%, (I28 − 10,922)/I24 − 75bps × year). Strips FY25 restructuring; then −0.75% of sales each year.
+WHY: MODEL7 audit: allow software operating leverage. Floor 15%; grind −75 bps so SG&amp;A can scale toward mid-teens as revenue expands (not stuck ~24–25%).
 SOURCE: SEC 10-K FY2025 — SG&amp;A + restructuring note
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="K9" authorId="0" shapeId="0">
-      <text>
-        <t>SGA % of Revenue
-HOW: Equation: MAX(20%, (I28 − 10,922)/I24 − 25bps × year). Strips FY25 restructuring; then −0.25% of sales each year.
-WHY: MODEL6 fix: enterprise software needs lasting G&amp;A (sales, legal, compliance). Floor raised from 5%→20%; grind cut from 50→25 bps so SGA stays in a realistic ~22–25% band near FY25 normalized (~25%).
+    <comment ref="K9" authorId="1" shapeId="0">
+      <text>
+        <t>SG&amp;A % of Revenue
+HOW: Equation: MAX(15%, (I28 − 10,922)/I24 − 75bps × year). Strips FY25 restructuring; then −0.75% of sales each year.
+WHY: MODEL7 audit: allow software operating leverage. Floor 15%; grind −75 bps so SG&amp;A can scale toward mid-teens as revenue expands (not stuck ~24–25%).
 SOURCE: SEC 10-K FY2025 — SG&amp;A + restructuring note
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="L9" authorId="0" shapeId="0">
-      <text>
-        <t>SGA % of Revenue
-HOW: Equation: MAX(20%, (I28 − 10,922)/I24 − 25bps × year). Strips FY25 restructuring; then −0.25% of sales each year.
-WHY: MODEL6 fix: enterprise software needs lasting G&amp;A (sales, legal, compliance). Floor raised from 5%→20%; grind cut from 50→25 bps so SGA stays in a realistic ~22–25% band near FY25 normalized (~25%).
+    <comment ref="L9" authorId="1" shapeId="0">
+      <text>
+        <t>SG&amp;A % of Revenue
+HOW: Equation: MAX(15%, (I28 − 10,922)/I24 − 75bps × year). Strips FY25 restructuring; then −0.75% of sales each year.
+WHY: MODEL7 audit: allow software operating leverage. Floor 15%; grind −75 bps so SG&amp;A can scale toward mid-teens as revenue expands (not stuck ~24–25%).
 SOURCE: SEC 10-K FY2025 — SG&amp;A + restructuring note
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="M9" authorId="0" shapeId="0">
-      <text>
-        <t>SGA % of Revenue
-HOW: Equation: MAX(20%, (I28 − 10,922)/I24 − 25bps × year). Strips FY25 restructuring; then −0.25% of sales each year.
-WHY: MODEL6 fix: enterprise software needs lasting G&amp;A (sales, legal, compliance). Floor raised from 5%→20%; grind cut from 50→25 bps so SGA stays in a realistic ~22–25% band near FY25 normalized (~25%).
+    <comment ref="M9" authorId="1" shapeId="0">
+      <text>
+        <t>SG&amp;A % of Revenue
+HOW: Equation: MAX(15%, (I28 − 10,922)/I24 − 75bps × year). Strips FY25 restructuring; then −0.75% of sales each year.
+WHY: MODEL7 audit: allow software operating leverage. Floor 15%; grind −75 bps so SG&amp;A can scale toward mid-teens as revenue expands (not stuck ~24–25%).
 SOURCE: SEC 10-K FY2025 — SG&amp;A + restructuring note
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="N9" authorId="0" shapeId="0">
-      <text>
-        <t>SGA % of Revenue
-HOW: Equation: MAX(20%, (I28 − 10,922)/I24 − 25bps × year). Strips FY25 restructuring; then −0.25% of sales each year.
-WHY: MODEL6 fix: enterprise software needs lasting G&amp;A (sales, legal, compliance). Floor raised from 5%→20%; grind cut from 50→25 bps so SGA stays in a realistic ~22–25% band near FY25 normalized (~25%).
+    <comment ref="N9" authorId="1" shapeId="0">
+      <text>
+        <t>SG&amp;A % of Revenue
+HOW: Equation: MAX(15%, (I28 − 10,922)/I24 − 75bps × year). Strips FY25 restructuring; then −0.75% of sales each year.
+WHY: MODEL7 audit: allow software operating leverage. Floor 15%; grind −75 bps so SG&amp;A can scale toward mid-teens as revenue expands (not stuck ~24–25%).
 SOURCE: SEC 10-K FY2025 — SG&amp;A + restructuring note
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="U9" authorId="0" shapeId="0">
-      <text>
-        <t>SGA % of Revenue
-HOW: Equation: MAX(20%, (I28 − 10,922)/I24 − 25bps × year). Strips FY25 restructuring; then −0.25% of sales each year.
-WHY: MODEL6 fix: enterprise software needs lasting G&amp;A (sales, legal, compliance). Floor raised from 5%→20%; grind cut from 50→25 bps so SGA stays in a realistic ~22–25% band near FY25 normalized (~25%).
+    <comment ref="U9" authorId="1" shapeId="0">
+      <text>
+        <t>SG&amp;A % of Revenue
+HOW: Equation: MAX(15%, (I28 − 10,922)/I24 − 75bps × year). Strips FY25 restructuring; then −0.75% of sales each year.
+WHY: MODEL7 audit: allow software operating leverage. Floor 15%; grind −75 bps so SG&amp;A can scale toward mid-teens as revenue expands (not stuck ~24–25%).
 SOURCE: SEC 10-K FY2025 — SG&amp;A + restructuring note
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="B10" authorId="0" shapeId="0">
+    <comment ref="B10" authorId="1" shapeId="0">
       <text>
         <t>R&amp;D % of Revenue
 HOW: Excel equation: I29/I24 held flat (~9.46%).
@@ -2104,7 +2103,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="J10" authorId="0" shapeId="0">
+    <comment ref="J10" authorId="1" shapeId="0">
       <text>
         <t>R&amp;D % of Revenue
 HOW: Excel equation: I29/I24 held flat (~9.46%).
@@ -2113,7 +2112,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="K10" authorId="0" shapeId="0">
+    <comment ref="K10" authorId="1" shapeId="0">
       <text>
         <t>R&amp;D % of Revenue
 HOW: Excel equation: I29/I24 held flat (~9.46%).
@@ -2122,7 +2121,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="L10" authorId="0" shapeId="0">
+    <comment ref="L10" authorId="1" shapeId="0">
       <text>
         <t>R&amp;D % of Revenue
 HOW: Excel equation: I29/I24 held flat (~9.46%).
@@ -2131,7 +2130,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="M10" authorId="0" shapeId="0">
+    <comment ref="M10" authorId="1" shapeId="0">
       <text>
         <t>R&amp;D % of Revenue
 HOW: Excel equation: I29/I24 held flat (~9.46%).
@@ -2140,7 +2139,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="N10" authorId="0" shapeId="0">
+    <comment ref="N10" authorId="1" shapeId="0">
       <text>
         <t>R&amp;D % of Revenue
 HOW: Excel equation: I29/I24 held flat (~9.46%).
@@ -2149,7 +2148,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="U10" authorId="0" shapeId="0">
+    <comment ref="U10" authorId="1" shapeId="0">
       <text>
         <t>R&amp;D % of Revenue
 HOW: Excel equation: I29/I24 held flat (~9.46%).
@@ -2158,7 +2157,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="B11" authorId="0" shapeId="0">
+    <comment ref="B11" authorId="1" shapeId="0">
       <text>
         <t>D&amp;A % of Avg PP&amp;E
 HOW: Rate = I30/I44 (FY25 DA ÷ FY25 PPE). Forecast DA$ = ((Open + Open+CapEx)/2) × rate.
@@ -2167,7 +2166,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="J11" authorId="0" shapeId="0">
+    <comment ref="J11" authorId="1" shapeId="0">
       <text>
         <t>D&amp;A % of Avg PP&amp;E
 HOW: Rate = I30/I44 (FY25 DA ÷ FY25 PPE). Forecast DA$ = ((Open + Open+CapEx)/2) × rate.
@@ -2176,7 +2175,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="K11" authorId="0" shapeId="0">
+    <comment ref="K11" authorId="1" shapeId="0">
       <text>
         <t>D&amp;A % of Avg PP&amp;E
 HOW: Rate = I30/I44 (FY25 DA ÷ FY25 PPE). Forecast DA$ = ((Open + Open+CapEx)/2) × rate.
@@ -2185,7 +2184,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="L11" authorId="0" shapeId="0">
+    <comment ref="L11" authorId="1" shapeId="0">
       <text>
         <t>D&amp;A % of Avg PP&amp;E
 HOW: Rate = I30/I44 (FY25 DA ÷ FY25 PPE). Forecast DA$ = ((Open + Open+CapEx)/2) × rate.
@@ -2194,7 +2193,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="M11" authorId="0" shapeId="0">
+    <comment ref="M11" authorId="1" shapeId="0">
       <text>
         <t>D&amp;A % of Avg PP&amp;E
 HOW: Rate = I30/I44 (FY25 DA ÷ FY25 PPE). Forecast DA$ = ((Open + Open+CapEx)/2) × rate.
@@ -2203,7 +2202,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="N11" authorId="0" shapeId="0">
+    <comment ref="N11" authorId="1" shapeId="0">
       <text>
         <t>D&amp;A % of Avg PP&amp;E
 HOW: Rate = I30/I44 (FY25 DA ÷ FY25 PPE). Forecast DA$ = ((Open + Open+CapEx)/2) × rate.
@@ -2212,7 +2211,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="U11" authorId="0" shapeId="0">
+    <comment ref="U11" authorId="1" shapeId="0">
       <text>
         <t>D&amp;A % of Avg PP&amp;E
 HOW: Rate = I30/I44 (FY25 DA ÷ FY25 PPE). Forecast DA$ = ((Open + Open+CapEx)/2) × rate.
@@ -2221,7 +2220,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="B12" authorId="0" shapeId="0">
+    <comment ref="B12" authorId="1" shapeId="0">
       <text>
         <t>Interest % of Debt Open
 HOW: Excel equation: I101/I98 (FY25 interest ÷ FY25 opening debt in schedule).
@@ -2230,7 +2229,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="J12" authorId="0" shapeId="0">
+    <comment ref="J12" authorId="1" shapeId="0">
       <text>
         <t>Interest % of Debt Open
 HOW: Excel equation: I101/I98 (FY25 interest ÷ FY25 opening debt in schedule).
@@ -2239,7 +2238,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="K12" authorId="0" shapeId="0">
+    <comment ref="K12" authorId="1" shapeId="0">
       <text>
         <t>Interest % of Debt Open
 HOW: Excel equation: I101/I98 (FY25 interest ÷ FY25 opening debt in schedule).
@@ -2248,7 +2247,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="L12" authorId="0" shapeId="0">
+    <comment ref="L12" authorId="1" shapeId="0">
       <text>
         <t>Interest % of Debt Open
 HOW: Excel equation: I101/I98 (FY25 interest ÷ FY25 opening debt in schedule).
@@ -2257,7 +2256,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="M12" authorId="0" shapeId="0">
+    <comment ref="M12" authorId="1" shapeId="0">
       <text>
         <t>Interest % of Debt Open
 HOW: Excel equation: I101/I98 (FY25 interest ÷ FY25 opening debt in schedule).
@@ -2266,7 +2265,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="N12" authorId="0" shapeId="0">
+    <comment ref="N12" authorId="1" shapeId="0">
       <text>
         <t>Interest % of Debt Open
 HOW: Excel equation: I101/I98 (FY25 interest ÷ FY25 opening debt in schedule).
@@ -2275,7 +2274,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="U12" authorId="0" shapeId="0">
+    <comment ref="U12" authorId="1" shapeId="0">
       <text>
         <t>Interest % of Debt Open
 HOW: Excel equation: I101/I98 (FY25 interest ÷ FY25 opening debt in schedule).
@@ -2284,7 +2283,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="B13" authorId="0" shapeId="0">
+    <comment ref="B13" authorId="1" shapeId="0">
       <text>
         <t>Tax Rate (% of EBT)
 HOW: Excel equation: I35/I33 (FY25 tax ÷ simplified FY25 EBT in this template).
@@ -2293,7 +2292,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="J13" authorId="0" shapeId="0">
+    <comment ref="J13" authorId="1" shapeId="0">
       <text>
         <t>Tax Rate (% of EBT)
 HOW: Excel equation: I35/I33 (FY25 tax ÷ simplified FY25 EBT in this template).
@@ -2302,7 +2301,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="K13" authorId="0" shapeId="0">
+    <comment ref="K13" authorId="1" shapeId="0">
       <text>
         <t>Tax Rate (% of EBT)
 HOW: Excel equation: I35/I33 (FY25 tax ÷ simplified FY25 EBT in this template).
@@ -2311,7 +2310,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="L13" authorId="0" shapeId="0">
+    <comment ref="L13" authorId="1" shapeId="0">
       <text>
         <t>Tax Rate (% of EBT)
 HOW: Excel equation: I35/I33 (FY25 tax ÷ simplified FY25 EBT in this template).
@@ -2320,7 +2319,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="M13" authorId="0" shapeId="0">
+    <comment ref="M13" authorId="1" shapeId="0">
       <text>
         <t>Tax Rate (% of EBT)
 HOW: Excel equation: I35/I33 (FY25 tax ÷ simplified FY25 EBT in this template).
@@ -2329,7 +2328,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="N13" authorId="0" shapeId="0">
+    <comment ref="N13" authorId="1" shapeId="0">
       <text>
         <t>Tax Rate (% of EBT)
 HOW: Excel equation: I35/I33 (FY25 tax ÷ simplified FY25 EBT in this template).
@@ -2338,7 +2337,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="U13" authorId="0" shapeId="0">
+    <comment ref="U13" authorId="1" shapeId="0">
       <text>
         <t>Tax Rate (% of EBT)
 HOW: Excel equation: I35/I33 (FY25 tax ÷ simplified FY25 EBT in this template).
@@ -2347,70 +2346,70 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="B15" authorId="0" shapeId="0">
-      <text>
-        <t>Accounts Receivable (Days)
-HOW: Excel equation: ROUND(I42/I24×365, 0). I42 is GROSS AR (not net of deferred).
-WHY: MODEL6 fix: DSO must use gross receivables. Deferred Revenue is a contract liability projected separately (WC row 88 = Rev × FY25 Def/Rev). NWC = GrossAR + Inv − AP − Deferred.
-SOURCE: SEC companyfacts XBRL — AR; DeferredRevenueCurrent separate
+    <comment ref="B15" authorId="1" shapeId="0">
+      <text>
+        <t>Operating NWC % of Revenue
+HOW: Equation: fade FY25 op. NWC/Sales → 3% steady (weights 70/50/30/15/0).
+WHY: MODEL7 audit: ends the gross-AR-days + deferred double-count that drained ~$297M of FCFF. Asset-light software WC fades toward ~3% of sales; BS AR is plugged so AR−AP−Deferred = NWC.
+SOURCE: SEC companyfacts XBRL — AR / AP / DeferredRevenueCurrent
 LINK: https://data.sec.gov/api/xbrl/companyfacts/CIK0000814547.json</t>
       </text>
     </comment>
-    <comment ref="J15" authorId="0" shapeId="0">
-      <text>
-        <t>Accounts Receivable (Days)
-HOW: Excel equation: ROUND(I42/I24×365, 0). I42 is GROSS AR (not net of deferred).
-WHY: MODEL6 fix: DSO must use gross receivables. Deferred Revenue is a contract liability projected separately (WC row 88 = Rev × FY25 Def/Rev). NWC = GrossAR + Inv − AP − Deferred.
-SOURCE: SEC companyfacts XBRL — AR; DeferredRevenueCurrent separate
+    <comment ref="J15" authorId="1" shapeId="0">
+      <text>
+        <t>Operating NWC % of Revenue
+HOW: Equation: fade FY25 op. NWC/Sales → 3% steady (weights 70/50/30/15/0).
+WHY: MODEL7 audit: ends the gross-AR-days + deferred double-count that drained ~$297M of FCFF. Asset-light software WC fades toward ~3% of sales; BS AR is plugged so AR−AP−Deferred = NWC.
+SOURCE: SEC companyfacts XBRL — AR / AP / DeferredRevenueCurrent
 LINK: https://data.sec.gov/api/xbrl/companyfacts/CIK0000814547.json</t>
       </text>
     </comment>
-    <comment ref="K15" authorId="0" shapeId="0">
-      <text>
-        <t>Accounts Receivable (Days)
-HOW: Excel equation: ROUND(I42/I24×365, 0). I42 is GROSS AR (not net of deferred).
-WHY: MODEL6 fix: DSO must use gross receivables. Deferred Revenue is a contract liability projected separately (WC row 88 = Rev × FY25 Def/Rev). NWC = GrossAR + Inv − AP − Deferred.
-SOURCE: SEC companyfacts XBRL — AR; DeferredRevenueCurrent separate
+    <comment ref="K15" authorId="1" shapeId="0">
+      <text>
+        <t>Operating NWC % of Revenue
+HOW: Equation: fade FY25 op. NWC/Sales → 3% steady (weights 70/50/30/15/0).
+WHY: MODEL7 audit: ends the gross-AR-days + deferred double-count that drained ~$297M of FCFF. Asset-light software WC fades toward ~3% of sales; BS AR is plugged so AR−AP−Deferred = NWC.
+SOURCE: SEC companyfacts XBRL — AR / AP / DeferredRevenueCurrent
 LINK: https://data.sec.gov/api/xbrl/companyfacts/CIK0000814547.json</t>
       </text>
     </comment>
-    <comment ref="L15" authorId="0" shapeId="0">
-      <text>
-        <t>Accounts Receivable (Days)
-HOW: Excel equation: ROUND(I42/I24×365, 0). I42 is GROSS AR (not net of deferred).
-WHY: MODEL6 fix: DSO must use gross receivables. Deferred Revenue is a contract liability projected separately (WC row 88 = Rev × FY25 Def/Rev). NWC = GrossAR + Inv − AP − Deferred.
-SOURCE: SEC companyfacts XBRL — AR; DeferredRevenueCurrent separate
+    <comment ref="L15" authorId="1" shapeId="0">
+      <text>
+        <t>Operating NWC % of Revenue
+HOW: Equation: fade FY25 op. NWC/Sales → 3% steady (weights 70/50/30/15/0).
+WHY: MODEL7 audit: ends the gross-AR-days + deferred double-count that drained ~$297M of FCFF. Asset-light software WC fades toward ~3% of sales; BS AR is plugged so AR−AP−Deferred = NWC.
+SOURCE: SEC companyfacts XBRL — AR / AP / DeferredRevenueCurrent
 LINK: https://data.sec.gov/api/xbrl/companyfacts/CIK0000814547.json</t>
       </text>
     </comment>
-    <comment ref="M15" authorId="0" shapeId="0">
-      <text>
-        <t>Accounts Receivable (Days)
-HOW: Excel equation: ROUND(I42/I24×365, 0). I42 is GROSS AR (not net of deferred).
-WHY: MODEL6 fix: DSO must use gross receivables. Deferred Revenue is a contract liability projected separately (WC row 88 = Rev × FY25 Def/Rev). NWC = GrossAR + Inv − AP − Deferred.
-SOURCE: SEC companyfacts XBRL — AR; DeferredRevenueCurrent separate
+    <comment ref="M15" authorId="1" shapeId="0">
+      <text>
+        <t>Operating NWC % of Revenue
+HOW: Equation: fade FY25 op. NWC/Sales → 3% steady (weights 70/50/30/15/0).
+WHY: MODEL7 audit: ends the gross-AR-days + deferred double-count that drained ~$297M of FCFF. Asset-light software WC fades toward ~3% of sales; BS AR is plugged so AR−AP−Deferred = NWC.
+SOURCE: SEC companyfacts XBRL — AR / AP / DeferredRevenueCurrent
 LINK: https://data.sec.gov/api/xbrl/companyfacts/CIK0000814547.json</t>
       </text>
     </comment>
-    <comment ref="N15" authorId="0" shapeId="0">
-      <text>
-        <t>Accounts Receivable (Days)
-HOW: Excel equation: ROUND(I42/I24×365, 0). I42 is GROSS AR (not net of deferred).
-WHY: MODEL6 fix: DSO must use gross receivables. Deferred Revenue is a contract liability projected separately (WC row 88 = Rev × FY25 Def/Rev). NWC = GrossAR + Inv − AP − Deferred.
-SOURCE: SEC companyfacts XBRL — AR; DeferredRevenueCurrent separate
+    <comment ref="N15" authorId="1" shapeId="0">
+      <text>
+        <t>Operating NWC % of Revenue
+HOW: Equation: fade FY25 op. NWC/Sales → 3% steady (weights 70/50/30/15/0).
+WHY: MODEL7 audit: ends the gross-AR-days + deferred double-count that drained ~$297M of FCFF. Asset-light software WC fades toward ~3% of sales; BS AR is plugged so AR−AP−Deferred = NWC.
+SOURCE: SEC companyfacts XBRL — AR / AP / DeferredRevenueCurrent
 LINK: https://data.sec.gov/api/xbrl/companyfacts/CIK0000814547.json</t>
       </text>
     </comment>
-    <comment ref="U15" authorId="0" shapeId="0">
-      <text>
-        <t>Accounts Receivable (Days)
-HOW: Excel equation: ROUND(I42/I24×365, 0). I42 is GROSS AR (not net of deferred).
-WHY: MODEL6 fix: DSO must use gross receivables. Deferred Revenue is a contract liability projected separately (WC row 88 = Rev × FY25 Def/Rev). NWC = GrossAR + Inv − AP − Deferred.
-SOURCE: SEC companyfacts XBRL — AR; DeferredRevenueCurrent separate
+    <comment ref="U15" authorId="1" shapeId="0">
+      <text>
+        <t>Operating NWC % of Revenue
+HOW: Equation: fade FY25 op. NWC/Sales → 3% steady (weights 70/50/30/15/0).
+WHY: MODEL7 audit: ends the gross-AR-days + deferred double-count that drained ~$297M of FCFF. Asset-light software WC fades toward ~3% of sales; BS AR is plugged so AR−AP−Deferred = NWC.
+SOURCE: SEC companyfacts XBRL — AR / AP / DeferredRevenueCurrent
 LINK: https://data.sec.gov/api/xbrl/companyfacts/CIK0000814547.json</t>
       </text>
     </comment>
-    <comment ref="B16" authorId="0" shapeId="0">
+    <comment ref="B16" authorId="1" shapeId="0">
       <text>
         <t>Inventory (Days)
 HOW: Hard zero — FICO is software / scores; inventory is immaterial.
@@ -2419,7 +2418,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="J16" authorId="0" shapeId="0">
+    <comment ref="J16" authorId="1" shapeId="0">
       <text>
         <t>Inventory (Days)
 HOW: Hard zero — FICO is software / scores; inventory is immaterial.
@@ -2428,7 +2427,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="K16" authorId="0" shapeId="0">
+    <comment ref="K16" authorId="1" shapeId="0">
       <text>
         <t>Inventory (Days)
 HOW: Hard zero — FICO is software / scores; inventory is immaterial.
@@ -2437,7 +2436,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="L16" authorId="0" shapeId="0">
+    <comment ref="L16" authorId="1" shapeId="0">
       <text>
         <t>Inventory (Days)
 HOW: Hard zero — FICO is software / scores; inventory is immaterial.
@@ -2446,7 +2445,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="M16" authorId="0" shapeId="0">
+    <comment ref="M16" authorId="1" shapeId="0">
       <text>
         <t>Inventory (Days)
 HOW: Hard zero — FICO is software / scores; inventory is immaterial.
@@ -2455,7 +2454,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="N16" authorId="0" shapeId="0">
+    <comment ref="N16" authorId="1" shapeId="0">
       <text>
         <t>Inventory (Days)
 HOW: Hard zero — FICO is software / scores; inventory is immaterial.
@@ -2464,7 +2463,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="U16" authorId="0" shapeId="0">
+    <comment ref="U16" authorId="1" shapeId="0">
       <text>
         <t>Inventory (Days)
 HOW: Hard zero — FICO is software / scores; inventory is immaterial.
@@ -2473,7 +2472,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="B17" authorId="0" shapeId="0">
+    <comment ref="B17" authorId="1" shapeId="0">
       <text>
         <t>Accounts Payable (Days)
 HOW: Excel equation: ROUND(I48/I25×365, 0) from FY25.
@@ -2482,7 +2481,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="J17" authorId="0" shapeId="0">
+    <comment ref="J17" authorId="1" shapeId="0">
       <text>
         <t>Accounts Payable (Days)
 HOW: Excel equation: ROUND(I48/I25×365, 0) from FY25.
@@ -2491,7 +2490,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="K17" authorId="0" shapeId="0">
+    <comment ref="K17" authorId="1" shapeId="0">
       <text>
         <t>Accounts Payable (Days)
 HOW: Excel equation: ROUND(I48/I25×365, 0) from FY25.
@@ -2500,7 +2499,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="L17" authorId="0" shapeId="0">
+    <comment ref="L17" authorId="1" shapeId="0">
       <text>
         <t>Accounts Payable (Days)
 HOW: Excel equation: ROUND(I48/I25×365, 0) from FY25.
@@ -2509,7 +2508,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="M17" authorId="0" shapeId="0">
+    <comment ref="M17" authorId="1" shapeId="0">
       <text>
         <t>Accounts Payable (Days)
 HOW: Excel equation: ROUND(I48/I25×365, 0) from FY25.
@@ -2518,7 +2517,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="N17" authorId="0" shapeId="0">
+    <comment ref="N17" authorId="1" shapeId="0">
       <text>
         <t>Accounts Payable (Days)
 HOW: Excel equation: ROUND(I48/I25×365, 0) from FY25.
@@ -2527,7 +2526,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="U17" authorId="0" shapeId="0">
+    <comment ref="U17" authorId="1" shapeId="0">
       <text>
         <t>Accounts Payable (Days)
 HOW: Excel equation: ROUND(I48/I25×365, 0) from FY25.
@@ -2536,70 +2535,70 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="B18" authorId="0" shapeId="0">
+    <comment ref="B18" authorId="1" shapeId="0">
       <text>
         <t>CapEx % of Revenue
-HOW: Equation: fade from I68/I24 (FY25 CapEx/Sales ~1.98%) toward 1.0% steady. Weights 85%→65%→45%→30%→0% on the peak.
-WHY: FY25 CapEx was elevated by capitalized internal-use software. Fading avoids locking a peak reinvestment rate forever.
+HOW: Equation: fade from I68/I24 toward 1.0% steady. MODEL7 weights 40%→20%→10%→0%→0% on the peak (faster fade).
+WHY: MODEL7 audit: prior path left CapEx ≫ D&amp;A (~$80M cumulative drag). Faster fade to maintenance ~1% so CapEx converges near D&amp;A by Y4–Y5.
 SOURCE: SEC 10-K FY2025 — PP&amp;E purchases + capitalized software
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="J18" authorId="0" shapeId="0">
+    <comment ref="J18" authorId="1" shapeId="0">
       <text>
         <t>CapEx % of Revenue
-HOW: Equation: fade from I68/I24 (FY25 CapEx/Sales ~1.98%) toward 1.0% steady. Weights 85%→65%→45%→30%→0% on the peak.
-WHY: FY25 CapEx was elevated by capitalized internal-use software. Fading avoids locking a peak reinvestment rate forever.
+HOW: Equation: fade from I68/I24 toward 1.0% steady. MODEL7 weights 40%→20%→10%→0%→0% on the peak (faster fade).
+WHY: MODEL7 audit: prior path left CapEx ≫ D&amp;A (~$80M cumulative drag). Faster fade to maintenance ~1% so CapEx converges near D&amp;A by Y4–Y5.
 SOURCE: SEC 10-K FY2025 — PP&amp;E purchases + capitalized software
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="K18" authorId="0" shapeId="0">
+    <comment ref="K18" authorId="1" shapeId="0">
       <text>
         <t>CapEx % of Revenue
-HOW: Equation: fade from I68/I24 (FY25 CapEx/Sales ~1.98%) toward 1.0% steady. Weights 85%→65%→45%→30%→0% on the peak.
-WHY: FY25 CapEx was elevated by capitalized internal-use software. Fading avoids locking a peak reinvestment rate forever.
+HOW: Equation: fade from I68/I24 toward 1.0% steady. MODEL7 weights 40%→20%→10%→0%→0% on the peak (faster fade).
+WHY: MODEL7 audit: prior path left CapEx ≫ D&amp;A (~$80M cumulative drag). Faster fade to maintenance ~1% so CapEx converges near D&amp;A by Y4–Y5.
 SOURCE: SEC 10-K FY2025 — PP&amp;E purchases + capitalized software
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="L18" authorId="0" shapeId="0">
+    <comment ref="L18" authorId="1" shapeId="0">
       <text>
         <t>CapEx % of Revenue
-HOW: Equation: fade from I68/I24 (FY25 CapEx/Sales ~1.98%) toward 1.0% steady. Weights 85%→65%→45%→30%→0% on the peak.
-WHY: FY25 CapEx was elevated by capitalized internal-use software. Fading avoids locking a peak reinvestment rate forever.
+HOW: Equation: fade from I68/I24 toward 1.0% steady. MODEL7 weights 40%→20%→10%→0%→0% on the peak (faster fade).
+WHY: MODEL7 audit: prior path left CapEx ≫ D&amp;A (~$80M cumulative drag). Faster fade to maintenance ~1% so CapEx converges near D&amp;A by Y4–Y5.
 SOURCE: SEC 10-K FY2025 — PP&amp;E purchases + capitalized software
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="M18" authorId="0" shapeId="0">
+    <comment ref="M18" authorId="1" shapeId="0">
       <text>
         <t>CapEx % of Revenue
-HOW: Equation: fade from I68/I24 (FY25 CapEx/Sales ~1.98%) toward 1.0% steady. Weights 85%→65%→45%→30%→0% on the peak.
-WHY: FY25 CapEx was elevated by capitalized internal-use software. Fading avoids locking a peak reinvestment rate forever.
+HOW: Equation: fade from I68/I24 toward 1.0% steady. MODEL7 weights 40%→20%→10%→0%→0% on the peak (faster fade).
+WHY: MODEL7 audit: prior path left CapEx ≫ D&amp;A (~$80M cumulative drag). Faster fade to maintenance ~1% so CapEx converges near D&amp;A by Y4–Y5.
 SOURCE: SEC 10-K FY2025 — PP&amp;E purchases + capitalized software
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="N18" authorId="0" shapeId="0">
+    <comment ref="N18" authorId="1" shapeId="0">
       <text>
         <t>CapEx % of Revenue
-HOW: Equation: fade from I68/I24 (FY25 CapEx/Sales ~1.98%) toward 1.0% steady. Weights 85%→65%→45%→30%→0% on the peak.
-WHY: FY25 CapEx was elevated by capitalized internal-use software. Fading avoids locking a peak reinvestment rate forever.
+HOW: Equation: fade from I68/I24 toward 1.0% steady. MODEL7 weights 40%→20%→10%→0%→0% on the peak (faster fade).
+WHY: MODEL7 audit: prior path left CapEx ≫ D&amp;A (~$80M cumulative drag). Faster fade to maintenance ~1% so CapEx converges near D&amp;A by Y4–Y5.
 SOURCE: SEC 10-K FY2025 — PP&amp;E purchases + capitalized software
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="U18" authorId="0" shapeId="0">
+    <comment ref="U18" authorId="1" shapeId="0">
       <text>
         <t>CapEx % of Revenue
-HOW: Equation: fade from I68/I24 (FY25 CapEx/Sales ~1.98%) toward 1.0% steady. Weights 85%→65%→45%→30%→0% on the peak.
-WHY: FY25 CapEx was elevated by capitalized internal-use software. Fading avoids locking a peak reinvestment rate forever.
+HOW: Equation: fade from I68/I24 toward 1.0% steady. MODEL7 weights 40%→20%→10%→0%→0% on the peak (faster fade).
+WHY: MODEL7 audit: prior path left CapEx ≫ D&amp;A (~$80M cumulative drag). Faster fade to maintenance ~1% so CapEx converges near D&amp;A by Y4–Y5.
 SOURCE: SEC 10-K FY2025 — PP&amp;E purchases + capitalized software
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="B19" authorId="0" shapeId="0">
+    <comment ref="B19" authorId="1" shapeId="0">
       <text>
         <t>Debt Issuance (Repayment)
 HOW: POLICY input = 0 every year.
@@ -2608,7 +2607,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454726000030/fico-20260630.htm</t>
       </text>
     </comment>
-    <comment ref="J19" authorId="0" shapeId="0">
+    <comment ref="J19" authorId="1" shapeId="0">
       <text>
         <t>Debt Issuance (Repayment)
 HOW: POLICY input = 0 every year.
@@ -2617,7 +2616,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454726000030/fico-20260630.htm</t>
       </text>
     </comment>
-    <comment ref="K19" authorId="0" shapeId="0">
+    <comment ref="K19" authorId="1" shapeId="0">
       <text>
         <t>Debt Issuance (Repayment)
 HOW: POLICY input = 0 every year.
@@ -2626,7 +2625,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454726000030/fico-20260630.htm</t>
       </text>
     </comment>
-    <comment ref="L19" authorId="0" shapeId="0">
+    <comment ref="L19" authorId="1" shapeId="0">
       <text>
         <t>Debt Issuance (Repayment)
 HOW: POLICY input = 0 every year.
@@ -2635,7 +2634,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454726000030/fico-20260630.htm</t>
       </text>
     </comment>
-    <comment ref="M19" authorId="0" shapeId="0">
+    <comment ref="M19" authorId="1" shapeId="0">
       <text>
         <t>Debt Issuance (Repayment)
 HOW: POLICY input = 0 every year.
@@ -2644,7 +2643,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454726000030/fico-20260630.htm</t>
       </text>
     </comment>
-    <comment ref="N19" authorId="0" shapeId="0">
+    <comment ref="N19" authorId="1" shapeId="0">
       <text>
         <t>Debt Issuance (Repayment)
 HOW: POLICY input = 0 every year.
@@ -2653,7 +2652,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454726000030/fico-20260630.htm</t>
       </text>
     </comment>
-    <comment ref="U19" authorId="0" shapeId="0">
+    <comment ref="U19" authorId="1" shapeId="0">
       <text>
         <t>Debt Issuance (Repayment)
 HOW: POLICY input = 0 every year.
@@ -2662,7 +2661,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454726000030/fico-20260630.htm</t>
       </text>
     </comment>
-    <comment ref="B20" authorId="0" shapeId="0">
+    <comment ref="B20" authorId="1" shapeId="0">
       <text>
         <t>Equity Issued (Repaid)
 HOW: POLICY input = 0 every year.
@@ -2671,7 +2670,7 @@
 LINK: https://pages.stern.nyu.edu/~adamodar/New_Home_Page/datafile/histfcff.html</t>
       </text>
     </comment>
-    <comment ref="J20" authorId="0" shapeId="0">
+    <comment ref="J20" authorId="1" shapeId="0">
       <text>
         <t>Equity Issued (Repaid)
 HOW: POLICY input = 0 every year.
@@ -2680,7 +2679,7 @@
 LINK: https://pages.stern.nyu.edu/~adamodar/New_Home_Page/datafile/histfcff.html</t>
       </text>
     </comment>
-    <comment ref="K20" authorId="0" shapeId="0">
+    <comment ref="K20" authorId="1" shapeId="0">
       <text>
         <t>Equity Issued (Repaid)
 HOW: POLICY input = 0 every year.
@@ -2689,7 +2688,7 @@
 LINK: https://pages.stern.nyu.edu/~adamodar/New_Home_Page/datafile/histfcff.html</t>
       </text>
     </comment>
-    <comment ref="L20" authorId="0" shapeId="0">
+    <comment ref="L20" authorId="1" shapeId="0">
       <text>
         <t>Equity Issued (Repaid)
 HOW: POLICY input = 0 every year.
@@ -2698,7 +2697,7 @@
 LINK: https://pages.stern.nyu.edu/~adamodar/New_Home_Page/datafile/histfcff.html</t>
       </text>
     </comment>
-    <comment ref="M20" authorId="0" shapeId="0">
+    <comment ref="M20" authorId="1" shapeId="0">
       <text>
         <t>Equity Issued (Repaid)
 HOW: POLICY input = 0 every year.
@@ -2707,7 +2706,7 @@
 LINK: https://pages.stern.nyu.edu/~adamodar/New_Home_Page/datafile/histfcff.html</t>
       </text>
     </comment>
-    <comment ref="N20" authorId="0" shapeId="0">
+    <comment ref="N20" authorId="1" shapeId="0">
       <text>
         <t>Equity Issued (Repaid)
 HOW: POLICY input = 0 every year.
@@ -2716,7 +2715,7 @@
 LINK: https://pages.stern.nyu.edu/~adamodar/New_Home_Page/datafile/histfcff.html</t>
       </text>
     </comment>
-    <comment ref="U20" authorId="0" shapeId="0">
+    <comment ref="U20" authorId="1" shapeId="0">
       <text>
         <t>Equity Issued (Repaid)
 HOW: POLICY input = 0 every year.
@@ -5180,7 +5179,7 @@
 <file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
-    <author>vengeanceaiUSCMODEL6</author>
+    <author>vengeanceaiUSCMODEL7</author>
   </authors>
   <commentList>
     <comment ref="D6" authorId="0" shapeId="0">
@@ -6055,7 +6054,7 @@
       <c r="B12" s="74" t="n"/>
       <c r="C12" s="75" t="inlineStr">
         <is>
-          <t>FICO — vengeanceaiUSCMODEL6 (3-Statement + DCF)</t>
+          <t>FICO — vengeanceaiUSCMODEL7 (3-Statement + DCF)</t>
         </is>
       </c>
       <c r="D12" s="74" t="n"/>
@@ -6223,7 +6222,7 @@
       <c r="B21" s="85" t="n"/>
       <c r="C21" s="85" t="inlineStr">
         <is>
-          <t>vengeanceaiUSCMODEL6: D&amp;A on avg PP&amp;E (new CapEx depreciated); gross AR days + separate Deferred Revenue in NWC; SGA floor 20% / grind −25bps. WACC=9.24%, Exit 25x. Every Source is a clickable URL. Click Cover Source Index (cols E–G) or 3S/DCF col U/V for filings.</t>
+          <t>vengeanceaiUSCMODEL7: NWC%=fade→3% of sales; SGA floor 15%/−75bps; CapEx fade→1%; primary exit 16x (bull 25x). WACC=9.24%. Click Cover Source Index (cols E–G) or 3S/DCF col U/V for filings.</t>
         </is>
       </c>
       <c r="D21" s="85" t="n"/>
@@ -6283,9 +6282,9 @@
         </is>
       </c>
       <c r="D24" s="89" t="n"/>
-      <c r="E24" s="133" t="inlineStr">
-        <is>
-          <t>vengeanceaiUSCMODEL6 — SOURCE INDEX (click any link)</t>
+      <c r="E24" s="132" t="inlineStr">
+        <is>
+          <t>vengeanceaiUSCMODEL7 — SOURCE INDEX (click any link)</t>
         </is>
       </c>
       <c r="H24" s="89" t="n"/>
@@ -6305,7 +6304,7 @@
         </is>
       </c>
       <c r="D25" s="91" t="n"/>
-      <c r="E25" s="134" t="inlineStr">
+      <c r="E25" s="133" t="inlineStr">
         <is>
           <t>Every assumption / WACC / filing source used in this workbook. Same links appear on 3-statement col U/V and DCF col U/V.</t>
         </is>
@@ -6327,17 +6326,17 @@
         </is>
       </c>
       <c r="D26" s="91" t="n"/>
-      <c r="E26" s="135" t="inlineStr">
+      <c r="E26" s="134" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="F26" s="135" t="inlineStr">
+      <c r="F26" s="134" t="inlineStr">
         <is>
           <t>Clickable link</t>
         </is>
       </c>
-      <c r="G26" s="135" t="inlineStr">
+      <c r="G26" s="134" t="inlineStr">
         <is>
           <t>URL</t>
         </is>
@@ -6359,17 +6358,17 @@
         </is>
       </c>
       <c r="D27" s="91" t="n"/>
-      <c r="E27" s="136" t="inlineStr">
+      <c r="E27" s="135" t="inlineStr">
         <is>
           <t>10-K FY2025</t>
         </is>
       </c>
-      <c r="F27" s="137" t="inlineStr">
+      <c r="F27" s="136" t="inlineStr">
         <is>
           <t>10-K FY2025</t>
         </is>
       </c>
-      <c r="G27" s="137" t="inlineStr">
+      <c r="G27" s="136" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
         </is>
@@ -6387,17 +6386,17 @@
       <c r="B28" s="90" t="n"/>
       <c r="C28" s="91" t="n"/>
       <c r="D28" s="91" t="n"/>
-      <c r="E28" s="136" t="inlineStr">
+      <c r="E28" s="135" t="inlineStr">
         <is>
           <t>10-Q Q3 FY2026</t>
         </is>
       </c>
-      <c r="F28" s="137" t="inlineStr">
+      <c r="F28" s="136" t="inlineStr">
         <is>
           <t>10-Q Q3 FY2026</t>
         </is>
       </c>
-      <c r="G28" s="137" t="inlineStr">
+      <c r="G28" s="136" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/814547/000081454726000030/fico-20260630.htm</t>
         </is>
@@ -6415,17 +6414,17 @@
       <c r="B29" s="90" t="n"/>
       <c r="C29" s="90" t="n"/>
       <c r="D29" s="90" t="n"/>
-      <c r="E29" s="138" t="inlineStr">
+      <c r="E29" s="137" t="inlineStr">
         <is>
           <t>8-K 6.250% notes</t>
         </is>
       </c>
-      <c r="F29" s="139" t="inlineStr">
+      <c r="F29" s="138" t="inlineStr">
         <is>
           <t>8-K 6.250% notes</t>
         </is>
       </c>
-      <c r="G29" s="139" t="inlineStr">
+      <c r="G29" s="138" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/814547/000119312526117936/d56220d8k.htm</t>
         </is>
@@ -6440,170 +6439,170 @@
       <c r="O29" s="90" t="n"/>
     </row>
     <row r="30" ht="19.5" customHeight="1">
-      <c r="E30" s="140" t="inlineStr">
+      <c r="E30" s="139" t="inlineStr">
         <is>
           <t>Damodaran ERP</t>
         </is>
       </c>
-      <c r="F30" s="141" t="inlineStr">
+      <c r="F30" s="140" t="inlineStr">
         <is>
           <t>Damodaran ERP</t>
         </is>
       </c>
-      <c r="G30" s="141" t="inlineStr">
+      <c r="G30" s="140" t="inlineStr">
         <is>
           <t>https://pages.stern.nyu.edu/adamodar/New_Home_Page/home.htm</t>
         </is>
       </c>
     </row>
     <row r="31" ht="19.5" customHeight="1">
-      <c r="E31" s="140" t="inlineStr">
+      <c r="E31" s="139" t="inlineStr">
         <is>
           <t>Damodaran FCFF</t>
         </is>
       </c>
-      <c r="F31" s="141" t="inlineStr">
+      <c r="F31" s="140" t="inlineStr">
         <is>
           <t>Damodaran FCFF</t>
         </is>
       </c>
-      <c r="G31" s="141" t="inlineStr">
+      <c r="G31" s="140" t="inlineStr">
         <is>
           <t>https://pages.stern.nyu.edu/~adamodar/New_Home_Page/datafile/histfcff.html</t>
         </is>
       </c>
     </row>
     <row r="32" ht="19.5" customHeight="1">
-      <c r="E32" s="140" t="inlineStr">
+      <c r="E32" s="139" t="inlineStr">
         <is>
           <t>Damodaran implied ERP table</t>
         </is>
       </c>
-      <c r="F32" s="141" t="inlineStr">
+      <c r="F32" s="140" t="inlineStr">
         <is>
           <t>Damodaran implied ERP table</t>
         </is>
       </c>
-      <c r="G32" s="141" t="inlineStr">
+      <c r="G32" s="140" t="inlineStr">
         <is>
           <t>https://pages.stern.nyu.edu/~adamodar/New_Home_Page/datafile/histimpl.html</t>
         </is>
       </c>
     </row>
     <row r="33" ht="19.5" customHeight="1">
-      <c r="E33" s="140" t="inlineStr">
+      <c r="E33" s="139" t="inlineStr">
         <is>
           <t>FICO IR</t>
         </is>
       </c>
-      <c r="F33" s="141" t="inlineStr">
+      <c r="F33" s="140" t="inlineStr">
         <is>
           <t>FICO IR</t>
         </is>
       </c>
-      <c r="G33" s="141" t="inlineStr">
+      <c r="G33" s="140" t="inlineStr">
         <is>
           <t>https://www.fico.com/en/investors</t>
         </is>
       </c>
     </row>
     <row r="34" ht="19.5" customHeight="1">
-      <c r="E34" s="140" t="inlineStr">
+      <c r="E34" s="139" t="inlineStr">
         <is>
           <t>FRED DGS10</t>
         </is>
       </c>
-      <c r="F34" s="141" t="inlineStr">
+      <c r="F34" s="140" t="inlineStr">
         <is>
           <t>FRED DGS10</t>
         </is>
       </c>
-      <c r="G34" s="141" t="inlineStr">
+      <c r="G34" s="140" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DGS10</t>
         </is>
       </c>
     </row>
     <row r="35" ht="19.5" customHeight="1">
-      <c r="E35" s="140" t="inlineStr">
+      <c r="E35" s="139" t="inlineStr">
         <is>
           <t>FY2026 guidance EX-99.1</t>
         </is>
       </c>
-      <c r="F35" s="141" t="inlineStr">
+      <c r="F35" s="140" t="inlineStr">
         <is>
           <t>FY2026 guidance EX-99.1</t>
         </is>
       </c>
-      <c r="G35" s="141" t="inlineStr">
+      <c r="G35" s="140" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/814547/000081454726000031/exhibit991erq32026.htm</t>
         </is>
       </c>
     </row>
     <row r="36" ht="19.5" customHeight="1">
-      <c r="E36" s="140" t="inlineStr">
+      <c r="E36" s="139" t="inlineStr">
         <is>
           <t>US Treasury yield curve</t>
         </is>
       </c>
-      <c r="F36" s="141" t="inlineStr">
+      <c r="F36" s="140" t="inlineStr">
         <is>
           <t>US Treasury yield curve</t>
         </is>
       </c>
-      <c r="G36" s="141" t="inlineStr">
+      <c r="G36" s="140" t="inlineStr">
         <is>
           <t>https://home.treasury.gov/resource-center/data-chart-center/interest-rates/TextView?type=daily_treasury_yield_curve</t>
         </is>
       </c>
     </row>
     <row r="37" ht="19.5" customHeight="1">
-      <c r="E37" s="140" t="inlineStr">
+      <c r="E37" s="139" t="inlineStr">
         <is>
           <t>Yahoo FICO</t>
         </is>
       </c>
-      <c r="F37" s="141" t="inlineStr">
+      <c r="F37" s="140" t="inlineStr">
         <is>
           <t>Yahoo FICO</t>
         </is>
       </c>
-      <c r="G37" s="141" t="inlineStr">
+      <c r="G37" s="140" t="inlineStr">
         <is>
           <t>https://finance.yahoo.com/quote/FICO/key-statistics/</t>
         </is>
       </c>
     </row>
     <row r="38" ht="19.5" customHeight="1">
-      <c r="E38" s="140" t="inlineStr">
+      <c r="E38" s="139" t="inlineStr">
         <is>
           <t>Yahoo FICO quote</t>
         </is>
       </c>
-      <c r="F38" s="141" t="inlineStr">
+      <c r="F38" s="140" t="inlineStr">
         <is>
           <t>Yahoo FICO quote</t>
         </is>
       </c>
-      <c r="G38" s="141" t="inlineStr">
+      <c r="G38" s="140" t="inlineStr">
         <is>
           <t>https://finance.yahoo.com/quote/FICO/</t>
         </is>
       </c>
     </row>
     <row r="39" ht="19.5" customHeight="1">
-      <c r="E39" s="140" t="inlineStr">
+      <c r="E39" s="139" t="inlineStr">
         <is>
           <t>companyfacts</t>
         </is>
       </c>
-      <c r="F39" s="141" t="inlineStr">
+      <c r="F39" s="140" t="inlineStr">
         <is>
           <t>companyfacts</t>
         </is>
       </c>
-      <c r="G39" s="141" t="inlineStr">
+      <c r="G39" s="140" t="inlineStr">
         <is>
           <t>https://data.sec.gov/api/xbrl/companyfacts/CIK0000814547.json</t>
         </is>
@@ -6727,42 +6726,42 @@
       </c>
       <c r="C2" s="62" t="n"/>
       <c r="D2" s="63" t="n"/>
-      <c r="E2" s="142" t="n">
+      <c r="E2" s="141" t="n">
         <v>2021</v>
       </c>
-      <c r="F2" s="143">
+      <c r="F2" s="142">
         <f>+E2+1</f>
         <v/>
       </c>
-      <c r="G2" s="143">
+      <c r="G2" s="142">
         <f>+F2+1</f>
         <v/>
       </c>
-      <c r="H2" s="143">
+      <c r="H2" s="142">
         <f>+G2+1</f>
         <v/>
       </c>
-      <c r="I2" s="143">
+      <c r="I2" s="142">
         <f>+H2+1</f>
         <v/>
       </c>
-      <c r="J2" s="144">
+      <c r="J2" s="143">
         <f>+I2+1</f>
         <v/>
       </c>
-      <c r="K2" s="144">
+      <c r="K2" s="143">
         <f>+J2+1</f>
         <v/>
       </c>
-      <c r="L2" s="144">
+      <c r="L2" s="143">
         <f>+K2+1</f>
         <v/>
       </c>
-      <c r="M2" s="144">
+      <c r="M2" s="143">
         <f>+L2+1</f>
         <v/>
       </c>
-      <c r="N2" s="144">
+      <c r="N2" s="143">
         <f>+M2+1</f>
         <v/>
       </c>
@@ -6773,54 +6772,54 @@
           <t>Balance Sheet Check</t>
         </is>
       </c>
-      <c r="E3" s="145">
+      <c r="E3" s="144">
         <f>IFERROR(IF(ABS(E57)&gt;1,"ERROR","OK"),"OK")</f>
         <v/>
       </c>
-      <c r="F3" s="145">
+      <c r="F3" s="144">
         <f>IFERROR(IF(ABS(F57)&gt;1,"ERROR","OK"),"OK")</f>
         <v/>
       </c>
-      <c r="G3" s="145">
+      <c r="G3" s="144">
         <f>IFERROR(IF(ABS(G57)&gt;1,"ERROR","OK"),"OK")</f>
         <v/>
       </c>
-      <c r="H3" s="145">
+      <c r="H3" s="144">
         <f>IFERROR(IF(ABS(H57)&gt;1,"ERROR","OK"),"OK")</f>
         <v/>
       </c>
-      <c r="I3" s="145">
+      <c r="I3" s="144">
         <f>IFERROR(IF(ABS(I57)&gt;1,"ERROR","OK"),"OK")</f>
         <v/>
       </c>
-      <c r="J3" s="145">
+      <c r="J3" s="144">
         <f>IFERROR(IF(ABS(J57)&gt;1,"ERROR","OK"),"OK")</f>
         <v/>
       </c>
-      <c r="K3" s="145">
+      <c r="K3" s="144">
         <f>IFERROR(IF(ABS(K57)&gt;1,"ERROR","OK"),"OK")</f>
         <v/>
       </c>
-      <c r="L3" s="145">
+      <c r="L3" s="144">
         <f>IFERROR(IF(ABS(L57)&gt;1,"ERROR","OK"),"OK")</f>
         <v/>
       </c>
-      <c r="M3" s="145">
+      <c r="M3" s="144">
         <f>IFERROR(IF(ABS(M57)&gt;1,"ERROR","OK"),"OK")</f>
         <v/>
       </c>
-      <c r="N3" s="145">
+      <c r="N3" s="144">
         <f>IFERROR(IF(ABS(N57)&gt;1,"ERROR","OK"),"OK")</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="146" t="inlineStr">
+      <c r="B4" s="145" t="inlineStr">
         <is>
           <t>vengeanceaiUSCMODEL6: hover J–N for WHY+SOURCE; click blue Source link in col U (or LINK: URL in col C / V) to open the filing</t>
         </is>
       </c>
-      <c r="P4" s="147" t="inlineStr">
+      <c r="P4" s="146" t="inlineStr">
         <is>
           <t>ASSUMPTIONS EXPLAINED — click blue Source (col U) for the filing/data</t>
         </is>
@@ -6844,7 +6843,7 @@
       <c r="L5" s="65" t="n"/>
       <c r="M5" s="65" t="n"/>
       <c r="N5" s="65" t="n"/>
-      <c r="P5" s="148" t="inlineStr">
+      <c r="P5" s="147" t="inlineStr">
         <is>
           <t>Yellow = policy. Green = FY25-linked equations. Col U = clickable hyperlink. Col V = full URL (also clickable).</t>
         </is>
@@ -6857,37 +6856,37 @@
         </is>
       </c>
       <c r="D6" s="47" t="n"/>
-      <c r="P6" s="149" t="inlineStr">
+      <c r="P6" s="148" t="inlineStr">
         <is>
           <t>Row</t>
         </is>
       </c>
-      <c r="Q6" s="149" t="inlineStr">
+      <c r="Q6" s="148" t="inlineStr">
         <is>
           <t>Assumption</t>
         </is>
       </c>
-      <c r="R6" s="149" t="inlineStr">
+      <c r="R6" s="148" t="inlineStr">
         <is>
           <t>What it is</t>
         </is>
       </c>
-      <c r="S6" s="149" t="inlineStr">
+      <c r="S6" s="148" t="inlineStr">
         <is>
           <t>How set in model</t>
         </is>
       </c>
-      <c r="T6" s="149" t="inlineStr">
+      <c r="T6" s="148" t="inlineStr">
         <is>
           <t>Why this choice</t>
         </is>
       </c>
-      <c r="U6" s="149" t="inlineStr">
+      <c r="U6" s="148" t="inlineStr">
         <is>
           <t>Source (click)</t>
         </is>
       </c>
-      <c r="V6" s="149" t="inlineStr">
+      <c r="V6" s="148" t="inlineStr">
         <is>
           <t>Source URL</t>
         </is>
@@ -6899,7 +6898,7 @@
           <t>Revenue Growth (% Change)</t>
         </is>
       </c>
-      <c r="C7" s="150" t="inlineStr">
+      <c r="C7" s="149" t="inlineStr">
         <is>
           <t>WHY: Y1 ≈ company FY2026 revenue guidance (~$2.53B / FY25 $1.991B − 1 ≈ 27%). Then fade toward terminal g=3% (not straight… | SOURCE: SEC EX-99.1 Q3 FY2026 — updated FY2026 revenue guidance $2.53B | LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454726000031/exhibit991erq32026.htm | HOW: Yellow POLICY input: 27% / 16% / 13% / 10% / 7%.</t>
         </is>
@@ -6922,50 +6921,50 @@
         <f>I24/H24-1</f>
         <v/>
       </c>
-      <c r="J7" s="151" t="n">
+      <c r="J7" s="150" t="n">
         <v>0.27</v>
       </c>
-      <c r="K7" s="151" t="n">
+      <c r="K7" s="150" t="n">
         <v>0.16</v>
       </c>
-      <c r="L7" s="151" t="n">
+      <c r="L7" s="150" t="n">
         <v>0.13</v>
       </c>
-      <c r="M7" s="151" t="n">
+      <c r="M7" s="150" t="n">
         <v>0.1</v>
       </c>
-      <c r="N7" s="151" t="n">
+      <c r="N7" s="150" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="P7" s="152" t="n">
+      <c r="P7" s="151" t="n">
         <v>7</v>
       </c>
-      <c r="Q7" s="152" t="inlineStr">
+      <c r="Q7" s="151" t="inlineStr">
         <is>
           <t>Revenue Growth</t>
         </is>
       </c>
-      <c r="R7" s="153" t="inlineStr">
+      <c r="R7" s="152" t="inlineStr">
         <is>
           <t>Year-over-year % increase in revenue for each forecast year.</t>
         </is>
       </c>
-      <c r="S7" s="153" t="inlineStr">
+      <c r="S7" s="152" t="inlineStr">
         <is>
           <t>Yellow POLICY input: 27% / 16% / 13% / 10% / 7%.</t>
         </is>
       </c>
-      <c r="T7" s="153" t="inlineStr">
+      <c r="T7" s="152" t="inlineStr">
         <is>
           <t>Y1 ≈ company FY2026 revenue guidance (~$2.53B / FY25 $1.991B − 1 ≈ 27%). Then fade toward terminal g=3% (not straight-lined). This is the main forward-looking judgment; it drives Rev → GP → EBT → Net Earnings → CF.</t>
         </is>
       </c>
-      <c r="U7" s="154" t="inlineStr">
+      <c r="U7" s="153" t="inlineStr">
         <is>
           <t>SEC EX-99.1 Q3 FY2026 — updated FY2026 revenue guidance $2.53B</t>
         </is>
       </c>
-      <c r="V7" s="154" t="inlineStr">
+      <c r="V7" s="153" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/814547/000081454726000031/exhibit991erq32026.htm</t>
         </is>
@@ -6977,7 +6976,7 @@
           <t>Cost of Goods Sold (% of Revenue)</t>
         </is>
       </c>
-      <c r="C8" s="150" t="inlineStr">
+      <c r="C8" s="149" t="inlineStr">
         <is>
           <t>WHY: Locks in latest reported cost structure (~17.8%). Scores mix is high-margin; holding FY25 is conservative vs further … | SOURCE: SEC 10-K FY2025 — Cost of revenues / Total revenues | LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm | HOW: Excel equation: I25/I24 (FY25 COGS ÷ FY25 Revenue) held flat.</t>
         </is>
@@ -7003,55 +7002,55 @@
         <f>I25/I24</f>
         <v/>
       </c>
-      <c r="J8" s="155">
+      <c r="J8" s="154">
         <f>$I$25/$I$24</f>
         <v/>
       </c>
-      <c r="K8" s="155">
+      <c r="K8" s="154">
         <f>$I$25/$I$24</f>
         <v/>
       </c>
-      <c r="L8" s="155">
+      <c r="L8" s="154">
         <f>$I$25/$I$24</f>
         <v/>
       </c>
-      <c r="M8" s="155">
+      <c r="M8" s="154">
         <f>$I$25/$I$24</f>
         <v/>
       </c>
-      <c r="N8" s="155">
+      <c r="N8" s="154">
         <f>$I$25/$I$24</f>
         <v/>
       </c>
-      <c r="P8" s="152" t="n">
+      <c r="P8" s="151" t="n">
         <v>8</v>
       </c>
-      <c r="Q8" s="152" t="inlineStr">
+      <c r="Q8" s="151" t="inlineStr">
         <is>
           <t>COGS % of Revenue</t>
         </is>
       </c>
-      <c r="R8" s="153" t="inlineStr">
+      <c r="R8" s="152" t="inlineStr">
         <is>
           <t>Cost of revenues as a % of sales (gross margin = 1 − this).</t>
         </is>
       </c>
-      <c r="S8" s="153" t="inlineStr">
+      <c r="S8" s="152" t="inlineStr">
         <is>
           <t>Excel equation: I25/I24 (FY25 COGS ÷ FY25 Revenue) held flat.</t>
         </is>
       </c>
-      <c r="T8" s="153" t="inlineStr">
+      <c r="T8" s="152" t="inlineStr">
         <is>
           <t>Locks in latest reported cost structure (~17.8%). Scores mix is high-margin; holding FY25 is conservative vs further mix shift.</t>
         </is>
       </c>
-      <c r="U8" s="154" t="inlineStr">
+      <c r="U8" s="153" t="inlineStr">
         <is>
           <t>SEC 10-K FY2025 — Cost of revenues / Total revenues</t>
         </is>
       </c>
-      <c r="V8" s="154" t="inlineStr">
+      <c r="V8" s="153" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
         </is>
@@ -7060,84 +7059,84 @@
     <row r="9" hidden="1" outlineLevel="1" ht="40" customHeight="1">
       <c r="B9" s="19" t="inlineStr">
         <is>
-          <t>SGA % of Revenue (floor 20%, −25bps×t)</t>
-        </is>
-      </c>
-      <c r="C9" s="150" t="inlineStr">
-        <is>
-          <t>WHY: MODEL6 fix: enterprise software needs lasting G&amp;A (sales, legal, compliance). Floor raised from 5%→20%; grind cut fro… | SOURCE: SEC 10-K FY2025 — SG&amp;A + restructuring note | LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm | HOW: Equation: MAX(20%, (I28 − 10,922)/I24 − 25bps × year). Strips FY25 restructuring; then −0.25% of sales each year.</t>
+          <t>SG&amp;A % of Revenue (floor 15%, −75bps×t)</t>
+        </is>
+      </c>
+      <c r="C9" s="149" t="inlineStr">
+        <is>
+          <t>WHY: MODEL7 audit: allow software operating leverage. Floor 15%; grind −75 bps so SG&amp;A can scale toward mid-teens as reven… | SOURCE: SEC 10-K FY2025 — SG&amp;A + restructuring note | LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm | HOW: Equation: MAX(15%, (I28 − 10,922)/I24 − 75bps × year). Strips FY25 restructuring; then −0.75% of sales each year.</t>
         </is>
       </c>
       <c r="D9" s="47" t="n"/>
-      <c r="E9" s="156">
+      <c r="E9" s="155">
         <f>E28</f>
         <v/>
       </c>
-      <c r="F9" s="156">
+      <c r="F9" s="155">
         <f>F28</f>
         <v/>
       </c>
-      <c r="G9" s="156">
+      <c r="G9" s="155">
         <f>G28</f>
         <v/>
       </c>
-      <c r="H9" s="156">
+      <c r="H9" s="155">
         <f>H28</f>
         <v/>
       </c>
-      <c r="I9" s="156">
+      <c r="I9" s="155">
         <f>I28</f>
         <v/>
       </c>
-      <c r="J9" s="157">
-        <f>MAX(0.2,(($I$28-10922.0)/$I$24)-0.0025)</f>
-        <v/>
-      </c>
-      <c r="K9" s="157">
-        <f>MAX(0.2,(($I$28-10922.0)/$I$24)-0.005)</f>
-        <v/>
-      </c>
-      <c r="L9" s="157">
-        <f>MAX(0.2,(($I$28-10922.0)/$I$24)-0.0075)</f>
-        <v/>
-      </c>
-      <c r="M9" s="157">
-        <f>MAX(0.2,(($I$28-10922.0)/$I$24)-0.01)</f>
-        <v/>
-      </c>
-      <c r="N9" s="157">
-        <f>MAX(0.2,(($I$28-10922.0)/$I$24)-0.0125)</f>
-        <v/>
-      </c>
-      <c r="P9" s="152" t="n">
+      <c r="J9" s="156">
+        <f>MAX(0.15,(($I$28-10922.0)/$I$24)-0.0075)</f>
+        <v/>
+      </c>
+      <c r="K9" s="156">
+        <f>MAX(0.15,(($I$28-10922.0)/$I$24)-0.015)</f>
+        <v/>
+      </c>
+      <c r="L9" s="156">
+        <f>MAX(0.15,(($I$28-10922.0)/$I$24)-0.0225)</f>
+        <v/>
+      </c>
+      <c r="M9" s="156">
+        <f>MAX(0.15,(($I$28-10922.0)/$I$24)-0.03)</f>
+        <v/>
+      </c>
+      <c r="N9" s="156">
+        <f>MAX(0.15,(($I$28-10922.0)/$I$24)-0.0375)</f>
+        <v/>
+      </c>
+      <c r="P9" s="151" t="n">
         <v>9</v>
       </c>
-      <c r="Q9" s="152" t="inlineStr">
-        <is>
-          <t>SGA % of Revenue</t>
-        </is>
-      </c>
-      <c r="R9" s="153" t="inlineStr">
-        <is>
-          <t>Operating opex (Salaries &amp; Benefits / SG&amp;A) as % of sales.</t>
-        </is>
-      </c>
-      <c r="S9" s="153" t="inlineStr">
-        <is>
-          <t>Equation: MAX(20%, (I28 − 10,922)/I24 − 25bps × year). Strips FY25 restructuring; then −0.25% of sales each year.</t>
-        </is>
-      </c>
-      <c r="T9" s="153" t="inlineStr">
-        <is>
-          <t>MODEL6 fix: enterprise software needs lasting G&amp;A (sales, legal, compliance). Floor raised from 5%→20%; grind cut from 50→25 bps so SGA stays in a realistic ~22–25% band near FY25 normalized (~25%).</t>
-        </is>
-      </c>
-      <c r="U9" s="154" t="inlineStr">
+      <c r="Q9" s="151" t="inlineStr">
+        <is>
+          <t>SG&amp;A % of Revenue</t>
+        </is>
+      </c>
+      <c r="R9" s="152" t="inlineStr">
+        <is>
+          <t>Operating opex (SG&amp;A) as % of sales.</t>
+        </is>
+      </c>
+      <c r="S9" s="152" t="inlineStr">
+        <is>
+          <t>Equation: MAX(15%, (I28 − 10,922)/I24 − 75bps × year). Strips FY25 restructuring; then −0.75% of sales each year.</t>
+        </is>
+      </c>
+      <c r="T9" s="152" t="inlineStr">
+        <is>
+          <t>MODEL7 audit: allow software operating leverage. Floor 15%; grind −75 bps so SG&amp;A can scale toward mid-teens as revenue expands (not stuck ~24–25%).</t>
+        </is>
+      </c>
+      <c r="U9" s="153" t="inlineStr">
         <is>
           <t>SEC 10-K FY2025 — SG&amp;A + restructuring note</t>
         </is>
       </c>
-      <c r="V9" s="154" t="inlineStr">
+      <c r="V9" s="153" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
         </is>
@@ -7149,81 +7148,81 @@
           <t>R&amp;D % of Revenue (equation)</t>
         </is>
       </c>
-      <c r="C10" s="150" t="inlineStr">
+      <c r="C10" s="149" t="inlineStr">
         <is>
           <t>WHY: FICO reinvests steadily in analytics/software. Flat % grows dollars with revenue. | SOURCE: SEC 10-K FY2025 — Research and development | LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm | HOW: Excel equation: I29/I24 held flat (~9.46%).</t>
         </is>
       </c>
       <c r="D10" s="47" t="n"/>
-      <c r="E10" s="156">
+      <c r="E10" s="155">
         <f>E29</f>
         <v/>
       </c>
-      <c r="F10" s="156">
+      <c r="F10" s="155">
         <f>F29</f>
         <v/>
       </c>
-      <c r="G10" s="156">
+      <c r="G10" s="155">
         <f>G29</f>
         <v/>
       </c>
-      <c r="H10" s="156">
+      <c r="H10" s="155">
         <f>H29</f>
         <v/>
       </c>
-      <c r="I10" s="156">
+      <c r="I10" s="155">
         <f>I29</f>
         <v/>
       </c>
-      <c r="J10" s="157">
+      <c r="J10" s="156">
         <f>$I$29/$I$24</f>
         <v/>
       </c>
-      <c r="K10" s="157">
+      <c r="K10" s="156">
         <f>$I$29/$I$24</f>
         <v/>
       </c>
-      <c r="L10" s="157">
+      <c r="L10" s="156">
         <f>$I$29/$I$24</f>
         <v/>
       </c>
-      <c r="M10" s="157">
+      <c r="M10" s="156">
         <f>$I$29/$I$24</f>
         <v/>
       </c>
-      <c r="N10" s="157">
+      <c r="N10" s="156">
         <f>$I$29/$I$24</f>
         <v/>
       </c>
-      <c r="P10" s="152" t="n">
+      <c r="P10" s="151" t="n">
         <v>10</v>
       </c>
-      <c r="Q10" s="152" t="inlineStr">
+      <c r="Q10" s="151" t="inlineStr">
         <is>
           <t>R&amp;D % of Revenue</t>
         </is>
       </c>
-      <c r="R10" s="153" t="inlineStr">
+      <c r="R10" s="152" t="inlineStr">
         <is>
           <t>Research &amp; development (template label may say Rent and Overhead) as % of sales.</t>
         </is>
       </c>
-      <c r="S10" s="153" t="inlineStr">
+      <c r="S10" s="152" t="inlineStr">
         <is>
           <t>Excel equation: I29/I24 held flat (~9.46%).</t>
         </is>
       </c>
-      <c r="T10" s="153" t="inlineStr">
+      <c r="T10" s="152" t="inlineStr">
         <is>
           <t>FICO reinvests steadily in analytics/software. Flat % grows dollars with revenue.</t>
         </is>
       </c>
-      <c r="U10" s="154" t="inlineStr">
+      <c r="U10" s="153" t="inlineStr">
         <is>
           <t>SEC 10-K FY2025 — Research and development</t>
         </is>
       </c>
-      <c r="V10" s="154" t="inlineStr">
+      <c r="V10" s="153" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
         </is>
@@ -7235,7 +7234,7 @@
           <t>D&amp;A % of Avg PP&amp;E (rate=FY25 DA/PPE; $ uses avg base)</t>
         </is>
       </c>
-      <c r="C11" s="150" t="inlineStr">
+      <c r="C11" s="149" t="inlineStr">
         <is>
           <t>WHY: MODEL6 fix: prior model depreciated only opening PP&amp;E, so ~$96M of forecast CapEx never hit D&amp;A/FCFF add-back. Averag… | SOURCE: SEC 10-K FY2025 — D&amp;A and PP&amp;E | LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm | HOW: Rate = I30/I44 (FY25 DA ÷ FY25 PPE). Forecast DA$ = ((Open + Open+CapEx)/2) × rate.</t>
         </is>
@@ -7261,55 +7260,55 @@
         <f>I30/I92</f>
         <v/>
       </c>
-      <c r="J11" s="155">
+      <c r="J11" s="154">
         <f>IF($I$44=0,0.25,$I$30/$I$44)</f>
         <v/>
       </c>
-      <c r="K11" s="155">
+      <c r="K11" s="154">
         <f>IF($I$44=0,0.25,$I$30/$I$44)</f>
         <v/>
       </c>
-      <c r="L11" s="155">
+      <c r="L11" s="154">
         <f>IF($I$44=0,0.25,$I$30/$I$44)</f>
         <v/>
       </c>
-      <c r="M11" s="155">
+      <c r="M11" s="154">
         <f>IF($I$44=0,0.25,$I$30/$I$44)</f>
         <v/>
       </c>
-      <c r="N11" s="155">
+      <c r="N11" s="154">
         <f>IF($I$44=0,0.25,$I$30/$I$44)</f>
         <v/>
       </c>
-      <c r="P11" s="152" t="n">
+      <c r="P11" s="151" t="n">
         <v>11</v>
       </c>
-      <c r="Q11" s="152" t="inlineStr">
+      <c r="Q11" s="151" t="inlineStr">
         <is>
           <t>D&amp;A % of Avg PP&amp;E</t>
         </is>
       </c>
-      <c r="R11" s="153" t="inlineStr">
+      <c r="R11" s="152" t="inlineStr">
         <is>
           <t>Depreciation rate from FY25; dollars applied to average PP&amp;E so new CapEx is depreciated.</t>
         </is>
       </c>
-      <c r="S11" s="153" t="inlineStr">
+      <c r="S11" s="152" t="inlineStr">
         <is>
           <t>Rate = I30/I44 (FY25 DA ÷ FY25 PPE). Forecast DA$ = ((Open + Open+CapEx)/2) × rate.</t>
         </is>
       </c>
-      <c r="T11" s="153" t="inlineStr">
+      <c r="T11" s="152" t="inlineStr">
         <is>
           <t>MODEL6 fix: prior model depreciated only opening PP&amp;E, so ~$96M of forecast CapEx never hit D&amp;A/FCFF add-back. Average PP&amp;E (Open ↔ pre-DA close) depreciates additions in the year they are placed in service.</t>
         </is>
       </c>
-      <c r="U11" s="154" t="inlineStr">
+      <c r="U11" s="153" t="inlineStr">
         <is>
           <t>SEC 10-K FY2025 — D&amp;A and PP&amp;E</t>
         </is>
       </c>
-      <c r="V11" s="154" t="inlineStr">
+      <c r="V11" s="153" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
         </is>
@@ -7321,7 +7320,7 @@
           <t>Interest (% of Debt Open Bal)</t>
         </is>
       </c>
-      <c r="C12" s="150" t="inlineStr">
+      <c r="C12" s="149" t="inlineStr">
         <is>
           <t>WHY: Approximates average coupon / cost of debt on the book. Debt held flat (issuance = 0), so interest stays linked to th… | SOURCE: SEC 10-K FY2025 — Interest expense; see also 8-K 6.250% notes | LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm | HOW: Excel equation: I101/I98 (FY25 interest ÷ FY25 opening debt in schedule).</t>
         </is>
@@ -7347,55 +7346,55 @@
         <f>I101/I98</f>
         <v/>
       </c>
-      <c r="J12" s="155">
+      <c r="J12" s="154">
         <f>IF($I$98=0,0.05,$I$101/$I$98)</f>
         <v/>
       </c>
-      <c r="K12" s="155">
+      <c r="K12" s="154">
         <f>IF($I$98=0,0.05,$I$101/$I$98)</f>
         <v/>
       </c>
-      <c r="L12" s="155">
+      <c r="L12" s="154">
         <f>IF($I$98=0,0.05,$I$101/$I$98)</f>
         <v/>
       </c>
-      <c r="M12" s="155">
+      <c r="M12" s="154">
         <f>IF($I$98=0,0.05,$I$101/$I$98)</f>
         <v/>
       </c>
-      <c r="N12" s="155">
+      <c r="N12" s="154">
         <f>IF($I$98=0,0.05,$I$101/$I$98)</f>
         <v/>
       </c>
-      <c r="P12" s="152" t="n">
+      <c r="P12" s="151" t="n">
         <v>12</v>
       </c>
-      <c r="Q12" s="152" t="inlineStr">
+      <c r="Q12" s="151" t="inlineStr">
         <is>
           <t>Interest % of Debt Open</t>
         </is>
       </c>
-      <c r="R12" s="153" t="inlineStr">
+      <c r="R12" s="152" t="inlineStr">
         <is>
           <t>Interest expense as % of opening debt balance.</t>
         </is>
       </c>
-      <c r="S12" s="153" t="inlineStr">
+      <c r="S12" s="152" t="inlineStr">
         <is>
           <t>Excel equation: I101/I98 (FY25 interest ÷ FY25 opening debt in schedule).</t>
         </is>
       </c>
-      <c r="T12" s="153" t="inlineStr">
+      <c r="T12" s="152" t="inlineStr">
         <is>
           <t>Approximates average coupon / cost of debt on the book. Debt held flat (issuance = 0), so interest stays linked to that stock.</t>
         </is>
       </c>
-      <c r="U12" s="154" t="inlineStr">
+      <c r="U12" s="153" t="inlineStr">
         <is>
           <t>SEC 10-K FY2025 — Interest expense; see also 8-K 6.250% notes</t>
         </is>
       </c>
-      <c r="V12" s="154" t="inlineStr">
+      <c r="V12" s="153" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
         </is>
@@ -7407,7 +7406,7 @@
           <t>Tax Rate (% of Earnings Before Tax)</t>
         </is>
       </c>
-      <c r="C13" s="150" t="inlineStr">
+      <c r="C13" s="149" t="inlineStr">
         <is>
           <t>WHY: Uses reported effective rate (~19% on template EBT; ~18.8% on 10-K EBT). UFCF in DCF also uses unlevered EBIT × t. | SOURCE: SEC 10-K FY2025 — Provision for income taxes / Income before taxes | LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm | HOW: Excel equation: I35/I33 (FY25 tax ÷ simplified FY25 EBT in this template).</t>
         </is>
@@ -7433,55 +7432,55 @@
         <f>I35/I33</f>
         <v/>
       </c>
-      <c r="J13" s="155">
+      <c r="J13" s="154">
         <f>IF($I$33=0,0.21,$I$35/$I$33)</f>
         <v/>
       </c>
-      <c r="K13" s="155">
+      <c r="K13" s="154">
         <f>IF($I$33=0,0.21,$I$35/$I$33)</f>
         <v/>
       </c>
-      <c r="L13" s="155">
+      <c r="L13" s="154">
         <f>IF($I$33=0,0.21,$I$35/$I$33)</f>
         <v/>
       </c>
-      <c r="M13" s="155">
+      <c r="M13" s="154">
         <f>IF($I$33=0,0.21,$I$35/$I$33)</f>
         <v/>
       </c>
-      <c r="N13" s="155">
+      <c r="N13" s="154">
         <f>IF($I$33=0,0.21,$I$35/$I$33)</f>
         <v/>
       </c>
-      <c r="P13" s="152" t="n">
+      <c r="P13" s="151" t="n">
         <v>13</v>
       </c>
-      <c r="Q13" s="152" t="inlineStr">
+      <c r="Q13" s="151" t="inlineStr">
         <is>
           <t>Tax Rate (% of EBT)</t>
         </is>
       </c>
-      <c r="R13" s="153" t="inlineStr">
+      <c r="R13" s="152" t="inlineStr">
         <is>
           <t>Effective book tax rate applied to forecast EBT.</t>
         </is>
       </c>
-      <c r="S13" s="153" t="inlineStr">
+      <c r="S13" s="152" t="inlineStr">
         <is>
           <t>Excel equation: I35/I33 (FY25 tax ÷ simplified FY25 EBT in this template).</t>
         </is>
       </c>
-      <c r="T13" s="153" t="inlineStr">
+      <c r="T13" s="152" t="inlineStr">
         <is>
           <t>Uses reported effective rate (~19% on template EBT; ~18.8% on 10-K EBT). UFCF in DCF also uses unlevered EBIT × t.</t>
         </is>
       </c>
-      <c r="U13" s="154" t="inlineStr">
+      <c r="U13" s="153" t="inlineStr">
         <is>
           <t>SEC 10-K FY2025 — Provision for income taxes / Income before taxes</t>
         </is>
       </c>
-      <c r="V13" s="154" t="inlineStr">
+      <c r="V13" s="153" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
         </is>
@@ -7509,84 +7508,84 @@
     <row r="15" hidden="1" outlineLevel="1" ht="40" customHeight="1">
       <c r="B15" s="19" t="inlineStr">
         <is>
-          <t>Accounts Receivable (Days)</t>
-        </is>
-      </c>
-      <c r="C15" s="158" t="inlineStr">
-        <is>
-          <t>WHY: MODEL6 fix: DSO must use gross receivables. Deferred Revenue is a contract liability projected separately (WC row 88 … | SOURCE: SEC companyfacts XBRL — AR; DeferredRevenueCurrent separate | LINK: https://data.sec.gov/api/xbrl/companyfacts/CIK0000814547.json | HOW: Excel equation: ROUND(I42/I24×365, 0). I42 is GROSS AR (not net of deferred).</t>
+          <t>Operating NWC % of Revenue (fade → 3%)</t>
+        </is>
+      </c>
+      <c r="C15" s="157" t="inlineStr">
+        <is>
+          <t>WHY: MODEL7 audit: ends the gross-AR-days + deferred double-count that drained ~$297M of FCFF. Asset-light software WC fad… | SOURCE: SEC companyfacts XBRL — AR / AP / DeferredRevenueCurrent | LINK: https://data.sec.gov/api/xbrl/companyfacts/CIK0000814547.json | HOW: Equation: fade FY25 op. NWC/Sales → 3% steady (weights 70/50/30/15/0).</t>
         </is>
       </c>
       <c r="D15" s="32" t="n"/>
-      <c r="E15" s="156">
+      <c r="E15" s="155">
         <f>E42/E24*365</f>
         <v/>
       </c>
-      <c r="F15" s="156">
+      <c r="F15" s="155">
         <f>F42/F24*365</f>
         <v/>
       </c>
-      <c r="G15" s="156">
+      <c r="G15" s="155">
         <f>G42/G24*365</f>
         <v/>
       </c>
-      <c r="H15" s="156">
+      <c r="H15" s="155">
         <f>H42/H24*365</f>
         <v/>
       </c>
-      <c r="I15" s="156">
+      <c r="I15" s="155">
         <f>I42/I24*365</f>
         <v/>
       </c>
-      <c r="J15" s="159">
-        <f>ROUND($I$42/$I$24*365,0)</f>
-        <v/>
-      </c>
-      <c r="K15" s="159">
-        <f>ROUND($I$42/$I$24*365,0)</f>
-        <v/>
-      </c>
-      <c r="L15" s="159">
-        <f>ROUND($I$42/$I$24*365,0)</f>
-        <v/>
-      </c>
-      <c r="M15" s="159">
-        <f>ROUND($I$42/$I$24*365,0)</f>
-        <v/>
-      </c>
-      <c r="N15" s="159">
-        <f>ROUND($I$42/$I$24*365,0)</f>
-        <v/>
-      </c>
-      <c r="P15" s="152" t="n">
+      <c r="J15" s="156">
+        <f>MAX(0,(($I$42+$I$43-$I$48-$I$88)/$I$24))*0.7+0.03*(1-0.7)</f>
+        <v/>
+      </c>
+      <c r="K15" s="156">
+        <f>MAX(0,(($I$42+$I$43-$I$48-$I$88)/$I$24))*0.5+0.03*(1-0.5)</f>
+        <v/>
+      </c>
+      <c r="L15" s="156">
+        <f>MAX(0,(($I$42+$I$43-$I$48-$I$88)/$I$24))*0.3+0.03*(1-0.3)</f>
+        <v/>
+      </c>
+      <c r="M15" s="156">
+        <f>MAX(0,(($I$42+$I$43-$I$48-$I$88)/$I$24))*0.15+0.03*(1-0.15)</f>
+        <v/>
+      </c>
+      <c r="N15" s="156">
+        <f>MAX(0,(($I$42+$I$43-$I$48-$I$88)/$I$24))*0.0+0.03*(1-0.0)</f>
+        <v/>
+      </c>
+      <c r="P15" s="151" t="n">
         <v>15</v>
       </c>
-      <c r="Q15" s="152" t="inlineStr">
-        <is>
-          <t>Accounts Receivable (Days)</t>
-        </is>
-      </c>
-      <c r="R15" s="153" t="inlineStr">
-        <is>
-          <t>Standard DSO: gross AR days used to project Gross AR = Rev × days/365.</t>
-        </is>
-      </c>
-      <c r="S15" s="153" t="inlineStr">
-        <is>
-          <t>Excel equation: ROUND(I42/I24×365, 0). I42 is GROSS AR (not net of deferred).</t>
-        </is>
-      </c>
-      <c r="T15" s="153" t="inlineStr">
-        <is>
-          <t>MODEL6 fix: DSO must use gross receivables. Deferred Revenue is a contract liability projected separately (WC row 88 = Rev × FY25 Def/Rev). NWC = GrossAR + Inv − AP − Deferred.</t>
-        </is>
-      </c>
-      <c r="U15" s="154" t="inlineStr">
-        <is>
-          <t>SEC companyfacts XBRL — AR; DeferredRevenueCurrent separate</t>
-        </is>
-      </c>
-      <c r="V15" s="154" t="inlineStr">
+      <c r="Q15" s="151" t="inlineStr">
+        <is>
+          <t>Operating NWC % of Revenue</t>
+        </is>
+      </c>
+      <c r="R15" s="152" t="inlineStr">
+        <is>
+          <t>Single consolidated operating working-capital ratio (AR+Inv−AP−Deferred)/Sales.</t>
+        </is>
+      </c>
+      <c r="S15" s="152" t="inlineStr">
+        <is>
+          <t>Equation: fade FY25 op. NWC/Sales → 3% steady (weights 70/50/30/15/0).</t>
+        </is>
+      </c>
+      <c r="T15" s="152" t="inlineStr">
+        <is>
+          <t>MODEL7 audit: ends the gross-AR-days + deferred double-count that drained ~$297M of FCFF. Asset-light software WC fades toward ~3% of sales; BS AR is plugged so AR−AP−Deferred = NWC.</t>
+        </is>
+      </c>
+      <c r="U15" s="153" t="inlineStr">
+        <is>
+          <t>SEC companyfacts XBRL — AR / AP / DeferredRevenueCurrent</t>
+        </is>
+      </c>
+      <c r="V15" s="153" t="inlineStr">
         <is>
           <t>https://data.sec.gov/api/xbrl/companyfacts/CIK0000814547.json</t>
         </is>
@@ -7598,76 +7597,76 @@
           <t>Inventory (Days)</t>
         </is>
       </c>
-      <c r="C16" s="158" t="inlineStr">
+      <c r="C16" s="157" t="inlineStr">
         <is>
           <t>WHY: No inventory cycle to fund. | SOURCE: SEC 10-K FY2025 — Inventory ≈ $0 | LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm | HOW: Hard zero — FICO is software / scores; inventory is immaterial.</t>
         </is>
       </c>
       <c r="D16" s="32" t="n"/>
-      <c r="E16" s="156">
+      <c r="E16" s="155">
         <f>E43/E25*365</f>
         <v/>
       </c>
-      <c r="F16" s="156">
+      <c r="F16" s="155">
         <f>F43/F25*365</f>
         <v/>
       </c>
-      <c r="G16" s="156">
+      <c r="G16" s="155">
         <f>G43/G25*365</f>
         <v/>
       </c>
-      <c r="H16" s="156">
+      <c r="H16" s="155">
         <f>H43/H25*365</f>
         <v/>
       </c>
-      <c r="I16" s="156">
+      <c r="I16" s="155">
         <f>I43/I25*365</f>
         <v/>
       </c>
-      <c r="J16" s="160" t="n">
+      <c r="J16" s="158" t="n">
         <v>0</v>
       </c>
-      <c r="K16" s="160" t="n">
+      <c r="K16" s="158" t="n">
         <v>0</v>
       </c>
-      <c r="L16" s="160" t="n">
+      <c r="L16" s="158" t="n">
         <v>0</v>
       </c>
-      <c r="M16" s="160" t="n">
+      <c r="M16" s="158" t="n">
         <v>0</v>
       </c>
-      <c r="N16" s="160" t="n">
+      <c r="N16" s="158" t="n">
         <v>0</v>
       </c>
-      <c r="P16" s="152" t="n">
+      <c r="P16" s="151" t="n">
         <v>16</v>
       </c>
-      <c r="Q16" s="152" t="inlineStr">
+      <c r="Q16" s="151" t="inlineStr">
         <is>
           <t>Inventory (Days)</t>
         </is>
       </c>
-      <c r="R16" s="153" t="inlineStr">
+      <c r="R16" s="152" t="inlineStr">
         <is>
           <t>Inventory days (Inv = COGS × days/365).</t>
         </is>
       </c>
-      <c r="S16" s="153" t="inlineStr">
+      <c r="S16" s="152" t="inlineStr">
         <is>
           <t>Hard zero — FICO is software / scores; inventory is immaterial.</t>
         </is>
       </c>
-      <c r="T16" s="153" t="inlineStr">
+      <c r="T16" s="152" t="inlineStr">
         <is>
           <t>No inventory cycle to fund.</t>
         </is>
       </c>
-      <c r="U16" s="154" t="inlineStr">
+      <c r="U16" s="153" t="inlineStr">
         <is>
           <t>SEC 10-K FY2025 — Inventory ≈ $0</t>
         </is>
       </c>
-      <c r="V16" s="154" t="inlineStr">
+      <c r="V16" s="153" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
         </is>
@@ -7679,29 +7678,29 @@
           <t>Accounts Payable (Days)</t>
         </is>
       </c>
-      <c r="C17" s="158" t="inlineStr">
+      <c r="C17" s="157" t="inlineStr">
         <is>
           <t>WHY: Payable timing offsets AR in operating NWC. | SOURCE: SEC 10-K FY2025 — Accounts payable | LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm | HOW: Excel equation: ROUND(I48/I25×365, 0) from FY25.</t>
         </is>
       </c>
       <c r="D17" s="32" t="n"/>
-      <c r="E17" s="156">
+      <c r="E17" s="155">
         <f>E48/E25*365</f>
         <v/>
       </c>
-      <c r="F17" s="156">
+      <c r="F17" s="155">
         <f>F48/F25*365</f>
         <v/>
       </c>
-      <c r="G17" s="156">
+      <c r="G17" s="155">
         <f>G48/G25*365</f>
         <v/>
       </c>
-      <c r="H17" s="156">
+      <c r="H17" s="155">
         <f>H48/H25*365</f>
         <v/>
       </c>
-      <c r="I17" s="156">
+      <c r="I17" s="155">
         <f>I48/I25*365</f>
         <v/>
       </c>
@@ -7725,35 +7724,35 @@
         <f>IF($I$25=0,0,ROUND($I$48/$I$25*365,0))</f>
         <v/>
       </c>
-      <c r="P17" s="152" t="n">
+      <c r="P17" s="151" t="n">
         <v>17</v>
       </c>
-      <c r="Q17" s="152" t="inlineStr">
+      <c r="Q17" s="151" t="inlineStr">
         <is>
           <t>Accounts Payable (Days)</t>
         </is>
       </c>
-      <c r="R17" s="153" t="inlineStr">
+      <c r="R17" s="152" t="inlineStr">
         <is>
           <t>AP days used to project AP = COGS × days/365.</t>
         </is>
       </c>
-      <c r="S17" s="153" t="inlineStr">
+      <c r="S17" s="152" t="inlineStr">
         <is>
           <t>Excel equation: ROUND(I48/I25×365, 0) from FY25.</t>
         </is>
       </c>
-      <c r="T17" s="153" t="inlineStr">
+      <c r="T17" s="152" t="inlineStr">
         <is>
           <t>Payable timing offsets AR in operating NWC.</t>
         </is>
       </c>
-      <c r="U17" s="154" t="inlineStr">
+      <c r="U17" s="153" t="inlineStr">
         <is>
           <t>SEC 10-K FY2025 — Accounts payable</t>
         </is>
       </c>
-      <c r="V17" s="154" t="inlineStr">
+      <c r="V17" s="153" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
         </is>
@@ -7762,83 +7761,83 @@
     <row r="18" hidden="1" outlineLevel="1" ht="40" customHeight="1">
       <c r="B18" s="19" t="inlineStr">
         <is>
-          <t>CapEx % of Revenue (fade equation)</t>
-        </is>
-      </c>
-      <c r="C18" s="158" t="inlineStr">
-        <is>
-          <t>WHY: FY25 CapEx was elevated by capitalized internal-use software. Fading avoids locking a peak reinvestment rate forever. | SOURCE: SEC 10-K FY2025 — PP&amp;E purchases + capitalized software | LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm | HOW: Equation: fade from I68/I24 (FY25 CapEx/Sales ~1.98%) toward 1.0% steady. Weights 85%→65%→45%→30%→0% on the peak.</t>
-        </is>
-      </c>
-      <c r="E18" s="156">
+          <t>CapEx % of Revenue (fast fade → 1%)</t>
+        </is>
+      </c>
+      <c r="C18" s="157" t="inlineStr">
+        <is>
+          <t>WHY: MODEL7 audit: prior path left CapEx ≫ D&amp;A (~$80M cumulative drag). Faster fade to maintenance ~1% so CapEx converges … | SOURCE: SEC 10-K FY2025 — PP&amp;E purchases + capitalized software | LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm | HOW: Equation: fade from I68/I24 toward 1.0% steady. MODEL7 weights 40%→20%→10%→0%→0% on the peak (faster fade).</t>
+        </is>
+      </c>
+      <c r="E18" s="155">
         <f>E68</f>
         <v/>
       </c>
-      <c r="F18" s="156">
+      <c r="F18" s="155">
         <f>F68</f>
         <v/>
       </c>
-      <c r="G18" s="156">
+      <c r="G18" s="155">
         <f>G68</f>
         <v/>
       </c>
-      <c r="H18" s="156">
+      <c r="H18" s="155">
         <f>H68</f>
         <v/>
       </c>
-      <c r="I18" s="156">
+      <c r="I18" s="155">
         <f>I68</f>
         <v/>
       </c>
-      <c r="J18" s="157">
-        <f>($I$68/$I$24)*0.85+0.01*(1-0.85)</f>
-        <v/>
-      </c>
-      <c r="K18" s="157">
-        <f>($I$68/$I$24)*0.65+0.01*(1-0.65)</f>
-        <v/>
-      </c>
-      <c r="L18" s="157">
-        <f>($I$68/$I$24)*0.45+0.01*(1-0.45)</f>
-        <v/>
-      </c>
-      <c r="M18" s="157">
-        <f>($I$68/$I$24)*0.3+0.01*(1-0.3)</f>
-        <v/>
-      </c>
-      <c r="N18" s="157">
+      <c r="J18" s="156">
+        <f>($I$68/$I$24)*0.4+0.01*(1-0.4)</f>
+        <v/>
+      </c>
+      <c r="K18" s="156">
+        <f>($I$68/$I$24)*0.2+0.01*(1-0.2)</f>
+        <v/>
+      </c>
+      <c r="L18" s="156">
+        <f>($I$68/$I$24)*0.1+0.01*(1-0.1)</f>
+        <v/>
+      </c>
+      <c r="M18" s="156">
         <f>($I$68/$I$24)*0.0+0.01*(1-0.0)</f>
         <v/>
       </c>
-      <c r="P18" s="152" t="n">
+      <c r="N18" s="156">
+        <f>($I$68/$I$24)*0.0+0.01*(1-0.0)</f>
+        <v/>
+      </c>
+      <c r="P18" s="151" t="n">
         <v>18</v>
       </c>
-      <c r="Q18" s="152" t="inlineStr">
+      <c r="Q18" s="151" t="inlineStr">
         <is>
           <t>CapEx % of Revenue</t>
         </is>
       </c>
-      <c r="R18" s="153" t="inlineStr">
+      <c r="R18" s="152" t="inlineStr">
         <is>
           <t>Capital investment (PPE + capitalized software) as % of sales.</t>
         </is>
       </c>
-      <c r="S18" s="153" t="inlineStr">
-        <is>
-          <t>Equation: fade from I68/I24 (FY25 CapEx/Sales ~1.98%) toward 1.0% steady. Weights 85%→65%→45%→30%→0% on the peak.</t>
-        </is>
-      </c>
-      <c r="T18" s="153" t="inlineStr">
-        <is>
-          <t>FY25 CapEx was elevated by capitalized internal-use software. Fading avoids locking a peak reinvestment rate forever.</t>
-        </is>
-      </c>
-      <c r="U18" s="154" t="inlineStr">
+      <c r="S18" s="152" t="inlineStr">
+        <is>
+          <t>Equation: fade from I68/I24 toward 1.0% steady. MODEL7 weights 40%→20%→10%→0%→0% on the peak (faster fade).</t>
+        </is>
+      </c>
+      <c r="T18" s="152" t="inlineStr">
+        <is>
+          <t>MODEL7 audit: prior path left CapEx ≫ D&amp;A (~$80M cumulative drag). Faster fade to maintenance ~1% so CapEx converges near D&amp;A by Y4–Y5.</t>
+        </is>
+      </c>
+      <c r="U18" s="153" t="inlineStr">
         <is>
           <t>SEC 10-K FY2025 — PP&amp;E purchases + capitalized software</t>
         </is>
       </c>
-      <c r="V18" s="154" t="inlineStr">
+      <c r="V18" s="153" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
         </is>
@@ -7850,75 +7849,75 @@
           <t>Debt Issuance (Repayment) ($000's)</t>
         </is>
       </c>
-      <c r="C19" s="158" t="inlineStr">
+      <c r="C19" s="157" t="inlineStr">
         <is>
           <t>WHY: Hold debt stock flat at FY25 level for the explicit period; interest follows. Net debt for DCF equity bridge uses the… | SOURCE: SEC 10-Q Q3 FY2026 — debt stock (financing excluded from FCFF) | LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454726000030/fico-20260630.htm | HOW: POLICY input = 0 every year.</t>
         </is>
       </c>
-      <c r="E19" s="156">
+      <c r="E19" s="155">
         <f>E99</f>
         <v/>
       </c>
-      <c r="F19" s="156">
+      <c r="F19" s="155">
         <f>F99</f>
         <v/>
       </c>
-      <c r="G19" s="156">
+      <c r="G19" s="155">
         <f>G99</f>
         <v/>
       </c>
-      <c r="H19" s="156">
+      <c r="H19" s="155">
         <f>H99</f>
         <v/>
       </c>
-      <c r="I19" s="156">
+      <c r="I19" s="155">
         <f>I99</f>
         <v/>
       </c>
-      <c r="J19" s="161" t="n">
+      <c r="J19" s="160" t="n">
         <v>0</v>
       </c>
-      <c r="K19" s="161" t="n">
+      <c r="K19" s="160" t="n">
         <v>0</v>
       </c>
-      <c r="L19" s="161" t="n">
+      <c r="L19" s="160" t="n">
         <v>0</v>
       </c>
-      <c r="M19" s="161" t="n">
+      <c r="M19" s="160" t="n">
         <v>0</v>
       </c>
-      <c r="N19" s="161" t="n">
+      <c r="N19" s="160" t="n">
         <v>0</v>
       </c>
-      <c r="P19" s="152" t="n">
+      <c r="P19" s="151" t="n">
         <v>19</v>
       </c>
-      <c r="Q19" s="152" t="inlineStr">
+      <c r="Q19" s="151" t="inlineStr">
         <is>
           <t>Debt Issuance (Repayment)</t>
         </is>
       </c>
-      <c r="R19" s="153" t="inlineStr">
+      <c r="R19" s="152" t="inlineStr">
         <is>
           <t>New borrowing (+) or repayment (−) in the forecast.</t>
         </is>
       </c>
-      <c r="S19" s="153" t="inlineStr">
+      <c r="S19" s="152" t="inlineStr">
         <is>
           <t>POLICY input = 0 every year.</t>
         </is>
       </c>
-      <c r="T19" s="153" t="inlineStr">
+      <c r="T19" s="152" t="inlineStr">
         <is>
           <t>Hold debt stock flat at FY25 level for the explicit period; interest follows. Net debt for DCF equity bridge uses the later 10-Q amount separately.</t>
         </is>
       </c>
-      <c r="U19" s="154" t="inlineStr">
+      <c r="U19" s="153" t="inlineStr">
         <is>
           <t>SEC 10-Q Q3 FY2026 — debt stock (financing excluded from FCFF)</t>
         </is>
       </c>
-      <c r="V19" s="154" t="inlineStr">
+      <c r="V19" s="153" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/814547/000081454726000030/fico-20260630.htm</t>
         </is>
@@ -7930,75 +7929,75 @@
           <t>Equity Issued (Repaid) ($000's)</t>
         </is>
       </c>
-      <c r="C20" s="158" t="inlineStr">
+      <c r="C20" s="157" t="inlineStr">
         <is>
           <t>WHY: Buybacks are real historically but are financing — excluded from FCFF. Share count for $/share is the spot shares out… | SOURCE: Damodaran FCFF framework — financing (buybacks) not in FCFF | LINK: https://pages.stern.nyu.edu/~adamodar/New_Home_Page/datafile/histfcff.html | HOW: POLICY input = 0 every year.</t>
         </is>
       </c>
-      <c r="E20" s="156">
+      <c r="E20" s="155">
         <f>E73</f>
         <v/>
       </c>
-      <c r="F20" s="156">
+      <c r="F20" s="155">
         <f>F73</f>
         <v/>
       </c>
-      <c r="G20" s="156">
+      <c r="G20" s="155">
         <f>G73</f>
         <v/>
       </c>
-      <c r="H20" s="156">
+      <c r="H20" s="155">
         <f>H73</f>
         <v/>
       </c>
-      <c r="I20" s="156">
+      <c r="I20" s="155">
         <f>I73</f>
         <v/>
       </c>
-      <c r="J20" s="161" t="n">
+      <c r="J20" s="160" t="n">
         <v>0</v>
       </c>
-      <c r="K20" s="161" t="n">
+      <c r="K20" s="160" t="n">
         <v>0</v>
       </c>
-      <c r="L20" s="161" t="n">
+      <c r="L20" s="160" t="n">
         <v>0</v>
       </c>
-      <c r="M20" s="161" t="n">
+      <c r="M20" s="160" t="n">
         <v>0</v>
       </c>
-      <c r="N20" s="161" t="n">
+      <c r="N20" s="160" t="n">
         <v>0</v>
       </c>
-      <c r="P20" s="152" t="n">
+      <c r="P20" s="151" t="n">
         <v>20</v>
       </c>
-      <c r="Q20" s="152" t="inlineStr">
+      <c r="Q20" s="151" t="inlineStr">
         <is>
           <t>Equity Issued (Repaid)</t>
         </is>
       </c>
-      <c r="R20" s="153" t="inlineStr">
+      <c r="R20" s="152" t="inlineStr">
         <is>
           <t>New equity issued (+) or buybacks (−) in the forecast BS/CF.</t>
         </is>
       </c>
-      <c r="S20" s="153" t="inlineStr">
+      <c r="S20" s="152" t="inlineStr">
         <is>
           <t>POLICY input = 0 every year.</t>
         </is>
       </c>
-      <c r="T20" s="153" t="inlineStr">
+      <c r="T20" s="152" t="inlineStr">
         <is>
           <t>Buybacks are real historically but are financing — excluded from FCFF. Share count for $/share is the spot shares outstanding assumption.</t>
         </is>
       </c>
-      <c r="U20" s="154" t="inlineStr">
+      <c r="U20" s="153" t="inlineStr">
         <is>
           <t>Damodaran FCFF framework — financing (buybacks) not in FCFF</t>
         </is>
       </c>
-      <c r="V20" s="154" t="inlineStr">
+      <c r="V20" s="153" t="inlineStr">
         <is>
           <t>https://pages.stern.nyu.edu/~adamodar/New_Home_Page/datafile/histfcff.html</t>
         </is>
@@ -8053,25 +8052,25 @@
           <t>Reveneue</t>
         </is>
       </c>
-      <c r="C24" s="162" t="inlineStr">
+      <c r="C24" s="161" t="inlineStr">
         <is>
           <t>eqn: PriorRev × (1 + growth)</t>
         </is>
       </c>
       <c r="D24" s="46" t="n"/>
-      <c r="E24" s="163" t="n">
+      <c r="E24" s="162" t="n">
         <v>1316536</v>
       </c>
-      <c r="F24" s="163" t="n">
+      <c r="F24" s="162" t="n">
         <v>1377270</v>
       </c>
-      <c r="G24" s="163" t="n">
+      <c r="G24" s="162" t="n">
         <v>1513557</v>
       </c>
-      <c r="H24" s="163" t="n">
+      <c r="H24" s="162" t="n">
         <v>1717526</v>
       </c>
-      <c r="I24" s="163" t="n">
+      <c r="I24" s="162" t="n">
         <v>1990869</v>
       </c>
       <c r="J24" s="159">
@@ -8101,25 +8100,25 @@
           <t>Cost of Goods Sold (COGS)</t>
         </is>
       </c>
-      <c r="C25" s="162" t="inlineStr">
+      <c r="C25" s="161" t="inlineStr">
         <is>
           <t>eqn: Rev × COGS%</t>
         </is>
       </c>
       <c r="D25" s="47" t="n"/>
-      <c r="E25" s="163" t="n">
+      <c r="E25" s="162" t="n">
         <v>332462</v>
       </c>
-      <c r="F25" s="163" t="n">
+      <c r="F25" s="162" t="n">
         <v>302174</v>
       </c>
-      <c r="G25" s="163" t="n">
+      <c r="G25" s="162" t="n">
         <v>311053</v>
       </c>
-      <c r="H25" s="163" t="n">
+      <c r="H25" s="162" t="n">
         <v>348206</v>
       </c>
-      <c r="I25" s="163" t="n">
+      <c r="I25" s="162" t="n">
         <v>353722</v>
       </c>
       <c r="J25" s="159">
@@ -8149,29 +8148,29 @@
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="C26" s="164" t="inlineStr">
+      <c r="C26" s="163" t="inlineStr">
         <is>
           <t>eqn: Rev − COGS</t>
         </is>
       </c>
       <c r="D26" s="22" t="n"/>
-      <c r="E26" s="165">
+      <c r="E26" s="164">
         <f>E24-E25</f>
         <v/>
       </c>
-      <c r="F26" s="165">
+      <c r="F26" s="164">
         <f>F24-F25</f>
         <v/>
       </c>
-      <c r="G26" s="165">
+      <c r="G26" s="164">
         <f>G24-G25</f>
         <v/>
       </c>
-      <c r="H26" s="165">
+      <c r="H26" s="164">
         <f>H24-H25</f>
         <v/>
       </c>
-      <c r="I26" s="165">
+      <c r="I26" s="164">
         <f>I24-I25</f>
         <v/>
       </c>
@@ -8218,27 +8217,27 @@
     <row r="28" hidden="1" outlineLevel="1">
       <c r="B28" s="19" t="inlineStr">
         <is>
-          <t>Salaries and Benefits</t>
-        </is>
-      </c>
-      <c r="C28" s="166" t="inlineStr">
-        <is>
-          <t>eqn: Rev × SGA%</t>
-        </is>
-      </c>
-      <c r="E28" s="163" t="n">
+          <t>SG&amp;A Expense</t>
+        </is>
+      </c>
+      <c r="C28" s="165" t="inlineStr">
+        <is>
+          <t>eqn: Rev × SG&amp;A%</t>
+        </is>
+      </c>
+      <c r="E28" s="162" t="n">
         <v>396281</v>
       </c>
-      <c r="F28" s="163" t="n">
+      <c r="F28" s="162" t="n">
         <v>383863</v>
       </c>
-      <c r="G28" s="163" t="n">
+      <c r="G28" s="162" t="n">
         <v>400565</v>
       </c>
-      <c r="H28" s="163" t="n">
+      <c r="H28" s="162" t="n">
         <v>462834</v>
       </c>
-      <c r="I28" s="163" t="n">
+      <c r="I28" s="162" t="n">
         <v>513028</v>
       </c>
       <c r="J28" s="159">
@@ -8265,27 +8264,27 @@
     <row r="29" hidden="1" outlineLevel="1">
       <c r="B29" s="19" t="inlineStr">
         <is>
-          <t>Rent and Overhead</t>
-        </is>
-      </c>
-      <c r="C29" s="166" t="inlineStr">
+          <t>Research &amp; Development (R&amp;D)</t>
+        </is>
+      </c>
+      <c r="C29" s="165" t="inlineStr">
         <is>
           <t>eqn: Rev × R&amp;D%</t>
         </is>
       </c>
-      <c r="E29" s="163" t="n">
+      <c r="E29" s="162" t="n">
         <v>171231</v>
       </c>
-      <c r="F29" s="163" t="n">
+      <c r="F29" s="162" t="n">
         <v>146758</v>
       </c>
-      <c r="G29" s="163" t="n">
+      <c r="G29" s="162" t="n">
         <v>159950</v>
       </c>
-      <c r="H29" s="163" t="n">
+      <c r="H29" s="162" t="n">
         <v>171940</v>
       </c>
-      <c r="I29" s="163" t="n">
+      <c r="I29" s="162" t="n">
         <v>188347</v>
       </c>
       <c r="J29" s="159">
@@ -8315,24 +8314,24 @@
           <t>Depreciation &amp; Amortization</t>
         </is>
       </c>
-      <c r="C30" s="166" t="inlineStr">
-        <is>
-          <t>eqn: AvgPPE × DA%  — Avg=(Open+Open+CapEx)/2</t>
-        </is>
-      </c>
-      <c r="E30" s="163" t="n">
+      <c r="C30" s="165" t="inlineStr">
+        <is>
+          <t>eqn: AvgPPE × DA%</t>
+        </is>
+      </c>
+      <c r="E30" s="162" t="n">
         <v>25592</v>
       </c>
-      <c r="F30" s="163" t="n">
+      <c r="F30" s="162" t="n">
         <v>20465</v>
       </c>
-      <c r="G30" s="163" t="n">
+      <c r="G30" s="162" t="n">
         <v>14638</v>
       </c>
-      <c r="H30" s="163" t="n">
+      <c r="H30" s="162" t="n">
         <v>13827</v>
       </c>
-      <c r="I30" s="163" t="n">
+      <c r="I30" s="162" t="n">
         <v>14952</v>
       </c>
       <c r="J30" s="159">
@@ -8362,25 +8361,25 @@
           <t>Interest</t>
         </is>
       </c>
-      <c r="C31" s="167" t="inlineStr">
+      <c r="C31" s="166" t="inlineStr">
         <is>
           <t>eqn: Debt_open × Int%</t>
         </is>
       </c>
       <c r="D31" s="24" t="n"/>
-      <c r="E31" s="168" t="n">
+      <c r="E31" s="167" t="n">
         <v>40092</v>
       </c>
-      <c r="F31" s="168" t="n">
+      <c r="F31" s="167" t="n">
         <v>68967</v>
       </c>
-      <c r="G31" s="168" t="n">
+      <c r="G31" s="167" t="n">
         <v>95546</v>
       </c>
-      <c r="H31" s="168" t="n">
+      <c r="H31" s="167" t="n">
         <v>105638</v>
       </c>
-      <c r="I31" s="168" t="n">
+      <c r="I31" s="167" t="n">
         <v>133647</v>
       </c>
       <c r="J31" s="159">
@@ -8412,23 +8411,23 @@
       </c>
       <c r="C32" s="19" t="n"/>
       <c r="D32" s="47" t="n"/>
-      <c r="E32" s="169">
+      <c r="E32" s="168">
         <f>SUM(E28:E31)</f>
         <v/>
       </c>
-      <c r="F32" s="169">
+      <c r="F32" s="168">
         <f>SUM(F28:F31)</f>
         <v/>
       </c>
-      <c r="G32" s="169">
+      <c r="G32" s="168">
         <f>SUM(G28:G31)</f>
         <v/>
       </c>
-      <c r="H32" s="169">
+      <c r="H32" s="168">
         <f>SUM(H28:H31)</f>
         <v/>
       </c>
-      <c r="I32" s="169">
+      <c r="I32" s="168">
         <f>SUM(I28:I31)</f>
         <v/>
       </c>
@@ -8459,29 +8458,29 @@
           <t>Earnings Before Tax</t>
         </is>
       </c>
-      <c r="C33" s="164" t="inlineStr">
+      <c r="C33" s="163" t="inlineStr">
         <is>
           <t>eqn: GP − Expenses</t>
         </is>
       </c>
       <c r="D33" s="22" t="n"/>
-      <c r="E33" s="165">
+      <c r="E33" s="164">
         <f>E26-E32</f>
         <v/>
       </c>
-      <c r="F33" s="165">
+      <c r="F33" s="164">
         <f>F26-F32</f>
         <v/>
       </c>
-      <c r="G33" s="165">
+      <c r="G33" s="164">
         <f>G26-G32</f>
         <v/>
       </c>
-      <c r="H33" s="165">
+      <c r="H33" s="164">
         <f>H26-H32</f>
         <v/>
       </c>
-      <c r="I33" s="165">
+      <c r="I33" s="164">
         <f>I26-I32</f>
         <v/>
       </c>
@@ -8527,25 +8526,25 @@
           <t>Taxes</t>
         </is>
       </c>
-      <c r="C35" s="162" t="inlineStr">
+      <c r="C35" s="161" t="inlineStr">
         <is>
           <t>eqn: EBT × tax%</t>
         </is>
       </c>
       <c r="D35" s="47" t="n"/>
-      <c r="E35" s="163" t="n">
+      <c r="E35" s="162" t="n">
         <v>81058</v>
       </c>
-      <c r="F35" s="163" t="n">
+      <c r="F35" s="162" t="n">
         <v>97768</v>
       </c>
-      <c r="G35" s="163" t="n">
+      <c r="G35" s="162" t="n">
         <v>124249</v>
       </c>
-      <c r="H35" s="163" t="n">
+      <c r="H35" s="162" t="n">
         <v>129214</v>
       </c>
-      <c r="I35" s="163" t="n">
+      <c r="I35" s="162" t="n">
         <v>150649</v>
       </c>
       <c r="J35" s="159">
@@ -8575,29 +8574,29 @@
           <t>Net Earnings</t>
         </is>
       </c>
-      <c r="C36" s="170" t="inlineStr">
+      <c r="C36" s="169" t="inlineStr">
         <is>
           <t>eqn: EBT × (1 − tax%)</t>
         </is>
       </c>
       <c r="D36" s="40" t="n"/>
-      <c r="E36" s="171">
+      <c r="E36" s="170">
         <f>E33-E35</f>
         <v/>
       </c>
-      <c r="F36" s="171">
+      <c r="F36" s="170">
         <f>F33-F35</f>
         <v/>
       </c>
-      <c r="G36" s="171">
+      <c r="G36" s="170">
         <f>G33-G35</f>
         <v/>
       </c>
-      <c r="H36" s="171">
+      <c r="H36" s="170">
         <f>H33-H35</f>
         <v/>
       </c>
-      <c r="I36" s="171">
+      <c r="I36" s="170">
         <f>I33-I35</f>
         <v/>
       </c>
@@ -8678,19 +8677,19 @@
           <t>Cash</t>
         </is>
       </c>
-      <c r="E41" s="163" t="n">
+      <c r="E41" s="162" t="n">
         <v>195354</v>
       </c>
-      <c r="F41" s="163" t="n">
+      <c r="F41" s="162" t="n">
         <v>133202</v>
       </c>
-      <c r="G41" s="163" t="n">
+      <c r="G41" s="162" t="n">
         <v>136778</v>
       </c>
-      <c r="H41" s="163" t="n">
+      <c r="H41" s="162" t="n">
         <v>150667</v>
       </c>
-      <c r="I41" s="163" t="n">
+      <c r="I41" s="162" t="n">
         <v>134136</v>
       </c>
       <c r="J41" s="159">
@@ -8720,44 +8719,44 @@
           <t>Accounts Receivable</t>
         </is>
       </c>
-      <c r="C42" s="166" t="inlineStr">
-        <is>
-          <t>eqn: Rev × GROSS AR_days / 365</t>
-        </is>
-      </c>
-      <c r="E42" s="163" t="n">
+      <c r="C42" s="165" t="inlineStr">
+        <is>
+          <t>eqn: NWC + AP + Deferred − Inv  (plug to NWC%)</t>
+        </is>
+      </c>
+      <c r="E42" s="162" t="n">
         <v>312107</v>
       </c>
-      <c r="F42" s="163" t="n">
+      <c r="F42" s="162" t="n">
         <v>322410</v>
       </c>
-      <c r="G42" s="163" t="n">
+      <c r="G42" s="162" t="n">
         <v>387947</v>
       </c>
-      <c r="H42" s="163" t="n">
+      <c r="H42" s="162" t="n">
         <v>426642</v>
       </c>
-      <c r="I42" s="163" t="n">
+      <c r="I42" s="162" t="n">
         <v>529148</v>
       </c>
       <c r="J42" s="159">
-        <f>J24*J15/365</f>
+        <f>J89+J48+J88-J43</f>
         <v/>
       </c>
       <c r="K42" s="159">
-        <f>K24*K15/365</f>
+        <f>K89+K48+K88-K43</f>
         <v/>
       </c>
       <c r="L42" s="159">
-        <f>L24*L15/365</f>
+        <f>L89+L48+L88-L43</f>
         <v/>
       </c>
       <c r="M42" s="159">
-        <f>M24*M15/365</f>
+        <f>M89+M48+M88-M43</f>
         <v/>
       </c>
       <c r="N42" s="159">
-        <f>N24*N15/365</f>
+        <f>N89+N48+N88-N43</f>
         <v/>
       </c>
     </row>
@@ -8767,19 +8766,19 @@
           <t>Inventory</t>
         </is>
       </c>
-      <c r="E43" s="163" t="n">
+      <c r="E43" s="162" t="n">
         <v>0</v>
       </c>
-      <c r="F43" s="163" t="n">
+      <c r="F43" s="162" t="n">
         <v>0</v>
       </c>
-      <c r="G43" s="163" t="n">
+      <c r="G43" s="162" t="n">
         <v>0</v>
       </c>
-      <c r="H43" s="163" t="n">
+      <c r="H43" s="162" t="n">
         <v>0</v>
       </c>
-      <c r="I43" s="163" t="n">
+      <c r="I43" s="162" t="n">
         <v>0</v>
       </c>
       <c r="J43" s="159">
@@ -8809,19 +8808,19 @@
           <t>Property &amp; Equipment</t>
         </is>
       </c>
-      <c r="E44" s="163" t="n">
+      <c r="E44" s="162" t="n">
         <v>27913</v>
       </c>
-      <c r="F44" s="163" t="n">
+      <c r="F44" s="162" t="n">
         <v>17580</v>
       </c>
-      <c r="G44" s="163" t="n">
+      <c r="G44" s="162" t="n">
         <v>10966</v>
       </c>
-      <c r="H44" s="163" t="n">
+      <c r="H44" s="162" t="n">
         <v>38465</v>
       </c>
-      <c r="I44" s="163" t="n">
+      <c r="I44" s="162" t="n">
         <v>67713</v>
       </c>
       <c r="J44" s="159">
@@ -8853,23 +8852,23 @@
       </c>
       <c r="C45" s="39" t="n"/>
       <c r="D45" s="40" t="n"/>
-      <c r="E45" s="171">
+      <c r="E45" s="170">
         <f>SUM(E41:E44)</f>
         <v/>
       </c>
-      <c r="F45" s="171">
+      <c r="F45" s="170">
         <f>SUM(F41:F44)</f>
         <v/>
       </c>
-      <c r="G45" s="171">
+      <c r="G45" s="170">
         <f>SUM(G41:G44)</f>
         <v/>
       </c>
-      <c r="H45" s="171">
+      <c r="H45" s="170">
         <f>SUM(H41:H44)</f>
         <v/>
       </c>
-      <c r="I45" s="171">
+      <c r="I45" s="170">
         <f>SUM(I41:I44)</f>
         <v/>
       </c>
@@ -8927,24 +8926,24 @@
           <t>Accounts Payable</t>
         </is>
       </c>
-      <c r="C48" s="166" t="inlineStr">
+      <c r="C48" s="165" t="inlineStr">
         <is>
           <t>eqn: COGS × AP_days / 365</t>
         </is>
       </c>
-      <c r="E48" s="163" t="n">
+      <c r="E48" s="162" t="n">
         <v>20749</v>
       </c>
-      <c r="F48" s="163" t="n">
+      <c r="F48" s="162" t="n">
         <v>17273</v>
       </c>
-      <c r="G48" s="163" t="n">
+      <c r="G48" s="162" t="n">
         <v>19009</v>
       </c>
-      <c r="H48" s="163" t="n">
+      <c r="H48" s="162" t="n">
         <v>22473</v>
       </c>
-      <c r="I48" s="163" t="n">
+      <c r="I48" s="162" t="n">
         <v>32315</v>
       </c>
       <c r="J48" s="159">
@@ -8974,19 +8973,19 @@
           <t>Debt</t>
         </is>
       </c>
-      <c r="E49" s="163" t="n">
+      <c r="E49" s="162" t="n">
         <v>1259018</v>
       </c>
-      <c r="F49" s="163" t="n">
+      <c r="F49" s="162" t="n">
         <v>1853669</v>
       </c>
-      <c r="G49" s="163" t="n">
+      <c r="G49" s="162" t="n">
         <v>1861658</v>
       </c>
-      <c r="H49" s="163" t="n">
+      <c r="H49" s="162" t="n">
         <v>2209021</v>
       </c>
-      <c r="I49" s="163" t="n">
+      <c r="I49" s="162" t="n">
         <v>3055691</v>
       </c>
       <c r="J49" s="159">
@@ -9016,29 +9015,29 @@
           <t>Total Liabilities</t>
         </is>
       </c>
-      <c r="C50" s="164" t="inlineStr">
+      <c r="C50" s="163" t="inlineStr">
         <is>
           <t>eqn: AP + Debt + DeferredRev</t>
         </is>
       </c>
       <c r="D50" s="22" t="n"/>
-      <c r="E50" s="172">
+      <c r="E50" s="171">
         <f>E48+E49+E88</f>
         <v/>
       </c>
-      <c r="F50" s="172">
+      <c r="F50" s="171">
         <f>F48+F49+F88</f>
         <v/>
       </c>
-      <c r="G50" s="172">
+      <c r="G50" s="171">
         <f>G48+G49+G88</f>
         <v/>
       </c>
-      <c r="H50" s="172">
+      <c r="H50" s="171">
         <f>H48+H49+H88</f>
         <v/>
       </c>
-      <c r="I50" s="172">
+      <c r="I50" s="171">
         <f>I48+I49+I88</f>
         <v/>
       </c>
@@ -9081,19 +9080,19 @@
           <t>Equity Capital</t>
         </is>
       </c>
-      <c r="E52" s="163" t="n">
+      <c r="E52" s="162" t="n">
         <v>-849810</v>
       </c>
-      <c r="F52" s="163" t="n">
+      <c r="F52" s="162" t="n">
         <v>-1517795</v>
       </c>
-      <c r="G52" s="163" t="n">
+      <c r="G52" s="162" t="n">
         <v>-1481706</v>
       </c>
-      <c r="H52" s="163" t="n">
+      <c r="H52" s="162" t="n">
         <v>-1772617</v>
       </c>
-      <c r="I52" s="163" t="n">
+      <c r="I52" s="162" t="n">
         <v>-2544381</v>
       </c>
       <c r="J52" s="159">
@@ -9123,24 +9122,24 @@
           <t>Retained Earnings</t>
         </is>
       </c>
-      <c r="C53" s="166" t="inlineStr">
+      <c r="C53" s="165" t="inlineStr">
         <is>
           <t>eqn: PriorRE + EBT×(1−t)</t>
         </is>
       </c>
-      <c r="E53" s="163" t="n">
+      <c r="E53" s="162" t="n">
         <v>0</v>
       </c>
-      <c r="F53" s="163" t="n">
+      <c r="F53" s="162" t="n">
         <v>0</v>
       </c>
-      <c r="G53" s="163" t="n">
+      <c r="G53" s="162" t="n">
         <v>0</v>
       </c>
-      <c r="H53" s="163" t="n">
+      <c r="H53" s="162" t="n">
         <v>0</v>
       </c>
-      <c r="I53" s="163" t="n">
+      <c r="I53" s="162" t="n">
         <v>0</v>
       </c>
       <c r="J53" s="159">
@@ -9172,23 +9171,23 @@
       </c>
       <c r="C54" s="8" t="n"/>
       <c r="D54" s="26" t="n"/>
-      <c r="E54" s="173">
+      <c r="E54" s="172">
         <f>SUM(E52:E53)</f>
         <v/>
       </c>
-      <c r="F54" s="173">
+      <c r="F54" s="172">
         <f>SUM(F52:F53)</f>
         <v/>
       </c>
-      <c r="G54" s="173">
+      <c r="G54" s="172">
         <f>SUM(G52:G53)</f>
         <v/>
       </c>
-      <c r="H54" s="173">
+      <c r="H54" s="172">
         <f>SUM(H52:H53)</f>
         <v/>
       </c>
-      <c r="I54" s="173">
+      <c r="I54" s="172">
         <f>SUM(I52:I53)</f>
         <v/>
       </c>
@@ -9221,23 +9220,23 @@
       </c>
       <c r="C55" s="39" t="n"/>
       <c r="D55" s="40" t="n"/>
-      <c r="E55" s="171">
+      <c r="E55" s="170">
         <f>E50+E54</f>
         <v/>
       </c>
-      <c r="F55" s="171">
+      <c r="F55" s="170">
         <f>F50+F54</f>
         <v/>
       </c>
-      <c r="G55" s="171">
+      <c r="G55" s="170">
         <f>G50+G54</f>
         <v/>
       </c>
-      <c r="H55" s="171">
+      <c r="H55" s="170">
         <f>H50+H54</f>
         <v/>
       </c>
-      <c r="I55" s="171">
+      <c r="I55" s="170">
         <f>I50+I54</f>
         <v/>
       </c>
@@ -9282,23 +9281,23 @@
       </c>
       <c r="C57" s="9" t="n"/>
       <c r="D57" s="27" t="n"/>
-      <c r="E57" s="174">
+      <c r="E57" s="173">
         <f>E55-E45</f>
         <v/>
       </c>
-      <c r="F57" s="174">
+      <c r="F57" s="173">
         <f>F55-F45</f>
         <v/>
       </c>
-      <c r="G57" s="174">
+      <c r="G57" s="173">
         <f>G55-G45</f>
         <v/>
       </c>
-      <c r="H57" s="174">
+      <c r="H57" s="173">
         <f>H55-H45</f>
         <v/>
       </c>
-      <c r="I57" s="174">
+      <c r="I57" s="173">
         <f>I55-I45</f>
         <v/>
       </c>
@@ -9382,28 +9381,28 @@
           <t>Net Earnings</t>
         </is>
       </c>
-      <c r="C62" s="166" t="inlineStr">
+      <c r="C62" s="165" t="inlineStr">
         <is>
           <t>eqn: EBT × (1 − tax%)</t>
         </is>
       </c>
-      <c r="E62" s="175">
+      <c r="E62" s="174">
         <f>E36</f>
         <v/>
       </c>
-      <c r="F62" s="175">
+      <c r="F62" s="174">
         <f>F36</f>
         <v/>
       </c>
-      <c r="G62" s="175">
+      <c r="G62" s="174">
         <f>G36</f>
         <v/>
       </c>
-      <c r="H62" s="175">
+      <c r="H62" s="174">
         <f>H36</f>
         <v/>
       </c>
-      <c r="I62" s="175">
+      <c r="I62" s="174">
         <f>I36</f>
         <v/>
       </c>
@@ -9434,28 +9433,28 @@
           <t>Plus: Depreciation &amp; Amortization</t>
         </is>
       </c>
-      <c r="C63" s="166" t="inlineStr">
+      <c r="C63" s="165" t="inlineStr">
         <is>
           <t>eqn: AvgPPE × DA%</t>
         </is>
       </c>
-      <c r="E63" s="175">
+      <c r="E63" s="174">
         <f>+E30</f>
         <v/>
       </c>
-      <c r="F63" s="175">
+      <c r="F63" s="174">
         <f>+F30</f>
         <v/>
       </c>
-      <c r="G63" s="175">
+      <c r="G63" s="174">
         <f>+G30</f>
         <v/>
       </c>
-      <c r="H63" s="175">
+      <c r="H63" s="174">
         <f>+H30</f>
         <v/>
       </c>
-      <c r="I63" s="175">
+      <c r="I63" s="174">
         <f>+I30</f>
         <v/>
       </c>
@@ -9486,24 +9485,24 @@
           <t>Less: Changes in Working Capital</t>
         </is>
       </c>
-      <c r="C64" s="166" t="inlineStr">
-        <is>
-          <t>eqn: NWC_t − NWC_t−1  (NWC=AR+Inv−AP−Deferred)</t>
-        </is>
-      </c>
-      <c r="E64" s="163" t="n">
+      <c r="C64" s="165" t="inlineStr">
+        <is>
+          <t>eqn: ΔNWC from consolidated NWC% of sales</t>
+        </is>
+      </c>
+      <c r="E64" s="162" t="n">
         <v>0</v>
       </c>
-      <c r="F64" s="163" t="n">
+      <c r="F64" s="162" t="n">
         <v>-849</v>
       </c>
-      <c r="G64" s="163" t="n">
+      <c r="G64" s="162" t="n">
         <v>47116</v>
       </c>
-      <c r="H64" s="163" t="n">
+      <c r="H64" s="162" t="n">
         <v>15064</v>
       </c>
-      <c r="I64" s="163" t="n">
+      <c r="I64" s="162" t="n">
         <v>62189</v>
       </c>
       <c r="J64" s="159">
@@ -9533,29 +9532,29 @@
           <t>Cash from Operations</t>
         </is>
       </c>
-      <c r="C65" s="164" t="inlineStr">
+      <c r="C65" s="163" t="inlineStr">
         <is>
           <t>eqn: NI + DA − ΔNWC</t>
         </is>
       </c>
       <c r="D65" s="28" t="n"/>
-      <c r="E65" s="165">
+      <c r="E65" s="164">
         <f>E62+E63-E64</f>
         <v/>
       </c>
-      <c r="F65" s="165">
+      <c r="F65" s="164">
         <f>F62+F63-F64</f>
         <v/>
       </c>
-      <c r="G65" s="165">
+      <c r="G65" s="164">
         <f>G62+G63-G64</f>
         <v/>
       </c>
-      <c r="H65" s="165">
+      <c r="H65" s="164">
         <f>H62+H63-H64</f>
         <v/>
       </c>
-      <c r="I65" s="165">
+      <c r="I65" s="164">
         <f>I62+I63-I64</f>
         <v/>
       </c>
@@ -9618,24 +9617,24 @@
           <t>Investments in Property &amp; Equipment</t>
         </is>
       </c>
-      <c r="C68" s="166" t="inlineStr">
+      <c r="C68" s="165" t="inlineStr">
         <is>
           <t>eqn: Rev × CapEx%</t>
         </is>
       </c>
-      <c r="E68" s="163" t="n">
+      <c r="E68" s="162" t="n">
         <v>7569</v>
       </c>
-      <c r="F68" s="163" t="n">
+      <c r="F68" s="162" t="n">
         <v>6029</v>
       </c>
-      <c r="G68" s="163" t="n">
+      <c r="G68" s="162" t="n">
         <v>4237</v>
       </c>
-      <c r="H68" s="163" t="n">
+      <c r="H68" s="162" t="n">
         <v>25551</v>
       </c>
-      <c r="I68" s="163" t="n">
+      <c r="I68" s="162" t="n">
         <v>39407</v>
       </c>
       <c r="J68" s="159">
@@ -9667,23 +9666,23 @@
       </c>
       <c r="C69" s="5" t="n"/>
       <c r="D69" s="28" t="n"/>
-      <c r="E69" s="165">
+      <c r="E69" s="164">
         <f>SUM(E68)</f>
         <v/>
       </c>
-      <c r="F69" s="165">
+      <c r="F69" s="164">
         <f>SUM(F68)</f>
         <v/>
       </c>
-      <c r="G69" s="165">
+      <c r="G69" s="164">
         <f>SUM(G68)</f>
         <v/>
       </c>
-      <c r="H69" s="165">
+      <c r="H69" s="164">
         <f>SUM(H68)</f>
         <v/>
       </c>
-      <c r="I69" s="165">
+      <c r="I69" s="164">
         <f>SUM(I68)</f>
         <v/>
       </c>
@@ -9746,19 +9745,19 @@
           <t>Issuance (repayment) of debt</t>
         </is>
       </c>
-      <c r="E72" s="163" t="n">
+      <c r="E72" s="162" t="n">
         <v>519583</v>
       </c>
-      <c r="F72" s="163" t="n">
+      <c r="F72" s="162" t="n">
         <v>594651</v>
       </c>
-      <c r="G72" s="163" t="n">
+      <c r="G72" s="162" t="n">
         <v>7989</v>
       </c>
-      <c r="H72" s="163" t="n">
+      <c r="H72" s="162" t="n">
         <v>347363</v>
       </c>
-      <c r="I72" s="163" t="n">
+      <c r="I72" s="162" t="n">
         <v>846670</v>
       </c>
       <c r="J72" s="159">
@@ -9788,19 +9787,19 @@
           <t>Issuance (repayment) of equity</t>
         </is>
       </c>
-      <c r="E73" s="163" t="n">
+      <c r="E73" s="162" t="n">
         <v>0</v>
       </c>
-      <c r="F73" s="163" t="n">
+      <c r="F73" s="162" t="n">
         <v>0</v>
       </c>
-      <c r="G73" s="163" t="n">
+      <c r="G73" s="162" t="n">
         <v>0</v>
       </c>
-      <c r="H73" s="163" t="n">
+      <c r="H73" s="162" t="n">
         <v>0</v>
       </c>
-      <c r="I73" s="163" t="n">
+      <c r="I73" s="162" t="n">
         <v>0</v>
       </c>
       <c r="J73" s="159">
@@ -9832,23 +9831,23 @@
       </c>
       <c r="C74" s="5" t="n"/>
       <c r="D74" s="28" t="n"/>
-      <c r="E74" s="165">
+      <c r="E74" s="164">
         <f>SUM(E72:E73)</f>
         <v/>
       </c>
-      <c r="F74" s="165">
+      <c r="F74" s="164">
         <f>SUM(F72:F73)</f>
         <v/>
       </c>
-      <c r="G74" s="165">
+      <c r="G74" s="164">
         <f>SUM(G72:G73)</f>
         <v/>
       </c>
-      <c r="H74" s="165">
+      <c r="H74" s="164">
         <f>SUM(H72:H73)</f>
         <v/>
       </c>
-      <c r="I74" s="165">
+      <c r="I74" s="164">
         <f>SUM(I72:I73)</f>
         <v/>
       </c>
@@ -9894,28 +9893,28 @@
           <t>Net Increase (decrease) in Cash</t>
         </is>
       </c>
-      <c r="C76" s="166" t="inlineStr">
+      <c r="C76" s="165" t="inlineStr">
         <is>
           <t>eqn: CFO − CapEx + Financing</t>
         </is>
       </c>
-      <c r="E76" s="176">
+      <c r="E76" s="175">
         <f>E41-E77</f>
         <v/>
       </c>
-      <c r="F76" s="176">
+      <c r="F76" s="175">
         <f>F41-F77</f>
         <v/>
       </c>
-      <c r="G76" s="176">
+      <c r="G76" s="175">
         <f>G41-G77</f>
         <v/>
       </c>
-      <c r="H76" s="176">
+      <c r="H76" s="175">
         <f>H41-H77</f>
         <v/>
       </c>
-      <c r="I76" s="176">
+      <c r="I76" s="175">
         <f>I41-I77</f>
         <v/>
       </c>
@@ -9946,22 +9945,22 @@
           <t>Opening Cash Balance</t>
         </is>
       </c>
-      <c r="E77" s="163" t="n">
+      <c r="E77" s="162" t="n">
         <v>157394</v>
       </c>
-      <c r="F77" s="176">
+      <c r="F77" s="175">
         <f>E41</f>
         <v/>
       </c>
-      <c r="G77" s="176">
+      <c r="G77" s="175">
         <f>F41</f>
         <v/>
       </c>
-      <c r="H77" s="176">
+      <c r="H77" s="175">
         <f>G41</f>
         <v/>
       </c>
-      <c r="I77" s="176">
+      <c r="I77" s="175">
         <f>H41</f>
         <v/>
       </c>
@@ -9993,26 +9992,26 @@
         </is>
       </c>
       <c r="C78" s="5" t="n"/>
-      <c r="D78" s="177" t="n">
+      <c r="D78" s="176" t="n">
         <v>157394</v>
       </c>
-      <c r="E78" s="165">
+      <c r="E78" s="164">
         <f>SUM(E76:E77)</f>
         <v/>
       </c>
-      <c r="F78" s="165">
+      <c r="F78" s="164">
         <f>SUM(F76:F77)</f>
         <v/>
       </c>
-      <c r="G78" s="165">
+      <c r="G78" s="164">
         <f>SUM(G76:G77)</f>
         <v/>
       </c>
-      <c r="H78" s="165">
+      <c r="H78" s="164">
         <f>SUM(H76:H77)</f>
         <v/>
       </c>
-      <c r="I78" s="165">
+      <c r="I78" s="164">
         <f>SUM(I76:I77)</f>
         <v/>
       </c>
@@ -10053,23 +10052,23 @@
       </c>
       <c r="C80" s="9" t="n"/>
       <c r="D80" s="27" t="n"/>
-      <c r="E80" s="174">
+      <c r="E80" s="173">
         <f>E78-E41</f>
         <v/>
       </c>
-      <c r="F80" s="174">
+      <c r="F80" s="173">
         <f>F78-F41</f>
         <v/>
       </c>
-      <c r="G80" s="174">
+      <c r="G80" s="173">
         <f>G78-G41</f>
         <v/>
       </c>
-      <c r="H80" s="174">
+      <c r="H80" s="173">
         <f>H78-H41</f>
         <v/>
       </c>
-      <c r="I80" s="174">
+      <c r="I80" s="173">
         <f>I78-I41</f>
         <v/>
       </c>
@@ -10142,22 +10141,22 @@
     <row r="85" hidden="1" outlineLevel="1">
       <c r="B85" s="19" t="inlineStr">
         <is>
-          <t>Accounts Receivable (Gross)</t>
-        </is>
-      </c>
-      <c r="E85" s="163" t="n">
+          <t>Accounts Receivable (plugged to NWC%)</t>
+        </is>
+      </c>
+      <c r="E85" s="162" t="n">
         <v>312107</v>
       </c>
-      <c r="F85" s="163" t="n">
+      <c r="F85" s="162" t="n">
         <v>322410</v>
       </c>
-      <c r="G85" s="163" t="n">
+      <c r="G85" s="162" t="n">
         <v>387947</v>
       </c>
-      <c r="H85" s="163" t="n">
+      <c r="H85" s="162" t="n">
         <v>426642</v>
       </c>
-      <c r="I85" s="163" t="n">
+      <c r="I85" s="162" t="n">
         <v>529148</v>
       </c>
       <c r="J85" s="159">
@@ -10187,19 +10186,19 @@
           <t>Inventory</t>
         </is>
       </c>
-      <c r="E86" s="163" t="n">
+      <c r="E86" s="162" t="n">
         <v>0</v>
       </c>
-      <c r="F86" s="163" t="n">
+      <c r="F86" s="162" t="n">
         <v>0</v>
       </c>
-      <c r="G86" s="163" t="n">
+      <c r="G86" s="162" t="n">
         <v>0</v>
       </c>
-      <c r="H86" s="163" t="n">
+      <c r="H86" s="162" t="n">
         <v>0</v>
       </c>
-      <c r="I86" s="163" t="n">
+      <c r="I86" s="162" t="n">
         <v>0</v>
       </c>
       <c r="J86" s="159">
@@ -10229,19 +10228,19 @@
           <t>Accounts Payable</t>
         </is>
       </c>
-      <c r="E87" s="163" t="n">
+      <c r="E87" s="162" t="n">
         <v>20749</v>
       </c>
-      <c r="F87" s="163" t="n">
+      <c r="F87" s="162" t="n">
         <v>17273</v>
       </c>
-      <c r="G87" s="163" t="n">
+      <c r="G87" s="162" t="n">
         <v>19009</v>
       </c>
-      <c r="H87" s="163" t="n">
+      <c r="H87" s="162" t="n">
         <v>22473</v>
       </c>
-      <c r="I87" s="163" t="n">
+      <c r="I87" s="162" t="n">
         <v>32315</v>
       </c>
       <c r="J87" s="159">
@@ -10271,25 +10270,25 @@
           <t>Deferred Revenue (contract liability)</t>
         </is>
       </c>
-      <c r="C88" s="164" t="inlineStr">
-        <is>
-          <t>eqn: Rev × (FY25 Deferred/FY25 Rev) — separate from AR</t>
+      <c r="C88" s="163" t="inlineStr">
+        <is>
+          <t>eqn: Rev × (FY25 Deferred/FY25 Rev)</t>
         </is>
       </c>
       <c r="D88" s="28" t="n"/>
-      <c r="E88" s="178" t="n">
+      <c r="E88" s="177" t="n">
         <v>105417</v>
       </c>
-      <c r="F88" s="178" t="n">
+      <c r="F88" s="177" t="n">
         <v>120045</v>
       </c>
-      <c r="G88" s="178" t="n">
+      <c r="G88" s="177" t="n">
         <v>136730</v>
       </c>
-      <c r="H88" s="178" t="n">
+      <c r="H88" s="177" t="n">
         <v>156897</v>
       </c>
-      <c r="I88" s="178" t="n">
+      <c r="I88" s="177" t="n">
         <v>187372</v>
       </c>
       <c r="J88" s="159">
@@ -10319,47 +10318,47 @@
           <t>Net Working Capital (NWC)</t>
         </is>
       </c>
-      <c r="C89" s="166" t="inlineStr">
-        <is>
-          <t>eqn: GrossAR + Inv − AP − Deferred</t>
-        </is>
-      </c>
-      <c r="D89" s="179" t="n">
+      <c r="C89" s="165" t="inlineStr">
+        <is>
+          <t>eqn: Rev × NWC%   (consolidated operating WC)</t>
+        </is>
+      </c>
+      <c r="D89" s="178" t="n">
         <v>205747</v>
       </c>
-      <c r="E89" s="163" t="n">
+      <c r="E89" s="162" t="n">
         <v>185941</v>
       </c>
-      <c r="F89" s="163" t="n">
+      <c r="F89" s="162" t="n">
         <v>185092</v>
       </c>
-      <c r="G89" s="163" t="n">
+      <c r="G89" s="162" t="n">
         <v>232208</v>
       </c>
-      <c r="H89" s="163" t="n">
+      <c r="H89" s="162" t="n">
         <v>247272</v>
       </c>
-      <c r="I89" s="163" t="n">
+      <c r="I89" s="162" t="n">
         <v>309461</v>
       </c>
       <c r="J89" s="159">
-        <f>J85+J86-J87-J88</f>
+        <f>J24*J15</f>
         <v/>
       </c>
       <c r="K89" s="159">
-        <f>K85+K86-K87-K88</f>
+        <f>K24*K15</f>
         <v/>
       </c>
       <c r="L89" s="159">
-        <f>L85+L86-L87-L88</f>
+        <f>L24*L15</f>
         <v/>
       </c>
       <c r="M89" s="159">
-        <f>M85+M86-M87-M88</f>
+        <f>M24*M15</f>
         <v/>
       </c>
       <c r="N89" s="159">
-        <f>N85+N86-N87-N88</f>
+        <f>N24*N15</f>
         <v/>
       </c>
     </row>
@@ -10369,38 +10368,38 @@
           <t>Change in NWC</t>
         </is>
       </c>
-      <c r="E90" s="163" t="n">
+      <c r="E90" s="162" t="n">
         <v>-19806</v>
       </c>
-      <c r="F90" s="163" t="n">
+      <c r="F90" s="162" t="n">
         <v>-849</v>
       </c>
-      <c r="G90" s="163" t="n">
+      <c r="G90" s="162" t="n">
         <v>47116</v>
       </c>
-      <c r="H90" s="163" t="n">
+      <c r="H90" s="162" t="n">
         <v>15064</v>
       </c>
-      <c r="I90" s="163" t="n">
+      <c r="I90" s="162" t="n">
         <v>62189</v>
       </c>
-      <c r="J90" s="180">
+      <c r="J90" s="179">
         <f>J89-I89</f>
         <v/>
       </c>
-      <c r="K90" s="180">
+      <c r="K90" s="179">
         <f>K89-J89</f>
         <v/>
       </c>
-      <c r="L90" s="180">
+      <c r="L90" s="179">
         <f>L89-K89</f>
         <v/>
       </c>
-      <c r="M90" s="180">
+      <c r="M90" s="179">
         <f>M89-L89</f>
         <v/>
       </c>
-      <c r="N90" s="180">
+      <c r="N90" s="179">
         <f>N89-M89</f>
         <v/>
       </c>
@@ -10423,22 +10422,22 @@
           <t>PPE Opening</t>
         </is>
       </c>
-      <c r="E92" s="163" t="n">
+      <c r="E92" s="162" t="n">
         <v>46419</v>
       </c>
-      <c r="F92" s="176">
+      <c r="F92" s="175">
         <f>E95</f>
         <v/>
       </c>
-      <c r="G92" s="176">
+      <c r="G92" s="175">
         <f>F95</f>
         <v/>
       </c>
-      <c r="H92" s="176">
+      <c r="H92" s="175">
         <f>G95</f>
         <v/>
       </c>
-      <c r="I92" s="176">
+      <c r="I92" s="175">
         <f>H95</f>
         <v/>
       </c>
@@ -10469,19 +10468,19 @@
           <t>Plus Capex</t>
         </is>
       </c>
-      <c r="E93" s="163" t="n">
+      <c r="E93" s="162" t="n">
         <v>7569</v>
       </c>
-      <c r="F93" s="163" t="n">
+      <c r="F93" s="162" t="n">
         <v>6029</v>
       </c>
-      <c r="G93" s="163" t="n">
+      <c r="G93" s="162" t="n">
         <v>4237</v>
       </c>
-      <c r="H93" s="163" t="n">
+      <c r="H93" s="162" t="n">
         <v>25551</v>
       </c>
-      <c r="I93" s="163" t="n">
+      <c r="I93" s="162" t="n">
         <v>39407</v>
       </c>
       <c r="J93" s="159">
@@ -10511,24 +10510,24 @@
           <t>Less Depreciation</t>
         </is>
       </c>
-      <c r="C94" s="166" t="inlineStr">
+      <c r="C94" s="165" t="inlineStr">
         <is>
           <t>eqn: ((Open+Open+CapEx)/2) × DA%</t>
         </is>
       </c>
-      <c r="E94" s="163" t="n">
+      <c r="E94" s="162" t="n">
         <v>25592</v>
       </c>
-      <c r="F94" s="163" t="n">
+      <c r="F94" s="162" t="n">
         <v>20465</v>
       </c>
-      <c r="G94" s="163" t="n">
+      <c r="G94" s="162" t="n">
         <v>14638</v>
       </c>
-      <c r="H94" s="163" t="n">
+      <c r="H94" s="162" t="n">
         <v>13827</v>
       </c>
-      <c r="I94" s="163" t="n">
+      <c r="I94" s="162" t="n">
         <v>14952</v>
       </c>
       <c r="J94" s="159">
@@ -10560,19 +10559,19 @@
       </c>
       <c r="C95" s="5" t="n"/>
       <c r="D95" s="28" t="n"/>
-      <c r="E95" s="178" t="n">
+      <c r="E95" s="177" t="n">
         <v>27913</v>
       </c>
-      <c r="F95" s="178" t="n">
+      <c r="F95" s="177" t="n">
         <v>17580</v>
       </c>
-      <c r="G95" s="178" t="n">
+      <c r="G95" s="177" t="n">
         <v>10966</v>
       </c>
-      <c r="H95" s="178" t="n">
+      <c r="H95" s="177" t="n">
         <v>38465</v>
       </c>
-      <c r="I95" s="178" t="n">
+      <c r="I95" s="177" t="n">
         <v>67713</v>
       </c>
       <c r="J95" s="159">
@@ -10626,22 +10625,22 @@
           <t>Debt Opening</t>
         </is>
       </c>
-      <c r="E98" s="163" t="n">
+      <c r="E98" s="162" t="n">
         <v>739435</v>
       </c>
-      <c r="F98" s="176">
+      <c r="F98" s="175">
         <f>E100</f>
         <v/>
       </c>
-      <c r="G98" s="176">
+      <c r="G98" s="175">
         <f>F100</f>
         <v/>
       </c>
-      <c r="H98" s="176">
+      <c r="H98" s="175">
         <f>G100</f>
         <v/>
       </c>
-      <c r="I98" s="176">
+      <c r="I98" s="175">
         <f>H100</f>
         <v/>
       </c>
@@ -10672,19 +10671,19 @@
           <t>Issuance (repayment)</t>
         </is>
       </c>
-      <c r="E99" s="163" t="n">
+      <c r="E99" s="162" t="n">
         <v>519583</v>
       </c>
-      <c r="F99" s="163" t="n">
+      <c r="F99" s="162" t="n">
         <v>594651</v>
       </c>
-      <c r="G99" s="163" t="n">
+      <c r="G99" s="162" t="n">
         <v>7989</v>
       </c>
-      <c r="H99" s="163" t="n">
+      <c r="H99" s="162" t="n">
         <v>347363</v>
       </c>
-      <c r="I99" s="163" t="n">
+      <c r="I99" s="162" t="n">
         <v>846670</v>
       </c>
       <c r="J99" s="159">
@@ -10716,19 +10715,19 @@
       </c>
       <c r="C100" s="5" t="n"/>
       <c r="D100" s="28" t="n"/>
-      <c r="E100" s="178" t="n">
+      <c r="E100" s="177" t="n">
         <v>1259018</v>
       </c>
-      <c r="F100" s="178" t="n">
+      <c r="F100" s="177" t="n">
         <v>1853669</v>
       </c>
-      <c r="G100" s="178" t="n">
+      <c r="G100" s="177" t="n">
         <v>1861658</v>
       </c>
-      <c r="H100" s="178" t="n">
+      <c r="H100" s="177" t="n">
         <v>2209021</v>
       </c>
-      <c r="I100" s="178" t="n">
+      <c r="I100" s="177" t="n">
         <v>3055691</v>
       </c>
       <c r="J100" s="159">
@@ -10758,19 +10757,19 @@
           <t>Interest Expense</t>
         </is>
       </c>
-      <c r="E101" s="163" t="n">
+      <c r="E101" s="162" t="n">
         <v>40092</v>
       </c>
-      <c r="F101" s="163" t="n">
+      <c r="F101" s="162" t="n">
         <v>68967</v>
       </c>
-      <c r="G101" s="163" t="n">
+      <c r="G101" s="162" t="n">
         <v>95546</v>
       </c>
-      <c r="H101" s="163" t="n">
+      <c r="H101" s="162" t="n">
         <v>105638</v>
       </c>
-      <c r="I101" s="163" t="n">
+      <c r="I101" s="162" t="n">
         <v>133647</v>
       </c>
       <c r="J101" s="159">
@@ -11145,7 +11144,7 @@
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="36" customWidth="1" min="12" max="12"/>
+    <col width="42" customWidth="1" min="12" max="12"/>
     <col width="18" customWidth="1" min="13" max="13"/>
     <col width="9.08984375" customWidth="1" min="15" max="15"/>
     <col width="40" customWidth="1" min="17" max="17"/>
@@ -11195,9 +11194,9 @@
       <c r="L2" s="96" t="n"/>
       <c r="M2" s="94" t="n"/>
       <c r="N2" s="94" t="n"/>
-      <c r="Q2" s="181" t="inlineStr">
-        <is>
-          <t>vengeanceaiUSCMODEL6 — LIVE EQUATIONS + SOURCE LINKS</t>
+      <c r="Q2" s="180" t="inlineStr">
+        <is>
+          <t>vengeanceaiUSCMODEL7 — LIVE EQUATIONS + SOURCE LINKS</t>
         </is>
       </c>
     </row>
@@ -11217,7 +11216,7 @@
       <c r="M3" s="97" t="n"/>
       <c r="N3" s="97" t="n"/>
       <c r="O3" s="97" t="n"/>
-      <c r="Q3" s="182" t="inlineStr">
+      <c r="Q3" s="181" t="inlineStr">
         <is>
           <t>Yellow = inputs (edit). Green = formulas. Blue underlined = clickable sources.</t>
         </is>
@@ -11243,32 +11242,32 @@
       <c r="M4" s="97" t="n"/>
       <c r="N4" s="97" t="n"/>
       <c r="O4" s="97" t="n"/>
-      <c r="Q4" s="183" t="inlineStr">
+      <c r="Q4" s="182" t="inlineStr">
         <is>
           <t>Input</t>
         </is>
       </c>
-      <c r="R4" s="183" t="inlineStr">
+      <c r="R4" s="182" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="S4" s="183" t="inlineStr">
+      <c r="S4" s="182" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="T4" s="183" t="inlineStr">
+      <c r="T4" s="182" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="U4" s="183" t="inlineStr">
+      <c r="U4" s="182" t="inlineStr">
         <is>
           <t>Primary source (click)</t>
         </is>
       </c>
-      <c r="V4" s="183" t="inlineStr">
+      <c r="V4" s="182" t="inlineStr">
         <is>
           <t>Secondary source (click)</t>
         </is>
@@ -11282,10 +11281,10 @@
         </is>
       </c>
       <c r="C5" s="100" t="n"/>
-      <c r="D5" s="184" t="n">
+      <c r="D5" s="183" t="n">
         <v>0.1877023903712333</v>
       </c>
-      <c r="E5" s="185" t="inlineStr">
+      <c r="E5" s="184" t="inlineStr">
         <is>
           <t>Tax source: SEC 10-K</t>
         </is>
@@ -11300,14 +11299,14 @@
       <c r="M5" s="97" t="n"/>
       <c r="N5" s="97" t="n"/>
       <c r="O5" s="97" t="n"/>
-      <c r="Q5" s="146" t="inlineStr">
+      <c r="Q5" s="145" t="inlineStr">
         <is>
           <t>1) CAPM → WACC   (D6 = R15)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="186" t="inlineStr">
+      <c r="A6" s="185" t="inlineStr">
         <is>
           <t>WACC sources → columns U–V</t>
         </is>
@@ -11317,26 +11316,26 @@
           <t>Discount Rate (WACC = We×Ke + Wd×Rd(1−t))</t>
         </is>
       </c>
-      <c r="C6" s="187" t="inlineStr">
+      <c r="C6" s="186" t="inlineStr">
         <is>
           <t>Sources →</t>
         </is>
       </c>
-      <c r="D6" s="188">
+      <c r="D6" s="187">
         <f>R15</f>
         <v/>
       </c>
-      <c r="E6" s="185" t="inlineStr">
+      <c r="E6" s="184" t="inlineStr">
         <is>
           <t>WACC sources → scroll to col U (Rf/ERP/β/Rd links)</t>
         </is>
       </c>
-      <c r="F6" s="185" t="inlineStr">
+      <c r="F6" s="184" t="inlineStr">
         <is>
           <t>Damodaran ERP</t>
         </is>
       </c>
-      <c r="G6" s="185" t="inlineStr">
+      <c r="G6" s="184" t="inlineStr">
         <is>
           <t>SEC 8-K Rd 6.250%</t>
         </is>
@@ -11349,30 +11348,30 @@
       <c r="M6" s="97" t="n"/>
       <c r="N6" s="97" t="n"/>
       <c r="O6" s="97" t="n"/>
-      <c r="Q6" s="189" t="inlineStr">
+      <c r="Q6" s="188" t="inlineStr">
         <is>
           <t>Risk-free rate (Rf)</t>
         </is>
       </c>
-      <c r="R6" s="190" t="n">
+      <c r="R6" s="189" t="n">
         <v>0.0463</v>
       </c>
-      <c r="S6" s="189" t="inlineStr">
+      <c r="S6" s="188" t="inlineStr">
         <is>
           <t>US 10Y Treasury yield</t>
         </is>
       </c>
-      <c r="T6" s="189" t="inlineStr">
+      <c r="T6" s="188" t="inlineStr">
         <is>
           <t>CAPM input</t>
         </is>
       </c>
-      <c r="U6" s="191" t="inlineStr">
+      <c r="U6" s="190" t="inlineStr">
         <is>
           <t>FRED DGS10 (US 10Y)</t>
         </is>
       </c>
-      <c r="V6" s="191" t="inlineStr">
+      <c r="V6" s="190" t="inlineStr">
         <is>
           <t>US Treasury Daily Par Yield Curve</t>
         </is>
@@ -11386,7 +11385,7 @@
         </is>
       </c>
       <c r="C7" s="97" t="n"/>
-      <c r="D7" s="184" t="n">
+      <c r="D7" s="183" t="n">
         <v>0.03</v>
       </c>
       <c r="E7" s="97" t="n"/>
@@ -11400,30 +11399,30 @@
       <c r="M7" s="97" t="n"/>
       <c r="N7" s="97" t="n"/>
       <c r="O7" s="97" t="n"/>
-      <c r="Q7" s="189" t="inlineStr">
+      <c r="Q7" s="188" t="inlineStr">
         <is>
           <t>Equity risk premium (ERP)</t>
         </is>
       </c>
-      <c r="R7" s="190" t="n">
+      <c r="R7" s="189" t="n">
         <v>0.0428</v>
       </c>
-      <c r="S7" s="189" t="inlineStr">
+      <c r="S7" s="188" t="inlineStr">
         <is>
           <t>Damodaran implied ERP</t>
         </is>
       </c>
-      <c r="T7" s="189" t="inlineStr">
+      <c r="T7" s="188" t="inlineStr">
         <is>
           <t>CAPM input</t>
         </is>
       </c>
-      <c r="U7" s="191" t="inlineStr">
+      <c r="U7" s="190" t="inlineStr">
         <is>
           <t>Damodaran Online — Implied ERP</t>
         </is>
       </c>
-      <c r="V7" s="191" t="inlineStr">
+      <c r="V7" s="190" t="inlineStr">
         <is>
           <t>Damodaran histimpl.xls / table</t>
         </is>
@@ -11437,10 +11436,10 @@
         </is>
       </c>
       <c r="C8" s="97" t="n"/>
-      <c r="D8" s="192" t="n">
-        <v>25</v>
-      </c>
-      <c r="E8" s="185" t="inlineStr">
+      <c r="D8" s="191" t="n">
+        <v>16</v>
+      </c>
+      <c r="E8" s="184" t="inlineStr">
         <is>
           <t>Rd source: SEC 8-K 6.250% notes</t>
         </is>
@@ -11455,30 +11454,30 @@
       <c r="M8" s="97" t="n"/>
       <c r="N8" s="97" t="n"/>
       <c r="O8" s="97" t="n"/>
-      <c r="Q8" s="189" t="inlineStr">
+      <c r="Q8" s="188" t="inlineStr">
         <is>
           <t>Beta (β)</t>
         </is>
       </c>
-      <c r="R8" s="193" t="n">
+      <c r="R8" s="192" t="n">
         <v>1.32</v>
       </c>
-      <c r="S8" s="189" t="inlineStr">
+      <c r="S8" s="188" t="inlineStr">
         <is>
           <t>Yahoo 5Y monthly beta</t>
         </is>
       </c>
-      <c r="T8" s="189" t="inlineStr">
+      <c r="T8" s="188" t="inlineStr">
         <is>
           <t>CAPM input</t>
         </is>
       </c>
-      <c r="U8" s="191" t="inlineStr">
+      <c r="U8" s="190" t="inlineStr">
         <is>
           <t>Yahoo Finance FICO Key Statistics</t>
         </is>
       </c>
-      <c r="V8" s="191" t="inlineStr">
+      <c r="V8" s="190" t="inlineStr">
         <is>
           <t>Yahoo Finance FICO quote</t>
         </is>
@@ -11492,7 +11491,7 @@
         </is>
       </c>
       <c r="C9" s="97" t="n"/>
-      <c r="D9" s="194" t="n">
+      <c r="D9" s="193" t="n">
         <v>45930</v>
       </c>
       <c r="E9" s="97" t="n"/>
@@ -11506,31 +11505,31 @@
       <c r="M9" s="97" t="n"/>
       <c r="N9" s="97" t="n"/>
       <c r="O9" s="97" t="n"/>
-      <c r="Q9" s="195" t="inlineStr">
+      <c r="Q9" s="194" t="inlineStr">
         <is>
           <t>Ke = Rf + β × ERP</t>
         </is>
       </c>
-      <c r="R9" s="196">
+      <c r="R9" s="195">
         <f>R6+R8*R7</f>
         <v/>
       </c>
-      <c r="S9" s="189" t="inlineStr">
+      <c r="S9" s="188" t="inlineStr">
         <is>
           <t>Cost of equity (CAPM)</t>
         </is>
       </c>
-      <c r="T9" s="195" t="inlineStr">
+      <c r="T9" s="194" t="inlineStr">
         <is>
           <t>→ WACC</t>
         </is>
       </c>
-      <c r="U9" s="189" t="inlineStr">
+      <c r="U9" s="188" t="inlineStr">
         <is>
           <t>Derived: R6 + R8 × R7</t>
         </is>
       </c>
-      <c r="V9" s="189" t="inlineStr"/>
+      <c r="V9" s="188" t="inlineStr"/>
     </row>
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="97" t="n"/>
@@ -11540,7 +11539,7 @@
         </is>
       </c>
       <c r="C10" s="97" t="n"/>
-      <c r="D10" s="194" t="n">
+      <c r="D10" s="193" t="n">
         <v>46295</v>
       </c>
       <c r="E10" s="97" t="n"/>
@@ -11554,30 +11553,30 @@
       <c r="M10" s="97" t="n"/>
       <c r="N10" s="97" t="n"/>
       <c r="O10" s="97" t="n"/>
-      <c r="Q10" s="189" t="inlineStr">
+      <c r="Q10" s="188" t="inlineStr">
         <is>
           <t>Pre-tax cost of debt (Rd)</t>
         </is>
       </c>
-      <c r="R10" s="190" t="n">
+      <c r="R10" s="189" t="n">
         <v>0.0625</v>
       </c>
-      <c r="S10" s="189" t="inlineStr">
+      <c r="S10" s="188" t="inlineStr">
         <is>
           <t>6.250% Senior Notes due 2034</t>
         </is>
       </c>
-      <c r="T10" s="189" t="inlineStr">
+      <c r="T10" s="188" t="inlineStr">
         <is>
           <t>WACC input</t>
         </is>
       </c>
-      <c r="U10" s="191" t="inlineStr">
+      <c r="U10" s="190" t="inlineStr">
         <is>
           <t>SEC 8-K — Notes closing (6.250%)</t>
         </is>
       </c>
-      <c r="V10" s="191" t="inlineStr">
+      <c r="V10" s="190" t="inlineStr">
         <is>
           <t>SEC EX-99.1 — Notes pricing press release</t>
         </is>
@@ -11591,7 +11590,7 @@
         </is>
       </c>
       <c r="C11" s="97" t="n"/>
-      <c r="D11" s="197" t="n">
+      <c r="D11" s="196" t="n">
         <v>1046.23</v>
       </c>
       <c r="E11" s="97" t="n"/>
@@ -11605,31 +11604,31 @@
       <c r="M11" s="97" t="n"/>
       <c r="N11" s="97" t="n"/>
       <c r="O11" s="97" t="n"/>
-      <c r="Q11" s="189" t="inlineStr">
+      <c r="Q11" s="188" t="inlineStr">
         <is>
           <t>Tax rate (t)</t>
         </is>
       </c>
-      <c r="R11" s="196">
+      <c r="R11" s="195">
         <f>$D$5</f>
         <v/>
       </c>
-      <c r="S11" s="189" t="inlineStr">
+      <c r="S11" s="188" t="inlineStr">
         <is>
           <t>FY25 effective = 150,649 / 802,595</t>
         </is>
       </c>
-      <c r="T11" s="189" t="inlineStr">
+      <c r="T11" s="188" t="inlineStr">
         <is>
           <t>Linked D5</t>
         </is>
       </c>
-      <c r="U11" s="191" t="inlineStr">
+      <c r="U11" s="190" t="inlineStr">
         <is>
           <t>SEC 10-K FY2025 (tax / EBT)</t>
         </is>
       </c>
-      <c r="V11" s="191" t="inlineStr">
+      <c r="V11" s="190" t="inlineStr">
         <is>
           <t>SEC companyfacts XBRL (CIK 0000814547)</t>
         </is>
@@ -11643,7 +11642,7 @@
         </is>
       </c>
       <c r="C12" s="97" t="n"/>
-      <c r="D12" s="198" t="n">
+      <c r="D12" s="197" t="n">
         <v>21597.635</v>
       </c>
       <c r="E12" s="97" t="n"/>
@@ -11657,31 +11656,31 @@
       <c r="M12" s="97" t="n"/>
       <c r="N12" s="97" t="n"/>
       <c r="O12" s="97" t="n"/>
-      <c r="Q12" s="195" t="inlineStr">
+      <c r="Q12" s="194" t="inlineStr">
         <is>
           <t>Rd_aftertax = Rd × (1 − t)</t>
         </is>
       </c>
-      <c r="R12" s="196">
+      <c r="R12" s="195">
         <f>R10*(1-R11)</f>
         <v/>
       </c>
-      <c r="S12" s="189" t="inlineStr">
+      <c r="S12" s="188" t="inlineStr">
         <is>
           <t>After-tax cost of debt</t>
         </is>
       </c>
-      <c r="T12" s="195" t="inlineStr">
+      <c r="T12" s="194" t="inlineStr">
         <is>
           <t>→ WACC</t>
         </is>
       </c>
-      <c r="U12" s="189" t="inlineStr">
+      <c r="U12" s="188" t="inlineStr">
         <is>
           <t>Derived: R10 × (1 − R11)</t>
         </is>
       </c>
-      <c r="V12" s="189" t="inlineStr"/>
+      <c r="V12" s="188" t="inlineStr"/>
     </row>
     <row r="13" ht="16" customHeight="1">
       <c r="A13" s="97" t="n"/>
@@ -11691,7 +11690,7 @@
         </is>
       </c>
       <c r="C13" s="97" t="n"/>
-      <c r="D13" s="198" t="n">
+      <c r="D13" s="197" t="n">
         <v>5582389</v>
       </c>
       <c r="E13" s="97" t="n"/>
@@ -11705,30 +11704,30 @@
       <c r="M13" s="97" t="n"/>
       <c r="N13" s="97" t="n"/>
       <c r="O13" s="97" t="n"/>
-      <c r="Q13" s="189" t="inlineStr">
+      <c r="Q13" s="188" t="inlineStr">
         <is>
           <t>Equity weight (We)</t>
         </is>
       </c>
-      <c r="R13" s="199" t="n">
+      <c r="R13" s="198" t="n">
         <v>0.8</v>
       </c>
-      <c r="S13" s="189" t="inlineStr">
+      <c r="S13" s="188" t="inlineStr">
         <is>
           <t>Target ~80% equity at market</t>
         </is>
       </c>
-      <c r="T13" s="189" t="inlineStr">
+      <c r="T13" s="188" t="inlineStr">
         <is>
           <t>WACC weight</t>
         </is>
       </c>
-      <c r="U13" s="191" t="inlineStr">
+      <c r="U13" s="190" t="inlineStr">
         <is>
           <t>SEC 10-Q Q3 FY2026 (debt / capital)</t>
         </is>
       </c>
-      <c r="V13" s="191" t="inlineStr">
+      <c r="V13" s="190" t="inlineStr">
         <is>
           <t>Yahoo market cap for E/(D+E)</t>
         </is>
@@ -11742,7 +11741,7 @@
         </is>
       </c>
       <c r="C14" s="97" t="n"/>
-      <c r="D14" s="198" t="n">
+      <c r="D14" s="197" t="n">
         <v>304537</v>
       </c>
       <c r="E14" s="97" t="n"/>
@@ -11756,30 +11755,30 @@
       <c r="M14" s="97" t="n"/>
       <c r="N14" s="97" t="n"/>
       <c r="O14" s="97" t="n"/>
-      <c r="Q14" s="189" t="inlineStr">
+      <c r="Q14" s="188" t="inlineStr">
         <is>
           <t>Debt weight (Wd)</t>
         </is>
       </c>
-      <c r="R14" s="199" t="n">
+      <c r="R14" s="198" t="n">
         <v>0.2</v>
       </c>
-      <c r="S14" s="189" t="inlineStr">
+      <c r="S14" s="188" t="inlineStr">
         <is>
           <t>Target ~20% debt (We+Wd=100%)</t>
         </is>
       </c>
-      <c r="T14" s="189" t="inlineStr">
+      <c r="T14" s="188" t="inlineStr">
         <is>
           <t>WACC weight</t>
         </is>
       </c>
-      <c r="U14" s="191" t="inlineStr">
+      <c r="U14" s="190" t="inlineStr">
         <is>
           <t>SEC 10-Q — total debt $5,582,389k</t>
         </is>
       </c>
-      <c r="V14" s="191" t="inlineStr">
+      <c r="V14" s="190" t="inlineStr">
         <is>
           <t>SEC 10-K — senior notes footnote</t>
         </is>
@@ -11793,7 +11792,7 @@
         </is>
       </c>
       <c r="C15" s="97" t="n"/>
-      <c r="D15" s="200">
+      <c r="D15" s="199">
         <f>'3 Statement Model'!J68</f>
         <v/>
       </c>
@@ -11808,31 +11807,31 @@
       <c r="M15" s="97" t="n"/>
       <c r="N15" s="97" t="n"/>
       <c r="O15" s="97" t="n"/>
-      <c r="Q15" s="195" t="inlineStr">
+      <c r="Q15" s="194" t="inlineStr">
         <is>
           <t>WACC = We×Ke + Wd×Rd_aftertax</t>
         </is>
       </c>
-      <c r="R15" s="196">
+      <c r="R15" s="195">
         <f>R13*R9+R14*R12</f>
         <v/>
       </c>
-      <c r="S15" s="189" t="inlineStr">
+      <c r="S15" s="188" t="inlineStr">
         <is>
           <t>PRIMARY discount rate → cell D6</t>
         </is>
       </c>
-      <c r="T15" s="195" t="inlineStr">
+      <c r="T15" s="194" t="inlineStr">
         <is>
           <t>→ D6</t>
         </is>
       </c>
-      <c r="U15" s="191" t="inlineStr">
+      <c r="U15" s="190" t="inlineStr">
         <is>
           <t>SEC filings (tax, debt coupons)</t>
         </is>
       </c>
-      <c r="V15" s="191" t="inlineStr">
+      <c r="V15" s="190" t="inlineStr">
         <is>
           <t>Damodaran (ERP methodology)</t>
         </is>
@@ -11863,23 +11862,23 @@
           <t>Entry</t>
         </is>
       </c>
-      <c r="E17" s="201">
+      <c r="E17" s="200">
         <f>YEAR(E18)</f>
         <v/>
       </c>
-      <c r="F17" s="201">
+      <c r="F17" s="200">
         <f>YEAR(F18)</f>
         <v/>
       </c>
-      <c r="G17" s="201">
+      <c r="G17" s="200">
         <f>YEAR(G18)</f>
         <v/>
       </c>
-      <c r="H17" s="201">
+      <c r="H17" s="200">
         <f>YEAR(H18)</f>
         <v/>
       </c>
-      <c r="I17" s="201">
+      <c r="I17" s="200">
         <f>YEAR(I18)</f>
         <v/>
       </c>
@@ -11891,13 +11890,13 @@
       <c r="K17" s="97" t="n"/>
       <c r="L17" s="114" t="inlineStr">
         <is>
-          <t>Terminal value methods (MODEL3)</t>
+          <t>Terminal value methods (MODEL7)</t>
         </is>
       </c>
       <c r="M17" s="111" t="n"/>
       <c r="N17" s="111" t="n"/>
       <c r="O17" s="97" t="n"/>
-      <c r="Q17" s="146" t="inlineStr">
+      <c r="Q17" s="145" t="inlineStr">
         <is>
           <t>2) Unlevered Free Cash Flow</t>
         </is>
@@ -11907,64 +11906,65 @@
       <c r="A18" s="97" t="n"/>
       <c r="B18" s="97" t="inlineStr">
         <is>
-          <t>Date (mid-year convention)</t>
+          <t>Date (mid-year via EDATE from transaction)</t>
         </is>
       </c>
       <c r="C18" s="97" t="n"/>
-      <c r="D18" s="202">
+      <c r="D18" s="201">
         <f>D9</f>
         <v/>
       </c>
-      <c r="E18" s="203">
-        <f>DATE(YEAR($D$10)+E19,3,31)</f>
-        <v/>
-      </c>
-      <c r="F18" s="203">
-        <f>DATE(YEAR($D$10)+F19,3,31)</f>
-        <v/>
-      </c>
-      <c r="G18" s="203">
-        <f>DATE(YEAR($D$10)+G19,3,31)</f>
-        <v/>
-      </c>
-      <c r="H18" s="203">
-        <f>DATE(YEAR($D$10)+H19,3,31)</f>
-        <v/>
-      </c>
-      <c r="I18" s="203">
-        <f>DATE(YEAR($D$10)+I19,3,31)</f>
-        <v/>
-      </c>
-      <c r="J18" s="204">
+      <c r="E18" s="202">
+        <f>EDATE($D$9,(E19-0.5)*12)</f>
+        <v/>
+      </c>
+      <c r="F18" s="202">
+        <f>EDATE($D$9,(F19-0.5)*12)</f>
+        <v/>
+      </c>
+      <c r="G18" s="202">
+        <f>EDATE($D$9,(G19-0.5)*12)</f>
+        <v/>
+      </c>
+      <c r="H18" s="202">
+        <f>EDATE($D$9,(H19-0.5)*12)</f>
+        <v/>
+      </c>
+      <c r="I18" s="202">
+        <f>EDATE($D$9,(I19-0.5)*12)</f>
+        <v/>
+      </c>
+      <c r="J18" s="199">
         <f>I18</f>
         <v/>
       </c>
       <c r="K18" s="97" t="n"/>
       <c r="L18" s="97" t="inlineStr">
         <is>
-          <t>Exit EV/EBITDA (in J27) — primary</t>
-        </is>
-      </c>
-      <c r="M18" s="200">
+          <t>Exit EV/EBITDA @ D8 (primary 16x)</t>
+        </is>
+      </c>
+      <c r="M18" s="199">
         <f>J27</f>
         <v/>
       </c>
-      <c r="N18" s="97">
-        <f>(I26*(1+D7))/(D6-D7)</f>
-        <v/>
+      <c r="N18" s="97" t="inlineStr">
+        <is>
+          <t>← used in XNPV</t>
+        </is>
       </c>
       <c r="O18" s="97" t="n"/>
-      <c r="Q18" s="195" t="inlineStr">
+      <c r="Q18" s="194" t="inlineStr">
         <is>
           <t>FCFF = EBIT − EBIT×t + D&amp;A − CapEx − ΔNWC</t>
         </is>
       </c>
-      <c r="U18" s="191" t="inlineStr">
+      <c r="U18" s="190" t="inlineStr">
         <is>
           <t>Drivers from SEC XBRL → 3-statement</t>
         </is>
       </c>
-      <c r="V18" s="191" t="inlineStr">
+      <c r="V18" s="190" t="inlineStr">
         <is>
           <t>SEC 10-K historical IS/CF</t>
         </is>
@@ -11972,29 +11972,29 @@
     </row>
     <row r="19" ht="16" customHeight="1">
       <c r="A19" s="97" t="n"/>
-      <c r="B19" s="118" t="inlineStr">
+      <c r="B19" s="117" t="inlineStr">
         <is>
           <t>Time Periods</t>
         </is>
       </c>
-      <c r="C19" s="118" t="n"/>
+      <c r="C19" s="117" t="n"/>
       <c r="D19" s="115" t="n"/>
-      <c r="E19" s="205" t="n">
+      <c r="E19" s="203" t="n">
         <v>0</v>
       </c>
-      <c r="F19" s="202">
+      <c r="F19" s="201">
         <f>E19+1</f>
         <v/>
       </c>
-      <c r="G19" s="202">
+      <c r="G19" s="201">
         <f>F19+1</f>
         <v/>
       </c>
-      <c r="H19" s="202">
+      <c r="H19" s="201">
         <f>G19+1</f>
         <v/>
       </c>
-      <c r="I19" s="202">
+      <c r="I19" s="201">
         <f>H19+1</f>
         <v/>
       </c>
@@ -12005,51 +12005,52 @@
           <t>Gordon cross-check</t>
         </is>
       </c>
-      <c r="M19" s="200">
+      <c r="M19" s="199">
         <f>IF(($D$6-$D$7)&lt;=0,"WACC must exceed g",$I$26*(1+$D$7)/($D$6-$D$7))</f>
         <v/>
       </c>
-      <c r="N19" s="121">
-        <f>D8*(I21+I23)</f>
-        <v/>
+      <c r="N19" s="120" t="inlineStr">
+        <is>
+          <t>← sanity check</t>
+        </is>
       </c>
       <c r="O19" s="97" t="n"/>
-      <c r="Q19" s="189" t="inlineStr">
+      <c r="Q19" s="188" t="inlineStr">
         <is>
           <t>Excel (col E example)</t>
         </is>
       </c>
-      <c r="R19" s="195">
+      <c r="R19" s="194">
         <f>E21-E22+E23-E24-E25</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="16" customHeight="1">
       <c r="A20" s="97" t="n"/>
-      <c r="B20" s="118" t="inlineStr">
-        <is>
-          <t>Year Fraction (display only; not applied to CF)</t>
+      <c r="B20" s="117" t="inlineStr">
+        <is>
+          <t>Year Fraction (display only; XNPV uses exact dates below)</t>
         </is>
       </c>
       <c r="C20" s="97" t="n"/>
       <c r="D20" s="97" t="n"/>
-      <c r="E20" s="202">
+      <c r="E20" s="201">
         <f>YEARFRAC(D18,E18)</f>
         <v/>
       </c>
-      <c r="F20" s="202">
+      <c r="F20" s="201">
         <f>YEARFRAC(E18,F18)</f>
         <v/>
       </c>
-      <c r="G20" s="202">
+      <c r="G20" s="201">
         <f>YEARFRAC(F18,G18)</f>
         <v/>
       </c>
-      <c r="H20" s="202">
+      <c r="H20" s="201">
         <f>YEARFRAC(G18,H18)</f>
         <v/>
       </c>
-      <c r="I20" s="202">
+      <c r="I20" s="201">
         <f>YEARFRAC(H18,I18)</f>
         <v/>
       </c>
@@ -12060,30 +12061,30 @@
           <t>Implied Gordon exit multiple</t>
         </is>
       </c>
-      <c r="M20" s="200">
+      <c r="M20" s="199">
         <f>IF(($I$21+$I$23)=0,0,M19/($I$21+$I$23))</f>
         <v/>
       </c>
-      <c r="N20" s="123">
+      <c r="N20" s="122">
         <f>AVERAGE(N18:N19)</f>
         <v/>
       </c>
       <c r="O20" s="97" t="n"/>
-      <c r="Q20" s="189" t="inlineStr">
+      <c r="Q20" s="188" t="inlineStr">
         <is>
           <t>Tax on EBIT (unlevered)</t>
         </is>
       </c>
-      <c r="R20" s="195">
+      <c r="R20" s="194">
         <f>E21*$D$5</f>
         <v/>
       </c>
-      <c r="S20" s="189" t="inlineStr">
+      <c r="S20" s="188" t="inlineStr">
         <is>
           <t>NOT levered IS tax dollars</t>
         </is>
       </c>
-      <c r="U20" s="191" t="inlineStr">
+      <c r="U20" s="190" t="inlineStr">
         <is>
           <t>Tax rate from SEC 10-K effective rate</t>
         </is>
@@ -12096,48 +12097,59 @@
           <t>EBIT (linked to 3-stmt)</t>
         </is>
       </c>
-      <c r="C21" s="206" t="inlineStr">
+      <c r="C21" s="204" t="inlineStr">
         <is>
           <t>EBIT</t>
         </is>
       </c>
       <c r="D21" s="97" t="n"/>
-      <c r="E21" s="200">
+      <c r="E21" s="199">
         <f>'3 Statement Model'!J26-'3 Statement Model'!J28-'3 Statement Model'!J29-'3 Statement Model'!J30</f>
         <v/>
       </c>
-      <c r="F21" s="200">
+      <c r="F21" s="199">
         <f>'3 Statement Model'!K26-'3 Statement Model'!K28-'3 Statement Model'!K29-'3 Statement Model'!K30</f>
         <v/>
       </c>
-      <c r="G21" s="200">
+      <c r="G21" s="199">
         <f>'3 Statement Model'!L26-'3 Statement Model'!L28-'3 Statement Model'!L29-'3 Statement Model'!L30</f>
         <v/>
       </c>
-      <c r="H21" s="200">
+      <c r="H21" s="199">
         <f>'3 Statement Model'!M26-'3 Statement Model'!M28-'3 Statement Model'!M29-'3 Statement Model'!M30</f>
         <v/>
       </c>
-      <c r="I21" s="200">
+      <c r="I21" s="199">
         <f>'3 Statement Model'!N26-'3 Statement Model'!N28-'3 Statement Model'!N29-'3 Statement Model'!N30</f>
         <v/>
       </c>
       <c r="J21" s="97" t="n"/>
       <c r="K21" s="97" t="n"/>
-      <c r="L21" s="97" t="n"/>
-      <c r="M21" s="97" t="n"/>
-      <c r="N21" s="97" t="n"/>
+      <c r="L21" s="97" t="inlineStr">
+        <is>
+          <t>Bull case TV @ 25x (sensitivity only)</t>
+        </is>
+      </c>
+      <c r="M21" s="199">
+        <f>($I$21+$I$23)*25.0</f>
+        <v/>
+      </c>
+      <c r="N21" s="97" t="inlineStr">
+        <is>
+          <t>← not in base case</t>
+        </is>
+      </c>
       <c r="O21" s="97" t="n"/>
-      <c r="Q21" s="189" t="inlineStr">
+      <c r="Q21" s="188" t="inlineStr">
         <is>
           <t>FCFF check (FY5 / col I)</t>
         </is>
       </c>
-      <c r="R21" s="207">
+      <c r="R21" s="205">
         <f>I26</f>
         <v/>
       </c>
-      <c r="S21" s="189" t="inlineStr">
+      <c r="S21" s="188" t="inlineStr">
         <is>
           <t>Must equal I21−I22+I23−I24−I25</t>
         </is>
@@ -12150,29 +12162,29 @@
           <t>Less: Unlevered Cash Taxes (EBIT×t)</t>
         </is>
       </c>
-      <c r="C22" s="206" t="inlineStr">
+      <c r="C22" s="204" t="inlineStr">
         <is>
           <t>EBIT×t</t>
         </is>
       </c>
       <c r="D22" s="97" t="n"/>
-      <c r="E22" s="200">
+      <c r="E22" s="199">
         <f>E21*$D$5</f>
         <v/>
       </c>
-      <c r="F22" s="200">
+      <c r="F22" s="199">
         <f>F21*$D$5</f>
         <v/>
       </c>
-      <c r="G22" s="200">
+      <c r="G22" s="199">
         <f>G21*$D$5</f>
         <v/>
       </c>
-      <c r="H22" s="200">
+      <c r="H22" s="199">
         <f>H21*$D$5</f>
         <v/>
       </c>
-      <c r="I22" s="200">
+      <c r="I22" s="199">
         <f>I21*$D$5</f>
         <v/>
       </c>
@@ -12190,29 +12202,29 @@
           <t>Plus: D&amp;A (linked to 3-stmt)</t>
         </is>
       </c>
-      <c r="C23" s="206" t="inlineStr">
+      <c r="C23" s="204" t="inlineStr">
         <is>
           <t>+D&amp;A</t>
         </is>
       </c>
       <c r="D23" s="97" t="n"/>
-      <c r="E23" s="200">
+      <c r="E23" s="199">
         <f>'3 Statement Model'!J30</f>
         <v/>
       </c>
-      <c r="F23" s="200">
+      <c r="F23" s="199">
         <f>'3 Statement Model'!K30</f>
         <v/>
       </c>
-      <c r="G23" s="200">
+      <c r="G23" s="199">
         <f>'3 Statement Model'!L30</f>
         <v/>
       </c>
-      <c r="H23" s="200">
+      <c r="H23" s="199">
         <f>'3 Statement Model'!M30</f>
         <v/>
       </c>
-      <c r="I23" s="200">
+      <c r="I23" s="199">
         <f>'3 Statement Model'!N30</f>
         <v/>
       </c>
@@ -12222,7 +12234,7 @@
       <c r="M23" s="97" t="n"/>
       <c r="N23" s="97" t="n"/>
       <c r="O23" s="97" t="n"/>
-      <c r="Q23" s="146" t="inlineStr">
+      <c r="Q23" s="145" t="inlineStr">
         <is>
           <t>3) Terminal Value</t>
         </is>
@@ -12235,29 +12247,29 @@
           <t>Less: Capex (linked to 3-stmt CF)</t>
         </is>
       </c>
-      <c r="C24" s="206" t="inlineStr">
+      <c r="C24" s="204" t="inlineStr">
         <is>
           <t>−CapEx</t>
         </is>
       </c>
       <c r="D24" s="97" t="n"/>
-      <c r="E24" s="200">
+      <c r="E24" s="199">
         <f>'3 Statement Model'!J68</f>
         <v/>
       </c>
-      <c r="F24" s="200">
+      <c r="F24" s="199">
         <f>'3 Statement Model'!K68</f>
         <v/>
       </c>
-      <c r="G24" s="200">
+      <c r="G24" s="199">
         <f>'3 Statement Model'!L68</f>
         <v/>
       </c>
-      <c r="H24" s="200">
+      <c r="H24" s="199">
         <f>'3 Statement Model'!M68</f>
         <v/>
       </c>
-      <c r="I24" s="200">
+      <c r="I24" s="199">
         <f>'3 Statement Model'!N68</f>
         <v/>
       </c>
@@ -12267,7 +12279,7 @@
       <c r="M24" s="97" t="n"/>
       <c r="N24" s="97" t="n"/>
       <c r="O24" s="97" t="n"/>
-      <c r="Q24" s="195" t="inlineStr">
+      <c r="Q24" s="194" t="inlineStr">
         <is>
           <t>TV_exit = EBITDA_n × ExitMultiple   [PRIMARY]</t>
         </is>
@@ -12280,29 +12292,29 @@
           <t>Less: ΔNWC (linked to 3-stmt CF)</t>
         </is>
       </c>
-      <c r="C25" s="206" t="inlineStr">
+      <c r="C25" s="204" t="inlineStr">
         <is>
           <t>−ΔNWC</t>
         </is>
       </c>
       <c r="D25" s="97" t="n"/>
-      <c r="E25" s="200">
+      <c r="E25" s="199">
         <f>'3 Statement Model'!J64</f>
         <v/>
       </c>
-      <c r="F25" s="200">
+      <c r="F25" s="199">
         <f>'3 Statement Model'!K64</f>
         <v/>
       </c>
-      <c r="G25" s="200">
+      <c r="G25" s="199">
         <f>'3 Statement Model'!L64</f>
         <v/>
       </c>
-      <c r="H25" s="200">
+      <c r="H25" s="199">
         <f>'3 Statement Model'!M64</f>
         <v/>
       </c>
-      <c r="I25" s="200">
+      <c r="I25" s="199">
         <f>'3 Statement Model'!N64</f>
         <v/>
       </c>
@@ -12312,20 +12324,20 @@
       <c r="M25" s="97" t="n"/>
       <c r="N25" s="97" t="n"/>
       <c r="O25" s="97" t="n"/>
-      <c r="Q25" s="189" t="inlineStr">
+      <c r="Q25" s="188" t="inlineStr">
         <is>
           <t>Excel</t>
         </is>
       </c>
-      <c r="R25" s="195">
+      <c r="R25" s="194">
         <f>($I$21+$I$23)*$D$8</f>
         <v/>
       </c>
-      <c r="T25" s="207">
+      <c r="T25" s="205">
         <f>J27</f>
         <v/>
       </c>
-      <c r="U25" s="191" t="inlineStr">
+      <c r="U25" s="190" t="inlineStr">
         <is>
           <t>Exit multiple policy vs Yahoo / market multiples</t>
         </is>
@@ -12338,29 +12350,29 @@
           <t>Unlevered FCF</t>
         </is>
       </c>
-      <c r="C26" s="206" t="inlineStr">
+      <c r="C26" s="204" t="inlineStr">
         <is>
           <t>FCFF=EBIT−tax+DA−CapEx−ΔNWC</t>
         </is>
       </c>
       <c r="D26" s="97" t="n"/>
-      <c r="E26" s="208">
+      <c r="E26" s="206">
         <f>E21-E22+E23-E24-E25</f>
         <v/>
       </c>
-      <c r="F26" s="208">
+      <c r="F26" s="206">
         <f>F21-F22+F23-F24-F25</f>
         <v/>
       </c>
-      <c r="G26" s="208">
+      <c r="G26" s="206">
         <f>G21-G22+G23-G24-G25</f>
         <v/>
       </c>
-      <c r="H26" s="208">
+      <c r="H26" s="206">
         <f>H21-H22+H23-H24-H25</f>
         <v/>
       </c>
-      <c r="I26" s="208">
+      <c r="I26" s="206">
         <f>I21-I22+I23-I24-I25</f>
         <v/>
       </c>
@@ -12370,7 +12382,7 @@
       <c r="M26" s="97" t="n"/>
       <c r="N26" s="97" t="n"/>
       <c r="O26" s="97" t="n"/>
-      <c r="Q26" s="195" t="inlineStr">
+      <c r="Q26" s="194" t="inlineStr">
         <is>
           <t>TV_gordon = FCFF_n×(1+g)/(WACC−g)   [CHECK]</t>
         </is>
@@ -12380,11 +12392,11 @@
       <c r="A27" s="97" t="n"/>
       <c r="B27" s="97" t="inlineStr">
         <is>
-          <t>(Entry)/Exit TV — Exit EV/EBITDA</t>
+          <t>(Entry)/Exit TV — Exit EV/EBITDA (primary 16x)</t>
         </is>
       </c>
       <c r="C27" s="97" t="n"/>
-      <c r="D27" s="209">
+      <c r="D27" s="207">
         <f>-I35</f>
         <v/>
       </c>
@@ -12393,7 +12405,7 @@
       <c r="G27" s="97" t="n"/>
       <c r="H27" s="97" t="n"/>
       <c r="I27" s="97" t="n"/>
-      <c r="J27" s="200">
+      <c r="J27" s="199">
         <f>($I$21+$I$23)*$D$8</f>
         <v/>
       </c>
@@ -12402,20 +12414,20 @@
       <c r="M27" s="97" t="n"/>
       <c r="N27" s="97" t="n"/>
       <c r="O27" s="97" t="n"/>
-      <c r="Q27" s="189" t="inlineStr">
+      <c r="Q27" s="188" t="inlineStr">
         <is>
           <t>Excel</t>
         </is>
       </c>
-      <c r="R27" s="195">
+      <c r="R27" s="194">
         <f>IF(($D$6-$D$7)&lt;=0,"err",$I$26*(1+$D$7)/($D$6-$D$7))</f>
         <v/>
       </c>
-      <c r="T27" s="207">
+      <c r="T27" s="205">
         <f>M19</f>
         <v/>
       </c>
-      <c r="U27" s="191" t="inlineStr">
+      <c r="U27" s="190" t="inlineStr">
         <is>
           <t>Gordon g vs Damodaran long-run growth framing</t>
         </is>
@@ -12429,30 +12441,30 @@
         </is>
       </c>
       <c r="C28" s="97" t="n"/>
-      <c r="D28" s="208" t="n">
+      <c r="D28" s="206" t="n">
         <v>0</v>
       </c>
-      <c r="E28" s="210">
+      <c r="E28" s="208">
         <f>E27+E26</f>
         <v/>
       </c>
-      <c r="F28" s="210">
+      <c r="F28" s="208">
         <f>F27+F26</f>
         <v/>
       </c>
-      <c r="G28" s="210">
+      <c r="G28" s="208">
         <f>G27+G26</f>
         <v/>
       </c>
-      <c r="H28" s="210">
+      <c r="H28" s="208">
         <f>H27+H26</f>
         <v/>
       </c>
-      <c r="I28" s="210">
+      <c r="I28" s="208">
         <f>I27+I26</f>
         <v/>
       </c>
-      <c r="J28" s="210">
+      <c r="J28" s="208">
         <f>J27+J26</f>
         <v/>
       </c>
@@ -12461,16 +12473,16 @@
       <c r="M28" s="97" t="n"/>
       <c r="N28" s="97" t="n"/>
       <c r="O28" s="97" t="n"/>
-      <c r="Q28" s="189" t="inlineStr">
+      <c r="Q28" s="188" t="inlineStr">
         <is>
           <t>Implied Gordon exit multiple</t>
         </is>
       </c>
-      <c r="R28" s="211">
+      <c r="R28" s="209">
         <f>IF(($I$21+$I$23)=0,0,T27/($I$21+$I$23))</f>
         <v/>
       </c>
-      <c r="S28" s="189" t="inlineStr">
+      <c r="S28" s="188" t="inlineStr">
         <is>
           <t>Gordon TV / EBITDA_n</t>
         </is>
@@ -12484,31 +12496,31 @@
         </is>
       </c>
       <c r="C29" s="97" t="n"/>
-      <c r="D29" s="209">
+      <c r="D29" s="207">
         <f>D27+D26</f>
         <v/>
       </c>
-      <c r="E29" s="200">
+      <c r="E29" s="199">
         <f>E27+E26</f>
         <v/>
       </c>
-      <c r="F29" s="200">
+      <c r="F29" s="199">
         <f>F27+F26</f>
         <v/>
       </c>
-      <c r="G29" s="200">
+      <c r="G29" s="199">
         <f>G27+G26</f>
         <v/>
       </c>
-      <c r="H29" s="200">
+      <c r="H29" s="199">
         <f>H27+H26</f>
         <v/>
       </c>
-      <c r="I29" s="200">
+      <c r="I29" s="199">
         <f>I27+I26</f>
         <v/>
       </c>
-      <c r="J29" s="200">
+      <c r="J29" s="199">
         <f>J27</f>
         <v/>
       </c>
@@ -12532,7 +12544,7 @@
       <c r="M30" s="97" t="n"/>
       <c r="N30" s="97" t="n"/>
       <c r="O30" s="97" t="n"/>
-      <c r="Q30" s="146" t="inlineStr">
+      <c r="Q30" s="145" t="inlineStr">
         <is>
           <t>4) Enterprise → Equity → $/share</t>
         </is>
@@ -12564,7 +12576,7 @@
       <c r="M31" s="111" t="n"/>
       <c r="N31" s="111" t="n"/>
       <c r="O31" s="97" t="n"/>
-      <c r="Q31" s="195" t="inlineStr">
+      <c r="Q31" s="194" t="inlineStr">
         <is>
           <t>EV = XNPV(WACC, TransactionCF, mid-year dates)</t>
         </is>
@@ -12574,11 +12586,11 @@
       <c r="A32" s="97" t="n"/>
       <c r="B32" s="97" t="inlineStr">
         <is>
-          <t>Enterprise Value (XNPV, mid-year dates)</t>
+          <t>Enterprise Value (XNPV, mid-year EDATE dates)</t>
         </is>
       </c>
       <c r="C32" s="97" t="n"/>
-      <c r="D32" s="200">
+      <c r="D32" s="199">
         <f>XNPV(D6,D28:J28,D18:J18)</f>
         <v/>
       </c>
@@ -12589,7 +12601,7 @@
         </is>
       </c>
       <c r="H32" s="97" t="n"/>
-      <c r="I32" s="209">
+      <c r="I32" s="207">
         <f>D12*D11</f>
         <v/>
       </c>
@@ -12600,21 +12612,21 @@
         </is>
       </c>
       <c r="M32" s="97" t="n"/>
-      <c r="N32" s="126">
+      <c r="N32" s="125">
         <f>D37/I37-1</f>
         <v/>
       </c>
       <c r="O32" s="97" t="n"/>
-      <c r="Q32" s="189" t="inlineStr">
+      <c r="Q32" s="188" t="inlineStr">
         <is>
           <t>Excel</t>
         </is>
       </c>
-      <c r="R32" s="195">
+      <c r="R32" s="194">
         <f>XNPV(D6,D28:J28,D18:J18)</f>
         <v/>
       </c>
-      <c r="T32" s="207">
+      <c r="T32" s="205">
         <f>D32</f>
         <v/>
       </c>
@@ -12627,7 +12639,7 @@
         </is>
       </c>
       <c r="C33" s="97" t="n"/>
-      <c r="D33" s="209">
+      <c r="D33" s="207">
         <f>+D14</f>
         <v/>
       </c>
@@ -12638,7 +12650,7 @@
         </is>
       </c>
       <c r="H33" s="97" t="n"/>
-      <c r="I33" s="209">
+      <c r="I33" s="207">
         <f>D13</f>
         <v/>
       </c>
@@ -12649,31 +12661,31 @@
         </is>
       </c>
       <c r="M33" s="97" t="n"/>
-      <c r="N33" s="126">
+      <c r="N33" s="125">
         <f>XIRR(D29:J29,D18:J18)</f>
         <v/>
       </c>
       <c r="O33" s="97" t="n"/>
-      <c r="Q33" s="195" t="inlineStr">
+      <c r="Q33" s="194" t="inlineStr">
         <is>
           <t>Equity = EV + Cash − Debt</t>
         </is>
       </c>
-      <c r="R33" s="207">
+      <c r="R33" s="205">
         <f>D35</f>
         <v/>
       </c>
-      <c r="S33" s="189" t="inlineStr">
+      <c r="S33" s="188" t="inlineStr">
         <is>
           <t>Net debt from 10-Q bridge</t>
         </is>
       </c>
-      <c r="U33" s="191" t="inlineStr">
+      <c r="U33" s="190" t="inlineStr">
         <is>
           <t>SEC 10-Q — cash, mkt secs, total debt</t>
         </is>
       </c>
-      <c r="V33" s="191" t="inlineStr">
+      <c r="V33" s="190" t="inlineStr">
         <is>
           <t>SEC 10-K — FY debt footnote</t>
         </is>
@@ -12687,7 +12699,7 @@
         </is>
       </c>
       <c r="C34" s="97" t="n"/>
-      <c r="D34" s="209">
+      <c r="D34" s="207">
         <f>+D13</f>
         <v/>
       </c>
@@ -12698,7 +12710,7 @@
         </is>
       </c>
       <c r="H34" s="97" t="n"/>
-      <c r="I34" s="209">
+      <c r="I34" s="207">
         <f>+D14</f>
         <v/>
       </c>
@@ -12707,26 +12719,26 @@
       <c r="M34" s="97" t="n"/>
       <c r="N34" s="97" t="n"/>
       <c r="O34" s="97" t="n"/>
-      <c r="Q34" s="195" t="inlineStr">
+      <c r="Q34" s="194" t="inlineStr">
         <is>
           <t>$/share = Equity / Shares</t>
         </is>
       </c>
-      <c r="R34" s="212">
+      <c r="R34" s="210">
         <f>D37</f>
         <v/>
       </c>
-      <c r="S34" s="189" t="inlineStr">
+      <c r="S34" s="188" t="inlineStr">
         <is>
           <t>Shares outstanding (Yahoo)</t>
         </is>
       </c>
-      <c r="U34" s="191" t="inlineStr">
+      <c r="U34" s="190" t="inlineStr">
         <is>
           <t>Yahoo Finance — shares outstanding</t>
         </is>
       </c>
-      <c r="V34" s="191" t="inlineStr">
+      <c r="V34" s="190" t="inlineStr">
         <is>
           <t>Yahoo FICO quote (price)</t>
         </is>
@@ -12740,7 +12752,7 @@
         </is>
       </c>
       <c r="C35" s="97" t="n"/>
-      <c r="D35" s="208">
+      <c r="D35" s="206">
         <f>D32+D33-D34</f>
         <v/>
       </c>
@@ -12751,7 +12763,7 @@
         </is>
       </c>
       <c r="H35" s="97" t="n"/>
-      <c r="I35" s="208">
+      <c r="I35" s="206">
         <f>I32+I33-I34</f>
         <v/>
       </c>
@@ -12764,16 +12776,16 @@
       <c r="M35" s="111" t="n"/>
       <c r="N35" s="111" t="n"/>
       <c r="O35" s="97" t="n"/>
-      <c r="Q35" s="189" t="inlineStr">
+      <c r="Q35" s="188" t="inlineStr">
         <is>
           <t>Upside vs market</t>
         </is>
       </c>
-      <c r="R35" s="213">
+      <c r="R35" s="211">
         <f>D37/D11-1</f>
         <v/>
       </c>
-      <c r="S35" s="189" t="inlineStr">
+      <c r="S35" s="188" t="inlineStr">
         <is>
           <t>Intrinsic / Current Price − 1</t>
         </is>
@@ -12787,7 +12799,7 @@
       <c r="E36" s="97" t="n"/>
       <c r="G36" s="97" t="n"/>
       <c r="H36" s="97" t="n"/>
-      <c r="I36" s="214" t="n"/>
+      <c r="I36" s="212" t="n"/>
       <c r="J36" s="97" t="n"/>
       <c r="L36" s="97" t="inlineStr">
         <is>
@@ -12795,7 +12807,7 @@
         </is>
       </c>
       <c r="M36" s="97" t="n"/>
-      <c r="N36" s="214">
+      <c r="N36" s="212">
         <f>I37</f>
         <v/>
       </c>
@@ -12809,7 +12821,7 @@
         </is>
       </c>
       <c r="C37" s="97" t="n"/>
-      <c r="D37" s="209">
+      <c r="D37" s="207">
         <f>D35/D12</f>
         <v/>
       </c>
@@ -12820,7 +12832,7 @@
         </is>
       </c>
       <c r="H37" s="97" t="n"/>
-      <c r="I37" s="209">
+      <c r="I37" s="207">
         <f>D11</f>
         <v/>
       </c>
@@ -12831,12 +12843,12 @@
         </is>
       </c>
       <c r="M37" s="97" t="n"/>
-      <c r="N37" s="214">
+      <c r="N37" s="212">
         <f>D37-I37</f>
         <v/>
       </c>
       <c r="O37" s="97" t="n"/>
-      <c r="Q37" s="146" t="inlineStr">
+      <c r="Q37" s="145" t="inlineStr">
         <is>
           <t>5) Operating NWC (feeds ΔNWC → FCFF)</t>
         </is>
@@ -12858,22 +12870,22 @@
         </is>
       </c>
       <c r="M38" s="97" t="n"/>
-      <c r="N38" s="214">
+      <c r="N38" s="212">
         <f>SUM(N36:N37)</f>
         <v/>
       </c>
       <c r="O38" s="97" t="n"/>
-      <c r="Q38" s="195" t="inlineStr">
+      <c r="Q38" s="194" t="inlineStr">
         <is>
           <t>NWC = AR + Inventory − AP − DeferredRevenue</t>
         </is>
       </c>
-      <c r="U38" s="191" t="inlineStr">
+      <c r="U38" s="190" t="inlineStr">
         <is>
           <t>SEC 10-K — AR / AP / deferred revenue</t>
         </is>
       </c>
-      <c r="V38" s="191" t="inlineStr">
+      <c r="V38" s="190" t="inlineStr">
         <is>
           <t>XBRL DeferredRevenueCurrent</t>
         </is>
@@ -12892,17 +12904,17 @@
       <c r="M39" s="97" t="n"/>
       <c r="N39" s="97" t="n"/>
       <c r="O39" s="97" t="n"/>
-      <c r="Q39" s="195" t="inlineStr">
+      <c r="Q39" s="194" t="inlineStr">
         <is>
           <t>ΔNWC_t = NWC_t − NWC_(t−1)</t>
         </is>
       </c>
-      <c r="S39" s="189" t="inlineStr">
+      <c r="S39" s="188" t="inlineStr">
         <is>
           <t>Linked from 3-statement CF row 64</t>
         </is>
       </c>
-      <c r="T39" s="207">
+      <c r="T39" s="205">
         <f>I25</f>
         <v/>
       </c>
@@ -12930,7 +12942,7 @@
         </is>
       </c>
       <c r="C41" s="111" t="n"/>
-      <c r="D41" s="128" t="n"/>
+      <c r="D41" s="127" t="n"/>
       <c r="E41" s="111" t="n"/>
       <c r="F41" s="111" t="n"/>
       <c r="G41" s="111" t="n"/>
@@ -12942,7 +12954,7 @@
       <c r="M41" s="111" t="n"/>
       <c r="N41" s="111" t="n"/>
       <c r="O41" s="97" t="n"/>
-      <c r="Q41" s="146" t="inlineStr">
+      <c r="Q41" s="145" t="inlineStr">
         <is>
           <t>6) Full source index (all clickable)</t>
         </is>
@@ -12961,20 +12973,20 @@
       <c r="F42" s="97" t="n"/>
       <c r="G42" s="97" t="n"/>
       <c r="H42" s="97" t="n"/>
-      <c r="N42" s="129" t="inlineStr">
+      <c r="N42" s="128" t="inlineStr">
         <is>
           <t>This file is for educational purposes only. E&amp;OE</t>
         </is>
       </c>
       <c r="O42" s="97" t="n"/>
-      <c r="Q42" s="191" t="inlineStr">
+      <c r="Q42" s="190" t="inlineStr">
         <is>
           <t>SEC 10-K FY2025</t>
         </is>
       </c>
-      <c r="R42" s="215" t="n"/>
-      <c r="S42" s="216" t="n"/>
-      <c r="T42" s="189" t="inlineStr">
+      <c r="R42" s="213" t="n"/>
+      <c r="S42" s="214" t="n"/>
+      <c r="T42" s="188" t="inlineStr">
         <is>
           <t>Tax 18.8%, IS/BS/CF, senior notes</t>
         </is>
@@ -12995,14 +13007,14 @@
       <c r="H43" s="97" t="n"/>
       <c r="N43" s="69" t="n"/>
       <c r="O43" s="97" t="n"/>
-      <c r="Q43" s="191" t="inlineStr">
+      <c r="Q43" s="190" t="inlineStr">
         <is>
           <t>SEC 10-Q Q3 FY2026</t>
         </is>
       </c>
-      <c r="R43" s="215" t="n"/>
-      <c r="S43" s="216" t="n"/>
-      <c r="T43" s="189" t="inlineStr">
+      <c r="R43" s="213" t="n"/>
+      <c r="S43" s="214" t="n"/>
+      <c r="T43" s="188" t="inlineStr">
         <is>
           <t>Debt $5,582M, cash+mkt secs net-debt bridge</t>
         </is>
@@ -13010,7 +13022,7 @@
     </row>
     <row r="44" ht="16" customHeight="1">
       <c r="A44" s="97" t="n"/>
-      <c r="B44" s="130" t="inlineStr">
+      <c r="B44" s="129" t="inlineStr">
         <is>
           <t>There are two ways to find NWC:</t>
         </is>
@@ -13023,14 +13035,14 @@
       <c r="H44" s="97" t="n"/>
       <c r="N44" s="69" t="n"/>
       <c r="O44" s="97" t="n"/>
-      <c r="Q44" s="191" t="inlineStr">
+      <c r="Q44" s="190" t="inlineStr">
         <is>
           <t>SEC 8-K 6.250% notes</t>
         </is>
       </c>
-      <c r="R44" s="215" t="n"/>
-      <c r="S44" s="216" t="n"/>
-      <c r="T44" s="189" t="inlineStr">
+      <c r="R44" s="213" t="n"/>
+      <c r="S44" s="214" t="n"/>
+      <c r="T44" s="188" t="inlineStr">
         <is>
           <t>Pre-tax Rd coupon 6.250% due 2034</t>
         </is>
@@ -13038,7 +13050,7 @@
     </row>
     <row r="45" ht="16" customHeight="1">
       <c r="A45" s="97" t="n"/>
-      <c r="B45" s="130" t="inlineStr">
+      <c r="B45" s="129" t="inlineStr">
         <is>
           <t>1. NWC = Current Assets (less cash) - Current Liabilities (less debt)</t>
         </is>
@@ -13051,14 +13063,14 @@
       <c r="H45" s="97" t="n"/>
       <c r="N45" s="69" t="n"/>
       <c r="O45" s="97" t="n"/>
-      <c r="Q45" s="191" t="inlineStr">
+      <c r="Q45" s="190" t="inlineStr">
         <is>
           <t>SEC EX-99.1 pricing</t>
         </is>
       </c>
-      <c r="R45" s="215" t="n"/>
-      <c r="S45" s="216" t="n"/>
-      <c r="T45" s="189" t="inlineStr">
+      <c r="R45" s="213" t="n"/>
+      <c r="S45" s="214" t="n"/>
+      <c r="T45" s="188" t="inlineStr">
         <is>
           <t>Notes priced at par / offering terms</t>
         </is>
@@ -13066,7 +13078,7 @@
     </row>
     <row r="46" ht="16" customHeight="1">
       <c r="A46" s="97" t="n"/>
-      <c r="B46" s="130" t="inlineStr">
+      <c r="B46" s="129" t="inlineStr">
         <is>
           <t>2. NWC = Accounts Receivable + Inventory - Accounts Payable</t>
         </is>
@@ -13079,14 +13091,14 @@
       <c r="H46" s="97" t="n"/>
       <c r="N46" s="69" t="n"/>
       <c r="O46" s="97" t="n"/>
-      <c r="Q46" s="191" t="inlineStr">
+      <c r="Q46" s="190" t="inlineStr">
         <is>
           <t>SEC companyfacts XBRL</t>
         </is>
       </c>
-      <c r="R46" s="215" t="n"/>
-      <c r="S46" s="216" t="n"/>
-      <c r="T46" s="189" t="inlineStr">
+      <c r="R46" s="213" t="n"/>
+      <c r="S46" s="214" t="n"/>
+      <c r="T46" s="188" t="inlineStr">
         <is>
           <t>Pipeline data source (CIK 0000814547)</t>
         </is>
@@ -13103,14 +13115,14 @@
       <c r="H47" s="97" t="n"/>
       <c r="N47" s="69" t="n"/>
       <c r="O47" s="97" t="n"/>
-      <c r="Q47" s="191" t="inlineStr">
+      <c r="Q47" s="190" t="inlineStr">
         <is>
           <t>FRED DGS10</t>
         </is>
       </c>
-      <c r="R47" s="215" t="n"/>
-      <c r="S47" s="216" t="n"/>
-      <c r="T47" s="189" t="inlineStr">
+      <c r="R47" s="213" t="n"/>
+      <c r="S47" s="214" t="n"/>
+      <c r="T47" s="188" t="inlineStr">
         <is>
           <t>Risk-free rate (US 10Y)</t>
         </is>
@@ -13125,20 +13137,20 @@
       <c r="F48" s="97" t="n"/>
       <c r="G48" s="97" t="n"/>
       <c r="H48" s="97" t="n"/>
-      <c r="N48" s="131" t="inlineStr">
+      <c r="N48" s="130" t="inlineStr">
         <is>
           <t xml:space="preserve">Corporate Finance Institute® </t>
         </is>
       </c>
       <c r="O48" s="97" t="n"/>
-      <c r="Q48" s="191" t="inlineStr">
+      <c r="Q48" s="190" t="inlineStr">
         <is>
           <t>US Treasury yield curve</t>
         </is>
       </c>
-      <c r="R48" s="215" t="n"/>
-      <c r="S48" s="216" t="n"/>
-      <c r="T48" s="189" t="inlineStr">
+      <c r="R48" s="213" t="n"/>
+      <c r="S48" s="214" t="n"/>
+      <c r="T48" s="188" t="inlineStr">
         <is>
           <t>Official daily par yields</t>
         </is>
@@ -13153,20 +13165,20 @@
       <c r="F49" s="97" t="n"/>
       <c r="G49" s="97" t="n"/>
       <c r="H49" s="97" t="n"/>
-      <c r="N49" s="132" t="inlineStr">
+      <c r="N49" s="131" t="inlineStr">
         <is>
           <t>https://corporatefinanceinstitute.com/</t>
         </is>
       </c>
       <c r="O49" s="97" t="n"/>
-      <c r="Q49" s="191" t="inlineStr">
+      <c r="Q49" s="190" t="inlineStr">
         <is>
           <t>Damodaran Implied ERP</t>
         </is>
       </c>
-      <c r="R49" s="215" t="n"/>
-      <c r="S49" s="216" t="n"/>
-      <c r="T49" s="189" t="inlineStr">
+      <c r="R49" s="213" t="n"/>
+      <c r="S49" s="214" t="n"/>
+      <c r="T49" s="188" t="inlineStr">
         <is>
           <t>Equity risk premium</t>
         </is>
@@ -13182,14 +13194,14 @@
       <c r="G50" s="97" t="n"/>
       <c r="H50" s="97" t="n"/>
       <c r="O50" s="97" t="n"/>
-      <c r="Q50" s="191" t="inlineStr">
+      <c r="Q50" s="190" t="inlineStr">
         <is>
           <t>Damodaran histimpl</t>
         </is>
       </c>
-      <c r="R50" s="215" t="n"/>
-      <c r="S50" s="216" t="n"/>
-      <c r="T50" s="189" t="inlineStr">
+      <c r="R50" s="213" t="n"/>
+      <c r="S50" s="214" t="n"/>
+      <c r="T50" s="188" t="inlineStr">
         <is>
           <t>Historical implied ERP table</t>
         </is>
@@ -13206,14 +13218,14 @@
       <c r="H51" s="97" t="n"/>
       <c r="M51" s="97" t="n"/>
       <c r="O51" s="97" t="n"/>
-      <c r="Q51" s="191" t="inlineStr">
+      <c r="Q51" s="190" t="inlineStr">
         <is>
           <t>Yahoo FICO stats</t>
         </is>
       </c>
-      <c r="R51" s="215" t="n"/>
-      <c r="S51" s="216" t="n"/>
-      <c r="T51" s="189" t="inlineStr">
+      <c r="R51" s="213" t="n"/>
+      <c r="S51" s="214" t="n"/>
+      <c r="T51" s="188" t="inlineStr">
         <is>
           <t>Beta 5Y monthly + shares out</t>
         </is>

--- a/FICO/output/FICO_Completed_Model.xlsx
+++ b/FICO/output/FICO_Completed_Model.xlsx
@@ -357,6 +357,12 @@
     </font>
     <font>
       <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00595959"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="001F4E79"/>
     </font>
@@ -368,12 +374,6 @@
       <name val="Consolas"/>
       <color rgb="00000000"/>
       <sz val="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <i val="1"/>
-      <color rgb="00595959"/>
-      <sz val="8"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -661,7 +661,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="215">
+  <cellXfs count="216">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="1"/>
@@ -829,6 +829,7 @@
     <xf numFmtId="9" fontId="32" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="164" fontId="39" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="171" fontId="32" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
@@ -846,7 +847,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="39" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="40" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="14" fontId="35" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="14" fontId="38" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="35" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -895,22 +896,22 @@
     <xf numFmtId="0" fontId="59" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="40" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="1" fontId="41" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="1" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="1" fontId="13" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="177" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="40" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="44" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="45" fillId="10" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="42" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="164" fontId="39" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="40" fillId="8" borderId="5" pivotButton="0" quotePrefix="0" xfId="2"/>
+    <xf numFmtId="166" fontId="41" fillId="8" borderId="5" pivotButton="0" quotePrefix="0" xfId="2"/>
     <xf numFmtId="0" fontId="46" fillId="11" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -923,37 +924,37 @@
     <xf numFmtId="166" fontId="38" fillId="7" borderId="5" pivotButton="0" quotePrefix="0" xfId="2"/>
     <xf numFmtId="177" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="166" fontId="38" fillId="7" borderId="5" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="40" fillId="8" borderId="5" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="177" fontId="41" fillId="8" borderId="5" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="177" fontId="38" fillId="7" borderId="5" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="166" fontId="40" fillId="8" borderId="5" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="164" fontId="41" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="177" fontId="40" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="164" fontId="41" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="166" fontId="41" fillId="8" borderId="5" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="164" fontId="42" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="177" fontId="41" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="164" fontId="42" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="177" fontId="6" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="41" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="177" fontId="40" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="42" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="177" fontId="41" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="177" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="164" fontId="41" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="164" fontId="42" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="177" fontId="6" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="177" fontId="38" fillId="7" borderId="2" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="177" fontId="6" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="177" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="177" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="177" fontId="38" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="177" fontId="40" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="177" fontId="41" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="40" fillId="8" borderId="2" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="177" fontId="40" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="177" fontId="41" fillId="8" borderId="2" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="177" fontId="41" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="177" fontId="38" fillId="7" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="49" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="50" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="39" fillId="9" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="40" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="40" fillId="9" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="41" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="51" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -967,26 +968,26 @@
     <xf numFmtId="0" fontId="38" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="40" fillId="8" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="41" fillId="8" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="179" fontId="40" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="179" fontId="41" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="40" fillId="8" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="41" fillId="8" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="178" fontId="32" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="38" fillId="7" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="176" fontId="40" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="176" fontId="41" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="40" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="41" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="40" fillId="8" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="41" fillId="8" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="177" fontId="38" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="31" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="177" fontId="35" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1806,7 +1807,6 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>vengeanceaiUSCMODEL7</author>
-    <author>vengeanceaiUSCMODEL6</author>
   </authors>
   <commentList>
     <comment ref="B2" authorId="0" shapeId="0">
@@ -1905,7 +1905,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="B7" authorId="1" shapeId="0">
+    <comment ref="B7" authorId="0" shapeId="0">
       <text>
         <t>Revenue Growth
 HOW: Yellow POLICY input: 27% / 16% / 13% / 10% / 7%.
@@ -1914,7 +1914,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454726000031/exhibit991erq32026.htm</t>
       </text>
     </comment>
-    <comment ref="J7" authorId="1" shapeId="0">
+    <comment ref="J7" authorId="0" shapeId="0">
       <text>
         <t>Revenue Growth
 HOW: Yellow POLICY input: 27% / 16% / 13% / 10% / 7%.
@@ -1923,7 +1923,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454726000031/exhibit991erq32026.htm</t>
       </text>
     </comment>
-    <comment ref="K7" authorId="1" shapeId="0">
+    <comment ref="K7" authorId="0" shapeId="0">
       <text>
         <t>Revenue Growth
 HOW: Yellow POLICY input: 27% / 16% / 13% / 10% / 7%.
@@ -1932,7 +1932,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454726000031/exhibit991erq32026.htm</t>
       </text>
     </comment>
-    <comment ref="L7" authorId="1" shapeId="0">
+    <comment ref="L7" authorId="0" shapeId="0">
       <text>
         <t>Revenue Growth
 HOW: Yellow POLICY input: 27% / 16% / 13% / 10% / 7%.
@@ -1941,7 +1941,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454726000031/exhibit991erq32026.htm</t>
       </text>
     </comment>
-    <comment ref="M7" authorId="1" shapeId="0">
+    <comment ref="M7" authorId="0" shapeId="0">
       <text>
         <t>Revenue Growth
 HOW: Yellow POLICY input: 27% / 16% / 13% / 10% / 7%.
@@ -1950,7 +1950,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454726000031/exhibit991erq32026.htm</t>
       </text>
     </comment>
-    <comment ref="N7" authorId="1" shapeId="0">
+    <comment ref="N7" authorId="0" shapeId="0">
       <text>
         <t>Revenue Growth
 HOW: Yellow POLICY input: 27% / 16% / 13% / 10% / 7%.
@@ -1959,7 +1959,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454726000031/exhibit991erq32026.htm</t>
       </text>
     </comment>
-    <comment ref="U7" authorId="1" shapeId="0">
+    <comment ref="U7" authorId="0" shapeId="0">
       <text>
         <t>Revenue Growth
 HOW: Yellow POLICY input: 27% / 16% / 13% / 10% / 7%.
@@ -1968,7 +1968,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454726000031/exhibit991erq32026.htm</t>
       </text>
     </comment>
-    <comment ref="B8" authorId="1" shapeId="0">
+    <comment ref="B8" authorId="0" shapeId="0">
       <text>
         <t>COGS % of Revenue
 HOW: Excel equation: I25/I24 (FY25 COGS ÷ FY25 Revenue) held flat.
@@ -1977,7 +1977,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="J8" authorId="1" shapeId="0">
+    <comment ref="J8" authorId="0" shapeId="0">
       <text>
         <t>COGS % of Revenue
 HOW: Excel equation: I25/I24 (FY25 COGS ÷ FY25 Revenue) held flat.
@@ -1986,7 +1986,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="K8" authorId="1" shapeId="0">
+    <comment ref="K8" authorId="0" shapeId="0">
       <text>
         <t>COGS % of Revenue
 HOW: Excel equation: I25/I24 (FY25 COGS ÷ FY25 Revenue) held flat.
@@ -1995,7 +1995,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="L8" authorId="1" shapeId="0">
+    <comment ref="L8" authorId="0" shapeId="0">
       <text>
         <t>COGS % of Revenue
 HOW: Excel equation: I25/I24 (FY25 COGS ÷ FY25 Revenue) held flat.
@@ -2004,7 +2004,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="M8" authorId="1" shapeId="0">
+    <comment ref="M8" authorId="0" shapeId="0">
       <text>
         <t>COGS % of Revenue
 HOW: Excel equation: I25/I24 (FY25 COGS ÷ FY25 Revenue) held flat.
@@ -2013,7 +2013,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="N8" authorId="1" shapeId="0">
+    <comment ref="N8" authorId="0" shapeId="0">
       <text>
         <t>COGS % of Revenue
 HOW: Excel equation: I25/I24 (FY25 COGS ÷ FY25 Revenue) held flat.
@@ -2022,7 +2022,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="U8" authorId="1" shapeId="0">
+    <comment ref="U8" authorId="0" shapeId="0">
       <text>
         <t>COGS % of Revenue
 HOW: Excel equation: I25/I24 (FY25 COGS ÷ FY25 Revenue) held flat.
@@ -2031,7 +2031,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="B9" authorId="1" shapeId="0">
+    <comment ref="B9" authorId="0" shapeId="0">
       <text>
         <t>SG&amp;A % of Revenue
 HOW: Equation: MAX(15%, (I28 − 10,922)/I24 − 75bps × year). Strips FY25 restructuring; then −0.75% of sales each year.
@@ -2040,7 +2040,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="J9" authorId="1" shapeId="0">
+    <comment ref="J9" authorId="0" shapeId="0">
       <text>
         <t>SG&amp;A % of Revenue
 HOW: Equation: MAX(15%, (I28 − 10,922)/I24 − 75bps × year). Strips FY25 restructuring; then −0.75% of sales each year.
@@ -2049,7 +2049,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="K9" authorId="1" shapeId="0">
+    <comment ref="K9" authorId="0" shapeId="0">
       <text>
         <t>SG&amp;A % of Revenue
 HOW: Equation: MAX(15%, (I28 − 10,922)/I24 − 75bps × year). Strips FY25 restructuring; then −0.75% of sales each year.
@@ -2058,7 +2058,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="L9" authorId="1" shapeId="0">
+    <comment ref="L9" authorId="0" shapeId="0">
       <text>
         <t>SG&amp;A % of Revenue
 HOW: Equation: MAX(15%, (I28 − 10,922)/I24 − 75bps × year). Strips FY25 restructuring; then −0.75% of sales each year.
@@ -2067,7 +2067,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="M9" authorId="1" shapeId="0">
+    <comment ref="M9" authorId="0" shapeId="0">
       <text>
         <t>SG&amp;A % of Revenue
 HOW: Equation: MAX(15%, (I28 − 10,922)/I24 − 75bps × year). Strips FY25 restructuring; then −0.75% of sales each year.
@@ -2076,7 +2076,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="N9" authorId="1" shapeId="0">
+    <comment ref="N9" authorId="0" shapeId="0">
       <text>
         <t>SG&amp;A % of Revenue
 HOW: Equation: MAX(15%, (I28 − 10,922)/I24 − 75bps × year). Strips FY25 restructuring; then −0.75% of sales each year.
@@ -2085,7 +2085,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="U9" authorId="1" shapeId="0">
+    <comment ref="U9" authorId="0" shapeId="0">
       <text>
         <t>SG&amp;A % of Revenue
 HOW: Equation: MAX(15%, (I28 − 10,922)/I24 − 75bps × year). Strips FY25 restructuring; then −0.75% of sales each year.
@@ -2094,7 +2094,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="B10" authorId="1" shapeId="0">
+    <comment ref="B10" authorId="0" shapeId="0">
       <text>
         <t>R&amp;D % of Revenue
 HOW: Excel equation: I29/I24 held flat (~9.46%).
@@ -2103,7 +2103,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="J10" authorId="1" shapeId="0">
+    <comment ref="J10" authorId="0" shapeId="0">
       <text>
         <t>R&amp;D % of Revenue
 HOW: Excel equation: I29/I24 held flat (~9.46%).
@@ -2112,7 +2112,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="K10" authorId="1" shapeId="0">
+    <comment ref="K10" authorId="0" shapeId="0">
       <text>
         <t>R&amp;D % of Revenue
 HOW: Excel equation: I29/I24 held flat (~9.46%).
@@ -2121,7 +2121,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="L10" authorId="1" shapeId="0">
+    <comment ref="L10" authorId="0" shapeId="0">
       <text>
         <t>R&amp;D % of Revenue
 HOW: Excel equation: I29/I24 held flat (~9.46%).
@@ -2130,7 +2130,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="M10" authorId="1" shapeId="0">
+    <comment ref="M10" authorId="0" shapeId="0">
       <text>
         <t>R&amp;D % of Revenue
 HOW: Excel equation: I29/I24 held flat (~9.46%).
@@ -2139,7 +2139,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="N10" authorId="1" shapeId="0">
+    <comment ref="N10" authorId="0" shapeId="0">
       <text>
         <t>R&amp;D % of Revenue
 HOW: Excel equation: I29/I24 held flat (~9.46%).
@@ -2148,7 +2148,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="U10" authorId="1" shapeId="0">
+    <comment ref="U10" authorId="0" shapeId="0">
       <text>
         <t>R&amp;D % of Revenue
 HOW: Excel equation: I29/I24 held flat (~9.46%).
@@ -2157,7 +2157,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="B11" authorId="1" shapeId="0">
+    <comment ref="B11" authorId="0" shapeId="0">
       <text>
         <t>D&amp;A % of Avg PP&amp;E
 HOW: Rate = I30/I44 (FY25 DA ÷ FY25 PPE). Forecast DA$ = ((Open + Open+CapEx)/2) × rate.
@@ -2166,7 +2166,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="J11" authorId="1" shapeId="0">
+    <comment ref="J11" authorId="0" shapeId="0">
       <text>
         <t>D&amp;A % of Avg PP&amp;E
 HOW: Rate = I30/I44 (FY25 DA ÷ FY25 PPE). Forecast DA$ = ((Open + Open+CapEx)/2) × rate.
@@ -2175,7 +2175,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="K11" authorId="1" shapeId="0">
+    <comment ref="K11" authorId="0" shapeId="0">
       <text>
         <t>D&amp;A % of Avg PP&amp;E
 HOW: Rate = I30/I44 (FY25 DA ÷ FY25 PPE). Forecast DA$ = ((Open + Open+CapEx)/2) × rate.
@@ -2184,7 +2184,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="L11" authorId="1" shapeId="0">
+    <comment ref="L11" authorId="0" shapeId="0">
       <text>
         <t>D&amp;A % of Avg PP&amp;E
 HOW: Rate = I30/I44 (FY25 DA ÷ FY25 PPE). Forecast DA$ = ((Open + Open+CapEx)/2) × rate.
@@ -2193,7 +2193,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="M11" authorId="1" shapeId="0">
+    <comment ref="M11" authorId="0" shapeId="0">
       <text>
         <t>D&amp;A % of Avg PP&amp;E
 HOW: Rate = I30/I44 (FY25 DA ÷ FY25 PPE). Forecast DA$ = ((Open + Open+CapEx)/2) × rate.
@@ -2202,7 +2202,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="N11" authorId="1" shapeId="0">
+    <comment ref="N11" authorId="0" shapeId="0">
       <text>
         <t>D&amp;A % of Avg PP&amp;E
 HOW: Rate = I30/I44 (FY25 DA ÷ FY25 PPE). Forecast DA$ = ((Open + Open+CapEx)/2) × rate.
@@ -2211,7 +2211,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="U11" authorId="1" shapeId="0">
+    <comment ref="U11" authorId="0" shapeId="0">
       <text>
         <t>D&amp;A % of Avg PP&amp;E
 HOW: Rate = I30/I44 (FY25 DA ÷ FY25 PPE). Forecast DA$ = ((Open + Open+CapEx)/2) × rate.
@@ -2220,7 +2220,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="B12" authorId="1" shapeId="0">
+    <comment ref="B12" authorId="0" shapeId="0">
       <text>
         <t>Interest % of Debt Open
 HOW: Excel equation: I101/I98 (FY25 interest ÷ FY25 opening debt in schedule).
@@ -2229,7 +2229,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="J12" authorId="1" shapeId="0">
+    <comment ref="J12" authorId="0" shapeId="0">
       <text>
         <t>Interest % of Debt Open
 HOW: Excel equation: I101/I98 (FY25 interest ÷ FY25 opening debt in schedule).
@@ -2238,7 +2238,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="K12" authorId="1" shapeId="0">
+    <comment ref="K12" authorId="0" shapeId="0">
       <text>
         <t>Interest % of Debt Open
 HOW: Excel equation: I101/I98 (FY25 interest ÷ FY25 opening debt in schedule).
@@ -2247,7 +2247,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="L12" authorId="1" shapeId="0">
+    <comment ref="L12" authorId="0" shapeId="0">
       <text>
         <t>Interest % of Debt Open
 HOW: Excel equation: I101/I98 (FY25 interest ÷ FY25 opening debt in schedule).
@@ -2256,7 +2256,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="M12" authorId="1" shapeId="0">
+    <comment ref="M12" authorId="0" shapeId="0">
       <text>
         <t>Interest % of Debt Open
 HOW: Excel equation: I101/I98 (FY25 interest ÷ FY25 opening debt in schedule).
@@ -2265,7 +2265,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="N12" authorId="1" shapeId="0">
+    <comment ref="N12" authorId="0" shapeId="0">
       <text>
         <t>Interest % of Debt Open
 HOW: Excel equation: I101/I98 (FY25 interest ÷ FY25 opening debt in schedule).
@@ -2274,7 +2274,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="U12" authorId="1" shapeId="0">
+    <comment ref="U12" authorId="0" shapeId="0">
       <text>
         <t>Interest % of Debt Open
 HOW: Excel equation: I101/I98 (FY25 interest ÷ FY25 opening debt in schedule).
@@ -2283,7 +2283,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="B13" authorId="1" shapeId="0">
+    <comment ref="B13" authorId="0" shapeId="0">
       <text>
         <t>Tax Rate (% of EBT)
 HOW: Excel equation: I35/I33 (FY25 tax ÷ simplified FY25 EBT in this template).
@@ -2292,7 +2292,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="J13" authorId="1" shapeId="0">
+    <comment ref="J13" authorId="0" shapeId="0">
       <text>
         <t>Tax Rate (% of EBT)
 HOW: Excel equation: I35/I33 (FY25 tax ÷ simplified FY25 EBT in this template).
@@ -2301,7 +2301,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="K13" authorId="1" shapeId="0">
+    <comment ref="K13" authorId="0" shapeId="0">
       <text>
         <t>Tax Rate (% of EBT)
 HOW: Excel equation: I35/I33 (FY25 tax ÷ simplified FY25 EBT in this template).
@@ -2310,7 +2310,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="L13" authorId="1" shapeId="0">
+    <comment ref="L13" authorId="0" shapeId="0">
       <text>
         <t>Tax Rate (% of EBT)
 HOW: Excel equation: I35/I33 (FY25 tax ÷ simplified FY25 EBT in this template).
@@ -2319,7 +2319,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="M13" authorId="1" shapeId="0">
+    <comment ref="M13" authorId="0" shapeId="0">
       <text>
         <t>Tax Rate (% of EBT)
 HOW: Excel equation: I35/I33 (FY25 tax ÷ simplified FY25 EBT in this template).
@@ -2328,7 +2328,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="N13" authorId="1" shapeId="0">
+    <comment ref="N13" authorId="0" shapeId="0">
       <text>
         <t>Tax Rate (% of EBT)
 HOW: Excel equation: I35/I33 (FY25 tax ÷ simplified FY25 EBT in this template).
@@ -2337,7 +2337,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="U13" authorId="1" shapeId="0">
+    <comment ref="U13" authorId="0" shapeId="0">
       <text>
         <t>Tax Rate (% of EBT)
 HOW: Excel equation: I35/I33 (FY25 tax ÷ simplified FY25 EBT in this template).
@@ -2346,7 +2346,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="B15" authorId="1" shapeId="0">
+    <comment ref="B15" authorId="0" shapeId="0">
       <text>
         <t>Operating NWC % of Revenue
 HOW: Equation: fade FY25 op. NWC/Sales → 3% steady (weights 70/50/30/15/0).
@@ -2355,7 +2355,7 @@
 LINK: https://data.sec.gov/api/xbrl/companyfacts/CIK0000814547.json</t>
       </text>
     </comment>
-    <comment ref="J15" authorId="1" shapeId="0">
+    <comment ref="J15" authorId="0" shapeId="0">
       <text>
         <t>Operating NWC % of Revenue
 HOW: Equation: fade FY25 op. NWC/Sales → 3% steady (weights 70/50/30/15/0).
@@ -2364,7 +2364,7 @@
 LINK: https://data.sec.gov/api/xbrl/companyfacts/CIK0000814547.json</t>
       </text>
     </comment>
-    <comment ref="K15" authorId="1" shapeId="0">
+    <comment ref="K15" authorId="0" shapeId="0">
       <text>
         <t>Operating NWC % of Revenue
 HOW: Equation: fade FY25 op. NWC/Sales → 3% steady (weights 70/50/30/15/0).
@@ -2373,7 +2373,7 @@
 LINK: https://data.sec.gov/api/xbrl/companyfacts/CIK0000814547.json</t>
       </text>
     </comment>
-    <comment ref="L15" authorId="1" shapeId="0">
+    <comment ref="L15" authorId="0" shapeId="0">
       <text>
         <t>Operating NWC % of Revenue
 HOW: Equation: fade FY25 op. NWC/Sales → 3% steady (weights 70/50/30/15/0).
@@ -2382,7 +2382,7 @@
 LINK: https://data.sec.gov/api/xbrl/companyfacts/CIK0000814547.json</t>
       </text>
     </comment>
-    <comment ref="M15" authorId="1" shapeId="0">
+    <comment ref="M15" authorId="0" shapeId="0">
       <text>
         <t>Operating NWC % of Revenue
 HOW: Equation: fade FY25 op. NWC/Sales → 3% steady (weights 70/50/30/15/0).
@@ -2391,7 +2391,7 @@
 LINK: https://data.sec.gov/api/xbrl/companyfacts/CIK0000814547.json</t>
       </text>
     </comment>
-    <comment ref="N15" authorId="1" shapeId="0">
+    <comment ref="N15" authorId="0" shapeId="0">
       <text>
         <t>Operating NWC % of Revenue
 HOW: Equation: fade FY25 op. NWC/Sales → 3% steady (weights 70/50/30/15/0).
@@ -2400,7 +2400,7 @@
 LINK: https://data.sec.gov/api/xbrl/companyfacts/CIK0000814547.json</t>
       </text>
     </comment>
-    <comment ref="U15" authorId="1" shapeId="0">
+    <comment ref="U15" authorId="0" shapeId="0">
       <text>
         <t>Operating NWC % of Revenue
 HOW: Equation: fade FY25 op. NWC/Sales → 3% steady (weights 70/50/30/15/0).
@@ -2409,7 +2409,7 @@
 LINK: https://data.sec.gov/api/xbrl/companyfacts/CIK0000814547.json</t>
       </text>
     </comment>
-    <comment ref="B16" authorId="1" shapeId="0">
+    <comment ref="B16" authorId="0" shapeId="0">
       <text>
         <t>Inventory (Days)
 HOW: Hard zero — FICO is software / scores; inventory is immaterial.
@@ -2418,7 +2418,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="J16" authorId="1" shapeId="0">
+    <comment ref="J16" authorId="0" shapeId="0">
       <text>
         <t>Inventory (Days)
 HOW: Hard zero — FICO is software / scores; inventory is immaterial.
@@ -2427,7 +2427,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="K16" authorId="1" shapeId="0">
+    <comment ref="K16" authorId="0" shapeId="0">
       <text>
         <t>Inventory (Days)
 HOW: Hard zero — FICO is software / scores; inventory is immaterial.
@@ -2436,7 +2436,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="L16" authorId="1" shapeId="0">
+    <comment ref="L16" authorId="0" shapeId="0">
       <text>
         <t>Inventory (Days)
 HOW: Hard zero — FICO is software / scores; inventory is immaterial.
@@ -2445,7 +2445,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="M16" authorId="1" shapeId="0">
+    <comment ref="M16" authorId="0" shapeId="0">
       <text>
         <t>Inventory (Days)
 HOW: Hard zero — FICO is software / scores; inventory is immaterial.
@@ -2454,7 +2454,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="N16" authorId="1" shapeId="0">
+    <comment ref="N16" authorId="0" shapeId="0">
       <text>
         <t>Inventory (Days)
 HOW: Hard zero — FICO is software / scores; inventory is immaterial.
@@ -2463,7 +2463,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="U16" authorId="1" shapeId="0">
+    <comment ref="U16" authorId="0" shapeId="0">
       <text>
         <t>Inventory (Days)
 HOW: Hard zero — FICO is software / scores; inventory is immaterial.
@@ -2472,7 +2472,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="B17" authorId="1" shapeId="0">
+    <comment ref="B17" authorId="0" shapeId="0">
       <text>
         <t>Accounts Payable (Days)
 HOW: Excel equation: ROUND(I48/I25×365, 0) from FY25.
@@ -2481,7 +2481,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="J17" authorId="1" shapeId="0">
+    <comment ref="J17" authorId="0" shapeId="0">
       <text>
         <t>Accounts Payable (Days)
 HOW: Excel equation: ROUND(I48/I25×365, 0) from FY25.
@@ -2490,7 +2490,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="K17" authorId="1" shapeId="0">
+    <comment ref="K17" authorId="0" shapeId="0">
       <text>
         <t>Accounts Payable (Days)
 HOW: Excel equation: ROUND(I48/I25×365, 0) from FY25.
@@ -2499,7 +2499,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="L17" authorId="1" shapeId="0">
+    <comment ref="L17" authorId="0" shapeId="0">
       <text>
         <t>Accounts Payable (Days)
 HOW: Excel equation: ROUND(I48/I25×365, 0) from FY25.
@@ -2508,7 +2508,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="M17" authorId="1" shapeId="0">
+    <comment ref="M17" authorId="0" shapeId="0">
       <text>
         <t>Accounts Payable (Days)
 HOW: Excel equation: ROUND(I48/I25×365, 0) from FY25.
@@ -2517,7 +2517,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="N17" authorId="1" shapeId="0">
+    <comment ref="N17" authorId="0" shapeId="0">
       <text>
         <t>Accounts Payable (Days)
 HOW: Excel equation: ROUND(I48/I25×365, 0) from FY25.
@@ -2526,7 +2526,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="U17" authorId="1" shapeId="0">
+    <comment ref="U17" authorId="0" shapeId="0">
       <text>
         <t>Accounts Payable (Days)
 HOW: Excel equation: ROUND(I48/I25×365, 0) from FY25.
@@ -2535,7 +2535,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="B18" authorId="1" shapeId="0">
+    <comment ref="B18" authorId="0" shapeId="0">
       <text>
         <t>CapEx % of Revenue
 HOW: Equation: fade from I68/I24 toward 1.0% steady. MODEL7 weights 40%→20%→10%→0%→0% on the peak (faster fade).
@@ -2544,7 +2544,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="J18" authorId="1" shapeId="0">
+    <comment ref="J18" authorId="0" shapeId="0">
       <text>
         <t>CapEx % of Revenue
 HOW: Equation: fade from I68/I24 toward 1.0% steady. MODEL7 weights 40%→20%→10%→0%→0% on the peak (faster fade).
@@ -2553,7 +2553,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="K18" authorId="1" shapeId="0">
+    <comment ref="K18" authorId="0" shapeId="0">
       <text>
         <t>CapEx % of Revenue
 HOW: Equation: fade from I68/I24 toward 1.0% steady. MODEL7 weights 40%→20%→10%→0%→0% on the peak (faster fade).
@@ -2562,7 +2562,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="L18" authorId="1" shapeId="0">
+    <comment ref="L18" authorId="0" shapeId="0">
       <text>
         <t>CapEx % of Revenue
 HOW: Equation: fade from I68/I24 toward 1.0% steady. MODEL7 weights 40%→20%→10%→0%→0% on the peak (faster fade).
@@ -2571,7 +2571,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="M18" authorId="1" shapeId="0">
+    <comment ref="M18" authorId="0" shapeId="0">
       <text>
         <t>CapEx % of Revenue
 HOW: Equation: fade from I68/I24 toward 1.0% steady. MODEL7 weights 40%→20%→10%→0%→0% on the peak (faster fade).
@@ -2580,7 +2580,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="N18" authorId="1" shapeId="0">
+    <comment ref="N18" authorId="0" shapeId="0">
       <text>
         <t>CapEx % of Revenue
 HOW: Equation: fade from I68/I24 toward 1.0% steady. MODEL7 weights 40%→20%→10%→0%→0% on the peak (faster fade).
@@ -2589,7 +2589,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="U18" authorId="1" shapeId="0">
+    <comment ref="U18" authorId="0" shapeId="0">
       <text>
         <t>CapEx % of Revenue
 HOW: Equation: fade from I68/I24 toward 1.0% steady. MODEL7 weights 40%→20%→10%→0%→0% on the peak (faster fade).
@@ -2598,7 +2598,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
       </text>
     </comment>
-    <comment ref="B19" authorId="1" shapeId="0">
+    <comment ref="B19" authorId="0" shapeId="0">
       <text>
         <t>Debt Issuance (Repayment)
 HOW: POLICY input = 0 every year.
@@ -2607,7 +2607,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454726000030/fico-20260630.htm</t>
       </text>
     </comment>
-    <comment ref="J19" authorId="1" shapeId="0">
+    <comment ref="J19" authorId="0" shapeId="0">
       <text>
         <t>Debt Issuance (Repayment)
 HOW: POLICY input = 0 every year.
@@ -2616,7 +2616,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454726000030/fico-20260630.htm</t>
       </text>
     </comment>
-    <comment ref="K19" authorId="1" shapeId="0">
+    <comment ref="K19" authorId="0" shapeId="0">
       <text>
         <t>Debt Issuance (Repayment)
 HOW: POLICY input = 0 every year.
@@ -2625,7 +2625,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454726000030/fico-20260630.htm</t>
       </text>
     </comment>
-    <comment ref="L19" authorId="1" shapeId="0">
+    <comment ref="L19" authorId="0" shapeId="0">
       <text>
         <t>Debt Issuance (Repayment)
 HOW: POLICY input = 0 every year.
@@ -2634,7 +2634,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454726000030/fico-20260630.htm</t>
       </text>
     </comment>
-    <comment ref="M19" authorId="1" shapeId="0">
+    <comment ref="M19" authorId="0" shapeId="0">
       <text>
         <t>Debt Issuance (Repayment)
 HOW: POLICY input = 0 every year.
@@ -2643,7 +2643,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454726000030/fico-20260630.htm</t>
       </text>
     </comment>
-    <comment ref="N19" authorId="1" shapeId="0">
+    <comment ref="N19" authorId="0" shapeId="0">
       <text>
         <t>Debt Issuance (Repayment)
 HOW: POLICY input = 0 every year.
@@ -2652,7 +2652,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454726000030/fico-20260630.htm</t>
       </text>
     </comment>
-    <comment ref="U19" authorId="1" shapeId="0">
+    <comment ref="U19" authorId="0" shapeId="0">
       <text>
         <t>Debt Issuance (Repayment)
 HOW: POLICY input = 0 every year.
@@ -2661,7 +2661,7 @@
 LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454726000030/fico-20260630.htm</t>
       </text>
     </comment>
-    <comment ref="B20" authorId="1" shapeId="0">
+    <comment ref="B20" authorId="0" shapeId="0">
       <text>
         <t>Equity Issued (Repaid)
 HOW: POLICY input = 0 every year.
@@ -2670,7 +2670,7 @@
 LINK: https://pages.stern.nyu.edu/~adamodar/New_Home_Page/datafile/histfcff.html</t>
       </text>
     </comment>
-    <comment ref="J20" authorId="1" shapeId="0">
+    <comment ref="J20" authorId="0" shapeId="0">
       <text>
         <t>Equity Issued (Repaid)
 HOW: POLICY input = 0 every year.
@@ -2679,7 +2679,7 @@
 LINK: https://pages.stern.nyu.edu/~adamodar/New_Home_Page/datafile/histfcff.html</t>
       </text>
     </comment>
-    <comment ref="K20" authorId="1" shapeId="0">
+    <comment ref="K20" authorId="0" shapeId="0">
       <text>
         <t>Equity Issued (Repaid)
 HOW: POLICY input = 0 every year.
@@ -2688,7 +2688,7 @@
 LINK: https://pages.stern.nyu.edu/~adamodar/New_Home_Page/datafile/histfcff.html</t>
       </text>
     </comment>
-    <comment ref="L20" authorId="1" shapeId="0">
+    <comment ref="L20" authorId="0" shapeId="0">
       <text>
         <t>Equity Issued (Repaid)
 HOW: POLICY input = 0 every year.
@@ -2697,7 +2697,7 @@
 LINK: https://pages.stern.nyu.edu/~adamodar/New_Home_Page/datafile/histfcff.html</t>
       </text>
     </comment>
-    <comment ref="M20" authorId="1" shapeId="0">
+    <comment ref="M20" authorId="0" shapeId="0">
       <text>
         <t>Equity Issued (Repaid)
 HOW: POLICY input = 0 every year.
@@ -2706,7 +2706,7 @@
 LINK: https://pages.stern.nyu.edu/~adamodar/New_Home_Page/datafile/histfcff.html</t>
       </text>
     </comment>
-    <comment ref="N20" authorId="1" shapeId="0">
+    <comment ref="N20" authorId="0" shapeId="0">
       <text>
         <t>Equity Issued (Repaid)
 HOW: POLICY input = 0 every year.
@@ -2715,7 +2715,7 @@
 LINK: https://pages.stern.nyu.edu/~adamodar/New_Home_Page/datafile/histfcff.html</t>
       </text>
     </comment>
-    <comment ref="U20" authorId="1" shapeId="0">
+    <comment ref="U20" authorId="0" shapeId="0">
       <text>
         <t>Equity Issued (Repaid)
 HOW: POLICY input = 0 every year.
@@ -5187,6 +5187,14 @@
         <t>WACC
 FORMULA: =R15
 WHY: Pulls the live CAPM WACC from the baked CAPM block so discounting uses researched Ke/Rd.</t>
+      </text>
+    </comment>
+    <comment ref="D8" authorId="0" shapeId="0">
+      <text>
+        <t>Exit EV/EBITDA multiple (primary)
+HOW: Yellow POLICY input in D8 = 16.0x; TV = Year-5 EBITDA × D8.
+WHY: Not from an SEC filing. MODEL7 audit required moving off 25x (which implied ~12.8x under Gordon) to a blended 15x–18x normalized exit. Midpoint 16x is the base case; 25x is bull sensitivity only (M21).
+SOURCE: Model policy / audit (15x–18x blend) — judgment, not a market quote.</t>
       </text>
     </comment>
     <comment ref="R15" authorId="0" shapeId="0">
@@ -6282,7 +6290,7 @@
         </is>
       </c>
       <c r="D24" s="89" t="n"/>
-      <c r="E24" s="132" t="inlineStr">
+      <c r="E24" s="133" t="inlineStr">
         <is>
           <t>vengeanceaiUSCMODEL7 — SOURCE INDEX (click any link)</t>
         </is>
@@ -6304,7 +6312,7 @@
         </is>
       </c>
       <c r="D25" s="91" t="n"/>
-      <c r="E25" s="133" t="inlineStr">
+      <c r="E25" s="134" t="inlineStr">
         <is>
           <t>Every assumption / WACC / filing source used in this workbook. Same links appear on 3-statement col U/V and DCF col U/V.</t>
         </is>
@@ -6326,17 +6334,17 @@
         </is>
       </c>
       <c r="D26" s="91" t="n"/>
-      <c r="E26" s="134" t="inlineStr">
+      <c r="E26" s="135" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="F26" s="134" t="inlineStr">
+      <c r="F26" s="135" t="inlineStr">
         <is>
           <t>Clickable link</t>
         </is>
       </c>
-      <c r="G26" s="134" t="inlineStr">
+      <c r="G26" s="135" t="inlineStr">
         <is>
           <t>URL</t>
         </is>
@@ -6358,17 +6366,17 @@
         </is>
       </c>
       <c r="D27" s="91" t="n"/>
-      <c r="E27" s="135" t="inlineStr">
+      <c r="E27" s="136" t="inlineStr">
         <is>
           <t>10-K FY2025</t>
         </is>
       </c>
-      <c r="F27" s="136" t="inlineStr">
+      <c r="F27" s="137" t="inlineStr">
         <is>
           <t>10-K FY2025</t>
         </is>
       </c>
-      <c r="G27" s="136" t="inlineStr">
+      <c r="G27" s="137" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
         </is>
@@ -6386,17 +6394,17 @@
       <c r="B28" s="90" t="n"/>
       <c r="C28" s="91" t="n"/>
       <c r="D28" s="91" t="n"/>
-      <c r="E28" s="135" t="inlineStr">
+      <c r="E28" s="136" t="inlineStr">
         <is>
           <t>10-Q Q3 FY2026</t>
         </is>
       </c>
-      <c r="F28" s="136" t="inlineStr">
+      <c r="F28" s="137" t="inlineStr">
         <is>
           <t>10-Q Q3 FY2026</t>
         </is>
       </c>
-      <c r="G28" s="136" t="inlineStr">
+      <c r="G28" s="137" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/814547/000081454726000030/fico-20260630.htm</t>
         </is>
@@ -6414,17 +6422,17 @@
       <c r="B29" s="90" t="n"/>
       <c r="C29" s="90" t="n"/>
       <c r="D29" s="90" t="n"/>
-      <c r="E29" s="137" t="inlineStr">
+      <c r="E29" s="138" t="inlineStr">
         <is>
           <t>8-K 6.250% notes</t>
         </is>
       </c>
-      <c r="F29" s="138" t="inlineStr">
+      <c r="F29" s="139" t="inlineStr">
         <is>
           <t>8-K 6.250% notes</t>
         </is>
       </c>
-      <c r="G29" s="138" t="inlineStr">
+      <c r="G29" s="139" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/814547/000119312526117936/d56220d8k.htm</t>
         </is>
@@ -6439,170 +6447,170 @@
       <c r="O29" s="90" t="n"/>
     </row>
     <row r="30" ht="19.5" customHeight="1">
-      <c r="E30" s="139" t="inlineStr">
+      <c r="E30" s="140" t="inlineStr">
         <is>
           <t>Damodaran ERP</t>
         </is>
       </c>
-      <c r="F30" s="140" t="inlineStr">
+      <c r="F30" s="141" t="inlineStr">
         <is>
           <t>Damodaran ERP</t>
         </is>
       </c>
-      <c r="G30" s="140" t="inlineStr">
+      <c r="G30" s="141" t="inlineStr">
         <is>
           <t>https://pages.stern.nyu.edu/adamodar/New_Home_Page/home.htm</t>
         </is>
       </c>
     </row>
     <row r="31" ht="19.5" customHeight="1">
-      <c r="E31" s="139" t="inlineStr">
+      <c r="E31" s="140" t="inlineStr">
         <is>
           <t>Damodaran FCFF</t>
         </is>
       </c>
-      <c r="F31" s="140" t="inlineStr">
+      <c r="F31" s="141" t="inlineStr">
         <is>
           <t>Damodaran FCFF</t>
         </is>
       </c>
-      <c r="G31" s="140" t="inlineStr">
+      <c r="G31" s="141" t="inlineStr">
         <is>
           <t>https://pages.stern.nyu.edu/~adamodar/New_Home_Page/datafile/histfcff.html</t>
         </is>
       </c>
     </row>
     <row r="32" ht="19.5" customHeight="1">
-      <c r="E32" s="139" t="inlineStr">
+      <c r="E32" s="140" t="inlineStr">
         <is>
           <t>Damodaran implied ERP table</t>
         </is>
       </c>
-      <c r="F32" s="140" t="inlineStr">
+      <c r="F32" s="141" t="inlineStr">
         <is>
           <t>Damodaran implied ERP table</t>
         </is>
       </c>
-      <c r="G32" s="140" t="inlineStr">
+      <c r="G32" s="141" t="inlineStr">
         <is>
           <t>https://pages.stern.nyu.edu/~adamodar/New_Home_Page/datafile/histimpl.html</t>
         </is>
       </c>
     </row>
     <row r="33" ht="19.5" customHeight="1">
-      <c r="E33" s="139" t="inlineStr">
+      <c r="E33" s="140" t="inlineStr">
         <is>
           <t>FICO IR</t>
         </is>
       </c>
-      <c r="F33" s="140" t="inlineStr">
+      <c r="F33" s="141" t="inlineStr">
         <is>
           <t>FICO IR</t>
         </is>
       </c>
-      <c r="G33" s="140" t="inlineStr">
+      <c r="G33" s="141" t="inlineStr">
         <is>
           <t>https://www.fico.com/en/investors</t>
         </is>
       </c>
     </row>
     <row r="34" ht="19.5" customHeight="1">
-      <c r="E34" s="139" t="inlineStr">
+      <c r="E34" s="140" t="inlineStr">
         <is>
           <t>FRED DGS10</t>
         </is>
       </c>
-      <c r="F34" s="140" t="inlineStr">
+      <c r="F34" s="141" t="inlineStr">
         <is>
           <t>FRED DGS10</t>
         </is>
       </c>
-      <c r="G34" s="140" t="inlineStr">
+      <c r="G34" s="141" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DGS10</t>
         </is>
       </c>
     </row>
     <row r="35" ht="19.5" customHeight="1">
-      <c r="E35" s="139" t="inlineStr">
+      <c r="E35" s="140" t="inlineStr">
         <is>
           <t>FY2026 guidance EX-99.1</t>
         </is>
       </c>
-      <c r="F35" s="140" t="inlineStr">
+      <c r="F35" s="141" t="inlineStr">
         <is>
           <t>FY2026 guidance EX-99.1</t>
         </is>
       </c>
-      <c r="G35" s="140" t="inlineStr">
+      <c r="G35" s="141" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/814547/000081454726000031/exhibit991erq32026.htm</t>
         </is>
       </c>
     </row>
     <row r="36" ht="19.5" customHeight="1">
-      <c r="E36" s="139" t="inlineStr">
+      <c r="E36" s="140" t="inlineStr">
         <is>
           <t>US Treasury yield curve</t>
         </is>
       </c>
-      <c r="F36" s="140" t="inlineStr">
+      <c r="F36" s="141" t="inlineStr">
         <is>
           <t>US Treasury yield curve</t>
         </is>
       </c>
-      <c r="G36" s="140" t="inlineStr">
+      <c r="G36" s="141" t="inlineStr">
         <is>
           <t>https://home.treasury.gov/resource-center/data-chart-center/interest-rates/TextView?type=daily_treasury_yield_curve</t>
         </is>
       </c>
     </row>
     <row r="37" ht="19.5" customHeight="1">
-      <c r="E37" s="139" t="inlineStr">
+      <c r="E37" s="140" t="inlineStr">
         <is>
           <t>Yahoo FICO</t>
         </is>
       </c>
-      <c r="F37" s="140" t="inlineStr">
+      <c r="F37" s="141" t="inlineStr">
         <is>
           <t>Yahoo FICO</t>
         </is>
       </c>
-      <c r="G37" s="140" t="inlineStr">
+      <c r="G37" s="141" t="inlineStr">
         <is>
           <t>https://finance.yahoo.com/quote/FICO/key-statistics/</t>
         </is>
       </c>
     </row>
     <row r="38" ht="19.5" customHeight="1">
-      <c r="E38" s="139" t="inlineStr">
+      <c r="E38" s="140" t="inlineStr">
         <is>
           <t>Yahoo FICO quote</t>
         </is>
       </c>
-      <c r="F38" s="140" t="inlineStr">
+      <c r="F38" s="141" t="inlineStr">
         <is>
           <t>Yahoo FICO quote</t>
         </is>
       </c>
-      <c r="G38" s="140" t="inlineStr">
+      <c r="G38" s="141" t="inlineStr">
         <is>
           <t>https://finance.yahoo.com/quote/FICO/</t>
         </is>
       </c>
     </row>
     <row r="39" ht="19.5" customHeight="1">
-      <c r="E39" s="139" t="inlineStr">
+      <c r="E39" s="140" t="inlineStr">
         <is>
           <t>companyfacts</t>
         </is>
       </c>
-      <c r="F39" s="140" t="inlineStr">
+      <c r="F39" s="141" t="inlineStr">
         <is>
           <t>companyfacts</t>
         </is>
       </c>
-      <c r="G39" s="140" t="inlineStr">
+      <c r="G39" s="141" t="inlineStr">
         <is>
           <t>https://data.sec.gov/api/xbrl/companyfacts/CIK0000814547.json</t>
         </is>
@@ -6726,42 +6734,42 @@
       </c>
       <c r="C2" s="62" t="n"/>
       <c r="D2" s="63" t="n"/>
-      <c r="E2" s="141" t="n">
+      <c r="E2" s="142" t="n">
         <v>2021</v>
       </c>
-      <c r="F2" s="142">
+      <c r="F2" s="143">
         <f>+E2+1</f>
         <v/>
       </c>
-      <c r="G2" s="142">
+      <c r="G2" s="143">
         <f>+F2+1</f>
         <v/>
       </c>
-      <c r="H2" s="142">
+      <c r="H2" s="143">
         <f>+G2+1</f>
         <v/>
       </c>
-      <c r="I2" s="142">
+      <c r="I2" s="143">
         <f>+H2+1</f>
         <v/>
       </c>
-      <c r="J2" s="143">
+      <c r="J2" s="144">
         <f>+I2+1</f>
         <v/>
       </c>
-      <c r="K2" s="143">
+      <c r="K2" s="144">
         <f>+J2+1</f>
         <v/>
       </c>
-      <c r="L2" s="143">
+      <c r="L2" s="144">
         <f>+K2+1</f>
         <v/>
       </c>
-      <c r="M2" s="143">
+      <c r="M2" s="144">
         <f>+L2+1</f>
         <v/>
       </c>
-      <c r="N2" s="143">
+      <c r="N2" s="144">
         <f>+M2+1</f>
         <v/>
       </c>
@@ -6772,54 +6780,54 @@
           <t>Balance Sheet Check</t>
         </is>
       </c>
-      <c r="E3" s="144">
+      <c r="E3" s="145">
         <f>IFERROR(IF(ABS(E57)&gt;1,"ERROR","OK"),"OK")</f>
         <v/>
       </c>
-      <c r="F3" s="144">
+      <c r="F3" s="145">
         <f>IFERROR(IF(ABS(F57)&gt;1,"ERROR","OK"),"OK")</f>
         <v/>
       </c>
-      <c r="G3" s="144">
+      <c r="G3" s="145">
         <f>IFERROR(IF(ABS(G57)&gt;1,"ERROR","OK"),"OK")</f>
         <v/>
       </c>
-      <c r="H3" s="144">
+      <c r="H3" s="145">
         <f>IFERROR(IF(ABS(H57)&gt;1,"ERROR","OK"),"OK")</f>
         <v/>
       </c>
-      <c r="I3" s="144">
+      <c r="I3" s="145">
         <f>IFERROR(IF(ABS(I57)&gt;1,"ERROR","OK"),"OK")</f>
         <v/>
       </c>
-      <c r="J3" s="144">
+      <c r="J3" s="145">
         <f>IFERROR(IF(ABS(J57)&gt;1,"ERROR","OK"),"OK")</f>
         <v/>
       </c>
-      <c r="K3" s="144">
+      <c r="K3" s="145">
         <f>IFERROR(IF(ABS(K57)&gt;1,"ERROR","OK"),"OK")</f>
         <v/>
       </c>
-      <c r="L3" s="144">
+      <c r="L3" s="145">
         <f>IFERROR(IF(ABS(L57)&gt;1,"ERROR","OK"),"OK")</f>
         <v/>
       </c>
-      <c r="M3" s="144">
+      <c r="M3" s="145">
         <f>IFERROR(IF(ABS(M57)&gt;1,"ERROR","OK"),"OK")</f>
         <v/>
       </c>
-      <c r="N3" s="144">
+      <c r="N3" s="145">
         <f>IFERROR(IF(ABS(N57)&gt;1,"ERROR","OK"),"OK")</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="145" t="inlineStr">
-        <is>
-          <t>vengeanceaiUSCMODEL6: hover J–N for WHY+SOURCE; click blue Source link in col U (or LINK: URL in col C / V) to open the filing</t>
-        </is>
-      </c>
-      <c r="P4" s="146" t="inlineStr">
+      <c r="B4" s="146" t="inlineStr">
+        <is>
+          <t>vengeanceaiUSCMODEL7: hover J–N for WHY+SOURCE; click blue Source link in col U (or LINK: URL in col C / V) to open the filing</t>
+        </is>
+      </c>
+      <c r="P4" s="147" t="inlineStr">
         <is>
           <t>ASSUMPTIONS EXPLAINED — click blue Source (col U) for the filing/data</t>
         </is>
@@ -6843,7 +6851,7 @@
       <c r="L5" s="65" t="n"/>
       <c r="M5" s="65" t="n"/>
       <c r="N5" s="65" t="n"/>
-      <c r="P5" s="147" t="inlineStr">
+      <c r="P5" s="148" t="inlineStr">
         <is>
           <t>Yellow = policy. Green = FY25-linked equations. Col U = clickable hyperlink. Col V = full URL (also clickable).</t>
         </is>
@@ -6856,37 +6864,37 @@
         </is>
       </c>
       <c r="D6" s="47" t="n"/>
-      <c r="P6" s="148" t="inlineStr">
+      <c r="P6" s="149" t="inlineStr">
         <is>
           <t>Row</t>
         </is>
       </c>
-      <c r="Q6" s="148" t="inlineStr">
+      <c r="Q6" s="149" t="inlineStr">
         <is>
           <t>Assumption</t>
         </is>
       </c>
-      <c r="R6" s="148" t="inlineStr">
+      <c r="R6" s="149" t="inlineStr">
         <is>
           <t>What it is</t>
         </is>
       </c>
-      <c r="S6" s="148" t="inlineStr">
+      <c r="S6" s="149" t="inlineStr">
         <is>
           <t>How set in model</t>
         </is>
       </c>
-      <c r="T6" s="148" t="inlineStr">
+      <c r="T6" s="149" t="inlineStr">
         <is>
           <t>Why this choice</t>
         </is>
       </c>
-      <c r="U6" s="148" t="inlineStr">
+      <c r="U6" s="149" t="inlineStr">
         <is>
           <t>Source (click)</t>
         </is>
       </c>
-      <c r="V6" s="148" t="inlineStr">
+      <c r="V6" s="149" t="inlineStr">
         <is>
           <t>Source URL</t>
         </is>
@@ -6898,7 +6906,7 @@
           <t>Revenue Growth (% Change)</t>
         </is>
       </c>
-      <c r="C7" s="149" t="inlineStr">
+      <c r="C7" s="150" t="inlineStr">
         <is>
           <t>WHY: Y1 ≈ company FY2026 revenue guidance (~$2.53B / FY25 $1.991B − 1 ≈ 27%). Then fade toward terminal g=3% (not straight… | SOURCE: SEC EX-99.1 Q3 FY2026 — updated FY2026 revenue guidance $2.53B | LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454726000031/exhibit991erq32026.htm | HOW: Yellow POLICY input: 27% / 16% / 13% / 10% / 7%.</t>
         </is>
@@ -6921,50 +6929,50 @@
         <f>I24/H24-1</f>
         <v/>
       </c>
-      <c r="J7" s="150" t="n">
+      <c r="J7" s="151" t="n">
         <v>0.27</v>
       </c>
-      <c r="K7" s="150" t="n">
+      <c r="K7" s="151" t="n">
         <v>0.16</v>
       </c>
-      <c r="L7" s="150" t="n">
+      <c r="L7" s="151" t="n">
         <v>0.13</v>
       </c>
-      <c r="M7" s="150" t="n">
+      <c r="M7" s="151" t="n">
         <v>0.1</v>
       </c>
-      <c r="N7" s="150" t="n">
+      <c r="N7" s="151" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="P7" s="151" t="n">
+      <c r="P7" s="152" t="n">
         <v>7</v>
       </c>
-      <c r="Q7" s="151" t="inlineStr">
+      <c r="Q7" s="152" t="inlineStr">
         <is>
           <t>Revenue Growth</t>
         </is>
       </c>
-      <c r="R7" s="152" t="inlineStr">
+      <c r="R7" s="153" t="inlineStr">
         <is>
           <t>Year-over-year % increase in revenue for each forecast year.</t>
         </is>
       </c>
-      <c r="S7" s="152" t="inlineStr">
+      <c r="S7" s="153" t="inlineStr">
         <is>
           <t>Yellow POLICY input: 27% / 16% / 13% / 10% / 7%.</t>
         </is>
       </c>
-      <c r="T7" s="152" t="inlineStr">
+      <c r="T7" s="153" t="inlineStr">
         <is>
           <t>Y1 ≈ company FY2026 revenue guidance (~$2.53B / FY25 $1.991B − 1 ≈ 27%). Then fade toward terminal g=3% (not straight-lined). This is the main forward-looking judgment; it drives Rev → GP → EBT → Net Earnings → CF.</t>
         </is>
       </c>
-      <c r="U7" s="153" t="inlineStr">
+      <c r="U7" s="154" t="inlineStr">
         <is>
           <t>SEC EX-99.1 Q3 FY2026 — updated FY2026 revenue guidance $2.53B</t>
         </is>
       </c>
-      <c r="V7" s="153" t="inlineStr">
+      <c r="V7" s="154" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/814547/000081454726000031/exhibit991erq32026.htm</t>
         </is>
@@ -6976,7 +6984,7 @@
           <t>Cost of Goods Sold (% of Revenue)</t>
         </is>
       </c>
-      <c r="C8" s="149" t="inlineStr">
+      <c r="C8" s="150" t="inlineStr">
         <is>
           <t>WHY: Locks in latest reported cost structure (~17.8%). Scores mix is high-margin; holding FY25 is conservative vs further … | SOURCE: SEC 10-K FY2025 — Cost of revenues / Total revenues | LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm | HOW: Excel equation: I25/I24 (FY25 COGS ÷ FY25 Revenue) held flat.</t>
         </is>
@@ -7002,55 +7010,55 @@
         <f>I25/I24</f>
         <v/>
       </c>
-      <c r="J8" s="154">
+      <c r="J8" s="155">
         <f>$I$25/$I$24</f>
         <v/>
       </c>
-      <c r="K8" s="154">
+      <c r="K8" s="155">
         <f>$I$25/$I$24</f>
         <v/>
       </c>
-      <c r="L8" s="154">
+      <c r="L8" s="155">
         <f>$I$25/$I$24</f>
         <v/>
       </c>
-      <c r="M8" s="154">
+      <c r="M8" s="155">
         <f>$I$25/$I$24</f>
         <v/>
       </c>
-      <c r="N8" s="154">
+      <c r="N8" s="155">
         <f>$I$25/$I$24</f>
         <v/>
       </c>
-      <c r="P8" s="151" t="n">
+      <c r="P8" s="152" t="n">
         <v>8</v>
       </c>
-      <c r="Q8" s="151" t="inlineStr">
+      <c r="Q8" s="152" t="inlineStr">
         <is>
           <t>COGS % of Revenue</t>
         </is>
       </c>
-      <c r="R8" s="152" t="inlineStr">
+      <c r="R8" s="153" t="inlineStr">
         <is>
           <t>Cost of revenues as a % of sales (gross margin = 1 − this).</t>
         </is>
       </c>
-      <c r="S8" s="152" t="inlineStr">
+      <c r="S8" s="153" t="inlineStr">
         <is>
           <t>Excel equation: I25/I24 (FY25 COGS ÷ FY25 Revenue) held flat.</t>
         </is>
       </c>
-      <c r="T8" s="152" t="inlineStr">
+      <c r="T8" s="153" t="inlineStr">
         <is>
           <t>Locks in latest reported cost structure (~17.8%). Scores mix is high-margin; holding FY25 is conservative vs further mix shift.</t>
         </is>
       </c>
-      <c r="U8" s="153" t="inlineStr">
+      <c r="U8" s="154" t="inlineStr">
         <is>
           <t>SEC 10-K FY2025 — Cost of revenues / Total revenues</t>
         </is>
       </c>
-      <c r="V8" s="153" t="inlineStr">
+      <c r="V8" s="154" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
         </is>
@@ -7062,81 +7070,81 @@
           <t>SG&amp;A % of Revenue (floor 15%, −75bps×t)</t>
         </is>
       </c>
-      <c r="C9" s="149" t="inlineStr">
+      <c r="C9" s="150" t="inlineStr">
         <is>
           <t>WHY: MODEL7 audit: allow software operating leverage. Floor 15%; grind −75 bps so SG&amp;A can scale toward mid-teens as reven… | SOURCE: SEC 10-K FY2025 — SG&amp;A + restructuring note | LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm | HOW: Equation: MAX(15%, (I28 − 10,922)/I24 − 75bps × year). Strips FY25 restructuring; then −0.75% of sales each year.</t>
         </is>
       </c>
       <c r="D9" s="47" t="n"/>
-      <c r="E9" s="155">
+      <c r="E9" s="156">
         <f>E28</f>
         <v/>
       </c>
-      <c r="F9" s="155">
+      <c r="F9" s="156">
         <f>F28</f>
         <v/>
       </c>
-      <c r="G9" s="155">
+      <c r="G9" s="156">
         <f>G28</f>
         <v/>
       </c>
-      <c r="H9" s="155">
+      <c r="H9" s="156">
         <f>H28</f>
         <v/>
       </c>
-      <c r="I9" s="155">
+      <c r="I9" s="156">
         <f>I28</f>
         <v/>
       </c>
-      <c r="J9" s="156">
+      <c r="J9" s="157">
         <f>MAX(0.15,(($I$28-10922.0)/$I$24)-0.0075)</f>
         <v/>
       </c>
-      <c r="K9" s="156">
+      <c r="K9" s="157">
         <f>MAX(0.15,(($I$28-10922.0)/$I$24)-0.015)</f>
         <v/>
       </c>
-      <c r="L9" s="156">
+      <c r="L9" s="157">
         <f>MAX(0.15,(($I$28-10922.0)/$I$24)-0.0225)</f>
         <v/>
       </c>
-      <c r="M9" s="156">
+      <c r="M9" s="157">
         <f>MAX(0.15,(($I$28-10922.0)/$I$24)-0.03)</f>
         <v/>
       </c>
-      <c r="N9" s="156">
+      <c r="N9" s="157">
         <f>MAX(0.15,(($I$28-10922.0)/$I$24)-0.0375)</f>
         <v/>
       </c>
-      <c r="P9" s="151" t="n">
+      <c r="P9" s="152" t="n">
         <v>9</v>
       </c>
-      <c r="Q9" s="151" t="inlineStr">
+      <c r="Q9" s="152" t="inlineStr">
         <is>
           <t>SG&amp;A % of Revenue</t>
         </is>
       </c>
-      <c r="R9" s="152" t="inlineStr">
+      <c r="R9" s="153" t="inlineStr">
         <is>
           <t>Operating opex (SG&amp;A) as % of sales.</t>
         </is>
       </c>
-      <c r="S9" s="152" t="inlineStr">
+      <c r="S9" s="153" t="inlineStr">
         <is>
           <t>Equation: MAX(15%, (I28 − 10,922)/I24 − 75bps × year). Strips FY25 restructuring; then −0.75% of sales each year.</t>
         </is>
       </c>
-      <c r="T9" s="152" t="inlineStr">
+      <c r="T9" s="153" t="inlineStr">
         <is>
           <t>MODEL7 audit: allow software operating leverage. Floor 15%; grind −75 bps so SG&amp;A can scale toward mid-teens as revenue expands (not stuck ~24–25%).</t>
         </is>
       </c>
-      <c r="U9" s="153" t="inlineStr">
+      <c r="U9" s="154" t="inlineStr">
         <is>
           <t>SEC 10-K FY2025 — SG&amp;A + restructuring note</t>
         </is>
       </c>
-      <c r="V9" s="153" t="inlineStr">
+      <c r="V9" s="154" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
         </is>
@@ -7148,81 +7156,81 @@
           <t>R&amp;D % of Revenue (equation)</t>
         </is>
       </c>
-      <c r="C10" s="149" t="inlineStr">
+      <c r="C10" s="150" t="inlineStr">
         <is>
           <t>WHY: FICO reinvests steadily in analytics/software. Flat % grows dollars with revenue. | SOURCE: SEC 10-K FY2025 — Research and development | LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm | HOW: Excel equation: I29/I24 held flat (~9.46%).</t>
         </is>
       </c>
       <c r="D10" s="47" t="n"/>
-      <c r="E10" s="155">
+      <c r="E10" s="156">
         <f>E29</f>
         <v/>
       </c>
-      <c r="F10" s="155">
+      <c r="F10" s="156">
         <f>F29</f>
         <v/>
       </c>
-      <c r="G10" s="155">
+      <c r="G10" s="156">
         <f>G29</f>
         <v/>
       </c>
-      <c r="H10" s="155">
+      <c r="H10" s="156">
         <f>H29</f>
         <v/>
       </c>
-      <c r="I10" s="155">
+      <c r="I10" s="156">
         <f>I29</f>
         <v/>
       </c>
-      <c r="J10" s="156">
+      <c r="J10" s="157">
         <f>$I$29/$I$24</f>
         <v/>
       </c>
-      <c r="K10" s="156">
+      <c r="K10" s="157">
         <f>$I$29/$I$24</f>
         <v/>
       </c>
-      <c r="L10" s="156">
+      <c r="L10" s="157">
         <f>$I$29/$I$24</f>
         <v/>
       </c>
-      <c r="M10" s="156">
+      <c r="M10" s="157">
         <f>$I$29/$I$24</f>
         <v/>
       </c>
-      <c r="N10" s="156">
+      <c r="N10" s="157">
         <f>$I$29/$I$24</f>
         <v/>
       </c>
-      <c r="P10" s="151" t="n">
+      <c r="P10" s="152" t="n">
         <v>10</v>
       </c>
-      <c r="Q10" s="151" t="inlineStr">
+      <c r="Q10" s="152" t="inlineStr">
         <is>
           <t>R&amp;D % of Revenue</t>
         </is>
       </c>
-      <c r="R10" s="152" t="inlineStr">
+      <c r="R10" s="153" t="inlineStr">
         <is>
           <t>Research &amp; development (template label may say Rent and Overhead) as % of sales.</t>
         </is>
       </c>
-      <c r="S10" s="152" t="inlineStr">
+      <c r="S10" s="153" t="inlineStr">
         <is>
           <t>Excel equation: I29/I24 held flat (~9.46%).</t>
         </is>
       </c>
-      <c r="T10" s="152" t="inlineStr">
+      <c r="T10" s="153" t="inlineStr">
         <is>
           <t>FICO reinvests steadily in analytics/software. Flat % grows dollars with revenue.</t>
         </is>
       </c>
-      <c r="U10" s="153" t="inlineStr">
+      <c r="U10" s="154" t="inlineStr">
         <is>
           <t>SEC 10-K FY2025 — Research and development</t>
         </is>
       </c>
-      <c r="V10" s="153" t="inlineStr">
+      <c r="V10" s="154" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
         </is>
@@ -7234,7 +7242,7 @@
           <t>D&amp;A % of Avg PP&amp;E (rate=FY25 DA/PPE; $ uses avg base)</t>
         </is>
       </c>
-      <c r="C11" s="149" t="inlineStr">
+      <c r="C11" s="150" t="inlineStr">
         <is>
           <t>WHY: MODEL6 fix: prior model depreciated only opening PP&amp;E, so ~$96M of forecast CapEx never hit D&amp;A/FCFF add-back. Averag… | SOURCE: SEC 10-K FY2025 — D&amp;A and PP&amp;E | LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm | HOW: Rate = I30/I44 (FY25 DA ÷ FY25 PPE). Forecast DA$ = ((Open + Open+CapEx)/2) × rate.</t>
         </is>
@@ -7260,55 +7268,55 @@
         <f>I30/I92</f>
         <v/>
       </c>
-      <c r="J11" s="154">
+      <c r="J11" s="155">
         <f>IF($I$44=0,0.25,$I$30/$I$44)</f>
         <v/>
       </c>
-      <c r="K11" s="154">
+      <c r="K11" s="155">
         <f>IF($I$44=0,0.25,$I$30/$I$44)</f>
         <v/>
       </c>
-      <c r="L11" s="154">
+      <c r="L11" s="155">
         <f>IF($I$44=0,0.25,$I$30/$I$44)</f>
         <v/>
       </c>
-      <c r="M11" s="154">
+      <c r="M11" s="155">
         <f>IF($I$44=0,0.25,$I$30/$I$44)</f>
         <v/>
       </c>
-      <c r="N11" s="154">
+      <c r="N11" s="155">
         <f>IF($I$44=0,0.25,$I$30/$I$44)</f>
         <v/>
       </c>
-      <c r="P11" s="151" t="n">
+      <c r="P11" s="152" t="n">
         <v>11</v>
       </c>
-      <c r="Q11" s="151" t="inlineStr">
+      <c r="Q11" s="152" t="inlineStr">
         <is>
           <t>D&amp;A % of Avg PP&amp;E</t>
         </is>
       </c>
-      <c r="R11" s="152" t="inlineStr">
+      <c r="R11" s="153" t="inlineStr">
         <is>
           <t>Depreciation rate from FY25; dollars applied to average PP&amp;E so new CapEx is depreciated.</t>
         </is>
       </c>
-      <c r="S11" s="152" t="inlineStr">
+      <c r="S11" s="153" t="inlineStr">
         <is>
           <t>Rate = I30/I44 (FY25 DA ÷ FY25 PPE). Forecast DA$ = ((Open + Open+CapEx)/2) × rate.</t>
         </is>
       </c>
-      <c r="T11" s="152" t="inlineStr">
+      <c r="T11" s="153" t="inlineStr">
         <is>
           <t>MODEL6 fix: prior model depreciated only opening PP&amp;E, so ~$96M of forecast CapEx never hit D&amp;A/FCFF add-back. Average PP&amp;E (Open ↔ pre-DA close) depreciates additions in the year they are placed in service.</t>
         </is>
       </c>
-      <c r="U11" s="153" t="inlineStr">
+      <c r="U11" s="154" t="inlineStr">
         <is>
           <t>SEC 10-K FY2025 — D&amp;A and PP&amp;E</t>
         </is>
       </c>
-      <c r="V11" s="153" t="inlineStr">
+      <c r="V11" s="154" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
         </is>
@@ -7320,7 +7328,7 @@
           <t>Interest (% of Debt Open Bal)</t>
         </is>
       </c>
-      <c r="C12" s="149" t="inlineStr">
+      <c r="C12" s="150" t="inlineStr">
         <is>
           <t>WHY: Approximates average coupon / cost of debt on the book. Debt held flat (issuance = 0), so interest stays linked to th… | SOURCE: SEC 10-K FY2025 — Interest expense; see also 8-K 6.250% notes | LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm | HOW: Excel equation: I101/I98 (FY25 interest ÷ FY25 opening debt in schedule).</t>
         </is>
@@ -7346,55 +7354,55 @@
         <f>I101/I98</f>
         <v/>
       </c>
-      <c r="J12" s="154">
+      <c r="J12" s="155">
         <f>IF($I$98=0,0.05,$I$101/$I$98)</f>
         <v/>
       </c>
-      <c r="K12" s="154">
+      <c r="K12" s="155">
         <f>IF($I$98=0,0.05,$I$101/$I$98)</f>
         <v/>
       </c>
-      <c r="L12" s="154">
+      <c r="L12" s="155">
         <f>IF($I$98=0,0.05,$I$101/$I$98)</f>
         <v/>
       </c>
-      <c r="M12" s="154">
+      <c r="M12" s="155">
         <f>IF($I$98=0,0.05,$I$101/$I$98)</f>
         <v/>
       </c>
-      <c r="N12" s="154">
+      <c r="N12" s="155">
         <f>IF($I$98=0,0.05,$I$101/$I$98)</f>
         <v/>
       </c>
-      <c r="P12" s="151" t="n">
+      <c r="P12" s="152" t="n">
         <v>12</v>
       </c>
-      <c r="Q12" s="151" t="inlineStr">
+      <c r="Q12" s="152" t="inlineStr">
         <is>
           <t>Interest % of Debt Open</t>
         </is>
       </c>
-      <c r="R12" s="152" t="inlineStr">
+      <c r="R12" s="153" t="inlineStr">
         <is>
           <t>Interest expense as % of opening debt balance.</t>
         </is>
       </c>
-      <c r="S12" s="152" t="inlineStr">
+      <c r="S12" s="153" t="inlineStr">
         <is>
           <t>Excel equation: I101/I98 (FY25 interest ÷ FY25 opening debt in schedule).</t>
         </is>
       </c>
-      <c r="T12" s="152" t="inlineStr">
+      <c r="T12" s="153" t="inlineStr">
         <is>
           <t>Approximates average coupon / cost of debt on the book. Debt held flat (issuance = 0), so interest stays linked to that stock.</t>
         </is>
       </c>
-      <c r="U12" s="153" t="inlineStr">
+      <c r="U12" s="154" t="inlineStr">
         <is>
           <t>SEC 10-K FY2025 — Interest expense; see also 8-K 6.250% notes</t>
         </is>
       </c>
-      <c r="V12" s="153" t="inlineStr">
+      <c r="V12" s="154" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
         </is>
@@ -7406,7 +7414,7 @@
           <t>Tax Rate (% of Earnings Before Tax)</t>
         </is>
       </c>
-      <c r="C13" s="149" t="inlineStr">
+      <c r="C13" s="150" t="inlineStr">
         <is>
           <t>WHY: Uses reported effective rate (~19% on template EBT; ~18.8% on 10-K EBT). UFCF in DCF also uses unlevered EBIT × t. | SOURCE: SEC 10-K FY2025 — Provision for income taxes / Income before taxes | LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm | HOW: Excel equation: I35/I33 (FY25 tax ÷ simplified FY25 EBT in this template).</t>
         </is>
@@ -7432,55 +7440,55 @@
         <f>I35/I33</f>
         <v/>
       </c>
-      <c r="J13" s="154">
+      <c r="J13" s="155">
         <f>IF($I$33=0,0.21,$I$35/$I$33)</f>
         <v/>
       </c>
-      <c r="K13" s="154">
+      <c r="K13" s="155">
         <f>IF($I$33=0,0.21,$I$35/$I$33)</f>
         <v/>
       </c>
-      <c r="L13" s="154">
+      <c r="L13" s="155">
         <f>IF($I$33=0,0.21,$I$35/$I$33)</f>
         <v/>
       </c>
-      <c r="M13" s="154">
+      <c r="M13" s="155">
         <f>IF($I$33=0,0.21,$I$35/$I$33)</f>
         <v/>
       </c>
-      <c r="N13" s="154">
+      <c r="N13" s="155">
         <f>IF($I$33=0,0.21,$I$35/$I$33)</f>
         <v/>
       </c>
-      <c r="P13" s="151" t="n">
+      <c r="P13" s="152" t="n">
         <v>13</v>
       </c>
-      <c r="Q13" s="151" t="inlineStr">
+      <c r="Q13" s="152" t="inlineStr">
         <is>
           <t>Tax Rate (% of EBT)</t>
         </is>
       </c>
-      <c r="R13" s="152" t="inlineStr">
+      <c r="R13" s="153" t="inlineStr">
         <is>
           <t>Effective book tax rate applied to forecast EBT.</t>
         </is>
       </c>
-      <c r="S13" s="152" t="inlineStr">
+      <c r="S13" s="153" t="inlineStr">
         <is>
           <t>Excel equation: I35/I33 (FY25 tax ÷ simplified FY25 EBT in this template).</t>
         </is>
       </c>
-      <c r="T13" s="152" t="inlineStr">
+      <c r="T13" s="153" t="inlineStr">
         <is>
           <t>Uses reported effective rate (~19% on template EBT; ~18.8% on 10-K EBT). UFCF in DCF also uses unlevered EBIT × t.</t>
         </is>
       </c>
-      <c r="U13" s="153" t="inlineStr">
+      <c r="U13" s="154" t="inlineStr">
         <is>
           <t>SEC 10-K FY2025 — Provision for income taxes / Income before taxes</t>
         </is>
       </c>
-      <c r="V13" s="153" t="inlineStr">
+      <c r="V13" s="154" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
         </is>
@@ -7511,81 +7519,81 @@
           <t>Operating NWC % of Revenue (fade → 3%)</t>
         </is>
       </c>
-      <c r="C15" s="157" t="inlineStr">
+      <c r="C15" s="158" t="inlineStr">
         <is>
           <t>WHY: MODEL7 audit: ends the gross-AR-days + deferred double-count that drained ~$297M of FCFF. Asset-light software WC fad… | SOURCE: SEC companyfacts XBRL — AR / AP / DeferredRevenueCurrent | LINK: https://data.sec.gov/api/xbrl/companyfacts/CIK0000814547.json | HOW: Equation: fade FY25 op. NWC/Sales → 3% steady (weights 70/50/30/15/0).</t>
         </is>
       </c>
       <c r="D15" s="32" t="n"/>
-      <c r="E15" s="155">
+      <c r="E15" s="156">
         <f>E42/E24*365</f>
         <v/>
       </c>
-      <c r="F15" s="155">
+      <c r="F15" s="156">
         <f>F42/F24*365</f>
         <v/>
       </c>
-      <c r="G15" s="155">
+      <c r="G15" s="156">
         <f>G42/G24*365</f>
         <v/>
       </c>
-      <c r="H15" s="155">
+      <c r="H15" s="156">
         <f>H42/H24*365</f>
         <v/>
       </c>
-      <c r="I15" s="155">
+      <c r="I15" s="156">
         <f>I42/I24*365</f>
         <v/>
       </c>
-      <c r="J15" s="156">
+      <c r="J15" s="157">
         <f>MAX(0,(($I$42+$I$43-$I$48-$I$88)/$I$24))*0.7+0.03*(1-0.7)</f>
         <v/>
       </c>
-      <c r="K15" s="156">
+      <c r="K15" s="157">
         <f>MAX(0,(($I$42+$I$43-$I$48-$I$88)/$I$24))*0.5+0.03*(1-0.5)</f>
         <v/>
       </c>
-      <c r="L15" s="156">
+      <c r="L15" s="157">
         <f>MAX(0,(($I$42+$I$43-$I$48-$I$88)/$I$24))*0.3+0.03*(1-0.3)</f>
         <v/>
       </c>
-      <c r="M15" s="156">
+      <c r="M15" s="157">
         <f>MAX(0,(($I$42+$I$43-$I$48-$I$88)/$I$24))*0.15+0.03*(1-0.15)</f>
         <v/>
       </c>
-      <c r="N15" s="156">
+      <c r="N15" s="157">
         <f>MAX(0,(($I$42+$I$43-$I$48-$I$88)/$I$24))*0.0+0.03*(1-0.0)</f>
         <v/>
       </c>
-      <c r="P15" s="151" t="n">
+      <c r="P15" s="152" t="n">
         <v>15</v>
       </c>
-      <c r="Q15" s="151" t="inlineStr">
+      <c r="Q15" s="152" t="inlineStr">
         <is>
           <t>Operating NWC % of Revenue</t>
         </is>
       </c>
-      <c r="R15" s="152" t="inlineStr">
+      <c r="R15" s="153" t="inlineStr">
         <is>
           <t>Single consolidated operating working-capital ratio (AR+Inv−AP−Deferred)/Sales.</t>
         </is>
       </c>
-      <c r="S15" s="152" t="inlineStr">
+      <c r="S15" s="153" t="inlineStr">
         <is>
           <t>Equation: fade FY25 op. NWC/Sales → 3% steady (weights 70/50/30/15/0).</t>
         </is>
       </c>
-      <c r="T15" s="152" t="inlineStr">
+      <c r="T15" s="153" t="inlineStr">
         <is>
           <t>MODEL7 audit: ends the gross-AR-days + deferred double-count that drained ~$297M of FCFF. Asset-light software WC fades toward ~3% of sales; BS AR is plugged so AR−AP−Deferred = NWC.</t>
         </is>
       </c>
-      <c r="U15" s="153" t="inlineStr">
+      <c r="U15" s="154" t="inlineStr">
         <is>
           <t>SEC companyfacts XBRL — AR / AP / DeferredRevenueCurrent</t>
         </is>
       </c>
-      <c r="V15" s="153" t="inlineStr">
+      <c r="V15" s="154" t="inlineStr">
         <is>
           <t>https://data.sec.gov/api/xbrl/companyfacts/CIK0000814547.json</t>
         </is>
@@ -7597,76 +7605,76 @@
           <t>Inventory (Days)</t>
         </is>
       </c>
-      <c r="C16" s="157" t="inlineStr">
+      <c r="C16" s="158" t="inlineStr">
         <is>
           <t>WHY: No inventory cycle to fund. | SOURCE: SEC 10-K FY2025 — Inventory ≈ $0 | LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm | HOW: Hard zero — FICO is software / scores; inventory is immaterial.</t>
         </is>
       </c>
       <c r="D16" s="32" t="n"/>
-      <c r="E16" s="155">
+      <c r="E16" s="156">
         <f>E43/E25*365</f>
         <v/>
       </c>
-      <c r="F16" s="155">
+      <c r="F16" s="156">
         <f>F43/F25*365</f>
         <v/>
       </c>
-      <c r="G16" s="155">
+      <c r="G16" s="156">
         <f>G43/G25*365</f>
         <v/>
       </c>
-      <c r="H16" s="155">
+      <c r="H16" s="156">
         <f>H43/H25*365</f>
         <v/>
       </c>
-      <c r="I16" s="155">
+      <c r="I16" s="156">
         <f>I43/I25*365</f>
         <v/>
       </c>
-      <c r="J16" s="158" t="n">
+      <c r="J16" s="159" t="n">
         <v>0</v>
       </c>
-      <c r="K16" s="158" t="n">
+      <c r="K16" s="159" t="n">
         <v>0</v>
       </c>
-      <c r="L16" s="158" t="n">
+      <c r="L16" s="159" t="n">
         <v>0</v>
       </c>
-      <c r="M16" s="158" t="n">
+      <c r="M16" s="159" t="n">
         <v>0</v>
       </c>
-      <c r="N16" s="158" t="n">
+      <c r="N16" s="159" t="n">
         <v>0</v>
       </c>
-      <c r="P16" s="151" t="n">
+      <c r="P16" s="152" t="n">
         <v>16</v>
       </c>
-      <c r="Q16" s="151" t="inlineStr">
+      <c r="Q16" s="152" t="inlineStr">
         <is>
           <t>Inventory (Days)</t>
         </is>
       </c>
-      <c r="R16" s="152" t="inlineStr">
+      <c r="R16" s="153" t="inlineStr">
         <is>
           <t>Inventory days (Inv = COGS × days/365).</t>
         </is>
       </c>
-      <c r="S16" s="152" t="inlineStr">
+      <c r="S16" s="153" t="inlineStr">
         <is>
           <t>Hard zero — FICO is software / scores; inventory is immaterial.</t>
         </is>
       </c>
-      <c r="T16" s="152" t="inlineStr">
+      <c r="T16" s="153" t="inlineStr">
         <is>
           <t>No inventory cycle to fund.</t>
         </is>
       </c>
-      <c r="U16" s="153" t="inlineStr">
+      <c r="U16" s="154" t="inlineStr">
         <is>
           <t>SEC 10-K FY2025 — Inventory ≈ $0</t>
         </is>
       </c>
-      <c r="V16" s="153" t="inlineStr">
+      <c r="V16" s="154" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
         </is>
@@ -7678,81 +7686,81 @@
           <t>Accounts Payable (Days)</t>
         </is>
       </c>
-      <c r="C17" s="157" t="inlineStr">
+      <c r="C17" s="158" t="inlineStr">
         <is>
           <t>WHY: Payable timing offsets AR in operating NWC. | SOURCE: SEC 10-K FY2025 — Accounts payable | LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm | HOW: Excel equation: ROUND(I48/I25×365, 0) from FY25.</t>
         </is>
       </c>
       <c r="D17" s="32" t="n"/>
-      <c r="E17" s="155">
+      <c r="E17" s="156">
         <f>E48/E25*365</f>
         <v/>
       </c>
-      <c r="F17" s="155">
+      <c r="F17" s="156">
         <f>F48/F25*365</f>
         <v/>
       </c>
-      <c r="G17" s="155">
+      <c r="G17" s="156">
         <f>G48/G25*365</f>
         <v/>
       </c>
-      <c r="H17" s="155">
+      <c r="H17" s="156">
         <f>H48/H25*365</f>
         <v/>
       </c>
-      <c r="I17" s="155">
+      <c r="I17" s="156">
         <f>I48/I25*365</f>
         <v/>
       </c>
-      <c r="J17" s="159">
+      <c r="J17" s="160">
         <f>IF($I$25=0,0,ROUND($I$48/$I$25*365,0))</f>
         <v/>
       </c>
-      <c r="K17" s="159">
+      <c r="K17" s="160">
         <f>IF($I$25=0,0,ROUND($I$48/$I$25*365,0))</f>
         <v/>
       </c>
-      <c r="L17" s="159">
+      <c r="L17" s="160">
         <f>IF($I$25=0,0,ROUND($I$48/$I$25*365,0))</f>
         <v/>
       </c>
-      <c r="M17" s="159">
+      <c r="M17" s="160">
         <f>IF($I$25=0,0,ROUND($I$48/$I$25*365,0))</f>
         <v/>
       </c>
-      <c r="N17" s="159">
+      <c r="N17" s="160">
         <f>IF($I$25=0,0,ROUND($I$48/$I$25*365,0))</f>
         <v/>
       </c>
-      <c r="P17" s="151" t="n">
+      <c r="P17" s="152" t="n">
         <v>17</v>
       </c>
-      <c r="Q17" s="151" t="inlineStr">
+      <c r="Q17" s="152" t="inlineStr">
         <is>
           <t>Accounts Payable (Days)</t>
         </is>
       </c>
-      <c r="R17" s="152" t="inlineStr">
+      <c r="R17" s="153" t="inlineStr">
         <is>
           <t>AP days used to project AP = COGS × days/365.</t>
         </is>
       </c>
-      <c r="S17" s="152" t="inlineStr">
+      <c r="S17" s="153" t="inlineStr">
         <is>
           <t>Excel equation: ROUND(I48/I25×365, 0) from FY25.</t>
         </is>
       </c>
-      <c r="T17" s="152" t="inlineStr">
+      <c r="T17" s="153" t="inlineStr">
         <is>
           <t>Payable timing offsets AR in operating NWC.</t>
         </is>
       </c>
-      <c r="U17" s="153" t="inlineStr">
+      <c r="U17" s="154" t="inlineStr">
         <is>
           <t>SEC 10-K FY2025 — Accounts payable</t>
         </is>
       </c>
-      <c r="V17" s="153" t="inlineStr">
+      <c r="V17" s="154" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
         </is>
@@ -7764,80 +7772,80 @@
           <t>CapEx % of Revenue (fast fade → 1%)</t>
         </is>
       </c>
-      <c r="C18" s="157" t="inlineStr">
+      <c r="C18" s="158" t="inlineStr">
         <is>
           <t>WHY: MODEL7 audit: prior path left CapEx ≫ D&amp;A (~$80M cumulative drag). Faster fade to maintenance ~1% so CapEx converges … | SOURCE: SEC 10-K FY2025 — PP&amp;E purchases + capitalized software | LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm | HOW: Equation: fade from I68/I24 toward 1.0% steady. MODEL7 weights 40%→20%→10%→0%→0% on the peak (faster fade).</t>
         </is>
       </c>
-      <c r="E18" s="155">
+      <c r="E18" s="156">
         <f>E68</f>
         <v/>
       </c>
-      <c r="F18" s="155">
+      <c r="F18" s="156">
         <f>F68</f>
         <v/>
       </c>
-      <c r="G18" s="155">
+      <c r="G18" s="156">
         <f>G68</f>
         <v/>
       </c>
-      <c r="H18" s="155">
+      <c r="H18" s="156">
         <f>H68</f>
         <v/>
       </c>
-      <c r="I18" s="155">
+      <c r="I18" s="156">
         <f>I68</f>
         <v/>
       </c>
-      <c r="J18" s="156">
+      <c r="J18" s="157">
         <f>($I$68/$I$24)*0.4+0.01*(1-0.4)</f>
         <v/>
       </c>
-      <c r="K18" s="156">
+      <c r="K18" s="157">
         <f>($I$68/$I$24)*0.2+0.01*(1-0.2)</f>
         <v/>
       </c>
-      <c r="L18" s="156">
+      <c r="L18" s="157">
         <f>($I$68/$I$24)*0.1+0.01*(1-0.1)</f>
         <v/>
       </c>
-      <c r="M18" s="156">
+      <c r="M18" s="157">
         <f>($I$68/$I$24)*0.0+0.01*(1-0.0)</f>
         <v/>
       </c>
-      <c r="N18" s="156">
+      <c r="N18" s="157">
         <f>($I$68/$I$24)*0.0+0.01*(1-0.0)</f>
         <v/>
       </c>
-      <c r="P18" s="151" t="n">
+      <c r="P18" s="152" t="n">
         <v>18</v>
       </c>
-      <c r="Q18" s="151" t="inlineStr">
+      <c r="Q18" s="152" t="inlineStr">
         <is>
           <t>CapEx % of Revenue</t>
         </is>
       </c>
-      <c r="R18" s="152" t="inlineStr">
+      <c r="R18" s="153" t="inlineStr">
         <is>
           <t>Capital investment (PPE + capitalized software) as % of sales.</t>
         </is>
       </c>
-      <c r="S18" s="152" t="inlineStr">
+      <c r="S18" s="153" t="inlineStr">
         <is>
           <t>Equation: fade from I68/I24 toward 1.0% steady. MODEL7 weights 40%→20%→10%→0%→0% on the peak (faster fade).</t>
         </is>
       </c>
-      <c r="T18" s="152" t="inlineStr">
+      <c r="T18" s="153" t="inlineStr">
         <is>
           <t>MODEL7 audit: prior path left CapEx ≫ D&amp;A (~$80M cumulative drag). Faster fade to maintenance ~1% so CapEx converges near D&amp;A by Y4–Y5.</t>
         </is>
       </c>
-      <c r="U18" s="153" t="inlineStr">
+      <c r="U18" s="154" t="inlineStr">
         <is>
           <t>SEC 10-K FY2025 — PP&amp;E purchases + capitalized software</t>
         </is>
       </c>
-      <c r="V18" s="153" t="inlineStr">
+      <c r="V18" s="154" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
         </is>
@@ -7849,75 +7857,75 @@
           <t>Debt Issuance (Repayment) ($000's)</t>
         </is>
       </c>
-      <c r="C19" s="157" t="inlineStr">
+      <c r="C19" s="158" t="inlineStr">
         <is>
           <t>WHY: Hold debt stock flat at FY25 level for the explicit period; interest follows. Net debt for DCF equity bridge uses the… | SOURCE: SEC 10-Q Q3 FY2026 — debt stock (financing excluded from FCFF) | LINK: https://www.sec.gov/Archives/edgar/data/814547/000081454726000030/fico-20260630.htm | HOW: POLICY input = 0 every year.</t>
         </is>
       </c>
-      <c r="E19" s="155">
+      <c r="E19" s="156">
         <f>E99</f>
         <v/>
       </c>
-      <c r="F19" s="155">
+      <c r="F19" s="156">
         <f>F99</f>
         <v/>
       </c>
-      <c r="G19" s="155">
+      <c r="G19" s="156">
         <f>G99</f>
         <v/>
       </c>
-      <c r="H19" s="155">
+      <c r="H19" s="156">
         <f>H99</f>
         <v/>
       </c>
-      <c r="I19" s="155">
+      <c r="I19" s="156">
         <f>I99</f>
         <v/>
       </c>
-      <c r="J19" s="160" t="n">
+      <c r="J19" s="161" t="n">
         <v>0</v>
       </c>
-      <c r="K19" s="160" t="n">
+      <c r="K19" s="161" t="n">
         <v>0</v>
       </c>
-      <c r="L19" s="160" t="n">
+      <c r="L19" s="161" t="n">
         <v>0</v>
       </c>
-      <c r="M19" s="160" t="n">
+      <c r="M19" s="161" t="n">
         <v>0</v>
       </c>
-      <c r="N19" s="160" t="n">
+      <c r="N19" s="161" t="n">
         <v>0</v>
       </c>
-      <c r="P19" s="151" t="n">
+      <c r="P19" s="152" t="n">
         <v>19</v>
       </c>
-      <c r="Q19" s="151" t="inlineStr">
+      <c r="Q19" s="152" t="inlineStr">
         <is>
           <t>Debt Issuance (Repayment)</t>
         </is>
       </c>
-      <c r="R19" s="152" t="inlineStr">
+      <c r="R19" s="153" t="inlineStr">
         <is>
           <t>New borrowing (+) or repayment (−) in the forecast.</t>
         </is>
       </c>
-      <c r="S19" s="152" t="inlineStr">
+      <c r="S19" s="153" t="inlineStr">
         <is>
           <t>POLICY input = 0 every year.</t>
         </is>
       </c>
-      <c r="T19" s="152" t="inlineStr">
+      <c r="T19" s="153" t="inlineStr">
         <is>
           <t>Hold debt stock flat at FY25 level for the explicit period; interest follows. Net debt for DCF equity bridge uses the later 10-Q amount separately.</t>
         </is>
       </c>
-      <c r="U19" s="153" t="inlineStr">
+      <c r="U19" s="154" t="inlineStr">
         <is>
           <t>SEC 10-Q Q3 FY2026 — debt stock (financing excluded from FCFF)</t>
         </is>
       </c>
-      <c r="V19" s="153" t="inlineStr">
+      <c r="V19" s="154" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/814547/000081454726000030/fico-20260630.htm</t>
         </is>
@@ -7929,75 +7937,75 @@
           <t>Equity Issued (Repaid) ($000's)</t>
         </is>
       </c>
-      <c r="C20" s="157" t="inlineStr">
+      <c r="C20" s="158" t="inlineStr">
         <is>
           <t>WHY: Buybacks are real historically but are financing — excluded from FCFF. Share count for $/share is the spot shares out… | SOURCE: Damodaran FCFF framework — financing (buybacks) not in FCFF | LINK: https://pages.stern.nyu.edu/~adamodar/New_Home_Page/datafile/histfcff.html | HOW: POLICY input = 0 every year.</t>
         </is>
       </c>
-      <c r="E20" s="155">
+      <c r="E20" s="156">
         <f>E73</f>
         <v/>
       </c>
-      <c r="F20" s="155">
+      <c r="F20" s="156">
         <f>F73</f>
         <v/>
       </c>
-      <c r="G20" s="155">
+      <c r="G20" s="156">
         <f>G73</f>
         <v/>
       </c>
-      <c r="H20" s="155">
+      <c r="H20" s="156">
         <f>H73</f>
         <v/>
       </c>
-      <c r="I20" s="155">
+      <c r="I20" s="156">
         <f>I73</f>
         <v/>
       </c>
-      <c r="J20" s="160" t="n">
+      <c r="J20" s="161" t="n">
         <v>0</v>
       </c>
-      <c r="K20" s="160" t="n">
+      <c r="K20" s="161" t="n">
         <v>0</v>
       </c>
-      <c r="L20" s="160" t="n">
+      <c r="L20" s="161" t="n">
         <v>0</v>
       </c>
-      <c r="M20" s="160" t="n">
+      <c r="M20" s="161" t="n">
         <v>0</v>
       </c>
-      <c r="N20" s="160" t="n">
+      <c r="N20" s="161" t="n">
         <v>0</v>
       </c>
-      <c r="P20" s="151" t="n">
+      <c r="P20" s="152" t="n">
         <v>20</v>
       </c>
-      <c r="Q20" s="151" t="inlineStr">
+      <c r="Q20" s="152" t="inlineStr">
         <is>
           <t>Equity Issued (Repaid)</t>
         </is>
       </c>
-      <c r="R20" s="152" t="inlineStr">
+      <c r="R20" s="153" t="inlineStr">
         <is>
           <t>New equity issued (+) or buybacks (−) in the forecast BS/CF.</t>
         </is>
       </c>
-      <c r="S20" s="152" t="inlineStr">
+      <c r="S20" s="153" t="inlineStr">
         <is>
           <t>POLICY input = 0 every year.</t>
         </is>
       </c>
-      <c r="T20" s="152" t="inlineStr">
+      <c r="T20" s="153" t="inlineStr">
         <is>
           <t>Buybacks are real historically but are financing — excluded from FCFF. Share count for $/share is the spot shares outstanding assumption.</t>
         </is>
       </c>
-      <c r="U20" s="153" t="inlineStr">
+      <c r="U20" s="154" t="inlineStr">
         <is>
           <t>Damodaran FCFF framework — financing (buybacks) not in FCFF</t>
         </is>
       </c>
-      <c r="V20" s="153" t="inlineStr">
+      <c r="V20" s="154" t="inlineStr">
         <is>
           <t>https://pages.stern.nyu.edu/~adamodar/New_Home_Page/datafile/histfcff.html</t>
         </is>
@@ -8052,44 +8060,44 @@
           <t>Reveneue</t>
         </is>
       </c>
-      <c r="C24" s="161" t="inlineStr">
+      <c r="C24" s="162" t="inlineStr">
         <is>
           <t>eqn: PriorRev × (1 + growth)</t>
         </is>
       </c>
       <c r="D24" s="46" t="n"/>
-      <c r="E24" s="162" t="n">
+      <c r="E24" s="163" t="n">
         <v>1316536</v>
       </c>
-      <c r="F24" s="162" t="n">
+      <c r="F24" s="163" t="n">
         <v>1377270</v>
       </c>
-      <c r="G24" s="162" t="n">
+      <c r="G24" s="163" t="n">
         <v>1513557</v>
       </c>
-      <c r="H24" s="162" t="n">
+      <c r="H24" s="163" t="n">
         <v>1717526</v>
       </c>
-      <c r="I24" s="162" t="n">
+      <c r="I24" s="163" t="n">
         <v>1990869</v>
       </c>
-      <c r="J24" s="159">
+      <c r="J24" s="160">
         <f>I24*(1+J7)</f>
         <v/>
       </c>
-      <c r="K24" s="159">
+      <c r="K24" s="160">
         <f>J24*(1+K7)</f>
         <v/>
       </c>
-      <c r="L24" s="159">
+      <c r="L24" s="160">
         <f>K24*(1+L7)</f>
         <v/>
       </c>
-      <c r="M24" s="159">
+      <c r="M24" s="160">
         <f>L24*(1+M7)</f>
         <v/>
       </c>
-      <c r="N24" s="159">
+      <c r="N24" s="160">
         <f>M24*(1+N7)</f>
         <v/>
       </c>
@@ -8100,44 +8108,44 @@
           <t>Cost of Goods Sold (COGS)</t>
         </is>
       </c>
-      <c r="C25" s="161" t="inlineStr">
+      <c r="C25" s="162" t="inlineStr">
         <is>
           <t>eqn: Rev × COGS%</t>
         </is>
       </c>
       <c r="D25" s="47" t="n"/>
-      <c r="E25" s="162" t="n">
+      <c r="E25" s="163" t="n">
         <v>332462</v>
       </c>
-      <c r="F25" s="162" t="n">
+      <c r="F25" s="163" t="n">
         <v>302174</v>
       </c>
-      <c r="G25" s="162" t="n">
+      <c r="G25" s="163" t="n">
         <v>311053</v>
       </c>
-      <c r="H25" s="162" t="n">
+      <c r="H25" s="163" t="n">
         <v>348206</v>
       </c>
-      <c r="I25" s="162" t="n">
+      <c r="I25" s="163" t="n">
         <v>353722</v>
       </c>
-      <c r="J25" s="159">
+      <c r="J25" s="160">
         <f>J24*J8</f>
         <v/>
       </c>
-      <c r="K25" s="159">
+      <c r="K25" s="160">
         <f>K24*K8</f>
         <v/>
       </c>
-      <c r="L25" s="159">
+      <c r="L25" s="160">
         <f>L24*L8</f>
         <v/>
       </c>
-      <c r="M25" s="159">
+      <c r="M25" s="160">
         <f>M24*M8</f>
         <v/>
       </c>
-      <c r="N25" s="159">
+      <c r="N25" s="160">
         <f>N24*N8</f>
         <v/>
       </c>
@@ -8148,49 +8156,49 @@
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="C26" s="163" t="inlineStr">
+      <c r="C26" s="164" t="inlineStr">
         <is>
           <t>eqn: Rev − COGS</t>
         </is>
       </c>
       <c r="D26" s="22" t="n"/>
-      <c r="E26" s="164">
+      <c r="E26" s="165">
         <f>E24-E25</f>
         <v/>
       </c>
-      <c r="F26" s="164">
+      <c r="F26" s="165">
         <f>F24-F25</f>
         <v/>
       </c>
-      <c r="G26" s="164">
+      <c r="G26" s="165">
         <f>G24-G25</f>
         <v/>
       </c>
-      <c r="H26" s="164">
+      <c r="H26" s="165">
         <f>H24-H25</f>
         <v/>
       </c>
-      <c r="I26" s="164">
+      <c r="I26" s="165">
         <f>I24-I25</f>
         <v/>
       </c>
-      <c r="J26" s="159">
+      <c r="J26" s="160">
         <f>J24-J25</f>
         <v/>
       </c>
-      <c r="K26" s="159">
+      <c r="K26" s="160">
         <f>K24-K25</f>
         <v/>
       </c>
-      <c r="L26" s="159">
+      <c r="L26" s="160">
         <f>L24-L25</f>
         <v/>
       </c>
-      <c r="M26" s="159">
+      <c r="M26" s="160">
         <f>M24-M25</f>
         <v/>
       </c>
-      <c r="N26" s="159">
+      <c r="N26" s="160">
         <f>N24-N25</f>
         <v/>
       </c>
@@ -8220,43 +8228,43 @@
           <t>SG&amp;A Expense</t>
         </is>
       </c>
-      <c r="C28" s="165" t="inlineStr">
+      <c r="C28" s="166" t="inlineStr">
         <is>
           <t>eqn: Rev × SG&amp;A%</t>
         </is>
       </c>
-      <c r="E28" s="162" t="n">
+      <c r="E28" s="163" t="n">
         <v>396281</v>
       </c>
-      <c r="F28" s="162" t="n">
+      <c r="F28" s="163" t="n">
         <v>383863</v>
       </c>
-      <c r="G28" s="162" t="n">
+      <c r="G28" s="163" t="n">
         <v>400565</v>
       </c>
-      <c r="H28" s="162" t="n">
+      <c r="H28" s="163" t="n">
         <v>462834</v>
       </c>
-      <c r="I28" s="162" t="n">
+      <c r="I28" s="163" t="n">
         <v>513028</v>
       </c>
-      <c r="J28" s="159">
+      <c r="J28" s="160">
         <f>J24*J9</f>
         <v/>
       </c>
-      <c r="K28" s="159">
+      <c r="K28" s="160">
         <f>K24*K9</f>
         <v/>
       </c>
-      <c r="L28" s="159">
+      <c r="L28" s="160">
         <f>L24*L9</f>
         <v/>
       </c>
-      <c r="M28" s="159">
+      <c r="M28" s="160">
         <f>M24*M9</f>
         <v/>
       </c>
-      <c r="N28" s="159">
+      <c r="N28" s="160">
         <f>N24*N9</f>
         <v/>
       </c>
@@ -8267,43 +8275,43 @@
           <t>Research &amp; Development (R&amp;D)</t>
         </is>
       </c>
-      <c r="C29" s="165" t="inlineStr">
+      <c r="C29" s="166" t="inlineStr">
         <is>
           <t>eqn: Rev × R&amp;D%</t>
         </is>
       </c>
-      <c r="E29" s="162" t="n">
+      <c r="E29" s="163" t="n">
         <v>171231</v>
       </c>
-      <c r="F29" s="162" t="n">
+      <c r="F29" s="163" t="n">
         <v>146758</v>
       </c>
-      <c r="G29" s="162" t="n">
+      <c r="G29" s="163" t="n">
         <v>159950</v>
       </c>
-      <c r="H29" s="162" t="n">
+      <c r="H29" s="163" t="n">
         <v>171940</v>
       </c>
-      <c r="I29" s="162" t="n">
+      <c r="I29" s="163" t="n">
         <v>188347</v>
       </c>
-      <c r="J29" s="159">
+      <c r="J29" s="160">
         <f>J24*J10</f>
         <v/>
       </c>
-      <c r="K29" s="159">
+      <c r="K29" s="160">
         <f>K24*K10</f>
         <v/>
       </c>
-      <c r="L29" s="159">
+      <c r="L29" s="160">
         <f>L24*L10</f>
         <v/>
       </c>
-      <c r="M29" s="159">
+      <c r="M29" s="160">
         <f>M24*M10</f>
         <v/>
       </c>
-      <c r="N29" s="159">
+      <c r="N29" s="160">
         <f>N24*N10</f>
         <v/>
       </c>
@@ -8314,43 +8322,43 @@
           <t>Depreciation &amp; Amortization</t>
         </is>
       </c>
-      <c r="C30" s="165" t="inlineStr">
+      <c r="C30" s="166" t="inlineStr">
         <is>
           <t>eqn: AvgPPE × DA%</t>
         </is>
       </c>
-      <c r="E30" s="162" t="n">
+      <c r="E30" s="163" t="n">
         <v>25592</v>
       </c>
-      <c r="F30" s="162" t="n">
+      <c r="F30" s="163" t="n">
         <v>20465</v>
       </c>
-      <c r="G30" s="162" t="n">
+      <c r="G30" s="163" t="n">
         <v>14638</v>
       </c>
-      <c r="H30" s="162" t="n">
+      <c r="H30" s="163" t="n">
         <v>13827</v>
       </c>
-      <c r="I30" s="162" t="n">
+      <c r="I30" s="163" t="n">
         <v>14952</v>
       </c>
-      <c r="J30" s="159">
+      <c r="J30" s="160">
         <f>((J92+(J92+J93))/2)*J11</f>
         <v/>
       </c>
-      <c r="K30" s="159">
+      <c r="K30" s="160">
         <f>((K92+(K92+K93))/2)*K11</f>
         <v/>
       </c>
-      <c r="L30" s="159">
+      <c r="L30" s="160">
         <f>((L92+(L92+L93))/2)*L11</f>
         <v/>
       </c>
-      <c r="M30" s="159">
+      <c r="M30" s="160">
         <f>((M92+(M92+M93))/2)*M11</f>
         <v/>
       </c>
-      <c r="N30" s="159">
+      <c r="N30" s="160">
         <f>((N92+(N92+N93))/2)*N11</f>
         <v/>
       </c>
@@ -8361,44 +8369,44 @@
           <t>Interest</t>
         </is>
       </c>
-      <c r="C31" s="166" t="inlineStr">
+      <c r="C31" s="167" t="inlineStr">
         <is>
           <t>eqn: Debt_open × Int%</t>
         </is>
       </c>
       <c r="D31" s="24" t="n"/>
-      <c r="E31" s="167" t="n">
+      <c r="E31" s="168" t="n">
         <v>40092</v>
       </c>
-      <c r="F31" s="167" t="n">
+      <c r="F31" s="168" t="n">
         <v>68967</v>
       </c>
-      <c r="G31" s="167" t="n">
+      <c r="G31" s="168" t="n">
         <v>95546</v>
       </c>
-      <c r="H31" s="167" t="n">
+      <c r="H31" s="168" t="n">
         <v>105638</v>
       </c>
-      <c r="I31" s="167" t="n">
+      <c r="I31" s="168" t="n">
         <v>133647</v>
       </c>
-      <c r="J31" s="159">
+      <c r="J31" s="160">
         <f>J98*J12</f>
         <v/>
       </c>
-      <c r="K31" s="159">
+      <c r="K31" s="160">
         <f>K98*K12</f>
         <v/>
       </c>
-      <c r="L31" s="159">
+      <c r="L31" s="160">
         <f>L98*L12</f>
         <v/>
       </c>
-      <c r="M31" s="159">
+      <c r="M31" s="160">
         <f>M98*M12</f>
         <v/>
       </c>
-      <c r="N31" s="159">
+      <c r="N31" s="160">
         <f>N98*N12</f>
         <v/>
       </c>
@@ -8411,43 +8419,43 @@
       </c>
       <c r="C32" s="19" t="n"/>
       <c r="D32" s="47" t="n"/>
-      <c r="E32" s="168">
+      <c r="E32" s="169">
         <f>SUM(E28:E31)</f>
         <v/>
       </c>
-      <c r="F32" s="168">
+      <c r="F32" s="169">
         <f>SUM(F28:F31)</f>
         <v/>
       </c>
-      <c r="G32" s="168">
+      <c r="G32" s="169">
         <f>SUM(G28:G31)</f>
         <v/>
       </c>
-      <c r="H32" s="168">
+      <c r="H32" s="169">
         <f>SUM(H28:H31)</f>
         <v/>
       </c>
-      <c r="I32" s="168">
+      <c r="I32" s="169">
         <f>SUM(I28:I31)</f>
         <v/>
       </c>
-      <c r="J32" s="159">
+      <c r="J32" s="160">
         <f>SUM(J28:J31)</f>
         <v/>
       </c>
-      <c r="K32" s="159">
+      <c r="K32" s="160">
         <f>SUM(K28:K31)</f>
         <v/>
       </c>
-      <c r="L32" s="159">
+      <c r="L32" s="160">
         <f>SUM(L28:L31)</f>
         <v/>
       </c>
-      <c r="M32" s="159">
+      <c r="M32" s="160">
         <f>SUM(M28:M31)</f>
         <v/>
       </c>
-      <c r="N32" s="159">
+      <c r="N32" s="160">
         <f>SUM(N28:N31)</f>
         <v/>
       </c>
@@ -8458,49 +8466,49 @@
           <t>Earnings Before Tax</t>
         </is>
       </c>
-      <c r="C33" s="163" t="inlineStr">
+      <c r="C33" s="164" t="inlineStr">
         <is>
           <t>eqn: GP − Expenses</t>
         </is>
       </c>
       <c r="D33" s="22" t="n"/>
-      <c r="E33" s="164">
+      <c r="E33" s="165">
         <f>E26-E32</f>
         <v/>
       </c>
-      <c r="F33" s="164">
+      <c r="F33" s="165">
         <f>F26-F32</f>
         <v/>
       </c>
-      <c r="G33" s="164">
+      <c r="G33" s="165">
         <f>G26-G32</f>
         <v/>
       </c>
-      <c r="H33" s="164">
+      <c r="H33" s="165">
         <f>H26-H32</f>
         <v/>
       </c>
-      <c r="I33" s="164">
+      <c r="I33" s="165">
         <f>I26-I32</f>
         <v/>
       </c>
-      <c r="J33" s="159">
+      <c r="J33" s="160">
         <f>J26-J32</f>
         <v/>
       </c>
-      <c r="K33" s="159">
+      <c r="K33" s="160">
         <f>K26-K32</f>
         <v/>
       </c>
-      <c r="L33" s="159">
+      <c r="L33" s="160">
         <f>L26-L32</f>
         <v/>
       </c>
-      <c r="M33" s="159">
+      <c r="M33" s="160">
         <f>M26-M32</f>
         <v/>
       </c>
-      <c r="N33" s="159">
+      <c r="N33" s="160">
         <f>N26-N32</f>
         <v/>
       </c>
@@ -8526,44 +8534,44 @@
           <t>Taxes</t>
         </is>
       </c>
-      <c r="C35" s="161" t="inlineStr">
+      <c r="C35" s="162" t="inlineStr">
         <is>
           <t>eqn: EBT × tax%</t>
         </is>
       </c>
       <c r="D35" s="47" t="n"/>
-      <c r="E35" s="162" t="n">
+      <c r="E35" s="163" t="n">
         <v>81058</v>
       </c>
-      <c r="F35" s="162" t="n">
+      <c r="F35" s="163" t="n">
         <v>97768</v>
       </c>
-      <c r="G35" s="162" t="n">
+      <c r="G35" s="163" t="n">
         <v>124249</v>
       </c>
-      <c r="H35" s="162" t="n">
+      <c r="H35" s="163" t="n">
         <v>129214</v>
       </c>
-      <c r="I35" s="162" t="n">
+      <c r="I35" s="163" t="n">
         <v>150649</v>
       </c>
-      <c r="J35" s="159">
+      <c r="J35" s="160">
         <f>J33*J13</f>
         <v/>
       </c>
-      <c r="K35" s="159">
+      <c r="K35" s="160">
         <f>K33*K13</f>
         <v/>
       </c>
-      <c r="L35" s="159">
+      <c r="L35" s="160">
         <f>L33*L13</f>
         <v/>
       </c>
-      <c r="M35" s="159">
+      <c r="M35" s="160">
         <f>M33*M13</f>
         <v/>
       </c>
-      <c r="N35" s="159">
+      <c r="N35" s="160">
         <f>N33*N13</f>
         <v/>
       </c>
@@ -8574,49 +8582,49 @@
           <t>Net Earnings</t>
         </is>
       </c>
-      <c r="C36" s="169" t="inlineStr">
+      <c r="C36" s="170" t="inlineStr">
         <is>
           <t>eqn: EBT × (1 − tax%)</t>
         </is>
       </c>
       <c r="D36" s="40" t="n"/>
-      <c r="E36" s="170">
+      <c r="E36" s="171">
         <f>E33-E35</f>
         <v/>
       </c>
-      <c r="F36" s="170">
+      <c r="F36" s="171">
         <f>F33-F35</f>
         <v/>
       </c>
-      <c r="G36" s="170">
+      <c r="G36" s="171">
         <f>G33-G35</f>
         <v/>
       </c>
-      <c r="H36" s="170">
+      <c r="H36" s="171">
         <f>H33-H35</f>
         <v/>
       </c>
-      <c r="I36" s="170">
+      <c r="I36" s="171">
         <f>I33-I35</f>
         <v/>
       </c>
-      <c r="J36" s="159">
+      <c r="J36" s="160">
         <f>J33*(1-J13)</f>
         <v/>
       </c>
-      <c r="K36" s="159">
+      <c r="K36" s="160">
         <f>K33*(1-K13)</f>
         <v/>
       </c>
-      <c r="L36" s="159">
+      <c r="L36" s="160">
         <f>L33*(1-L13)</f>
         <v/>
       </c>
-      <c r="M36" s="159">
+      <c r="M36" s="160">
         <f>M33*(1-M13)</f>
         <v/>
       </c>
-      <c r="N36" s="159">
+      <c r="N36" s="160">
         <f>N33*(1-N13)</f>
         <v/>
       </c>
@@ -8677,38 +8685,38 @@
           <t>Cash</t>
         </is>
       </c>
-      <c r="E41" s="162" t="n">
+      <c r="E41" s="163" t="n">
         <v>195354</v>
       </c>
-      <c r="F41" s="162" t="n">
+      <c r="F41" s="163" t="n">
         <v>133202</v>
       </c>
-      <c r="G41" s="162" t="n">
+      <c r="G41" s="163" t="n">
         <v>136778</v>
       </c>
-      <c r="H41" s="162" t="n">
+      <c r="H41" s="163" t="n">
         <v>150667</v>
       </c>
-      <c r="I41" s="162" t="n">
+      <c r="I41" s="163" t="n">
         <v>134136</v>
       </c>
-      <c r="J41" s="159">
+      <c r="J41" s="160">
         <f>J78</f>
         <v/>
       </c>
-      <c r="K41" s="159">
+      <c r="K41" s="160">
         <f>K78</f>
         <v/>
       </c>
-      <c r="L41" s="159">
+      <c r="L41" s="160">
         <f>L78</f>
         <v/>
       </c>
-      <c r="M41" s="159">
+      <c r="M41" s="160">
         <f>M78</f>
         <v/>
       </c>
-      <c r="N41" s="159">
+      <c r="N41" s="160">
         <f>N78</f>
         <v/>
       </c>
@@ -8719,43 +8727,43 @@
           <t>Accounts Receivable</t>
         </is>
       </c>
-      <c r="C42" s="165" t="inlineStr">
+      <c r="C42" s="166" t="inlineStr">
         <is>
           <t>eqn: NWC + AP + Deferred − Inv  (plug to NWC%)</t>
         </is>
       </c>
-      <c r="E42" s="162" t="n">
+      <c r="E42" s="163" t="n">
         <v>312107</v>
       </c>
-      <c r="F42" s="162" t="n">
+      <c r="F42" s="163" t="n">
         <v>322410</v>
       </c>
-      <c r="G42" s="162" t="n">
+      <c r="G42" s="163" t="n">
         <v>387947</v>
       </c>
-      <c r="H42" s="162" t="n">
+      <c r="H42" s="163" t="n">
         <v>426642</v>
       </c>
-      <c r="I42" s="162" t="n">
+      <c r="I42" s="163" t="n">
         <v>529148</v>
       </c>
-      <c r="J42" s="159">
+      <c r="J42" s="160">
         <f>J89+J48+J88-J43</f>
         <v/>
       </c>
-      <c r="K42" s="159">
+      <c r="K42" s="160">
         <f>K89+K48+K88-K43</f>
         <v/>
       </c>
-      <c r="L42" s="159">
+      <c r="L42" s="160">
         <f>L89+L48+L88-L43</f>
         <v/>
       </c>
-      <c r="M42" s="159">
+      <c r="M42" s="160">
         <f>M89+M48+M88-M43</f>
         <v/>
       </c>
-      <c r="N42" s="159">
+      <c r="N42" s="160">
         <f>N89+N48+N88-N43</f>
         <v/>
       </c>
@@ -8766,38 +8774,38 @@
           <t>Inventory</t>
         </is>
       </c>
-      <c r="E43" s="162" t="n">
+      <c r="E43" s="163" t="n">
         <v>0</v>
       </c>
-      <c r="F43" s="162" t="n">
+      <c r="F43" s="163" t="n">
         <v>0</v>
       </c>
-      <c r="G43" s="162" t="n">
+      <c r="G43" s="163" t="n">
         <v>0</v>
       </c>
-      <c r="H43" s="162" t="n">
+      <c r="H43" s="163" t="n">
         <v>0</v>
       </c>
-      <c r="I43" s="162" t="n">
+      <c r="I43" s="163" t="n">
         <v>0</v>
       </c>
-      <c r="J43" s="159">
+      <c r="J43" s="160">
         <f>J25*J16/365</f>
         <v/>
       </c>
-      <c r="K43" s="159">
+      <c r="K43" s="160">
         <f>K25*K16/365</f>
         <v/>
       </c>
-      <c r="L43" s="159">
+      <c r="L43" s="160">
         <f>L25*L16/365</f>
         <v/>
       </c>
-      <c r="M43" s="159">
+      <c r="M43" s="160">
         <f>M25*M16/365</f>
         <v/>
       </c>
-      <c r="N43" s="159">
+      <c r="N43" s="160">
         <f>N25*N16/365</f>
         <v/>
       </c>
@@ -8808,38 +8816,38 @@
           <t>Property &amp; Equipment</t>
         </is>
       </c>
-      <c r="E44" s="162" t="n">
+      <c r="E44" s="163" t="n">
         <v>27913</v>
       </c>
-      <c r="F44" s="162" t="n">
+      <c r="F44" s="163" t="n">
         <v>17580</v>
       </c>
-      <c r="G44" s="162" t="n">
+      <c r="G44" s="163" t="n">
         <v>10966</v>
       </c>
-      <c r="H44" s="162" t="n">
+      <c r="H44" s="163" t="n">
         <v>38465</v>
       </c>
-      <c r="I44" s="162" t="n">
+      <c r="I44" s="163" t="n">
         <v>67713</v>
       </c>
-      <c r="J44" s="159">
+      <c r="J44" s="160">
         <f>J95</f>
         <v/>
       </c>
-      <c r="K44" s="159">
+      <c r="K44" s="160">
         <f>K95</f>
         <v/>
       </c>
-      <c r="L44" s="159">
+      <c r="L44" s="160">
         <f>L95</f>
         <v/>
       </c>
-      <c r="M44" s="159">
+      <c r="M44" s="160">
         <f>M95</f>
         <v/>
       </c>
-      <c r="N44" s="159">
+      <c r="N44" s="160">
         <f>N95</f>
         <v/>
       </c>
@@ -8852,43 +8860,43 @@
       </c>
       <c r="C45" s="39" t="n"/>
       <c r="D45" s="40" t="n"/>
-      <c r="E45" s="170">
+      <c r="E45" s="171">
         <f>SUM(E41:E44)</f>
         <v/>
       </c>
-      <c r="F45" s="170">
+      <c r="F45" s="171">
         <f>SUM(F41:F44)</f>
         <v/>
       </c>
-      <c r="G45" s="170">
+      <c r="G45" s="171">
         <f>SUM(G41:G44)</f>
         <v/>
       </c>
-      <c r="H45" s="170">
+      <c r="H45" s="171">
         <f>SUM(H41:H44)</f>
         <v/>
       </c>
-      <c r="I45" s="170">
+      <c r="I45" s="171">
         <f>SUM(I41:I44)</f>
         <v/>
       </c>
-      <c r="J45" s="159">
+      <c r="J45" s="160">
         <f>SUM(J41:J44)</f>
         <v/>
       </c>
-      <c r="K45" s="159">
+      <c r="K45" s="160">
         <f>SUM(K41:K44)</f>
         <v/>
       </c>
-      <c r="L45" s="159">
+      <c r="L45" s="160">
         <f>SUM(L41:L44)</f>
         <v/>
       </c>
-      <c r="M45" s="159">
+      <c r="M45" s="160">
         <f>SUM(M41:M44)</f>
         <v/>
       </c>
-      <c r="N45" s="159">
+      <c r="N45" s="160">
         <f>SUM(N41:N44)</f>
         <v/>
       </c>
@@ -8926,43 +8934,43 @@
           <t>Accounts Payable</t>
         </is>
       </c>
-      <c r="C48" s="165" t="inlineStr">
+      <c r="C48" s="166" t="inlineStr">
         <is>
           <t>eqn: COGS × AP_days / 365</t>
         </is>
       </c>
-      <c r="E48" s="162" t="n">
+      <c r="E48" s="163" t="n">
         <v>20749</v>
       </c>
-      <c r="F48" s="162" t="n">
+      <c r="F48" s="163" t="n">
         <v>17273</v>
       </c>
-      <c r="G48" s="162" t="n">
+      <c r="G48" s="163" t="n">
         <v>19009</v>
       </c>
-      <c r="H48" s="162" t="n">
+      <c r="H48" s="163" t="n">
         <v>22473</v>
       </c>
-      <c r="I48" s="162" t="n">
+      <c r="I48" s="163" t="n">
         <v>32315</v>
       </c>
-      <c r="J48" s="159">
+      <c r="J48" s="160">
         <f>J25*J17/365</f>
         <v/>
       </c>
-      <c r="K48" s="159">
+      <c r="K48" s="160">
         <f>K25*K17/365</f>
         <v/>
       </c>
-      <c r="L48" s="159">
+      <c r="L48" s="160">
         <f>L25*L17/365</f>
         <v/>
       </c>
-      <c r="M48" s="159">
+      <c r="M48" s="160">
         <f>M25*M17/365</f>
         <v/>
       </c>
-      <c r="N48" s="159">
+      <c r="N48" s="160">
         <f>N25*N17/365</f>
         <v/>
       </c>
@@ -8973,38 +8981,38 @@
           <t>Debt</t>
         </is>
       </c>
-      <c r="E49" s="162" t="n">
+      <c r="E49" s="163" t="n">
         <v>1259018</v>
       </c>
-      <c r="F49" s="162" t="n">
+      <c r="F49" s="163" t="n">
         <v>1853669</v>
       </c>
-      <c r="G49" s="162" t="n">
+      <c r="G49" s="163" t="n">
         <v>1861658</v>
       </c>
-      <c r="H49" s="162" t="n">
+      <c r="H49" s="163" t="n">
         <v>2209021</v>
       </c>
-      <c r="I49" s="162" t="n">
+      <c r="I49" s="163" t="n">
         <v>3055691</v>
       </c>
-      <c r="J49" s="159">
+      <c r="J49" s="160">
         <f>J100</f>
         <v/>
       </c>
-      <c r="K49" s="159">
+      <c r="K49" s="160">
         <f>K100</f>
         <v/>
       </c>
-      <c r="L49" s="159">
+      <c r="L49" s="160">
         <f>L100</f>
         <v/>
       </c>
-      <c r="M49" s="159">
+      <c r="M49" s="160">
         <f>M100</f>
         <v/>
       </c>
-      <c r="N49" s="159">
+      <c r="N49" s="160">
         <f>N100</f>
         <v/>
       </c>
@@ -9015,49 +9023,49 @@
           <t>Total Liabilities</t>
         </is>
       </c>
-      <c r="C50" s="163" t="inlineStr">
+      <c r="C50" s="164" t="inlineStr">
         <is>
           <t>eqn: AP + Debt + DeferredRev</t>
         </is>
       </c>
       <c r="D50" s="22" t="n"/>
-      <c r="E50" s="171">
+      <c r="E50" s="172">
         <f>E48+E49+E88</f>
         <v/>
       </c>
-      <c r="F50" s="171">
+      <c r="F50" s="172">
         <f>F48+F49+F88</f>
         <v/>
       </c>
-      <c r="G50" s="171">
+      <c r="G50" s="172">
         <f>G48+G49+G88</f>
         <v/>
       </c>
-      <c r="H50" s="171">
+      <c r="H50" s="172">
         <f>H48+H49+H88</f>
         <v/>
       </c>
-      <c r="I50" s="171">
+      <c r="I50" s="172">
         <f>I48+I49+I88</f>
         <v/>
       </c>
-      <c r="J50" s="159">
+      <c r="J50" s="160">
         <f>J48+J49+J88</f>
         <v/>
       </c>
-      <c r="K50" s="159">
+      <c r="K50" s="160">
         <f>K48+K49+K88</f>
         <v/>
       </c>
-      <c r="L50" s="159">
+      <c r="L50" s="160">
         <f>L48+L49+L88</f>
         <v/>
       </c>
-      <c r="M50" s="159">
+      <c r="M50" s="160">
         <f>M48+M49+M88</f>
         <v/>
       </c>
-      <c r="N50" s="159">
+      <c r="N50" s="160">
         <f>N48+N49+N88</f>
         <v/>
       </c>
@@ -9080,38 +9088,38 @@
           <t>Equity Capital</t>
         </is>
       </c>
-      <c r="E52" s="162" t="n">
+      <c r="E52" s="163" t="n">
         <v>-849810</v>
       </c>
-      <c r="F52" s="162" t="n">
+      <c r="F52" s="163" t="n">
         <v>-1517795</v>
       </c>
-      <c r="G52" s="162" t="n">
+      <c r="G52" s="163" t="n">
         <v>-1481706</v>
       </c>
-      <c r="H52" s="162" t="n">
+      <c r="H52" s="163" t="n">
         <v>-1772617</v>
       </c>
-      <c r="I52" s="162" t="n">
+      <c r="I52" s="163" t="n">
         <v>-2544381</v>
       </c>
-      <c r="J52" s="159">
+      <c r="J52" s="160">
         <f>I52+J20</f>
         <v/>
       </c>
-      <c r="K52" s="159">
+      <c r="K52" s="160">
         <f>J52+K20</f>
         <v/>
       </c>
-      <c r="L52" s="159">
+      <c r="L52" s="160">
         <f>K52+L20</f>
         <v/>
       </c>
-      <c r="M52" s="159">
+      <c r="M52" s="160">
         <f>L52+M20</f>
         <v/>
       </c>
-      <c r="N52" s="159">
+      <c r="N52" s="160">
         <f>M52+N20</f>
         <v/>
       </c>
@@ -9122,43 +9130,43 @@
           <t>Retained Earnings</t>
         </is>
       </c>
-      <c r="C53" s="165" t="inlineStr">
+      <c r="C53" s="166" t="inlineStr">
         <is>
           <t>eqn: PriorRE + EBT×(1−t)</t>
         </is>
       </c>
-      <c r="E53" s="162" t="n">
+      <c r="E53" s="163" t="n">
         <v>0</v>
       </c>
-      <c r="F53" s="162" t="n">
+      <c r="F53" s="163" t="n">
         <v>0</v>
       </c>
-      <c r="G53" s="162" t="n">
+      <c r="G53" s="163" t="n">
         <v>0</v>
       </c>
-      <c r="H53" s="162" t="n">
+      <c r="H53" s="163" t="n">
         <v>0</v>
       </c>
-      <c r="I53" s="162" t="n">
+      <c r="I53" s="163" t="n">
         <v>0</v>
       </c>
-      <c r="J53" s="159">
+      <c r="J53" s="160">
         <f>I53+J33*(1-J13)</f>
         <v/>
       </c>
-      <c r="K53" s="159">
+      <c r="K53" s="160">
         <f>J53+K33*(1-K13)</f>
         <v/>
       </c>
-      <c r="L53" s="159">
+      <c r="L53" s="160">
         <f>K53+L33*(1-L13)</f>
         <v/>
       </c>
-      <c r="M53" s="159">
+      <c r="M53" s="160">
         <f>L53+M33*(1-M13)</f>
         <v/>
       </c>
-      <c r="N53" s="159">
+      <c r="N53" s="160">
         <f>M53+N33*(1-N13)</f>
         <v/>
       </c>
@@ -9171,43 +9179,43 @@
       </c>
       <c r="C54" s="8" t="n"/>
       <c r="D54" s="26" t="n"/>
-      <c r="E54" s="172">
+      <c r="E54" s="173">
         <f>SUM(E52:E53)</f>
         <v/>
       </c>
-      <c r="F54" s="172">
+      <c r="F54" s="173">
         <f>SUM(F52:F53)</f>
         <v/>
       </c>
-      <c r="G54" s="172">
+      <c r="G54" s="173">
         <f>SUM(G52:G53)</f>
         <v/>
       </c>
-      <c r="H54" s="172">
+      <c r="H54" s="173">
         <f>SUM(H52:H53)</f>
         <v/>
       </c>
-      <c r="I54" s="172">
+      <c r="I54" s="173">
         <f>SUM(I52:I53)</f>
         <v/>
       </c>
-      <c r="J54" s="159">
+      <c r="J54" s="160">
         <f>SUM(J52:J53)</f>
         <v/>
       </c>
-      <c r="K54" s="159">
+      <c r="K54" s="160">
         <f>SUM(K52:K53)</f>
         <v/>
       </c>
-      <c r="L54" s="159">
+      <c r="L54" s="160">
         <f>SUM(L52:L53)</f>
         <v/>
       </c>
-      <c r="M54" s="159">
+      <c r="M54" s="160">
         <f>SUM(M52:M53)</f>
         <v/>
       </c>
-      <c r="N54" s="159">
+      <c r="N54" s="160">
         <f>SUM(N52:N53)</f>
         <v/>
       </c>
@@ -9220,43 +9228,43 @@
       </c>
       <c r="C55" s="39" t="n"/>
       <c r="D55" s="40" t="n"/>
-      <c r="E55" s="170">
+      <c r="E55" s="171">
         <f>E50+E54</f>
         <v/>
       </c>
-      <c r="F55" s="170">
+      <c r="F55" s="171">
         <f>F50+F54</f>
         <v/>
       </c>
-      <c r="G55" s="170">
+      <c r="G55" s="171">
         <f>G50+G54</f>
         <v/>
       </c>
-      <c r="H55" s="170">
+      <c r="H55" s="171">
         <f>H50+H54</f>
         <v/>
       </c>
-      <c r="I55" s="170">
+      <c r="I55" s="171">
         <f>I50+I54</f>
         <v/>
       </c>
-      <c r="J55" s="159">
+      <c r="J55" s="160">
         <f>J50+J54</f>
         <v/>
       </c>
-      <c r="K55" s="159">
+      <c r="K55" s="160">
         <f>K50+K54</f>
         <v/>
       </c>
-      <c r="L55" s="159">
+      <c r="L55" s="160">
         <f>L50+L54</f>
         <v/>
       </c>
-      <c r="M55" s="159">
+      <c r="M55" s="160">
         <f>M50+M54</f>
         <v/>
       </c>
-      <c r="N55" s="159">
+      <c r="N55" s="160">
         <f>N50+N54</f>
         <v/>
       </c>
@@ -9281,43 +9289,43 @@
       </c>
       <c r="C57" s="9" t="n"/>
       <c r="D57" s="27" t="n"/>
-      <c r="E57" s="173">
+      <c r="E57" s="174">
         <f>E55-E45</f>
         <v/>
       </c>
-      <c r="F57" s="173">
+      <c r="F57" s="174">
         <f>F55-F45</f>
         <v/>
       </c>
-      <c r="G57" s="173">
+      <c r="G57" s="174">
         <f>G55-G45</f>
         <v/>
       </c>
-      <c r="H57" s="173">
+      <c r="H57" s="174">
         <f>H55-H45</f>
         <v/>
       </c>
-      <c r="I57" s="173">
+      <c r="I57" s="174">
         <f>I55-I45</f>
         <v/>
       </c>
-      <c r="J57" s="159">
+      <c r="J57" s="160">
         <f>J55-J45</f>
         <v/>
       </c>
-      <c r="K57" s="159">
+      <c r="K57" s="160">
         <f>K55-K45</f>
         <v/>
       </c>
-      <c r="L57" s="159">
+      <c r="L57" s="160">
         <f>L55-L45</f>
         <v/>
       </c>
-      <c r="M57" s="159">
+      <c r="M57" s="160">
         <f>M55-M45</f>
         <v/>
       </c>
-      <c r="N57" s="159">
+      <c r="N57" s="160">
         <f>N55-N45</f>
         <v/>
       </c>
@@ -9381,48 +9389,48 @@
           <t>Net Earnings</t>
         </is>
       </c>
-      <c r="C62" s="165" t="inlineStr">
+      <c r="C62" s="166" t="inlineStr">
         <is>
           <t>eqn: EBT × (1 − tax%)</t>
         </is>
       </c>
-      <c r="E62" s="174">
+      <c r="E62" s="175">
         <f>E36</f>
         <v/>
       </c>
-      <c r="F62" s="174">
+      <c r="F62" s="175">
         <f>F36</f>
         <v/>
       </c>
-      <c r="G62" s="174">
+      <c r="G62" s="175">
         <f>G36</f>
         <v/>
       </c>
-      <c r="H62" s="174">
+      <c r="H62" s="175">
         <f>H36</f>
         <v/>
       </c>
-      <c r="I62" s="174">
+      <c r="I62" s="175">
         <f>I36</f>
         <v/>
       </c>
-      <c r="J62" s="159">
+      <c r="J62" s="160">
         <f>J33*(1-J13)</f>
         <v/>
       </c>
-      <c r="K62" s="159">
+      <c r="K62" s="160">
         <f>K33*(1-K13)</f>
         <v/>
       </c>
-      <c r="L62" s="159">
+      <c r="L62" s="160">
         <f>L33*(1-L13)</f>
         <v/>
       </c>
-      <c r="M62" s="159">
+      <c r="M62" s="160">
         <f>M33*(1-M13)</f>
         <v/>
       </c>
-      <c r="N62" s="159">
+      <c r="N62" s="160">
         <f>N33*(1-N13)</f>
         <v/>
       </c>
@@ -9433,48 +9441,48 @@
           <t>Plus: Depreciation &amp; Amortization</t>
         </is>
       </c>
-      <c r="C63" s="165" t="inlineStr">
+      <c r="C63" s="166" t="inlineStr">
         <is>
           <t>eqn: AvgPPE × DA%</t>
         </is>
       </c>
-      <c r="E63" s="174">
+      <c r="E63" s="175">
         <f>+E30</f>
         <v/>
       </c>
-      <c r="F63" s="174">
+      <c r="F63" s="175">
         <f>+F30</f>
         <v/>
       </c>
-      <c r="G63" s="174">
+      <c r="G63" s="175">
         <f>+G30</f>
         <v/>
       </c>
-      <c r="H63" s="174">
+      <c r="H63" s="175">
         <f>+H30</f>
         <v/>
       </c>
-      <c r="I63" s="174">
+      <c r="I63" s="175">
         <f>+I30</f>
         <v/>
       </c>
-      <c r="J63" s="159">
+      <c r="J63" s="160">
         <f>((J92+(J92+J93))/2)*J11</f>
         <v/>
       </c>
-      <c r="K63" s="159">
+      <c r="K63" s="160">
         <f>((K92+(K92+K93))/2)*K11</f>
         <v/>
       </c>
-      <c r="L63" s="159">
+      <c r="L63" s="160">
         <f>((L92+(L92+L93))/2)*L11</f>
         <v/>
       </c>
-      <c r="M63" s="159">
+      <c r="M63" s="160">
         <f>((M92+(M92+M93))/2)*M11</f>
         <v/>
       </c>
-      <c r="N63" s="159">
+      <c r="N63" s="160">
         <f>((N92+(N92+N93))/2)*N11</f>
         <v/>
       </c>
@@ -9485,43 +9493,43 @@
           <t>Less: Changes in Working Capital</t>
         </is>
       </c>
-      <c r="C64" s="165" t="inlineStr">
+      <c r="C64" s="166" t="inlineStr">
         <is>
           <t>eqn: ΔNWC from consolidated NWC% of sales</t>
         </is>
       </c>
-      <c r="E64" s="162" t="n">
+      <c r="E64" s="163" t="n">
         <v>0</v>
       </c>
-      <c r="F64" s="162" t="n">
+      <c r="F64" s="163" t="n">
         <v>-849</v>
       </c>
-      <c r="G64" s="162" t="n">
+      <c r="G64" s="163" t="n">
         <v>47116</v>
       </c>
-      <c r="H64" s="162" t="n">
+      <c r="H64" s="163" t="n">
         <v>15064</v>
       </c>
-      <c r="I64" s="162" t="n">
+      <c r="I64" s="163" t="n">
         <v>62189</v>
       </c>
-      <c r="J64" s="159">
+      <c r="J64" s="160">
         <f>J90</f>
         <v/>
       </c>
-      <c r="K64" s="159">
+      <c r="K64" s="160">
         <f>K90</f>
         <v/>
       </c>
-      <c r="L64" s="159">
+      <c r="L64" s="160">
         <f>L90</f>
         <v/>
       </c>
-      <c r="M64" s="159">
+      <c r="M64" s="160">
         <f>M90</f>
         <v/>
       </c>
-      <c r="N64" s="159">
+      <c r="N64" s="160">
         <f>N90</f>
         <v/>
       </c>
@@ -9532,49 +9540,49 @@
           <t>Cash from Operations</t>
         </is>
       </c>
-      <c r="C65" s="163" t="inlineStr">
+      <c r="C65" s="164" t="inlineStr">
         <is>
           <t>eqn: NI + DA − ΔNWC</t>
         </is>
       </c>
       <c r="D65" s="28" t="n"/>
-      <c r="E65" s="164">
+      <c r="E65" s="165">
         <f>E62+E63-E64</f>
         <v/>
       </c>
-      <c r="F65" s="164">
+      <c r="F65" s="165">
         <f>F62+F63-F64</f>
         <v/>
       </c>
-      <c r="G65" s="164">
+      <c r="G65" s="165">
         <f>G62+G63-G64</f>
         <v/>
       </c>
-      <c r="H65" s="164">
+      <c r="H65" s="165">
         <f>H62+H63-H64</f>
         <v/>
       </c>
-      <c r="I65" s="164">
+      <c r="I65" s="165">
         <f>I62+I63-I64</f>
         <v/>
       </c>
-      <c r="J65" s="159">
+      <c r="J65" s="160">
         <f>J33*(1-J13)+(((J92+(J92+J93))/2)*J11)-J90</f>
         <v/>
       </c>
-      <c r="K65" s="159">
+      <c r="K65" s="160">
         <f>K33*(1-K13)+(((K92+(K92+K93))/2)*K11)-K90</f>
         <v/>
       </c>
-      <c r="L65" s="159">
+      <c r="L65" s="160">
         <f>L33*(1-L13)+(((L92+(L92+L93))/2)*L11)-L90</f>
         <v/>
       </c>
-      <c r="M65" s="159">
+      <c r="M65" s="160">
         <f>M33*(1-M13)+(((M92+(M92+M93))/2)*M11)-M90</f>
         <v/>
       </c>
-      <c r="N65" s="159">
+      <c r="N65" s="160">
         <f>N33*(1-N13)+(((N92+(N92+N93))/2)*N11)-N90</f>
         <v/>
       </c>
@@ -9617,43 +9625,43 @@
           <t>Investments in Property &amp; Equipment</t>
         </is>
       </c>
-      <c r="C68" s="165" t="inlineStr">
+      <c r="C68" s="166" t="inlineStr">
         <is>
           <t>eqn: Rev × CapEx%</t>
         </is>
       </c>
-      <c r="E68" s="162" t="n">
+      <c r="E68" s="163" t="n">
         <v>7569</v>
       </c>
-      <c r="F68" s="162" t="n">
+      <c r="F68" s="163" t="n">
         <v>6029</v>
       </c>
-      <c r="G68" s="162" t="n">
+      <c r="G68" s="163" t="n">
         <v>4237</v>
       </c>
-      <c r="H68" s="162" t="n">
+      <c r="H68" s="163" t="n">
         <v>25551</v>
       </c>
-      <c r="I68" s="162" t="n">
+      <c r="I68" s="163" t="n">
         <v>39407</v>
       </c>
-      <c r="J68" s="159">
+      <c r="J68" s="160">
         <f>J24*J18</f>
         <v/>
       </c>
-      <c r="K68" s="159">
+      <c r="K68" s="160">
         <f>K24*K18</f>
         <v/>
       </c>
-      <c r="L68" s="159">
+      <c r="L68" s="160">
         <f>L24*L18</f>
         <v/>
       </c>
-      <c r="M68" s="159">
+      <c r="M68" s="160">
         <f>M24*M18</f>
         <v/>
       </c>
-      <c r="N68" s="159">
+      <c r="N68" s="160">
         <f>N24*N18</f>
         <v/>
       </c>
@@ -9666,43 +9674,43 @@
       </c>
       <c r="C69" s="5" t="n"/>
       <c r="D69" s="28" t="n"/>
-      <c r="E69" s="164">
+      <c r="E69" s="165">
         <f>SUM(E68)</f>
         <v/>
       </c>
-      <c r="F69" s="164">
+      <c r="F69" s="165">
         <f>SUM(F68)</f>
         <v/>
       </c>
-      <c r="G69" s="164">
+      <c r="G69" s="165">
         <f>SUM(G68)</f>
         <v/>
       </c>
-      <c r="H69" s="164">
+      <c r="H69" s="165">
         <f>SUM(H68)</f>
         <v/>
       </c>
-      <c r="I69" s="164">
+      <c r="I69" s="165">
         <f>SUM(I68)</f>
         <v/>
       </c>
-      <c r="J69" s="159">
+      <c r="J69" s="160">
         <f>J68</f>
         <v/>
       </c>
-      <c r="K69" s="159">
+      <c r="K69" s="160">
         <f>K68</f>
         <v/>
       </c>
-      <c r="L69" s="159">
+      <c r="L69" s="160">
         <f>L68</f>
         <v/>
       </c>
-      <c r="M69" s="159">
+      <c r="M69" s="160">
         <f>M68</f>
         <v/>
       </c>
-      <c r="N69" s="159">
+      <c r="N69" s="160">
         <f>N68</f>
         <v/>
       </c>
@@ -9745,38 +9753,38 @@
           <t>Issuance (repayment) of debt</t>
         </is>
       </c>
-      <c r="E72" s="162" t="n">
+      <c r="E72" s="163" t="n">
         <v>519583</v>
       </c>
-      <c r="F72" s="162" t="n">
+      <c r="F72" s="163" t="n">
         <v>594651</v>
       </c>
-      <c r="G72" s="162" t="n">
+      <c r="G72" s="163" t="n">
         <v>7989</v>
       </c>
-      <c r="H72" s="162" t="n">
+      <c r="H72" s="163" t="n">
         <v>347363</v>
       </c>
-      <c r="I72" s="162" t="n">
+      <c r="I72" s="163" t="n">
         <v>846670</v>
       </c>
-      <c r="J72" s="159">
+      <c r="J72" s="160">
         <f>J19</f>
         <v/>
       </c>
-      <c r="K72" s="159">
+      <c r="K72" s="160">
         <f>K19</f>
         <v/>
       </c>
-      <c r="L72" s="159">
+      <c r="L72" s="160">
         <f>L19</f>
         <v/>
       </c>
-      <c r="M72" s="159">
+      <c r="M72" s="160">
         <f>M19</f>
         <v/>
       </c>
-      <c r="N72" s="159">
+      <c r="N72" s="160">
         <f>N19</f>
         <v/>
       </c>
@@ -9787,38 +9795,38 @@
           <t>Issuance (repayment) of equity</t>
         </is>
       </c>
-      <c r="E73" s="162" t="n">
+      <c r="E73" s="163" t="n">
         <v>0</v>
       </c>
-      <c r="F73" s="162" t="n">
+      <c r="F73" s="163" t="n">
         <v>0</v>
       </c>
-      <c r="G73" s="162" t="n">
+      <c r="G73" s="163" t="n">
         <v>0</v>
       </c>
-      <c r="H73" s="162" t="n">
+      <c r="H73" s="163" t="n">
         <v>0</v>
       </c>
-      <c r="I73" s="162" t="n">
+      <c r="I73" s="163" t="n">
         <v>0</v>
       </c>
-      <c r="J73" s="159">
+      <c r="J73" s="160">
         <f>J20</f>
         <v/>
       </c>
-      <c r="K73" s="159">
+      <c r="K73" s="160">
         <f>K20</f>
         <v/>
       </c>
-      <c r="L73" s="159">
+      <c r="L73" s="160">
         <f>L20</f>
         <v/>
       </c>
-      <c r="M73" s="159">
+      <c r="M73" s="160">
         <f>M20</f>
         <v/>
       </c>
-      <c r="N73" s="159">
+      <c r="N73" s="160">
         <f>N20</f>
         <v/>
       </c>
@@ -9831,43 +9839,43 @@
       </c>
       <c r="C74" s="5" t="n"/>
       <c r="D74" s="28" t="n"/>
-      <c r="E74" s="164">
+      <c r="E74" s="165">
         <f>SUM(E72:E73)</f>
         <v/>
       </c>
-      <c r="F74" s="164">
+      <c r="F74" s="165">
         <f>SUM(F72:F73)</f>
         <v/>
       </c>
-      <c r="G74" s="164">
+      <c r="G74" s="165">
         <f>SUM(G72:G73)</f>
         <v/>
       </c>
-      <c r="H74" s="164">
+      <c r="H74" s="165">
         <f>SUM(H72:H73)</f>
         <v/>
       </c>
-      <c r="I74" s="164">
+      <c r="I74" s="165">
         <f>SUM(I72:I73)</f>
         <v/>
       </c>
-      <c r="J74" s="159">
+      <c r="J74" s="160">
         <f>J19+J20</f>
         <v/>
       </c>
-      <c r="K74" s="159">
+      <c r="K74" s="160">
         <f>K19+K20</f>
         <v/>
       </c>
-      <c r="L74" s="159">
+      <c r="L74" s="160">
         <f>L19+L20</f>
         <v/>
       </c>
-      <c r="M74" s="159">
+      <c r="M74" s="160">
         <f>M19+M20</f>
         <v/>
       </c>
-      <c r="N74" s="159">
+      <c r="N74" s="160">
         <f>N19+N20</f>
         <v/>
       </c>
@@ -9893,48 +9901,48 @@
           <t>Net Increase (decrease) in Cash</t>
         </is>
       </c>
-      <c r="C76" s="165" t="inlineStr">
+      <c r="C76" s="166" t="inlineStr">
         <is>
           <t>eqn: CFO − CapEx + Financing</t>
         </is>
       </c>
-      <c r="E76" s="175">
+      <c r="E76" s="176">
         <f>E41-E77</f>
         <v/>
       </c>
-      <c r="F76" s="175">
+      <c r="F76" s="176">
         <f>F41-F77</f>
         <v/>
       </c>
-      <c r="G76" s="175">
+      <c r="G76" s="176">
         <f>G41-G77</f>
         <v/>
       </c>
-      <c r="H76" s="175">
+      <c r="H76" s="176">
         <f>H41-H77</f>
         <v/>
       </c>
-      <c r="I76" s="175">
+      <c r="I76" s="176">
         <f>I41-I77</f>
         <v/>
       </c>
-      <c r="J76" s="159">
+      <c r="J76" s="160">
         <f>J65-J69+J74</f>
         <v/>
       </c>
-      <c r="K76" s="159">
+      <c r="K76" s="160">
         <f>K65-K69+K74</f>
         <v/>
       </c>
-      <c r="L76" s="159">
+      <c r="L76" s="160">
         <f>L65-L69+L74</f>
         <v/>
       </c>
-      <c r="M76" s="159">
+      <c r="M76" s="160">
         <f>M65-M69+M74</f>
         <v/>
       </c>
-      <c r="N76" s="159">
+      <c r="N76" s="160">
         <f>N65-N69+N74</f>
         <v/>
       </c>
@@ -9945,42 +9953,42 @@
           <t>Opening Cash Balance</t>
         </is>
       </c>
-      <c r="E77" s="162" t="n">
+      <c r="E77" s="163" t="n">
         <v>157394</v>
       </c>
-      <c r="F77" s="175">
+      <c r="F77" s="176">
         <f>E41</f>
         <v/>
       </c>
-      <c r="G77" s="175">
+      <c r="G77" s="176">
         <f>F41</f>
         <v/>
       </c>
-      <c r="H77" s="175">
+      <c r="H77" s="176">
         <f>G41</f>
         <v/>
       </c>
-      <c r="I77" s="175">
+      <c r="I77" s="176">
         <f>H41</f>
         <v/>
       </c>
-      <c r="J77" s="159">
+      <c r="J77" s="160">
         <f>I41</f>
         <v/>
       </c>
-      <c r="K77" s="159">
+      <c r="K77" s="160">
         <f>J41</f>
         <v/>
       </c>
-      <c r="L77" s="159">
+      <c r="L77" s="160">
         <f>K41</f>
         <v/>
       </c>
-      <c r="M77" s="159">
+      <c r="M77" s="160">
         <f>L41</f>
         <v/>
       </c>
-      <c r="N77" s="159">
+      <c r="N77" s="160">
         <f>M41</f>
         <v/>
       </c>
@@ -9992,46 +10000,46 @@
         </is>
       </c>
       <c r="C78" s="5" t="n"/>
-      <c r="D78" s="176" t="n">
+      <c r="D78" s="177" t="n">
         <v>157394</v>
       </c>
-      <c r="E78" s="164">
+      <c r="E78" s="165">
         <f>SUM(E76:E77)</f>
         <v/>
       </c>
-      <c r="F78" s="164">
+      <c r="F78" s="165">
         <f>SUM(F76:F77)</f>
         <v/>
       </c>
-      <c r="G78" s="164">
+      <c r="G78" s="165">
         <f>SUM(G76:G77)</f>
         <v/>
       </c>
-      <c r="H78" s="164">
+      <c r="H78" s="165">
         <f>SUM(H76:H77)</f>
         <v/>
       </c>
-      <c r="I78" s="164">
+      <c r="I78" s="165">
         <f>SUM(I76:I77)</f>
         <v/>
       </c>
-      <c r="J78" s="159">
+      <c r="J78" s="160">
         <f>J77+J76</f>
         <v/>
       </c>
-      <c r="K78" s="159">
+      <c r="K78" s="160">
         <f>K77+K76</f>
         <v/>
       </c>
-      <c r="L78" s="159">
+      <c r="L78" s="160">
         <f>L77+L76</f>
         <v/>
       </c>
-      <c r="M78" s="159">
+      <c r="M78" s="160">
         <f>M77+M76</f>
         <v/>
       </c>
-      <c r="N78" s="159">
+      <c r="N78" s="160">
         <f>N77+N76</f>
         <v/>
       </c>
@@ -10052,43 +10060,43 @@
       </c>
       <c r="C80" s="9" t="n"/>
       <c r="D80" s="27" t="n"/>
-      <c r="E80" s="173">
+      <c r="E80" s="174">
         <f>E78-E41</f>
         <v/>
       </c>
-      <c r="F80" s="173">
+      <c r="F80" s="174">
         <f>F78-F41</f>
         <v/>
       </c>
-      <c r="G80" s="173">
+      <c r="G80" s="174">
         <f>G78-G41</f>
         <v/>
       </c>
-      <c r="H80" s="173">
+      <c r="H80" s="174">
         <f>H78-H41</f>
         <v/>
       </c>
-      <c r="I80" s="173">
+      <c r="I80" s="174">
         <f>I78-I41</f>
         <v/>
       </c>
-      <c r="J80" s="159">
+      <c r="J80" s="160">
         <f>J78-J41</f>
         <v/>
       </c>
-      <c r="K80" s="159">
+      <c r="K80" s="160">
         <f>K78-K41</f>
         <v/>
       </c>
-      <c r="L80" s="159">
+      <c r="L80" s="160">
         <f>L78-L41</f>
         <v/>
       </c>
-      <c r="M80" s="159">
+      <c r="M80" s="160">
         <f>M78-M41</f>
         <v/>
       </c>
-      <c r="N80" s="159">
+      <c r="N80" s="160">
         <f>N78-N41</f>
         <v/>
       </c>
@@ -10144,38 +10152,38 @@
           <t>Accounts Receivable (plugged to NWC%)</t>
         </is>
       </c>
-      <c r="E85" s="162" t="n">
+      <c r="E85" s="163" t="n">
         <v>312107</v>
       </c>
-      <c r="F85" s="162" t="n">
+      <c r="F85" s="163" t="n">
         <v>322410</v>
       </c>
-      <c r="G85" s="162" t="n">
+      <c r="G85" s="163" t="n">
         <v>387947</v>
       </c>
-      <c r="H85" s="162" t="n">
+      <c r="H85" s="163" t="n">
         <v>426642</v>
       </c>
-      <c r="I85" s="162" t="n">
+      <c r="I85" s="163" t="n">
         <v>529148</v>
       </c>
-      <c r="J85" s="159">
+      <c r="J85" s="160">
         <f>J42</f>
         <v/>
       </c>
-      <c r="K85" s="159">
+      <c r="K85" s="160">
         <f>K42</f>
         <v/>
       </c>
-      <c r="L85" s="159">
+      <c r="L85" s="160">
         <f>L42</f>
         <v/>
       </c>
-      <c r="M85" s="159">
+      <c r="M85" s="160">
         <f>M42</f>
         <v/>
       </c>
-      <c r="N85" s="159">
+      <c r="N85" s="160">
         <f>N42</f>
         <v/>
       </c>
@@ -10186,38 +10194,38 @@
           <t>Inventory</t>
         </is>
       </c>
-      <c r="E86" s="162" t="n">
+      <c r="E86" s="163" t="n">
         <v>0</v>
       </c>
-      <c r="F86" s="162" t="n">
+      <c r="F86" s="163" t="n">
         <v>0</v>
       </c>
-      <c r="G86" s="162" t="n">
+      <c r="G86" s="163" t="n">
         <v>0</v>
       </c>
-      <c r="H86" s="162" t="n">
+      <c r="H86" s="163" t="n">
         <v>0</v>
       </c>
-      <c r="I86" s="162" t="n">
+      <c r="I86" s="163" t="n">
         <v>0</v>
       </c>
-      <c r="J86" s="159">
+      <c r="J86" s="160">
         <f>J43</f>
         <v/>
       </c>
-      <c r="K86" s="159">
+      <c r="K86" s="160">
         <f>K43</f>
         <v/>
       </c>
-      <c r="L86" s="159">
+      <c r="L86" s="160">
         <f>L43</f>
         <v/>
       </c>
-      <c r="M86" s="159">
+      <c r="M86" s="160">
         <f>M43</f>
         <v/>
       </c>
-      <c r="N86" s="159">
+      <c r="N86" s="160">
         <f>N43</f>
         <v/>
       </c>
@@ -10228,38 +10236,38 @@
           <t>Accounts Payable</t>
         </is>
       </c>
-      <c r="E87" s="162" t="n">
+      <c r="E87" s="163" t="n">
         <v>20749</v>
       </c>
-      <c r="F87" s="162" t="n">
+      <c r="F87" s="163" t="n">
         <v>17273</v>
       </c>
-      <c r="G87" s="162" t="n">
+      <c r="G87" s="163" t="n">
         <v>19009</v>
       </c>
-      <c r="H87" s="162" t="n">
+      <c r="H87" s="163" t="n">
         <v>22473</v>
       </c>
-      <c r="I87" s="162" t="n">
+      <c r="I87" s="163" t="n">
         <v>32315</v>
       </c>
-      <c r="J87" s="159">
+      <c r="J87" s="160">
         <f>J48</f>
         <v/>
       </c>
-      <c r="K87" s="159">
+      <c r="K87" s="160">
         <f>K48</f>
         <v/>
       </c>
-      <c r="L87" s="159">
+      <c r="L87" s="160">
         <f>L48</f>
         <v/>
       </c>
-      <c r="M87" s="159">
+      <c r="M87" s="160">
         <f>M48</f>
         <v/>
       </c>
-      <c r="N87" s="159">
+      <c r="N87" s="160">
         <f>N48</f>
         <v/>
       </c>
@@ -10270,44 +10278,44 @@
           <t>Deferred Revenue (contract liability)</t>
         </is>
       </c>
-      <c r="C88" s="163" t="inlineStr">
+      <c r="C88" s="164" t="inlineStr">
         <is>
           <t>eqn: Rev × (FY25 Deferred/FY25 Rev)</t>
         </is>
       </c>
       <c r="D88" s="28" t="n"/>
-      <c r="E88" s="177" t="n">
+      <c r="E88" s="178" t="n">
         <v>105417</v>
       </c>
-      <c r="F88" s="177" t="n">
+      <c r="F88" s="178" t="n">
         <v>120045</v>
       </c>
-      <c r="G88" s="177" t="n">
+      <c r="G88" s="178" t="n">
         <v>136730</v>
       </c>
-      <c r="H88" s="177" t="n">
+      <c r="H88" s="178" t="n">
         <v>156897</v>
       </c>
-      <c r="I88" s="177" t="n">
+      <c r="I88" s="178" t="n">
         <v>187372</v>
       </c>
-      <c r="J88" s="159">
+      <c r="J88" s="160">
         <f>J24*IF($I$24=0,0,$I$88/$I$24)</f>
         <v/>
       </c>
-      <c r="K88" s="159">
+      <c r="K88" s="160">
         <f>K24*IF($I$24=0,0,$I$88/$I$24)</f>
         <v/>
       </c>
-      <c r="L88" s="159">
+      <c r="L88" s="160">
         <f>L24*IF($I$24=0,0,$I$88/$I$24)</f>
         <v/>
       </c>
-      <c r="M88" s="159">
+      <c r="M88" s="160">
         <f>M24*IF($I$24=0,0,$I$88/$I$24)</f>
         <v/>
       </c>
-      <c r="N88" s="159">
+      <c r="N88" s="160">
         <f>N24*IF($I$24=0,0,$I$88/$I$24)</f>
         <v/>
       </c>
@@ -10318,46 +10326,46 @@
           <t>Net Working Capital (NWC)</t>
         </is>
       </c>
-      <c r="C89" s="165" t="inlineStr">
+      <c r="C89" s="166" t="inlineStr">
         <is>
           <t>eqn: Rev × NWC%   (consolidated operating WC)</t>
         </is>
       </c>
-      <c r="D89" s="178" t="n">
+      <c r="D89" s="179" t="n">
         <v>205747</v>
       </c>
-      <c r="E89" s="162" t="n">
+      <c r="E89" s="163" t="n">
         <v>185941</v>
       </c>
-      <c r="F89" s="162" t="n">
+      <c r="F89" s="163" t="n">
         <v>185092</v>
       </c>
-      <c r="G89" s="162" t="n">
+      <c r="G89" s="163" t="n">
         <v>232208</v>
       </c>
-      <c r="H89" s="162" t="n">
+      <c r="H89" s="163" t="n">
         <v>247272</v>
       </c>
-      <c r="I89" s="162" t="n">
+      <c r="I89" s="163" t="n">
         <v>309461</v>
       </c>
-      <c r="J89" s="159">
+      <c r="J89" s="160">
         <f>J24*J15</f>
         <v/>
       </c>
-      <c r="K89" s="159">
+      <c r="K89" s="160">
         <f>K24*K15</f>
         <v/>
       </c>
-      <c r="L89" s="159">
+      <c r="L89" s="160">
         <f>L24*L15</f>
         <v/>
       </c>
-      <c r="M89" s="159">
+      <c r="M89" s="160">
         <f>M24*M15</f>
         <v/>
       </c>
-      <c r="N89" s="159">
+      <c r="N89" s="160">
         <f>N24*N15</f>
         <v/>
       </c>
@@ -10368,38 +10376,38 @@
           <t>Change in NWC</t>
         </is>
       </c>
-      <c r="E90" s="162" t="n">
+      <c r="E90" s="163" t="n">
         <v>-19806</v>
       </c>
-      <c r="F90" s="162" t="n">
+      <c r="F90" s="163" t="n">
         <v>-849</v>
       </c>
-      <c r="G90" s="162" t="n">
+      <c r="G90" s="163" t="n">
         <v>47116</v>
       </c>
-      <c r="H90" s="162" t="n">
+      <c r="H90" s="163" t="n">
         <v>15064</v>
       </c>
-      <c r="I90" s="162" t="n">
+      <c r="I90" s="163" t="n">
         <v>62189</v>
       </c>
-      <c r="J90" s="179">
+      <c r="J90" s="180">
         <f>J89-I89</f>
         <v/>
       </c>
-      <c r="K90" s="179">
+      <c r="K90" s="180">
         <f>K89-J89</f>
         <v/>
       </c>
-      <c r="L90" s="179">
+      <c r="L90" s="180">
         <f>L89-K89</f>
         <v/>
       </c>
-      <c r="M90" s="179">
+      <c r="M90" s="180">
         <f>M89-L89</f>
         <v/>
       </c>
-      <c r="N90" s="179">
+      <c r="N90" s="180">
         <f>N89-M89</f>
         <v/>
       </c>
@@ -10422,42 +10430,42 @@
           <t>PPE Opening</t>
         </is>
       </c>
-      <c r="E92" s="162" t="n">
+      <c r="E92" s="163" t="n">
         <v>46419</v>
       </c>
-      <c r="F92" s="175">
+      <c r="F92" s="176">
         <f>E95</f>
         <v/>
       </c>
-      <c r="G92" s="175">
+      <c r="G92" s="176">
         <f>F95</f>
         <v/>
       </c>
-      <c r="H92" s="175">
+      <c r="H92" s="176">
         <f>G95</f>
         <v/>
       </c>
-      <c r="I92" s="175">
+      <c r="I92" s="176">
         <f>H95</f>
         <v/>
       </c>
-      <c r="J92" s="159">
+      <c r="J92" s="160">
         <f>I44</f>
         <v/>
       </c>
-      <c r="K92" s="159">
+      <c r="K92" s="160">
         <f>J95</f>
         <v/>
       </c>
-      <c r="L92" s="159">
+      <c r="L92" s="160">
         <f>K95</f>
         <v/>
       </c>
-      <c r="M92" s="159">
+      <c r="M92" s="160">
         <f>L95</f>
         <v/>
       </c>
-      <c r="N92" s="159">
+      <c r="N92" s="160">
         <f>M95</f>
         <v/>
       </c>
@@ -10468,38 +10476,38 @@
           <t>Plus Capex</t>
         </is>
       </c>
-      <c r="E93" s="162" t="n">
+      <c r="E93" s="163" t="n">
         <v>7569</v>
       </c>
-      <c r="F93" s="162" t="n">
+      <c r="F93" s="163" t="n">
         <v>6029</v>
       </c>
-      <c r="G93" s="162" t="n">
+      <c r="G93" s="163" t="n">
         <v>4237</v>
       </c>
-      <c r="H93" s="162" t="n">
+      <c r="H93" s="163" t="n">
         <v>25551</v>
       </c>
-      <c r="I93" s="162" t="n">
+      <c r="I93" s="163" t="n">
         <v>39407</v>
       </c>
-      <c r="J93" s="159">
+      <c r="J93" s="160">
         <f>J24*J18</f>
         <v/>
       </c>
-      <c r="K93" s="159">
+      <c r="K93" s="160">
         <f>K24*K18</f>
         <v/>
       </c>
-      <c r="L93" s="159">
+      <c r="L93" s="160">
         <f>L24*L18</f>
         <v/>
       </c>
-      <c r="M93" s="159">
+      <c r="M93" s="160">
         <f>M24*M18</f>
         <v/>
       </c>
-      <c r="N93" s="159">
+      <c r="N93" s="160">
         <f>N24*N18</f>
         <v/>
       </c>
@@ -10510,43 +10518,43 @@
           <t>Less Depreciation</t>
         </is>
       </c>
-      <c r="C94" s="165" t="inlineStr">
+      <c r="C94" s="166" t="inlineStr">
         <is>
           <t>eqn: ((Open+Open+CapEx)/2) × DA%</t>
         </is>
       </c>
-      <c r="E94" s="162" t="n">
+      <c r="E94" s="163" t="n">
         <v>25592</v>
       </c>
-      <c r="F94" s="162" t="n">
+      <c r="F94" s="163" t="n">
         <v>20465</v>
       </c>
-      <c r="G94" s="162" t="n">
+      <c r="G94" s="163" t="n">
         <v>14638</v>
       </c>
-      <c r="H94" s="162" t="n">
+      <c r="H94" s="163" t="n">
         <v>13827</v>
       </c>
-      <c r="I94" s="162" t="n">
+      <c r="I94" s="163" t="n">
         <v>14952</v>
       </c>
-      <c r="J94" s="159">
+      <c r="J94" s="160">
         <f>((J92+(J92+J93))/2)*J11</f>
         <v/>
       </c>
-      <c r="K94" s="159">
+      <c r="K94" s="160">
         <f>((K92+(K92+K93))/2)*K11</f>
         <v/>
       </c>
-      <c r="L94" s="159">
+      <c r="L94" s="160">
         <f>((L92+(L92+L93))/2)*L11</f>
         <v/>
       </c>
-      <c r="M94" s="159">
+      <c r="M94" s="160">
         <f>((M92+(M92+M93))/2)*M11</f>
         <v/>
       </c>
-      <c r="N94" s="159">
+      <c r="N94" s="160">
         <f>((N92+(N92+N93))/2)*N11</f>
         <v/>
       </c>
@@ -10559,38 +10567,38 @@
       </c>
       <c r="C95" s="5" t="n"/>
       <c r="D95" s="28" t="n"/>
-      <c r="E95" s="177" t="n">
+      <c r="E95" s="178" t="n">
         <v>27913</v>
       </c>
-      <c r="F95" s="177" t="n">
+      <c r="F95" s="178" t="n">
         <v>17580</v>
       </c>
-      <c r="G95" s="177" t="n">
+      <c r="G95" s="178" t="n">
         <v>10966</v>
       </c>
-      <c r="H95" s="177" t="n">
+      <c r="H95" s="178" t="n">
         <v>38465</v>
       </c>
-      <c r="I95" s="177" t="n">
+      <c r="I95" s="178" t="n">
         <v>67713</v>
       </c>
-      <c r="J95" s="159">
+      <c r="J95" s="160">
         <f>J92+J93-J94</f>
         <v/>
       </c>
-      <c r="K95" s="159">
+      <c r="K95" s="160">
         <f>K92+K93-K94</f>
         <v/>
       </c>
-      <c r="L95" s="159">
+      <c r="L95" s="160">
         <f>L92+L93-L94</f>
         <v/>
       </c>
-      <c r="M95" s="159">
+      <c r="M95" s="160">
         <f>M92+M93-M94</f>
         <v/>
       </c>
-      <c r="N95" s="159">
+      <c r="N95" s="160">
         <f>N92+N93-N94</f>
         <v/>
       </c>
@@ -10625,42 +10633,42 @@
           <t>Debt Opening</t>
         </is>
       </c>
-      <c r="E98" s="162" t="n">
+      <c r="E98" s="163" t="n">
         <v>739435</v>
       </c>
-      <c r="F98" s="175">
+      <c r="F98" s="176">
         <f>E100</f>
         <v/>
       </c>
-      <c r="G98" s="175">
+      <c r="G98" s="176">
         <f>F100</f>
         <v/>
       </c>
-      <c r="H98" s="175">
+      <c r="H98" s="176">
         <f>G100</f>
         <v/>
       </c>
-      <c r="I98" s="175">
+      <c r="I98" s="176">
         <f>H100</f>
         <v/>
       </c>
-      <c r="J98" s="159">
+      <c r="J98" s="160">
         <f>I49</f>
         <v/>
       </c>
-      <c r="K98" s="159">
+      <c r="K98" s="160">
         <f>J100</f>
         <v/>
       </c>
-      <c r="L98" s="159">
+      <c r="L98" s="160">
         <f>K100</f>
         <v/>
       </c>
-      <c r="M98" s="159">
+      <c r="M98" s="160">
         <f>L100</f>
         <v/>
       </c>
-      <c r="N98" s="159">
+      <c r="N98" s="160">
         <f>M100</f>
         <v/>
       </c>
@@ -10671,38 +10679,38 @@
           <t>Issuance (repayment)</t>
         </is>
       </c>
-      <c r="E99" s="162" t="n">
+      <c r="E99" s="163" t="n">
         <v>519583</v>
       </c>
-      <c r="F99" s="162" t="n">
+      <c r="F99" s="163" t="n">
         <v>594651</v>
       </c>
-      <c r="G99" s="162" t="n">
+      <c r="G99" s="163" t="n">
         <v>7989</v>
       </c>
-      <c r="H99" s="162" t="n">
+      <c r="H99" s="163" t="n">
         <v>347363</v>
       </c>
-      <c r="I99" s="162" t="n">
+      <c r="I99" s="163" t="n">
         <v>846670</v>
       </c>
-      <c r="J99" s="159">
+      <c r="J99" s="160">
         <f>J19</f>
         <v/>
       </c>
-      <c r="K99" s="159">
+      <c r="K99" s="160">
         <f>K19</f>
         <v/>
       </c>
-      <c r="L99" s="159">
+      <c r="L99" s="160">
         <f>L19</f>
         <v/>
       </c>
-      <c r="M99" s="159">
+      <c r="M99" s="160">
         <f>M19</f>
         <v/>
       </c>
-      <c r="N99" s="159">
+      <c r="N99" s="160">
         <f>N19</f>
         <v/>
       </c>
@@ -10715,38 +10723,38 @@
       </c>
       <c r="C100" s="5" t="n"/>
       <c r="D100" s="28" t="n"/>
-      <c r="E100" s="177" t="n">
+      <c r="E100" s="178" t="n">
         <v>1259018</v>
       </c>
-      <c r="F100" s="177" t="n">
+      <c r="F100" s="178" t="n">
         <v>1853669</v>
       </c>
-      <c r="G100" s="177" t="n">
+      <c r="G100" s="178" t="n">
         <v>1861658</v>
       </c>
-      <c r="H100" s="177" t="n">
+      <c r="H100" s="178" t="n">
         <v>2209021</v>
       </c>
-      <c r="I100" s="177" t="n">
+      <c r="I100" s="178" t="n">
         <v>3055691</v>
       </c>
-      <c r="J100" s="159">
+      <c r="J100" s="160">
         <f>J98+J99</f>
         <v/>
       </c>
-      <c r="K100" s="159">
+      <c r="K100" s="160">
         <f>K98+K99</f>
         <v/>
       </c>
-      <c r="L100" s="159">
+      <c r="L100" s="160">
         <f>L98+L99</f>
         <v/>
       </c>
-      <c r="M100" s="159">
+      <c r="M100" s="160">
         <f>M98+M99</f>
         <v/>
       </c>
-      <c r="N100" s="159">
+      <c r="N100" s="160">
         <f>N98+N99</f>
         <v/>
       </c>
@@ -10757,38 +10765,38 @@
           <t>Interest Expense</t>
         </is>
       </c>
-      <c r="E101" s="162" t="n">
+      <c r="E101" s="163" t="n">
         <v>40092</v>
       </c>
-      <c r="F101" s="162" t="n">
+      <c r="F101" s="163" t="n">
         <v>68967</v>
       </c>
-      <c r="G101" s="162" t="n">
+      <c r="G101" s="163" t="n">
         <v>95546</v>
       </c>
-      <c r="H101" s="162" t="n">
+      <c r="H101" s="163" t="n">
         <v>105638</v>
       </c>
-      <c r="I101" s="162" t="n">
+      <c r="I101" s="163" t="n">
         <v>133647</v>
       </c>
-      <c r="J101" s="159">
+      <c r="J101" s="160">
         <f>J98*J12</f>
         <v/>
       </c>
-      <c r="K101" s="159">
+      <c r="K101" s="160">
         <f>K98*K12</f>
         <v/>
       </c>
-      <c r="L101" s="159">
+      <c r="L101" s="160">
         <f>L98*L12</f>
         <v/>
       </c>
-      <c r="M101" s="159">
+      <c r="M101" s="160">
         <f>M98*M12</f>
         <v/>
       </c>
-      <c r="N101" s="159">
+      <c r="N101" s="160">
         <f>N98*N12</f>
         <v/>
       </c>
@@ -11194,7 +11202,7 @@
       <c r="L2" s="96" t="n"/>
       <c r="M2" s="94" t="n"/>
       <c r="N2" s="94" t="n"/>
-      <c r="Q2" s="180" t="inlineStr">
+      <c r="Q2" s="181" t="inlineStr">
         <is>
           <t>vengeanceaiUSCMODEL7 — LIVE EQUATIONS + SOURCE LINKS</t>
         </is>
@@ -11216,7 +11224,7 @@
       <c r="M3" s="97" t="n"/>
       <c r="N3" s="97" t="n"/>
       <c r="O3" s="97" t="n"/>
-      <c r="Q3" s="181" t="inlineStr">
+      <c r="Q3" s="182" t="inlineStr">
         <is>
           <t>Yellow = inputs (edit). Green = formulas. Blue underlined = clickable sources.</t>
         </is>
@@ -11242,32 +11250,32 @@
       <c r="M4" s="97" t="n"/>
       <c r="N4" s="97" t="n"/>
       <c r="O4" s="97" t="n"/>
-      <c r="Q4" s="182" t="inlineStr">
+      <c r="Q4" s="183" t="inlineStr">
         <is>
           <t>Input</t>
         </is>
       </c>
-      <c r="R4" s="182" t="inlineStr">
+      <c r="R4" s="183" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="S4" s="182" t="inlineStr">
+      <c r="S4" s="183" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="T4" s="182" t="inlineStr">
+      <c r="T4" s="183" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="U4" s="182" t="inlineStr">
+      <c r="U4" s="183" t="inlineStr">
         <is>
           <t>Primary source (click)</t>
         </is>
       </c>
-      <c r="V4" s="182" t="inlineStr">
+      <c r="V4" s="183" t="inlineStr">
         <is>
           <t>Secondary source (click)</t>
         </is>
@@ -11281,10 +11289,10 @@
         </is>
       </c>
       <c r="C5" s="100" t="n"/>
-      <c r="D5" s="183" t="n">
+      <c r="D5" s="184" t="n">
         <v>0.1877023903712333</v>
       </c>
-      <c r="E5" s="184" t="inlineStr">
+      <c r="E5" s="185" t="inlineStr">
         <is>
           <t>Tax source: SEC 10-K</t>
         </is>
@@ -11299,14 +11307,14 @@
       <c r="M5" s="97" t="n"/>
       <c r="N5" s="97" t="n"/>
       <c r="O5" s="97" t="n"/>
-      <c r="Q5" s="145" t="inlineStr">
+      <c r="Q5" s="146" t="inlineStr">
         <is>
           <t>1) CAPM → WACC   (D6 = R15)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="185" t="inlineStr">
+      <c r="A6" s="186" t="inlineStr">
         <is>
           <t>WACC sources → columns U–V</t>
         </is>
@@ -11316,26 +11324,26 @@
           <t>Discount Rate (WACC = We×Ke + Wd×Rd(1−t))</t>
         </is>
       </c>
-      <c r="C6" s="186" t="inlineStr">
+      <c r="C6" s="187" t="inlineStr">
         <is>
           <t>Sources →</t>
         </is>
       </c>
-      <c r="D6" s="187">
+      <c r="D6" s="188">
         <f>R15</f>
         <v/>
       </c>
-      <c r="E6" s="184" t="inlineStr">
+      <c r="E6" s="185" t="inlineStr">
         <is>
           <t>WACC sources → scroll to col U (Rf/ERP/β/Rd links)</t>
         </is>
       </c>
-      <c r="F6" s="184" t="inlineStr">
+      <c r="F6" s="185" t="inlineStr">
         <is>
           <t>Damodaran ERP</t>
         </is>
       </c>
-      <c r="G6" s="184" t="inlineStr">
+      <c r="G6" s="185" t="inlineStr">
         <is>
           <t>SEC 8-K Rd 6.250%</t>
         </is>
@@ -11348,30 +11356,30 @@
       <c r="M6" s="97" t="n"/>
       <c r="N6" s="97" t="n"/>
       <c r="O6" s="97" t="n"/>
-      <c r="Q6" s="188" t="inlineStr">
+      <c r="Q6" s="189" t="inlineStr">
         <is>
           <t>Risk-free rate (Rf)</t>
         </is>
       </c>
-      <c r="R6" s="189" t="n">
+      <c r="R6" s="190" t="n">
         <v>0.0463</v>
       </c>
-      <c r="S6" s="188" t="inlineStr">
+      <c r="S6" s="189" t="inlineStr">
         <is>
           <t>US 10Y Treasury yield</t>
         </is>
       </c>
-      <c r="T6" s="188" t="inlineStr">
+      <c r="T6" s="189" t="inlineStr">
         <is>
           <t>CAPM input</t>
         </is>
       </c>
-      <c r="U6" s="190" t="inlineStr">
+      <c r="U6" s="191" t="inlineStr">
         <is>
           <t>FRED DGS10 (US 10Y)</t>
         </is>
       </c>
-      <c r="V6" s="190" t="inlineStr">
+      <c r="V6" s="191" t="inlineStr">
         <is>
           <t>US Treasury Daily Par Yield Curve</t>
         </is>
@@ -11385,7 +11393,7 @@
         </is>
       </c>
       <c r="C7" s="97" t="n"/>
-      <c r="D7" s="183" t="n">
+      <c r="D7" s="184" t="n">
         <v>0.03</v>
       </c>
       <c r="E7" s="97" t="n"/>
@@ -11399,30 +11407,30 @@
       <c r="M7" s="97" t="n"/>
       <c r="N7" s="97" t="n"/>
       <c r="O7" s="97" t="n"/>
-      <c r="Q7" s="188" t="inlineStr">
+      <c r="Q7" s="189" t="inlineStr">
         <is>
           <t>Equity risk premium (ERP)</t>
         </is>
       </c>
-      <c r="R7" s="189" t="n">
+      <c r="R7" s="190" t="n">
         <v>0.0428</v>
       </c>
-      <c r="S7" s="188" t="inlineStr">
+      <c r="S7" s="189" t="inlineStr">
         <is>
           <t>Damodaran implied ERP</t>
         </is>
       </c>
-      <c r="T7" s="188" t="inlineStr">
+      <c r="T7" s="189" t="inlineStr">
         <is>
           <t>CAPM input</t>
         </is>
       </c>
-      <c r="U7" s="190" t="inlineStr">
+      <c r="U7" s="191" t="inlineStr">
         <is>
           <t>Damodaran Online — Implied ERP</t>
         </is>
       </c>
-      <c r="V7" s="190" t="inlineStr">
+      <c r="V7" s="191" t="inlineStr">
         <is>
           <t>Damodaran histimpl.xls / table</t>
         </is>
@@ -11435,11 +11443,15 @@
           <t>EV/EBITDA Mulltiple</t>
         </is>
       </c>
-      <c r="C8" s="97" t="n"/>
-      <c r="D8" s="191" t="n">
+      <c r="C8" s="105" t="inlineStr">
+        <is>
+          <t>POLICY 16x = mid of audit 15–18x blend (25x = bull only). Not from 10-K.</t>
+        </is>
+      </c>
+      <c r="D8" s="192" t="n">
         <v>16</v>
       </c>
-      <c r="E8" s="184" t="inlineStr">
+      <c r="E8" s="185" t="inlineStr">
         <is>
           <t>Rd source: SEC 8-K 6.250% notes</t>
         </is>
@@ -11454,30 +11466,30 @@
       <c r="M8" s="97" t="n"/>
       <c r="N8" s="97" t="n"/>
       <c r="O8" s="97" t="n"/>
-      <c r="Q8" s="188" t="inlineStr">
+      <c r="Q8" s="189" t="inlineStr">
         <is>
           <t>Beta (β)</t>
         </is>
       </c>
-      <c r="R8" s="192" t="n">
+      <c r="R8" s="193" t="n">
         <v>1.32</v>
       </c>
-      <c r="S8" s="188" t="inlineStr">
+      <c r="S8" s="189" t="inlineStr">
         <is>
           <t>Yahoo 5Y monthly beta</t>
         </is>
       </c>
-      <c r="T8" s="188" t="inlineStr">
+      <c r="T8" s="189" t="inlineStr">
         <is>
           <t>CAPM input</t>
         </is>
       </c>
-      <c r="U8" s="190" t="inlineStr">
+      <c r="U8" s="191" t="inlineStr">
         <is>
           <t>Yahoo Finance FICO Key Statistics</t>
         </is>
       </c>
-      <c r="V8" s="190" t="inlineStr">
+      <c r="V8" s="191" t="inlineStr">
         <is>
           <t>Yahoo Finance FICO quote</t>
         </is>
@@ -11491,7 +11503,7 @@
         </is>
       </c>
       <c r="C9" s="97" t="n"/>
-      <c r="D9" s="193" t="n">
+      <c r="D9" s="194" t="n">
         <v>45930</v>
       </c>
       <c r="E9" s="97" t="n"/>
@@ -11505,31 +11517,31 @@
       <c r="M9" s="97" t="n"/>
       <c r="N9" s="97" t="n"/>
       <c r="O9" s="97" t="n"/>
-      <c r="Q9" s="194" t="inlineStr">
+      <c r="Q9" s="195" t="inlineStr">
         <is>
           <t>Ke = Rf + β × ERP</t>
         </is>
       </c>
-      <c r="R9" s="195">
+      <c r="R9" s="196">
         <f>R6+R8*R7</f>
         <v/>
       </c>
-      <c r="S9" s="188" t="inlineStr">
+      <c r="S9" s="189" t="inlineStr">
         <is>
           <t>Cost of equity (CAPM)</t>
         </is>
       </c>
-      <c r="T9" s="194" t="inlineStr">
+      <c r="T9" s="195" t="inlineStr">
         <is>
           <t>→ WACC</t>
         </is>
       </c>
-      <c r="U9" s="188" t="inlineStr">
+      <c r="U9" s="189" t="inlineStr">
         <is>
           <t>Derived: R6 + R8 × R7</t>
         </is>
       </c>
-      <c r="V9" s="188" t="inlineStr"/>
+      <c r="V9" s="189" t="inlineStr"/>
     </row>
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="97" t="n"/>
@@ -11539,7 +11551,7 @@
         </is>
       </c>
       <c r="C10" s="97" t="n"/>
-      <c r="D10" s="193" t="n">
+      <c r="D10" s="194" t="n">
         <v>46295</v>
       </c>
       <c r="E10" s="97" t="n"/>
@@ -11553,30 +11565,30 @@
       <c r="M10" s="97" t="n"/>
       <c r="N10" s="97" t="n"/>
       <c r="O10" s="97" t="n"/>
-      <c r="Q10" s="188" t="inlineStr">
+      <c r="Q10" s="189" t="inlineStr">
         <is>
           <t>Pre-tax cost of debt (Rd)</t>
         </is>
       </c>
-      <c r="R10" s="189" t="n">
+      <c r="R10" s="190" t="n">
         <v>0.0625</v>
       </c>
-      <c r="S10" s="188" t="inlineStr">
+      <c r="S10" s="189" t="inlineStr">
         <is>
           <t>6.250% Senior Notes due 2034</t>
         </is>
       </c>
-      <c r="T10" s="188" t="inlineStr">
+      <c r="T10" s="189" t="inlineStr">
         <is>
           <t>WACC input</t>
         </is>
       </c>
-      <c r="U10" s="190" t="inlineStr">
+      <c r="U10" s="191" t="inlineStr">
         <is>
           <t>SEC 8-K — Notes closing (6.250%)</t>
         </is>
       </c>
-      <c r="V10" s="190" t="inlineStr">
+      <c r="V10" s="191" t="inlineStr">
         <is>
           <t>SEC EX-99.1 — Notes pricing press release</t>
         </is>
@@ -11590,7 +11602,7 @@
         </is>
       </c>
       <c r="C11" s="97" t="n"/>
-      <c r="D11" s="196" t="n">
+      <c r="D11" s="197" t="n">
         <v>1046.23</v>
       </c>
       <c r="E11" s="97" t="n"/>
@@ -11604,31 +11616,31 @@
       <c r="M11" s="97" t="n"/>
       <c r="N11" s="97" t="n"/>
       <c r="O11" s="97" t="n"/>
-      <c r="Q11" s="188" t="inlineStr">
+      <c r="Q11" s="189" t="inlineStr">
         <is>
           <t>Tax rate (t)</t>
         </is>
       </c>
-      <c r="R11" s="195">
+      <c r="R11" s="196">
         <f>$D$5</f>
         <v/>
       </c>
-      <c r="S11" s="188" t="inlineStr">
+      <c r="S11" s="189" t="inlineStr">
         <is>
           <t>FY25 effective = 150,649 / 802,595</t>
         </is>
       </c>
-      <c r="T11" s="188" t="inlineStr">
+      <c r="T11" s="189" t="inlineStr">
         <is>
           <t>Linked D5</t>
         </is>
       </c>
-      <c r="U11" s="190" t="inlineStr">
+      <c r="U11" s="191" t="inlineStr">
         <is>
           <t>SEC 10-K FY2025 (tax / EBT)</t>
         </is>
       </c>
-      <c r="V11" s="190" t="inlineStr">
+      <c r="V11" s="191" t="inlineStr">
         <is>
           <t>SEC companyfacts XBRL (CIK 0000814547)</t>
         </is>
@@ -11642,7 +11654,7 @@
         </is>
       </c>
       <c r="C12" s="97" t="n"/>
-      <c r="D12" s="197" t="n">
+      <c r="D12" s="198" t="n">
         <v>21597.635</v>
       </c>
       <c r="E12" s="97" t="n"/>
@@ -11656,31 +11668,31 @@
       <c r="M12" s="97" t="n"/>
       <c r="N12" s="97" t="n"/>
       <c r="O12" s="97" t="n"/>
-      <c r="Q12" s="194" t="inlineStr">
+      <c r="Q12" s="195" t="inlineStr">
         <is>
           <t>Rd_aftertax = Rd × (1 − t)</t>
         </is>
       </c>
-      <c r="R12" s="195">
+      <c r="R12" s="196">
         <f>R10*(1-R11)</f>
         <v/>
       </c>
-      <c r="S12" s="188" t="inlineStr">
+      <c r="S12" s="189" t="inlineStr">
         <is>
           <t>After-tax cost of debt</t>
         </is>
       </c>
-      <c r="T12" s="194" t="inlineStr">
+      <c r="T12" s="195" t="inlineStr">
         <is>
           <t>→ WACC</t>
         </is>
       </c>
-      <c r="U12" s="188" t="inlineStr">
+      <c r="U12" s="189" t="inlineStr">
         <is>
           <t>Derived: R10 × (1 − R11)</t>
         </is>
       </c>
-      <c r="V12" s="188" t="inlineStr"/>
+      <c r="V12" s="189" t="inlineStr"/>
     </row>
     <row r="13" ht="16" customHeight="1">
       <c r="A13" s="97" t="n"/>
@@ -11690,7 +11702,7 @@
         </is>
       </c>
       <c r="C13" s="97" t="n"/>
-      <c r="D13" s="197" t="n">
+      <c r="D13" s="198" t="n">
         <v>5582389</v>
       </c>
       <c r="E13" s="97" t="n"/>
@@ -11704,30 +11716,30 @@
       <c r="M13" s="97" t="n"/>
       <c r="N13" s="97" t="n"/>
       <c r="O13" s="97" t="n"/>
-      <c r="Q13" s="188" t="inlineStr">
+      <c r="Q13" s="189" t="inlineStr">
         <is>
           <t>Equity weight (We)</t>
         </is>
       </c>
-      <c r="R13" s="198" t="n">
+      <c r="R13" s="199" t="n">
         <v>0.8</v>
       </c>
-      <c r="S13" s="188" t="inlineStr">
+      <c r="S13" s="189" t="inlineStr">
         <is>
           <t>Target ~80% equity at market</t>
         </is>
       </c>
-      <c r="T13" s="188" t="inlineStr">
+      <c r="T13" s="189" t="inlineStr">
         <is>
           <t>WACC weight</t>
         </is>
       </c>
-      <c r="U13" s="190" t="inlineStr">
+      <c r="U13" s="191" t="inlineStr">
         <is>
           <t>SEC 10-Q Q3 FY2026 (debt / capital)</t>
         </is>
       </c>
-      <c r="V13" s="190" t="inlineStr">
+      <c r="V13" s="191" t="inlineStr">
         <is>
           <t>Yahoo market cap for E/(D+E)</t>
         </is>
@@ -11741,7 +11753,7 @@
         </is>
       </c>
       <c r="C14" s="97" t="n"/>
-      <c r="D14" s="197" t="n">
+      <c r="D14" s="198" t="n">
         <v>304537</v>
       </c>
       <c r="E14" s="97" t="n"/>
@@ -11755,30 +11767,30 @@
       <c r="M14" s="97" t="n"/>
       <c r="N14" s="97" t="n"/>
       <c r="O14" s="97" t="n"/>
-      <c r="Q14" s="188" t="inlineStr">
+      <c r="Q14" s="189" t="inlineStr">
         <is>
           <t>Debt weight (Wd)</t>
         </is>
       </c>
-      <c r="R14" s="198" t="n">
+      <c r="R14" s="199" t="n">
         <v>0.2</v>
       </c>
-      <c r="S14" s="188" t="inlineStr">
+      <c r="S14" s="189" t="inlineStr">
         <is>
           <t>Target ~20% debt (We+Wd=100%)</t>
         </is>
       </c>
-      <c r="T14" s="188" t="inlineStr">
+      <c r="T14" s="189" t="inlineStr">
         <is>
           <t>WACC weight</t>
         </is>
       </c>
-      <c r="U14" s="190" t="inlineStr">
+      <c r="U14" s="191" t="inlineStr">
         <is>
           <t>SEC 10-Q — total debt $5,582,389k</t>
         </is>
       </c>
-      <c r="V14" s="190" t="inlineStr">
+      <c r="V14" s="191" t="inlineStr">
         <is>
           <t>SEC 10-K — senior notes footnote</t>
         </is>
@@ -11792,7 +11804,7 @@
         </is>
       </c>
       <c r="C15" s="97" t="n"/>
-      <c r="D15" s="199">
+      <c r="D15" s="200">
         <f>'3 Statement Model'!J68</f>
         <v/>
       </c>
@@ -11807,31 +11819,31 @@
       <c r="M15" s="97" t="n"/>
       <c r="N15" s="97" t="n"/>
       <c r="O15" s="97" t="n"/>
-      <c r="Q15" s="194" t="inlineStr">
+      <c r="Q15" s="195" t="inlineStr">
         <is>
           <t>WACC = We×Ke + Wd×Rd_aftertax</t>
         </is>
       </c>
-      <c r="R15" s="195">
+      <c r="R15" s="196">
         <f>R13*R9+R14*R12</f>
         <v/>
       </c>
-      <c r="S15" s="188" t="inlineStr">
+      <c r="S15" s="189" t="inlineStr">
         <is>
           <t>PRIMARY discount rate → cell D6</t>
         </is>
       </c>
-      <c r="T15" s="194" t="inlineStr">
+      <c r="T15" s="195" t="inlineStr">
         <is>
           <t>→ D6</t>
         </is>
       </c>
-      <c r="U15" s="190" t="inlineStr">
+      <c r="U15" s="191" t="inlineStr">
         <is>
           <t>SEC filings (tax, debt coupons)</t>
         </is>
       </c>
-      <c r="V15" s="190" t="inlineStr">
+      <c r="V15" s="191" t="inlineStr">
         <is>
           <t>Damodaran (ERP methodology)</t>
         </is>
@@ -11841,7 +11853,7 @@
       <c r="A16" s="97" t="n"/>
       <c r="B16" s="97" t="n"/>
       <c r="C16" s="97" t="n"/>
-      <c r="D16" s="106" t="n"/>
+      <c r="D16" s="107" t="n"/>
       <c r="J16" s="97" t="n"/>
       <c r="K16" s="97" t="n"/>
       <c r="L16" s="97" t="n"/>
@@ -11851,52 +11863,52 @@
     </row>
     <row r="17" ht="16" customHeight="1">
       <c r="A17" s="97" t="n"/>
-      <c r="B17" s="110" t="inlineStr">
+      <c r="B17" s="111" t="inlineStr">
         <is>
           <t>Discounted Cash Flow</t>
         </is>
       </c>
-      <c r="C17" s="111" t="n"/>
-      <c r="D17" s="112" t="inlineStr">
+      <c r="C17" s="112" t="n"/>
+      <c r="D17" s="113" t="inlineStr">
         <is>
           <t>Entry</t>
         </is>
       </c>
-      <c r="E17" s="200">
+      <c r="E17" s="201">
         <f>YEAR(E18)</f>
         <v/>
       </c>
-      <c r="F17" s="200">
+      <c r="F17" s="201">
         <f>YEAR(F18)</f>
         <v/>
       </c>
-      <c r="G17" s="200">
+      <c r="G17" s="201">
         <f>YEAR(G18)</f>
         <v/>
       </c>
-      <c r="H17" s="200">
+      <c r="H17" s="201">
         <f>YEAR(H18)</f>
         <v/>
       </c>
-      <c r="I17" s="200">
+      <c r="I17" s="201">
         <f>YEAR(I18)</f>
         <v/>
       </c>
-      <c r="J17" s="112" t="inlineStr">
+      <c r="J17" s="113" t="inlineStr">
         <is>
           <t>Exit</t>
         </is>
       </c>
       <c r="K17" s="97" t="n"/>
-      <c r="L17" s="114" t="inlineStr">
+      <c r="L17" s="115" t="inlineStr">
         <is>
           <t>Terminal value methods (MODEL7)</t>
         </is>
       </c>
-      <c r="M17" s="111" t="n"/>
-      <c r="N17" s="111" t="n"/>
+      <c r="M17" s="112" t="n"/>
+      <c r="N17" s="112" t="n"/>
       <c r="O17" s="97" t="n"/>
-      <c r="Q17" s="145" t="inlineStr">
+      <c r="Q17" s="146" t="inlineStr">
         <is>
           <t>2) Unlevered Free Cash Flow</t>
         </is>
@@ -11910,31 +11922,31 @@
         </is>
       </c>
       <c r="C18" s="97" t="n"/>
-      <c r="D18" s="201">
+      <c r="D18" s="202">
         <f>D9</f>
         <v/>
       </c>
-      <c r="E18" s="202">
+      <c r="E18" s="203">
         <f>EDATE($D$9,(E19-0.5)*12)</f>
         <v/>
       </c>
-      <c r="F18" s="202">
+      <c r="F18" s="203">
         <f>EDATE($D$9,(F19-0.5)*12)</f>
         <v/>
       </c>
-      <c r="G18" s="202">
+      <c r="G18" s="203">
         <f>EDATE($D$9,(G19-0.5)*12)</f>
         <v/>
       </c>
-      <c r="H18" s="202">
+      <c r="H18" s="203">
         <f>EDATE($D$9,(H19-0.5)*12)</f>
         <v/>
       </c>
-      <c r="I18" s="202">
+      <c r="I18" s="203">
         <f>EDATE($D$9,(I19-0.5)*12)</f>
         <v/>
       </c>
-      <c r="J18" s="199">
+      <c r="J18" s="200">
         <f>I18</f>
         <v/>
       </c>
@@ -11944,7 +11956,7 @@
           <t>Exit EV/EBITDA @ D8 (primary 16x)</t>
         </is>
       </c>
-      <c r="M18" s="199">
+      <c r="M18" s="200">
         <f>J27</f>
         <v/>
       </c>
@@ -11954,17 +11966,17 @@
         </is>
       </c>
       <c r="O18" s="97" t="n"/>
-      <c r="Q18" s="194" t="inlineStr">
+      <c r="Q18" s="195" t="inlineStr">
         <is>
           <t>FCFF = EBIT − EBIT×t + D&amp;A − CapEx − ΔNWC</t>
         </is>
       </c>
-      <c r="U18" s="190" t="inlineStr">
+      <c r="U18" s="191" t="inlineStr">
         <is>
           <t>Drivers from SEC XBRL → 3-statement</t>
         </is>
       </c>
-      <c r="V18" s="190" t="inlineStr">
+      <c r="V18" s="191" t="inlineStr">
         <is>
           <t>SEC 10-K historical IS/CF</t>
         </is>
@@ -11972,85 +11984,85 @@
     </row>
     <row r="19" ht="16" customHeight="1">
       <c r="A19" s="97" t="n"/>
-      <c r="B19" s="117" t="inlineStr">
+      <c r="B19" s="118" t="inlineStr">
         <is>
           <t>Time Periods</t>
         </is>
       </c>
-      <c r="C19" s="117" t="n"/>
-      <c r="D19" s="115" t="n"/>
-      <c r="E19" s="203" t="n">
+      <c r="C19" s="118" t="n"/>
+      <c r="D19" s="116" t="n"/>
+      <c r="E19" s="204" t="n">
         <v>0</v>
       </c>
-      <c r="F19" s="201">
+      <c r="F19" s="202">
         <f>E19+1</f>
         <v/>
       </c>
-      <c r="G19" s="201">
+      <c r="G19" s="202">
         <f>F19+1</f>
         <v/>
       </c>
-      <c r="H19" s="201">
+      <c r="H19" s="202">
         <f>G19+1</f>
         <v/>
       </c>
-      <c r="I19" s="201">
+      <c r="I19" s="202">
         <f>H19+1</f>
         <v/>
       </c>
-      <c r="J19" s="115" t="n"/>
+      <c r="J19" s="116" t="n"/>
       <c r="K19" s="97" t="n"/>
       <c r="L19" s="97" t="inlineStr">
         <is>
           <t>Gordon cross-check</t>
         </is>
       </c>
-      <c r="M19" s="199">
+      <c r="M19" s="200">
         <f>IF(($D$6-$D$7)&lt;=0,"WACC must exceed g",$I$26*(1+$D$7)/($D$6-$D$7))</f>
         <v/>
       </c>
-      <c r="N19" s="120" t="inlineStr">
+      <c r="N19" s="121" t="inlineStr">
         <is>
           <t>← sanity check</t>
         </is>
       </c>
       <c r="O19" s="97" t="n"/>
-      <c r="Q19" s="188" t="inlineStr">
+      <c r="Q19" s="189" t="inlineStr">
         <is>
           <t>Excel (col E example)</t>
         </is>
       </c>
-      <c r="R19" s="194">
+      <c r="R19" s="195">
         <f>E21-E22+E23-E24-E25</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="16" customHeight="1">
       <c r="A20" s="97" t="n"/>
-      <c r="B20" s="117" t="inlineStr">
+      <c r="B20" s="118" t="inlineStr">
         <is>
           <t>Year Fraction (display only; XNPV uses exact dates below)</t>
         </is>
       </c>
       <c r="C20" s="97" t="n"/>
       <c r="D20" s="97" t="n"/>
-      <c r="E20" s="201">
+      <c r="E20" s="202">
         <f>YEARFRAC(D18,E18)</f>
         <v/>
       </c>
-      <c r="F20" s="201">
+      <c r="F20" s="202">
         <f>YEARFRAC(E18,F18)</f>
         <v/>
       </c>
-      <c r="G20" s="201">
+      <c r="G20" s="202">
         <f>YEARFRAC(F18,G18)</f>
         <v/>
       </c>
-      <c r="H20" s="201">
+      <c r="H20" s="202">
         <f>YEARFRAC(G18,H18)</f>
         <v/>
       </c>
-      <c r="I20" s="201">
+      <c r="I20" s="202">
         <f>YEARFRAC(H18,I18)</f>
         <v/>
       </c>
@@ -12061,30 +12073,30 @@
           <t>Implied Gordon exit multiple</t>
         </is>
       </c>
-      <c r="M20" s="199">
+      <c r="M20" s="200">
         <f>IF(($I$21+$I$23)=0,0,M19/($I$21+$I$23))</f>
         <v/>
       </c>
-      <c r="N20" s="122">
+      <c r="N20" s="123">
         <f>AVERAGE(N18:N19)</f>
         <v/>
       </c>
       <c r="O20" s="97" t="n"/>
-      <c r="Q20" s="188" t="inlineStr">
+      <c r="Q20" s="189" t="inlineStr">
         <is>
           <t>Tax on EBIT (unlevered)</t>
         </is>
       </c>
-      <c r="R20" s="194">
+      <c r="R20" s="195">
         <f>E21*$D$5</f>
         <v/>
       </c>
-      <c r="S20" s="188" t="inlineStr">
+      <c r="S20" s="189" t="inlineStr">
         <is>
           <t>NOT levered IS tax dollars</t>
         </is>
       </c>
-      <c r="U20" s="190" t="inlineStr">
+      <c r="U20" s="191" t="inlineStr">
         <is>
           <t>Tax rate from SEC 10-K effective rate</t>
         </is>
@@ -12097,29 +12109,29 @@
           <t>EBIT (linked to 3-stmt)</t>
         </is>
       </c>
-      <c r="C21" s="204" t="inlineStr">
+      <c r="C21" s="205" t="inlineStr">
         <is>
           <t>EBIT</t>
         </is>
       </c>
       <c r="D21" s="97" t="n"/>
-      <c r="E21" s="199">
+      <c r="E21" s="200">
         <f>'3 Statement Model'!J26-'3 Statement Model'!J28-'3 Statement Model'!J29-'3 Statement Model'!J30</f>
         <v/>
       </c>
-      <c r="F21" s="199">
+      <c r="F21" s="200">
         <f>'3 Statement Model'!K26-'3 Statement Model'!K28-'3 Statement Model'!K29-'3 Statement Model'!K30</f>
         <v/>
       </c>
-      <c r="G21" s="199">
+      <c r="G21" s="200">
         <f>'3 Statement Model'!L26-'3 Statement Model'!L28-'3 Statement Model'!L29-'3 Statement Model'!L30</f>
         <v/>
       </c>
-      <c r="H21" s="199">
+      <c r="H21" s="200">
         <f>'3 Statement Model'!M26-'3 Statement Model'!M28-'3 Statement Model'!M29-'3 Statement Model'!M30</f>
         <v/>
       </c>
-      <c r="I21" s="199">
+      <c r="I21" s="200">
         <f>'3 Statement Model'!N26-'3 Statement Model'!N28-'3 Statement Model'!N29-'3 Statement Model'!N30</f>
         <v/>
       </c>
@@ -12130,7 +12142,7 @@
           <t>Bull case TV @ 25x (sensitivity only)</t>
         </is>
       </c>
-      <c r="M21" s="199">
+      <c r="M21" s="200">
         <f>($I$21+$I$23)*25.0</f>
         <v/>
       </c>
@@ -12140,16 +12152,16 @@
         </is>
       </c>
       <c r="O21" s="97" t="n"/>
-      <c r="Q21" s="188" t="inlineStr">
+      <c r="Q21" s="189" t="inlineStr">
         <is>
           <t>FCFF check (FY5 / col I)</t>
         </is>
       </c>
-      <c r="R21" s="205">
+      <c r="R21" s="206">
         <f>I26</f>
         <v/>
       </c>
-      <c r="S21" s="188" t="inlineStr">
+      <c r="S21" s="189" t="inlineStr">
         <is>
           <t>Must equal I21−I22+I23−I24−I25</t>
         </is>
@@ -12162,29 +12174,29 @@
           <t>Less: Unlevered Cash Taxes (EBIT×t)</t>
         </is>
       </c>
-      <c r="C22" s="204" t="inlineStr">
+      <c r="C22" s="205" t="inlineStr">
         <is>
           <t>EBIT×t</t>
         </is>
       </c>
       <c r="D22" s="97" t="n"/>
-      <c r="E22" s="199">
+      <c r="E22" s="200">
         <f>E21*$D$5</f>
         <v/>
       </c>
-      <c r="F22" s="199">
+      <c r="F22" s="200">
         <f>F21*$D$5</f>
         <v/>
       </c>
-      <c r="G22" s="199">
+      <c r="G22" s="200">
         <f>G21*$D$5</f>
         <v/>
       </c>
-      <c r="H22" s="199">
+      <c r="H22" s="200">
         <f>H21*$D$5</f>
         <v/>
       </c>
-      <c r="I22" s="199">
+      <c r="I22" s="200">
         <f>I21*$D$5</f>
         <v/>
       </c>
@@ -12202,29 +12214,29 @@
           <t>Plus: D&amp;A (linked to 3-stmt)</t>
         </is>
       </c>
-      <c r="C23" s="204" t="inlineStr">
+      <c r="C23" s="205" t="inlineStr">
         <is>
           <t>+D&amp;A</t>
         </is>
       </c>
       <c r="D23" s="97" t="n"/>
-      <c r="E23" s="199">
+      <c r="E23" s="200">
         <f>'3 Statement Model'!J30</f>
         <v/>
       </c>
-      <c r="F23" s="199">
+      <c r="F23" s="200">
         <f>'3 Statement Model'!K30</f>
         <v/>
       </c>
-      <c r="G23" s="199">
+      <c r="G23" s="200">
         <f>'3 Statement Model'!L30</f>
         <v/>
       </c>
-      <c r="H23" s="199">
+      <c r="H23" s="200">
         <f>'3 Statement Model'!M30</f>
         <v/>
       </c>
-      <c r="I23" s="199">
+      <c r="I23" s="200">
         <f>'3 Statement Model'!N30</f>
         <v/>
       </c>
@@ -12234,7 +12246,7 @@
       <c r="M23" s="97" t="n"/>
       <c r="N23" s="97" t="n"/>
       <c r="O23" s="97" t="n"/>
-      <c r="Q23" s="145" t="inlineStr">
+      <c r="Q23" s="146" t="inlineStr">
         <is>
           <t>3) Terminal Value</t>
         </is>
@@ -12247,29 +12259,29 @@
           <t>Less: Capex (linked to 3-stmt CF)</t>
         </is>
       </c>
-      <c r="C24" s="204" t="inlineStr">
+      <c r="C24" s="205" t="inlineStr">
         <is>
           <t>−CapEx</t>
         </is>
       </c>
       <c r="D24" s="97" t="n"/>
-      <c r="E24" s="199">
+      <c r="E24" s="200">
         <f>'3 Statement Model'!J68</f>
         <v/>
       </c>
-      <c r="F24" s="199">
+      <c r="F24" s="200">
         <f>'3 Statement Model'!K68</f>
         <v/>
       </c>
-      <c r="G24" s="199">
+      <c r="G24" s="200">
         <f>'3 Statement Model'!L68</f>
         <v/>
       </c>
-      <c r="H24" s="199">
+      <c r="H24" s="200">
         <f>'3 Statement Model'!M68</f>
         <v/>
       </c>
-      <c r="I24" s="199">
+      <c r="I24" s="200">
         <f>'3 Statement Model'!N68</f>
         <v/>
       </c>
@@ -12279,7 +12291,7 @@
       <c r="M24" s="97" t="n"/>
       <c r="N24" s="97" t="n"/>
       <c r="O24" s="97" t="n"/>
-      <c r="Q24" s="194" t="inlineStr">
+      <c r="Q24" s="195" t="inlineStr">
         <is>
           <t>TV_exit = EBITDA_n × ExitMultiple   [PRIMARY]</t>
         </is>
@@ -12292,29 +12304,29 @@
           <t>Less: ΔNWC (linked to 3-stmt CF)</t>
         </is>
       </c>
-      <c r="C25" s="204" t="inlineStr">
+      <c r="C25" s="205" t="inlineStr">
         <is>
           <t>−ΔNWC</t>
         </is>
       </c>
       <c r="D25" s="97" t="n"/>
-      <c r="E25" s="199">
+      <c r="E25" s="200">
         <f>'3 Statement Model'!J64</f>
         <v/>
       </c>
-      <c r="F25" s="199">
+      <c r="F25" s="200">
         <f>'3 Statement Model'!K64</f>
         <v/>
       </c>
-      <c r="G25" s="199">
+      <c r="G25" s="200">
         <f>'3 Statement Model'!L64</f>
         <v/>
       </c>
-      <c r="H25" s="199">
+      <c r="H25" s="200">
         <f>'3 Statement Model'!M64</f>
         <v/>
       </c>
-      <c r="I25" s="199">
+      <c r="I25" s="200">
         <f>'3 Statement Model'!N64</f>
         <v/>
       </c>
@@ -12324,20 +12336,20 @@
       <c r="M25" s="97" t="n"/>
       <c r="N25" s="97" t="n"/>
       <c r="O25" s="97" t="n"/>
-      <c r="Q25" s="188" t="inlineStr">
+      <c r="Q25" s="189" t="inlineStr">
         <is>
           <t>Excel</t>
         </is>
       </c>
-      <c r="R25" s="194">
+      <c r="R25" s="195">
         <f>($I$21+$I$23)*$D$8</f>
         <v/>
       </c>
-      <c r="T25" s="205">
+      <c r="T25" s="206">
         <f>J27</f>
         <v/>
       </c>
-      <c r="U25" s="190" t="inlineStr">
+      <c r="U25" s="191" t="inlineStr">
         <is>
           <t>Exit multiple policy vs Yahoo / market multiples</t>
         </is>
@@ -12350,29 +12362,29 @@
           <t>Unlevered FCF</t>
         </is>
       </c>
-      <c r="C26" s="204" t="inlineStr">
+      <c r="C26" s="205" t="inlineStr">
         <is>
           <t>FCFF=EBIT−tax+DA−CapEx−ΔNWC</t>
         </is>
       </c>
       <c r="D26" s="97" t="n"/>
-      <c r="E26" s="206">
+      <c r="E26" s="207">
         <f>E21-E22+E23-E24-E25</f>
         <v/>
       </c>
-      <c r="F26" s="206">
+      <c r="F26" s="207">
         <f>F21-F22+F23-F24-F25</f>
         <v/>
       </c>
-      <c r="G26" s="206">
+      <c r="G26" s="207">
         <f>G21-G22+G23-G24-G25</f>
         <v/>
       </c>
-      <c r="H26" s="206">
+      <c r="H26" s="207">
         <f>H21-H22+H23-H24-H25</f>
         <v/>
       </c>
-      <c r="I26" s="206">
+      <c r="I26" s="207">
         <f>I21-I22+I23-I24-I25</f>
         <v/>
       </c>
@@ -12382,7 +12394,7 @@
       <c r="M26" s="97" t="n"/>
       <c r="N26" s="97" t="n"/>
       <c r="O26" s="97" t="n"/>
-      <c r="Q26" s="194" t="inlineStr">
+      <c r="Q26" s="195" t="inlineStr">
         <is>
           <t>TV_gordon = FCFF_n×(1+g)/(WACC−g)   [CHECK]</t>
         </is>
@@ -12396,7 +12408,7 @@
         </is>
       </c>
       <c r="C27" s="97" t="n"/>
-      <c r="D27" s="207">
+      <c r="D27" s="208">
         <f>-I35</f>
         <v/>
       </c>
@@ -12405,7 +12417,7 @@
       <c r="G27" s="97" t="n"/>
       <c r="H27" s="97" t="n"/>
       <c r="I27" s="97" t="n"/>
-      <c r="J27" s="199">
+      <c r="J27" s="200">
         <f>($I$21+$I$23)*$D$8</f>
         <v/>
       </c>
@@ -12414,20 +12426,20 @@
       <c r="M27" s="97" t="n"/>
       <c r="N27" s="97" t="n"/>
       <c r="O27" s="97" t="n"/>
-      <c r="Q27" s="188" t="inlineStr">
+      <c r="Q27" s="189" t="inlineStr">
         <is>
           <t>Excel</t>
         </is>
       </c>
-      <c r="R27" s="194">
+      <c r="R27" s="195">
         <f>IF(($D$6-$D$7)&lt;=0,"err",$I$26*(1+$D$7)/($D$6-$D$7))</f>
         <v/>
       </c>
-      <c r="T27" s="205">
+      <c r="T27" s="206">
         <f>M19</f>
         <v/>
       </c>
-      <c r="U27" s="190" t="inlineStr">
+      <c r="U27" s="191" t="inlineStr">
         <is>
           <t>Gordon g vs Damodaran long-run growth framing</t>
         </is>
@@ -12441,30 +12453,30 @@
         </is>
       </c>
       <c r="C28" s="97" t="n"/>
-      <c r="D28" s="206" t="n">
+      <c r="D28" s="207" t="n">
         <v>0</v>
       </c>
-      <c r="E28" s="208">
+      <c r="E28" s="209">
         <f>E27+E26</f>
         <v/>
       </c>
-      <c r="F28" s="208">
+      <c r="F28" s="209">
         <f>F27+F26</f>
         <v/>
       </c>
-      <c r="G28" s="208">
+      <c r="G28" s="209">
         <f>G27+G26</f>
         <v/>
       </c>
-      <c r="H28" s="208">
+      <c r="H28" s="209">
         <f>H27+H26</f>
         <v/>
       </c>
-      <c r="I28" s="208">
+      <c r="I28" s="209">
         <f>I27+I26</f>
         <v/>
       </c>
-      <c r="J28" s="208">
+      <c r="J28" s="209">
         <f>J27+J26</f>
         <v/>
       </c>
@@ -12473,16 +12485,16 @@
       <c r="M28" s="97" t="n"/>
       <c r="N28" s="97" t="n"/>
       <c r="O28" s="97" t="n"/>
-      <c r="Q28" s="188" t="inlineStr">
+      <c r="Q28" s="189" t="inlineStr">
         <is>
           <t>Implied Gordon exit multiple</t>
         </is>
       </c>
-      <c r="R28" s="209">
+      <c r="R28" s="210">
         <f>IF(($I$21+$I$23)=0,0,T27/($I$21+$I$23))</f>
         <v/>
       </c>
-      <c r="S28" s="188" t="inlineStr">
+      <c r="S28" s="189" t="inlineStr">
         <is>
           <t>Gordon TV / EBITDA_n</t>
         </is>
@@ -12496,31 +12508,31 @@
         </is>
       </c>
       <c r="C29" s="97" t="n"/>
-      <c r="D29" s="207">
+      <c r="D29" s="208">
         <f>D27+D26</f>
         <v/>
       </c>
-      <c r="E29" s="199">
+      <c r="E29" s="200">
         <f>E27+E26</f>
         <v/>
       </c>
-      <c r="F29" s="199">
+      <c r="F29" s="200">
         <f>F27+F26</f>
         <v/>
       </c>
-      <c r="G29" s="199">
+      <c r="G29" s="200">
         <f>G27+G26</f>
         <v/>
       </c>
-      <c r="H29" s="199">
+      <c r="H29" s="200">
         <f>H27+H26</f>
         <v/>
       </c>
-      <c r="I29" s="199">
+      <c r="I29" s="200">
         <f>I27+I26</f>
         <v/>
       </c>
-      <c r="J29" s="199">
+      <c r="J29" s="200">
         <f>J27</f>
         <v/>
       </c>
@@ -12544,7 +12556,7 @@
       <c r="M30" s="97" t="n"/>
       <c r="N30" s="97" t="n"/>
       <c r="O30" s="97" t="n"/>
-      <c r="Q30" s="145" t="inlineStr">
+      <c r="Q30" s="146" t="inlineStr">
         <is>
           <t>4) Enterprise → Equity → $/share</t>
         </is>
@@ -12552,31 +12564,31 @@
     </row>
     <row r="31" ht="16" customHeight="1">
       <c r="A31" s="97" t="n"/>
-      <c r="B31" s="110" t="inlineStr">
+      <c r="B31" s="111" t="inlineStr">
         <is>
           <t>Intrinsic Value</t>
         </is>
       </c>
-      <c r="C31" s="111" t="n"/>
-      <c r="D31" s="111" t="n"/>
+      <c r="C31" s="112" t="n"/>
+      <c r="D31" s="112" t="n"/>
       <c r="E31" s="97" t="n"/>
-      <c r="G31" s="110" t="inlineStr">
+      <c r="G31" s="111" t="inlineStr">
         <is>
           <t>Market Value</t>
         </is>
       </c>
-      <c r="H31" s="111" t="n"/>
-      <c r="I31" s="111" t="n"/>
+      <c r="H31" s="112" t="n"/>
+      <c r="I31" s="112" t="n"/>
       <c r="J31" s="97" t="n"/>
-      <c r="L31" s="110" t="inlineStr">
+      <c r="L31" s="111" t="inlineStr">
         <is>
           <t>Rate of Return</t>
         </is>
       </c>
-      <c r="M31" s="111" t="n"/>
-      <c r="N31" s="111" t="n"/>
+      <c r="M31" s="112" t="n"/>
+      <c r="N31" s="112" t="n"/>
       <c r="O31" s="97" t="n"/>
-      <c r="Q31" s="194" t="inlineStr">
+      <c r="Q31" s="195" t="inlineStr">
         <is>
           <t>EV = XNPV(WACC, TransactionCF, mid-year dates)</t>
         </is>
@@ -12590,7 +12602,7 @@
         </is>
       </c>
       <c r="C32" s="97" t="n"/>
-      <c r="D32" s="199">
+      <c r="D32" s="200">
         <f>XNPV(D6,D28:J28,D18:J18)</f>
         <v/>
       </c>
@@ -12601,7 +12613,7 @@
         </is>
       </c>
       <c r="H32" s="97" t="n"/>
-      <c r="I32" s="207">
+      <c r="I32" s="208">
         <f>D12*D11</f>
         <v/>
       </c>
@@ -12612,21 +12624,21 @@
         </is>
       </c>
       <c r="M32" s="97" t="n"/>
-      <c r="N32" s="125">
+      <c r="N32" s="126">
         <f>D37/I37-1</f>
         <v/>
       </c>
       <c r="O32" s="97" t="n"/>
-      <c r="Q32" s="188" t="inlineStr">
+      <c r="Q32" s="189" t="inlineStr">
         <is>
           <t>Excel</t>
         </is>
       </c>
-      <c r="R32" s="194">
+      <c r="R32" s="195">
         <f>XNPV(D6,D28:J28,D18:J18)</f>
         <v/>
       </c>
-      <c r="T32" s="205">
+      <c r="T32" s="206">
         <f>D32</f>
         <v/>
       </c>
@@ -12639,7 +12651,7 @@
         </is>
       </c>
       <c r="C33" s="97" t="n"/>
-      <c r="D33" s="207">
+      <c r="D33" s="208">
         <f>+D14</f>
         <v/>
       </c>
@@ -12650,7 +12662,7 @@
         </is>
       </c>
       <c r="H33" s="97" t="n"/>
-      <c r="I33" s="207">
+      <c r="I33" s="208">
         <f>D13</f>
         <v/>
       </c>
@@ -12661,31 +12673,31 @@
         </is>
       </c>
       <c r="M33" s="97" t="n"/>
-      <c r="N33" s="125">
+      <c r="N33" s="126">
         <f>XIRR(D29:J29,D18:J18)</f>
         <v/>
       </c>
       <c r="O33" s="97" t="n"/>
-      <c r="Q33" s="194" t="inlineStr">
+      <c r="Q33" s="195" t="inlineStr">
         <is>
           <t>Equity = EV + Cash − Debt</t>
         </is>
       </c>
-      <c r="R33" s="205">
+      <c r="R33" s="206">
         <f>D35</f>
         <v/>
       </c>
-      <c r="S33" s="188" t="inlineStr">
+      <c r="S33" s="189" t="inlineStr">
         <is>
           <t>Net debt from 10-Q bridge</t>
         </is>
       </c>
-      <c r="U33" s="190" t="inlineStr">
+      <c r="U33" s="191" t="inlineStr">
         <is>
           <t>SEC 10-Q — cash, mkt secs, total debt</t>
         </is>
       </c>
-      <c r="V33" s="190" t="inlineStr">
+      <c r="V33" s="191" t="inlineStr">
         <is>
           <t>SEC 10-K — FY debt footnote</t>
         </is>
@@ -12699,7 +12711,7 @@
         </is>
       </c>
       <c r="C34" s="97" t="n"/>
-      <c r="D34" s="207">
+      <c r="D34" s="208">
         <f>+D13</f>
         <v/>
       </c>
@@ -12710,7 +12722,7 @@
         </is>
       </c>
       <c r="H34" s="97" t="n"/>
-      <c r="I34" s="207">
+      <c r="I34" s="208">
         <f>+D14</f>
         <v/>
       </c>
@@ -12719,26 +12731,26 @@
       <c r="M34" s="97" t="n"/>
       <c r="N34" s="97" t="n"/>
       <c r="O34" s="97" t="n"/>
-      <c r="Q34" s="194" t="inlineStr">
+      <c r="Q34" s="195" t="inlineStr">
         <is>
           <t>$/share = Equity / Shares</t>
         </is>
       </c>
-      <c r="R34" s="210">
+      <c r="R34" s="211">
         <f>D37</f>
         <v/>
       </c>
-      <c r="S34" s="188" t="inlineStr">
+      <c r="S34" s="189" t="inlineStr">
         <is>
           <t>Shares outstanding (Yahoo)</t>
         </is>
       </c>
-      <c r="U34" s="190" t="inlineStr">
+      <c r="U34" s="191" t="inlineStr">
         <is>
           <t>Yahoo Finance — shares outstanding</t>
         </is>
       </c>
-      <c r="V34" s="190" t="inlineStr">
+      <c r="V34" s="191" t="inlineStr">
         <is>
           <t>Yahoo FICO quote (price)</t>
         </is>
@@ -12752,7 +12764,7 @@
         </is>
       </c>
       <c r="C35" s="97" t="n"/>
-      <c r="D35" s="206">
+      <c r="D35" s="207">
         <f>D32+D33-D34</f>
         <v/>
       </c>
@@ -12763,29 +12775,29 @@
         </is>
       </c>
       <c r="H35" s="97" t="n"/>
-      <c r="I35" s="206">
+      <c r="I35" s="207">
         <f>I32+I33-I34</f>
         <v/>
       </c>
       <c r="J35" s="97" t="n"/>
-      <c r="L35" s="110" t="inlineStr">
+      <c r="L35" s="111" t="inlineStr">
         <is>
           <t>Market Value vs Intrinsic Value</t>
         </is>
       </c>
-      <c r="M35" s="111" t="n"/>
-      <c r="N35" s="111" t="n"/>
+      <c r="M35" s="112" t="n"/>
+      <c r="N35" s="112" t="n"/>
       <c r="O35" s="97" t="n"/>
-      <c r="Q35" s="188" t="inlineStr">
+      <c r="Q35" s="189" t="inlineStr">
         <is>
           <t>Upside vs market</t>
         </is>
       </c>
-      <c r="R35" s="211">
+      <c r="R35" s="212">
         <f>D37/D11-1</f>
         <v/>
       </c>
-      <c r="S35" s="188" t="inlineStr">
+      <c r="S35" s="189" t="inlineStr">
         <is>
           <t>Intrinsic / Current Price − 1</t>
         </is>
@@ -12799,7 +12811,7 @@
       <c r="E36" s="97" t="n"/>
       <c r="G36" s="97" t="n"/>
       <c r="H36" s="97" t="n"/>
-      <c r="I36" s="212" t="n"/>
+      <c r="I36" s="213" t="n"/>
       <c r="J36" s="97" t="n"/>
       <c r="L36" s="97" t="inlineStr">
         <is>
@@ -12807,7 +12819,7 @@
         </is>
       </c>
       <c r="M36" s="97" t="n"/>
-      <c r="N36" s="212">
+      <c r="N36" s="213">
         <f>I37</f>
         <v/>
       </c>
@@ -12821,7 +12833,7 @@
         </is>
       </c>
       <c r="C37" s="97" t="n"/>
-      <c r="D37" s="207">
+      <c r="D37" s="208">
         <f>D35/D12</f>
         <v/>
       </c>
@@ -12832,7 +12844,7 @@
         </is>
       </c>
       <c r="H37" s="97" t="n"/>
-      <c r="I37" s="207">
+      <c r="I37" s="208">
         <f>D11</f>
         <v/>
       </c>
@@ -12843,12 +12855,12 @@
         </is>
       </c>
       <c r="M37" s="97" t="n"/>
-      <c r="N37" s="212">
+      <c r="N37" s="213">
         <f>D37-I37</f>
         <v/>
       </c>
       <c r="O37" s="97" t="n"/>
-      <c r="Q37" s="145" t="inlineStr">
+      <c r="Q37" s="146" t="inlineStr">
         <is>
           <t>5) Operating NWC (feeds ΔNWC → FCFF)</t>
         </is>
@@ -12870,22 +12882,22 @@
         </is>
       </c>
       <c r="M38" s="97" t="n"/>
-      <c r="N38" s="212">
+      <c r="N38" s="213">
         <f>SUM(N36:N37)</f>
         <v/>
       </c>
       <c r="O38" s="97" t="n"/>
-      <c r="Q38" s="194" t="inlineStr">
+      <c r="Q38" s="195" t="inlineStr">
         <is>
           <t>NWC = AR + Inventory − AP − DeferredRevenue</t>
         </is>
       </c>
-      <c r="U38" s="190" t="inlineStr">
+      <c r="U38" s="191" t="inlineStr">
         <is>
           <t>SEC 10-K — AR / AP / deferred revenue</t>
         </is>
       </c>
-      <c r="V38" s="190" t="inlineStr">
+      <c r="V38" s="191" t="inlineStr">
         <is>
           <t>XBRL DeferredRevenueCurrent</t>
         </is>
@@ -12904,17 +12916,17 @@
       <c r="M39" s="97" t="n"/>
       <c r="N39" s="97" t="n"/>
       <c r="O39" s="97" t="n"/>
-      <c r="Q39" s="194" t="inlineStr">
+      <c r="Q39" s="195" t="inlineStr">
         <is>
           <t>ΔNWC_t = NWC_t − NWC_(t−1)</t>
         </is>
       </c>
-      <c r="S39" s="188" t="inlineStr">
+      <c r="S39" s="189" t="inlineStr">
         <is>
           <t>Linked from 3-statement CF row 64</t>
         </is>
       </c>
-      <c r="T39" s="205">
+      <c r="T39" s="206">
         <f>I25</f>
         <v/>
       </c>
@@ -12936,25 +12948,25 @@
     </row>
     <row r="41" ht="16" customHeight="1">
       <c r="A41" s="97" t="n"/>
-      <c r="B41" s="110" t="inlineStr">
+      <c r="B41" s="111" t="inlineStr">
         <is>
           <t>Instructions</t>
         </is>
       </c>
-      <c r="C41" s="111" t="n"/>
-      <c r="D41" s="127" t="n"/>
-      <c r="E41" s="111" t="n"/>
-      <c r="F41" s="111" t="n"/>
-      <c r="G41" s="111" t="n"/>
-      <c r="H41" s="111" t="n"/>
-      <c r="I41" s="111" t="n"/>
-      <c r="J41" s="111" t="n"/>
-      <c r="K41" s="111" t="n"/>
-      <c r="L41" s="111" t="n"/>
-      <c r="M41" s="111" t="n"/>
-      <c r="N41" s="111" t="n"/>
+      <c r="C41" s="112" t="n"/>
+      <c r="D41" s="128" t="n"/>
+      <c r="E41" s="112" t="n"/>
+      <c r="F41" s="112" t="n"/>
+      <c r="G41" s="112" t="n"/>
+      <c r="H41" s="112" t="n"/>
+      <c r="I41" s="112" t="n"/>
+      <c r="J41" s="112" t="n"/>
+      <c r="K41" s="112" t="n"/>
+      <c r="L41" s="112" t="n"/>
+      <c r="M41" s="112" t="n"/>
+      <c r="N41" s="112" t="n"/>
       <c r="O41" s="97" t="n"/>
-      <c r="Q41" s="145" t="inlineStr">
+      <c r="Q41" s="146" t="inlineStr">
         <is>
           <t>6) Full source index (all clickable)</t>
         </is>
@@ -12973,20 +12985,20 @@
       <c r="F42" s="97" t="n"/>
       <c r="G42" s="97" t="n"/>
       <c r="H42" s="97" t="n"/>
-      <c r="N42" s="128" t="inlineStr">
+      <c r="N42" s="129" t="inlineStr">
         <is>
           <t>This file is for educational purposes only. E&amp;OE</t>
         </is>
       </c>
       <c r="O42" s="97" t="n"/>
-      <c r="Q42" s="190" t="inlineStr">
+      <c r="Q42" s="191" t="inlineStr">
         <is>
           <t>SEC 10-K FY2025</t>
         </is>
       </c>
-      <c r="R42" s="213" t="n"/>
-      <c r="S42" s="214" t="n"/>
-      <c r="T42" s="188" t="inlineStr">
+      <c r="R42" s="214" t="n"/>
+      <c r="S42" s="215" t="n"/>
+      <c r="T42" s="189" t="inlineStr">
         <is>
           <t>Tax 18.8%, IS/BS/CF, senior notes</t>
         </is>
@@ -13007,14 +13019,14 @@
       <c r="H43" s="97" t="n"/>
       <c r="N43" s="69" t="n"/>
       <c r="O43" s="97" t="n"/>
-      <c r="Q43" s="190" t="inlineStr">
+      <c r="Q43" s="191" t="inlineStr">
         <is>
           <t>SEC 10-Q Q3 FY2026</t>
         </is>
       </c>
-      <c r="R43" s="213" t="n"/>
-      <c r="S43" s="214" t="n"/>
-      <c r="T43" s="188" t="inlineStr">
+      <c r="R43" s="214" t="n"/>
+      <c r="S43" s="215" t="n"/>
+      <c r="T43" s="189" t="inlineStr">
         <is>
           <t>Debt $5,582M, cash+mkt secs net-debt bridge</t>
         </is>
@@ -13022,7 +13034,7 @@
     </row>
     <row r="44" ht="16" customHeight="1">
       <c r="A44" s="97" t="n"/>
-      <c r="B44" s="129" t="inlineStr">
+      <c r="B44" s="130" t="inlineStr">
         <is>
           <t>There are two ways to find NWC:</t>
         </is>
@@ -13035,14 +13047,14 @@
       <c r="H44" s="97" t="n"/>
       <c r="N44" s="69" t="n"/>
       <c r="O44" s="97" t="n"/>
-      <c r="Q44" s="190" t="inlineStr">
+      <c r="Q44" s="191" t="inlineStr">
         <is>
           <t>SEC 8-K 6.250% notes</t>
         </is>
       </c>
-      <c r="R44" s="213" t="n"/>
-      <c r="S44" s="214" t="n"/>
-      <c r="T44" s="188" t="inlineStr">
+      <c r="R44" s="214" t="n"/>
+      <c r="S44" s="215" t="n"/>
+      <c r="T44" s="189" t="inlineStr">
         <is>
           <t>Pre-tax Rd coupon 6.250% due 2034</t>
         </is>
@@ -13050,7 +13062,7 @@
     </row>
     <row r="45" ht="16" customHeight="1">
       <c r="A45" s="97" t="n"/>
-      <c r="B45" s="129" t="inlineStr">
+      <c r="B45" s="130" t="inlineStr">
         <is>
           <t>1. NWC = Current Assets (less cash) - Current Liabilities (less debt)</t>
         </is>
@@ -13063,14 +13075,14 @@
       <c r="H45" s="97" t="n"/>
       <c r="N45" s="69" t="n"/>
       <c r="O45" s="97" t="n"/>
-      <c r="Q45" s="190" t="inlineStr">
+      <c r="Q45" s="191" t="inlineStr">
         <is>
           <t>SEC EX-99.1 pricing</t>
         </is>
       </c>
-      <c r="R45" s="213" t="n"/>
-      <c r="S45" s="214" t="n"/>
-      <c r="T45" s="188" t="inlineStr">
+      <c r="R45" s="214" t="n"/>
+      <c r="S45" s="215" t="n"/>
+      <c r="T45" s="189" t="inlineStr">
         <is>
           <t>Notes priced at par / offering terms</t>
         </is>
@@ -13078,7 +13090,7 @@
     </row>
     <row r="46" ht="16" customHeight="1">
       <c r="A46" s="97" t="n"/>
-      <c r="B46" s="129" t="inlineStr">
+      <c r="B46" s="130" t="inlineStr">
         <is>
           <t>2. NWC = Accounts Receivable + Inventory - Accounts Payable</t>
         </is>
@@ -13091,14 +13103,14 @@
       <c r="H46" s="97" t="n"/>
       <c r="N46" s="69" t="n"/>
       <c r="O46" s="97" t="n"/>
-      <c r="Q46" s="190" t="inlineStr">
+      <c r="Q46" s="191" t="inlineStr">
         <is>
           <t>SEC companyfacts XBRL</t>
         </is>
       </c>
-      <c r="R46" s="213" t="n"/>
-      <c r="S46" s="214" t="n"/>
-      <c r="T46" s="188" t="inlineStr">
+      <c r="R46" s="214" t="n"/>
+      <c r="S46" s="215" t="n"/>
+      <c r="T46" s="189" t="inlineStr">
         <is>
           <t>Pipeline data source (CIK 0000814547)</t>
         </is>
@@ -13115,14 +13127,14 @@
       <c r="H47" s="97" t="n"/>
       <c r="N47" s="69" t="n"/>
       <c r="O47" s="97" t="n"/>
-      <c r="Q47" s="190" t="inlineStr">
+      <c r="Q47" s="191" t="inlineStr">
         <is>
           <t>FRED DGS10</t>
         </is>
       </c>
-      <c r="R47" s="213" t="n"/>
-      <c r="S47" s="214" t="n"/>
-      <c r="T47" s="188" t="inlineStr">
+      <c r="R47" s="214" t="n"/>
+      <c r="S47" s="215" t="n"/>
+      <c r="T47" s="189" t="inlineStr">
         <is>
           <t>Risk-free rate (US 10Y)</t>
         </is>
@@ -13137,20 +13149,20 @@
       <c r="F48" s="97" t="n"/>
       <c r="G48" s="97" t="n"/>
       <c r="H48" s="97" t="n"/>
-      <c r="N48" s="130" t="inlineStr">
+      <c r="N48" s="131" t="inlineStr">
         <is>
           <t xml:space="preserve">Corporate Finance Institute® </t>
         </is>
       </c>
       <c r="O48" s="97" t="n"/>
-      <c r="Q48" s="190" t="inlineStr">
+      <c r="Q48" s="191" t="inlineStr">
         <is>
           <t>US Treasury yield curve</t>
         </is>
       </c>
-      <c r="R48" s="213" t="n"/>
-      <c r="S48" s="214" t="n"/>
-      <c r="T48" s="188" t="inlineStr">
+      <c r="R48" s="214" t="n"/>
+      <c r="S48" s="215" t="n"/>
+      <c r="T48" s="189" t="inlineStr">
         <is>
           <t>Official daily par yields</t>
         </is>
@@ -13165,20 +13177,20 @@
       <c r="F49" s="97" t="n"/>
       <c r="G49" s="97" t="n"/>
       <c r="H49" s="97" t="n"/>
-      <c r="N49" s="131" t="inlineStr">
+      <c r="N49" s="132" t="inlineStr">
         <is>
           <t>https://corporatefinanceinstitute.com/</t>
         </is>
       </c>
       <c r="O49" s="97" t="n"/>
-      <c r="Q49" s="190" t="inlineStr">
+      <c r="Q49" s="191" t="inlineStr">
         <is>
           <t>Damodaran Implied ERP</t>
         </is>
       </c>
-      <c r="R49" s="213" t="n"/>
-      <c r="S49" s="214" t="n"/>
-      <c r="T49" s="188" t="inlineStr">
+      <c r="R49" s="214" t="n"/>
+      <c r="S49" s="215" t="n"/>
+      <c r="T49" s="189" t="inlineStr">
         <is>
           <t>Equity risk premium</t>
         </is>
@@ -13194,14 +13206,14 @@
       <c r="G50" s="97" t="n"/>
       <c r="H50" s="97" t="n"/>
       <c r="O50" s="97" t="n"/>
-      <c r="Q50" s="190" t="inlineStr">
+      <c r="Q50" s="191" t="inlineStr">
         <is>
           <t>Damodaran histimpl</t>
         </is>
       </c>
-      <c r="R50" s="213" t="n"/>
-      <c r="S50" s="214" t="n"/>
-      <c r="T50" s="188" t="inlineStr">
+      <c r="R50" s="214" t="n"/>
+      <c r="S50" s="215" t="n"/>
+      <c r="T50" s="189" t="inlineStr">
         <is>
           <t>Historical implied ERP table</t>
         </is>
@@ -13218,14 +13230,14 @@
       <c r="H51" s="97" t="n"/>
       <c r="M51" s="97" t="n"/>
       <c r="O51" s="97" t="n"/>
-      <c r="Q51" s="190" t="inlineStr">
+      <c r="Q51" s="191" t="inlineStr">
         <is>
           <t>Yahoo FICO stats</t>
         </is>
       </c>
-      <c r="R51" s="213" t="n"/>
-      <c r="S51" s="214" t="n"/>
-      <c r="T51" s="188" t="inlineStr">
+      <c r="R51" s="214" t="n"/>
+      <c r="S51" s="215" t="n"/>
+      <c r="T51" s="189" t="inlineStr">
         <is>
           <t>Beta 5Y monthly + shares out</t>
         </is>

--- a/FICO/output/FICO_Completed_Model.xlsx
+++ b/FICO/output/FICO_Completed_Model.xlsx
@@ -848,9 +848,9 @@
     </xf>
     <xf numFmtId="0" fontId="31" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="40" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="14" fontId="35" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="14" fontId="38" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="35" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="14" fontId="35" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="37" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="35" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -990,9 +990,9 @@
     <xf numFmtId="9" fontId="41" fillId="8" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="177" fontId="38" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="31" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="177" fontId="35" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="178" fontId="38" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="177" fontId="37" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="177" fontId="35" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="55" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="174" fontId="38" fillId="7" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="177" fontId="30" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -11918,32 +11918,32 @@
       <c r="A18" s="97" t="n"/>
       <c r="B18" s="97" t="inlineStr">
         <is>
-          <t>Date (mid-year via EDATE from transaction)</t>
+          <t>Date (mid-year via EDATE; periods are 0-based)</t>
         </is>
       </c>
       <c r="C18" s="97" t="n"/>
-      <c r="D18" s="202">
-        <f>D9</f>
-        <v/>
-      </c>
-      <c r="E18" s="203">
-        <f>EDATE($D$9,(E19-0.5)*12)</f>
-        <v/>
-      </c>
-      <c r="F18" s="203">
-        <f>EDATE($D$9,(F19-0.5)*12)</f>
-        <v/>
-      </c>
-      <c r="G18" s="203">
-        <f>EDATE($D$9,(G19-0.5)*12)</f>
-        <v/>
-      </c>
-      <c r="H18" s="203">
-        <f>EDATE($D$9,(H19-0.5)*12)</f>
-        <v/>
-      </c>
-      <c r="I18" s="203">
-        <f>EDATE($D$9,(I19-0.5)*12)</f>
+      <c r="D18" s="200">
+        <f>$D$9</f>
+        <v/>
+      </c>
+      <c r="E18" s="202">
+        <f>EDATE($D$9,(E19+0.5)*12)</f>
+        <v/>
+      </c>
+      <c r="F18" s="202">
+        <f>EDATE($D$9,(F19+0.5)*12)</f>
+        <v/>
+      </c>
+      <c r="G18" s="202">
+        <f>EDATE($D$9,(G19+0.5)*12)</f>
+        <v/>
+      </c>
+      <c r="H18" s="202">
+        <f>EDATE($D$9,(H19+0.5)*12)</f>
+        <v/>
+      </c>
+      <c r="I18" s="202">
+        <f>EDATE($D$9,(I19+0.5)*12)</f>
         <v/>
       </c>
       <c r="J18" s="200">
@@ -11984,33 +11984,33 @@
     </row>
     <row r="19" ht="16" customHeight="1">
       <c r="A19" s="97" t="n"/>
-      <c r="B19" s="118" t="inlineStr">
+      <c r="B19" s="117" t="inlineStr">
         <is>
           <t>Time Periods</t>
         </is>
       </c>
-      <c r="C19" s="118" t="n"/>
-      <c r="D19" s="116" t="n"/>
-      <c r="E19" s="204" t="n">
+      <c r="C19" s="117" t="n"/>
+      <c r="D19" s="118" t="n"/>
+      <c r="E19" s="203" t="n">
         <v>0</v>
       </c>
-      <c r="F19" s="202">
+      <c r="F19" s="204">
         <f>E19+1</f>
         <v/>
       </c>
-      <c r="G19" s="202">
+      <c r="G19" s="204">
         <f>F19+1</f>
         <v/>
       </c>
-      <c r="H19" s="202">
+      <c r="H19" s="204">
         <f>G19+1</f>
         <v/>
       </c>
-      <c r="I19" s="202">
+      <c r="I19" s="204">
         <f>H19+1</f>
         <v/>
       </c>
-      <c r="J19" s="116" t="n"/>
+      <c r="J19" s="118" t="n"/>
       <c r="K19" s="97" t="n"/>
       <c r="L19" s="97" t="inlineStr">
         <is>
@@ -12039,30 +12039,30 @@
     </row>
     <row r="20" ht="16" customHeight="1">
       <c r="A20" s="97" t="n"/>
-      <c r="B20" s="118" t="inlineStr">
+      <c r="B20" s="117" t="inlineStr">
         <is>
           <t>Year Fraction (display only; XNPV uses exact dates below)</t>
         </is>
       </c>
       <c r="C20" s="97" t="n"/>
       <c r="D20" s="97" t="n"/>
-      <c r="E20" s="202">
+      <c r="E20" s="204">
         <f>YEARFRAC(D18,E18)</f>
         <v/>
       </c>
-      <c r="F20" s="202">
+      <c r="F20" s="204">
         <f>YEARFRAC(E18,F18)</f>
         <v/>
       </c>
-      <c r="G20" s="202">
+      <c r="G20" s="204">
         <f>YEARFRAC(F18,G18)</f>
         <v/>
       </c>
-      <c r="H20" s="202">
+      <c r="H20" s="204">
         <f>YEARFRAC(G18,H18)</f>
         <v/>
       </c>
-      <c r="I20" s="202">
+      <c r="I20" s="204">
         <f>YEARFRAC(H18,I18)</f>
         <v/>
       </c>

--- a/FICO/output/FICO_Completed_Model.xlsx
+++ b/FICO/output/FICO_Completed_Model.xlsx
@@ -100,7 +100,7 @@
     <numFmt numFmtId="178" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="179" formatCode="0.0"/>
   </numFmts>
-  <fonts count="60">
+  <fonts count="61">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -360,6 +360,12 @@
       <i val="1"/>
       <color rgb="00595959"/>
       <sz val="8"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="000563C1"/>
+      <sz val="8"/>
+      <u val="single"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -661,7 +667,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="216">
+  <cellXfs count="217">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="1"/>
@@ -833,6 +839,7 @@
     <xf numFmtId="171" fontId="32" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="164" fontId="40" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="14" fontId="32" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="172" fontId="32" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
@@ -847,7 +854,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="40" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="41" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="14" fontId="38" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="35" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="14" fontId="35" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -875,50 +882,50 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="7"/>
-    <xf numFmtId="0" fontId="56" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="7"/>
-    <xf numFmtId="0" fontId="57" fillId="13" borderId="5" pivotButton="0" quotePrefix="0" xfId="7"/>
-    <xf numFmtId="0" fontId="58" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="7">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="50" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="7"/>
+    <xf numFmtId="0" fontId="57" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="7"/>
+    <xf numFmtId="0" fontId="58" fillId="13" borderId="5" pivotButton="0" quotePrefix="0" xfId="7"/>
     <xf numFmtId="0" fontId="59" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="7">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="58" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="7">
+    <xf numFmtId="0" fontId="60" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="7">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="59" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="7">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="60" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="7">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="41" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="42" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="1" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="1" fontId="13" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="177" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="41" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="44" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="45" fillId="10" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="46" fillId="10" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="39" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="41" fillId="8" borderId="5" pivotButton="0" quotePrefix="0" xfId="2"/>
-    <xf numFmtId="0" fontId="46" fillId="11" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="42" fillId="8" borderId="5" pivotButton="0" quotePrefix="0" xfId="2"/>
+    <xf numFmtId="0" fontId="47" fillId="11" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="38" fillId="7" borderId="5" pivotButton="0" quotePrefix="0" xfId="2"/>
@@ -927,73 +934,73 @@
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="41" fillId="8" borderId="5" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="177" fontId="42" fillId="8" borderId="5" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="177" fontId="38" fillId="7" borderId="5" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="166" fontId="41" fillId="8" borderId="5" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="164" fontId="42" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="177" fontId="41" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="164" fontId="42" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="166" fontId="42" fillId="8" borderId="5" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="164" fontId="43" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="177" fontId="42" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="164" fontId="43" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="177" fontId="6" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="42" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="177" fontId="41" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="43" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="177" fontId="42" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="177" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="164" fontId="42" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="164" fontId="43" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="177" fontId="6" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="177" fontId="38" fillId="7" borderId="2" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="177" fontId="6" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="177" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="177" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="177" fontId="38" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="177" fontId="41" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="177" fontId="42" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="41" fillId="8" borderId="2" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="177" fontId="41" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="177" fontId="42" fillId="8" borderId="2" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="177" fontId="42" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="177" fontId="38" fillId="7" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="49" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="40" fillId="9" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="41" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="50" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="41" fillId="9" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="42" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="51" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="52" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="55" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="54" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="53" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="38" fillId="7" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="41" fillId="8" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="42" fillId="8" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="179" fontId="41" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="179" fontId="42" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="41" fillId="8" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="42" fillId="8" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="178" fontId="32" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="38" fillId="7" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="176" fontId="41" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="176" fontId="42" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="41" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="42" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="41" fillId="8" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="42" fillId="8" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="177" fontId="38" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="31" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="178" fontId="38" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="177" fontId="37" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="177" fontId="35" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="55" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="56" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="174" fontId="38" fillId="7" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="177" fontId="30" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="177" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -5192,9 +5199,10 @@
     <comment ref="D8" authorId="0" shapeId="0">
       <text>
         <t>Exit EV/EBITDA multiple (primary)
-HOW: Yellow POLICY input in D8 = 16.0x; TV = Year-5 EBITDA × D8.
-WHY: Not from an SEC filing. MODEL7 audit required moving off 25x (which implied ~12.8x under Gordon) to a blended 15x–18x normalized exit. Midpoint 16x is the base case; 25x is bull sensitivity only (M21).
-SOURCE: Model policy / audit (15x–18x blend) — judgment, not a market quote.</t>
+HOW: Yellow POLICY input D8 = 16.0x; TV = Year-5 EBITDA × D8.
+WHY: 16x is NOT FICO's spot trading multiple. Spot EV/EBITDA is ~25x (mid-2026). Gordon cross-check implies ~13–14x. Audit asked for a 15x–18x mature-exit blend → midpoint 16x base; 25x = bull/spot sensitivity (M21).
+SOURCE (spot ~25x): https://valueinvesting.io/FICO/valuation/ev_ebitda-multiples
+SOURCE (sector table): https://pages.stern.nyu.edu/adamodar/New_Home_Page/datafile/vebitda.htm</t>
       </text>
     </comment>
     <comment ref="R15" authorId="0" shapeId="0">
@@ -5898,7 +5906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B3:O39"/>
+  <dimension ref="B3:O42"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.109375" defaultRowHeight="13.8"/>
   <cols>
     <col width="11" customWidth="1" style="73" min="1" max="2"/>
@@ -6290,7 +6298,7 @@
         </is>
       </c>
       <c r="D24" s="89" t="n"/>
-      <c r="E24" s="133" t="inlineStr">
+      <c r="E24" s="134" t="i